--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -6,11 +6,11 @@
     <sheet state="visible" name="Feuille 1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_9C72371F_0E2C_4FFE_8A69_38EA37B46DE5_.wvu.FilterData">'Feuille 1'!$A$1:$AC$678</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_BE891185_2BCE_4368_9F2F_D1CEAA962AFF_.wvu.FilterData">'Feuille 1'!$A$1:$AC$678</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{9C72371F-0E2C-4FFE-8A69-38EA37B46DE5}" name="Filtre 1"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{BE891185-2BCE-4368-9F2F-D1CEAA962AFF}" name="Filtre 1"/>
   </customWorkbookViews>
 </workbook>
 </file>
@@ -5011,7 +5011,7 @@
     <t>emblématique ; personnification des vices et des vertus ; héraldique ; mythologie gréco-romaine ; personnification des villes, des États et des fleuves ; personnification</t>
   </si>
   <si>
-    <t>temple ; soleil ; armoiries ; Renommée (personnification) ; Victoire (personnification) ; lion (animal) ; pyramide ; amours ; corne d'abondance ; globe terrestre ; bouclier ; massue ; rameau d'olivier ; France (personnification) ; trophée ; Bavière (personnification) ; Hymen (personnification) ; Paix (personnification) ; Valeur (personnification) ; lion ; palme ;</t>
+    <t>temple ; soleil ; armoiries ; Renommée (personnification) ; Victoire (personnification) ; lion (animal) ; pyramide ; amours ; corne d'abondance ; globe terrestre ; bouclier ; massue ; rameau d'olivier ; France (personnification) ; trophée ; Bavière (personnification) ; Hymen (personnification) ; Paix (personnification) ; Valeur (personnification) ; lion (animal) ; palme ;</t>
   </si>
   <si>
     <r>
@@ -27951,7 +27951,7 @@
       <c r="M131" s="36" t="s">
         <v>1213</v>
       </c>
-      <c r="N131" s="38" t="s">
+      <c r="N131" s="179" t="s">
         <v>1214</v>
       </c>
       <c r="O131" s="38"/>
@@ -62767,7 +62767,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{9C72371F-0E2C-4FFE-8A69-38EA37B46DE5}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{BE891185-2BCE-4368-9F2F-D1CEAA962AFF}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$AC$678"/>
     </customSheetView>
   </customSheetViews>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -6,11 +6,11 @@
     <sheet state="visible" name="Feuille 1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_7D2142DF_EA57_49EF_9659_14F3963649E6_.wvu.FilterData">'Feuille 1'!$A$1:$AC$678</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_65CD057B_49E3_482E_A40A_F23D7F7626AA_.wvu.FilterData">'Feuille 1'!$A$1:$AC$678</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{7D2142DF-EA57-49EF-9659-14F3963649E6}" name="Filtre 1"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{65CD057B-49E3-482E-A40A-F23D7F7626AA}" name="Filtre 1"/>
   </customWorkbookViews>
 </workbook>
 </file>
@@ -16046,7 +16046,7 @@
     <t>[Jetons de l'année 1703]*</t>
   </si>
   <si>
-    <t>MEUDON : 2911</t>
+    <t xml:space="preserve">2911: MEUDON </t>
   </si>
   <si>
     <t>emblématique ; personnification des villes, des États et des fleuves ; mythologie gréco-romaine ; architecture</t>
@@ -52676,7 +52676,7 @@
       </c>
       <c r="J464" s="106"/>
       <c r="K464" s="22"/>
-      <c r="L464" s="22" t="s">
+      <c r="L464" s="192" t="s">
         <v>3859</v>
       </c>
       <c r="M464" s="169" t="s">
@@ -62767,7 +62767,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{7D2142DF-EA57-49EF-9659-14F3963649E6}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{65CD057B-49E3-482E-A40A-F23D7F7626AA}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$AC$678"/>
     </customSheetView>
   </customSheetViews>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -6,11 +6,11 @@
     <sheet state="visible" name="Feuille 1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_65CD057B_49E3_482E_A40A_F23D7F7626AA_.wvu.FilterData">'Feuille 1'!$A$1:$AC$678</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_CDB312C8_EF45_44D8_B316_E4A590B5DAF9_.wvu.FilterData">'Feuille 1'!$A$1:$AC$678</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{65CD057B-49E3-482E-A40A-F23D7F7626AA}" name="Filtre 1"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" name="Filtre 1"/>
   </customWorkbookViews>
 </workbook>
 </file>
@@ -16046,7 +16046,7 @@
     <t>[Jetons de l'année 1703]*</t>
   </si>
   <si>
-    <t xml:space="preserve">2911: MEUDON </t>
+    <t xml:space="preserve">2911 : MEUDON </t>
   </si>
   <si>
     <t>emblématique ; personnification des villes, des États et des fleuves ; mythologie gréco-romaine ; architecture</t>
@@ -62767,7 +62767,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{65CD057B-49E3-482E-A40A-F23D7F7626AA}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$1:$AC$678"/>
     </customSheetView>
   </customSheetViews>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70F6DF0-A0A7-114C-B4F3-18A0A5A7ECB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC25336E-81AE-4B47-A62A-80E65603F15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="-16800" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2080" yWindow="-16800" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6989" uniqueCount="4010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6989" uniqueCount="4011">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17192,6 +17192,9 @@
   </si>
   <si>
     <t>1679-01_299 à transcrire</t>
+  </si>
+  <si>
+    <t>MG-1679-02_357</t>
   </si>
 </sst>
 </file>
@@ -18300,7 +18303,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="377">
+  <cellXfs count="376">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -19290,9 +19293,6 @@
     <xf numFmtId="0" fontId="123" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="111" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -19722,7 +19722,7 @@
       <c r="AQ1" s="3"/>
     </row>
     <row r="2" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A2" s="359" t="s">
+      <c r="A2" s="358" t="s">
         <v>3898</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -19870,7 +19870,7 @@
       <c r="AQ3" s="32"/>
     </row>
     <row r="4" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A4" s="356" t="s">
+      <c r="A4" s="355" t="s">
         <v>55</v>
       </c>
       <c r="B4" s="33" t="s">
@@ -19957,7 +19957,7 @@
       <c r="AQ4" s="32"/>
     </row>
     <row r="5" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A5" s="360" t="s">
+      <c r="A5" s="359" t="s">
         <v>3884</v>
       </c>
       <c r="B5" s="32" t="s">
@@ -20032,7 +20032,7 @@
       <c r="AQ5" s="32"/>
     </row>
     <row r="6" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A6" s="374" t="s">
+      <c r="A6" s="373" t="s">
         <v>3965</v>
       </c>
       <c r="B6" s="33" t="s">
@@ -20182,7 +20182,7 @@
       <c r="AQ7" s="32"/>
     </row>
     <row r="8" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A8" s="360" t="s">
+      <c r="A8" s="359" t="s">
         <v>3883</v>
       </c>
       <c r="B8" s="32" t="s">
@@ -20259,7 +20259,7 @@
       <c r="AQ8" s="32"/>
     </row>
     <row r="9" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A9" s="359" t="s">
+      <c r="A9" s="358" t="s">
         <v>3966</v>
       </c>
       <c r="B9" s="32" t="s">
@@ -20332,7 +20332,7 @@
       <c r="AQ9" s="32"/>
     </row>
     <row r="10" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A10" s="360" t="s">
+      <c r="A10" s="359" t="s">
         <v>123</v>
       </c>
       <c r="B10" s="32" t="s">
@@ -20407,7 +20407,7 @@
       <c r="B11" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="351" t="s">
+      <c r="C11" s="348" t="s">
         <v>132</v>
       </c>
       <c r="D11" s="313"/>
@@ -20616,7 +20616,7 @@
       <c r="AQ13" s="32"/>
     </row>
     <row r="14" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A14" s="354" t="s">
+      <c r="A14" s="353" t="s">
         <v>160</v>
       </c>
       <c r="B14" s="32" t="s">
@@ -20758,13 +20758,13 @@
       <c r="AQ15" s="32"/>
     </row>
     <row r="16" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A16" s="361" t="s">
+      <c r="A16" s="360" t="s">
         <v>3882</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="351" t="s">
+      <c r="C16" s="348" t="s">
         <v>3878</v>
       </c>
       <c r="D16" s="311" t="s">
@@ -20851,7 +20851,7 @@
       <c r="B17" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="352" t="s">
+      <c r="C17" s="351" t="s">
         <v>3879</v>
       </c>
       <c r="D17" s="311" t="s">
@@ -20932,7 +20932,7 @@
       <c r="AQ17" s="32"/>
     </row>
     <row r="18" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A18" s="355" t="s">
+      <c r="A18" s="354" t="s">
         <v>203</v>
       </c>
       <c r="B18" s="94" t="s">
@@ -21019,7 +21019,7 @@
       <c r="AQ18" s="32"/>
     </row>
     <row r="19" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A19" s="353" t="s">
+      <c r="A19" s="352" t="s">
         <v>211</v>
       </c>
       <c r="B19" s="32" t="s">
@@ -21106,7 +21106,7 @@
       <c r="AQ19" s="32"/>
     </row>
     <row r="20" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A20" s="361" t="s">
+      <c r="A20" s="360" t="s">
         <v>3880</v>
       </c>
       <c r="B20" s="32" t="s">
@@ -21191,7 +21191,7 @@
       <c r="AQ20" s="32"/>
     </row>
     <row r="21" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A21" s="353" t="s">
+      <c r="A21" s="352" t="s">
         <v>3881</v>
       </c>
       <c r="B21" s="32" t="s">
@@ -21422,7 +21422,7 @@
       <c r="AQ23" s="32"/>
     </row>
     <row r="24" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A24" s="362" t="s">
+      <c r="A24" s="361" t="s">
         <v>3885</v>
       </c>
       <c r="B24" s="32" t="s">
@@ -21491,7 +21491,7 @@
       <c r="AQ24" s="32"/>
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A25" s="362" t="s">
+      <c r="A25" s="361" t="s">
         <v>3886</v>
       </c>
       <c r="B25" s="32" t="s">
@@ -21560,7 +21560,7 @@
       <c r="AQ25" s="32"/>
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A26" s="376" t="s">
+      <c r="A26" s="375" t="s">
         <v>3968</v>
       </c>
       <c r="B26" s="14" t="s">
@@ -21631,7 +21631,7 @@
       <c r="AQ26" s="32"/>
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A27" s="376" t="s">
+      <c r="A27" s="375" t="s">
         <v>269</v>
       </c>
       <c r="B27" s="14" t="s">
@@ -21702,7 +21702,7 @@
       <c r="AQ27" s="32"/>
     </row>
     <row r="28" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A28" s="362" t="s">
+      <c r="A28" s="361" t="s">
         <v>3969</v>
       </c>
       <c r="B28" s="32" t="s">
@@ -21717,7 +21717,7 @@
       <c r="E28" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="F28" s="375" t="s">
+      <c r="F28" s="374" t="s">
         <v>275</v>
       </c>
       <c r="G28" s="32" t="s">
@@ -21781,7 +21781,7 @@
       <c r="AQ28" s="32"/>
     </row>
     <row r="29" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A29" s="359" t="s">
+      <c r="A29" s="358" t="s">
         <v>3887</v>
       </c>
       <c r="B29" s="33" t="s">
@@ -21856,7 +21856,7 @@
       <c r="AQ29" s="32"/>
     </row>
     <row r="30" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A30" s="359" t="s">
+      <c r="A30" s="358" t="s">
         <v>3888</v>
       </c>
       <c r="B30" s="33" t="s">
@@ -21937,7 +21937,7 @@
       <c r="AQ30" s="32"/>
     </row>
     <row r="31" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A31" s="362" t="s">
+      <c r="A31" s="361" t="s">
         <v>3970</v>
       </c>
       <c r="B31" s="33" t="s">
@@ -22010,7 +22010,7 @@
       <c r="AQ31" s="32"/>
     </row>
     <row r="32" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A32" s="359" t="s">
+      <c r="A32" s="358" t="s">
         <v>3889</v>
       </c>
       <c r="B32" s="32" t="s">
@@ -22085,7 +22085,7 @@
       <c r="AQ32" s="32"/>
     </row>
     <row r="33" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A33" s="357" t="s">
+      <c r="A33" s="356" t="s">
         <v>319</v>
       </c>
       <c r="B33" s="108" t="s">
@@ -22156,7 +22156,7 @@
       <c r="AQ33" s="32"/>
     </row>
     <row r="34" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A34" s="363" t="s">
+      <c r="A34" s="362" t="s">
         <v>3974</v>
       </c>
       <c r="B34" s="108" t="s">
@@ -22237,7 +22237,7 @@
       <c r="AQ34" s="32"/>
     </row>
     <row r="35" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A35" s="362" t="s">
+      <c r="A35" s="361" t="s">
         <v>3975</v>
       </c>
       <c r="B35" s="14" t="s">
@@ -22318,7 +22318,7 @@
       <c r="AQ35" s="32"/>
     </row>
     <row r="36" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A36" s="362" t="s">
+      <c r="A36" s="361" t="s">
         <v>3977</v>
       </c>
       <c r="B36" s="14" t="s">
@@ -22397,7 +22397,7 @@
       <c r="AQ36" s="32"/>
     </row>
     <row r="37" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A37" s="357" t="s">
+      <c r="A37" s="356" t="s">
         <v>351</v>
       </c>
       <c r="B37" s="32" t="s">
@@ -22468,7 +22468,7 @@
       <c r="AQ37" s="32"/>
     </row>
     <row r="38" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A38" s="359" t="s">
+      <c r="A38" s="358" t="s">
         <v>3890</v>
       </c>
       <c r="B38" s="14" t="s">
@@ -22547,7 +22547,7 @@
       <c r="AQ38" s="32"/>
     </row>
     <row r="39" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A39" s="359" t="s">
+      <c r="A39" s="358" t="s">
         <v>3891</v>
       </c>
       <c r="B39" s="14" t="s">
@@ -22618,7 +22618,7 @@
       <c r="AQ39" s="32"/>
     </row>
     <row r="40" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A40" s="357" t="s">
+      <c r="A40" s="356" t="s">
         <v>378</v>
       </c>
       <c r="B40" s="17" t="s">
@@ -22685,7 +22685,7 @@
       <c r="AQ40" s="32"/>
     </row>
     <row r="41" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A41" s="357" t="s">
+      <c r="A41" s="356" t="s">
         <v>383</v>
       </c>
       <c r="B41" s="14" t="s">
@@ -22752,7 +22752,7 @@
       <c r="AQ41" s="32"/>
     </row>
     <row r="42" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A42" s="362" t="s">
+      <c r="A42" s="361" t="s">
         <v>3981</v>
       </c>
       <c r="B42" s="14" t="s">
@@ -22823,7 +22823,7 @@
       <c r="AQ42" s="32"/>
     </row>
     <row r="43" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A43" s="362" t="s">
+      <c r="A43" s="361" t="s">
         <v>3982</v>
       </c>
       <c r="B43" s="14" t="s">
@@ -22898,7 +22898,7 @@
       <c r="AQ43" s="32"/>
     </row>
     <row r="44" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A44" s="357" t="s">
+      <c r="A44" s="356" t="s">
         <v>410</v>
       </c>
       <c r="B44" s="32" t="s">
@@ -22965,7 +22965,7 @@
       <c r="AQ44" s="32"/>
     </row>
     <row r="45" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A45" s="357" t="s">
+      <c r="A45" s="356" t="s">
         <v>417</v>
       </c>
       <c r="B45" s="32" t="s">
@@ -23034,7 +23034,7 @@
       <c r="AQ45" s="32"/>
     </row>
     <row r="46" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A46" s="362" t="s">
+      <c r="A46" s="361" t="s">
         <v>3983</v>
       </c>
       <c r="B46" s="14" t="s">
@@ -23111,7 +23111,7 @@
       <c r="AQ46" s="32"/>
     </row>
     <row r="47" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A47" s="358" t="s">
+      <c r="A47" s="357" t="s">
         <v>433</v>
       </c>
       <c r="B47" s="32" t="s">
@@ -23178,7 +23178,7 @@
       <c r="AQ47" s="32"/>
     </row>
     <row r="48" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A48" s="362" t="s">
+      <c r="A48" s="361" t="s">
         <v>3987</v>
       </c>
       <c r="B48" s="32" t="s">
@@ -23254,7 +23254,7 @@
       <c r="AQ48" s="32"/>
     </row>
     <row r="49" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A49" s="357" t="s">
+      <c r="A49" s="356" t="s">
         <v>448</v>
       </c>
       <c r="B49" s="14" t="s">
@@ -23421,7 +23421,7 @@
       <c r="E51" s="62" t="s">
         <v>471</v>
       </c>
-      <c r="F51" s="375" t="s">
+      <c r="F51" s="374" t="s">
         <v>472</v>
       </c>
       <c r="G51" s="32" t="s">
@@ -23477,7 +23477,7 @@
       <c r="AQ51" s="32"/>
     </row>
     <row r="52" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A52" s="362" t="s">
+      <c r="A52" s="361" t="s">
         <v>3992</v>
       </c>
       <c r="B52" s="14" t="s">
@@ -23560,7 +23560,7 @@
       <c r="AQ52" s="32"/>
     </row>
     <row r="53" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A53" s="358" t="s">
+      <c r="A53" s="357" t="s">
         <v>491</v>
       </c>
       <c r="B53" s="14" t="s">
@@ -23639,7 +23639,7 @@
       <c r="AQ53" s="32"/>
     </row>
     <row r="54" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A54" s="362" t="s">
+      <c r="A54" s="361" t="s">
         <v>3993</v>
       </c>
       <c r="B54" s="155" t="s">
@@ -23712,7 +23712,7 @@
       <c r="AQ54" s="32"/>
     </row>
     <row r="55" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A55" s="357" t="s">
+      <c r="A55" s="356" t="s">
         <v>512</v>
       </c>
       <c r="B55" s="32" t="s">
@@ -23781,7 +23781,7 @@
       <c r="AQ55" s="32"/>
     </row>
     <row r="56" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A56" s="357" t="s">
+      <c r="A56" s="356" t="s">
         <v>518</v>
       </c>
       <c r="B56" s="32" t="s">
@@ -23858,7 +23858,7 @@
       <c r="AQ56" s="32"/>
     </row>
     <row r="57" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A57" s="362" t="s">
+      <c r="A57" s="361" t="s">
         <v>3899</v>
       </c>
       <c r="B57" s="32" t="s">
@@ -23925,7 +23925,7 @@
       <c r="AQ57" s="32"/>
     </row>
     <row r="58" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A58" s="362" t="s">
+      <c r="A58" s="361" t="s">
         <v>3995</v>
       </c>
       <c r="B58" s="32" t="s">
@@ -24000,7 +24000,7 @@
       <c r="AQ58" s="32"/>
     </row>
     <row r="59" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A59" s="362" t="s">
+      <c r="A59" s="361" t="s">
         <v>3997</v>
       </c>
       <c r="B59" s="32" t="s">
@@ -24071,7 +24071,7 @@
       <c r="AQ59" s="32"/>
     </row>
     <row r="60" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A60" s="362" t="s">
+      <c r="A60" s="361" t="s">
         <v>3900</v>
       </c>
       <c r="B60" s="32" t="s">
@@ -24146,7 +24146,7 @@
       <c r="AQ60" s="32"/>
     </row>
     <row r="61" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A61" s="362" t="s">
+      <c r="A61" s="361" t="s">
         <v>4000</v>
       </c>
       <c r="B61" s="32" t="s">
@@ -24217,7 +24217,7 @@
       <c r="AQ61" s="32"/>
     </row>
     <row r="62" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A62" s="362" t="s">
+      <c r="A62" s="361" t="s">
         <v>3901</v>
       </c>
       <c r="B62" s="32" t="s">
@@ -24284,7 +24284,7 @@
       <c r="AQ62" s="32"/>
     </row>
     <row r="63" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A63" s="358" t="s">
+      <c r="A63" s="357" t="s">
         <v>568</v>
       </c>
       <c r="B63" s="32" t="s">
@@ -24299,7 +24299,7 @@
       <c r="E63" s="62" t="s">
         <v>4001</v>
       </c>
-      <c r="F63" s="375" t="s">
+      <c r="F63" s="374" t="s">
         <v>571</v>
       </c>
       <c r="G63" s="32" t="s">
@@ -24357,7 +24357,7 @@
       <c r="AQ63" s="32"/>
     </row>
     <row r="64" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A64" s="362" t="s">
+      <c r="A64" s="361" t="s">
         <v>4003</v>
       </c>
       <c r="B64" s="32" t="s">
@@ -24430,7 +24430,7 @@
       <c r="AQ64" s="32"/>
     </row>
     <row r="65" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A65" s="362" t="s">
+      <c r="A65" s="361" t="s">
         <v>4005</v>
       </c>
       <c r="B65" s="32" t="s">
@@ -24503,7 +24503,7 @@
       <c r="AQ65" s="32"/>
     </row>
     <row r="66" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A66" s="362" t="s">
+      <c r="A66" s="361" t="s">
         <v>3902</v>
       </c>
       <c r="B66" s="32" t="s">
@@ -24736,7 +24736,7 @@
       <c r="AQ68" s="32"/>
     </row>
     <row r="69" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A69" s="362" t="s">
+      <c r="A69" s="361" t="s">
         <v>4007</v>
       </c>
       <c r="B69" s="32" t="s">
@@ -24823,7 +24823,7 @@
       <c r="AQ69" s="32"/>
     </row>
     <row r="70" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A70" s="359" t="s">
+      <c r="A70" s="358" t="s">
         <v>3892</v>
       </c>
       <c r="B70" s="32" t="s">
@@ -24892,7 +24892,7 @@
       <c r="AQ70" s="32"/>
     </row>
     <row r="71" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A71" s="362" t="s">
+      <c r="A71" s="361" t="s">
         <v>4008</v>
       </c>
       <c r="B71" s="32" t="s">
@@ -24961,7 +24961,7 @@
       <c r="AQ71" s="32"/>
     </row>
     <row r="72" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A72" s="359" t="s">
+      <c r="A72" s="358" t="s">
         <v>3893</v>
       </c>
       <c r="B72" s="32" t="s">
@@ -25107,7 +25107,7 @@
       <c r="AQ73" s="32"/>
     </row>
     <row r="74" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A74" s="359" t="s">
+      <c r="A74" s="358" t="s">
         <v>3894</v>
       </c>
       <c r="B74" s="39" t="s">
@@ -25176,14 +25176,14 @@
       <c r="AQ74" s="32"/>
     </row>
     <row r="75" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="356" t="s">
         <v>677</v>
       </c>
       <c r="B75" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C75" s="331" t="s">
-        <v>172</v>
+        <v>4010</v>
       </c>
       <c r="D75" s="318"/>
       <c r="E75" s="62"/>
@@ -25243,7 +25243,7 @@
       <c r="AQ75" s="32"/>
     </row>
     <row r="76" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A76" s="357" t="s">
+      <c r="A76" s="356" t="s">
         <v>682</v>
       </c>
       <c r="B76" s="32" t="s">
@@ -25829,7 +25829,7 @@
       <c r="AQ83" s="32"/>
     </row>
     <row r="84" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A84" s="359" t="s">
+      <c r="A84" s="358" t="s">
         <v>3895</v>
       </c>
       <c r="B84" s="14" t="s">
@@ -25965,7 +25965,7 @@
       <c r="AQ85" s="32"/>
     </row>
     <row r="86" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A86" s="359" t="s">
+      <c r="A86" s="358" t="s">
         <v>3896</v>
       </c>
       <c r="B86" s="14" t="s">
@@ -26342,7 +26342,7 @@
       <c r="AQ90" s="32"/>
     </row>
     <row r="91" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A91" s="359" t="s">
+      <c r="A91" s="358" t="s">
         <v>3897</v>
       </c>
       <c r="B91" s="14" t="s">
@@ -26561,7 +26561,7 @@
       <c r="AQ93" s="32"/>
     </row>
     <row r="94" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A94" s="362" t="s">
+      <c r="A94" s="361" t="s">
         <v>3903</v>
       </c>
       <c r="B94" s="32" t="s">
@@ -26695,7 +26695,7 @@
       <c r="AQ95" s="32"/>
     </row>
     <row r="96" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A96" s="362" t="s">
+      <c r="A96" s="361" t="s">
         <v>3904</v>
       </c>
       <c r="B96" s="14" t="s">
@@ -26762,7 +26762,7 @@
       <c r="AQ96" s="32"/>
     </row>
     <row r="97" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A97" s="362" t="s">
+      <c r="A97" s="361" t="s">
         <v>3905</v>
       </c>
       <c r="B97" s="32" t="s">
@@ -26965,7 +26965,7 @@
       <c r="AQ99" s="32"/>
     </row>
     <row r="100" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A100" s="362" t="s">
+      <c r="A100" s="361" t="s">
         <v>3906</v>
       </c>
       <c r="B100" s="32" t="s">
@@ -27111,7 +27111,7 @@
       <c r="AQ101" s="32"/>
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A102" s="362" t="s">
+      <c r="A102" s="361" t="s">
         <v>3907</v>
       </c>
       <c r="B102" s="32" t="s">
@@ -27257,7 +27257,7 @@
       <c r="AQ103" s="32"/>
     </row>
     <row r="104" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A104" s="362" t="s">
+      <c r="A104" s="361" t="s">
         <v>3908</v>
       </c>
       <c r="B104" s="32" t="s">
@@ -27470,7 +27470,7 @@
       <c r="AQ106" s="32"/>
     </row>
     <row r="107" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A107" s="362" t="s">
+      <c r="A107" s="361" t="s">
         <v>3909</v>
       </c>
       <c r="B107" s="32" t="s">
@@ -27553,7 +27553,7 @@
       <c r="AQ107" s="32"/>
     </row>
     <row r="108" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A108" s="362" t="s">
+      <c r="A108" s="361" t="s">
         <v>3910</v>
       </c>
       <c r="B108" s="32" t="s">
@@ -27760,7 +27760,7 @@
       <c r="AQ110" s="32"/>
     </row>
     <row r="111" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A111" s="362" t="s">
+      <c r="A111" s="361" t="s">
         <v>3911</v>
       </c>
       <c r="B111" s="32" t="s">
@@ -27827,7 +27827,7 @@
       <c r="AQ111" s="32"/>
     </row>
     <row r="112" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A112" s="357" t="s">
+      <c r="A112" s="356" t="s">
         <v>973</v>
       </c>
       <c r="B112" s="32" t="s">
@@ -28336,7 +28336,7 @@
       <c r="AQ118" s="32"/>
     </row>
     <row r="119" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A119" s="362" t="s">
+      <c r="A119" s="361" t="s">
         <v>3912</v>
       </c>
       <c r="B119" s="14" t="s">
@@ -28547,7 +28547,7 @@
       <c r="AQ121" s="32"/>
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A122" s="363" t="s">
+      <c r="A122" s="362" t="s">
         <v>3913</v>
       </c>
       <c r="B122" s="52" t="s">
@@ -29064,7 +29064,7 @@
       <c r="AQ128" s="32"/>
     </row>
     <row r="129" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A129" s="363" t="s">
+      <c r="A129" s="362" t="s">
         <v>3914</v>
       </c>
       <c r="B129" s="32" t="s">
@@ -29135,7 +29135,7 @@
       <c r="AQ129" s="32"/>
     </row>
     <row r="130" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A130" s="362" t="s">
+      <c r="A130" s="361" t="s">
         <v>3915</v>
       </c>
       <c r="B130" s="14" t="s">
@@ -29208,7 +29208,7 @@
       <c r="AQ130" s="32"/>
     </row>
     <row r="131" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A131" s="362" t="s">
+      <c r="A131" s="361" t="s">
         <v>3916</v>
       </c>
       <c r="B131" s="33" t="s">
@@ -29644,7 +29644,7 @@
       <c r="AQ136" s="32"/>
     </row>
     <row r="137" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A137" s="362" t="s">
+      <c r="A137" s="361" t="s">
         <v>3917</v>
       </c>
       <c r="B137" s="14" t="s">
@@ -29784,7 +29784,7 @@
       <c r="AQ138" s="32"/>
     </row>
     <row r="139" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A139" s="363" t="s">
+      <c r="A139" s="362" t="s">
         <v>3918</v>
       </c>
       <c r="B139" s="33" t="s">
@@ -30281,7 +30281,7 @@
       <c r="AQ145" s="32"/>
     </row>
     <row r="146" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A146" s="364" t="s">
+      <c r="A146" s="363" t="s">
         <v>1256</v>
       </c>
       <c r="B146" s="52" t="s">
@@ -31972,7 +31972,7 @@
       <c r="AQ168" s="21"/>
     </row>
     <row r="169" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A169" s="362" t="s">
+      <c r="A169" s="361" t="s">
         <v>3919</v>
       </c>
       <c r="B169" s="33" t="s">
@@ -32337,7 +32337,7 @@
       <c r="AQ173" s="21"/>
     </row>
     <row r="174" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A174" s="357" t="s">
+      <c r="A174" s="356" t="s">
         <v>1488</v>
       </c>
       <c r="B174" s="14" t="s">
@@ -32402,7 +32402,7 @@
       <c r="AQ174" s="32"/>
     </row>
     <row r="175" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A175" s="362" t="s">
+      <c r="A175" s="361" t="s">
         <v>3920</v>
       </c>
       <c r="B175" s="33" t="s">
@@ -32471,7 +32471,7 @@
       <c r="AQ175" s="32"/>
     </row>
     <row r="176" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A176" s="362" t="s">
+      <c r="A176" s="361" t="s">
         <v>3921</v>
       </c>
       <c r="B176" s="33" t="s">
@@ -32538,7 +32538,7 @@
       <c r="AQ176" s="32"/>
     </row>
     <row r="177" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A177" s="363" t="s">
+      <c r="A177" s="362" t="s">
         <v>3922</v>
       </c>
       <c r="B177" s="15" t="s">
@@ -32619,7 +32619,7 @@
       <c r="AQ177" s="21"/>
     </row>
     <row r="178" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A178" s="364" t="s">
+      <c r="A178" s="363" t="s">
         <v>1516</v>
       </c>
       <c r="B178" s="15" t="s">
@@ -32775,7 +32775,7 @@
       <c r="AQ179" s="21"/>
     </row>
     <row r="180" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A180" s="364" t="s">
+      <c r="A180" s="363" t="s">
         <v>1535</v>
       </c>
       <c r="B180" s="15" t="s">
@@ -32996,7 +32996,7 @@
       <c r="AQ182" s="32"/>
     </row>
     <row r="183" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A183" s="362" t="s">
+      <c r="A183" s="361" t="s">
         <v>3923</v>
       </c>
       <c r="B183" s="33" t="s">
@@ -33065,7 +33065,7 @@
       <c r="AQ183" s="32"/>
     </row>
     <row r="184" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A184" s="362" t="s">
+      <c r="A184" s="361" t="s">
         <v>3924</v>
       </c>
       <c r="B184" s="33" t="s">
@@ -33499,7 +33499,7 @@
       <c r="AQ189" s="21"/>
     </row>
     <row r="190" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A190" s="363" t="s">
+      <c r="A190" s="362" t="s">
         <v>3925</v>
       </c>
       <c r="B190" s="15" t="s">
@@ -33710,7 +33710,7 @@
       <c r="AQ192" s="32"/>
     </row>
     <row r="193" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A193" s="362" t="s">
+      <c r="A193" s="361" t="s">
         <v>3927</v>
       </c>
       <c r="B193" s="33" t="s">
@@ -33783,7 +33783,7 @@
       <c r="AQ193" s="32"/>
     </row>
     <row r="194" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A194" s="364" t="s">
+      <c r="A194" s="363" t="s">
         <v>1641</v>
       </c>
       <c r="B194" s="52" t="s">
@@ -33862,7 +33862,7 @@
       <c r="AQ194" s="21"/>
     </row>
     <row r="195" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A195" s="357" t="s">
+      <c r="A195" s="356" t="s">
         <v>1652</v>
       </c>
       <c r="B195" s="14" t="s">
@@ -34221,7 +34221,7 @@
       <c r="AQ199" s="32"/>
     </row>
     <row r="200" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A200" s="357" t="s">
+      <c r="A200" s="356" t="s">
         <v>1691</v>
       </c>
       <c r="B200" s="33" t="s">
@@ -34290,7 +34290,7 @@
       <c r="AQ200" s="32"/>
     </row>
     <row r="201" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A201" s="357" t="s">
+      <c r="A201" s="356" t="s">
         <v>1698</v>
       </c>
       <c r="B201" s="32" t="s">
@@ -34444,7 +34444,7 @@
       <c r="AQ202" s="32"/>
     </row>
     <row r="203" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A203" s="357" t="s">
+      <c r="A203" s="356" t="s">
         <v>1716</v>
       </c>
       <c r="B203" s="14" t="s">
@@ -34584,7 +34584,7 @@
       <c r="AQ204" s="32"/>
     </row>
     <row r="205" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A205" s="362" t="s">
+      <c r="A205" s="361" t="s">
         <v>3928</v>
       </c>
       <c r="B205" s="33" t="s">
@@ -34730,7 +34730,7 @@
       <c r="AQ206" s="32"/>
     </row>
     <row r="207" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A207" s="362" t="s">
+      <c r="A207" s="361" t="s">
         <v>3929</v>
       </c>
       <c r="B207" s="14" t="s">
@@ -35048,7 +35048,7 @@
       <c r="AQ210" s="32"/>
     </row>
     <row r="211" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A211" s="362" t="s">
+      <c r="A211" s="361" t="s">
         <v>3930</v>
       </c>
       <c r="B211" s="14" t="s">
@@ -35210,7 +35210,7 @@
       <c r="AQ212" s="32"/>
     </row>
     <row r="213" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A213" s="362" t="s">
+      <c r="A213" s="361" t="s">
         <v>3931</v>
       </c>
       <c r="B213" s="14" t="s">
@@ -35360,7 +35360,7 @@
       <c r="AQ214" s="32"/>
     </row>
     <row r="215" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A215" s="364" t="s">
+      <c r="A215" s="363" t="s">
         <v>1817</v>
       </c>
       <c r="B215" s="14" t="s">
@@ -35790,7 +35790,7 @@
       <c r="AQ220" s="32"/>
     </row>
     <row r="221" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A221" s="365" t="s">
+      <c r="A221" s="364" t="s">
         <v>1866</v>
       </c>
       <c r="B221" s="14" t="s">
@@ -35861,7 +35861,7 @@
       <c r="AQ221" s="32"/>
     </row>
     <row r="222" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A222" s="363" t="s">
+      <c r="A222" s="362" t="s">
         <v>3932</v>
       </c>
       <c r="B222" s="14" t="s">
@@ -35936,7 +35936,7 @@
       <c r="AQ222" s="32"/>
     </row>
     <row r="223" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A223" s="357" t="s">
+      <c r="A223" s="356" t="s">
         <v>1885</v>
       </c>
       <c r="B223" s="14" t="s">
@@ -36019,7 +36019,7 @@
       <c r="AQ223" s="32"/>
     </row>
     <row r="224" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A224" s="362" t="s">
+      <c r="A224" s="361" t="s">
         <v>3933</v>
       </c>
       <c r="B224" s="14" t="s">
@@ -36305,7 +36305,7 @@
       <c r="AQ227" s="32"/>
     </row>
     <row r="228" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A228" s="362" t="s">
+      <c r="A228" s="361" t="s">
         <v>3934</v>
       </c>
       <c r="B228" s="14" t="s">
@@ -36455,7 +36455,7 @@
       <c r="AQ229" s="32"/>
     </row>
     <row r="230" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A230" s="357" t="s">
+      <c r="A230" s="356" t="s">
         <v>1949</v>
       </c>
       <c r="B230" s="14" t="s">
@@ -36747,7 +36747,7 @@
       <c r="AQ233" s="32"/>
     </row>
     <row r="234" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A234" s="362" t="s">
+      <c r="A234" s="361" t="s">
         <v>3935</v>
       </c>
       <c r="B234" s="14" t="s">
@@ -36903,7 +36903,7 @@
       <c r="AQ235" s="32"/>
     </row>
     <row r="236" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A236" s="357" t="s">
+      <c r="A236" s="356" t="s">
         <v>1995</v>
       </c>
       <c r="B236" s="14" t="s">
@@ -37223,7 +37223,7 @@
       <c r="AQ239" s="32"/>
     </row>
     <row r="240" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A240" s="362" t="s">
+      <c r="A240" s="361" t="s">
         <v>3936</v>
       </c>
       <c r="B240" s="14" t="s">
@@ -37454,7 +37454,7 @@
       <c r="AQ242" s="32"/>
     </row>
     <row r="243" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A243" s="357" t="s">
+      <c r="A243" s="356" t="s">
         <v>2062</v>
       </c>
       <c r="B243" s="14" t="s">
@@ -37537,7 +37537,7 @@
       <c r="AQ243" s="32"/>
     </row>
     <row r="244" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A244" s="357" t="s">
+      <c r="A244" s="356" t="s">
         <v>2071</v>
       </c>
       <c r="B244" s="14" t="s">
@@ -38200,7 +38200,7 @@
       <c r="AQ252" s="32"/>
     </row>
     <row r="253" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A253" s="357" t="s">
+      <c r="A253" s="356" t="s">
         <v>2137</v>
       </c>
       <c r="B253" s="14" t="s">
@@ -38411,7 +38411,7 @@
       <c r="AQ255" s="32"/>
     </row>
     <row r="256" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A256" s="363" t="s">
+      <c r="A256" s="362" t="s">
         <v>3938</v>
       </c>
       <c r="B256" s="21" t="s">
@@ -38565,7 +38565,7 @@
       <c r="AQ257" s="32"/>
     </row>
     <row r="258" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A258" s="362" t="s">
+      <c r="A258" s="361" t="s">
         <v>3939</v>
       </c>
       <c r="B258" s="14" t="s">
@@ -38932,7 +38932,7 @@
       <c r="AQ262" s="32"/>
     </row>
     <row r="263" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A263" s="362" t="s">
+      <c r="A263" s="361" t="s">
         <v>3940</v>
       </c>
       <c r="B263" s="14" t="s">
@@ -39139,7 +39139,7 @@
       <c r="AQ265" s="32"/>
     </row>
     <row r="266" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A266" s="362" t="s">
+      <c r="A266" s="361" t="s">
         <v>3941</v>
       </c>
       <c r="B266" s="14" t="s">
@@ -39358,7 +39358,7 @@
       <c r="AQ268" s="32"/>
     </row>
     <row r="269" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A269" s="363" t="s">
+      <c r="A269" s="362" t="s">
         <v>3942</v>
       </c>
       <c r="B269" s="71" t="s">
@@ -40374,7 +40374,7 @@
       <c r="AQ282" s="32"/>
     </row>
     <row r="283" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A283" s="357" t="s">
+      <c r="A283" s="356" t="s">
         <v>2360</v>
       </c>
       <c r="B283" s="108" t="s">
@@ -41232,7 +41232,7 @@
       <c r="AQ294" s="32"/>
     </row>
     <row r="295" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A295" s="362" t="s">
+      <c r="A295" s="361" t="s">
         <v>3943</v>
       </c>
       <c r="B295" s="14" t="s">
@@ -41956,13 +41956,13 @@
       <c r="AQ304" s="32"/>
     </row>
     <row r="305" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A305" s="366" t="s">
+      <c r="A305" s="365" t="s">
         <v>2521</v>
       </c>
       <c r="B305" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C305" s="351" t="s">
+      <c r="C305" s="348" t="s">
         <v>2521</v>
       </c>
       <c r="D305" s="312"/>
@@ -42027,7 +42027,7 @@
       <c r="AQ305" s="32"/>
     </row>
     <row r="306" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A306" s="367" t="s">
+      <c r="A306" s="366" t="s">
         <v>3944</v>
       </c>
       <c r="B306" s="33" t="s">
@@ -42185,7 +42185,7 @@
       <c r="AQ307" s="32"/>
     </row>
     <row r="308" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A308" s="367" t="s">
+      <c r="A308" s="366" t="s">
         <v>3945</v>
       </c>
       <c r="B308" s="33" t="s">
@@ -42262,7 +42262,7 @@
       <c r="AQ308" s="32"/>
     </row>
     <row r="309" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A309" s="368" t="s">
+      <c r="A309" s="367" t="s">
         <v>2561</v>
       </c>
       <c r="B309" s="14" t="s">
@@ -42339,7 +42339,7 @@
       <c r="AQ309" s="32"/>
     </row>
     <row r="310" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A310" s="369" t="s">
+      <c r="A310" s="368" t="s">
         <v>3946</v>
       </c>
       <c r="B310" s="33" t="s">
@@ -42935,7 +42935,7 @@
       <c r="AQ317" s="32"/>
     </row>
     <row r="318" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A318" s="370" t="s">
+      <c r="A318" s="369" t="s">
         <v>3947</v>
       </c>
       <c r="B318" s="33" t="s">
@@ -43094,7 +43094,7 @@
       <c r="AQ319" s="32"/>
     </row>
     <row r="320" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A320" s="367" t="s">
+      <c r="A320" s="366" t="s">
         <v>3948</v>
       </c>
       <c r="B320" s="33" t="s">
@@ -43163,7 +43163,7 @@
       <c r="AQ320" s="32"/>
     </row>
     <row r="321" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A321" s="367" t="s">
+      <c r="A321" s="366" t="s">
         <v>3949</v>
       </c>
       <c r="B321" s="33" t="s">
@@ -43694,7 +43694,7 @@
       <c r="AQ327" s="32"/>
     </row>
     <row r="328" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A328" s="366" t="s">
+      <c r="A328" s="365" t="s">
         <v>2721</v>
       </c>
       <c r="B328" s="33" t="s">
@@ -43937,7 +43937,7 @@
       <c r="AQ330" s="32"/>
     </row>
     <row r="331" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A331" s="371" t="s">
+      <c r="A331" s="370" t="s">
         <v>2751</v>
       </c>
       <c r="B331" s="33" t="s">
@@ -44164,7 +44164,7 @@
       <c r="AQ333" s="32"/>
     </row>
     <row r="334" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A334" s="366" t="s">
+      <c r="A334" s="365" t="s">
         <v>2773</v>
       </c>
       <c r="B334" s="33" t="s">
@@ -44533,7 +44533,7 @@
       <c r="AQ338" s="32"/>
     </row>
     <row r="339" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A339" s="366" t="s">
+      <c r="A339" s="365" t="s">
         <v>2816</v>
       </c>
       <c r="B339" s="33" t="s">
@@ -44610,7 +44610,7 @@
       <c r="AQ339" s="32"/>
     </row>
     <row r="340" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A340" s="366" t="s">
+      <c r="A340" s="365" t="s">
         <v>2826</v>
       </c>
       <c r="B340" s="33" t="s">
@@ -44693,7 +44693,7 @@
       <c r="AQ340" s="32"/>
     </row>
     <row r="341" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A341" s="366" t="s">
+      <c r="A341" s="365" t="s">
         <v>2837</v>
       </c>
       <c r="B341" s="33" t="s">
@@ -44766,7 +44766,7 @@
       <c r="AQ341" s="32"/>
     </row>
     <row r="342" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A342" s="367" t="s">
+      <c r="A342" s="366" t="s">
         <v>3951</v>
       </c>
       <c r="B342" s="33" t="s">
@@ -44916,7 +44916,7 @@
       <c r="AQ343" s="32"/>
     </row>
     <row r="344" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A344" s="366" t="s">
+      <c r="A344" s="365" t="s">
         <v>2861</v>
       </c>
       <c r="B344" s="33" t="s">
@@ -44995,7 +44995,7 @@
       <c r="AQ344" s="32"/>
     </row>
     <row r="345" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A345" s="367" t="s">
+      <c r="A345" s="366" t="s">
         <v>3952</v>
       </c>
       <c r="B345" s="33" t="s">
@@ -45937,7 +45937,7 @@
       <c r="AQ356" s="32"/>
     </row>
     <row r="357" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A357" s="366" t="s">
+      <c r="A357" s="365" t="s">
         <v>2971</v>
       </c>
       <c r="B357" s="33" t="s">
@@ -46089,7 +46089,7 @@
       <c r="AQ358" s="32"/>
     </row>
     <row r="359" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A359" s="366" t="s">
+      <c r="A359" s="365" t="s">
         <v>2987</v>
       </c>
       <c r="B359" s="33" t="s">
@@ -46616,7 +46616,7 @@
       <c r="AQ365" s="32"/>
     </row>
     <row r="366" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A366" s="367" t="s">
+      <c r="A366" s="366" t="s">
         <v>3953</v>
       </c>
       <c r="B366" s="33" t="s">
@@ -46851,7 +46851,7 @@
       <c r="AQ368" s="32"/>
     </row>
     <row r="369" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A369" s="371" t="s">
+      <c r="A369" s="370" t="s">
         <v>3066</v>
       </c>
       <c r="B369" s="33" t="s">
@@ -46932,7 +46932,7 @@
       <c r="AQ369" s="32"/>
     </row>
     <row r="370" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A370" s="366" t="s">
+      <c r="A370" s="365" t="s">
         <v>3078</v>
       </c>
       <c r="B370" s="33" t="s">
@@ -47011,7 +47011,7 @@
       <c r="AQ370" s="32"/>
     </row>
     <row r="371" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A371" s="366" t="s">
+      <c r="A371" s="365" t="s">
         <v>3086</v>
       </c>
       <c r="B371" s="33" t="s">
@@ -47090,7 +47090,7 @@
       <c r="AQ371" s="32"/>
     </row>
     <row r="372" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A372" s="366" t="s">
+      <c r="A372" s="365" t="s">
         <v>3094</v>
       </c>
       <c r="B372" s="33" t="s">
@@ -47707,7 +47707,7 @@
       <c r="AQ379" s="32"/>
     </row>
     <row r="380" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A380" s="366" t="s">
+      <c r="A380" s="365" t="s">
         <v>3158</v>
       </c>
       <c r="B380" s="33" t="s">
@@ -47867,7 +47867,7 @@
       <c r="AQ381" s="32"/>
     </row>
     <row r="382" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A382" s="366" t="s">
+      <c r="A382" s="365" t="s">
         <v>3177</v>
       </c>
       <c r="B382" s="33" t="s">
@@ -47944,7 +47944,7 @@
       <c r="AQ382" s="32"/>
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A383" s="367" t="s">
+      <c r="A383" s="366" t="s">
         <v>3954</v>
       </c>
       <c r="B383" s="33" t="s">
@@ -48013,7 +48013,7 @@
       <c r="AQ383" s="32"/>
     </row>
     <row r="384" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A384" s="367" t="s">
+      <c r="A384" s="366" t="s">
         <v>3955</v>
       </c>
       <c r="B384" s="33" t="s">
@@ -48082,7 +48082,7 @@
       <c r="AQ384" s="32"/>
     </row>
     <row r="385" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A385" s="366" t="s">
+      <c r="A385" s="365" t="s">
         <v>3191</v>
       </c>
       <c r="B385" s="33" t="s">
@@ -48151,7 +48151,7 @@
       <c r="AQ385" s="32"/>
     </row>
     <row r="386" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A386" s="366" t="s">
+      <c r="A386" s="365" t="s">
         <v>3196</v>
       </c>
       <c r="B386" s="33" t="s">
@@ -48226,7 +48226,7 @@
       <c r="AQ386" s="32"/>
     </row>
     <row r="387" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A387" s="367" t="s">
+      <c r="A387" s="366" t="s">
         <v>3956</v>
       </c>
       <c r="B387" s="33" t="s">
@@ -48833,7 +48833,7 @@
       <c r="AQ394" s="32"/>
     </row>
     <row r="395" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A395" s="366" t="s">
+      <c r="A395" s="365" t="s">
         <v>3262</v>
       </c>
       <c r="B395" s="33" t="s">
@@ -49826,7 +49826,7 @@
       <c r="AQ407" s="32"/>
     </row>
     <row r="408" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A408" s="367" t="s">
+      <c r="A408" s="366" t="s">
         <v>3958</v>
       </c>
       <c r="B408" s="33" t="s">
@@ -49899,7 +49899,7 @@
       <c r="AQ408" s="32"/>
     </row>
     <row r="409" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A409" s="372" t="s">
+      <c r="A409" s="371" t="s">
         <v>3959</v>
       </c>
       <c r="B409" s="33" t="s">
@@ -50274,7 +50274,7 @@
       <c r="AQ413" s="32"/>
     </row>
     <row r="414" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A414" s="372" t="s">
+      <c r="A414" s="371" t="s">
         <v>3960</v>
       </c>
       <c r="B414" s="33" t="s">
@@ -51022,7 +51022,7 @@
       <c r="AQ423" s="32"/>
     </row>
     <row r="424" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A424" s="372" t="s">
+      <c r="A424" s="371" t="s">
         <v>3961</v>
       </c>
       <c r="B424" s="33" t="s">
@@ -51854,7 +51854,7 @@
       <c r="AQ435" s="32"/>
     </row>
     <row r="436" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A436" s="366" t="s">
+      <c r="A436" s="365" t="s">
         <v>3539</v>
       </c>
       <c r="B436" s="33" t="s">
@@ -53660,7 +53660,7 @@
       <c r="AQ459" s="32"/>
     </row>
     <row r="460" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A460" s="372" t="s">
+      <c r="A460" s="371" t="s">
         <v>3962</v>
       </c>
       <c r="B460" s="108" t="s">
@@ -53960,7 +53960,7 @@
       <c r="AQ463" s="32"/>
     </row>
     <row r="464" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A464" s="372" t="s">
+      <c r="A464" s="371" t="s">
         <v>3963</v>
       </c>
       <c r="B464" s="108" t="s">
@@ -54114,7 +54114,7 @@
       <c r="AQ465" s="32"/>
     </row>
     <row r="466" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A466" s="373" t="s">
+      <c r="A466" s="372" t="s">
         <v>3964</v>
       </c>
       <c r="B466" s="108" t="s">
@@ -54775,7 +54775,7 @@
       <c r="AQ474" s="32"/>
     </row>
     <row r="475" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A475" s="366" t="s">
+      <c r="A475" s="365" t="s">
         <v>3812</v>
       </c>
       <c r="B475" s="108" t="s">
@@ -55012,7 +55012,7 @@
       <c r="AQ477" s="32"/>
     </row>
     <row r="478" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A478" s="366" t="s">
+      <c r="A478" s="365" t="s">
         <v>3839</v>
       </c>
       <c r="B478" s="108" t="s">
@@ -64155,7 +64155,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{38C87D68-71FC-7A41-A313-797EF044067A}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{AEEB9956-05E6-8046-B542-DFA582BD0402}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC25336E-81AE-4B47-A62A-80E65603F15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C165ACF-EA60-BD4A-B9D3-E49BA061995C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2080" yWindow="-16800" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="-19980" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6989" uniqueCount="4011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6989" uniqueCount="4010">
   <si>
     <t>ID estampe</t>
   </si>
@@ -16715,25 +16715,6 @@
     <t xml:space="preserve">Article à </t>
   </si>
   <si>
-    <t>BnF, Ars, 8-H-26484(244)</t>
-  </si>
-  <si>
-    <r>
-      <t>https://gallica.bnf.fr/ark:/12148/bpt6k6261188b/f304.item</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color theme="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ; Planche manque dans Gallica au 20/05/21. Commande cliché Ars. le 18/10/22</t>
-    </r>
-  </si>
-  <si>
     <t>[Ordre de bataille tenu en Flandres sous le commandement du Maréchal duc de Luxembourg]*</t>
   </si>
   <si>
@@ -17195,6 +17176,9 @@
   </si>
   <si>
     <t>MG-1679-02_357</t>
+  </si>
+  <si>
+    <t>https://gallica.bnf.fr/ark:/12148/bpt6k6261188b/f277.item</t>
   </si>
 </sst>
 </file>
@@ -18303,7 +18287,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="376">
+  <cellXfs count="377">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -19167,7 +19151,6 @@
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -19368,6 +19351,8 @@
     <xf numFmtId="0" fontId="128" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -19591,8 +19576,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="15.1640625" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="346" customWidth="1"/>
-    <col min="4" max="4" width="14" style="326" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="345" customWidth="1"/>
+    <col min="4" max="4" width="14" style="325" customWidth="1"/>
     <col min="5" max="7" width="19.1640625" customWidth="1"/>
     <col min="8" max="8" width="25.6640625" customWidth="1"/>
     <col min="9" max="9" width="18.1640625" customWidth="1"/>
@@ -19623,10 +19608,10 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="329" t="s">
+      <c r="C1" s="328" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="308" t="s">
+      <c r="D1" s="307" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -19722,16 +19707,16 @@
       <c r="AQ1" s="3"/>
     </row>
     <row r="2" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A2" s="358" t="s">
-        <v>3898</v>
+      <c r="A2" s="357" t="s">
+        <v>3896</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="330" t="s">
+      <c r="C2" s="329" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="309"/>
+      <c r="D2" s="308"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19" t="s">
         <v>32</v>
@@ -19799,8 +19784,8 @@
       <c r="B3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="331"/>
-      <c r="D3" s="310"/>
+      <c r="C3" s="330"/>
+      <c r="D3" s="309"/>
       <c r="E3" s="18"/>
       <c r="F3" s="34" t="s">
         <v>44</v>
@@ -19870,16 +19855,16 @@
       <c r="AQ3" s="32"/>
     </row>
     <row r="4" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A4" s="355" t="s">
+      <c r="A4" s="354" t="s">
         <v>55</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="332" t="s">
+      <c r="C4" s="331" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="310" t="s">
+      <c r="D4" s="309" t="s">
         <v>57</v>
       </c>
       <c r="E4" s="18" t="s">
@@ -19957,16 +19942,16 @@
       <c r="AQ4" s="32"/>
     </row>
     <row r="5" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A5" s="359" t="s">
-        <v>3884</v>
+      <c r="A5" s="358" t="s">
+        <v>3882</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="330" t="s">
+      <c r="C5" s="329" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="309"/>
+      <c r="D5" s="308"/>
       <c r="E5" s="18"/>
       <c r="F5" s="34" t="s">
         <v>75</v>
@@ -20032,16 +20017,16 @@
       <c r="AQ5" s="32"/>
     </row>
     <row r="6" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A6" s="373" t="s">
-        <v>3965</v>
+      <c r="A6" s="372" t="s">
+        <v>3963</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="330" t="s">
+      <c r="C6" s="329" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="311" t="s">
+      <c r="D6" s="310" t="s">
         <v>87</v>
       </c>
       <c r="E6" s="53" t="s">
@@ -20117,8 +20102,8 @@
       <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="333"/>
-      <c r="D7" s="309"/>
+      <c r="C7" s="332"/>
+      <c r="D7" s="308"/>
       <c r="E7" s="58"/>
       <c r="F7" s="19" t="s">
         <v>98</v>
@@ -20182,16 +20167,16 @@
       <c r="AQ7" s="32"/>
     </row>
     <row r="8" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A8" s="359" t="s">
-        <v>3883</v>
+      <c r="A8" s="358" t="s">
+        <v>3881</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="334" t="s">
+      <c r="C8" s="333" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="312"/>
+      <c r="D8" s="311"/>
       <c r="E8" s="62"/>
       <c r="F8" s="16" t="s">
         <v>103</v>
@@ -20259,16 +20244,16 @@
       <c r="AQ8" s="32"/>
     </row>
     <row r="9" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A9" s="358" t="s">
-        <v>3966</v>
+      <c r="A9" s="357" t="s">
+        <v>3964</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="350" t="s">
+      <c r="C9" s="349" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="311" t="s">
+      <c r="D9" s="310" t="s">
         <v>115</v>
       </c>
       <c r="E9" s="62" t="s">
@@ -20332,16 +20317,16 @@
       <c r="AQ9" s="32"/>
     </row>
     <row r="10" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A10" s="359" t="s">
+      <c r="A10" s="358" t="s">
         <v>123</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="330" t="s">
+      <c r="C10" s="329" t="s">
         <v>124</v>
       </c>
-      <c r="D10" s="309"/>
+      <c r="D10" s="308"/>
       <c r="E10" s="18"/>
       <c r="F10" s="34" t="s">
         <v>125</v>
@@ -20407,10 +20392,10 @@
       <c r="B11" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="348" t="s">
+      <c r="C11" s="347" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="313"/>
+      <c r="D11" s="312"/>
       <c r="E11" s="72"/>
       <c r="F11" s="16" t="s">
         <v>133</v>
@@ -20480,10 +20465,10 @@
       <c r="B12" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="332" t="s">
-        <v>3877</v>
-      </c>
-      <c r="D12" s="313"/>
+      <c r="C12" s="331" t="s">
+        <v>3875</v>
+      </c>
+      <c r="D12" s="312"/>
       <c r="E12" s="72"/>
       <c r="F12" s="16" t="s">
         <v>133</v>
@@ -20551,10 +20536,10 @@
       <c r="B13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="332" t="s">
-        <v>3877</v>
-      </c>
-      <c r="D13" s="312"/>
+      <c r="C13" s="331" t="s">
+        <v>3875</v>
+      </c>
+      <c r="D13" s="311"/>
       <c r="E13" s="62"/>
       <c r="F13" s="16" t="s">
         <v>152</v>
@@ -20616,16 +20601,16 @@
       <c r="AQ13" s="32"/>
     </row>
     <row r="14" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A14" s="353" t="s">
+      <c r="A14" s="352" t="s">
         <v>160</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="335" t="s">
+      <c r="C14" s="334" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="312"/>
+      <c r="D14" s="311"/>
       <c r="E14" s="62"/>
       <c r="F14" s="16" t="s">
         <v>163</v>
@@ -20695,10 +20680,10 @@
       <c r="B15" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="331" t="s">
+      <c r="C15" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D15" s="312"/>
+      <c r="D15" s="311"/>
       <c r="E15" s="62"/>
       <c r="F15" s="32" t="s">
         <v>173</v>
@@ -20758,16 +20743,16 @@
       <c r="AQ15" s="32"/>
     </row>
     <row r="16" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A16" s="360" t="s">
-        <v>3882</v>
+      <c r="A16" s="359" t="s">
+        <v>3880</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="348" t="s">
-        <v>3878</v>
-      </c>
-      <c r="D16" s="311" t="s">
+      <c r="C16" s="347" t="s">
+        <v>3876</v>
+      </c>
+      <c r="D16" s="310" t="s">
         <v>180</v>
       </c>
       <c r="E16" s="62" t="s">
@@ -20851,10 +20836,10 @@
       <c r="B17" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="351" t="s">
-        <v>3879</v>
-      </c>
-      <c r="D17" s="311" t="s">
+      <c r="C17" s="350" t="s">
+        <v>3877</v>
+      </c>
+      <c r="D17" s="310" t="s">
         <v>180</v>
       </c>
       <c r="E17" s="62" t="s">
@@ -20932,7 +20917,7 @@
       <c r="AQ17" s="32"/>
     </row>
     <row r="18" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A18" s="354" t="s">
+      <c r="A18" s="353" t="s">
         <v>203</v>
       </c>
       <c r="B18" s="94" t="s">
@@ -20941,7 +20926,7 @@
       <c r="C18" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="D18" s="314" t="s">
+      <c r="D18" s="313" t="s">
         <v>180</v>
       </c>
       <c r="E18" s="62" t="s">
@@ -21019,7 +21004,7 @@
       <c r="AQ18" s="32"/>
     </row>
     <row r="19" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A19" s="352" t="s">
+      <c r="A19" s="351" t="s">
         <v>211</v>
       </c>
       <c r="B19" s="32" t="s">
@@ -21028,7 +21013,7 @@
       <c r="C19" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="D19" s="311" t="s">
+      <c r="D19" s="310" t="s">
         <v>180</v>
       </c>
       <c r="E19" s="62" t="s">
@@ -21106,8 +21091,8 @@
       <c r="AQ19" s="32"/>
     </row>
     <row r="20" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A20" s="360" t="s">
-        <v>3880</v>
+      <c r="A20" s="359" t="s">
+        <v>3878</v>
       </c>
       <c r="B20" s="32" t="s">
         <v>43</v>
@@ -21115,7 +21100,7 @@
       <c r="C20" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="D20" s="311" t="s">
+      <c r="D20" s="310" t="s">
         <v>180</v>
       </c>
       <c r="E20" s="62" t="s">
@@ -21191,8 +21176,8 @@
       <c r="AQ20" s="32"/>
     </row>
     <row r="21" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A21" s="352" t="s">
-        <v>3881</v>
+      <c r="A21" s="351" t="s">
+        <v>3879</v>
       </c>
       <c r="B21" s="32" t="s">
         <v>43</v>
@@ -21200,7 +21185,7 @@
       <c r="C21" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="D21" s="311" t="s">
+      <c r="D21" s="310" t="s">
         <v>180</v>
       </c>
       <c r="E21" s="62" t="s">
@@ -21280,10 +21265,10 @@
       <c r="B22" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="332" t="s">
+      <c r="C22" s="331" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="312"/>
+      <c r="D22" s="311"/>
       <c r="E22" s="62"/>
       <c r="F22" s="16" t="s">
         <v>231</v>
@@ -21355,10 +21340,10 @@
       <c r="B23" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="336" t="s">
+      <c r="C23" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D23" s="312"/>
+      <c r="D23" s="311"/>
       <c r="E23" s="62"/>
       <c r="F23" s="16" t="s">
         <v>241</v>
@@ -21422,16 +21407,16 @@
       <c r="AQ23" s="32"/>
     </row>
     <row r="24" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A24" s="361" t="s">
-        <v>3885</v>
+      <c r="A24" s="360" t="s">
+        <v>3883</v>
       </c>
       <c r="B24" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="C24" s="330" t="s">
+      <c r="C24" s="329" t="s">
         <v>250</v>
       </c>
-      <c r="D24" s="309"/>
+      <c r="D24" s="308"/>
       <c r="E24" s="18"/>
       <c r="F24" s="34" t="s">
         <v>251</v>
@@ -21491,16 +21476,16 @@
       <c r="AQ24" s="32"/>
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A25" s="361" t="s">
-        <v>3886</v>
+      <c r="A25" s="360" t="s">
+        <v>3884</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="C25" s="330" t="s">
+      <c r="C25" s="329" t="s">
         <v>250</v>
       </c>
-      <c r="D25" s="312"/>
+      <c r="D25" s="311"/>
       <c r="E25" s="62"/>
       <c r="F25" s="16" t="s">
         <v>258</v>
@@ -21560,16 +21545,16 @@
       <c r="AQ25" s="32"/>
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A26" s="375" t="s">
-        <v>3968</v>
+      <c r="A26" s="374" t="s">
+        <v>3966</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="331" t="s">
-        <v>3967</v>
-      </c>
-      <c r="D26" s="311" t="s">
+      <c r="C26" s="330" t="s">
+        <v>3965</v>
+      </c>
+      <c r="D26" s="310" t="s">
         <v>180</v>
       </c>
       <c r="E26" s="62" t="s">
@@ -21631,16 +21616,16 @@
       <c r="AQ26" s="32"/>
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A27" s="375" t="s">
+      <c r="A27" s="374" t="s">
         <v>269</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="331" t="s">
-        <v>3967</v>
-      </c>
-      <c r="D27" s="311" t="s">
+      <c r="C27" s="330" t="s">
+        <v>3965</v>
+      </c>
+      <c r="D27" s="310" t="s">
         <v>180</v>
       </c>
       <c r="E27" s="62" t="s">
@@ -21702,22 +21687,22 @@
       <c r="AQ27" s="32"/>
     </row>
     <row r="28" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A28" s="361" t="s">
-        <v>3969</v>
+      <c r="A28" s="360" t="s">
+        <v>3967</v>
       </c>
       <c r="B28" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="C28" s="330" t="s">
+      <c r="C28" s="329" t="s">
         <v>272</v>
       </c>
-      <c r="D28" s="314" t="s">
+      <c r="D28" s="313" t="s">
         <v>273</v>
       </c>
       <c r="E28" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="F28" s="374" t="s">
+      <c r="F28" s="373" t="s">
         <v>275</v>
       </c>
       <c r="G28" s="32" t="s">
@@ -21781,16 +21766,16 @@
       <c r="AQ28" s="32"/>
     </row>
     <row r="29" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A29" s="358" t="s">
-        <v>3887</v>
+      <c r="A29" s="357" t="s">
+        <v>3885</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="C29" s="330" t="s">
+      <c r="C29" s="329" t="s">
         <v>282</v>
       </c>
-      <c r="D29" s="315" t="s">
+      <c r="D29" s="314" t="s">
         <v>283</v>
       </c>
       <c r="E29" s="62"/>
@@ -21856,16 +21841,16 @@
       <c r="AQ29" s="32"/>
     </row>
     <row r="30" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A30" s="358" t="s">
-        <v>3888</v>
+      <c r="A30" s="357" t="s">
+        <v>3886</v>
       </c>
       <c r="B30" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="C30" s="330" t="s">
+      <c r="C30" s="329" t="s">
         <v>282</v>
       </c>
-      <c r="D30" s="316" t="s">
+      <c r="D30" s="315" t="s">
         <v>283</v>
       </c>
       <c r="E30" s="62" t="s">
@@ -21937,16 +21922,16 @@
       <c r="AQ30" s="32"/>
     </row>
     <row r="31" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A31" s="361" t="s">
-        <v>3970</v>
+      <c r="A31" s="360" t="s">
+        <v>3968</v>
       </c>
       <c r="B31" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="C31" s="331" t="s">
-        <v>3972</v>
-      </c>
-      <c r="D31" s="309"/>
+      <c r="C31" s="330" t="s">
+        <v>3970</v>
+      </c>
+      <c r="D31" s="308"/>
       <c r="E31" s="18"/>
       <c r="F31" s="34" t="s">
         <v>304</v>
@@ -22010,16 +21995,16 @@
       <c r="AQ31" s="32"/>
     </row>
     <row r="32" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A32" s="358" t="s">
-        <v>3889</v>
+      <c r="A32" s="357" t="s">
+        <v>3887</v>
       </c>
       <c r="B32" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="C32" s="330" t="s">
+      <c r="C32" s="329" t="s">
         <v>273</v>
       </c>
-      <c r="D32" s="317"/>
+      <c r="D32" s="316"/>
       <c r="E32" s="62"/>
       <c r="F32" s="16" t="s">
         <v>313</v>
@@ -22085,16 +22070,16 @@
       <c r="AQ32" s="32"/>
     </row>
     <row r="33" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A33" s="356" t="s">
+      <c r="A33" s="355" t="s">
         <v>319</v>
       </c>
       <c r="B33" s="108" t="s">
         <v>294</v>
       </c>
-      <c r="C33" s="331" t="s">
-        <v>3971</v>
-      </c>
-      <c r="D33" s="309"/>
+      <c r="C33" s="330" t="s">
+        <v>3969</v>
+      </c>
+      <c r="D33" s="308"/>
       <c r="E33" s="18"/>
       <c r="F33" s="34" t="s">
         <v>320</v>
@@ -22156,16 +22141,16 @@
       <c r="AQ33" s="32"/>
     </row>
     <row r="34" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A34" s="362" t="s">
-        <v>3974</v>
+      <c r="A34" s="361" t="s">
+        <v>3972</v>
       </c>
       <c r="B34" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="332" t="s">
-        <v>3973</v>
-      </c>
-      <c r="D34" s="311" t="s">
+      <c r="C34" s="331" t="s">
+        <v>3971</v>
+      </c>
+      <c r="D34" s="310" t="s">
         <v>282</v>
       </c>
       <c r="E34" s="62" t="s">
@@ -22237,16 +22222,16 @@
       <c r="AQ34" s="32"/>
     </row>
     <row r="35" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A35" s="361" t="s">
-        <v>3975</v>
+      <c r="A35" s="360" t="s">
+        <v>3973</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="332" t="s">
-        <v>3973</v>
-      </c>
-      <c r="D35" s="311" t="s">
+      <c r="C35" s="331" t="s">
+        <v>3971</v>
+      </c>
+      <c r="D35" s="310" t="s">
         <v>282</v>
       </c>
       <c r="E35" s="62" t="s">
@@ -22318,16 +22303,16 @@
       <c r="AQ35" s="32"/>
     </row>
     <row r="36" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A36" s="361" t="s">
-        <v>3977</v>
+      <c r="A36" s="360" t="s">
+        <v>3975</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="331" t="s">
-        <v>3976</v>
-      </c>
-      <c r="D36" s="312"/>
+      <c r="C36" s="330" t="s">
+        <v>3974</v>
+      </c>
+      <c r="D36" s="311"/>
       <c r="E36" s="62"/>
       <c r="F36" s="16" t="s">
         <v>340</v>
@@ -22397,16 +22382,16 @@
       <c r="AQ36" s="32"/>
     </row>
     <row r="37" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A37" s="356" t="s">
+      <c r="A37" s="355" t="s">
         <v>351</v>
       </c>
       <c r="B37" s="32" t="s">
         <v>352</v>
       </c>
-      <c r="C37" s="330" t="s">
+      <c r="C37" s="329" t="s">
         <v>353</v>
       </c>
-      <c r="D37" s="311" t="s">
+      <c r="D37" s="310" t="s">
         <v>354</v>
       </c>
       <c r="E37" s="62"/>
@@ -22468,17 +22453,17 @@
       <c r="AQ37" s="32"/>
     </row>
     <row r="38" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A38" s="358" t="s">
-        <v>3890</v>
+      <c r="A38" s="357" t="s">
+        <v>3888</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="337" t="s">
+      <c r="C38" s="336" t="s">
         <v>361</v>
       </c>
-      <c r="D38" s="312" t="s">
-        <v>3978</v>
+      <c r="D38" s="311" t="s">
+        <v>3976</v>
       </c>
       <c r="E38" s="62"/>
       <c r="F38" s="32" t="s">
@@ -22547,16 +22532,16 @@
       <c r="AQ38" s="32"/>
     </row>
     <row r="39" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A39" s="358" t="s">
-        <v>3891</v>
+      <c r="A39" s="357" t="s">
+        <v>3889</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="334" t="s">
+      <c r="C39" s="333" t="s">
         <v>361</v>
       </c>
-      <c r="D39" s="312"/>
+      <c r="D39" s="311"/>
       <c r="E39" s="62"/>
       <c r="F39" s="32" t="s">
         <v>173</v>
@@ -22618,16 +22603,16 @@
       <c r="AQ39" s="32"/>
     </row>
     <row r="40" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A40" s="356" t="s">
+      <c r="A40" s="355" t="s">
         <v>378</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="C40" s="331" t="s">
-        <v>3979</v>
-      </c>
-      <c r="D40" s="312"/>
+      <c r="C40" s="330" t="s">
+        <v>3977</v>
+      </c>
+      <c r="D40" s="311"/>
       <c r="E40" s="62"/>
       <c r="F40" s="32" t="s">
         <v>173</v>
@@ -22685,16 +22670,16 @@
       <c r="AQ40" s="32"/>
     </row>
     <row r="41" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A41" s="356" t="s">
+      <c r="A41" s="355" t="s">
         <v>383</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="330" t="s">
+      <c r="C41" s="329" t="s">
         <v>384</v>
       </c>
-      <c r="D41" s="312"/>
+      <c r="D41" s="311"/>
       <c r="E41" s="62"/>
       <c r="F41" s="16" t="s">
         <v>385</v>
@@ -22752,16 +22737,16 @@
       <c r="AQ41" s="32"/>
     </row>
     <row r="42" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A42" s="361" t="s">
-        <v>3981</v>
+      <c r="A42" s="360" t="s">
+        <v>3979</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="331" t="s">
-        <v>3980</v>
-      </c>
-      <c r="D42" s="312"/>
+      <c r="C42" s="330" t="s">
+        <v>3978</v>
+      </c>
+      <c r="D42" s="311"/>
       <c r="E42" s="62"/>
       <c r="F42" s="16" t="s">
         <v>393</v>
@@ -22823,16 +22808,16 @@
       <c r="AQ42" s="32"/>
     </row>
     <row r="43" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A43" s="361" t="s">
-        <v>3982</v>
+      <c r="A43" s="360" t="s">
+        <v>3980</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="331" t="s">
-        <v>3980</v>
-      </c>
-      <c r="D43" s="312"/>
+      <c r="C43" s="330" t="s">
+        <v>3978</v>
+      </c>
+      <c r="D43" s="311"/>
       <c r="E43" s="62"/>
       <c r="F43" s="16" t="s">
         <v>401</v>
@@ -22898,16 +22883,16 @@
       <c r="AQ43" s="32"/>
     </row>
     <row r="44" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A44" s="356" t="s">
+      <c r="A44" s="355" t="s">
         <v>410</v>
       </c>
       <c r="B44" s="32" t="s">
         <v>411</v>
       </c>
-      <c r="C44" s="330" t="s">
+      <c r="C44" s="329" t="s">
         <v>412</v>
       </c>
-      <c r="D44" s="312"/>
+      <c r="D44" s="311"/>
       <c r="E44" s="62"/>
       <c r="F44" s="16" t="s">
         <v>413</v>
@@ -22965,16 +22950,16 @@
       <c r="AQ44" s="32"/>
     </row>
     <row r="45" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A45" s="356" t="s">
+      <c r="A45" s="355" t="s">
         <v>417</v>
       </c>
       <c r="B45" s="32" t="s">
         <v>418</v>
       </c>
-      <c r="C45" s="332" t="s">
+      <c r="C45" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D45" s="312"/>
+      <c r="D45" s="311"/>
       <c r="E45" s="62"/>
       <c r="F45" s="16" t="s">
         <v>419</v>
@@ -23034,16 +23019,16 @@
       <c r="AQ45" s="32"/>
     </row>
     <row r="46" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A46" s="361" t="s">
-        <v>3983</v>
+      <c r="A46" s="360" t="s">
+        <v>3981</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C46" s="331" t="s">
-        <v>3984</v>
-      </c>
-      <c r="D46" s="312"/>
+      <c r="C46" s="330" t="s">
+        <v>3982</v>
+      </c>
+      <c r="D46" s="311"/>
       <c r="E46" s="62"/>
       <c r="F46" s="16" t="s">
         <v>425</v>
@@ -23111,16 +23096,16 @@
       <c r="AQ46" s="32"/>
     </row>
     <row r="47" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A47" s="357" t="s">
+      <c r="A47" s="356" t="s">
         <v>433</v>
       </c>
       <c r="B47" s="32" t="s">
         <v>418</v>
       </c>
-      <c r="C47" s="331" t="s">
-        <v>3985</v>
-      </c>
-      <c r="D47" s="312"/>
+      <c r="C47" s="330" t="s">
+        <v>3983</v>
+      </c>
+      <c r="D47" s="311"/>
       <c r="E47" s="62"/>
       <c r="F47" s="16" t="s">
         <v>434</v>
@@ -23178,16 +23163,16 @@
       <c r="AQ47" s="32"/>
     </row>
     <row r="48" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A48" s="361" t="s">
-        <v>3987</v>
+      <c r="A48" s="360" t="s">
+        <v>3985</v>
       </c>
       <c r="B48" s="32" t="s">
         <v>439</v>
       </c>
-      <c r="C48" s="331" t="s">
-        <v>3986</v>
-      </c>
-      <c r="D48" s="312"/>
+      <c r="C48" s="330" t="s">
+        <v>3984</v>
+      </c>
+      <c r="D48" s="311"/>
       <c r="E48" s="62"/>
       <c r="F48" s="16" t="s">
         <v>440</v>
@@ -23254,16 +23239,16 @@
       <c r="AQ48" s="32"/>
     </row>
     <row r="49" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A49" s="356" t="s">
+      <c r="A49" s="355" t="s">
         <v>448</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="C49" s="330" t="s">
+      <c r="C49" s="329" t="s">
         <v>450</v>
       </c>
-      <c r="D49" s="312"/>
+      <c r="D49" s="311"/>
       <c r="E49" s="62"/>
       <c r="F49" s="48" t="s">
         <v>451</v>
@@ -23336,15 +23321,15 @@
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>3988</v>
+        <v>3986</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>439</v>
       </c>
-      <c r="C50" s="331" t="s">
-        <v>3989</v>
-      </c>
-      <c r="D50" s="312"/>
+      <c r="C50" s="330" t="s">
+        <v>3987</v>
+      </c>
+      <c r="D50" s="311"/>
       <c r="E50" s="62"/>
       <c r="F50" s="48" t="s">
         <v>463</v>
@@ -23407,21 +23392,21 @@
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>3990</v>
+        <v>3988</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="C51" s="331" t="s">
-        <v>3991</v>
-      </c>
-      <c r="D51" s="311" t="s">
+      <c r="C51" s="330" t="s">
+        <v>3989</v>
+      </c>
+      <c r="D51" s="310" t="s">
         <v>470</v>
       </c>
       <c r="E51" s="62" t="s">
         <v>471</v>
       </c>
-      <c r="F51" s="374" t="s">
+      <c r="F51" s="373" t="s">
         <v>472</v>
       </c>
       <c r="G51" s="32" t="s">
@@ -23477,16 +23462,16 @@
       <c r="AQ51" s="32"/>
     </row>
     <row r="52" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A52" s="361" t="s">
-        <v>3992</v>
+      <c r="A52" s="360" t="s">
+        <v>3990</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C52" s="330" t="s">
+      <c r="C52" s="329" t="s">
         <v>477</v>
       </c>
-      <c r="D52" s="311" t="s">
+      <c r="D52" s="310" t="s">
         <v>478</v>
       </c>
       <c r="E52" s="62" t="s">
@@ -23560,16 +23545,16 @@
       <c r="AQ52" s="32"/>
     </row>
     <row r="53" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A53" s="357" t="s">
+      <c r="A53" s="356" t="s">
         <v>491</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C53" s="330" t="s">
+      <c r="C53" s="329" t="s">
         <v>492</v>
       </c>
-      <c r="D53" s="312"/>
+      <c r="D53" s="311"/>
       <c r="E53" s="62"/>
       <c r="F53" s="16" t="s">
         <v>493</v>
@@ -23639,16 +23624,16 @@
       <c r="AQ53" s="32"/>
     </row>
     <row r="54" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A54" s="361" t="s">
-        <v>3993</v>
+      <c r="A54" s="360" t="s">
+        <v>3991</v>
       </c>
       <c r="B54" s="155" t="s">
         <v>502</v>
       </c>
-      <c r="C54" s="330" t="s">
+      <c r="C54" s="329" t="s">
         <v>478</v>
       </c>
-      <c r="D54" s="312"/>
+      <c r="D54" s="311"/>
       <c r="E54" s="62"/>
       <c r="F54" s="16" t="s">
         <v>503</v>
@@ -23712,16 +23697,16 @@
       <c r="AQ54" s="32"/>
     </row>
     <row r="55" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A55" s="356" t="s">
+      <c r="A55" s="355" t="s">
         <v>512</v>
       </c>
       <c r="B55" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="331" t="s">
-        <v>3994</v>
-      </c>
-      <c r="D55" s="312"/>
+      <c r="C55" s="330" t="s">
+        <v>3992</v>
+      </c>
+      <c r="D55" s="311"/>
       <c r="E55" s="62"/>
       <c r="F55" s="48" t="s">
         <v>513</v>
@@ -23781,16 +23766,16 @@
       <c r="AQ55" s="32"/>
     </row>
     <row r="56" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A56" s="356" t="s">
+      <c r="A56" s="355" t="s">
         <v>518</v>
       </c>
       <c r="B56" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C56" s="332" t="s">
+      <c r="C56" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D56" s="312"/>
+      <c r="D56" s="311"/>
       <c r="E56" s="62"/>
       <c r="F56" s="16" t="s">
         <v>519</v>
@@ -23858,16 +23843,16 @@
       <c r="AQ56" s="32"/>
     </row>
     <row r="57" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A57" s="361" t="s">
-        <v>3899</v>
+      <c r="A57" s="360" t="s">
+        <v>3897</v>
       </c>
       <c r="B57" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C57" s="330" t="s">
+      <c r="C57" s="329" t="s">
         <v>470</v>
       </c>
-      <c r="D57" s="312"/>
+      <c r="D57" s="311"/>
       <c r="E57" s="62"/>
       <c r="F57" s="16" t="s">
         <v>531</v>
@@ -23925,16 +23910,16 @@
       <c r="AQ57" s="32"/>
     </row>
     <row r="58" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A58" s="361" t="s">
-        <v>3995</v>
+      <c r="A58" s="360" t="s">
+        <v>3993</v>
       </c>
       <c r="B58" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="331" t="s">
-        <v>3996</v>
-      </c>
-      <c r="D58" s="311" t="s">
+      <c r="C58" s="330" t="s">
+        <v>3994</v>
+      </c>
+      <c r="D58" s="310" t="s">
         <v>180</v>
       </c>
       <c r="E58" s="62" t="s">
@@ -24000,16 +23985,16 @@
       <c r="AQ58" s="32"/>
     </row>
     <row r="59" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A59" s="361" t="s">
-        <v>3997</v>
+      <c r="A59" s="360" t="s">
+        <v>3995</v>
       </c>
       <c r="B59" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="331" t="s">
-        <v>3996</v>
-      </c>
-      <c r="D59" s="311" t="s">
+      <c r="C59" s="330" t="s">
+        <v>3994</v>
+      </c>
+      <c r="D59" s="310" t="s">
         <v>180</v>
       </c>
       <c r="E59" s="62" t="s">
@@ -24071,16 +24056,16 @@
       <c r="AQ59" s="32"/>
     </row>
     <row r="60" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A60" s="361" t="s">
-        <v>3900</v>
+      <c r="A60" s="360" t="s">
+        <v>3898</v>
       </c>
       <c r="B60" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C60" s="330" t="s">
+      <c r="C60" s="329" t="s">
         <v>542</v>
       </c>
-      <c r="D60" s="312"/>
+      <c r="D60" s="311"/>
       <c r="E60" s="62"/>
       <c r="F60" s="16" t="s">
         <v>543</v>
@@ -24146,19 +24131,19 @@
       <c r="AQ60" s="32"/>
     </row>
     <row r="61" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A61" s="361" t="s">
-        <v>4000</v>
+      <c r="A61" s="360" t="s">
+        <v>3998</v>
       </c>
       <c r="B61" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C61" s="331" t="s">
-        <v>3999</v>
-      </c>
-      <c r="D61" s="312"/>
+      <c r="C61" s="330" t="s">
+        <v>3997</v>
+      </c>
+      <c r="D61" s="311"/>
       <c r="E61" s="62"/>
       <c r="F61" s="48" t="s">
-        <v>3998</v>
+        <v>3996</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>554</v>
@@ -24217,16 +24202,16 @@
       <c r="AQ61" s="32"/>
     </row>
     <row r="62" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A62" s="361" t="s">
-        <v>3901</v>
+      <c r="A62" s="360" t="s">
+        <v>3899</v>
       </c>
       <c r="B62" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C62" s="330" t="s">
+      <c r="C62" s="329" t="s">
         <v>560</v>
       </c>
-      <c r="D62" s="312"/>
+      <c r="D62" s="311"/>
       <c r="E62" s="62"/>
       <c r="F62" s="16" t="s">
         <v>561</v>
@@ -24284,22 +24269,22 @@
       <c r="AQ62" s="32"/>
     </row>
     <row r="63" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A63" s="357" t="s">
+      <c r="A63" s="356" t="s">
         <v>568</v>
       </c>
       <c r="B63" s="32" t="s">
         <v>569</v>
       </c>
-      <c r="C63" s="331" t="s">
-        <v>4002</v>
-      </c>
-      <c r="D63" s="311" t="s">
+      <c r="C63" s="330" t="s">
+        <v>4000</v>
+      </c>
+      <c r="D63" s="310" t="s">
         <v>570</v>
       </c>
       <c r="E63" s="62" t="s">
-        <v>4001</v>
-      </c>
-      <c r="F63" s="374" t="s">
+        <v>3999</v>
+      </c>
+      <c r="F63" s="373" t="s">
         <v>571</v>
       </c>
       <c r="G63" s="32" t="s">
@@ -24357,16 +24342,16 @@
       <c r="AQ63" s="32"/>
     </row>
     <row r="64" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A64" s="361" t="s">
-        <v>4003</v>
+      <c r="A64" s="360" t="s">
+        <v>4001</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C64" s="331" t="s">
-        <v>4004</v>
-      </c>
-      <c r="D64" s="312"/>
+      <c r="C64" s="330" t="s">
+        <v>4002</v>
+      </c>
+      <c r="D64" s="311"/>
       <c r="E64" s="62"/>
       <c r="F64" s="16" t="s">
         <v>576</v>
@@ -24430,16 +24415,16 @@
       <c r="AQ64" s="32"/>
     </row>
     <row r="65" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A65" s="361" t="s">
-        <v>4005</v>
+      <c r="A65" s="360" t="s">
+        <v>4003</v>
       </c>
       <c r="B65" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C65" s="331" t="s">
-        <v>4006</v>
-      </c>
-      <c r="D65" s="312"/>
+      <c r="C65" s="330" t="s">
+        <v>4004</v>
+      </c>
+      <c r="D65" s="311"/>
       <c r="E65" s="62"/>
       <c r="F65" s="16" t="s">
         <v>585</v>
@@ -24503,16 +24488,16 @@
       <c r="AQ65" s="32"/>
     </row>
     <row r="66" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A66" s="361" t="s">
-        <v>3902</v>
+      <c r="A66" s="360" t="s">
+        <v>3900</v>
       </c>
       <c r="B66" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C66" s="330" t="s">
+      <c r="C66" s="329" t="s">
         <v>570</v>
       </c>
-      <c r="D66" s="311" t="s">
+      <c r="D66" s="310" t="s">
         <v>594</v>
       </c>
       <c r="E66" s="62" t="s">
@@ -24582,10 +24567,10 @@
       <c r="B67" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C67" s="337" t="s">
+      <c r="C67" s="336" t="s">
         <v>172</v>
       </c>
-      <c r="D67" s="311" t="s">
+      <c r="D67" s="310" t="s">
         <v>601</v>
       </c>
       <c r="E67" s="62"/>
@@ -24665,10 +24650,10 @@
       <c r="B68" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C68" s="336" t="s">
+      <c r="C68" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D68" s="312"/>
+      <c r="D68" s="311"/>
       <c r="E68" s="62"/>
       <c r="F68" s="16" t="s">
         <v>614</v>
@@ -24736,16 +24721,16 @@
       <c r="AQ68" s="32"/>
     </row>
     <row r="69" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A69" s="361" t="s">
-        <v>4007</v>
+      <c r="A69" s="360" t="s">
+        <v>4005</v>
       </c>
       <c r="B69" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C69" s="332" t="s">
+      <c r="C69" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D69" s="314"/>
+      <c r="D69" s="313"/>
       <c r="E69" s="62"/>
       <c r="F69" s="16" t="s">
         <v>623</v>
@@ -24823,16 +24808,16 @@
       <c r="AQ69" s="32"/>
     </row>
     <row r="70" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A70" s="358" t="s">
-        <v>3892</v>
+      <c r="A70" s="357" t="s">
+        <v>3890</v>
       </c>
       <c r="B70" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C70" s="339" t="s">
+      <c r="C70" s="338" t="s">
         <v>634</v>
       </c>
-      <c r="D70" s="312"/>
+      <c r="D70" s="311"/>
       <c r="E70" s="62"/>
       <c r="F70" s="16" t="s">
         <v>635</v>
@@ -24892,16 +24877,16 @@
       <c r="AQ70" s="32"/>
     </row>
     <row r="71" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A71" s="361" t="s">
-        <v>4008</v>
+      <c r="A71" s="360" t="s">
+        <v>4006</v>
       </c>
       <c r="B71" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C71" s="331" t="s">
-        <v>4009</v>
-      </c>
-      <c r="D71" s="312"/>
+      <c r="C71" s="330" t="s">
+        <v>4007</v>
+      </c>
+      <c r="D71" s="311"/>
       <c r="E71" s="62"/>
       <c r="F71" s="16" t="s">
         <v>641</v>
@@ -24961,16 +24946,16 @@
       <c r="AQ71" s="32"/>
     </row>
     <row r="72" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A72" s="358" t="s">
-        <v>3893</v>
+      <c r="A72" s="357" t="s">
+        <v>3891</v>
       </c>
       <c r="B72" s="32" t="s">
         <v>649</v>
       </c>
-      <c r="C72" s="340" t="s">
+      <c r="C72" s="339" t="s">
         <v>650</v>
       </c>
-      <c r="D72" s="312"/>
+      <c r="D72" s="311"/>
       <c r="E72" s="62"/>
       <c r="F72" s="16" t="s">
         <v>651</v>
@@ -25036,10 +25021,10 @@
       <c r="B73" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C73" s="332" t="s">
+      <c r="C73" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D73" s="312"/>
+      <c r="D73" s="311"/>
       <c r="E73" s="62"/>
       <c r="F73" s="48" t="s">
         <v>658</v>
@@ -25107,16 +25092,16 @@
       <c r="AQ73" s="32"/>
     </row>
     <row r="74" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A74" s="358" t="s">
-        <v>3894</v>
+      <c r="A74" s="357" t="s">
+        <v>3892</v>
       </c>
       <c r="B74" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C74" s="330" t="s">
+      <c r="C74" s="329" t="s">
         <v>669</v>
       </c>
-      <c r="D74" s="312"/>
+      <c r="D74" s="311"/>
       <c r="E74" s="62"/>
       <c r="F74" s="16" t="s">
         <v>670</v>
@@ -25176,16 +25161,16 @@
       <c r="AQ74" s="32"/>
     </row>
     <row r="75" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A75" s="356" t="s">
+      <c r="A75" s="355" t="s">
         <v>677</v>
       </c>
       <c r="B75" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C75" s="331" t="s">
-        <v>4010</v>
-      </c>
-      <c r="D75" s="318"/>
+      <c r="C75" s="330" t="s">
+        <v>4008</v>
+      </c>
+      <c r="D75" s="317"/>
       <c r="E75" s="62"/>
       <c r="F75" s="16" t="s">
         <v>678</v>
@@ -25243,16 +25228,16 @@
       <c r="AQ75" s="32"/>
     </row>
     <row r="76" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A76" s="356" t="s">
+      <c r="A76" s="355" t="s">
         <v>682</v>
       </c>
       <c r="B76" s="32" t="s">
         <v>683</v>
       </c>
-      <c r="C76" s="330" t="s">
+      <c r="C76" s="329" t="s">
         <v>684</v>
       </c>
-      <c r="D76" s="312"/>
+      <c r="D76" s="311"/>
       <c r="E76" s="62"/>
       <c r="F76" s="16" t="s">
         <v>685</v>
@@ -25318,10 +25303,10 @@
       <c r="B77" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C77" s="332" t="s">
+      <c r="C77" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D77" s="312"/>
+      <c r="D77" s="311"/>
       <c r="E77" s="62"/>
       <c r="F77" s="16" t="s">
         <v>693</v>
@@ -25393,10 +25378,10 @@
       <c r="B78" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C78" s="338" t="s">
+      <c r="C78" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D78" s="318"/>
+      <c r="D78" s="317"/>
       <c r="E78" s="166"/>
       <c r="F78" s="16" t="s">
         <v>704</v>
@@ -25462,10 +25447,10 @@
       <c r="B79" s="32" t="s">
         <v>476</v>
       </c>
-      <c r="C79" s="331" t="s">
+      <c r="C79" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D79" s="312"/>
+      <c r="D79" s="311"/>
       <c r="E79" s="62"/>
       <c r="F79" s="16" t="s">
         <v>710</v>
@@ -25539,10 +25524,10 @@
       <c r="B80" s="155" t="s">
         <v>719</v>
       </c>
-      <c r="C80" s="340" t="s">
+      <c r="C80" s="339" t="s">
         <v>172</v>
       </c>
-      <c r="D80" s="319" t="s">
+      <c r="D80" s="318" t="s">
         <v>601</v>
       </c>
       <c r="E80" s="62" t="s">
@@ -25620,10 +25605,10 @@
       <c r="B81" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C81" s="341" t="s">
+      <c r="C81" s="340" t="s">
         <v>172</v>
       </c>
-      <c r="D81" s="320" t="s">
+      <c r="D81" s="319" t="s">
         <v>601</v>
       </c>
       <c r="E81" s="166" t="s">
@@ -25691,10 +25676,10 @@
       <c r="B82" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C82" s="331" t="s">
+      <c r="C82" s="330" t="s">
         <v>738</v>
       </c>
-      <c r="D82" s="312"/>
+      <c r="D82" s="311"/>
       <c r="E82" s="62"/>
       <c r="F82" s="48" t="s">
         <v>739</v>
@@ -25762,10 +25747,10 @@
       <c r="B83" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C83" s="332" t="s">
+      <c r="C83" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D83" s="312"/>
+      <c r="D83" s="311"/>
       <c r="E83" s="62"/>
       <c r="F83" s="48" t="s">
         <v>747</v>
@@ -25829,16 +25814,16 @@
       <c r="AQ83" s="32"/>
     </row>
     <row r="84" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A84" s="358" t="s">
-        <v>3895</v>
+      <c r="A84" s="357" t="s">
+        <v>3893</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>754</v>
       </c>
-      <c r="C84" s="330" t="s">
+      <c r="C84" s="329" t="s">
         <v>755</v>
       </c>
-      <c r="D84" s="312"/>
+      <c r="D84" s="311"/>
       <c r="E84" s="62"/>
       <c r="F84" s="16" t="s">
         <v>756</v>
@@ -25902,10 +25887,10 @@
       <c r="B85" s="14" t="s">
         <v>754</v>
       </c>
-      <c r="C85" s="331" t="s">
+      <c r="C85" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D85" s="312"/>
+      <c r="D85" s="311"/>
       <c r="E85" s="62"/>
       <c r="F85" s="16" t="s">
         <v>762</v>
@@ -25965,16 +25950,16 @@
       <c r="AQ85" s="32"/>
     </row>
     <row r="86" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A86" s="358" t="s">
-        <v>3896</v>
+      <c r="A86" s="357" t="s">
+        <v>3894</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C86" s="330" t="s">
+      <c r="C86" s="329" t="s">
         <v>767</v>
       </c>
-      <c r="D86" s="312"/>
+      <c r="D86" s="311"/>
       <c r="E86" s="62"/>
       <c r="F86" s="16" t="s">
         <v>768</v>
@@ -26042,10 +26027,10 @@
       <c r="B87" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C87" s="332" t="s">
+      <c r="C87" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D87" s="312"/>
+      <c r="D87" s="311"/>
       <c r="E87" s="62"/>
       <c r="F87" s="48" t="s">
         <v>774</v>
@@ -26121,10 +26106,10 @@
       <c r="B88" s="14" t="s">
         <v>786</v>
       </c>
-      <c r="C88" s="331" t="s">
+      <c r="C88" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D88" s="311" t="s">
+      <c r="D88" s="310" t="s">
         <v>787</v>
       </c>
       <c r="E88" s="62" t="s">
@@ -26194,10 +26179,10 @@
       <c r="B89" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C89" s="332" t="s">
+      <c r="C89" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D89" s="312"/>
+      <c r="D89" s="311"/>
       <c r="E89" s="62"/>
       <c r="F89" s="16" t="s">
         <v>795</v>
@@ -26271,10 +26256,10 @@
       <c r="B90" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C90" s="342" t="s">
+      <c r="C90" s="341" t="s">
         <v>144</v>
       </c>
-      <c r="D90" s="318"/>
+      <c r="D90" s="317"/>
       <c r="E90" s="166"/>
       <c r="F90" s="16" t="s">
         <v>805</v>
@@ -26342,16 +26327,16 @@
       <c r="AQ90" s="32"/>
     </row>
     <row r="91" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A91" s="358" t="s">
-        <v>3897</v>
+      <c r="A91" s="357" t="s">
+        <v>3895</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C91" s="334" t="s">
+      <c r="C91" s="333" t="s">
         <v>787</v>
       </c>
-      <c r="D91" s="321" t="s">
+      <c r="D91" s="320" t="s">
         <v>815</v>
       </c>
       <c r="E91" s="166"/>
@@ -26419,10 +26404,10 @@
       <c r="B92" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C92" s="338" t="s">
+      <c r="C92" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D92" s="312"/>
+      <c r="D92" s="311"/>
       <c r="E92" s="62"/>
       <c r="F92" s="16" t="s">
         <v>822</v>
@@ -26490,10 +26475,10 @@
       <c r="B93" s="32" t="s">
         <v>476</v>
       </c>
-      <c r="C93" s="332" t="s">
+      <c r="C93" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D93" s="312"/>
+      <c r="D93" s="311"/>
       <c r="E93" s="62"/>
       <c r="F93" s="16" t="s">
         <v>828</v>
@@ -26561,16 +26546,16 @@
       <c r="AQ93" s="32"/>
     </row>
     <row r="94" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A94" s="361" t="s">
-        <v>3903</v>
+      <c r="A94" s="360" t="s">
+        <v>3901</v>
       </c>
       <c r="B94" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C94" s="330" t="s">
+      <c r="C94" s="329" t="s">
         <v>838</v>
       </c>
-      <c r="D94" s="312"/>
+      <c r="D94" s="311"/>
       <c r="E94" s="62"/>
       <c r="F94" s="48" t="s">
         <v>839</v>
@@ -26634,10 +26619,10 @@
       <c r="B95" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C95" s="332" t="s">
+      <c r="C95" s="331" t="s">
         <v>846</v>
       </c>
-      <c r="D95" s="312"/>
+      <c r="D95" s="311"/>
       <c r="E95" s="62"/>
       <c r="F95" s="48" t="s">
         <v>847</v>
@@ -26695,16 +26680,16 @@
       <c r="AQ95" s="32"/>
     </row>
     <row r="96" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A96" s="361" t="s">
-        <v>3904</v>
+      <c r="A96" s="360" t="s">
+        <v>3902</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C96" s="334" t="s">
+      <c r="C96" s="333" t="s">
         <v>815</v>
       </c>
-      <c r="D96" s="318"/>
+      <c r="D96" s="317"/>
       <c r="E96" s="166"/>
       <c r="F96" s="16" t="s">
         <v>852</v>
@@ -26762,16 +26747,16 @@
       <c r="AQ96" s="32"/>
     </row>
     <row r="97" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A97" s="361" t="s">
-        <v>3905</v>
+      <c r="A97" s="360" t="s">
+        <v>3903</v>
       </c>
       <c r="B97" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C97" s="330" t="s">
+      <c r="C97" s="329" t="s">
         <v>856</v>
       </c>
-      <c r="D97" s="312"/>
+      <c r="D97" s="311"/>
       <c r="E97" s="62"/>
       <c r="F97" s="16" t="s">
         <v>857</v>
@@ -26835,10 +26820,10 @@
       <c r="B98" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C98" s="331" t="s">
+      <c r="C98" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D98" s="312"/>
+      <c r="D98" s="311"/>
       <c r="E98" s="62"/>
       <c r="F98" s="16" t="s">
         <v>864</v>
@@ -26902,10 +26887,10 @@
       <c r="B99" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C99" s="331" t="s">
+      <c r="C99" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D99" s="311" t="s">
+      <c r="D99" s="310" t="s">
         <v>870</v>
       </c>
       <c r="E99" s="62"/>
@@ -26965,16 +26950,16 @@
       <c r="AQ99" s="32"/>
     </row>
     <row r="100" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A100" s="361" t="s">
-        <v>3906</v>
+      <c r="A100" s="360" t="s">
+        <v>3904</v>
       </c>
       <c r="B100" s="32" t="s">
         <v>875</v>
       </c>
-      <c r="C100" s="330" t="s">
+      <c r="C100" s="329" t="s">
         <v>876</v>
       </c>
-      <c r="D100" s="312"/>
+      <c r="D100" s="311"/>
       <c r="E100" s="62"/>
       <c r="F100" s="48" t="s">
         <v>877</v>
@@ -27048,10 +27033,10 @@
       <c r="B101" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C101" s="332" t="s">
+      <c r="C101" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D101" s="312"/>
+      <c r="D101" s="311"/>
       <c r="E101" s="62"/>
       <c r="F101" s="48" t="s">
         <v>888</v>
@@ -27111,16 +27096,16 @@
       <c r="AQ101" s="32"/>
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A102" s="361" t="s">
-        <v>3907</v>
+      <c r="A102" s="360" t="s">
+        <v>3905</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>895</v>
       </c>
-      <c r="C102" s="330" t="s">
+      <c r="C102" s="329" t="s">
         <v>870</v>
       </c>
-      <c r="D102" s="312"/>
+      <c r="D102" s="311"/>
       <c r="E102" s="62"/>
       <c r="F102" s="16" t="s">
         <v>896</v>
@@ -27184,10 +27169,10 @@
       <c r="B103" s="32" t="s">
         <v>476</v>
       </c>
-      <c r="C103" s="331" t="s">
+      <c r="C103" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D103" s="312"/>
+      <c r="D103" s="311"/>
       <c r="E103" s="62"/>
       <c r="F103" s="32" t="s">
         <v>173</v>
@@ -27257,16 +27242,16 @@
       <c r="AQ103" s="32"/>
     </row>
     <row r="104" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A104" s="361" t="s">
-        <v>3908</v>
+      <c r="A104" s="360" t="s">
+        <v>3906</v>
       </c>
       <c r="B104" s="32" t="s">
         <v>476</v>
       </c>
-      <c r="C104" s="330" t="s">
+      <c r="C104" s="329" t="s">
         <v>911</v>
       </c>
-      <c r="D104" s="312"/>
+      <c r="D104" s="311"/>
       <c r="E104" s="62"/>
       <c r="F104" s="32" t="s">
         <v>173</v>
@@ -27334,10 +27319,10 @@
       <c r="B105" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C105" s="331" t="s">
+      <c r="C105" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D105" s="312"/>
+      <c r="D105" s="311"/>
       <c r="E105" s="62"/>
       <c r="F105" s="16" t="s">
         <v>920</v>
@@ -27409,10 +27394,10 @@
       <c r="B106" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C106" s="331" t="s">
+      <c r="C106" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D106" s="312"/>
+      <c r="D106" s="311"/>
       <c r="E106" s="62"/>
       <c r="F106" s="16" t="s">
         <v>930</v>
@@ -27470,16 +27455,16 @@
       <c r="AQ106" s="32"/>
     </row>
     <row r="107" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A107" s="361" t="s">
-        <v>3909</v>
+      <c r="A107" s="360" t="s">
+        <v>3907</v>
       </c>
       <c r="B107" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C107" s="330" t="s">
+      <c r="C107" s="329" t="s">
         <v>934</v>
       </c>
-      <c r="D107" s="312"/>
+      <c r="D107" s="311"/>
       <c r="E107" s="62"/>
       <c r="F107" s="16" t="s">
         <v>935</v>
@@ -27553,16 +27538,16 @@
       <c r="AQ107" s="32"/>
     </row>
     <row r="108" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A108" s="361" t="s">
-        <v>3910</v>
+      <c r="A108" s="360" t="s">
+        <v>3908</v>
       </c>
       <c r="B108" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C108" s="330" t="s">
+      <c r="C108" s="329" t="s">
         <v>934</v>
       </c>
-      <c r="D108" s="312"/>
+      <c r="D108" s="311"/>
       <c r="E108" s="62"/>
       <c r="F108" s="48" t="s">
         <v>945</v>
@@ -27630,10 +27615,10 @@
       <c r="B109" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C109" s="336" t="s">
+      <c r="C109" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D109" s="312"/>
+      <c r="D109" s="311"/>
       <c r="E109" s="62"/>
       <c r="F109" s="48" t="s">
         <v>955</v>
@@ -27695,10 +27680,10 @@
       <c r="B110" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C110" s="331" t="s">
+      <c r="C110" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D110" s="312"/>
+      <c r="D110" s="311"/>
       <c r="E110" s="62"/>
       <c r="F110" s="16" t="s">
         <v>961</v>
@@ -27760,16 +27745,16 @@
       <c r="AQ110" s="32"/>
     </row>
     <row r="111" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A111" s="361" t="s">
-        <v>3911</v>
+      <c r="A111" s="360" t="s">
+        <v>3909</v>
       </c>
       <c r="B111" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C111" s="330" t="s">
+      <c r="C111" s="329" t="s">
         <v>967</v>
       </c>
-      <c r="D111" s="312"/>
+      <c r="D111" s="311"/>
       <c r="E111" s="62"/>
       <c r="F111" s="16" t="s">
         <v>968</v>
@@ -27827,16 +27812,16 @@
       <c r="AQ111" s="32"/>
     </row>
     <row r="112" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A112" s="356" t="s">
+      <c r="A112" s="355" t="s">
         <v>973</v>
       </c>
       <c r="B112" s="32" t="s">
         <v>974</v>
       </c>
-      <c r="C112" s="330" t="s">
+      <c r="C112" s="329" t="s">
         <v>975</v>
       </c>
-      <c r="D112" s="312"/>
+      <c r="D112" s="311"/>
       <c r="E112" s="62"/>
       <c r="F112" s="16" t="s">
         <v>976</v>
@@ -27902,10 +27887,10 @@
       <c r="B113" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C113" s="331" t="s">
+      <c r="C113" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D113" s="312"/>
+      <c r="D113" s="311"/>
       <c r="E113" s="62"/>
       <c r="F113" s="16" t="s">
         <v>982</v>
@@ -27979,10 +27964,10 @@
       <c r="B114" s="32" t="s">
         <v>439</v>
       </c>
-      <c r="C114" s="331" t="s">
+      <c r="C114" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D114" s="312"/>
+      <c r="D114" s="311"/>
       <c r="E114" s="62"/>
       <c r="F114" s="48" t="s">
         <v>994</v>
@@ -28056,10 +28041,10 @@
       <c r="B115" s="32" t="s">
         <v>1005</v>
       </c>
-      <c r="C115" s="331" t="s">
+      <c r="C115" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D115" s="312"/>
+      <c r="D115" s="311"/>
       <c r="E115" s="62"/>
       <c r="F115" s="16" t="s">
         <v>1006</v>
@@ -28125,10 +28110,10 @@
       <c r="B116" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C116" s="331" t="s">
+      <c r="C116" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D116" s="312"/>
+      <c r="D116" s="311"/>
       <c r="E116" s="62"/>
       <c r="F116" s="16" t="s">
         <v>1013</v>
@@ -28192,10 +28177,10 @@
       <c r="B117" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C117" s="332" t="s">
+      <c r="C117" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D117" s="312"/>
+      <c r="D117" s="311"/>
       <c r="E117" s="62"/>
       <c r="F117" s="16" t="s">
         <v>1020</v>
@@ -28267,10 +28252,10 @@
       <c r="B118" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C118" s="331" t="s">
+      <c r="C118" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D118" s="312"/>
+      <c r="D118" s="311"/>
       <c r="E118" s="62"/>
       <c r="F118" s="16" t="s">
         <v>1030</v>
@@ -28336,16 +28321,16 @@
       <c r="AQ118" s="32"/>
     </row>
     <row r="119" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A119" s="361" t="s">
-        <v>3912</v>
+      <c r="A119" s="360" t="s">
+        <v>3910</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C119" s="330" t="s">
+      <c r="C119" s="329" t="s">
         <v>1041</v>
       </c>
-      <c r="D119" s="312"/>
+      <c r="D119" s="311"/>
       <c r="E119" s="62"/>
       <c r="F119" s="16" t="s">
         <v>1042</v>
@@ -28415,10 +28400,10 @@
       <c r="B120" s="32" t="s">
         <v>1052</v>
       </c>
-      <c r="C120" s="331" t="s">
+      <c r="C120" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D120" s="312"/>
+      <c r="D120" s="311"/>
       <c r="E120" s="62"/>
       <c r="F120" s="16" t="s">
         <v>1053</v>
@@ -28482,10 +28467,10 @@
       <c r="B121" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C121" s="331" t="s">
+      <c r="C121" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D121" s="312"/>
+      <c r="D121" s="311"/>
       <c r="E121" s="62"/>
       <c r="F121" s="48" t="s">
         <v>1058</v>
@@ -28547,16 +28532,16 @@
       <c r="AQ121" s="32"/>
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A122" s="362" t="s">
-        <v>3913</v>
+      <c r="A122" s="361" t="s">
+        <v>3911</v>
       </c>
       <c r="B122" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C122" s="343" t="s">
+      <c r="C122" s="342" t="s">
         <v>1063</v>
       </c>
-      <c r="D122" s="315"/>
+      <c r="D122" s="314"/>
       <c r="E122" s="62"/>
       <c r="F122" s="95" t="s">
         <v>1064</v>
@@ -28632,10 +28617,10 @@
       <c r="B123" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C123" s="330" t="s">
+      <c r="C123" s="329" t="s">
         <v>1078</v>
       </c>
-      <c r="D123" s="312"/>
+      <c r="D123" s="311"/>
       <c r="E123" s="62"/>
       <c r="F123" s="16" t="s">
         <v>1079</v>
@@ -28703,10 +28688,10 @@
       <c r="B124" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C124" s="331" t="s">
+      <c r="C124" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D124" s="312"/>
+      <c r="D124" s="311"/>
       <c r="E124" s="62"/>
       <c r="F124" s="48" t="s">
         <v>1088</v>
@@ -28770,10 +28755,10 @@
       <c r="B125" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C125" s="332" t="s">
+      <c r="C125" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D125" s="311" t="s">
+      <c r="D125" s="310" t="s">
         <v>1093</v>
       </c>
       <c r="E125" s="62" t="s">
@@ -28857,10 +28842,10 @@
       <c r="B126" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C126" s="331" t="s">
+      <c r="C126" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D126" s="312"/>
+      <c r="D126" s="311"/>
       <c r="E126" s="62"/>
       <c r="F126" s="32" t="s">
         <v>1108</v>
@@ -28924,10 +28909,10 @@
       <c r="B127" s="179" t="s">
         <v>1116</v>
       </c>
-      <c r="C127" s="331" t="s">
+      <c r="C127" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="315"/>
+      <c r="D127" s="314"/>
       <c r="E127" s="62"/>
       <c r="F127" s="32" t="s">
         <v>1108</v>
@@ -29001,10 +28986,10 @@
       <c r="B128" s="181" t="s">
         <v>1126</v>
       </c>
-      <c r="C128" s="338" t="s">
+      <c r="C128" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D128" s="312"/>
+      <c r="D128" s="311"/>
       <c r="E128" s="62"/>
       <c r="F128" s="32" t="s">
         <v>1108</v>
@@ -29064,16 +29049,16 @@
       <c r="AQ128" s="32"/>
     </row>
     <row r="129" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A129" s="362" t="s">
-        <v>3914</v>
+      <c r="A129" s="361" t="s">
+        <v>3912</v>
       </c>
       <c r="B129" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C129" s="330" t="s">
+      <c r="C129" s="329" t="s">
         <v>1131</v>
       </c>
-      <c r="D129" s="312"/>
+      <c r="D129" s="311"/>
       <c r="E129" s="62"/>
       <c r="F129" s="48" t="s">
         <v>1132</v>
@@ -29135,16 +29120,16 @@
       <c r="AQ129" s="32"/>
     </row>
     <row r="130" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A130" s="361" t="s">
-        <v>3915</v>
+      <c r="A130" s="360" t="s">
+        <v>3913</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C130" s="330" t="s">
+      <c r="C130" s="329" t="s">
         <v>1140</v>
       </c>
-      <c r="D130" s="312"/>
+      <c r="D130" s="311"/>
       <c r="E130" s="62"/>
       <c r="F130" s="48" t="s">
         <v>1141</v>
@@ -29208,16 +29193,16 @@
       <c r="AQ130" s="32"/>
     </row>
     <row r="131" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A131" s="361" t="s">
-        <v>3916</v>
+      <c r="A131" s="360" t="s">
+        <v>3914</v>
       </c>
       <c r="B131" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C131" s="344" t="s">
+      <c r="C131" s="343" t="s">
         <v>1148</v>
       </c>
-      <c r="D131" s="312"/>
+      <c r="D131" s="311"/>
       <c r="E131" s="62"/>
       <c r="F131" s="16" t="s">
         <v>1149</v>
@@ -29293,10 +29278,10 @@
       <c r="B132" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C132" s="331" t="s">
+      <c r="C132" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D132" s="312"/>
+      <c r="D132" s="311"/>
       <c r="E132" s="62"/>
       <c r="F132" s="16" t="s">
         <v>1158</v>
@@ -29360,10 +29345,10 @@
       <c r="B133" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C133" s="331" t="s">
+      <c r="C133" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D133" s="312"/>
+      <c r="D133" s="311"/>
       <c r="E133" s="62"/>
       <c r="F133" s="16" t="s">
         <v>1161</v>
@@ -29427,10 +29412,10 @@
       <c r="B134" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C134" s="331" t="s">
+      <c r="C134" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D134" s="311" t="s">
+      <c r="D134" s="310" t="s">
         <v>1168</v>
       </c>
       <c r="E134" s="18"/>
@@ -29500,10 +29485,10 @@
       <c r="B135" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C135" s="331" t="s">
+      <c r="C135" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D135" s="312"/>
+      <c r="D135" s="311"/>
       <c r="E135" s="62"/>
       <c r="F135" s="17" t="s">
         <v>1108</v>
@@ -29581,10 +29566,10 @@
       <c r="B136" s="32" t="s">
         <v>1186</v>
       </c>
-      <c r="C136" s="331" t="s">
+      <c r="C136" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D136" s="312"/>
+      <c r="D136" s="311"/>
       <c r="E136" s="62"/>
       <c r="F136" s="17" t="s">
         <v>1108</v>
@@ -29644,16 +29629,16 @@
       <c r="AQ136" s="32"/>
     </row>
     <row r="137" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A137" s="361" t="s">
-        <v>3917</v>
+      <c r="A137" s="360" t="s">
+        <v>3915</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C137" s="340" t="s">
+      <c r="C137" s="339" t="s">
         <v>1192</v>
       </c>
-      <c r="D137" s="312"/>
+      <c r="D137" s="311"/>
       <c r="E137" s="62"/>
       <c r="F137" s="16" t="s">
         <v>1193</v>
@@ -29719,10 +29704,10 @@
       <c r="B138" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C138" s="331" t="s">
+      <c r="C138" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D138" s="312"/>
+      <c r="D138" s="311"/>
       <c r="E138" s="62"/>
       <c r="F138" s="16" t="s">
         <v>1199</v>
@@ -29784,16 +29769,16 @@
       <c r="AQ138" s="32"/>
     </row>
     <row r="139" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A139" s="362" t="s">
-        <v>3918</v>
+      <c r="A139" s="361" t="s">
+        <v>3916</v>
       </c>
       <c r="B139" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C139" s="330" t="s">
+      <c r="C139" s="329" t="s">
         <v>1207</v>
       </c>
-      <c r="D139" s="312"/>
+      <c r="D139" s="311"/>
       <c r="E139" s="62"/>
       <c r="F139" s="48" t="s">
         <v>1208</v>
@@ -29859,10 +29844,10 @@
       <c r="B140" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C140" s="331" t="s">
+      <c r="C140" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D140" s="312"/>
+      <c r="D140" s="311"/>
       <c r="E140" s="62"/>
       <c r="F140" s="16" t="s">
         <v>1213</v>
@@ -29926,10 +29911,10 @@
       <c r="B141" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C141" s="332" t="s">
+      <c r="C141" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D141" s="315"/>
+      <c r="D141" s="314"/>
       <c r="E141" s="62"/>
       <c r="F141" s="95" t="s">
         <v>1220</v>
@@ -30005,10 +29990,10 @@
       <c r="B142" s="32" t="s">
         <v>1232</v>
       </c>
-      <c r="C142" s="331" t="s">
+      <c r="C142" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D142" s="312"/>
+      <c r="D142" s="311"/>
       <c r="E142" s="62"/>
       <c r="F142" s="16" t="s">
         <v>1233</v>
@@ -30072,10 +30057,10 @@
       <c r="B143" s="21" t="s">
         <v>1237</v>
       </c>
-      <c r="C143" s="331" t="s">
+      <c r="C143" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D143" s="315"/>
+      <c r="D143" s="314"/>
       <c r="E143" s="62"/>
       <c r="F143" s="95" t="s">
         <v>1238</v>
@@ -30141,10 +30126,10 @@
       <c r="B144" s="21" t="s">
         <v>1012</v>
       </c>
-      <c r="C144" s="331" t="s">
+      <c r="C144" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D144" s="315"/>
+      <c r="D144" s="314"/>
       <c r="E144" s="62"/>
       <c r="F144" s="177" t="s">
         <v>1244</v>
@@ -30210,10 +30195,10 @@
       <c r="B145" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C145" s="331" t="s">
+      <c r="C145" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D145" s="312"/>
+      <c r="D145" s="311"/>
       <c r="E145" s="62"/>
       <c r="F145" s="32" t="s">
         <v>1108</v>
@@ -30281,16 +30266,16 @@
       <c r="AQ145" s="32"/>
     </row>
     <row r="146" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A146" s="363" t="s">
+      <c r="A146" s="362" t="s">
         <v>1256</v>
       </c>
       <c r="B146" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C146" s="340" t="s">
+      <c r="C146" s="339" t="s">
         <v>1257</v>
       </c>
-      <c r="D146" s="315"/>
+      <c r="D146" s="314"/>
       <c r="E146" s="62"/>
       <c r="F146" s="21" t="s">
         <v>1108</v>
@@ -30368,10 +30353,10 @@
       <c r="B147" s="21" t="s">
         <v>1267</v>
       </c>
-      <c r="C147" s="331" t="s">
+      <c r="C147" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D147" s="315"/>
+      <c r="D147" s="314"/>
       <c r="E147" s="62"/>
       <c r="F147" s="21" t="s">
         <v>1108</v>
@@ -30437,10 +30422,10 @@
       <c r="B148" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C148" s="331" t="s">
+      <c r="C148" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D148" s="322"/>
+      <c r="D148" s="321"/>
       <c r="E148" s="187"/>
       <c r="F148" s="21" t="s">
         <v>1108</v>
@@ -30516,10 +30501,10 @@
       <c r="B149" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C149" s="331" t="s">
+      <c r="C149" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D149" s="315"/>
+      <c r="D149" s="314"/>
       <c r="E149" s="62"/>
       <c r="F149" s="21" t="s">
         <v>1108</v>
@@ -30595,10 +30580,10 @@
       <c r="B150" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C150" s="331" t="s">
+      <c r="C150" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D150" s="312"/>
+      <c r="D150" s="311"/>
       <c r="E150" s="62"/>
       <c r="F150" s="32" t="s">
         <v>1108</v>
@@ -30662,10 +30647,10 @@
       <c r="B151" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C151" s="331" t="s">
+      <c r="C151" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D151" s="312"/>
+      <c r="D151" s="311"/>
       <c r="E151" s="62"/>
       <c r="F151" s="16" t="s">
         <v>1294</v>
@@ -30737,10 +30722,10 @@
       <c r="B152" s="32" t="s">
         <v>1232</v>
       </c>
-      <c r="C152" s="331" t="s">
+      <c r="C152" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D152" s="312"/>
+      <c r="D152" s="311"/>
       <c r="E152" s="62"/>
       <c r="F152" s="16" t="s">
         <v>1304</v>
@@ -30804,10 +30789,10 @@
       <c r="B153" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="C153" s="331" t="s">
+      <c r="C153" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D153" s="312"/>
+      <c r="D153" s="311"/>
       <c r="E153" s="62"/>
       <c r="F153" s="16" t="s">
         <v>1310</v>
@@ -30871,10 +30856,10 @@
       <c r="B154" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="C154" s="331" t="s">
+      <c r="C154" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D154" s="312"/>
+      <c r="D154" s="311"/>
       <c r="E154" s="62"/>
       <c r="F154" s="16" t="s">
         <v>1316</v>
@@ -30942,10 +30927,10 @@
       <c r="B155" s="21" t="s">
         <v>1325</v>
       </c>
-      <c r="C155" s="332" t="s">
+      <c r="C155" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D155" s="315"/>
+      <c r="D155" s="314"/>
       <c r="E155" s="62"/>
       <c r="F155" s="177" t="s">
         <v>1326</v>
@@ -31023,10 +31008,10 @@
       <c r="B156" s="21" t="s">
         <v>1325</v>
       </c>
-      <c r="C156" s="332" t="s">
+      <c r="C156" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D156" s="323"/>
+      <c r="D156" s="322"/>
       <c r="E156" s="188"/>
       <c r="F156" s="189" t="s">
         <v>1338</v>
@@ -31104,10 +31089,10 @@
       <c r="B157" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C157" s="331" t="s">
+      <c r="C157" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D157" s="315"/>
+      <c r="D157" s="314"/>
       <c r="E157" s="62"/>
       <c r="F157" s="177" t="s">
         <v>1349</v>
@@ -31177,10 +31162,10 @@
       <c r="B158" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C158" s="332" t="s">
+      <c r="C158" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D158" s="315"/>
+      <c r="D158" s="314"/>
       <c r="E158" s="62"/>
       <c r="F158" s="95" t="s">
         <v>1355</v>
@@ -31246,10 +31231,10 @@
       <c r="B159" s="32" t="s">
         <v>1363</v>
       </c>
-      <c r="C159" s="331" t="s">
+      <c r="C159" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D159" s="312"/>
+      <c r="D159" s="311"/>
       <c r="E159" s="62"/>
       <c r="F159" s="16" t="s">
         <v>1364</v>
@@ -31313,10 +31298,10 @@
       <c r="B160" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C160" s="331" t="s">
+      <c r="C160" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D160" s="315"/>
+      <c r="D160" s="314"/>
       <c r="E160" s="62"/>
       <c r="F160" s="95" t="s">
         <v>1369</v>
@@ -31388,10 +31373,10 @@
       <c r="B161" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C161" s="331" t="s">
+      <c r="C161" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D161" s="324"/>
+      <c r="D161" s="323"/>
       <c r="E161" s="18"/>
       <c r="F161" s="19" t="s">
         <v>1378</v>
@@ -31467,10 +31452,10 @@
       <c r="B162" s="32" t="s">
         <v>1386</v>
       </c>
-      <c r="C162" s="331" t="s">
+      <c r="C162" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D162" s="312"/>
+      <c r="D162" s="311"/>
       <c r="E162" s="62"/>
       <c r="F162" s="16" t="s">
         <v>1387</v>
@@ -31534,10 +31519,10 @@
       <c r="B163" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C163" s="331" t="s">
+      <c r="C163" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D163" s="312"/>
+      <c r="D163" s="311"/>
       <c r="E163" s="62"/>
       <c r="F163" s="48" t="s">
         <v>1393</v>
@@ -31605,10 +31590,10 @@
       <c r="B164" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C164" s="331" t="s">
+      <c r="C164" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D164" s="312"/>
+      <c r="D164" s="311"/>
       <c r="E164" s="62"/>
       <c r="F164" s="16" t="s">
         <v>1401</v>
@@ -31682,10 +31667,10 @@
       <c r="B165" s="32" t="s">
         <v>1412</v>
       </c>
-      <c r="C165" s="331" t="s">
+      <c r="C165" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D165" s="312"/>
+      <c r="D165" s="311"/>
       <c r="E165" s="62"/>
       <c r="F165" s="16" t="s">
         <v>1413</v>
@@ -31749,10 +31734,10 @@
       <c r="B166" s="52" t="s">
         <v>476</v>
       </c>
-      <c r="C166" s="331" t="s">
+      <c r="C166" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D166" s="315"/>
+      <c r="D166" s="314"/>
       <c r="E166" s="62"/>
       <c r="F166" s="95" t="s">
         <v>1418</v>
@@ -31828,10 +31813,10 @@
       <c r="B167" s="52" t="s">
         <v>476</v>
       </c>
-      <c r="C167" s="331" t="s">
+      <c r="C167" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D167" s="315"/>
+      <c r="D167" s="314"/>
       <c r="E167" s="62"/>
       <c r="F167" s="95" t="s">
         <v>1426</v>
@@ -31899,10 +31884,10 @@
       <c r="B168" s="52" t="s">
         <v>476</v>
       </c>
-      <c r="C168" s="331" t="s">
+      <c r="C168" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D168" s="315"/>
+      <c r="D168" s="314"/>
       <c r="E168" s="62"/>
       <c r="F168" s="95" t="s">
         <v>1435</v>
@@ -31972,16 +31957,16 @@
       <c r="AQ168" s="21"/>
     </row>
     <row r="169" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A169" s="361" t="s">
-        <v>3919</v>
+      <c r="A169" s="360" t="s">
+        <v>3917</v>
       </c>
       <c r="B169" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C169" s="330" t="s">
+      <c r="C169" s="329" t="s">
         <v>1441</v>
       </c>
-      <c r="D169" s="312"/>
+      <c r="D169" s="311"/>
       <c r="E169" s="62"/>
       <c r="F169" s="16" t="s">
         <v>1442</v>
@@ -32053,10 +32038,10 @@
       <c r="B170" s="32" t="s">
         <v>1453</v>
       </c>
-      <c r="C170" s="331" t="s">
+      <c r="C170" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D170" s="312"/>
+      <c r="D170" s="311"/>
       <c r="E170" s="62"/>
       <c r="F170" s="16" t="s">
         <v>1454</v>
@@ -32120,10 +32105,10 @@
       <c r="B171" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C171" s="336" t="s">
+      <c r="C171" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D171" s="312"/>
+      <c r="D171" s="311"/>
       <c r="E171" s="62"/>
       <c r="F171" s="48" t="s">
         <v>1461</v>
@@ -32189,10 +32174,10 @@
       <c r="B172" s="14" t="s">
         <v>1469</v>
       </c>
-      <c r="C172" s="336" t="s">
+      <c r="C172" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D172" s="312"/>
+      <c r="D172" s="311"/>
       <c r="E172" s="62"/>
       <c r="F172" s="16" t="s">
         <v>1470</v>
@@ -32264,10 +32249,10 @@
       <c r="B173" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C173" s="331" t="s">
+      <c r="C173" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D173" s="315"/>
+      <c r="D173" s="314"/>
       <c r="E173" s="62"/>
       <c r="F173" s="95" t="s">
         <v>1478</v>
@@ -32337,16 +32322,16 @@
       <c r="AQ173" s="21"/>
     </row>
     <row r="174" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A174" s="356" t="s">
+      <c r="A174" s="355" t="s">
         <v>1488</v>
       </c>
       <c r="B174" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C174" s="330" t="s">
+      <c r="C174" s="329" t="s">
         <v>1489</v>
       </c>
-      <c r="D174" s="312"/>
+      <c r="D174" s="311"/>
       <c r="E174" s="62"/>
       <c r="F174" s="16" t="s">
         <v>1490</v>
@@ -32402,16 +32387,16 @@
       <c r="AQ174" s="32"/>
     </row>
     <row r="175" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A175" s="361" t="s">
-        <v>3920</v>
+      <c r="A175" s="360" t="s">
+        <v>3918</v>
       </c>
       <c r="B175" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C175" s="330" t="s">
+      <c r="C175" s="329" t="s">
         <v>1493</v>
       </c>
-      <c r="D175" s="312"/>
+      <c r="D175" s="311"/>
       <c r="E175" s="62"/>
       <c r="F175" s="16" t="s">
         <v>1494</v>
@@ -32471,16 +32456,16 @@
       <c r="AQ175" s="32"/>
     </row>
     <row r="176" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A176" s="361" t="s">
-        <v>3921</v>
+      <c r="A176" s="360" t="s">
+        <v>3919</v>
       </c>
       <c r="B176" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C176" s="330" t="s">
+      <c r="C176" s="329" t="s">
         <v>1493</v>
       </c>
-      <c r="D176" s="312"/>
+      <c r="D176" s="311"/>
       <c r="E176" s="62"/>
       <c r="F176" s="48" t="s">
         <v>1501</v>
@@ -32538,16 +32523,16 @@
       <c r="AQ176" s="32"/>
     </row>
     <row r="177" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A177" s="362" t="s">
-        <v>3922</v>
+      <c r="A177" s="361" t="s">
+        <v>3920</v>
       </c>
       <c r="B177" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="C177" s="340" t="s">
+      <c r="C177" s="339" t="s">
         <v>1506</v>
       </c>
-      <c r="D177" s="315"/>
+      <c r="D177" s="314"/>
       <c r="E177" s="62"/>
       <c r="F177" s="21" t="s">
         <v>1108</v>
@@ -32619,16 +32604,16 @@
       <c r="AQ177" s="21"/>
     </row>
     <row r="178" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A178" s="363" t="s">
+      <c r="A178" s="362" t="s">
         <v>1516</v>
       </c>
       <c r="B178" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="C178" s="340" t="s">
+      <c r="C178" s="339" t="s">
         <v>1517</v>
       </c>
-      <c r="D178" s="315"/>
+      <c r="D178" s="314"/>
       <c r="E178" s="62"/>
       <c r="F178" s="21" t="s">
         <v>1108</v>
@@ -32706,10 +32691,10 @@
       <c r="B179" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="C179" s="331" t="s">
+      <c r="C179" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D179" s="315"/>
+      <c r="D179" s="314"/>
       <c r="E179" s="62"/>
       <c r="F179" s="95" t="s">
         <v>1527</v>
@@ -32775,16 +32760,16 @@
       <c r="AQ179" s="21"/>
     </row>
     <row r="180" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A180" s="363" t="s">
+      <c r="A180" s="362" t="s">
         <v>1535</v>
       </c>
       <c r="B180" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C180" s="340" t="s">
+      <c r="C180" s="339" t="s">
         <v>1536</v>
       </c>
-      <c r="D180" s="315"/>
+      <c r="D180" s="314"/>
       <c r="E180" s="62"/>
       <c r="F180" s="95" t="s">
         <v>1537</v>
@@ -32850,10 +32835,10 @@
       <c r="B181" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C181" s="331" t="s">
+      <c r="C181" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D181" s="315"/>
+      <c r="D181" s="314"/>
       <c r="E181" s="62"/>
       <c r="F181" s="95" t="s">
         <v>1543</v>
@@ -32929,10 +32914,10 @@
       <c r="B182" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C182" s="331" t="s">
+      <c r="C182" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D182" s="312"/>
+      <c r="D182" s="311"/>
       <c r="E182" s="62"/>
       <c r="F182" s="48" t="s">
         <v>1552</v>
@@ -32996,16 +32981,16 @@
       <c r="AQ182" s="32"/>
     </row>
     <row r="183" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A183" s="361" t="s">
-        <v>3923</v>
+      <c r="A183" s="360" t="s">
+        <v>3921</v>
       </c>
       <c r="B183" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C183" s="330" t="s">
+      <c r="C183" s="329" t="s">
         <v>1558</v>
       </c>
-      <c r="D183" s="312"/>
+      <c r="D183" s="311"/>
       <c r="E183" s="62"/>
       <c r="F183" s="16" t="s">
         <v>1559</v>
@@ -33065,16 +33050,16 @@
       <c r="AQ183" s="32"/>
     </row>
     <row r="184" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A184" s="361" t="s">
-        <v>3924</v>
+      <c r="A184" s="360" t="s">
+        <v>3922</v>
       </c>
       <c r="B184" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C184" s="330" t="s">
+      <c r="C184" s="329" t="s">
         <v>1558</v>
       </c>
-      <c r="D184" s="312"/>
+      <c r="D184" s="311"/>
       <c r="E184" s="62"/>
       <c r="F184" s="16" t="s">
         <v>1567</v>
@@ -33140,10 +33125,10 @@
       <c r="B185" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="C185" s="331" t="s">
+      <c r="C185" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D185" s="324"/>
+      <c r="D185" s="323"/>
       <c r="E185" s="18"/>
       <c r="F185" s="20" t="s">
         <v>1574</v>
@@ -33219,10 +33204,10 @@
       <c r="B186" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="C186" s="331" t="s">
+      <c r="C186" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D186" s="315"/>
+      <c r="D186" s="314"/>
       <c r="E186" s="62"/>
       <c r="F186" s="20" t="s">
         <v>1574</v>
@@ -33298,10 +33283,10 @@
       <c r="B187" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C187" s="331" t="s">
+      <c r="C187" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D187" s="315"/>
+      <c r="D187" s="314"/>
       <c r="E187" s="62"/>
       <c r="F187" s="95" t="s">
         <v>1591</v>
@@ -33367,10 +33352,10 @@
       <c r="B188" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C188" s="331" t="s">
+      <c r="C188" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D188" s="323"/>
+      <c r="D188" s="322"/>
       <c r="E188" s="188"/>
       <c r="F188" s="189" t="s">
         <v>1599</v>
@@ -33436,10 +33421,10 @@
       <c r="B189" s="52" t="s">
         <v>439</v>
       </c>
-      <c r="C189" s="331" t="s">
+      <c r="C189" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D189" s="324"/>
+      <c r="D189" s="323"/>
       <c r="E189" s="18"/>
       <c r="F189" s="20" t="s">
         <v>1108</v>
@@ -33499,16 +33484,16 @@
       <c r="AQ189" s="21"/>
     </row>
     <row r="190" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A190" s="362" t="s">
-        <v>3925</v>
+      <c r="A190" s="361" t="s">
+        <v>3923</v>
       </c>
       <c r="B190" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C190" s="340" t="s">
+      <c r="C190" s="339" t="s">
         <v>1610</v>
       </c>
-      <c r="D190" s="315"/>
+      <c r="D190" s="314"/>
       <c r="E190" s="62"/>
       <c r="F190" s="95" t="s">
         <v>1611</v>
@@ -33572,10 +33557,10 @@
       <c r="B191" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C191" s="331" t="s">
+      <c r="C191" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D191" s="312"/>
+      <c r="D191" s="311"/>
       <c r="E191" s="62"/>
       <c r="F191" s="48" t="s">
         <v>1617</v>
@@ -33647,10 +33632,10 @@
       <c r="B192" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C192" s="331" t="s">
+      <c r="C192" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D192" s="312"/>
+      <c r="D192" s="311"/>
       <c r="E192" s="62"/>
       <c r="F192" s="48" t="s">
         <v>1627</v>
@@ -33710,16 +33695,16 @@
       <c r="AQ192" s="32"/>
     </row>
     <row r="193" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A193" s="361" t="s">
-        <v>3927</v>
+      <c r="A193" s="360" t="s">
+        <v>3925</v>
       </c>
       <c r="B193" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C193" s="332" t="s">
-        <v>3926</v>
-      </c>
-      <c r="D193" s="312"/>
+      <c r="C193" s="331" t="s">
+        <v>3924</v>
+      </c>
+      <c r="D193" s="311"/>
       <c r="E193" s="62"/>
       <c r="F193" s="16" t="s">
         <v>1634</v>
@@ -33783,16 +33768,16 @@
       <c r="AQ193" s="32"/>
     </row>
     <row r="194" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A194" s="363" t="s">
+      <c r="A194" s="362" t="s">
         <v>1641</v>
       </c>
       <c r="B194" s="52" t="s">
         <v>1012</v>
       </c>
-      <c r="C194" s="340" t="s">
+      <c r="C194" s="339" t="s">
         <v>1642</v>
       </c>
-      <c r="D194" s="315"/>
+      <c r="D194" s="314"/>
       <c r="E194" s="62"/>
       <c r="F194" s="177" t="s">
         <v>1643</v>
@@ -33862,16 +33847,16 @@
       <c r="AQ194" s="21"/>
     </row>
     <row r="195" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A195" s="356" t="s">
+      <c r="A195" s="355" t="s">
         <v>1652</v>
       </c>
       <c r="B195" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C195" s="330" t="s">
+      <c r="C195" s="329" t="s">
         <v>1653</v>
       </c>
-      <c r="D195" s="312"/>
+      <c r="D195" s="311"/>
       <c r="E195" s="62"/>
       <c r="F195" s="48" t="s">
         <v>1654</v>
@@ -33947,10 +33932,10 @@
       <c r="B196" s="14" t="s">
         <v>1663</v>
       </c>
-      <c r="C196" s="331" t="s">
+      <c r="C196" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D196" s="312"/>
+      <c r="D196" s="311"/>
       <c r="E196" s="62"/>
       <c r="F196" s="48" t="s">
         <v>1664</v>
@@ -34014,10 +33999,10 @@
       <c r="B197" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C197" s="331" t="s">
+      <c r="C197" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D197" s="312"/>
+      <c r="D197" s="311"/>
       <c r="E197" s="62"/>
       <c r="F197" s="48" t="s">
         <v>1670</v>
@@ -34081,10 +34066,10 @@
       <c r="B198" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C198" s="338" t="s">
+      <c r="C198" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D198" s="312"/>
+      <c r="D198" s="311"/>
       <c r="E198" s="62"/>
       <c r="F198" s="48" t="s">
         <v>1677</v>
@@ -34148,10 +34133,10 @@
       <c r="B199" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C199" s="331" t="s">
+      <c r="C199" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D199" s="312"/>
+      <c r="D199" s="311"/>
       <c r="E199" s="62"/>
       <c r="F199" s="16" t="s">
         <v>1684</v>
@@ -34221,16 +34206,16 @@
       <c r="AQ199" s="32"/>
     </row>
     <row r="200" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A200" s="356" t="s">
+      <c r="A200" s="355" t="s">
         <v>1691</v>
       </c>
       <c r="B200" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C200" s="332" t="s">
+      <c r="C200" s="331" t="s">
         <v>1692</v>
       </c>
-      <c r="D200" s="312"/>
+      <c r="D200" s="311"/>
       <c r="E200" s="62"/>
       <c r="F200" s="16" t="s">
         <v>1693</v>
@@ -34290,16 +34275,16 @@
       <c r="AQ200" s="32"/>
     </row>
     <row r="201" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A201" s="356" t="s">
+      <c r="A201" s="355" t="s">
         <v>1698</v>
       </c>
       <c r="B201" s="32" t="s">
         <v>1699</v>
       </c>
-      <c r="C201" s="330" t="s">
+      <c r="C201" s="329" t="s">
         <v>1700</v>
       </c>
-      <c r="D201" s="312"/>
+      <c r="D201" s="311"/>
       <c r="E201" s="62"/>
       <c r="F201" s="16" t="s">
         <v>1701</v>
@@ -34369,10 +34354,10 @@
       <c r="B202" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C202" s="331" t="s">
+      <c r="C202" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D202" s="312"/>
+      <c r="D202" s="311"/>
       <c r="E202" s="62"/>
       <c r="F202" s="32" t="s">
         <v>1108</v>
@@ -34444,16 +34429,16 @@
       <c r="AQ202" s="32"/>
     </row>
     <row r="203" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A203" s="356" t="s">
+      <c r="A203" s="355" t="s">
         <v>1716</v>
       </c>
       <c r="B203" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C203" s="340" t="s">
+      <c r="C203" s="339" t="s">
         <v>1717</v>
       </c>
-      <c r="D203" s="312"/>
+      <c r="D203" s="311"/>
       <c r="E203" s="62"/>
       <c r="F203" s="32" t="s">
         <v>1108</v>
@@ -34521,10 +34506,10 @@
       <c r="B204" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C204" s="331" t="s">
+      <c r="C204" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D204" s="312"/>
+      <c r="D204" s="311"/>
       <c r="E204" s="166"/>
       <c r="F204" s="48" t="s">
         <v>1724</v>
@@ -34584,16 +34569,16 @@
       <c r="AQ204" s="32"/>
     </row>
     <row r="205" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A205" s="361" t="s">
-        <v>3928</v>
+      <c r="A205" s="360" t="s">
+        <v>3926</v>
       </c>
       <c r="B205" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C205" s="340" t="s">
+      <c r="C205" s="339" t="s">
         <v>1729</v>
       </c>
-      <c r="D205" s="312"/>
+      <c r="D205" s="311"/>
       <c r="E205" s="202"/>
       <c r="F205" s="48" t="s">
         <v>1730</v>
@@ -34659,10 +34644,10 @@
       <c r="B206" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C206" s="331" t="s">
+      <c r="C206" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D206" s="312"/>
+      <c r="D206" s="311"/>
       <c r="E206" s="62"/>
       <c r="F206" s="16" t="s">
         <v>1737</v>
@@ -34730,16 +34715,16 @@
       <c r="AQ206" s="32"/>
     </row>
     <row r="207" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A207" s="361" t="s">
-        <v>3929</v>
+      <c r="A207" s="360" t="s">
+        <v>3927</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C207" s="330" t="s">
+      <c r="C207" s="329" t="s">
         <v>1093</v>
       </c>
-      <c r="D207" s="312"/>
+      <c r="D207" s="311"/>
       <c r="E207" s="53"/>
       <c r="F207" s="16" t="s">
         <v>1745</v>
@@ -34823,10 +34808,10 @@
       <c r="B208" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C208" s="332" t="s">
+      <c r="C208" s="331" t="s">
         <v>1760</v>
       </c>
-      <c r="D208" s="312"/>
+      <c r="D208" s="311"/>
       <c r="E208" s="62"/>
       <c r="F208" s="16" t="s">
         <v>1761</v>
@@ -34896,10 +34881,10 @@
       <c r="B209" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C209" s="331" t="s">
+      <c r="C209" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D209" s="312"/>
+      <c r="D209" s="311"/>
       <c r="E209" s="62"/>
       <c r="F209" s="48" t="s">
         <v>1768</v>
@@ -34975,10 +34960,10 @@
       <c r="B210" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C210" s="331" t="s">
+      <c r="C210" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D210" s="312"/>
+      <c r="D210" s="311"/>
       <c r="E210" s="62"/>
       <c r="F210" s="32" t="s">
         <v>1108</v>
@@ -35048,16 +35033,16 @@
       <c r="AQ210" s="32"/>
     </row>
     <row r="211" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A211" s="361" t="s">
-        <v>3930</v>
+      <c r="A211" s="360" t="s">
+        <v>3928</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C211" s="330" t="s">
+      <c r="C211" s="329" t="s">
         <v>1783</v>
       </c>
-      <c r="D211" s="312"/>
+      <c r="D211" s="311"/>
       <c r="E211" s="62"/>
       <c r="F211" s="32" t="s">
         <v>1108</v>
@@ -35133,10 +35118,10 @@
       <c r="B212" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C212" s="331" t="s">
+      <c r="C212" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D212" s="312"/>
+      <c r="D212" s="311"/>
       <c r="E212" s="62"/>
       <c r="F212" s="16" t="s">
         <v>1792</v>
@@ -35210,16 +35195,16 @@
       <c r="AQ212" s="32"/>
     </row>
     <row r="213" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A213" s="361" t="s">
-        <v>3931</v>
+      <c r="A213" s="360" t="s">
+        <v>3929</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C213" s="340" t="s">
+      <c r="C213" s="339" t="s">
         <v>1801</v>
       </c>
-      <c r="D213" s="312"/>
+      <c r="D213" s="311"/>
       <c r="E213" s="62"/>
       <c r="F213" s="32" t="s">
         <v>1108</v>
@@ -35285,10 +35270,10 @@
       <c r="B214" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C214" s="331" t="s">
+      <c r="C214" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D214" s="312"/>
+      <c r="D214" s="311"/>
       <c r="E214" s="62"/>
       <c r="F214" s="32" t="s">
         <v>1108</v>
@@ -35360,16 +35345,16 @@
       <c r="AQ214" s="32"/>
     </row>
     <row r="215" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A215" s="363" t="s">
+      <c r="A215" s="362" t="s">
         <v>1817</v>
       </c>
       <c r="B215" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C215" s="340" t="s">
+      <c r="C215" s="339" t="s">
         <v>1818</v>
       </c>
-      <c r="D215" s="312"/>
+      <c r="D215" s="311"/>
       <c r="E215" s="62"/>
       <c r="F215" s="48" t="s">
         <v>1819</v>
@@ -35445,10 +35430,10 @@
       <c r="B216" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C216" s="331" t="s">
+      <c r="C216" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D216" s="312"/>
+      <c r="D216" s="311"/>
       <c r="E216" s="62"/>
       <c r="F216" s="16" t="s">
         <v>1827</v>
@@ -35506,16 +35491,16 @@
       <c r="AQ216" s="32"/>
     </row>
     <row r="217" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A217" s="349" t="s">
+      <c r="A217" s="348" t="s">
         <v>1833</v>
       </c>
       <c r="B217" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C217" s="330" t="s">
+      <c r="C217" s="329" t="s">
         <v>1834</v>
       </c>
-      <c r="D217" s="312"/>
+      <c r="D217" s="311"/>
       <c r="E217" s="62"/>
       <c r="F217" s="32" t="s">
         <v>1108</v>
@@ -35583,10 +35568,10 @@
       <c r="B218" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C218" s="331" t="s">
+      <c r="C218" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D218" s="312"/>
+      <c r="D218" s="311"/>
       <c r="E218" s="62"/>
       <c r="F218" s="32" t="s">
         <v>1108</v>
@@ -35652,10 +35637,10 @@
       <c r="B219" s="32" t="s">
         <v>1849</v>
       </c>
-      <c r="C219" s="331" t="s">
+      <c r="C219" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D219" s="312"/>
+      <c r="D219" s="311"/>
       <c r="E219" s="62"/>
       <c r="F219" s="48" t="s">
         <v>1850</v>
@@ -35727,10 +35712,10 @@
       <c r="B220" s="32" t="s">
         <v>1860</v>
       </c>
-      <c r="C220" s="331" t="s">
+      <c r="C220" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D220" s="311"/>
+      <c r="D220" s="310"/>
       <c r="E220" s="62"/>
       <c r="F220" s="48" t="s">
         <v>1861</v>
@@ -35790,16 +35775,16 @@
       <c r="AQ220" s="32"/>
     </row>
     <row r="221" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A221" s="364" t="s">
+      <c r="A221" s="363" t="s">
         <v>1866</v>
       </c>
       <c r="B221" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C221" s="330" t="s">
+      <c r="C221" s="329" t="s">
         <v>1867</v>
       </c>
-      <c r="D221" s="312"/>
+      <c r="D221" s="311"/>
       <c r="E221" s="62"/>
       <c r="F221" s="16" t="s">
         <v>1868</v>
@@ -35861,16 +35846,16 @@
       <c r="AQ221" s="32"/>
     </row>
     <row r="222" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A222" s="362" t="s">
-        <v>3932</v>
+      <c r="A222" s="361" t="s">
+        <v>3930</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C222" s="330" t="s">
+      <c r="C222" s="329" t="s">
         <v>1875</v>
       </c>
-      <c r="D222" s="312"/>
+      <c r="D222" s="311"/>
       <c r="E222" s="62"/>
       <c r="F222" s="16" t="s">
         <v>1876</v>
@@ -35936,16 +35921,16 @@
       <c r="AQ222" s="32"/>
     </row>
     <row r="223" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A223" s="356" t="s">
+      <c r="A223" s="355" t="s">
         <v>1885</v>
       </c>
       <c r="B223" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C223" s="332" t="s">
+      <c r="C223" s="331" t="s">
         <v>1886</v>
       </c>
-      <c r="D223" s="312"/>
+      <c r="D223" s="311"/>
       <c r="E223" s="62"/>
       <c r="F223" s="16" t="s">
         <v>1887</v>
@@ -36019,16 +36004,16 @@
       <c r="AQ223" s="32"/>
     </row>
     <row r="224" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A224" s="361" t="s">
-        <v>3933</v>
+      <c r="A224" s="360" t="s">
+        <v>3931</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C224" s="334" t="s">
+      <c r="C224" s="333" t="s">
         <v>1900</v>
       </c>
-      <c r="D224" s="312"/>
+      <c r="D224" s="311"/>
       <c r="E224" s="62"/>
       <c r="F224" s="16" t="s">
         <v>1901</v>
@@ -36090,10 +36075,10 @@
       <c r="B225" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C225" s="331" t="s">
+      <c r="C225" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D225" s="312"/>
+      <c r="D225" s="311"/>
       <c r="E225" s="62"/>
       <c r="F225" s="16" t="s">
         <v>1907</v>
@@ -36157,10 +36142,10 @@
       <c r="B226" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C226" s="331" t="s">
+      <c r="C226" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D226" s="312"/>
+      <c r="D226" s="311"/>
       <c r="E226" s="62"/>
       <c r="F226" s="32" t="s">
         <v>1108</v>
@@ -36234,10 +36219,10 @@
       <c r="B227" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C227" s="331" t="s">
+      <c r="C227" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D227" s="312"/>
+      <c r="D227" s="311"/>
       <c r="E227" s="62"/>
       <c r="F227" s="32" t="s">
         <v>1108</v>
@@ -36305,16 +36290,16 @@
       <c r="AQ227" s="32"/>
     </row>
     <row r="228" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A228" s="361" t="s">
-        <v>3934</v>
+      <c r="A228" s="360" t="s">
+        <v>3932</v>
       </c>
       <c r="B228" s="14" t="s">
         <v>1929</v>
       </c>
-      <c r="C228" s="340" t="s">
+      <c r="C228" s="339" t="s">
         <v>1930</v>
       </c>
-      <c r="D228" s="309"/>
+      <c r="D228" s="308"/>
       <c r="E228" s="18"/>
       <c r="F228" s="219" t="s">
         <v>1931</v>
@@ -36392,10 +36377,10 @@
       <c r="B229" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C229" s="331" t="s">
+      <c r="C229" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D229" s="312"/>
+      <c r="D229" s="311"/>
       <c r="E229" s="62"/>
       <c r="F229" s="32" t="s">
         <v>1108</v>
@@ -36455,16 +36440,16 @@
       <c r="AQ229" s="32"/>
     </row>
     <row r="230" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A230" s="356" t="s">
+      <c r="A230" s="355" t="s">
         <v>1949</v>
       </c>
       <c r="B230" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C230" s="330" t="s">
+      <c r="C230" s="329" t="s">
         <v>1950</v>
       </c>
-      <c r="D230" s="325"/>
+      <c r="D230" s="324"/>
       <c r="E230" s="53"/>
       <c r="F230" s="32" t="s">
         <v>1108</v>
@@ -36542,10 +36527,10 @@
       <c r="B231" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C231" s="331" t="s">
+      <c r="C231" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D231" s="312"/>
+      <c r="D231" s="311"/>
       <c r="E231" s="62"/>
       <c r="F231" s="48" t="s">
         <v>1960</v>
@@ -36611,10 +36596,10 @@
       <c r="B232" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C232" s="332" t="s">
+      <c r="C232" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D232" s="312"/>
+      <c r="D232" s="311"/>
       <c r="E232" s="62"/>
       <c r="F232" s="48" t="s">
         <v>1967</v>
@@ -36686,10 +36671,10 @@
       <c r="B233" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C233" s="331" t="s">
+      <c r="C233" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D233" s="312"/>
+      <c r="D233" s="311"/>
       <c r="E233" s="62"/>
       <c r="F233" s="16" t="s">
         <v>1977</v>
@@ -36747,16 +36732,16 @@
       <c r="AQ233" s="32"/>
     </row>
     <row r="234" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A234" s="361" t="s">
-        <v>3935</v>
+      <c r="A234" s="360" t="s">
+        <v>3933</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C234" s="345" t="s">
-        <v>3876</v>
-      </c>
-      <c r="D234" s="312"/>
+      <c r="C234" s="344" t="s">
+        <v>3874</v>
+      </c>
+      <c r="D234" s="311"/>
       <c r="E234" s="62"/>
       <c r="F234" s="221" t="s">
         <v>1982</v>
@@ -36824,10 +36809,10 @@
       <c r="B235" s="142" t="s">
         <v>1012</v>
       </c>
-      <c r="C235" s="331" t="s">
+      <c r="C235" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D235" s="312"/>
+      <c r="D235" s="311"/>
       <c r="E235" s="62"/>
       <c r="F235" s="32" t="s">
         <v>1108</v>
@@ -36903,16 +36888,16 @@
       <c r="AQ235" s="32"/>
     </row>
     <row r="236" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A236" s="356" t="s">
+      <c r="A236" s="355" t="s">
         <v>1995</v>
       </c>
       <c r="B236" s="14" t="s">
         <v>1996</v>
       </c>
-      <c r="C236" s="340" t="s">
+      <c r="C236" s="339" t="s">
         <v>1997</v>
       </c>
-      <c r="D236" s="312"/>
+      <c r="D236" s="311"/>
       <c r="E236" s="62"/>
       <c r="F236" s="48" t="s">
         <v>1998</v>
@@ -36984,10 +36969,10 @@
       <c r="B237" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C237" s="331" t="s">
+      <c r="C237" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D237" s="312"/>
+      <c r="D237" s="311"/>
       <c r="E237" s="62"/>
       <c r="F237" s="48" t="s">
         <v>2007</v>
@@ -37067,10 +37052,10 @@
       <c r="B238" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C238" s="332" t="s">
+      <c r="C238" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D238" s="312"/>
+      <c r="D238" s="311"/>
       <c r="E238" s="62"/>
       <c r="F238" s="48" t="s">
         <v>2020</v>
@@ -37152,10 +37137,10 @@
       <c r="B239" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C239" s="331" t="s">
+      <c r="C239" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D239" s="312"/>
+      <c r="D239" s="311"/>
       <c r="E239" s="62"/>
       <c r="F239" s="48" t="s">
         <v>2030</v>
@@ -37223,16 +37208,16 @@
       <c r="AQ239" s="32"/>
     </row>
     <row r="240" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A240" s="361" t="s">
-        <v>3936</v>
+      <c r="A240" s="360" t="s">
+        <v>3934</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C240" s="330" t="s">
+      <c r="C240" s="329" t="s">
         <v>2038</v>
       </c>
-      <c r="D240" s="312"/>
+      <c r="D240" s="311"/>
       <c r="E240" s="62"/>
       <c r="F240" s="16" t="s">
         <v>2039</v>
@@ -37308,10 +37293,10 @@
       <c r="B241" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C241" s="331" t="s">
+      <c r="C241" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D241" s="312"/>
+      <c r="D241" s="311"/>
       <c r="E241" s="62"/>
       <c r="F241" s="32" t="s">
         <v>1108</v>
@@ -37385,10 +37370,10 @@
       <c r="B242" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C242" s="331" t="s">
+      <c r="C242" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D242" s="312"/>
+      <c r="D242" s="311"/>
       <c r="E242" s="62"/>
       <c r="F242" s="32" t="s">
         <v>1108</v>
@@ -37454,16 +37439,16 @@
       <c r="AQ242" s="32"/>
     </row>
     <row r="243" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A243" s="356" t="s">
+      <c r="A243" s="355" t="s">
         <v>2062</v>
       </c>
       <c r="B243" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C243" s="330" t="s">
+      <c r="C243" s="329" t="s">
         <v>2063</v>
       </c>
-      <c r="D243" s="312"/>
+      <c r="D243" s="311"/>
       <c r="E243" s="62"/>
       <c r="F243" s="16" t="s">
         <v>2064</v>
@@ -37537,16 +37522,16 @@
       <c r="AQ243" s="32"/>
     </row>
     <row r="244" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A244" s="356" t="s">
+      <c r="A244" s="355" t="s">
         <v>2071</v>
       </c>
       <c r="B244" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C244" s="330" t="s">
+      <c r="C244" s="329" t="s">
         <v>2072</v>
       </c>
-      <c r="D244" s="312"/>
+      <c r="D244" s="311"/>
       <c r="E244" s="62"/>
       <c r="F244" s="16" t="s">
         <v>2073</v>
@@ -37624,10 +37609,10 @@
       <c r="B245" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C245" s="332" t="s">
+      <c r="C245" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D245" s="312"/>
+      <c r="D245" s="311"/>
       <c r="E245" s="62"/>
       <c r="F245" s="48" t="s">
         <v>2086</v>
@@ -37699,10 +37684,10 @@
       <c r="B246" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C246" s="331" t="s">
+      <c r="C246" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D246" s="312"/>
+      <c r="D246" s="311"/>
       <c r="E246" s="62"/>
       <c r="F246" s="48" t="s">
         <v>2095</v>
@@ -37768,7 +37753,7 @@
       <c r="B247" s="303" t="s">
         <v>2102</v>
       </c>
-      <c r="C247" s="346" t="s">
+      <c r="C247" s="345" t="s">
         <v>3863</v>
       </c>
       <c r="E247" s="301"/>
@@ -37844,7 +37829,7 @@
       <c r="B248" s="298" t="s">
         <v>3854</v>
       </c>
-      <c r="C248" s="346" t="s">
+      <c r="C248" s="345" t="s">
         <v>3863</v>
       </c>
       <c r="E248" s="301"/>
@@ -37914,10 +37899,10 @@
       <c r="B249" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C249" s="331" t="s">
+      <c r="C249" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D249" s="312"/>
+      <c r="D249" s="311"/>
       <c r="E249" s="62"/>
       <c r="F249" s="48" t="s">
         <v>2107</v>
@@ -37991,10 +37976,10 @@
       <c r="B250" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C250" s="331" t="s">
+      <c r="C250" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D250" s="312"/>
+      <c r="D250" s="311"/>
       <c r="E250" s="62"/>
       <c r="F250" s="16" t="s">
         <v>2116</v>
@@ -38060,10 +38045,10 @@
       <c r="B251" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C251" s="331" t="s">
+      <c r="C251" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D251" s="312"/>
+      <c r="D251" s="311"/>
       <c r="E251" s="62"/>
       <c r="F251" s="48" t="s">
         <v>2122</v>
@@ -38131,10 +38116,10 @@
       <c r="B252" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C252" s="331" t="s">
+      <c r="C252" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D252" s="312"/>
+      <c r="D252" s="311"/>
       <c r="E252" s="62"/>
       <c r="F252" s="16" t="s">
         <v>2130</v>
@@ -38200,16 +38185,16 @@
       <c r="AQ252" s="32"/>
     </row>
     <row r="253" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A253" s="356" t="s">
+      <c r="A253" s="355" t="s">
         <v>2137</v>
       </c>
       <c r="B253" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C253" s="332" t="s">
-        <v>3937</v>
-      </c>
-      <c r="D253" s="312"/>
+      <c r="C253" s="331" t="s">
+        <v>3935</v>
+      </c>
+      <c r="D253" s="311"/>
       <c r="E253" s="62"/>
       <c r="F253" s="16" t="s">
         <v>2138</v>
@@ -38275,10 +38260,10 @@
       <c r="B254" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C254" s="331" t="s">
+      <c r="C254" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D254" s="312"/>
+      <c r="D254" s="311"/>
       <c r="E254" s="62"/>
       <c r="F254" s="48" t="s">
         <v>2146</v>
@@ -38348,10 +38333,10 @@
       <c r="B255" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C255" s="336" t="s">
+      <c r="C255" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D255" s="312"/>
+      <c r="D255" s="311"/>
       <c r="E255" s="62"/>
       <c r="F255" s="48" t="s">
         <v>2155</v>
@@ -38411,16 +38396,16 @@
       <c r="AQ255" s="32"/>
     </row>
     <row r="256" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A256" s="362" t="s">
-        <v>3938</v>
+      <c r="A256" s="361" t="s">
+        <v>3936</v>
       </c>
       <c r="B256" s="21" t="s">
         <v>1012</v>
       </c>
-      <c r="C256" s="340" t="s">
+      <c r="C256" s="339" t="s">
         <v>2162</v>
       </c>
-      <c r="D256" s="315"/>
+      <c r="D256" s="314"/>
       <c r="E256" s="62" t="s">
         <v>2163</v>
       </c>
@@ -38500,10 +38485,10 @@
       <c r="B257" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C257" s="331" t="s">
+      <c r="C257" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D257" s="312"/>
+      <c r="D257" s="311"/>
       <c r="E257" s="62"/>
       <c r="F257" s="48" t="s">
         <v>2173</v>
@@ -38565,16 +38550,16 @@
       <c r="AQ257" s="32"/>
     </row>
     <row r="258" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A258" s="361" t="s">
-        <v>3939</v>
+      <c r="A258" s="360" t="s">
+        <v>3937</v>
       </c>
       <c r="B258" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C258" s="340" t="s">
+      <c r="C258" s="339" t="s">
         <v>2180</v>
       </c>
-      <c r="D258" s="312"/>
+      <c r="D258" s="311"/>
       <c r="E258" s="62"/>
       <c r="F258" s="48" t="s">
         <v>2181</v>
@@ -38644,10 +38629,10 @@
       <c r="B259" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C259" s="331" t="s">
+      <c r="C259" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D259" s="312"/>
+      <c r="D259" s="311"/>
       <c r="E259" s="62"/>
       <c r="F259" s="32" t="s">
         <v>1108</v>
@@ -38719,10 +38704,10 @@
       <c r="B260" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C260" s="331" t="s">
+      <c r="C260" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D260" s="312"/>
+      <c r="D260" s="311"/>
       <c r="E260" s="62"/>
       <c r="F260" s="32" t="s">
         <v>1108</v>
@@ -38792,10 +38777,10 @@
       <c r="B261" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C261" s="331" t="s">
+      <c r="C261" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D261" s="312"/>
+      <c r="D261" s="311"/>
       <c r="E261" s="62"/>
       <c r="F261" s="16" t="s">
         <v>2204</v>
@@ -38869,10 +38854,10 @@
       <c r="B262" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C262" s="331" t="s">
+      <c r="C262" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D262" s="312"/>
+      <c r="D262" s="311"/>
       <c r="E262" s="62"/>
       <c r="F262" s="16" t="s">
         <v>2211</v>
@@ -38932,16 +38917,16 @@
       <c r="AQ262" s="32"/>
     </row>
     <row r="263" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A263" s="361" t="s">
-        <v>3940</v>
+      <c r="A263" s="360" t="s">
+        <v>3938</v>
       </c>
       <c r="B263" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C263" s="330" t="s">
+      <c r="C263" s="329" t="s">
         <v>2217</v>
       </c>
-      <c r="D263" s="312"/>
+      <c r="D263" s="311"/>
       <c r="E263" s="62"/>
       <c r="F263" s="16" t="s">
         <v>2218</v>
@@ -39003,10 +38988,10 @@
       <c r="B264" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C264" s="331" t="s">
+      <c r="C264" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D264" s="312"/>
+      <c r="D264" s="311"/>
       <c r="E264" s="62"/>
       <c r="F264" s="16" t="s">
         <v>2224</v>
@@ -39078,10 +39063,10 @@
       <c r="B265" s="14" t="s">
         <v>2231</v>
       </c>
-      <c r="C265" s="331" t="s">
+      <c r="C265" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D265" s="312"/>
+      <c r="D265" s="311"/>
       <c r="E265" s="62"/>
       <c r="F265" s="32" t="s">
         <v>1108</v>
@@ -39139,16 +39124,16 @@
       <c r="AQ265" s="32"/>
     </row>
     <row r="266" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A266" s="361" t="s">
-        <v>3941</v>
+      <c r="A266" s="360" t="s">
+        <v>3939</v>
       </c>
       <c r="B266" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C266" s="330" t="s">
+      <c r="C266" s="329" t="s">
         <v>2236</v>
       </c>
-      <c r="D266" s="312"/>
+      <c r="D266" s="311"/>
       <c r="E266" s="62"/>
       <c r="F266" s="221" t="s">
         <v>2237</v>
@@ -39216,10 +39201,10 @@
       <c r="B267" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C267" s="336" t="s">
+      <c r="C267" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D267" s="312"/>
+      <c r="D267" s="311"/>
       <c r="E267" s="62"/>
       <c r="F267" s="48" t="s">
         <v>2245</v>
@@ -39289,10 +39274,10 @@
       <c r="B268" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C268" s="331" t="s">
+      <c r="C268" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D268" s="312"/>
+      <c r="D268" s="311"/>
       <c r="E268" s="62"/>
       <c r="F268" s="48" t="s">
         <v>2254</v>
@@ -39358,16 +39343,16 @@
       <c r="AQ268" s="32"/>
     </row>
     <row r="269" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A269" s="362" t="s">
-        <v>3942</v>
+      <c r="A269" s="361" t="s">
+        <v>3940</v>
       </c>
       <c r="B269" s="71" t="s">
         <v>2262</v>
       </c>
-      <c r="C269" s="330" t="s">
+      <c r="C269" s="329" t="s">
         <v>2263</v>
       </c>
-      <c r="D269" s="312"/>
+      <c r="D269" s="311"/>
       <c r="E269" s="62"/>
       <c r="F269" s="32" t="s">
         <v>2264</v>
@@ -39441,10 +39426,10 @@
       <c r="B270" s="33" t="s">
         <v>1012</v>
       </c>
-      <c r="C270" s="331" t="s">
+      <c r="C270" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D270" s="312"/>
+      <c r="D270" s="311"/>
       <c r="E270" s="62"/>
       <c r="F270" s="16" t="s">
         <v>2274</v>
@@ -39514,10 +39499,10 @@
       <c r="B271" s="32" t="s">
         <v>2282</v>
       </c>
-      <c r="C271" s="331" t="s">
+      <c r="C271" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D271" s="312"/>
+      <c r="D271" s="311"/>
       <c r="E271" s="62"/>
       <c r="F271" s="32" t="s">
         <v>1108</v>
@@ -39581,10 +39566,10 @@
       <c r="B272" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C272" s="331" t="s">
+      <c r="C272" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D272" s="312"/>
+      <c r="D272" s="311"/>
       <c r="E272" s="62"/>
       <c r="F272" s="48" t="s">
         <v>2289</v>
@@ -39648,10 +39633,10 @@
       <c r="B273" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C273" s="331" t="s">
+      <c r="C273" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D273" s="312"/>
+      <c r="D273" s="311"/>
       <c r="E273" s="62"/>
       <c r="F273" s="16" t="s">
         <v>2295</v>
@@ -39717,10 +39702,10 @@
       <c r="B274" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C274" s="331" t="s">
+      <c r="C274" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D274" s="312"/>
+      <c r="D274" s="311"/>
       <c r="E274" s="62"/>
       <c r="F274" s="48" t="s">
         <v>2302</v>
@@ -39788,10 +39773,10 @@
       <c r="B275" s="14" t="s">
         <v>2310</v>
       </c>
-      <c r="C275" s="331" t="s">
+      <c r="C275" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D275" s="312"/>
+      <c r="D275" s="311"/>
       <c r="E275" s="62"/>
       <c r="F275" s="32" t="s">
         <v>2311</v>
@@ -39859,10 +39844,10 @@
       <c r="B276" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C276" s="332" t="s">
+      <c r="C276" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D276" s="312"/>
+      <c r="D276" s="311"/>
       <c r="E276" s="62"/>
       <c r="F276" s="32" t="s">
         <v>2311</v>
@@ -39938,10 +39923,10 @@
       <c r="B277" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C277" s="331" t="s">
+      <c r="C277" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D277" s="312"/>
+      <c r="D277" s="311"/>
       <c r="E277" s="62"/>
       <c r="F277" s="32" t="s">
         <v>2311</v>
@@ -40011,10 +39996,10 @@
       <c r="B278" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C278" s="331" t="s">
+      <c r="C278" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D278" s="312"/>
+      <c r="D278" s="311"/>
       <c r="E278" s="62"/>
       <c r="F278" s="16" t="s">
         <v>2331</v>
@@ -40092,10 +40077,10 @@
       <c r="B279" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C279" s="331" t="s">
+      <c r="C279" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D279" s="312"/>
+      <c r="D279" s="311"/>
       <c r="E279" s="62"/>
       <c r="F279" s="32" t="s">
         <v>2311</v>
@@ -40161,10 +40146,10 @@
       <c r="B280" s="14" t="s">
         <v>1663</v>
       </c>
-      <c r="C280" s="331" t="s">
+      <c r="C280" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D280" s="312"/>
+      <c r="D280" s="311"/>
       <c r="E280" s="62"/>
       <c r="F280" s="16" t="s">
         <v>2344</v>
@@ -40238,10 +40223,10 @@
       <c r="B281" s="108" t="s">
         <v>439</v>
       </c>
-      <c r="C281" s="331" t="s">
+      <c r="C281" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D281" s="312"/>
+      <c r="D281" s="311"/>
       <c r="E281" s="62"/>
       <c r="F281" s="16" t="s">
         <v>2349</v>
@@ -40305,10 +40290,10 @@
       <c r="B282" s="108" t="s">
         <v>1012</v>
       </c>
-      <c r="C282" s="331" t="s">
+      <c r="C282" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D282" s="312"/>
+      <c r="D282" s="311"/>
       <c r="E282" s="62"/>
       <c r="F282" s="48" t="s">
         <v>2354</v>
@@ -40374,16 +40359,16 @@
       <c r="AQ282" s="32"/>
     </row>
     <row r="283" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A283" s="356" t="s">
+      <c r="A283" s="355" t="s">
         <v>2360</v>
       </c>
       <c r="B283" s="108" t="s">
         <v>439</v>
       </c>
-      <c r="C283" s="334" t="s">
+      <c r="C283" s="333" t="s">
         <v>2361</v>
       </c>
-      <c r="D283" s="312"/>
+      <c r="D283" s="311"/>
       <c r="E283" s="62"/>
       <c r="F283" s="16" t="s">
         <v>2362</v>
@@ -40453,10 +40438,10 @@
       <c r="B284" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C284" s="331" t="s">
+      <c r="C284" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D284" s="312"/>
+      <c r="D284" s="311"/>
       <c r="E284" s="62"/>
       <c r="F284" s="48" t="s">
         <v>2370</v>
@@ -40524,10 +40509,10 @@
       <c r="B285" s="32" t="s">
         <v>2378</v>
       </c>
-      <c r="C285" s="331" t="s">
+      <c r="C285" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D285" s="312"/>
+      <c r="D285" s="311"/>
       <c r="E285" s="62"/>
       <c r="F285" s="48" t="s">
         <v>2379</v>
@@ -40589,10 +40574,10 @@
       <c r="B286" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C286" s="331" t="s">
+      <c r="C286" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D286" s="312"/>
+      <c r="D286" s="311"/>
       <c r="E286" s="62"/>
       <c r="F286" s="32" t="s">
         <v>2311</v>
@@ -40660,10 +40645,10 @@
       <c r="B287" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C287" s="331" t="s">
+      <c r="C287" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D287" s="312"/>
+      <c r="D287" s="311"/>
       <c r="E287" s="62"/>
       <c r="F287" s="32" t="s">
         <v>2311</v>
@@ -40729,10 +40714,10 @@
       <c r="B288" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C288" s="331" t="s">
+      <c r="C288" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D288" s="312"/>
+      <c r="D288" s="311"/>
       <c r="E288" s="62"/>
       <c r="F288" s="16" t="s">
         <v>2393</v>
@@ -40796,10 +40781,10 @@
       <c r="B289" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C289" s="338" t="s">
+      <c r="C289" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D289" s="312"/>
+      <c r="D289" s="311"/>
       <c r="E289" s="62"/>
       <c r="F289" s="16" t="s">
         <v>2398</v>
@@ -40877,10 +40862,10 @@
       <c r="B290" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="C290" s="331" t="s">
+      <c r="C290" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D290" s="312"/>
+      <c r="D290" s="311"/>
       <c r="E290" s="62"/>
       <c r="F290" s="32" t="s">
         <v>2311</v>
@@ -40942,10 +40927,10 @@
       <c r="B291" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C291" s="331" t="s">
+      <c r="C291" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D291" s="312"/>
+      <c r="D291" s="311"/>
       <c r="E291" s="62"/>
       <c r="F291" s="48" t="s">
         <v>2415</v>
@@ -41011,10 +40996,10 @@
       <c r="B292" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C292" s="331" t="s">
+      <c r="C292" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D292" s="312"/>
+      <c r="D292" s="311"/>
       <c r="E292" s="62"/>
       <c r="F292" s="16" t="s">
         <v>2422</v>
@@ -41086,10 +41071,10 @@
       <c r="B293" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C293" s="331" t="s">
+      <c r="C293" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D293" s="312"/>
+      <c r="D293" s="311"/>
       <c r="E293" s="62"/>
       <c r="F293" s="48" t="s">
         <v>2433</v>
@@ -41163,10 +41148,10 @@
       <c r="B294" s="33" t="s">
         <v>1012</v>
       </c>
-      <c r="C294" s="331" t="s">
+      <c r="C294" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D294" s="312"/>
+      <c r="D294" s="311"/>
       <c r="E294" s="62"/>
       <c r="F294" s="221" t="s">
         <v>2442</v>
@@ -41232,16 +41217,16 @@
       <c r="AQ294" s="32"/>
     </row>
     <row r="295" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A295" s="361" t="s">
-        <v>3943</v>
+      <c r="A295" s="360" t="s">
+        <v>3941</v>
       </c>
       <c r="B295" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C295" s="330" t="s">
+      <c r="C295" s="329" t="s">
         <v>2448</v>
       </c>
-      <c r="D295" s="312"/>
+      <c r="D295" s="311"/>
       <c r="E295" s="62"/>
       <c r="F295" s="48" t="s">
         <v>2449</v>
@@ -41317,10 +41302,10 @@
       <c r="B296" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C296" s="331" t="s">
+      <c r="C296" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D296" s="312"/>
+      <c r="D296" s="311"/>
       <c r="E296" s="62"/>
       <c r="F296" s="48" t="s">
         <v>2458</v>
@@ -41398,10 +41383,10 @@
       <c r="B297" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C297" s="331" t="s">
+      <c r="C297" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D297" s="312"/>
+      <c r="D297" s="311"/>
       <c r="E297" s="62"/>
       <c r="F297" s="48" t="s">
         <v>2469</v>
@@ -41467,10 +41452,10 @@
       <c r="B298" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C298" s="331" t="s">
+      <c r="C298" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D298" s="312"/>
+      <c r="D298" s="311"/>
       <c r="E298" s="62"/>
       <c r="F298" s="16" t="s">
         <v>2476</v>
@@ -41534,10 +41519,10 @@
       <c r="B299" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C299" s="331" t="s">
+      <c r="C299" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D299" s="312"/>
+      <c r="D299" s="311"/>
       <c r="E299" s="62"/>
       <c r="F299" s="48" t="s">
         <v>2481</v>
@@ -41609,10 +41594,10 @@
       <c r="B300" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C300" s="332" t="s">
+      <c r="C300" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D300" s="312"/>
+      <c r="D300" s="311"/>
       <c r="E300" s="62"/>
       <c r="F300" s="16" t="s">
         <v>2487</v>
@@ -41686,10 +41671,10 @@
       <c r="B301" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C301" s="331" t="s">
+      <c r="C301" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D301" s="312"/>
+      <c r="D301" s="311"/>
       <c r="E301" s="62"/>
       <c r="F301" s="48" t="s">
         <v>2495</v>
@@ -41755,10 +41740,10 @@
       <c r="B302" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C302" s="338" t="s">
+      <c r="C302" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D302" s="312"/>
+      <c r="D302" s="311"/>
       <c r="E302" s="62"/>
       <c r="F302" s="16" t="s">
         <v>2502</v>
@@ -41828,10 +41813,10 @@
       <c r="B303" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C303" s="338" t="s">
+      <c r="C303" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D303" s="312"/>
+      <c r="D303" s="311"/>
       <c r="E303" s="62"/>
       <c r="F303" s="32" t="s">
         <v>2510</v>
@@ -41895,10 +41880,10 @@
       <c r="B304" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C304" s="331" t="s">
+      <c r="C304" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D304" s="312"/>
+      <c r="D304" s="311"/>
       <c r="E304" s="62"/>
       <c r="F304" s="32" t="s">
         <v>2510</v>
@@ -41956,16 +41941,16 @@
       <c r="AQ304" s="32"/>
     </row>
     <row r="305" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A305" s="365" t="s">
+      <c r="A305" s="364" t="s">
         <v>2521</v>
       </c>
       <c r="B305" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C305" s="348" t="s">
+      <c r="C305" s="347" t="s">
         <v>2521</v>
       </c>
-      <c r="D305" s="312"/>
+      <c r="D305" s="311"/>
       <c r="E305" s="62"/>
       <c r="F305" s="48" t="s">
         <v>2522</v>
@@ -42027,16 +42012,16 @@
       <c r="AQ305" s="32"/>
     </row>
     <row r="306" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A306" s="366" t="s">
-        <v>3944</v>
+      <c r="A306" s="365" t="s">
+        <v>3942</v>
       </c>
       <c r="B306" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C306" s="330" t="s">
+      <c r="C306" s="329" t="s">
         <v>2529</v>
       </c>
-      <c r="D306" s="312"/>
+      <c r="D306" s="311"/>
       <c r="E306" s="62"/>
       <c r="F306" s="16" t="s">
         <v>2530</v>
@@ -42114,10 +42099,10 @@
       <c r="B307" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C307" s="331" t="s">
+      <c r="C307" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D307" s="327"/>
+      <c r="D307" s="326"/>
       <c r="E307" s="238"/>
       <c r="F307" s="239" t="s">
         <v>2542</v>
@@ -42185,16 +42170,16 @@
       <c r="AQ307" s="32"/>
     </row>
     <row r="308" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A308" s="366" t="s">
-        <v>3945</v>
+      <c r="A308" s="365" t="s">
+        <v>3943</v>
       </c>
       <c r="B308" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C308" s="330" t="s">
+      <c r="C308" s="329" t="s">
         <v>2552</v>
       </c>
-      <c r="D308" s="327"/>
+      <c r="D308" s="326"/>
       <c r="E308" s="238"/>
       <c r="F308" s="239" t="s">
         <v>2553</v>
@@ -42262,16 +42247,16 @@
       <c r="AQ308" s="32"/>
     </row>
     <row r="309" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A309" s="367" t="s">
+      <c r="A309" s="366" t="s">
         <v>2561</v>
       </c>
       <c r="B309" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C309" s="330" t="s">
+      <c r="C309" s="329" t="s">
         <v>2562</v>
       </c>
-      <c r="D309" s="312"/>
+      <c r="D309" s="311"/>
       <c r="E309" s="62"/>
       <c r="F309" s="16" t="s">
         <v>2563</v>
@@ -42339,16 +42324,16 @@
       <c r="AQ309" s="32"/>
     </row>
     <row r="310" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A310" s="368" t="s">
-        <v>3946</v>
+      <c r="A310" s="367" t="s">
+        <v>3944</v>
       </c>
       <c r="B310" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C310" s="330" t="s">
+      <c r="C310" s="329" t="s">
         <v>2573</v>
       </c>
-      <c r="D310" s="311"/>
+      <c r="D310" s="310"/>
       <c r="E310" s="62"/>
       <c r="F310" s="16" t="s">
         <v>2574</v>
@@ -42428,10 +42413,10 @@
       <c r="B311" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C311" s="331" t="s">
+      <c r="C311" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D311" s="312"/>
+      <c r="D311" s="311"/>
       <c r="E311" s="62"/>
       <c r="F311" s="16" t="s">
         <v>2583</v>
@@ -42495,10 +42480,10 @@
       <c r="B312" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C312" s="331" t="s">
+      <c r="C312" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D312" s="312"/>
+      <c r="D312" s="311"/>
       <c r="E312" s="62"/>
       <c r="F312" s="48" t="s">
         <v>2589</v>
@@ -42566,10 +42551,10 @@
       <c r="B313" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C313" s="336" t="s">
+      <c r="C313" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D313" s="312"/>
+      <c r="D313" s="311"/>
       <c r="E313" s="62"/>
       <c r="F313" s="48" t="s">
         <v>2597</v>
@@ -42639,10 +42624,10 @@
       <c r="B314" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="C314" s="343" t="s">
+      <c r="C314" s="342" t="s">
         <v>144</v>
       </c>
-      <c r="D314" s="315"/>
+      <c r="D314" s="314"/>
       <c r="E314" s="62"/>
       <c r="F314" s="21" t="s">
         <v>2606</v>
@@ -42724,10 +42709,10 @@
       <c r="B315" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C315" s="331" t="s">
+      <c r="C315" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D315" s="312"/>
+      <c r="D315" s="311"/>
       <c r="E315" s="62"/>
       <c r="F315" s="48" t="s">
         <v>2617</v>
@@ -42795,10 +42780,10 @@
       <c r="B316" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C316" s="331" t="s">
+      <c r="C316" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D316" s="312"/>
+      <c r="D316" s="311"/>
       <c r="E316" s="62"/>
       <c r="F316" s="16" t="s">
         <v>2625</v>
@@ -42866,10 +42851,10 @@
       <c r="B317" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C317" s="331" t="s">
+      <c r="C317" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D317" s="312"/>
+      <c r="D317" s="311"/>
       <c r="E317" s="62"/>
       <c r="F317" s="16" t="s">
         <v>2630</v>
@@ -42935,14 +42920,14 @@
       <c r="AQ317" s="32"/>
     </row>
     <row r="318" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A318" s="369" t="s">
-        <v>3947</v>
+      <c r="A318" s="368" t="s">
+        <v>3945</v>
       </c>
       <c r="B318" s="33" t="s">
         <v>2636</v>
       </c>
-      <c r="C318" s="347" t="s">
-        <v>3875</v>
+      <c r="C318" s="346" t="s">
+        <v>3873</v>
       </c>
       <c r="E318" s="62" t="s">
         <v>2637</v>
@@ -43019,10 +43004,10 @@
       <c r="B319" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C319" s="340" t="s">
+      <c r="C319" s="339" t="s">
         <v>172</v>
       </c>
-      <c r="D319" s="311" t="s">
+      <c r="D319" s="310" t="s">
         <v>2647</v>
       </c>
       <c r="E319" s="62"/>
@@ -43094,16 +43079,16 @@
       <c r="AQ319" s="32"/>
     </row>
     <row r="320" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A320" s="366" t="s">
-        <v>3948</v>
+      <c r="A320" s="365" t="s">
+        <v>3946</v>
       </c>
       <c r="B320" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C320" s="340" t="s">
+      <c r="C320" s="339" t="s">
         <v>2656</v>
       </c>
-      <c r="D320" s="325"/>
+      <c r="D320" s="324"/>
       <c r="E320" s="53"/>
       <c r="F320" s="14" t="s">
         <v>2311</v>
@@ -43163,16 +43148,16 @@
       <c r="AQ320" s="32"/>
     </row>
     <row r="321" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A321" s="366" t="s">
-        <v>3949</v>
+      <c r="A321" s="365" t="s">
+        <v>3947</v>
       </c>
       <c r="B321" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C321" s="330" t="s">
+      <c r="C321" s="329" t="s">
         <v>2661</v>
       </c>
-      <c r="D321" s="325"/>
+      <c r="D321" s="324"/>
       <c r="E321" s="53"/>
       <c r="F321" s="14" t="s">
         <v>2311</v>
@@ -43254,10 +43239,10 @@
       <c r="B322" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C322" s="331" t="s">
+      <c r="C322" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D322" s="312"/>
+      <c r="D322" s="311"/>
       <c r="E322" s="62"/>
       <c r="F322" s="16" t="s">
         <v>2674</v>
@@ -43327,10 +43312,10 @@
       <c r="B323" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C323" s="331" t="s">
+      <c r="C323" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D323" s="312"/>
+      <c r="D323" s="311"/>
       <c r="E323" s="62"/>
       <c r="F323" s="16" t="s">
         <v>2681</v>
@@ -43400,10 +43385,10 @@
       <c r="B324" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C324" s="331" t="s">
+      <c r="C324" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D324" s="312"/>
+      <c r="D324" s="311"/>
       <c r="E324" s="62"/>
       <c r="F324" s="16" t="s">
         <v>2689</v>
@@ -43473,10 +43458,10 @@
       <c r="B325" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C325" s="331" t="s">
+      <c r="C325" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D325" s="312"/>
+      <c r="D325" s="311"/>
       <c r="E325" s="62"/>
       <c r="F325" s="16" t="s">
         <v>2697</v>
@@ -43544,10 +43529,10 @@
       <c r="B326" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C326" s="331" t="s">
+      <c r="C326" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D326" s="328"/>
+      <c r="D326" s="327"/>
       <c r="E326" s="238"/>
       <c r="F326" s="239" t="s">
         <v>2704</v>
@@ -43621,10 +43606,10 @@
       <c r="B327" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C327" s="331" t="s">
+      <c r="C327" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D327" s="325"/>
+      <c r="D327" s="324"/>
       <c r="E327" s="53"/>
       <c r="F327" s="16" t="s">
         <v>2712</v>
@@ -43694,16 +43679,16 @@
       <c r="AQ327" s="32"/>
     </row>
     <row r="328" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A328" s="365" t="s">
+      <c r="A328" s="364" t="s">
         <v>2721</v>
       </c>
       <c r="B328" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C328" s="332" t="s">
-        <v>3950</v>
-      </c>
-      <c r="D328" s="327"/>
+      <c r="C328" s="331" t="s">
+        <v>3948</v>
+      </c>
+      <c r="D328" s="326"/>
       <c r="E328" s="238"/>
       <c r="F328" s="251" t="s">
         <v>2722</v>
@@ -43781,10 +43766,10 @@
       <c r="B329" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C329" s="331" t="s">
+      <c r="C329" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D329" s="312"/>
+      <c r="D329" s="311"/>
       <c r="E329" s="62"/>
       <c r="F329" s="16" t="s">
         <v>2731</v>
@@ -43864,10 +43849,10 @@
       <c r="B330" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C330" s="331" t="s">
+      <c r="C330" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D330" s="325"/>
+      <c r="D330" s="324"/>
       <c r="E330" s="53"/>
       <c r="F330" s="16" t="s">
         <v>2742</v>
@@ -43937,16 +43922,16 @@
       <c r="AQ330" s="32"/>
     </row>
     <row r="331" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A331" s="370" t="s">
+      <c r="A331" s="369" t="s">
         <v>2751</v>
       </c>
       <c r="B331" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C331" s="330" t="s">
+      <c r="C331" s="329" t="s">
         <v>2752</v>
       </c>
-      <c r="D331" s="325"/>
+      <c r="D331" s="324"/>
       <c r="E331" s="53"/>
       <c r="F331" s="16" t="s">
         <v>2753</v>
@@ -44022,10 +44007,10 @@
       <c r="B332" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C332" s="331" t="s">
+      <c r="C332" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D332" s="312"/>
+      <c r="D332" s="311"/>
       <c r="E332" s="62"/>
       <c r="F332" s="48" t="s">
         <v>2762</v>
@@ -44097,10 +44082,10 @@
       <c r="B333" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C333" s="331" t="s">
+      <c r="C333" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D333" s="325"/>
+      <c r="D333" s="324"/>
       <c r="E333" s="53"/>
       <c r="F333" s="49" t="s">
         <v>2311</v>
@@ -44164,16 +44149,16 @@
       <c r="AQ333" s="32"/>
     </row>
     <row r="334" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A334" s="365" t="s">
+      <c r="A334" s="364" t="s">
         <v>2773</v>
       </c>
       <c r="B334" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C334" s="330" t="s">
+      <c r="C334" s="329" t="s">
         <v>2774</v>
       </c>
-      <c r="D334" s="312"/>
+      <c r="D334" s="311"/>
       <c r="E334" s="62"/>
       <c r="F334" s="48" t="s">
         <v>2775</v>
@@ -44243,10 +44228,10 @@
       <c r="B335" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C335" s="331" t="s">
+      <c r="C335" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D335" s="312"/>
+      <c r="D335" s="311"/>
       <c r="E335" s="62"/>
       <c r="F335" s="16" t="s">
         <v>2780</v>
@@ -44316,10 +44301,10 @@
       <c r="B336" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C336" s="331" t="s">
+      <c r="C336" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D336" s="312"/>
+      <c r="D336" s="311"/>
       <c r="E336" s="62"/>
       <c r="F336" s="48" t="s">
         <v>2788</v>
@@ -44395,10 +44380,10 @@
       <c r="B337" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C337" s="331" t="s">
+      <c r="C337" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D337" s="312"/>
+      <c r="D337" s="311"/>
       <c r="E337" s="62"/>
       <c r="F337" s="48" t="s">
         <v>2798</v>
@@ -44466,10 +44451,10 @@
       <c r="B338" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C338" s="331" t="s">
+      <c r="C338" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D338" s="325"/>
+      <c r="D338" s="324"/>
       <c r="E338" s="53"/>
       <c r="F338" s="49" t="s">
         <v>2311</v>
@@ -44533,16 +44518,16 @@
       <c r="AQ338" s="32"/>
     </row>
     <row r="339" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A339" s="365" t="s">
+      <c r="A339" s="364" t="s">
         <v>2816</v>
       </c>
       <c r="B339" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C339" s="330" t="s">
+      <c r="C339" s="329" t="s">
         <v>2817</v>
       </c>
-      <c r="D339" s="311"/>
+      <c r="D339" s="310"/>
       <c r="E339" s="62"/>
       <c r="F339" s="48" t="s">
         <v>2818</v>
@@ -44610,16 +44595,16 @@
       <c r="AQ339" s="32"/>
     </row>
     <row r="340" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A340" s="365" t="s">
+      <c r="A340" s="364" t="s">
         <v>2826</v>
       </c>
       <c r="B340" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C340" s="330" t="s">
+      <c r="C340" s="329" t="s">
         <v>2827</v>
       </c>
-      <c r="D340" s="325"/>
+      <c r="D340" s="324"/>
       <c r="E340" s="53"/>
       <c r="F340" s="16" t="s">
         <v>2828</v>
@@ -44693,16 +44678,16 @@
       <c r="AQ340" s="32"/>
     </row>
     <row r="341" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A341" s="365" t="s">
+      <c r="A341" s="364" t="s">
         <v>2837</v>
       </c>
       <c r="B341" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C341" s="340" t="s">
+      <c r="C341" s="339" t="s">
         <v>2838</v>
       </c>
-      <c r="D341" s="312"/>
+      <c r="D341" s="311"/>
       <c r="E341" s="62"/>
       <c r="F341" s="16" t="s">
         <v>2839</v>
@@ -44766,16 +44751,16 @@
       <c r="AQ341" s="32"/>
     </row>
     <row r="342" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A342" s="366" t="s">
-        <v>3951</v>
+      <c r="A342" s="365" t="s">
+        <v>3949</v>
       </c>
       <c r="B342" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C342" s="330" t="s">
+      <c r="C342" s="329" t="s">
         <v>2845</v>
       </c>
-      <c r="D342" s="312"/>
+      <c r="D342" s="311"/>
       <c r="E342" s="62"/>
       <c r="F342" s="48" t="s">
         <v>2846</v>
@@ -44849,10 +44834,10 @@
       <c r="B343" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C343" s="331" t="s">
+      <c r="C343" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D343" s="312"/>
+      <c r="D343" s="311"/>
       <c r="E343" s="62"/>
       <c r="F343" s="16" t="s">
         <v>2855</v>
@@ -44916,16 +44901,16 @@
       <c r="AQ343" s="32"/>
     </row>
     <row r="344" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A344" s="365" t="s">
+      <c r="A344" s="364" t="s">
         <v>2861</v>
       </c>
       <c r="B344" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C344" s="330" t="s">
+      <c r="C344" s="329" t="s">
         <v>2862</v>
       </c>
-      <c r="D344" s="312"/>
+      <c r="D344" s="311"/>
       <c r="E344" s="62"/>
       <c r="F344" s="16" t="s">
         <v>2863</v>
@@ -44995,16 +44980,16 @@
       <c r="AQ344" s="32"/>
     </row>
     <row r="345" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A345" s="366" t="s">
-        <v>3952</v>
+      <c r="A345" s="365" t="s">
+        <v>3950</v>
       </c>
       <c r="B345" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C345" s="330" t="s">
+      <c r="C345" s="329" t="s">
         <v>2871</v>
       </c>
-      <c r="D345" s="312"/>
+      <c r="D345" s="311"/>
       <c r="E345" s="62"/>
       <c r="F345" s="16" t="s">
         <v>2872</v>
@@ -45080,10 +45065,10 @@
       <c r="B346" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C346" s="331" t="s">
+      <c r="C346" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D346" s="312"/>
+      <c r="D346" s="311"/>
       <c r="E346" s="62"/>
       <c r="F346" s="16" t="s">
         <v>2882</v>
@@ -45161,10 +45146,10 @@
       <c r="B347" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C347" s="331" t="s">
+      <c r="C347" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D347" s="312"/>
+      <c r="D347" s="311"/>
       <c r="E347" s="62"/>
       <c r="F347" s="16" t="s">
         <v>2891</v>
@@ -45236,10 +45221,10 @@
       <c r="B348" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C348" s="331" t="s">
+      <c r="C348" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D348" s="327"/>
+      <c r="D348" s="326"/>
       <c r="E348" s="238"/>
       <c r="F348" s="264" t="s">
         <v>2899</v>
@@ -45315,10 +45300,10 @@
       <c r="B349" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C349" s="331" t="s">
+      <c r="C349" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D349" s="312"/>
+      <c r="D349" s="311"/>
       <c r="E349" s="62"/>
       <c r="F349" s="48" t="s">
         <v>2906</v>
@@ -45392,10 +45377,10 @@
       <c r="B350" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C350" s="331" t="s">
+      <c r="C350" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D350" s="325"/>
+      <c r="D350" s="324"/>
       <c r="E350" s="53"/>
       <c r="F350" s="16" t="s">
         <v>2913</v>
@@ -45473,10 +45458,10 @@
       <c r="B351" s="234" t="s">
         <v>2925</v>
       </c>
-      <c r="C351" s="331" t="s">
+      <c r="C351" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D351" s="312"/>
+      <c r="D351" s="311"/>
       <c r="E351" s="62"/>
       <c r="F351" s="48" t="s">
         <v>2926</v>
@@ -45548,10 +45533,10 @@
       <c r="B352" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C352" s="331" t="s">
+      <c r="C352" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D352" s="312"/>
+      <c r="D352" s="311"/>
       <c r="E352" s="62"/>
       <c r="F352" s="48" t="s">
         <v>2932</v>
@@ -45629,10 +45614,10 @@
       <c r="B353" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C353" s="331" t="s">
+      <c r="C353" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D353" s="312"/>
+      <c r="D353" s="311"/>
       <c r="E353" s="62"/>
       <c r="F353" s="48" t="s">
         <v>2939</v>
@@ -45702,10 +45687,10 @@
       <c r="B354" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C354" s="331" t="s">
+      <c r="C354" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D354" s="312"/>
+      <c r="D354" s="311"/>
       <c r="E354" s="62"/>
       <c r="F354" s="48" t="s">
         <v>2946</v>
@@ -45781,10 +45766,10 @@
       <c r="B355" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C355" s="331" t="s">
+      <c r="C355" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D355" s="312"/>
+      <c r="D355" s="311"/>
       <c r="E355" s="62"/>
       <c r="F355" s="48" t="s">
         <v>2954</v>
@@ -45862,10 +45847,10 @@
       <c r="B356" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C356" s="331" t="s">
+      <c r="C356" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D356" s="312"/>
+      <c r="D356" s="311"/>
       <c r="E356" s="62"/>
       <c r="F356" s="48" t="s">
         <v>2962</v>
@@ -45937,16 +45922,16 @@
       <c r="AQ356" s="32"/>
     </row>
     <row r="357" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A357" s="365" t="s">
+      <c r="A357" s="364" t="s">
         <v>2971</v>
       </c>
       <c r="B357" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C357" s="330" t="s">
+      <c r="C357" s="329" t="s">
         <v>2972</v>
       </c>
-      <c r="D357" s="312"/>
+      <c r="D357" s="311"/>
       <c r="E357" s="62"/>
       <c r="F357" s="48" t="s">
         <v>2973</v>
@@ -46020,10 +46005,10 @@
       <c r="B358" s="234" t="s">
         <v>2979</v>
       </c>
-      <c r="C358" s="331" t="s">
+      <c r="C358" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D358" s="312"/>
+      <c r="D358" s="311"/>
       <c r="E358" s="62"/>
       <c r="F358" s="48" t="s">
         <v>2980</v>
@@ -46089,16 +46074,16 @@
       <c r="AQ358" s="32"/>
     </row>
     <row r="359" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A359" s="365" t="s">
+      <c r="A359" s="364" t="s">
         <v>2987</v>
       </c>
       <c r="B359" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C359" s="330" t="s">
+      <c r="C359" s="329" t="s">
         <v>2988</v>
       </c>
-      <c r="D359" s="312"/>
+      <c r="D359" s="311"/>
       <c r="E359" s="62"/>
       <c r="F359" s="48" t="s">
         <v>2989</v>
@@ -46172,10 +46157,10 @@
       <c r="B360" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C360" s="331" t="s">
+      <c r="C360" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D360" s="312"/>
+      <c r="D360" s="311"/>
       <c r="E360" s="62"/>
       <c r="F360" s="48" t="s">
         <v>2997</v>
@@ -46251,10 +46236,10 @@
       <c r="B361" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C361" s="331" t="s">
+      <c r="C361" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D361" s="312"/>
+      <c r="D361" s="311"/>
       <c r="E361" s="62"/>
       <c r="F361" s="32" t="s">
         <v>2311</v>
@@ -46326,10 +46311,10 @@
       <c r="B362" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C362" s="331" t="s">
+      <c r="C362" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D362" s="312"/>
+      <c r="D362" s="311"/>
       <c r="E362" s="62"/>
       <c r="F362" s="16" t="s">
         <v>3014</v>
@@ -46403,10 +46388,10 @@
       <c r="B363" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C363" s="331" t="s">
+      <c r="C363" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D363" s="312"/>
+      <c r="D363" s="311"/>
       <c r="E363" s="62"/>
       <c r="F363" s="48" t="s">
         <v>3023</v>
@@ -46476,10 +46461,10 @@
       <c r="B364" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C364" s="331" t="s">
+      <c r="C364" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D364" s="312"/>
+      <c r="D364" s="311"/>
       <c r="E364" s="62"/>
       <c r="F364" s="16" t="s">
         <v>3028</v>
@@ -46543,10 +46528,10 @@
       <c r="B365" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C365" s="331" t="s">
+      <c r="C365" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D365" s="312"/>
+      <c r="D365" s="311"/>
       <c r="E365" s="62"/>
       <c r="F365" s="48" t="s">
         <v>3034</v>
@@ -46616,16 +46601,16 @@
       <c r="AQ365" s="32"/>
     </row>
     <row r="366" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A366" s="366" t="s">
-        <v>3953</v>
+      <c r="A366" s="365" t="s">
+        <v>3951</v>
       </c>
       <c r="B366" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C366" s="330" t="s">
+      <c r="C366" s="329" t="s">
         <v>3040</v>
       </c>
-      <c r="D366" s="312"/>
+      <c r="D366" s="311"/>
       <c r="E366" s="62"/>
       <c r="F366" s="48" t="s">
         <v>3041</v>
@@ -46697,10 +46682,10 @@
       <c r="B367" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C367" s="331" t="s">
+      <c r="C367" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D367" s="312"/>
+      <c r="D367" s="311"/>
       <c r="E367" s="62"/>
       <c r="F367" s="48" t="s">
         <v>3047</v>
@@ -46778,10 +46763,10 @@
       <c r="B368" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C368" s="331" t="s">
+      <c r="C368" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D368" s="312"/>
+      <c r="D368" s="311"/>
       <c r="E368" s="62"/>
       <c r="F368" s="48" t="s">
         <v>3057</v>
@@ -46851,16 +46836,16 @@
       <c r="AQ368" s="32"/>
     </row>
     <row r="369" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A369" s="370" t="s">
+      <c r="A369" s="369" t="s">
         <v>3066</v>
       </c>
       <c r="B369" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C369" s="330" t="s">
+      <c r="C369" s="329" t="s">
         <v>3067</v>
       </c>
-      <c r="D369" s="312"/>
+      <c r="D369" s="311"/>
       <c r="E369" s="62"/>
       <c r="F369" s="16" t="s">
         <v>3068</v>
@@ -46932,16 +46917,16 @@
       <c r="AQ369" s="32"/>
     </row>
     <row r="370" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A370" s="365" t="s">
+      <c r="A370" s="364" t="s">
         <v>3078</v>
       </c>
       <c r="B370" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C370" s="330" t="s">
+      <c r="C370" s="329" t="s">
         <v>3079</v>
       </c>
-      <c r="D370" s="312"/>
+      <c r="D370" s="311"/>
       <c r="E370" s="62"/>
       <c r="F370" s="48" t="s">
         <v>3080</v>
@@ -47011,16 +46996,16 @@
       <c r="AQ370" s="32"/>
     </row>
     <row r="371" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A371" s="365" t="s">
+      <c r="A371" s="364" t="s">
         <v>3086</v>
       </c>
       <c r="B371" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C371" s="330" t="s">
+      <c r="C371" s="329" t="s">
         <v>3087</v>
       </c>
-      <c r="D371" s="311" t="s">
+      <c r="D371" s="310" t="s">
         <v>3079</v>
       </c>
       <c r="E371" s="62" t="s">
@@ -47090,16 +47075,16 @@
       <c r="AQ371" s="32"/>
     </row>
     <row r="372" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A372" s="365" t="s">
+      <c r="A372" s="364" t="s">
         <v>3094</v>
       </c>
       <c r="B372" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C372" s="330" t="s">
+      <c r="C372" s="329" t="s">
         <v>3095</v>
       </c>
-      <c r="D372" s="312"/>
+      <c r="D372" s="311"/>
       <c r="E372" s="62"/>
       <c r="F372" s="16" t="s">
         <v>3096</v>
@@ -47173,10 +47158,10 @@
       <c r="B373" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C373" s="331" t="s">
+      <c r="C373" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D373" s="312"/>
+      <c r="D373" s="311"/>
       <c r="E373" s="62"/>
       <c r="F373" s="48" t="s">
         <v>3104</v>
@@ -47248,10 +47233,10 @@
       <c r="B374" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C374" s="330" t="s">
+      <c r="C374" s="329" t="s">
         <v>3111</v>
       </c>
-      <c r="D374" s="312"/>
+      <c r="D374" s="311"/>
       <c r="E374" s="62"/>
       <c r="F374" s="48" t="s">
         <v>3112</v>
@@ -47329,10 +47314,10 @@
       <c r="B375" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C375" s="330" t="s">
+      <c r="C375" s="329" t="s">
         <v>3121</v>
       </c>
-      <c r="D375" s="312"/>
+      <c r="D375" s="311"/>
       <c r="E375" s="62"/>
       <c r="F375" s="16" t="s">
         <v>3122</v>
@@ -47404,22 +47389,22 @@
       <c r="AQ375" s="32"/>
     </row>
     <row r="376" spans="1:43" ht="48" customHeight="1">
-      <c r="A376" s="305" t="s">
+      <c r="A376" s="375" t="s">
         <v>3130</v>
       </c>
-      <c r="B376" s="307" t="s">
-        <v>3864</v>
-      </c>
-      <c r="C376" s="346" t="s">
+      <c r="B376" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="C376" s="345" t="s">
         <v>172</v>
       </c>
       <c r="E376" s="301"/>
       <c r="F376" s="304" t="s">
-        <v>3865</v>
+        <v>4009</v>
       </c>
       <c r="G376" s="301"/>
       <c r="H376" s="298" t="s">
-        <v>3866</v>
+        <v>3864</v>
       </c>
       <c r="I376" s="298" t="s">
         <v>3131</v>
@@ -47443,7 +47428,7 @@
         <v>41</v>
       </c>
       <c r="T376" s="298" t="s">
-        <v>3867</v>
+        <v>3865</v>
       </c>
       <c r="U376" s="301"/>
       <c r="V376" s="301"/>
@@ -47455,7 +47440,7 @@
       <c r="AB376" s="301"/>
       <c r="AC376" s="301"/>
       <c r="AD376" s="298" t="s">
-        <v>3868</v>
+        <v>3866</v>
       </c>
       <c r="AE376" s="301"/>
       <c r="AF376" s="301"/>
@@ -47478,10 +47463,10 @@
       <c r="B377" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C377" s="331" t="s">
+      <c r="C377" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D377" s="312"/>
+      <c r="D377" s="311"/>
       <c r="E377" s="62"/>
       <c r="F377" s="16" t="s">
         <v>3133</v>
@@ -47557,10 +47542,10 @@
       <c r="B378" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C378" s="331" t="s">
+      <c r="C378" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D378" s="312"/>
+      <c r="D378" s="311"/>
       <c r="E378" s="62"/>
       <c r="F378" s="48" t="s">
         <v>3141</v>
@@ -47634,10 +47619,10 @@
       <c r="B379" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C379" s="331" t="s">
+      <c r="C379" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D379" s="312"/>
+      <c r="D379" s="311"/>
       <c r="E379" s="62"/>
       <c r="F379" s="48" t="s">
         <v>3149</v>
@@ -47707,16 +47692,16 @@
       <c r="AQ379" s="32"/>
     </row>
     <row r="380" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A380" s="365" t="s">
+      <c r="A380" s="364" t="s">
         <v>3158</v>
       </c>
       <c r="B380" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C380" s="330" t="s">
+      <c r="C380" s="329" t="s">
         <v>3159</v>
       </c>
-      <c r="D380" s="312"/>
+      <c r="D380" s="311"/>
       <c r="E380" s="62"/>
       <c r="F380" s="16" t="s">
         <v>3160</v>
@@ -47796,10 +47781,10 @@
       <c r="B381" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C381" s="331" t="s">
+      <c r="C381" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D381" s="312"/>
+      <c r="D381" s="311"/>
       <c r="E381" s="62"/>
       <c r="F381" s="221" t="s">
         <v>3171</v>
@@ -47867,16 +47852,16 @@
       <c r="AQ381" s="32"/>
     </row>
     <row r="382" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A382" s="365" t="s">
+      <c r="A382" s="364" t="s">
         <v>3177</v>
       </c>
       <c r="B382" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C382" s="330" t="s">
+      <c r="C382" s="329" t="s">
         <v>3178</v>
       </c>
-      <c r="D382" s="312"/>
+      <c r="D382" s="311"/>
       <c r="E382" s="62"/>
       <c r="F382" s="16" t="s">
         <v>3179</v>
@@ -47944,16 +47929,16 @@
       <c r="AQ382" s="32"/>
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A383" s="366" t="s">
-        <v>3954</v>
+      <c r="A383" s="365" t="s">
+        <v>3952</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C383" s="330" t="s">
+      <c r="C383" s="329" t="s">
         <v>3184</v>
       </c>
-      <c r="D383" s="312"/>
+      <c r="D383" s="311"/>
       <c r="E383" s="62"/>
       <c r="F383" s="32" t="s">
         <v>2311</v>
@@ -48013,16 +47998,16 @@
       <c r="AQ383" s="32"/>
     </row>
     <row r="384" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A384" s="366" t="s">
-        <v>3955</v>
+      <c r="A384" s="365" t="s">
+        <v>3953</v>
       </c>
       <c r="B384" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C384" s="330" t="s">
+      <c r="C384" s="329" t="s">
         <v>3184</v>
       </c>
-      <c r="D384" s="312"/>
+      <c r="D384" s="311"/>
       <c r="E384" s="62"/>
       <c r="F384" s="32" t="s">
         <v>2311</v>
@@ -48082,16 +48067,16 @@
       <c r="AQ384" s="32"/>
     </row>
     <row r="385" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A385" s="365" t="s">
+      <c r="A385" s="364" t="s">
         <v>3191</v>
       </c>
       <c r="B385" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C385" s="330" t="s">
+      <c r="C385" s="329" t="s">
         <v>3192</v>
       </c>
-      <c r="D385" s="312"/>
+      <c r="D385" s="311"/>
       <c r="E385" s="62"/>
       <c r="F385" s="16" t="s">
         <v>3193</v>
@@ -48151,16 +48136,16 @@
       <c r="AQ385" s="32"/>
     </row>
     <row r="386" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A386" s="365" t="s">
+      <c r="A386" s="364" t="s">
         <v>3196</v>
       </c>
       <c r="B386" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C386" s="330" t="s">
+      <c r="C386" s="329" t="s">
         <v>3197</v>
       </c>
-      <c r="D386" s="312"/>
+      <c r="D386" s="311"/>
       <c r="E386" s="62"/>
       <c r="F386" s="48" t="s">
         <v>3198</v>
@@ -48226,16 +48211,16 @@
       <c r="AQ386" s="32"/>
     </row>
     <row r="387" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A387" s="366" t="s">
-        <v>3956</v>
+      <c r="A387" s="365" t="s">
+        <v>3954</v>
       </c>
       <c r="B387" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C387" s="344" t="s">
+      <c r="C387" s="343" t="s">
         <v>3206</v>
       </c>
-      <c r="D387" s="312"/>
+      <c r="D387" s="311"/>
       <c r="E387" s="62"/>
       <c r="F387" s="48" t="s">
         <v>3207</v>
@@ -48305,22 +48290,22 @@
       <c r="AQ387" s="32"/>
     </row>
     <row r="388" spans="1:43" ht="45.75" customHeight="1">
-      <c r="A388" s="305" t="s">
+      <c r="A388" s="376" t="s">
         <v>3215</v>
       </c>
       <c r="B388" s="299" t="s">
-        <v>3869</v>
-      </c>
-      <c r="C388" s="346" t="s">
+        <v>3867</v>
+      </c>
+      <c r="C388" s="345" t="s">
         <v>172</v>
       </c>
       <c r="E388" s="301"/>
       <c r="F388" s="304" t="s">
-        <v>3870</v>
+        <v>3868</v>
       </c>
       <c r="G388" s="301"/>
       <c r="H388" s="305" t="s">
-        <v>3871</v>
+        <v>3869</v>
       </c>
       <c r="I388" s="305" t="s">
         <v>3216</v>
@@ -48328,7 +48313,7 @@
       <c r="J388" s="301"/>
       <c r="K388" s="301"/>
       <c r="L388" s="301" t="s">
-        <v>3872</v>
+        <v>3870</v>
       </c>
       <c r="M388" s="306" t="s">
         <v>2100</v>
@@ -48346,7 +48331,7 @@
         <v>41</v>
       </c>
       <c r="T388" s="298" t="s">
-        <v>3873</v>
+        <v>3871</v>
       </c>
       <c r="U388" s="301"/>
       <c r="V388" s="301"/>
@@ -48358,7 +48343,7 @@
       <c r="AB388" s="301"/>
       <c r="AC388" s="301"/>
       <c r="AD388" s="298" t="s">
-        <v>3874</v>
+        <v>3872</v>
       </c>
       <c r="AE388" s="301"/>
       <c r="AF388" s="301"/>
@@ -48381,10 +48366,10 @@
       <c r="B389" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C389" s="336" t="s">
+      <c r="C389" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D389" s="312"/>
+      <c r="D389" s="311"/>
       <c r="E389" s="62"/>
       <c r="F389" s="48" t="s">
         <v>3218</v>
@@ -48454,10 +48439,10 @@
       <c r="B390" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C390" s="336" t="s">
+      <c r="C390" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D390" s="312"/>
+      <c r="D390" s="311"/>
       <c r="E390" s="62"/>
       <c r="F390" s="16" t="s">
         <v>3226</v>
@@ -48539,10 +48524,10 @@
       <c r="B391" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C391" s="331" t="s">
+      <c r="C391" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D391" s="312"/>
+      <c r="D391" s="311"/>
       <c r="E391" s="62"/>
       <c r="F391" s="16" t="s">
         <v>3236</v>
@@ -48614,10 +48599,10 @@
       <c r="B392" s="142" t="s">
         <v>439</v>
       </c>
-      <c r="C392" s="338" t="s">
+      <c r="C392" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D392" s="318"/>
+      <c r="D392" s="317"/>
       <c r="E392" s="166"/>
       <c r="F392" s="61" t="s">
         <v>3243</v>
@@ -48691,10 +48676,10 @@
       <c r="B393" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C393" s="331" t="s">
+      <c r="C393" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D393" s="312"/>
+      <c r="D393" s="311"/>
       <c r="E393" s="62"/>
       <c r="F393" s="48" t="s">
         <v>3250</v>
@@ -48768,10 +48753,10 @@
       <c r="B394" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C394" s="331" t="s">
+      <c r="C394" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D394" s="325"/>
+      <c r="D394" s="324"/>
       <c r="E394" s="53"/>
       <c r="F394" s="16" t="s">
         <v>3256</v>
@@ -48833,16 +48818,16 @@
       <c r="AQ394" s="32"/>
     </row>
     <row r="395" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A395" s="365" t="s">
+      <c r="A395" s="364" t="s">
         <v>3262</v>
       </c>
       <c r="B395" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C395" s="332" t="s">
+      <c r="C395" s="331" t="s">
         <v>3262</v>
       </c>
-      <c r="D395" s="312"/>
+      <c r="D395" s="311"/>
       <c r="E395" s="62"/>
       <c r="F395" s="16" t="s">
         <v>3263</v>
@@ -48918,10 +48903,10 @@
       <c r="B396" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C396" s="331" t="s">
+      <c r="C396" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D396" s="312"/>
+      <c r="D396" s="311"/>
       <c r="E396" s="62"/>
       <c r="F396" s="16" t="s">
         <v>3271</v>
@@ -48999,10 +48984,10 @@
       <c r="B397" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C397" s="331" t="s">
+      <c r="C397" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D397" s="312"/>
+      <c r="D397" s="311"/>
       <c r="E397" s="62"/>
       <c r="F397" s="16" t="s">
         <v>3283</v>
@@ -49064,10 +49049,10 @@
       <c r="B398" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C398" s="331" t="s">
+      <c r="C398" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D398" s="312"/>
+      <c r="D398" s="311"/>
       <c r="E398" s="62"/>
       <c r="F398" s="48" t="s">
         <v>3287</v>
@@ -49131,10 +49116,10 @@
       <c r="B399" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C399" s="331" t="s">
+      <c r="C399" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D399" s="312"/>
+      <c r="D399" s="311"/>
       <c r="E399" s="62"/>
       <c r="F399" s="16" t="s">
         <v>3294</v>
@@ -49210,10 +49195,10 @@
       <c r="B400" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C400" s="331" t="s">
+      <c r="C400" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D400" s="312"/>
+      <c r="D400" s="311"/>
       <c r="E400" s="62"/>
       <c r="F400" s="16" t="s">
         <v>3303</v>
@@ -49283,10 +49268,10 @@
       <c r="B401" s="49" t="s">
         <v>3310</v>
       </c>
-      <c r="C401" s="331" t="s">
+      <c r="C401" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D401" s="312"/>
+      <c r="D401" s="311"/>
       <c r="E401" s="62"/>
       <c r="F401" s="16" t="s">
         <v>3311</v>
@@ -49360,10 +49345,10 @@
       <c r="B402" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C402" s="331" t="s">
+      <c r="C402" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D402" s="312"/>
+      <c r="D402" s="311"/>
       <c r="E402" s="62"/>
       <c r="F402" s="16" t="s">
         <v>3318</v>
@@ -49441,10 +49426,10 @@
       <c r="B403" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C403" s="331" t="s">
+      <c r="C403" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D403" s="312"/>
+      <c r="D403" s="311"/>
       <c r="E403" s="62"/>
       <c r="F403" s="48" t="s">
         <v>3329</v>
@@ -49522,10 +49507,10 @@
       <c r="B404" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C404" s="331" t="s">
+      <c r="C404" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D404" s="312"/>
+      <c r="D404" s="311"/>
       <c r="E404" s="62"/>
       <c r="F404" s="16" t="s">
         <v>3339</v>
@@ -49603,10 +49588,10 @@
       <c r="B405" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C405" s="331" t="s">
+      <c r="C405" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D405" s="312"/>
+      <c r="D405" s="311"/>
       <c r="E405" s="62"/>
       <c r="F405" s="48" t="s">
         <v>3346</v>
@@ -49684,10 +49669,10 @@
       <c r="B406" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C406" s="331" t="s">
+      <c r="C406" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D406" s="312"/>
+      <c r="D406" s="311"/>
       <c r="E406" s="62"/>
       <c r="F406" s="48" t="s">
         <v>3354</v>
@@ -49761,10 +49746,10 @@
       <c r="B407" s="32" t="s">
         <v>3360</v>
       </c>
-      <c r="C407" s="331" t="s">
+      <c r="C407" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D407" s="327"/>
+      <c r="D407" s="326"/>
       <c r="E407" s="238"/>
       <c r="F407" s="239" t="s">
         <v>3361</v>
@@ -49826,16 +49811,16 @@
       <c r="AQ407" s="32"/>
     </row>
     <row r="408" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A408" s="366" t="s">
-        <v>3958</v>
+      <c r="A408" s="365" t="s">
+        <v>3956</v>
       </c>
       <c r="B408" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C408" s="332" t="s">
-        <v>3957</v>
-      </c>
-      <c r="D408" s="327"/>
+      <c r="C408" s="331" t="s">
+        <v>3955</v>
+      </c>
+      <c r="D408" s="326"/>
       <c r="E408" s="238"/>
       <c r="F408" s="264" t="s">
         <v>3368</v>
@@ -49899,16 +49884,16 @@
       <c r="AQ408" s="32"/>
     </row>
     <row r="409" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A409" s="371" t="s">
-        <v>3959</v>
+      <c r="A409" s="370" t="s">
+        <v>3957</v>
       </c>
       <c r="B409" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C409" s="330" t="s">
+      <c r="C409" s="329" t="s">
         <v>3375</v>
       </c>
-      <c r="D409" s="312"/>
+      <c r="D409" s="311"/>
       <c r="E409" s="62"/>
       <c r="F409" s="48" t="s">
         <v>3376</v>
@@ -49980,10 +49965,10 @@
       <c r="B410" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C410" s="331" t="s">
+      <c r="C410" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D410" s="312"/>
+      <c r="D410" s="311"/>
       <c r="E410" s="62"/>
       <c r="F410" s="48" t="s">
         <v>3384</v>
@@ -50055,10 +50040,10 @@
       <c r="B411" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C411" s="331" t="s">
+      <c r="C411" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D411" s="312"/>
+      <c r="D411" s="311"/>
       <c r="E411" s="62"/>
       <c r="F411" s="48" t="s">
         <v>3390</v>
@@ -50128,10 +50113,10 @@
       <c r="B412" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C412" s="331" t="s">
+      <c r="C412" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D412" s="312"/>
+      <c r="D412" s="311"/>
       <c r="E412" s="62"/>
       <c r="F412" s="16" t="s">
         <v>3397</v>
@@ -50205,10 +50190,10 @@
       <c r="B413" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C413" s="338" t="s">
+      <c r="C413" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D413" s="312"/>
+      <c r="D413" s="311"/>
       <c r="E413" s="62"/>
       <c r="F413" s="48" t="s">
         <v>3404</v>
@@ -50274,16 +50259,16 @@
       <c r="AQ413" s="32"/>
     </row>
     <row r="414" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A414" s="371" t="s">
-        <v>3960</v>
+      <c r="A414" s="370" t="s">
+        <v>3958</v>
       </c>
       <c r="B414" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C414" s="334" t="s">
+      <c r="C414" s="333" t="s">
         <v>3410</v>
       </c>
-      <c r="D414" s="327"/>
+      <c r="D414" s="326"/>
       <c r="E414" s="238"/>
       <c r="F414" s="239" t="s">
         <v>3411</v>
@@ -50355,10 +50340,10 @@
       <c r="B415" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C415" s="338" t="s">
+      <c r="C415" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D415" s="312"/>
+      <c r="D415" s="311"/>
       <c r="E415" s="62"/>
       <c r="F415" s="48" t="s">
         <v>3417</v>
@@ -50434,10 +50419,10 @@
       <c r="B416" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C416" s="338" t="s">
+      <c r="C416" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D416" s="312"/>
+      <c r="D416" s="311"/>
       <c r="E416" s="62"/>
       <c r="F416" s="48" t="s">
         <v>3424</v>
@@ -50501,10 +50486,10 @@
       <c r="B417" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C417" s="338" t="s">
+      <c r="C417" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D417" s="312"/>
+      <c r="D417" s="311"/>
       <c r="E417" s="62"/>
       <c r="F417" s="48" t="s">
         <v>3430</v>
@@ -50570,10 +50555,10 @@
       <c r="B418" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C418" s="338" t="s">
+      <c r="C418" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D418" s="312"/>
+      <c r="D418" s="311"/>
       <c r="E418" s="62"/>
       <c r="F418" s="48" t="s">
         <v>3436</v>
@@ -50639,10 +50624,10 @@
       <c r="B419" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C419" s="338" t="s">
+      <c r="C419" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D419" s="327"/>
+      <c r="D419" s="326"/>
       <c r="E419" s="238"/>
       <c r="F419" s="239" t="s">
         <v>3443</v>
@@ -50714,10 +50699,10 @@
       <c r="B420" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C420" s="338" t="s">
+      <c r="C420" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D420" s="327"/>
+      <c r="D420" s="326"/>
       <c r="E420" s="62"/>
       <c r="F420" s="16" t="s">
         <v>3449</v>
@@ -50793,10 +50778,10 @@
       <c r="B421" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C421" s="338" t="s">
+      <c r="C421" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D421" s="327"/>
+      <c r="D421" s="326"/>
       <c r="E421" s="238"/>
       <c r="F421" s="239" t="s">
         <v>3458</v>
@@ -50876,10 +50861,10 @@
       <c r="B422" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C422" s="338" t="s">
+      <c r="C422" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D422" s="327"/>
+      <c r="D422" s="326"/>
       <c r="E422" s="238"/>
       <c r="F422" s="239" t="s">
         <v>3469</v>
@@ -50957,10 +50942,10 @@
       <c r="B423" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C423" s="338" t="s">
+      <c r="C423" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D423" s="312"/>
+      <c r="D423" s="311"/>
       <c r="E423" s="62"/>
       <c r="F423" s="16" t="s">
         <v>3478</v>
@@ -51022,16 +51007,16 @@
       <c r="AQ423" s="32"/>
     </row>
     <row r="424" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A424" s="371" t="s">
-        <v>3961</v>
+      <c r="A424" s="370" t="s">
+        <v>3959</v>
       </c>
       <c r="B424" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C424" s="341" t="s">
+      <c r="C424" s="340" t="s">
         <v>3482</v>
       </c>
-      <c r="D424" s="312"/>
+      <c r="D424" s="311"/>
       <c r="E424" s="62"/>
       <c r="F424" s="16" t="s">
         <v>3483</v>
@@ -51105,10 +51090,10 @@
       <c r="B425" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C425" s="331" t="s">
+      <c r="C425" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D425" s="312"/>
+      <c r="D425" s="311"/>
       <c r="E425" s="62"/>
       <c r="F425" s="48" t="s">
         <v>3491</v>
@@ -51170,10 +51155,10 @@
       <c r="B426" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C426" s="331" t="s">
+      <c r="C426" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D426" s="312"/>
+      <c r="D426" s="311"/>
       <c r="E426" s="62"/>
       <c r="F426" s="16" t="s">
         <v>3494</v>
@@ -51237,10 +51222,10 @@
       <c r="B427" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C427" s="331" t="s">
+      <c r="C427" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D427" s="312"/>
+      <c r="D427" s="311"/>
       <c r="E427" s="62"/>
       <c r="F427" s="48" t="s">
         <v>3497</v>
@@ -51310,10 +51295,10 @@
       <c r="B428" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C428" s="331" t="s">
+      <c r="C428" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D428" s="312"/>
+      <c r="D428" s="311"/>
       <c r="E428" s="62"/>
       <c r="F428" s="48" t="s">
         <v>3503</v>
@@ -51383,10 +51368,10 @@
       <c r="B429" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C429" s="331" t="s">
+      <c r="C429" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D429" s="312"/>
+      <c r="D429" s="311"/>
       <c r="E429" s="62"/>
       <c r="F429" s="48" t="s">
         <v>3506</v>
@@ -51448,10 +51433,10 @@
       <c r="B430" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C430" s="331" t="s">
+      <c r="C430" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D430" s="312"/>
+      <c r="D430" s="311"/>
       <c r="E430" s="62"/>
       <c r="F430" s="48" t="s">
         <v>3510</v>
@@ -51513,10 +51498,10 @@
       <c r="B431" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C431" s="332" t="s">
+      <c r="C431" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D431" s="312"/>
+      <c r="D431" s="311"/>
       <c r="E431" s="62"/>
       <c r="F431" s="16" t="s">
         <v>3513</v>
@@ -51580,10 +51565,10 @@
       <c r="B432" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C432" s="338" t="s">
+      <c r="C432" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D432" s="312"/>
+      <c r="D432" s="311"/>
       <c r="E432" s="62"/>
       <c r="F432" s="48" t="s">
         <v>3520</v>
@@ -51657,10 +51642,10 @@
       <c r="B433" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C433" s="338" t="s">
+      <c r="C433" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D433" s="312"/>
+      <c r="D433" s="311"/>
       <c r="E433" s="62"/>
       <c r="F433" s="48" t="s">
         <v>3527</v>
@@ -51728,10 +51713,10 @@
       <c r="B434" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C434" s="338" t="s">
+      <c r="C434" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D434" s="312"/>
+      <c r="D434" s="311"/>
       <c r="E434" s="62"/>
       <c r="F434" s="16" t="s">
         <v>3532</v>
@@ -51793,10 +51778,10 @@
       <c r="B435" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C435" s="338" t="s">
+      <c r="C435" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D435" s="312"/>
+      <c r="D435" s="311"/>
       <c r="E435" s="62"/>
       <c r="F435" s="48" t="s">
         <v>3536</v>
@@ -51854,16 +51839,16 @@
       <c r="AQ435" s="32"/>
     </row>
     <row r="436" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A436" s="365" t="s">
+      <c r="A436" s="364" t="s">
         <v>3539</v>
       </c>
       <c r="B436" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C436" s="342" t="s">
+      <c r="C436" s="341" t="s">
         <v>3539</v>
       </c>
-      <c r="D436" s="312"/>
+      <c r="D436" s="311"/>
       <c r="E436" s="62"/>
       <c r="F436" s="48" t="s">
         <v>3540</v>
@@ -51939,10 +51924,10 @@
       <c r="B437" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C437" s="331" t="s">
+      <c r="C437" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D437" s="312"/>
+      <c r="D437" s="311"/>
       <c r="E437" s="62"/>
       <c r="F437" s="48" t="s">
         <v>3549</v>
@@ -52012,10 +51997,10 @@
       <c r="B438" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C438" s="332" t="s">
+      <c r="C438" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D438" s="312"/>
+      <c r="D438" s="311"/>
       <c r="E438" s="62"/>
       <c r="F438" s="16" t="s">
         <v>3554</v>
@@ -52087,10 +52072,10 @@
       <c r="B439" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C439" s="331" t="s">
+      <c r="C439" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D439" s="312"/>
+      <c r="D439" s="311"/>
       <c r="E439" s="62"/>
       <c r="F439" s="16" t="s">
         <v>3562</v>
@@ -52162,10 +52147,10 @@
       <c r="B440" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C440" s="331" t="s">
+      <c r="C440" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D440" s="312"/>
+      <c r="D440" s="311"/>
       <c r="E440" s="62"/>
       <c r="F440" s="16" t="s">
         <v>3565</v>
@@ -52241,10 +52226,10 @@
       <c r="B441" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C441" s="338" t="s">
+      <c r="C441" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D441" s="312"/>
+      <c r="D441" s="311"/>
       <c r="E441" s="62"/>
       <c r="F441" s="48" t="s">
         <v>3574</v>
@@ -52322,10 +52307,10 @@
       <c r="B442" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C442" s="338" t="s">
+      <c r="C442" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D442" s="312"/>
+      <c r="D442" s="311"/>
       <c r="E442" s="62"/>
       <c r="F442" s="48" t="s">
         <v>3584</v>
@@ -52395,10 +52380,10 @@
       <c r="B443" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C443" s="338" t="s">
+      <c r="C443" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D443" s="312"/>
+      <c r="D443" s="311"/>
       <c r="E443" s="62"/>
       <c r="F443" s="16" t="s">
         <v>3590</v>
@@ -52464,10 +52449,10 @@
       <c r="B444" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C444" s="332" t="s">
+      <c r="C444" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D444" s="327"/>
+      <c r="D444" s="326"/>
       <c r="E444" s="238"/>
       <c r="F444" s="239" t="s">
         <v>3595</v>
@@ -52545,10 +52530,10 @@
       <c r="B445" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C445" s="332" t="s">
+      <c r="C445" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D445" s="327"/>
+      <c r="D445" s="326"/>
       <c r="E445" s="238"/>
       <c r="F445" s="239" t="s">
         <v>3603</v>
@@ -52626,10 +52611,10 @@
       <c r="B446" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C446" s="338" t="s">
+      <c r="C446" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D446" s="312"/>
+      <c r="D446" s="311"/>
       <c r="E446" s="62"/>
       <c r="F446" s="48" t="s">
         <v>3611</v>
@@ -52699,10 +52684,10 @@
       <c r="B447" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C447" s="331" t="s">
+      <c r="C447" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D447" s="312"/>
+      <c r="D447" s="311"/>
       <c r="E447" s="62"/>
       <c r="F447" s="48" t="s">
         <v>3617</v>
@@ -52766,10 +52751,10 @@
       <c r="B448" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C448" s="331" t="s">
+      <c r="C448" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D448" s="312"/>
+      <c r="D448" s="311"/>
       <c r="E448" s="62"/>
       <c r="F448" s="48" t="s">
         <v>3622</v>
@@ -52839,10 +52824,10 @@
       <c r="B449" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C449" s="338" t="s">
+      <c r="C449" s="337" t="s">
         <v>172</v>
       </c>
-      <c r="D449" s="312"/>
+      <c r="D449" s="311"/>
       <c r="E449" s="62"/>
       <c r="F449" s="48" t="s">
         <v>3628</v>
@@ -52912,10 +52897,10 @@
       <c r="B450" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C450" s="332" t="s">
+      <c r="C450" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D450" s="312"/>
+      <c r="D450" s="311"/>
       <c r="E450" s="62"/>
       <c r="F450" s="48" t="s">
         <v>3632</v>
@@ -52993,10 +52978,10 @@
       <c r="B451" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C451" s="331" t="s">
+      <c r="C451" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D451" s="312"/>
+      <c r="D451" s="311"/>
       <c r="E451" s="62"/>
       <c r="F451" s="48" t="s">
         <v>3638</v>
@@ -53058,10 +53043,10 @@
       <c r="B452" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C452" s="331" t="s">
+      <c r="C452" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D452" s="312"/>
+      <c r="D452" s="311"/>
       <c r="E452" s="62"/>
       <c r="F452" s="48" t="s">
         <v>3643</v>
@@ -53131,10 +53116,10 @@
       <c r="B453" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C453" s="331" t="s">
+      <c r="C453" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D453" s="312"/>
+      <c r="D453" s="311"/>
       <c r="E453" s="62"/>
       <c r="F453" s="48" t="s">
         <v>3652</v>
@@ -53204,10 +53189,10 @@
       <c r="B454" s="108" t="s">
         <v>439</v>
       </c>
-      <c r="C454" s="336" t="s">
+      <c r="C454" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D454" s="312"/>
+      <c r="D454" s="311"/>
       <c r="E454" s="62"/>
       <c r="F454" s="48" t="s">
         <v>3657</v>
@@ -53277,10 +53262,10 @@
       <c r="B455" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C455" s="331" t="s">
+      <c r="C455" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D455" s="312"/>
+      <c r="D455" s="311"/>
       <c r="E455" s="62"/>
       <c r="F455" s="48" t="s">
         <v>3664</v>
@@ -53356,10 +53341,10 @@
       <c r="B456" s="32" t="s">
         <v>439</v>
       </c>
-      <c r="C456" s="331" t="s">
+      <c r="C456" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D456" s="312"/>
+      <c r="D456" s="311"/>
       <c r="E456" s="62"/>
       <c r="F456" s="48" t="s">
         <v>3671</v>
@@ -53437,10 +53422,10 @@
       <c r="B457" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C457" s="331" t="s">
+      <c r="C457" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D457" s="312"/>
+      <c r="D457" s="311"/>
       <c r="E457" s="62"/>
       <c r="F457" s="16" t="s">
         <v>3678</v>
@@ -53518,10 +53503,10 @@
       <c r="B458" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C458" s="331" t="s">
+      <c r="C458" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D458" s="313"/>
+      <c r="D458" s="312"/>
       <c r="E458" s="72"/>
       <c r="F458" s="16" t="s">
         <v>3684</v>
@@ -53587,10 +53572,10 @@
       <c r="B459" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C459" s="336" t="s">
+      <c r="C459" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="D459" s="312"/>
+      <c r="D459" s="311"/>
       <c r="E459" s="62"/>
       <c r="F459" s="16" t="s">
         <v>3690</v>
@@ -53660,16 +53645,16 @@
       <c r="AQ459" s="32"/>
     </row>
     <row r="460" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A460" s="371" t="s">
-        <v>3962</v>
+      <c r="A460" s="370" t="s">
+        <v>3960</v>
       </c>
       <c r="B460" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C460" s="330" t="s">
+      <c r="C460" s="329" t="s">
         <v>3697</v>
       </c>
-      <c r="D460" s="312"/>
+      <c r="D460" s="311"/>
       <c r="E460" s="62"/>
       <c r="F460" s="48" t="s">
         <v>3698</v>
@@ -53741,10 +53726,10 @@
       <c r="B461" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C461" s="331" t="s">
+      <c r="C461" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D461" s="312"/>
+      <c r="D461" s="311"/>
       <c r="E461" s="62"/>
       <c r="F461" s="48" t="s">
         <v>3707</v>
@@ -53822,10 +53807,10 @@
       <c r="B462" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C462" s="331" t="s">
+      <c r="C462" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D462" s="313"/>
+      <c r="D462" s="312"/>
       <c r="E462" s="72"/>
       <c r="F462" s="16" t="s">
         <v>3713</v>
@@ -53897,10 +53882,10 @@
       <c r="B463" s="108" t="s">
         <v>3718</v>
       </c>
-      <c r="C463" s="331" t="s">
+      <c r="C463" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D463" s="312"/>
+      <c r="D463" s="311"/>
       <c r="E463" s="62"/>
       <c r="F463" s="49" t="s">
         <v>3719</v>
@@ -53960,16 +53945,16 @@
       <c r="AQ463" s="32"/>
     </row>
     <row r="464" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A464" s="371" t="s">
-        <v>3963</v>
+      <c r="A464" s="370" t="s">
+        <v>3961</v>
       </c>
       <c r="B464" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C464" s="330" t="s">
+      <c r="C464" s="329" t="s">
         <v>3724</v>
       </c>
-      <c r="D464" s="312"/>
+      <c r="D464" s="311"/>
       <c r="E464" s="62"/>
       <c r="F464" s="48" t="s">
         <v>3725</v>
@@ -54043,10 +54028,10 @@
       <c r="B465" s="108" t="s">
         <v>439</v>
       </c>
-      <c r="C465" s="331" t="s">
+      <c r="C465" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D465" s="312"/>
+      <c r="D465" s="311"/>
       <c r="E465" s="62"/>
       <c r="F465" s="48" t="s">
         <v>3736</v>
@@ -54114,16 +54099,16 @@
       <c r="AQ465" s="32"/>
     </row>
     <row r="466" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A466" s="372" t="s">
-        <v>3964</v>
+      <c r="A466" s="371" t="s">
+        <v>3962</v>
       </c>
       <c r="B466" s="108" t="s">
         <v>439</v>
       </c>
-      <c r="C466" s="340" t="s">
+      <c r="C466" s="339" t="s">
         <v>3742</v>
       </c>
-      <c r="D466" s="311" t="s">
+      <c r="D466" s="310" t="s">
         <v>3743</v>
       </c>
       <c r="E466" s="62" t="s">
@@ -54195,10 +54180,10 @@
       <c r="B467" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C467" s="331" t="s">
+      <c r="C467" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D467" s="313"/>
+      <c r="D467" s="312"/>
       <c r="E467" s="72"/>
       <c r="F467" s="16" t="s">
         <v>3753</v>
@@ -54270,10 +54255,10 @@
       <c r="B468" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C468" s="331" t="s">
+      <c r="C468" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D468" s="312"/>
+      <c r="D468" s="311"/>
       <c r="E468" s="62"/>
       <c r="F468" s="48" t="s">
         <v>3759</v>
@@ -54345,10 +54330,10 @@
       <c r="B469" s="108" t="s">
         <v>439</v>
       </c>
-      <c r="C469" s="331" t="s">
+      <c r="C469" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D469" s="313"/>
+      <c r="D469" s="312"/>
       <c r="E469" s="72"/>
       <c r="F469" s="16" t="s">
         <v>3770</v>
@@ -54416,10 +54401,10 @@
       <c r="B470" s="108" t="s">
         <v>439</v>
       </c>
-      <c r="C470" s="331" t="s">
+      <c r="C470" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D470" s="312"/>
+      <c r="D470" s="311"/>
       <c r="E470" s="62"/>
       <c r="F470" s="48" t="s">
         <v>3777</v>
@@ -54491,10 +54476,10 @@
       <c r="B471" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C471" s="331" t="s">
+      <c r="C471" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D471" s="312"/>
+      <c r="D471" s="311"/>
       <c r="E471" s="62"/>
       <c r="F471" s="16" t="s">
         <v>3786</v>
@@ -54558,10 +54543,10 @@
       <c r="B472" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C472" s="331" t="s">
+      <c r="C472" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D472" s="313"/>
+      <c r="D472" s="312"/>
       <c r="E472" s="72"/>
       <c r="F472" s="61" t="s">
         <v>3793</v>
@@ -54627,10 +54612,10 @@
       <c r="B473" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C473" s="331" t="s">
+      <c r="C473" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D473" s="312"/>
+      <c r="D473" s="311"/>
       <c r="E473" s="62"/>
       <c r="F473" s="16" t="s">
         <v>3798</v>
@@ -54702,10 +54687,10 @@
       <c r="B474" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C474" s="331" t="s">
+      <c r="C474" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D474" s="312"/>
+      <c r="D474" s="311"/>
       <c r="E474" s="62"/>
       <c r="F474" s="48" t="s">
         <v>3804</v>
@@ -54775,16 +54760,16 @@
       <c r="AQ474" s="32"/>
     </row>
     <row r="475" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A475" s="365" t="s">
+      <c r="A475" s="364" t="s">
         <v>3812</v>
       </c>
       <c r="B475" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C475" s="340" t="s">
+      <c r="C475" s="339" t="s">
         <v>3813</v>
       </c>
-      <c r="D475" s="312"/>
+      <c r="D475" s="311"/>
       <c r="E475" s="62"/>
       <c r="F475" s="16" t="s">
         <v>3814</v>
@@ -54862,10 +54847,10 @@
       <c r="B476" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C476" s="331" t="s">
+      <c r="C476" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D476" s="313"/>
+      <c r="D476" s="312"/>
       <c r="E476" s="62"/>
       <c r="F476" s="48" t="s">
         <v>3824</v>
@@ -54941,10 +54926,10 @@
       <c r="B477" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C477" s="331" t="s">
+      <c r="C477" s="330" t="s">
         <v>172</v>
       </c>
-      <c r="D477" s="313"/>
+      <c r="D477" s="312"/>
       <c r="E477" s="62"/>
       <c r="F477" s="61" t="s">
         <v>3832</v>
@@ -55012,16 +54997,16 @@
       <c r="AQ477" s="32"/>
     </row>
     <row r="478" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A478" s="365" t="s">
+      <c r="A478" s="364" t="s">
         <v>3839</v>
       </c>
       <c r="B478" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C478" s="330" t="s">
+      <c r="C478" s="329" t="s">
         <v>3840</v>
       </c>
-      <c r="D478" s="312"/>
+      <c r="D478" s="311"/>
       <c r="E478" s="166"/>
       <c r="F478" s="48" t="s">
         <v>3841</v>
@@ -55087,10 +55072,10 @@
       <c r="B479" s="108" t="s">
         <v>2310</v>
       </c>
-      <c r="C479" s="332" t="s">
+      <c r="C479" s="331" t="s">
         <v>144</v>
       </c>
-      <c r="D479" s="313"/>
+      <c r="D479" s="312"/>
       <c r="E479" s="62"/>
       <c r="F479" s="48" t="s">
         <v>3848</v>
@@ -55154,8 +55139,8 @@
     <row r="480" spans="1:43" ht="15.75" customHeight="1">
       <c r="A480" s="115"/>
       <c r="B480" s="115"/>
-      <c r="C480" s="348"/>
-      <c r="D480" s="312"/>
+      <c r="C480" s="347"/>
+      <c r="D480" s="311"/>
       <c r="E480" s="292"/>
       <c r="F480" s="115"/>
       <c r="G480" s="115"/>
@@ -55199,8 +55184,8 @@
     <row r="481" spans="1:43" ht="15.75" customHeight="1">
       <c r="A481" s="115"/>
       <c r="B481" s="115"/>
-      <c r="C481" s="348"/>
-      <c r="D481" s="312"/>
+      <c r="C481" s="347"/>
+      <c r="D481" s="311"/>
       <c r="E481" s="292"/>
       <c r="F481" s="115"/>
       <c r="G481" s="115"/>
@@ -55244,8 +55229,8 @@
     <row r="482" spans="1:43" ht="15.75" customHeight="1">
       <c r="A482" s="115"/>
       <c r="B482" s="115"/>
-      <c r="C482" s="348"/>
-      <c r="D482" s="312"/>
+      <c r="C482" s="347"/>
+      <c r="D482" s="311"/>
       <c r="E482" s="292"/>
       <c r="F482" s="115"/>
       <c r="G482" s="115"/>
@@ -55289,8 +55274,8 @@
     <row r="483" spans="1:43" ht="15.75" customHeight="1">
       <c r="A483" s="115"/>
       <c r="B483" s="115"/>
-      <c r="C483" s="348"/>
-      <c r="D483" s="312"/>
+      <c r="C483" s="347"/>
+      <c r="D483" s="311"/>
       <c r="E483" s="292"/>
       <c r="F483" s="115"/>
       <c r="G483" s="115"/>
@@ -55334,8 +55319,8 @@
     <row r="484" spans="1:43" ht="15.75" customHeight="1">
       <c r="A484" s="115"/>
       <c r="B484" s="115"/>
-      <c r="C484" s="348"/>
-      <c r="D484" s="312"/>
+      <c r="C484" s="347"/>
+      <c r="D484" s="311"/>
       <c r="E484" s="292"/>
       <c r="F484" s="115"/>
       <c r="G484" s="115"/>
@@ -55379,8 +55364,8 @@
     <row r="485" spans="1:43" ht="15.75" customHeight="1">
       <c r="A485" s="115"/>
       <c r="B485" s="115"/>
-      <c r="C485" s="348"/>
-      <c r="D485" s="312"/>
+      <c r="C485" s="347"/>
+      <c r="D485" s="311"/>
       <c r="E485" s="292"/>
       <c r="F485" s="115"/>
       <c r="G485" s="115"/>
@@ -55424,8 +55409,8 @@
     <row r="486" spans="1:43" ht="15.75" customHeight="1">
       <c r="A486" s="115"/>
       <c r="B486" s="115"/>
-      <c r="C486" s="348"/>
-      <c r="D486" s="312"/>
+      <c r="C486" s="347"/>
+      <c r="D486" s="311"/>
       <c r="E486" s="292"/>
       <c r="F486" s="115"/>
       <c r="G486" s="115"/>
@@ -55469,8 +55454,8 @@
     <row r="487" spans="1:43" ht="15.75" customHeight="1">
       <c r="A487" s="115"/>
       <c r="B487" s="115"/>
-      <c r="C487" s="348"/>
-      <c r="D487" s="312"/>
+      <c r="C487" s="347"/>
+      <c r="D487" s="311"/>
       <c r="E487" s="292"/>
       <c r="F487" s="115"/>
       <c r="G487" s="115"/>
@@ -55514,8 +55499,8 @@
     <row r="488" spans="1:43" ht="15.75" customHeight="1">
       <c r="A488" s="115"/>
       <c r="B488" s="115"/>
-      <c r="C488" s="348"/>
-      <c r="D488" s="312"/>
+      <c r="C488" s="347"/>
+      <c r="D488" s="311"/>
       <c r="E488" s="292"/>
       <c r="F488" s="115"/>
       <c r="G488" s="115"/>
@@ -55559,8 +55544,8 @@
     <row r="489" spans="1:43" ht="15.75" customHeight="1">
       <c r="A489" s="115"/>
       <c r="B489" s="115"/>
-      <c r="C489" s="348"/>
-      <c r="D489" s="312"/>
+      <c r="C489" s="347"/>
+      <c r="D489" s="311"/>
       <c r="E489" s="292"/>
       <c r="F489" s="115"/>
       <c r="G489" s="115"/>
@@ -55604,8 +55589,8 @@
     <row r="490" spans="1:43" ht="15.75" customHeight="1">
       <c r="A490" s="115"/>
       <c r="B490" s="115"/>
-      <c r="C490" s="348"/>
-      <c r="D490" s="312"/>
+      <c r="C490" s="347"/>
+      <c r="D490" s="311"/>
       <c r="E490" s="292"/>
       <c r="F490" s="115"/>
       <c r="G490" s="115"/>
@@ -55649,8 +55634,8 @@
     <row r="491" spans="1:43" ht="15.75" customHeight="1">
       <c r="A491" s="115"/>
       <c r="B491" s="115"/>
-      <c r="C491" s="348"/>
-      <c r="D491" s="312"/>
+      <c r="C491" s="347"/>
+      <c r="D491" s="311"/>
       <c r="E491" s="292"/>
       <c r="F491" s="115"/>
       <c r="G491" s="115"/>
@@ -55694,8 +55679,8 @@
     <row r="492" spans="1:43" ht="15.75" customHeight="1">
       <c r="A492" s="115"/>
       <c r="B492" s="115"/>
-      <c r="C492" s="348"/>
-      <c r="D492" s="312"/>
+      <c r="C492" s="347"/>
+      <c r="D492" s="311"/>
       <c r="E492" s="292"/>
       <c r="F492" s="115"/>
       <c r="G492" s="115"/>
@@ -55739,8 +55724,8 @@
     <row r="493" spans="1:43" ht="15.75" customHeight="1">
       <c r="A493" s="115"/>
       <c r="B493" s="115"/>
-      <c r="C493" s="348"/>
-      <c r="D493" s="312"/>
+      <c r="C493" s="347"/>
+      <c r="D493" s="311"/>
       <c r="E493" s="292"/>
       <c r="F493" s="115"/>
       <c r="G493" s="115"/>
@@ -55784,8 +55769,8 @@
     <row r="494" spans="1:43" ht="15.75" customHeight="1">
       <c r="A494" s="115"/>
       <c r="B494" s="115"/>
-      <c r="C494" s="348"/>
-      <c r="D494" s="312"/>
+      <c r="C494" s="347"/>
+      <c r="D494" s="311"/>
       <c r="E494" s="292"/>
       <c r="F494" s="115"/>
       <c r="G494" s="115"/>
@@ -55829,8 +55814,8 @@
     <row r="495" spans="1:43" ht="15.75" customHeight="1">
       <c r="A495" s="115"/>
       <c r="B495" s="115"/>
-      <c r="C495" s="348"/>
-      <c r="D495" s="312"/>
+      <c r="C495" s="347"/>
+      <c r="D495" s="311"/>
       <c r="E495" s="292"/>
       <c r="F495" s="115"/>
       <c r="G495" s="115"/>
@@ -55874,8 +55859,8 @@
     <row r="496" spans="1:43" ht="15.75" customHeight="1">
       <c r="A496" s="115"/>
       <c r="B496" s="115"/>
-      <c r="C496" s="348"/>
-      <c r="D496" s="312"/>
+      <c r="C496" s="347"/>
+      <c r="D496" s="311"/>
       <c r="E496" s="292"/>
       <c r="F496" s="115"/>
       <c r="G496" s="115"/>
@@ -55919,8 +55904,8 @@
     <row r="497" spans="1:43" ht="15.75" customHeight="1">
       <c r="A497" s="115"/>
       <c r="B497" s="115"/>
-      <c r="C497" s="348"/>
-      <c r="D497" s="312"/>
+      <c r="C497" s="347"/>
+      <c r="D497" s="311"/>
       <c r="E497" s="292"/>
       <c r="F497" s="115"/>
       <c r="G497" s="115"/>
@@ -55964,8 +55949,8 @@
     <row r="498" spans="1:43" ht="15.75" customHeight="1">
       <c r="A498" s="115"/>
       <c r="B498" s="115"/>
-      <c r="C498" s="348"/>
-      <c r="D498" s="312"/>
+      <c r="C498" s="347"/>
+      <c r="D498" s="311"/>
       <c r="E498" s="292"/>
       <c r="F498" s="115"/>
       <c r="G498" s="115"/>
@@ -56009,8 +55994,8 @@
     <row r="499" spans="1:43" ht="15.75" customHeight="1">
       <c r="A499" s="115"/>
       <c r="B499" s="115"/>
-      <c r="C499" s="348"/>
-      <c r="D499" s="312"/>
+      <c r="C499" s="347"/>
+      <c r="D499" s="311"/>
       <c r="E499" s="292"/>
       <c r="F499" s="115"/>
       <c r="G499" s="115"/>
@@ -56054,8 +56039,8 @@
     <row r="500" spans="1:43" ht="15.75" customHeight="1">
       <c r="A500" s="115"/>
       <c r="B500" s="115"/>
-      <c r="C500" s="348"/>
-      <c r="D500" s="312"/>
+      <c r="C500" s="347"/>
+      <c r="D500" s="311"/>
       <c r="E500" s="292"/>
       <c r="F500" s="115"/>
       <c r="G500" s="115"/>
@@ -56099,8 +56084,8 @@
     <row r="501" spans="1:43" ht="15.75" customHeight="1">
       <c r="A501" s="115"/>
       <c r="B501" s="115"/>
-      <c r="C501" s="348"/>
-      <c r="D501" s="312"/>
+      <c r="C501" s="347"/>
+      <c r="D501" s="311"/>
       <c r="E501" s="292"/>
       <c r="F501" s="115"/>
       <c r="G501" s="115"/>
@@ -56144,8 +56129,8 @@
     <row r="502" spans="1:43" ht="15.75" customHeight="1">
       <c r="A502" s="115"/>
       <c r="B502" s="115"/>
-      <c r="C502" s="348"/>
-      <c r="D502" s="312"/>
+      <c r="C502" s="347"/>
+      <c r="D502" s="311"/>
       <c r="E502" s="292"/>
       <c r="F502" s="115"/>
       <c r="G502" s="115"/>
@@ -56189,8 +56174,8 @@
     <row r="503" spans="1:43" ht="15.75" customHeight="1">
       <c r="A503" s="115"/>
       <c r="B503" s="115"/>
-      <c r="C503" s="348"/>
-      <c r="D503" s="312"/>
+      <c r="C503" s="347"/>
+      <c r="D503" s="311"/>
       <c r="E503" s="292"/>
       <c r="F503" s="115"/>
       <c r="G503" s="115"/>
@@ -56234,8 +56219,8 @@
     <row r="504" spans="1:43" ht="15.75" customHeight="1">
       <c r="A504" s="115"/>
       <c r="B504" s="115"/>
-      <c r="C504" s="348"/>
-      <c r="D504" s="312"/>
+      <c r="C504" s="347"/>
+      <c r="D504" s="311"/>
       <c r="E504" s="292"/>
       <c r="F504" s="115"/>
       <c r="G504" s="115"/>
@@ -56279,8 +56264,8 @@
     <row r="505" spans="1:43" ht="15.75" customHeight="1">
       <c r="A505" s="115"/>
       <c r="B505" s="115"/>
-      <c r="C505" s="348"/>
-      <c r="D505" s="312"/>
+      <c r="C505" s="347"/>
+      <c r="D505" s="311"/>
       <c r="E505" s="292"/>
       <c r="F505" s="115"/>
       <c r="G505" s="115"/>
@@ -56324,8 +56309,8 @@
     <row r="506" spans="1:43" ht="15.75" customHeight="1">
       <c r="A506" s="115"/>
       <c r="B506" s="115"/>
-      <c r="C506" s="348"/>
-      <c r="D506" s="312"/>
+      <c r="C506" s="347"/>
+      <c r="D506" s="311"/>
       <c r="E506" s="292"/>
       <c r="F506" s="115"/>
       <c r="G506" s="115"/>
@@ -56369,8 +56354,8 @@
     <row r="507" spans="1:43" ht="15.75" customHeight="1">
       <c r="A507" s="115"/>
       <c r="B507" s="115"/>
-      <c r="C507" s="348"/>
-      <c r="D507" s="312"/>
+      <c r="C507" s="347"/>
+      <c r="D507" s="311"/>
       <c r="E507" s="292"/>
       <c r="F507" s="115"/>
       <c r="G507" s="115"/>
@@ -56414,8 +56399,8 @@
     <row r="508" spans="1:43" ht="15.75" customHeight="1">
       <c r="A508" s="115"/>
       <c r="B508" s="115"/>
-      <c r="C508" s="348"/>
-      <c r="D508" s="312"/>
+      <c r="C508" s="347"/>
+      <c r="D508" s="311"/>
       <c r="E508" s="292"/>
       <c r="F508" s="115"/>
       <c r="G508" s="115"/>
@@ -56459,8 +56444,8 @@
     <row r="509" spans="1:43" ht="15.75" customHeight="1">
       <c r="A509" s="115"/>
       <c r="B509" s="115"/>
-      <c r="C509" s="348"/>
-      <c r="D509" s="312"/>
+      <c r="C509" s="347"/>
+      <c r="D509" s="311"/>
       <c r="E509" s="292"/>
       <c r="F509" s="115"/>
       <c r="G509" s="115"/>
@@ -56504,8 +56489,8 @@
     <row r="510" spans="1:43" ht="15.75" customHeight="1">
       <c r="A510" s="115"/>
       <c r="B510" s="115"/>
-      <c r="C510" s="348"/>
-      <c r="D510" s="312"/>
+      <c r="C510" s="347"/>
+      <c r="D510" s="311"/>
       <c r="E510" s="292"/>
       <c r="F510" s="115"/>
       <c r="G510" s="115"/>
@@ -56549,8 +56534,8 @@
     <row r="511" spans="1:43" ht="15.75" customHeight="1">
       <c r="A511" s="115"/>
       <c r="B511" s="115"/>
-      <c r="C511" s="348"/>
-      <c r="D511" s="312"/>
+      <c r="C511" s="347"/>
+      <c r="D511" s="311"/>
       <c r="E511" s="292"/>
       <c r="F511" s="115"/>
       <c r="G511" s="115"/>
@@ -56594,8 +56579,8 @@
     <row r="512" spans="1:43" ht="15.75" customHeight="1">
       <c r="A512" s="115"/>
       <c r="B512" s="115"/>
-      <c r="C512" s="348"/>
-      <c r="D512" s="312"/>
+      <c r="C512" s="347"/>
+      <c r="D512" s="311"/>
       <c r="E512" s="292"/>
       <c r="F512" s="115"/>
       <c r="G512" s="115"/>
@@ -56639,8 +56624,8 @@
     <row r="513" spans="1:43" ht="15.75" customHeight="1">
       <c r="A513" s="115"/>
       <c r="B513" s="115"/>
-      <c r="C513" s="348"/>
-      <c r="D513" s="312"/>
+      <c r="C513" s="347"/>
+      <c r="D513" s="311"/>
       <c r="E513" s="292"/>
       <c r="F513" s="115"/>
       <c r="G513" s="115"/>
@@ -56684,8 +56669,8 @@
     <row r="514" spans="1:43" ht="15.75" customHeight="1">
       <c r="A514" s="115"/>
       <c r="B514" s="115"/>
-      <c r="C514" s="348"/>
-      <c r="D514" s="312"/>
+      <c r="C514" s="347"/>
+      <c r="D514" s="311"/>
       <c r="E514" s="292"/>
       <c r="F514" s="115"/>
       <c r="G514" s="115"/>
@@ -56729,8 +56714,8 @@
     <row r="515" spans="1:43" ht="15.75" customHeight="1">
       <c r="A515" s="115"/>
       <c r="B515" s="115"/>
-      <c r="C515" s="348"/>
-      <c r="D515" s="312"/>
+      <c r="C515" s="347"/>
+      <c r="D515" s="311"/>
       <c r="E515" s="292"/>
       <c r="F515" s="115"/>
       <c r="G515" s="115"/>
@@ -56774,8 +56759,8 @@
     <row r="516" spans="1:43" ht="15.75" customHeight="1">
       <c r="A516" s="115"/>
       <c r="B516" s="115"/>
-      <c r="C516" s="348"/>
-      <c r="D516" s="312"/>
+      <c r="C516" s="347"/>
+      <c r="D516" s="311"/>
       <c r="E516" s="292"/>
       <c r="F516" s="115"/>
       <c r="G516" s="115"/>
@@ -56819,8 +56804,8 @@
     <row r="517" spans="1:43" ht="15.75" customHeight="1">
       <c r="A517" s="115"/>
       <c r="B517" s="115"/>
-      <c r="C517" s="348"/>
-      <c r="D517" s="312"/>
+      <c r="C517" s="347"/>
+      <c r="D517" s="311"/>
       <c r="E517" s="292"/>
       <c r="F517" s="115"/>
       <c r="G517" s="115"/>
@@ -56864,8 +56849,8 @@
     <row r="518" spans="1:43" ht="15.75" customHeight="1">
       <c r="A518" s="115"/>
       <c r="B518" s="115"/>
-      <c r="C518" s="348"/>
-      <c r="D518" s="312"/>
+      <c r="C518" s="347"/>
+      <c r="D518" s="311"/>
       <c r="E518" s="292"/>
       <c r="F518" s="115"/>
       <c r="G518" s="115"/>
@@ -56909,8 +56894,8 @@
     <row r="519" spans="1:43" ht="15.75" customHeight="1">
       <c r="A519" s="115"/>
       <c r="B519" s="115"/>
-      <c r="C519" s="348"/>
-      <c r="D519" s="312"/>
+      <c r="C519" s="347"/>
+      <c r="D519" s="311"/>
       <c r="E519" s="292"/>
       <c r="F519" s="115"/>
       <c r="G519" s="115"/>
@@ -56954,8 +56939,8 @@
     <row r="520" spans="1:43" ht="15.75" customHeight="1">
       <c r="A520" s="115"/>
       <c r="B520" s="115"/>
-      <c r="C520" s="348"/>
-      <c r="D520" s="312"/>
+      <c r="C520" s="347"/>
+      <c r="D520" s="311"/>
       <c r="E520" s="292"/>
       <c r="F520" s="115"/>
       <c r="G520" s="115"/>
@@ -56999,8 +56984,8 @@
     <row r="521" spans="1:43" ht="15.75" customHeight="1">
       <c r="A521" s="115"/>
       <c r="B521" s="115"/>
-      <c r="C521" s="348"/>
-      <c r="D521" s="312"/>
+      <c r="C521" s="347"/>
+      <c r="D521" s="311"/>
       <c r="E521" s="292"/>
       <c r="F521" s="115"/>
       <c r="G521" s="115"/>
@@ -57044,8 +57029,8 @@
     <row r="522" spans="1:43" ht="15.75" customHeight="1">
       <c r="A522" s="115"/>
       <c r="B522" s="115"/>
-      <c r="C522" s="348"/>
-      <c r="D522" s="312"/>
+      <c r="C522" s="347"/>
+      <c r="D522" s="311"/>
       <c r="E522" s="292"/>
       <c r="F522" s="115"/>
       <c r="G522" s="115"/>
@@ -57089,8 +57074,8 @@
     <row r="523" spans="1:43" ht="15.75" customHeight="1">
       <c r="A523" s="115"/>
       <c r="B523" s="115"/>
-      <c r="C523" s="348"/>
-      <c r="D523" s="312"/>
+      <c r="C523" s="347"/>
+      <c r="D523" s="311"/>
       <c r="E523" s="292"/>
       <c r="F523" s="115"/>
       <c r="G523" s="115"/>
@@ -57134,8 +57119,8 @@
     <row r="524" spans="1:43" ht="15.75" customHeight="1">
       <c r="A524" s="115"/>
       <c r="B524" s="115"/>
-      <c r="C524" s="348"/>
-      <c r="D524" s="312"/>
+      <c r="C524" s="347"/>
+      <c r="D524" s="311"/>
       <c r="E524" s="292"/>
       <c r="F524" s="115"/>
       <c r="G524" s="115"/>
@@ -57179,8 +57164,8 @@
     <row r="525" spans="1:43" ht="15.75" customHeight="1">
       <c r="A525" s="115"/>
       <c r="B525" s="115"/>
-      <c r="C525" s="348"/>
-      <c r="D525" s="312"/>
+      <c r="C525" s="347"/>
+      <c r="D525" s="311"/>
       <c r="E525" s="292"/>
       <c r="F525" s="115"/>
       <c r="G525" s="115"/>
@@ -57224,8 +57209,8 @@
     <row r="526" spans="1:43" ht="15.75" customHeight="1">
       <c r="A526" s="115"/>
       <c r="B526" s="115"/>
-      <c r="C526" s="348"/>
-      <c r="D526" s="312"/>
+      <c r="C526" s="347"/>
+      <c r="D526" s="311"/>
       <c r="E526" s="292"/>
       <c r="F526" s="115"/>
       <c r="G526" s="115"/>
@@ -57269,8 +57254,8 @@
     <row r="527" spans="1:43" ht="15.75" customHeight="1">
       <c r="A527" s="115"/>
       <c r="B527" s="115"/>
-      <c r="C527" s="348"/>
-      <c r="D527" s="312"/>
+      <c r="C527" s="347"/>
+      <c r="D527" s="311"/>
       <c r="E527" s="292"/>
       <c r="F527" s="115"/>
       <c r="G527" s="115"/>
@@ -57314,8 +57299,8 @@
     <row r="528" spans="1:43" ht="15.75" customHeight="1">
       <c r="A528" s="115"/>
       <c r="B528" s="115"/>
-      <c r="C528" s="348"/>
-      <c r="D528" s="312"/>
+      <c r="C528" s="347"/>
+      <c r="D528" s="311"/>
       <c r="E528" s="292"/>
       <c r="F528" s="115"/>
       <c r="G528" s="115"/>
@@ -57359,8 +57344,8 @@
     <row r="529" spans="1:43" ht="15.75" customHeight="1">
       <c r="A529" s="115"/>
       <c r="B529" s="115"/>
-      <c r="C529" s="348"/>
-      <c r="D529" s="312"/>
+      <c r="C529" s="347"/>
+      <c r="D529" s="311"/>
       <c r="E529" s="292"/>
       <c r="F529" s="115"/>
       <c r="G529" s="115"/>
@@ -57404,8 +57389,8 @@
     <row r="530" spans="1:43" ht="15.75" customHeight="1">
       <c r="A530" s="115"/>
       <c r="B530" s="115"/>
-      <c r="C530" s="348"/>
-      <c r="D530" s="312"/>
+      <c r="C530" s="347"/>
+      <c r="D530" s="311"/>
       <c r="E530" s="292"/>
       <c r="F530" s="115"/>
       <c r="G530" s="115"/>
@@ -57449,8 +57434,8 @@
     <row r="531" spans="1:43" ht="15.75" customHeight="1">
       <c r="A531" s="115"/>
       <c r="B531" s="115"/>
-      <c r="C531" s="348"/>
-      <c r="D531" s="312"/>
+      <c r="C531" s="347"/>
+      <c r="D531" s="311"/>
       <c r="E531" s="292"/>
       <c r="F531" s="115"/>
       <c r="G531" s="115"/>
@@ -57494,8 +57479,8 @@
     <row r="532" spans="1:43" ht="15.75" customHeight="1">
       <c r="A532" s="115"/>
       <c r="B532" s="115"/>
-      <c r="C532" s="348"/>
-      <c r="D532" s="312"/>
+      <c r="C532" s="347"/>
+      <c r="D532" s="311"/>
       <c r="E532" s="292"/>
       <c r="F532" s="115"/>
       <c r="G532" s="115"/>
@@ -57539,8 +57524,8 @@
     <row r="533" spans="1:43" ht="15.75" customHeight="1">
       <c r="A533" s="115"/>
       <c r="B533" s="115"/>
-      <c r="C533" s="348"/>
-      <c r="D533" s="312"/>
+      <c r="C533" s="347"/>
+      <c r="D533" s="311"/>
       <c r="E533" s="292"/>
       <c r="F533" s="115"/>
       <c r="G533" s="115"/>
@@ -57584,8 +57569,8 @@
     <row r="534" spans="1:43" ht="15.75" customHeight="1">
       <c r="A534" s="115"/>
       <c r="B534" s="115"/>
-      <c r="C534" s="348"/>
-      <c r="D534" s="312"/>
+      <c r="C534" s="347"/>
+      <c r="D534" s="311"/>
       <c r="E534" s="292"/>
       <c r="F534" s="115"/>
       <c r="G534" s="115"/>
@@ -57629,8 +57614,8 @@
     <row r="535" spans="1:43" ht="15.75" customHeight="1">
       <c r="A535" s="115"/>
       <c r="B535" s="115"/>
-      <c r="C535" s="348"/>
-      <c r="D535" s="312"/>
+      <c r="C535" s="347"/>
+      <c r="D535" s="311"/>
       <c r="E535" s="292"/>
       <c r="F535" s="115"/>
       <c r="G535" s="115"/>
@@ -57674,8 +57659,8 @@
     <row r="536" spans="1:43" ht="15.75" customHeight="1">
       <c r="A536" s="115"/>
       <c r="B536" s="115"/>
-      <c r="C536" s="348"/>
-      <c r="D536" s="312"/>
+      <c r="C536" s="347"/>
+      <c r="D536" s="311"/>
       <c r="E536" s="292"/>
       <c r="F536" s="115"/>
       <c r="G536" s="115"/>
@@ -57719,8 +57704,8 @@
     <row r="537" spans="1:43" ht="15.75" customHeight="1">
       <c r="A537" s="115"/>
       <c r="B537" s="115"/>
-      <c r="C537" s="348"/>
-      <c r="D537" s="312"/>
+      <c r="C537" s="347"/>
+      <c r="D537" s="311"/>
       <c r="E537" s="292"/>
       <c r="F537" s="115"/>
       <c r="G537" s="115"/>
@@ -57764,8 +57749,8 @@
     <row r="538" spans="1:43" ht="15.75" customHeight="1">
       <c r="A538" s="115"/>
       <c r="B538" s="115"/>
-      <c r="C538" s="348"/>
-      <c r="D538" s="312"/>
+      <c r="C538" s="347"/>
+      <c r="D538" s="311"/>
       <c r="E538" s="292"/>
       <c r="F538" s="115"/>
       <c r="G538" s="115"/>
@@ -57809,8 +57794,8 @@
     <row r="539" spans="1:43" ht="15.75" customHeight="1">
       <c r="A539" s="115"/>
       <c r="B539" s="115"/>
-      <c r="C539" s="348"/>
-      <c r="D539" s="312"/>
+      <c r="C539" s="347"/>
+      <c r="D539" s="311"/>
       <c r="E539" s="292"/>
       <c r="F539" s="115"/>
       <c r="G539" s="115"/>
@@ -57854,8 +57839,8 @@
     <row r="540" spans="1:43" ht="15.75" customHeight="1">
       <c r="A540" s="115"/>
       <c r="B540" s="115"/>
-      <c r="C540" s="348"/>
-      <c r="D540" s="312"/>
+      <c r="C540" s="347"/>
+      <c r="D540" s="311"/>
       <c r="E540" s="292"/>
       <c r="F540" s="115"/>
       <c r="G540" s="115"/>
@@ -57899,8 +57884,8 @@
     <row r="541" spans="1:43" ht="15.75" customHeight="1">
       <c r="A541" s="115"/>
       <c r="B541" s="115"/>
-      <c r="C541" s="348"/>
-      <c r="D541" s="312"/>
+      <c r="C541" s="347"/>
+      <c r="D541" s="311"/>
       <c r="E541" s="292"/>
       <c r="F541" s="115"/>
       <c r="G541" s="115"/>
@@ -57944,8 +57929,8 @@
     <row r="542" spans="1:43" ht="15.75" customHeight="1">
       <c r="A542" s="115"/>
       <c r="B542" s="115"/>
-      <c r="C542" s="348"/>
-      <c r="D542" s="312"/>
+      <c r="C542" s="347"/>
+      <c r="D542" s="311"/>
       <c r="E542" s="292"/>
       <c r="F542" s="115"/>
       <c r="G542" s="115"/>
@@ -57989,8 +57974,8 @@
     <row r="543" spans="1:43" ht="15.75" customHeight="1">
       <c r="A543" s="115"/>
       <c r="B543" s="115"/>
-      <c r="C543" s="348"/>
-      <c r="D543" s="312"/>
+      <c r="C543" s="347"/>
+      <c r="D543" s="311"/>
       <c r="E543" s="292"/>
       <c r="F543" s="115"/>
       <c r="G543" s="115"/>
@@ -58034,8 +58019,8 @@
     <row r="544" spans="1:43" ht="15.75" customHeight="1">
       <c r="A544" s="115"/>
       <c r="B544" s="115"/>
-      <c r="C544" s="348"/>
-      <c r="D544" s="312"/>
+      <c r="C544" s="347"/>
+      <c r="D544" s="311"/>
       <c r="E544" s="292"/>
       <c r="F544" s="115"/>
       <c r="G544" s="115"/>
@@ -58079,8 +58064,8 @@
     <row r="545" spans="1:43" ht="15.75" customHeight="1">
       <c r="A545" s="115"/>
       <c r="B545" s="115"/>
-      <c r="C545" s="348"/>
-      <c r="D545" s="312"/>
+      <c r="C545" s="347"/>
+      <c r="D545" s="311"/>
       <c r="E545" s="292"/>
       <c r="F545" s="115"/>
       <c r="G545" s="115"/>
@@ -58124,8 +58109,8 @@
     <row r="546" spans="1:43" ht="15.75" customHeight="1">
       <c r="A546" s="115"/>
       <c r="B546" s="115"/>
-      <c r="C546" s="348"/>
-      <c r="D546" s="312"/>
+      <c r="C546" s="347"/>
+      <c r="D546" s="311"/>
       <c r="E546" s="292"/>
       <c r="F546" s="115"/>
       <c r="G546" s="115"/>
@@ -58169,8 +58154,8 @@
     <row r="547" spans="1:43" ht="15.75" customHeight="1">
       <c r="A547" s="115"/>
       <c r="B547" s="115"/>
-      <c r="C547" s="348"/>
-      <c r="D547" s="312"/>
+      <c r="C547" s="347"/>
+      <c r="D547" s="311"/>
       <c r="E547" s="292"/>
       <c r="F547" s="115"/>
       <c r="G547" s="115"/>
@@ -58214,8 +58199,8 @@
     <row r="548" spans="1:43" ht="15.75" customHeight="1">
       <c r="A548" s="115"/>
       <c r="B548" s="115"/>
-      <c r="C548" s="348"/>
-      <c r="D548" s="312"/>
+      <c r="C548" s="347"/>
+      <c r="D548" s="311"/>
       <c r="E548" s="292"/>
       <c r="F548" s="115"/>
       <c r="G548" s="115"/>
@@ -58259,8 +58244,8 @@
     <row r="549" spans="1:43" ht="15.75" customHeight="1">
       <c r="A549" s="115"/>
       <c r="B549" s="115"/>
-      <c r="C549" s="348"/>
-      <c r="D549" s="312"/>
+      <c r="C549" s="347"/>
+      <c r="D549" s="311"/>
       <c r="E549" s="292"/>
       <c r="F549" s="115"/>
       <c r="G549" s="115"/>
@@ -58304,8 +58289,8 @@
     <row r="550" spans="1:43" ht="15.75" customHeight="1">
       <c r="A550" s="115"/>
       <c r="B550" s="115"/>
-      <c r="C550" s="348"/>
-      <c r="D550" s="312"/>
+      <c r="C550" s="347"/>
+      <c r="D550" s="311"/>
       <c r="E550" s="292"/>
       <c r="F550" s="115"/>
       <c r="G550" s="115"/>
@@ -58349,8 +58334,8 @@
     <row r="551" spans="1:43" ht="15.75" customHeight="1">
       <c r="A551" s="115"/>
       <c r="B551" s="115"/>
-      <c r="C551" s="348"/>
-      <c r="D551" s="312"/>
+      <c r="C551" s="347"/>
+      <c r="D551" s="311"/>
       <c r="E551" s="292"/>
       <c r="F551" s="115"/>
       <c r="G551" s="115"/>
@@ -58394,8 +58379,8 @@
     <row r="552" spans="1:43" ht="15.75" customHeight="1">
       <c r="A552" s="115"/>
       <c r="B552" s="115"/>
-      <c r="C552" s="348"/>
-      <c r="D552" s="312"/>
+      <c r="C552" s="347"/>
+      <c r="D552" s="311"/>
       <c r="E552" s="292"/>
       <c r="F552" s="115"/>
       <c r="G552" s="115"/>
@@ -58439,8 +58424,8 @@
     <row r="553" spans="1:43" ht="15.75" customHeight="1">
       <c r="A553" s="115"/>
       <c r="B553" s="115"/>
-      <c r="C553" s="348"/>
-      <c r="D553" s="312"/>
+      <c r="C553" s="347"/>
+      <c r="D553" s="311"/>
       <c r="E553" s="292"/>
       <c r="F553" s="115"/>
       <c r="G553" s="115"/>
@@ -58484,8 +58469,8 @@
     <row r="554" spans="1:43" ht="15.75" customHeight="1">
       <c r="A554" s="115"/>
       <c r="B554" s="115"/>
-      <c r="C554" s="348"/>
-      <c r="D554" s="312"/>
+      <c r="C554" s="347"/>
+      <c r="D554" s="311"/>
       <c r="E554" s="292"/>
       <c r="F554" s="115"/>
       <c r="G554" s="115"/>
@@ -58529,8 +58514,8 @@
     <row r="555" spans="1:43" ht="15.75" customHeight="1">
       <c r="A555" s="115"/>
       <c r="B555" s="115"/>
-      <c r="C555" s="348"/>
-      <c r="D555" s="312"/>
+      <c r="C555" s="347"/>
+      <c r="D555" s="311"/>
       <c r="E555" s="292"/>
       <c r="F555" s="115"/>
       <c r="G555" s="115"/>
@@ -58574,8 +58559,8 @@
     <row r="556" spans="1:43" ht="15.75" customHeight="1">
       <c r="A556" s="115"/>
       <c r="B556" s="115"/>
-      <c r="C556" s="348"/>
-      <c r="D556" s="312"/>
+      <c r="C556" s="347"/>
+      <c r="D556" s="311"/>
       <c r="E556" s="292"/>
       <c r="F556" s="115"/>
       <c r="G556" s="115"/>
@@ -58619,8 +58604,8 @@
     <row r="557" spans="1:43" ht="15.75" customHeight="1">
       <c r="A557" s="115"/>
       <c r="B557" s="115"/>
-      <c r="C557" s="348"/>
-      <c r="D557" s="312"/>
+      <c r="C557" s="347"/>
+      <c r="D557" s="311"/>
       <c r="E557" s="292"/>
       <c r="F557" s="115"/>
       <c r="G557" s="115"/>
@@ -58664,8 +58649,8 @@
     <row r="558" spans="1:43" ht="15.75" customHeight="1">
       <c r="A558" s="115"/>
       <c r="B558" s="115"/>
-      <c r="C558" s="348"/>
-      <c r="D558" s="312"/>
+      <c r="C558" s="347"/>
+      <c r="D558" s="311"/>
       <c r="E558" s="292"/>
       <c r="F558" s="115"/>
       <c r="G558" s="115"/>
@@ -58709,8 +58694,8 @@
     <row r="559" spans="1:43" ht="15.75" customHeight="1">
       <c r="A559" s="115"/>
       <c r="B559" s="115"/>
-      <c r="C559" s="348"/>
-      <c r="D559" s="312"/>
+      <c r="C559" s="347"/>
+      <c r="D559" s="311"/>
       <c r="E559" s="292"/>
       <c r="F559" s="115"/>
       <c r="G559" s="115"/>
@@ -58754,8 +58739,8 @@
     <row r="560" spans="1:43" ht="15.75" customHeight="1">
       <c r="A560" s="115"/>
       <c r="B560" s="115"/>
-      <c r="C560" s="348"/>
-      <c r="D560" s="312"/>
+      <c r="C560" s="347"/>
+      <c r="D560" s="311"/>
       <c r="E560" s="292"/>
       <c r="F560" s="115"/>
       <c r="G560" s="115"/>
@@ -58799,8 +58784,8 @@
     <row r="561" spans="1:43" ht="15.75" customHeight="1">
       <c r="A561" s="115"/>
       <c r="B561" s="115"/>
-      <c r="C561" s="348"/>
-      <c r="D561" s="312"/>
+      <c r="C561" s="347"/>
+      <c r="D561" s="311"/>
       <c r="E561" s="292"/>
       <c r="F561" s="115"/>
       <c r="G561" s="115"/>
@@ -58844,8 +58829,8 @@
     <row r="562" spans="1:43" ht="15.75" customHeight="1">
       <c r="A562" s="115"/>
       <c r="B562" s="115"/>
-      <c r="C562" s="348"/>
-      <c r="D562" s="312"/>
+      <c r="C562" s="347"/>
+      <c r="D562" s="311"/>
       <c r="E562" s="292"/>
       <c r="F562" s="115"/>
       <c r="G562" s="115"/>
@@ -58889,8 +58874,8 @@
     <row r="563" spans="1:43" ht="15.75" customHeight="1">
       <c r="A563" s="115"/>
       <c r="B563" s="115"/>
-      <c r="C563" s="348"/>
-      <c r="D563" s="312"/>
+      <c r="C563" s="347"/>
+      <c r="D563" s="311"/>
       <c r="E563" s="292"/>
       <c r="F563" s="115"/>
       <c r="G563" s="115"/>
@@ -58934,8 +58919,8 @@
     <row r="564" spans="1:43" ht="15.75" customHeight="1">
       <c r="A564" s="115"/>
       <c r="B564" s="115"/>
-      <c r="C564" s="348"/>
-      <c r="D564" s="312"/>
+      <c r="C564" s="347"/>
+      <c r="D564" s="311"/>
       <c r="E564" s="292"/>
       <c r="F564" s="115"/>
       <c r="G564" s="115"/>
@@ -58979,8 +58964,8 @@
     <row r="565" spans="1:43" ht="15.75" customHeight="1">
       <c r="A565" s="115"/>
       <c r="B565" s="115"/>
-      <c r="C565" s="348"/>
-      <c r="D565" s="312"/>
+      <c r="C565" s="347"/>
+      <c r="D565" s="311"/>
       <c r="E565" s="292"/>
       <c r="F565" s="115"/>
       <c r="G565" s="115"/>
@@ -59024,8 +59009,8 @@
     <row r="566" spans="1:43" ht="15.75" customHeight="1">
       <c r="A566" s="115"/>
       <c r="B566" s="115"/>
-      <c r="C566" s="348"/>
-      <c r="D566" s="312"/>
+      <c r="C566" s="347"/>
+      <c r="D566" s="311"/>
       <c r="E566" s="292"/>
       <c r="F566" s="115"/>
       <c r="G566" s="115"/>
@@ -59069,8 +59054,8 @@
     <row r="567" spans="1:43" ht="15.75" customHeight="1">
       <c r="A567" s="115"/>
       <c r="B567" s="115"/>
-      <c r="C567" s="348"/>
-      <c r="D567" s="312"/>
+      <c r="C567" s="347"/>
+      <c r="D567" s="311"/>
       <c r="E567" s="292"/>
       <c r="F567" s="115"/>
       <c r="G567" s="115"/>
@@ -59114,8 +59099,8 @@
     <row r="568" spans="1:43" ht="15.75" customHeight="1">
       <c r="A568" s="115"/>
       <c r="B568" s="115"/>
-      <c r="C568" s="348"/>
-      <c r="D568" s="312"/>
+      <c r="C568" s="347"/>
+      <c r="D568" s="311"/>
       <c r="E568" s="292"/>
       <c r="F568" s="115"/>
       <c r="G568" s="115"/>
@@ -59159,8 +59144,8 @@
     <row r="569" spans="1:43" ht="15.75" customHeight="1">
       <c r="A569" s="115"/>
       <c r="B569" s="115"/>
-      <c r="C569" s="348"/>
-      <c r="D569" s="312"/>
+      <c r="C569" s="347"/>
+      <c r="D569" s="311"/>
       <c r="E569" s="292"/>
       <c r="F569" s="115"/>
       <c r="G569" s="115"/>
@@ -59204,8 +59189,8 @@
     <row r="570" spans="1:43" ht="15.75" customHeight="1">
       <c r="A570" s="115"/>
       <c r="B570" s="115"/>
-      <c r="C570" s="348"/>
-      <c r="D570" s="312"/>
+      <c r="C570" s="347"/>
+      <c r="D570" s="311"/>
       <c r="E570" s="292"/>
       <c r="F570" s="115"/>
       <c r="G570" s="115"/>
@@ -59249,8 +59234,8 @@
     <row r="571" spans="1:43" ht="15.75" customHeight="1">
       <c r="A571" s="115"/>
       <c r="B571" s="115"/>
-      <c r="C571" s="348"/>
-      <c r="D571" s="312"/>
+      <c r="C571" s="347"/>
+      <c r="D571" s="311"/>
       <c r="E571" s="292"/>
       <c r="F571" s="115"/>
       <c r="G571" s="115"/>
@@ -59294,8 +59279,8 @@
     <row r="572" spans="1:43" ht="15.75" customHeight="1">
       <c r="A572" s="115"/>
       <c r="B572" s="115"/>
-      <c r="C572" s="348"/>
-      <c r="D572" s="312"/>
+      <c r="C572" s="347"/>
+      <c r="D572" s="311"/>
       <c r="E572" s="292"/>
       <c r="F572" s="115"/>
       <c r="G572" s="115"/>
@@ -59339,8 +59324,8 @@
     <row r="573" spans="1:43" ht="15.75" customHeight="1">
       <c r="A573" s="115"/>
       <c r="B573" s="115"/>
-      <c r="C573" s="348"/>
-      <c r="D573" s="312"/>
+      <c r="C573" s="347"/>
+      <c r="D573" s="311"/>
       <c r="E573" s="292"/>
       <c r="F573" s="115"/>
       <c r="G573" s="115"/>
@@ -59384,8 +59369,8 @@
     <row r="574" spans="1:43" ht="15.75" customHeight="1">
       <c r="A574" s="115"/>
       <c r="B574" s="115"/>
-      <c r="C574" s="348"/>
-      <c r="D574" s="312"/>
+      <c r="C574" s="347"/>
+      <c r="D574" s="311"/>
       <c r="E574" s="292"/>
       <c r="F574" s="115"/>
       <c r="G574" s="115"/>
@@ -59429,8 +59414,8 @@
     <row r="575" spans="1:43" ht="15.75" customHeight="1">
       <c r="A575" s="115"/>
       <c r="B575" s="115"/>
-      <c r="C575" s="348"/>
-      <c r="D575" s="312"/>
+      <c r="C575" s="347"/>
+      <c r="D575" s="311"/>
       <c r="E575" s="292"/>
       <c r="F575" s="115"/>
       <c r="G575" s="115"/>
@@ -59474,8 +59459,8 @@
     <row r="576" spans="1:43" ht="15.75" customHeight="1">
       <c r="A576" s="115"/>
       <c r="B576" s="115"/>
-      <c r="C576" s="348"/>
-      <c r="D576" s="312"/>
+      <c r="C576" s="347"/>
+      <c r="D576" s="311"/>
       <c r="E576" s="292"/>
       <c r="F576" s="115"/>
       <c r="G576" s="115"/>
@@ -59519,8 +59504,8 @@
     <row r="577" spans="1:43" ht="15.75" customHeight="1">
       <c r="A577" s="115"/>
       <c r="B577" s="115"/>
-      <c r="C577" s="348"/>
-      <c r="D577" s="312"/>
+      <c r="C577" s="347"/>
+      <c r="D577" s="311"/>
       <c r="E577" s="292"/>
       <c r="F577" s="115"/>
       <c r="G577" s="115"/>
@@ -59564,8 +59549,8 @@
     <row r="578" spans="1:43" ht="15.75" customHeight="1">
       <c r="A578" s="115"/>
       <c r="B578" s="115"/>
-      <c r="C578" s="348"/>
-      <c r="D578" s="312"/>
+      <c r="C578" s="347"/>
+      <c r="D578" s="311"/>
       <c r="E578" s="292"/>
       <c r="F578" s="115"/>
       <c r="G578" s="115"/>
@@ -59609,8 +59594,8 @@
     <row r="579" spans="1:43" ht="15.75" customHeight="1">
       <c r="A579" s="115"/>
       <c r="B579" s="115"/>
-      <c r="C579" s="348"/>
-      <c r="D579" s="312"/>
+      <c r="C579" s="347"/>
+      <c r="D579" s="311"/>
       <c r="E579" s="292"/>
       <c r="F579" s="115"/>
       <c r="G579" s="115"/>
@@ -59654,8 +59639,8 @@
     <row r="580" spans="1:43" ht="15.75" customHeight="1">
       <c r="A580" s="115"/>
       <c r="B580" s="115"/>
-      <c r="C580" s="348"/>
-      <c r="D580" s="312"/>
+      <c r="C580" s="347"/>
+      <c r="D580" s="311"/>
       <c r="E580" s="292"/>
       <c r="F580" s="115"/>
       <c r="G580" s="115"/>
@@ -59699,8 +59684,8 @@
     <row r="581" spans="1:43" ht="15.75" customHeight="1">
       <c r="A581" s="115"/>
       <c r="B581" s="115"/>
-      <c r="C581" s="348"/>
-      <c r="D581" s="312"/>
+      <c r="C581" s="347"/>
+      <c r="D581" s="311"/>
       <c r="E581" s="292"/>
       <c r="F581" s="115"/>
       <c r="G581" s="115"/>
@@ -59744,8 +59729,8 @@
     <row r="582" spans="1:43" ht="15.75" customHeight="1">
       <c r="A582" s="115"/>
       <c r="B582" s="115"/>
-      <c r="C582" s="348"/>
-      <c r="D582" s="312"/>
+      <c r="C582" s="347"/>
+      <c r="D582" s="311"/>
       <c r="E582" s="292"/>
       <c r="F582" s="115"/>
       <c r="G582" s="115"/>
@@ -59789,8 +59774,8 @@
     <row r="583" spans="1:43" ht="15.75" customHeight="1">
       <c r="A583" s="115"/>
       <c r="B583" s="115"/>
-      <c r="C583" s="348"/>
-      <c r="D583" s="312"/>
+      <c r="C583" s="347"/>
+      <c r="D583" s="311"/>
       <c r="E583" s="292"/>
       <c r="F583" s="115"/>
       <c r="G583" s="115"/>
@@ -59834,8 +59819,8 @@
     <row r="584" spans="1:43" ht="15.75" customHeight="1">
       <c r="A584" s="115"/>
       <c r="B584" s="115"/>
-      <c r="C584" s="348"/>
-      <c r="D584" s="312"/>
+      <c r="C584" s="347"/>
+      <c r="D584" s="311"/>
       <c r="E584" s="292"/>
       <c r="F584" s="115"/>
       <c r="G584" s="115"/>
@@ -59879,8 +59864,8 @@
     <row r="585" spans="1:43" ht="15.75" customHeight="1">
       <c r="A585" s="115"/>
       <c r="B585" s="115"/>
-      <c r="C585" s="348"/>
-      <c r="D585" s="312"/>
+      <c r="C585" s="347"/>
+      <c r="D585" s="311"/>
       <c r="E585" s="292"/>
       <c r="F585" s="115"/>
       <c r="G585" s="115"/>
@@ -59924,8 +59909,8 @@
     <row r="586" spans="1:43" ht="15.75" customHeight="1">
       <c r="A586" s="115"/>
       <c r="B586" s="115"/>
-      <c r="C586" s="348"/>
-      <c r="D586" s="312"/>
+      <c r="C586" s="347"/>
+      <c r="D586" s="311"/>
       <c r="E586" s="292"/>
       <c r="F586" s="115"/>
       <c r="G586" s="115"/>
@@ -59969,8 +59954,8 @@
     <row r="587" spans="1:43" ht="15.75" customHeight="1">
       <c r="A587" s="115"/>
       <c r="B587" s="115"/>
-      <c r="C587" s="348"/>
-      <c r="D587" s="312"/>
+      <c r="C587" s="347"/>
+      <c r="D587" s="311"/>
       <c r="E587" s="292"/>
       <c r="F587" s="115"/>
       <c r="G587" s="115"/>
@@ -60014,8 +59999,8 @@
     <row r="588" spans="1:43" ht="15.75" customHeight="1">
       <c r="A588" s="115"/>
       <c r="B588" s="115"/>
-      <c r="C588" s="348"/>
-      <c r="D588" s="312"/>
+      <c r="C588" s="347"/>
+      <c r="D588" s="311"/>
       <c r="E588" s="292"/>
       <c r="F588" s="115"/>
       <c r="G588" s="115"/>
@@ -60059,8 +60044,8 @@
     <row r="589" spans="1:43" ht="15.75" customHeight="1">
       <c r="A589" s="115"/>
       <c r="B589" s="115"/>
-      <c r="C589" s="348"/>
-      <c r="D589" s="312"/>
+      <c r="C589" s="347"/>
+      <c r="D589" s="311"/>
       <c r="E589" s="292"/>
       <c r="F589" s="115"/>
       <c r="G589" s="115"/>
@@ -60104,8 +60089,8 @@
     <row r="590" spans="1:43" ht="15.75" customHeight="1">
       <c r="A590" s="115"/>
       <c r="B590" s="115"/>
-      <c r="C590" s="348"/>
-      <c r="D590" s="312"/>
+      <c r="C590" s="347"/>
+      <c r="D590" s="311"/>
       <c r="E590" s="292"/>
       <c r="F590" s="115"/>
       <c r="G590" s="115"/>
@@ -60149,8 +60134,8 @@
     <row r="591" spans="1:43" ht="15.75" customHeight="1">
       <c r="A591" s="115"/>
       <c r="B591" s="115"/>
-      <c r="C591" s="348"/>
-      <c r="D591" s="312"/>
+      <c r="C591" s="347"/>
+      <c r="D591" s="311"/>
       <c r="E591" s="292"/>
       <c r="F591" s="115"/>
       <c r="G591" s="115"/>
@@ -60194,8 +60179,8 @@
     <row r="592" spans="1:43" ht="15.75" customHeight="1">
       <c r="A592" s="115"/>
       <c r="B592" s="115"/>
-      <c r="C592" s="348"/>
-      <c r="D592" s="312"/>
+      <c r="C592" s="347"/>
+      <c r="D592" s="311"/>
       <c r="E592" s="292"/>
       <c r="F592" s="115"/>
       <c r="G592" s="115"/>
@@ -60239,8 +60224,8 @@
     <row r="593" spans="1:43" ht="15.75" customHeight="1">
       <c r="A593" s="115"/>
       <c r="B593" s="115"/>
-      <c r="C593" s="348"/>
-      <c r="D593" s="312"/>
+      <c r="C593" s="347"/>
+      <c r="D593" s="311"/>
       <c r="E593" s="292"/>
       <c r="F593" s="115"/>
       <c r="G593" s="115"/>
@@ -60284,8 +60269,8 @@
     <row r="594" spans="1:43" ht="15.75" customHeight="1">
       <c r="A594" s="115"/>
       <c r="B594" s="115"/>
-      <c r="C594" s="348"/>
-      <c r="D594" s="312"/>
+      <c r="C594" s="347"/>
+      <c r="D594" s="311"/>
       <c r="E594" s="292"/>
       <c r="F594" s="115"/>
       <c r="G594" s="115"/>
@@ -60329,8 +60314,8 @@
     <row r="595" spans="1:43" ht="15.75" customHeight="1">
       <c r="A595" s="115"/>
       <c r="B595" s="115"/>
-      <c r="C595" s="348"/>
-      <c r="D595" s="312"/>
+      <c r="C595" s="347"/>
+      <c r="D595" s="311"/>
       <c r="E595" s="292"/>
       <c r="F595" s="115"/>
       <c r="G595" s="115"/>
@@ -60374,8 +60359,8 @@
     <row r="596" spans="1:43" ht="15.75" customHeight="1">
       <c r="A596" s="115"/>
       <c r="B596" s="115"/>
-      <c r="C596" s="348"/>
-      <c r="D596" s="312"/>
+      <c r="C596" s="347"/>
+      <c r="D596" s="311"/>
       <c r="E596" s="292"/>
       <c r="F596" s="115"/>
       <c r="G596" s="115"/>
@@ -60419,8 +60404,8 @@
     <row r="597" spans="1:43" ht="15.75" customHeight="1">
       <c r="A597" s="115"/>
       <c r="B597" s="115"/>
-      <c r="C597" s="348"/>
-      <c r="D597" s="312"/>
+      <c r="C597" s="347"/>
+      <c r="D597" s="311"/>
       <c r="E597" s="292"/>
       <c r="F597" s="115"/>
       <c r="G597" s="115"/>
@@ -60464,8 +60449,8 @@
     <row r="598" spans="1:43" ht="15.75" customHeight="1">
       <c r="A598" s="115"/>
       <c r="B598" s="115"/>
-      <c r="C598" s="348"/>
-      <c r="D598" s="312"/>
+      <c r="C598" s="347"/>
+      <c r="D598" s="311"/>
       <c r="E598" s="292"/>
       <c r="F598" s="115"/>
       <c r="G598" s="115"/>
@@ -60509,8 +60494,8 @@
     <row r="599" spans="1:43" ht="15.75" customHeight="1">
       <c r="A599" s="115"/>
       <c r="B599" s="115"/>
-      <c r="C599" s="348"/>
-      <c r="D599" s="312"/>
+      <c r="C599" s="347"/>
+      <c r="D599" s="311"/>
       <c r="E599" s="292"/>
       <c r="F599" s="115"/>
       <c r="G599" s="115"/>
@@ -60554,8 +60539,8 @@
     <row r="600" spans="1:43" ht="15.75" customHeight="1">
       <c r="A600" s="115"/>
       <c r="B600" s="115"/>
-      <c r="C600" s="348"/>
-      <c r="D600" s="312"/>
+      <c r="C600" s="347"/>
+      <c r="D600" s="311"/>
       <c r="E600" s="292"/>
       <c r="F600" s="115"/>
       <c r="G600" s="115"/>
@@ -60599,8 +60584,8 @@
     <row r="601" spans="1:43" ht="15.75" customHeight="1">
       <c r="A601" s="115"/>
       <c r="B601" s="115"/>
-      <c r="C601" s="348"/>
-      <c r="D601" s="312"/>
+      <c r="C601" s="347"/>
+      <c r="D601" s="311"/>
       <c r="E601" s="292"/>
       <c r="F601" s="115"/>
       <c r="G601" s="115"/>
@@ -60644,8 +60629,8 @@
     <row r="602" spans="1:43" ht="15.75" customHeight="1">
       <c r="A602" s="115"/>
       <c r="B602" s="115"/>
-      <c r="C602" s="348"/>
-      <c r="D602" s="312"/>
+      <c r="C602" s="347"/>
+      <c r="D602" s="311"/>
       <c r="E602" s="292"/>
       <c r="F602" s="115"/>
       <c r="G602" s="115"/>
@@ -60689,8 +60674,8 @@
     <row r="603" spans="1:43" ht="15.75" customHeight="1">
       <c r="A603" s="115"/>
       <c r="B603" s="115"/>
-      <c r="C603" s="348"/>
-      <c r="D603" s="312"/>
+      <c r="C603" s="347"/>
+      <c r="D603" s="311"/>
       <c r="E603" s="292"/>
       <c r="F603" s="115"/>
       <c r="G603" s="115"/>
@@ -60734,8 +60719,8 @@
     <row r="604" spans="1:43" ht="15.75" customHeight="1">
       <c r="A604" s="115"/>
       <c r="B604" s="115"/>
-      <c r="C604" s="348"/>
-      <c r="D604" s="312"/>
+      <c r="C604" s="347"/>
+      <c r="D604" s="311"/>
       <c r="E604" s="292"/>
       <c r="F604" s="115"/>
       <c r="G604" s="115"/>
@@ -60779,8 +60764,8 @@
     <row r="605" spans="1:43" ht="15.75" customHeight="1">
       <c r="A605" s="115"/>
       <c r="B605" s="115"/>
-      <c r="C605" s="348"/>
-      <c r="D605" s="312"/>
+      <c r="C605" s="347"/>
+      <c r="D605" s="311"/>
       <c r="E605" s="292"/>
       <c r="F605" s="115"/>
       <c r="G605" s="115"/>
@@ -60824,8 +60809,8 @@
     <row r="606" spans="1:43" ht="15.75" customHeight="1">
       <c r="A606" s="115"/>
       <c r="B606" s="115"/>
-      <c r="C606" s="348"/>
-      <c r="D606" s="312"/>
+      <c r="C606" s="347"/>
+      <c r="D606" s="311"/>
       <c r="E606" s="292"/>
       <c r="F606" s="115"/>
       <c r="G606" s="115"/>
@@ -60869,8 +60854,8 @@
     <row r="607" spans="1:43" ht="15.75" customHeight="1">
       <c r="A607" s="115"/>
       <c r="B607" s="115"/>
-      <c r="C607" s="348"/>
-      <c r="D607" s="312"/>
+      <c r="C607" s="347"/>
+      <c r="D607" s="311"/>
       <c r="E607" s="292"/>
       <c r="F607" s="115"/>
       <c r="G607" s="115"/>
@@ -60914,8 +60899,8 @@
     <row r="608" spans="1:43" ht="15.75" customHeight="1">
       <c r="A608" s="115"/>
       <c r="B608" s="115"/>
-      <c r="C608" s="348"/>
-      <c r="D608" s="312"/>
+      <c r="C608" s="347"/>
+      <c r="D608" s="311"/>
       <c r="E608" s="292"/>
       <c r="F608" s="115"/>
       <c r="G608" s="115"/>
@@ -60959,8 +60944,8 @@
     <row r="609" spans="1:43" ht="15.75" customHeight="1">
       <c r="A609" s="115"/>
       <c r="B609" s="115"/>
-      <c r="C609" s="348"/>
-      <c r="D609" s="312"/>
+      <c r="C609" s="347"/>
+      <c r="D609" s="311"/>
       <c r="E609" s="292"/>
       <c r="F609" s="115"/>
       <c r="G609" s="115"/>
@@ -61004,8 +60989,8 @@
     <row r="610" spans="1:43" ht="15.75" customHeight="1">
       <c r="A610" s="115"/>
       <c r="B610" s="115"/>
-      <c r="C610" s="348"/>
-      <c r="D610" s="312"/>
+      <c r="C610" s="347"/>
+      <c r="D610" s="311"/>
       <c r="E610" s="292"/>
       <c r="F610" s="115"/>
       <c r="G610" s="115"/>
@@ -61049,8 +61034,8 @@
     <row r="611" spans="1:43" ht="15.75" customHeight="1">
       <c r="A611" s="115"/>
       <c r="B611" s="115"/>
-      <c r="C611" s="348"/>
-      <c r="D611" s="312"/>
+      <c r="C611" s="347"/>
+      <c r="D611" s="311"/>
       <c r="E611" s="292"/>
       <c r="F611" s="115"/>
       <c r="G611" s="115"/>
@@ -61094,8 +61079,8 @@
     <row r="612" spans="1:43" ht="15.75" customHeight="1">
       <c r="A612" s="115"/>
       <c r="B612" s="115"/>
-      <c r="C612" s="348"/>
-      <c r="D612" s="312"/>
+      <c r="C612" s="347"/>
+      <c r="D612" s="311"/>
       <c r="E612" s="292"/>
       <c r="F612" s="115"/>
       <c r="G612" s="115"/>
@@ -61139,8 +61124,8 @@
     <row r="613" spans="1:43" ht="15.75" customHeight="1">
       <c r="A613" s="115"/>
       <c r="B613" s="115"/>
-      <c r="C613" s="348"/>
-      <c r="D613" s="312"/>
+      <c r="C613" s="347"/>
+      <c r="D613" s="311"/>
       <c r="E613" s="292"/>
       <c r="F613" s="115"/>
       <c r="G613" s="115"/>
@@ -61184,8 +61169,8 @@
     <row r="614" spans="1:43" ht="15.75" customHeight="1">
       <c r="A614" s="115"/>
       <c r="B614" s="115"/>
-      <c r="C614" s="348"/>
-      <c r="D614" s="312"/>
+      <c r="C614" s="347"/>
+      <c r="D614" s="311"/>
       <c r="E614" s="292"/>
       <c r="F614" s="115"/>
       <c r="G614" s="115"/>
@@ -61229,8 +61214,8 @@
     <row r="615" spans="1:43" ht="15.75" customHeight="1">
       <c r="A615" s="115"/>
       <c r="B615" s="115"/>
-      <c r="C615" s="348"/>
-      <c r="D615" s="312"/>
+      <c r="C615" s="347"/>
+      <c r="D615" s="311"/>
       <c r="E615" s="292"/>
       <c r="F615" s="115"/>
       <c r="G615" s="115"/>
@@ -61274,8 +61259,8 @@
     <row r="616" spans="1:43" ht="15.75" customHeight="1">
       <c r="A616" s="115"/>
       <c r="B616" s="115"/>
-      <c r="C616" s="348"/>
-      <c r="D616" s="312"/>
+      <c r="C616" s="347"/>
+      <c r="D616" s="311"/>
       <c r="E616" s="292"/>
       <c r="F616" s="115"/>
       <c r="G616" s="115"/>
@@ -61319,8 +61304,8 @@
     <row r="617" spans="1:43" ht="15.75" customHeight="1">
       <c r="A617" s="115"/>
       <c r="B617" s="115"/>
-      <c r="C617" s="348"/>
-      <c r="D617" s="312"/>
+      <c r="C617" s="347"/>
+      <c r="D617" s="311"/>
       <c r="E617" s="292"/>
       <c r="F617" s="115"/>
       <c r="G617" s="115"/>
@@ -61364,8 +61349,8 @@
     <row r="618" spans="1:43" ht="15.75" customHeight="1">
       <c r="A618" s="115"/>
       <c r="B618" s="115"/>
-      <c r="C618" s="348"/>
-      <c r="D618" s="312"/>
+      <c r="C618" s="347"/>
+      <c r="D618" s="311"/>
       <c r="E618" s="292"/>
       <c r="F618" s="115"/>
       <c r="G618" s="115"/>
@@ -61409,8 +61394,8 @@
     <row r="619" spans="1:43" ht="15.75" customHeight="1">
       <c r="A619" s="115"/>
       <c r="B619" s="115"/>
-      <c r="C619" s="348"/>
-      <c r="D619" s="312"/>
+      <c r="C619" s="347"/>
+      <c r="D619" s="311"/>
       <c r="E619" s="292"/>
       <c r="F619" s="115"/>
       <c r="G619" s="115"/>
@@ -61454,8 +61439,8 @@
     <row r="620" spans="1:43" ht="15.75" customHeight="1">
       <c r="A620" s="115"/>
       <c r="B620" s="115"/>
-      <c r="C620" s="348"/>
-      <c r="D620" s="312"/>
+      <c r="C620" s="347"/>
+      <c r="D620" s="311"/>
       <c r="E620" s="292"/>
       <c r="F620" s="115"/>
       <c r="G620" s="115"/>
@@ -61499,8 +61484,8 @@
     <row r="621" spans="1:43" ht="15.75" customHeight="1">
       <c r="A621" s="115"/>
       <c r="B621" s="115"/>
-      <c r="C621" s="348"/>
-      <c r="D621" s="312"/>
+      <c r="C621" s="347"/>
+      <c r="D621" s="311"/>
       <c r="E621" s="292"/>
       <c r="F621" s="115"/>
       <c r="G621" s="115"/>
@@ -61544,8 +61529,8 @@
     <row r="622" spans="1:43" ht="15.75" customHeight="1">
       <c r="A622" s="115"/>
       <c r="B622" s="115"/>
-      <c r="C622" s="348"/>
-      <c r="D622" s="312"/>
+      <c r="C622" s="347"/>
+      <c r="D622" s="311"/>
       <c r="E622" s="292"/>
       <c r="F622" s="115"/>
       <c r="G622" s="115"/>
@@ -61589,8 +61574,8 @@
     <row r="623" spans="1:43" ht="15.75" customHeight="1">
       <c r="A623" s="115"/>
       <c r="B623" s="115"/>
-      <c r="C623" s="348"/>
-      <c r="D623" s="312"/>
+      <c r="C623" s="347"/>
+      <c r="D623" s="311"/>
       <c r="E623" s="292"/>
       <c r="F623" s="115"/>
       <c r="G623" s="115"/>
@@ -61634,8 +61619,8 @@
     <row r="624" spans="1:43" ht="15.75" customHeight="1">
       <c r="A624" s="115"/>
       <c r="B624" s="115"/>
-      <c r="C624" s="348"/>
-      <c r="D624" s="312"/>
+      <c r="C624" s="347"/>
+      <c r="D624" s="311"/>
       <c r="E624" s="292"/>
       <c r="F624" s="115"/>
       <c r="G624" s="115"/>
@@ -61679,8 +61664,8 @@
     <row r="625" spans="1:43" ht="15.75" customHeight="1">
       <c r="A625" s="115"/>
       <c r="B625" s="115"/>
-      <c r="C625" s="348"/>
-      <c r="D625" s="312"/>
+      <c r="C625" s="347"/>
+      <c r="D625" s="311"/>
       <c r="E625" s="292"/>
       <c r="F625" s="115"/>
       <c r="G625" s="115"/>
@@ -61724,8 +61709,8 @@
     <row r="626" spans="1:43" ht="15.75" customHeight="1">
       <c r="A626" s="115"/>
       <c r="B626" s="115"/>
-      <c r="C626" s="348"/>
-      <c r="D626" s="312"/>
+      <c r="C626" s="347"/>
+      <c r="D626" s="311"/>
       <c r="E626" s="292"/>
       <c r="F626" s="115"/>
       <c r="G626" s="115"/>
@@ -61769,8 +61754,8 @@
     <row r="627" spans="1:43" ht="15.75" customHeight="1">
       <c r="A627" s="115"/>
       <c r="B627" s="115"/>
-      <c r="C627" s="348"/>
-      <c r="D627" s="312"/>
+      <c r="C627" s="347"/>
+      <c r="D627" s="311"/>
       <c r="E627" s="292"/>
       <c r="F627" s="115"/>
       <c r="G627" s="115"/>
@@ -61814,8 +61799,8 @@
     <row r="628" spans="1:43" ht="15.75" customHeight="1">
       <c r="A628" s="115"/>
       <c r="B628" s="115"/>
-      <c r="C628" s="348"/>
-      <c r="D628" s="312"/>
+      <c r="C628" s="347"/>
+      <c r="D628" s="311"/>
       <c r="E628" s="292"/>
       <c r="F628" s="115"/>
       <c r="G628" s="115"/>
@@ -61859,8 +61844,8 @@
     <row r="629" spans="1:43" ht="15.75" customHeight="1">
       <c r="A629" s="115"/>
       <c r="B629" s="115"/>
-      <c r="C629" s="348"/>
-      <c r="D629" s="312"/>
+      <c r="C629" s="347"/>
+      <c r="D629" s="311"/>
       <c r="E629" s="292"/>
       <c r="F629" s="115"/>
       <c r="G629" s="115"/>
@@ -61904,8 +61889,8 @@
     <row r="630" spans="1:43" ht="15.75" customHeight="1">
       <c r="A630" s="115"/>
       <c r="B630" s="115"/>
-      <c r="C630" s="348"/>
-      <c r="D630" s="312"/>
+      <c r="C630" s="347"/>
+      <c r="D630" s="311"/>
       <c r="E630" s="292"/>
       <c r="F630" s="115"/>
       <c r="G630" s="115"/>
@@ -61949,8 +61934,8 @@
     <row r="631" spans="1:43" ht="15.75" customHeight="1">
       <c r="A631" s="115"/>
       <c r="B631" s="115"/>
-      <c r="C631" s="348"/>
-      <c r="D631" s="312"/>
+      <c r="C631" s="347"/>
+      <c r="D631" s="311"/>
       <c r="E631" s="292"/>
       <c r="F631" s="115"/>
       <c r="G631" s="115"/>
@@ -61994,8 +61979,8 @@
     <row r="632" spans="1:43" ht="15.75" customHeight="1">
       <c r="A632" s="115"/>
       <c r="B632" s="115"/>
-      <c r="C632" s="348"/>
-      <c r="D632" s="312"/>
+      <c r="C632" s="347"/>
+      <c r="D632" s="311"/>
       <c r="E632" s="292"/>
       <c r="F632" s="115"/>
       <c r="G632" s="115"/>
@@ -62039,8 +62024,8 @@
     <row r="633" spans="1:43" ht="15.75" customHeight="1">
       <c r="A633" s="115"/>
       <c r="B633" s="115"/>
-      <c r="C633" s="348"/>
-      <c r="D633" s="312"/>
+      <c r="C633" s="347"/>
+      <c r="D633" s="311"/>
       <c r="E633" s="292"/>
       <c r="F633" s="115"/>
       <c r="G633" s="115"/>
@@ -62084,8 +62069,8 @@
     <row r="634" spans="1:43" ht="15.75" customHeight="1">
       <c r="A634" s="115"/>
       <c r="B634" s="115"/>
-      <c r="C634" s="348"/>
-      <c r="D634" s="312"/>
+      <c r="C634" s="347"/>
+      <c r="D634" s="311"/>
       <c r="E634" s="292"/>
       <c r="F634" s="115"/>
       <c r="G634" s="115"/>
@@ -62129,8 +62114,8 @@
     <row r="635" spans="1:43" ht="15.75" customHeight="1">
       <c r="A635" s="115"/>
       <c r="B635" s="115"/>
-      <c r="C635" s="348"/>
-      <c r="D635" s="312"/>
+      <c r="C635" s="347"/>
+      <c r="D635" s="311"/>
       <c r="E635" s="292"/>
       <c r="F635" s="115"/>
       <c r="G635" s="115"/>
@@ -62174,8 +62159,8 @@
     <row r="636" spans="1:43" ht="15.75" customHeight="1">
       <c r="A636" s="115"/>
       <c r="B636" s="115"/>
-      <c r="C636" s="348"/>
-      <c r="D636" s="312"/>
+      <c r="C636" s="347"/>
+      <c r="D636" s="311"/>
       <c r="E636" s="292"/>
       <c r="F636" s="115"/>
       <c r="G636" s="115"/>
@@ -62219,8 +62204,8 @@
     <row r="637" spans="1:43" ht="15.75" customHeight="1">
       <c r="A637" s="115"/>
       <c r="B637" s="115"/>
-      <c r="C637" s="348"/>
-      <c r="D637" s="312"/>
+      <c r="C637" s="347"/>
+      <c r="D637" s="311"/>
       <c r="E637" s="292"/>
       <c r="F637" s="115"/>
       <c r="G637" s="115"/>
@@ -62264,8 +62249,8 @@
     <row r="638" spans="1:43" ht="15.75" customHeight="1">
       <c r="A638" s="115"/>
       <c r="B638" s="115"/>
-      <c r="C638" s="348"/>
-      <c r="D638" s="312"/>
+      <c r="C638" s="347"/>
+      <c r="D638" s="311"/>
       <c r="E638" s="292"/>
       <c r="F638" s="115"/>
       <c r="G638" s="115"/>
@@ -62309,8 +62294,8 @@
     <row r="639" spans="1:43" ht="15.75" customHeight="1">
       <c r="A639" s="115"/>
       <c r="B639" s="115"/>
-      <c r="C639" s="348"/>
-      <c r="D639" s="312"/>
+      <c r="C639" s="347"/>
+      <c r="D639" s="311"/>
       <c r="E639" s="292"/>
       <c r="F639" s="115"/>
       <c r="G639" s="115"/>
@@ -62354,8 +62339,8 @@
     <row r="640" spans="1:43" ht="15.75" customHeight="1">
       <c r="A640" s="115"/>
       <c r="B640" s="115"/>
-      <c r="C640" s="348"/>
-      <c r="D640" s="312"/>
+      <c r="C640" s="347"/>
+      <c r="D640" s="311"/>
       <c r="E640" s="292"/>
       <c r="F640" s="115"/>
       <c r="G640" s="115"/>
@@ -62399,8 +62384,8 @@
     <row r="641" spans="1:43" ht="15.75" customHeight="1">
       <c r="A641" s="115"/>
       <c r="B641" s="115"/>
-      <c r="C641" s="348"/>
-      <c r="D641" s="312"/>
+      <c r="C641" s="347"/>
+      <c r="D641" s="311"/>
       <c r="E641" s="292"/>
       <c r="F641" s="115"/>
       <c r="G641" s="115"/>
@@ -62444,8 +62429,8 @@
     <row r="642" spans="1:43" ht="15.75" customHeight="1">
       <c r="A642" s="115"/>
       <c r="B642" s="115"/>
-      <c r="C642" s="348"/>
-      <c r="D642" s="312"/>
+      <c r="C642" s="347"/>
+      <c r="D642" s="311"/>
       <c r="E642" s="292"/>
       <c r="F642" s="115"/>
       <c r="G642" s="115"/>
@@ -62489,8 +62474,8 @@
     <row r="643" spans="1:43" ht="15.75" customHeight="1">
       <c r="A643" s="115"/>
       <c r="B643" s="115"/>
-      <c r="C643" s="348"/>
-      <c r="D643" s="312"/>
+      <c r="C643" s="347"/>
+      <c r="D643" s="311"/>
       <c r="E643" s="292"/>
       <c r="F643" s="115"/>
       <c r="G643" s="115"/>
@@ -62534,8 +62519,8 @@
     <row r="644" spans="1:43" ht="15.75" customHeight="1">
       <c r="A644" s="115"/>
       <c r="B644" s="115"/>
-      <c r="C644" s="348"/>
-      <c r="D644" s="312"/>
+      <c r="C644" s="347"/>
+      <c r="D644" s="311"/>
       <c r="E644" s="292"/>
       <c r="F644" s="115"/>
       <c r="G644" s="115"/>
@@ -62579,8 +62564,8 @@
     <row r="645" spans="1:43" ht="15.75" customHeight="1">
       <c r="A645" s="115"/>
       <c r="B645" s="115"/>
-      <c r="C645" s="348"/>
-      <c r="D645" s="312"/>
+      <c r="C645" s="347"/>
+      <c r="D645" s="311"/>
       <c r="E645" s="292"/>
       <c r="F645" s="115"/>
       <c r="G645" s="115"/>
@@ -62624,8 +62609,8 @@
     <row r="646" spans="1:43" ht="15.75" customHeight="1">
       <c r="A646" s="115"/>
       <c r="B646" s="115"/>
-      <c r="C646" s="348"/>
-      <c r="D646" s="312"/>
+      <c r="C646" s="347"/>
+      <c r="D646" s="311"/>
       <c r="E646" s="292"/>
       <c r="F646" s="115"/>
       <c r="G646" s="115"/>
@@ -62669,8 +62654,8 @@
     <row r="647" spans="1:43" ht="15.75" customHeight="1">
       <c r="A647" s="115"/>
       <c r="B647" s="115"/>
-      <c r="C647" s="348"/>
-      <c r="D647" s="312"/>
+      <c r="C647" s="347"/>
+      <c r="D647" s="311"/>
       <c r="E647" s="292"/>
       <c r="F647" s="115"/>
       <c r="G647" s="115"/>
@@ -62714,8 +62699,8 @@
     <row r="648" spans="1:43" ht="15.75" customHeight="1">
       <c r="A648" s="115"/>
       <c r="B648" s="115"/>
-      <c r="C648" s="348"/>
-      <c r="D648" s="312"/>
+      <c r="C648" s="347"/>
+      <c r="D648" s="311"/>
       <c r="E648" s="292"/>
       <c r="F648" s="115"/>
       <c r="G648" s="115"/>
@@ -62759,8 +62744,8 @@
     <row r="649" spans="1:43" ht="15.75" customHeight="1">
       <c r="A649" s="115"/>
       <c r="B649" s="115"/>
-      <c r="C649" s="348"/>
-      <c r="D649" s="312"/>
+      <c r="C649" s="347"/>
+      <c r="D649" s="311"/>
       <c r="E649" s="292"/>
       <c r="F649" s="115"/>
       <c r="G649" s="115"/>
@@ -62804,8 +62789,8 @@
     <row r="650" spans="1:43" ht="15.75" customHeight="1">
       <c r="A650" s="115"/>
       <c r="B650" s="115"/>
-      <c r="C650" s="348"/>
-      <c r="D650" s="312"/>
+      <c r="C650" s="347"/>
+      <c r="D650" s="311"/>
       <c r="E650" s="292"/>
       <c r="F650" s="115"/>
       <c r="G650" s="115"/>
@@ -62849,8 +62834,8 @@
     <row r="651" spans="1:43" ht="15.75" customHeight="1">
       <c r="A651" s="115"/>
       <c r="B651" s="115"/>
-      <c r="C651" s="348"/>
-      <c r="D651" s="312"/>
+      <c r="C651" s="347"/>
+      <c r="D651" s="311"/>
       <c r="E651" s="292"/>
       <c r="F651" s="115"/>
       <c r="G651" s="115"/>
@@ -62894,8 +62879,8 @@
     <row r="652" spans="1:43" ht="15.75" customHeight="1">
       <c r="A652" s="115"/>
       <c r="B652" s="115"/>
-      <c r="C652" s="348"/>
-      <c r="D652" s="312"/>
+      <c r="C652" s="347"/>
+      <c r="D652" s="311"/>
       <c r="E652" s="292"/>
       <c r="F652" s="115"/>
       <c r="G652" s="115"/>
@@ -62939,8 +62924,8 @@
     <row r="653" spans="1:43" ht="15.75" customHeight="1">
       <c r="A653" s="115"/>
       <c r="B653" s="115"/>
-      <c r="C653" s="348"/>
-      <c r="D653" s="312"/>
+      <c r="C653" s="347"/>
+      <c r="D653" s="311"/>
       <c r="E653" s="292"/>
       <c r="F653" s="115"/>
       <c r="G653" s="115"/>
@@ -62984,8 +62969,8 @@
     <row r="654" spans="1:43" ht="15.75" customHeight="1">
       <c r="A654" s="115"/>
       <c r="B654" s="115"/>
-      <c r="C654" s="348"/>
-      <c r="D654" s="312"/>
+      <c r="C654" s="347"/>
+      <c r="D654" s="311"/>
       <c r="E654" s="292"/>
       <c r="F654" s="115"/>
       <c r="G654" s="115"/>
@@ -63029,8 +63014,8 @@
     <row r="655" spans="1:43" ht="15.75" customHeight="1">
       <c r="A655" s="115"/>
       <c r="B655" s="115"/>
-      <c r="C655" s="348"/>
-      <c r="D655" s="312"/>
+      <c r="C655" s="347"/>
+      <c r="D655" s="311"/>
       <c r="E655" s="292"/>
       <c r="F655" s="115"/>
       <c r="G655" s="115"/>
@@ -63074,8 +63059,8 @@
     <row r="656" spans="1:43" ht="15.75" customHeight="1">
       <c r="A656" s="115"/>
       <c r="B656" s="115"/>
-      <c r="C656" s="348"/>
-      <c r="D656" s="312"/>
+      <c r="C656" s="347"/>
+      <c r="D656" s="311"/>
       <c r="E656" s="292"/>
       <c r="F656" s="115"/>
       <c r="G656" s="115"/>
@@ -63119,8 +63104,8 @@
     <row r="657" spans="1:43" ht="15.75" customHeight="1">
       <c r="A657" s="115"/>
       <c r="B657" s="115"/>
-      <c r="C657" s="348"/>
-      <c r="D657" s="312"/>
+      <c r="C657" s="347"/>
+      <c r="D657" s="311"/>
       <c r="E657" s="292"/>
       <c r="F657" s="115"/>
       <c r="G657" s="115"/>
@@ -63164,8 +63149,8 @@
     <row r="658" spans="1:43" ht="15.75" customHeight="1">
       <c r="A658" s="115"/>
       <c r="B658" s="115"/>
-      <c r="C658" s="348"/>
-      <c r="D658" s="312"/>
+      <c r="C658" s="347"/>
+      <c r="D658" s="311"/>
       <c r="E658" s="292"/>
       <c r="F658" s="115"/>
       <c r="G658" s="115"/>
@@ -63209,8 +63194,8 @@
     <row r="659" spans="1:43" ht="15.75" customHeight="1">
       <c r="A659" s="115"/>
       <c r="B659" s="115"/>
-      <c r="C659" s="348"/>
-      <c r="D659" s="312"/>
+      <c r="C659" s="347"/>
+      <c r="D659" s="311"/>
       <c r="E659" s="292"/>
       <c r="F659" s="115"/>
       <c r="G659" s="115"/>
@@ -63254,8 +63239,8 @@
     <row r="660" spans="1:43" ht="15.75" customHeight="1">
       <c r="A660" s="115"/>
       <c r="B660" s="115"/>
-      <c r="C660" s="348"/>
-      <c r="D660" s="312"/>
+      <c r="C660" s="347"/>
+      <c r="D660" s="311"/>
       <c r="E660" s="292"/>
       <c r="F660" s="115"/>
       <c r="G660" s="115"/>
@@ -63299,8 +63284,8 @@
     <row r="661" spans="1:43" ht="15.75" customHeight="1">
       <c r="A661" s="115"/>
       <c r="B661" s="115"/>
-      <c r="C661" s="348"/>
-      <c r="D661" s="312"/>
+      <c r="C661" s="347"/>
+      <c r="D661" s="311"/>
       <c r="E661" s="292"/>
       <c r="F661" s="115"/>
       <c r="G661" s="115"/>
@@ -63344,8 +63329,8 @@
     <row r="662" spans="1:43" ht="15.75" customHeight="1">
       <c r="A662" s="115"/>
       <c r="B662" s="115"/>
-      <c r="C662" s="348"/>
-      <c r="D662" s="312"/>
+      <c r="C662" s="347"/>
+      <c r="D662" s="311"/>
       <c r="E662" s="292"/>
       <c r="F662" s="115"/>
       <c r="G662" s="115"/>
@@ -63389,8 +63374,8 @@
     <row r="663" spans="1:43" ht="15.75" customHeight="1">
       <c r="A663" s="115"/>
       <c r="B663" s="115"/>
-      <c r="C663" s="348"/>
-      <c r="D663" s="312"/>
+      <c r="C663" s="347"/>
+      <c r="D663" s="311"/>
       <c r="E663" s="292"/>
       <c r="F663" s="115"/>
       <c r="G663" s="115"/>
@@ -63434,8 +63419,8 @@
     <row r="664" spans="1:43" ht="15.75" customHeight="1">
       <c r="A664" s="115"/>
       <c r="B664" s="115"/>
-      <c r="C664" s="348"/>
-      <c r="D664" s="312"/>
+      <c r="C664" s="347"/>
+      <c r="D664" s="311"/>
       <c r="E664" s="292"/>
       <c r="F664" s="115"/>
       <c r="G664" s="115"/>
@@ -63479,8 +63464,8 @@
     <row r="665" spans="1:43" ht="15.75" customHeight="1">
       <c r="A665" s="115"/>
       <c r="B665" s="115"/>
-      <c r="C665" s="348"/>
-      <c r="D665" s="312"/>
+      <c r="C665" s="347"/>
+      <c r="D665" s="311"/>
       <c r="E665" s="292"/>
       <c r="F665" s="115"/>
       <c r="G665" s="115"/>
@@ -63524,8 +63509,8 @@
     <row r="666" spans="1:43" ht="15.75" customHeight="1">
       <c r="A666" s="115"/>
       <c r="B666" s="115"/>
-      <c r="C666" s="348"/>
-      <c r="D666" s="312"/>
+      <c r="C666" s="347"/>
+      <c r="D666" s="311"/>
       <c r="E666" s="292"/>
       <c r="F666" s="115"/>
       <c r="G666" s="115"/>
@@ -63569,8 +63554,8 @@
     <row r="667" spans="1:43" ht="15.75" customHeight="1">
       <c r="A667" s="115"/>
       <c r="B667" s="115"/>
-      <c r="C667" s="348"/>
-      <c r="D667" s="312"/>
+      <c r="C667" s="347"/>
+      <c r="D667" s="311"/>
       <c r="E667" s="292"/>
       <c r="F667" s="115"/>
       <c r="G667" s="115"/>
@@ -63614,8 +63599,8 @@
     <row r="668" spans="1:43" ht="15.75" customHeight="1">
       <c r="A668" s="115"/>
       <c r="B668" s="115"/>
-      <c r="C668" s="348"/>
-      <c r="D668" s="312"/>
+      <c r="C668" s="347"/>
+      <c r="D668" s="311"/>
       <c r="E668" s="292"/>
       <c r="F668" s="115"/>
       <c r="G668" s="115"/>
@@ -63659,8 +63644,8 @@
     <row r="669" spans="1:43" ht="15.75" customHeight="1">
       <c r="A669" s="115"/>
       <c r="B669" s="115"/>
-      <c r="C669" s="348"/>
-      <c r="D669" s="312"/>
+      <c r="C669" s="347"/>
+      <c r="D669" s="311"/>
       <c r="E669" s="292"/>
       <c r="F669" s="115"/>
       <c r="G669" s="115"/>
@@ -63704,8 +63689,8 @@
     <row r="670" spans="1:43" ht="15.75" customHeight="1">
       <c r="A670" s="115"/>
       <c r="B670" s="115"/>
-      <c r="C670" s="348"/>
-      <c r="D670" s="312"/>
+      <c r="C670" s="347"/>
+      <c r="D670" s="311"/>
       <c r="E670" s="292"/>
       <c r="F670" s="115"/>
       <c r="G670" s="115"/>
@@ -63749,8 +63734,8 @@
     <row r="671" spans="1:43" ht="15.75" customHeight="1">
       <c r="A671" s="115"/>
       <c r="B671" s="115"/>
-      <c r="C671" s="348"/>
-      <c r="D671" s="312"/>
+      <c r="C671" s="347"/>
+      <c r="D671" s="311"/>
       <c r="E671" s="292"/>
       <c r="F671" s="115"/>
       <c r="G671" s="115"/>
@@ -63794,8 +63779,8 @@
     <row r="672" spans="1:43" ht="15.75" customHeight="1">
       <c r="A672" s="115"/>
       <c r="B672" s="115"/>
-      <c r="C672" s="348"/>
-      <c r="D672" s="312"/>
+      <c r="C672" s="347"/>
+      <c r="D672" s="311"/>
       <c r="E672" s="292"/>
       <c r="F672" s="115"/>
       <c r="G672" s="115"/>
@@ -63839,8 +63824,8 @@
     <row r="673" spans="1:43" ht="15.75" customHeight="1">
       <c r="A673" s="115"/>
       <c r="B673" s="115"/>
-      <c r="C673" s="348"/>
-      <c r="D673" s="312"/>
+      <c r="C673" s="347"/>
+      <c r="D673" s="311"/>
       <c r="E673" s="292"/>
       <c r="F673" s="115"/>
       <c r="G673" s="115"/>
@@ -63884,8 +63869,8 @@
     <row r="674" spans="1:43" ht="15.75" customHeight="1">
       <c r="A674" s="115"/>
       <c r="B674" s="115"/>
-      <c r="C674" s="348"/>
-      <c r="D674" s="312"/>
+      <c r="C674" s="347"/>
+      <c r="D674" s="311"/>
       <c r="E674" s="292"/>
       <c r="F674" s="115"/>
       <c r="G674" s="115"/>
@@ -63929,8 +63914,8 @@
     <row r="675" spans="1:43" ht="15.75" customHeight="1">
       <c r="A675" s="115"/>
       <c r="B675" s="115"/>
-      <c r="C675" s="348"/>
-      <c r="D675" s="312"/>
+      <c r="C675" s="347"/>
+      <c r="D675" s="311"/>
       <c r="E675" s="292"/>
       <c r="F675" s="115"/>
       <c r="G675" s="115"/>
@@ -63974,8 +63959,8 @@
     <row r="676" spans="1:43" ht="15.75" customHeight="1">
       <c r="A676" s="115"/>
       <c r="B676" s="115"/>
-      <c r="C676" s="348"/>
-      <c r="D676" s="312"/>
+      <c r="C676" s="347"/>
+      <c r="D676" s="311"/>
       <c r="E676" s="292"/>
       <c r="F676" s="115"/>
       <c r="G676" s="115"/>
@@ -64019,8 +64004,8 @@
     <row r="677" spans="1:43" ht="15.75" customHeight="1">
       <c r="A677" s="115"/>
       <c r="B677" s="115"/>
-      <c r="C677" s="348"/>
-      <c r="D677" s="312"/>
+      <c r="C677" s="347"/>
+      <c r="D677" s="311"/>
       <c r="E677" s="292"/>
       <c r="F677" s="115"/>
       <c r="G677" s="115"/>
@@ -64064,8 +64049,8 @@
     <row r="678" spans="1:43" ht="15.75" customHeight="1">
       <c r="A678" s="115"/>
       <c r="B678" s="115"/>
-      <c r="C678" s="348"/>
-      <c r="D678" s="312"/>
+      <c r="C678" s="347"/>
+      <c r="D678" s="311"/>
       <c r="E678" s="292"/>
       <c r="F678" s="115"/>
       <c r="G678" s="115"/>
@@ -64109,8 +64094,8 @@
     <row r="679" spans="1:43" ht="15.75" customHeight="1">
       <c r="A679" s="115"/>
       <c r="B679" s="115"/>
-      <c r="C679" s="348"/>
-      <c r="D679" s="312"/>
+      <c r="C679" s="347"/>
+      <c r="D679" s="311"/>
       <c r="E679" s="292"/>
       <c r="F679" s="115"/>
       <c r="G679" s="115"/>
@@ -64155,7 +64140,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{AEEB9956-05E6-8046-B542-DFA582BD0402}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{23C9AB3D-D227-5647-AB8E-FBD18DE2369C}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>
@@ -64951,11 +64936,10 @@
     <hyperlink ref="F478" r:id="rId790" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
     <hyperlink ref="F479" r:id="rId791" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
     <hyperlink ref="Y247" r:id="rId792" display="https://gallica.bnf.fr/ark:/12148/bpt6k56069895" xr:uid="{406C8F90-712D-EA4E-983E-641EE322383B}"/>
-    <hyperlink ref="F376" r:id="rId793" display="https://gallica.bnf.fr/ark:/12148/bpt6k6261188b/f304.item" xr:uid="{16C50DDE-BBB2-8741-AE50-3B32AA0D6224}"/>
-    <hyperlink ref="F388" r:id="rId794" display="https://gallica.bnf.fr/ark:/12148/bpt6k6274143z/f227.item" xr:uid="{E92130F0-40E3-964F-9C82-6A4A8E98FE4A}"/>
+    <hyperlink ref="F388" r:id="rId793" display="https://gallica.bnf.fr/ark:/12148/bpt6k6274143z/f227.item" xr:uid="{E92130F0-40E3-964F-9C82-6A4A8E98FE4A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <legacyDrawing r:id="rId795"/>
+  <legacyDrawing r:id="rId794"/>
 </worksheet>
 </file>
--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCFB57F-C829-EC4C-A541-72D3B4468E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96949C83-0702-2547-846E-C5E3F6CF5282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="500" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6989" uniqueCount="4011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6989" uniqueCount="4012">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17171,6 +17171,9 @@
   </si>
   <si>
     <t>1706-11_005</t>
+  </si>
+  <si>
+    <t>transcription en cours</t>
   </si>
 </sst>
 </file>
@@ -50705,8 +50708,8 @@
       <c r="B418" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C418" s="335" t="s">
-        <v>172</v>
+      <c r="C418" s="379" t="s">
+        <v>4011</v>
       </c>
       <c r="D418" s="309"/>
       <c r="E418" s="62"/>
@@ -52302,7 +52305,7 @@
       </c>
       <c r="D440" s="309"/>
       <c r="E440" s="62"/>
-      <c r="F440" s="16" t="s">
+      <c r="F440" s="371" t="s">
         <v>3548</v>
       </c>
       <c r="G440" s="32"/>
@@ -64290,7 +64293,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{3DEF98E4-58BF-F741-BAEC-0B1332785F92}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{50931856-EF18-1846-A443-B0938DF1DA30}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96949C83-0702-2547-846E-C5E3F6CF5282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551821FB-18A0-064F-B1B9-E14BD390A677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="800" yWindow="500" windowWidth="24800" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -112,27 +112,188 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>Sont traitées comme des "personnes associées", les personnes non représentées mais qui sont liées à l'estampe, tels :  
-- les dédicataires de l'image ; 
-- les acteurs importants des fêtes et cérémonies représentées ;
-- les personnes dont les armes font l'objet d'une représentation ; 
-- les personnes dont la table généalogique est retracée ; 
-- les personnes à l'origine d'un décor, d'un monument ou d'une invention.
-	-Louise Quentel
-Sont traitées comme personnes associées les personnes non représentées mais liées à l'estampe, tels : 
-- les dédicataires de l'image ;
-- les principaux acteurs des fêtes et cérémonies représentées ;
-- les personnes dont les armes font l'objet d'une représentation ;
-- les personnes dont la table généalogique est retracée ;
-- les personnes à l'origine d'un décor, d'un monument ou d'une invention.
-	-Anne Piéjus
-peut-être que l'expression "à l'origine d'un décor" pourrait etre précisée.
-	-Anne Piéjus
-Proposition : 
-"- les personnes à l'origine d'un décor, d'un monument ou d'une invention (auteur, commanditaire ou dédicataire)."
-	-Louise Quentel</t>
+          <t xml:space="preserve">Sont traitées comme des "personnes associées", les personnes non représentées mais qui sont liées à l'estampe, tels :  
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les dédicataires de l'image ; 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les acteurs importants des fêtes et cérémonies représentées ;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les personnes dont les armes font l'objet d'une représentation ; 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les personnes dont la table généalogique est retracée ; 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les personnes à l'origine d'un décor, d'un monument ou d'une invention.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Louise Quentel
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Sont traitées comme personnes associées les personnes non représentées mais liées à l'estampe, tels : 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les dédicataires de l'image ;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les principaux acteurs des fêtes et cérémonies représentées ;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les personnes dont les armes font l'objet d'une représentation ;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les personnes dont la table généalogique est retracée ;
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- les personnes à l'origine d'un décor, d'un monument ou d'une invention.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Anne Piéjus
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">peut-être que l'expression "à l'origine d'un décor" pourrait etre précisée.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Anne Piéjus
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Proposition : 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">"- les personnes à l'origine d'un décor, d'un monument ou d'une invention (auteur, commanditaire ou dédicataire)."
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Louise Quentel</t>
         </r>
       </text>
     </comment>
@@ -321,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6989" uniqueCount="4012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6990" uniqueCount="4013">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17174,6 +17335,9 @@
   </si>
   <si>
     <t>transcription en cours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autre relevé, commenté, de la cloche figurant sur ce plan : https://catalogue.bnf.fr/ark:/12148/cb41504283h </t>
   </si>
 </sst>
 </file>
@@ -35401,7 +35565,9 @@
       <c r="AA213" s="205"/>
       <c r="AB213" s="206"/>
       <c r="AC213" s="32"/>
-      <c r="AD213" s="21"/>
+      <c r="AD213" s="21" t="s">
+        <v>4012</v>
+      </c>
       <c r="AE213" s="32"/>
       <c r="AF213" s="32"/>
       <c r="AG213" s="32"/>
@@ -64293,7 +64459,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{50931856-EF18-1846-A443-B0938DF1DA30}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{851FEAAE-A936-B345-A6A3-FF2BCED4EF5D}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551821FB-18A0-064F-B1B9-E14BD390A677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BD03D9-48E1-214D-8149-62A68839AA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="500" windowWidth="24800" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1160" yWindow="500" windowWidth="24440" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6990" uniqueCount="4013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6991" uniqueCount="4014">
   <si>
     <t>ID estampe</t>
   </si>
@@ -16738,22 +16738,6 @@
     <t>19,8 x 12,3 cm</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Traité de Comiers "Suite du traité des lunettes" [troisième partie]. Sur la gravure : "1677". </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color theme="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://gallica.bnf.fr/ark:/12148/bpt6k56069895</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Article à </t>
   </si>
   <si>
@@ -17338,6 +17322,12 @@
   </si>
   <si>
     <t xml:space="preserve">Autre relevé, commenté, de la cloche figurant sur ce plan : https://catalogue.bnf.fr/ark:/12148/cb41504283h </t>
+  </si>
+  <si>
+    <t>Traité de Comiers "Suite du traité des lunettes" [troisième partie]. Sur la gravure : "1677". https://gallica.bnf.fr/ark:/12148/bpt6k56069895</t>
+  </si>
+  <si>
+    <t>Le principe du pantographe, outil de reproduction de dessins à différentes échelles (aussi appelé singe), a été énoncé en 1603 par le jésuite Christophe Scheiner. Voir aussi article dans l'Encyclopédie, XI, p. 827.</t>
   </si>
 </sst>
 </file>
@@ -20025,7 +20015,7 @@
     </row>
     <row r="2" spans="1:43" ht="15.75" customHeight="1">
       <c r="A2" s="355" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>30</v>
@@ -20260,7 +20250,7 @@
     </row>
     <row r="5" spans="1:43" ht="15.75" customHeight="1">
       <c r="A5" s="356" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>73</v>
@@ -20335,7 +20325,7 @@
     </row>
     <row r="6" spans="1:43" ht="15.75" customHeight="1">
       <c r="A6" s="370" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>43</v>
@@ -20485,7 +20475,7 @@
     </row>
     <row r="8" spans="1:43" ht="15.75" customHeight="1">
       <c r="A8" s="356" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>101</v>
@@ -20562,7 +20552,7 @@
     </row>
     <row r="9" spans="1:43" ht="15.75" customHeight="1">
       <c r="A9" s="355" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>101</v>
@@ -20783,7 +20773,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="329" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="D12" s="310"/>
       <c r="E12" s="72"/>
@@ -20854,7 +20844,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="329" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="D13" s="309"/>
       <c r="E13" s="62"/>
@@ -21061,13 +21051,13 @@
     </row>
     <row r="16" spans="1:43" ht="15.75" customHeight="1">
       <c r="A16" s="357" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="345" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="D16" s="308" t="s">
         <v>180</v>
@@ -21154,7 +21144,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="348" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="D17" s="308" t="s">
         <v>180</v>
@@ -21409,7 +21399,7 @@
     </row>
     <row r="20" spans="1:43" ht="15.75" customHeight="1">
       <c r="A20" s="357" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="B20" s="32" t="s">
         <v>43</v>
@@ -21494,7 +21484,7 @@
     </row>
     <row r="21" spans="1:43" ht="15.75" customHeight="1">
       <c r="A21" s="349" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="B21" s="32" t="s">
         <v>43</v>
@@ -21725,7 +21715,7 @@
     </row>
     <row r="24" spans="1:43" ht="15.75" customHeight="1">
       <c r="A24" s="358" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="B24" s="32" t="s">
         <v>249</v>
@@ -21794,7 +21784,7 @@
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
       <c r="A25" s="358" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>249</v>
@@ -21863,13 +21853,13 @@
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
       <c r="A26" s="372" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="328" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="D26" s="308" t="s">
         <v>180</v>
@@ -21940,7 +21930,7 @@
         <v>43</v>
       </c>
       <c r="C27" s="328" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="D27" s="308" t="s">
         <v>180</v>
@@ -22005,7 +21995,7 @@
     </row>
     <row r="28" spans="1:43" ht="15.75" customHeight="1">
       <c r="A28" s="358" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="B28" s="32" t="s">
         <v>249</v>
@@ -22084,7 +22074,7 @@
     </row>
     <row r="29" spans="1:43" ht="15.75" customHeight="1">
       <c r="A29" s="355" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>281</v>
@@ -22159,7 +22149,7 @@
     </row>
     <row r="30" spans="1:43" ht="15.75" customHeight="1">
       <c r="A30" s="355" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="B30" s="33" t="s">
         <v>294</v>
@@ -22240,13 +22230,13 @@
     </row>
     <row r="31" spans="1:43" ht="15.75" customHeight="1">
       <c r="A31" s="358" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="B31" s="33" t="s">
         <v>294</v>
       </c>
       <c r="C31" s="328" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="D31" s="306"/>
       <c r="E31" s="18"/>
@@ -22313,7 +22303,7 @@
     </row>
     <row r="32" spans="1:43" ht="15.75" customHeight="1">
       <c r="A32" s="355" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="B32" s="32" t="s">
         <v>312</v>
@@ -22394,7 +22384,7 @@
         <v>294</v>
       </c>
       <c r="C33" s="328" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="D33" s="306"/>
       <c r="E33" s="18"/>
@@ -22459,13 +22449,13 @@
     </row>
     <row r="34" spans="1:43" ht="15.75" customHeight="1">
       <c r="A34" s="359" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="B34" s="108" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="329" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="D34" s="308" t="s">
         <v>282</v>
@@ -22540,13 +22530,13 @@
     </row>
     <row r="35" spans="1:43" ht="15.75" customHeight="1">
       <c r="A35" s="358" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="329" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="D35" s="308" t="s">
         <v>282</v>
@@ -22621,13 +22611,13 @@
     </row>
     <row r="36" spans="1:43" ht="15.75" customHeight="1">
       <c r="A36" s="358" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="328" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="D36" s="309"/>
       <c r="E36" s="62"/>
@@ -22771,7 +22761,7 @@
     </row>
     <row r="38" spans="1:43" ht="15.75" customHeight="1">
       <c r="A38" s="355" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>43</v>
@@ -22780,7 +22770,7 @@
         <v>361</v>
       </c>
       <c r="D38" s="309" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="E38" s="62"/>
       <c r="F38" s="32" t="s">
@@ -22850,7 +22840,7 @@
     </row>
     <row r="39" spans="1:43" ht="15.75" customHeight="1">
       <c r="A39" s="355" t="s">
-        <v>3907</v>
+        <v>3906</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>43</v>
@@ -22927,7 +22917,7 @@
         <v>379</v>
       </c>
       <c r="C40" s="328" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="D40" s="309"/>
       <c r="E40" s="62"/>
@@ -23055,13 +23045,13 @@
     </row>
     <row r="42" spans="1:43" ht="15.75" customHeight="1">
       <c r="A42" s="358" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="328" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="D42" s="309"/>
       <c r="E42" s="62"/>
@@ -23126,13 +23116,13 @@
     </row>
     <row r="43" spans="1:43" ht="15.75" customHeight="1">
       <c r="A43" s="358" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="328" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="D43" s="309"/>
       <c r="E43" s="62"/>
@@ -23337,13 +23327,13 @@
     </row>
     <row r="46" spans="1:43" ht="15.75" customHeight="1">
       <c r="A46" s="358" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="328" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="D46" s="309"/>
       <c r="E46" s="62"/>
@@ -23420,7 +23410,7 @@
         <v>418</v>
       </c>
       <c r="C47" s="328" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="D47" s="309"/>
       <c r="E47" s="62"/>
@@ -23481,13 +23471,13 @@
     </row>
     <row r="48" spans="1:43" ht="15.75" customHeight="1">
       <c r="A48" s="358" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="B48" s="32" t="s">
         <v>439</v>
       </c>
       <c r="C48" s="328" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="D48" s="309"/>
       <c r="E48" s="62"/>
@@ -23638,13 +23628,13 @@
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>439</v>
       </c>
       <c r="C50" s="328" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="D50" s="309"/>
       <c r="E50" s="62"/>
@@ -23709,13 +23699,13 @@
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>449</v>
       </c>
       <c r="C51" s="328" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="D51" s="308" t="s">
         <v>470</v>
@@ -23780,7 +23770,7 @@
     </row>
     <row r="52" spans="1:43" ht="15.75" customHeight="1">
       <c r="A52" s="358" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>476</v>
@@ -23942,7 +23932,7 @@
     </row>
     <row r="54" spans="1:43" ht="15.75" customHeight="1">
       <c r="A54" s="358" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="B54" s="155" t="s">
         <v>502</v>
@@ -24021,7 +24011,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="328" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="D55" s="309"/>
       <c r="E55" s="62"/>
@@ -24161,7 +24151,7 @@
     </row>
     <row r="57" spans="1:43" ht="15.75" customHeight="1">
       <c r="A57" s="358" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="B57" s="32" t="s">
         <v>43</v>
@@ -24228,13 +24218,13 @@
     </row>
     <row r="58" spans="1:43" ht="15.75" customHeight="1">
       <c r="A58" s="358" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="B58" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="328" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="D58" s="308" t="s">
         <v>180</v>
@@ -24303,13 +24293,13 @@
     </row>
     <row r="59" spans="1:43" ht="15.75" customHeight="1">
       <c r="A59" s="358" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="B59" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="328" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="D59" s="308" t="s">
         <v>180</v>
@@ -24374,7 +24364,7 @@
     </row>
     <row r="60" spans="1:43" ht="15.75" customHeight="1">
       <c r="A60" s="358" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="B60" s="32" t="s">
         <v>43</v>
@@ -24449,18 +24439,18 @@
     </row>
     <row r="61" spans="1:43" ht="15.75" customHeight="1">
       <c r="A61" s="358" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="B61" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="328" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="D61" s="309"/>
       <c r="E61" s="62"/>
       <c r="F61" s="48" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>554</v>
@@ -24520,7 +24510,7 @@
     </row>
     <row r="62" spans="1:43" ht="15.75" customHeight="1">
       <c r="A62" s="358" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="B62" s="32" t="s">
         <v>43</v>
@@ -24593,13 +24583,13 @@
         <v>569</v>
       </c>
       <c r="C63" s="328" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="D63" s="308" t="s">
         <v>570</v>
       </c>
       <c r="E63" s="62" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="F63" s="371" t="s">
         <v>571</v>
@@ -24660,13 +24650,13 @@
     </row>
     <row r="64" spans="1:43" ht="15.75" customHeight="1">
       <c r="A64" s="358" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="328" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="D64" s="309"/>
       <c r="E64" s="62"/>
@@ -24733,13 +24723,13 @@
     </row>
     <row r="65" spans="1:43" ht="15.75" customHeight="1">
       <c r="A65" s="358" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="B65" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="328" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="D65" s="309"/>
       <c r="E65" s="62"/>
@@ -24806,7 +24796,7 @@
     </row>
     <row r="66" spans="1:43" ht="15.75" customHeight="1">
       <c r="A66" s="358" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="B66" s="32" t="s">
         <v>43</v>
@@ -25039,7 +25029,7 @@
     </row>
     <row r="69" spans="1:43" ht="15.75" customHeight="1">
       <c r="A69" s="358" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="B69" s="32" t="s">
         <v>43</v>
@@ -25126,7 +25116,7 @@
     </row>
     <row r="70" spans="1:43" ht="15.75" customHeight="1">
       <c r="A70" s="355" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="B70" s="32" t="s">
         <v>43</v>
@@ -25195,13 +25185,13 @@
     </row>
     <row r="71" spans="1:43" ht="15.75" customHeight="1">
       <c r="A71" s="358" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="B71" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="328" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="D71" s="309"/>
       <c r="E71" s="62"/>
@@ -25264,7 +25254,7 @@
     </row>
     <row r="72" spans="1:43" ht="15.75" customHeight="1">
       <c r="A72" s="355" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="B72" s="32" t="s">
         <v>649</v>
@@ -25410,7 +25400,7 @@
     </row>
     <row r="74" spans="1:43" ht="15.75" customHeight="1">
       <c r="A74" s="355" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="B74" s="39" t="s">
         <v>43</v>
@@ -25485,7 +25475,7 @@
         <v>43</v>
       </c>
       <c r="C75" s="328" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="D75" s="315"/>
       <c r="E75" s="62"/>
@@ -26132,7 +26122,7 @@
     </row>
     <row r="84" spans="1:43" ht="15.75" customHeight="1">
       <c r="A84" s="355" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>754</v>
@@ -26268,7 +26258,7 @@
     </row>
     <row r="86" spans="1:43" ht="15.75" customHeight="1">
       <c r="A86" s="355" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>439</v>
@@ -26645,7 +26635,7 @@
     </row>
     <row r="91" spans="1:43" ht="15.75" customHeight="1">
       <c r="A91" s="355" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>43</v>
@@ -26998,7 +26988,7 @@
     </row>
     <row r="96" spans="1:43" ht="15.75" customHeight="1">
       <c r="A96" s="358" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>439</v>
@@ -27065,7 +27055,7 @@
     </row>
     <row r="97" spans="1:43" ht="15.75" customHeight="1">
       <c r="A97" s="358" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="B97" s="32" t="s">
         <v>43</v>
@@ -27268,7 +27258,7 @@
     </row>
     <row r="100" spans="1:43" ht="15.75" customHeight="1">
       <c r="A100" s="358" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
       <c r="B100" s="32" t="s">
         <v>875</v>
@@ -27414,7 +27404,7 @@
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
       <c r="A102" s="358" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>895</v>
@@ -27560,7 +27550,7 @@
     </row>
     <row r="104" spans="1:43" ht="15.75" customHeight="1">
       <c r="A104" s="358" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="B104" s="32" t="s">
         <v>476</v>
@@ -27773,7 +27763,7 @@
     </row>
     <row r="107" spans="1:43" ht="15.75" customHeight="1">
       <c r="A107" s="358" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="B107" s="32" t="s">
         <v>43</v>
@@ -27856,7 +27846,7 @@
     </row>
     <row r="108" spans="1:43" ht="15.75" customHeight="1">
       <c r="A108" s="358" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="B108" s="32" t="s">
         <v>43</v>
@@ -28063,7 +28053,7 @@
     </row>
     <row r="111" spans="1:43" ht="15.75" customHeight="1">
       <c r="A111" s="358" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="B111" s="32" t="s">
         <v>43</v>
@@ -28639,7 +28629,7 @@
     </row>
     <row r="119" spans="1:43" ht="15.75" customHeight="1">
       <c r="A119" s="358" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>43</v>
@@ -28850,7 +28840,7 @@
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
       <c r="A122" s="359" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="B122" s="52" t="s">
         <v>43</v>
@@ -29367,7 +29357,7 @@
     </row>
     <row r="129" spans="1:43" ht="15.75" customHeight="1">
       <c r="A129" s="359" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="B129" s="32" t="s">
         <v>43</v>
@@ -29438,7 +29428,7 @@
     </row>
     <row r="130" spans="1:43" ht="15.75" customHeight="1">
       <c r="A130" s="358" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>43</v>
@@ -29511,7 +29501,7 @@
     </row>
     <row r="131" spans="1:43" ht="15.75" customHeight="1">
       <c r="A131" s="358" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="B131" s="33" t="s">
         <v>43</v>
@@ -29947,7 +29937,7 @@
     </row>
     <row r="137" spans="1:43" ht="15.75" customHeight="1">
       <c r="A137" s="358" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>43</v>
@@ -30087,7 +30077,7 @@
     </row>
     <row r="139" spans="1:43" ht="15.75" customHeight="1">
       <c r="A139" s="359" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="B139" s="33" t="s">
         <v>43</v>
@@ -32275,7 +32265,7 @@
     </row>
     <row r="169" spans="1:43" ht="15.75" customHeight="1">
       <c r="A169" s="358" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
       <c r="B169" s="33" t="s">
         <v>43</v>
@@ -32705,7 +32695,7 @@
     </row>
     <row r="175" spans="1:43" ht="15.75" customHeight="1">
       <c r="A175" s="358" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="B175" s="33" t="s">
         <v>43</v>
@@ -32774,7 +32764,7 @@
     </row>
     <row r="176" spans="1:43" ht="15.75" customHeight="1">
       <c r="A176" s="358" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="B176" s="33" t="s">
         <v>43</v>
@@ -32841,7 +32831,7 @@
     </row>
     <row r="177" spans="1:43" ht="15.75" customHeight="1">
       <c r="A177" s="359" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="B177" s="15" t="s">
         <v>476</v>
@@ -33299,7 +33289,7 @@
     </row>
     <row r="183" spans="1:43" ht="15.75" customHeight="1">
       <c r="A183" s="358" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="B183" s="33" t="s">
         <v>43</v>
@@ -33368,7 +33358,7 @@
     </row>
     <row r="184" spans="1:43" ht="15.75" customHeight="1">
       <c r="A184" s="358" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="B184" s="33" t="s">
         <v>43</v>
@@ -33802,7 +33792,7 @@
     </row>
     <row r="190" spans="1:43" ht="15.75" customHeight="1">
       <c r="A190" s="359" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="B190" s="15" t="s">
         <v>43</v>
@@ -34013,13 +34003,13 @@
     </row>
     <row r="193" spans="1:43" ht="15.75" customHeight="1">
       <c r="A193" s="358" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="B193" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C193" s="329" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="D193" s="309"/>
       <c r="E193" s="62"/>
@@ -34887,7 +34877,7 @@
     </row>
     <row r="205" spans="1:43" ht="15.75" customHeight="1">
       <c r="A205" s="358" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="B205" s="33" t="s">
         <v>43</v>
@@ -35033,7 +35023,7 @@
     </row>
     <row r="207" spans="1:43" ht="15.75" customHeight="1">
       <c r="A207" s="358" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>439</v>
@@ -35351,7 +35341,7 @@
     </row>
     <row r="211" spans="1:43" ht="15.75" customHeight="1">
       <c r="A211" s="358" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>1012</v>
@@ -35513,7 +35503,7 @@
     </row>
     <row r="213" spans="1:43" ht="15.75" customHeight="1">
       <c r="A213" s="358" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>439</v>
@@ -35566,7 +35556,7 @@
       <c r="AB213" s="206"/>
       <c r="AC213" s="32"/>
       <c r="AD213" s="21" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="AE213" s="32"/>
       <c r="AF213" s="32"/>
@@ -36166,7 +36156,7 @@
     </row>
     <row r="222" spans="1:43" ht="15.75" customHeight="1">
       <c r="A222" s="359" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>439</v>
@@ -36324,7 +36314,7 @@
     </row>
     <row r="224" spans="1:43" ht="15.75" customHeight="1">
       <c r="A224" s="358" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>439</v>
@@ -36610,7 +36600,7 @@
     </row>
     <row r="228" spans="1:43" ht="15.75" customHeight="1">
       <c r="A228" s="358" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="B228" s="14" t="s">
         <v>1929</v>
@@ -37052,13 +37042,13 @@
     </row>
     <row r="234" spans="1:43" ht="15.75" customHeight="1">
       <c r="A234" s="358" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>439</v>
       </c>
       <c r="C234" s="342" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="D234" s="309"/>
       <c r="E234" s="62"/>
@@ -37528,7 +37518,7 @@
     </row>
     <row r="240" spans="1:43" ht="15.75" customHeight="1">
       <c r="A240" s="358" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>439</v>
@@ -38073,7 +38063,7 @@
         <v>2102</v>
       </c>
       <c r="C247" s="343" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="E247" s="299"/>
       <c r="F247" s="299" t="s">
@@ -38094,7 +38084,7 @@
       <c r="M247" s="297" t="s">
         <v>1916</v>
       </c>
-      <c r="N247" s="298" t="s">
+      <c r="N247" s="182" t="s">
         <v>2104</v>
       </c>
       <c r="O247" s="298"/>
@@ -38118,7 +38108,7 @@
       <c r="W247" s="299"/>
       <c r="X247" s="299"/>
       <c r="Y247" s="302" t="s">
-        <v>3831</v>
+        <v>4012</v>
       </c>
       <c r="Z247" s="299"/>
       <c r="AA247" s="299"/>
@@ -38126,7 +38116,9 @@
       <c r="AC247" s="296" t="s">
         <v>2105</v>
       </c>
-      <c r="AD247" s="299"/>
+      <c r="AD247" s="299" t="s">
+        <v>4013</v>
+      </c>
       <c r="AE247" s="299"/>
       <c r="AF247" s="299"/>
       <c r="AG247" s="299"/>
@@ -38149,7 +38141,7 @@
         <v>3823</v>
       </c>
       <c r="C248" s="343" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="E248" s="299"/>
       <c r="F248" s="299"/>
@@ -38511,7 +38503,7 @@
         <v>439</v>
       </c>
       <c r="C253" s="329" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="D253" s="309"/>
       <c r="E253" s="62"/>
@@ -38870,7 +38862,7 @@
     </row>
     <row r="258" spans="1:43" ht="15.75" customHeight="1">
       <c r="A258" s="358" t="s">
-        <v>3920</v>
+        <v>3919</v>
       </c>
       <c r="B258" s="14" t="s">
         <v>439</v>
@@ -39237,7 +39229,7 @@
     </row>
     <row r="263" spans="1:43" ht="15.75" customHeight="1">
       <c r="A263" s="358" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
       <c r="B263" s="14" t="s">
         <v>439</v>
@@ -39444,7 +39436,7 @@
     </row>
     <row r="266" spans="1:43" ht="15.75" customHeight="1">
       <c r="A266" s="358" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
       <c r="B266" s="14" t="s">
         <v>439</v>
@@ -39663,7 +39655,7 @@
     </row>
     <row r="269" spans="1:43" ht="15.75" customHeight="1">
       <c r="A269" s="359" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
       <c r="B269" s="71" t="s">
         <v>2262</v>
@@ -41537,7 +41529,7 @@
     </row>
     <row r="295" spans="1:43" ht="15.75" customHeight="1">
       <c r="A295" s="358" t="s">
-        <v>3916</v>
+        <v>3915</v>
       </c>
       <c r="B295" s="14" t="s">
         <v>439</v>
@@ -42332,7 +42324,7 @@
     </row>
     <row r="306" spans="1:43" ht="15.75" customHeight="1">
       <c r="A306" s="363" t="s">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="B306" s="33" t="s">
         <v>439</v>
@@ -42490,7 +42482,7 @@
     </row>
     <row r="308" spans="1:43" ht="15.75" customHeight="1">
       <c r="A308" s="363" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="B308" s="33" t="s">
         <v>439</v>
@@ -42644,7 +42636,7 @@
     </row>
     <row r="310" spans="1:43" ht="15.75" customHeight="1">
       <c r="A310" s="365" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="B310" s="33" t="s">
         <v>439</v>
@@ -43240,13 +43232,13 @@
     </row>
     <row r="318" spans="1:43" ht="15.75" customHeight="1">
       <c r="A318" s="366" t="s">
-        <v>3912</v>
+        <v>3911</v>
       </c>
       <c r="B318" s="33" t="s">
         <v>2636</v>
       </c>
       <c r="C318" s="344" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="E318" s="62" t="s">
         <v>2637</v>
@@ -43399,7 +43391,7 @@
     </row>
     <row r="320" spans="1:43" ht="15.75" customHeight="1">
       <c r="A320" s="363" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
       <c r="B320" s="33" t="s">
         <v>439</v>
@@ -43468,7 +43460,7 @@
     </row>
     <row r="321" spans="1:43" ht="15.75" customHeight="1">
       <c r="A321" s="363" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="B321" s="33" t="s">
         <v>439</v>
@@ -44005,7 +43997,7 @@
         <v>439</v>
       </c>
       <c r="C328" s="329" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="D328" s="324"/>
       <c r="E328" s="238"/>
@@ -45071,7 +45063,7 @@
     </row>
     <row r="342" spans="1:43" ht="15.75" customHeight="1">
       <c r="A342" s="363" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="B342" s="33" t="s">
         <v>439</v>
@@ -45300,7 +45292,7 @@
     </row>
     <row r="345" spans="1:43" ht="15.75" customHeight="1">
       <c r="A345" s="363" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="B345" s="33" t="s">
         <v>439</v>
@@ -46921,7 +46913,7 @@
     </row>
     <row r="366" spans="1:43" ht="15.75" customHeight="1">
       <c r="A366" s="363" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="B366" s="33" t="s">
         <v>439</v>
@@ -47719,11 +47711,11 @@
       </c>
       <c r="E376" s="299"/>
       <c r="F376" s="302" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="G376" s="299"/>
       <c r="H376" s="296" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="I376" s="296" t="s">
         <v>3131</v>
@@ -47747,7 +47739,7 @@
         <v>41</v>
       </c>
       <c r="T376" s="296" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
       <c r="U376" s="299"/>
       <c r="V376" s="299"/>
@@ -47759,7 +47751,7 @@
       <c r="AB376" s="299"/>
       <c r="AC376" s="299"/>
       <c r="AD376" s="296" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="AE376" s="299"/>
       <c r="AF376" s="299"/>
@@ -48249,7 +48241,7 @@
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
       <c r="A383" s="363" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>439</v>
@@ -48318,7 +48310,7 @@
     </row>
     <row r="384" spans="1:43" ht="15.75" customHeight="1">
       <c r="A384" s="363" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="B384" s="33" t="s">
         <v>439</v>
@@ -48531,7 +48523,7 @@
     </row>
     <row r="387" spans="1:43" ht="15.75" customHeight="1">
       <c r="A387" s="363" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="B387" s="33" t="s">
         <v>439</v>
@@ -48613,18 +48605,18 @@
         <v>3215</v>
       </c>
       <c r="B388" s="297" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="C388" s="343" t="s">
         <v>172</v>
       </c>
       <c r="E388" s="299"/>
       <c r="F388" s="302" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="G388" s="299"/>
       <c r="H388" s="303" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="I388" s="303" t="s">
         <v>3216</v>
@@ -48632,7 +48624,7 @@
       <c r="J388" s="299"/>
       <c r="K388" s="299"/>
       <c r="L388" s="299" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="M388" s="304" t="s">
         <v>2100</v>
@@ -48650,7 +48642,7 @@
         <v>41</v>
       </c>
       <c r="T388" s="296" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="U388" s="299"/>
       <c r="V388" s="299"/>
@@ -48662,7 +48654,7 @@
       <c r="AB388" s="299"/>
       <c r="AC388" s="299"/>
       <c r="AD388" s="296" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="AE388" s="299"/>
       <c r="AF388" s="299"/>
@@ -49298,7 +49290,7 @@
     </row>
     <row r="397" spans="1:43" ht="15.75" customHeight="1">
       <c r="A397" s="363" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="B397" s="33" t="s">
         <v>439</v>
@@ -49313,7 +49305,7 @@
       </c>
       <c r="G397" s="32"/>
       <c r="H397" s="375" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="I397" s="240" t="s">
         <v>2544</v>
@@ -49430,7 +49422,7 @@
     </row>
     <row r="399" spans="1:43" ht="15.75" customHeight="1">
       <c r="A399" s="363" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="B399" s="33" t="s">
         <v>439</v>
@@ -49659,7 +49651,7 @@
     </row>
     <row r="402" spans="1:43" ht="15.75" customHeight="1">
       <c r="A402" s="376" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="B402" s="33" t="s">
         <v>439</v>
@@ -49902,7 +49894,7 @@
     </row>
     <row r="405" spans="1:43" ht="15.75" customHeight="1">
       <c r="A405" s="363" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="B405" s="14" t="s">
         <v>439</v>
@@ -50131,13 +50123,13 @@
     </row>
     <row r="408" spans="1:43" ht="15.75" customHeight="1">
       <c r="A408" s="363" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="B408" s="33" t="s">
         <v>439</v>
       </c>
       <c r="C408" s="329" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="D408" s="324"/>
       <c r="E408" s="238"/>
@@ -50204,7 +50196,7 @@
     </row>
     <row r="409" spans="1:43" ht="15.75" customHeight="1">
       <c r="A409" s="368" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="B409" s="33" t="s">
         <v>439</v>
@@ -50579,7 +50571,7 @@
     </row>
     <row r="414" spans="1:43" ht="15.75" customHeight="1">
       <c r="A414" s="368" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="B414" s="33" t="s">
         <v>439</v>
@@ -50654,13 +50646,13 @@
     </row>
     <row r="415" spans="1:43" ht="15.75" customHeight="1">
       <c r="A415" s="380" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="B415" s="33" t="s">
         <v>439</v>
       </c>
       <c r="C415" s="335" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="D415" s="309"/>
       <c r="E415" s="62"/>
@@ -50733,7 +50725,7 @@
     </row>
     <row r="416" spans="1:43" ht="15.75" customHeight="1">
       <c r="A416" s="363" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="B416" s="33" t="s">
         <v>439</v>
@@ -50800,7 +50792,7 @@
     </row>
     <row r="417" spans="1:43" ht="15.75" customHeight="1">
       <c r="A417" s="241" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="B417" s="33" t="s">
         <v>439</v>
@@ -50869,13 +50861,13 @@
     </row>
     <row r="418" spans="1:43" ht="15.75" customHeight="1">
       <c r="A418" s="234" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="B418" s="33" t="s">
         <v>439</v>
       </c>
       <c r="C418" s="379" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D418" s="309"/>
       <c r="E418" s="62"/>
@@ -51019,7 +51011,7 @@
         <v>439</v>
       </c>
       <c r="C420" s="379" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="D420" s="324"/>
       <c r="E420" s="62"/>
@@ -51256,7 +51248,7 @@
     </row>
     <row r="423" spans="1:43" ht="15.75" customHeight="1">
       <c r="A423" s="234" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="B423" s="14" t="s">
         <v>439</v>
@@ -51327,7 +51319,7 @@
     </row>
     <row r="424" spans="1:43" ht="15.75" customHeight="1">
       <c r="A424" s="368" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="B424" s="33" t="s">
         <v>439</v>
@@ -51682,7 +51674,7 @@
     </row>
     <row r="429" spans="1:43" ht="15.75" customHeight="1">
       <c r="A429" s="363" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="B429" s="33" t="s">
         <v>439</v>
@@ -51747,7 +51739,7 @@
     </row>
     <row r="430" spans="1:43" ht="15.75" customHeight="1">
       <c r="A430" s="363" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="B430" s="33" t="s">
         <v>439</v>
@@ -51812,7 +51804,7 @@
     </row>
     <row r="431" spans="1:43" ht="15.75" customHeight="1">
       <c r="A431" s="363" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="B431" s="33" t="s">
         <v>439</v>
@@ -52027,7 +52019,7 @@
     </row>
     <row r="434" spans="1:43" ht="15.75" customHeight="1">
       <c r="A434" s="234" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="B434" s="33" t="s">
         <v>439</v>
@@ -52092,7 +52084,7 @@
     </row>
     <row r="435" spans="1:43" ht="15.75" customHeight="1">
       <c r="A435" s="363" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="B435" s="33" t="s">
         <v>439</v>
@@ -52238,7 +52230,7 @@
     </row>
     <row r="437" spans="1:43" ht="15.75" customHeight="1">
       <c r="A437" s="363" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="B437" s="33" t="s">
         <v>439</v>
@@ -52397,7 +52389,7 @@
       <c r="D439" s="309"/>
       <c r="E439" s="62"/>
       <c r="F439" s="371" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="G439" s="32"/>
       <c r="H439" s="259" t="s">
@@ -52467,7 +52459,7 @@
         <v>439</v>
       </c>
       <c r="C440" s="378" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="D440" s="309"/>
       <c r="E440" s="62"/>
@@ -52621,7 +52613,7 @@
     </row>
     <row r="442" spans="1:43" ht="15.75" customHeight="1">
       <c r="A442" s="380" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="B442" s="33" t="s">
         <v>439</v>
@@ -52925,7 +52917,7 @@
     </row>
     <row r="446" spans="1:43" ht="15.75" customHeight="1">
       <c r="A446" s="380" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="B446" s="33" t="s">
         <v>439</v>
@@ -52998,7 +52990,7 @@
     </row>
     <row r="447" spans="1:43" ht="15.75" customHeight="1">
       <c r="A447" s="234" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="B447" s="33" t="s">
         <v>439</v>
@@ -53503,7 +53495,7 @@
     </row>
     <row r="454" spans="1:43" ht="15.75" customHeight="1">
       <c r="A454" s="234" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="B454" s="108" t="s">
         <v>439</v>
@@ -53518,7 +53510,7 @@
       </c>
       <c r="G454" s="32"/>
       <c r="H454" s="240" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="I454" s="32" t="s">
         <v>3637</v>
@@ -53655,7 +53647,7 @@
     </row>
     <row r="456" spans="1:43" ht="15.75" customHeight="1">
       <c r="A456" s="380" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="B456" s="32" t="s">
         <v>439</v>
@@ -53736,7 +53728,7 @@
     </row>
     <row r="457" spans="1:43" ht="15.75" customHeight="1">
       <c r="A457" s="380" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="B457" s="108" t="s">
         <v>2310</v>
@@ -53817,7 +53809,7 @@
     </row>
     <row r="458" spans="1:43" ht="15.75" customHeight="1">
       <c r="A458" s="380" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="B458" s="108" t="s">
         <v>2310</v>
@@ -53965,7 +53957,7 @@
     </row>
     <row r="460" spans="1:43" ht="15.75" customHeight="1">
       <c r="A460" s="368" t="s">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="B460" s="108" t="s">
         <v>2310</v>
@@ -54040,7 +54032,7 @@
     </row>
     <row r="461" spans="1:43" ht="15.75" customHeight="1">
       <c r="A461" s="234" t="s">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="B461" s="108" t="s">
         <v>2310</v>
@@ -54265,7 +54257,7 @@
     </row>
     <row r="464" spans="1:43" ht="15.75" customHeight="1">
       <c r="A464" s="368" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="B464" s="108" t="s">
         <v>2310</v>
@@ -54342,7 +54334,7 @@
     </row>
     <row r="465" spans="1:43" ht="15.75" customHeight="1">
       <c r="A465" s="380" t="s">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="B465" s="108" t="s">
         <v>439</v>
@@ -54419,7 +54411,7 @@
     </row>
     <row r="466" spans="1:43" ht="15.75" customHeight="1">
       <c r="A466" s="369" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="B466" s="108" t="s">
         <v>439</v>
@@ -54575,7 +54567,7 @@
         <v>2310</v>
       </c>
       <c r="C468" s="328" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="D468" s="309"/>
       <c r="E468" s="62"/>
@@ -54644,7 +54636,7 @@
     </row>
     <row r="469" spans="1:43" ht="15.75" customHeight="1">
       <c r="A469" s="380" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="B469" s="108" t="s">
         <v>439</v>
@@ -54796,12 +54788,12 @@
         <v>2310</v>
       </c>
       <c r="C471" s="378" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="D471" s="309"/>
       <c r="E471" s="62"/>
       <c r="F471" s="371" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="G471" s="39"/>
       <c r="H471" s="49" t="s">
@@ -54926,7 +54918,7 @@
     </row>
     <row r="473" spans="1:43" ht="15.75" customHeight="1">
       <c r="A473" s="234" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="B473" s="108" t="s">
         <v>2310</v>
@@ -55001,7 +54993,7 @@
     </row>
     <row r="474" spans="1:43" ht="15.75" customHeight="1">
       <c r="A474" s="363" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="B474" s="108" t="s">
         <v>2310</v>
@@ -64459,7 +64451,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{851FEAAE-A936-B345-A6A3-FF2BCED4EF5D}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{0E1F4BCB-E13B-424C-86AF-D3A044E37BE2}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1F6F4F-BA58-3040-89E5-25CE88BF439D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54E29C9-5F8F-C142-ADAA-2EAA394BD2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="-19700" windowWidth="31040" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1240" yWindow="-17820" windowWidth="31040" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CF6CF5-783E-C846-8AD3-C2A336C15FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3119306-6EAC-C04D-B2DC-33DDCBCB7282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3740" yWindow="-18900" windowWidth="31040" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F93075-AF2D-5645-AF4C-34A7EFFA7BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5275BC-8D44-184E-A545-A41651B940DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19960" yWindow="-27420" windowWidth="57480" windowHeight="25480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7340" yWindow="-27540" windowWidth="57480" windowHeight="25480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6998" uniqueCount="4016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7000" uniqueCount="4016">
   <si>
     <t>ID estampe</t>
   </si>
@@ -29774,8 +29774,12 @@
         <v>2036</v>
       </c>
       <c r="O131" s="54"/>
-      <c r="P131" s="25"/>
-      <c r="Q131" s="56"/>
+      <c r="P131" s="130" t="s">
+        <v>1919</v>
+      </c>
+      <c r="Q131" s="26" t="s">
+        <v>1920</v>
+      </c>
       <c r="R131" s="99" t="s">
         <v>391</v>
       </c>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E99E9E-D20C-0649-8F83-A0B610D3EB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15D577B-9563-0548-B22A-E2CBD33BA467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-7340" yWindow="-27540" windowWidth="57480" windowHeight="25480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7000" uniqueCount="4016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7001" uniqueCount="4015">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17464,9 +17464,6 @@
   </si>
   <si>
     <t>Le principe du pantographe, outil de reproduction de dessins à différentes échelles (aussi appelé singe), a été énoncé en 1603 par le jésuite Christophe Scheiner. Voir aussi article dans l'Encyclopédie, XI, p. 827.</t>
-  </si>
-  <si>
-    <t>Antier, Vincent</t>
   </si>
   <si>
     <t>[Planche (4e du traité des lunetes) figurant un binocle accompagné d'une légende sur son fonctionnement]*</t>
@@ -18673,7 +18670,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="470">
+  <cellXfs count="469">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -19662,9 +19659,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="133" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="133" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20472,7 +20466,7 @@
       <c r="Q3" s="26" t="s">
         <v>2365</v>
       </c>
-      <c r="R3" s="352" t="s">
+      <c r="R3" s="351" t="s">
         <v>1432</v>
       </c>
       <c r="S3" s="32" t="s">
@@ -20541,7 +20535,7 @@
       <c r="O4" s="54"/>
       <c r="P4" s="55"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="352" t="s">
+      <c r="R4" s="351" t="s">
         <v>655</v>
       </c>
       <c r="S4" s="32" t="s">
@@ -20610,7 +20604,7 @@
       <c r="O5" s="54"/>
       <c r="P5" s="55"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="361" t="s">
+      <c r="R5" s="360" t="s">
         <v>655</v>
       </c>
       <c r="S5" s="32" t="s">
@@ -20679,7 +20673,7 @@
       <c r="O6" s="38"/>
       <c r="P6" s="25"/>
       <c r="Q6" s="26"/>
-      <c r="R6" s="431" t="s">
+      <c r="R6" s="430" t="s">
         <v>81</v>
       </c>
       <c r="S6" s="40" t="s">
@@ -20756,7 +20750,7 @@
       <c r="Q7" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="R7" s="431" t="s">
+      <c r="R7" s="430" t="s">
         <v>81</v>
       </c>
       <c r="S7" s="40" t="s">
@@ -20767,10 +20761,10 @@
       </c>
       <c r="U7" s="28"/>
       <c r="V7" s="28"/>
-      <c r="W7" s="453" t="s">
+      <c r="W7" s="452" t="s">
         <v>111</v>
       </c>
-      <c r="X7" s="453" t="s">
+      <c r="X7" s="452" t="s">
         <v>112</v>
       </c>
       <c r="Y7" s="62" t="s">
@@ -20802,7 +20796,7 @@
       <c r="B8" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="359" t="s">
+      <c r="C8" s="358" t="s">
         <v>124</v>
       </c>
       <c r="D8" s="253"/>
@@ -20828,7 +20822,7 @@
       <c r="N8" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="O8" s="407"/>
+      <c r="O8" s="406"/>
       <c r="P8" s="130"/>
       <c r="Q8" s="26"/>
       <c r="R8" s="49" t="s">
@@ -20900,7 +20894,7 @@
       <c r="O9" s="84"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="26"/>
-      <c r="R9" s="431" t="s">
+      <c r="R9" s="430" t="s">
         <v>81</v>
       </c>
       <c r="S9" s="32" t="s">
@@ -21038,7 +21032,7 @@
       <c r="O11" s="54"/>
       <c r="P11" s="55"/>
       <c r="Q11" s="56"/>
-      <c r="R11" s="422" t="s">
+      <c r="R11" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S11" s="32" t="s">
@@ -21103,13 +21097,13 @@
       <c r="M12" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="N12" s="408" t="s">
+      <c r="N12" s="407" t="s">
         <v>424</v>
       </c>
-      <c r="O12" s="408"/>
+      <c r="O12" s="407"/>
       <c r="P12" s="118"/>
       <c r="Q12" s="127"/>
-      <c r="R12" s="422" t="s">
+      <c r="R12" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S12" s="32" t="s">
@@ -21180,7 +21174,7 @@
       <c r="Q13" s="133" t="s">
         <v>458</v>
       </c>
-      <c r="R13" s="422" t="s">
+      <c r="R13" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S13" s="32" t="s">
@@ -21265,7 +21259,7 @@
       <c r="Q14" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="R14" s="422" t="s">
+      <c r="R14" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S14" s="32" t="s">
@@ -21312,7 +21306,7 @@
       <c r="C15" s="279" t="s">
         <v>172</v>
       </c>
-      <c r="D15" s="366" t="s">
+      <c r="D15" s="365" t="s">
         <v>601</v>
       </c>
       <c r="E15" s="58" t="s">
@@ -21409,7 +21403,7 @@
       <c r="O16" s="38"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="145"/>
-      <c r="R16" s="422" t="s">
+      <c r="R16" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S16" s="32" t="s">
@@ -21474,7 +21468,7 @@
       <c r="O17" s="38"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="26"/>
-      <c r="R17" s="422" t="s">
+      <c r="R17" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S17" s="32" t="s">
@@ -21545,7 +21539,7 @@
       <c r="Q18" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="R18" s="422" t="s">
+      <c r="R18" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S18" s="32" t="s">
@@ -21622,7 +21616,7 @@
       <c r="O19" s="54"/>
       <c r="P19" s="55"/>
       <c r="Q19" s="56"/>
-      <c r="R19" s="422" t="s">
+      <c r="R19" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S19" s="32" t="s">
@@ -21689,7 +21683,7 @@
       <c r="O20" s="54"/>
       <c r="P20" s="55"/>
       <c r="Q20" s="56"/>
-      <c r="R20" s="422" t="s">
+      <c r="R20" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S20" s="32" t="s">
@@ -21756,7 +21750,7 @@
       <c r="O21" s="66"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="26"/>
-      <c r="R21" s="422" t="s">
+      <c r="R21" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S21" s="21" t="s">
@@ -21831,7 +21825,7 @@
       <c r="O22" s="54"/>
       <c r="P22" s="55"/>
       <c r="Q22" s="56"/>
-      <c r="R22" s="422" t="s">
+      <c r="R22" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S22" s="32" t="s">
@@ -21898,7 +21892,7 @@
       <c r="O23" s="38"/>
       <c r="P23" s="25"/>
       <c r="Q23" s="26"/>
-      <c r="R23" s="422" t="s">
+      <c r="R23" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S23" s="32" t="s">
@@ -22119,7 +22113,7 @@
       <c r="O26" s="54"/>
       <c r="P26" s="55"/>
       <c r="Q26" s="56"/>
-      <c r="R26" s="422" t="s">
+      <c r="R26" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S26" s="32" t="s">
@@ -22184,7 +22178,7 @@
       <c r="O27" s="38"/>
       <c r="P27" s="25"/>
       <c r="Q27" s="26"/>
-      <c r="R27" s="422" t="s">
+      <c r="R27" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S27" s="32" t="s">
@@ -22253,7 +22247,7 @@
       <c r="Q28" s="56" t="s">
         <v>2400</v>
       </c>
-      <c r="R28" s="381" t="s">
+      <c r="R28" s="380" t="s">
         <v>81</v>
       </c>
       <c r="S28" s="32" t="s">
@@ -22267,7 +22261,7 @@
         <v>2402</v>
       </c>
       <c r="W28" s="73"/>
-      <c r="X28" s="453" t="s">
+      <c r="X28" s="452" t="s">
         <v>2403</v>
       </c>
       <c r="Y28" s="30" t="s">
@@ -22330,7 +22324,7 @@
       <c r="O29" s="38"/>
       <c r="P29" s="25"/>
       <c r="Q29" s="56"/>
-      <c r="R29" s="422" t="s">
+      <c r="R29" s="421" t="s">
         <v>81</v>
       </c>
       <c r="S29" s="78" t="s">
@@ -22469,10 +22463,10 @@
         <v>2582</v>
       </c>
       <c r="J31" s="22"/>
-      <c r="K31" s="396" t="s">
+      <c r="K31" s="395" t="s">
         <v>34</v>
       </c>
-      <c r="L31" s="396"/>
+      <c r="L31" s="395"/>
       <c r="M31" s="226" t="s">
         <v>3299</v>
       </c>
@@ -22480,11 +22474,11 @@
         <v>3300</v>
       </c>
       <c r="O31" s="38"/>
-      <c r="P31" s="342" t="s">
+      <c r="P31" s="341" t="s">
         <v>38</v>
       </c>
-      <c r="Q31" s="344" t="s">
-        <v>4013</v>
+      <c r="Q31" s="343" t="s">
+        <v>4012</v>
       </c>
       <c r="R31" s="119" t="s">
         <v>81</v>
@@ -22729,7 +22723,7 @@
       <c r="AA34" s="30"/>
       <c r="AB34" s="41"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="352"/>
+      <c r="AD34" s="351"/>
       <c r="AE34" s="32"/>
       <c r="AF34" s="32"/>
       <c r="AG34" s="32"/>
@@ -22791,8 +22785,8 @@
       <c r="V35" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="W35" s="452"/>
-      <c r="X35" s="452"/>
+      <c r="W35" s="451"/>
+      <c r="X35" s="451"/>
       <c r="Y35" s="30" t="s">
         <v>100</v>
       </c>
@@ -22913,15 +22907,15 @@
         <v>120</v>
       </c>
       <c r="J37" s="77"/>
-      <c r="K37" s="390"/>
-      <c r="L37" s="390"/>
+      <c r="K37" s="389"/>
+      <c r="L37" s="389"/>
       <c r="M37" s="53" t="s">
         <v>93</v>
       </c>
       <c r="N37" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="O37" s="408"/>
+      <c r="O37" s="407"/>
       <c r="P37" s="118"/>
       <c r="Q37" s="56"/>
       <c r="R37" s="32" t="s">
@@ -22936,7 +22930,7 @@
       <c r="W37" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="X37" s="456" t="s">
+      <c r="X37" s="455" t="s">
         <v>168</v>
       </c>
       <c r="Y37" s="81" t="s">
@@ -22998,7 +22992,7 @@
       <c r="N38" s="54" t="s">
         <v>279</v>
       </c>
-      <c r="O38" s="408"/>
+      <c r="O38" s="407"/>
       <c r="P38" s="118"/>
       <c r="Q38" s="56"/>
       <c r="R38" s="32" t="s">
@@ -23015,7 +23009,7 @@
       <c r="W38" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="X38" s="456" t="s">
+      <c r="X38" s="455" t="s">
         <v>168</v>
       </c>
       <c r="Y38" s="62" t="s">
@@ -23047,7 +23041,7 @@
       <c r="B39" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="C39" s="359" t="s">
+      <c r="C39" s="358" t="s">
         <v>273</v>
       </c>
       <c r="D39" s="261"/>
@@ -23090,7 +23084,7 @@
       <c r="W39" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="X39" s="456" t="s">
+      <c r="X39" s="455" t="s">
         <v>168</v>
       </c>
       <c r="Y39" s="30" t="s">
@@ -23409,7 +23403,7 @@
       <c r="G44" s="32" t="s">
         <v>532</v>
       </c>
-      <c r="H44" s="383" t="s">
+      <c r="H44" s="382" t="s">
         <v>533</v>
       </c>
       <c r="I44" s="43" t="s">
@@ -23696,7 +23690,7 @@
       <c r="F48" s="16" t="s">
         <v>678</v>
       </c>
-      <c r="G48" s="352" t="s">
+      <c r="G48" s="351" t="s">
         <v>679</v>
       </c>
       <c r="H48" s="40" t="s">
@@ -23708,13 +23702,13 @@
       <c r="J48" s="22"/>
       <c r="K48" s="22"/>
       <c r="L48" s="22"/>
-      <c r="M48" s="400" t="s">
+      <c r="M48" s="399" t="s">
         <v>93</v>
       </c>
       <c r="N48" s="54" t="s">
         <v>681</v>
       </c>
-      <c r="O48" s="408"/>
+      <c r="O48" s="407"/>
       <c r="P48" s="118"/>
       <c r="Q48" s="127"/>
       <c r="R48" s="32" t="s">
@@ -23732,7 +23726,7 @@
       <c r="Z48" s="30"/>
       <c r="AA48" s="30"/>
       <c r="AB48" s="113"/>
-      <c r="AC48" s="352"/>
+      <c r="AC48" s="351"/>
       <c r="AD48" s="32"/>
       <c r="AE48" s="32"/>
       <c r="AF48" s="32"/>
@@ -23781,7 +23775,7 @@
       <c r="N49" s="54" t="s">
         <v>707</v>
       </c>
-      <c r="O49" s="408"/>
+      <c r="O49" s="407"/>
       <c r="P49" s="118"/>
       <c r="Q49" s="127"/>
       <c r="R49" s="32" t="s">
@@ -23848,7 +23842,7 @@
       <c r="N50" s="54" t="s">
         <v>742</v>
       </c>
-      <c r="O50" s="408"/>
+      <c r="O50" s="407"/>
       <c r="P50" s="118" t="s">
         <v>743</v>
       </c>
@@ -24074,7 +24068,7 @@
       <c r="S53" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T53" s="438" t="s">
+      <c r="T53" s="437" t="s">
         <v>820</v>
       </c>
       <c r="U53" s="28"/>
@@ -24818,7 +24812,7 @@
       <c r="N64" s="54" t="s">
         <v>1191</v>
       </c>
-      <c r="O64" s="411"/>
+      <c r="O64" s="410"/>
       <c r="P64" s="118"/>
       <c r="Q64" s="127"/>
       <c r="R64" s="32" t="s">
@@ -24934,7 +24928,7 @@
       <c r="F66" s="21" t="s">
         <v>1108</v>
       </c>
-      <c r="G66" s="381" t="s">
+      <c r="G66" s="380" t="s">
         <v>1268</v>
       </c>
       <c r="H66" s="125" t="s">
@@ -25021,7 +25015,7 @@
       <c r="N67" s="38" t="s">
         <v>1292</v>
       </c>
-      <c r="O67" s="416"/>
+      <c r="O67" s="415"/>
       <c r="P67" s="130"/>
       <c r="Q67" s="139"/>
       <c r="R67" s="32" t="s">
@@ -25088,7 +25082,7 @@
       <c r="N68" s="54" t="s">
         <v>1308</v>
       </c>
-      <c r="O68" s="408"/>
+      <c r="O68" s="407"/>
       <c r="P68" s="118"/>
       <c r="Q68" s="56"/>
       <c r="R68" s="32" t="s">
@@ -25473,7 +25467,7 @@
       <c r="A74" s="51" t="s">
         <v>600</v>
       </c>
-      <c r="B74" s="352" t="s">
+      <c r="B74" s="351" t="s">
         <v>43</v>
       </c>
       <c r="C74" s="276" t="s">
@@ -25504,14 +25498,14 @@
       <c r="N74" s="140" t="s">
         <v>607</v>
       </c>
-      <c r="O74" s="414"/>
+      <c r="O74" s="413"/>
       <c r="P74" s="60" t="s">
         <v>38</v>
       </c>
       <c r="Q74" s="72" t="s">
         <v>608</v>
       </c>
-      <c r="R74" s="425" t="s">
+      <c r="R74" s="424" t="s">
         <v>609</v>
       </c>
       <c r="S74" s="32" t="s">
@@ -25525,7 +25519,7 @@
       <c r="W74" s="142" t="s">
         <v>191</v>
       </c>
-      <c r="X74" s="454" t="s">
+      <c r="X74" s="453" t="s">
         <v>192</v>
       </c>
       <c r="Y74" s="62" t="s">
@@ -25562,7 +25556,7 @@
       <c r="C75" s="272" t="s">
         <v>1692</v>
       </c>
-      <c r="D75" s="364"/>
+      <c r="D75" s="363"/>
       <c r="E75" s="58"/>
       <c r="F75" s="16" t="s">
         <v>1693</v>
@@ -25590,7 +25584,7 @@
       <c r="O75" s="54"/>
       <c r="P75" s="55"/>
       <c r="Q75" s="56"/>
-      <c r="R75" s="425" t="s">
+      <c r="R75" s="424" t="s">
         <v>609</v>
       </c>
       <c r="S75" s="32" t="s">
@@ -25805,7 +25799,7 @@
       <c r="C78" s="108" t="s">
         <v>203</v>
       </c>
-      <c r="D78" s="369" t="s">
+      <c r="D78" s="368" t="s">
         <v>180</v>
       </c>
       <c r="E78" s="144" t="s">
@@ -25861,7 +25855,7 @@
       </c>
       <c r="Z78" s="30"/>
       <c r="AA78" s="30"/>
-      <c r="AB78" s="468" t="s">
+      <c r="AB78" s="467" t="s">
         <v>209</v>
       </c>
       <c r="AC78" s="32" t="s">
@@ -26009,7 +26003,7 @@
       <c r="O80" s="38"/>
       <c r="P80" s="25"/>
       <c r="Q80" s="26"/>
-      <c r="R80" s="361" t="s">
+      <c r="R80" s="360" t="s">
         <v>187</v>
       </c>
       <c r="S80" s="32" t="s">
@@ -26033,7 +26027,7 @@
       </c>
       <c r="Z80" s="30"/>
       <c r="AA80" s="30"/>
-      <c r="AB80" s="465" t="s">
+      <c r="AB80" s="464" t="s">
         <v>222</v>
       </c>
       <c r="AC80" s="32" t="s">
@@ -26061,10 +26055,10 @@
       <c r="B81" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C81" s="361" t="s">
+      <c r="C81" s="360" t="s">
         <v>218</v>
       </c>
-      <c r="D81" s="367" t="s">
+      <c r="D81" s="366" t="s">
         <v>180</v>
       </c>
       <c r="E81" s="144" t="s">
@@ -26092,7 +26086,7 @@
       <c r="O81" s="91"/>
       <c r="P81" s="92"/>
       <c r="Q81" s="93"/>
-      <c r="R81" s="361" t="s">
+      <c r="R81" s="360" t="s">
         <v>187</v>
       </c>
       <c r="S81" s="32" t="s">
@@ -26319,7 +26313,7 @@
       <c r="O84" s="38"/>
       <c r="P84" s="25"/>
       <c r="Q84" s="26"/>
-      <c r="R84" s="361" t="s">
+      <c r="R84" s="360" t="s">
         <v>187</v>
       </c>
       <c r="S84" s="32" t="s">
@@ -26394,7 +26388,7 @@
       <c r="O85" s="38"/>
       <c r="P85" s="25"/>
       <c r="Q85" s="26"/>
-      <c r="R85" s="352" t="s">
+      <c r="R85" s="351" t="s">
         <v>187</v>
       </c>
       <c r="S85" s="32" t="s">
@@ -26461,7 +26455,7 @@
       <c r="O86" s="54"/>
       <c r="P86" s="55"/>
       <c r="Q86" s="56"/>
-      <c r="R86" s="400" t="s">
+      <c r="R86" s="399" t="s">
         <v>1832</v>
       </c>
       <c r="S86" s="53" t="s">
@@ -26714,10 +26708,10 @@
       <c r="B90" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C90" s="363" t="s">
+      <c r="C90" s="362" t="s">
         <v>172</v>
       </c>
-      <c r="D90" s="364"/>
+      <c r="D90" s="363"/>
       <c r="E90" s="144"/>
       <c r="F90" s="47" t="s">
         <v>1461</v>
@@ -26783,10 +26777,10 @@
       <c r="B91" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C91" s="356" t="s">
+      <c r="C91" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="D91" s="364"/>
+      <c r="D91" s="363"/>
       <c r="E91" s="144"/>
       <c r="F91" s="47" t="s">
         <v>1724</v>
@@ -26814,13 +26808,13 @@
       <c r="O91" s="38"/>
       <c r="P91" s="25"/>
       <c r="Q91" s="26"/>
-      <c r="R91" s="425" t="s">
+      <c r="R91" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S91" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T91" s="381"/>
+      <c r="T91" s="380"/>
       <c r="U91" s="28"/>
       <c r="V91" s="28"/>
       <c r="W91" s="29"/>
@@ -26881,7 +26875,7 @@
       <c r="O92" s="66"/>
       <c r="P92" s="25"/>
       <c r="Q92" s="26"/>
-      <c r="R92" s="425" t="s">
+      <c r="R92" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S92" s="32" t="s">
@@ -26958,7 +26952,7 @@
       <c r="O93" s="38"/>
       <c r="P93" s="25"/>
       <c r="Q93" s="26"/>
-      <c r="R93" s="425" t="s">
+      <c r="R93" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S93" s="32" t="s">
@@ -27035,7 +27029,7 @@
       <c r="O94" s="38"/>
       <c r="P94" s="25"/>
       <c r="Q94" s="56"/>
-      <c r="R94" s="425" t="s">
+      <c r="R94" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S94" s="78" t="s">
@@ -27102,7 +27096,7 @@
       <c r="O95" s="38"/>
       <c r="P95" s="25"/>
       <c r="Q95" s="56"/>
-      <c r="R95" s="428" t="s">
+      <c r="R95" s="427" t="s">
         <v>1114</v>
       </c>
       <c r="S95" s="78" t="s">
@@ -27146,10 +27140,10 @@
       <c r="B96" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C96" s="359" t="s">
+      <c r="C96" s="358" t="s">
         <v>2771</v>
       </c>
-      <c r="D96" s="364"/>
+      <c r="D96" s="363"/>
       <c r="E96" s="144"/>
       <c r="F96" s="47" t="s">
         <v>2772</v>
@@ -27166,7 +27160,7 @@
       <c r="J96" s="22"/>
       <c r="K96" s="22"/>
       <c r="L96" s="22"/>
-      <c r="M96" s="404" t="s">
+      <c r="M96" s="403" t="s">
         <v>662</v>
       </c>
       <c r="N96" s="66" t="s">
@@ -27250,7 +27244,7 @@
       <c r="O97" s="38"/>
       <c r="P97" s="25"/>
       <c r="Q97" s="56"/>
-      <c r="R97" s="425" t="s">
+      <c r="R97" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S97" s="78" t="s">
@@ -27325,7 +27319,7 @@
       <c r="O98" s="54"/>
       <c r="P98" s="55"/>
       <c r="Q98" s="56"/>
-      <c r="R98" s="425" t="s">
+      <c r="R98" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S98" s="78" t="s">
@@ -27477,7 +27471,7 @@
       <c r="O100" s="54"/>
       <c r="P100" s="55"/>
       <c r="Q100" s="56"/>
-      <c r="R100" s="425" t="s">
+      <c r="R100" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S100" s="226" t="s">
@@ -27550,7 +27544,7 @@
       <c r="O101" s="38"/>
       <c r="P101" s="25"/>
       <c r="Q101" s="26"/>
-      <c r="R101" s="428" t="s">
+      <c r="R101" s="427" t="s">
         <v>1114</v>
       </c>
       <c r="S101" s="78" t="s">
@@ -27627,7 +27621,7 @@
       <c r="Q102" s="56" t="s">
         <v>3626</v>
       </c>
-      <c r="R102" s="425" t="s">
+      <c r="R102" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S102" s="78" t="s">
@@ -27696,7 +27690,7 @@
       <c r="O103" s="54"/>
       <c r="P103" s="55"/>
       <c r="Q103" s="56"/>
-      <c r="R103" s="425" t="s">
+      <c r="R103" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S103" s="78" t="s">
@@ -28079,7 +28073,7 @@
       <c r="O108" s="38"/>
       <c r="P108" s="25"/>
       <c r="Q108" s="56"/>
-      <c r="R108" s="425" t="s">
+      <c r="R108" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S108" s="78" t="s">
@@ -28153,10 +28147,10 @@
       <c r="N109" s="66" t="s">
         <v>3750</v>
       </c>
-      <c r="O109" s="409"/>
+      <c r="O109" s="408"/>
       <c r="P109" s="130"/>
       <c r="Q109" s="26"/>
-      <c r="R109" s="425" t="s">
+      <c r="R109" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S109" s="78" t="s">
@@ -28231,7 +28225,7 @@
       <c r="O110" s="38"/>
       <c r="P110" s="25"/>
       <c r="Q110" s="26"/>
-      <c r="R110" s="425" t="s">
+      <c r="R110" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S110" s="32" t="s">
@@ -28302,7 +28296,7 @@
       <c r="O111" s="38"/>
       <c r="P111" s="25"/>
       <c r="Q111" s="26"/>
-      <c r="R111" s="428" t="s">
+      <c r="R111" s="427" t="s">
         <v>1114</v>
       </c>
       <c r="S111" s="78" t="s">
@@ -28381,7 +28375,7 @@
       <c r="O112" s="54"/>
       <c r="P112" s="55"/>
       <c r="Q112" s="56"/>
-      <c r="R112" s="425" t="s">
+      <c r="R112" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S112" s="78" t="s">
@@ -28460,7 +28454,7 @@
       <c r="O113" s="54"/>
       <c r="P113" s="55"/>
       <c r="Q113" s="56"/>
-      <c r="R113" s="425" t="s">
+      <c r="R113" s="424" t="s">
         <v>1114</v>
       </c>
       <c r="S113" s="78" t="s">
@@ -28752,7 +28746,7 @@
       <c r="Q117" s="56" t="s">
         <v>2131</v>
       </c>
-      <c r="R117" s="352" t="s">
+      <c r="R117" s="351" t="s">
         <v>2149</v>
       </c>
       <c r="S117" s="21" t="s">
@@ -28821,7 +28815,7 @@
       <c r="O118" s="54"/>
       <c r="P118" s="55"/>
       <c r="Q118" s="56"/>
-      <c r="R118" s="352" t="s">
+      <c r="R118" s="351" t="s">
         <v>2149</v>
       </c>
       <c r="S118" s="32" t="s">
@@ -28896,7 +28890,7 @@
       <c r="Q119" s="133" t="s">
         <v>2535</v>
       </c>
-      <c r="R119" s="412" t="s">
+      <c r="R119" s="411" t="s">
         <v>2536</v>
       </c>
       <c r="S119" s="78" t="s">
@@ -28968,10 +28962,10 @@
       <c r="N120" s="54" t="s">
         <v>390</v>
       </c>
-      <c r="O120" s="408"/>
+      <c r="O120" s="407"/>
       <c r="P120" s="118"/>
       <c r="Q120" s="56"/>
-      <c r="R120" s="422" t="s">
+      <c r="R120" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S120" s="88" t="s">
@@ -29034,13 +29028,13 @@
       <c r="M121" s="48" t="s">
         <v>581</v>
       </c>
-      <c r="N121" s="410" t="s">
+      <c r="N121" s="409" t="s">
         <v>582</v>
       </c>
-      <c r="O121" s="410"/>
+      <c r="O121" s="409"/>
       <c r="P121" s="130"/>
       <c r="Q121" s="139"/>
-      <c r="R121" s="422" t="s">
+      <c r="R121" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S121" s="21" t="s">
@@ -29108,7 +29102,7 @@
       <c r="N122" s="54" t="s">
         <v>1459</v>
       </c>
-      <c r="O122" s="411"/>
+      <c r="O122" s="410"/>
       <c r="P122" s="118"/>
       <c r="Q122" s="56"/>
       <c r="R122" s="99" t="s">
@@ -29180,7 +29174,7 @@
       <c r="O123" s="54"/>
       <c r="P123" s="55"/>
       <c r="Q123" s="56"/>
-      <c r="R123" s="422" t="s">
+      <c r="R123" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S123" s="32" t="s">
@@ -29253,7 +29247,7 @@
       <c r="O124" s="54"/>
       <c r="P124" s="55"/>
       <c r="Q124" s="56"/>
-      <c r="R124" s="422" t="s">
+      <c r="R124" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S124" s="32" t="s">
@@ -29320,7 +29314,7 @@
       <c r="O125" s="54"/>
       <c r="P125" s="55"/>
       <c r="Q125" s="56"/>
-      <c r="R125" s="422" t="s">
+      <c r="R125" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S125" s="32" t="s">
@@ -29382,20 +29376,20 @@
       <c r="J126" s="22"/>
       <c r="K126" s="22"/>
       <c r="L126" s="22"/>
-      <c r="M126" s="400" t="s">
+      <c r="M126" s="399" t="s">
         <v>1916</v>
       </c>
       <c r="N126" s="54" t="s">
         <v>1917</v>
       </c>
       <c r="O126" s="54"/>
-      <c r="P126" s="343" t="s">
+      <c r="P126" s="342" t="s">
         <v>1919</v>
       </c>
-      <c r="Q126" s="343" t="s">
+      <c r="Q126" s="342" t="s">
         <v>1920</v>
       </c>
-      <c r="R126" s="422" t="s">
+      <c r="R126" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S126" s="32" t="s">
@@ -29440,7 +29434,7 @@
       <c r="A127" s="14" t="s">
         <v>1923</v>
       </c>
-      <c r="B127" s="351" t="s">
+      <c r="B127" s="350" t="s">
         <v>1012</v>
       </c>
       <c r="C127" s="271" t="s">
@@ -29463,20 +29457,20 @@
       <c r="J127" s="22"/>
       <c r="K127" s="22"/>
       <c r="L127" s="22"/>
-      <c r="M127" s="400" t="s">
+      <c r="M127" s="399" t="s">
         <v>1916</v>
       </c>
       <c r="N127" s="54" t="s">
         <v>1927</v>
       </c>
       <c r="O127" s="54"/>
-      <c r="P127" s="343" t="s">
+      <c r="P127" s="342" t="s">
         <v>1919</v>
       </c>
-      <c r="Q127" s="343" t="s">
+      <c r="Q127" s="342" t="s">
         <v>1920</v>
       </c>
-      <c r="R127" s="422" t="s">
+      <c r="R127" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S127" s="32" t="s">
@@ -29544,7 +29538,7 @@
       <c r="L128" s="22" t="s">
         <v>1963</v>
       </c>
-      <c r="M128" s="398" t="s">
+      <c r="M128" s="397" t="s">
         <v>1838</v>
       </c>
       <c r="N128" s="54" t="s">
@@ -29553,7 +29547,7 @@
       <c r="O128" s="117"/>
       <c r="P128" s="118"/>
       <c r="Q128" s="56"/>
-      <c r="R128" s="422" t="s">
+      <c r="R128" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S128" s="32" t="s">
@@ -29613,7 +29607,7 @@
       <c r="L129" s="22" t="s">
         <v>1980</v>
       </c>
-      <c r="M129" s="386" t="s">
+      <c r="M129" s="385" t="s">
         <v>1458</v>
       </c>
       <c r="N129" s="38" t="s">
@@ -29622,7 +29616,7 @@
       <c r="O129" s="59"/>
       <c r="P129" s="130"/>
       <c r="Q129" s="26"/>
-      <c r="R129" s="422" t="s">
+      <c r="R129" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S129" s="32" t="s">
@@ -29680,20 +29674,20 @@
       <c r="L130" s="22" t="s">
         <v>2023</v>
       </c>
-      <c r="M130" s="398" t="s">
+      <c r="M130" s="397" t="s">
         <v>389</v>
       </c>
       <c r="N130" s="38" t="s">
         <v>1668</v>
       </c>
-      <c r="O130" s="409"/>
+      <c r="O130" s="408"/>
       <c r="P130" s="130" t="s">
         <v>1919</v>
       </c>
       <c r="Q130" s="26" t="s">
         <v>1920</v>
       </c>
-      <c r="R130" s="422" t="s">
+      <c r="R130" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S130" s="32" t="s">
@@ -29768,10 +29762,10 @@
         <v>2034</v>
       </c>
       <c r="M131" s="131" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="N131" s="54" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="O131" s="54"/>
       <c r="P131" s="130" t="s">
@@ -29915,7 +29909,7 @@
         <v>2052</v>
       </c>
       <c r="H133" s="48" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="I133" s="43" t="s">
         <v>2053</v>
@@ -29972,68 +29966,68 @@
       <c r="AQ133" s="32"/>
     </row>
     <row r="134" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A134" s="347" t="s">
+      <c r="A134" s="346" t="s">
         <v>3824</v>
       </c>
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="346" t="s">
         <v>2099</v>
       </c>
-      <c r="C134" s="358" t="s">
+      <c r="C134" s="357" t="s">
         <v>3828</v>
       </c>
-      <c r="D134" s="365"/>
-      <c r="E134" s="370"/>
-      <c r="F134" s="370" t="s">
+      <c r="D134" s="364"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369" t="s">
         <v>3825</v>
       </c>
-      <c r="G134" s="370" t="s">
+      <c r="G134" s="369" t="s">
         <v>3826</v>
       </c>
-      <c r="H134" s="354" t="s">
+      <c r="H134" s="353" t="s">
         <v>2100</v>
       </c>
-      <c r="I134" s="353" t="s">
+      <c r="I134" s="352" t="s">
         <v>1926</v>
       </c>
-      <c r="J134" s="370"/>
-      <c r="K134" s="370"/>
-      <c r="L134" s="370"/>
-      <c r="M134" s="353" t="s">
+      <c r="J134" s="369"/>
+      <c r="K134" s="369"/>
+      <c r="L134" s="369"/>
+      <c r="M134" s="352" t="s">
         <v>1916</v>
       </c>
       <c r="N134" s="138" t="s">
         <v>2101</v>
       </c>
-      <c r="O134" s="406"/>
-      <c r="P134" s="370"/>
-      <c r="Q134" s="370"/>
+      <c r="O134" s="405"/>
+      <c r="P134" s="369"/>
+      <c r="Q134" s="369"/>
       <c r="R134" s="250" t="s">
         <v>391</v>
       </c>
-      <c r="S134" s="354" t="s">
+      <c r="S134" s="353" t="s">
         <v>41</v>
       </c>
-      <c r="T134" s="354" t="s">
+      <c r="T134" s="353" t="s">
         <v>3827</v>
       </c>
-      <c r="U134" s="354" t="s">
+      <c r="U134" s="353" t="s">
         <v>1919</v>
       </c>
-      <c r="V134" s="354" t="s">
+      <c r="V134" s="353" t="s">
         <v>1920</v>
       </c>
-      <c r="W134" s="370"/>
-      <c r="X134" s="455"/>
-      <c r="Y134" s="375" t="s">
+      <c r="W134" s="369"/>
+      <c r="X134" s="454"/>
+      <c r="Y134" s="374" t="s">
         <v>4009</v>
       </c>
-      <c r="Z134" s="370"/>
-      <c r="AA134" s="370"/>
-      <c r="AB134" s="370"/>
-      <c r="AC134" s="354" t="s">
+      <c r="Z134" s="369"/>
+      <c r="AA134" s="369"/>
+      <c r="AB134" s="369"/>
+      <c r="AC134" s="353" t="s">
         <v>2102</v>
       </c>
-      <c r="AD134" s="370" t="s">
+      <c r="AD134" s="369" t="s">
         <v>4010</v>
       </c>
       <c r="AE134" s="32"/>
@@ -30051,62 +30045,62 @@
       <c r="AQ134" s="32"/>
     </row>
     <row r="135" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A135" s="347" t="s">
+      <c r="A135" s="346" t="s">
         <v>3819</v>
       </c>
-      <c r="B135" s="354" t="s">
+      <c r="B135" s="353" t="s">
         <v>3820</v>
       </c>
-      <c r="C135" s="358" t="s">
+      <c r="C135" s="357" t="s">
         <v>3828</v>
       </c>
-      <c r="D135" s="365"/>
-      <c r="E135" s="370"/>
-      <c r="F135" s="370"/>
-      <c r="G135" s="354"/>
-      <c r="H135" s="354" t="s">
+      <c r="D135" s="364"/>
+      <c r="E135" s="369"/>
+      <c r="F135" s="369"/>
+      <c r="G135" s="353"/>
+      <c r="H135" s="353" t="s">
         <v>3821</v>
       </c>
-      <c r="I135" s="353" t="s">
+      <c r="I135" s="352" t="s">
         <v>2047</v>
       </c>
-      <c r="J135" s="370"/>
-      <c r="K135" s="370"/>
-      <c r="L135" s="370"/>
-      <c r="M135" s="353" t="s">
+      <c r="J135" s="369"/>
+      <c r="K135" s="369"/>
+      <c r="L135" s="369"/>
+      <c r="M135" s="352" t="s">
         <v>1916</v>
       </c>
-      <c r="N135" s="406" t="s">
+      <c r="N135" s="405" t="s">
         <v>2101</v>
       </c>
-      <c r="O135" s="406"/>
-      <c r="P135" s="370"/>
-      <c r="Q135" s="370"/>
+      <c r="O135" s="405"/>
+      <c r="P135" s="369"/>
+      <c r="Q135" s="369"/>
       <c r="R135" s="250" t="s">
         <v>391</v>
       </c>
-      <c r="S135" s="354" t="s">
+      <c r="S135" s="353" t="s">
         <v>41</v>
       </c>
-      <c r="T135" s="354" t="s">
+      <c r="T135" s="353" t="s">
         <v>3822</v>
       </c>
-      <c r="U135" s="354" t="s">
+      <c r="U135" s="353" t="s">
         <v>1919</v>
       </c>
-      <c r="V135" s="354" t="s">
+      <c r="V135" s="353" t="s">
         <v>1920</v>
       </c>
-      <c r="W135" s="370"/>
-      <c r="X135" s="370"/>
-      <c r="Y135" s="354" t="s">
+      <c r="W135" s="369"/>
+      <c r="X135" s="369"/>
+      <c r="Y135" s="353" t="s">
         <v>3823</v>
       </c>
-      <c r="Z135" s="370"/>
-      <c r="AA135" s="370"/>
-      <c r="AB135" s="370"/>
-      <c r="AC135" s="354"/>
-      <c r="AD135" s="370"/>
+      <c r="Z135" s="369"/>
+      <c r="AA135" s="369"/>
+      <c r="AB135" s="369"/>
+      <c r="AC135" s="353"/>
+      <c r="AD135" s="369"/>
       <c r="AE135" s="32"/>
       <c r="AF135" s="32"/>
       <c r="AG135" s="32"/>
@@ -30157,7 +30151,7 @@
       <c r="O136" s="54"/>
       <c r="P136" s="55"/>
       <c r="Q136" s="56"/>
-      <c r="R136" s="422" t="s">
+      <c r="R136" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S136" s="32" t="s">
@@ -30223,10 +30217,10 @@
       <c r="N137" s="54" t="s">
         <v>2157</v>
       </c>
-      <c r="O137" s="408"/>
+      <c r="O137" s="407"/>
       <c r="P137" s="118"/>
       <c r="Q137" s="56"/>
-      <c r="R137" s="422" t="s">
+      <c r="R137" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S137" s="32" t="s">
@@ -30295,7 +30289,7 @@
       <c r="O138" s="54"/>
       <c r="P138" s="55"/>
       <c r="Q138" s="56"/>
-      <c r="R138" s="422" t="s">
+      <c r="R138" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S138" s="32" t="s">
@@ -30435,7 +30429,7 @@
       <c r="O140" s="38"/>
       <c r="P140" s="75"/>
       <c r="Q140" s="76"/>
-      <c r="R140" s="422" t="s">
+      <c r="R140" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S140" s="32" t="s">
@@ -30630,7 +30624,7 @@
       </c>
       <c r="D143" s="256"/>
       <c r="E143" s="58"/>
-      <c r="F143" s="372" t="s">
+      <c r="F143" s="371" t="s">
         <v>2439</v>
       </c>
       <c r="G143" s="32" t="s">
@@ -30806,7 +30800,7 @@
       <c r="O145" s="38"/>
       <c r="P145" s="25"/>
       <c r="Q145" s="56"/>
-      <c r="R145" s="422" t="s">
+      <c r="R145" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S145" s="32" t="s">
@@ -30944,7 +30938,7 @@
       <c r="Q147" s="93" t="s">
         <v>2365</v>
       </c>
-      <c r="R147" s="422" t="s">
+      <c r="R147" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S147" s="78" t="s">
@@ -31157,7 +31151,7 @@
       <c r="O150" s="54"/>
       <c r="P150" s="235"/>
       <c r="Q150" s="56"/>
-      <c r="R150" s="422" t="s">
+      <c r="R150" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S150" s="78" t="s">
@@ -31224,7 +31218,7 @@
       <c r="O151" s="38"/>
       <c r="P151" s="25"/>
       <c r="Q151" s="26"/>
-      <c r="R151" s="422" t="s">
+      <c r="R151" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S151" s="78" t="s">
@@ -31239,7 +31233,7 @@
       <c r="Z151" s="30"/>
       <c r="AA151" s="30"/>
       <c r="AB151" s="41"/>
-      <c r="AC151" s="352"/>
+      <c r="AC151" s="351"/>
       <c r="AD151" s="21"/>
       <c r="AE151" s="32"/>
       <c r="AF151" s="32"/>
@@ -31289,7 +31283,7 @@
       <c r="O152" s="38"/>
       <c r="P152" s="25"/>
       <c r="Q152" s="26"/>
-      <c r="R152" s="422" t="s">
+      <c r="R152" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S152" s="224" t="s">
@@ -31356,7 +31350,7 @@
       <c r="O153" s="38"/>
       <c r="P153" s="25"/>
       <c r="Q153" s="56"/>
-      <c r="R153" s="422" t="s">
+      <c r="R153" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S153" s="224" t="s">
@@ -31429,7 +31423,7 @@
       <c r="O154" s="54"/>
       <c r="P154" s="55"/>
       <c r="Q154" s="56"/>
-      <c r="R154" s="422" t="s">
+      <c r="R154" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S154" s="78" t="s">
@@ -31632,7 +31626,7 @@
       <c r="O157" s="54"/>
       <c r="P157" s="55"/>
       <c r="Q157" s="56"/>
-      <c r="R157" s="422" t="s">
+      <c r="R157" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S157" s="78" t="s">
@@ -31770,11 +31764,13 @@
         <v>3660</v>
       </c>
       <c r="O159" s="91"/>
-      <c r="P159" s="341" t="s">
-        <v>4011</v>
-      </c>
-      <c r="Q159" s="93"/>
-      <c r="R159" s="422" t="s">
+      <c r="P159" s="75" t="s">
+        <v>3560</v>
+      </c>
+      <c r="Q159" s="56" t="s">
+        <v>3744</v>
+      </c>
+      <c r="R159" s="421" t="s">
         <v>391</v>
       </c>
       <c r="S159" s="78" t="s">
@@ -31847,7 +31843,7 @@
       <c r="Q160" s="93" t="s">
         <v>2365</v>
       </c>
-      <c r="R160" s="423" t="s">
+      <c r="R160" s="422" t="s">
         <v>3016</v>
       </c>
       <c r="S160" s="78" t="s">
@@ -31924,7 +31920,7 @@
       <c r="Q161" s="56" t="s">
         <v>3744</v>
       </c>
-      <c r="R161" s="434" t="s">
+      <c r="R161" s="433" t="s">
         <v>3016</v>
       </c>
       <c r="S161" s="78" t="s">
@@ -31993,7 +31989,7 @@
       <c r="Q162" s="26" t="s">
         <v>3561</v>
       </c>
-      <c r="R162" s="399" t="s">
+      <c r="R162" s="398" t="s">
         <v>3572</v>
       </c>
       <c r="S162" s="78" t="s">
@@ -32060,7 +32056,7 @@
       <c r="O163" s="54"/>
       <c r="P163" s="55"/>
       <c r="Q163" s="56"/>
-      <c r="R163" s="433" t="s">
+      <c r="R163" s="432" t="s">
         <v>1565</v>
       </c>
       <c r="S163" s="33" t="s">
@@ -32129,7 +32125,7 @@
       <c r="O164" s="38"/>
       <c r="P164" s="25"/>
       <c r="Q164" s="26"/>
-      <c r="R164" s="399" t="s">
+      <c r="R164" s="398" t="s">
         <v>1565</v>
       </c>
       <c r="S164" s="98" t="s">
@@ -32200,7 +32196,7 @@
       <c r="O165" s="140"/>
       <c r="P165" s="55"/>
       <c r="Q165" s="56"/>
-      <c r="R165" s="399" t="s">
+      <c r="R165" s="398" t="s">
         <v>1565</v>
       </c>
       <c r="S165" s="21" t="s">
@@ -32267,7 +32263,7 @@
       <c r="O166" s="54"/>
       <c r="P166" s="118"/>
       <c r="Q166" s="56"/>
-      <c r="R166" s="433" t="s">
+      <c r="R166" s="432" t="s">
         <v>1565</v>
       </c>
       <c r="S166" s="32" t="s">
@@ -32415,7 +32411,7 @@
       <c r="O168" s="38"/>
       <c r="P168" s="25"/>
       <c r="Q168" s="56"/>
-      <c r="R168" s="404" t="s">
+      <c r="R168" s="403" t="s">
         <v>2692</v>
       </c>
       <c r="S168" s="143" t="s">
@@ -32488,7 +32484,7 @@
       <c r="O169" s="38"/>
       <c r="P169" s="25"/>
       <c r="Q169" s="56"/>
-      <c r="R169" s="429" t="s">
+      <c r="R169" s="428" t="s">
         <v>3365</v>
       </c>
       <c r="S169" s="78" t="s">
@@ -32565,7 +32561,7 @@
       <c r="Q170" s="93" t="s">
         <v>3561</v>
       </c>
-      <c r="R170" s="404" t="s">
+      <c r="R170" s="403" t="s">
         <v>3365</v>
       </c>
       <c r="S170" s="119" t="s">
@@ -32648,7 +32644,7 @@
       <c r="Q171" s="56" t="s">
         <v>368</v>
       </c>
-      <c r="R171" s="429" t="s">
+      <c r="R171" s="428" t="s">
         <v>369</v>
       </c>
       <c r="S171" s="32" t="s">
@@ -32721,7 +32717,7 @@
       <c r="Q172" s="65" t="s">
         <v>714</v>
       </c>
-      <c r="R172" s="361" t="s">
+      <c r="R172" s="360" t="s">
         <v>715</v>
       </c>
       <c r="S172" s="32" t="s">
@@ -32800,7 +32796,7 @@
       <c r="Q173" s="93" t="s">
         <v>2190</v>
       </c>
-      <c r="R173" s="361" t="s">
+      <c r="R173" s="360" t="s">
         <v>715</v>
       </c>
       <c r="S173" s="32" t="s">
@@ -32870,7 +32866,7 @@
       <c r="N174" s="38" t="s">
         <v>2697</v>
       </c>
-      <c r="O174" s="409" t="s">
+      <c r="O174" s="408" t="s">
         <v>2698</v>
       </c>
       <c r="P174" s="130"/>
@@ -33120,7 +33116,7 @@
       <c r="Q177" s="76" t="s">
         <v>1753</v>
       </c>
-      <c r="R177" s="361" t="s">
+      <c r="R177" s="360" t="s">
         <v>1754</v>
       </c>
       <c r="S177" s="32" t="s">
@@ -33205,7 +33201,7 @@
       <c r="Q178" s="56" t="s">
         <v>2802</v>
       </c>
-      <c r="R178" s="361" t="s">
+      <c r="R178" s="360" t="s">
         <v>1754</v>
       </c>
       <c r="S178" s="78" t="s">
@@ -33278,7 +33274,7 @@
       <c r="Q179" s="76" t="s">
         <v>527</v>
       </c>
-      <c r="R179" s="361" t="s">
+      <c r="R179" s="360" t="s">
         <v>528</v>
       </c>
       <c r="S179" s="32" t="s">
@@ -33357,7 +33353,7 @@
       <c r="Q180" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="R180" s="361" t="s">
+      <c r="R180" s="360" t="s">
         <v>528</v>
       </c>
       <c r="S180" s="32" t="s">
@@ -33440,7 +33436,7 @@
       <c r="Q181" s="56" t="s">
         <v>665</v>
       </c>
-      <c r="R181" s="361" t="s">
+      <c r="R181" s="360" t="s">
         <v>528</v>
       </c>
       <c r="S181" s="32" t="s">
@@ -33567,7 +33563,7 @@
       <c r="F183" s="47" t="s">
         <v>774</v>
       </c>
-      <c r="G183" s="352"/>
+      <c r="G183" s="351"/>
       <c r="H183" s="32" t="s">
         <v>775</v>
       </c>
@@ -33677,7 +33673,7 @@
       <c r="S184" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T184" s="381" t="s">
+      <c r="T184" s="380" t="s">
         <v>801</v>
       </c>
       <c r="U184" s="28"/>
@@ -35025,7 +35021,7 @@
       <c r="I202" s="43" t="s">
         <v>1739</v>
       </c>
-      <c r="J202" s="393" t="s">
+      <c r="J202" s="392" t="s">
         <v>1740</v>
       </c>
       <c r="K202" s="83"/>
@@ -35855,7 +35851,7 @@
       <c r="F213" s="16" t="s">
         <v>2560</v>
       </c>
-      <c r="G213" s="352"/>
+      <c r="G213" s="351"/>
       <c r="H213" s="32" t="s">
         <v>2561</v>
       </c>
@@ -36605,7 +36601,7 @@
       <c r="S222" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="T222" s="381"/>
+      <c r="T222" s="380"/>
       <c r="U222" s="109"/>
       <c r="V222" s="109"/>
       <c r="W222" s="29" t="s">
@@ -36728,7 +36724,7 @@
       <c r="B224" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C224" s="356" t="s">
+      <c r="C224" s="355" t="s">
         <v>172</v>
       </c>
       <c r="D224" s="256"/>
@@ -36752,7 +36748,7 @@
       <c r="N224" s="38" t="s">
         <v>3057</v>
       </c>
-      <c r="O224" s="409" t="s">
+      <c r="O224" s="408" t="s">
         <v>3058</v>
       </c>
       <c r="P224" s="130"/>
@@ -37157,7 +37153,7 @@
       <c r="N229" s="38" t="s">
         <v>3315</v>
       </c>
-      <c r="O229" s="416" t="s">
+      <c r="O229" s="415" t="s">
         <v>3316</v>
       </c>
       <c r="P229" s="130"/>
@@ -37319,7 +37315,7 @@
       <c r="N231" s="54" t="s">
         <v>1251</v>
       </c>
-      <c r="O231" s="408" t="s">
+      <c r="O231" s="407" t="s">
         <v>3506</v>
       </c>
       <c r="P231" s="118"/>
@@ -37477,7 +37473,7 @@
       <c r="N233" s="38" t="s">
         <v>3647</v>
       </c>
-      <c r="O233" s="409" t="s">
+      <c r="O233" s="408" t="s">
         <v>906</v>
       </c>
       <c r="P233" s="130"/>
@@ -37537,7 +37533,7 @@
       </c>
       <c r="D234" s="256"/>
       <c r="E234" s="58"/>
-      <c r="F234" s="374" t="s">
+      <c r="F234" s="373" t="s">
         <v>3651</v>
       </c>
       <c r="G234" s="32"/>
@@ -37591,7 +37587,7 @@
       </c>
       <c r="AB234" s="41"/>
       <c r="AC234" s="32"/>
-      <c r="AD234" s="352"/>
+      <c r="AD234" s="351"/>
       <c r="AE234" s="32"/>
       <c r="AF234" s="32"/>
       <c r="AG234" s="32"/>
@@ -37610,7 +37606,7 @@
       <c r="A235" s="310" t="s">
         <v>3996</v>
       </c>
-      <c r="B235" s="355" t="s">
+      <c r="B235" s="354" t="s">
         <v>2307</v>
       </c>
       <c r="C235" s="270" t="s">
@@ -37936,10 +37932,10 @@
       <c r="I239" s="326" t="s">
         <v>3692</v>
       </c>
-      <c r="J239" s="394" t="s">
+      <c r="J239" s="393" t="s">
         <v>2296</v>
       </c>
-      <c r="K239" s="394"/>
+      <c r="K239" s="393"/>
       <c r="L239" s="327"/>
       <c r="M239" s="328" t="s">
         <v>1614</v>
@@ -38108,7 +38104,7 @@
       <c r="U241" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="V241" s="448" t="s">
+      <c r="V241" s="447" t="s">
         <v>69</v>
       </c>
       <c r="W241" s="29"/>
@@ -38176,18 +38172,18 @@
       <c r="N242" s="54" t="s">
         <v>290</v>
       </c>
-      <c r="O242" s="408"/>
+      <c r="O242" s="407"/>
       <c r="P242" s="118"/>
       <c r="Q242" s="56"/>
       <c r="R242" s="104" t="s">
         <v>40</v>
       </c>
       <c r="S242" s="32"/>
-      <c r="T242" s="442"/>
-      <c r="U242" s="444" t="s">
+      <c r="T242" s="441"/>
+      <c r="U242" s="443" t="s">
         <v>291</v>
       </c>
-      <c r="V242" s="444" t="s">
+      <c r="V242" s="443" t="s">
         <v>292</v>
       </c>
       <c r="W242" s="29"/>
@@ -38251,7 +38247,7 @@
       <c r="N243" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="O243" s="408"/>
+      <c r="O243" s="407"/>
       <c r="P243" s="118"/>
       <c r="Q243" s="56"/>
       <c r="R243" s="104" t="s">
@@ -38260,13 +38256,13 @@
       <c r="S243" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T243" s="442" t="s">
+      <c r="T243" s="441" t="s">
         <v>301</v>
       </c>
-      <c r="U243" s="444" t="s">
+      <c r="U243" s="443" t="s">
         <v>291</v>
       </c>
-      <c r="V243" s="444" t="s">
+      <c r="V243" s="443" t="s">
         <v>292</v>
       </c>
       <c r="W243" s="105"/>
@@ -38278,7 +38274,7 @@
       <c r="AA243" s="30"/>
       <c r="AB243" s="41"/>
       <c r="AC243" s="32"/>
-      <c r="AD243" s="469" t="s">
+      <c r="AD243" s="468" t="s">
         <v>303</v>
       </c>
       <c r="AE243" s="32"/>
@@ -38324,8 +38320,8 @@
         <v>330</v>
       </c>
       <c r="J244" s="35"/>
-      <c r="K244" s="392"/>
-      <c r="L244" s="392" t="s">
+      <c r="K244" s="391"/>
+      <c r="L244" s="391" t="s">
         <v>288</v>
       </c>
       <c r="M244" s="36" t="s">
@@ -38343,13 +38339,13 @@
       <c r="S244" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="T244" s="439" t="s">
+      <c r="T244" s="438" t="s">
         <v>332</v>
       </c>
-      <c r="U244" s="444" t="s">
+      <c r="U244" s="443" t="s">
         <v>291</v>
       </c>
-      <c r="V244" s="444" t="s">
+      <c r="V244" s="443" t="s">
         <v>292</v>
       </c>
       <c r="W244" s="115"/>
@@ -38405,11 +38401,11 @@
         <v>336</v>
       </c>
       <c r="J245" s="107"/>
-      <c r="K245" s="388"/>
+      <c r="K245" s="387"/>
       <c r="L245" s="69" t="s">
         <v>288</v>
       </c>
-      <c r="M245" s="401" t="s">
+      <c r="M245" s="400" t="s">
         <v>299</v>
       </c>
       <c r="N245" s="74" t="s">
@@ -38534,74 +38530,74 @@
       <c r="AQ246" s="32"/>
     </row>
     <row r="247" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A247" s="348" t="s">
+      <c r="A247" s="347" t="s">
         <v>3963</v>
       </c>
-      <c r="B247" s="346" t="s">
+      <c r="B247" s="345" t="s">
         <v>476</v>
       </c>
-      <c r="C247" s="359" t="s">
+      <c r="C247" s="358" t="s">
         <v>477</v>
       </c>
-      <c r="D247" s="368" t="s">
+      <c r="D247" s="367" t="s">
         <v>478</v>
       </c>
-      <c r="E247" s="371" t="s">
+      <c r="E247" s="370" t="s">
         <v>479</v>
       </c>
-      <c r="F247" s="373" t="s">
+      <c r="F247" s="372" t="s">
         <v>480</v>
       </c>
-      <c r="G247" s="352" t="s">
+      <c r="G247" s="351" t="s">
         <v>481</v>
       </c>
-      <c r="H247" s="352" t="s">
+      <c r="H247" s="351" t="s">
         <v>482</v>
       </c>
-      <c r="I247" s="386" t="s">
+      <c r="I247" s="385" t="s">
         <v>483</v>
       </c>
-      <c r="J247" s="391"/>
-      <c r="K247" s="391"/>
-      <c r="L247" s="391" t="s">
+      <c r="J247" s="390"/>
+      <c r="K247" s="390"/>
+      <c r="L247" s="390" t="s">
         <v>484</v>
       </c>
-      <c r="M247" s="355" t="s">
+      <c r="M247" s="354" t="s">
         <v>485</v>
       </c>
-      <c r="N247" s="409" t="s">
+      <c r="N247" s="408" t="s">
         <v>486</v>
       </c>
-      <c r="O247" s="409"/>
-      <c r="P247" s="417"/>
-      <c r="Q247" s="421"/>
-      <c r="R247" s="432" t="s">
+      <c r="O247" s="408"/>
+      <c r="P247" s="416"/>
+      <c r="Q247" s="420"/>
+      <c r="R247" s="431" t="s">
         <v>40</v>
       </c>
-      <c r="S247" s="352" t="s">
+      <c r="S247" s="351" t="s">
         <v>41</v>
       </c>
-      <c r="T247" s="441"/>
-      <c r="U247" s="446"/>
-      <c r="V247" s="446"/>
-      <c r="W247" s="451" t="s">
+      <c r="T247" s="440"/>
+      <c r="U247" s="445"/>
+      <c r="V247" s="445"/>
+      <c r="W247" s="450" t="s">
         <v>407</v>
       </c>
-      <c r="X247" s="451" t="s">
+      <c r="X247" s="450" t="s">
         <v>487</v>
       </c>
-      <c r="Y247" s="458" t="s">
+      <c r="Y247" s="457" t="s">
         <v>488</v>
       </c>
-      <c r="Z247" s="458"/>
-      <c r="AA247" s="458"/>
-      <c r="AB247" s="467" t="s">
+      <c r="Z247" s="457"/>
+      <c r="AA247" s="457"/>
+      <c r="AB247" s="466" t="s">
         <v>489</v>
       </c>
-      <c r="AC247" s="373" t="s">
+      <c r="AC247" s="372" t="s">
         <v>490</v>
       </c>
-      <c r="AD247" s="352"/>
+      <c r="AD247" s="351"/>
       <c r="AE247" s="249"/>
       <c r="AF247" s="249"/>
       <c r="AG247" s="249"/>
@@ -38617,64 +38613,64 @@
       <c r="AQ247" s="249"/>
     </row>
     <row r="248" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A248" s="348" t="s">
+      <c r="A248" s="347" t="s">
         <v>3958</v>
       </c>
-      <c r="B248" s="352" t="s">
+      <c r="B248" s="351" t="s">
         <v>43</v>
       </c>
-      <c r="C248" s="356" t="s">
+      <c r="C248" s="355" t="s">
         <v>3869</v>
       </c>
-      <c r="D248" s="364"/>
-      <c r="E248" s="371"/>
-      <c r="F248" s="374" t="s">
+      <c r="D248" s="363"/>
+      <c r="E248" s="370"/>
+      <c r="F248" s="373" t="s">
         <v>585</v>
       </c>
-      <c r="G248" s="352"/>
-      <c r="H248" s="352" t="s">
+      <c r="G248" s="351"/>
+      <c r="H248" s="351" t="s">
         <v>586</v>
       </c>
-      <c r="I248" s="386" t="s">
+      <c r="I248" s="385" t="s">
         <v>587</v>
       </c>
-      <c r="J248" s="391"/>
-      <c r="K248" s="391"/>
-      <c r="L248" s="391" t="s">
+      <c r="J248" s="390"/>
+      <c r="K248" s="390"/>
+      <c r="L248" s="390" t="s">
         <v>588</v>
       </c>
-      <c r="M248" s="355" t="s">
+      <c r="M248" s="354" t="s">
         <v>589</v>
       </c>
-      <c r="N248" s="408" t="s">
+      <c r="N248" s="407" t="s">
         <v>590</v>
       </c>
-      <c r="O248" s="408"/>
-      <c r="P248" s="418" t="s">
+      <c r="O248" s="407"/>
+      <c r="P248" s="417" t="s">
         <v>591</v>
       </c>
-      <c r="Q248" s="420" t="s">
+      <c r="Q248" s="419" t="s">
         <v>592</v>
       </c>
-      <c r="R248" s="432" t="s">
+      <c r="R248" s="431" t="s">
         <v>40</v>
       </c>
-      <c r="S248" s="381" t="s">
+      <c r="S248" s="380" t="s">
         <v>41</v>
       </c>
-      <c r="T248" s="441" t="s">
+      <c r="T248" s="440" t="s">
         <v>593</v>
       </c>
-      <c r="U248" s="446"/>
-      <c r="V248" s="446"/>
-      <c r="W248" s="451"/>
-      <c r="X248" s="451"/>
-      <c r="Y248" s="458"/>
-      <c r="Z248" s="458"/>
-      <c r="AA248" s="458"/>
-      <c r="AB248" s="464"/>
-      <c r="AC248" s="352"/>
-      <c r="AD248" s="352"/>
+      <c r="U248" s="445"/>
+      <c r="V248" s="445"/>
+      <c r="W248" s="450"/>
+      <c r="X248" s="450"/>
+      <c r="Y248" s="457"/>
+      <c r="Z248" s="457"/>
+      <c r="AA248" s="457"/>
+      <c r="AB248" s="463"/>
+      <c r="AC248" s="351"/>
+      <c r="AD248" s="351"/>
       <c r="AE248" s="249"/>
       <c r="AF248" s="249"/>
       <c r="AG248" s="249"/>
@@ -39924,7 +39920,7 @@
       </c>
       <c r="D266" s="256"/>
       <c r="E266" s="58"/>
-      <c r="F266" s="374" t="s">
+      <c r="F266" s="373" t="s">
         <v>2473</v>
       </c>
       <c r="G266" s="32"/>
@@ -40214,7 +40210,7 @@
       <c r="C270" s="286" t="s">
         <v>3838</v>
       </c>
-      <c r="D270" s="365"/>
+      <c r="D270" s="364"/>
       <c r="E270" s="58" t="s">
         <v>2634</v>
       </c>
@@ -40308,7 +40304,7 @@
       <c r="J271" s="22"/>
       <c r="K271" s="22"/>
       <c r="L271" s="22"/>
-      <c r="M271" s="402" t="s">
+      <c r="M271" s="401" t="s">
         <v>2932</v>
       </c>
       <c r="N271" s="38" t="s">
@@ -40391,7 +40387,7 @@
       <c r="L272" s="211" t="s">
         <v>3225</v>
       </c>
-      <c r="M272" s="402" t="s">
+      <c r="M272" s="401" t="s">
         <v>3226</v>
       </c>
       <c r="N272" s="140" t="s">
@@ -40476,7 +40472,7 @@
       <c r="L273" s="83" t="s">
         <v>3355</v>
       </c>
-      <c r="M273" s="355" t="s">
+      <c r="M273" s="354" t="s">
         <v>3356</v>
       </c>
       <c r="N273" s="66" t="s">
@@ -40547,7 +40543,7 @@
       <c r="L274" s="22" t="s">
         <v>3472</v>
       </c>
-      <c r="M274" s="384" t="s">
+      <c r="M274" s="383" t="s">
         <v>3473</v>
       </c>
       <c r="N274" s="54" t="s">
@@ -40624,7 +40620,7 @@
       <c r="L275" s="22" t="s">
         <v>3486</v>
       </c>
-      <c r="M275" s="402" t="s">
+      <c r="M275" s="401" t="s">
         <v>3487</v>
       </c>
       <c r="N275" s="54" t="s">
@@ -40940,7 +40936,7 @@
       <c r="N279" s="54" t="s">
         <v>3586</v>
       </c>
-      <c r="O279" s="408"/>
+      <c r="O279" s="407"/>
       <c r="P279" s="118"/>
       <c r="Q279" s="56"/>
       <c r="R279" s="104" t="s">
@@ -40959,7 +40955,7 @@
       <c r="W279" s="134" t="s">
         <v>3199</v>
       </c>
-      <c r="X279" s="457" t="s">
+      <c r="X279" s="456" t="s">
         <v>3200</v>
       </c>
       <c r="Y279" s="30" t="s">
@@ -41173,7 +41169,7 @@
       <c r="N282" s="91" t="s">
         <v>3680</v>
       </c>
-      <c r="O282" s="412"/>
+      <c r="O282" s="411"/>
       <c r="P282" s="60" t="s">
         <v>1621</v>
       </c>
@@ -41228,7 +41224,7 @@
       <c r="B283" s="98" t="s">
         <v>2307</v>
       </c>
-      <c r="C283" s="362" t="s">
+      <c r="C283" s="361" t="s">
         <v>4004</v>
       </c>
       <c r="D283" s="256"/>
@@ -41248,7 +41244,7 @@
       <c r="L283" s="22" t="s">
         <v>3757</v>
       </c>
-      <c r="M283" s="352" t="s">
+      <c r="M283" s="351" t="s">
         <v>3758</v>
       </c>
       <c r="N283" s="38" t="s">
@@ -41392,7 +41388,7 @@
       <c r="N285" s="38" t="s">
         <v>1806</v>
       </c>
-      <c r="O285" s="409"/>
+      <c r="O285" s="408"/>
       <c r="P285" s="130"/>
       <c r="Q285" s="26"/>
       <c r="R285" s="119" t="s">
@@ -41607,7 +41603,7 @@
       <c r="N288" s="140" t="s">
         <v>639</v>
       </c>
-      <c r="O288" s="408"/>
+      <c r="O288" s="407"/>
       <c r="P288" s="118"/>
       <c r="Q288" s="127"/>
       <c r="R288" s="119" t="s">
@@ -41650,7 +41646,7 @@
       <c r="B289" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="C289" s="357" t="s">
+      <c r="C289" s="356" t="s">
         <v>767</v>
       </c>
       <c r="D289" s="256"/>
@@ -42012,7 +42008,7 @@
       </c>
       <c r="D294" s="256"/>
       <c r="E294" s="58"/>
-      <c r="F294" s="374" t="s">
+      <c r="F294" s="373" t="s">
         <v>1079</v>
       </c>
       <c r="G294" s="32"/>
@@ -42033,7 +42029,7 @@
       <c r="N294" s="140" t="s">
         <v>1084</v>
       </c>
-      <c r="O294" s="414"/>
+      <c r="O294" s="413"/>
       <c r="P294" s="60" t="s">
         <v>1085</v>
       </c>
@@ -42173,7 +42169,7 @@
       <c r="L296" s="22" t="s">
         <v>1171</v>
       </c>
-      <c r="M296" s="400" t="s">
+      <c r="M296" s="399" t="s">
         <v>868</v>
       </c>
       <c r="N296" s="38" t="s">
@@ -42319,7 +42315,7 @@
       <c r="N298" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="O298" s="408"/>
+      <c r="O298" s="407"/>
       <c r="P298" s="118"/>
       <c r="Q298" s="56"/>
       <c r="R298" s="119" t="s">
@@ -42569,7 +42565,7 @@
       <c r="B302" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C302" s="357" t="s">
+      <c r="C302" s="356" t="s">
         <v>1493</v>
       </c>
       <c r="D302" s="256"/>
@@ -42821,7 +42817,7 @@
       <c r="S305" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T305" s="427" t="s">
+      <c r="T305" s="426" t="s">
         <v>1884</v>
       </c>
       <c r="U305" s="109"/>
@@ -43024,7 +43020,7 @@
       </c>
       <c r="D308" s="256"/>
       <c r="E308" s="58"/>
-      <c r="F308" s="372" t="s">
+      <c r="F308" s="371" t="s">
         <v>1982</v>
       </c>
       <c r="G308" s="32"/>
@@ -43289,7 +43285,7 @@
       <c r="S311" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="T311" s="440" t="s">
+      <c r="T311" s="439" t="s">
         <v>2620</v>
       </c>
       <c r="U311" s="28"/>
@@ -43349,7 +43345,7 @@
       <c r="N312" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="O312" s="409"/>
+      <c r="O312" s="408"/>
       <c r="P312" s="130"/>
       <c r="Q312" s="127"/>
       <c r="R312" s="39" t="s">
@@ -43583,7 +43579,7 @@
       <c r="S315" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="T315" s="381" t="s">
+      <c r="T315" s="380" t="s">
         <v>3184</v>
       </c>
       <c r="U315" s="28"/>
@@ -43646,7 +43642,7 @@
       <c r="O316" s="54"/>
       <c r="P316" s="55"/>
       <c r="Q316" s="56"/>
-      <c r="R316" s="361" t="s">
+      <c r="R316" s="360" t="s">
         <v>377</v>
       </c>
       <c r="S316" s="78" t="s">
@@ -43706,7 +43702,7 @@
       <c r="L317" s="83" t="s">
         <v>546</v>
       </c>
-      <c r="M317" s="400" t="s">
+      <c r="M317" s="399" t="s">
         <v>547</v>
       </c>
       <c r="N317" s="91" t="s">
@@ -43764,7 +43760,7 @@
       <c r="C318" s="272" t="s">
         <v>846</v>
       </c>
-      <c r="D318" s="364"/>
+      <c r="D318" s="363"/>
       <c r="E318" s="58"/>
       <c r="F318" s="47" t="s">
         <v>847</v>
@@ -43781,7 +43777,7 @@
       <c r="L318" s="22" t="s">
         <v>546</v>
       </c>
-      <c r="M318" s="400" t="s">
+      <c r="M318" s="399" t="s">
         <v>850</v>
       </c>
       <c r="N318" s="74" t="s">
@@ -43790,7 +43786,7 @@
       <c r="O318" s="74"/>
       <c r="P318" s="75"/>
       <c r="Q318" s="76"/>
-      <c r="R318" s="422" t="s">
+      <c r="R318" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S318" s="32" t="s">
@@ -43850,7 +43846,7 @@
       <c r="L319" s="112" t="s">
         <v>892</v>
       </c>
-      <c r="M319" s="400" t="s">
+      <c r="M319" s="399" t="s">
         <v>893</v>
       </c>
       <c r="N319" s="91" t="s">
@@ -43859,7 +43855,7 @@
       <c r="O319" s="74"/>
       <c r="P319" s="75"/>
       <c r="Q319" s="76"/>
-      <c r="R319" s="422" t="s">
+      <c r="R319" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S319" s="32" t="s">
@@ -43993,7 +43989,7 @@
       <c r="O321" s="74"/>
       <c r="P321" s="75"/>
       <c r="Q321" s="76"/>
-      <c r="R321" s="422" t="s">
+      <c r="R321" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S321" s="32" t="s">
@@ -44057,7 +44053,7 @@
       <c r="L322" s="83" t="s">
         <v>1631</v>
       </c>
-      <c r="M322" s="386" t="s">
+      <c r="M322" s="385" t="s">
         <v>1632</v>
       </c>
       <c r="N322" s="54" t="s">
@@ -44066,7 +44062,7 @@
       <c r="O322" s="54"/>
       <c r="P322" s="55"/>
       <c r="Q322" s="56"/>
-      <c r="R322" s="352" t="s">
+      <c r="R322" s="351" t="s">
         <v>549</v>
       </c>
       <c r="S322" s="32" t="s">
@@ -44133,7 +44129,7 @@
       <c r="O323" s="54"/>
       <c r="P323" s="55"/>
       <c r="Q323" s="56"/>
-      <c r="R323" s="422" t="s">
+      <c r="R323" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S323" s="32" t="s">
@@ -44204,7 +44200,7 @@
       <c r="O324" s="54"/>
       <c r="P324" s="75"/>
       <c r="Q324" s="56"/>
-      <c r="R324" s="422" t="s">
+      <c r="R324" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S324" s="32" t="s">
@@ -44216,7 +44212,7 @@
       <c r="W324" s="29"/>
       <c r="X324" s="29"/>
       <c r="Y324" s="30"/>
-      <c r="Z324" s="460" t="s">
+      <c r="Z324" s="459" t="s">
         <v>1911</v>
       </c>
       <c r="AA324" s="30"/>
@@ -44249,7 +44245,7 @@
       </c>
       <c r="D325" s="256"/>
       <c r="E325" s="58"/>
-      <c r="F325" s="372" t="s">
+      <c r="F325" s="371" t="s">
         <v>2234</v>
       </c>
       <c r="G325" s="32"/>
@@ -44273,7 +44269,7 @@
       <c r="O325" s="54"/>
       <c r="P325" s="55"/>
       <c r="Q325" s="56"/>
-      <c r="R325" s="425" t="s">
+      <c r="R325" s="424" t="s">
         <v>549</v>
       </c>
       <c r="S325" s="32" t="s">
@@ -44318,7 +44314,7 @@
       <c r="C326" s="271" t="s">
         <v>172</v>
       </c>
-      <c r="D326" s="364"/>
+      <c r="D326" s="363"/>
       <c r="E326" s="58"/>
       <c r="F326" s="32" t="s">
         <v>2507</v>
@@ -44342,7 +44338,7 @@
       <c r="O326" s="38"/>
       <c r="P326" s="25"/>
       <c r="Q326" s="26"/>
-      <c r="R326" s="427" t="s">
+      <c r="R326" s="426" t="s">
         <v>549</v>
       </c>
       <c r="S326" s="78" t="s">
@@ -44409,7 +44405,7 @@
       <c r="O327" s="38"/>
       <c r="P327" s="25"/>
       <c r="Q327" s="56"/>
-      <c r="R327" s="422" t="s">
+      <c r="R327" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S327" s="78" t="s">
@@ -44462,7 +44458,7 @@
       </c>
       <c r="D328" s="266"/>
       <c r="E328" s="52"/>
-      <c r="F328" s="346" t="s">
+      <c r="F328" s="345" t="s">
         <v>2308</v>
       </c>
       <c r="G328" s="48"/>
@@ -44571,7 +44567,7 @@
       <c r="O329" s="38"/>
       <c r="P329" s="25"/>
       <c r="Q329" s="56"/>
-      <c r="R329" s="422" t="s">
+      <c r="R329" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S329" s="78" t="s">
@@ -44624,7 +44620,7 @@
       </c>
       <c r="D330" s="268"/>
       <c r="E330" s="205"/>
-      <c r="F330" s="378" t="s">
+      <c r="F330" s="377" t="s">
         <v>2719</v>
       </c>
       <c r="G330" s="201"/>
@@ -44810,7 +44806,7 @@
       <c r="O332" s="38"/>
       <c r="P332" s="25"/>
       <c r="Q332" s="56"/>
-      <c r="R332" s="422" t="s">
+      <c r="R332" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S332" s="78" t="s">
@@ -44885,7 +44881,7 @@
       <c r="O333" s="38"/>
       <c r="P333" s="25"/>
       <c r="Q333" s="56"/>
-      <c r="R333" s="428" t="s">
+      <c r="R333" s="427" t="s">
         <v>549</v>
       </c>
       <c r="S333" s="78" t="s">
@@ -44958,7 +44954,7 @@
       <c r="O334" s="38"/>
       <c r="P334" s="25"/>
       <c r="Q334" s="56"/>
-      <c r="R334" s="422" t="s">
+      <c r="R334" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S334" s="78" t="s">
@@ -45032,10 +45028,10 @@
       <c r="N335" s="54" t="s">
         <v>2847</v>
       </c>
-      <c r="O335" s="408"/>
+      <c r="O335" s="407"/>
       <c r="P335" s="118"/>
       <c r="Q335" s="56"/>
-      <c r="R335" s="422" t="s">
+      <c r="R335" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S335" s="78" t="s">
@@ -45108,7 +45104,7 @@
       <c r="O336" s="54"/>
       <c r="P336" s="55"/>
       <c r="Q336" s="56"/>
-      <c r="R336" s="352" t="s">
+      <c r="R336" s="351" t="s">
         <v>549</v>
       </c>
       <c r="S336" s="78" t="s">
@@ -45174,7 +45170,7 @@
       <c r="J337" s="83"/>
       <c r="K337" s="83"/>
       <c r="L337" s="83"/>
-      <c r="M337" s="402" t="s">
+      <c r="M337" s="401" t="s">
         <v>2898</v>
       </c>
       <c r="N337" s="38" t="s">
@@ -45187,7 +45183,7 @@
       <c r="Q337" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="R337" s="422" t="s">
+      <c r="R337" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S337" s="78" t="s">
@@ -45268,7 +45264,7 @@
       <c r="Q338" s="26" t="s">
         <v>2908</v>
       </c>
-      <c r="R338" s="432" t="s">
+      <c r="R338" s="431" t="s">
         <v>549</v>
       </c>
       <c r="S338" s="78" t="s">
@@ -45341,7 +45337,7 @@
       <c r="O339" s="59"/>
       <c r="P339" s="130"/>
       <c r="Q339" s="26"/>
-      <c r="R339" s="428" t="s">
+      <c r="R339" s="427" t="s">
         <v>549</v>
       </c>
       <c r="S339" s="78" t="s">
@@ -45413,14 +45409,14 @@
       <c r="N340" s="38" t="s">
         <v>2945</v>
       </c>
-      <c r="O340" s="409" t="s">
+      <c r="O340" s="408" t="s">
         <v>2130</v>
       </c>
       <c r="P340" s="60"/>
       <c r="Q340" s="26" t="s">
         <v>2946</v>
       </c>
-      <c r="R340" s="422" t="s">
+      <c r="R340" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S340" s="78"/>
@@ -45495,7 +45491,7 @@
       <c r="O341" s="54"/>
       <c r="P341" s="55"/>
       <c r="Q341" s="56"/>
-      <c r="R341" s="425" t="s">
+      <c r="R341" s="424" t="s">
         <v>549</v>
       </c>
       <c r="S341" s="78" t="s">
@@ -45555,7 +45551,7 @@
       <c r="H342" s="222" t="s">
         <v>2978</v>
       </c>
-      <c r="I342" s="385" t="s">
+      <c r="I342" s="384" t="s">
         <v>2541</v>
       </c>
       <c r="J342" s="22"/>
@@ -45570,7 +45566,7 @@
       <c r="O342" s="66"/>
       <c r="P342" s="55"/>
       <c r="Q342" s="56"/>
-      <c r="R342" s="428" t="s">
+      <c r="R342" s="427" t="s">
         <v>549</v>
       </c>
       <c r="S342" s="78" t="s">
@@ -45588,7 +45584,7 @@
       <c r="Y342" s="227" t="s">
         <v>2981</v>
       </c>
-      <c r="Z342" s="459" t="s">
+      <c r="Z342" s="458" t="s">
         <v>2982</v>
       </c>
       <c r="AA342" s="228"/>
@@ -45720,10 +45716,10 @@
       <c r="M344" s="143" t="s">
         <v>547</v>
       </c>
-      <c r="N344" s="409" t="s">
+      <c r="N344" s="408" t="s">
         <v>3040</v>
       </c>
-      <c r="O344" s="409"/>
+      <c r="O344" s="408"/>
       <c r="P344" s="25"/>
       <c r="Q344" s="26"/>
       <c r="R344" s="102" t="s">
@@ -45825,7 +45821,7 @@
       <c r="AA345" s="213" t="s">
         <v>3081</v>
       </c>
-      <c r="AB345" s="466"/>
+      <c r="AB345" s="465"/>
       <c r="AC345" s="16" t="s">
         <v>3082</v>
       </c>
@@ -45871,7 +45867,7 @@
       <c r="L346" s="22" t="s">
         <v>3095</v>
       </c>
-      <c r="M346" s="397" t="s">
+      <c r="M346" s="396" t="s">
         <v>547</v>
       </c>
       <c r="N346" s="54" t="s">
@@ -45948,7 +45944,7 @@
       </c>
       <c r="K347" s="22"/>
       <c r="L347" s="22"/>
-      <c r="M347" s="404" t="s">
+      <c r="M347" s="403" t="s">
         <v>3122</v>
       </c>
       <c r="N347" s="54" t="s">
@@ -46114,7 +46110,7 @@
       <c r="N349" s="38" t="s">
         <v>3142</v>
       </c>
-      <c r="O349" s="409"/>
+      <c r="O349" s="408"/>
       <c r="P349" s="130"/>
       <c r="Q349" s="26"/>
       <c r="R349" s="102" t="s">
@@ -46170,7 +46166,7 @@
       </c>
       <c r="D350" s="256"/>
       <c r="E350" s="58"/>
-      <c r="F350" s="372" t="s">
+      <c r="F350" s="371" t="s">
         <v>3168</v>
       </c>
       <c r="G350" s="32"/>
@@ -46266,7 +46262,7 @@
       <c r="N351" s="54" t="s">
         <v>3179</v>
       </c>
-      <c r="O351" s="408" t="s">
+      <c r="O351" s="407" t="s">
         <v>38</v>
       </c>
       <c r="P351" s="118"/>
@@ -46414,7 +46410,7 @@
       <c r="N353" s="38" t="s">
         <v>3198</v>
       </c>
-      <c r="O353" s="409"/>
+      <c r="O353" s="408"/>
       <c r="P353" s="118"/>
       <c r="Q353" s="56"/>
       <c r="R353" s="121" t="s">
@@ -46622,7 +46618,7 @@
       </c>
       <c r="D356" s="256"/>
       <c r="E356" s="58"/>
-      <c r="F356" s="376" t="s">
+      <c r="F356" s="375" t="s">
         <v>3240</v>
       </c>
       <c r="G356" s="32"/>
@@ -46670,7 +46666,7 @@
       <c r="AA356" s="30" t="s">
         <v>3245</v>
       </c>
-      <c r="AB356" s="466"/>
+      <c r="AB356" s="465"/>
       <c r="AC356" s="32"/>
       <c r="AD356" s="21"/>
       <c r="AE356" s="32"/>
@@ -46984,7 +46980,7 @@
       </c>
       <c r="Z360" s="30"/>
       <c r="AA360" s="30"/>
-      <c r="AB360" s="463" t="s">
+      <c r="AB360" s="462" t="s">
         <v>3295</v>
       </c>
       <c r="AC360" s="32"/>
@@ -47063,7 +47059,7 @@
       <c r="AA361" s="213" t="s">
         <v>3328</v>
       </c>
-      <c r="AB361" s="463" t="s">
+      <c r="AB361" s="462" t="s">
         <v>3329</v>
       </c>
       <c r="AC361" s="47" t="s">
@@ -47144,7 +47140,7 @@
       <c r="AA362" s="213" t="s">
         <v>3336</v>
       </c>
-      <c r="AB362" s="462" t="s">
+      <c r="AB362" s="461" t="s">
         <v>3337</v>
       </c>
       <c r="AC362" s="47" t="s">
@@ -47192,7 +47188,7 @@
       <c r="L363" s="22" t="s">
         <v>3095</v>
       </c>
-      <c r="M363" s="402" t="s">
+      <c r="M363" s="401" t="s">
         <v>2722</v>
       </c>
       <c r="N363" s="38" t="s">
@@ -47223,7 +47219,7 @@
       <c r="AA363" s="30" t="s">
         <v>3349</v>
       </c>
-      <c r="AB363" s="462" t="s">
+      <c r="AB363" s="461" t="s">
         <v>3350</v>
       </c>
       <c r="AC363" s="32"/>
@@ -47482,7 +47478,7 @@
       <c r="F367" s="313" t="s">
         <v>3408</v>
       </c>
-      <c r="G367" s="352"/>
+      <c r="G367" s="351"/>
       <c r="H367" s="222" t="s">
         <v>3409</v>
       </c>
@@ -47505,7 +47501,7 @@
       <c r="Q367" s="26" t="s">
         <v>1179</v>
       </c>
-      <c r="R367" s="425" t="s">
+      <c r="R367" s="424" t="s">
         <v>549</v>
       </c>
       <c r="S367" s="78" t="s">
@@ -47561,7 +47557,7 @@
       <c r="F368" s="317" t="s">
         <v>3431</v>
       </c>
-      <c r="G368" s="379"/>
+      <c r="G368" s="378"/>
       <c r="H368" s="207" t="s">
         <v>3432</v>
       </c>
@@ -47582,7 +47578,7 @@
       <c r="O368" s="38"/>
       <c r="P368" s="25"/>
       <c r="Q368" s="56"/>
-      <c r="R368" s="422" t="s">
+      <c r="R368" s="421" t="s">
         <v>549</v>
       </c>
       <c r="S368" s="78" t="s">
@@ -47628,7 +47624,7 @@
       <c r="B369" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C369" s="360" t="s">
+      <c r="C369" s="359" t="s">
         <v>3985</v>
       </c>
       <c r="D369" s="268"/>
@@ -47715,7 +47711,7 @@
       <c r="F370" s="206" t="s">
         <v>3457</v>
       </c>
-      <c r="G370" s="379"/>
+      <c r="G370" s="378"/>
       <c r="H370" s="222" t="s">
         <v>3458</v>
       </c>
@@ -47740,7 +47736,7 @@
       <c r="Q370" s="56" t="s">
         <v>3461</v>
       </c>
-      <c r="R370" s="425" t="s">
+      <c r="R370" s="424" t="s">
         <v>549</v>
       </c>
       <c r="S370" s="78" t="s">
@@ -47817,7 +47813,7 @@
       <c r="O371" s="54"/>
       <c r="P371" s="55"/>
       <c r="Q371" s="56"/>
-      <c r="R371" s="352" t="s">
+      <c r="R371" s="351" t="s">
         <v>382</v>
       </c>
       <c r="S371" s="32" t="s">
@@ -47863,7 +47859,7 @@
       <c r="F372" s="16" t="s">
         <v>493</v>
       </c>
-      <c r="G372" s="352" t="s">
+      <c r="G372" s="351" t="s">
         <v>494</v>
       </c>
       <c r="H372" s="14" t="s">
@@ -47967,7 +47963,7 @@
       <c r="Q373" s="93" t="s">
         <v>2267</v>
       </c>
-      <c r="R373" s="352" t="s">
+      <c r="R373" s="351" t="s">
         <v>382</v>
       </c>
       <c r="S373" s="32" t="s">
@@ -48019,7 +48015,7 @@
       <c r="F374" s="47" t="s">
         <v>747</v>
       </c>
-      <c r="G374" s="352"/>
+      <c r="G374" s="351"/>
       <c r="H374" s="48" t="s">
         <v>748</v>
       </c>
@@ -48108,14 +48104,14 @@
       <c r="N375" s="38" t="s">
         <v>3340</v>
       </c>
-      <c r="O375" s="407" t="s">
+      <c r="O375" s="406" t="s">
         <v>38</v>
       </c>
       <c r="P375" s="130"/>
       <c r="Q375" s="26" t="s">
         <v>1179</v>
       </c>
-      <c r="R375" s="428" t="s">
+      <c r="R375" s="427" t="s">
         <v>3341</v>
       </c>
       <c r="S375" s="78" t="s">
@@ -48159,60 +48155,60 @@
       <c r="AQ375" s="32"/>
     </row>
     <row r="376" spans="1:43" ht="48" customHeight="1">
-      <c r="A376" s="348" t="s">
+      <c r="A376" s="347" t="s">
         <v>3954</v>
       </c>
       <c r="B376" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C376" s="356" t="s">
+      <c r="C376" s="355" t="s">
         <v>3870</v>
       </c>
-      <c r="D376" s="364"/>
-      <c r="E376" s="371"/>
-      <c r="F376" s="374" t="s">
+      <c r="D376" s="363"/>
+      <c r="E376" s="370"/>
+      <c r="F376" s="373" t="s">
         <v>641</v>
       </c>
-      <c r="G376" s="352"/>
-      <c r="H376" s="352" t="s">
+      <c r="G376" s="351"/>
+      <c r="H376" s="351" t="s">
         <v>642</v>
       </c>
-      <c r="I376" s="386" t="s">
+      <c r="I376" s="385" t="s">
         <v>643</v>
       </c>
-      <c r="J376" s="395"/>
-      <c r="K376" s="391"/>
-      <c r="L376" s="391" t="s">
+      <c r="J376" s="394"/>
+      <c r="K376" s="390"/>
+      <c r="L376" s="390" t="s">
         <v>644</v>
       </c>
-      <c r="M376" s="401" t="s">
+      <c r="M376" s="400" t="s">
         <v>645</v>
       </c>
-      <c r="N376" s="409" t="s">
+      <c r="N376" s="408" t="s">
         <v>646</v>
       </c>
-      <c r="O376" s="409"/>
-      <c r="P376" s="417"/>
-      <c r="Q376" s="421"/>
-      <c r="R376" s="436" t="s">
+      <c r="O376" s="408"/>
+      <c r="P376" s="416"/>
+      <c r="Q376" s="420"/>
+      <c r="R376" s="435" t="s">
         <v>647</v>
       </c>
-      <c r="S376" s="352" t="s">
+      <c r="S376" s="351" t="s">
         <v>41</v>
       </c>
-      <c r="T376" s="441" t="s">
+      <c r="T376" s="440" t="s">
         <v>648</v>
       </c>
-      <c r="U376" s="446"/>
-      <c r="V376" s="446"/>
-      <c r="W376" s="451"/>
-      <c r="X376" s="451"/>
-      <c r="Y376" s="458"/>
-      <c r="Z376" s="458"/>
-      <c r="AA376" s="458"/>
-      <c r="AB376" s="464"/>
-      <c r="AC376" s="352"/>
-      <c r="AD376" s="352"/>
+      <c r="U376" s="445"/>
+      <c r="V376" s="445"/>
+      <c r="W376" s="450"/>
+      <c r="X376" s="450"/>
+      <c r="Y376" s="457"/>
+      <c r="Z376" s="457"/>
+      <c r="AA376" s="457"/>
+      <c r="AB376" s="463"/>
+      <c r="AC376" s="351"/>
+      <c r="AD376" s="351"/>
       <c r="AE376" s="249"/>
       <c r="AF376" s="249"/>
       <c r="AG376" s="249"/>
@@ -48263,7 +48259,7 @@
       <c r="O377" s="54"/>
       <c r="P377" s="55"/>
       <c r="Q377" s="56"/>
-      <c r="R377" s="436" t="s">
+      <c r="R377" s="435" t="s">
         <v>647</v>
       </c>
       <c r="S377" s="32" t="s">
@@ -48330,7 +48326,7 @@
       <c r="O378" s="66"/>
       <c r="P378" s="25"/>
       <c r="Q378" s="56"/>
-      <c r="R378" s="436" t="s">
+      <c r="R378" s="435" t="s">
         <v>647</v>
       </c>
       <c r="S378" s="32" t="s">
@@ -48344,7 +48340,7 @@
       <c r="Y378" s="30"/>
       <c r="Z378" s="30"/>
       <c r="AA378" s="30"/>
-      <c r="AB378" s="462" t="s">
+      <c r="AB378" s="461" t="s">
         <v>1948</v>
       </c>
       <c r="AC378" s="32"/>
@@ -48385,21 +48381,21 @@
       <c r="I379" s="43" t="s">
         <v>2288</v>
       </c>
-      <c r="J379" s="390" t="s">
+      <c r="J379" s="389" t="s">
         <v>2289</v>
       </c>
-      <c r="K379" s="390"/>
-      <c r="L379" s="390"/>
+      <c r="K379" s="389"/>
+      <c r="L379" s="389"/>
       <c r="M379" s="36" t="s">
         <v>138</v>
       </c>
       <c r="N379" s="74" t="s">
         <v>2290</v>
       </c>
-      <c r="O379" s="415"/>
+      <c r="O379" s="414"/>
       <c r="P379" s="60"/>
       <c r="Q379" s="76"/>
-      <c r="R379" s="352" t="s">
+      <c r="R379" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S379" s="32" t="s">
@@ -48468,7 +48464,7 @@
       <c r="O380" s="54"/>
       <c r="P380" s="55"/>
       <c r="Q380" s="56"/>
-      <c r="R380" s="352" t="s">
+      <c r="R380" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S380" s="32" t="s">
@@ -48511,7 +48507,7 @@
       </c>
       <c r="D381" s="256"/>
       <c r="E381" s="58"/>
-      <c r="F381" s="373" t="s">
+      <c r="F381" s="372" t="s">
         <v>2299</v>
       </c>
       <c r="G381" s="32" t="s">
@@ -48537,7 +48533,7 @@
       <c r="O381" s="74"/>
       <c r="P381" s="75"/>
       <c r="Q381" s="76"/>
-      <c r="R381" s="352" t="s">
+      <c r="R381" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S381" s="32" t="s">
@@ -48585,7 +48581,7 @@
       <c r="F382" s="32" t="s">
         <v>2308</v>
       </c>
-      <c r="G382" s="352" t="s">
+      <c r="G382" s="351" t="s">
         <v>2309</v>
       </c>
       <c r="H382" s="98" t="s">
@@ -48608,7 +48604,7 @@
       <c r="O382" s="38"/>
       <c r="P382" s="25"/>
       <c r="Q382" s="26"/>
-      <c r="R382" s="352" t="s">
+      <c r="R382" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S382" s="32" t="s">
@@ -48679,7 +48675,7 @@
       <c r="O383" s="54"/>
       <c r="P383" s="55"/>
       <c r="Q383" s="56"/>
-      <c r="R383" s="352" t="s">
+      <c r="R383" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S383" s="32" t="s">
@@ -48735,7 +48731,7 @@
       <c r="F384" s="32" t="s">
         <v>2308</v>
       </c>
-      <c r="G384" s="352" t="s">
+      <c r="G384" s="351" t="s">
         <v>2336</v>
       </c>
       <c r="H384" s="32" t="s">
@@ -48758,7 +48754,7 @@
       <c r="O384" s="91"/>
       <c r="P384" s="92"/>
       <c r="Q384" s="93"/>
-      <c r="R384" s="352" t="s">
+      <c r="R384" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S384" s="32" t="s">
@@ -48804,7 +48800,7 @@
       <c r="F385" s="16" t="s">
         <v>2346</v>
       </c>
-      <c r="G385" s="352"/>
+      <c r="G385" s="351"/>
       <c r="H385" s="98" t="s">
         <v>2347</v>
       </c>
@@ -48825,7 +48821,7 @@
       <c r="O385" s="54"/>
       <c r="P385" s="55"/>
       <c r="Q385" s="56"/>
-      <c r="R385" s="352" t="s">
+      <c r="R385" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S385" s="32" t="s">
@@ -48871,7 +48867,7 @@
       <c r="F386" s="47" t="s">
         <v>2367</v>
       </c>
-      <c r="G386" s="352" t="s">
+      <c r="G386" s="351" t="s">
         <v>2368</v>
       </c>
       <c r="H386" s="48" t="s">
@@ -48894,7 +48890,7 @@
       <c r="O386" s="38"/>
       <c r="P386" s="25"/>
       <c r="Q386" s="26"/>
-      <c r="R386" s="361" t="s">
+      <c r="R386" s="360" t="s">
         <v>647</v>
       </c>
       <c r="S386" s="32" t="s">
@@ -48965,7 +48961,7 @@
       <c r="O387" s="38"/>
       <c r="P387" s="25"/>
       <c r="Q387" s="26"/>
-      <c r="R387" s="352" t="s">
+      <c r="R387" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S387" s="32" t="s">
@@ -48997,58 +48993,58 @@
       <c r="AQ387" s="32"/>
     </row>
     <row r="388" spans="1:43" ht="45.75" customHeight="1">
-      <c r="A388" s="346" t="s">
+      <c r="A388" s="345" t="s">
         <v>2389</v>
       </c>
-      <c r="B388" s="346" t="s">
+      <c r="B388" s="345" t="s">
         <v>439</v>
       </c>
-      <c r="C388" s="356" t="s">
+      <c r="C388" s="355" t="s">
         <v>172</v>
       </c>
-      <c r="D388" s="364"/>
-      <c r="E388" s="371"/>
-      <c r="F388" s="374" t="s">
+      <c r="D388" s="363"/>
+      <c r="E388" s="370"/>
+      <c r="F388" s="373" t="s">
         <v>2390</v>
       </c>
-      <c r="G388" s="352" t="s">
+      <c r="G388" s="351" t="s">
         <v>2391</v>
       </c>
-      <c r="H388" s="383" t="s">
+      <c r="H388" s="382" t="s">
         <v>2392</v>
       </c>
-      <c r="I388" s="386" t="s">
+      <c r="I388" s="385" t="s">
         <v>1464</v>
       </c>
-      <c r="J388" s="391"/>
-      <c r="K388" s="391"/>
-      <c r="L388" s="391"/>
-      <c r="M388" s="400" t="s">
+      <c r="J388" s="390"/>
+      <c r="K388" s="390"/>
+      <c r="L388" s="390"/>
+      <c r="M388" s="399" t="s">
         <v>1112</v>
       </c>
-      <c r="N388" s="407" t="s">
+      <c r="N388" s="406" t="s">
         <v>2393</v>
       </c>
       <c r="O388" s="59"/>
-      <c r="P388" s="417"/>
-      <c r="Q388" s="419"/>
-      <c r="R388" s="352" t="s">
+      <c r="P388" s="416"/>
+      <c r="Q388" s="418"/>
+      <c r="R388" s="351" t="s">
         <v>647</v>
       </c>
-      <c r="S388" s="352" t="s">
+      <c r="S388" s="351" t="s">
         <v>41</v>
       </c>
-      <c r="T388" s="381"/>
-      <c r="U388" s="445"/>
-      <c r="V388" s="445"/>
-      <c r="W388" s="450"/>
-      <c r="X388" s="450"/>
-      <c r="Y388" s="458"/>
-      <c r="Z388" s="458"/>
-      <c r="AA388" s="458"/>
-      <c r="AB388" s="464"/>
-      <c r="AC388" s="352"/>
-      <c r="AD388" s="352"/>
+      <c r="T388" s="380"/>
+      <c r="U388" s="444"/>
+      <c r="V388" s="444"/>
+      <c r="W388" s="449"/>
+      <c r="X388" s="449"/>
+      <c r="Y388" s="457"/>
+      <c r="Z388" s="457"/>
+      <c r="AA388" s="457"/>
+      <c r="AB388" s="463"/>
+      <c r="AC388" s="351"/>
+      <c r="AD388" s="351"/>
       <c r="AE388" s="249"/>
       <c r="AF388" s="249"/>
       <c r="AG388" s="249"/>
@@ -49094,10 +49090,10 @@
       <c r="N389" s="54" t="s">
         <v>2410</v>
       </c>
-      <c r="O389" s="408"/>
+      <c r="O389" s="407"/>
       <c r="P389" s="118"/>
       <c r="Q389" s="56"/>
-      <c r="R389" s="352" t="s">
+      <c r="R389" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S389" s="32" t="s">
@@ -49166,7 +49162,7 @@
       <c r="O390" s="54"/>
       <c r="P390" s="55"/>
       <c r="Q390" s="56"/>
-      <c r="R390" s="352" t="s">
+      <c r="R390" s="351" t="s">
         <v>647</v>
       </c>
       <c r="S390" s="32" t="s">
@@ -49233,7 +49229,7 @@
       <c r="O391" s="54"/>
       <c r="P391" s="55"/>
       <c r="Q391" s="56"/>
-      <c r="R391" s="361" t="s">
+      <c r="R391" s="360" t="s">
         <v>647</v>
       </c>
       <c r="S391" s="32" t="s">
@@ -49273,25 +49269,25 @@
       <c r="AQ391" s="32"/>
     </row>
     <row r="392" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A392" s="346" t="s">
+      <c r="A392" s="345" t="s">
         <v>2429</v>
       </c>
-      <c r="B392" s="352" t="s">
+      <c r="B392" s="351" t="s">
         <v>43</v>
       </c>
       <c r="C392" s="277" t="s">
         <v>172</v>
       </c>
-      <c r="D392" s="364"/>
+      <c r="D392" s="363"/>
       <c r="E392" s="144"/>
-      <c r="F392" s="373" t="s">
+      <c r="F392" s="372" t="s">
         <v>2430</v>
       </c>
       <c r="G392" s="32"/>
-      <c r="H392" s="383" t="s">
+      <c r="H392" s="382" t="s">
         <v>2431</v>
       </c>
-      <c r="I392" s="386" t="s">
+      <c r="I392" s="385" t="s">
         <v>2432</v>
       </c>
       <c r="J392" s="83" t="s">
@@ -49302,7 +49298,7 @@
       <c r="M392" s="119" t="s">
         <v>2433</v>
       </c>
-      <c r="N392" s="408" t="s">
+      <c r="N392" s="407" t="s">
         <v>2434</v>
       </c>
       <c r="O392" s="117" t="s">
@@ -49312,10 +49308,10 @@
       <c r="Q392" s="127" t="s">
         <v>812</v>
       </c>
-      <c r="R392" s="361" t="s">
+      <c r="R392" s="360" t="s">
         <v>647</v>
       </c>
-      <c r="S392" s="352" t="s">
+      <c r="S392" s="351" t="s">
         <v>41</v>
       </c>
       <c r="T392" s="108"/>
@@ -49333,8 +49329,8 @@
         <v>2437</v>
       </c>
       <c r="AB392" s="113"/>
-      <c r="AC392" s="352"/>
-      <c r="AD392" s="361"/>
+      <c r="AC392" s="351"/>
+      <c r="AD392" s="360"/>
       <c r="AE392" s="39"/>
       <c r="AF392" s="39"/>
       <c r="AG392" s="39"/>
@@ -49903,7 +49899,7 @@
       </c>
       <c r="K400" s="22"/>
       <c r="L400" s="22"/>
-      <c r="M400" s="402" t="s">
+      <c r="M400" s="401" t="s">
         <v>138</v>
       </c>
       <c r="N400" s="91" t="s">
@@ -49912,7 +49908,7 @@
       <c r="O400" s="91"/>
       <c r="P400" s="92"/>
       <c r="Q400" s="93"/>
-      <c r="R400" s="423" t="s">
+      <c r="R400" s="422" t="s">
         <v>647</v>
       </c>
       <c r="S400" s="78" t="s">
@@ -49978,7 +49974,7 @@
       <c r="L401" s="22" t="s">
         <v>3029</v>
       </c>
-      <c r="M401" s="405" t="s">
+      <c r="M401" s="404" t="s">
         <v>2097</v>
       </c>
       <c r="N401" s="143" t="s">
@@ -49987,7 +49983,7 @@
       <c r="O401" s="143"/>
       <c r="P401" s="25"/>
       <c r="Q401" s="56"/>
-      <c r="R401" s="423" t="s">
+      <c r="R401" s="422" t="s">
         <v>647</v>
       </c>
       <c r="S401" s="78"/>
@@ -50017,58 +50013,58 @@
       <c r="AQ401" s="32"/>
     </row>
     <row r="402" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A402" s="350" t="s">
+      <c r="A402" s="349" t="s">
         <v>3127</v>
       </c>
       <c r="B402" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C402" s="358" t="s">
+      <c r="C402" s="357" t="s">
         <v>172</v>
       </c>
-      <c r="D402" s="365"/>
-      <c r="E402" s="370"/>
-      <c r="F402" s="375" t="s">
+      <c r="D402" s="364"/>
+      <c r="E402" s="369"/>
+      <c r="F402" s="374" t="s">
         <v>3872</v>
       </c>
-      <c r="G402" s="370"/>
-      <c r="H402" s="354" t="s">
+      <c r="G402" s="369"/>
+      <c r="H402" s="353" t="s">
         <v>3829</v>
       </c>
-      <c r="I402" s="354" t="s">
+      <c r="I402" s="353" t="s">
         <v>3128</v>
       </c>
-      <c r="J402" s="370"/>
-      <c r="K402" s="370"/>
-      <c r="L402" s="370"/>
+      <c r="J402" s="369"/>
+      <c r="K402" s="369"/>
+      <c r="L402" s="369"/>
       <c r="M402" s="251" t="s">
         <v>2097</v>
       </c>
-      <c r="N402" s="406" t="s">
+      <c r="N402" s="405" t="s">
         <v>2098</v>
       </c>
-      <c r="O402" s="370"/>
-      <c r="P402" s="370"/>
-      <c r="Q402" s="370"/>
+      <c r="O402" s="369"/>
+      <c r="P402" s="369"/>
+      <c r="Q402" s="369"/>
       <c r="R402" s="249" t="s">
         <v>647</v>
       </c>
-      <c r="S402" s="354" t="s">
+      <c r="S402" s="353" t="s">
         <v>41</v>
       </c>
-      <c r="T402" s="354" t="s">
+      <c r="T402" s="353" t="s">
         <v>3830</v>
       </c>
-      <c r="U402" s="370"/>
-      <c r="V402" s="370"/>
-      <c r="W402" s="370"/>
-      <c r="X402" s="370"/>
-      <c r="Y402" s="370"/>
-      <c r="Z402" s="455"/>
-      <c r="AA402" s="370"/>
-      <c r="AB402" s="370"/>
-      <c r="AC402" s="370"/>
-      <c r="AD402" s="354" t="s">
+      <c r="U402" s="369"/>
+      <c r="V402" s="369"/>
+      <c r="W402" s="369"/>
+      <c r="X402" s="369"/>
+      <c r="Y402" s="369"/>
+      <c r="Z402" s="454"/>
+      <c r="AA402" s="369"/>
+      <c r="AB402" s="369"/>
+      <c r="AC402" s="369"/>
+      <c r="AD402" s="353" t="s">
         <v>3831</v>
       </c>
       <c r="AE402" s="32"/>
@@ -50086,60 +50082,60 @@
       <c r="AQ402" s="32"/>
     </row>
     <row r="403" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A403" s="345" t="s">
+      <c r="A403" s="344" t="s">
         <v>3212</v>
       </c>
-      <c r="B403" s="353" t="s">
+      <c r="B403" s="352" t="s">
         <v>3832</v>
       </c>
-      <c r="C403" s="358" t="s">
+      <c r="C403" s="357" t="s">
         <v>172</v>
       </c>
-      <c r="D403" s="365"/>
-      <c r="E403" s="370"/>
-      <c r="F403" s="375" t="s">
+      <c r="D403" s="364"/>
+      <c r="E403" s="369"/>
+      <c r="F403" s="374" t="s">
         <v>3833</v>
       </c>
-      <c r="G403" s="370"/>
-      <c r="H403" s="382" t="s">
+      <c r="G403" s="369"/>
+      <c r="H403" s="381" t="s">
         <v>3834</v>
       </c>
-      <c r="I403" s="382" t="s">
+      <c r="I403" s="381" t="s">
         <v>3213</v>
       </c>
-      <c r="J403" s="370"/>
-      <c r="K403" s="370"/>
-      <c r="L403" s="370" t="s">
+      <c r="J403" s="369"/>
+      <c r="K403" s="369"/>
+      <c r="L403" s="369" t="s">
         <v>3835</v>
       </c>
       <c r="M403" s="251" t="s">
         <v>2097</v>
       </c>
-      <c r="N403" s="406" t="s">
+      <c r="N403" s="405" t="s">
         <v>2098</v>
       </c>
-      <c r="O403" s="370"/>
-      <c r="P403" s="370"/>
-      <c r="Q403" s="370"/>
+      <c r="O403" s="369"/>
+      <c r="P403" s="369"/>
+      <c r="Q403" s="369"/>
       <c r="R403" s="249" t="s">
         <v>647</v>
       </c>
-      <c r="S403" s="354" t="s">
+      <c r="S403" s="353" t="s">
         <v>41</v>
       </c>
-      <c r="T403" s="354" t="s">
+      <c r="T403" s="353" t="s">
         <v>3836</v>
       </c>
-      <c r="U403" s="370"/>
-      <c r="V403" s="370"/>
-      <c r="W403" s="370"/>
-      <c r="X403" s="455"/>
-      <c r="Y403" s="370"/>
-      <c r="Z403" s="455"/>
-      <c r="AA403" s="370"/>
-      <c r="AB403" s="370"/>
-      <c r="AC403" s="370"/>
-      <c r="AD403" s="354" t="s">
+      <c r="U403" s="369"/>
+      <c r="V403" s="369"/>
+      <c r="W403" s="369"/>
+      <c r="X403" s="454"/>
+      <c r="Y403" s="369"/>
+      <c r="Z403" s="454"/>
+      <c r="AA403" s="369"/>
+      <c r="AB403" s="369"/>
+      <c r="AC403" s="369"/>
+      <c r="AD403" s="353" t="s">
         <v>3837</v>
       </c>
       <c r="AE403" s="32"/>
@@ -50183,7 +50179,7 @@
       </c>
       <c r="K404" s="83"/>
       <c r="L404" s="83"/>
-      <c r="M404" s="397" t="s">
+      <c r="M404" s="396" t="s">
         <v>3219</v>
       </c>
       <c r="N404" s="54" t="s">
@@ -50192,7 +50188,7 @@
       <c r="O404" s="54"/>
       <c r="P404" s="55"/>
       <c r="Q404" s="56"/>
-      <c r="R404" s="424" t="s">
+      <c r="R404" s="423" t="s">
         <v>647</v>
       </c>
       <c r="S404" s="78" t="s">
@@ -50263,7 +50259,7 @@
       <c r="O405" s="143"/>
       <c r="P405" s="55"/>
       <c r="Q405" s="56"/>
-      <c r="R405" s="423" t="s">
+      <c r="R405" s="422" t="s">
         <v>647</v>
       </c>
       <c r="S405" s="78" t="s">
@@ -50327,7 +50323,7 @@
       <c r="N406" s="143" t="s">
         <v>2098</v>
       </c>
-      <c r="O406" s="402"/>
+      <c r="O406" s="401"/>
       <c r="P406" s="118"/>
       <c r="Q406" s="56"/>
       <c r="R406" s="78" t="s">
@@ -50452,10 +50448,10 @@
       <c r="I408" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="J408" s="388" t="s">
+      <c r="J408" s="387" t="s">
         <v>137</v>
       </c>
-      <c r="K408" s="388"/>
+      <c r="K408" s="387"/>
       <c r="L408" s="69"/>
       <c r="M408" s="36" t="s">
         <v>138</v>
@@ -50626,7 +50622,7 @@
       <c r="Y410" s="30"/>
       <c r="Z410" s="30"/>
       <c r="AA410" s="30"/>
-      <c r="AB410" s="461" t="s">
+      <c r="AB410" s="460" t="s">
         <v>238</v>
       </c>
       <c r="AC410" s="70" t="s">
@@ -50662,7 +50658,7 @@
       <c r="F411" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="G411" s="352" t="s">
+      <c r="G411" s="351" t="s">
         <v>242</v>
       </c>
       <c r="H411" s="98" t="s">
@@ -50822,7 +50818,7 @@
       </c>
       <c r="K413" s="112"/>
       <c r="L413" s="112"/>
-      <c r="M413" s="401" t="s">
+      <c r="M413" s="400" t="s">
         <v>138</v>
       </c>
       <c r="N413" s="38" t="s">
@@ -50831,7 +50827,7 @@
       <c r="O413" s="38"/>
       <c r="P413" s="25"/>
       <c r="Q413" s="56"/>
-      <c r="R413" s="435" t="s">
+      <c r="R413" s="434" t="s">
         <v>140</v>
       </c>
       <c r="S413" s="32" t="s">
@@ -50871,7 +50867,7 @@
       <c r="B414" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C414" s="356" t="s">
+      <c r="C414" s="355" t="s">
         <v>3851</v>
       </c>
       <c r="D414" s="256"/>
@@ -50902,7 +50898,7 @@
       <c r="O414" s="54"/>
       <c r="P414" s="55"/>
       <c r="Q414" s="56"/>
-      <c r="R414" s="401" t="s">
+      <c r="R414" s="400" t="s">
         <v>140</v>
       </c>
       <c r="S414" s="32" t="s">
@@ -50972,7 +50968,7 @@
       </c>
       <c r="K415" s="22"/>
       <c r="L415" s="22"/>
-      <c r="M415" s="401" t="s">
+      <c r="M415" s="400" t="s">
         <v>138</v>
       </c>
       <c r="N415" s="54" t="s">
@@ -51101,7 +51097,7 @@
       <c r="G417" s="32" t="s">
         <v>554</v>
       </c>
-      <c r="H417" s="383" t="s">
+      <c r="H417" s="382" t="s">
         <v>555</v>
       </c>
       <c r="I417" s="43" t="s">
@@ -51192,7 +51188,7 @@
       <c r="O418" s="91"/>
       <c r="P418" s="55"/>
       <c r="Q418" s="56"/>
-      <c r="R418" s="401" t="s">
+      <c r="R418" s="400" t="s">
         <v>140</v>
       </c>
       <c r="S418" s="32" t="s">
@@ -51261,7 +51257,7 @@
       <c r="O419" s="54"/>
       <c r="P419" s="55"/>
       <c r="Q419" s="56"/>
-      <c r="R419" s="398" t="s">
+      <c r="R419" s="397" t="s">
         <v>140</v>
       </c>
       <c r="S419" s="32" t="s">
@@ -51330,7 +51326,7 @@
       <c r="O420" s="38"/>
       <c r="P420" s="25"/>
       <c r="Q420" s="26"/>
-      <c r="R420" s="355" t="s">
+      <c r="R420" s="354" t="s">
         <v>140</v>
       </c>
       <c r="S420" s="32" t="s">
@@ -51548,7 +51544,7 @@
       <c r="N423" s="38" t="s">
         <v>3386</v>
       </c>
-      <c r="O423" s="409"/>
+      <c r="O423" s="408"/>
       <c r="P423" s="130"/>
       <c r="Q423" s="56"/>
       <c r="R423" s="160" t="s">
@@ -51617,7 +51613,7 @@
       </c>
       <c r="K424" s="112"/>
       <c r="L424" s="112"/>
-      <c r="M424" s="403" t="s">
+      <c r="M424" s="402" t="s">
         <v>138</v>
       </c>
       <c r="N424" s="38" t="s">
@@ -51816,7 +51812,7 @@
       <c r="B427" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="C427" s="360" t="s">
+      <c r="C427" s="359" t="s">
         <v>4007</v>
       </c>
       <c r="D427" s="256"/>
@@ -51911,7 +51907,7 @@
       <c r="N428" s="54" t="s">
         <v>3533</v>
       </c>
-      <c r="O428" s="408"/>
+      <c r="O428" s="407"/>
       <c r="P428" s="118"/>
       <c r="Q428" s="127"/>
       <c r="R428" s="119" t="s">
@@ -52127,7 +52123,7 @@
       <c r="O431" s="59"/>
       <c r="P431" s="130"/>
       <c r="Q431" s="127"/>
-      <c r="R431" s="401" t="s">
+      <c r="R431" s="400" t="s">
         <v>3734</v>
       </c>
       <c r="S431" s="78" t="s">
@@ -52344,7 +52340,7 @@
       <c r="O434" s="54"/>
       <c r="P434" s="55"/>
       <c r="Q434" s="56"/>
-      <c r="R434" s="403" t="s">
+      <c r="R434" s="402" t="s">
         <v>399</v>
       </c>
       <c r="S434" s="32" t="s">
@@ -52401,10 +52397,10 @@
       <c r="I435" s="43" t="s">
         <v>404</v>
       </c>
-      <c r="J435" s="389" t="s">
+      <c r="J435" s="388" t="s">
         <v>405</v>
       </c>
-      <c r="K435" s="389"/>
+      <c r="K435" s="388"/>
       <c r="L435" s="123"/>
       <c r="M435" s="53" t="s">
         <v>344</v>
@@ -52642,9 +52638,9 @@
       <c r="S438" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T438" s="437"/>
-      <c r="U438" s="443"/>
-      <c r="V438" s="443"/>
+      <c r="T438" s="436"/>
+      <c r="U438" s="442"/>
+      <c r="V438" s="442"/>
       <c r="W438" s="116"/>
       <c r="X438" s="116"/>
       <c r="Y438" s="30"/>
@@ -52700,14 +52696,14 @@
       <c r="N439" s="54" t="s">
         <v>1955</v>
       </c>
-      <c r="O439" s="408"/>
+      <c r="O439" s="407"/>
       <c r="P439" s="60" t="s">
         <v>1937</v>
       </c>
       <c r="Q439" s="56" t="s">
         <v>1938</v>
       </c>
-      <c r="R439" s="426" t="s">
+      <c r="R439" s="425" t="s">
         <v>567</v>
       </c>
       <c r="S439" s="32" t="s">
@@ -52941,7 +52937,7 @@
       <c r="N442" s="150" t="s">
         <v>1242</v>
       </c>
-      <c r="O442" s="413"/>
+      <c r="O442" s="412"/>
       <c r="P442" s="60"/>
       <c r="Q442" s="76"/>
       <c r="R442" s="160" t="s">
@@ -53781,7 +53777,7 @@
       </c>
       <c r="J453" s="35"/>
       <c r="K453" s="168"/>
-      <c r="L453" s="389" t="s">
+      <c r="L453" s="388" t="s">
         <v>1541</v>
       </c>
       <c r="M453" s="15" t="s">
@@ -53941,7 +53937,7 @@
       <c r="O455" s="140"/>
       <c r="P455" s="55"/>
       <c r="Q455" s="56"/>
-      <c r="R455" s="430" t="s">
+      <c r="R455" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S455" s="21" t="s">
@@ -54020,7 +54016,7 @@
       <c r="O456" s="140"/>
       <c r="P456" s="55"/>
       <c r="Q456" s="56"/>
-      <c r="R456" s="430" t="s">
+      <c r="R456" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S456" s="21" t="s">
@@ -54085,7 +54081,7 @@
       <c r="I457" s="131" t="s">
         <v>1594</v>
       </c>
-      <c r="J457" s="392" t="s">
+      <c r="J457" s="391" t="s">
         <v>1595</v>
       </c>
       <c r="K457" s="35"/>
@@ -54099,7 +54095,7 @@
       <c r="O457" s="140"/>
       <c r="P457" s="55"/>
       <c r="Q457" s="56"/>
-      <c r="R457" s="430" t="s">
+      <c r="R457" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S457" s="21" t="s">
@@ -54235,7 +54231,7 @@
       <c r="O459" s="140"/>
       <c r="P459" s="55"/>
       <c r="Q459" s="56"/>
-      <c r="R459" s="430" t="s">
+      <c r="R459" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S459" s="21" t="s">
@@ -54245,7 +54241,7 @@
       <c r="U459" s="28" t="s">
         <v>1072</v>
       </c>
-      <c r="V459" s="449" t="s">
+      <c r="V459" s="448" t="s">
         <v>1650</v>
       </c>
       <c r="W459" s="29"/>
@@ -54311,10 +54307,10 @@
       <c r="N460" s="74" t="s">
         <v>1712</v>
       </c>
-      <c r="O460" s="415"/>
+      <c r="O460" s="414"/>
       <c r="P460" s="60"/>
       <c r="Q460" s="76"/>
-      <c r="R460" s="430" t="s">
+      <c r="R460" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S460" s="32" t="s">
@@ -54395,7 +54391,7 @@
       <c r="O461" s="74"/>
       <c r="P461" s="75"/>
       <c r="Q461" s="76"/>
-      <c r="R461" s="430" t="s">
+      <c r="R461" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S461" s="32" t="s">
@@ -54466,7 +54462,7 @@
       <c r="O462" s="54"/>
       <c r="P462" s="55"/>
       <c r="Q462" s="56"/>
-      <c r="R462" s="430" t="s">
+      <c r="R462" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S462" s="32" t="s">
@@ -54535,7 +54531,7 @@
       <c r="O463" s="54"/>
       <c r="P463" s="55"/>
       <c r="Q463" s="56"/>
-      <c r="R463" s="430" t="s">
+      <c r="R463" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S463" s="32" t="s">
@@ -54614,7 +54610,7 @@
       <c r="O464" s="140"/>
       <c r="P464" s="55"/>
       <c r="Q464" s="56"/>
-      <c r="R464" s="430" t="s">
+      <c r="R464" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S464" s="32" t="s">
@@ -54695,7 +54691,7 @@
       <c r="O465" s="54"/>
       <c r="P465" s="55"/>
       <c r="Q465" s="56"/>
-      <c r="R465" s="430" t="s">
+      <c r="R465" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S465" s="32" t="s">
@@ -54774,7 +54770,7 @@
       <c r="O466" s="54"/>
       <c r="P466" s="55"/>
       <c r="Q466" s="56"/>
-      <c r="R466" s="430" t="s">
+      <c r="R466" s="429" t="s">
         <v>1071</v>
       </c>
       <c r="S466" s="32" t="s">
@@ -54844,7 +54840,7 @@
       <c r="L467" s="22" t="s">
         <v>2164</v>
       </c>
-      <c r="M467" s="400" t="s">
+      <c r="M467" s="399" t="s">
         <v>1360</v>
       </c>
       <c r="N467" s="137" t="s">
@@ -54929,7 +54925,7 @@
       <c r="N468" s="54" t="s">
         <v>3603</v>
       </c>
-      <c r="O468" s="408"/>
+      <c r="O468" s="407"/>
       <c r="P468" s="118"/>
       <c r="Q468" s="56"/>
       <c r="R468" s="160" t="s">
@@ -54984,7 +54980,7 @@
       <c r="F469" s="313" t="s">
         <v>3605</v>
       </c>
-      <c r="G469" s="352"/>
+      <c r="G469" s="351"/>
       <c r="H469" s="201" t="s">
         <v>3606</v>
       </c>
@@ -55057,7 +55053,7 @@
       <c r="F470" s="21" t="s">
         <v>1108</v>
       </c>
-      <c r="G470" s="349" t="s">
+      <c r="G470" s="348" t="s">
         <v>1272</v>
       </c>
       <c r="H470" s="114" t="s">
@@ -55136,7 +55132,7 @@
       <c r="F471" s="21" t="s">
         <v>1108</v>
       </c>
-      <c r="G471" s="381" t="s">
+      <c r="G471" s="380" t="s">
         <v>1281</v>
       </c>
       <c r="H471" s="125" t="s">
@@ -55201,7 +55197,7 @@
       <c r="AQ471" s="32"/>
     </row>
     <row r="472" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A472" s="349" t="s">
+      <c r="A472" s="348" t="s">
         <v>1377</v>
       </c>
       <c r="B472" s="51" t="s">
@@ -55212,16 +55208,16 @@
       </c>
       <c r="D472" s="265"/>
       <c r="E472" s="18"/>
-      <c r="F472" s="377" t="s">
+      <c r="F472" s="376" t="s">
         <v>1378</v>
       </c>
-      <c r="G472" s="380" t="s">
+      <c r="G472" s="379" t="s">
         <v>1379</v>
       </c>
-      <c r="H472" s="384" t="s">
+      <c r="H472" s="383" t="s">
         <v>1380</v>
       </c>
-      <c r="I472" s="387" t="s">
+      <c r="I472" s="386" t="s">
         <v>1381</v>
       </c>
       <c r="J472" s="83" t="s">
@@ -55229,26 +55225,26 @@
       </c>
       <c r="K472" s="101"/>
       <c r="L472" s="101"/>
-      <c r="M472" s="387" t="s">
+      <c r="M472" s="386" t="s">
         <v>1360</v>
       </c>
       <c r="N472" s="141" t="s">
         <v>1382</v>
       </c>
-      <c r="O472" s="414"/>
+      <c r="O472" s="413"/>
       <c r="P472" s="118"/>
       <c r="Q472" s="127"/>
       <c r="R472" s="160" t="s">
         <v>1277</v>
       </c>
-      <c r="S472" s="381" t="s">
+      <c r="S472" s="380" t="s">
         <v>41</v>
       </c>
       <c r="T472" s="108"/>
       <c r="U472" s="109" t="s">
         <v>1072</v>
       </c>
-      <c r="V472" s="449" t="s">
+      <c r="V472" s="448" t="s">
         <v>1383</v>
       </c>
       <c r="W472" s="73"/>
@@ -55258,13 +55254,13 @@
       </c>
       <c r="Z472" s="106"/>
       <c r="AA472" s="106"/>
-      <c r="AB472" s="463" t="s">
+      <c r="AB472" s="462" t="s">
         <v>1075</v>
       </c>
-      <c r="AC472" s="381" t="s">
+      <c r="AC472" s="380" t="s">
         <v>1230</v>
       </c>
-      <c r="AD472" s="381"/>
+      <c r="AD472" s="380"/>
       <c r="AE472" s="39"/>
       <c r="AF472" s="39"/>
       <c r="AG472" s="39"/>
@@ -55294,7 +55290,7 @@
       <c r="F473" s="20" t="s">
         <v>1108</v>
       </c>
-      <c r="G473" s="380" t="s">
+      <c r="G473" s="379" t="s">
         <v>1606</v>
       </c>
       <c r="H473" s="114" t="s">
@@ -55318,7 +55314,7 @@
       <c r="R473" s="160" t="s">
         <v>1277</v>
       </c>
-      <c r="S473" s="381" t="s">
+      <c r="S473" s="380" t="s">
         <v>41</v>
       </c>
       <c r="T473" s="108"/>
@@ -55377,7 +55373,7 @@
       </c>
       <c r="K474" s="35"/>
       <c r="L474" s="35"/>
-      <c r="M474" s="399" t="s">
+      <c r="M474" s="398" t="s">
         <v>1360</v>
       </c>
       <c r="N474" s="54" t="s">
@@ -55389,7 +55385,7 @@
       <c r="R474" s="160" t="s">
         <v>1277</v>
       </c>
-      <c r="S474" s="381" t="s">
+      <c r="S474" s="380" t="s">
         <v>41</v>
       </c>
       <c r="T474" s="108"/>
@@ -55456,7 +55452,7 @@
       </c>
       <c r="K475" s="35"/>
       <c r="L475" s="35"/>
-      <c r="M475" s="400" t="s">
+      <c r="M475" s="399" t="s">
         <v>1360</v>
       </c>
       <c r="N475" s="74" t="s">
@@ -55475,7 +55471,7 @@
       <c r="U475" s="28" t="s">
         <v>1072</v>
       </c>
-      <c r="V475" s="447" t="s">
+      <c r="V475" s="446" t="s">
         <v>1689</v>
       </c>
       <c r="W475" s="29"/>
@@ -55597,7 +55593,7 @@
       </c>
       <c r="D477" s="256"/>
       <c r="E477" s="58"/>
-      <c r="F477" s="352" t="s">
+      <c r="F477" s="351" t="s">
         <v>1108</v>
       </c>
       <c r="G477" s="32" t="s">

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F410E910-163C-3A48-A127-E6D45719798F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0C7C3D-58DD-AC4D-9620-4BDDCF9DA11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21360" yWindow="-28300" windowWidth="60360" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11060" yWindow="-26520" windowWidth="60360" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7030" uniqueCount="4012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7031" uniqueCount="4013">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17467,6 +17467,9 @@
   </si>
   <si>
     <t>[Médaille avec légende versifiée : portrait du chancelier Louis Boucherat gravé à la demande des Grands Officiers de la Chancellerie de France]*</t>
+  </si>
+  <si>
+    <t>Lucas, conseiller au parlement de Toulouse</t>
   </si>
 </sst>
 </file>
@@ -18674,7 +18677,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="473">
+  <cellXfs count="474">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -20008,6 +20011,9 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -43025,8 +43031,8 @@
         <v>1569</v>
       </c>
       <c r="O303" s="38"/>
-      <c r="P303" s="25"/>
-      <c r="Q303" s="26"/>
+      <c r="P303" s="55"/>
+      <c r="Q303" s="473"/>
       <c r="R303" s="33" t="s">
         <v>1563</v>
       </c>
@@ -46556,7 +46562,7 @@
       </c>
       <c r="D352" s="241"/>
       <c r="E352" s="58"/>
-      <c r="F352" s="16" t="s">
+      <c r="F352" s="295" t="s">
         <v>2213</v>
       </c>
       <c r="G352" s="32"/>
@@ -53513,7 +53519,9 @@
         <v>3488</v>
       </c>
       <c r="O447" s="38"/>
-      <c r="P447" s="25"/>
+      <c r="P447" s="324" t="s">
+        <v>4012</v>
+      </c>
       <c r="Q447" s="26"/>
       <c r="R447" s="119" t="s">
         <v>389</v>
@@ -64879,8 +64887,8 @@
       <c r="AQ679" s="101"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD679">
-    <sortCondition ref="Q1:Q679"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD680">
+    <sortCondition ref="Q1:Q680"/>
   </sortState>
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D2105E-81A0-CD44-BC79-D8186B0503BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D37C0C-3D8B-074F-9BD7-417C3C030CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1660" yWindow="-20020" windowWidth="32500" windowHeight="20020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="860" yWindow="500" windowWidth="32500" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -630,7 +630,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7042" uniqueCount="4017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7043" uniqueCount="4018">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17471,20 +17471,23 @@
     <t>https://gallica.bnf.fr/ark:/12148/bpt6k6372917v/f113.item#</t>
   </si>
   <si>
-    <t xml:space="preserve">médaille ; </t>
-  </si>
-  <si>
-    <t>Sur l'estampe : "J. Dolivar delineavit et fecit"</t>
-  </si>
-  <si>
     <t>[Planche de huit médailles frappées pour l'entrée triomphale de Guillaume III d'Orange en 1691]*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIO. FEL. INCL. GUILIELMO III. M. BRIT. R. TRIOMPHA PATRIA PATRI. GUB. P. C. L. P. RST. BELG. FOED. LIB. ANGL. SERV. SCOT. PAC. HIB. REDUCI. </t>
+  </si>
+  <si>
+    <t>Sur l'estampe : "J. Dolivar delineavit et fecit". La 1re est dessinée par Jan Smeltzing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">médaille ; arc de triomphe ; navire ; mer ; soleil ; </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="135">
+  <fonts count="136">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -18442,6 +18445,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -18697,7 +18706,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="454">
+  <cellXfs count="455">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -19992,6 +20001,7 @@
     <xf numFmtId="0" fontId="134" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -48502,7 +48512,7 @@
       </c>
       <c r="G381" s="32"/>
       <c r="H381" s="216" t="s">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="I381" s="202" t="s">
         <v>2525</v>
@@ -48514,7 +48524,7 @@
         <v>3161</v>
       </c>
       <c r="N381" s="318" t="s">
-        <v>4014</v>
+        <v>4017</v>
       </c>
       <c r="O381" s="318"/>
       <c r="P381" s="415"/>
@@ -48533,9 +48543,11 @@
         <v>2249</v>
       </c>
       <c r="Y381" s="453" t="s">
+        <v>4016</v>
+      </c>
+      <c r="Z381" s="454" t="s">
         <v>4015</v>
       </c>
-      <c r="Z381" s="105"/>
       <c r="AA381" s="30"/>
       <c r="AB381" s="112"/>
       <c r="AC381" s="32"/>
@@ -64933,7 +64945,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{9BA19808-EFBD-1F46-9981-4C2405C12C73}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{340DCA94-4E25-EE46-9025-1D5AC845FA43}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D37C0C-3D8B-074F-9BD7-417C3C030CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00CF39D-224C-D54A-92DE-BC2F514E815A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="500" windowWidth="32500" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="-21100" windowWidth="34000" windowHeight="19280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -630,7 +630,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7043" uniqueCount="4018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7043" uniqueCount="4019">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17471,9 +17471,6 @@
     <t>https://gallica.bnf.fr/ark:/12148/bpt6k6372917v/f113.item#</t>
   </si>
   <si>
-    <t>[Planche de huit médailles frappées pour l'entrée triomphale de Guillaume III d'Orange en 1691]*</t>
-  </si>
-  <si>
     <t xml:space="preserve">PIO. FEL. INCL. GUILIELMO III. M. BRIT. R. TRIOMPHA PATRIA PATRI. GUB. P. C. L. P. RST. BELG. FOED. LIB. ANGL. SERV. SCOT. PAC. HIB. REDUCI. </t>
   </si>
   <si>
@@ -17481,13 +17478,19 @@
   </si>
   <si>
     <t xml:space="preserve">médaille ; arc de triomphe ; navire ; mer ; soleil ; </t>
+  </si>
+  <si>
+    <t>article transcrit fichier xml</t>
+  </si>
+  <si>
+    <t>[Planche de quatre médailles (avers et revers) frappées pour le retour triomphal de Guillaume III d'Orange en 1691]*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="136">
+  <fonts count="142">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -18440,16 +18443,57 @@
       <family val="4"/>
     </font>
     <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial (Corps)"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Garamond"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFF0000"/>
       <name val="Times"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -18706,7 +18750,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="455">
+  <cellXfs count="474">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -19992,16 +20036,71 @@
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="99" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="134" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="133" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="133" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="24" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -46482,7 +46581,7 @@
         <v>436</v>
       </c>
       <c r="C355" s="261" t="s">
-        <v>171</v>
+        <v>4017</v>
       </c>
       <c r="D355" s="246"/>
       <c r="E355" s="58"/>
@@ -48085,7 +48184,7 @@
       <c r="X375" s="29" t="s">
         <v>2249</v>
       </c>
-      <c r="Y375" s="452" t="s">
+      <c r="Y375" s="451" t="s">
         <v>3107</v>
       </c>
       <c r="Z375" s="217"/>
@@ -48497,74 +48596,74 @@
       <c r="AP380" s="32"/>
       <c r="AQ380" s="32"/>
     </row>
-    <row r="381" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A381" s="293" t="s">
+    <row r="381" spans="1:43" s="473" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A381" s="455" t="s">
         <v>4012</v>
       </c>
-      <c r="B381" s="33" t="s">
+      <c r="B381" s="425" t="s">
         <v>436</v>
       </c>
-      <c r="C381" s="260"/>
-      <c r="D381" s="246"/>
-      <c r="E381" s="58"/>
-      <c r="F381" s="451" t="s">
+      <c r="C381" s="456"/>
+      <c r="D381" s="457"/>
+      <c r="E381" s="458"/>
+      <c r="F381" s="459" t="s">
         <v>4013</v>
       </c>
-      <c r="G381" s="32"/>
-      <c r="H381" s="216" t="s">
+      <c r="G381" s="460"/>
+      <c r="H381" s="461" t="s">
+        <v>4018</v>
+      </c>
+      <c r="I381" s="461" t="s">
+        <v>2525</v>
+      </c>
+      <c r="J381" s="462"/>
+      <c r="K381" s="462"/>
+      <c r="L381" s="462"/>
+      <c r="M381" s="463" t="s">
+        <v>3161</v>
+      </c>
+      <c r="N381" s="452" t="s">
+        <v>4016</v>
+      </c>
+      <c r="O381" s="452"/>
+      <c r="P381" s="453"/>
+      <c r="Q381" s="454"/>
+      <c r="R381" s="464"/>
+      <c r="S381" s="465" t="s">
+        <v>41</v>
+      </c>
+      <c r="T381" s="466"/>
+      <c r="U381" s="467"/>
+      <c r="V381" s="467"/>
+      <c r="W381" s="468" t="s">
+        <v>2248</v>
+      </c>
+      <c r="X381" s="468" t="s">
+        <v>2249</v>
+      </c>
+      <c r="Y381" s="469" t="s">
+        <v>4015</v>
+      </c>
+      <c r="Z381" s="470" t="s">
         <v>4014</v>
       </c>
-      <c r="I381" s="202" t="s">
-        <v>2525</v>
-      </c>
-      <c r="J381" s="82"/>
-      <c r="K381" s="82"/>
-      <c r="L381" s="82"/>
-      <c r="M381" s="141" t="s">
-        <v>3161</v>
-      </c>
-      <c r="N381" s="318" t="s">
-        <v>4017</v>
-      </c>
-      <c r="O381" s="318"/>
-      <c r="P381" s="415"/>
-      <c r="Q381" s="409"/>
-      <c r="R381" s="39"/>
-      <c r="S381" s="77" t="s">
-        <v>41</v>
-      </c>
-      <c r="T381" s="21"/>
-      <c r="U381" s="28"/>
-      <c r="V381" s="28"/>
-      <c r="W381" s="29" t="s">
-        <v>2248</v>
-      </c>
-      <c r="X381" s="29" t="s">
-        <v>2249</v>
-      </c>
-      <c r="Y381" s="453" t="s">
-        <v>4016</v>
-      </c>
-      <c r="Z381" s="454" t="s">
-        <v>4015</v>
-      </c>
-      <c r="AA381" s="30"/>
-      <c r="AB381" s="112"/>
-      <c r="AC381" s="32"/>
-      <c r="AD381" s="21"/>
-      <c r="AE381" s="32"/>
-      <c r="AF381" s="32"/>
-      <c r="AG381" s="32"/>
-      <c r="AH381" s="32"/>
-      <c r="AI381" s="32"/>
-      <c r="AJ381" s="32"/>
-      <c r="AK381" s="32"/>
-      <c r="AL381" s="32"/>
-      <c r="AM381" s="32"/>
-      <c r="AN381" s="32"/>
-      <c r="AO381" s="32"/>
-      <c r="AP381" s="32"/>
-      <c r="AQ381" s="32"/>
+      <c r="AA381" s="471"/>
+      <c r="AB381" s="472"/>
+      <c r="AC381" s="460"/>
+      <c r="AD381" s="466"/>
+      <c r="AE381" s="460"/>
+      <c r="AF381" s="460"/>
+      <c r="AG381" s="460"/>
+      <c r="AH381" s="460"/>
+      <c r="AI381" s="460"/>
+      <c r="AJ381" s="460"/>
+      <c r="AK381" s="460"/>
+      <c r="AL381" s="460"/>
+      <c r="AM381" s="460"/>
+      <c r="AN381" s="460"/>
+      <c r="AO381" s="460"/>
+      <c r="AP381" s="460"/>
+      <c r="AQ381" s="460"/>
     </row>
     <row r="382" spans="1:43" ht="15.75" customHeight="1">
       <c r="A382" s="196" t="s">
@@ -64945,7 +65044,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{340DCA94-4E25-EE46-9025-1D5AC845FA43}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{966FAEB1-26B4-B44A-A5EB-AC4D8C544E19}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C4CD51-D3B9-B74F-94BA-7DD0A2B2D3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9282B354-219D-1348-93EB-8AB698FE8357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-2020" yWindow="-20320" windowWidth="35000" windowHeight="20320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15235,9 +15235,6 @@
     <t>https://gallica.bnf.fr/ark:/12148/bpt6k6299675r/f191.item</t>
   </si>
   <si>
-    <t>[Médaille sur la vie du roi frappée après la conquête de la Franche-Comté, représentant la Fortune entourée des armes francomtoises]*</t>
-  </si>
-  <si>
     <t>emblématique ; personnification ; mythologie gréco-romaine ; vie militaire</t>
   </si>
   <si>
@@ -17449,6 +17446,9 @@
   </si>
   <si>
     <t>Ménestrier 1689 f. 33</t>
+  </si>
+  <si>
+    <t>[Médaille sur la vie du roi frappée après la conquête de la Franche-Comté, représentant la Fortune entourée des armes franc-comtoises]*</t>
   </si>
 </sst>
 </file>
@@ -20570,7 +20570,7 @@
     </row>
     <row r="2" spans="1:43" ht="15.75" customHeight="1">
       <c r="A2" s="277" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="B2" s="131" t="s">
         <v>497</v>
@@ -20643,7 +20643,7 @@
     </row>
     <row r="3" spans="1:43" ht="54" customHeight="1">
       <c r="A3" s="186" t="s">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="B3" s="95" t="s">
         <v>434</v>
@@ -20654,13 +20654,13 @@
       <c r="D3" s="235"/>
       <c r="E3" s="58"/>
       <c r="F3" s="47" t="s">
+        <v>3722</v>
+      </c>
+      <c r="G3" s="32" t="s">
         <v>3723</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="H3" s="95" t="s">
         <v>3724</v>
-      </c>
-      <c r="H3" s="95" t="s">
-        <v>3725</v>
       </c>
       <c r="I3" s="187" t="s">
         <v>2654</v>
@@ -20668,13 +20668,13 @@
       <c r="J3" s="22"/>
       <c r="K3" s="22"/>
       <c r="L3" s="22" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
       <c r="M3" s="137" t="s">
         <v>804</v>
       </c>
       <c r="N3" s="65" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
       <c r="O3" s="38"/>
       <c r="P3" s="25"/>
@@ -20689,13 +20689,13 @@
       <c r="U3" s="28"/>
       <c r="V3" s="28"/>
       <c r="W3" s="29" t="s">
+        <v>3727</v>
+      </c>
+      <c r="X3" s="29" t="s">
         <v>3728</v>
       </c>
-      <c r="X3" s="29" t="s">
+      <c r="Y3" s="30" t="s">
         <v>3729</v>
-      </c>
-      <c r="Y3" s="30" t="s">
-        <v>3730</v>
       </c>
       <c r="Z3" s="30"/>
       <c r="AA3" s="30"/>
@@ -20718,13 +20718,13 @@
     </row>
     <row r="4" spans="1:43" ht="15.75" customHeight="1">
       <c r="A4" s="277" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="250" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="D4" s="235"/>
       <c r="E4" s="58"/>
@@ -20797,7 +20797,7 @@
     </row>
     <row r="5" spans="1:43" ht="15.75" customHeight="1">
       <c r="A5" s="274" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>43</v>
@@ -20806,7 +20806,7 @@
         <v>359</v>
       </c>
       <c r="D5" s="235" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="E5" s="58"/>
       <c r="F5" s="32" t="s">
@@ -20876,13 +20876,13 @@
     </row>
     <row r="6" spans="1:43" ht="15.75" customHeight="1">
       <c r="A6" s="277" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="250" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="D6" s="235"/>
       <c r="E6" s="58"/>
@@ -20953,7 +20953,7 @@
     </row>
     <row r="7" spans="1:43" ht="15.75" customHeight="1">
       <c r="A7" s="275" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>100</v>
@@ -21030,28 +21030,28 @@
     </row>
     <row r="8" spans="1:43" ht="15.75" customHeight="1">
       <c r="A8" s="187" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="B8" s="95" t="s">
         <v>2294</v>
       </c>
       <c r="C8" s="402" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="D8" s="235"/>
       <c r="E8" s="58"/>
       <c r="F8" s="290" t="s">
-        <v>3706</v>
+        <v>3705</v>
       </c>
       <c r="G8" s="32"/>
       <c r="H8" s="48" t="s">
+        <v>3706</v>
+      </c>
+      <c r="I8" s="187" t="s">
         <v>3707</v>
       </c>
-      <c r="I8" s="187" t="s">
+      <c r="J8" s="109" t="s">
         <v>3708</v>
-      </c>
-      <c r="J8" s="109" t="s">
-        <v>3709</v>
       </c>
       <c r="K8" s="109"/>
       <c r="L8" s="109"/>
@@ -21059,13 +21059,13 @@
         <v>137</v>
       </c>
       <c r="N8" s="38" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="O8" s="322"/>
       <c r="P8" s="126"/>
       <c r="Q8" s="56"/>
       <c r="R8" s="488" t="s">
-        <v>3711</v>
+        <v>3710</v>
       </c>
       <c r="S8" s="77" t="s">
         <v>41</v>
@@ -21074,19 +21074,19 @@
       <c r="U8" s="28"/>
       <c r="V8" s="28"/>
       <c r="W8" s="112" t="s">
+        <v>3711</v>
+      </c>
+      <c r="X8" s="29" t="s">
         <v>3712</v>
       </c>
-      <c r="X8" s="29" t="s">
+      <c r="Y8" s="30" t="s">
         <v>3713</v>
-      </c>
-      <c r="Y8" s="30" t="s">
-        <v>3714</v>
       </c>
       <c r="Z8" s="30"/>
       <c r="AA8" s="30"/>
       <c r="AB8" s="31"/>
       <c r="AC8" s="69" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="AD8" s="21"/>
       <c r="AE8" s="32"/>
@@ -21192,7 +21192,7 @@
     </row>
     <row r="10" spans="1:43" ht="15.75" customHeight="1">
       <c r="A10" s="277" t="s">
-        <v>3912</v>
+        <v>3911</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>43</v>
@@ -21664,7 +21664,7 @@
     </row>
     <row r="16" spans="1:43" ht="15.75" customHeight="1">
       <c r="A16" s="282" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="B16" s="33" t="s">
         <v>434</v>
@@ -21976,13 +21976,13 @@
     </row>
     <row r="20" spans="1:43" ht="15.75" customHeight="1">
       <c r="A20" s="285" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>2613</v>
       </c>
       <c r="C20" s="263" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="D20" s="414"/>
       <c r="E20" s="58" t="s">
@@ -22136,7 +22136,7 @@
     </row>
     <row r="22" spans="1:43" ht="15.75" customHeight="1">
       <c r="A22" s="282" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="B22" s="33" t="s">
         <v>434</v>
@@ -22490,7 +22490,7 @@
         <v>2246</v>
       </c>
       <c r="Y26" s="30" t="s">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="Z26" s="30"/>
       <c r="AA26" s="30" t="s">
@@ -22602,7 +22602,7 @@
         <v>434</v>
       </c>
       <c r="C28" s="251" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="D28" s="247"/>
       <c r="E28" s="190"/>
@@ -23299,7 +23299,7 @@
     </row>
     <row r="37" spans="1:43" ht="15.75" customHeight="1">
       <c r="A37" s="282" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="B37" s="33" t="s">
         <v>434</v>
@@ -23528,7 +23528,7 @@
     </row>
     <row r="40" spans="1:43" ht="15.75" customHeight="1">
       <c r="A40" s="282" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="B40" s="33" t="s">
         <v>434</v>
@@ -24233,7 +24233,7 @@
         <v>434</v>
       </c>
       <c r="C49" s="250" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D49" s="235"/>
       <c r="E49" s="58"/>
@@ -24776,7 +24776,7 @@
     </row>
     <row r="56" spans="1:43" ht="15.75" customHeight="1">
       <c r="A56" s="282" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="B56" s="33" t="s">
         <v>434</v>
@@ -25801,7 +25801,7 @@
     </row>
     <row r="69" spans="1:43" ht="15.75" customHeight="1">
       <c r="A69" s="373" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="B69" s="366" t="s">
         <v>434</v>
@@ -25810,11 +25810,11 @@
       <c r="D69" s="375"/>
       <c r="E69" s="376"/>
       <c r="F69" s="426" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="G69" s="377"/>
       <c r="H69" s="378" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="I69" s="378" t="s">
         <v>2522</v>
@@ -25826,7 +25826,7 @@
         <v>3157</v>
       </c>
       <c r="N69" s="370" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="O69" s="370"/>
       <c r="P69" s="371"/>
@@ -25845,10 +25845,10 @@
         <v>2246</v>
       </c>
       <c r="Y69" s="385" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="Z69" s="518" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="AA69" s="386"/>
       <c r="AB69" s="526"/>
@@ -26101,7 +26101,7 @@
     </row>
     <row r="73" spans="1:43" ht="15.75" customHeight="1">
       <c r="A73" s="278" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="B73" s="66" t="s">
         <v>2248</v>
@@ -26253,7 +26253,7 @@
     </row>
     <row r="75" spans="1:43" ht="15.75" customHeight="1">
       <c r="A75" s="282" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="B75" s="33" t="s">
         <v>434</v>
@@ -26721,7 +26721,7 @@
     </row>
     <row r="81" spans="1:43" ht="15.75" customHeight="1">
       <c r="A81" s="282" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="B81" s="33" t="s">
         <v>434</v>
@@ -26836,7 +26836,7 @@
         <v>38</v>
       </c>
       <c r="Q82" s="319" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="R82" s="324" t="s">
         <v>80</v>
@@ -26954,7 +26954,7 @@
     </row>
     <row r="84" spans="1:43" ht="15.75" customHeight="1">
       <c r="A84" s="293" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="B84" s="33" t="s">
         <v>434</v>
@@ -27197,7 +27197,7 @@
     </row>
     <row r="87" spans="1:43" ht="15.75" customHeight="1">
       <c r="A87" s="282" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="B87" s="14" t="s">
         <v>434</v>
@@ -27355,13 +27355,13 @@
     </row>
     <row r="89" spans="1:43" ht="15.75" customHeight="1">
       <c r="A89" s="282" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="B89" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C89" s="251" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="D89" s="247"/>
       <c r="E89" s="190"/>
@@ -27728,7 +27728,7 @@
     </row>
     <row r="94" spans="1:43" ht="15.75" customHeight="1">
       <c r="A94" s="287" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="B94" s="33" t="s">
         <v>434</v>
@@ -27803,13 +27803,13 @@
     </row>
     <row r="95" spans="1:43" ht="15.75" customHeight="1">
       <c r="A95" s="296" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="B95" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C95" s="250" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="D95" s="235"/>
       <c r="E95" s="58"/>
@@ -27963,7 +27963,7 @@
         <v>434</v>
       </c>
       <c r="C97" s="403" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="D97" s="247"/>
       <c r="E97" s="58"/>
@@ -27972,7 +27972,7 @@
       </c>
       <c r="G97" s="186"/>
       <c r="H97" s="206" t="s">
-        <v>3417</v>
+        <v>4019</v>
       </c>
       <c r="I97" s="32" t="s">
         <v>2522</v>
@@ -27983,10 +27983,10 @@
         <v>2768</v>
       </c>
       <c r="M97" s="137" t="s">
+        <v>3417</v>
+      </c>
+      <c r="N97" s="38" t="s">
         <v>3418</v>
-      </c>
-      <c r="N97" s="38" t="s">
-        <v>3419</v>
       </c>
       <c r="O97" s="38"/>
       <c r="P97" s="25"/>
@@ -28007,17 +28007,17 @@
         <v>3179</v>
       </c>
       <c r="Y97" s="30" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="Z97" s="200"/>
       <c r="AA97" s="30" t="s">
+        <v>3420</v>
+      </c>
+      <c r="AB97" s="46" t="s">
         <v>3421</v>
       </c>
-      <c r="AB97" s="46" t="s">
+      <c r="AC97" s="66" t="s">
         <v>3422</v>
-      </c>
-      <c r="AC97" s="66" t="s">
-        <v>3423</v>
       </c>
       <c r="AD97" s="32"/>
       <c r="AE97" s="32"/>
@@ -28036,7 +28036,7 @@
     </row>
     <row r="98" spans="1:43" ht="15.75" customHeight="1">
       <c r="A98" s="186" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="B98" s="33" t="s">
         <v>434</v>
@@ -28047,17 +28047,17 @@
       <c r="D98" s="247"/>
       <c r="E98" s="190"/>
       <c r="F98" s="191" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="G98" s="186"/>
       <c r="H98" s="206" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="I98" s="192" t="s">
         <v>2522</v>
       </c>
       <c r="J98" s="22" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="K98" s="22"/>
       <c r="L98" s="22"/>
@@ -28065,14 +28065,14 @@
         <v>657</v>
       </c>
       <c r="N98" s="38" t="s">
+        <v>3427</v>
+      </c>
+      <c r="O98" s="38" t="s">
         <v>3428</v>
-      </c>
-      <c r="O98" s="38" t="s">
-        <v>3429</v>
       </c>
       <c r="P98" s="25"/>
       <c r="Q98" s="26" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="R98" s="39" t="s">
         <v>523</v>
@@ -28090,16 +28090,16 @@
         <v>3179</v>
       </c>
       <c r="Y98" s="30" t="s">
+        <v>3430</v>
+      </c>
+      <c r="Z98" s="30" t="s">
         <v>3431</v>
       </c>
-      <c r="Z98" s="30" t="s">
+      <c r="AA98" s="30" t="s">
         <v>3432</v>
       </c>
-      <c r="AA98" s="30" t="s">
+      <c r="AB98" s="46" t="s">
         <v>3433</v>
-      </c>
-      <c r="AB98" s="46" t="s">
-        <v>3434</v>
       </c>
       <c r="AC98" s="32"/>
       <c r="AD98" s="32"/>
@@ -28119,7 +28119,7 @@
     </row>
     <row r="99" spans="1:43" ht="15.75" customHeight="1">
       <c r="A99" s="186" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B99" s="33" t="s">
         <v>434</v>
@@ -28130,11 +28130,11 @@
       <c r="D99" s="247"/>
       <c r="E99" s="190"/>
       <c r="F99" s="191" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="G99" s="186"/>
       <c r="H99" s="206" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="I99" s="192" t="s">
         <v>2522</v>
@@ -28148,14 +28148,14 @@
         <v>657</v>
       </c>
       <c r="N99" s="38" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="O99" s="38"/>
       <c r="P99" s="25" t="s">
+        <v>3437</v>
+      </c>
+      <c r="Q99" s="56" t="s">
         <v>3438</v>
-      </c>
-      <c r="Q99" s="56" t="s">
-        <v>3439</v>
       </c>
       <c r="R99" s="481" t="s">
         <v>544</v>
@@ -28164,7 +28164,7 @@
         <v>41</v>
       </c>
       <c r="T99" s="21" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="U99" s="28"/>
       <c r="V99" s="28"/>
@@ -28175,14 +28175,14 @@
         <v>3179</v>
       </c>
       <c r="Y99" s="30" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="Z99" s="30"/>
       <c r="AA99" s="30" t="s">
+        <v>4017</v>
+      </c>
+      <c r="AB99" s="41" t="s">
         <v>4018</v>
-      </c>
-      <c r="AB99" s="41" t="s">
-        <v>4019</v>
       </c>
       <c r="AC99" s="32"/>
       <c r="AD99" s="32"/>
@@ -28202,7 +28202,7 @@
     </row>
     <row r="100" spans="1:43" ht="15.75" customHeight="1">
       <c r="A100" s="186" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>434</v>
@@ -28213,14 +28213,14 @@
       <c r="D100" s="235"/>
       <c r="E100" s="58"/>
       <c r="F100" s="290" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="G100" s="32"/>
       <c r="H100" s="206" t="s">
+        <v>3442</v>
+      </c>
+      <c r="I100" s="187" t="s">
         <v>3443</v>
-      </c>
-      <c r="I100" s="187" t="s">
-        <v>3444</v>
       </c>
       <c r="J100" s="22"/>
       <c r="K100" s="22"/>
@@ -28250,7 +28250,7 @@
         <v>3179</v>
       </c>
       <c r="Y100" s="30" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="Z100" s="30"/>
       <c r="AA100" s="30"/>
@@ -28273,22 +28273,22 @@
     </row>
     <row r="101" spans="1:43" ht="15.75" customHeight="1">
       <c r="A101" s="287" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="B101" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C101" s="256" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="D101" s="235"/>
       <c r="E101" s="58"/>
       <c r="F101" s="16" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="G101" s="32"/>
       <c r="H101" s="206" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="I101" s="217" t="s">
         <v>582</v>
@@ -28296,20 +28296,20 @@
       <c r="J101" s="35"/>
       <c r="K101" s="22"/>
       <c r="L101" s="22" t="s">
+        <v>3448</v>
+      </c>
+      <c r="M101" s="111" t="s">
         <v>3449</v>
       </c>
-      <c r="M101" s="111" t="s">
+      <c r="N101" s="54" t="s">
         <v>3450</v>
-      </c>
-      <c r="N101" s="54" t="s">
-        <v>3451</v>
       </c>
       <c r="O101" s="54"/>
       <c r="P101" s="74" t="s">
+        <v>3451</v>
+      </c>
+      <c r="Q101" s="56" t="s">
         <v>3452</v>
-      </c>
-      <c r="Q101" s="56" t="s">
-        <v>3453</v>
       </c>
       <c r="R101" s="486" t="s">
         <v>40</v>
@@ -28350,7 +28350,7 @@
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
       <c r="A102" s="186" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="B102" s="14" t="s">
         <v>434</v>
@@ -28361,11 +28361,11 @@
       <c r="D102" s="235"/>
       <c r="E102" s="58"/>
       <c r="F102" s="290" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="G102" s="32"/>
       <c r="H102" s="48" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="I102" s="187" t="s">
         <v>2562</v>
@@ -28373,13 +28373,13 @@
       <c r="J102" s="22"/>
       <c r="K102" s="22"/>
       <c r="L102" s="22" t="s">
+        <v>3462</v>
+      </c>
+      <c r="M102" s="137" t="s">
         <v>3463</v>
       </c>
-      <c r="M102" s="137" t="s">
+      <c r="N102" s="54" t="s">
         <v>3464</v>
-      </c>
-      <c r="N102" s="54" t="s">
-        <v>3465</v>
       </c>
       <c r="O102" s="54"/>
       <c r="P102" s="55"/>
@@ -28423,7 +28423,7 @@
     </row>
     <row r="103" spans="1:43" ht="15.75" customHeight="1">
       <c r="A103" s="186" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="B103" s="33" t="s">
         <v>434</v>
@@ -28434,11 +28434,11 @@
       <c r="D103" s="235"/>
       <c r="E103" s="58"/>
       <c r="F103" s="290" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="G103" s="32"/>
       <c r="H103" s="206" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="I103" s="192" t="s">
         <v>2562</v>
@@ -28496,7 +28496,7 @@
     </row>
     <row r="104" spans="1:43" ht="15.75" customHeight="1">
       <c r="A104" s="186" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="B104" s="33" t="s">
         <v>434</v>
@@ -28507,11 +28507,11 @@
       <c r="D104" s="235"/>
       <c r="E104" s="58"/>
       <c r="F104" s="47" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="G104" s="32"/>
       <c r="H104" s="206" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="I104" s="192" t="s">
         <v>2522</v>
@@ -28526,11 +28526,11 @@
         <v>1242</v>
       </c>
       <c r="O104" s="54" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="P104" s="55"/>
       <c r="Q104" s="56" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="R104" s="398" t="s">
         <v>523</v>
@@ -28548,10 +28548,10 @@
         <v>3179</v>
       </c>
       <c r="Y104" s="30" t="s">
+        <v>3484</v>
+      </c>
+      <c r="Z104" s="30" t="s">
         <v>3485</v>
-      </c>
-      <c r="Z104" s="30" t="s">
-        <v>3486</v>
       </c>
       <c r="AA104" s="30"/>
       <c r="AB104" s="41"/>
@@ -28573,7 +28573,7 @@
     </row>
     <row r="105" spans="1:43" ht="15.75" customHeight="1">
       <c r="A105" s="186" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="B105" s="33" t="s">
         <v>434</v>
@@ -28584,11 +28584,11 @@
       <c r="D105" s="235"/>
       <c r="E105" s="58"/>
       <c r="F105" s="290" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="G105" s="32"/>
       <c r="H105" s="206" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="I105" s="192" t="s">
         <v>2562</v>
@@ -28600,7 +28600,7 @@
         <v>2746</v>
       </c>
       <c r="N105" s="136" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="O105" s="54"/>
       <c r="P105" s="55"/>
@@ -28621,7 +28621,7 @@
         <v>3179</v>
       </c>
       <c r="Y105" s="30" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Z105" s="30"/>
       <c r="AA105" s="30"/>
@@ -28644,24 +28644,24 @@
     </row>
     <row r="106" spans="1:43" ht="15.75" customHeight="1">
       <c r="A106" s="281" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="B106" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C106" s="251" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="D106" s="235"/>
       <c r="E106" s="58"/>
       <c r="F106" s="290" t="s">
+        <v>3498</v>
+      </c>
+      <c r="G106" s="32" t="s">
         <v>3499</v>
       </c>
-      <c r="G106" s="32" t="s">
+      <c r="H106" s="206" t="s">
         <v>3500</v>
-      </c>
-      <c r="H106" s="206" t="s">
-        <v>3501</v>
       </c>
       <c r="I106" s="192" t="s">
         <v>2562</v>
@@ -28669,13 +28669,13 @@
       <c r="J106" s="35"/>
       <c r="K106" s="22"/>
       <c r="L106" s="22" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="M106" s="209" t="s">
         <v>480</v>
       </c>
       <c r="N106" s="54" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="O106" s="54"/>
       <c r="P106" s="55"/>
@@ -28688,10 +28688,10 @@
       </c>
       <c r="T106" s="21"/>
       <c r="U106" s="28" t="s">
+        <v>3503</v>
+      </c>
+      <c r="V106" s="28" t="s">
         <v>3504</v>
-      </c>
-      <c r="V106" s="28" t="s">
-        <v>3505</v>
       </c>
       <c r="W106" s="29" t="s">
         <v>3178</v>
@@ -28700,7 +28700,7 @@
         <v>3179</v>
       </c>
       <c r="Y106" s="30" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="Z106" s="30"/>
       <c r="AA106" s="30"/>
@@ -28723,7 +28723,7 @@
     </row>
     <row r="107" spans="1:43" ht="15.75" customHeight="1">
       <c r="A107" s="282" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="B107" s="33" t="s">
         <v>434</v>
@@ -28734,17 +28734,17 @@
       <c r="D107" s="235"/>
       <c r="E107" s="58"/>
       <c r="F107" s="290" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="G107" s="32"/>
       <c r="H107" s="206" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="I107" s="192" t="s">
         <v>2562</v>
       </c>
       <c r="J107" s="109" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="K107" s="104"/>
       <c r="L107" s="104"/>
@@ -28752,7 +28752,7 @@
         <v>137</v>
       </c>
       <c r="N107" s="54" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="O107" s="54"/>
       <c r="P107" s="55"/>
@@ -28796,7 +28796,7 @@
     </row>
     <row r="108" spans="1:43" ht="15.75" customHeight="1">
       <c r="A108" s="186" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="B108" s="14" t="s">
         <v>434</v>
@@ -28807,11 +28807,11 @@
       <c r="D108" s="235"/>
       <c r="E108" s="58"/>
       <c r="F108" s="290" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="G108" s="32"/>
       <c r="H108" s="206" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="I108" s="32" t="s">
         <v>2562</v>
@@ -28871,22 +28871,22 @@
     </row>
     <row r="109" spans="1:43" ht="15.75" customHeight="1">
       <c r="A109" s="186" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="B109" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C109" s="295" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="D109" s="235"/>
       <c r="E109" s="58"/>
       <c r="F109" s="290" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="G109" s="32"/>
       <c r="H109" s="206" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="I109" s="192" t="s">
         <v>2522</v>
@@ -28895,17 +28895,17 @@
       <c r="K109" s="82"/>
       <c r="L109" s="22"/>
       <c r="M109" s="137" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="N109" s="136" t="s">
         <v>1242</v>
       </c>
       <c r="O109" s="471" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="P109" s="59"/>
       <c r="Q109" s="56" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="R109" s="398" t="s">
         <v>523</v>
@@ -28923,14 +28923,14 @@
         <v>3179</v>
       </c>
       <c r="Y109" s="30" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="Z109" s="200"/>
       <c r="AA109" s="30" t="s">
+        <v>3527</v>
+      </c>
+      <c r="AB109" s="31" t="s">
         <v>3528</v>
-      </c>
-      <c r="AB109" s="31" t="s">
-        <v>3529</v>
       </c>
       <c r="AC109" s="32"/>
       <c r="AD109" s="32"/>
@@ -28950,7 +28950,7 @@
     </row>
     <row r="110" spans="1:43" ht="15.75" customHeight="1">
       <c r="A110" s="296" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="B110" s="33" t="s">
         <v>434</v>
@@ -28961,13 +28961,13 @@
       <c r="D110" s="235"/>
       <c r="E110" s="58"/>
       <c r="F110" s="290" t="s">
+        <v>3539</v>
+      </c>
+      <c r="G110" s="429" t="s">
         <v>3540</v>
       </c>
-      <c r="G110" s="429" t="s">
+      <c r="H110" s="95" t="s">
         <v>3541</v>
-      </c>
-      <c r="H110" s="95" t="s">
-        <v>3542</v>
       </c>
       <c r="I110" s="187" t="s">
         <v>2503</v>
@@ -28979,7 +28979,7 @@
         <v>657</v>
       </c>
       <c r="N110" s="65" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="O110" s="38"/>
       <c r="P110" s="25"/>
@@ -29000,7 +29000,7 @@
         <v>3179</v>
       </c>
       <c r="Y110" s="30" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="Z110" s="30"/>
       <c r="AA110" s="30"/>
@@ -29023,7 +29023,7 @@
     </row>
     <row r="111" spans="1:43" ht="15.75" customHeight="1">
       <c r="A111" s="186" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="B111" s="33" t="s">
         <v>434</v>
@@ -29034,13 +29034,13 @@
       <c r="D111" s="247"/>
       <c r="E111" s="190"/>
       <c r="F111" s="191" t="s">
+        <v>3550</v>
+      </c>
+      <c r="G111" s="186" t="s">
         <v>3551</v>
       </c>
-      <c r="G111" s="186" t="s">
+      <c r="H111" s="48" t="s">
         <v>3552</v>
-      </c>
-      <c r="H111" s="48" t="s">
-        <v>3553</v>
       </c>
       <c r="I111" s="32" t="s">
         <v>2562</v>
@@ -29048,13 +29048,13 @@
       <c r="J111" s="35"/>
       <c r="K111" s="109"/>
       <c r="L111" s="109" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="M111" s="209" t="s">
         <v>480</v>
       </c>
       <c r="N111" s="38" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="O111" s="38"/>
       <c r="P111" s="25"/>
@@ -29067,10 +29067,10 @@
       </c>
       <c r="T111" s="21"/>
       <c r="U111" s="28" t="s">
+        <v>3503</v>
+      </c>
+      <c r="V111" s="28" t="s">
         <v>3504</v>
-      </c>
-      <c r="V111" s="28" t="s">
-        <v>3505</v>
       </c>
       <c r="W111" s="29" t="s">
         <v>3178</v>
@@ -29079,12 +29079,12 @@
         <v>3179</v>
       </c>
       <c r="Y111" s="30" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="Z111" s="30"/>
       <c r="AA111" s="30"/>
       <c r="AB111" s="31" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="AC111" s="32"/>
       <c r="AD111" s="21"/>
@@ -29104,7 +29104,7 @@
     </row>
     <row r="112" spans="1:43" ht="15.75" customHeight="1">
       <c r="A112" s="186" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="B112" s="33" t="s">
         <v>434</v>
@@ -29115,13 +29115,13 @@
       <c r="D112" s="247"/>
       <c r="E112" s="190"/>
       <c r="F112" s="191" t="s">
+        <v>3558</v>
+      </c>
+      <c r="G112" s="186" t="s">
         <v>3559</v>
       </c>
-      <c r="G112" s="186" t="s">
+      <c r="H112" s="48" t="s">
         <v>3560</v>
-      </c>
-      <c r="H112" s="48" t="s">
-        <v>3561</v>
       </c>
       <c r="I112" s="32" t="s">
         <v>2562</v>
@@ -29129,13 +29129,13 @@
       <c r="J112" s="35"/>
       <c r="K112" s="109"/>
       <c r="L112" s="109" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="M112" s="209" t="s">
         <v>480</v>
       </c>
       <c r="N112" s="54" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="O112" s="54"/>
       <c r="P112" s="55"/>
@@ -29148,10 +29148,10 @@
       </c>
       <c r="T112" s="21"/>
       <c r="U112" s="28" t="s">
+        <v>3503</v>
+      </c>
+      <c r="V112" s="122" t="s">
         <v>3504</v>
-      </c>
-      <c r="V112" s="122" t="s">
-        <v>3505</v>
       </c>
       <c r="W112" s="113" t="s">
         <v>3178</v>
@@ -29160,12 +29160,12 @@
         <v>3179</v>
       </c>
       <c r="Y112" s="30" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="Z112" s="30"/>
       <c r="AA112" s="30"/>
       <c r="AB112" s="41" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="AC112" s="32"/>
       <c r="AD112" s="21"/>
@@ -29185,7 +29185,7 @@
     </row>
     <row r="113" spans="1:43" ht="15.75" customHeight="1">
       <c r="A113" s="296" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="B113" s="33" t="s">
         <v>434</v>
@@ -29196,17 +29196,17 @@
       <c r="D113" s="235"/>
       <c r="E113" s="58"/>
       <c r="F113" s="47" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="G113" s="32"/>
       <c r="H113" s="206" t="s">
+        <v>3566</v>
+      </c>
+      <c r="I113" s="192" t="s">
         <v>3567</v>
       </c>
-      <c r="I113" s="192" t="s">
+      <c r="J113" s="22" t="s">
         <v>3568</v>
-      </c>
-      <c r="J113" s="22" t="s">
-        <v>3569</v>
       </c>
       <c r="K113" s="22"/>
       <c r="L113" s="22"/>
@@ -29235,7 +29235,7 @@
         <v>3179</v>
       </c>
       <c r="Y113" s="30" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="Z113" s="30"/>
       <c r="AA113" s="30"/>
@@ -29258,7 +29258,7 @@
     </row>
     <row r="114" spans="1:43" ht="15.75" customHeight="1">
       <c r="A114" s="186" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="B114" s="33" t="s">
         <v>434</v>
@@ -29269,11 +29269,11 @@
       <c r="D114" s="235"/>
       <c r="E114" s="58"/>
       <c r="F114" s="47" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="G114" s="32"/>
       <c r="H114" s="206" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="I114" s="192" t="s">
         <v>2562</v>
@@ -29281,13 +29281,13 @@
       <c r="J114" s="98"/>
       <c r="K114" s="104"/>
       <c r="L114" s="104" t="s">
+        <v>3577</v>
+      </c>
+      <c r="M114" s="137" t="s">
         <v>3578</v>
       </c>
-      <c r="M114" s="137" t="s">
+      <c r="N114" s="54" t="s">
         <v>3579</v>
-      </c>
-      <c r="N114" s="54" t="s">
-        <v>3580</v>
       </c>
       <c r="O114" s="54"/>
       <c r="P114" s="55"/>
@@ -29331,7 +29331,7 @@
     </row>
     <row r="115" spans="1:43" ht="15.75" customHeight="1">
       <c r="A115" s="186" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="B115" s="33" t="s">
         <v>434</v>
@@ -29342,11 +29342,11 @@
       <c r="D115" s="235"/>
       <c r="E115" s="58"/>
       <c r="F115" s="290" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="G115" s="32"/>
       <c r="H115" s="186" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="I115" s="192" t="s">
         <v>2562</v>
@@ -29354,13 +29354,13 @@
       <c r="J115" s="98"/>
       <c r="K115" s="104"/>
       <c r="L115" s="109" t="s">
+        <v>3577</v>
+      </c>
+      <c r="M115" s="137" t="s">
         <v>3578</v>
       </c>
-      <c r="M115" s="137" t="s">
-        <v>3579</v>
-      </c>
       <c r="N115" s="73" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="O115" s="73"/>
       <c r="P115" s="74"/>
@@ -29404,7 +29404,7 @@
     </row>
     <row r="116" spans="1:43" ht="15.75" customHeight="1">
       <c r="A116" s="186" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="B116" s="33" t="s">
         <v>434</v>
@@ -29415,13 +29415,13 @@
       <c r="D116" s="235"/>
       <c r="E116" s="58"/>
       <c r="F116" s="290" t="s">
+        <v>3585</v>
+      </c>
+      <c r="G116" s="32" t="s">
         <v>3586</v>
       </c>
-      <c r="G116" s="32" t="s">
+      <c r="H116" s="206" t="s">
         <v>3587</v>
-      </c>
-      <c r="H116" s="206" t="s">
-        <v>3588</v>
       </c>
       <c r="I116" s="192" t="s">
         <v>2562</v>
@@ -29429,13 +29429,13 @@
       <c r="J116" s="35"/>
       <c r="K116" s="109"/>
       <c r="L116" s="109" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="M116" s="77" t="s">
         <v>480</v>
       </c>
       <c r="N116" s="38" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="O116" s="38"/>
       <c r="P116" s="25"/>
@@ -29448,10 +29448,10 @@
       </c>
       <c r="T116" s="21"/>
       <c r="U116" s="28" t="s">
+        <v>3503</v>
+      </c>
+      <c r="V116" s="122" t="s">
         <v>3504</v>
-      </c>
-      <c r="V116" s="122" t="s">
-        <v>3505</v>
       </c>
       <c r="W116" s="113" t="s">
         <v>3280</v>
@@ -29460,12 +29460,12 @@
         <v>3179</v>
       </c>
       <c r="Y116" s="30" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="Z116" s="30"/>
       <c r="AA116" s="30"/>
       <c r="AB116" s="219" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="AC116" s="32"/>
       <c r="AD116" s="21"/>
@@ -29485,7 +29485,7 @@
     </row>
     <row r="117" spans="1:43" ht="15.75" customHeight="1">
       <c r="A117" s="186" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="B117" s="33" t="s">
         <v>434</v>
@@ -29496,16 +29496,16 @@
       <c r="D117" s="235"/>
       <c r="E117" s="58"/>
       <c r="F117" s="290" t="s">
+        <v>3605</v>
+      </c>
+      <c r="G117" s="32" t="s">
         <v>3606</v>
       </c>
-      <c r="G117" s="32" t="s">
+      <c r="H117" s="95" t="s">
         <v>3607</v>
       </c>
-      <c r="H117" s="95" t="s">
-        <v>3608</v>
-      </c>
       <c r="I117" s="187" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="J117" s="22"/>
       <c r="K117" s="22"/>
@@ -29514,7 +29514,7 @@
         <v>804</v>
       </c>
       <c r="N117" s="136" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="O117" s="54"/>
       <c r="P117" s="55"/>
@@ -29558,7 +29558,7 @@
     </row>
     <row r="118" spans="1:43" ht="15.75" customHeight="1">
       <c r="A118" s="186" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="B118" s="95" t="s">
         <v>434</v>
@@ -29569,14 +29569,14 @@
       <c r="D118" s="235"/>
       <c r="E118" s="58"/>
       <c r="F118" s="290" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="G118" s="32"/>
       <c r="H118" s="192" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="I118" s="32" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="J118" s="82"/>
       <c r="K118" s="82"/>
@@ -29585,7 +29585,7 @@
         <v>184</v>
       </c>
       <c r="N118" s="38" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="O118" s="38"/>
       <c r="P118" s="25"/>
@@ -29606,12 +29606,12 @@
         <v>3179</v>
       </c>
       <c r="Y118" s="30" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="Z118" s="30"/>
       <c r="AA118" s="30"/>
       <c r="AB118" s="46" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="AC118" s="32"/>
       <c r="AD118" s="21"/>
@@ -29631,7 +29631,7 @@
     </row>
     <row r="119" spans="1:43" ht="15.75" customHeight="1">
       <c r="A119" s="186" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="B119" s="95" t="s">
         <v>2294</v>
@@ -29642,34 +29642,34 @@
       <c r="D119" s="235"/>
       <c r="E119" s="58"/>
       <c r="F119" s="290" t="s">
+        <v>3615</v>
+      </c>
+      <c r="G119" s="32" t="s">
         <v>3616</v>
       </c>
-      <c r="G119" s="32" t="s">
+      <c r="H119" s="33" t="s">
         <v>3617</v>
-      </c>
-      <c r="H119" s="33" t="s">
-        <v>3618</v>
       </c>
       <c r="I119" s="187" t="s">
         <v>3068</v>
       </c>
       <c r="J119" s="22" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="K119" s="22"/>
       <c r="L119" s="22"/>
       <c r="M119" s="115" t="s">
+        <v>3619</v>
+      </c>
+      <c r="N119" s="65" t="s">
         <v>3620</v>
       </c>
-      <c r="N119" s="65" t="s">
-        <v>3621</v>
-      </c>
       <c r="O119" s="38" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="P119" s="25"/>
       <c r="Q119" s="56" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="R119" s="94" t="s">
         <v>1107</v>
@@ -29687,7 +29687,7 @@
         <v>3179</v>
       </c>
       <c r="Y119" s="30" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="Z119" s="30"/>
       <c r="AA119" s="30"/>
@@ -29710,7 +29710,7 @@
     </row>
     <row r="120" spans="1:43" ht="15.75" customHeight="1">
       <c r="A120" s="296" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="B120" s="32" t="s">
         <v>434</v>
@@ -29721,11 +29721,11 @@
       <c r="D120" s="235"/>
       <c r="E120" s="58"/>
       <c r="F120" s="290" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="G120" s="32"/>
       <c r="H120" s="192" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="I120" s="192" t="s">
         <v>2522</v>
@@ -29739,14 +29739,14 @@
         <v>804</v>
       </c>
       <c r="N120" s="38" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="O120" s="465" t="s">
         <v>901</v>
       </c>
       <c r="P120" s="126"/>
       <c r="Q120" s="56" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="R120" s="39" t="s">
         <v>523</v>
@@ -29767,10 +29767,10 @@
         <v>3273</v>
       </c>
       <c r="Z120" s="30" t="s">
+        <v>3625</v>
+      </c>
+      <c r="AA120" s="30" t="s">
         <v>3626</v>
-      </c>
-      <c r="AA120" s="30" t="s">
-        <v>3627</v>
       </c>
       <c r="AB120" s="41"/>
       <c r="AC120" s="32"/>
@@ -29791,7 +29791,7 @@
     </row>
     <row r="121" spans="1:43" ht="15.75" customHeight="1">
       <c r="A121" s="296" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="B121" s="95" t="s">
         <v>2294</v>
@@ -29802,11 +29802,11 @@
       <c r="D121" s="235"/>
       <c r="E121" s="58"/>
       <c r="F121" s="16" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="G121" s="32"/>
       <c r="H121" s="32" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="I121" s="32" t="s">
         <v>2522</v>
@@ -29820,14 +29820,14 @@
         <v>657</v>
       </c>
       <c r="N121" s="464" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="O121" s="464" t="s">
         <v>901</v>
       </c>
       <c r="P121" s="126"/>
       <c r="Q121" s="123" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="R121" s="39" t="s">
         <v>523</v>
@@ -29848,10 +29848,10 @@
         <v>3281</v>
       </c>
       <c r="Z121" s="30" t="s">
+        <v>3630</v>
+      </c>
+      <c r="AA121" s="30" t="s">
         <v>3631</v>
-      </c>
-      <c r="AA121" s="30" t="s">
-        <v>3632</v>
       </c>
       <c r="AB121" s="41"/>
       <c r="AC121" s="32"/>
@@ -29872,7 +29872,7 @@
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
       <c r="A122" s="186" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="B122" s="95" t="s">
         <v>2294</v>
@@ -29883,34 +29883,34 @@
       <c r="D122" s="235"/>
       <c r="E122" s="58"/>
       <c r="F122" s="290" t="s">
+        <v>3638</v>
+      </c>
+      <c r="G122" s="32" t="s">
         <v>3639</v>
       </c>
-      <c r="G122" s="32" t="s">
+      <c r="H122" s="206" t="s">
         <v>3640</v>
       </c>
-      <c r="H122" s="206" t="s">
+      <c r="I122" s="32" t="s">
         <v>3641</v>
-      </c>
-      <c r="I122" s="32" t="s">
-        <v>3642</v>
       </c>
       <c r="J122" s="22"/>
       <c r="K122" s="93" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="L122" s="22"/>
       <c r="M122" s="137" t="s">
         <v>657</v>
       </c>
       <c r="N122" s="136" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="O122" s="469" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="P122" s="114"/>
       <c r="Q122" s="56" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="R122" s="490" t="s">
         <v>1107</v>
@@ -29928,7 +29928,7 @@
         <v>3179</v>
       </c>
       <c r="Y122" s="30" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="Z122" s="30"/>
       <c r="AA122" s="30"/>
@@ -29951,43 +29951,43 @@
     </row>
     <row r="123" spans="1:43" ht="15.75" customHeight="1">
       <c r="A123" s="287" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="B123" s="95" t="s">
         <v>2294</v>
       </c>
       <c r="C123" s="249" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="D123" s="235"/>
       <c r="E123" s="58"/>
       <c r="F123" s="47" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="G123" s="32"/>
       <c r="H123" s="48" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="I123" s="187" t="s">
         <v>2522</v>
       </c>
       <c r="J123" s="109" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="K123" s="109"/>
       <c r="L123" s="109"/>
       <c r="M123" s="137" t="s">
+        <v>3649</v>
+      </c>
+      <c r="N123" s="136" t="s">
         <v>3650</v>
       </c>
-      <c r="N123" s="136" t="s">
+      <c r="O123" s="54" t="s">
         <v>3651</v>
-      </c>
-      <c r="O123" s="54" t="s">
-        <v>3652</v>
       </c>
       <c r="P123" s="55"/>
       <c r="Q123" s="56" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="R123" s="39" t="s">
         <v>523</v>
@@ -30003,7 +30003,7 @@
         <v>3179</v>
       </c>
       <c r="Y123" s="30" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="Z123" s="30"/>
       <c r="AA123" s="30"/>
@@ -30026,7 +30026,7 @@
     </row>
     <row r="124" spans="1:43" ht="15.75" customHeight="1">
       <c r="A124" s="186" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="B124" s="95" t="s">
         <v>2294</v>
@@ -30037,11 +30037,11 @@
       <c r="D124" s="235"/>
       <c r="E124" s="58"/>
       <c r="F124" s="47" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="G124" s="32"/>
       <c r="H124" s="186" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="I124" s="32" t="s">
         <v>2053</v>
@@ -30055,14 +30055,14 @@
         <v>683</v>
       </c>
       <c r="N124" s="89" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="O124" s="89"/>
       <c r="P124" s="74" t="s">
         <v>1612</v>
       </c>
       <c r="Q124" s="91" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="R124" s="333" t="s">
         <v>40</v>
@@ -30084,7 +30084,7 @@
         <v>3179</v>
       </c>
       <c r="Y124" s="30" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="Z124" s="30"/>
       <c r="AA124" s="30"/>
@@ -30107,7 +30107,7 @@
     </row>
     <row r="125" spans="1:43" ht="15.75" customHeight="1">
       <c r="A125" s="186" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="B125" s="95" t="s">
         <v>2294</v>
@@ -30118,13 +30118,13 @@
       <c r="D125" s="236"/>
       <c r="E125" s="67"/>
       <c r="F125" s="16" t="s">
+        <v>3660</v>
+      </c>
+      <c r="G125" s="32" t="s">
         <v>3661</v>
       </c>
-      <c r="G125" s="32" t="s">
+      <c r="H125" s="32" t="s">
         <v>3662</v>
-      </c>
-      <c r="H125" s="32" t="s">
-        <v>3663</v>
       </c>
       <c r="I125" s="187" t="s">
         <v>2654</v>
@@ -30138,7 +30138,7 @@
         <v>2969</v>
       </c>
       <c r="N125" s="65" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="O125" s="83"/>
       <c r="P125" s="25"/>
@@ -30182,7 +30182,7 @@
     </row>
     <row r="126" spans="1:43" ht="15.75" customHeight="1">
       <c r="A126" s="296" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="B126" s="95" t="s">
         <v>434</v>
@@ -30193,13 +30193,13 @@
       <c r="D126" s="235"/>
       <c r="E126" s="58"/>
       <c r="F126" s="47" t="s">
+        <v>3682</v>
+      </c>
+      <c r="G126" s="32" t="s">
         <v>3683</v>
       </c>
-      <c r="G126" s="32" t="s">
+      <c r="H126" s="95" t="s">
         <v>3684</v>
-      </c>
-      <c r="H126" s="95" t="s">
-        <v>3685</v>
       </c>
       <c r="I126" s="187" t="s">
         <v>2654</v>
@@ -30207,20 +30207,20 @@
       <c r="J126" s="93"/>
       <c r="K126" s="22"/>
       <c r="L126" s="22" t="s">
+        <v>3685</v>
+      </c>
+      <c r="M126" s="453" t="s">
         <v>3686</v>
       </c>
-      <c r="M126" s="453" t="s">
+      <c r="N126" s="136" t="s">
         <v>3687</v>
       </c>
-      <c r="N126" s="136" t="s">
-        <v>3688</v>
-      </c>
       <c r="O126" s="38" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="P126" s="55"/>
       <c r="Q126" s="56" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="R126" s="94" t="s">
         <v>1107</v>
@@ -30259,7 +30259,7 @@
     </row>
     <row r="127" spans="1:43" ht="15.75" customHeight="1">
       <c r="A127" s="186" t="s">
-        <v>3699</v>
+        <v>3698</v>
       </c>
       <c r="B127" s="400" t="s">
         <v>2294</v>
@@ -30270,13 +30270,13 @@
       <c r="D127" s="236"/>
       <c r="E127" s="67"/>
       <c r="F127" s="290" t="s">
+        <v>3699</v>
+      </c>
+      <c r="G127" s="32" t="s">
         <v>3700</v>
       </c>
-      <c r="G127" s="32" t="s">
+      <c r="H127" s="95" t="s">
         <v>3701</v>
-      </c>
-      <c r="H127" s="95" t="s">
-        <v>3702</v>
       </c>
       <c r="I127" s="187" t="s">
         <v>2654</v>
@@ -30288,7 +30288,7 @@
         <v>1992</v>
       </c>
       <c r="N127" s="65" t="s">
-        <v>3703</v>
+        <v>3702</v>
       </c>
       <c r="O127" s="38"/>
       <c r="P127" s="25"/>
@@ -30314,7 +30314,7 @@
       <c r="Z127" s="30"/>
       <c r="AA127" s="30"/>
       <c r="AB127" s="46" t="s">
-        <v>3704</v>
+        <v>3703</v>
       </c>
       <c r="AC127" s="32"/>
       <c r="AD127" s="32"/>
@@ -30334,7 +30334,7 @@
     </row>
     <row r="128" spans="1:43" ht="70.5" customHeight="1">
       <c r="A128" s="282" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="B128" s="95" t="s">
         <v>2294</v>
@@ -30345,14 +30345,14 @@
       <c r="D128" s="235"/>
       <c r="E128" s="58"/>
       <c r="F128" s="290" t="s">
-        <v>3747</v>
+        <v>3746</v>
       </c>
       <c r="G128" s="32"/>
       <c r="H128" s="48" t="s">
+        <v>3747</v>
+      </c>
+      <c r="I128" s="187" t="s">
         <v>3748</v>
-      </c>
-      <c r="I128" s="187" t="s">
-        <v>3749</v>
       </c>
       <c r="J128" s="22"/>
       <c r="K128" s="22"/>
@@ -30361,14 +30361,14 @@
         <v>1623</v>
       </c>
       <c r="N128" s="38" t="s">
+        <v>3749</v>
+      </c>
+      <c r="O128" s="465" t="s">
         <v>3750</v>
-      </c>
-      <c r="O128" s="465" t="s">
-        <v>3751</v>
       </c>
       <c r="P128" s="126"/>
       <c r="Q128" s="26" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="R128" s="398" t="s">
         <v>523</v>
@@ -30389,10 +30389,10 @@
         <v>3314</v>
       </c>
       <c r="Z128" s="30" t="s">
+        <v>3752</v>
+      </c>
+      <c r="AA128" s="30" t="s">
         <v>3753</v>
-      </c>
-      <c r="AA128" s="30" t="s">
-        <v>3754</v>
       </c>
       <c r="AB128" s="41"/>
       <c r="AC128" s="32"/>
@@ -30413,40 +30413,40 @@
     </row>
     <row r="129" spans="1:43" ht="15.75" customHeight="1">
       <c r="A129" s="281" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="B129" s="95" t="s">
         <v>2294</v>
       </c>
       <c r="C129" s="256" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="D129" s="235"/>
       <c r="E129" s="58"/>
       <c r="F129" s="16" t="s">
+        <v>3756</v>
+      </c>
+      <c r="G129" s="32" t="s">
         <v>3757</v>
       </c>
-      <c r="G129" s="32" t="s">
+      <c r="H129" s="95" t="s">
         <v>3758</v>
       </c>
-      <c r="H129" s="95" t="s">
+      <c r="I129" s="187" t="s">
         <v>3759</v>
-      </c>
-      <c r="I129" s="187" t="s">
-        <v>3760</v>
       </c>
       <c r="J129" s="22" t="s">
         <v>2968</v>
       </c>
       <c r="K129" s="93" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="L129" s="22"/>
       <c r="M129" s="331" t="s">
+        <v>3760</v>
+      </c>
+      <c r="N129" s="65" t="s">
         <v>3761</v>
-      </c>
-      <c r="N129" s="65" t="s">
-        <v>3762</v>
       </c>
       <c r="O129" s="465"/>
       <c r="P129" s="126"/>
@@ -30458,7 +30458,7 @@
         <v>41</v>
       </c>
       <c r="T129" s="21" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="U129" s="28"/>
       <c r="V129" s="28"/>
@@ -30469,12 +30469,12 @@
         <v>3179</v>
       </c>
       <c r="Y129" s="30" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="Z129" s="30"/>
       <c r="AA129" s="30"/>
       <c r="AB129" s="31" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="AC129" s="32"/>
       <c r="AD129" s="32"/>
@@ -30494,7 +30494,7 @@
     </row>
     <row r="130" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A130" s="186" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="B130" s="95" t="s">
         <v>2294</v>
@@ -30505,19 +30505,19 @@
       <c r="D130" s="236"/>
       <c r="E130" s="58"/>
       <c r="F130" s="47" t="s">
+        <v>3766</v>
+      </c>
+      <c r="G130" s="32" t="s">
         <v>3767</v>
       </c>
-      <c r="G130" s="32" t="s">
+      <c r="H130" s="95" t="s">
         <v>3768</v>
-      </c>
-      <c r="H130" s="95" t="s">
-        <v>3769</v>
       </c>
       <c r="I130" s="187" t="s">
         <v>2654</v>
       </c>
       <c r="J130" s="22" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="K130" s="22"/>
       <c r="L130" s="22"/>
@@ -30525,7 +30525,7 @@
         <v>2969</v>
       </c>
       <c r="N130" s="136" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="O130" s="463"/>
       <c r="P130" s="114"/>
@@ -30537,7 +30537,7 @@
         <v>41</v>
       </c>
       <c r="T130" s="21" t="s">
-        <v>3771</v>
+        <v>3770</v>
       </c>
       <c r="U130" s="28"/>
       <c r="V130" s="28"/>
@@ -30548,12 +30548,12 @@
         <v>3179</v>
       </c>
       <c r="Y130" s="30" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="Z130" s="30"/>
       <c r="AA130" s="30"/>
       <c r="AB130" s="46" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="AC130" s="32"/>
       <c r="AD130" s="32"/>
@@ -30573,7 +30573,7 @@
     </row>
     <row r="131" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A131" s="186" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="B131" s="95" t="s">
         <v>2294</v>
@@ -30584,27 +30584,27 @@
       <c r="D131" s="236"/>
       <c r="E131" s="58"/>
       <c r="F131" s="290" t="s">
+        <v>3774</v>
+      </c>
+      <c r="G131" s="32" t="s">
         <v>3775</v>
       </c>
-      <c r="G131" s="32" t="s">
+      <c r="H131" s="95" t="s">
         <v>3776</v>
       </c>
-      <c r="H131" s="95" t="s">
+      <c r="I131" s="187" t="s">
         <v>3777</v>
-      </c>
-      <c r="I131" s="187" t="s">
-        <v>3778</v>
       </c>
       <c r="J131" s="22"/>
       <c r="K131" s="93" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="L131" s="22"/>
       <c r="M131" s="212" t="s">
         <v>2746</v>
       </c>
       <c r="N131" s="136" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="O131" s="54"/>
       <c r="P131" s="114"/>
@@ -30616,7 +30616,7 @@
         <v>41</v>
       </c>
       <c r="T131" s="21" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="U131" s="28"/>
       <c r="V131" s="28"/>
@@ -30627,7 +30627,7 @@
         <v>3179</v>
       </c>
       <c r="Y131" s="30" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="Z131" s="30"/>
       <c r="AA131" s="30"/>
@@ -30723,7 +30723,7 @@
     </row>
     <row r="133" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A133" s="284" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="B133" s="33" t="s">
         <v>434</v>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="G133" s="32"/>
       <c r="H133" s="192" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="I133" s="32" t="s">
         <v>2522</v>
@@ -30806,7 +30806,7 @@
     </row>
     <row r="134" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A134" s="186" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="B134" s="33" t="s">
         <v>434</v>
@@ -30817,32 +30817,32 @@
       <c r="D134" s="235"/>
       <c r="E134" s="58"/>
       <c r="F134" s="47" t="s">
+        <v>3530</v>
+      </c>
+      <c r="G134" s="32" t="s">
         <v>3531</v>
       </c>
-      <c r="G134" s="32" t="s">
+      <c r="H134" s="206" t="s">
         <v>3532</v>
       </c>
-      <c r="H134" s="206" t="s">
+      <c r="I134" s="187" t="s">
         <v>3533</v>
-      </c>
-      <c r="I134" s="187" t="s">
-        <v>3534</v>
       </c>
       <c r="J134" s="22"/>
       <c r="K134" s="22"/>
       <c r="L134" s="22"/>
       <c r="M134" s="137" t="s">
+        <v>3534</v>
+      </c>
+      <c r="N134" s="73" t="s">
         <v>3535</v>
-      </c>
-      <c r="N134" s="73" t="s">
-        <v>3536</v>
       </c>
       <c r="O134" s="73"/>
       <c r="P134" s="74" t="s">
+        <v>3536</v>
+      </c>
+      <c r="Q134" s="91" t="s">
         <v>3537</v>
-      </c>
-      <c r="Q134" s="91" t="s">
-        <v>3538</v>
       </c>
       <c r="R134" s="461" t="s">
         <v>3344</v>
@@ -30855,16 +30855,16 @@
         <v>3178</v>
       </c>
       <c r="V134" s="28" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="W134" s="113" t="s">
         <v>3178</v>
       </c>
       <c r="X134" s="130" t="s">
+        <v>3537</v>
+      </c>
+      <c r="Y134" s="30" t="s">
         <v>3538</v>
-      </c>
-      <c r="Y134" s="30" t="s">
-        <v>3539</v>
       </c>
       <c r="Z134" s="30"/>
       <c r="AA134" s="30"/>
@@ -31041,7 +31041,7 @@
     </row>
     <row r="137" spans="1:43" ht="15.75" customHeight="1">
       <c r="A137" s="277" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="B137" s="32" t="s">
         <v>247</v>
@@ -31120,7 +31120,7 @@
     </row>
     <row r="138" spans="1:43" ht="15.75" customHeight="1">
       <c r="A138" s="274" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="B138" s="32" t="s">
         <v>310</v>
@@ -31272,7 +31272,7 @@
     </row>
     <row r="140" spans="1:43" ht="15.75" customHeight="1">
       <c r="A140" s="289" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="B140" s="33" t="s">
         <v>43</v>
@@ -31430,13 +31430,13 @@
     </row>
     <row r="142" spans="1:43" ht="15.75" customHeight="1">
       <c r="A142" s="276" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="B142" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C142" s="264" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="D142" s="234" t="s">
         <v>179</v>
@@ -31490,7 +31490,7 @@
         <v>191</v>
       </c>
       <c r="Y142" s="30" t="s">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="Z142" s="30"/>
       <c r="AA142" s="30"/>
@@ -31523,7 +31523,7 @@
         <v>43</v>
       </c>
       <c r="C143" s="267" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="D143" s="234" t="s">
         <v>179</v>
@@ -31778,7 +31778,7 @@
     </row>
     <row r="146" spans="1:43" ht="15.75" customHeight="1">
       <c r="A146" s="276" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="B146" s="32" t="s">
         <v>43</v>
@@ -31863,7 +31863,7 @@
     </row>
     <row r="147" spans="1:43" ht="15.75" customHeight="1">
       <c r="A147" s="268" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="B147" s="32" t="s">
         <v>43</v>
@@ -32029,7 +32029,7 @@
     </row>
     <row r="149" spans="1:43" ht="15.75" customHeight="1">
       <c r="A149" s="277" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="B149" s="32" t="s">
         <v>870</v>
@@ -32187,7 +32187,7 @@
     </row>
     <row r="151" spans="1:43" ht="15.75" customHeight="1">
       <c r="A151" s="277" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="B151" s="14" t="s">
         <v>1919</v>
@@ -32452,7 +32452,7 @@
         <v>2013</v>
       </c>
       <c r="M154" s="95" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="N154" s="38" t="s">
         <v>1659</v>
@@ -32511,7 +32511,7 @@
     </row>
     <row r="155" spans="1:43" ht="15.75" customHeight="1">
       <c r="A155" s="277" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="B155" s="14" t="s">
         <v>434</v>
@@ -33550,7 +33550,7 @@
     </row>
     <row r="168" spans="1:43" ht="15.75" customHeight="1">
       <c r="A168" s="277" t="s">
-        <v>3916</v>
+        <v>3915</v>
       </c>
       <c r="B168" s="14" t="s">
         <v>43</v>
@@ -33565,7 +33565,7 @@
       </c>
       <c r="G168" s="32"/>
       <c r="H168" s="32" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="I168" s="43" t="s">
         <v>1038</v>
@@ -33698,7 +33698,7 @@
     </row>
     <row r="170" spans="1:43" ht="15.75" customHeight="1">
       <c r="A170" s="277" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="B170" s="14" t="s">
         <v>471</v>
@@ -33858,7 +33858,7 @@
     </row>
     <row r="172" spans="1:43" ht="15.75" customHeight="1">
       <c r="A172" s="366" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="B172" s="314" t="s">
         <v>43</v>
@@ -34022,7 +34022,7 @@
     </row>
     <row r="174" spans="1:43" ht="15.75" customHeight="1">
       <c r="A174" s="277" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
       <c r="B174" s="32" t="s">
         <v>43</v>
@@ -34105,7 +34105,7 @@
     </row>
     <row r="175" spans="1:43" ht="15.75" customHeight="1">
       <c r="A175" s="277" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="B175" s="14" t="s">
         <v>434</v>
@@ -34192,13 +34192,13 @@
     </row>
     <row r="176" spans="1:43" ht="15.75" customHeight="1">
       <c r="A176" s="277" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="B176" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C176" s="250" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
       <c r="D176" s="235"/>
       <c r="E176" s="58"/>
@@ -34244,7 +34244,7 @@
         <v>404</v>
       </c>
       <c r="Y176" s="30" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="Z176" s="30"/>
       <c r="AA176" s="30"/>
@@ -34348,7 +34348,7 @@
     </row>
     <row r="178" spans="1:43" ht="15.75" customHeight="1">
       <c r="A178" s="274" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="B178" s="15" t="s">
         <v>30</v>
@@ -34479,7 +34479,7 @@
       <c r="W179" s="29"/>
       <c r="X179" s="29"/>
       <c r="Y179" s="30" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="Z179" s="30"/>
       <c r="AA179" s="30"/>
@@ -34506,7 +34506,7 @@
     </row>
     <row r="180" spans="1:43" ht="15.75" customHeight="1">
       <c r="A180" s="275" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="B180" s="32" t="s">
         <v>72</v>
@@ -34721,7 +34721,7 @@
     </row>
     <row r="183" spans="1:43" ht="15.75" customHeight="1">
       <c r="A183" s="274" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="B183" s="32" t="s">
         <v>100</v>
@@ -34873,7 +34873,7 @@
         <v>43</v>
       </c>
       <c r="C185" s="251" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="D185" s="236"/>
       <c r="E185" s="67"/>
@@ -34944,7 +34944,7 @@
         <v>43</v>
       </c>
       <c r="C186" s="251" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="D186" s="235"/>
       <c r="E186" s="58"/>
@@ -35226,7 +35226,7 @@
     </row>
     <row r="190" spans="1:43" ht="15.75" customHeight="1">
       <c r="A190" s="277" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="B190" s="32" t="s">
         <v>247</v>
@@ -35295,7 +35295,7 @@
     </row>
     <row r="191" spans="1:43" ht="15.75" customHeight="1">
       <c r="A191" s="277" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="B191" s="32" t="s">
         <v>247</v>
@@ -35364,13 +35364,13 @@
     </row>
     <row r="192" spans="1:43" ht="15.75" customHeight="1">
       <c r="A192" s="291" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="B192" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C192" s="250" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="D192" s="234" t="s">
         <v>179</v>
@@ -35441,7 +35441,7 @@
         <v>43</v>
       </c>
       <c r="C193" s="250" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="D193" s="234" t="s">
         <v>179</v>
@@ -35506,7 +35506,7 @@
     </row>
     <row r="194" spans="1:43" ht="15.75" customHeight="1">
       <c r="A194" s="274" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="B194" s="33" t="s">
         <v>279</v>
@@ -35581,7 +35581,7 @@
     </row>
     <row r="195" spans="1:43" ht="15.75" customHeight="1">
       <c r="A195" s="274" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="B195" s="33" t="s">
         <v>292</v>
@@ -35662,13 +35662,13 @@
     </row>
     <row r="196" spans="1:43" ht="15.75" customHeight="1">
       <c r="A196" s="277" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="B196" s="33" t="s">
         <v>292</v>
       </c>
       <c r="C196" s="250" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="D196" s="232"/>
       <c r="E196" s="18"/>
@@ -35741,7 +35741,7 @@
         <v>292</v>
       </c>
       <c r="C197" s="250" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="D197" s="232"/>
       <c r="E197" s="18"/>
@@ -35806,13 +35806,13 @@
     </row>
     <row r="198" spans="1:43" ht="15.75" customHeight="1">
       <c r="A198" s="278" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="B198" s="95" t="s">
         <v>43</v>
       </c>
       <c r="C198" s="258" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="D198" s="234" t="s">
         <v>280</v>
@@ -35887,13 +35887,13 @@
     </row>
     <row r="199" spans="1:43" ht="15.75" customHeight="1">
       <c r="A199" s="277" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="B199" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C199" s="251" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="D199" s="234" t="s">
         <v>280</v>
@@ -36039,7 +36039,7 @@
     </row>
     <row r="201" spans="1:43" ht="15.75" customHeight="1">
       <c r="A201" s="274" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="B201" s="14" t="s">
         <v>43</v>
@@ -36116,7 +36116,7 @@
         <v>377</v>
       </c>
       <c r="C202" s="250" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="D202" s="235"/>
       <c r="E202" s="58"/>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="G203" s="32"/>
       <c r="H203" s="48" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="I203" s="43" t="s">
         <v>384</v>
@@ -36203,7 +36203,7 @@
         <v>385</v>
       </c>
       <c r="M203" s="95" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="N203" s="54" t="s">
         <v>386</v>
@@ -36244,13 +36244,13 @@
     </row>
     <row r="204" spans="1:43" ht="15.75" customHeight="1">
       <c r="A204" s="277" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="B204" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C204" s="250" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
       <c r="D204" s="235"/>
       <c r="E204" s="138"/>
@@ -36457,7 +36457,7 @@
         <v>413</v>
       </c>
       <c r="C207" s="250" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="D207" s="235"/>
       <c r="E207" s="58"/>
@@ -36518,13 +36518,13 @@
     </row>
     <row r="208" spans="1:43" ht="15.75" customHeight="1">
       <c r="A208" s="277" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="B208" s="32" t="s">
         <v>434</v>
       </c>
       <c r="C208" s="250" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="D208" s="235"/>
       <c r="E208" s="58"/>
@@ -36675,13 +36675,13 @@
     </row>
     <row r="210" spans="1:43" ht="15.75" customHeight="1">
       <c r="A210" s="14" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
       <c r="B210" s="32" t="s">
         <v>434</v>
       </c>
       <c r="C210" s="250" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="D210" s="235"/>
       <c r="E210" s="58"/>
@@ -36746,13 +36746,13 @@
     </row>
     <row r="211" spans="1:43" ht="15.75" customHeight="1">
       <c r="A211" s="14" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>444</v>
       </c>
       <c r="C211" s="250" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="D211" s="234" t="s">
         <v>465</v>
@@ -36823,7 +36823,7 @@
         <v>43</v>
       </c>
       <c r="C212" s="250" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="D212" s="235"/>
       <c r="E212" s="58"/>
@@ -36963,7 +36963,7 @@
     </row>
     <row r="214" spans="1:43" ht="15.75" customHeight="1">
       <c r="A214" s="277" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="B214" s="32" t="s">
         <v>43</v>
@@ -37030,13 +37030,13 @@
     </row>
     <row r="215" spans="1:43" ht="15.75" customHeight="1">
       <c r="A215" s="277" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="B215" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C215" s="250" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="D215" s="234" t="s">
         <v>179</v>
@@ -37105,13 +37105,13 @@
     </row>
     <row r="216" spans="1:43" ht="15.75" customHeight="1">
       <c r="A216" s="277" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="B216" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C216" s="250" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="D216" s="234" t="s">
         <v>179</v>
@@ -37176,7 +37176,7 @@
     </row>
     <row r="217" spans="1:43" ht="15.75" customHeight="1">
       <c r="A217" s="277" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="B217" s="32" t="s">
         <v>43</v>
@@ -37251,18 +37251,18 @@
     </row>
     <row r="218" spans="1:43" ht="15.75" customHeight="1">
       <c r="A218" s="277" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="B218" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C218" s="250" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="D218" s="235"/>
       <c r="E218" s="58"/>
       <c r="F218" s="47" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="G218" s="32" t="s">
         <v>549</v>
@@ -37322,7 +37322,7 @@
     </row>
     <row r="219" spans="1:43" ht="15.75" customHeight="1">
       <c r="A219" s="277" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="B219" s="32" t="s">
         <v>43</v>
@@ -37395,13 +37395,13 @@
         <v>564</v>
       </c>
       <c r="C220" s="250" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="D220" s="234" t="s">
         <v>565</v>
       </c>
       <c r="E220" s="58" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="F220" s="290" t="s">
         <v>566</v>
@@ -37462,13 +37462,13 @@
     </row>
     <row r="221" spans="1:43" ht="15.75" customHeight="1">
       <c r="A221" s="277" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="B221" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C221" s="250" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="D221" s="235"/>
       <c r="E221" s="58"/>
@@ -37535,13 +37535,13 @@
     </row>
     <row r="222" spans="1:43" ht="15.75" customHeight="1">
       <c r="A222" s="277" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="B222" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C222" s="250" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="D222" s="235"/>
       <c r="E222" s="58"/>
@@ -37608,7 +37608,7 @@
     </row>
     <row r="223" spans="1:43" ht="15.75" customHeight="1">
       <c r="A223" s="277" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="B223" s="32" t="s">
         <v>43</v>
@@ -37681,7 +37681,7 @@
     </row>
     <row r="224" spans="1:43" ht="15.75" customHeight="1">
       <c r="A224" s="274" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="B224" s="32" t="s">
         <v>43</v>
@@ -37750,13 +37750,13 @@
     </row>
     <row r="225" spans="1:43" ht="15.75" customHeight="1">
       <c r="A225" s="277" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="B225" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C225" s="250" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="D225" s="235"/>
       <c r="E225" s="58"/>
@@ -37819,7 +37819,7 @@
     </row>
     <row r="226" spans="1:43" ht="15.75" customHeight="1">
       <c r="A226" s="274" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="B226" s="32" t="s">
         <v>644</v>
@@ -37965,7 +37965,7 @@
     </row>
     <row r="228" spans="1:43" ht="15.75" customHeight="1">
       <c r="A228" s="274" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="B228" s="32" t="s">
         <v>43</v>
@@ -38040,7 +38040,7 @@
         <v>43</v>
       </c>
       <c r="C229" s="250" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="D229" s="235"/>
       <c r="E229" s="58"/>
@@ -38529,7 +38529,7 @@
     </row>
     <row r="236" spans="1:43" ht="15.75" customHeight="1">
       <c r="A236" s="274" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="B236" s="14" t="s">
         <v>749</v>
@@ -38665,7 +38665,7 @@
     </row>
     <row r="238" spans="1:43" ht="15.75" customHeight="1">
       <c r="A238" s="274" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="B238" s="14" t="s">
         <v>434</v>
@@ -39042,7 +39042,7 @@
     </row>
     <row r="243" spans="1:43" ht="15.75" customHeight="1">
       <c r="A243" s="274" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="B243" s="14" t="s">
         <v>43</v>
@@ -39395,7 +39395,7 @@
     </row>
     <row r="248" spans="1:43" ht="15.75" customHeight="1">
       <c r="A248" s="394" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="B248" s="393" t="s">
         <v>434</v>
@@ -39462,7 +39462,7 @@
     </row>
     <row r="249" spans="1:43" ht="15.75" customHeight="1">
       <c r="A249" s="277" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="B249" s="32" t="s">
         <v>43</v>
@@ -39734,7 +39734,7 @@
     </row>
     <row r="253" spans="1:43" ht="15.75" customHeight="1">
       <c r="A253" s="277" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="B253" s="32" t="s">
         <v>890</v>
@@ -39880,7 +39880,7 @@
     </row>
     <row r="255" spans="1:43" ht="15.75" customHeight="1">
       <c r="A255" s="277" t="s">
-        <v>3920</v>
+        <v>3919</v>
       </c>
       <c r="B255" s="32" t="s">
         <v>471</v>
@@ -40093,7 +40093,7 @@
     </row>
     <row r="258" spans="1:43" ht="15.75" customHeight="1">
       <c r="A258" s="277" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
       <c r="B258" s="32" t="s">
         <v>43</v>
@@ -40300,7 +40300,7 @@
     </row>
     <row r="261" spans="1:43" ht="15.75" customHeight="1">
       <c r="A261" s="277" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
       <c r="B261" s="32" t="s">
         <v>43</v>
@@ -41014,7 +41014,7 @@
     </row>
     <row r="271" spans="1:43" ht="15.75" customHeight="1">
       <c r="A271" s="278" t="s">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="B271" s="51" t="s">
         <v>43</v>
@@ -41066,7 +41066,7 @@
       <c r="W271" s="29"/>
       <c r="X271" s="29"/>
       <c r="Y271" s="30" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="Z271" s="30"/>
       <c r="AA271" s="30"/>
@@ -41444,7 +41444,7 @@
     </row>
     <row r="277" spans="1:43" ht="15.75" customHeight="1">
       <c r="A277" s="278" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="B277" s="32" t="s">
         <v>43</v>
@@ -41515,7 +41515,7 @@
     </row>
     <row r="278" spans="1:43" ht="15.75" customHeight="1">
       <c r="A278" s="277" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="B278" s="14" t="s">
         <v>43</v>
@@ -41945,7 +41945,7 @@
     </row>
     <row r="284" spans="1:43" ht="15.75" customHeight="1">
       <c r="A284" s="277" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="B284" s="14" t="s">
         <v>43</v>
@@ -41960,7 +41960,7 @@
       </c>
       <c r="G284" s="32"/>
       <c r="H284" s="48" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="I284" s="43" t="s">
         <v>1187</v>
@@ -42085,7 +42085,7 @@
     </row>
     <row r="286" spans="1:43" ht="15.75" customHeight="1">
       <c r="A286" s="278" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
       <c r="B286" s="33" t="s">
         <v>43</v>
@@ -42100,7 +42100,7 @@
       </c>
       <c r="G286" s="32"/>
       <c r="H286" s="48" t="s">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="I286" s="43" t="s">
         <v>1201</v>
@@ -44273,7 +44273,7 @@
     </row>
     <row r="316" spans="1:43" ht="15.75" customHeight="1">
       <c r="A316" s="277" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="B316" s="33" t="s">
         <v>43</v>
@@ -44703,7 +44703,7 @@
     </row>
     <row r="322" spans="1:43" ht="15.75" customHeight="1">
       <c r="A322" s="277" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="B322" s="33" t="s">
         <v>43</v>
@@ -44772,7 +44772,7 @@
     </row>
     <row r="323" spans="1:43" ht="15.75" customHeight="1">
       <c r="A323" s="277" t="s">
-        <v>3907</v>
+        <v>3906</v>
       </c>
       <c r="B323" s="33" t="s">
         <v>43</v>
@@ -44839,7 +44839,7 @@
     </row>
     <row r="324" spans="1:43" ht="15.75" customHeight="1">
       <c r="A324" s="278" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="B324" s="15" t="s">
         <v>471</v>
@@ -45222,7 +45222,7 @@
     </row>
     <row r="329" spans="1:43" ht="15.75" customHeight="1">
       <c r="A329" s="277" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="B329" s="33" t="s">
         <v>43</v>
@@ -45291,7 +45291,7 @@
     </row>
     <row r="330" spans="1:43" ht="15.75" customHeight="1">
       <c r="A330" s="277" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="B330" s="33" t="s">
         <v>43</v>
@@ -45725,7 +45725,7 @@
     </row>
     <row r="336" spans="1:43" ht="15.75" customHeight="1">
       <c r="A336" s="278" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="B336" s="15" t="s">
         <v>43</v>
@@ -45936,13 +45936,13 @@
     </row>
     <row r="339" spans="1:43" ht="15.75" customHeight="1">
       <c r="A339" s="277" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="B339" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C339" s="251" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="D339" s="235"/>
       <c r="E339" s="58"/>
@@ -46193,7 +46193,7 @@
         <v>1658</v>
       </c>
       <c r="M342" s="95" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="N342" s="54" t="s">
         <v>1659</v>
@@ -46737,7 +46737,7 @@
     </row>
     <row r="350" spans="1:43" ht="15.75" customHeight="1">
       <c r="A350" s="277" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="B350" s="33" t="s">
         <v>43</v>
@@ -47114,7 +47114,7 @@
     </row>
     <row r="355" spans="1:43" ht="135" customHeight="1">
       <c r="A355" s="277" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="B355" s="14" t="s">
         <v>1007</v>
@@ -47193,7 +47193,7 @@
     </row>
     <row r="356" spans="1:43" ht="15.75" customHeight="1">
       <c r="A356" s="277" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="B356" s="14" t="s">
         <v>434</v>
@@ -47246,7 +47246,7 @@
       <c r="AB356" s="167"/>
       <c r="AC356" s="32"/>
       <c r="AD356" s="21" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="AE356" s="32"/>
       <c r="AF356" s="32"/>
@@ -47846,7 +47846,7 @@
     </row>
     <row r="365" spans="1:43" ht="15.75" customHeight="1">
       <c r="A365" s="278" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="B365" s="14" t="s">
         <v>434</v>
@@ -47921,7 +47921,7 @@
     </row>
     <row r="366" spans="1:43" ht="15.75" customHeight="1">
       <c r="A366" s="277" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="B366" s="14" t="s">
         <v>434</v>
@@ -48079,7 +48079,7 @@
       <c r="K368" s="22"/>
       <c r="L368" s="22"/>
       <c r="M368" s="53" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N368" s="54" t="s">
         <v>1907</v>
@@ -48160,7 +48160,7 @@
       <c r="K369" s="82"/>
       <c r="L369" s="22"/>
       <c r="M369" s="53" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N369" s="54" t="s">
         <v>1917</v>
@@ -48495,13 +48495,13 @@
     </row>
     <row r="374" spans="1:43" ht="15.75" customHeight="1">
       <c r="A374" s="277" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="B374" s="14" t="s">
         <v>434</v>
       </c>
       <c r="C374" s="261" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
       <c r="D374" s="235"/>
       <c r="E374" s="58"/>
@@ -48594,10 +48594,10 @@
         <v>2024</v>
       </c>
       <c r="M375" s="127" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="N375" s="54" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="O375" s="463"/>
       <c r="P375" s="126" t="s">
@@ -48673,7 +48673,7 @@
       <c r="K376" s="439"/>
       <c r="L376" s="439"/>
       <c r="M376" s="448" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N376" s="463" t="s">
         <v>2038</v>
@@ -48745,7 +48745,7 @@
         <v>2042</v>
       </c>
       <c r="H377" s="48" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="I377" s="43" t="s">
         <v>2043</v>
@@ -48754,7 +48754,7 @@
       <c r="K377" s="82"/>
       <c r="L377" s="82"/>
       <c r="M377" s="53" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N377" s="54" t="s">
         <v>2044</v>
@@ -48951,24 +48951,24 @@
     </row>
     <row r="380" spans="1:43" ht="15.75" customHeight="1">
       <c r="A380" s="396" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="B380" s="396" t="s">
         <v>2089</v>
       </c>
       <c r="C380" s="401" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="D380" s="414"/>
       <c r="E380" s="416"/>
       <c r="F380" s="416" t="s">
+        <v>3800</v>
+      </c>
+      <c r="G380" s="416" t="s">
         <v>3801</v>
       </c>
-      <c r="G380" s="416" t="s">
-        <v>3802</v>
-      </c>
       <c r="H380" s="399" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="I380" s="320" t="s">
         <v>1916</v>
@@ -48977,7 +48977,7 @@
       <c r="K380" s="427"/>
       <c r="L380" s="427"/>
       <c r="M380" s="320" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N380" s="134" t="s">
         <v>2090</v>
@@ -48996,7 +48996,7 @@
         <v>41</v>
       </c>
       <c r="T380" s="399" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="U380" s="399" t="s">
         <v>1909</v>
@@ -49007,7 +49007,7 @@
       <c r="W380" s="416"/>
       <c r="X380" s="416"/>
       <c r="Y380" s="419" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="Z380" s="427"/>
       <c r="AA380" s="416"/>
@@ -49016,7 +49016,7 @@
         <v>2091</v>
       </c>
       <c r="AD380" s="416" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="AE380" s="32"/>
       <c r="AF380" s="32"/>
@@ -49034,20 +49034,20 @@
     </row>
     <row r="381" spans="1:43" s="387" customFormat="1" ht="15.75" customHeight="1">
       <c r="A381" s="396" t="s">
+        <v>3795</v>
+      </c>
+      <c r="B381" s="399" t="s">
         <v>3796</v>
       </c>
-      <c r="B381" s="399" t="s">
-        <v>3797</v>
-      </c>
       <c r="C381" s="401" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="D381" s="414"/>
       <c r="E381" s="416"/>
       <c r="F381" s="427"/>
       <c r="G381" s="399"/>
       <c r="H381" s="399" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="I381" s="320" t="s">
         <v>2037</v>
@@ -49056,7 +49056,7 @@
       <c r="K381" s="427"/>
       <c r="L381" s="427"/>
       <c r="M381" s="320" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N381" s="462" t="s">
         <v>2090</v>
@@ -49075,7 +49075,7 @@
         <v>41</v>
       </c>
       <c r="T381" s="399" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="U381" s="399" t="s">
         <v>1909</v>
@@ -49086,7 +49086,7 @@
       <c r="W381" s="416"/>
       <c r="X381" s="416"/>
       <c r="Y381" s="399" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="Z381" s="230"/>
       <c r="AA381" s="416"/>
@@ -49332,7 +49332,7 @@
         <v>434</v>
       </c>
       <c r="C385" s="251" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="D385" s="235"/>
       <c r="E385" s="58"/>
@@ -49691,7 +49691,7 @@
     </row>
     <row r="390" spans="1:43" ht="15.75" customHeight="1">
       <c r="A390" s="277" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="B390" s="14" t="s">
         <v>434</v>
@@ -49906,7 +49906,7 @@
     </row>
     <row r="393" spans="1:43" ht="15.75" customHeight="1">
       <c r="A393" s="394" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="B393" s="393" t="s">
         <v>434</v>
@@ -50072,7 +50072,7 @@
       <c r="K395" s="82"/>
       <c r="L395" s="82"/>
       <c r="M395" s="53" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N395" s="54" t="s">
         <v>2221</v>
@@ -50117,7 +50117,7 @@
     </row>
     <row r="396" spans="1:43" ht="15.75" customHeight="1">
       <c r="A396" s="277" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="B396" s="14" t="s">
         <v>434</v>
@@ -50287,7 +50287,7 @@
       <c r="K398" s="22"/>
       <c r="L398" s="22"/>
       <c r="M398" s="320" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N398" s="73" t="s">
         <v>2264</v>
@@ -50315,7 +50315,7 @@
       <c r="W398" s="29"/>
       <c r="X398" s="29"/>
       <c r="Y398" s="30" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="Z398" s="30"/>
       <c r="AA398" s="30"/>
@@ -50709,7 +50709,7 @@
       <c r="K404" s="22"/>
       <c r="L404" s="22"/>
       <c r="M404" s="449" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N404" s="38" t="s">
         <v>2313</v>
@@ -50922,7 +50922,7 @@
       <c r="K407" s="22"/>
       <c r="L407" s="22"/>
       <c r="M407" s="320" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N407" s="38" t="s">
         <v>2342</v>
@@ -50950,7 +50950,7 @@
       <c r="W407" s="29"/>
       <c r="X407" s="29"/>
       <c r="Y407" s="30" t="s">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="Z407" s="30"/>
       <c r="AA407" s="30"/>
@@ -51210,7 +51210,7 @@
       <c r="K411" s="22"/>
       <c r="L411" s="22"/>
       <c r="M411" s="320" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N411" s="89" t="s">
         <v>2264</v>
@@ -51417,7 +51417,7 @@
       <c r="K414" s="22"/>
       <c r="L414" s="22"/>
       <c r="M414" s="449" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N414" s="54" t="s">
         <v>2393</v>
@@ -51634,7 +51634,7 @@
       <c r="K417" s="22"/>
       <c r="L417" s="22"/>
       <c r="M417" s="33" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="N417" s="89" t="s">
         <v>2425</v>
@@ -51662,7 +51662,7 @@
       <c r="W417" s="29"/>
       <c r="X417" s="29"/>
       <c r="Y417" s="30" t="s">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="Z417" s="30"/>
       <c r="AA417" s="30"/>
@@ -51687,7 +51687,7 @@
     </row>
     <row r="418" spans="1:43" ht="15.75" customHeight="1">
       <c r="A418" s="277" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="B418" s="14" t="s">
         <v>434</v>
@@ -51928,7 +51928,7 @@
       <c r="K421" s="22"/>
       <c r="L421" s="22"/>
       <c r="M421" s="320" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="N421" s="89" t="s">
         <v>2462</v>
@@ -52482,7 +52482,7 @@
     </row>
     <row r="429" spans="1:43" ht="15.75" customHeight="1">
       <c r="A429" s="282" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="B429" s="33" t="s">
         <v>434</v>
@@ -52918,7 +52918,7 @@
     </row>
     <row r="435" spans="1:43" ht="15.75" customHeight="1">
       <c r="A435" s="282" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="B435" s="33" t="s">
         <v>434</v>
@@ -53742,11 +53742,11 @@
       <c r="D446" s="414"/>
       <c r="E446" s="416"/>
       <c r="F446" s="419" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="G446" s="416"/>
       <c r="H446" s="399" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
       <c r="I446" s="399" t="s">
         <v>3107</v>
@@ -53770,7 +53770,7 @@
         <v>41</v>
       </c>
       <c r="T446" s="399" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="U446" s="416"/>
       <c r="V446" s="416"/>
@@ -53782,7 +53782,7 @@
       <c r="AB446" s="416"/>
       <c r="AC446" s="416"/>
       <c r="AD446" s="399" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="AE446" s="32"/>
       <c r="AF446" s="32"/>
@@ -53800,7 +53800,7 @@
     </row>
     <row r="447" spans="1:43" ht="15.75" customHeight="1">
       <c r="A447" s="282" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="B447" s="33" t="s">
         <v>434</v>
@@ -53869,7 +53869,7 @@
     </row>
     <row r="448" spans="1:43" ht="15.75" customHeight="1">
       <c r="A448" s="282" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="B448" s="33" t="s">
         <v>434</v>
@@ -54010,7 +54010,7 @@
         <v>3191</v>
       </c>
       <c r="B450" s="320" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="C450" s="405" t="s">
         <v>171</v>
@@ -54018,11 +54018,11 @@
       <c r="D450" s="414"/>
       <c r="E450" s="416"/>
       <c r="F450" s="419" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
       <c r="G450" s="416"/>
       <c r="H450" s="432" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="I450" s="432" t="s">
         <v>3192</v>
@@ -54030,7 +54030,7 @@
       <c r="J450" s="427"/>
       <c r="K450" s="427"/>
       <c r="L450" s="416" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="M450" s="452" t="s">
         <v>2087</v>
@@ -54048,7 +54048,7 @@
         <v>41</v>
       </c>
       <c r="T450" s="399" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="U450" s="416"/>
       <c r="V450" s="416"/>
@@ -54060,7 +54060,7 @@
       <c r="AB450" s="416"/>
       <c r="AC450" s="416"/>
       <c r="AD450" s="399" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="AE450" s="32"/>
       <c r="AF450" s="32"/>
@@ -54108,7 +54108,7 @@
         <v>3236</v>
       </c>
       <c r="M451" s="95" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="N451" s="54" t="s">
         <v>3237</v>
@@ -54149,7 +54149,7 @@
     </row>
     <row r="452" spans="1:43" ht="15.75" customHeight="1">
       <c r="A452" s="282" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="B452" s="33" t="s">
         <v>434</v>
@@ -54164,7 +54164,7 @@
       </c>
       <c r="G452" s="32"/>
       <c r="H452" s="292" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="I452" s="192" t="s">
         <v>2522</v>
@@ -54352,7 +54352,7 @@
     </row>
     <row r="455" spans="1:43" ht="15.75" customHeight="1">
       <c r="A455" s="287" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="B455" s="33" t="s">
         <v>434</v>
@@ -54427,7 +54427,7 @@
     </row>
     <row r="456" spans="1:43" ht="15.75" customHeight="1">
       <c r="A456" s="282" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="B456" s="33" t="s">
         <v>434</v>
@@ -54494,7 +54494,7 @@
     </row>
     <row r="457" spans="1:43" ht="15.75" customHeight="1">
       <c r="A457" s="193" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
       <c r="B457" s="33" t="s">
         <v>434</v>
@@ -54563,13 +54563,13 @@
     </row>
     <row r="458" spans="1:43" ht="15.75" customHeight="1">
       <c r="A458" s="186" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="B458" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C458" s="403" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="D458" s="235"/>
       <c r="E458" s="58"/>
@@ -54632,7 +54632,7 @@
     </row>
     <row r="459" spans="1:43" ht="15.75" customHeight="1">
       <c r="A459" s="186" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="B459" s="33" t="s">
         <v>434</v>
@@ -54643,11 +54643,11 @@
       <c r="D459" s="235"/>
       <c r="E459" s="58"/>
       <c r="F459" s="47" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="G459" s="32"/>
       <c r="H459" s="192" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="I459" s="217" t="s">
         <v>3107</v>
@@ -54697,7 +54697,7 @@
     </row>
     <row r="460" spans="1:43" ht="15.75" customHeight="1">
       <c r="A460" s="186" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="B460" s="33" t="s">
         <v>434</v>
@@ -54708,11 +54708,11 @@
       <c r="D460" s="235"/>
       <c r="E460" s="58"/>
       <c r="F460" s="290" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="G460" s="32"/>
       <c r="H460" s="192" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="I460" s="32" t="s">
         <v>3107</v>
@@ -54764,7 +54764,7 @@
     </row>
     <row r="461" spans="1:43" ht="15.75" customHeight="1">
       <c r="A461" s="282" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="B461" s="33" t="s">
         <v>434</v>
@@ -54775,11 +54775,11 @@
       <c r="D461" s="235"/>
       <c r="E461" s="58"/>
       <c r="F461" s="290" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="G461" s="32"/>
       <c r="H461" s="206" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="I461" s="192" t="s">
         <v>2562</v>
@@ -54791,11 +54791,11 @@
         <v>2985</v>
       </c>
       <c r="N461" s="38" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="O461" s="465"/>
       <c r="P461" s="473" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="Q461" s="26"/>
       <c r="R461" s="479" t="s">
@@ -54831,7 +54831,7 @@
     </row>
     <row r="462" spans="1:43" ht="15.75" customHeight="1">
       <c r="A462" s="282" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="B462" s="33" t="s">
         <v>434</v>
@@ -54842,11 +54842,11 @@
       <c r="D462" s="235"/>
       <c r="E462" s="58"/>
       <c r="F462" s="47" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="G462" s="32"/>
       <c r="H462" s="206" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="I462" s="192" t="s">
         <v>2562</v>
@@ -54858,7 +54858,7 @@
         <v>2985</v>
       </c>
       <c r="N462" s="38" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="O462" s="38"/>
       <c r="P462" s="25"/>
@@ -54896,7 +54896,7 @@
     </row>
     <row r="463" spans="1:43" ht="15.75" customHeight="1">
       <c r="A463" s="282" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="B463" s="33" t="s">
         <v>434</v>
@@ -54907,11 +54907,11 @@
       <c r="D463" s="235"/>
       <c r="E463" s="58"/>
       <c r="F463" s="16" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="G463" s="32"/>
       <c r="H463" s="206" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="I463" s="192" t="s">
         <v>2562</v>
@@ -54919,19 +54919,19 @@
       <c r="J463" s="35"/>
       <c r="K463" s="109"/>
       <c r="L463" s="109" t="s">
+        <v>3475</v>
+      </c>
+      <c r="M463" s="137" t="s">
         <v>3476</v>
       </c>
-      <c r="M463" s="137" t="s">
+      <c r="N463" s="54" t="s">
         <v>3477</v>
-      </c>
-      <c r="N463" s="54" t="s">
-        <v>3478</v>
       </c>
       <c r="O463" s="54"/>
       <c r="P463" s="55"/>
       <c r="Q463" s="56"/>
       <c r="R463" s="324" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="S463" s="137" t="s">
         <v>41</v>
@@ -54963,7 +54963,7 @@
     </row>
     <row r="464" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A464" s="186" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="B464" s="33" t="s">
         <v>434</v>
@@ -54974,11 +54974,11 @@
       <c r="D464" s="235"/>
       <c r="E464" s="58"/>
       <c r="F464" s="290" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="G464" s="32"/>
       <c r="H464" s="206" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="I464" s="192" t="s">
         <v>2562</v>
@@ -54990,7 +54990,7 @@
         <v>253</v>
       </c>
       <c r="N464" s="54" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="O464" s="54"/>
       <c r="P464" s="55"/>
@@ -55028,7 +55028,7 @@
     </row>
     <row r="465" spans="1:43" ht="15.75" customHeight="1">
       <c r="A465" s="282" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="B465" s="33" t="s">
         <v>434</v>
@@ -55039,14 +55039,14 @@
       <c r="D465" s="235"/>
       <c r="E465" s="58"/>
       <c r="F465" s="290" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="G465" s="32"/>
       <c r="H465" s="192" t="s">
+        <v>3495</v>
+      </c>
+      <c r="I465" s="32" t="s">
         <v>3496</v>
-      </c>
-      <c r="I465" s="32" t="s">
-        <v>3497</v>
       </c>
       <c r="J465" s="22" t="s">
         <v>3008</v>
@@ -55095,7 +55095,7 @@
     </row>
     <row r="466" spans="1:43" ht="15.75" customHeight="1">
       <c r="A466" s="186" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="B466" s="95" t="s">
         <v>2294</v>
@@ -55106,13 +55106,13 @@
       <c r="D466" s="235"/>
       <c r="E466" s="58"/>
       <c r="F466" s="16" t="s">
+        <v>3511</v>
+      </c>
+      <c r="G466" s="32" t="s">
         <v>3512</v>
       </c>
-      <c r="G466" s="32" t="s">
+      <c r="H466" s="206" t="s">
         <v>3513</v>
-      </c>
-      <c r="H466" s="206" t="s">
-        <v>3514</v>
       </c>
       <c r="I466" s="32" t="s">
         <v>2562</v>
@@ -55120,13 +55120,13 @@
       <c r="J466" s="35"/>
       <c r="K466" s="22"/>
       <c r="L466" s="22" t="s">
+        <v>3514</v>
+      </c>
+      <c r="M466" s="209" t="s">
         <v>3515</v>
       </c>
-      <c r="M466" s="209" t="s">
+      <c r="N466" s="54" t="s">
         <v>3516</v>
-      </c>
-      <c r="N466" s="54" t="s">
-        <v>3517</v>
       </c>
       <c r="O466" s="54"/>
       <c r="P466" s="55"/>
@@ -55139,15 +55139,15 @@
       </c>
       <c r="T466" s="21"/>
       <c r="U466" s="28" t="s">
+        <v>3503</v>
+      </c>
+      <c r="V466" s="28" t="s">
         <v>3504</v>
-      </c>
-      <c r="V466" s="28" t="s">
-        <v>3505</v>
       </c>
       <c r="W466" s="113"/>
       <c r="X466" s="113"/>
       <c r="Y466" s="30" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="Z466" s="30"/>
       <c r="AA466" s="30"/>
@@ -55170,7 +55170,7 @@
     </row>
     <row r="467" spans="1:43" ht="15.75" customHeight="1">
       <c r="A467" s="186" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="B467" s="33" t="s">
         <v>434</v>
@@ -55181,11 +55181,11 @@
       <c r="D467" s="235"/>
       <c r="E467" s="58"/>
       <c r="F467" s="16" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="G467" s="32"/>
       <c r="H467" s="206" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="I467" s="187" t="s">
         <v>2562</v>
@@ -55197,17 +55197,17 @@
         <v>2985</v>
       </c>
       <c r="N467" s="38" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="O467" s="38"/>
       <c r="P467" s="74" t="s">
+        <v>3536</v>
+      </c>
+      <c r="Q467" s="26" t="s">
         <v>3537</v>
       </c>
-      <c r="Q467" s="26" t="s">
-        <v>3538</v>
-      </c>
       <c r="R467" s="397" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="S467" s="77" t="s">
         <v>41</v>
@@ -55239,7 +55239,7 @@
     </row>
     <row r="468" spans="1:43" ht="15.75" customHeight="1">
       <c r="A468" s="186" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="B468" s="33" t="s">
         <v>434</v>
@@ -55250,17 +55250,17 @@
       <c r="D468" s="235"/>
       <c r="E468" s="58"/>
       <c r="F468" s="290" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G468" s="32"/>
       <c r="H468" s="206" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="I468" s="32" t="s">
         <v>2134</v>
       </c>
       <c r="J468" s="22" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="K468" s="22"/>
       <c r="L468" s="22"/>
@@ -55268,7 +55268,7 @@
         <v>137</v>
       </c>
       <c r="N468" s="54" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="O468" s="54"/>
       <c r="P468" s="55"/>
@@ -55306,7 +55306,7 @@
     </row>
     <row r="469" spans="1:43" ht="15.75" customHeight="1">
       <c r="A469" s="186" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="B469" s="33" t="s">
         <v>434</v>
@@ -55317,11 +55317,11 @@
       <c r="D469" s="235"/>
       <c r="E469" s="58"/>
       <c r="F469" s="47" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="G469" s="32"/>
       <c r="H469" s="206" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="I469" s="192" t="s">
         <v>2562</v>
@@ -55330,10 +55330,10 @@
       <c r="K469" s="22"/>
       <c r="L469" s="22"/>
       <c r="M469" s="95" t="s">
+        <v>3593</v>
+      </c>
+      <c r="N469" s="89" t="s">
         <v>3594</v>
-      </c>
-      <c r="N469" s="89" t="s">
-        <v>3595</v>
       </c>
       <c r="O469" s="470"/>
       <c r="P469" s="70"/>
@@ -55371,7 +55371,7 @@
     </row>
     <row r="470" spans="1:43" ht="15.75" customHeight="1">
       <c r="A470" s="186" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="B470" s="33" t="s">
         <v>434</v>
@@ -55382,16 +55382,16 @@
       <c r="D470" s="235"/>
       <c r="E470" s="58"/>
       <c r="F470" s="290" t="s">
+        <v>3596</v>
+      </c>
+      <c r="G470" s="398" t="s">
         <v>3597</v>
       </c>
-      <c r="G470" s="398" t="s">
+      <c r="H470" s="48" t="s">
         <v>3598</v>
       </c>
-      <c r="H470" s="48" t="s">
+      <c r="I470" s="187" t="s">
         <v>3599</v>
-      </c>
-      <c r="I470" s="187" t="s">
-        <v>3600</v>
       </c>
       <c r="J470" s="22"/>
       <c r="K470" s="22"/>
@@ -55400,14 +55400,14 @@
         <v>804</v>
       </c>
       <c r="N470" s="136" t="s">
+        <v>3600</v>
+      </c>
+      <c r="O470" s="54" t="s">
         <v>3601</v>
-      </c>
-      <c r="O470" s="54" t="s">
-        <v>3602</v>
       </c>
       <c r="P470" s="55"/>
       <c r="Q470" s="56" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="R470" s="99" t="s">
         <v>1107</v>
@@ -55416,7 +55416,7 @@
         <v>41</v>
       </c>
       <c r="T470" s="121" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="U470" s="122"/>
       <c r="V470" s="122"/>
@@ -55444,7 +55444,7 @@
     </row>
     <row r="471" spans="1:43" ht="15.75" customHeight="1">
       <c r="A471" s="296" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="B471" s="95" t="s">
         <v>2294</v>
@@ -55455,16 +55455,16 @@
       <c r="D471" s="236"/>
       <c r="E471" s="67"/>
       <c r="F471" s="16" t="s">
+        <v>3632</v>
+      </c>
+      <c r="G471" s="398" t="s">
         <v>3633</v>
       </c>
-      <c r="G471" s="398" t="s">
+      <c r="H471" s="32" t="s">
         <v>3634</v>
       </c>
-      <c r="H471" s="32" t="s">
+      <c r="I471" s="187" t="s">
         <v>3635</v>
-      </c>
-      <c r="I471" s="187" t="s">
-        <v>3636</v>
       </c>
       <c r="J471" s="82"/>
       <c r="K471" s="82"/>
@@ -55473,14 +55473,14 @@
         <v>2496</v>
       </c>
       <c r="N471" s="89" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="O471" s="89"/>
       <c r="P471" s="74" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="Q471" s="56" t="s">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="R471" s="117" t="s">
         <v>387</v>
@@ -55517,10 +55517,10 @@
     </row>
     <row r="472" spans="1:43" ht="15.75" customHeight="1">
       <c r="A472" s="297" t="s">
+        <v>3664</v>
+      </c>
+      <c r="B472" s="298" t="s">
         <v>3665</v>
-      </c>
-      <c r="B472" s="298" t="s">
-        <v>3666</v>
       </c>
       <c r="C472" s="299" t="s">
         <v>171</v>
@@ -55528,16 +55528,16 @@
       <c r="D472" s="300"/>
       <c r="E472" s="301"/>
       <c r="F472" s="302" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="G472" s="430" t="s">
         <v>2296</v>
       </c>
       <c r="H472" s="302" t="s">
+        <v>3667</v>
+      </c>
+      <c r="I472" s="303" t="s">
         <v>3668</v>
-      </c>
-      <c r="I472" s="303" t="s">
-        <v>3669</v>
       </c>
       <c r="J472" s="441" t="s">
         <v>2283</v>
@@ -55548,13 +55548,13 @@
         <v>1605</v>
       </c>
       <c r="N472" s="305" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="O472" s="305"/>
       <c r="P472" s="306"/>
       <c r="Q472" s="307"/>
       <c r="R472" s="308" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="S472" s="308" t="s">
         <v>41</v>
@@ -55586,43 +55586,43 @@
     </row>
     <row r="473" spans="1:43" ht="15.75" customHeight="1">
       <c r="A473" s="395" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="B473" s="95" t="s">
         <v>2294</v>
       </c>
       <c r="C473" s="249" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="D473" s="235"/>
       <c r="E473" s="58"/>
       <c r="F473" s="421" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="G473" s="398"/>
       <c r="H473" s="429" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="I473" s="435" t="s">
         <v>2522</v>
       </c>
       <c r="J473" s="104" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="K473" s="104"/>
       <c r="L473" s="104"/>
       <c r="M473" s="453" t="s">
+        <v>3675</v>
+      </c>
+      <c r="N473" s="466" t="s">
         <v>3676</v>
       </c>
-      <c r="N473" s="466" t="s">
+      <c r="O473" s="463" t="s">
         <v>3677</v>
-      </c>
-      <c r="O473" s="463" t="s">
-        <v>3678</v>
       </c>
       <c r="P473" s="114"/>
       <c r="Q473" s="123" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="R473" s="32" t="s">
         <v>523</v>
@@ -55636,13 +55636,13 @@
       <c r="W473" s="130"/>
       <c r="X473" s="130"/>
       <c r="Y473" s="103" t="s">
+        <v>3679</v>
+      </c>
+      <c r="Z473" s="103" t="s">
         <v>3680</v>
       </c>
-      <c r="Z473" s="103" t="s">
+      <c r="AA473" s="103" t="s">
         <v>3681</v>
-      </c>
-      <c r="AA473" s="103" t="s">
-        <v>3682</v>
       </c>
       <c r="AB473" s="110"/>
       <c r="AC473" s="398"/>
@@ -55663,47 +55663,47 @@
     </row>
     <row r="474" spans="1:43" ht="15.75" customHeight="1">
       <c r="A474" s="288" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="B474" s="95" t="s">
         <v>434</v>
       </c>
       <c r="C474" s="256" t="s">
+        <v>3688</v>
+      </c>
+      <c r="D474" s="234" t="s">
         <v>3689</v>
       </c>
-      <c r="D474" s="234" t="s">
+      <c r="E474" s="58" t="s">
         <v>3690</v>
       </c>
-      <c r="E474" s="58" t="s">
+      <c r="F474" s="223" t="s">
         <v>3691</v>
       </c>
-      <c r="F474" s="223" t="s">
+      <c r="G474" s="424" t="s">
+        <v>3688</v>
+      </c>
+      <c r="H474" s="207" t="s">
         <v>3692</v>
       </c>
-      <c r="G474" s="424" t="s">
-        <v>3689</v>
-      </c>
-      <c r="H474" s="207" t="s">
+      <c r="I474" s="187" t="s">
         <v>3693</v>
-      </c>
-      <c r="I474" s="187" t="s">
-        <v>3694</v>
       </c>
       <c r="J474" s="22"/>
       <c r="K474" s="22"/>
       <c r="L474" s="22"/>
       <c r="M474" s="137" t="s">
+        <v>3694</v>
+      </c>
+      <c r="N474" s="38" t="s">
         <v>3695</v>
-      </c>
-      <c r="N474" s="38" t="s">
-        <v>3696</v>
       </c>
       <c r="O474" s="38"/>
       <c r="P474" s="25" t="s">
+        <v>3696</v>
+      </c>
+      <c r="Q474" s="56" t="s">
         <v>3697</v>
-      </c>
-      <c r="Q474" s="56" t="s">
-        <v>3698</v>
       </c>
       <c r="R474" s="66" t="s">
         <v>2790</v>
@@ -55738,7 +55738,7 @@
     </row>
     <row r="475" spans="1:43" ht="15.75" customHeight="1">
       <c r="A475" s="296" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="B475" s="95" t="s">
         <v>434</v>
@@ -55749,16 +55749,16 @@
       <c r="D475" s="236"/>
       <c r="E475" s="67"/>
       <c r="F475" s="290" t="s">
+        <v>3715</v>
+      </c>
+      <c r="G475" s="48" t="s">
         <v>3716</v>
       </c>
-      <c r="G475" s="48" t="s">
+      <c r="H475" s="48" t="s">
         <v>3717</v>
       </c>
-      <c r="H475" s="48" t="s">
+      <c r="I475" s="187" t="s">
         <v>3718</v>
-      </c>
-      <c r="I475" s="187" t="s">
-        <v>3719</v>
       </c>
       <c r="J475" s="22"/>
       <c r="K475" s="22"/>
@@ -55767,14 +55767,14 @@
         <v>2496</v>
       </c>
       <c r="N475" s="54" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="O475" s="54"/>
       <c r="P475" s="74" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="Q475" s="56" t="s">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="R475" s="48" t="s">
         <v>2995</v>
@@ -55809,36 +55809,36 @@
     </row>
     <row r="476" spans="1:43" ht="15.75" customHeight="1">
       <c r="A476" s="186" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="B476" s="95" t="s">
         <v>2294</v>
       </c>
       <c r="C476" s="295" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="D476" s="235"/>
       <c r="E476" s="58"/>
       <c r="F476" s="290" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="G476" s="32"/>
       <c r="H476" s="48" t="s">
+        <v>3731</v>
+      </c>
+      <c r="I476" s="115" t="s">
         <v>3732</v>
-      </c>
-      <c r="I476" s="115" t="s">
-        <v>3733</v>
       </c>
       <c r="J476" s="22"/>
       <c r="K476" s="22"/>
       <c r="L476" s="22" t="s">
+        <v>3733</v>
+      </c>
+      <c r="M476" s="398" t="s">
         <v>3734</v>
       </c>
-      <c r="M476" s="398" t="s">
+      <c r="N476" s="38" t="s">
         <v>3735</v>
-      </c>
-      <c r="N476" s="38" t="s">
-        <v>3736</v>
       </c>
       <c r="O476" s="38"/>
       <c r="P476" s="25"/>
@@ -55876,7 +55876,7 @@
     </row>
     <row r="477" spans="1:43" ht="15.75" customHeight="1">
       <c r="A477" s="186" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
       <c r="B477" s="95" t="s">
         <v>2294</v>
@@ -55887,13 +55887,13 @@
       <c r="D477" s="236"/>
       <c r="E477" s="67"/>
       <c r="F477" s="290" t="s">
+        <v>3737</v>
+      </c>
+      <c r="G477" s="32" t="s">
         <v>3738</v>
       </c>
-      <c r="G477" s="32" t="s">
+      <c r="H477" s="48" t="s">
         <v>3739</v>
-      </c>
-      <c r="H477" s="48" t="s">
-        <v>3740</v>
       </c>
       <c r="I477" s="187" t="s">
         <v>2654</v>
@@ -55907,7 +55907,7 @@
         <v>2969</v>
       </c>
       <c r="N477" s="65" t="s">
-        <v>3741</v>
+        <v>3740</v>
       </c>
       <c r="O477" s="38"/>
       <c r="P477" s="25"/>
@@ -55945,7 +55945,7 @@
     </row>
     <row r="478" spans="1:43" ht="15.75" customHeight="1">
       <c r="A478" s="186" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="B478" s="95" t="s">
         <v>2294</v>
@@ -55956,11 +55956,11 @@
       <c r="D478" s="235"/>
       <c r="E478" s="58"/>
       <c r="F478" s="328" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
       <c r="G478" s="32"/>
       <c r="H478" s="206" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="I478" s="192" t="s">
         <v>2522</v>
@@ -55974,7 +55974,7 @@
         <v>804</v>
       </c>
       <c r="N478" s="38" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
       <c r="O478" s="38" t="s">
         <v>806</v>
@@ -55996,10 +55996,10 @@
       <c r="X478" s="29"/>
       <c r="Y478" s="30"/>
       <c r="Z478" s="30" t="s">
+        <v>3744</v>
+      </c>
+      <c r="AA478" s="30" t="s">
         <v>3745</v>
-      </c>
-      <c r="AA478" s="30" t="s">
-        <v>3746</v>
       </c>
       <c r="AB478" s="41"/>
       <c r="AC478" s="32"/>
@@ -56020,33 +56020,33 @@
     </row>
     <row r="479" spans="1:43" ht="15.75" customHeight="1">
       <c r="A479" s="281" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="B479" s="95" t="s">
         <v>2294</v>
       </c>
       <c r="C479" s="249" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="D479" s="235"/>
       <c r="E479" s="138"/>
       <c r="F479" s="47" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="G479" s="32"/>
       <c r="H479" s="48" t="s">
+        <v>3784</v>
+      </c>
+      <c r="I479" s="115" t="s">
         <v>3785</v>
       </c>
-      <c r="I479" s="115" t="s">
+      <c r="J479" s="22" t="s">
         <v>3786</v>
-      </c>
-      <c r="J479" s="22" t="s">
-        <v>3787</v>
       </c>
       <c r="K479" s="22"/>
       <c r="L479" s="22"/>
       <c r="M479" s="137" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="N479" s="54" t="s">
         <v>2137</v>
@@ -56061,7 +56061,7 @@
         <v>41</v>
       </c>
       <c r="T479" s="21" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="U479" s="28"/>
       <c r="V479" s="28"/>
@@ -56089,7 +56089,7 @@
     </row>
     <row r="480" spans="1:43" ht="54" customHeight="1">
       <c r="A480" s="48" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="B480" s="95" t="s">
         <v>2294</v>
@@ -56100,13 +56100,13 @@
       <c r="D480" s="236"/>
       <c r="E480" s="58"/>
       <c r="F480" s="47" t="s">
+        <v>3790</v>
+      </c>
+      <c r="G480" s="32" t="s">
         <v>3791</v>
       </c>
-      <c r="G480" s="32" t="s">
+      <c r="H480" s="48" t="s">
         <v>3792</v>
-      </c>
-      <c r="H480" s="48" t="s">
-        <v>3793</v>
       </c>
       <c r="I480" s="32" t="s">
         <v>2654</v>
@@ -56120,7 +56120,7 @@
         <v>2227</v>
       </c>
       <c r="N480" s="65" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="O480" s="38"/>
       <c r="P480" s="25"/>
@@ -56132,7 +56132,7 @@
         <v>41</v>
       </c>
       <c r="T480" s="21" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="U480" s="28"/>
       <c r="V480" s="28"/>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amleth/Xobpord/Xobpord3/Dropbox/CNRS/iremus/data-iremus/in/mercure-galant-sources-github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9282B354-219D-1348-93EB-8AB698FE8357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BD78B4-50ED-AF44-9951-A8A2E6AC12AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2020" yWindow="-20320" windowWidth="35000" windowHeight="20320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -18715,7 +18715,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="529">
+  <cellXfs count="518">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -19847,24 +19847,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="129" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -19872,7 +19869,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="122" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="122" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="131" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -19885,13 +19882,10 @@
     <xf numFmtId="0" fontId="123" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="118" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -19900,18 +19894,15 @@
     <xf numFmtId="0" fontId="110" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="110" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -19921,16 +19912,16 @@
     <xf numFmtId="0" fontId="85" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -19940,26 +19931,23 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -19971,7 +19959,7 @@
     <xf numFmtId="0" fontId="76" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -19998,102 +19986,83 @@
     <xf numFmtId="0" fontId="137" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="133" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="133" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -20101,7 +20070,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -20113,23 +20082,23 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -20148,7 +20117,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20166,7 +20135,7 @@
     <xf numFmtId="0" fontId="48" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -20176,7 +20145,7 @@
     <xf numFmtId="0" fontId="47" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20195,7 +20164,7 @@
     <xf numFmtId="0" fontId="18" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="87" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20679,7 +20648,7 @@
       <c r="O3" s="38"/>
       <c r="P3" s="25"/>
       <c r="Q3" s="26"/>
-      <c r="R3" s="481" t="s">
+      <c r="R3" s="94" t="s">
         <v>1107</v>
       </c>
       <c r="S3" s="77" t="s">
@@ -20754,7 +20723,7 @@
       <c r="O4" s="54"/>
       <c r="P4" s="55"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="457" t="s">
+      <c r="R4" s="339" t="s">
         <v>139</v>
       </c>
       <c r="S4" s="32" t="s">
@@ -20837,7 +20806,7 @@
       <c r="Q5" s="56" t="s">
         <v>366</v>
       </c>
-      <c r="R5" s="455" t="s">
+      <c r="R5" s="449" t="s">
         <v>367</v>
       </c>
       <c r="S5" s="32" t="s">
@@ -20912,7 +20881,7 @@
       <c r="O6" s="54"/>
       <c r="P6" s="55"/>
       <c r="Q6" s="56"/>
-      <c r="R6" s="434" t="s">
+      <c r="R6" s="338" t="s">
         <v>395</v>
       </c>
       <c r="S6" s="32" t="s">
@@ -20989,7 +20958,7 @@
       <c r="Q7" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="R7" s="487" t="s">
+      <c r="R7" s="476" t="s">
         <v>80</v>
       </c>
       <c r="S7" s="40" t="s">
@@ -21000,10 +20969,10 @@
       </c>
       <c r="U7" s="28"/>
       <c r="V7" s="28"/>
-      <c r="W7" s="512" t="s">
+      <c r="W7" s="501" t="s">
         <v>110</v>
       </c>
-      <c r="X7" s="512" t="s">
+      <c r="X7" s="501" t="s">
         <v>111</v>
       </c>
       <c r="Y7" s="61" t="s">
@@ -21035,7 +21004,7 @@
       <c r="B8" s="95" t="s">
         <v>2294</v>
       </c>
-      <c r="C8" s="402" t="s">
+      <c r="C8" s="401" t="s">
         <v>3977</v>
       </c>
       <c r="D8" s="235"/>
@@ -21064,7 +21033,7 @@
       <c r="O8" s="322"/>
       <c r="P8" s="126"/>
       <c r="Q8" s="56"/>
-      <c r="R8" s="488" t="s">
+      <c r="R8" s="477" t="s">
         <v>3710</v>
       </c>
       <c r="S8" s="77" t="s">
@@ -21307,7 +21276,7 @@
       <c r="O11" s="38"/>
       <c r="P11" s="25"/>
       <c r="Q11" s="26"/>
-      <c r="R11" s="481" t="s">
+      <c r="R11" s="94" t="s">
         <v>1107</v>
       </c>
       <c r="S11" s="32" t="s">
@@ -21376,13 +21345,13 @@
       <c r="M12" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="N12" s="463" t="s">
+      <c r="N12" s="455" t="s">
         <v>2306</v>
       </c>
-      <c r="O12" s="463"/>
+      <c r="O12" s="455"/>
       <c r="P12" s="114"/>
       <c r="Q12" s="123"/>
-      <c r="R12" s="398" t="s">
+      <c r="R12" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S12" s="32" t="s">
@@ -21465,7 +21434,7 @@
       <c r="Q13" s="26" t="s">
         <v>1172</v>
       </c>
-      <c r="R13" s="480" t="s">
+      <c r="R13" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S13" s="32" t="s">
@@ -21544,7 +21513,7 @@
       <c r="Q14" s="26" t="s">
         <v>2120</v>
       </c>
-      <c r="R14" s="480" t="s">
+      <c r="R14" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S14" s="32" t="s">
@@ -21704,7 +21673,7 @@
       <c r="Q16" s="129" t="s">
         <v>2516</v>
       </c>
-      <c r="R16" s="470" t="s">
+      <c r="R16" s="461" t="s">
         <v>2517</v>
       </c>
       <c r="S16" s="77" t="s">
@@ -21862,7 +21831,7 @@
       <c r="O18" s="38"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="56"/>
-      <c r="R18" s="479" t="s">
+      <c r="R18" s="470" t="s">
         <v>80</v>
       </c>
       <c r="S18" s="77" t="s">
@@ -21933,7 +21902,7 @@
       <c r="O19" s="38"/>
       <c r="P19" s="25"/>
       <c r="Q19" s="56"/>
-      <c r="R19" s="479" t="s">
+      <c r="R19" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S19" s="77" t="s">
@@ -21984,7 +21953,7 @@
       <c r="C20" s="263" t="s">
         <v>3813</v>
       </c>
-      <c r="D20" s="414"/>
+      <c r="D20" s="411"/>
       <c r="E20" s="58" t="s">
         <v>2614</v>
       </c>
@@ -22034,7 +22003,7 @@
       </c>
       <c r="Z20" s="30"/>
       <c r="AA20" s="30"/>
-      <c r="AB20" s="519" t="s">
+      <c r="AB20" s="508" t="s">
         <v>2622</v>
       </c>
       <c r="AC20" s="32"/>
@@ -22401,7 +22370,7 @@
       <c r="O25" s="38"/>
       <c r="P25" s="25"/>
       <c r="Q25" s="56"/>
-      <c r="R25" s="455" t="s">
+      <c r="R25" s="449" t="s">
         <v>2672</v>
       </c>
       <c r="S25" s="137" t="s">
@@ -22474,7 +22443,7 @@
       <c r="O26" s="38"/>
       <c r="P26" s="25"/>
       <c r="Q26" s="56"/>
-      <c r="R26" s="479" t="s">
+      <c r="R26" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S26" s="77" t="s">
@@ -22606,7 +22575,7 @@
       </c>
       <c r="D28" s="247"/>
       <c r="E28" s="190"/>
-      <c r="F28" s="420" t="s">
+      <c r="F28" s="417" t="s">
         <v>2698</v>
       </c>
       <c r="G28" s="186"/>
@@ -22717,11 +22686,11 @@
       <c r="S29" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="T29" s="496"/>
-      <c r="U29" s="503" t="s">
+      <c r="T29" s="485"/>
+      <c r="U29" s="492" t="s">
         <v>1096</v>
       </c>
-      <c r="V29" s="509" t="s">
+      <c r="V29" s="498" t="s">
         <v>2712</v>
       </c>
       <c r="W29" s="29" t="s">
@@ -22730,7 +22699,7 @@
       <c r="X29" s="29" t="s">
         <v>2246</v>
       </c>
-      <c r="Y29" s="515" t="s">
+      <c r="Y29" s="504" t="s">
         <v>2713</v>
       </c>
       <c r="Z29" s="200"/>
@@ -22804,9 +22773,9 @@
       <c r="S30" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="T30" s="496"/>
-      <c r="U30" s="503"/>
-      <c r="V30" s="503"/>
+      <c r="T30" s="485"/>
+      <c r="U30" s="492"/>
+      <c r="V30" s="492"/>
       <c r="W30" s="29" t="s">
         <v>2245</v>
       </c>
@@ -23122,7 +23091,7 @@
       <c r="AA34" s="30"/>
       <c r="AB34" s="41"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="428"/>
+      <c r="AD34" s="425"/>
       <c r="AE34" s="32"/>
       <c r="AF34" s="32"/>
       <c r="AG34" s="32"/>
@@ -23330,7 +23299,7 @@
       <c r="N37" s="54" t="s">
         <v>2826</v>
       </c>
-      <c r="O37" s="463"/>
+      <c r="O37" s="455"/>
       <c r="P37" s="114"/>
       <c r="Q37" s="56"/>
       <c r="R37" s="117" t="s">
@@ -23403,7 +23372,7 @@
       <c r="N38" s="54" t="s">
         <v>2833</v>
       </c>
-      <c r="O38" s="463"/>
+      <c r="O38" s="455"/>
       <c r="P38" s="114"/>
       <c r="Q38" s="56"/>
       <c r="R38" s="32" t="s">
@@ -23454,7 +23423,7 @@
       <c r="B39" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C39" s="407" t="s">
+      <c r="C39" s="336" t="s">
         <v>2838</v>
       </c>
       <c r="D39" s="235"/>
@@ -23856,7 +23825,7 @@
         <v>2882</v>
       </c>
       <c r="G44" s="32"/>
-      <c r="H44" s="431" t="s">
+      <c r="H44" s="428" t="s">
         <v>2883</v>
       </c>
       <c r="I44" s="187" t="s">
@@ -24161,7 +24130,7 @@
       <c r="F48" s="47" t="s">
         <v>2922</v>
       </c>
-      <c r="G48" s="398"/>
+      <c r="G48" s="39"/>
       <c r="H48" s="206" t="s">
         <v>2923</v>
       </c>
@@ -24173,13 +24142,13 @@
       <c r="L48" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="M48" s="453" t="s">
+      <c r="M48" s="331" t="s">
         <v>1105</v>
       </c>
       <c r="N48" s="38" t="s">
         <v>2924</v>
       </c>
-      <c r="O48" s="465" t="s">
+      <c r="O48" s="322" t="s">
         <v>2119</v>
       </c>
       <c r="P48" s="59"/>
@@ -24206,10 +24175,10 @@
       <c r="AA48" s="30" t="s">
         <v>2927</v>
       </c>
-      <c r="AB48" s="520" t="s">
+      <c r="AB48" s="509" t="s">
         <v>2928</v>
       </c>
-      <c r="AC48" s="398"/>
+      <c r="AC48" s="39"/>
       <c r="AD48" s="21"/>
       <c r="AE48" s="32"/>
       <c r="AF48" s="32"/>
@@ -24258,7 +24227,7 @@
       <c r="N49" s="54" t="s">
         <v>2932</v>
       </c>
-      <c r="O49" s="463" t="s">
+      <c r="O49" s="455" t="s">
         <v>2933</v>
       </c>
       <c r="P49" s="114"/>
@@ -24337,7 +24306,7 @@
       <c r="N50" s="54" t="s">
         <v>2940</v>
       </c>
-      <c r="O50" s="463" t="s">
+      <c r="O50" s="455" t="s">
         <v>2941</v>
       </c>
       <c r="P50" s="114"/>
@@ -24414,7 +24383,7 @@
       </c>
       <c r="K51" s="104"/>
       <c r="L51" s="104"/>
-      <c r="M51" s="456" t="s">
+      <c r="M51" s="450" t="s">
         <v>542</v>
       </c>
       <c r="N51" s="54" t="s">
@@ -25069,7 +25038,7 @@
       <c r="AA59" s="389" t="s">
         <v>3060</v>
       </c>
-      <c r="AB59" s="522"/>
+      <c r="AB59" s="511"/>
       <c r="AC59" s="16" t="s">
         <v>3061</v>
       </c>
@@ -25433,7 +25402,7 @@
       <c r="N64" s="54" t="s">
         <v>3102</v>
       </c>
-      <c r="O64" s="469" t="s">
+      <c r="O64" s="460" t="s">
         <v>38</v>
       </c>
       <c r="P64" s="114"/>
@@ -25575,7 +25544,7 @@
       <c r="F66" s="47" t="s">
         <v>3117</v>
       </c>
-      <c r="G66" s="398"/>
+      <c r="G66" s="39"/>
       <c r="H66" s="206" t="s">
         <v>3118</v>
       </c>
@@ -25668,7 +25637,7 @@
       <c r="N67" s="54" t="s">
         <v>3128</v>
       </c>
-      <c r="O67" s="466" t="s">
+      <c r="O67" s="457" t="s">
         <v>3129</v>
       </c>
       <c r="P67" s="114"/>
@@ -25749,7 +25718,7 @@
       <c r="N68" s="38" t="s">
         <v>3139</v>
       </c>
-      <c r="O68" s="465" t="s">
+      <c r="O68" s="322" t="s">
         <v>3140</v>
       </c>
       <c r="P68" s="59" t="s">
@@ -25773,7 +25742,7 @@
       <c r="X68" s="29" t="s">
         <v>2246</v>
       </c>
-      <c r="Y68" s="516" t="s">
+      <c r="Y68" s="505" t="s">
         <v>3143</v>
       </c>
       <c r="Z68" s="30" t="s">
@@ -25809,7 +25778,7 @@
       <c r="C69" s="374"/>
       <c r="D69" s="375"/>
       <c r="E69" s="376"/>
-      <c r="F69" s="426" t="s">
+      <c r="F69" s="423" t="s">
         <v>4006</v>
       </c>
       <c r="G69" s="377"/>
@@ -25821,7 +25790,7 @@
       </c>
       <c r="J69" s="379"/>
       <c r="K69" s="379"/>
-      <c r="L69" s="447"/>
+      <c r="L69" s="443"/>
       <c r="M69" s="380" t="s">
         <v>3157</v>
       </c>
@@ -25847,11 +25816,11 @@
       <c r="Y69" s="385" t="s">
         <v>4008</v>
       </c>
-      <c r="Z69" s="518" t="s">
+      <c r="Z69" s="507" t="s">
         <v>4007</v>
       </c>
       <c r="AA69" s="386"/>
-      <c r="AB69" s="526"/>
+      <c r="AB69" s="515"/>
       <c r="AC69" s="377"/>
       <c r="AD69" s="382"/>
       <c r="AE69" s="32"/>
@@ -26034,7 +26003,7 @@
       </c>
       <c r="D72" s="235"/>
       <c r="E72" s="58"/>
-      <c r="F72" s="425" t="s">
+      <c r="F72" s="422" t="s">
         <v>3219</v>
       </c>
       <c r="G72" s="32"/>
@@ -26082,7 +26051,7 @@
       <c r="AA72" s="30" t="s">
         <v>3224</v>
       </c>
-      <c r="AB72" s="522"/>
+      <c r="AB72" s="511"/>
       <c r="AC72" s="32"/>
       <c r="AD72" s="21"/>
       <c r="AE72" s="32"/>
@@ -26209,10 +26178,10 @@
       <c r="N74" s="38" t="s">
         <v>3177</v>
       </c>
-      <c r="O74" s="465"/>
+      <c r="O74" s="322"/>
       <c r="P74" s="114"/>
       <c r="Q74" s="123"/>
-      <c r="R74" s="479" t="s">
+      <c r="R74" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S74" s="77" t="s">
@@ -26261,7 +26230,7 @@
       <c r="C75" s="260" t="s">
         <v>3182</v>
       </c>
-      <c r="D75" s="413"/>
+      <c r="D75" s="337"/>
       <c r="E75" s="58"/>
       <c r="F75" s="47" t="s">
         <v>3183</v>
@@ -26498,7 +26467,7 @@
       <c r="C78" s="255" t="s">
         <v>171</v>
       </c>
-      <c r="D78" s="413"/>
+      <c r="D78" s="337"/>
       <c r="E78" s="138"/>
       <c r="F78" s="290" t="s">
         <v>3212</v>
@@ -26522,7 +26491,7 @@
       <c r="O78" s="54"/>
       <c r="P78" s="55"/>
       <c r="Q78" s="56"/>
-      <c r="R78" s="479" t="s">
+      <c r="R78" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S78" s="77" t="s">
@@ -26599,7 +26568,7 @@
       <c r="O79" s="54"/>
       <c r="P79" s="55"/>
       <c r="Q79" s="56"/>
-      <c r="R79" s="479" t="s">
+      <c r="R79" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S79" s="77" t="s">
@@ -26729,7 +26698,7 @@
       <c r="C81" s="255" t="s">
         <v>171</v>
       </c>
-      <c r="D81" s="411"/>
+      <c r="D81" s="409"/>
       <c r="E81" s="138"/>
       <c r="F81" s="290" t="s">
         <v>3267</v>
@@ -26779,7 +26748,7 @@
       </c>
       <c r="Z81" s="30"/>
       <c r="AA81" s="30"/>
-      <c r="AB81" s="519" t="s">
+      <c r="AB81" s="508" t="s">
         <v>3274</v>
       </c>
       <c r="AC81" s="32"/>
@@ -26821,10 +26790,10 @@
         <v>2562</v>
       </c>
       <c r="J82" s="22"/>
-      <c r="K82" s="446" t="s">
+      <c r="K82" s="442" t="s">
         <v>34</v>
       </c>
-      <c r="L82" s="446"/>
+      <c r="L82" s="442"/>
       <c r="M82" s="209" t="s">
         <v>3278</v>
       </c>
@@ -27152,7 +27121,7 @@
       <c r="Q86" s="56" t="s">
         <v>1172</v>
       </c>
-      <c r="R86" s="479" t="s">
+      <c r="R86" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S86" s="77" t="s">
@@ -27312,7 +27281,7 @@
       <c r="O88" s="38"/>
       <c r="P88" s="25"/>
       <c r="Q88" s="56"/>
-      <c r="R88" s="479" t="s">
+      <c r="R88" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S88" s="77" t="s">
@@ -27389,7 +27358,7 @@
       <c r="O89" s="38"/>
       <c r="P89" s="25"/>
       <c r="Q89" s="56"/>
-      <c r="R89" s="461" t="s">
+      <c r="R89" s="324" t="s">
         <v>3344</v>
       </c>
       <c r="S89" s="77" t="s">
@@ -27436,7 +27405,7 @@
       <c r="C90" s="255" t="s">
         <v>171</v>
       </c>
-      <c r="D90" s="413"/>
+      <c r="D90" s="337"/>
       <c r="E90" s="138"/>
       <c r="F90" s="47" t="s">
         <v>3355</v>
@@ -27464,7 +27433,7 @@
       <c r="O90" s="38"/>
       <c r="P90" s="25"/>
       <c r="Q90" s="56"/>
-      <c r="R90" s="398" t="s">
+      <c r="R90" s="39" t="s">
         <v>544</v>
       </c>
       <c r="S90" s="77" t="s">
@@ -27508,10 +27477,10 @@
       <c r="B91" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C91" s="402" t="s">
+      <c r="C91" s="401" t="s">
         <v>171</v>
       </c>
-      <c r="D91" s="413"/>
+      <c r="D91" s="337"/>
       <c r="E91" s="138"/>
       <c r="F91" s="47" t="s">
         <v>3361</v>
@@ -27537,13 +27506,13 @@
       <c r="O91" s="38"/>
       <c r="P91" s="25"/>
       <c r="Q91" s="56"/>
-      <c r="R91" s="482" t="s">
+      <c r="R91" s="471" t="s">
         <v>139</v>
       </c>
       <c r="S91" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="T91" s="428"/>
+      <c r="T91" s="425"/>
       <c r="U91" s="28"/>
       <c r="V91" s="28"/>
       <c r="W91" s="29" t="s">
@@ -27612,7 +27581,7 @@
       <c r="O92" s="38"/>
       <c r="P92" s="25"/>
       <c r="Q92" s="56"/>
-      <c r="R92" s="482" t="s">
+      <c r="R92" s="471" t="s">
         <v>139</v>
       </c>
       <c r="S92" s="137" t="s">
@@ -27689,7 +27658,7 @@
       <c r="O93" s="38"/>
       <c r="P93" s="25"/>
       <c r="Q93" s="56"/>
-      <c r="R93" s="482" t="s">
+      <c r="R93" s="471" t="s">
         <v>139</v>
       </c>
       <c r="S93" s="77" t="s">
@@ -27839,7 +27808,7 @@
       <c r="Q95" s="26" t="s">
         <v>1172</v>
       </c>
-      <c r="R95" s="490" t="s">
+      <c r="R95" s="479" t="s">
         <v>544</v>
       </c>
       <c r="S95" s="77" t="s">
@@ -27887,11 +27856,11 @@
       <c r="B96" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C96" s="402" t="s">
+      <c r="C96" s="401" t="s">
         <v>171</v>
       </c>
-      <c r="D96" s="415"/>
-      <c r="E96" s="418"/>
+      <c r="D96" s="412"/>
+      <c r="E96" s="415"/>
       <c r="F96" s="294" t="s">
         <v>3410</v>
       </c>
@@ -27907,7 +27876,7 @@
       <c r="L96" s="22" t="s">
         <v>3287</v>
       </c>
-      <c r="M96" s="456" t="s">
+      <c r="M96" s="450" t="s">
         <v>3120</v>
       </c>
       <c r="N96" s="38" t="s">
@@ -27916,7 +27885,7 @@
       <c r="O96" s="38"/>
       <c r="P96" s="25"/>
       <c r="Q96" s="56"/>
-      <c r="R96" s="479" t="s">
+      <c r="R96" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S96" s="77" t="s">
@@ -27962,7 +27931,7 @@
       <c r="B97" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C97" s="403" t="s">
+      <c r="C97" s="402" t="s">
         <v>3960</v>
       </c>
       <c r="D97" s="247"/>
@@ -28157,7 +28126,7 @@
       <c r="Q99" s="56" t="s">
         <v>3438</v>
       </c>
-      <c r="R99" s="481" t="s">
+      <c r="R99" s="94" t="s">
         <v>544</v>
       </c>
       <c r="S99" s="77" t="s">
@@ -28234,7 +28203,7 @@
       <c r="O100" s="38"/>
       <c r="P100" s="25"/>
       <c r="Q100" s="56"/>
-      <c r="R100" s="479" t="s">
+      <c r="R100" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S100" s="207" t="s">
@@ -28311,7 +28280,7 @@
       <c r="Q101" s="56" t="s">
         <v>3452</v>
       </c>
-      <c r="R101" s="486" t="s">
+      <c r="R101" s="475" t="s">
         <v>40</v>
       </c>
       <c r="S101" s="77" t="s">
@@ -28384,7 +28353,7 @@
       <c r="O102" s="54"/>
       <c r="P102" s="55"/>
       <c r="Q102" s="56"/>
-      <c r="R102" s="480" t="s">
+      <c r="R102" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S102" s="137" t="s">
@@ -28457,7 +28426,7 @@
       <c r="O103" s="54"/>
       <c r="P103" s="55"/>
       <c r="Q103" s="56"/>
-      <c r="R103" s="479" t="s">
+      <c r="R103" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S103" s="77" t="s">
@@ -28532,7 +28501,7 @@
       <c r="Q104" s="56" t="s">
         <v>3483</v>
       </c>
-      <c r="R104" s="398" t="s">
+      <c r="R104" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S104" s="209" t="s">
@@ -28605,7 +28574,7 @@
       <c r="O105" s="54"/>
       <c r="P105" s="55"/>
       <c r="Q105" s="56"/>
-      <c r="R105" s="481" t="s">
+      <c r="R105" s="94" t="s">
         <v>1107</v>
       </c>
       <c r="S105" s="209" t="s">
@@ -28680,7 +28649,7 @@
       <c r="O106" s="54"/>
       <c r="P106" s="55"/>
       <c r="Q106" s="56"/>
-      <c r="R106" s="480" t="s">
+      <c r="R106" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S106" s="209" t="s">
@@ -28757,7 +28726,7 @@
       <c r="O107" s="54"/>
       <c r="P107" s="55"/>
       <c r="Q107" s="56"/>
-      <c r="R107" s="461" t="s">
+      <c r="R107" s="324" t="s">
         <v>139</v>
       </c>
       <c r="S107" s="209" t="s">
@@ -28830,7 +28799,7 @@
       <c r="O108" s="54"/>
       <c r="P108" s="55"/>
       <c r="Q108" s="56"/>
-      <c r="R108" s="479" t="s">
+      <c r="R108" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S108" s="77" t="s">
@@ -28900,14 +28869,14 @@
       <c r="N109" s="136" t="s">
         <v>1242</v>
       </c>
-      <c r="O109" s="471" t="s">
+      <c r="O109" s="462" t="s">
         <v>3524</v>
       </c>
       <c r="P109" s="59"/>
       <c r="Q109" s="56" t="s">
         <v>3525</v>
       </c>
-      <c r="R109" s="398" t="s">
+      <c r="R109" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S109" s="77" t="s">
@@ -28963,7 +28932,7 @@
       <c r="F110" s="290" t="s">
         <v>3539</v>
       </c>
-      <c r="G110" s="429" t="s">
+      <c r="G110" s="426" t="s">
         <v>3540</v>
       </c>
       <c r="H110" s="95" t="s">
@@ -28984,7 +28953,7 @@
       <c r="O110" s="38"/>
       <c r="P110" s="25"/>
       <c r="Q110" s="26"/>
-      <c r="R110" s="481" t="s">
+      <c r="R110" s="94" t="s">
         <v>1107</v>
       </c>
       <c r="S110" s="77" t="s">
@@ -28996,7 +28965,7 @@
       <c r="W110" s="72" t="s">
         <v>3178</v>
       </c>
-      <c r="X110" s="513" t="s">
+      <c r="X110" s="502" t="s">
         <v>3179</v>
       </c>
       <c r="Y110" s="30" t="s">
@@ -29059,7 +29028,7 @@
       <c r="O111" s="38"/>
       <c r="P111" s="25"/>
       <c r="Q111" s="26"/>
-      <c r="R111" s="486" t="s">
+      <c r="R111" s="475" t="s">
         <v>40</v>
       </c>
       <c r="S111" s="77" t="s">
@@ -29140,7 +29109,7 @@
       <c r="O112" s="54"/>
       <c r="P112" s="55"/>
       <c r="Q112" s="56"/>
-      <c r="R112" s="480" t="s">
+      <c r="R112" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S112" s="77" t="s">
@@ -29219,7 +29188,7 @@
       <c r="O113" s="54"/>
       <c r="P113" s="55"/>
       <c r="Q113" s="56"/>
-      <c r="R113" s="457" t="s">
+      <c r="R113" s="339" t="s">
         <v>139</v>
       </c>
       <c r="S113" s="77" t="s">
@@ -29365,7 +29334,7 @@
       <c r="O115" s="73"/>
       <c r="P115" s="74"/>
       <c r="Q115" s="75"/>
-      <c r="R115" s="482" t="s">
+      <c r="R115" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S115" s="32" t="s">
@@ -29440,7 +29409,7 @@
       <c r="O116" s="38"/>
       <c r="P116" s="25"/>
       <c r="Q116" s="26"/>
-      <c r="R116" s="480" t="s">
+      <c r="R116" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S116" s="32" t="s">
@@ -29519,7 +29488,7 @@
       <c r="O117" s="54"/>
       <c r="P117" s="55"/>
       <c r="Q117" s="56"/>
-      <c r="R117" s="481" t="s">
+      <c r="R117" s="94" t="s">
         <v>1107</v>
       </c>
       <c r="S117" s="77" t="s">
@@ -29590,7 +29559,7 @@
       <c r="O118" s="38"/>
       <c r="P118" s="25"/>
       <c r="Q118" s="56"/>
-      <c r="R118" s="480" t="s">
+      <c r="R118" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S118" s="77" t="s">
@@ -29741,7 +29710,7 @@
       <c r="N120" s="38" t="s">
         <v>3623</v>
       </c>
-      <c r="O120" s="465" t="s">
+      <c r="O120" s="322" t="s">
         <v>901</v>
       </c>
       <c r="P120" s="126"/>
@@ -29819,10 +29788,10 @@
       <c r="M121" s="137" t="s">
         <v>657</v>
       </c>
-      <c r="N121" s="464" t="s">
+      <c r="N121" s="456" t="s">
         <v>3629</v>
       </c>
-      <c r="O121" s="464" t="s">
+      <c r="O121" s="456" t="s">
         <v>901</v>
       </c>
       <c r="P121" s="126"/>
@@ -29905,14 +29874,14 @@
       <c r="N122" s="136" t="s">
         <v>3643</v>
       </c>
-      <c r="O122" s="469" t="s">
+      <c r="O122" s="460" t="s">
         <v>3601</v>
       </c>
       <c r="P122" s="114"/>
       <c r="Q122" s="56" t="s">
         <v>3602</v>
       </c>
-      <c r="R122" s="490" t="s">
+      <c r="R122" s="479" t="s">
         <v>1107</v>
       </c>
       <c r="S122" s="77" t="s">
@@ -30209,7 +30178,7 @@
       <c r="L126" s="22" t="s">
         <v>3685</v>
       </c>
-      <c r="M126" s="453" t="s">
+      <c r="M126" s="331" t="s">
         <v>3686</v>
       </c>
       <c r="N126" s="136" t="s">
@@ -30261,7 +30230,7 @@
       <c r="A127" s="186" t="s">
         <v>3698</v>
       </c>
-      <c r="B127" s="400" t="s">
+      <c r="B127" s="399" t="s">
         <v>2294</v>
       </c>
       <c r="C127" s="250" t="s">
@@ -30293,7 +30262,7 @@
       <c r="O127" s="38"/>
       <c r="P127" s="25"/>
       <c r="Q127" s="56"/>
-      <c r="R127" s="481" t="s">
+      <c r="R127" s="94" t="s">
         <v>1107</v>
       </c>
       <c r="S127" s="77" t="s">
@@ -30357,20 +30326,20 @@
       <c r="J128" s="22"/>
       <c r="K128" s="22"/>
       <c r="L128" s="22"/>
-      <c r="M128" s="456" t="s">
+      <c r="M128" s="450" t="s">
         <v>1623</v>
       </c>
       <c r="N128" s="38" t="s">
         <v>3749</v>
       </c>
-      <c r="O128" s="465" t="s">
+      <c r="O128" s="322" t="s">
         <v>3750</v>
       </c>
       <c r="P128" s="126"/>
       <c r="Q128" s="26" t="s">
         <v>3751</v>
       </c>
-      <c r="R128" s="398" t="s">
+      <c r="R128" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S128" s="77" t="s">
@@ -30448,10 +30417,10 @@
       <c r="N129" s="65" t="s">
         <v>3761</v>
       </c>
-      <c r="O129" s="465"/>
+      <c r="O129" s="322"/>
       <c r="P129" s="126"/>
       <c r="Q129" s="26"/>
-      <c r="R129" s="481" t="s">
+      <c r="R129" s="94" t="s">
         <v>1107</v>
       </c>
       <c r="S129" s="77" t="s">
@@ -30521,16 +30490,16 @@
       </c>
       <c r="K130" s="22"/>
       <c r="L130" s="22"/>
-      <c r="M130" s="456" t="s">
+      <c r="M130" s="450" t="s">
         <v>2969</v>
       </c>
       <c r="N130" s="136" t="s">
         <v>3769</v>
       </c>
-      <c r="O130" s="463"/>
+      <c r="O130" s="455"/>
       <c r="P130" s="114"/>
       <c r="Q130" s="56"/>
-      <c r="R130" s="481" t="s">
+      <c r="R130" s="94" t="s">
         <v>1107</v>
       </c>
       <c r="S130" s="77" t="s">
@@ -30609,7 +30578,7 @@
       <c r="O131" s="54"/>
       <c r="P131" s="114"/>
       <c r="Q131" s="56"/>
-      <c r="R131" s="490" t="s">
+      <c r="R131" s="479" t="s">
         <v>1107</v>
       </c>
       <c r="S131" s="77" t="s">
@@ -30754,7 +30723,7 @@
       <c r="N133" s="89" t="s">
         <v>2544</v>
       </c>
-      <c r="O133" s="470" t="s">
+      <c r="O133" s="461" t="s">
         <v>2545</v>
       </c>
       <c r="P133" s="126"/>
@@ -30844,7 +30813,7 @@
       <c r="Q134" s="91" t="s">
         <v>3537</v>
       </c>
-      <c r="R134" s="461" t="s">
+      <c r="R134" s="324" t="s">
         <v>3344</v>
       </c>
       <c r="S134" s="115" t="s">
@@ -30923,7 +30892,7 @@
       <c r="Q135" s="56" t="s">
         <v>2384</v>
       </c>
-      <c r="R135" s="428" t="s">
+      <c r="R135" s="425" t="s">
         <v>80</v>
       </c>
       <c r="S135" s="32" t="s">
@@ -30990,8 +30959,8 @@
       <c r="I136" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="J136" s="440"/>
-      <c r="K136" s="440"/>
+      <c r="J136" s="436"/>
+      <c r="K136" s="436"/>
       <c r="L136" s="76"/>
       <c r="M136" s="53" t="s">
         <v>92</v>
@@ -31076,7 +31045,7 @@
       <c r="N137" s="54" t="s">
         <v>277</v>
       </c>
-      <c r="O137" s="463"/>
+      <c r="O137" s="455"/>
       <c r="P137" s="114"/>
       <c r="Q137" s="56"/>
       <c r="R137" s="39" t="s">
@@ -31154,7 +31123,7 @@
       <c r="O138" s="54"/>
       <c r="P138" s="55"/>
       <c r="Q138" s="56"/>
-      <c r="R138" s="398" t="s">
+      <c r="R138" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S138" s="32" t="s">
@@ -31668,7 +31637,7 @@
       </c>
       <c r="Z144" s="30"/>
       <c r="AA144" s="30"/>
-      <c r="AB144" s="524" t="s">
+      <c r="AB144" s="513" t="s">
         <v>207</v>
       </c>
       <c r="AC144" s="32" t="s">
@@ -31840,7 +31809,7 @@
       </c>
       <c r="Z146" s="30"/>
       <c r="AA146" s="30"/>
-      <c r="AB146" s="525" t="s">
+      <c r="AB146" s="514" t="s">
         <v>220</v>
       </c>
       <c r="AC146" s="32" t="s">
@@ -31925,7 +31894,7 @@
       </c>
       <c r="Z147" s="30"/>
       <c r="AA147" s="30"/>
-      <c r="AB147" s="527"/>
+      <c r="AB147" s="516"/>
       <c r="AC147" s="92" t="s">
         <v>227</v>
       </c>
@@ -31986,7 +31955,7 @@
       <c r="Q148" s="357" t="s">
         <v>603</v>
       </c>
-      <c r="R148" s="492" t="s">
+      <c r="R148" s="481" t="s">
         <v>604</v>
       </c>
       <c r="S148" s="314" t="s">
@@ -32063,7 +32032,7 @@
       <c r="O149" s="54"/>
       <c r="P149" s="55"/>
       <c r="Q149" s="56"/>
-      <c r="R149" s="455" t="s">
+      <c r="R149" s="449" t="s">
         <v>375</v>
       </c>
       <c r="S149" s="32" t="s">
@@ -32140,7 +32109,7 @@
       <c r="O150" s="54"/>
       <c r="P150" s="55"/>
       <c r="Q150" s="56"/>
-      <c r="R150" s="479" t="s">
+      <c r="R150" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S150" s="77" t="s">
@@ -32227,7 +32196,7 @@
       <c r="Q151" s="26" t="s">
         <v>1928</v>
       </c>
-      <c r="R151" s="398" t="s">
+      <c r="R151" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S151" s="32" t="s">
@@ -32248,7 +32217,7 @@
       <c r="Z151" s="30"/>
       <c r="AA151" s="30"/>
       <c r="AB151" s="41"/>
-      <c r="AC151" s="398" t="s">
+      <c r="AC151" s="39" t="s">
         <v>1932</v>
       </c>
       <c r="AD151" s="32"/>
@@ -32302,7 +32271,7 @@
       <c r="O152" s="65"/>
       <c r="P152" s="25"/>
       <c r="Q152" s="26"/>
-      <c r="R152" s="481" t="s">
+      <c r="R152" s="94" t="s">
         <v>1107</v>
       </c>
       <c r="S152" s="32" t="s">
@@ -32379,7 +32348,7 @@
       <c r="Q153" s="91" t="s">
         <v>2001</v>
       </c>
-      <c r="R153" s="398" t="s">
+      <c r="R153" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S153" s="32" t="s">
@@ -32464,7 +32433,7 @@
       <c r="Q154" s="26" t="s">
         <v>1910</v>
       </c>
-      <c r="R154" s="479" t="s">
+      <c r="R154" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S154" s="32" t="s">
@@ -32707,7 +32676,7 @@
       <c r="Q157" s="91" t="s">
         <v>2120</v>
       </c>
-      <c r="R157" s="398" t="s">
+      <c r="R157" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S157" s="32" t="s">
@@ -32861,7 +32830,7 @@
       <c r="Q159" s="56" t="s">
         <v>2120</v>
       </c>
-      <c r="R159" s="480" t="s">
+      <c r="R159" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S159" s="32" t="s">
@@ -32940,7 +32909,7 @@
       <c r="Q160" s="56" t="s">
         <v>2068</v>
       </c>
-      <c r="R160" s="480" t="s">
+      <c r="R160" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S160" s="32" t="s">
@@ -33102,7 +33071,7 @@
       <c r="Q162" s="56" t="s">
         <v>1885</v>
       </c>
-      <c r="R162" s="398" t="s">
+      <c r="R162" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S162" s="32" t="s">
@@ -33272,7 +33241,7 @@
       <c r="Q164" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="R164" s="479" t="s">
+      <c r="R164" s="470" t="s">
         <v>80</v>
       </c>
       <c r="S164" s="32" t="s">
@@ -33345,7 +33314,7 @@
       <c r="O165" s="65"/>
       <c r="P165" s="25"/>
       <c r="Q165" s="26"/>
-      <c r="R165" s="479" t="s">
+      <c r="R165" s="470" t="s">
         <v>80</v>
       </c>
       <c r="S165" s="21" t="s">
@@ -33507,7 +33476,7 @@
       <c r="Q167" s="56" t="s">
         <v>1928</v>
       </c>
-      <c r="R167" s="483" t="s">
+      <c r="R167" s="472" t="s">
         <v>562</v>
       </c>
       <c r="S167" s="32" t="s">
@@ -33584,7 +33553,7 @@
       <c r="O168" s="54"/>
       <c r="P168" s="55"/>
       <c r="Q168" s="56"/>
-      <c r="R168" s="486" t="s">
+      <c r="R168" s="475" t="s">
         <v>40</v>
       </c>
       <c r="S168" s="32" t="s">
@@ -33657,7 +33626,7 @@
       <c r="O169" s="54"/>
       <c r="P169" s="55"/>
       <c r="Q169" s="56"/>
-      <c r="R169" s="398" t="s">
+      <c r="R169" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S169" s="32" t="s">
@@ -33738,7 +33707,7 @@
       <c r="O170" s="38"/>
       <c r="P170" s="25"/>
       <c r="Q170" s="26"/>
-      <c r="R170" s="486" t="s">
+      <c r="R170" s="475" t="s">
         <v>40</v>
       </c>
       <c r="S170" s="32" t="s">
@@ -33813,7 +33782,7 @@
       <c r="O171" s="305"/>
       <c r="P171" s="306"/>
       <c r="Q171" s="307"/>
-      <c r="R171" s="493" t="s">
+      <c r="R171" s="482" t="s">
         <v>49</v>
       </c>
       <c r="S171" s="314" t="s">
@@ -33900,7 +33869,7 @@
       <c r="Q172" s="357" t="s">
         <v>39</v>
       </c>
-      <c r="R172" s="494" t="s">
+      <c r="R172" s="483" t="s">
         <v>523</v>
       </c>
       <c r="S172" s="314" t="s">
@@ -34053,11 +34022,11 @@
       <c r="N174" s="89" t="s">
         <v>934</v>
       </c>
-      <c r="O174" s="470" t="s">
+      <c r="O174" s="461" t="s">
         <v>935</v>
       </c>
       <c r="P174" s="70"/>
-      <c r="Q174" s="478" t="s">
+      <c r="Q174" s="469" t="s">
         <v>936</v>
       </c>
       <c r="R174" s="39" t="s">
@@ -34145,7 +34114,7 @@
       <c r="Q175" s="75" t="s">
         <v>1744</v>
       </c>
-      <c r="R175" s="398" t="s">
+      <c r="R175" s="39" t="s">
         <v>1745</v>
       </c>
       <c r="S175" s="32" t="s">
@@ -34214,11 +34183,11 @@
       <c r="I176" s="43" t="s">
         <v>400</v>
       </c>
-      <c r="J176" s="443" t="s">
+      <c r="J176" s="439" t="s">
         <v>401</v>
       </c>
-      <c r="K176" s="443"/>
-      <c r="L176" s="443"/>
+      <c r="K176" s="439"/>
+      <c r="L176" s="439"/>
       <c r="M176" s="53" t="s">
         <v>342</v>
       </c>
@@ -34228,7 +34197,7 @@
       <c r="O176" s="54"/>
       <c r="P176" s="55"/>
       <c r="Q176" s="56"/>
-      <c r="R176" s="434" t="s">
+      <c r="R176" s="338" t="s">
         <v>395</v>
       </c>
       <c r="S176" s="32" t="s">
@@ -34461,7 +34430,7 @@
       <c r="O179" s="38"/>
       <c r="P179" s="25"/>
       <c r="Q179" s="26"/>
-      <c r="R179" s="486" t="s">
+      <c r="R179" s="475" t="s">
         <v>40</v>
       </c>
       <c r="S179" s="40" t="s">
@@ -34626,8 +34595,8 @@
       <c r="V181" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="W181" s="511"/>
-      <c r="X181" s="511"/>
+      <c r="W181" s="500"/>
+      <c r="X181" s="500"/>
       <c r="Y181" s="30" t="s">
         <v>99</v>
       </c>
@@ -34686,7 +34655,7 @@
       <c r="O182" s="65"/>
       <c r="P182" s="25"/>
       <c r="Q182" s="26"/>
-      <c r="R182" s="485" t="s">
+      <c r="R182" s="474" t="s">
         <v>80</v>
       </c>
       <c r="S182" s="40" t="s">
@@ -34738,7 +34707,7 @@
       <c r="F183" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G183" s="398" t="s">
+      <c r="G183" s="39" t="s">
         <v>117</v>
       </c>
       <c r="H183" s="40" t="s">
@@ -34816,10 +34785,10 @@
       <c r="I184" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="J184" s="444" t="s">
+      <c r="J184" s="440" t="s">
         <v>136</v>
       </c>
-      <c r="K184" s="444"/>
+      <c r="K184" s="440"/>
       <c r="L184" s="68"/>
       <c r="M184" s="36" t="s">
         <v>137</v>
@@ -34836,7 +34805,7 @@
       <c r="S184" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="T184" s="428"/>
+      <c r="T184" s="425"/>
       <c r="U184" s="28"/>
       <c r="V184" s="28"/>
       <c r="W184" s="29"/>
@@ -35043,7 +35012,7 @@
       <c r="O187" s="83"/>
       <c r="P187" s="25"/>
       <c r="Q187" s="26"/>
-      <c r="R187" s="485" t="s">
+      <c r="R187" s="474" t="s">
         <v>80</v>
       </c>
       <c r="S187" s="32" t="s">
@@ -35130,7 +35099,7 @@
       <c r="Y188" s="30"/>
       <c r="Z188" s="30"/>
       <c r="AA188" s="30"/>
-      <c r="AB188" s="523" t="s">
+      <c r="AB188" s="512" t="s">
         <v>236</v>
       </c>
       <c r="AC188" s="69" t="s">
@@ -35548,11 +35517,11 @@
         <v>40</v>
       </c>
       <c r="S194" s="32"/>
-      <c r="T194" s="500"/>
-      <c r="U194" s="506" t="s">
+      <c r="T194" s="489"/>
+      <c r="U194" s="495" t="s">
         <v>289</v>
       </c>
-      <c r="V194" s="506" t="s">
+      <c r="V194" s="495" t="s">
         <v>290</v>
       </c>
       <c r="W194" s="29"/>
@@ -35607,7 +35576,7 @@
       </c>
       <c r="J195" s="35"/>
       <c r="K195" s="100"/>
-      <c r="L195" s="444" t="s">
+      <c r="L195" s="440" t="s">
         <v>286</v>
       </c>
       <c r="M195" s="53" t="s">
@@ -35625,13 +35594,13 @@
       <c r="S195" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T195" s="500" t="s">
+      <c r="T195" s="489" t="s">
         <v>299</v>
       </c>
-      <c r="U195" s="506" t="s">
+      <c r="U195" s="495" t="s">
         <v>289</v>
       </c>
-      <c r="V195" s="506" t="s">
+      <c r="V195" s="495" t="s">
         <v>290</v>
       </c>
       <c r="W195" s="102"/>
@@ -35643,7 +35612,7 @@
       <c r="AA195" s="30"/>
       <c r="AB195" s="41"/>
       <c r="AC195" s="32"/>
-      <c r="AD195" s="528" t="s">
+      <c r="AD195" s="517" t="s">
         <v>301</v>
       </c>
       <c r="AE195" s="32"/>
@@ -35852,13 +35821,13 @@
       <c r="S198" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="T198" s="501" t="s">
+      <c r="T198" s="490" t="s">
         <v>330</v>
       </c>
-      <c r="U198" s="506" t="s">
+      <c r="U198" s="495" t="s">
         <v>289</v>
       </c>
-      <c r="V198" s="506" t="s">
+      <c r="V198" s="495" t="s">
         <v>290</v>
       </c>
       <c r="W198" s="112"/>
@@ -35914,7 +35883,7 @@
         <v>334</v>
       </c>
       <c r="J199" s="104"/>
-      <c r="K199" s="444"/>
+      <c r="K199" s="440"/>
       <c r="L199" s="68" t="s">
         <v>286</v>
       </c>
@@ -35933,13 +35902,13 @@
       <c r="S199" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="T199" s="499" t="s">
+      <c r="T199" s="488" t="s">
         <v>336</v>
       </c>
-      <c r="U199" s="505" t="s">
+      <c r="U199" s="494" t="s">
         <v>289</v>
       </c>
-      <c r="V199" s="505" t="s">
+      <c r="V199" s="494" t="s">
         <v>290</v>
       </c>
       <c r="W199" s="112"/>
@@ -36491,9 +36460,9 @@
       <c r="S207" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T207" s="496"/>
-      <c r="U207" s="503"/>
-      <c r="V207" s="503"/>
+      <c r="T207" s="485"/>
+      <c r="U207" s="492"/>
+      <c r="V207" s="492"/>
       <c r="W207" s="113"/>
       <c r="X207" s="113"/>
       <c r="Y207" s="30"/>
@@ -36899,7 +36868,7 @@
       <c r="F213" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="G213" s="398" t="s">
+      <c r="G213" s="39" t="s">
         <v>515</v>
       </c>
       <c r="H213" s="95" t="s">
@@ -37293,11 +37262,11 @@
       <c r="S218" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T218" s="496" t="s">
+      <c r="T218" s="485" t="s">
         <v>554</v>
       </c>
-      <c r="U218" s="503"/>
-      <c r="V218" s="503"/>
+      <c r="U218" s="492"/>
+      <c r="V218" s="492"/>
       <c r="W218" s="113"/>
       <c r="X218" s="113"/>
       <c r="Y218" s="30"/>
@@ -37579,11 +37548,11 @@
       <c r="S222" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="T222" s="497" t="s">
+      <c r="T222" s="486" t="s">
         <v>588</v>
       </c>
-      <c r="U222" s="503"/>
-      <c r="V222" s="503"/>
+      <c r="U222" s="492"/>
+      <c r="V222" s="492"/>
       <c r="W222" s="113"/>
       <c r="X222" s="113"/>
       <c r="Y222" s="30"/>
@@ -37686,7 +37655,7 @@
       <c r="B224" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C224" s="409" t="s">
+      <c r="C224" s="407" t="s">
         <v>629</v>
       </c>
       <c r="D224" s="235"/>
@@ -37712,7 +37681,7 @@
       <c r="N224" s="136" t="s">
         <v>634</v>
       </c>
-      <c r="O224" s="463"/>
+      <c r="O224" s="455"/>
       <c r="P224" s="114"/>
       <c r="Q224" s="56"/>
       <c r="R224" s="115" t="s">
@@ -37919,7 +37888,7 @@
       <c r="N227" s="54" t="s">
         <v>658</v>
       </c>
-      <c r="O227" s="463" t="s">
+      <c r="O227" s="455" t="s">
         <v>659</v>
       </c>
       <c r="P227" s="55"/>
@@ -38065,7 +38034,7 @@
       <c r="N229" s="54" t="s">
         <v>676</v>
       </c>
-      <c r="O229" s="466"/>
+      <c r="O229" s="457"/>
       <c r="P229" s="114"/>
       <c r="Q229" s="56"/>
       <c r="R229" s="32" t="s">
@@ -38203,7 +38172,7 @@
       <c r="N231" s="355" t="s">
         <v>694</v>
       </c>
-      <c r="O231" s="468" t="s">
+      <c r="O231" s="459" t="s">
         <v>695</v>
       </c>
       <c r="P231" s="363"/>
@@ -38322,7 +38291,7 @@
       <c r="C233" s="256" t="s">
         <v>171</v>
       </c>
-      <c r="D233" s="410" t="s">
+      <c r="D233" s="408" t="s">
         <v>596</v>
       </c>
       <c r="E233" s="58" t="s">
@@ -38349,7 +38318,7 @@
       <c r="N233" s="54" t="s">
         <v>731</v>
       </c>
-      <c r="O233" s="463"/>
+      <c r="O233" s="455"/>
       <c r="P233" s="114"/>
       <c r="Q233" s="56"/>
       <c r="R233" s="117" t="s">
@@ -38395,7 +38364,7 @@
       </c>
       <c r="D234" s="300"/>
       <c r="E234" s="301"/>
-      <c r="F234" s="423" t="s">
+      <c r="F234" s="420" t="s">
         <v>734</v>
       </c>
       <c r="G234" s="314"/>
@@ -38439,7 +38408,7 @@
       <c r="AA234" s="312"/>
       <c r="AB234" s="313"/>
       <c r="AC234" s="314"/>
-      <c r="AD234" s="493"/>
+      <c r="AD234" s="482"/>
       <c r="AE234" s="32"/>
       <c r="AF234" s="32"/>
       <c r="AG234" s="32"/>
@@ -38996,7 +38965,7 @@
       <c r="N242" s="54" t="s">
         <v>805</v>
       </c>
-      <c r="O242" s="463" t="s">
+      <c r="O242" s="455" t="s">
         <v>806</v>
       </c>
       <c r="P242" s="55"/>
@@ -39075,7 +39044,7 @@
       <c r="N243" s="54" t="s">
         <v>814</v>
       </c>
-      <c r="O243" s="463"/>
+      <c r="O243" s="455"/>
       <c r="P243" s="114"/>
       <c r="Q243" s="56"/>
       <c r="R243" s="32" t="s">
@@ -39084,7 +39053,7 @@
       <c r="S243" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T243" s="498" t="s">
+      <c r="T243" s="487" t="s">
         <v>815</v>
       </c>
       <c r="U243" s="28"/>
@@ -39213,7 +39182,7 @@
       <c r="L245" s="22" t="s">
         <v>827</v>
       </c>
-      <c r="M245" s="448" t="s">
+      <c r="M245" s="444" t="s">
         <v>828</v>
       </c>
       <c r="N245" s="73" t="s">
@@ -39330,55 +39299,55 @@
       <c r="A247" s="393" t="s">
         <v>840</v>
       </c>
-      <c r="B247" s="398" t="s">
+      <c r="B247" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C247" s="408" t="s">
+      <c r="C247" s="406" t="s">
         <v>841</v>
       </c>
-      <c r="D247" s="413"/>
-      <c r="E247" s="417"/>
-      <c r="F247" s="421" t="s">
+      <c r="D247" s="337"/>
+      <c r="E247" s="414"/>
+      <c r="F247" s="418" t="s">
         <v>842</v>
       </c>
-      <c r="G247" s="398"/>
-      <c r="H247" s="429" t="s">
+      <c r="G247" s="39"/>
+      <c r="H247" s="426" t="s">
         <v>843</v>
       </c>
-      <c r="I247" s="434" t="s">
+      <c r="I247" s="338" t="s">
         <v>844</v>
       </c>
-      <c r="J247" s="439"/>
-      <c r="K247" s="439"/>
-      <c r="L247" s="439" t="s">
+      <c r="J247" s="435"/>
+      <c r="K247" s="435"/>
+      <c r="L247" s="435" t="s">
         <v>541</v>
       </c>
-      <c r="M247" s="448" t="s">
+      <c r="M247" s="444" t="s">
         <v>845</v>
       </c>
-      <c r="N247" s="467" t="s">
+      <c r="N247" s="458" t="s">
         <v>846</v>
       </c>
-      <c r="O247" s="467"/>
+      <c r="O247" s="458"/>
       <c r="P247" s="74"/>
       <c r="Q247" s="75"/>
-      <c r="R247" s="479" t="s">
+      <c r="R247" s="470" t="s">
         <v>544</v>
       </c>
-      <c r="S247" s="398" t="s">
+      <c r="S247" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="T247" s="428"/>
-      <c r="U247" s="504"/>
-      <c r="V247" s="504"/>
-      <c r="W247" s="510"/>
-      <c r="X247" s="510"/>
-      <c r="Y247" s="514"/>
-      <c r="Z247" s="514"/>
-      <c r="AA247" s="514"/>
-      <c r="AB247" s="521"/>
-      <c r="AC247" s="398"/>
-      <c r="AD247" s="398"/>
+      <c r="T247" s="425"/>
+      <c r="U247" s="493"/>
+      <c r="V247" s="493"/>
+      <c r="W247" s="499"/>
+      <c r="X247" s="499"/>
+      <c r="Y247" s="503"/>
+      <c r="Z247" s="503"/>
+      <c r="AA247" s="503"/>
+      <c r="AB247" s="510"/>
+      <c r="AC247" s="39"/>
+      <c r="AD247" s="39"/>
       <c r="AE247" s="230"/>
       <c r="AF247" s="230"/>
       <c r="AG247" s="230"/>
@@ -39404,48 +39373,48 @@
         <v>810</v>
       </c>
       <c r="D248" s="337"/>
-      <c r="E248" s="417"/>
-      <c r="F248" s="424" t="s">
+      <c r="E248" s="414"/>
+      <c r="F248" s="421" t="s">
         <v>847</v>
       </c>
-      <c r="G248" s="398" t="s">
+      <c r="G248" s="39" t="s">
         <v>848</v>
       </c>
-      <c r="H248" s="433" t="s">
+      <c r="H248" s="430" t="s">
         <v>849</v>
       </c>
-      <c r="I248" s="434" t="s">
+      <c r="I248" s="338" t="s">
         <v>119</v>
       </c>
-      <c r="J248" s="439"/>
-      <c r="K248" s="439"/>
-      <c r="L248" s="439"/>
-      <c r="M248" s="448" t="s">
+      <c r="J248" s="435"/>
+      <c r="K248" s="435"/>
+      <c r="L248" s="435"/>
+      <c r="M248" s="444" t="s">
         <v>92</v>
       </c>
-      <c r="N248" s="463" t="s">
+      <c r="N248" s="455" t="s">
         <v>850</v>
       </c>
-      <c r="O248" s="463"/>
+      <c r="O248" s="455"/>
       <c r="P248" s="55"/>
       <c r="Q248" s="56"/>
       <c r="R248" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="S248" s="398" t="s">
+      <c r="S248" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="T248" s="428"/>
-      <c r="U248" s="504"/>
-      <c r="V248" s="504"/>
-      <c r="W248" s="510"/>
-      <c r="X248" s="510"/>
-      <c r="Y248" s="514"/>
-      <c r="Z248" s="514"/>
-      <c r="AA248" s="514"/>
-      <c r="AB248" s="521"/>
-      <c r="AC248" s="398"/>
-      <c r="AD248" s="398"/>
+      <c r="T248" s="425"/>
+      <c r="U248" s="493"/>
+      <c r="V248" s="493"/>
+      <c r="W248" s="499"/>
+      <c r="X248" s="499"/>
+      <c r="Y248" s="503"/>
+      <c r="Z248" s="503"/>
+      <c r="AA248" s="503"/>
+      <c r="AB248" s="510"/>
+      <c r="AC248" s="39"/>
+      <c r="AD248" s="39"/>
       <c r="AE248" s="230"/>
       <c r="AF248" s="230"/>
       <c r="AG248" s="230"/>
@@ -40669,7 +40638,7 @@
       </c>
       <c r="D266" s="235"/>
       <c r="E266" s="58"/>
-      <c r="F266" s="424" t="s">
+      <c r="F266" s="421" t="s">
         <v>1008</v>
       </c>
       <c r="G266" s="32"/>
@@ -40832,7 +40801,7 @@
       <c r="N268" s="143" t="s">
         <v>1030</v>
       </c>
-      <c r="O268" s="467" t="s">
+      <c r="O268" s="458" t="s">
         <v>1031</v>
       </c>
       <c r="P268" s="59" t="s">
@@ -40989,7 +40958,7 @@
       </c>
       <c r="T270" s="21"/>
       <c r="U270" s="28"/>
-      <c r="V270" s="507"/>
+      <c r="V270" s="496"/>
       <c r="W270" s="29"/>
       <c r="X270" s="29"/>
       <c r="Y270" s="30"/>
@@ -41041,7 +41010,7 @@
       </c>
       <c r="K271" s="35"/>
       <c r="L271" s="35"/>
-      <c r="M271" s="458" t="s">
+      <c r="M271" s="451" t="s">
         <v>1063</v>
       </c>
       <c r="N271" s="143" t="s">
@@ -41118,7 +41087,7 @@
       <c r="L272" s="22" t="s">
         <v>1075</v>
       </c>
-      <c r="M272" s="448" t="s">
+      <c r="M272" s="444" t="s">
         <v>1076</v>
       </c>
       <c r="N272" s="136" t="s">
@@ -41189,7 +41158,7 @@
       <c r="J273" s="82"/>
       <c r="K273" s="82"/>
       <c r="L273" s="82"/>
-      <c r="M273" s="448" t="s">
+      <c r="M273" s="444" t="s">
         <v>92</v>
       </c>
       <c r="N273" s="54" t="s">
@@ -41490,7 +41459,7 @@
       </c>
       <c r="T277" s="21"/>
       <c r="U277" s="28"/>
-      <c r="V277" s="507"/>
+      <c r="V277" s="496"/>
       <c r="W277" s="29"/>
       <c r="X277" s="29"/>
       <c r="Y277" s="30"/>
@@ -41619,7 +41588,7 @@
       <c r="N279" s="54" t="s">
         <v>731</v>
       </c>
-      <c r="O279" s="463"/>
+      <c r="O279" s="455"/>
       <c r="P279" s="114"/>
       <c r="Q279" s="56"/>
       <c r="R279" s="117" t="s">
@@ -41826,7 +41795,7 @@
       <c r="N282" s="73" t="s">
         <v>1171</v>
       </c>
-      <c r="O282" s="467" t="s">
+      <c r="O282" s="458" t="s">
         <v>38</v>
       </c>
       <c r="P282" s="59"/>
@@ -41881,7 +41850,7 @@
       <c r="B283" s="32" t="s">
         <v>1179</v>
       </c>
-      <c r="C283" s="402" t="s">
+      <c r="C283" s="401" t="s">
         <v>171</v>
       </c>
       <c r="D283" s="235"/>
@@ -41903,7 +41872,7 @@
       <c r="L283" s="22" t="s">
         <v>1182</v>
       </c>
-      <c r="M283" s="448" t="s">
+      <c r="M283" s="444" t="s">
         <v>1183</v>
       </c>
       <c r="N283" s="54" t="s">
@@ -42045,7 +42014,7 @@
       <c r="N285" s="54" t="s">
         <v>1196</v>
       </c>
-      <c r="O285" s="463"/>
+      <c r="O285" s="455"/>
       <c r="P285" s="59" t="s">
         <v>1197</v>
       </c>
@@ -42254,7 +42223,7 @@
       <c r="N288" s="143" t="s">
         <v>1217</v>
       </c>
-      <c r="O288" s="472"/>
+      <c r="O288" s="463"/>
       <c r="P288" s="59"/>
       <c r="Q288" s="71"/>
       <c r="R288" s="150" t="s">
@@ -42615,7 +42584,7 @@
       <c r="N293" s="143" t="s">
         <v>1253</v>
       </c>
-      <c r="O293" s="472"/>
+      <c r="O293" s="463"/>
       <c r="P293" s="59"/>
       <c r="Q293" s="75"/>
       <c r="R293" s="150" t="s">
@@ -42673,7 +42642,7 @@
       </c>
       <c r="D294" s="238"/>
       <c r="E294" s="58"/>
-      <c r="F294" s="428" t="s">
+      <c r="F294" s="425" t="s">
         <v>1101</v>
       </c>
       <c r="G294" s="21" t="s">
@@ -42694,7 +42663,7 @@
       <c r="N294" s="136" t="s">
         <v>1261</v>
       </c>
-      <c r="O294" s="471"/>
+      <c r="O294" s="462"/>
       <c r="P294" s="114"/>
       <c r="Q294" s="56"/>
       <c r="R294" s="32" t="s">
@@ -42759,7 +42728,7 @@
       </c>
       <c r="K295" s="35"/>
       <c r="L295" s="35"/>
-      <c r="M295" s="460" t="s">
+      <c r="M295" s="453" t="s">
         <v>1063</v>
       </c>
       <c r="N295" s="143" t="s">
@@ -42838,7 +42807,7 @@
       </c>
       <c r="K296" s="35"/>
       <c r="L296" s="35"/>
-      <c r="M296" s="450" t="s">
+      <c r="M296" s="446" t="s">
         <v>1063</v>
       </c>
       <c r="N296" s="143" t="s">
@@ -42988,7 +42957,7 @@
       <c r="N298" s="54" t="s">
         <v>1290</v>
       </c>
-      <c r="O298" s="463" t="s">
+      <c r="O298" s="455" t="s">
         <v>994</v>
       </c>
       <c r="P298" s="114"/>
@@ -43353,7 +43322,7 @@
       </c>
       <c r="O303" s="143"/>
       <c r="P303" s="74"/>
-      <c r="Q303" s="476"/>
+      <c r="Q303" s="467"/>
       <c r="R303" s="150" t="s">
         <v>1065</v>
       </c>
@@ -44008,7 +43977,7 @@
       <c r="N312" s="54" t="s">
         <v>1407</v>
       </c>
-      <c r="O312" s="463"/>
+      <c r="O312" s="455"/>
       <c r="P312" s="114"/>
       <c r="Q312" s="123"/>
       <c r="R312" s="39" t="s">
@@ -44077,10 +44046,10 @@
       <c r="N313" s="136" t="s">
         <v>1413</v>
       </c>
-      <c r="O313" s="471"/>
+      <c r="O313" s="462"/>
       <c r="P313" s="114"/>
       <c r="Q313" s="56"/>
-      <c r="R313" s="482" t="s">
+      <c r="R313" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S313" s="21" t="s">
@@ -44230,13 +44199,13 @@
       <c r="O315" s="143"/>
       <c r="P315" s="74"/>
       <c r="Q315" s="75"/>
-      <c r="R315" s="482" t="s">
+      <c r="R315" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S315" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="T315" s="428"/>
+      <c r="T315" s="425"/>
       <c r="U315" s="28" t="s">
         <v>1066</v>
       </c>
@@ -44373,7 +44342,7 @@
       <c r="L317" s="82" t="s">
         <v>1448</v>
       </c>
-      <c r="M317" s="459" t="s">
+      <c r="M317" s="452" t="s">
         <v>1449</v>
       </c>
       <c r="N317" s="54" t="s">
@@ -44423,7 +44392,7 @@
       <c r="C318" s="253" t="s">
         <v>171</v>
       </c>
-      <c r="D318" s="413"/>
+      <c r="D318" s="337"/>
       <c r="E318" s="58"/>
       <c r="F318" s="47" t="s">
         <v>1452</v>
@@ -44440,7 +44409,7 @@
       <c r="J318" s="22"/>
       <c r="K318" s="22"/>
       <c r="L318" s="22"/>
-      <c r="M318" s="457" t="s">
+      <c r="M318" s="339" t="s">
         <v>1456</v>
       </c>
       <c r="N318" s="54" t="s">
@@ -44511,7 +44480,7 @@
       <c r="L319" s="22" t="s">
         <v>1448</v>
       </c>
-      <c r="M319" s="459" t="s">
+      <c r="M319" s="452" t="s">
         <v>1449</v>
       </c>
       <c r="N319" s="54" t="s">
@@ -44520,7 +44489,7 @@
       <c r="O319" s="54"/>
       <c r="P319" s="55"/>
       <c r="Q319" s="56"/>
-      <c r="R319" s="479" t="s">
+      <c r="R319" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S319" s="32" t="s">
@@ -44595,7 +44564,7 @@
       <c r="O320" s="136"/>
       <c r="P320" s="55"/>
       <c r="Q320" s="56"/>
-      <c r="R320" s="482" t="s">
+      <c r="R320" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S320" s="21" t="s">
@@ -44728,7 +44697,7 @@
       <c r="L322" s="82" t="s">
         <v>1488</v>
       </c>
-      <c r="M322" s="448" t="s">
+      <c r="M322" s="444" t="s">
         <v>1489</v>
       </c>
       <c r="N322" s="54" t="s">
@@ -44875,7 +44844,7 @@
       <c r="O324" s="143"/>
       <c r="P324" s="74"/>
       <c r="Q324" s="75"/>
-      <c r="R324" s="482" t="s">
+      <c r="R324" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S324" s="21" t="s">
@@ -44956,7 +44925,7 @@
       <c r="O325" s="143"/>
       <c r="P325" s="74"/>
       <c r="Q325" s="75"/>
-      <c r="R325" s="482" t="s">
+      <c r="R325" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S325" s="21" t="s">
@@ -45009,7 +44978,7 @@
       <c r="C326" s="256" t="s">
         <v>1527</v>
       </c>
-      <c r="D326" s="412"/>
+      <c r="D326" s="410"/>
       <c r="E326" s="58"/>
       <c r="F326" s="88" t="s">
         <v>1528</v>
@@ -45024,7 +44993,7 @@
         <v>1531</v>
       </c>
       <c r="J326" s="35"/>
-      <c r="K326" s="445"/>
+      <c r="K326" s="441"/>
       <c r="L326" s="119" t="s">
         <v>1532</v>
       </c>
@@ -45106,7 +45075,7 @@
       <c r="O327" s="136"/>
       <c r="P327" s="55"/>
       <c r="Q327" s="56"/>
-      <c r="R327" s="482" t="s">
+      <c r="R327" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S327" s="21" t="s">
@@ -45159,7 +45128,7 @@
       </c>
       <c r="D328" s="235"/>
       <c r="E328" s="58"/>
-      <c r="F328" s="421" t="s">
+      <c r="F328" s="418" t="s">
         <v>1543</v>
       </c>
       <c r="G328" s="32" t="s">
@@ -45189,7 +45158,7 @@
       <c r="Q328" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="R328" s="398" t="s">
+      <c r="R328" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S328" s="32" t="s">
@@ -45396,7 +45365,7 @@
       <c r="O331" s="136"/>
       <c r="P331" s="55"/>
       <c r="Q331" s="56"/>
-      <c r="R331" s="482" t="s">
+      <c r="R331" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S331" s="21" t="s">
@@ -45475,7 +45444,7 @@
       <c r="O332" s="136"/>
       <c r="P332" s="55"/>
       <c r="Q332" s="56"/>
-      <c r="R332" s="482" t="s">
+      <c r="R332" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S332" s="21" t="s">
@@ -45540,7 +45509,7 @@
       <c r="I333" s="127" t="s">
         <v>1585</v>
       </c>
-      <c r="J333" s="437" t="s">
+      <c r="J333" s="433" t="s">
         <v>1586</v>
       </c>
       <c r="K333" s="35"/>
@@ -45687,10 +45656,10 @@
       <c r="N335" s="143" t="s">
         <v>1600</v>
       </c>
-      <c r="O335" s="472"/>
+      <c r="O335" s="463"/>
       <c r="P335" s="59"/>
       <c r="Q335" s="75"/>
-      <c r="R335" s="482" t="s">
+      <c r="R335" s="471" t="s">
         <v>1268</v>
       </c>
       <c r="S335" s="21" t="s">
@@ -45759,7 +45728,7 @@
       <c r="O336" s="136"/>
       <c r="P336" s="55"/>
       <c r="Q336" s="56"/>
-      <c r="R336" s="482" t="s">
+      <c r="R336" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S336" s="21" t="s">
@@ -45815,7 +45784,7 @@
       <c r="J337" s="82"/>
       <c r="K337" s="82"/>
       <c r="L337" s="82"/>
-      <c r="M337" s="453" t="s">
+      <c r="M337" s="331" t="s">
         <v>657</v>
       </c>
       <c r="N337" s="89" t="s">
@@ -45828,7 +45797,7 @@
       <c r="Q337" s="91" t="s">
         <v>1613</v>
       </c>
-      <c r="R337" s="398" t="s">
+      <c r="R337" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S337" s="32" t="s">
@@ -45887,7 +45856,7 @@
       <c r="I338" s="43" t="s">
         <v>1620</v>
       </c>
-      <c r="J338" s="436"/>
+      <c r="J338" s="432"/>
       <c r="K338" s="140" t="s">
         <v>1621</v>
       </c>
@@ -45903,7 +45872,7 @@
       <c r="O338" s="54"/>
       <c r="P338" s="55"/>
       <c r="Q338" s="56"/>
-      <c r="R338" s="398" t="s">
+      <c r="R338" s="39" t="s">
         <v>544</v>
       </c>
       <c r="S338" s="32" t="s">
@@ -45965,7 +45934,7 @@
       <c r="N339" s="73" t="s">
         <v>1242</v>
       </c>
-      <c r="O339" s="467" t="s">
+      <c r="O339" s="458" t="s">
         <v>1628</v>
       </c>
       <c r="P339" s="59"/>
@@ -46042,10 +46011,10 @@
       <c r="N340" s="136" t="s">
         <v>1640</v>
       </c>
-      <c r="O340" s="471"/>
+      <c r="O340" s="462"/>
       <c r="P340" s="114"/>
       <c r="Q340" s="56"/>
-      <c r="R340" s="482" t="s">
+      <c r="R340" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S340" s="21" t="s">
@@ -46124,7 +46093,7 @@
       <c r="O341" s="54"/>
       <c r="P341" s="55"/>
       <c r="Q341" s="56"/>
-      <c r="R341" s="482" t="s">
+      <c r="R341" s="471" t="s">
         <v>1268</v>
       </c>
       <c r="S341" s="21" t="s">
@@ -46184,7 +46153,7 @@
       <c r="H342" s="95" t="s">
         <v>1656</v>
       </c>
-      <c r="I342" s="434" t="s">
+      <c r="I342" s="338" t="s">
         <v>1657</v>
       </c>
       <c r="J342" s="22"/>
@@ -46329,10 +46298,10 @@
       <c r="M344" s="36" t="s">
         <v>1672</v>
       </c>
-      <c r="N344" s="463" t="s">
+      <c r="N344" s="455" t="s">
         <v>1673</v>
       </c>
-      <c r="O344" s="463"/>
+      <c r="O344" s="455"/>
       <c r="P344" s="55"/>
       <c r="Q344" s="56"/>
       <c r="R344" s="334" t="s">
@@ -46414,7 +46383,7 @@
       <c r="U345" s="28" t="s">
         <v>1066</v>
       </c>
-      <c r="V345" s="508" t="s">
+      <c r="V345" s="497" t="s">
         <v>1680</v>
       </c>
       <c r="W345" s="29"/>
@@ -46474,7 +46443,7 @@
       <c r="L346" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="M346" s="457" t="s">
+      <c r="M346" s="339" t="s">
         <v>1687</v>
       </c>
       <c r="N346" s="54" t="s">
@@ -46574,7 +46543,7 @@
       </c>
       <c r="Z347" s="103"/>
       <c r="AA347" s="30"/>
-      <c r="AB347" s="519" t="s">
+      <c r="AB347" s="508" t="s">
         <v>1068</v>
       </c>
       <c r="AC347" s="21" t="s">
@@ -46701,7 +46670,7 @@
       <c r="N349" s="65" t="s">
         <v>1719</v>
       </c>
-      <c r="O349" s="465"/>
+      <c r="O349" s="322"/>
       <c r="P349" s="126"/>
       <c r="Q349" s="26"/>
       <c r="R349" s="99" t="s">
@@ -46837,7 +46806,7 @@
       <c r="N351" s="38" t="s">
         <v>1732</v>
       </c>
-      <c r="O351" s="465" t="s">
+      <c r="O351" s="322" t="s">
         <v>1612</v>
       </c>
       <c r="P351" s="126"/>
@@ -46903,7 +46872,7 @@
       <c r="I352" s="43" t="s">
         <v>1017</v>
       </c>
-      <c r="J352" s="437" t="s">
+      <c r="J352" s="433" t="s">
         <v>886</v>
       </c>
       <c r="K352" s="35"/>
@@ -46989,7 +46958,7 @@
       <c r="N353" s="54" t="s">
         <v>1726</v>
       </c>
-      <c r="O353" s="463"/>
+      <c r="O353" s="455"/>
       <c r="P353" s="114"/>
       <c r="Q353" s="56"/>
       <c r="R353" s="150" t="s">
@@ -47825,7 +47794,7 @@
       <c r="Y364" s="30"/>
       <c r="Z364" s="103"/>
       <c r="AA364" s="30"/>
-      <c r="AB364" s="520" t="s">
+      <c r="AB364" s="509" t="s">
         <v>1865</v>
       </c>
       <c r="AC364" s="32"/>
@@ -47999,7 +47968,7 @@
       <c r="F367" s="16" t="s">
         <v>1898</v>
       </c>
-      <c r="G367" s="398"/>
+      <c r="G367" s="39"/>
       <c r="H367" s="48" t="s">
         <v>1899</v>
       </c>
@@ -48018,7 +47987,7 @@
       <c r="O367" s="54"/>
       <c r="P367" s="74"/>
       <c r="Q367" s="56"/>
-      <c r="R367" s="479" t="s">
+      <c r="R367" s="470" t="s">
         <v>544</v>
       </c>
       <c r="S367" s="32" t="s">
@@ -48066,7 +48035,7 @@
       <c r="F368" s="32" t="s">
         <v>1101</v>
       </c>
-      <c r="G368" s="398" t="s">
+      <c r="G368" s="39" t="s">
         <v>1904</v>
       </c>
       <c r="H368" s="95" t="s">
@@ -48091,7 +48060,7 @@
       <c r="Q368" s="318" t="s">
         <v>1910</v>
       </c>
-      <c r="R368" s="479" t="s">
+      <c r="R368" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S368" s="32" t="s">
@@ -48172,7 +48141,7 @@
       <c r="Q369" s="318" t="s">
         <v>1910</v>
       </c>
-      <c r="R369" s="479" t="s">
+      <c r="R369" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S369" s="32" t="s">
@@ -48228,7 +48197,7 @@
       <c r="F370" s="32" t="s">
         <v>1101</v>
       </c>
-      <c r="G370" s="398"/>
+      <c r="G370" s="39"/>
       <c r="H370" s="48" t="s">
         <v>1934</v>
       </c>
@@ -48249,7 +48218,7 @@
       <c r="O370" s="65"/>
       <c r="P370" s="25"/>
       <c r="Q370" s="56"/>
-      <c r="R370" s="495" t="s">
+      <c r="R370" s="484" t="s">
         <v>642</v>
       </c>
       <c r="S370" s="32" t="s">
@@ -48263,7 +48232,7 @@
       <c r="Y370" s="30"/>
       <c r="Z370" s="30"/>
       <c r="AA370" s="30"/>
-      <c r="AB370" s="520" t="s">
+      <c r="AB370" s="509" t="s">
         <v>1938</v>
       </c>
       <c r="AC370" s="32"/>
@@ -48318,7 +48287,7 @@
       <c r="O371" s="54"/>
       <c r="P371" s="55"/>
       <c r="Q371" s="56"/>
-      <c r="R371" s="479" t="s">
+      <c r="R371" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S371" s="32" t="s">
@@ -48366,7 +48335,7 @@
       <c r="F372" s="47" t="s">
         <v>1957</v>
       </c>
-      <c r="G372" s="398"/>
+      <c r="G372" s="39"/>
       <c r="H372" s="95" t="s">
         <v>1958</v>
       </c>
@@ -48407,7 +48376,7 @@
       <c r="Y372" s="30"/>
       <c r="Z372" s="30"/>
       <c r="AA372" s="30"/>
-      <c r="AB372" s="520" t="s">
+      <c r="AB372" s="509" t="s">
         <v>1965</v>
       </c>
       <c r="AC372" s="32"/>
@@ -48462,7 +48431,7 @@
       <c r="O373" s="38"/>
       <c r="P373" s="25"/>
       <c r="Q373" s="26"/>
-      <c r="R373" s="479" t="s">
+      <c r="R373" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S373" s="32" t="s">
@@ -48505,10 +48474,10 @@
       </c>
       <c r="D374" s="235"/>
       <c r="E374" s="58"/>
-      <c r="F374" s="422" t="s">
+      <c r="F374" s="419" t="s">
         <v>1972</v>
       </c>
-      <c r="G374" s="398"/>
+      <c r="G374" s="39"/>
       <c r="H374" s="48" t="s">
         <v>1973</v>
       </c>
@@ -48533,7 +48502,7 @@
       <c r="Q374" s="26" t="s">
         <v>1963</v>
       </c>
-      <c r="R374" s="398" t="s">
+      <c r="R374" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S374" s="32" t="s">
@@ -48599,7 +48568,7 @@
       <c r="N375" s="54" t="s">
         <v>3987</v>
       </c>
-      <c r="O375" s="463"/>
+      <c r="O375" s="455"/>
       <c r="P375" s="126" t="s">
         <v>1909</v>
       </c>
@@ -48652,66 +48621,66 @@
       <c r="B376" s="14" t="s">
         <v>1007</v>
       </c>
-      <c r="C376" s="402" t="s">
+      <c r="C376" s="401" t="s">
         <v>171</v>
       </c>
-      <c r="D376" s="413"/>
-      <c r="E376" s="417"/>
-      <c r="F376" s="398" t="s">
+      <c r="D376" s="337"/>
+      <c r="E376" s="414"/>
+      <c r="F376" s="39" t="s">
         <v>1101</v>
       </c>
-      <c r="G376" s="398" t="s">
+      <c r="G376" s="39" t="s">
         <v>2035</v>
       </c>
-      <c r="H376" s="429" t="s">
+      <c r="H376" s="426" t="s">
         <v>2036</v>
       </c>
-      <c r="I376" s="434" t="s">
+      <c r="I376" s="338" t="s">
         <v>2037</v>
       </c>
-      <c r="J376" s="439"/>
-      <c r="K376" s="439"/>
-      <c r="L376" s="439"/>
-      <c r="M376" s="448" t="s">
+      <c r="J376" s="435"/>
+      <c r="K376" s="435"/>
+      <c r="L376" s="435"/>
+      <c r="M376" s="444" t="s">
         <v>3993</v>
       </c>
-      <c r="N376" s="463" t="s">
+      <c r="N376" s="455" t="s">
         <v>2038</v>
       </c>
-      <c r="O376" s="463"/>
-      <c r="P376" s="474" t="s">
+      <c r="O376" s="455"/>
+      <c r="P376" s="465" t="s">
         <v>1909</v>
       </c>
-      <c r="Q376" s="474" t="s">
+      <c r="Q376" s="465" t="s">
         <v>1910</v>
       </c>
-      <c r="R376" s="479" t="s">
+      <c r="R376" s="470" t="s">
         <v>387</v>
       </c>
-      <c r="S376" s="398" t="s">
+      <c r="S376" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="T376" s="428" t="s">
+      <c r="T376" s="425" t="s">
         <v>2039</v>
       </c>
-      <c r="U376" s="504" t="s">
+      <c r="U376" s="493" t="s">
         <v>1909</v>
       </c>
-      <c r="V376" s="504" t="s">
+      <c r="V376" s="493" t="s">
         <v>1910</v>
       </c>
-      <c r="W376" s="510"/>
-      <c r="X376" s="510"/>
-      <c r="Y376" s="514" t="s">
+      <c r="W376" s="499"/>
+      <c r="X376" s="499"/>
+      <c r="Y376" s="503" t="s">
         <v>2040</v>
       </c>
-      <c r="Z376" s="514"/>
-      <c r="AA376" s="514"/>
-      <c r="AB376" s="521"/>
-      <c r="AC376" s="398" t="s">
+      <c r="Z376" s="503"/>
+      <c r="AA376" s="503"/>
+      <c r="AB376" s="510"/>
+      <c r="AC376" s="39" t="s">
         <v>1912</v>
       </c>
-      <c r="AD376" s="398"/>
+      <c r="AD376" s="39"/>
       <c r="AE376" s="230"/>
       <c r="AF376" s="230"/>
       <c r="AG376" s="230"/>
@@ -48766,7 +48735,7 @@
       <c r="Q377" s="318" t="s">
         <v>1910</v>
       </c>
-      <c r="R377" s="479" t="s">
+      <c r="R377" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S377" s="32" t="s">
@@ -48843,7 +48812,7 @@
       <c r="Q378" s="180" t="s">
         <v>2078</v>
       </c>
-      <c r="R378" s="398" t="s">
+      <c r="R378" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S378" s="32" t="s">
@@ -48915,10 +48884,10 @@
       <c r="N379" s="89" t="s">
         <v>2088</v>
       </c>
-      <c r="O379" s="470"/>
+      <c r="O379" s="461"/>
       <c r="P379" s="114"/>
       <c r="Q379" s="56"/>
-      <c r="R379" s="457" t="s">
+      <c r="R379" s="339" t="s">
         <v>139</v>
       </c>
       <c r="S379" s="32" t="s">
@@ -48956,33 +48925,33 @@
       <c r="B380" s="396" t="s">
         <v>2089</v>
       </c>
-      <c r="C380" s="401" t="s">
+      <c r="C380" s="400" t="s">
         <v>3803</v>
       </c>
-      <c r="D380" s="414"/>
-      <c r="E380" s="416"/>
-      <c r="F380" s="416" t="s">
+      <c r="D380" s="411"/>
+      <c r="E380" s="413"/>
+      <c r="F380" s="413" t="s">
         <v>3800</v>
       </c>
-      <c r="G380" s="416" t="s">
+      <c r="G380" s="413" t="s">
         <v>3801</v>
       </c>
-      <c r="H380" s="399" t="s">
+      <c r="H380" s="398" t="s">
         <v>3995</v>
       </c>
       <c r="I380" s="320" t="s">
         <v>1916</v>
       </c>
-      <c r="J380" s="427"/>
-      <c r="K380" s="427"/>
-      <c r="L380" s="427"/>
+      <c r="J380" s="424"/>
+      <c r="K380" s="424"/>
+      <c r="L380" s="424"/>
       <c r="M380" s="320" t="s">
         <v>3993</v>
       </c>
       <c r="N380" s="134" t="s">
         <v>2090</v>
       </c>
-      <c r="O380" s="462"/>
+      <c r="O380" s="454"/>
       <c r="P380" s="318" t="s">
         <v>1909</v>
       </c>
@@ -48992,30 +48961,30 @@
       <c r="R380" s="327" t="s">
         <v>387</v>
       </c>
-      <c r="S380" s="399" t="s">
+      <c r="S380" s="398" t="s">
         <v>41</v>
       </c>
-      <c r="T380" s="399" t="s">
+      <c r="T380" s="398" t="s">
         <v>3802</v>
       </c>
-      <c r="U380" s="399" t="s">
+      <c r="U380" s="398" t="s">
         <v>1909</v>
       </c>
-      <c r="V380" s="399" t="s">
+      <c r="V380" s="398" t="s">
         <v>1910</v>
       </c>
-      <c r="W380" s="416"/>
-      <c r="X380" s="416"/>
-      <c r="Y380" s="419" t="s">
+      <c r="W380" s="413"/>
+      <c r="X380" s="413"/>
+      <c r="Y380" s="416" t="s">
         <v>3984</v>
       </c>
-      <c r="Z380" s="427"/>
-      <c r="AA380" s="416"/>
-      <c r="AB380" s="427"/>
-      <c r="AC380" s="399" t="s">
+      <c r="Z380" s="424"/>
+      <c r="AA380" s="413"/>
+      <c r="AB380" s="424"/>
+      <c r="AC380" s="398" t="s">
         <v>2091</v>
       </c>
-      <c r="AD380" s="416" t="s">
+      <c r="AD380" s="413" t="s">
         <v>3985</v>
       </c>
       <c r="AE380" s="32"/>
@@ -49036,32 +49005,32 @@
       <c r="A381" s="396" t="s">
         <v>3795</v>
       </c>
-      <c r="B381" s="399" t="s">
+      <c r="B381" s="398" t="s">
         <v>3796</v>
       </c>
-      <c r="C381" s="401" t="s">
+      <c r="C381" s="400" t="s">
         <v>3803</v>
       </c>
-      <c r="D381" s="414"/>
-      <c r="E381" s="416"/>
-      <c r="F381" s="427"/>
-      <c r="G381" s="399"/>
-      <c r="H381" s="399" t="s">
+      <c r="D381" s="411"/>
+      <c r="E381" s="413"/>
+      <c r="F381" s="424"/>
+      <c r="G381" s="398"/>
+      <c r="H381" s="398" t="s">
         <v>3996</v>
       </c>
       <c r="I381" s="320" t="s">
         <v>2037</v>
       </c>
-      <c r="J381" s="427"/>
-      <c r="K381" s="427"/>
-      <c r="L381" s="427"/>
+      <c r="J381" s="424"/>
+      <c r="K381" s="424"/>
+      <c r="L381" s="424"/>
       <c r="M381" s="320" t="s">
         <v>3993</v>
       </c>
-      <c r="N381" s="462" t="s">
+      <c r="N381" s="454" t="s">
         <v>2090</v>
       </c>
-      <c r="O381" s="462"/>
+      <c r="O381" s="454"/>
       <c r="P381" s="318" t="s">
         <v>1909</v>
       </c>
@@ -49071,28 +49040,28 @@
       <c r="R381" s="327" t="s">
         <v>387</v>
       </c>
-      <c r="S381" s="399" t="s">
+      <c r="S381" s="398" t="s">
         <v>41</v>
       </c>
-      <c r="T381" s="399" t="s">
+      <c r="T381" s="398" t="s">
         <v>3797</v>
       </c>
-      <c r="U381" s="399" t="s">
+      <c r="U381" s="398" t="s">
         <v>1909</v>
       </c>
-      <c r="V381" s="399" t="s">
+      <c r="V381" s="398" t="s">
         <v>1910</v>
       </c>
-      <c r="W381" s="416"/>
-      <c r="X381" s="416"/>
-      <c r="Y381" s="399" t="s">
+      <c r="W381" s="413"/>
+      <c r="X381" s="413"/>
+      <c r="Y381" s="398" t="s">
         <v>3798</v>
       </c>
       <c r="Z381" s="230"/>
-      <c r="AA381" s="416"/>
-      <c r="AB381" s="427"/>
-      <c r="AC381" s="399"/>
-      <c r="AD381" s="416"/>
+      <c r="AA381" s="413"/>
+      <c r="AB381" s="424"/>
+      <c r="AC381" s="398"/>
+      <c r="AD381" s="413"/>
       <c r="AE381" s="377"/>
       <c r="AF381" s="377"/>
       <c r="AG381" s="377"/>
@@ -49119,7 +49088,7 @@
       </c>
       <c r="D382" s="235"/>
       <c r="E382" s="58"/>
-      <c r="F382" s="421" t="s">
+      <c r="F382" s="418" t="s">
         <v>2093</v>
       </c>
       <c r="G382" s="32" t="s">
@@ -49145,7 +49114,7 @@
       <c r="O382" s="54"/>
       <c r="P382" s="55"/>
       <c r="Q382" s="56"/>
-      <c r="R382" s="482" t="s">
+      <c r="R382" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S382" s="32" t="s">
@@ -49199,7 +49168,7 @@
       <c r="F383" s="16" t="s">
         <v>2102</v>
       </c>
-      <c r="G383" s="398" t="s">
+      <c r="G383" s="39" t="s">
         <v>2103</v>
       </c>
       <c r="H383" s="48" t="s">
@@ -49339,7 +49308,7 @@
       <c r="F385" s="16" t="s">
         <v>2124</v>
       </c>
-      <c r="G385" s="398"/>
+      <c r="G385" s="39"/>
       <c r="H385" s="32" t="s">
         <v>2125</v>
       </c>
@@ -49360,7 +49329,7 @@
       <c r="O385" s="54"/>
       <c r="P385" s="55"/>
       <c r="Q385" s="56"/>
-      <c r="R385" s="479" t="s">
+      <c r="R385" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S385" s="32" t="s">
@@ -49408,7 +49377,7 @@
       <c r="F386" s="47" t="s">
         <v>2132</v>
       </c>
-      <c r="G386" s="398"/>
+      <c r="G386" s="39"/>
       <c r="H386" s="95" t="s">
         <v>2133</v>
       </c>
@@ -49433,7 +49402,7 @@
       <c r="Q386" s="56" t="s">
         <v>2120</v>
       </c>
-      <c r="R386" s="398" t="s">
+      <c r="R386" s="39" t="s">
         <v>2138</v>
       </c>
       <c r="S386" s="21" t="s">
@@ -49481,7 +49450,7 @@
       <c r="F387" s="47" t="s">
         <v>2141</v>
       </c>
-      <c r="G387" s="398"/>
+      <c r="G387" s="39"/>
       <c r="H387" s="32" t="s">
         <v>2142</v>
       </c>
@@ -49575,7 +49544,7 @@
       <c r="O388" s="133"/>
       <c r="P388" s="90"/>
       <c r="Q388" s="91"/>
-      <c r="R388" s="482" t="s">
+      <c r="R388" s="471" t="s">
         <v>1065</v>
       </c>
       <c r="S388" s="21" t="s">
@@ -49625,56 +49594,56 @@
       <c r="B389" s="393" t="s">
         <v>434</v>
       </c>
-      <c r="C389" s="402" t="s">
+      <c r="C389" s="401" t="s">
         <v>171</v>
       </c>
-      <c r="D389" s="413"/>
-      <c r="E389" s="417"/>
-      <c r="F389" s="421" t="s">
+      <c r="D389" s="337"/>
+      <c r="E389" s="414"/>
+      <c r="F389" s="418" t="s">
         <v>2159</v>
       </c>
-      <c r="G389" s="398"/>
-      <c r="H389" s="398" t="s">
+      <c r="G389" s="39"/>
+      <c r="H389" s="39" t="s">
         <v>2160</v>
       </c>
-      <c r="I389" s="434" t="s">
+      <c r="I389" s="338" t="s">
         <v>2161</v>
       </c>
-      <c r="J389" s="439"/>
-      <c r="K389" s="439"/>
-      <c r="L389" s="439" t="s">
+      <c r="J389" s="435"/>
+      <c r="K389" s="435"/>
+      <c r="L389" s="435" t="s">
         <v>2162</v>
       </c>
       <c r="M389" s="391" t="s">
         <v>2163</v>
       </c>
-      <c r="N389" s="465" t="s">
+      <c r="N389" s="322" t="s">
         <v>2164</v>
       </c>
-      <c r="O389" s="465" t="s">
+      <c r="O389" s="322" t="s">
         <v>2119</v>
       </c>
-      <c r="P389" s="475"/>
-      <c r="Q389" s="477" t="s">
+      <c r="P389" s="466"/>
+      <c r="Q389" s="468" t="s">
         <v>2165</v>
       </c>
-      <c r="R389" s="480" t="s">
+      <c r="R389" s="333" t="s">
         <v>40</v>
       </c>
-      <c r="S389" s="398" t="s">
+      <c r="S389" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="T389" s="428"/>
-      <c r="U389" s="504"/>
-      <c r="V389" s="504"/>
-      <c r="W389" s="510"/>
-      <c r="X389" s="510"/>
-      <c r="Y389" s="514"/>
-      <c r="Z389" s="514"/>
-      <c r="AA389" s="514"/>
-      <c r="AB389" s="521"/>
-      <c r="AC389" s="398"/>
-      <c r="AD389" s="398"/>
+      <c r="T389" s="425"/>
+      <c r="U389" s="493"/>
+      <c r="V389" s="493"/>
+      <c r="W389" s="499"/>
+      <c r="X389" s="499"/>
+      <c r="Y389" s="503"/>
+      <c r="Z389" s="503"/>
+      <c r="AA389" s="503"/>
+      <c r="AB389" s="510"/>
+      <c r="AC389" s="39"/>
+      <c r="AD389" s="39"/>
       <c r="AE389" s="230"/>
       <c r="AF389" s="230"/>
       <c r="AG389" s="230"/>
@@ -49722,14 +49691,14 @@
       <c r="N390" s="38" t="s">
         <v>2172</v>
       </c>
-      <c r="O390" s="465"/>
+      <c r="O390" s="322"/>
       <c r="P390" s="70" t="s">
         <v>2119</v>
       </c>
       <c r="Q390" s="26" t="s">
         <v>2120</v>
       </c>
-      <c r="R390" s="480" t="s">
+      <c r="R390" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S390" s="32" t="s">
@@ -49800,7 +49769,7 @@
       <c r="O391" s="54"/>
       <c r="P391" s="55"/>
       <c r="Q391" s="56"/>
-      <c r="R391" s="480" t="s">
+      <c r="R391" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S391" s="32" t="s">
@@ -49859,7 +49828,7 @@
       <c r="I392" s="43" t="s">
         <v>2200</v>
       </c>
-      <c r="J392" s="438" t="s">
+      <c r="J392" s="434" t="s">
         <v>2201</v>
       </c>
       <c r="K392" s="104"/>
@@ -49911,19 +49880,19 @@
       <c r="B393" s="393" t="s">
         <v>434</v>
       </c>
-      <c r="C393" s="406" t="s">
+      <c r="C393" s="405" t="s">
         <v>2203</v>
       </c>
-      <c r="D393" s="413"/>
+      <c r="D393" s="337"/>
       <c r="E393" s="138"/>
       <c r="F393" s="328" t="s">
         <v>2204</v>
       </c>
       <c r="G393" s="32"/>
-      <c r="H393" s="398" t="s">
+      <c r="H393" s="39" t="s">
         <v>2205</v>
       </c>
-      <c r="I393" s="434" t="s">
+      <c r="I393" s="338" t="s">
         <v>2206</v>
       </c>
       <c r="J393" s="82"/>
@@ -49932,16 +49901,16 @@
       <c r="M393" s="95" t="s">
         <v>2207</v>
       </c>
-      <c r="N393" s="465" t="s">
+      <c r="N393" s="322" t="s">
         <v>2208</v>
       </c>
-      <c r="O393" s="465"/>
+      <c r="O393" s="322"/>
       <c r="P393" s="126"/>
       <c r="Q393" s="135"/>
-      <c r="R393" s="486" t="s">
+      <c r="R393" s="475" t="s">
         <v>40</v>
       </c>
-      <c r="S393" s="398" t="s">
+      <c r="S393" s="39" t="s">
         <v>41</v>
       </c>
       <c r="T393" s="105"/>
@@ -49953,7 +49922,7 @@
       <c r="Z393" s="103"/>
       <c r="AA393" s="103"/>
       <c r="AB393" s="110"/>
-      <c r="AC393" s="398"/>
+      <c r="AC393" s="39"/>
       <c r="AD393" s="105"/>
       <c r="AE393" s="39"/>
       <c r="AF393" s="39"/>
@@ -50127,7 +50096,7 @@
       </c>
       <c r="D396" s="235"/>
       <c r="E396" s="58"/>
-      <c r="F396" s="422" t="s">
+      <c r="F396" s="419" t="s">
         <v>2223</v>
       </c>
       <c r="G396" s="32"/>
@@ -50494,7 +50463,7 @@
       <c r="I401" s="43" t="s">
         <v>2282</v>
       </c>
-      <c r="J401" s="442" t="s">
+      <c r="J401" s="438" t="s">
         <v>2283</v>
       </c>
       <c r="K401" s="109"/>
@@ -50508,7 +50477,7 @@
       <c r="O401" s="54"/>
       <c r="P401" s="55"/>
       <c r="Q401" s="56"/>
-      <c r="R401" s="398" t="s">
+      <c r="R401" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S401" s="32" t="s">
@@ -50577,7 +50546,7 @@
       <c r="O402" s="73"/>
       <c r="P402" s="74"/>
       <c r="Q402" s="75"/>
-      <c r="R402" s="398" t="s">
+      <c r="R402" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S402" s="32" t="s">
@@ -50648,7 +50617,7 @@
       <c r="O403" s="38"/>
       <c r="P403" s="25"/>
       <c r="Q403" s="26"/>
-      <c r="R403" s="398" t="s">
+      <c r="R403" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S403" s="32" t="s">
@@ -50708,7 +50677,7 @@
       <c r="J404" s="22"/>
       <c r="K404" s="22"/>
       <c r="L404" s="22"/>
-      <c r="M404" s="449" t="s">
+      <c r="M404" s="445" t="s">
         <v>3993</v>
       </c>
       <c r="N404" s="38" t="s">
@@ -50721,7 +50690,7 @@
       <c r="Q404" s="318" t="s">
         <v>1910</v>
       </c>
-      <c r="R404" s="479" t="s">
+      <c r="R404" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S404" s="32" t="s">
@@ -50854,7 +50823,7 @@
       </c>
       <c r="K406" s="22"/>
       <c r="L406" s="22"/>
-      <c r="M406" s="451" t="s">
+      <c r="M406" s="447" t="s">
         <v>2087</v>
       </c>
       <c r="N406" s="54" t="s">
@@ -50863,7 +50832,7 @@
       <c r="O406" s="54"/>
       <c r="P406" s="55"/>
       <c r="Q406" s="56"/>
-      <c r="R406" s="398" t="s">
+      <c r="R406" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S406" s="32" t="s">
@@ -51270,7 +51239,7 @@
       <c r="F412" s="32" t="s">
         <v>2295</v>
       </c>
-      <c r="G412" s="398" t="s">
+      <c r="G412" s="39" t="s">
         <v>2368</v>
       </c>
       <c r="H412" s="48" t="s">
@@ -51416,7 +51385,7 @@
       <c r="J414" s="22"/>
       <c r="K414" s="22"/>
       <c r="L414" s="22"/>
-      <c r="M414" s="449" t="s">
+      <c r="M414" s="445" t="s">
         <v>3993</v>
       </c>
       <c r="N414" s="54" t="s">
@@ -51467,7 +51436,7 @@
       <c r="B415" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C415" s="402" t="s">
+      <c r="C415" s="401" t="s">
         <v>171</v>
       </c>
       <c r="D415" s="235"/>
@@ -51498,7 +51467,7 @@
       <c r="O415" s="54"/>
       <c r="P415" s="55"/>
       <c r="Q415" s="56"/>
-      <c r="R415" s="398" t="s">
+      <c r="R415" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S415" s="32" t="s">
@@ -51556,7 +51525,7 @@
       </c>
       <c r="K416" s="22"/>
       <c r="L416" s="22"/>
-      <c r="M416" s="461" t="s">
+      <c r="M416" s="324" t="s">
         <v>2416</v>
       </c>
       <c r="N416" s="54" t="s">
@@ -51580,7 +51549,7 @@
       <c r="V416" s="28"/>
       <c r="W416" s="29"/>
       <c r="X416" s="29"/>
-      <c r="Y416" s="517" t="s">
+      <c r="Y416" s="506" t="s">
         <v>2418</v>
       </c>
       <c r="Z416" s="30" t="s">
@@ -51618,7 +51587,7 @@
       </c>
       <c r="D417" s="235"/>
       <c r="E417" s="58"/>
-      <c r="F417" s="422" t="s">
+      <c r="F417" s="419" t="s">
         <v>2422</v>
       </c>
       <c r="G417" s="32" t="s">
@@ -51692,7 +51661,7 @@
       <c r="B418" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="C418" s="406" t="s">
+      <c r="C418" s="405" t="s">
         <v>2426</v>
       </c>
       <c r="D418" s="235"/>
@@ -51802,7 +51771,7 @@
       <c r="O419" s="38"/>
       <c r="P419" s="25"/>
       <c r="Q419" s="26"/>
-      <c r="R419" s="398" t="s">
+      <c r="R419" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S419" s="32" t="s">
@@ -51869,7 +51838,7 @@
       <c r="O420" s="89"/>
       <c r="P420" s="90"/>
       <c r="Q420" s="91"/>
-      <c r="R420" s="486" t="s">
+      <c r="R420" s="475" t="s">
         <v>40</v>
       </c>
       <c r="S420" s="32" t="s">
@@ -51940,7 +51909,7 @@
       <c r="Q421" s="56" t="s">
         <v>1910</v>
       </c>
-      <c r="R421" s="479" t="s">
+      <c r="R421" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S421" s="32" t="s">
@@ -52019,7 +51988,7 @@
       <c r="Q422" s="56" t="s">
         <v>995</v>
       </c>
-      <c r="R422" s="398" t="s">
+      <c r="R422" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S422" s="32" t="s">
@@ -52156,7 +52125,7 @@
       <c r="N424" s="38" t="s">
         <v>2484</v>
       </c>
-      <c r="O424" s="465" t="s">
+      <c r="O424" s="322" t="s">
         <v>738</v>
       </c>
       <c r="P424" s="126"/>
@@ -52223,7 +52192,7 @@
       <c r="J425" s="22"/>
       <c r="K425" s="22"/>
       <c r="L425" s="22"/>
-      <c r="M425" s="455" t="s">
+      <c r="M425" s="449" t="s">
         <v>657</v>
       </c>
       <c r="N425" s="38" t="s">
@@ -52290,7 +52259,7 @@
       <c r="J426" s="22"/>
       <c r="K426" s="22"/>
       <c r="L426" s="22"/>
-      <c r="M426" s="454" t="s">
+      <c r="M426" s="323" t="s">
         <v>2496</v>
       </c>
       <c r="N426" s="38" t="s">
@@ -52511,7 +52480,7 @@
       <c r="N429" s="38" t="s">
         <v>2534</v>
       </c>
-      <c r="O429" s="465" t="s">
+      <c r="O429" s="322" t="s">
         <v>38</v>
       </c>
       <c r="P429" s="126"/>
@@ -52779,7 +52748,7 @@
       <c r="B433" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C433" s="404" t="s">
+      <c r="C433" s="403" t="s">
         <v>171</v>
       </c>
       <c r="D433" s="235"/>
@@ -52889,7 +52858,7 @@
       <c r="S434" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="T434" s="502" t="s">
+      <c r="T434" s="491" t="s">
         <v>2600</v>
       </c>
       <c r="U434" s="28"/>
@@ -53316,14 +53285,14 @@
       <c r="N440" s="38" t="s">
         <v>2787</v>
       </c>
-      <c r="O440" s="465"/>
+      <c r="O440" s="322"/>
       <c r="P440" s="126" t="s">
         <v>2788</v>
       </c>
       <c r="Q440" s="56" t="s">
         <v>2789</v>
       </c>
-      <c r="R440" s="484" t="s">
+      <c r="R440" s="473" t="s">
         <v>2790</v>
       </c>
       <c r="S440" s="77" t="s">
@@ -53389,7 +53358,7 @@
       <c r="N441" s="54" t="s">
         <v>2819</v>
       </c>
-      <c r="O441" s="466"/>
+      <c r="O441" s="457"/>
       <c r="P441" s="70" t="s">
         <v>2809</v>
       </c>
@@ -53537,7 +53506,7 @@
       <c r="N443" s="54" t="s">
         <v>2994</v>
       </c>
-      <c r="O443" s="463"/>
+      <c r="O443" s="455"/>
       <c r="P443" s="126" t="s">
         <v>1909</v>
       </c>
@@ -53736,52 +53705,52 @@
       <c r="B446" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C446" s="401" t="s">
+      <c r="C446" s="400" t="s">
         <v>171</v>
       </c>
-      <c r="D446" s="414"/>
-      <c r="E446" s="416"/>
-      <c r="F446" s="419" t="s">
+      <c r="D446" s="411"/>
+      <c r="E446" s="413"/>
+      <c r="F446" s="416" t="s">
         <v>3847</v>
       </c>
-      <c r="G446" s="416"/>
-      <c r="H446" s="399" t="s">
+      <c r="G446" s="413"/>
+      <c r="H446" s="398" t="s">
         <v>3804</v>
       </c>
-      <c r="I446" s="399" t="s">
+      <c r="I446" s="398" t="s">
         <v>3107</v>
       </c>
-      <c r="J446" s="416"/>
-      <c r="K446" s="416"/>
-      <c r="L446" s="416"/>
-      <c r="M446" s="452" t="s">
+      <c r="J446" s="413"/>
+      <c r="K446" s="413"/>
+      <c r="L446" s="413"/>
+      <c r="M446" s="448" t="s">
         <v>2087</v>
       </c>
-      <c r="N446" s="462" t="s">
+      <c r="N446" s="454" t="s">
         <v>2088</v>
       </c>
-      <c r="O446" s="416"/>
-      <c r="P446" s="416"/>
-      <c r="Q446" s="416"/>
-      <c r="R446" s="416" t="s">
+      <c r="O446" s="413"/>
+      <c r="P446" s="413"/>
+      <c r="Q446" s="413"/>
+      <c r="R446" s="413" t="s">
         <v>642</v>
       </c>
-      <c r="S446" s="399" t="s">
+      <c r="S446" s="398" t="s">
         <v>41</v>
       </c>
-      <c r="T446" s="399" t="s">
+      <c r="T446" s="398" t="s">
         <v>3805</v>
       </c>
-      <c r="U446" s="416"/>
-      <c r="V446" s="416"/>
-      <c r="W446" s="416"/>
-      <c r="X446" s="416"/>
-      <c r="Y446" s="416"/>
-      <c r="Z446" s="416"/>
-      <c r="AA446" s="416"/>
-      <c r="AB446" s="416"/>
-      <c r="AC446" s="416"/>
-      <c r="AD446" s="399" t="s">
+      <c r="U446" s="413"/>
+      <c r="V446" s="413"/>
+      <c r="W446" s="413"/>
+      <c r="X446" s="413"/>
+      <c r="Y446" s="413"/>
+      <c r="Z446" s="413"/>
+      <c r="AA446" s="413"/>
+      <c r="AB446" s="413"/>
+      <c r="AC446" s="413"/>
+      <c r="AD446" s="398" t="s">
         <v>3806</v>
       </c>
       <c r="AE446" s="32"/>
@@ -53805,7 +53774,7 @@
       <c r="B447" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C447" s="406" t="s">
+      <c r="C447" s="405" t="s">
         <v>3160</v>
       </c>
       <c r="D447" s="235"/>
@@ -54012,54 +53981,54 @@
       <c r="B450" s="320" t="s">
         <v>3807</v>
       </c>
-      <c r="C450" s="405" t="s">
+      <c r="C450" s="404" t="s">
         <v>171</v>
       </c>
-      <c r="D450" s="414"/>
-      <c r="E450" s="416"/>
-      <c r="F450" s="419" t="s">
+      <c r="D450" s="411"/>
+      <c r="E450" s="413"/>
+      <c r="F450" s="416" t="s">
         <v>3808</v>
       </c>
-      <c r="G450" s="416"/>
-      <c r="H450" s="432" t="s">
+      <c r="G450" s="413"/>
+      <c r="H450" s="429" t="s">
         <v>3809</v>
       </c>
-      <c r="I450" s="432" t="s">
+      <c r="I450" s="429" t="s">
         <v>3192</v>
       </c>
-      <c r="J450" s="427"/>
-      <c r="K450" s="427"/>
-      <c r="L450" s="416" t="s">
+      <c r="J450" s="424"/>
+      <c r="K450" s="424"/>
+      <c r="L450" s="413" t="s">
         <v>3810</v>
       </c>
-      <c r="M450" s="452" t="s">
+      <c r="M450" s="448" t="s">
         <v>2087</v>
       </c>
-      <c r="N450" s="462" t="s">
+      <c r="N450" s="454" t="s">
         <v>2088</v>
       </c>
-      <c r="O450" s="416"/>
-      <c r="P450" s="416"/>
-      <c r="Q450" s="416"/>
-      <c r="R450" s="416" t="s">
+      <c r="O450" s="413"/>
+      <c r="P450" s="413"/>
+      <c r="Q450" s="413"/>
+      <c r="R450" s="413" t="s">
         <v>642</v>
       </c>
-      <c r="S450" s="399" t="s">
+      <c r="S450" s="398" t="s">
         <v>41</v>
       </c>
-      <c r="T450" s="399" t="s">
+      <c r="T450" s="398" t="s">
         <v>3811</v>
       </c>
-      <c r="U450" s="416"/>
-      <c r="V450" s="416"/>
-      <c r="W450" s="416"/>
-      <c r="X450" s="416"/>
-      <c r="Y450" s="416"/>
-      <c r="Z450" s="416"/>
-      <c r="AA450" s="416"/>
-      <c r="AB450" s="416"/>
-      <c r="AC450" s="416"/>
-      <c r="AD450" s="399" t="s">
+      <c r="U450" s="413"/>
+      <c r="V450" s="413"/>
+      <c r="W450" s="413"/>
+      <c r="X450" s="413"/>
+      <c r="Y450" s="413"/>
+      <c r="Z450" s="413"/>
+      <c r="AA450" s="413"/>
+      <c r="AB450" s="413"/>
+      <c r="AC450" s="413"/>
+      <c r="AD450" s="398" t="s">
         <v>3812</v>
       </c>
       <c r="AE450" s="32"/>
@@ -54459,7 +54428,7 @@
       <c r="O456" s="38"/>
       <c r="P456" s="25"/>
       <c r="Q456" s="26"/>
-      <c r="R456" s="479" t="s">
+      <c r="R456" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S456" s="207" t="s">
@@ -54530,7 +54499,7 @@
       <c r="O457" s="38"/>
       <c r="P457" s="25"/>
       <c r="Q457" s="56"/>
-      <c r="R457" s="457" t="s">
+      <c r="R457" s="339" t="s">
         <v>139</v>
       </c>
       <c r="S457" s="207" t="s">
@@ -54568,7 +54537,7 @@
       <c r="B458" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C458" s="403" t="s">
+      <c r="C458" s="402" t="s">
         <v>3982</v>
       </c>
       <c r="D458" s="235"/>
@@ -54664,7 +54633,7 @@
       <c r="O459" s="137"/>
       <c r="P459" s="55"/>
       <c r="Q459" s="56"/>
-      <c r="R459" s="489" t="s">
+      <c r="R459" s="478" t="s">
         <v>642</v>
       </c>
       <c r="S459" s="77" t="s">
@@ -54731,7 +54700,7 @@
       <c r="O460" s="137"/>
       <c r="P460" s="55"/>
       <c r="Q460" s="56"/>
-      <c r="R460" s="454" t="s">
+      <c r="R460" s="323" t="s">
         <v>642</v>
       </c>
       <c r="S460" s="77" t="s">
@@ -54793,12 +54762,12 @@
       <c r="N461" s="38" t="s">
         <v>3470</v>
       </c>
-      <c r="O461" s="465"/>
-      <c r="P461" s="473" t="s">
+      <c r="O461" s="322"/>
+      <c r="P461" s="464"/>
+      <c r="Q461" s="464" t="s">
         <v>3992</v>
       </c>
-      <c r="Q461" s="26"/>
-      <c r="R461" s="479" t="s">
+      <c r="R461" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S461" s="77" t="s">
@@ -54863,7 +54832,7 @@
       <c r="O462" s="38"/>
       <c r="P462" s="25"/>
       <c r="Q462" s="26"/>
-      <c r="R462" s="479" t="s">
+      <c r="R462" s="470" t="s">
         <v>387</v>
       </c>
       <c r="S462" s="209" t="s">
@@ -54995,7 +54964,7 @@
       <c r="O464" s="54"/>
       <c r="P464" s="55"/>
       <c r="Q464" s="56"/>
-      <c r="R464" s="479" t="s">
+      <c r="R464" s="470" t="s">
         <v>80</v>
       </c>
       <c r="S464" s="209" t="s">
@@ -55062,7 +55031,7 @@
       <c r="O465" s="54"/>
       <c r="P465" s="55"/>
       <c r="Q465" s="56"/>
-      <c r="R465" s="491" t="s">
+      <c r="R465" s="480" t="s">
         <v>642</v>
       </c>
       <c r="S465" s="209" t="s">
@@ -55131,7 +55100,7 @@
       <c r="O466" s="54"/>
       <c r="P466" s="55"/>
       <c r="Q466" s="56"/>
-      <c r="R466" s="480" t="s">
+      <c r="R466" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S466" s="77" t="s">
@@ -55264,7 +55233,7 @@
       </c>
       <c r="K468" s="22"/>
       <c r="L468" s="22"/>
-      <c r="M468" s="434" t="s">
+      <c r="M468" s="338" t="s">
         <v>137</v>
       </c>
       <c r="N468" s="54" t="s">
@@ -55335,7 +55304,7 @@
       <c r="N469" s="89" t="s">
         <v>3594</v>
       </c>
-      <c r="O469" s="470"/>
+      <c r="O469" s="461"/>
       <c r="P469" s="70"/>
       <c r="Q469" s="91"/>
       <c r="R469" s="117" t="s">
@@ -55384,7 +55353,7 @@
       <c r="F470" s="290" t="s">
         <v>3596</v>
       </c>
-      <c r="G470" s="398" t="s">
+      <c r="G470" s="39" t="s">
         <v>3597</v>
       </c>
       <c r="H470" s="48" t="s">
@@ -55457,7 +55426,7 @@
       <c r="F471" s="16" t="s">
         <v>3632</v>
       </c>
-      <c r="G471" s="398" t="s">
+      <c r="G471" s="39" t="s">
         <v>3633</v>
       </c>
       <c r="H471" s="32" t="s">
@@ -55530,7 +55499,7 @@
       <c r="F472" s="302" t="s">
         <v>3666</v>
       </c>
-      <c r="G472" s="430" t="s">
+      <c r="G472" s="427" t="s">
         <v>2296</v>
       </c>
       <c r="H472" s="302" t="s">
@@ -55539,11 +55508,11 @@
       <c r="I472" s="303" t="s">
         <v>3668</v>
       </c>
-      <c r="J472" s="441" t="s">
+      <c r="J472" s="437" t="s">
         <v>2283</v>
       </c>
-      <c r="K472" s="441"/>
-      <c r="L472" s="441"/>
+      <c r="K472" s="437"/>
+      <c r="L472" s="437"/>
       <c r="M472" s="304" t="s">
         <v>1605</v>
       </c>
@@ -55596,14 +55565,14 @@
       </c>
       <c r="D473" s="235"/>
       <c r="E473" s="58"/>
-      <c r="F473" s="421" t="s">
+      <c r="F473" s="418" t="s">
         <v>3672</v>
       </c>
-      <c r="G473" s="398"/>
-      <c r="H473" s="429" t="s">
+      <c r="G473" s="39"/>
+      <c r="H473" s="426" t="s">
         <v>3673</v>
       </c>
-      <c r="I473" s="435" t="s">
+      <c r="I473" s="431" t="s">
         <v>2522</v>
       </c>
       <c r="J473" s="104" t="s">
@@ -55611,13 +55580,13 @@
       </c>
       <c r="K473" s="104"/>
       <c r="L473" s="104"/>
-      <c r="M473" s="453" t="s">
+      <c r="M473" s="331" t="s">
         <v>3675</v>
       </c>
-      <c r="N473" s="466" t="s">
+      <c r="N473" s="457" t="s">
         <v>3676</v>
       </c>
-      <c r="O473" s="463" t="s">
+      <c r="O473" s="455" t="s">
         <v>3677</v>
       </c>
       <c r="P473" s="114"/>
@@ -55627,7 +55596,7 @@
       <c r="R473" s="32" t="s">
         <v>523</v>
       </c>
-      <c r="S473" s="454" t="s">
+      <c r="S473" s="323" t="s">
         <v>41</v>
       </c>
       <c r="T473" s="105"/>
@@ -55645,8 +55614,8 @@
         <v>3681</v>
       </c>
       <c r="AB473" s="110"/>
-      <c r="AC473" s="398"/>
-      <c r="AD473" s="398"/>
+      <c r="AC473" s="39"/>
+      <c r="AD473" s="39"/>
       <c r="AE473" s="39"/>
       <c r="AF473" s="39"/>
       <c r="AG473" s="39"/>
@@ -55680,7 +55649,7 @@
       <c r="F474" s="223" t="s">
         <v>3691</v>
       </c>
-      <c r="G474" s="424" t="s">
+      <c r="G474" s="421" t="s">
         <v>3688</v>
       </c>
       <c r="H474" s="207" t="s">
@@ -55708,7 +55677,7 @@
       <c r="R474" s="66" t="s">
         <v>2790</v>
       </c>
-      <c r="S474" s="454" t="s">
+      <c r="S474" s="323" t="s">
         <v>41</v>
       </c>
       <c r="T474" s="105"/>
@@ -55763,7 +55732,7 @@
       <c r="J475" s="22"/>
       <c r="K475" s="22"/>
       <c r="L475" s="22"/>
-      <c r="M475" s="453" t="s">
+      <c r="M475" s="331" t="s">
         <v>2496</v>
       </c>
       <c r="N475" s="54" t="s">
@@ -55779,7 +55748,7 @@
       <c r="R475" s="48" t="s">
         <v>2995</v>
       </c>
-      <c r="S475" s="454" t="s">
+      <c r="S475" s="323" t="s">
         <v>41</v>
       </c>
       <c r="T475" s="105"/>
@@ -55834,7 +55803,7 @@
       <c r="L476" s="22" t="s">
         <v>3733</v>
       </c>
-      <c r="M476" s="398" t="s">
+      <c r="M476" s="39" t="s">
         <v>3734</v>
       </c>
       <c r="N476" s="38" t="s">
@@ -65165,7 +65134,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{0D60B016-02E9-004E-B944-8557CD0B3D64}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{D6CC31C4-722C-3047-9C03-8B34606CFCE6}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40386CE1-76E0-A947-8266-8FD993D59B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466E414F-59FD-5344-872E-116293DDEA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2240" yWindow="-20340" windowWidth="36000" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -638,7 +638,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7046" uniqueCount="4021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7045" uniqueCount="4020">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17455,9 +17455,6 @@
       </rPr>
       <t>; cuirasse</t>
     </r>
-  </si>
-  <si>
-    <t>Guérin, Gilles</t>
   </si>
   <si>
     <t>https://www.persee.fr/doc/bsnaf_0081-1181_2012_num_2006_1_10985</t>
@@ -18824,7 +18821,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="518">
+  <cellXfs count="504">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -20029,64 +20026,52 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="131" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="123" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="118" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="136" fillId="24" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20095,17 +20080,17 @@
     <xf numFmtId="0" fontId="103" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20126,20 +20111,11 @@
     <xf numFmtId="0" fontId="64" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20149,26 +20125,20 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -20181,10 +20151,10 @@
     <xf numFmtId="0" fontId="5" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20202,29 +20172,22 @@
     <xf numFmtId="0" fontId="5" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20236,8 +20199,8 @@
     <xf numFmtId="0" fontId="3" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="83" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="83" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -20277,7 +20240,7 @@
     <xf numFmtId="0" fontId="3" fillId="41" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -20753,7 +20716,7 @@
       <c r="O3" s="38"/>
       <c r="P3" s="25"/>
       <c r="Q3" s="26"/>
-      <c r="R3" s="422" t="s">
+      <c r="R3" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S3" s="40" t="s">
@@ -20842,7 +20805,7 @@
       <c r="O4" s="38"/>
       <c r="P4" s="25"/>
       <c r="Q4" s="26"/>
-      <c r="R4" s="483" t="s">
+      <c r="R4" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S4" s="40" t="s">
@@ -21046,9 +21009,9 @@
       <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="428"/>
+      <c r="C7" s="425"/>
       <c r="D7" s="232"/>
-      <c r="E7" s="437"/>
+      <c r="E7" s="431"/>
       <c r="F7" s="19" t="s">
         <v>97</v>
       </c>
@@ -21071,7 +21034,7 @@
       <c r="O7" s="37"/>
       <c r="P7" s="57"/>
       <c r="Q7" s="26"/>
-      <c r="R7" s="422" t="s">
+      <c r="R7" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S7" s="40" t="s">
@@ -21086,8 +21049,8 @@
       <c r="V7" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="W7" s="503"/>
-      <c r="X7" s="503"/>
+      <c r="W7" s="489"/>
+      <c r="X7" s="489"/>
       <c r="Y7" s="30" t="s">
         <v>99</v>
       </c>
@@ -21141,7 +21104,7 @@
       <c r="N8" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="O8" s="468"/>
+      <c r="O8" s="322"/>
       <c r="P8" s="59" t="s">
         <v>107</v>
       </c>
@@ -21223,7 +21186,7 @@
       <c r="O9" s="65"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="26"/>
-      <c r="R9" s="487" t="s">
+      <c r="R9" s="474" t="s">
         <v>80</v>
       </c>
       <c r="S9" s="40" t="s">
@@ -21367,7 +21330,7 @@
       <c r="O11" s="38"/>
       <c r="P11" s="25"/>
       <c r="Q11" s="56"/>
-      <c r="R11" s="422" t="s">
+      <c r="R11" s="39" t="s">
         <v>139</v>
       </c>
       <c r="S11" s="40" t="s">
@@ -21434,13 +21397,13 @@
       <c r="M12" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="N12" s="467" t="s">
+      <c r="N12" s="457" t="s">
         <v>148</v>
       </c>
-      <c r="O12" s="467"/>
+      <c r="O12" s="457"/>
       <c r="P12" s="70"/>
       <c r="Q12" s="71"/>
-      <c r="R12" s="422" t="s">
+      <c r="R12" s="39" t="s">
         <v>139</v>
       </c>
       <c r="S12" s="32" t="s">
@@ -21511,7 +21474,7 @@
       <c r="O13" s="73"/>
       <c r="P13" s="74"/>
       <c r="Q13" s="75"/>
-      <c r="R13" s="422" t="s">
+      <c r="R13" s="39" t="s">
         <v>157</v>
       </c>
       <c r="S13" s="32" t="s">
@@ -21592,7 +21555,7 @@
       <c r="W14" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="X14" s="504" t="s">
+      <c r="X14" s="490" t="s">
         <v>167</v>
       </c>
       <c r="Y14" s="80" t="s">
@@ -21726,7 +21689,7 @@
       <c r="O16" s="38"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="26"/>
-      <c r="R16" s="422" t="s">
+      <c r="R16" s="39" t="s">
         <v>186</v>
       </c>
       <c r="S16" s="32" t="s">
@@ -21813,7 +21776,7 @@
       <c r="O17" s="38"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="26"/>
-      <c r="R17" s="422" t="s">
+      <c r="R17" s="39" t="s">
         <v>186</v>
       </c>
       <c r="S17" s="32" t="s">
@@ -21900,7 +21863,7 @@
       <c r="O18" s="38"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="26"/>
-      <c r="R18" s="422" t="s">
+      <c r="R18" s="39" t="s">
         <v>186</v>
       </c>
       <c r="S18" s="32" t="s">
@@ -21926,7 +21889,7 @@
       </c>
       <c r="Z18" s="30"/>
       <c r="AA18" s="30"/>
-      <c r="AB18" s="513" t="s">
+      <c r="AB18" s="499" t="s">
         <v>207</v>
       </c>
       <c r="AC18" s="32" t="s">
@@ -22062,7 +22025,7 @@
       <c r="I20" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="J20" s="452"/>
+      <c r="J20" s="446"/>
       <c r="K20" s="330"/>
       <c r="L20" s="82"/>
       <c r="M20" s="32" t="s">
@@ -22074,7 +22037,7 @@
       <c r="O20" s="38"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="26"/>
-      <c r="R20" s="422" t="s">
+      <c r="R20" s="39" t="s">
         <v>186</v>
       </c>
       <c r="S20" s="32" t="s">
@@ -22098,7 +22061,7 @@
       </c>
       <c r="Z20" s="30"/>
       <c r="AA20" s="30"/>
-      <c r="AB20" s="514" t="s">
+      <c r="AB20" s="500" t="s">
         <v>220</v>
       </c>
       <c r="AC20" s="32" t="s">
@@ -22183,7 +22146,7 @@
       </c>
       <c r="Z21" s="30"/>
       <c r="AA21" s="30"/>
-      <c r="AB21" s="515"/>
+      <c r="AB21" s="501"/>
       <c r="AC21" s="92" t="s">
         <v>227</v>
       </c>
@@ -22240,7 +22203,7 @@
       <c r="O22" s="54"/>
       <c r="P22" s="55"/>
       <c r="Q22" s="56"/>
-      <c r="R22" s="484" t="s">
+      <c r="R22" s="94" t="s">
         <v>139</v>
       </c>
       <c r="S22" s="32" t="s">
@@ -22256,7 +22219,7 @@
       <c r="Y22" s="30"/>
       <c r="Z22" s="30"/>
       <c r="AA22" s="30"/>
-      <c r="AB22" s="511" t="s">
+      <c r="AB22" s="497" t="s">
         <v>236</v>
       </c>
       <c r="AC22" s="69" t="s">
@@ -22315,7 +22278,7 @@
       <c r="O23" s="73"/>
       <c r="P23" s="74"/>
       <c r="Q23" s="91"/>
-      <c r="R23" s="484" t="s">
+      <c r="R23" s="94" t="s">
         <v>139</v>
       </c>
       <c r="S23" s="32" t="s">
@@ -22421,7 +22384,7 @@
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
       <c r="A25" s="277" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>247</v>
@@ -22490,7 +22453,7 @@
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
       <c r="A26" s="291" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>43</v>
@@ -22528,7 +22491,7 @@
       <c r="O26" s="38"/>
       <c r="P26" s="55"/>
       <c r="Q26" s="26"/>
-      <c r="R26" s="422" t="s">
+      <c r="R26" s="39" t="s">
         <v>186</v>
       </c>
       <c r="S26" s="32" t="s">
@@ -22561,7 +22524,7 @@
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
       <c r="A27" s="277" t="s">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="B27" s="32" t="s">
         <v>247</v>
@@ -22678,7 +22641,7 @@
       <c r="O28" s="38"/>
       <c r="P28" s="55"/>
       <c r="Q28" s="26"/>
-      <c r="R28" s="422" t="s">
+      <c r="R28" s="39" t="s">
         <v>186</v>
       </c>
       <c r="S28" s="32" t="s">
@@ -22749,15 +22712,15 @@
       <c r="O29" s="54"/>
       <c r="P29" s="55"/>
       <c r="Q29" s="56"/>
-      <c r="R29" s="483" t="s">
+      <c r="R29" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S29" s="32"/>
-      <c r="T29" s="492"/>
-      <c r="U29" s="497" t="s">
+      <c r="T29" s="478"/>
+      <c r="U29" s="483" t="s">
         <v>289</v>
       </c>
-      <c r="V29" s="497" t="s">
+      <c r="V29" s="483" t="s">
         <v>290</v>
       </c>
       <c r="W29" s="29"/>
@@ -22830,13 +22793,13 @@
       <c r="S30" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T30" s="492" t="s">
+      <c r="T30" s="478" t="s">
         <v>299</v>
       </c>
-      <c r="U30" s="497" t="s">
+      <c r="U30" s="483" t="s">
         <v>289</v>
       </c>
-      <c r="V30" s="497" t="s">
+      <c r="V30" s="483" t="s">
         <v>290</v>
       </c>
       <c r="W30" s="102"/>
@@ -22848,7 +22811,7 @@
       <c r="AA30" s="30"/>
       <c r="AB30" s="41"/>
       <c r="AC30" s="32"/>
-      <c r="AD30" s="517" t="s">
+      <c r="AD30" s="503" t="s">
         <v>301</v>
       </c>
       <c r="AE30" s="32"/>
@@ -22988,7 +22951,7 @@
       <c r="W32" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="X32" s="504" t="s">
+      <c r="X32" s="490" t="s">
         <v>167</v>
       </c>
       <c r="Y32" s="30" t="s">
@@ -23132,16 +23095,16 @@
       <c r="S34" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="T34" s="493" t="s">
+      <c r="T34" s="479" t="s">
         <v>330</v>
       </c>
-      <c r="U34" s="497" t="s">
+      <c r="U34" s="483" t="s">
         <v>289</v>
       </c>
-      <c r="V34" s="497" t="s">
+      <c r="V34" s="483" t="s">
         <v>290</v>
       </c>
-      <c r="W34" s="502"/>
+      <c r="W34" s="488"/>
       <c r="X34" s="72"/>
       <c r="Y34" s="30" t="s">
         <v>331</v>
@@ -23150,7 +23113,7 @@
       <c r="AA34" s="30"/>
       <c r="AB34" s="41"/>
       <c r="AC34" s="32"/>
-      <c r="AD34" s="484"/>
+      <c r="AD34" s="94"/>
       <c r="AE34" s="32"/>
       <c r="AF34" s="32"/>
       <c r="AG34" s="32"/>
@@ -23360,7 +23323,7 @@
       <c r="N37" s="54" t="s">
         <v>357</v>
       </c>
-      <c r="O37" s="469"/>
+      <c r="O37" s="458"/>
       <c r="P37" s="114"/>
       <c r="Q37" s="56"/>
       <c r="R37" s="32" t="s">
@@ -23431,10 +23394,10 @@
       <c r="N38" s="38" t="s">
         <v>364</v>
       </c>
-      <c r="O38" s="468" t="s">
+      <c r="O38" s="322" t="s">
         <v>365</v>
       </c>
-      <c r="P38" s="478"/>
+      <c r="P38" s="467"/>
       <c r="Q38" s="56" t="s">
         <v>366</v>
       </c>
@@ -23482,7 +23445,7 @@
       <c r="B39" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="425" t="s">
+      <c r="C39" s="336" t="s">
         <v>359</v>
       </c>
       <c r="D39" s="235"/>
@@ -24121,7 +24084,7 @@
       <c r="F48" s="16" t="s">
         <v>435</v>
       </c>
-      <c r="G48" s="422"/>
+      <c r="G48" s="39"/>
       <c r="H48" s="48" t="s">
         <v>436</v>
       </c>
@@ -24131,13 +24094,13 @@
       <c r="J48" s="22"/>
       <c r="K48" s="22"/>
       <c r="L48" s="22"/>
-      <c r="M48" s="457" t="s">
+      <c r="M48" s="339" t="s">
         <v>438</v>
       </c>
       <c r="N48" s="54" t="s">
         <v>439</v>
       </c>
-      <c r="O48" s="469" t="s">
+      <c r="O48" s="458" t="s">
         <v>440</v>
       </c>
       <c r="P48" s="114"/>
@@ -24166,7 +24129,7 @@
       <c r="Z48" s="30"/>
       <c r="AA48" s="30"/>
       <c r="AB48" s="110"/>
-      <c r="AC48" s="422"/>
+      <c r="AC48" s="39"/>
       <c r="AD48" s="32"/>
       <c r="AE48" s="32"/>
       <c r="AF48" s="32"/>
@@ -24215,11 +24178,11 @@
       <c r="N49" s="54" t="s">
         <v>451</v>
       </c>
-      <c r="O49" s="469"/>
+      <c r="O49" s="458"/>
       <c r="P49" s="126" t="s">
         <v>452</v>
       </c>
-      <c r="Q49" s="480" t="s">
+      <c r="Q49" s="469" t="s">
         <v>453</v>
       </c>
       <c r="R49" s="117" t="s">
@@ -24265,7 +24228,7 @@
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>434</v>
@@ -24298,9 +24261,9 @@
       <c r="N50" s="54" t="s">
         <v>463</v>
       </c>
-      <c r="O50" s="469"/>
+      <c r="O50" s="458"/>
       <c r="P50" s="114"/>
-      <c r="Q50" s="480"/>
+      <c r="Q50" s="469"/>
       <c r="R50" s="43" t="s">
         <v>139</v>
       </c>
@@ -24336,7 +24299,7 @@
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>444</v>
@@ -25320,7 +25283,7 @@
       <c r="N64" s="83" t="s">
         <v>577</v>
       </c>
-      <c r="O64" s="474"/>
+      <c r="O64" s="463"/>
       <c r="P64" s="126"/>
       <c r="Q64" s="135"/>
       <c r="R64" s="117" t="s">
@@ -25450,7 +25413,7 @@
       <c r="F66" s="16" t="s">
         <v>580</v>
       </c>
-      <c r="G66" s="422" t="s">
+      <c r="G66" s="39" t="s">
         <v>591</v>
       </c>
       <c r="H66" s="40" t="s">
@@ -25539,11 +25502,11 @@
       <c r="N67" s="362" t="s">
         <v>602</v>
       </c>
-      <c r="O67" s="475"/>
+      <c r="O67" s="464"/>
       <c r="P67" s="363" t="s">
         <v>38</v>
       </c>
-      <c r="Q67" s="482" t="s">
+      <c r="Q67" s="471" t="s">
         <v>603</v>
       </c>
       <c r="R67" s="343" t="s">
@@ -25618,8 +25581,8 @@
       <c r="N68" s="305" t="s">
         <v>613</v>
       </c>
-      <c r="O68" s="476"/>
-      <c r="P68" s="479"/>
+      <c r="O68" s="465"/>
+      <c r="P68" s="468"/>
       <c r="Q68" s="307"/>
       <c r="R68" s="314" t="s">
         <v>49</v>
@@ -25638,7 +25601,7 @@
       <c r="X68" s="311" t="s">
         <v>482</v>
       </c>
-      <c r="Y68" s="508" t="s">
+      <c r="Y68" s="494" t="s">
         <v>615</v>
       </c>
       <c r="Z68" s="312"/>
@@ -25758,7 +25721,7 @@
       <c r="B70" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C70" s="429" t="s">
+      <c r="C70" s="426" t="s">
         <v>629</v>
       </c>
       <c r="D70" s="235"/>
@@ -26039,7 +26002,7 @@
       <c r="A74" s="274" t="s">
         <v>3912</v>
       </c>
-      <c r="B74" s="422" t="s">
+      <c r="B74" s="39" t="s">
         <v>43</v>
       </c>
       <c r="C74" s="249" t="s">
@@ -26068,10 +26031,10 @@
       <c r="N74" s="54" t="s">
         <v>670</v>
       </c>
-      <c r="O74" s="469"/>
+      <c r="O74" s="458"/>
       <c r="P74" s="114"/>
       <c r="Q74" s="123"/>
-      <c r="R74" s="422" t="s">
+      <c r="R74" s="39" t="s">
         <v>650</v>
       </c>
       <c r="S74" s="32" t="s">
@@ -26114,7 +26077,7 @@
       <c r="C75" s="250" t="s">
         <v>3836</v>
       </c>
-      <c r="D75" s="431"/>
+      <c r="D75" s="337"/>
       <c r="E75" s="58"/>
       <c r="F75" s="16" t="s">
         <v>673</v>
@@ -26140,7 +26103,7 @@
       <c r="O75" s="54"/>
       <c r="P75" s="55"/>
       <c r="Q75" s="56"/>
-      <c r="R75" s="422" t="s">
+      <c r="R75" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S75" s="32" t="s">
@@ -26209,7 +26172,7 @@
       <c r="Q76" s="75" t="s">
         <v>686</v>
       </c>
-      <c r="R76" s="483" t="s">
+      <c r="R76" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S76" s="32" t="s">
@@ -26282,7 +26245,7 @@
       <c r="Q77" s="357" t="s">
         <v>696</v>
       </c>
-      <c r="R77" s="485" t="s">
+      <c r="R77" s="472" t="s">
         <v>523</v>
       </c>
       <c r="S77" s="314" t="s">
@@ -26325,7 +26288,7 @@
       <c r="C78" s="255" t="s">
         <v>171</v>
       </c>
-      <c r="D78" s="431"/>
+      <c r="D78" s="337"/>
       <c r="E78" s="138"/>
       <c r="F78" s="16" t="s">
         <v>699</v>
@@ -26351,7 +26314,7 @@
       <c r="O78" s="54"/>
       <c r="P78" s="55"/>
       <c r="Q78" s="56"/>
-      <c r="R78" s="422" t="s">
+      <c r="R78" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S78" s="32" t="s">
@@ -26420,7 +26383,7 @@
       <c r="Q79" s="64" t="s">
         <v>709</v>
       </c>
-      <c r="R79" s="422" t="s">
+      <c r="R79" s="39" t="s">
         <v>710</v>
       </c>
       <c r="S79" s="32" t="s">
@@ -26552,7 +26515,7 @@
       <c r="C81" s="257" t="s">
         <v>171</v>
       </c>
-      <c r="D81" s="435" t="s">
+      <c r="D81" s="430" t="s">
         <v>596</v>
       </c>
       <c r="E81" s="138" t="s">
@@ -26651,17 +26614,17 @@
       <c r="Q82" s="350" t="s">
         <v>739</v>
       </c>
-      <c r="R82" s="485" t="s">
+      <c r="R82" s="472" t="s">
         <v>49</v>
       </c>
       <c r="S82" s="314" t="s">
         <v>41</v>
       </c>
-      <c r="T82" s="494" t="s">
+      <c r="T82" s="480" t="s">
         <v>740</v>
       </c>
-      <c r="U82" s="499"/>
-      <c r="V82" s="499"/>
+      <c r="U82" s="485"/>
+      <c r="V82" s="485"/>
       <c r="W82" s="352"/>
       <c r="X82" s="352"/>
       <c r="Y82" s="312"/>
@@ -26722,7 +26685,7 @@
       <c r="Q83" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="R83" s="484" t="s">
+      <c r="R83" s="94" t="s">
         <v>746</v>
       </c>
       <c r="S83" s="32" t="s">
@@ -26860,7 +26823,7 @@
       <c r="O85" s="54"/>
       <c r="P85" s="55"/>
       <c r="Q85" s="56"/>
-      <c r="R85" s="422" t="s">
+      <c r="R85" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S85" s="32" t="s">
@@ -26933,7 +26896,7 @@
       <c r="Q86" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="R86" s="458" t="s">
+      <c r="R86" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S86" s="32" t="s">
@@ -27004,7 +26967,7 @@
       <c r="Q87" s="75" t="s">
         <v>775</v>
       </c>
-      <c r="R87" s="422" t="s">
+      <c r="R87" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S87" s="32" t="s">
@@ -27083,7 +27046,7 @@
       <c r="O88" s="54"/>
       <c r="P88" s="55"/>
       <c r="Q88" s="56"/>
-      <c r="R88" s="422" t="s">
+      <c r="R88" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S88" s="32" t="s">
@@ -27156,7 +27119,7 @@
       <c r="Q89" s="91" t="s">
         <v>795</v>
       </c>
-      <c r="R89" s="422" t="s">
+      <c r="R89" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S89" s="32" t="s">
@@ -27203,7 +27166,7 @@
       <c r="C90" s="258" t="s">
         <v>143</v>
       </c>
-      <c r="D90" s="431"/>
+      <c r="D90" s="337"/>
       <c r="E90" s="138"/>
       <c r="F90" s="16" t="s">
         <v>800</v>
@@ -27233,7 +27196,7 @@
       <c r="Q90" s="56" t="s">
         <v>807</v>
       </c>
-      <c r="R90" s="422" t="s">
+      <c r="R90" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S90" s="32" t="s">
@@ -27277,10 +27240,10 @@
       <c r="B91" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C91" s="425" t="s">
+      <c r="C91" s="336" t="s">
         <v>782</v>
       </c>
-      <c r="D91" s="433" t="s">
+      <c r="D91" s="428" t="s">
         <v>810</v>
       </c>
       <c r="E91" s="138"/>
@@ -27308,13 +27271,13 @@
       <c r="O91" s="54"/>
       <c r="P91" s="55"/>
       <c r="Q91" s="56"/>
-      <c r="R91" s="422" t="s">
+      <c r="R91" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S91" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T91" s="495" t="s">
+      <c r="T91" s="481" t="s">
         <v>815</v>
       </c>
       <c r="U91" s="28"/>
@@ -27381,7 +27344,7 @@
       <c r="Q92" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="R92" s="422" t="s">
+      <c r="R92" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S92" s="32" t="s">
@@ -27456,7 +27419,7 @@
       <c r="Q93" s="91" t="s">
         <v>831</v>
       </c>
-      <c r="R93" s="422" t="s">
+      <c r="R93" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S93" s="32" t="s">
@@ -27525,7 +27488,7 @@
       <c r="O94" s="54"/>
       <c r="P94" s="55"/>
       <c r="Q94" s="56"/>
-      <c r="R94" s="483" t="s">
+      <c r="R94" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S94" s="32" t="s">
@@ -27726,7 +27689,7 @@
       <c r="O97" s="54"/>
       <c r="P97" s="55"/>
       <c r="Q97" s="56"/>
-      <c r="R97" s="483" t="s">
+      <c r="R97" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S97" s="32" t="s">
@@ -27793,7 +27756,7 @@
       <c r="O98" s="54"/>
       <c r="P98" s="55"/>
       <c r="Q98" s="56"/>
-      <c r="R98" s="458" t="s">
+      <c r="R98" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S98" s="32" t="s">
@@ -27862,7 +27825,7 @@
       <c r="O99" s="54"/>
       <c r="P99" s="55"/>
       <c r="Q99" s="56"/>
-      <c r="R99" s="422" t="s">
+      <c r="R99" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S99" s="32" t="s">
@@ -27929,7 +27892,7 @@
       <c r="O100" s="54"/>
       <c r="P100" s="55"/>
       <c r="Q100" s="56"/>
-      <c r="R100" s="458" t="s">
+      <c r="R100" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S100" s="32" t="s">
@@ -28041,7 +28004,7 @@
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
       <c r="A102" s="277" t="s">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>890</v>
@@ -28075,7 +28038,7 @@
       <c r="O102" s="54"/>
       <c r="P102" s="55"/>
       <c r="Q102" s="56"/>
-      <c r="R102" s="422" t="s">
+      <c r="R102" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S102" s="32" t="s">
@@ -28146,7 +28109,7 @@
       <c r="Q103" s="64" t="s">
         <v>902</v>
       </c>
-      <c r="R103" s="422" t="s">
+      <c r="R103" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S103" s="32" t="s">
@@ -28223,7 +28186,7 @@
       <c r="O104" s="38"/>
       <c r="P104" s="25"/>
       <c r="Q104" s="26"/>
-      <c r="R104" s="458" t="s">
+      <c r="R104" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S104" s="32" t="s">
@@ -28298,7 +28261,7 @@
       <c r="Q105" s="91" t="s">
         <v>922</v>
       </c>
-      <c r="R105" s="422" t="s">
+      <c r="R105" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S105" s="32" t="s">
@@ -28367,7 +28330,7 @@
       <c r="O106" s="38"/>
       <c r="P106" s="25"/>
       <c r="Q106" s="26"/>
-      <c r="R106" s="422" t="s">
+      <c r="R106" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S106" s="32" t="s">
@@ -28521,7 +28484,7 @@
       <c r="Q108" s="26" t="s">
         <v>947</v>
       </c>
-      <c r="R108" s="458" t="s">
+      <c r="R108" s="324" t="s">
         <v>948</v>
       </c>
       <c r="S108" s="95" t="s">
@@ -28583,10 +28546,10 @@
       <c r="N109" s="38" t="s">
         <v>954</v>
       </c>
-      <c r="O109" s="468"/>
+      <c r="O109" s="322"/>
       <c r="P109" s="126"/>
       <c r="Q109" s="26"/>
-      <c r="R109" s="483" t="s">
+      <c r="R109" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S109" s="32" t="s">
@@ -28632,7 +28595,7 @@
       <c r="F110" s="290" t="s">
         <v>956</v>
       </c>
-      <c r="G110" s="422"/>
+      <c r="G110" s="39"/>
       <c r="H110" s="48" t="s">
         <v>957</v>
       </c>
@@ -28657,7 +28620,7 @@
       <c r="Q110" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="R110" s="483" t="s">
+      <c r="R110" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S110" s="32" t="s">
@@ -28791,7 +28754,7 @@
       <c r="O112" s="38"/>
       <c r="P112" s="25"/>
       <c r="Q112" s="26"/>
-      <c r="R112" s="422" t="s">
+      <c r="R112" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S112" s="32" t="s">
@@ -28862,7 +28825,7 @@
       <c r="Q113" s="91" t="s">
         <v>983</v>
       </c>
-      <c r="R113" s="422" t="s">
+      <c r="R113" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S113" s="32" t="s">
@@ -28903,7 +28866,7 @@
     </row>
     <row r="114" spans="1:43" ht="15.75" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="B114" s="32" t="s">
         <v>434</v>
@@ -29014,7 +28977,7 @@
       <c r="O115" s="38"/>
       <c r="P115" s="25"/>
       <c r="Q115" s="26"/>
-      <c r="R115" s="422" t="s">
+      <c r="R115" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S115" s="32" t="s">
@@ -29083,7 +29046,7 @@
       <c r="O116" s="38"/>
       <c r="P116" s="25"/>
       <c r="Q116" s="26"/>
-      <c r="R116" s="483" t="s">
+      <c r="R116" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S116" s="32" t="s">
@@ -29154,7 +29117,7 @@
       <c r="Q117" s="91" t="s">
         <v>1020</v>
       </c>
-      <c r="R117" s="422" t="s">
+      <c r="R117" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S117" s="32" t="s">
@@ -29231,7 +29194,7 @@
       <c r="Q118" s="75" t="s">
         <v>1032</v>
       </c>
-      <c r="R118" s="484" t="s">
+      <c r="R118" s="94" t="s">
         <v>1033</v>
       </c>
       <c r="S118" s="32" t="s">
@@ -29300,7 +29263,7 @@
       <c r="O119" s="54"/>
       <c r="P119" s="55"/>
       <c r="Q119" s="56"/>
-      <c r="R119" s="483" t="s">
+      <c r="R119" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S119" s="32" t="s">
@@ -29370,10 +29333,10 @@
       <c r="N120" s="54" t="s">
         <v>1049</v>
       </c>
-      <c r="O120" s="469"/>
+      <c r="O120" s="458"/>
       <c r="P120" s="114"/>
       <c r="Q120" s="56"/>
-      <c r="R120" s="422" t="s">
+      <c r="R120" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S120" s="32" t="s">
@@ -29434,17 +29397,17 @@
       <c r="M121" s="53" t="s">
         <v>863</v>
       </c>
-      <c r="N121" s="469" t="s">
+      <c r="N121" s="458" t="s">
         <v>37</v>
       </c>
-      <c r="O121" s="469"/>
+      <c r="O121" s="458"/>
       <c r="P121" s="59" t="s">
         <v>1054</v>
       </c>
       <c r="Q121" s="123" t="s">
         <v>1055</v>
       </c>
-      <c r="R121" s="458" t="s">
+      <c r="R121" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S121" s="32" t="s">
@@ -29477,7 +29440,7 @@
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
       <c r="A122" s="278" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="B122" s="51" t="s">
         <v>43</v>
@@ -29510,7 +29473,7 @@
       <c r="N122" s="143" t="s">
         <v>1062</v>
       </c>
-      <c r="O122" s="473"/>
+      <c r="O122" s="462"/>
       <c r="P122" s="59"/>
       <c r="Q122" s="75"/>
       <c r="R122" s="144" t="s">
@@ -29594,7 +29557,7 @@
       <c r="Q123" s="56" t="s">
         <v>1077</v>
       </c>
-      <c r="R123" s="458" t="s">
+      <c r="R123" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S123" s="32" t="s">
@@ -29661,7 +29624,7 @@
       <c r="O124" s="54"/>
       <c r="P124" s="55"/>
       <c r="Q124" s="56"/>
-      <c r="R124" s="422" t="s">
+      <c r="R124" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S124" s="32" t="s">
@@ -29815,7 +29778,7 @@
       <c r="O126" s="38"/>
       <c r="P126" s="25"/>
       <c r="Q126" s="26"/>
-      <c r="R126" s="484" t="s">
+      <c r="R126" s="94" t="s">
         <v>1105</v>
       </c>
       <c r="S126" s="32" t="s">
@@ -29850,7 +29813,7 @@
       <c r="A127" s="111" t="s">
         <v>1106</v>
       </c>
-      <c r="B127" s="423" t="s">
+      <c r="B127" s="422" t="s">
         <v>1107</v>
       </c>
       <c r="C127" s="250" t="s">
@@ -29884,7 +29847,7 @@
       <c r="Q127" s="26" t="s">
         <v>1111</v>
       </c>
-      <c r="R127" s="422" t="s">
+      <c r="R127" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S127" s="21" t="s">
@@ -29956,10 +29919,10 @@
       <c r="N128" s="38" t="s">
         <v>1120</v>
       </c>
-      <c r="O128" s="468"/>
+      <c r="O128" s="322"/>
       <c r="P128" s="126"/>
       <c r="Q128" s="26"/>
-      <c r="R128" s="422" t="s">
+      <c r="R128" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S128" s="32" t="s">
@@ -30019,20 +29982,20 @@
       <c r="J129" s="22"/>
       <c r="K129" s="22"/>
       <c r="L129" s="22"/>
-      <c r="M129" s="422" t="s">
+      <c r="M129" s="39" t="s">
         <v>560</v>
       </c>
       <c r="N129" s="54" t="s">
         <v>1127</v>
       </c>
-      <c r="O129" s="469"/>
+      <c r="O129" s="458"/>
       <c r="P129" s="59" t="s">
         <v>1128</v>
       </c>
       <c r="Q129" s="56" t="s">
         <v>1129</v>
       </c>
-      <c r="R129" s="471" t="s">
+      <c r="R129" s="460" t="s">
         <v>1130</v>
       </c>
       <c r="S129" s="32" t="s">
@@ -30090,20 +30053,20 @@
       <c r="L130" s="22" t="s">
         <v>1135</v>
       </c>
-      <c r="M130" s="456" t="s">
+      <c r="M130" s="449" t="s">
         <v>863</v>
       </c>
       <c r="N130" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="O130" s="469"/>
+      <c r="O130" s="458"/>
       <c r="P130" s="59" t="s">
         <v>1136</v>
       </c>
       <c r="Q130" s="56" t="s">
         <v>1137</v>
       </c>
-      <c r="R130" s="458" t="s">
+      <c r="R130" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S130" s="32" t="s">
@@ -30315,7 +30278,7 @@
       <c r="N133" s="54" t="s">
         <v>1157</v>
       </c>
-      <c r="O133" s="469"/>
+      <c r="O133" s="458"/>
       <c r="P133" s="114"/>
       <c r="Q133" s="56"/>
       <c r="R133" s="96" t="s">
@@ -30391,7 +30354,7 @@
       <c r="Q134" s="26" t="s">
         <v>1164</v>
       </c>
-      <c r="R134" s="458" t="s">
+      <c r="R134" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S134" s="32" t="s">
@@ -30462,7 +30425,7 @@
       <c r="Q135" s="75" t="s">
         <v>1170</v>
       </c>
-      <c r="R135" s="422" t="s">
+      <c r="R135" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S135" s="32" t="s">
@@ -30541,7 +30504,7 @@
       <c r="O136" s="54"/>
       <c r="P136" s="55"/>
       <c r="Q136" s="56"/>
-      <c r="R136" s="422" t="s">
+      <c r="R136" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S136" s="32" t="s">
@@ -30605,10 +30568,10 @@
       <c r="N137" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="O137" s="469"/>
+      <c r="O137" s="458"/>
       <c r="P137" s="114"/>
       <c r="Q137" s="56"/>
-      <c r="R137" s="458" t="s">
+      <c r="R137" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S137" s="95" t="s">
@@ -30681,7 +30644,7 @@
       <c r="Q138" s="56" t="s">
         <v>1196</v>
       </c>
-      <c r="R138" s="483" t="s">
+      <c r="R138" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S138" s="32" t="s">
@@ -30817,7 +30780,7 @@
       <c r="O140" s="38"/>
       <c r="P140" s="25"/>
       <c r="Q140" s="26"/>
-      <c r="R140" s="422" t="s">
+      <c r="R140" s="39" t="s">
         <v>544</v>
       </c>
       <c r="S140" s="32" t="s">
@@ -31170,7 +31133,7 @@
       <c r="Q145" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="R145" s="422" t="s">
+      <c r="R145" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S145" s="32" t="s">
@@ -31326,7 +31289,7 @@
       <c r="O147" s="136"/>
       <c r="P147" s="55"/>
       <c r="Q147" s="56"/>
-      <c r="R147" s="422" t="s">
+      <c r="R147" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S147" s="21" t="s">
@@ -31553,7 +31516,7 @@
       <c r="O150" s="38"/>
       <c r="P150" s="25"/>
       <c r="Q150" s="26"/>
-      <c r="R150" s="422" t="s">
+      <c r="R150" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S150" s="32" t="s">
@@ -31624,7 +31587,7 @@
       <c r="Q151" s="56" t="s">
         <v>1289</v>
       </c>
-      <c r="R151" s="422" t="s">
+      <c r="R151" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S151" s="32" t="s">
@@ -31643,7 +31606,7 @@
         <v>1291</v>
       </c>
       <c r="AB151" s="41"/>
-      <c r="AC151" s="422"/>
+      <c r="AC151" s="39"/>
       <c r="AD151" s="32"/>
       <c r="AE151" s="32"/>
       <c r="AF151" s="32"/>
@@ -31695,7 +31658,7 @@
       <c r="O152" s="54"/>
       <c r="P152" s="55"/>
       <c r="Q152" s="56"/>
-      <c r="R152" s="422" t="s">
+      <c r="R152" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S152" s="32" t="s">
@@ -31762,7 +31725,7 @@
       <c r="O153" s="54"/>
       <c r="P153" s="55"/>
       <c r="Q153" s="56"/>
-      <c r="R153" s="458" t="s">
+      <c r="R153" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S153" s="32" t="s">
@@ -31831,7 +31794,7 @@
       <c r="O154" s="54"/>
       <c r="P154" s="55"/>
       <c r="Q154" s="56"/>
-      <c r="R154" s="458" t="s">
+      <c r="R154" s="324" t="s">
         <v>375</v>
       </c>
       <c r="S154" s="32" t="s">
@@ -32064,7 +32027,7 @@
       <c r="Q157" s="56" t="s">
         <v>739</v>
       </c>
-      <c r="R157" s="422" t="s">
+      <c r="R157" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S157" s="21" t="s">
@@ -32204,7 +32167,7 @@
       <c r="O159" s="54"/>
       <c r="P159" s="55"/>
       <c r="Q159" s="56"/>
-      <c r="R159" s="422" t="s">
+      <c r="R159" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S159" s="32" t="s">
@@ -32275,7 +32238,7 @@
       <c r="Q160" s="319" t="s">
         <v>1363</v>
       </c>
-      <c r="R160" s="422" t="s">
+      <c r="R160" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S160" s="21" t="s">
@@ -32425,7 +32388,7 @@
       <c r="O162" s="54"/>
       <c r="P162" s="55"/>
       <c r="Q162" s="56"/>
-      <c r="R162" s="422" t="s">
+      <c r="R162" s="39" t="s">
         <v>49</v>
       </c>
       <c r="S162" s="32" t="s">
@@ -32567,7 +32530,7 @@
       <c r="Q164" s="75" t="s">
         <v>1396</v>
       </c>
-      <c r="R164" s="422" t="s">
+      <c r="R164" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S164" s="32" t="s">
@@ -32938,7 +32901,7 @@
       <c r="Q169" s="56" t="s">
         <v>1437</v>
       </c>
-      <c r="R169" s="422" t="s">
+      <c r="R169" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S169" s="32" t="s">
@@ -33296,7 +33259,7 @@
       <c r="N174" s="54" t="s">
         <v>1481</v>
       </c>
-      <c r="O174" s="469"/>
+      <c r="O174" s="458"/>
       <c r="P174" s="114"/>
       <c r="Q174" s="123"/>
       <c r="R174" s="39" t="s">
@@ -33728,7 +33691,7 @@
         <v>1529</v>
       </c>
       <c r="J180" s="98"/>
-      <c r="K180" s="454"/>
+      <c r="K180" s="448"/>
       <c r="L180" s="119" t="s">
         <v>1530</v>
       </c>
@@ -33939,7 +33902,7 @@
       <c r="F183" s="16" t="s">
         <v>1548</v>
       </c>
-      <c r="G183" s="422"/>
+      <c r="G183" s="39"/>
       <c r="H183" s="48" t="s">
         <v>1549</v>
       </c>
@@ -34035,7 +33998,7 @@
       <c r="S184" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="T184" s="483" t="s">
+      <c r="T184" s="333" t="s">
         <v>1561</v>
       </c>
       <c r="U184" s="28"/>
@@ -35118,7 +35081,7 @@
       <c r="U199" s="106" t="s">
         <v>1064</v>
       </c>
-      <c r="V199" s="500" t="s">
+      <c r="V199" s="486" t="s">
         <v>1678</v>
       </c>
       <c r="W199" s="29"/>
@@ -36153,7 +36116,7 @@
       <c r="F213" s="32" t="s">
         <v>1099</v>
       </c>
-      <c r="G213" s="422"/>
+      <c r="G213" s="39"/>
       <c r="H213" s="48" t="s">
         <v>1791</v>
       </c>
@@ -36839,7 +36802,7 @@
       <c r="S222" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T222" s="483" t="s">
+      <c r="T222" s="333" t="s">
         <v>1873</v>
       </c>
       <c r="U222" s="106"/>
@@ -36956,7 +36919,7 @@
       <c r="B224" s="14" t="s">
         <v>1917</v>
       </c>
-      <c r="C224" s="430" t="s">
+      <c r="C224" s="427" t="s">
         <v>1918</v>
       </c>
       <c r="D224" s="232"/>
@@ -36984,7 +36947,7 @@
       <c r="N224" s="65" t="s">
         <v>1924</v>
       </c>
-      <c r="O224" s="477"/>
+      <c r="O224" s="466"/>
       <c r="P224" s="59" t="s">
         <v>1925</v>
       </c>
@@ -37195,7 +37158,7 @@
       <c r="N227" s="54" t="s">
         <v>1905</v>
       </c>
-      <c r="O227" s="469"/>
+      <c r="O227" s="458"/>
       <c r="P227" s="318" t="s">
         <v>1907</v>
       </c>
@@ -37357,7 +37320,7 @@
       <c r="N229" s="65" t="s">
         <v>1935</v>
       </c>
-      <c r="O229" s="466"/>
+      <c r="O229" s="456"/>
       <c r="P229" s="126"/>
       <c r="Q229" s="56"/>
       <c r="R229" s="334" t="s">
@@ -37507,7 +37470,7 @@
       <c r="N231" s="54" t="s">
         <v>1952</v>
       </c>
-      <c r="O231" s="469"/>
+      <c r="O231" s="458"/>
       <c r="P231" s="114"/>
       <c r="Q231" s="56"/>
       <c r="R231" s="117" t="s">
@@ -37651,7 +37614,7 @@
       <c r="N233" s="38" t="s">
         <v>1969</v>
       </c>
-      <c r="O233" s="468"/>
+      <c r="O233" s="322"/>
       <c r="P233" s="126"/>
       <c r="Q233" s="26"/>
       <c r="R233" s="117" t="s">
@@ -37697,7 +37660,7 @@
       </c>
       <c r="D234" s="235"/>
       <c r="E234" s="58"/>
-      <c r="F234" s="440" t="s">
+      <c r="F234" s="434" t="s">
         <v>1970</v>
       </c>
       <c r="G234" s="32"/>
@@ -37741,7 +37704,7 @@
       <c r="AA234" s="30"/>
       <c r="AB234" s="41"/>
       <c r="AC234" s="32"/>
-      <c r="AD234" s="422"/>
+      <c r="AD234" s="39"/>
       <c r="AE234" s="32"/>
       <c r="AF234" s="32"/>
       <c r="AG234" s="32"/>
@@ -37886,7 +37849,7 @@
       <c r="T236" s="21"/>
       <c r="U236" s="28"/>
       <c r="V236" s="28"/>
-      <c r="W236" s="502" t="s">
+      <c r="W236" s="488" t="s">
         <v>1927</v>
       </c>
       <c r="X236" s="120" t="s">
@@ -38358,7 +38321,7 @@
       <c r="N242" s="54" t="s">
         <v>2042</v>
       </c>
-      <c r="O242" s="469"/>
+      <c r="O242" s="458"/>
       <c r="P242" s="318" t="s">
         <v>1907</v>
       </c>
@@ -38437,7 +38400,7 @@
       <c r="N243" s="38" t="s">
         <v>2053</v>
       </c>
-      <c r="O243" s="468"/>
+      <c r="O243" s="322"/>
       <c r="P243" s="59" t="s">
         <v>107</v>
       </c>
@@ -38593,7 +38556,7 @@
       <c r="J245" s="82"/>
       <c r="K245" s="82"/>
       <c r="L245" s="22"/>
-      <c r="M245" s="455" t="s">
+      <c r="M245" s="331" t="s">
         <v>657</v>
       </c>
       <c r="N245" s="178" t="s">
@@ -38719,33 +38682,32 @@
       <c r="B247" s="419" t="s">
         <v>2087</v>
       </c>
-      <c r="C247" s="426" t="s">
+      <c r="C247" s="262" t="s">
         <v>3795</v>
       </c>
-      <c r="D247" s="432"/>
-      <c r="E247" s="436"/>
-      <c r="F247" s="436" t="s">
+      <c r="E247" s="230"/>
+      <c r="F247" s="230" t="s">
         <v>3792</v>
       </c>
-      <c r="G247" s="436" t="s">
+      <c r="G247" s="230" t="s">
         <v>3793</v>
       </c>
-      <c r="H247" s="424" t="s">
+      <c r="H247" s="423" t="s">
         <v>3980</v>
       </c>
       <c r="I247" s="421" t="s">
         <v>1914</v>
       </c>
-      <c r="J247" s="436"/>
-      <c r="K247" s="436"/>
-      <c r="L247" s="436"/>
+      <c r="J247" s="230"/>
+      <c r="K247" s="230"/>
+      <c r="L247" s="230"/>
       <c r="M247" s="421" t="s">
         <v>3978</v>
       </c>
-      <c r="N247" s="471" t="s">
+      <c r="N247" s="460" t="s">
         <v>2088</v>
       </c>
-      <c r="O247" s="470"/>
+      <c r="O247" s="459"/>
       <c r="P247" s="318" t="s">
         <v>1907</v>
       </c>
@@ -38755,30 +38717,30 @@
       <c r="R247" s="327" t="s">
         <v>387</v>
       </c>
-      <c r="S247" s="424" t="s">
+      <c r="S247" s="423" t="s">
         <v>41</v>
       </c>
-      <c r="T247" s="424" t="s">
+      <c r="T247" s="423" t="s">
         <v>3794</v>
       </c>
-      <c r="U247" s="424" t="s">
+      <c r="U247" s="423" t="s">
         <v>1907</v>
       </c>
-      <c r="V247" s="424" t="s">
+      <c r="V247" s="423" t="s">
         <v>1908</v>
       </c>
-      <c r="W247" s="436"/>
-      <c r="X247" s="436"/>
-      <c r="Y247" s="439" t="s">
+      <c r="W247" s="230"/>
+      <c r="X247" s="230"/>
+      <c r="Y247" s="433" t="s">
         <v>3969</v>
       </c>
-      <c r="Z247" s="436"/>
-      <c r="AA247" s="436"/>
-      <c r="AB247" s="436"/>
-      <c r="AC247" s="424" t="s">
+      <c r="Z247" s="230"/>
+      <c r="AA247" s="230"/>
+      <c r="AB247" s="230"/>
+      <c r="AC247" s="423" t="s">
         <v>2089</v>
       </c>
-      <c r="AD247" s="436" t="s">
+      <c r="AD247" s="230" t="s">
         <v>3970</v>
       </c>
       <c r="AE247" s="230"/>
@@ -38799,32 +38761,31 @@
       <c r="A248" s="419" t="s">
         <v>3787</v>
       </c>
-      <c r="B248" s="424" t="s">
+      <c r="B248" s="423" t="s">
         <v>3788</v>
       </c>
-      <c r="C248" s="426" t="s">
+      <c r="C248" s="262" t="s">
         <v>3795</v>
       </c>
-      <c r="D248" s="432"/>
-      <c r="E248" s="436"/>
-      <c r="F248" s="436"/>
-      <c r="G248" s="424"/>
-      <c r="H248" s="424" t="s">
+      <c r="E248" s="230"/>
+      <c r="F248" s="230"/>
+      <c r="G248" s="423"/>
+      <c r="H248" s="423" t="s">
         <v>3981</v>
       </c>
       <c r="I248" s="421" t="s">
         <v>2035</v>
       </c>
-      <c r="J248" s="436"/>
-      <c r="K248" s="436"/>
-      <c r="L248" s="436"/>
+      <c r="J248" s="230"/>
+      <c r="K248" s="230"/>
+      <c r="L248" s="230"/>
       <c r="M248" s="421" t="s">
         <v>3978</v>
       </c>
-      <c r="N248" s="470" t="s">
+      <c r="N248" s="459" t="s">
         <v>2088</v>
       </c>
-      <c r="O248" s="470"/>
+      <c r="O248" s="459"/>
       <c r="P248" s="318" t="s">
         <v>1907</v>
       </c>
@@ -38834,28 +38795,28 @@
       <c r="R248" s="327" t="s">
         <v>387</v>
       </c>
-      <c r="S248" s="424" t="s">
+      <c r="S248" s="423" t="s">
         <v>41</v>
       </c>
-      <c r="T248" s="424" t="s">
+      <c r="T248" s="423" t="s">
         <v>3789</v>
       </c>
-      <c r="U248" s="424" t="s">
+      <c r="U248" s="423" t="s">
         <v>1907</v>
       </c>
-      <c r="V248" s="424" t="s">
+      <c r="V248" s="423" t="s">
         <v>1908</v>
       </c>
-      <c r="W248" s="436"/>
-      <c r="X248" s="436"/>
-      <c r="Y248" s="424" t="s">
+      <c r="W248" s="230"/>
+      <c r="X248" s="230"/>
+      <c r="Y248" s="423" t="s">
         <v>3790</v>
       </c>
       <c r="Z248" s="230"/>
-      <c r="AA248" s="436"/>
-      <c r="AB248" s="436"/>
-      <c r="AC248" s="424"/>
-      <c r="AD248" s="436"/>
+      <c r="AA248" s="230"/>
+      <c r="AB248" s="230"/>
+      <c r="AC248" s="423"/>
+      <c r="AD248" s="230"/>
       <c r="AE248" s="230"/>
       <c r="AF248" s="230"/>
       <c r="AG248" s="230"/>
@@ -39849,7 +39810,7 @@
       <c r="I262" s="43" t="s">
         <v>2198</v>
       </c>
-      <c r="J262" s="451" t="s">
+      <c r="J262" s="445" t="s">
         <v>2199</v>
       </c>
       <c r="K262" s="109"/>
@@ -40036,7 +39997,7 @@
     </row>
     <row r="265" spans="1:43" ht="15.75" customHeight="1">
       <c r="A265" s="14" t="s">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="B265" s="14" t="s">
         <v>2214</v>
@@ -40117,7 +40078,7 @@
       </c>
       <c r="D266" s="235"/>
       <c r="E266" s="58"/>
-      <c r="F266" s="440" t="s">
+      <c r="F266" s="434" t="s">
         <v>2220</v>
       </c>
       <c r="G266" s="32"/>
@@ -40284,7 +40245,7 @@
       <c r="N268" s="38" t="s">
         <v>2241</v>
       </c>
-      <c r="O268" s="468"/>
+      <c r="O268" s="322"/>
       <c r="P268" s="126"/>
       <c r="Q268" s="26"/>
       <c r="R268" s="99" t="s">
@@ -40451,7 +40412,7 @@
       <c r="U270" s="318" t="s">
         <v>1907</v>
       </c>
-      <c r="V270" s="501" t="s">
+      <c r="V270" s="487" t="s">
         <v>1908</v>
       </c>
       <c r="W270" s="29"/>
@@ -40505,7 +40466,7 @@
       <c r="J271" s="22"/>
       <c r="K271" s="22"/>
       <c r="L271" s="22"/>
-      <c r="M271" s="457" t="s">
+      <c r="M271" s="339" t="s">
         <v>2267</v>
       </c>
       <c r="N271" s="54" t="s">
@@ -40572,7 +40533,7 @@
       </c>
       <c r="K272" s="76"/>
       <c r="L272" s="76"/>
-      <c r="M272" s="457" t="s">
+      <c r="M272" s="339" t="s">
         <v>137</v>
       </c>
       <c r="N272" s="73" t="s">
@@ -40636,7 +40597,7 @@
       <c r="I273" s="43" t="s">
         <v>2279</v>
       </c>
-      <c r="J273" s="449" t="s">
+      <c r="J273" s="443" t="s">
         <v>2280</v>
       </c>
       <c r="K273" s="104"/>
@@ -40952,7 +40913,7 @@
       <c r="U277" s="318" t="s">
         <v>1907</v>
       </c>
-      <c r="V277" s="501" t="s">
+      <c r="V277" s="487" t="s">
         <v>1908</v>
       </c>
       <c r="W277" s="29"/>
@@ -41095,7 +41056,7 @@
       <c r="N279" s="89" t="s">
         <v>2086</v>
       </c>
-      <c r="O279" s="467"/>
+      <c r="O279" s="457"/>
       <c r="P279" s="70"/>
       <c r="Q279" s="91"/>
       <c r="R279" s="32" t="s">
@@ -41359,7 +41320,7 @@
       <c r="B283" s="95" t="s">
         <v>434</v>
       </c>
-      <c r="C283" s="425" t="s">
+      <c r="C283" s="336" t="s">
         <v>2341</v>
       </c>
       <c r="D283" s="235"/>
@@ -41379,7 +41340,7 @@
       <c r="J283" s="22"/>
       <c r="K283" s="22"/>
       <c r="L283" s="22"/>
-      <c r="M283" s="465" t="s">
+      <c r="M283" s="455" t="s">
         <v>2346</v>
       </c>
       <c r="N283" s="38" t="s">
@@ -41527,7 +41488,7 @@
       <c r="N285" s="38" t="s">
         <v>2360</v>
       </c>
-      <c r="O285" s="468"/>
+      <c r="O285" s="322"/>
       <c r="P285" s="126"/>
       <c r="Q285" s="26"/>
       <c r="R285" s="117" t="s">
@@ -41588,7 +41549,7 @@
       <c r="J286" s="22"/>
       <c r="K286" s="22"/>
       <c r="L286" s="22"/>
-      <c r="M286" s="463" t="s">
+      <c r="M286" s="454" t="s">
         <v>3978</v>
       </c>
       <c r="N286" s="89" t="s">
@@ -41736,7 +41697,7 @@
       <c r="N288" s="65" t="s">
         <v>2374</v>
       </c>
-      <c r="O288" s="468"/>
+      <c r="O288" s="322"/>
       <c r="P288" s="126"/>
       <c r="Q288" s="123"/>
       <c r="R288" s="32" t="s">
@@ -42097,7 +42058,7 @@
       <c r="N293" s="54" t="s">
         <v>2414</v>
       </c>
-      <c r="O293" s="469" t="s">
+      <c r="O293" s="458" t="s">
         <v>806</v>
       </c>
       <c r="P293" s="114"/>
@@ -42115,7 +42076,7 @@
       <c r="V293" s="28"/>
       <c r="W293" s="72"/>
       <c r="X293" s="72"/>
-      <c r="Y293" s="507" t="s">
+      <c r="Y293" s="493" t="s">
         <v>2415</v>
       </c>
       <c r="Z293" s="30" t="s">
@@ -42153,7 +42114,7 @@
       </c>
       <c r="D294" s="235"/>
       <c r="E294" s="58"/>
-      <c r="F294" s="440" t="s">
+      <c r="F294" s="434" t="s">
         <v>2419</v>
       </c>
       <c r="G294" s="32" t="s">
@@ -42174,7 +42135,7 @@
       <c r="N294" s="89" t="s">
         <v>2422</v>
       </c>
-      <c r="O294" s="467"/>
+      <c r="O294" s="457"/>
       <c r="P294" s="114" t="s">
         <v>1907</v>
       </c>
@@ -42328,7 +42289,7 @@
       </c>
       <c r="K296" s="22"/>
       <c r="L296" s="22"/>
-      <c r="M296" s="422" t="s">
+      <c r="M296" s="39" t="s">
         <v>137</v>
       </c>
       <c r="N296" s="38" t="s">
@@ -42482,7 +42443,7 @@
       <c r="N298" s="89" t="s">
         <v>2184</v>
       </c>
-      <c r="O298" s="467"/>
+      <c r="O298" s="457"/>
       <c r="P298" s="70"/>
       <c r="Q298" s="91"/>
       <c r="R298" s="101" t="s">
@@ -42847,7 +42808,7 @@
       </c>
       <c r="O303" s="38"/>
       <c r="P303" s="25"/>
-      <c r="Q303" s="481"/>
+      <c r="Q303" s="470"/>
       <c r="R303" s="101" t="s">
         <v>544</v>
       </c>
@@ -43583,14 +43544,14 @@
       <c r="N313" s="38" t="s">
         <v>2574</v>
       </c>
-      <c r="O313" s="468"/>
+      <c r="O313" s="322"/>
       <c r="P313" s="59" t="s">
         <v>2575</v>
       </c>
       <c r="Q313" s="26" t="s">
         <v>2576</v>
       </c>
-      <c r="R313" s="483" t="s">
+      <c r="R313" s="333" t="s">
         <v>40</v>
       </c>
       <c r="S313" s="77" t="s">
@@ -43748,13 +43709,13 @@
       <c r="O315" s="38"/>
       <c r="P315" s="25"/>
       <c r="Q315" s="26"/>
-      <c r="R315" s="422" t="s">
+      <c r="R315" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S315" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="T315" s="496" t="s">
+      <c r="T315" s="482" t="s">
         <v>2597</v>
       </c>
       <c r="U315" s="28"/>
@@ -43877,7 +43838,7 @@
       <c r="J317" s="22"/>
       <c r="K317" s="82"/>
       <c r="L317" s="82"/>
-      <c r="M317" s="458" t="s">
+      <c r="M317" s="324" t="s">
         <v>1621</v>
       </c>
       <c r="N317" s="38" t="s">
@@ -43937,7 +43898,6 @@
       <c r="C318" s="263" t="s">
         <v>3805</v>
       </c>
-      <c r="D318" s="432"/>
       <c r="E318" s="58" t="s">
         <v>2611</v>
       </c>
@@ -43956,7 +43916,7 @@
       </c>
       <c r="K318" s="22"/>
       <c r="L318" s="168"/>
-      <c r="M318" s="464" t="s">
+      <c r="M318" s="338" t="s">
         <v>2615</v>
       </c>
       <c r="N318" s="89" t="s">
@@ -44033,7 +43993,7 @@
       <c r="J319" s="82"/>
       <c r="K319" s="82"/>
       <c r="L319" s="22"/>
-      <c r="M319" s="458" t="s">
+      <c r="M319" s="324" t="s">
         <v>1287</v>
       </c>
       <c r="N319" s="38" t="s">
@@ -44114,7 +44074,7 @@
       <c r="L320" s="22" t="s">
         <v>2633</v>
       </c>
-      <c r="M320" s="462" t="s">
+      <c r="M320" s="453" t="s">
         <v>863</v>
       </c>
       <c r="N320" s="38" t="s">
@@ -44123,7 +44083,7 @@
       <c r="O320" s="38"/>
       <c r="P320" s="25"/>
       <c r="Q320" s="56"/>
-      <c r="R320" s="422" t="s">
+      <c r="R320" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S320" s="77" t="s">
@@ -44268,7 +44228,7 @@
       <c r="J322" s="22"/>
       <c r="K322" s="82"/>
       <c r="L322" s="82"/>
-      <c r="M322" s="458" t="s">
+      <c r="M322" s="324" t="s">
         <v>804</v>
       </c>
       <c r="N322" s="38" t="s">
@@ -44350,7 +44310,7 @@
       <c r="O323" s="38"/>
       <c r="P323" s="25"/>
       <c r="Q323" s="56"/>
-      <c r="R323" s="422" t="s">
+      <c r="R323" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S323" s="77" t="s">
@@ -44423,7 +44383,7 @@
       <c r="O324" s="38"/>
       <c r="P324" s="25"/>
       <c r="Q324" s="56"/>
-      <c r="R324" s="458" t="s">
+      <c r="R324" s="324" t="s">
         <v>2669</v>
       </c>
       <c r="S324" s="137" t="s">
@@ -44500,7 +44460,7 @@
       <c r="Q325" s="56" t="s">
         <v>2676</v>
       </c>
-      <c r="R325" s="422" t="s">
+      <c r="R325" s="39" t="s">
         <v>710</v>
       </c>
       <c r="S325" s="77" t="s">
@@ -44541,7 +44501,7 @@
       <c r="C326" s="250" t="s">
         <v>171</v>
       </c>
-      <c r="D326" s="434"/>
+      <c r="D326" s="429"/>
       <c r="E326" s="190"/>
       <c r="F326" s="191" t="s">
         <v>2678</v>
@@ -44699,7 +44659,7 @@
       </c>
       <c r="D328" s="247"/>
       <c r="E328" s="190"/>
-      <c r="F328" s="441" t="s">
+      <c r="F328" s="435" t="s">
         <v>2695</v>
       </c>
       <c r="G328" s="186"/>
@@ -44891,7 +44851,7 @@
       <c r="Q330" s="56" t="s">
         <v>2721</v>
       </c>
-      <c r="R330" s="422" t="s">
+      <c r="R330" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S330" s="77" t="s">
@@ -44970,7 +44930,7 @@
       <c r="O331" s="38"/>
       <c r="P331" s="25"/>
       <c r="Q331" s="56"/>
-      <c r="R331" s="422" t="s">
+      <c r="R331" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S331" s="77" t="s">
@@ -45047,7 +45007,7 @@
       <c r="O332" s="38"/>
       <c r="P332" s="25"/>
       <c r="Q332" s="56"/>
-      <c r="R332" s="422" t="s">
+      <c r="R332" s="39" t="s">
         <v>642</v>
       </c>
       <c r="S332" s="77" t="s">
@@ -45193,7 +45153,7 @@
       <c r="O334" s="38"/>
       <c r="P334" s="25"/>
       <c r="Q334" s="56"/>
-      <c r="R334" s="484" t="s">
+      <c r="R334" s="94" t="s">
         <v>1105</v>
       </c>
       <c r="S334" s="77" t="s">
@@ -45263,10 +45223,10 @@
       <c r="N335" s="38" t="s">
         <v>2756</v>
       </c>
-      <c r="O335" s="468"/>
+      <c r="O335" s="322"/>
       <c r="P335" s="126"/>
       <c r="Q335" s="56"/>
-      <c r="R335" s="484" t="s">
+      <c r="R335" s="94" t="s">
         <v>544</v>
       </c>
       <c r="S335" s="77" t="s">
@@ -45345,7 +45305,7 @@
       <c r="Q336" s="56" t="s">
         <v>1908</v>
       </c>
-      <c r="R336" s="465" t="s">
+      <c r="R336" s="455" t="s">
         <v>1554</v>
       </c>
       <c r="S336" s="137" t="s">
@@ -45413,7 +45373,7 @@
       <c r="L337" s="82" t="s">
         <v>2774</v>
       </c>
-      <c r="M337" s="458" t="s">
+      <c r="M337" s="324" t="s">
         <v>2775</v>
       </c>
       <c r="N337" s="38" t="s">
@@ -45426,7 +45386,7 @@
       <c r="Q337" s="56" t="s">
         <v>2778</v>
       </c>
-      <c r="R337" s="422" t="s">
+      <c r="R337" s="39" t="s">
         <v>1743</v>
       </c>
       <c r="S337" s="77" t="s">
@@ -45497,7 +45457,7 @@
       <c r="Q338" s="56" t="s">
         <v>2786</v>
       </c>
-      <c r="R338" s="486" t="s">
+      <c r="R338" s="473" t="s">
         <v>2787</v>
       </c>
       <c r="S338" s="77" t="s">
@@ -45563,7 +45523,7 @@
       <c r="N339" s="38" t="s">
         <v>2795</v>
       </c>
-      <c r="O339" s="468"/>
+      <c r="O339" s="322"/>
       <c r="P339" s="126"/>
       <c r="Q339" s="56"/>
       <c r="R339" s="96" t="s">
@@ -45640,14 +45600,14 @@
       <c r="N340" s="38" t="s">
         <v>2805</v>
       </c>
-      <c r="O340" s="468"/>
+      <c r="O340" s="322"/>
       <c r="P340" s="70" t="s">
         <v>2806</v>
       </c>
       <c r="Q340" s="56" t="s">
         <v>2807</v>
       </c>
-      <c r="R340" s="422" t="s">
+      <c r="R340" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S340" s="77" t="s">
@@ -45730,7 +45690,7 @@
       <c r="Q341" s="56" t="s">
         <v>2807</v>
       </c>
-      <c r="R341" s="422" t="s">
+      <c r="R341" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S341" s="77" t="s">
@@ -45782,7 +45742,7 @@
       <c r="H342" s="206" t="s">
         <v>2820</v>
       </c>
-      <c r="I342" s="448" t="s">
+      <c r="I342" s="442" t="s">
         <v>2519</v>
       </c>
       <c r="J342" s="22" t="s">
@@ -45817,7 +45777,7 @@
       <c r="Y342" s="30" t="s">
         <v>2824</v>
       </c>
-      <c r="Z342" s="505"/>
+      <c r="Z342" s="491"/>
       <c r="AA342" s="30" t="s">
         <v>2825</v>
       </c>
@@ -45941,10 +45901,10 @@
       <c r="M344" s="137" t="s">
         <v>2838</v>
       </c>
-      <c r="N344" s="468" t="s">
+      <c r="N344" s="322" t="s">
         <v>2839</v>
       </c>
-      <c r="O344" s="468" t="s">
+      <c r="O344" s="322" t="s">
         <v>2840</v>
       </c>
       <c r="P344" s="25"/>
@@ -46073,7 +46033,7 @@
     </row>
     <row r="346" spans="1:43" ht="15.75" customHeight="1">
       <c r="A346" s="193" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="B346" s="33" t="s">
         <v>434</v>
@@ -46098,7 +46058,7 @@
       <c r="L346" s="22" t="s">
         <v>1286</v>
       </c>
-      <c r="M346" s="455" t="s">
+      <c r="M346" s="331" t="s">
         <v>657</v>
       </c>
       <c r="N346" s="38" t="s">
@@ -46181,7 +46141,7 @@
       </c>
       <c r="K347" s="22"/>
       <c r="L347" s="22"/>
-      <c r="M347" s="461" t="s">
+      <c r="M347" s="452" t="s">
         <v>2822</v>
       </c>
       <c r="N347" s="65" t="s">
@@ -46339,7 +46299,7 @@
       <c r="N349" s="38" t="s">
         <v>2882</v>
       </c>
-      <c r="O349" s="468" t="s">
+      <c r="O349" s="322" t="s">
         <v>774</v>
       </c>
       <c r="P349" s="126"/>
@@ -46497,7 +46457,7 @@
       <c r="N351" s="38" t="s">
         <v>2900</v>
       </c>
-      <c r="O351" s="468"/>
+      <c r="O351" s="322"/>
       <c r="P351" s="126"/>
       <c r="Q351" s="26"/>
       <c r="R351" s="99" t="s">
@@ -46653,7 +46613,7 @@
       <c r="N353" s="89" t="s">
         <v>2915</v>
       </c>
-      <c r="O353" s="467"/>
+      <c r="O353" s="457"/>
       <c r="P353" s="70"/>
       <c r="Q353" s="91"/>
       <c r="R353" s="77" t="s">
@@ -47598,7 +47558,7 @@
       <c r="Y365" s="198" t="s">
         <v>3009</v>
       </c>
-      <c r="Z365" s="505"/>
+      <c r="Z365" s="491"/>
       <c r="AA365" s="198" t="s">
         <v>3010</v>
       </c>
@@ -47711,7 +47671,7 @@
       <c r="F367" s="47" t="s">
         <v>3019</v>
       </c>
-      <c r="G367" s="422"/>
+      <c r="G367" s="39"/>
       <c r="H367" s="206" t="s">
         <v>3020</v>
       </c>
@@ -47736,7 +47696,7 @@
       <c r="Q367" s="26" t="s">
         <v>3024</v>
       </c>
-      <c r="R367" s="422" t="s">
+      <c r="R367" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S367" s="77" t="s">
@@ -47792,7 +47752,7 @@
       <c r="F368" s="47" t="s">
         <v>3029</v>
       </c>
-      <c r="G368" s="422"/>
+      <c r="G368" s="39"/>
       <c r="H368" s="206" t="s">
         <v>3030</v>
       </c>
@@ -47815,7 +47775,7 @@
       <c r="Q368" s="26" t="s">
         <v>3034</v>
       </c>
-      <c r="R368" s="422" t="s">
+      <c r="R368" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S368" s="77" t="s">
@@ -47894,16 +47854,14 @@
       <c r="Q369" s="403" t="s">
         <v>1170</v>
       </c>
-      <c r="R369" s="489" t="s">
+      <c r="R369" s="476" t="s">
         <v>523</v>
       </c>
       <c r="S369" s="404" t="s">
         <v>41</v>
       </c>
       <c r="T369" s="405"/>
-      <c r="U369" s="412" t="s">
-        <v>4008</v>
-      </c>
+      <c r="U369" s="412"/>
       <c r="V369" s="406"/>
       <c r="W369" s="407" t="s">
         <v>3042</v>
@@ -47914,7 +47872,7 @@
       <c r="Y369" s="408" t="s">
         <v>3044</v>
       </c>
-      <c r="Z369" s="509" t="s">
+      <c r="Z369" s="495" t="s">
         <v>3045</v>
       </c>
       <c r="AA369" s="408" t="s">
@@ -47924,7 +47882,7 @@
         <v>4005</v>
       </c>
       <c r="AC369" s="413" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="AD369" s="405"/>
       <c r="AE369" s="32"/>
@@ -47956,7 +47914,7 @@
       <c r="F370" s="47" t="s">
         <v>3049</v>
       </c>
-      <c r="G370" s="422"/>
+      <c r="G370" s="39"/>
       <c r="H370" s="206" t="s">
         <v>3050</v>
       </c>
@@ -47979,7 +47937,7 @@
       <c r="Q370" s="26" t="s">
         <v>1170</v>
       </c>
-      <c r="R370" s="484" t="s">
+      <c r="R370" s="94" t="s">
         <v>544</v>
       </c>
       <c r="S370" s="77" t="s">
@@ -48001,7 +47959,7 @@
       <c r="AA370" s="389" t="s">
         <v>3053</v>
       </c>
-      <c r="AB370" s="512"/>
+      <c r="AB370" s="498"/>
       <c r="AC370" s="16" t="s">
         <v>3054</v>
       </c>
@@ -48062,7 +48020,7 @@
       <c r="O371" s="54"/>
       <c r="P371" s="55"/>
       <c r="Q371" s="56"/>
-      <c r="R371" s="484" t="s">
+      <c r="R371" s="94" t="s">
         <v>1105</v>
       </c>
       <c r="S371" s="77" t="s">
@@ -48114,7 +48072,7 @@
       <c r="F372" s="16" t="s">
         <v>3065</v>
       </c>
-      <c r="G372" s="422"/>
+      <c r="G372" s="39"/>
       <c r="H372" s="206" t="s">
         <v>3066</v>
       </c>
@@ -48214,7 +48172,7 @@
       <c r="O373" s="54"/>
       <c r="P373" s="55"/>
       <c r="Q373" s="56"/>
-      <c r="R373" s="490" t="s">
+      <c r="R373" s="323" t="s">
         <v>139</v>
       </c>
       <c r="S373" s="77" t="s">
@@ -48266,7 +48224,7 @@
       <c r="F374" s="47" t="s">
         <v>3081</v>
       </c>
-      <c r="G374" s="422"/>
+      <c r="G374" s="39"/>
       <c r="H374" s="206" t="s">
         <v>3082</v>
       </c>
@@ -48291,7 +48249,7 @@
       <c r="Q374" s="56" t="s">
         <v>3085</v>
       </c>
-      <c r="R374" s="422" t="s">
+      <c r="R374" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S374" s="77" t="s">
@@ -48365,7 +48323,7 @@
       <c r="N375" s="54" t="s">
         <v>3095</v>
       </c>
-      <c r="O375" s="468" t="s">
+      <c r="O375" s="322" t="s">
         <v>38</v>
       </c>
       <c r="P375" s="114"/>
@@ -48387,10 +48345,10 @@
       <c r="X375" s="29" t="s">
         <v>2243</v>
       </c>
-      <c r="Y375" s="506" t="s">
+      <c r="Y375" s="492" t="s">
         <v>3096</v>
       </c>
-      <c r="Z375" s="505"/>
+      <c r="Z375" s="491"/>
       <c r="AA375" s="30" t="s">
         <v>3097</v>
       </c>
@@ -48420,52 +48378,51 @@
       <c r="B376" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C376" s="426" t="s">
+      <c r="C376" s="262" t="s">
         <v>171</v>
       </c>
-      <c r="D376" s="432"/>
-      <c r="E376" s="436"/>
-      <c r="F376" s="439" t="s">
+      <c r="E376" s="230"/>
+      <c r="F376" s="433" t="s">
         <v>3837</v>
       </c>
-      <c r="G376" s="436"/>
-      <c r="H376" s="424" t="s">
+      <c r="G376" s="230"/>
+      <c r="H376" s="423" t="s">
         <v>3796</v>
       </c>
-      <c r="I376" s="424" t="s">
+      <c r="I376" s="423" t="s">
         <v>3100</v>
       </c>
-      <c r="J376" s="436"/>
-      <c r="K376" s="436"/>
-      <c r="L376" s="436"/>
-      <c r="M376" s="459" t="s">
+      <c r="J376" s="230"/>
+      <c r="K376" s="230"/>
+      <c r="L376" s="230"/>
+      <c r="M376" s="450" t="s">
         <v>2085</v>
       </c>
-      <c r="N376" s="470" t="s">
+      <c r="N376" s="459" t="s">
         <v>2086</v>
       </c>
-      <c r="O376" s="436"/>
-      <c r="P376" s="436"/>
-      <c r="Q376" s="436"/>
-      <c r="R376" s="436" t="s">
+      <c r="O376" s="230"/>
+      <c r="P376" s="230"/>
+      <c r="Q376" s="230"/>
+      <c r="R376" s="230" t="s">
         <v>642</v>
       </c>
-      <c r="S376" s="424" t="s">
+      <c r="S376" s="423" t="s">
         <v>41</v>
       </c>
-      <c r="T376" s="424" t="s">
+      <c r="T376" s="423" t="s">
         <v>3797</v>
       </c>
-      <c r="U376" s="436"/>
-      <c r="V376" s="436"/>
-      <c r="W376" s="436"/>
-      <c r="X376" s="436"/>
-      <c r="Y376" s="436"/>
-      <c r="Z376" s="436"/>
-      <c r="AA376" s="436"/>
-      <c r="AB376" s="436"/>
-      <c r="AC376" s="436"/>
-      <c r="AD376" s="424" t="s">
+      <c r="U376" s="230"/>
+      <c r="V376" s="230"/>
+      <c r="W376" s="230"/>
+      <c r="X376" s="230"/>
+      <c r="Y376" s="230"/>
+      <c r="Z376" s="230"/>
+      <c r="AA376" s="230"/>
+      <c r="AB376" s="230"/>
+      <c r="AC376" s="230"/>
+      <c r="AD376" s="423" t="s">
         <v>3798</v>
       </c>
       <c r="AE376" s="230"/>
@@ -48522,7 +48479,7 @@
       <c r="Q377" s="56" t="s">
         <v>3107</v>
       </c>
-      <c r="R377" s="484" t="s">
+      <c r="R377" s="94" t="s">
         <v>544</v>
       </c>
       <c r="S377" s="77" t="s">
@@ -48537,10 +48494,10 @@
       <c r="X377" s="29" t="s">
         <v>2243</v>
       </c>
-      <c r="Y377" s="505" t="s">
+      <c r="Y377" s="491" t="s">
         <v>2824</v>
       </c>
-      <c r="Z377" s="505"/>
+      <c r="Z377" s="491"/>
       <c r="AA377" s="198" t="s">
         <v>3108</v>
       </c>
@@ -48597,7 +48554,7 @@
       <c r="O378" s="38"/>
       <c r="P378" s="25"/>
       <c r="Q378" s="26"/>
-      <c r="R378" s="484" t="s">
+      <c r="R378" s="94" t="s">
         <v>544</v>
       </c>
       <c r="S378" s="77" t="s">
@@ -48669,14 +48626,14 @@
       <c r="N379" s="54" t="s">
         <v>3121</v>
       </c>
-      <c r="O379" s="469" t="s">
+      <c r="O379" s="458" t="s">
         <v>3122</v>
       </c>
       <c r="P379" s="114"/>
       <c r="Q379" s="56" t="s">
         <v>3123</v>
       </c>
-      <c r="R379" s="422" t="s">
+      <c r="R379" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S379" s="77" t="s">
@@ -48759,7 +48716,7 @@
       <c r="Q380" s="56" t="s">
         <v>3135</v>
       </c>
-      <c r="R380" s="422" t="s">
+      <c r="R380" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S380" s="77" t="s">
@@ -48812,7 +48769,7 @@
       </c>
       <c r="D381" s="235"/>
       <c r="E381" s="58"/>
-      <c r="F381" s="443" t="s">
+      <c r="F381" s="437" t="s">
         <v>3140</v>
       </c>
       <c r="G381" s="32"/>
@@ -48836,7 +48793,7 @@
       <c r="O381" s="54"/>
       <c r="P381" s="55"/>
       <c r="Q381" s="213"/>
-      <c r="R381" s="484" t="s">
+      <c r="R381" s="94" t="s">
         <v>544</v>
       </c>
       <c r="S381" s="77" t="s">
@@ -48854,7 +48811,7 @@
       <c r="Y381" s="198" t="s">
         <v>2824</v>
       </c>
-      <c r="Z381" s="510"/>
+      <c r="Z381" s="496"/>
       <c r="AA381" s="214" t="s">
         <v>3144</v>
       </c>
@@ -48887,7 +48844,7 @@
       <c r="C382" s="374"/>
       <c r="D382" s="375"/>
       <c r="E382" s="376"/>
-      <c r="F382" s="442" t="s">
+      <c r="F382" s="436" t="s">
         <v>3991</v>
       </c>
       <c r="G382" s="377"/>
@@ -48909,7 +48866,7 @@
       <c r="O382" s="370"/>
       <c r="P382" s="371"/>
       <c r="Q382" s="372"/>
-      <c r="R382" s="491"/>
+      <c r="R382" s="477"/>
       <c r="S382" s="381" t="s">
         <v>41</v>
       </c>
@@ -48929,7 +48886,7 @@
         <v>3992</v>
       </c>
       <c r="AA382" s="386"/>
-      <c r="AB382" s="516"/>
+      <c r="AB382" s="502"/>
       <c r="AC382" s="377"/>
       <c r="AD382" s="382"/>
       <c r="AE382" s="32"/>
@@ -48948,7 +48905,7 @@
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
       <c r="A383" s="281" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>434</v>
@@ -48961,7 +48918,7 @@
       <c r="F383" s="16" t="s">
         <v>3147</v>
       </c>
-      <c r="G383" s="422"/>
+      <c r="G383" s="39"/>
       <c r="H383" s="206" t="s">
         <v>3148</v>
       </c>
@@ -48984,7 +48941,7 @@
       <c r="Q383" s="56" t="s">
         <v>1170</v>
       </c>
-      <c r="R383" s="484" t="s">
+      <c r="R383" s="94" t="s">
         <v>544</v>
       </c>
       <c r="S383" s="77" t="s">
@@ -49059,7 +49016,7 @@
       <c r="O384" s="54"/>
       <c r="P384" s="55"/>
       <c r="Q384" s="56"/>
-      <c r="R384" s="422" t="s">
+      <c r="R384" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S384" s="77" t="s">
@@ -49107,7 +49064,7 @@
       <c r="F385" s="32" t="s">
         <v>2292</v>
       </c>
-      <c r="G385" s="422"/>
+      <c r="G385" s="39"/>
       <c r="H385" s="206" t="s">
         <v>3156</v>
       </c>
@@ -49128,7 +49085,7 @@
       <c r="O385" s="54"/>
       <c r="P385" s="55"/>
       <c r="Q385" s="56"/>
-      <c r="R385" s="422" t="s">
+      <c r="R385" s="39" t="s">
         <v>375</v>
       </c>
       <c r="S385" s="77" t="s">
@@ -49176,7 +49133,7 @@
       <c r="F386" s="16" t="s">
         <v>3161</v>
       </c>
-      <c r="G386" s="422"/>
+      <c r="G386" s="39"/>
       <c r="H386" s="206" t="s">
         <v>3162</v>
       </c>
@@ -49197,7 +49154,7 @@
       <c r="O386" s="54"/>
       <c r="P386" s="55"/>
       <c r="Q386" s="56"/>
-      <c r="R386" s="484" t="s">
+      <c r="R386" s="94" t="s">
         <v>544</v>
       </c>
       <c r="S386" s="77" t="s">
@@ -49245,7 +49202,7 @@
       <c r="F387" s="47" t="s">
         <v>3166</v>
       </c>
-      <c r="G387" s="422"/>
+      <c r="G387" s="39"/>
       <c r="H387" s="206" t="s">
         <v>3167</v>
       </c>
@@ -49391,54 +49348,53 @@
       <c r="B389" s="421" t="s">
         <v>3799</v>
       </c>
-      <c r="C389" s="426" t="s">
+      <c r="C389" s="262" t="s">
         <v>171</v>
       </c>
-      <c r="D389" s="432"/>
-      <c r="E389" s="436"/>
-      <c r="F389" s="439" t="s">
+      <c r="E389" s="230"/>
+      <c r="F389" s="433" t="s">
         <v>3800</v>
       </c>
-      <c r="G389" s="436"/>
-      <c r="H389" s="446" t="s">
+      <c r="G389" s="230"/>
+      <c r="H389" s="440" t="s">
         <v>3801</v>
       </c>
-      <c r="I389" s="446" t="s">
+      <c r="I389" s="440" t="s">
         <v>3184</v>
       </c>
-      <c r="J389" s="436"/>
-      <c r="K389" s="436"/>
-      <c r="L389" s="436" t="s">
+      <c r="J389" s="230"/>
+      <c r="K389" s="230"/>
+      <c r="L389" s="230" t="s">
         <v>3802</v>
       </c>
-      <c r="M389" s="459" t="s">
+      <c r="M389" s="450" t="s">
         <v>2085</v>
       </c>
-      <c r="N389" s="470" t="s">
+      <c r="N389" s="459" t="s">
         <v>2086</v>
       </c>
-      <c r="O389" s="436"/>
-      <c r="P389" s="436"/>
-      <c r="Q389" s="436"/>
-      <c r="R389" s="436" t="s">
+      <c r="O389" s="230"/>
+      <c r="P389" s="230"/>
+      <c r="Q389" s="230"/>
+      <c r="R389" s="230" t="s">
         <v>642</v>
       </c>
-      <c r="S389" s="424" t="s">
+      <c r="S389" s="423" t="s">
         <v>41</v>
       </c>
-      <c r="T389" s="424" t="s">
+      <c r="T389" s="423" t="s">
         <v>3803</v>
       </c>
-      <c r="U389" s="436"/>
-      <c r="V389" s="436"/>
-      <c r="W389" s="436"/>
-      <c r="X389" s="436"/>
-      <c r="Y389" s="436"/>
-      <c r="Z389" s="436"/>
-      <c r="AA389" s="436"/>
-      <c r="AB389" s="436"/>
-      <c r="AC389" s="436"/>
-      <c r="AD389" s="424" t="s">
+      <c r="U389" s="230"/>
+      <c r="V389" s="230"/>
+      <c r="W389" s="230"/>
+      <c r="X389" s="230"/>
+      <c r="Y389" s="230"/>
+      <c r="Z389" s="230"/>
+      <c r="AA389" s="230"/>
+      <c r="AB389" s="230"/>
+      <c r="AC389" s="230"/>
+      <c r="AD389" s="423" t="s">
         <v>3804</v>
       </c>
       <c r="AE389" s="230"/>
@@ -49488,7 +49444,7 @@
       <c r="N390" s="54" t="s">
         <v>3191</v>
       </c>
-      <c r="O390" s="469"/>
+      <c r="O390" s="458"/>
       <c r="P390" s="114"/>
       <c r="Q390" s="56"/>
       <c r="R390" s="323" t="s">
@@ -49698,16 +49654,16 @@
       <c r="C393" s="255" t="s">
         <v>171</v>
       </c>
-      <c r="D393" s="431"/>
+      <c r="D393" s="337"/>
       <c r="E393" s="138"/>
-      <c r="F393" s="438" t="s">
+      <c r="F393" s="432" t="s">
         <v>3211</v>
       </c>
       <c r="G393" s="32"/>
-      <c r="H393" s="445" t="s">
+      <c r="H393" s="439" t="s">
         <v>3212</v>
       </c>
-      <c r="I393" s="422" t="s">
+      <c r="I393" s="39" t="s">
         <v>2519</v>
       </c>
       <c r="J393" s="82"/>
@@ -49718,23 +49674,23 @@
       <c r="M393" s="137" t="s">
         <v>542</v>
       </c>
-      <c r="N393" s="469" t="s">
+      <c r="N393" s="458" t="s">
         <v>3213</v>
       </c>
-      <c r="O393" s="469"/>
+      <c r="O393" s="458"/>
       <c r="P393" s="114"/>
       <c r="Q393" s="123"/>
       <c r="R393" s="96" t="s">
         <v>544</v>
       </c>
-      <c r="S393" s="490" t="s">
+      <c r="S393" s="323" t="s">
         <v>41</v>
       </c>
       <c r="T393" s="105" t="s">
         <v>3214</v>
       </c>
-      <c r="U393" s="498"/>
-      <c r="V393" s="498"/>
+      <c r="U393" s="484"/>
+      <c r="V393" s="484"/>
       <c r="W393" s="29" t="s">
         <v>2242</v>
       </c>
@@ -49748,8 +49704,8 @@
       <c r="AA393" s="103" t="s">
         <v>3216</v>
       </c>
-      <c r="AB393" s="512"/>
-      <c r="AC393" s="422"/>
+      <c r="AB393" s="498"/>
+      <c r="AC393" s="39"/>
       <c r="AD393" s="105"/>
       <c r="AE393" s="39"/>
       <c r="AF393" s="39"/>
@@ -50307,11 +50263,11 @@
         <v>2559</v>
       </c>
       <c r="J401" s="22"/>
-      <c r="K401" s="453" t="s">
+      <c r="K401" s="447" t="s">
         <v>34</v>
       </c>
-      <c r="L401" s="453"/>
-      <c r="M401" s="460" t="s">
+      <c r="L401" s="447"/>
+      <c r="M401" s="451" t="s">
         <v>3270</v>
       </c>
       <c r="N401" s="38" t="s">
@@ -50390,7 +50346,7 @@
       </c>
       <c r="K402" s="22"/>
       <c r="L402" s="22"/>
-      <c r="M402" s="464" t="s">
+      <c r="M402" s="338" t="s">
         <v>137</v>
       </c>
       <c r="N402" s="54" t="s">
@@ -50465,7 +50421,7 @@
       <c r="L403" s="22" t="s">
         <v>3284</v>
       </c>
-      <c r="M403" s="460" t="s">
+      <c r="M403" s="451" t="s">
         <v>3285</v>
       </c>
       <c r="N403" s="38" t="s">
@@ -50478,7 +50434,7 @@
       <c r="Q403" s="56" t="s">
         <v>3288</v>
       </c>
-      <c r="R403" s="422" t="s">
+      <c r="R403" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S403" s="77" t="s">
@@ -50548,7 +50504,7 @@
       <c r="L404" s="22" t="s">
         <v>3296</v>
       </c>
-      <c r="M404" s="455" t="s">
+      <c r="M404" s="331" t="s">
         <v>601</v>
       </c>
       <c r="N404" s="38" t="s">
@@ -50575,7 +50531,7 @@
       <c r="Y404" s="198" t="s">
         <v>3298</v>
       </c>
-      <c r="Z404" s="505"/>
+      <c r="Z404" s="491"/>
       <c r="AA404" s="198" t="s">
         <v>3299</v>
       </c>
@@ -50625,7 +50581,7 @@
       <c r="J405" s="82"/>
       <c r="K405" s="82"/>
       <c r="L405" s="82"/>
-      <c r="M405" s="455" t="s">
+      <c r="M405" s="331" t="s">
         <v>1287</v>
       </c>
       <c r="N405" s="38" t="s">
@@ -50656,7 +50612,7 @@
       <c r="Y405" s="198" t="s">
         <v>3306</v>
       </c>
-      <c r="Z405" s="505"/>
+      <c r="Z405" s="491"/>
       <c r="AA405" s="198" t="s">
         <v>3307</v>
       </c>
@@ -50706,7 +50662,7 @@
       <c r="J406" s="22"/>
       <c r="K406" s="22"/>
       <c r="L406" s="22"/>
-      <c r="M406" s="455" t="s">
+      <c r="M406" s="331" t="s">
         <v>3149</v>
       </c>
       <c r="N406" s="38" t="s">
@@ -50739,7 +50695,7 @@
       <c r="Y406" s="198" t="s">
         <v>3273</v>
       </c>
-      <c r="Z406" s="505"/>
+      <c r="Z406" s="491"/>
       <c r="AA406" s="198" t="s">
         <v>3314</v>
       </c>
@@ -50795,7 +50751,7 @@
       <c r="N407" s="38" t="s">
         <v>3319</v>
       </c>
-      <c r="O407" s="468"/>
+      <c r="O407" s="322"/>
       <c r="P407" s="126"/>
       <c r="Q407" s="56"/>
       <c r="R407" s="117" t="s">
@@ -51148,7 +51104,7 @@
       <c r="F412" s="47" t="s">
         <v>3353</v>
       </c>
-      <c r="G412" s="422"/>
+      <c r="G412" s="39"/>
       <c r="H412" s="206" t="s">
         <v>3354</v>
       </c>
@@ -51312,7 +51268,7 @@
       </c>
       <c r="K414" s="22"/>
       <c r="L414" s="22"/>
-      <c r="M414" s="464" t="s">
+      <c r="M414" s="338" t="s">
         <v>137</v>
       </c>
       <c r="N414" s="38" t="s">
@@ -51365,7 +51321,7 @@
       <c r="B415" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C415" s="425" t="s">
+      <c r="C415" s="336" t="s">
         <v>3373</v>
       </c>
       <c r="D415" s="247"/>
@@ -51458,7 +51414,7 @@
       <c r="J416" s="22"/>
       <c r="K416" s="22"/>
       <c r="L416" s="22"/>
-      <c r="M416" s="455" t="s">
+      <c r="M416" s="331" t="s">
         <v>1842</v>
       </c>
       <c r="N416" s="38" t="s">
@@ -51595,7 +51551,7 @@
         <v>3390</v>
       </c>
       <c r="G418" s="32"/>
-      <c r="H418" s="422" t="s">
+      <c r="H418" s="39" t="s">
         <v>3391</v>
       </c>
       <c r="I418" s="192" t="s">
@@ -51655,7 +51611,7 @@
       <c r="B419" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C419" s="427" t="s">
+      <c r="C419" s="424" t="s">
         <v>3967</v>
       </c>
       <c r="D419" s="235"/>
@@ -51771,7 +51727,7 @@
       <c r="Y420" s="30" t="s">
         <v>3405</v>
       </c>
-      <c r="Z420" s="505"/>
+      <c r="Z420" s="491"/>
       <c r="AA420" s="30" t="s">
         <v>3406</v>
       </c>
@@ -51799,7 +51755,7 @@
       <c r="B421" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C421" s="427" t="s">
+      <c r="C421" s="424" t="s">
         <v>3945</v>
       </c>
       <c r="D421" s="247"/>
@@ -52068,7 +52024,7 @@
       <c r="N424" s="38" t="s">
         <v>2494</v>
       </c>
-      <c r="O424" s="468"/>
+      <c r="O424" s="322"/>
       <c r="P424" s="126"/>
       <c r="Q424" s="56"/>
       <c r="R424" s="117" t="s">
@@ -52210,7 +52166,7 @@
       <c r="J426" s="22"/>
       <c r="K426" s="93"/>
       <c r="L426" s="93"/>
-      <c r="M426" s="422" t="s">
+      <c r="M426" s="39" t="s">
         <v>2085</v>
       </c>
       <c r="N426" s="137" t="s">
@@ -52423,7 +52379,7 @@
       <c r="N429" s="54" t="s">
         <v>3389</v>
       </c>
-      <c r="O429" s="469"/>
+      <c r="O429" s="458"/>
       <c r="P429" s="114"/>
       <c r="Q429" s="123"/>
       <c r="R429" s="117" t="s">
@@ -52628,7 +52584,7 @@
       <c r="N432" s="54" t="s">
         <v>3469</v>
       </c>
-      <c r="O432" s="469"/>
+      <c r="O432" s="458"/>
       <c r="P432" s="114"/>
       <c r="Q432" s="123"/>
       <c r="R432" s="324" t="s">
@@ -53202,7 +53158,7 @@
       <c r="N440" s="54" t="s">
         <v>1952</v>
       </c>
-      <c r="O440" s="469"/>
+      <c r="O440" s="458"/>
       <c r="P440" s="114"/>
       <c r="Q440" s="56"/>
       <c r="R440" s="96" t="s">
@@ -53275,7 +53231,7 @@
       <c r="N441" s="136" t="s">
         <v>1240</v>
       </c>
-      <c r="O441" s="472" t="s">
+      <c r="O441" s="461" t="s">
         <v>3516</v>
       </c>
       <c r="P441" s="59"/>
@@ -53437,7 +53393,7 @@
       <c r="N443" s="65" t="s">
         <v>3534</v>
       </c>
-      <c r="O443" s="468"/>
+      <c r="O443" s="322"/>
       <c r="P443" s="126"/>
       <c r="Q443" s="26"/>
       <c r="R443" s="99" t="s">
@@ -54715,7 +54671,7 @@
       <c r="Q460" s="56" t="s">
         <v>3594</v>
       </c>
-      <c r="R460" s="484" t="s">
+      <c r="R460" s="94" t="s">
         <v>1105</v>
       </c>
       <c r="S460" s="77" t="s">
@@ -54785,7 +54741,7 @@
       <c r="N461" s="136" t="s">
         <v>3642</v>
       </c>
-      <c r="O461" s="469" t="s">
+      <c r="O461" s="458" t="s">
         <v>3643</v>
       </c>
       <c r="P461" s="114"/>
@@ -55007,11 +54963,11 @@
       <c r="I464" s="303" t="s">
         <v>3660</v>
       </c>
-      <c r="J464" s="450" t="s">
+      <c r="J464" s="444" t="s">
         <v>2280</v>
       </c>
-      <c r="K464" s="450"/>
-      <c r="L464" s="450"/>
+      <c r="K464" s="444"/>
+      <c r="L464" s="444"/>
       <c r="M464" s="304" t="s">
         <v>1603</v>
       </c>
@@ -55021,7 +54977,7 @@
       <c r="O464" s="305"/>
       <c r="P464" s="306"/>
       <c r="Q464" s="307"/>
-      <c r="R464" s="488" t="s">
+      <c r="R464" s="475" t="s">
         <v>3662</v>
       </c>
       <c r="S464" s="308" t="s">
@@ -55092,7 +55048,7 @@
       <c r="Q465" s="56" t="s">
         <v>3670</v>
       </c>
-      <c r="R465" s="422" t="s">
+      <c r="R465" s="39" t="s">
         <v>523</v>
       </c>
       <c r="S465" s="77" t="s">
@@ -55250,7 +55206,7 @@
       <c r="Q467" s="56" t="s">
         <v>3689</v>
       </c>
-      <c r="R467" s="486" t="s">
+      <c r="R467" s="473" t="s">
         <v>2787</v>
       </c>
       <c r="S467" s="77" t="s">
@@ -55446,7 +55402,7 @@
       <c r="F470" s="290" t="s">
         <v>3707</v>
       </c>
-      <c r="G470" s="444" t="s">
+      <c r="G470" s="438" t="s">
         <v>3708</v>
       </c>
       <c r="H470" s="48" t="s">
@@ -55517,7 +55473,7 @@
       <c r="F471" s="47" t="s">
         <v>3714</v>
       </c>
-      <c r="G471" s="422" t="s">
+      <c r="G471" s="39" t="s">
         <v>3715</v>
       </c>
       <c r="H471" s="95" t="s">
@@ -55592,7 +55548,7 @@
       <c r="F472" s="290" t="s">
         <v>3963</v>
       </c>
-      <c r="G472" s="422"/>
+      <c r="G472" s="39"/>
       <c r="H472" s="48" t="s">
         <v>3723</v>
       </c>
@@ -55659,13 +55615,13 @@
       <c r="F473" s="328" t="s">
         <v>3729</v>
       </c>
-      <c r="G473" s="422" t="s">
+      <c r="G473" s="39" t="s">
         <v>3730</v>
       </c>
-      <c r="H473" s="444" t="s">
+      <c r="H473" s="438" t="s">
         <v>3731</v>
       </c>
-      <c r="I473" s="447" t="s">
+      <c r="I473" s="441" t="s">
         <v>2651</v>
       </c>
       <c r="J473" s="82" t="s">
@@ -55673,19 +55629,19 @@
       </c>
       <c r="K473" s="82"/>
       <c r="L473" s="82"/>
-      <c r="M473" s="455" t="s">
+      <c r="M473" s="331" t="s">
         <v>2965</v>
       </c>
-      <c r="N473" s="466" t="s">
+      <c r="N473" s="456" t="s">
         <v>3732</v>
       </c>
-      <c r="O473" s="468"/>
+      <c r="O473" s="322"/>
       <c r="P473" s="126"/>
       <c r="Q473" s="135"/>
       <c r="R473" s="99" t="s">
         <v>1105</v>
       </c>
-      <c r="S473" s="422" t="s">
+      <c r="S473" s="39" t="s">
         <v>41</v>
       </c>
       <c r="T473" s="105"/>
@@ -55697,8 +55653,8 @@
       <c r="Z473" s="103"/>
       <c r="AA473" s="103"/>
       <c r="AB473" s="110"/>
-      <c r="AC473" s="422"/>
-      <c r="AD473" s="422"/>
+      <c r="AC473" s="39"/>
+      <c r="AD473" s="39"/>
       <c r="AE473" s="39"/>
       <c r="AF473" s="39"/>
       <c r="AG473" s="39"/>
@@ -55728,7 +55684,7 @@
       <c r="F474" s="290" t="s">
         <v>3733</v>
       </c>
-      <c r="G474" s="422"/>
+      <c r="G474" s="39"/>
       <c r="H474" s="206" t="s">
         <v>3734</v>
       </c>
@@ -55756,7 +55712,7 @@
       <c r="R474" s="32" t="s">
         <v>523</v>
       </c>
-      <c r="S474" s="490" t="s">
+      <c r="S474" s="323" t="s">
         <v>41</v>
       </c>
       <c r="T474" s="105"/>
@@ -55813,7 +55769,7 @@
       <c r="J475" s="22"/>
       <c r="K475" s="22"/>
       <c r="L475" s="22"/>
-      <c r="M475" s="455" t="s">
+      <c r="M475" s="331" t="s">
         <v>1621</v>
       </c>
       <c r="N475" s="38" t="s">
@@ -55829,7 +55785,7 @@
       <c r="R475" s="32" t="s">
         <v>523</v>
       </c>
-      <c r="S475" s="490" t="s">
+      <c r="S475" s="323" t="s">
         <v>41</v>
       </c>
       <c r="T475" s="105"/>
@@ -65251,7 +65207,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{E57053D5-4E2C-724F-963E-4FF482037ED6}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{9215926A-73C3-044E-9C2A-F1707A71ED79}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5D5699-A69B-DC43-99AD-3B503EB9F74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE65A8B2-1D11-5E47-9C02-C45B3F707294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3200" yWindow="-17320" windowWidth="37740" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3580" yWindow="-20960" windowWidth="37740" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -17122,9 +17122,6 @@
     <t>Lavau, Louis de (?-1694), abbé</t>
   </si>
   <si>
-    <t>anémoscope (autocuiseur) ; armoiries ; couronne</t>
-  </si>
-  <si>
     <t>physique ; héraldique</t>
   </si>
   <si>
@@ -17439,9 +17436,6 @@
     <t>lentille ; camera obscura ; schéma scientifique</t>
   </si>
   <si>
-    <t>camera obscura ; schéma scientifique ; lentille</t>
-  </si>
-  <si>
     <t>télescope ; schéma scientifique</t>
   </si>
   <si>
@@ -17490,7 +17484,13 @@
     <t>planche de texte</t>
   </si>
   <si>
-    <t>1684-06a_140</t>
+    <t>schema</t>
+  </si>
+  <si>
+    <t>camera obscura ;  lentille</t>
+  </si>
+  <si>
+    <t>anémoscope ; armoiries ; couronne</t>
   </si>
 </sst>
 </file>
@@ -20827,7 +20827,7 @@
       <c r="W4" s="29"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="30" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="Z4" s="30"/>
       <c r="AA4" s="30"/>
@@ -21715,7 +21715,7 @@
         <v>191</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="Z16" s="30"/>
       <c r="AA16" s="30"/>
@@ -22388,7 +22388,7 @@
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
       <c r="A25" s="277" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>247</v>
@@ -22457,7 +22457,7 @@
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
       <c r="A26" s="291" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>43</v>
@@ -22528,7 +22528,7 @@
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
       <c r="A27" s="277" t="s">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="B27" s="32" t="s">
         <v>247</v>
@@ -23597,7 +23597,7 @@
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="48" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="I41" s="43" t="s">
         <v>384</v>
@@ -23608,7 +23608,7 @@
         <v>385</v>
       </c>
       <c r="M41" s="95" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="N41" s="54" t="s">
         <v>386</v>
@@ -23772,7 +23772,7 @@
         <v>404</v>
       </c>
       <c r="Y43" s="30" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="Z43" s="30"/>
       <c r="AA43" s="30"/>
@@ -24232,7 +24232,7 @@
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>434</v>
@@ -24303,7 +24303,7 @@
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>444</v>
@@ -28008,7 +28008,7 @@
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
       <c r="A102" s="277" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>890</v>
@@ -28870,7 +28870,7 @@
     </row>
     <row r="114" spans="1:43" ht="15.75" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="B114" s="32" t="s">
         <v>434</v>
@@ -29248,7 +29248,7 @@
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="32" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="I119" s="43" t="s">
         <v>1037</v>
@@ -29444,7 +29444,7 @@
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
       <c r="A122" s="278" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="B122" s="51" t="s">
         <v>43</v>
@@ -29496,7 +29496,7 @@
       <c r="W122" s="29"/>
       <c r="X122" s="29"/>
       <c r="Y122" s="30" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="Z122" s="30"/>
       <c r="AA122" s="30"/>
@@ -30556,7 +30556,7 @@
       </c>
       <c r="G137" s="32"/>
       <c r="H137" s="48" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="I137" s="43" t="s">
         <v>1185</v>
@@ -30696,7 +30696,7 @@
       </c>
       <c r="G139" s="32"/>
       <c r="H139" s="48" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="I139" s="43" t="s">
         <v>1199</v>
@@ -32746,7 +32746,7 @@
         <v>176</v>
       </c>
       <c r="N167" s="136" t="s">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="O167" s="136"/>
       <c r="P167" s="155" t="s">
@@ -32756,7 +32756,7 @@
         <v>1419</v>
       </c>
       <c r="R167" s="39" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="S167" s="21" t="s">
         <v>41</v>
@@ -34864,7 +34864,7 @@
         <v>1654</v>
       </c>
       <c r="M196" s="95" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="N196" s="54" t="s">
         <v>1655</v>
@@ -37157,10 +37157,10 @@
       <c r="K227" s="82"/>
       <c r="L227" s="22"/>
       <c r="M227" s="53" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N227" s="54" t="s">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="O227" s="458"/>
       <c r="P227" s="318" t="s">
@@ -37238,10 +37238,10 @@
       <c r="K228" s="22"/>
       <c r="L228" s="22"/>
       <c r="M228" s="53" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N228" s="54" t="s">
-        <v>4002</v>
+        <v>4018</v>
       </c>
       <c r="O228" s="54"/>
       <c r="P228" s="318" t="s">
@@ -37994,7 +37994,7 @@
         <v>2007</v>
       </c>
       <c r="M238" s="95" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="N238" s="38" t="s">
         <v>1655</v>
@@ -38081,10 +38081,10 @@
         <v>2018</v>
       </c>
       <c r="M239" s="127" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="N239" s="54" t="s">
-        <v>3953</v>
+        <v>4019</v>
       </c>
       <c r="O239" s="54"/>
       <c r="P239" s="25" t="s">
@@ -38239,7 +38239,7 @@
       <c r="K241" s="82"/>
       <c r="L241" s="82"/>
       <c r="M241" s="53" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N241" s="54" t="s">
         <v>2032</v>
@@ -38311,7 +38311,7 @@
         <v>2036</v>
       </c>
       <c r="H242" s="48" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="I242" s="43" t="s">
         <v>2037</v>
@@ -38320,7 +38320,7 @@
       <c r="K242" s="22"/>
       <c r="L242" s="22"/>
       <c r="M242" s="53" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N242" s="54" t="s">
         <v>2038</v>
@@ -38697,7 +38697,7 @@
         <v>3774</v>
       </c>
       <c r="H247" s="423" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="I247" s="421" t="s">
         <v>1911</v>
@@ -38706,10 +38706,10 @@
       <c r="K247" s="230"/>
       <c r="L247" s="230"/>
       <c r="M247" s="421" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N247" s="460" t="s">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="O247" s="459"/>
       <c r="P247" s="318" t="s">
@@ -38775,7 +38775,7 @@
       <c r="F248" s="230"/>
       <c r="G248" s="423"/>
       <c r="H248" s="423" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="I248" s="421" t="s">
         <v>2031</v>
@@ -38784,10 +38784,10 @@
       <c r="K248" s="230"/>
       <c r="L248" s="230"/>
       <c r="M248" s="421" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N248" s="459" t="s">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="O248" s="459"/>
       <c r="P248" s="318" t="s">
@@ -40001,7 +40001,7 @@
     </row>
     <row r="265" spans="1:43" ht="15.75" customHeight="1">
       <c r="A265" s="14" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="B265" s="14" t="s">
         <v>2209</v>
@@ -40027,10 +40027,10 @@
       <c r="K265" s="22"/>
       <c r="L265" s="22"/>
       <c r="M265" s="53" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N265" s="54" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="O265" s="54"/>
       <c r="P265" s="318" t="s">
@@ -40394,10 +40394,10 @@
       <c r="K270" s="22"/>
       <c r="L270" s="22"/>
       <c r="M270" s="320" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N270" s="73" t="s">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="O270" s="73"/>
       <c r="P270" s="318" t="s">
@@ -40422,7 +40422,7 @@
       <c r="W270" s="29"/>
       <c r="X270" s="29"/>
       <c r="Y270" s="30" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="Z270" s="30"/>
       <c r="AA270" s="30"/>
@@ -40648,7 +40648,7 @@
     </row>
     <row r="274" spans="1:43" ht="15.75" customHeight="1">
       <c r="A274" s="14" t="s">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="B274" s="14" t="s">
         <v>434</v>
@@ -40895,10 +40895,10 @@
       <c r="K277" s="82"/>
       <c r="L277" s="22"/>
       <c r="M277" s="320" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N277" s="38" t="s">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="O277" s="38"/>
       <c r="P277" s="318" t="s">
@@ -41266,10 +41266,10 @@
       <c r="K282" s="22"/>
       <c r="L282" s="22"/>
       <c r="M282" s="320" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N282" s="38" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="O282" s="322"/>
       <c r="P282" s="126" t="s">
@@ -41294,7 +41294,7 @@
       <c r="W282" s="29"/>
       <c r="X282" s="29"/>
       <c r="Y282" s="30" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="Z282" s="30"/>
       <c r="AA282" s="30"/>
@@ -41358,7 +41358,7 @@
         <v>1905</v>
       </c>
       <c r="R283" s="32" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="S283" s="32" t="s">
         <v>41</v>
@@ -41554,10 +41554,10 @@
       <c r="K286" s="22"/>
       <c r="L286" s="22"/>
       <c r="M286" s="454" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N286" s="89" t="s">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="O286" s="89"/>
       <c r="P286" s="126" t="s">
@@ -41842,7 +41842,7 @@
       <c r="K290" s="82"/>
       <c r="L290" s="22"/>
       <c r="M290" s="320" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N290" s="54" t="s">
         <v>2380</v>
@@ -42134,10 +42134,10 @@
       <c r="K294" s="82"/>
       <c r="L294" s="82"/>
       <c r="M294" s="33" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="N294" s="89" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="O294" s="457"/>
       <c r="P294" s="114" t="s">
@@ -42162,7 +42162,7 @@
       <c r="W294" s="29"/>
       <c r="X294" s="29"/>
       <c r="Y294" s="30" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="Z294" s="30"/>
       <c r="AA294" s="30"/>
@@ -42509,10 +42509,10 @@
       <c r="K299" s="22"/>
       <c r="L299" s="22"/>
       <c r="M299" s="320" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="N299" s="89" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="O299" s="89"/>
       <c r="P299" s="114" t="s">
@@ -42670,7 +42670,7 @@
         <v>2462</v>
       </c>
       <c r="N301" s="38" t="s">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="O301" s="38"/>
       <c r="P301" s="25"/>
@@ -43313,7 +43313,7 @@
       </c>
       <c r="G310" s="32"/>
       <c r="H310" s="414" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="I310" s="32" t="s">
         <v>2506</v>
@@ -44547,7 +44547,7 @@
         <v>2237</v>
       </c>
       <c r="Y326" s="30" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="Z326" s="30"/>
       <c r="AA326" s="30" t="s">
@@ -45438,7 +45438,7 @@
       </c>
       <c r="G338" s="48"/>
       <c r="H338" s="32" t="s">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="I338" s="187" t="s">
         <v>2767</v>
@@ -45452,7 +45452,7 @@
         <v>2769</v>
       </c>
       <c r="N338" s="38" t="s">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="O338" s="38"/>
       <c r="P338" s="25" t="s">
@@ -45462,7 +45462,7 @@
         <v>2771</v>
       </c>
       <c r="R338" s="503" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="S338" s="77" t="s">
         <v>41</v>
@@ -46037,7 +46037,7 @@
     </row>
     <row r="346" spans="1:43" ht="15.75" customHeight="1">
       <c r="A346" s="193" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="B346" s="33" t="s">
         <v>434</v>
@@ -46744,7 +46744,7 @@
         <v>434</v>
       </c>
       <c r="C355" s="250" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="D355" s="235"/>
       <c r="E355" s="58"/>
@@ -47237,7 +47237,7 @@
         <v>2965</v>
       </c>
       <c r="N361" s="54" t="s">
-        <v>4011</v>
+        <v>4009</v>
       </c>
       <c r="O361" s="54"/>
       <c r="P361" s="25" t="s">
@@ -47322,7 +47322,7 @@
         <v>1905</v>
       </c>
       <c r="R362" s="77" t="s">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="S362" s="77" t="s">
         <v>41</v>
@@ -47837,7 +47837,7 @@
       </c>
       <c r="G369" s="396"/>
       <c r="H369" s="411" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="I369" s="397" t="s">
         <v>2506</v>
@@ -47849,7 +47849,7 @@
         <v>3023</v>
       </c>
       <c r="N369" s="401" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="O369" s="401" t="s">
         <v>38</v>
@@ -47883,10 +47883,10 @@
         <v>3028</v>
       </c>
       <c r="AB369" s="409" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="AC369" s="413" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="AD369" s="405"/>
       <c r="AE369" s="32"/>
@@ -48840,7 +48840,7 @@
     </row>
     <row r="382" spans="1:43" ht="15.75" customHeight="1">
       <c r="A382" s="373" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="B382" s="366" t="s">
         <v>434</v>
@@ -48849,11 +48849,11 @@
       <c r="D382" s="375"/>
       <c r="E382" s="376"/>
       <c r="F382" s="436" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="G382" s="377"/>
       <c r="H382" s="378" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="I382" s="378" t="s">
         <v>2506</v>
@@ -48865,7 +48865,7 @@
         <v>3131</v>
       </c>
       <c r="N382" s="370" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="O382" s="370"/>
       <c r="P382" s="371"/>
@@ -48884,10 +48884,10 @@
         <v>2237</v>
       </c>
       <c r="Y382" s="385" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="Z382" s="390" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="AA382" s="386"/>
       <c r="AB382" s="501"/>
@@ -48909,7 +48909,7 @@
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
       <c r="A383" s="281" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>434</v>
@@ -49834,7 +49834,7 @@
         <v>3210</v>
       </c>
       <c r="M395" s="95" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="N395" s="54" t="s">
         <v>3211</v>
@@ -51769,7 +51769,7 @@
       </c>
       <c r="G421" s="186"/>
       <c r="H421" s="206" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="I421" s="32" t="s">
         <v>2506</v>
@@ -51931,7 +51931,7 @@
       </c>
       <c r="G423" s="186"/>
       <c r="H423" s="206" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="I423" s="192" t="s">
         <v>2506</v>
@@ -51976,10 +51976,10 @@
       </c>
       <c r="Z423" s="30"/>
       <c r="AA423" s="30" t="s">
+        <v>3982</v>
+      </c>
+      <c r="AB423" s="41" t="s">
         <v>3983</v>
-      </c>
-      <c r="AB423" s="41" t="s">
-        <v>3984</v>
       </c>
       <c r="AC423" s="32"/>
       <c r="AD423" s="32"/>
@@ -52456,7 +52456,7 @@
       </c>
       <c r="O430" s="38"/>
       <c r="P430" s="317" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="Q430" s="26"/>
       <c r="R430" s="117" t="s">
@@ -55211,7 +55211,7 @@
         <v>3671</v>
       </c>
       <c r="R467" s="94" t="s">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="S467" s="77" t="s">
         <v>41</v>
@@ -55422,7 +55422,7 @@
         <v>2480</v>
       </c>
       <c r="N470" s="54" t="s">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="O470" s="54"/>
       <c r="P470" s="74" t="s">
@@ -55432,7 +55432,7 @@
         <v>3693</v>
       </c>
       <c r="R470" s="48" t="s">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="S470" s="77" t="s">
         <v>41</v>
@@ -65211,7 +65211,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{C9A2F3C2-6F06-AA4A-9798-78AFB3BE90F6}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{6BD8D08E-3F1D-FB43-8280-9052F8FDD6BE}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE65A8B2-1D11-5E47-9C02-C45B3F707294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2422D3-46C8-1B4E-B5CF-AF52EF73A4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3580" yWindow="-20960" windowWidth="37740" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4240" yWindow="-14960" windowWidth="37740" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -638,7 +638,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7045" uniqueCount="4020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7045" uniqueCount="4018">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17371,32 +17371,6 @@
     <t>[Médailles offertes par Mr du Bois-Guérin au roi, au dauphin et à Monsieur : Louis XIV foulant la Fronde]*</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">médaille ; piédestal ; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Comic Sans MS"/>
-        <family val="4"/>
-      </rPr>
-      <t xml:space="preserve">Hérésie (personnification) SUPPRIMER </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Comic Sans MS"/>
-        <family val="4"/>
-      </rPr>
-      <t>; cuirasse</t>
-    </r>
-  </si>
-  <si>
     <t>https://www.persee.fr/doc/bsnaf_0081-1181_2012_num_2006_1_10985</t>
   </si>
   <si>
@@ -17433,39 +17407,6 @@
     <t>1678-06e_390b</t>
   </si>
   <si>
-    <t>lentille ; camera obscura ; schéma scientifique</t>
-  </si>
-  <si>
-    <t>télescope ; schéma scientifique</t>
-  </si>
-  <si>
-    <t>lentille ; église ; fleuve, rivière, ruisseau ; montagne ; schéma scientifique</t>
-  </si>
-  <si>
-    <t>lunette d'optique ; schéma scientifique</t>
-  </si>
-  <si>
-    <t>lentille ; schéma scientifique</t>
-  </si>
-  <si>
-    <t>lunette d'optique ; schéma scientifique ; montagne ; navire</t>
-  </si>
-  <si>
-    <t>binocle ; armoiries ; schéma scientifique</t>
-  </si>
-  <si>
-    <t>schéma scientifique ; binocle</t>
-  </si>
-  <si>
-    <t>schéma scientifique</t>
-  </si>
-  <si>
-    <t>cadran ou horloge ; schéma scientifique</t>
-  </si>
-  <si>
-    <t>système d'orientation spatiale ; église ; schéma scientifique ;</t>
-  </si>
-  <si>
     <t>planche scientifique ; planche de texte (types de représentation)</t>
   </si>
   <si>
@@ -17484,13 +17425,43 @@
     <t>planche de texte</t>
   </si>
   <si>
-    <t>schema</t>
-  </si>
-  <si>
     <t>camera obscura ;  lentille</t>
   </si>
   <si>
     <t>anémoscope ; armoiries ; couronne</t>
+  </si>
+  <si>
+    <t>1684-06a_140</t>
+  </si>
+  <si>
+    <t>lentille ; camera obscura ;</t>
+  </si>
+  <si>
+    <t>télescope ;</t>
+  </si>
+  <si>
+    <t>lentille ; église ; fleuve, rivière, ruisseau ; montagne ;</t>
+  </si>
+  <si>
+    <t>lunette d'optique ;</t>
+  </si>
+  <si>
+    <t>lentille ;</t>
+  </si>
+  <si>
+    <t>binocle ; armoiries ;</t>
+  </si>
+  <si>
+    <t>écriture codée; figure géométrique ;</t>
+  </si>
+  <si>
+    <t>cadran ou horloge ;</t>
+  </si>
+  <si>
+    <t>système d'orientation spatiale ; église ;</t>
+  </si>
+  <si>
+    <t>médaille ; piédestal ; cuirasse</t>
   </si>
 </sst>
 </file>
@@ -18511,15 +18482,13 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Comic Sans MS"/>
-      <family val="4"/>
+      <sz val="13.5"/>
+      <color rgb="FF000000"/>
+      <name val="Garamond"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="13.5"/>
+      <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Garamond"/>
       <family val="1"/>
@@ -18827,7 +18796,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="504">
+  <cellXfs count="505">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -20263,6 +20232,7 @@
     <xf numFmtId="0" fontId="41" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="144" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -22388,7 +22358,7 @@
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
       <c r="A25" s="277" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>247</v>
@@ -22457,7 +22427,7 @@
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
       <c r="A26" s="291" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>43</v>
@@ -22528,7 +22498,7 @@
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
       <c r="A27" s="277" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="B27" s="32" t="s">
         <v>247</v>
@@ -24232,7 +24202,7 @@
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>434</v>
@@ -24303,7 +24273,7 @@
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>444</v>
@@ -28008,7 +27978,7 @@
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
       <c r="A102" s="277" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>890</v>
@@ -28870,7 +28840,7 @@
     </row>
     <row r="114" spans="1:43" ht="15.75" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="B114" s="32" t="s">
         <v>434</v>
@@ -29444,7 +29414,7 @@
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
       <c r="A122" s="278" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="B122" s="51" t="s">
         <v>43</v>
@@ -32746,7 +32716,7 @@
         <v>176</v>
       </c>
       <c r="N167" s="136" t="s">
-        <v>4012</v>
+        <v>4000</v>
       </c>
       <c r="O167" s="136"/>
       <c r="P167" s="155" t="s">
@@ -32756,7 +32726,7 @@
         <v>1419</v>
       </c>
       <c r="R167" s="39" t="s">
-        <v>4013</v>
+        <v>4001</v>
       </c>
       <c r="S167" s="21" t="s">
         <v>41</v>
@@ -37160,7 +37130,7 @@
         <v>3958</v>
       </c>
       <c r="N227" s="54" t="s">
-        <v>4000</v>
+        <v>4008</v>
       </c>
       <c r="O227" s="458"/>
       <c r="P227" s="318" t="s">
@@ -37241,7 +37211,7 @@
         <v>3958</v>
       </c>
       <c r="N228" s="54" t="s">
-        <v>4018</v>
+        <v>4005</v>
       </c>
       <c r="O228" s="54"/>
       <c r="P228" s="318" t="s">
@@ -38084,7 +38054,7 @@
         <v>3953</v>
       </c>
       <c r="N239" s="54" t="s">
-        <v>4019</v>
+        <v>4006</v>
       </c>
       <c r="O239" s="54"/>
       <c r="P239" s="25" t="s">
@@ -38709,7 +38679,7 @@
         <v>3958</v>
       </c>
       <c r="N247" s="460" t="s">
-        <v>4001</v>
+        <v>4009</v>
       </c>
       <c r="O247" s="459"/>
       <c r="P247" s="318" t="s">
@@ -38786,8 +38756,8 @@
       <c r="M248" s="421" t="s">
         <v>3958</v>
       </c>
-      <c r="N248" s="459" t="s">
-        <v>4001</v>
+      <c r="N248" s="460" t="s">
+        <v>4009</v>
       </c>
       <c r="O248" s="459"/>
       <c r="P248" s="318" t="s">
@@ -40001,7 +39971,7 @@
     </row>
     <row r="265" spans="1:43" ht="15.75" customHeight="1">
       <c r="A265" s="14" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="B265" s="14" t="s">
         <v>2209</v>
@@ -40030,7 +40000,7 @@
         <v>3958</v>
       </c>
       <c r="N265" s="54" t="s">
-        <v>4002</v>
+        <v>4010</v>
       </c>
       <c r="O265" s="54"/>
       <c r="P265" s="318" t="s">
@@ -40397,7 +40367,7 @@
         <v>3958</v>
       </c>
       <c r="N270" s="73" t="s">
-        <v>4003</v>
+        <v>4011</v>
       </c>
       <c r="O270" s="73"/>
       <c r="P270" s="318" t="s">
@@ -40648,7 +40618,7 @@
     </row>
     <row r="274" spans="1:43" ht="15.75" customHeight="1">
       <c r="A274" s="14" t="s">
-        <v>4017</v>
+        <v>4007</v>
       </c>
       <c r="B274" s="14" t="s">
         <v>434</v>
@@ -40898,7 +40868,7 @@
         <v>3958</v>
       </c>
       <c r="N277" s="38" t="s">
-        <v>4004</v>
+        <v>4012</v>
       </c>
       <c r="O277" s="38"/>
       <c r="P277" s="318" t="s">
@@ -41268,8 +41238,8 @@
       <c r="M282" s="320" t="s">
         <v>3958</v>
       </c>
-      <c r="N282" s="38" t="s">
-        <v>4005</v>
+      <c r="N282" s="504" t="s">
+        <v>2457</v>
       </c>
       <c r="O282" s="322"/>
       <c r="P282" s="126" t="s">
@@ -41358,7 +41328,7 @@
         <v>1905</v>
       </c>
       <c r="R283" s="32" t="s">
-        <v>4013</v>
+        <v>4001</v>
       </c>
       <c r="S283" s="32" t="s">
         <v>41</v>
@@ -41557,7 +41527,7 @@
         <v>3958</v>
       </c>
       <c r="N286" s="89" t="s">
-        <v>4003</v>
+        <v>4011</v>
       </c>
       <c r="O286" s="89"/>
       <c r="P286" s="126" t="s">
@@ -42137,7 +42107,7 @@
         <v>3959</v>
       </c>
       <c r="N294" s="89" t="s">
-        <v>4006</v>
+        <v>4013</v>
       </c>
       <c r="O294" s="457"/>
       <c r="P294" s="114" t="s">
@@ -42512,7 +42482,7 @@
         <v>3958</v>
       </c>
       <c r="N299" s="89" t="s">
-        <v>4007</v>
+        <v>2038</v>
       </c>
       <c r="O299" s="89"/>
       <c r="P299" s="114" t="s">
@@ -42670,7 +42640,7 @@
         <v>2462</v>
       </c>
       <c r="N301" s="38" t="s">
-        <v>4008</v>
+        <v>4014</v>
       </c>
       <c r="O301" s="38"/>
       <c r="P301" s="25"/>
@@ -45438,7 +45408,7 @@
       </c>
       <c r="G338" s="48"/>
       <c r="H338" s="32" t="s">
-        <v>4014</v>
+        <v>4002</v>
       </c>
       <c r="I338" s="187" t="s">
         <v>2767</v>
@@ -45452,7 +45422,7 @@
         <v>2769</v>
       </c>
       <c r="N338" s="38" t="s">
-        <v>4015</v>
+        <v>4003</v>
       </c>
       <c r="O338" s="38"/>
       <c r="P338" s="25" t="s">
@@ -45462,7 +45432,7 @@
         <v>2771</v>
       </c>
       <c r="R338" s="503" t="s">
-        <v>4013</v>
+        <v>4001</v>
       </c>
       <c r="S338" s="77" t="s">
         <v>41</v>
@@ -46037,7 +46007,7 @@
     </row>
     <row r="346" spans="1:43" ht="15.75" customHeight="1">
       <c r="A346" s="193" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="B346" s="33" t="s">
         <v>434</v>
@@ -47237,7 +47207,7 @@
         <v>2965</v>
       </c>
       <c r="N361" s="54" t="s">
-        <v>4009</v>
+        <v>4015</v>
       </c>
       <c r="O361" s="54"/>
       <c r="P361" s="25" t="s">
@@ -47322,7 +47292,7 @@
         <v>1905</v>
       </c>
       <c r="R362" s="77" t="s">
-        <v>4011</v>
+        <v>3999</v>
       </c>
       <c r="S362" s="77" t="s">
         <v>41</v>
@@ -47849,7 +47819,7 @@
         <v>3023</v>
       </c>
       <c r="N369" s="401" t="s">
-        <v>3987</v>
+        <v>4017</v>
       </c>
       <c r="O369" s="401" t="s">
         <v>38</v>
@@ -47886,7 +47856,7 @@
         <v>3985</v>
       </c>
       <c r="AC369" s="413" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="AD369" s="405"/>
       <c r="AE369" s="32"/>
@@ -48909,7 +48879,7 @@
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
       <c r="A383" s="281" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>434</v>
@@ -55211,7 +55181,7 @@
         <v>3671</v>
       </c>
       <c r="R467" s="94" t="s">
-        <v>4016</v>
+        <v>4004</v>
       </c>
       <c r="S467" s="77" t="s">
         <v>41</v>
@@ -55422,7 +55392,7 @@
         <v>2480</v>
       </c>
       <c r="N470" s="54" t="s">
-        <v>4010</v>
+        <v>4016</v>
       </c>
       <c r="O470" s="54"/>
       <c r="P470" s="74" t="s">
@@ -55432,7 +55402,7 @@
         <v>3693</v>
       </c>
       <c r="R470" s="48" t="s">
-        <v>4011</v>
+        <v>3999</v>
       </c>
       <c r="S470" s="77" t="s">
         <v>41</v>
@@ -65211,7 +65181,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{6BD8D08E-3F1D-FB43-8280-9052F8FDD6BE}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{39807D6A-D476-4A43-9E32-DE10B04B2CFA}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>
@@ -65682,332 +65652,332 @@
     <hyperlink ref="F270" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
     <hyperlink ref="F272" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
     <hyperlink ref="F273" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="F274" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="AB276" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="F278" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="AB278" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="F280" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="F281" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="F282" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="C283" r:id="rId475" location="MG-1684-10_128" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="F283" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="F284" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="F285" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="F288" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="F289" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="V289" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="F291" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="F292" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="AC292" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="F293" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="Y293" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="F294" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="C295" r:id="rId488" location="MG-1685-07_263" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="F295" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="V295" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="F296" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="AB296" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="F297" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="F298" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="F299" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="F300" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="F301" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="F302" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="F305" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="C306" r:id="rId500" location="MG-1686-02b_159" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="F306" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="AB306" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="F307" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="C308" r:id="rId504" location="MG-1686-04_215" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="F308" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="C309" r:id="rId506" location="MG-1686-05_243" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="F309" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="Y309" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="C310" r:id="rId509" location="MG-1686-06_080" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="F310" r:id="rId510" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="Y310" r:id="rId511" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="AB310" r:id="rId512" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="F311" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="F312" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
-    <hyperlink ref="F313" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
-    <hyperlink ref="AB313" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
-    <hyperlink ref="F315" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="F316" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="F317" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="F318" r:id="rId520" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="AB318" r:id="rId521" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="D319" r:id="rId522" location="MG-1687-01a_158" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="F319" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="C320" r:id="rId524" location="MG-1687-02_001" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="C321" r:id="rId525" location="MG-1687-02_073" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="F322" r:id="rId526" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="F323" r:id="rId527" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="F324" r:id="rId528" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
-    <hyperlink ref="F325" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
-    <hyperlink ref="F326" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
-    <hyperlink ref="AB326" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
-    <hyperlink ref="F327" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
-    <hyperlink ref="F328" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
-    <hyperlink ref="AB328" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
-    <hyperlink ref="F329" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
-    <hyperlink ref="V329" r:id="rId536" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
-    <hyperlink ref="AB329" r:id="rId537" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
-    <hyperlink ref="F330" r:id="rId538" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
-    <hyperlink ref="C331" r:id="rId539" location="MG-1687-11_244" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
-    <hyperlink ref="F331" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
-    <hyperlink ref="F332" r:id="rId541" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
-    <hyperlink ref="C334" r:id="rId542" location="MG-1688-02_146" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
-    <hyperlink ref="F334" r:id="rId543" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
-    <hyperlink ref="F335" r:id="rId544" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
-    <hyperlink ref="AB335" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
-    <hyperlink ref="F336" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
-    <hyperlink ref="AB336" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
-    <hyperlink ref="F337" r:id="rId548" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
-    <hyperlink ref="C339" r:id="rId549" location="MG-1688-06a_189" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
-    <hyperlink ref="F339" r:id="rId550" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
-    <hyperlink ref="C340" r:id="rId551" location="MG-1688-07_301" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
-    <hyperlink ref="F340" r:id="rId552" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
-    <hyperlink ref="V340" r:id="rId553" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
-    <hyperlink ref="AB340" r:id="rId554" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
-    <hyperlink ref="C341" r:id="rId555" location="MG-1688-08_246" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
-    <hyperlink ref="F341" r:id="rId556" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
-    <hyperlink ref="C342" r:id="rId557" location="MG-1688-09a_237" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
-    <hyperlink ref="F342" r:id="rId558" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
-    <hyperlink ref="AB342" r:id="rId559" location="infos-principales" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
-    <hyperlink ref="F343" r:id="rId560" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
-    <hyperlink ref="AB343" r:id="rId561" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
-    <hyperlink ref="C344" r:id="rId562" location="MG-1688-11a_283" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
-    <hyperlink ref="F344" r:id="rId563" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
-    <hyperlink ref="C345" r:id="rId564" location="MG-1688-12a_131" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
-    <hyperlink ref="F345" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
-    <hyperlink ref="F346" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
-    <hyperlink ref="F347" r:id="rId567" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
-    <hyperlink ref="F348" r:id="rId568" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
-    <hyperlink ref="AB348" r:id="rId569" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
-    <hyperlink ref="F349" r:id="rId570" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
-    <hyperlink ref="F350" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
-    <hyperlink ref="V350" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
-    <hyperlink ref="X350" r:id="rId573" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
-    <hyperlink ref="F351" r:id="rId574" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
-    <hyperlink ref="F352" r:id="rId575" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
-    <hyperlink ref="AB352" r:id="rId576" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
-    <hyperlink ref="F353" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
-    <hyperlink ref="F354" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
-    <hyperlink ref="Y354" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
-    <hyperlink ref="AB354" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
-    <hyperlink ref="F355" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
-    <hyperlink ref="F356" r:id="rId582" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
-    <hyperlink ref="C357" r:id="rId583" location="MG-1689-12_227" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
-    <hyperlink ref="F357" r:id="rId584" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
-    <hyperlink ref="F358" r:id="rId585" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
-    <hyperlink ref="AB358" r:id="rId586" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
-    <hyperlink ref="C359" r:id="rId587" location="MG-1690-02_151" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
-    <hyperlink ref="F359" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
-    <hyperlink ref="F360" r:id="rId589" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
-    <hyperlink ref="F362" r:id="rId590" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
-    <hyperlink ref="AD362" r:id="rId591" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
-    <hyperlink ref="F363" r:id="rId592" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
-    <hyperlink ref="F364" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
-    <hyperlink ref="F365" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
-    <hyperlink ref="AB365" r:id="rId595" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
-    <hyperlink ref="C366" r:id="rId596" location="MG-1690-09_187" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
-    <hyperlink ref="F366" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
-    <hyperlink ref="F367" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
-    <hyperlink ref="F368" r:id="rId599" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
-    <hyperlink ref="Y368" r:id="rId600" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
-    <hyperlink ref="C369" r:id="rId601" location="MG-1691-01_227" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
-    <hyperlink ref="F369" r:id="rId602" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
-    <hyperlink ref="AB369" r:id="rId603" display="https://gallica.bnf.fr/ark:/12148 ; btv1b550039004 ; https://data.bnf.fr/fr/12356952/cornelis_vermeulen/ " xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
-    <hyperlink ref="C370" r:id="rId604" location="MG-1691-02_177" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
-    <hyperlink ref="F370" r:id="rId605" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
-    <hyperlink ref="AC370" r:id="rId606" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
-    <hyperlink ref="C371" r:id="rId607" location="MG-1691-03_131" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
-    <hyperlink ref="D371" r:id="rId608" location="MG-1691-02_177" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
-    <hyperlink ref="F371" r:id="rId609" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
-    <hyperlink ref="C372" r:id="rId610" location="MG-1691-04_162" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
-    <hyperlink ref="F372" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
-    <hyperlink ref="F373" r:id="rId612" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
-    <hyperlink ref="C374" r:id="rId613" location="MG-1691-06_208" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
-    <hyperlink ref="F374" r:id="rId614" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
-    <hyperlink ref="C375" r:id="rId615" location="MG-1691-07_181" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
-    <hyperlink ref="F375" r:id="rId616" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
-    <hyperlink ref="F377" r:id="rId617" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
-    <hyperlink ref="F378" r:id="rId618" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
-    <hyperlink ref="F379" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
-    <hyperlink ref="Y379" r:id="rId620" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
-    <hyperlink ref="C380" r:id="rId621" location="MG-1691-11_156" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
-    <hyperlink ref="F380" r:id="rId622" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
-    <hyperlink ref="Y380" r:id="rId623" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
-    <hyperlink ref="F381" r:id="rId624" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
-    <hyperlink ref="AC381" r:id="rId625" location="v=onepage&amp;q=Terraque%2C%20marique%20m%C3%A9daille&amp;f=false" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
-    <hyperlink ref="C383" r:id="rId626" location="MG-1692-01a_288" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
-    <hyperlink ref="F383" r:id="rId627" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
-    <hyperlink ref="C384" r:id="rId628" location="MG-1692-02a_307" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
-    <hyperlink ref="C385" r:id="rId629" location="MG-1692-02a_307" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
-    <hyperlink ref="C386" r:id="rId630" location="MG-1692-03_175" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
-    <hyperlink ref="F386" r:id="rId631" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
-    <hyperlink ref="C387" r:id="rId632" location="MG-1692-04_181" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
-    <hyperlink ref="F387" r:id="rId633" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
-    <hyperlink ref="C388" r:id="rId634" location="MG-1692-05_217" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
-    <hyperlink ref="F388" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
-    <hyperlink ref="AB388" r:id="rId636" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
-    <hyperlink ref="F390" r:id="rId637" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
-    <hyperlink ref="F391" r:id="rId638" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
-    <hyperlink ref="F392" r:id="rId639" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
-    <hyperlink ref="F393" r:id="rId640" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
-    <hyperlink ref="F394" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
-    <hyperlink ref="F395" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
-    <hyperlink ref="F396" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
-    <hyperlink ref="Y396" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
-    <hyperlink ref="AB396" r:id="rId645" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
-    <hyperlink ref="F397" r:id="rId646" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
-    <hyperlink ref="AB397" r:id="rId647" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
-    <hyperlink ref="AC397" r:id="rId648" location="v=onepage&amp;q=Providenter.%20Philisburgum%20expugnatum&amp;f=false" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
-    <hyperlink ref="F398" r:id="rId649" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
-    <hyperlink ref="F399" r:id="rId650" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
-    <hyperlink ref="F400" r:id="rId651" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
-    <hyperlink ref="AB400" r:id="rId652" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
-    <hyperlink ref="F401" r:id="rId653" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
-    <hyperlink ref="F402" r:id="rId654" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
-    <hyperlink ref="AB402" r:id="rId655" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
-    <hyperlink ref="F403" r:id="rId656" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
-    <hyperlink ref="Y403" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
-    <hyperlink ref="F404" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
-    <hyperlink ref="AB404" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
-    <hyperlink ref="AC404" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
-    <hyperlink ref="F405" r:id="rId661" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
-    <hyperlink ref="AB405" r:id="rId662" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
-    <hyperlink ref="AC405" r:id="rId663" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
-    <hyperlink ref="F406" r:id="rId664" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
-    <hyperlink ref="AB406" r:id="rId665" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
-    <hyperlink ref="F407" r:id="rId666" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
-    <hyperlink ref="AB407" r:id="rId667" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
-    <hyperlink ref="F408" r:id="rId668" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
-    <hyperlink ref="F409" r:id="rId669" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
-    <hyperlink ref="C410" r:id="rId670" location="MG-1694-04_112" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
-    <hyperlink ref="F410" r:id="rId671" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
-    <hyperlink ref="F411" r:id="rId672" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
-    <hyperlink ref="F412" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
-    <hyperlink ref="F413" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
-    <hyperlink ref="AB413" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
-    <hyperlink ref="F414" r:id="rId676" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
-    <hyperlink ref="C415" r:id="rId677" location="MG-1694-08_227" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
-    <hyperlink ref="F415" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
-    <hyperlink ref="F416" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
-    <hyperlink ref="AB416" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
-    <hyperlink ref="F417" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
-    <hyperlink ref="F418" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
-    <hyperlink ref="F419" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
-    <hyperlink ref="F420" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
-    <hyperlink ref="F421" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
-    <hyperlink ref="AB421" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
-    <hyperlink ref="F422" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
-    <hyperlink ref="AB422" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
-    <hyperlink ref="F423" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
-    <hyperlink ref="F424" r:id="rId690" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
-    <hyperlink ref="C425" r:id="rId691" location="MG-1695-05_244" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
-    <hyperlink ref="F425" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
-    <hyperlink ref="F426" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
-    <hyperlink ref="F427" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
-    <hyperlink ref="F428" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
-    <hyperlink ref="X428" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
-    <hyperlink ref="F429" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
-    <hyperlink ref="X429" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
-    <hyperlink ref="F430" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
-    <hyperlink ref="F431" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
-    <hyperlink ref="F432" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
-    <hyperlink ref="F433" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
-    <hyperlink ref="X433" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
-    <hyperlink ref="F434" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
-    <hyperlink ref="X434" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
-    <hyperlink ref="F435" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
-    <hyperlink ref="F436" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
-    <hyperlink ref="F437" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
-    <hyperlink ref="X437" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
-    <hyperlink ref="F438" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
-    <hyperlink ref="X438" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
-    <hyperlink ref="F439" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
-    <hyperlink ref="X440" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
-    <hyperlink ref="F441" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
-    <hyperlink ref="X441" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
-    <hyperlink ref="AB441" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
-    <hyperlink ref="F442" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
-    <hyperlink ref="F443" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
-    <hyperlink ref="X443" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
-    <hyperlink ref="F444" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
-    <hyperlink ref="F445" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
-    <hyperlink ref="X445" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
-    <hyperlink ref="F446" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
-    <hyperlink ref="X446" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
-    <hyperlink ref="F447" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
-    <hyperlink ref="X447" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
-    <hyperlink ref="F448" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
-    <hyperlink ref="F449" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
-    <hyperlink ref="X449" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
-    <hyperlink ref="F450" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
-    <hyperlink ref="X450" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
-    <hyperlink ref="F451" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
-    <hyperlink ref="X451" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
-    <hyperlink ref="F452" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
-    <hyperlink ref="F453" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
-    <hyperlink ref="F454" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
-    <hyperlink ref="X454" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
-    <hyperlink ref="F455" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
-    <hyperlink ref="X455" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
-    <hyperlink ref="AB455" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
-    <hyperlink ref="F456" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
-    <hyperlink ref="X456" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
-    <hyperlink ref="F457" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
-    <hyperlink ref="X457" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
-    <hyperlink ref="F458" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
-    <hyperlink ref="X458" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
-    <hyperlink ref="F459" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
-    <hyperlink ref="AC459" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
-    <hyperlink ref="F460" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
-    <hyperlink ref="X460" r:id="rId750" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
-    <hyperlink ref="C461" r:id="rId751" location="MG-1701-04B_003" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
-    <hyperlink ref="F461" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
-    <hyperlink ref="X461" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
-    <hyperlink ref="F462" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
-    <hyperlink ref="V462" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
-    <hyperlink ref="X462" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
-    <hyperlink ref="F463" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
-    <hyperlink ref="X463" r:id="rId758" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
-    <hyperlink ref="C465" r:id="rId759" location="MG-1702-10_63" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
-    <hyperlink ref="F465" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
-    <hyperlink ref="F466" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
-    <hyperlink ref="X466" r:id="rId762" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
-    <hyperlink ref="C467" r:id="rId763" location="MG-1703-02_71" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
-    <hyperlink ref="D467" r:id="rId764" location="MG-1703-03_363" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
-    <hyperlink ref="F467" r:id="rId765" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
-    <hyperlink ref="G467" r:id="rId766" location="MG-1703-02_71" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
-    <hyperlink ref="F468" r:id="rId767" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
-    <hyperlink ref="X468" r:id="rId768" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
-    <hyperlink ref="AB468" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
-    <hyperlink ref="F469" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
-    <hyperlink ref="F470" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
-    <hyperlink ref="F471" r:id="rId772" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
-    <hyperlink ref="F472" r:id="rId773" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
-    <hyperlink ref="F473" r:id="rId774" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
-    <hyperlink ref="F474" r:id="rId775" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
-    <hyperlink ref="F475" r:id="rId776" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
-    <hyperlink ref="X475" r:id="rId777" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
-    <hyperlink ref="C476" r:id="rId778" location="MG-1707-01_162" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
-    <hyperlink ref="F476" r:id="rId779" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
-    <hyperlink ref="X476" r:id="rId780" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
-    <hyperlink ref="AB476" r:id="rId781" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
-    <hyperlink ref="F477" r:id="rId782" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
-    <hyperlink ref="X477" r:id="rId783" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
-    <hyperlink ref="AB477" r:id="rId784" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
-    <hyperlink ref="F478" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
-    <hyperlink ref="X478" r:id="rId786" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
-    <hyperlink ref="C479" r:id="rId787" location="MG-1709-03_125" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
-    <hyperlink ref="F479" r:id="rId788" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
-    <hyperlink ref="F480" r:id="rId789" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
-    <hyperlink ref="Y247" r:id="rId790" display="https://gallica.bnf.fr/ark:/12148/bpt6k56069895" xr:uid="{406C8F90-712D-EA4E-983E-641EE322383B}"/>
-    <hyperlink ref="F389" r:id="rId791" display="https://gallica.bnf.fr/ark:/12148/bpt6k6274143z/f227.item" xr:uid="{E92130F0-40E3-964F-9C82-6A4A8E98FE4A}"/>
-    <hyperlink ref="F382" r:id="rId792" xr:uid="{CB05E3EA-1CBE-F14B-8929-CCBCA00FE15C}"/>
-    <hyperlink ref="AC369" r:id="rId793" xr:uid="{6661D188-986C-EA4F-9D9E-F3E7E746DD57}"/>
+    <hyperlink ref="AB276" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="F278" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="AB278" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="F280" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="F281" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="F282" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="C283" r:id="rId474" location="MG-1684-10_128" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="F283" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="F284" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="F285" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="F288" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="F289" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="V289" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="F291" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="F292" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="AC292" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="F293" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="Y293" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="F294" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="C295" r:id="rId487" location="MG-1685-07_263" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="F295" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="V295" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="F296" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="AB296" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="F297" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="F298" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="F299" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="F300" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="F301" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="F302" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="F305" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="C306" r:id="rId499" location="MG-1686-02b_159" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="F306" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="AB306" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="F307" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="C308" r:id="rId503" location="MG-1686-04_215" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="F308" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="C309" r:id="rId505" location="MG-1686-05_243" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="F309" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="Y309" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="C310" r:id="rId508" location="MG-1686-06_080" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="F310" r:id="rId509" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="Y310" r:id="rId510" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="AB310" r:id="rId511" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="F311" r:id="rId512" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="F312" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="F313" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="AB313" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="F315" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="F316" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="F317" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="F318" r:id="rId519" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="AB318" r:id="rId520" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="D319" r:id="rId521" location="MG-1687-01a_158" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="F319" r:id="rId522" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="C320" r:id="rId523" location="MG-1687-02_001" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="C321" r:id="rId524" location="MG-1687-02_073" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="F322" r:id="rId525" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="F323" r:id="rId526" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="F324" r:id="rId527" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="F325" r:id="rId528" xr:uid="{00000000-0004-0000-0000-000013020000}"/>
+    <hyperlink ref="F326" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000014020000}"/>
+    <hyperlink ref="AB326" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
+    <hyperlink ref="F327" r:id="rId531" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
+    <hyperlink ref="F328" r:id="rId532" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="AB328" r:id="rId533" xr:uid="{00000000-0004-0000-0000-000018020000}"/>
+    <hyperlink ref="F329" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000019020000}"/>
+    <hyperlink ref="V329" r:id="rId535" xr:uid="{00000000-0004-0000-0000-00001A020000}"/>
+    <hyperlink ref="AB329" r:id="rId536" xr:uid="{00000000-0004-0000-0000-00001B020000}"/>
+    <hyperlink ref="F330" r:id="rId537" xr:uid="{00000000-0004-0000-0000-00001C020000}"/>
+    <hyperlink ref="C331" r:id="rId538" location="MG-1687-11_244" xr:uid="{00000000-0004-0000-0000-00001D020000}"/>
+    <hyperlink ref="F331" r:id="rId539" xr:uid="{00000000-0004-0000-0000-00001E020000}"/>
+    <hyperlink ref="F332" r:id="rId540" xr:uid="{00000000-0004-0000-0000-00001F020000}"/>
+    <hyperlink ref="C334" r:id="rId541" location="MG-1688-02_146" xr:uid="{00000000-0004-0000-0000-000020020000}"/>
+    <hyperlink ref="F334" r:id="rId542" xr:uid="{00000000-0004-0000-0000-000021020000}"/>
+    <hyperlink ref="F335" r:id="rId543" xr:uid="{00000000-0004-0000-0000-000022020000}"/>
+    <hyperlink ref="AB335" r:id="rId544" xr:uid="{00000000-0004-0000-0000-000023020000}"/>
+    <hyperlink ref="F336" r:id="rId545" xr:uid="{00000000-0004-0000-0000-000024020000}"/>
+    <hyperlink ref="AB336" r:id="rId546" xr:uid="{00000000-0004-0000-0000-000025020000}"/>
+    <hyperlink ref="F337" r:id="rId547" xr:uid="{00000000-0004-0000-0000-000026020000}"/>
+    <hyperlink ref="C339" r:id="rId548" location="MG-1688-06a_189" xr:uid="{00000000-0004-0000-0000-000027020000}"/>
+    <hyperlink ref="F339" r:id="rId549" xr:uid="{00000000-0004-0000-0000-000028020000}"/>
+    <hyperlink ref="C340" r:id="rId550" location="MG-1688-07_301" xr:uid="{00000000-0004-0000-0000-000029020000}"/>
+    <hyperlink ref="F340" r:id="rId551" xr:uid="{00000000-0004-0000-0000-00002A020000}"/>
+    <hyperlink ref="V340" r:id="rId552" xr:uid="{00000000-0004-0000-0000-00002B020000}"/>
+    <hyperlink ref="AB340" r:id="rId553" xr:uid="{00000000-0004-0000-0000-00002C020000}"/>
+    <hyperlink ref="C341" r:id="rId554" location="MG-1688-08_246" xr:uid="{00000000-0004-0000-0000-00002D020000}"/>
+    <hyperlink ref="F341" r:id="rId555" xr:uid="{00000000-0004-0000-0000-00002E020000}"/>
+    <hyperlink ref="C342" r:id="rId556" location="MG-1688-09a_237" xr:uid="{00000000-0004-0000-0000-00002F020000}"/>
+    <hyperlink ref="F342" r:id="rId557" xr:uid="{00000000-0004-0000-0000-000030020000}"/>
+    <hyperlink ref="AB342" r:id="rId558" location="infos-principales" xr:uid="{00000000-0004-0000-0000-000031020000}"/>
+    <hyperlink ref="F343" r:id="rId559" xr:uid="{00000000-0004-0000-0000-000032020000}"/>
+    <hyperlink ref="AB343" r:id="rId560" xr:uid="{00000000-0004-0000-0000-000033020000}"/>
+    <hyperlink ref="C344" r:id="rId561" location="MG-1688-11a_283" xr:uid="{00000000-0004-0000-0000-000034020000}"/>
+    <hyperlink ref="F344" r:id="rId562" xr:uid="{00000000-0004-0000-0000-000035020000}"/>
+    <hyperlink ref="C345" r:id="rId563" location="MG-1688-12a_131" xr:uid="{00000000-0004-0000-0000-000036020000}"/>
+    <hyperlink ref="F345" r:id="rId564" xr:uid="{00000000-0004-0000-0000-000037020000}"/>
+    <hyperlink ref="F346" r:id="rId565" xr:uid="{00000000-0004-0000-0000-000038020000}"/>
+    <hyperlink ref="F347" r:id="rId566" xr:uid="{00000000-0004-0000-0000-000039020000}"/>
+    <hyperlink ref="F348" r:id="rId567" xr:uid="{00000000-0004-0000-0000-00003A020000}"/>
+    <hyperlink ref="AB348" r:id="rId568" xr:uid="{00000000-0004-0000-0000-00003B020000}"/>
+    <hyperlink ref="F349" r:id="rId569" xr:uid="{00000000-0004-0000-0000-00003C020000}"/>
+    <hyperlink ref="F350" r:id="rId570" xr:uid="{00000000-0004-0000-0000-00003D020000}"/>
+    <hyperlink ref="V350" r:id="rId571" xr:uid="{00000000-0004-0000-0000-00003E020000}"/>
+    <hyperlink ref="X350" r:id="rId572" xr:uid="{00000000-0004-0000-0000-00003F020000}"/>
+    <hyperlink ref="F351" r:id="rId573" xr:uid="{00000000-0004-0000-0000-000040020000}"/>
+    <hyperlink ref="F352" r:id="rId574" xr:uid="{00000000-0004-0000-0000-000041020000}"/>
+    <hyperlink ref="AB352" r:id="rId575" xr:uid="{00000000-0004-0000-0000-000042020000}"/>
+    <hyperlink ref="F353" r:id="rId576" xr:uid="{00000000-0004-0000-0000-000043020000}"/>
+    <hyperlink ref="F354" r:id="rId577" xr:uid="{00000000-0004-0000-0000-000044020000}"/>
+    <hyperlink ref="Y354" r:id="rId578" xr:uid="{00000000-0004-0000-0000-000045020000}"/>
+    <hyperlink ref="AB354" r:id="rId579" xr:uid="{00000000-0004-0000-0000-000046020000}"/>
+    <hyperlink ref="F355" r:id="rId580" xr:uid="{00000000-0004-0000-0000-000047020000}"/>
+    <hyperlink ref="F356" r:id="rId581" xr:uid="{00000000-0004-0000-0000-000048020000}"/>
+    <hyperlink ref="C357" r:id="rId582" location="MG-1689-12_227" xr:uid="{00000000-0004-0000-0000-000049020000}"/>
+    <hyperlink ref="F357" r:id="rId583" xr:uid="{00000000-0004-0000-0000-00004A020000}"/>
+    <hyperlink ref="F358" r:id="rId584" xr:uid="{00000000-0004-0000-0000-00004B020000}"/>
+    <hyperlink ref="AB358" r:id="rId585" xr:uid="{00000000-0004-0000-0000-00004C020000}"/>
+    <hyperlink ref="C359" r:id="rId586" location="MG-1690-02_151" xr:uid="{00000000-0004-0000-0000-00004D020000}"/>
+    <hyperlink ref="F359" r:id="rId587" xr:uid="{00000000-0004-0000-0000-00004E020000}"/>
+    <hyperlink ref="F360" r:id="rId588" xr:uid="{00000000-0004-0000-0000-00004F020000}"/>
+    <hyperlink ref="F362" r:id="rId589" xr:uid="{00000000-0004-0000-0000-000050020000}"/>
+    <hyperlink ref="AD362" r:id="rId590" xr:uid="{00000000-0004-0000-0000-000051020000}"/>
+    <hyperlink ref="F363" r:id="rId591" xr:uid="{00000000-0004-0000-0000-000052020000}"/>
+    <hyperlink ref="F364" r:id="rId592" xr:uid="{00000000-0004-0000-0000-000053020000}"/>
+    <hyperlink ref="F365" r:id="rId593" xr:uid="{00000000-0004-0000-0000-000054020000}"/>
+    <hyperlink ref="AB365" r:id="rId594" xr:uid="{00000000-0004-0000-0000-000055020000}"/>
+    <hyperlink ref="C366" r:id="rId595" location="MG-1690-09_187" xr:uid="{00000000-0004-0000-0000-000056020000}"/>
+    <hyperlink ref="F366" r:id="rId596" xr:uid="{00000000-0004-0000-0000-000057020000}"/>
+    <hyperlink ref="F367" r:id="rId597" xr:uid="{00000000-0004-0000-0000-000058020000}"/>
+    <hyperlink ref="F368" r:id="rId598" xr:uid="{00000000-0004-0000-0000-000059020000}"/>
+    <hyperlink ref="Y368" r:id="rId599" xr:uid="{00000000-0004-0000-0000-00005A020000}"/>
+    <hyperlink ref="C369" r:id="rId600" location="MG-1691-01_227" xr:uid="{00000000-0004-0000-0000-00005B020000}"/>
+    <hyperlink ref="F369" r:id="rId601" xr:uid="{00000000-0004-0000-0000-00005C020000}"/>
+    <hyperlink ref="AB369" r:id="rId602" display="https://gallica.bnf.fr/ark:/12148 ; btv1b550039004 ; https://data.bnf.fr/fr/12356952/cornelis_vermeulen/ " xr:uid="{00000000-0004-0000-0000-00005D020000}"/>
+    <hyperlink ref="C370" r:id="rId603" location="MG-1691-02_177" xr:uid="{00000000-0004-0000-0000-00005E020000}"/>
+    <hyperlink ref="F370" r:id="rId604" xr:uid="{00000000-0004-0000-0000-00005F020000}"/>
+    <hyperlink ref="AC370" r:id="rId605" xr:uid="{00000000-0004-0000-0000-000060020000}"/>
+    <hyperlink ref="C371" r:id="rId606" location="MG-1691-03_131" xr:uid="{00000000-0004-0000-0000-000061020000}"/>
+    <hyperlink ref="D371" r:id="rId607" location="MG-1691-02_177" xr:uid="{00000000-0004-0000-0000-000062020000}"/>
+    <hyperlink ref="F371" r:id="rId608" xr:uid="{00000000-0004-0000-0000-000063020000}"/>
+    <hyperlink ref="C372" r:id="rId609" location="MG-1691-04_162" xr:uid="{00000000-0004-0000-0000-000064020000}"/>
+    <hyperlink ref="F372" r:id="rId610" xr:uid="{00000000-0004-0000-0000-000065020000}"/>
+    <hyperlink ref="F373" r:id="rId611" xr:uid="{00000000-0004-0000-0000-000066020000}"/>
+    <hyperlink ref="C374" r:id="rId612" location="MG-1691-06_208" xr:uid="{00000000-0004-0000-0000-000067020000}"/>
+    <hyperlink ref="F374" r:id="rId613" xr:uid="{00000000-0004-0000-0000-000068020000}"/>
+    <hyperlink ref="C375" r:id="rId614" location="MG-1691-07_181" xr:uid="{00000000-0004-0000-0000-000069020000}"/>
+    <hyperlink ref="F375" r:id="rId615" xr:uid="{00000000-0004-0000-0000-00006A020000}"/>
+    <hyperlink ref="F377" r:id="rId616" xr:uid="{00000000-0004-0000-0000-00006C020000}"/>
+    <hyperlink ref="F378" r:id="rId617" xr:uid="{00000000-0004-0000-0000-00006D020000}"/>
+    <hyperlink ref="F379" r:id="rId618" xr:uid="{00000000-0004-0000-0000-00006E020000}"/>
+    <hyperlink ref="Y379" r:id="rId619" xr:uid="{00000000-0004-0000-0000-00006F020000}"/>
+    <hyperlink ref="C380" r:id="rId620" location="MG-1691-11_156" xr:uid="{00000000-0004-0000-0000-000070020000}"/>
+    <hyperlink ref="F380" r:id="rId621" xr:uid="{00000000-0004-0000-0000-000071020000}"/>
+    <hyperlink ref="Y380" r:id="rId622" xr:uid="{00000000-0004-0000-0000-000072020000}"/>
+    <hyperlink ref="F381" r:id="rId623" xr:uid="{00000000-0004-0000-0000-000073020000}"/>
+    <hyperlink ref="AC381" r:id="rId624" location="v=onepage&amp;q=Terraque%2C%20marique%20m%C3%A9daille&amp;f=false" xr:uid="{00000000-0004-0000-0000-000074020000}"/>
+    <hyperlink ref="C383" r:id="rId625" location="MG-1692-01a_288" xr:uid="{00000000-0004-0000-0000-000075020000}"/>
+    <hyperlink ref="F383" r:id="rId626" xr:uid="{00000000-0004-0000-0000-000076020000}"/>
+    <hyperlink ref="C384" r:id="rId627" location="MG-1692-02a_307" xr:uid="{00000000-0004-0000-0000-000077020000}"/>
+    <hyperlink ref="C385" r:id="rId628" location="MG-1692-02a_307" xr:uid="{00000000-0004-0000-0000-000078020000}"/>
+    <hyperlink ref="C386" r:id="rId629" location="MG-1692-03_175" xr:uid="{00000000-0004-0000-0000-000079020000}"/>
+    <hyperlink ref="F386" r:id="rId630" xr:uid="{00000000-0004-0000-0000-00007A020000}"/>
+    <hyperlink ref="C387" r:id="rId631" location="MG-1692-04_181" xr:uid="{00000000-0004-0000-0000-00007B020000}"/>
+    <hyperlink ref="F387" r:id="rId632" xr:uid="{00000000-0004-0000-0000-00007C020000}"/>
+    <hyperlink ref="C388" r:id="rId633" location="MG-1692-05_217" xr:uid="{00000000-0004-0000-0000-00007D020000}"/>
+    <hyperlink ref="F388" r:id="rId634" xr:uid="{00000000-0004-0000-0000-00007E020000}"/>
+    <hyperlink ref="AB388" r:id="rId635" xr:uid="{00000000-0004-0000-0000-00007F020000}"/>
+    <hyperlink ref="F390" r:id="rId636" xr:uid="{00000000-0004-0000-0000-000081020000}"/>
+    <hyperlink ref="F391" r:id="rId637" xr:uid="{00000000-0004-0000-0000-000082020000}"/>
+    <hyperlink ref="F392" r:id="rId638" xr:uid="{00000000-0004-0000-0000-000083020000}"/>
+    <hyperlink ref="F393" r:id="rId639" xr:uid="{00000000-0004-0000-0000-000084020000}"/>
+    <hyperlink ref="F394" r:id="rId640" xr:uid="{00000000-0004-0000-0000-000085020000}"/>
+    <hyperlink ref="F395" r:id="rId641" xr:uid="{00000000-0004-0000-0000-000086020000}"/>
+    <hyperlink ref="F396" r:id="rId642" xr:uid="{00000000-0004-0000-0000-000087020000}"/>
+    <hyperlink ref="Y396" r:id="rId643" xr:uid="{00000000-0004-0000-0000-000088020000}"/>
+    <hyperlink ref="AB396" r:id="rId644" xr:uid="{00000000-0004-0000-0000-000089020000}"/>
+    <hyperlink ref="F397" r:id="rId645" xr:uid="{00000000-0004-0000-0000-00008A020000}"/>
+    <hyperlink ref="AB397" r:id="rId646" xr:uid="{00000000-0004-0000-0000-00008B020000}"/>
+    <hyperlink ref="AC397" r:id="rId647" location="v=onepage&amp;q=Providenter.%20Philisburgum%20expugnatum&amp;f=false" xr:uid="{00000000-0004-0000-0000-00008C020000}"/>
+    <hyperlink ref="F398" r:id="rId648" xr:uid="{00000000-0004-0000-0000-00008D020000}"/>
+    <hyperlink ref="F399" r:id="rId649" xr:uid="{00000000-0004-0000-0000-00008E020000}"/>
+    <hyperlink ref="F400" r:id="rId650" xr:uid="{00000000-0004-0000-0000-00008F020000}"/>
+    <hyperlink ref="AB400" r:id="rId651" xr:uid="{00000000-0004-0000-0000-000090020000}"/>
+    <hyperlink ref="F401" r:id="rId652" xr:uid="{00000000-0004-0000-0000-000091020000}"/>
+    <hyperlink ref="F402" r:id="rId653" xr:uid="{00000000-0004-0000-0000-000092020000}"/>
+    <hyperlink ref="AB402" r:id="rId654" xr:uid="{00000000-0004-0000-0000-000093020000}"/>
+    <hyperlink ref="F403" r:id="rId655" xr:uid="{00000000-0004-0000-0000-000094020000}"/>
+    <hyperlink ref="Y403" r:id="rId656" xr:uid="{00000000-0004-0000-0000-000095020000}"/>
+    <hyperlink ref="F404" r:id="rId657" xr:uid="{00000000-0004-0000-0000-000096020000}"/>
+    <hyperlink ref="AB404" r:id="rId658" xr:uid="{00000000-0004-0000-0000-000097020000}"/>
+    <hyperlink ref="AC404" r:id="rId659" xr:uid="{00000000-0004-0000-0000-000098020000}"/>
+    <hyperlink ref="F405" r:id="rId660" xr:uid="{00000000-0004-0000-0000-000099020000}"/>
+    <hyperlink ref="AB405" r:id="rId661" xr:uid="{00000000-0004-0000-0000-00009A020000}"/>
+    <hyperlink ref="AC405" r:id="rId662" xr:uid="{00000000-0004-0000-0000-00009B020000}"/>
+    <hyperlink ref="F406" r:id="rId663" xr:uid="{00000000-0004-0000-0000-00009C020000}"/>
+    <hyperlink ref="AB406" r:id="rId664" xr:uid="{00000000-0004-0000-0000-00009D020000}"/>
+    <hyperlink ref="F407" r:id="rId665" xr:uid="{00000000-0004-0000-0000-00009E020000}"/>
+    <hyperlink ref="AB407" r:id="rId666" xr:uid="{00000000-0004-0000-0000-00009F020000}"/>
+    <hyperlink ref="F408" r:id="rId667" xr:uid="{00000000-0004-0000-0000-0000A0020000}"/>
+    <hyperlink ref="F409" r:id="rId668" xr:uid="{00000000-0004-0000-0000-0000A1020000}"/>
+    <hyperlink ref="C410" r:id="rId669" location="MG-1694-04_112" xr:uid="{00000000-0004-0000-0000-0000A2020000}"/>
+    <hyperlink ref="F410" r:id="rId670" xr:uid="{00000000-0004-0000-0000-0000A3020000}"/>
+    <hyperlink ref="F411" r:id="rId671" xr:uid="{00000000-0004-0000-0000-0000A4020000}"/>
+    <hyperlink ref="F412" r:id="rId672" xr:uid="{00000000-0004-0000-0000-0000A5020000}"/>
+    <hyperlink ref="F413" r:id="rId673" xr:uid="{00000000-0004-0000-0000-0000A6020000}"/>
+    <hyperlink ref="AB413" r:id="rId674" xr:uid="{00000000-0004-0000-0000-0000A7020000}"/>
+    <hyperlink ref="F414" r:id="rId675" xr:uid="{00000000-0004-0000-0000-0000A8020000}"/>
+    <hyperlink ref="C415" r:id="rId676" location="MG-1694-08_227" xr:uid="{00000000-0004-0000-0000-0000A9020000}"/>
+    <hyperlink ref="F415" r:id="rId677" xr:uid="{00000000-0004-0000-0000-0000AA020000}"/>
+    <hyperlink ref="F416" r:id="rId678" xr:uid="{00000000-0004-0000-0000-0000AB020000}"/>
+    <hyperlink ref="AB416" r:id="rId679" xr:uid="{00000000-0004-0000-0000-0000AC020000}"/>
+    <hyperlink ref="F417" r:id="rId680" xr:uid="{00000000-0004-0000-0000-0000AD020000}"/>
+    <hyperlink ref="F418" r:id="rId681" xr:uid="{00000000-0004-0000-0000-0000AE020000}"/>
+    <hyperlink ref="F419" r:id="rId682" xr:uid="{00000000-0004-0000-0000-0000AF020000}"/>
+    <hyperlink ref="F420" r:id="rId683" xr:uid="{00000000-0004-0000-0000-0000B0020000}"/>
+    <hyperlink ref="F421" r:id="rId684" xr:uid="{00000000-0004-0000-0000-0000B1020000}"/>
+    <hyperlink ref="AB421" r:id="rId685" xr:uid="{00000000-0004-0000-0000-0000B2020000}"/>
+    <hyperlink ref="F422" r:id="rId686" xr:uid="{00000000-0004-0000-0000-0000B3020000}"/>
+    <hyperlink ref="AB422" r:id="rId687" xr:uid="{00000000-0004-0000-0000-0000B4020000}"/>
+    <hyperlink ref="F423" r:id="rId688" xr:uid="{00000000-0004-0000-0000-0000B5020000}"/>
+    <hyperlink ref="F424" r:id="rId689" xr:uid="{00000000-0004-0000-0000-0000B6020000}"/>
+    <hyperlink ref="C425" r:id="rId690" location="MG-1695-05_244" xr:uid="{00000000-0004-0000-0000-0000B7020000}"/>
+    <hyperlink ref="F425" r:id="rId691" xr:uid="{00000000-0004-0000-0000-0000B8020000}"/>
+    <hyperlink ref="F426" r:id="rId692" xr:uid="{00000000-0004-0000-0000-0000B9020000}"/>
+    <hyperlink ref="F427" r:id="rId693" xr:uid="{00000000-0004-0000-0000-0000BA020000}"/>
+    <hyperlink ref="F428" r:id="rId694" xr:uid="{00000000-0004-0000-0000-0000BB020000}"/>
+    <hyperlink ref="X428" r:id="rId695" xr:uid="{00000000-0004-0000-0000-0000BC020000}"/>
+    <hyperlink ref="F429" r:id="rId696" xr:uid="{00000000-0004-0000-0000-0000BD020000}"/>
+    <hyperlink ref="X429" r:id="rId697" xr:uid="{00000000-0004-0000-0000-0000BE020000}"/>
+    <hyperlink ref="F430" r:id="rId698" xr:uid="{00000000-0004-0000-0000-0000BF020000}"/>
+    <hyperlink ref="F431" r:id="rId699" xr:uid="{00000000-0004-0000-0000-0000C0020000}"/>
+    <hyperlink ref="F432" r:id="rId700" xr:uid="{00000000-0004-0000-0000-0000C1020000}"/>
+    <hyperlink ref="F433" r:id="rId701" xr:uid="{00000000-0004-0000-0000-0000C2020000}"/>
+    <hyperlink ref="X433" r:id="rId702" xr:uid="{00000000-0004-0000-0000-0000C3020000}"/>
+    <hyperlink ref="F434" r:id="rId703" xr:uid="{00000000-0004-0000-0000-0000C4020000}"/>
+    <hyperlink ref="X434" r:id="rId704" xr:uid="{00000000-0004-0000-0000-0000C5020000}"/>
+    <hyperlink ref="F435" r:id="rId705" xr:uid="{00000000-0004-0000-0000-0000C6020000}"/>
+    <hyperlink ref="F436" r:id="rId706" xr:uid="{00000000-0004-0000-0000-0000C7020000}"/>
+    <hyperlink ref="F437" r:id="rId707" xr:uid="{00000000-0004-0000-0000-0000C8020000}"/>
+    <hyperlink ref="X437" r:id="rId708" xr:uid="{00000000-0004-0000-0000-0000C9020000}"/>
+    <hyperlink ref="F438" r:id="rId709" xr:uid="{00000000-0004-0000-0000-0000CA020000}"/>
+    <hyperlink ref="X438" r:id="rId710" xr:uid="{00000000-0004-0000-0000-0000CB020000}"/>
+    <hyperlink ref="F439" r:id="rId711" xr:uid="{00000000-0004-0000-0000-0000CC020000}"/>
+    <hyperlink ref="X440" r:id="rId712" xr:uid="{00000000-0004-0000-0000-0000CE020000}"/>
+    <hyperlink ref="F441" r:id="rId713" xr:uid="{00000000-0004-0000-0000-0000CF020000}"/>
+    <hyperlink ref="X441" r:id="rId714" xr:uid="{00000000-0004-0000-0000-0000D0020000}"/>
+    <hyperlink ref="AB441" r:id="rId715" xr:uid="{00000000-0004-0000-0000-0000D1020000}"/>
+    <hyperlink ref="F442" r:id="rId716" xr:uid="{00000000-0004-0000-0000-0000D2020000}"/>
+    <hyperlink ref="F443" r:id="rId717" xr:uid="{00000000-0004-0000-0000-0000D3020000}"/>
+    <hyperlink ref="X443" r:id="rId718" xr:uid="{00000000-0004-0000-0000-0000D4020000}"/>
+    <hyperlink ref="F444" r:id="rId719" xr:uid="{00000000-0004-0000-0000-0000D5020000}"/>
+    <hyperlink ref="F445" r:id="rId720" xr:uid="{00000000-0004-0000-0000-0000D6020000}"/>
+    <hyperlink ref="X445" r:id="rId721" xr:uid="{00000000-0004-0000-0000-0000D7020000}"/>
+    <hyperlink ref="F446" r:id="rId722" xr:uid="{00000000-0004-0000-0000-0000D8020000}"/>
+    <hyperlink ref="X446" r:id="rId723" xr:uid="{00000000-0004-0000-0000-0000D9020000}"/>
+    <hyperlink ref="F447" r:id="rId724" xr:uid="{00000000-0004-0000-0000-0000DA020000}"/>
+    <hyperlink ref="X447" r:id="rId725" xr:uid="{00000000-0004-0000-0000-0000DB020000}"/>
+    <hyperlink ref="F448" r:id="rId726" xr:uid="{00000000-0004-0000-0000-0000DC020000}"/>
+    <hyperlink ref="F449" r:id="rId727" xr:uid="{00000000-0004-0000-0000-0000DD020000}"/>
+    <hyperlink ref="X449" r:id="rId728" xr:uid="{00000000-0004-0000-0000-0000DE020000}"/>
+    <hyperlink ref="F450" r:id="rId729" xr:uid="{00000000-0004-0000-0000-0000DF020000}"/>
+    <hyperlink ref="X450" r:id="rId730" xr:uid="{00000000-0004-0000-0000-0000E0020000}"/>
+    <hyperlink ref="F451" r:id="rId731" xr:uid="{00000000-0004-0000-0000-0000E1020000}"/>
+    <hyperlink ref="X451" r:id="rId732" xr:uid="{00000000-0004-0000-0000-0000E2020000}"/>
+    <hyperlink ref="F452" r:id="rId733" xr:uid="{00000000-0004-0000-0000-0000E3020000}"/>
+    <hyperlink ref="F453" r:id="rId734" xr:uid="{00000000-0004-0000-0000-0000E4020000}"/>
+    <hyperlink ref="F454" r:id="rId735" xr:uid="{00000000-0004-0000-0000-0000E5020000}"/>
+    <hyperlink ref="X454" r:id="rId736" xr:uid="{00000000-0004-0000-0000-0000E6020000}"/>
+    <hyperlink ref="F455" r:id="rId737" xr:uid="{00000000-0004-0000-0000-0000E7020000}"/>
+    <hyperlink ref="X455" r:id="rId738" xr:uid="{00000000-0004-0000-0000-0000E8020000}"/>
+    <hyperlink ref="AB455" r:id="rId739" xr:uid="{00000000-0004-0000-0000-0000E9020000}"/>
+    <hyperlink ref="F456" r:id="rId740" xr:uid="{00000000-0004-0000-0000-0000EA020000}"/>
+    <hyperlink ref="X456" r:id="rId741" xr:uid="{00000000-0004-0000-0000-0000EB020000}"/>
+    <hyperlink ref="F457" r:id="rId742" xr:uid="{00000000-0004-0000-0000-0000EC020000}"/>
+    <hyperlink ref="X457" r:id="rId743" xr:uid="{00000000-0004-0000-0000-0000ED020000}"/>
+    <hyperlink ref="F458" r:id="rId744" xr:uid="{00000000-0004-0000-0000-0000EE020000}"/>
+    <hyperlink ref="X458" r:id="rId745" xr:uid="{00000000-0004-0000-0000-0000EF020000}"/>
+    <hyperlink ref="F459" r:id="rId746" xr:uid="{00000000-0004-0000-0000-0000F0020000}"/>
+    <hyperlink ref="AC459" r:id="rId747" xr:uid="{00000000-0004-0000-0000-0000F1020000}"/>
+    <hyperlink ref="F460" r:id="rId748" xr:uid="{00000000-0004-0000-0000-0000F2020000}"/>
+    <hyperlink ref="X460" r:id="rId749" xr:uid="{00000000-0004-0000-0000-0000F3020000}"/>
+    <hyperlink ref="C461" r:id="rId750" location="MG-1701-04B_003" xr:uid="{00000000-0004-0000-0000-0000F4020000}"/>
+    <hyperlink ref="F461" r:id="rId751" xr:uid="{00000000-0004-0000-0000-0000F5020000}"/>
+    <hyperlink ref="X461" r:id="rId752" xr:uid="{00000000-0004-0000-0000-0000F6020000}"/>
+    <hyperlink ref="F462" r:id="rId753" xr:uid="{00000000-0004-0000-0000-0000F7020000}"/>
+    <hyperlink ref="V462" r:id="rId754" xr:uid="{00000000-0004-0000-0000-0000F8020000}"/>
+    <hyperlink ref="X462" r:id="rId755" xr:uid="{00000000-0004-0000-0000-0000F9020000}"/>
+    <hyperlink ref="F463" r:id="rId756" xr:uid="{00000000-0004-0000-0000-0000FA020000}"/>
+    <hyperlink ref="X463" r:id="rId757" xr:uid="{00000000-0004-0000-0000-0000FB020000}"/>
+    <hyperlink ref="C465" r:id="rId758" location="MG-1702-10_63" xr:uid="{00000000-0004-0000-0000-0000FC020000}"/>
+    <hyperlink ref="F465" r:id="rId759" xr:uid="{00000000-0004-0000-0000-0000FD020000}"/>
+    <hyperlink ref="F466" r:id="rId760" xr:uid="{00000000-0004-0000-0000-0000FE020000}"/>
+    <hyperlink ref="X466" r:id="rId761" xr:uid="{00000000-0004-0000-0000-0000FF020000}"/>
+    <hyperlink ref="C467" r:id="rId762" location="MG-1703-02_71" xr:uid="{00000000-0004-0000-0000-000000030000}"/>
+    <hyperlink ref="D467" r:id="rId763" location="MG-1703-03_363" xr:uid="{00000000-0004-0000-0000-000001030000}"/>
+    <hyperlink ref="F467" r:id="rId764" xr:uid="{00000000-0004-0000-0000-000002030000}"/>
+    <hyperlink ref="G467" r:id="rId765" location="MG-1703-02_71" xr:uid="{00000000-0004-0000-0000-000003030000}"/>
+    <hyperlink ref="F468" r:id="rId766" xr:uid="{00000000-0004-0000-0000-000004030000}"/>
+    <hyperlink ref="X468" r:id="rId767" xr:uid="{00000000-0004-0000-0000-000005030000}"/>
+    <hyperlink ref="AB468" r:id="rId768" xr:uid="{00000000-0004-0000-0000-000006030000}"/>
+    <hyperlink ref="F469" r:id="rId769" xr:uid="{00000000-0004-0000-0000-000007030000}"/>
+    <hyperlink ref="F470" r:id="rId770" xr:uid="{00000000-0004-0000-0000-000008030000}"/>
+    <hyperlink ref="F471" r:id="rId771" xr:uid="{00000000-0004-0000-0000-000009030000}"/>
+    <hyperlink ref="F472" r:id="rId772" xr:uid="{00000000-0004-0000-0000-00000A030000}"/>
+    <hyperlink ref="F473" r:id="rId773" xr:uid="{00000000-0004-0000-0000-00000B030000}"/>
+    <hyperlink ref="F474" r:id="rId774" xr:uid="{00000000-0004-0000-0000-00000C030000}"/>
+    <hyperlink ref="F475" r:id="rId775" xr:uid="{00000000-0004-0000-0000-00000D030000}"/>
+    <hyperlink ref="X475" r:id="rId776" xr:uid="{00000000-0004-0000-0000-00000E030000}"/>
+    <hyperlink ref="C476" r:id="rId777" location="MG-1707-01_162" xr:uid="{00000000-0004-0000-0000-00000F030000}"/>
+    <hyperlink ref="F476" r:id="rId778" xr:uid="{00000000-0004-0000-0000-000010030000}"/>
+    <hyperlink ref="X476" r:id="rId779" xr:uid="{00000000-0004-0000-0000-000011030000}"/>
+    <hyperlink ref="AB476" r:id="rId780" xr:uid="{00000000-0004-0000-0000-000012030000}"/>
+    <hyperlink ref="F477" r:id="rId781" xr:uid="{00000000-0004-0000-0000-000013030000}"/>
+    <hyperlink ref="X477" r:id="rId782" xr:uid="{00000000-0004-0000-0000-000014030000}"/>
+    <hyperlink ref="AB477" r:id="rId783" xr:uid="{00000000-0004-0000-0000-000015030000}"/>
+    <hyperlink ref="F478" r:id="rId784" xr:uid="{00000000-0004-0000-0000-000016030000}"/>
+    <hyperlink ref="X478" r:id="rId785" xr:uid="{00000000-0004-0000-0000-000017030000}"/>
+    <hyperlink ref="C479" r:id="rId786" location="MG-1709-03_125" xr:uid="{00000000-0004-0000-0000-000018030000}"/>
+    <hyperlink ref="F479" r:id="rId787" xr:uid="{00000000-0004-0000-0000-000019030000}"/>
+    <hyperlink ref="F480" r:id="rId788" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
+    <hyperlink ref="Y247" r:id="rId789" display="https://gallica.bnf.fr/ark:/12148/bpt6k56069895" xr:uid="{406C8F90-712D-EA4E-983E-641EE322383B}"/>
+    <hyperlink ref="F389" r:id="rId790" display="https://gallica.bnf.fr/ark:/12148/bpt6k6274143z/f227.item" xr:uid="{E92130F0-40E3-964F-9C82-6A4A8E98FE4A}"/>
+    <hyperlink ref="F382" r:id="rId791" xr:uid="{CB05E3EA-1CBE-F14B-8929-CCBCA00FE15C}"/>
+    <hyperlink ref="AC369" r:id="rId792" xr:uid="{6661D188-986C-EA4F-9D9E-F3E7E746DD57}"/>
+    <hyperlink ref="F274" r:id="rId793" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B48ECF8-C3A5-0D48-B7AC-E2F45576BB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0B6408-6927-DB48-A504-156D668AE27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4060" yWindow="-11660" windowWidth="37740" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3760" yWindow="-21000" windowWidth="37740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -12782,9 +12782,6 @@
     <t>https://collections.louvre.fr/en/ark:/53355/cl010393604</t>
   </si>
   <si>
-    <t>1689-04_236</t>
-  </si>
-  <si>
     <t>https://gallica.bnf.fr/ark:/12148/bpt6k6437997k/f239.item</t>
   </si>
   <si>
@@ -17377,9 +17374,6 @@
     <t>1692-01a_288</t>
   </si>
   <si>
-    <t>1689-01_215</t>
-  </si>
-  <si>
     <t>1683-12e_166</t>
   </si>
   <si>
@@ -17462,6 +17456,12 @@
   </si>
   <si>
     <t>1687-09a_269</t>
+  </si>
+  <si>
+    <t>1689-01a_215</t>
+  </si>
+  <si>
+    <t>1689-04a_236</t>
   </si>
 </sst>
 </file>
@@ -20606,7 +20606,7 @@
     </row>
     <row r="2" spans="1:43" ht="15.75" customHeight="1">
       <c r="A2" s="274" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>30</v>
@@ -20814,7 +20814,7 @@
       <c r="W4" s="29"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="30" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="Z4" s="30"/>
       <c r="AA4" s="30"/>
@@ -20841,7 +20841,7 @@
     </row>
     <row r="5" spans="1:43" ht="15.75" customHeight="1">
       <c r="A5" s="275" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>72</v>
@@ -20916,7 +20916,7 @@
     </row>
     <row r="6" spans="1:43" ht="15.75" customHeight="1">
       <c r="A6" s="289" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>43</v>
@@ -21066,7 +21066,7 @@
     </row>
     <row r="8" spans="1:43" ht="15.75" customHeight="1">
       <c r="A8" s="275" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>100</v>
@@ -21212,7 +21212,7 @@
     </row>
     <row r="10" spans="1:43" ht="15.75" customHeight="1">
       <c r="A10" s="274" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>100</v>
@@ -21364,7 +21364,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="251" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="D12" s="236"/>
       <c r="E12" s="67"/>
@@ -21435,7 +21435,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="251" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="D13" s="235"/>
       <c r="E13" s="58"/>
@@ -21642,13 +21642,13 @@
     </row>
     <row r="16" spans="1:43" ht="15.75" customHeight="1">
       <c r="A16" s="276" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="264" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="D16" s="234" t="s">
         <v>179</v>
@@ -21702,7 +21702,7 @@
         <v>191</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="Z16" s="30"/>
       <c r="AA16" s="30"/>
@@ -21735,7 +21735,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="267" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="D17" s="234" t="s">
         <v>179</v>
@@ -21990,7 +21990,7 @@
     </row>
     <row r="20" spans="1:43" ht="15.75" customHeight="1">
       <c r="A20" s="276" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
       <c r="B20" s="32" t="s">
         <v>43</v>
@@ -22075,7 +22075,7 @@
     </row>
     <row r="21" spans="1:43" ht="15.75" customHeight="1">
       <c r="A21" s="268" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="B21" s="32" t="s">
         <v>43</v>
@@ -22306,7 +22306,7 @@
     </row>
     <row r="24" spans="1:43" ht="15.75" customHeight="1">
       <c r="A24" s="277" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="B24" s="32" t="s">
         <v>247</v>
@@ -22375,7 +22375,7 @@
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
       <c r="A25" s="277" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>247</v>
@@ -22444,13 +22444,13 @@
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
       <c r="A26" s="291" t="s">
-        <v>3996</v>
+        <v>3994</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="250" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="D26" s="234" t="s">
         <v>179</v>
@@ -22515,7 +22515,7 @@
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
       <c r="A27" s="277" t="s">
-        <v>3997</v>
+        <v>3995</v>
       </c>
       <c r="B27" s="32" t="s">
         <v>247</v>
@@ -22600,7 +22600,7 @@
         <v>43</v>
       </c>
       <c r="C28" s="250" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="D28" s="234" t="s">
         <v>179</v>
@@ -22665,7 +22665,7 @@
     </row>
     <row r="29" spans="1:43" ht="15.75" customHeight="1">
       <c r="A29" s="274" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>279</v>
@@ -22740,7 +22740,7 @@
     </row>
     <row r="30" spans="1:43" ht="15.75" customHeight="1">
       <c r="A30" s="274" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="B30" s="33" t="s">
         <v>292</v>
@@ -22821,13 +22821,13 @@
     </row>
     <row r="31" spans="1:43" ht="15.75" customHeight="1">
       <c r="A31" s="277" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="B31" s="33" t="s">
         <v>292</v>
       </c>
       <c r="C31" s="250" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="D31" s="232"/>
       <c r="E31" s="18"/>
@@ -22894,7 +22894,7 @@
     </row>
     <row r="32" spans="1:43" ht="15.75" customHeight="1">
       <c r="A32" s="274" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="B32" s="32" t="s">
         <v>310</v>
@@ -22975,7 +22975,7 @@
         <v>292</v>
       </c>
       <c r="C33" s="250" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="D33" s="232"/>
       <c r="E33" s="18"/>
@@ -23040,13 +23040,13 @@
     </row>
     <row r="34" spans="1:43" ht="15.75" customHeight="1">
       <c r="A34" s="278" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="B34" s="95" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="251" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="D34" s="234" t="s">
         <v>280</v>
@@ -23121,13 +23121,13 @@
     </row>
     <row r="35" spans="1:43" ht="15.75" customHeight="1">
       <c r="A35" s="277" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="251" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="D35" s="234" t="s">
         <v>280</v>
@@ -23202,13 +23202,13 @@
     </row>
     <row r="36" spans="1:43" ht="15.75" customHeight="1">
       <c r="A36" s="277" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="250" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="D36" s="235"/>
       <c r="E36" s="58"/>
@@ -23352,7 +23352,7 @@
     </row>
     <row r="38" spans="1:43" ht="15.75" customHeight="1">
       <c r="A38" s="274" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>43</v>
@@ -23361,7 +23361,7 @@
         <v>359</v>
       </c>
       <c r="D38" s="235" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="E38" s="58"/>
       <c r="F38" s="32" t="s">
@@ -23431,7 +23431,7 @@
     </row>
     <row r="39" spans="1:43" ht="15.75" customHeight="1">
       <c r="A39" s="274" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>43</v>
@@ -23508,7 +23508,7 @@
         <v>377</v>
       </c>
       <c r="C40" s="250" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="D40" s="235"/>
       <c r="E40" s="58"/>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="48" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="I41" s="43" t="s">
         <v>384</v>
@@ -23595,7 +23595,7 @@
         <v>385</v>
       </c>
       <c r="M41" s="95" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="N41" s="54" t="s">
         <v>386</v>
@@ -23636,13 +23636,13 @@
     </row>
     <row r="42" spans="1:43" ht="15.75" customHeight="1">
       <c r="A42" s="277" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="250" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="D42" s="235"/>
       <c r="E42" s="58"/>
@@ -23707,13 +23707,13 @@
     </row>
     <row r="43" spans="1:43" ht="15.75" customHeight="1">
       <c r="A43" s="277" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="250" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="D43" s="235"/>
       <c r="E43" s="58"/>
@@ -23759,7 +23759,7 @@
         <v>404</v>
       </c>
       <c r="Y43" s="30" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="Z43" s="30"/>
       <c r="AA43" s="30"/>
@@ -23918,13 +23918,13 @@
     </row>
     <row r="46" spans="1:43" ht="15.75" customHeight="1">
       <c r="A46" s="277" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="250" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="D46" s="235"/>
       <c r="E46" s="58"/>
@@ -24001,7 +24001,7 @@
         <v>413</v>
       </c>
       <c r="C47" s="250" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="D47" s="235"/>
       <c r="E47" s="58"/>
@@ -24062,13 +24062,13 @@
     </row>
     <row r="48" spans="1:43" ht="15.75" customHeight="1">
       <c r="A48" s="277" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="B48" s="32" t="s">
         <v>434</v>
       </c>
       <c r="C48" s="250" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="D48" s="235"/>
       <c r="E48" s="58"/>
@@ -24219,13 +24219,13 @@
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>3995</v>
+        <v>3993</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>434</v>
       </c>
       <c r="C50" s="250" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
       <c r="D50" s="235"/>
       <c r="E50" s="58"/>
@@ -24290,13 +24290,13 @@
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>3994</v>
+        <v>3992</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>444</v>
       </c>
       <c r="C51" s="250" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="D51" s="234" t="s">
         <v>465</v>
@@ -24361,7 +24361,7 @@
     </row>
     <row r="52" spans="1:43" ht="15.75" customHeight="1">
       <c r="A52" s="277" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>471</v>
@@ -24523,7 +24523,7 @@
     </row>
     <row r="54" spans="1:43" ht="15.75" customHeight="1">
       <c r="A54" s="277" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="B54" s="131" t="s">
         <v>497</v>
@@ -24602,7 +24602,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="250" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="D55" s="235"/>
       <c r="E55" s="58"/>
@@ -24742,7 +24742,7 @@
     </row>
     <row r="57" spans="1:43" ht="15.75" customHeight="1">
       <c r="A57" s="277" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="B57" s="32" t="s">
         <v>43</v>
@@ -24809,13 +24809,13 @@
     </row>
     <row r="58" spans="1:43" ht="15.75" customHeight="1">
       <c r="A58" s="277" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="B58" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="250" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="D58" s="234" t="s">
         <v>179</v>
@@ -24884,13 +24884,13 @@
     </row>
     <row r="59" spans="1:43" ht="15.75" customHeight="1">
       <c r="A59" s="277" t="s">
-        <v>3907</v>
+        <v>3906</v>
       </c>
       <c r="B59" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="250" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="D59" s="234" t="s">
         <v>179</v>
@@ -24955,7 +24955,7 @@
     </row>
     <row r="60" spans="1:43" ht="15.75" customHeight="1">
       <c r="A60" s="277" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="B60" s="32" t="s">
         <v>43</v>
@@ -25030,18 +25030,18 @@
     </row>
     <row r="61" spans="1:43" ht="15.75" customHeight="1">
       <c r="A61" s="277" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="B61" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="250" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="D61" s="235"/>
       <c r="E61" s="58"/>
       <c r="F61" s="47" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>549</v>
@@ -25101,7 +25101,7 @@
     </row>
     <row r="62" spans="1:43" ht="15.75" customHeight="1">
       <c r="A62" s="277" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="B62" s="32" t="s">
         <v>43</v>
@@ -25174,13 +25174,13 @@
         <v>564</v>
       </c>
       <c r="C63" s="250" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="D63" s="234" t="s">
         <v>565</v>
       </c>
       <c r="E63" s="58" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="F63" s="290" t="s">
         <v>566</v>
@@ -25241,13 +25241,13 @@
     </row>
     <row r="64" spans="1:43" ht="15.75" customHeight="1">
       <c r="A64" s="277" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="250" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="D64" s="235"/>
       <c r="E64" s="58"/>
@@ -25314,13 +25314,13 @@
     </row>
     <row r="65" spans="1:43" ht="15.75" customHeight="1">
       <c r="A65" s="277" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="B65" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="250" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="D65" s="235"/>
       <c r="E65" s="58"/>
@@ -25387,7 +25387,7 @@
     </row>
     <row r="66" spans="1:43" ht="15.75" customHeight="1">
       <c r="A66" s="277" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="B66" s="32" t="s">
         <v>43</v>
@@ -25620,7 +25620,7 @@
     </row>
     <row r="69" spans="1:43" ht="15.75" customHeight="1">
       <c r="A69" s="366" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="B69" s="314" t="s">
         <v>43</v>
@@ -25707,7 +25707,7 @@
     </row>
     <row r="70" spans="1:43" ht="15.75" customHeight="1">
       <c r="A70" s="274" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="B70" s="32" t="s">
         <v>43</v>
@@ -25776,13 +25776,13 @@
     </row>
     <row r="71" spans="1:43" ht="15.75" customHeight="1">
       <c r="A71" s="277" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="B71" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="250" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
       <c r="D71" s="235"/>
       <c r="E71" s="58"/>
@@ -25845,7 +25845,7 @@
     </row>
     <row r="72" spans="1:43" ht="15.75" customHeight="1">
       <c r="A72" s="274" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="B72" s="32" t="s">
         <v>644</v>
@@ -25991,7 +25991,7 @@
     </row>
     <row r="74" spans="1:43" ht="15.75" customHeight="1">
       <c r="A74" s="274" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="B74" s="39" t="s">
         <v>43</v>
@@ -26066,7 +26066,7 @@
         <v>43</v>
       </c>
       <c r="C75" s="250" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="D75" s="337"/>
       <c r="E75" s="58"/>
@@ -26713,7 +26713,7 @@
     </row>
     <row r="84" spans="1:43" ht="15.75" customHeight="1">
       <c r="A84" s="274" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>749</v>
@@ -26849,7 +26849,7 @@
     </row>
     <row r="86" spans="1:43" ht="15.75" customHeight="1">
       <c r="A86" s="274" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>434</v>
@@ -27226,7 +27226,7 @@
     </row>
     <row r="91" spans="1:43" ht="15.75" customHeight="1">
       <c r="A91" s="274" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>43</v>
@@ -27579,7 +27579,7 @@
     </row>
     <row r="96" spans="1:43" ht="15.75" customHeight="1">
       <c r="A96" s="277" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>434</v>
@@ -27646,7 +27646,7 @@
     </row>
     <row r="97" spans="1:43" ht="15.75" customHeight="1">
       <c r="A97" s="277" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="B97" s="32" t="s">
         <v>43</v>
@@ -27849,7 +27849,7 @@
     </row>
     <row r="100" spans="1:43" ht="15.75" customHeight="1">
       <c r="A100" s="277" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="B100" s="32" t="s">
         <v>870</v>
@@ -27995,7 +27995,7 @@
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
       <c r="A102" s="277" t="s">
-        <v>3993</v>
+        <v>3991</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>890</v>
@@ -28141,7 +28141,7 @@
     </row>
     <row r="104" spans="1:43" ht="15.75" customHeight="1">
       <c r="A104" s="277" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="B104" s="32" t="s">
         <v>471</v>
@@ -28354,7 +28354,7 @@
     </row>
     <row r="107" spans="1:43" ht="15.75" customHeight="1">
       <c r="A107" s="277" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="B107" s="32" t="s">
         <v>43</v>
@@ -28437,7 +28437,7 @@
     </row>
     <row r="108" spans="1:43" ht="15.75" customHeight="1">
       <c r="A108" s="277" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="B108" s="32" t="s">
         <v>43</v>
@@ -28644,7 +28644,7 @@
     </row>
     <row r="111" spans="1:43" ht="15.75" customHeight="1">
       <c r="A111" s="277" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="B111" s="32" t="s">
         <v>43</v>
@@ -28857,7 +28857,7 @@
     </row>
     <row r="114" spans="1:43" ht="15.75" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>3992</v>
+        <v>3990</v>
       </c>
       <c r="B114" s="32" t="s">
         <v>434</v>
@@ -29220,7 +29220,7 @@
     </row>
     <row r="119" spans="1:43" ht="15.75" customHeight="1">
       <c r="A119" s="277" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>43</v>
@@ -29235,7 +29235,7 @@
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="32" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="I119" s="43" t="s">
         <v>1037</v>
@@ -29431,7 +29431,7 @@
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
       <c r="A122" s="278" t="s">
-        <v>3991</v>
+        <v>3989</v>
       </c>
       <c r="B122" s="51" t="s">
         <v>43</v>
@@ -29483,7 +29483,7 @@
       <c r="W122" s="29"/>
       <c r="X122" s="29"/>
       <c r="Y122" s="30" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="Z122" s="30"/>
       <c r="AA122" s="30"/>
@@ -29948,7 +29948,7 @@
     </row>
     <row r="129" spans="1:43" ht="15.75" customHeight="1">
       <c r="A129" s="278" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="B129" s="32" t="s">
         <v>43</v>
@@ -30019,7 +30019,7 @@
     </row>
     <row r="130" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A130" s="277" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>43</v>
@@ -30092,7 +30092,7 @@
     </row>
     <row r="131" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A131" s="277" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="B131" s="33" t="s">
         <v>43</v>
@@ -30528,7 +30528,7 @@
     </row>
     <row r="137" spans="1:43" ht="15.75" customHeight="1">
       <c r="A137" s="277" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>43</v>
@@ -30543,7 +30543,7 @@
       </c>
       <c r="G137" s="32"/>
       <c r="H137" s="48" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="I137" s="43" t="s">
         <v>1185</v>
@@ -30668,7 +30668,7 @@
     </row>
     <row r="139" spans="1:43" ht="15.75" customHeight="1">
       <c r="A139" s="278" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="B139" s="33" t="s">
         <v>43</v>
@@ -30683,7 +30683,7 @@
       </c>
       <c r="G139" s="32"/>
       <c r="H139" s="48" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="I139" s="43" t="s">
         <v>1199</v>
@@ -32733,7 +32733,7 @@
         <v>176</v>
       </c>
       <c r="N167" s="136" t="s">
-        <v>3999</v>
+        <v>3997</v>
       </c>
       <c r="O167" s="136"/>
       <c r="P167" s="155" t="s">
@@ -32743,7 +32743,7 @@
         <v>1419</v>
       </c>
       <c r="R167" s="39" t="s">
-        <v>4000</v>
+        <v>3998</v>
       </c>
       <c r="S167" s="21" t="s">
         <v>41</v>
@@ -32856,7 +32856,7 @@
     </row>
     <row r="169" spans="1:43" ht="15.75" customHeight="1">
       <c r="A169" s="277" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="B169" s="33" t="s">
         <v>43</v>
@@ -33286,7 +33286,7 @@
     </row>
     <row r="175" spans="1:43" ht="15.75" customHeight="1">
       <c r="A175" s="277" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="B175" s="33" t="s">
         <v>43</v>
@@ -33355,7 +33355,7 @@
     </row>
     <row r="176" spans="1:43" ht="15.75" customHeight="1">
       <c r="A176" s="277" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="B176" s="33" t="s">
         <v>43</v>
@@ -33422,7 +33422,7 @@
     </row>
     <row r="177" spans="1:43" s="410" customFormat="1" ht="15.75" customHeight="1">
       <c r="A177" s="278" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="B177" s="15" t="s">
         <v>471</v>
@@ -33880,7 +33880,7 @@
     </row>
     <row r="183" spans="1:43" ht="15.75" customHeight="1">
       <c r="A183" s="277" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="B183" s="33" t="s">
         <v>43</v>
@@ -33949,7 +33949,7 @@
     </row>
     <row r="184" spans="1:43" ht="15.75" customHeight="1">
       <c r="A184" s="277" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="B184" s="33" t="s">
         <v>43</v>
@@ -34383,7 +34383,7 @@
     </row>
     <row r="190" spans="1:43" ht="15.75" customHeight="1">
       <c r="A190" s="278" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="B190" s="15" t="s">
         <v>43</v>
@@ -34594,13 +34594,13 @@
     </row>
     <row r="193" spans="1:43" ht="15.75" customHeight="1">
       <c r="A193" s="277" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="B193" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C193" s="251" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="D193" s="235"/>
       <c r="E193" s="58"/>
@@ -34851,7 +34851,7 @@
         <v>1654</v>
       </c>
       <c r="M196" s="95" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="N196" s="54" t="s">
         <v>1655</v>
@@ -35468,7 +35468,7 @@
     </row>
     <row r="205" spans="1:43" ht="15.75" customHeight="1">
       <c r="A205" s="277" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="B205" s="33" t="s">
         <v>43</v>
@@ -35614,7 +35614,7 @@
     </row>
     <row r="207" spans="1:43" ht="15.75" customHeight="1">
       <c r="A207" s="277" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>434</v>
@@ -35932,7 +35932,7 @@
     </row>
     <row r="211" spans="1:43" ht="15.75" customHeight="1">
       <c r="A211" s="277" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>1006</v>
@@ -36094,7 +36094,7 @@
     </row>
     <row r="213" spans="1:43" ht="15.75" customHeight="1">
       <c r="A213" s="277" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>434</v>
@@ -36147,7 +36147,7 @@
       <c r="AB213" s="167"/>
       <c r="AC213" s="32"/>
       <c r="AD213" s="21" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="AE213" s="32"/>
       <c r="AF213" s="32"/>
@@ -36747,7 +36747,7 @@
     </row>
     <row r="222" spans="1:43" ht="15.75" customHeight="1">
       <c r="A222" s="278" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>434</v>
@@ -36905,7 +36905,7 @@
     </row>
     <row r="224" spans="1:43" ht="15.75" customHeight="1">
       <c r="A224" s="277" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>1913</v>
@@ -36986,7 +36986,7 @@
     </row>
     <row r="225" spans="1:43" ht="15.75" customHeight="1">
       <c r="A225" s="277" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="B225" s="14" t="s">
         <v>434</v>
@@ -37144,10 +37144,10 @@
       <c r="K227" s="82"/>
       <c r="L227" s="22"/>
       <c r="M227" s="53" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N227" s="54" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="O227" s="458"/>
       <c r="P227" s="318" t="s">
@@ -37225,10 +37225,10 @@
       <c r="K228" s="22"/>
       <c r="L228" s="22"/>
       <c r="M228" s="53" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N228" s="54" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="O228" s="54"/>
       <c r="P228" s="318" t="s">
@@ -37641,13 +37641,13 @@
     </row>
     <row r="234" spans="1:43" ht="15.75" customHeight="1">
       <c r="A234" s="277" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>434</v>
       </c>
       <c r="C234" s="261" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="D234" s="235"/>
       <c r="E234" s="58"/>
@@ -37981,7 +37981,7 @@
         <v>2007</v>
       </c>
       <c r="M238" s="95" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="N238" s="38" t="s">
         <v>1655</v>
@@ -38068,10 +38068,10 @@
         <v>2018</v>
       </c>
       <c r="M239" s="127" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="N239" s="54" t="s">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="O239" s="54"/>
       <c r="P239" s="25" t="s">
@@ -38121,7 +38121,7 @@
     </row>
     <row r="240" spans="1:43" ht="15.75" customHeight="1">
       <c r="A240" s="277" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>434</v>
@@ -38226,7 +38226,7 @@
       <c r="K241" s="82"/>
       <c r="L241" s="82"/>
       <c r="M241" s="53" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N241" s="54" t="s">
         <v>2032</v>
@@ -38298,7 +38298,7 @@
         <v>2036</v>
       </c>
       <c r="H242" s="48" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="I242" s="43" t="s">
         <v>2037</v>
@@ -38307,7 +38307,7 @@
       <c r="K242" s="22"/>
       <c r="L242" s="22"/>
       <c r="M242" s="53" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N242" s="54" t="s">
         <v>2038</v>
@@ -38668,23 +38668,23 @@
     </row>
     <row r="247" spans="1:43" ht="15.75" customHeight="1">
       <c r="A247" s="419" t="s">
-        <v>3771</v>
+        <v>3770</v>
       </c>
       <c r="B247" s="419" t="s">
         <v>2083</v>
       </c>
       <c r="C247" s="262" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="E247" s="230"/>
       <c r="F247" s="230" t="s">
+        <v>3771</v>
+      </c>
+      <c r="G247" s="230" t="s">
         <v>3772</v>
       </c>
-      <c r="G247" s="230" t="s">
-        <v>3773</v>
-      </c>
       <c r="H247" s="423" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="I247" s="421" t="s">
         <v>1911</v>
@@ -38693,10 +38693,10 @@
       <c r="K247" s="230"/>
       <c r="L247" s="230"/>
       <c r="M247" s="421" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N247" s="460" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="O247" s="459"/>
       <c r="P247" s="318" t="s">
@@ -38712,7 +38712,7 @@
         <v>41</v>
       </c>
       <c r="T247" s="423" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="U247" s="423" t="s">
         <v>1904</v>
@@ -38723,7 +38723,7 @@
       <c r="W247" s="230"/>
       <c r="X247" s="230"/>
       <c r="Y247" s="433" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="Z247" s="230"/>
       <c r="AA247" s="230"/>
@@ -38732,7 +38732,7 @@
         <v>2084</v>
       </c>
       <c r="AD247" s="230" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
       <c r="AE247" s="230"/>
       <c r="AF247" s="230"/>
@@ -38750,19 +38750,19 @@
     </row>
     <row r="248" spans="1:43" ht="15.75" customHeight="1">
       <c r="A248" s="419" t="s">
+        <v>3766</v>
+      </c>
+      <c r="B248" s="423" t="s">
         <v>3767</v>
       </c>
-      <c r="B248" s="423" t="s">
-        <v>3768</v>
-      </c>
       <c r="C248" s="262" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="E248" s="230"/>
       <c r="F248" s="230"/>
       <c r="G248" s="423"/>
       <c r="H248" s="423" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="I248" s="421" t="s">
         <v>2031</v>
@@ -38771,10 +38771,10 @@
       <c r="K248" s="230"/>
       <c r="L248" s="230"/>
       <c r="M248" s="421" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N248" s="460" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="O248" s="459"/>
       <c r="P248" s="318" t="s">
@@ -38790,7 +38790,7 @@
         <v>41</v>
       </c>
       <c r="T248" s="423" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="U248" s="423" t="s">
         <v>1904</v>
@@ -38801,7 +38801,7 @@
       <c r="W248" s="230"/>
       <c r="X248" s="230"/>
       <c r="Y248" s="423" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="Z248" s="230"/>
       <c r="AA248" s="230"/>
@@ -39122,7 +39122,7 @@
         <v>434</v>
       </c>
       <c r="C253" s="251" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="D253" s="235"/>
       <c r="E253" s="58"/>
@@ -39481,7 +39481,7 @@
     </row>
     <row r="258" spans="1:43" ht="15.75" customHeight="1">
       <c r="A258" s="277" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="B258" s="14" t="s">
         <v>434</v>
@@ -39848,7 +39848,7 @@
     </row>
     <row r="263" spans="1:43" ht="15.75" customHeight="1">
       <c r="A263" s="277" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="B263" s="14" t="s">
         <v>434</v>
@@ -39988,7 +39988,7 @@
     </row>
     <row r="265" spans="1:43" ht="15.75" customHeight="1">
       <c r="A265" s="14" t="s">
-        <v>3990</v>
+        <v>3988</v>
       </c>
       <c r="B265" s="14" t="s">
         <v>2209</v>
@@ -40014,10 +40014,10 @@
       <c r="K265" s="22"/>
       <c r="L265" s="22"/>
       <c r="M265" s="53" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N265" s="54" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="O265" s="54"/>
       <c r="P265" s="318" t="s">
@@ -40059,7 +40059,7 @@
     </row>
     <row r="266" spans="1:43" ht="15.75" customHeight="1">
       <c r="A266" s="277" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="B266" s="14" t="s">
         <v>434</v>
@@ -40278,7 +40278,7 @@
     </row>
     <row r="269" spans="1:43" ht="15.75" customHeight="1">
       <c r="A269" s="278" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="B269" s="66" t="s">
         <v>2239</v>
@@ -40381,10 +40381,10 @@
       <c r="K270" s="22"/>
       <c r="L270" s="22"/>
       <c r="M270" s="320" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N270" s="73" t="s">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="O270" s="73"/>
       <c r="P270" s="318" t="s">
@@ -40409,7 +40409,7 @@
       <c r="W270" s="29"/>
       <c r="X270" s="29"/>
       <c r="Y270" s="30" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="Z270" s="30"/>
       <c r="AA270" s="30"/>
@@ -40635,7 +40635,7 @@
     </row>
     <row r="274" spans="1:43" ht="15.75" customHeight="1">
       <c r="A274" s="14" t="s">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="B274" s="14" t="s">
         <v>434</v>
@@ -40882,10 +40882,10 @@
       <c r="K277" s="82"/>
       <c r="L277" s="22"/>
       <c r="M277" s="320" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N277" s="38" t="s">
-        <v>4011</v>
+        <v>4009</v>
       </c>
       <c r="O277" s="38"/>
       <c r="P277" s="318" t="s">
@@ -41253,7 +41253,7 @@
       <c r="K282" s="22"/>
       <c r="L282" s="22"/>
       <c r="M282" s="320" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N282" s="504" t="s">
         <v>2457</v>
@@ -41281,7 +41281,7 @@
       <c r="W282" s="29"/>
       <c r="X282" s="29"/>
       <c r="Y282" s="30" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="Z282" s="30"/>
       <c r="AA282" s="30"/>
@@ -41345,7 +41345,7 @@
         <v>1905</v>
       </c>
       <c r="R283" s="32" t="s">
-        <v>4000</v>
+        <v>3998</v>
       </c>
       <c r="S283" s="32" t="s">
         <v>41</v>
@@ -41541,10 +41541,10 @@
       <c r="K286" s="22"/>
       <c r="L286" s="22"/>
       <c r="M286" s="454" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N286" s="89" t="s">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="O286" s="89"/>
       <c r="P286" s="126" t="s">
@@ -41829,7 +41829,7 @@
       <c r="K290" s="82"/>
       <c r="L290" s="22"/>
       <c r="M290" s="320" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N290" s="54" t="s">
         <v>2380</v>
@@ -42121,10 +42121,10 @@
       <c r="K294" s="82"/>
       <c r="L294" s="82"/>
       <c r="M294" s="33" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="N294" s="89" t="s">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="O294" s="457"/>
       <c r="P294" s="114" t="s">
@@ -42149,7 +42149,7 @@
       <c r="W294" s="29"/>
       <c r="X294" s="29"/>
       <c r="Y294" s="30" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="Z294" s="30"/>
       <c r="AA294" s="30"/>
@@ -42174,7 +42174,7 @@
     </row>
     <row r="295" spans="1:43" ht="15.75" customHeight="1">
       <c r="A295" s="277" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="B295" s="14" t="s">
         <v>434</v>
@@ -42496,7 +42496,7 @@
       <c r="K299" s="22"/>
       <c r="L299" s="22"/>
       <c r="M299" s="320" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N299" s="89" t="s">
         <v>2038</v>
@@ -42657,7 +42657,7 @@
         <v>2462</v>
       </c>
       <c r="N301" s="38" t="s">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="O301" s="38"/>
       <c r="P301" s="25"/>
@@ -42973,7 +42973,7 @@
     </row>
     <row r="306" spans="1:43" ht="15.75" customHeight="1">
       <c r="A306" s="282" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="B306" s="33" t="s">
         <v>434</v>
@@ -43131,7 +43131,7 @@
     </row>
     <row r="308" spans="1:43" ht="15.75" customHeight="1">
       <c r="A308" s="282" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="B308" s="33" t="s">
         <v>434</v>
@@ -43285,7 +43285,7 @@
     </row>
     <row r="310" spans="1:43" ht="15.75" customHeight="1">
       <c r="A310" s="284" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="B310" s="33" t="s">
         <v>434</v>
@@ -43300,7 +43300,7 @@
       </c>
       <c r="G310" s="32"/>
       <c r="H310" s="414" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="I310" s="32" t="s">
         <v>2506</v>
@@ -43881,13 +43881,13 @@
     </row>
     <row r="318" spans="1:43" ht="15.75" customHeight="1">
       <c r="A318" s="285" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="B318" s="33" t="s">
         <v>2597</v>
       </c>
       <c r="C318" s="263" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="E318" s="58" t="s">
         <v>2598</v>
@@ -44040,7 +44040,7 @@
     </row>
     <row r="320" spans="1:43" ht="15.75" customHeight="1">
       <c r="A320" s="282" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="B320" s="33" t="s">
         <v>434</v>
@@ -44109,7 +44109,7 @@
     </row>
     <row r="321" spans="1:43" ht="15.75" customHeight="1">
       <c r="A321" s="282" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="B321" s="33" t="s">
         <v>434</v>
@@ -44534,7 +44534,7 @@
         <v>2237</v>
       </c>
       <c r="Y326" s="30" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="Z326" s="30"/>
       <c r="AA326" s="30" t="s">
@@ -44646,7 +44646,7 @@
         <v>434</v>
       </c>
       <c r="C328" s="251" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="D328" s="247"/>
       <c r="E328" s="190"/>
@@ -44721,7 +44721,7 @@
     </row>
     <row r="329" spans="1:43" ht="15.75" customHeight="1">
       <c r="A329" s="186" t="s">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="B329" s="33" t="s">
         <v>434</v>
@@ -45425,7 +45425,7 @@
       </c>
       <c r="G338" s="48"/>
       <c r="H338" s="32" t="s">
-        <v>4001</v>
+        <v>3999</v>
       </c>
       <c r="I338" s="187" t="s">
         <v>2766</v>
@@ -45439,7 +45439,7 @@
         <v>2768</v>
       </c>
       <c r="N338" s="38" t="s">
-        <v>4002</v>
+        <v>4000</v>
       </c>
       <c r="O338" s="38"/>
       <c r="P338" s="25" t="s">
@@ -45449,7 +45449,7 @@
         <v>2770</v>
       </c>
       <c r="R338" s="503" t="s">
-        <v>4000</v>
+        <v>3998</v>
       </c>
       <c r="S338" s="77" t="s">
         <v>41</v>
@@ -45716,7 +45716,7 @@
     </row>
     <row r="342" spans="1:43" ht="15.75" customHeight="1">
       <c r="A342" s="282" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
       <c r="B342" s="33" t="s">
         <v>434</v>
@@ -45945,7 +45945,7 @@
     </row>
     <row r="345" spans="1:43" ht="15.75" customHeight="1">
       <c r="A345" s="282" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="B345" s="33" t="s">
         <v>434</v>
@@ -46024,7 +46024,7 @@
     </row>
     <row r="346" spans="1:43" ht="15.75" customHeight="1">
       <c r="A346" s="193" t="s">
-        <v>3989</v>
+        <v>4016</v>
       </c>
       <c r="B346" s="33" t="s">
         <v>434</v>
@@ -46259,7 +46259,7 @@
     </row>
     <row r="349" spans="1:43" ht="15.75" customHeight="1">
       <c r="A349" s="186" t="s">
-        <v>2860</v>
+        <v>4017</v>
       </c>
       <c r="B349" s="33" t="s">
         <v>434</v>
@@ -46270,32 +46270,32 @@
       <c r="D349" s="235"/>
       <c r="E349" s="58"/>
       <c r="F349" s="47" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="G349" s="32"/>
       <c r="H349" s="207" t="s">
+        <v>2861</v>
+      </c>
+      <c r="I349" s="187" t="s">
         <v>2862</v>
-      </c>
-      <c r="I349" s="187" t="s">
-        <v>2863</v>
       </c>
       <c r="J349" s="22"/>
       <c r="K349" s="22"/>
       <c r="L349" s="22" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="M349" s="137" t="s">
         <v>1028</v>
       </c>
       <c r="N349" s="38" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="O349" s="322" t="s">
         <v>774</v>
       </c>
       <c r="P349" s="126"/>
       <c r="Q349" s="26" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="R349" s="101" t="s">
         <v>544</v>
@@ -46336,7 +46336,7 @@
     </row>
     <row r="350" spans="1:43" ht="15.75" customHeight="1">
       <c r="A350" s="186" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="B350" s="33" t="s">
         <v>434</v>
@@ -46347,30 +46347,30 @@
       <c r="D350" s="245"/>
       <c r="E350" s="52"/>
       <c r="F350" s="16" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="G350" s="48"/>
       <c r="H350" s="32" t="s">
+        <v>2868</v>
+      </c>
+      <c r="I350" s="187" t="s">
         <v>2869</v>
-      </c>
-      <c r="I350" s="187" t="s">
-        <v>2870</v>
       </c>
       <c r="J350" s="22"/>
       <c r="K350" s="22"/>
       <c r="L350" s="22"/>
       <c r="M350" s="32" t="s">
+        <v>2870</v>
+      </c>
+      <c r="N350" s="38" t="s">
         <v>2871</v>
-      </c>
-      <c r="N350" s="38" t="s">
-        <v>2872</v>
       </c>
       <c r="O350" s="38"/>
       <c r="P350" s="74" t="s">
         <v>2370</v>
       </c>
       <c r="Q350" s="56" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="R350" s="32" t="s">
         <v>49</v>
@@ -46379,26 +46379,26 @@
         <v>41</v>
       </c>
       <c r="T350" s="88" t="s">
+        <v>2873</v>
+      </c>
+      <c r="U350" s="45" t="s">
         <v>2874</v>
       </c>
-      <c r="U350" s="45" t="s">
+      <c r="V350" s="45" t="s">
         <v>2875</v>
-      </c>
-      <c r="V350" s="45" t="s">
-        <v>2876</v>
       </c>
       <c r="W350" s="113"/>
       <c r="X350" s="120" t="s">
+        <v>2875</v>
+      </c>
+      <c r="Y350" s="30" t="s">
         <v>2876</v>
-      </c>
-      <c r="Y350" s="30" t="s">
-        <v>2877</v>
       </c>
       <c r="Z350" s="103"/>
       <c r="AA350" s="30"/>
       <c r="AB350" s="31"/>
       <c r="AC350" s="21" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="AD350" s="21"/>
       <c r="AE350" s="32"/>
@@ -46417,10 +46417,10 @@
     </row>
     <row r="351" spans="1:43" ht="15.75" customHeight="1">
       <c r="A351" s="186" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B351" s="186" t="s">
         <v>2879</v>
-      </c>
-      <c r="B351" s="186" t="s">
-        <v>2880</v>
       </c>
       <c r="C351" s="250" t="s">
         <v>171</v>
@@ -46428,11 +46428,11 @@
       <c r="D351" s="235"/>
       <c r="E351" s="58"/>
       <c r="F351" s="290" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="G351" s="32"/>
       <c r="H351" s="192" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="I351" s="192" t="s">
         <v>2506</v>
@@ -46446,7 +46446,7 @@
         <v>2693</v>
       </c>
       <c r="N351" s="38" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="O351" s="322"/>
       <c r="P351" s="126"/>
@@ -46467,11 +46467,11 @@
         <v>2237</v>
       </c>
       <c r="Y351" s="30" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="Z351" s="200"/>
       <c r="AA351" s="30" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="AB351" s="31"/>
       <c r="AC351" s="32"/>
@@ -46492,7 +46492,7 @@
     </row>
     <row r="352" spans="1:43" ht="15.75" customHeight="1">
       <c r="A352" s="186" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="B352" s="33" t="s">
         <v>434</v>
@@ -46503,23 +46503,23 @@
       <c r="D352" s="235"/>
       <c r="E352" s="58"/>
       <c r="F352" s="47" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="G352" s="32"/>
       <c r="H352" s="194" t="s">
+        <v>2887</v>
+      </c>
+      <c r="I352" s="187" t="s">
         <v>2888</v>
-      </c>
-      <c r="I352" s="187" t="s">
-        <v>2889</v>
       </c>
       <c r="J352" s="22"/>
       <c r="K352" s="22"/>
       <c r="L352" s="22"/>
       <c r="M352" s="137" t="s">
+        <v>2889</v>
+      </c>
+      <c r="N352" s="38" t="s">
         <v>2890</v>
-      </c>
-      <c r="N352" s="38" t="s">
-        <v>2891</v>
       </c>
       <c r="O352" s="38"/>
       <c r="P352" s="74" t="s">
@@ -46548,7 +46548,7 @@
         <v>2237</v>
       </c>
       <c r="Y352" s="30" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="Z352" s="30"/>
       <c r="AA352" s="30"/>
@@ -46573,7 +46573,7 @@
     </row>
     <row r="353" spans="1:43" ht="15.75" customHeight="1">
       <c r="A353" s="186" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="B353" s="33" t="s">
         <v>434</v>
@@ -46584,17 +46584,17 @@
       <c r="D353" s="235"/>
       <c r="E353" s="58"/>
       <c r="F353" s="47" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="G353" s="32"/>
       <c r="H353" s="206" t="s">
+        <v>2894</v>
+      </c>
+      <c r="I353" s="187" t="s">
         <v>2895</v>
       </c>
-      <c r="I353" s="187" t="s">
+      <c r="J353" s="82" t="s">
         <v>2896</v>
-      </c>
-      <c r="J353" s="82" t="s">
-        <v>2897</v>
       </c>
       <c r="K353" s="82"/>
       <c r="L353" s="22"/>
@@ -46602,7 +46602,7 @@
         <v>137</v>
       </c>
       <c r="N353" s="89" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="O353" s="457"/>
       <c r="P353" s="70"/>
@@ -46623,7 +46623,7 @@
         <v>2237</v>
       </c>
       <c r="Y353" s="30" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="Z353" s="103"/>
       <c r="AA353" s="30"/>
@@ -46646,7 +46646,7 @@
     </row>
     <row r="354" spans="1:43" ht="15.75" customHeight="1">
       <c r="A354" s="186" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="B354" s="33" t="s">
         <v>434</v>
@@ -46657,11 +46657,11 @@
       <c r="D354" s="235"/>
       <c r="E354" s="58"/>
       <c r="F354" s="47" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="G354" s="32"/>
       <c r="H354" s="206" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="I354" s="192" t="s">
         <v>2506</v>
@@ -46675,14 +46675,14 @@
         <v>1103</v>
       </c>
       <c r="N354" s="38" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="O354" s="38" t="s">
         <v>2112</v>
       </c>
       <c r="P354" s="74"/>
       <c r="Q354" s="26" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="R354" s="117" t="s">
         <v>544</v>
@@ -46698,14 +46698,14 @@
         <v>2237</v>
       </c>
       <c r="Y354" s="170" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Z354" s="200"/>
       <c r="AA354" s="30" t="s">
+        <v>2905</v>
+      </c>
+      <c r="AB354" s="46" t="s">
         <v>2906</v>
-      </c>
-      <c r="AB354" s="46" t="s">
-        <v>2907</v>
       </c>
       <c r="AC354" s="32"/>
       <c r="AD354" s="21"/>
@@ -46725,22 +46725,22 @@
     </row>
     <row r="355" spans="1:43" ht="135" customHeight="1">
       <c r="A355" s="186" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="B355" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C355" s="250" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="D355" s="235"/>
       <c r="E355" s="58"/>
       <c r="F355" s="47" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="G355" s="32"/>
       <c r="H355" s="206" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="I355" s="192" t="s">
         <v>2506</v>
@@ -46754,14 +46754,14 @@
         <v>1619</v>
       </c>
       <c r="N355" s="54" t="s">
+        <v>2910</v>
+      </c>
+      <c r="O355" s="54" t="s">
         <v>2911</v>
-      </c>
-      <c r="O355" s="54" t="s">
-        <v>2912</v>
       </c>
       <c r="P355" s="55"/>
       <c r="Q355" s="56" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="R355" s="32" t="s">
         <v>523</v>
@@ -46782,10 +46782,10 @@
         <v>2807</v>
       </c>
       <c r="Z355" s="30" t="s">
+        <v>2913</v>
+      </c>
+      <c r="AA355" s="30" t="s">
         <v>2914</v>
-      </c>
-      <c r="AA355" s="30" t="s">
-        <v>2915</v>
       </c>
       <c r="AB355" s="41"/>
       <c r="AC355" s="32"/>
@@ -46806,7 +46806,7 @@
     </row>
     <row r="356" spans="1:43" ht="15.75" customHeight="1">
       <c r="A356" s="186" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="B356" s="33" t="s">
         <v>434</v>
@@ -46817,11 +46817,11 @@
       <c r="D356" s="235"/>
       <c r="E356" s="58"/>
       <c r="F356" s="47" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="G356" s="32"/>
       <c r="H356" s="206" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="I356" s="192" t="s">
         <v>2506</v>
@@ -46833,14 +46833,14 @@
         <v>804</v>
       </c>
       <c r="N356" s="54" t="s">
+        <v>2918</v>
+      </c>
+      <c r="O356" s="54" t="s">
         <v>2919</v>
-      </c>
-      <c r="O356" s="54" t="s">
-        <v>2920</v>
       </c>
       <c r="P356" s="55"/>
       <c r="Q356" s="56" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="R356" s="32" t="s">
         <v>523</v>
@@ -46849,7 +46849,7 @@
         <v>41</v>
       </c>
       <c r="T356" s="21" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="U356" s="28"/>
       <c r="V356" s="28"/>
@@ -46860,13 +46860,13 @@
         <v>2237</v>
       </c>
       <c r="Y356" s="30" t="s">
+        <v>2922</v>
+      </c>
+      <c r="Z356" s="30" t="s">
         <v>2923</v>
       </c>
-      <c r="Z356" s="30" t="s">
+      <c r="AA356" s="30" t="s">
         <v>2924</v>
-      </c>
-      <c r="AA356" s="30" t="s">
-        <v>2925</v>
       </c>
       <c r="AB356" s="41"/>
       <c r="AC356" s="32"/>
@@ -46887,22 +46887,22 @@
     </row>
     <row r="357" spans="1:43" ht="15.75" customHeight="1">
       <c r="A357" s="281" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B357" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C357" s="249" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="D357" s="235"/>
       <c r="E357" s="58"/>
       <c r="F357" s="47" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="G357" s="32"/>
       <c r="H357" s="32" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="I357" s="192" t="s">
         <v>2506</v>
@@ -46916,7 +46916,7 @@
         <v>542</v>
       </c>
       <c r="N357" s="54" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="O357" s="54"/>
       <c r="P357" s="55"/>
@@ -46941,10 +46941,10 @@
       </c>
       <c r="Z357" s="30"/>
       <c r="AA357" s="30" t="s">
+        <v>2930</v>
+      </c>
+      <c r="AB357" s="41" t="s">
         <v>2931</v>
-      </c>
-      <c r="AB357" s="41" t="s">
-        <v>2932</v>
       </c>
       <c r="AC357" s="32"/>
       <c r="AD357" s="21"/>
@@ -46964,10 +46964,10 @@
     </row>
     <row r="358" spans="1:43" ht="15.75" customHeight="1">
       <c r="A358" s="186" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B358" s="186" t="s">
         <v>2933</v>
-      </c>
-      <c r="B358" s="186" t="s">
-        <v>2934</v>
       </c>
       <c r="C358" s="250" t="s">
         <v>171</v>
@@ -46975,11 +46975,11 @@
       <c r="D358" s="235"/>
       <c r="E358" s="58"/>
       <c r="F358" s="47" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="G358" s="32"/>
       <c r="H358" s="206" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="I358" s="192" t="s">
         <v>2506</v>
@@ -46988,10 +46988,10 @@
       <c r="K358" s="93"/>
       <c r="L358" s="93"/>
       <c r="M358" s="137" t="s">
+        <v>2936</v>
+      </c>
+      <c r="N358" s="65" t="s">
         <v>2937</v>
-      </c>
-      <c r="N358" s="65" t="s">
-        <v>2938</v>
       </c>
       <c r="O358" s="65"/>
       <c r="P358" s="55"/>
@@ -47012,14 +47012,14 @@
         <v>2237</v>
       </c>
       <c r="Y358" s="210" t="s">
+        <v>2938</v>
+      </c>
+      <c r="Z358" s="211" t="s">
         <v>2939</v>
-      </c>
-      <c r="Z358" s="211" t="s">
-        <v>2940</v>
       </c>
       <c r="AA358" s="211"/>
       <c r="AB358" s="31" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="AC358" s="32"/>
       <c r="AD358" s="21"/>
@@ -47039,38 +47039,38 @@
     </row>
     <row r="359" spans="1:43" ht="15.75" customHeight="1">
       <c r="A359" s="281" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="B359" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C359" s="249" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="D359" s="235"/>
       <c r="E359" s="58"/>
       <c r="F359" s="47" t="s">
+        <v>2943</v>
+      </c>
+      <c r="G359" s="32" t="s">
         <v>2944</v>
       </c>
-      <c r="G359" s="32" t="s">
+      <c r="H359" s="95" t="s">
         <v>2945</v>
-      </c>
-      <c r="H359" s="95" t="s">
-        <v>2946</v>
       </c>
       <c r="I359" s="187" t="s">
         <v>2638</v>
       </c>
       <c r="J359" s="22" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="K359" s="22"/>
       <c r="L359" s="22"/>
       <c r="M359" s="137" t="s">
+        <v>2947</v>
+      </c>
+      <c r="N359" s="136" t="s">
         <v>2948</v>
-      </c>
-      <c r="N359" s="136" t="s">
-        <v>2949</v>
       </c>
       <c r="O359" s="54"/>
       <c r="P359" s="55"/>
@@ -47082,7 +47082,7 @@
         <v>41</v>
       </c>
       <c r="T359" s="21" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="U359" s="28"/>
       <c r="V359" s="28"/>
@@ -47116,7 +47116,7 @@
     </row>
     <row r="360" spans="1:43" ht="15.75" customHeight="1">
       <c r="A360" s="186" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="B360" s="33" t="s">
         <v>434</v>
@@ -47127,11 +47127,11 @@
       <c r="D360" s="235"/>
       <c r="E360" s="58"/>
       <c r="F360" s="47" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="G360" s="32"/>
       <c r="H360" s="48" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="I360" s="187" t="s">
         <v>2506</v>
@@ -47140,17 +47140,17 @@
       <c r="K360" s="22"/>
       <c r="L360" s="22"/>
       <c r="M360" s="137" t="s">
+        <v>2953</v>
+      </c>
+      <c r="N360" s="54" t="s">
         <v>2954</v>
-      </c>
-      <c r="N360" s="54" t="s">
-        <v>2955</v>
       </c>
       <c r="O360" s="54" t="s">
         <v>1869</v>
       </c>
       <c r="P360" s="55"/>
       <c r="Q360" s="56" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="R360" s="32" t="s">
         <v>523</v>
@@ -47168,13 +47168,13 @@
         <v>2237</v>
       </c>
       <c r="Y360" s="30" t="s">
+        <v>2956</v>
+      </c>
+      <c r="Z360" s="30" t="s">
         <v>2957</v>
       </c>
-      <c r="Z360" s="30" t="s">
+      <c r="AA360" s="30" t="s">
         <v>2958</v>
-      </c>
-      <c r="AA360" s="30" t="s">
-        <v>2959</v>
       </c>
       <c r="AB360" s="110"/>
       <c r="AC360" s="32"/>
@@ -47195,7 +47195,7 @@
     </row>
     <row r="361" spans="1:43" ht="15.75" customHeight="1">
       <c r="A361" s="186" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="B361" s="33" t="s">
         <v>434</v>
@@ -47209,22 +47209,22 @@
         <v>2284</v>
       </c>
       <c r="G361" s="186" t="s">
+        <v>2960</v>
+      </c>
+      <c r="H361" s="48" t="s">
         <v>2961</v>
       </c>
-      <c r="H361" s="48" t="s">
+      <c r="I361" s="187" t="s">
         <v>2962</v>
-      </c>
-      <c r="I361" s="187" t="s">
-        <v>2963</v>
       </c>
       <c r="J361" s="22"/>
       <c r="K361" s="22"/>
       <c r="L361" s="22"/>
       <c r="M361" s="137" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="N361" s="54" t="s">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="O361" s="54"/>
       <c r="P361" s="25" t="s">
@@ -47240,7 +47240,7 @@
         <v>41</v>
       </c>
       <c r="T361" s="21" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="U361" s="28"/>
       <c r="V361" s="28"/>
@@ -47251,7 +47251,7 @@
       <c r="AA361" s="30"/>
       <c r="AB361" s="110"/>
       <c r="AC361" s="32" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="AD361" s="21"/>
       <c r="AE361" s="32"/>
@@ -47270,7 +47270,7 @@
     </row>
     <row r="362" spans="1:43" ht="15.75" customHeight="1">
       <c r="A362" s="186" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="B362" s="33" t="s">
         <v>434</v>
@@ -47281,13 +47281,13 @@
       <c r="D362" s="235"/>
       <c r="E362" s="58"/>
       <c r="F362" s="16" t="s">
+        <v>2967</v>
+      </c>
+      <c r="G362" s="48" t="s">
         <v>2968</v>
       </c>
-      <c r="G362" s="48" t="s">
+      <c r="H362" s="206" t="s">
         <v>2969</v>
-      </c>
-      <c r="H362" s="206" t="s">
-        <v>2970</v>
       </c>
       <c r="I362" s="32" t="s">
         <v>2546</v>
@@ -47296,10 +47296,10 @@
       <c r="K362" s="82"/>
       <c r="L362" s="82"/>
       <c r="M362" s="95" t="s">
+        <v>2970</v>
+      </c>
+      <c r="N362" s="54" t="s">
         <v>2971</v>
-      </c>
-      <c r="N362" s="54" t="s">
-        <v>2972</v>
       </c>
       <c r="O362" s="54"/>
       <c r="P362" s="25" t="s">
@@ -47309,7 +47309,7 @@
         <v>1905</v>
       </c>
       <c r="R362" s="77" t="s">
-        <v>3998</v>
+        <v>3996</v>
       </c>
       <c r="S362" s="77" t="s">
         <v>41</v>
@@ -47324,7 +47324,7 @@
       <c r="W362" s="113"/>
       <c r="X362" s="113"/>
       <c r="Y362" s="30" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="Z362" s="30"/>
       <c r="AA362" s="30"/>
@@ -47333,7 +47333,7 @@
         <v>1907</v>
       </c>
       <c r="AD362" s="146" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="AE362" s="32"/>
       <c r="AF362" s="32"/>
@@ -47351,7 +47351,7 @@
     </row>
     <row r="363" spans="1:43" ht="15.75" customHeight="1">
       <c r="A363" s="186" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="B363" s="33" t="s">
         <v>434</v>
@@ -47362,11 +47362,11 @@
       <c r="D363" s="235"/>
       <c r="E363" s="58"/>
       <c r="F363" s="47" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="G363" s="48"/>
       <c r="H363" s="48" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="I363" s="32" t="s">
         <v>2546</v>
@@ -47378,7 +47378,7 @@
         <v>491</v>
       </c>
       <c r="N363" s="54" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="O363" s="54"/>
       <c r="P363" s="25" t="s">
@@ -47403,7 +47403,7 @@
       <c r="W363" s="113"/>
       <c r="X363" s="113"/>
       <c r="Y363" s="30" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="Z363" s="30"/>
       <c r="AA363" s="30"/>
@@ -47428,7 +47428,7 @@
     </row>
     <row r="364" spans="1:43" ht="15.75" customHeight="1">
       <c r="A364" s="186" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="B364" s="33" t="s">
         <v>434</v>
@@ -47439,21 +47439,21 @@
       <c r="D364" s="235"/>
       <c r="E364" s="58"/>
       <c r="F364" s="16" t="s">
+        <v>2980</v>
+      </c>
+      <c r="G364" s="48" t="s">
         <v>2981</v>
       </c>
-      <c r="G364" s="48" t="s">
+      <c r="H364" s="206" t="s">
         <v>2982</v>
       </c>
-      <c r="H364" s="206" t="s">
+      <c r="I364" s="32" t="s">
         <v>2983</v>
-      </c>
-      <c r="I364" s="32" t="s">
-        <v>2984</v>
       </c>
       <c r="J364" s="22"/>
       <c r="K364" s="22"/>
       <c r="L364" s="22" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="M364" s="183" t="s">
         <v>2081</v>
@@ -47495,7 +47495,7 @@
     </row>
     <row r="365" spans="1:43" ht="15.75" customHeight="1">
       <c r="A365" s="186" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="B365" s="33" t="s">
         <v>434</v>
@@ -47506,11 +47506,11 @@
       <c r="D365" s="235"/>
       <c r="E365" s="58"/>
       <c r="F365" s="47" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="G365" s="32"/>
       <c r="H365" s="206" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="I365" s="32" t="s">
         <v>2506</v>
@@ -47522,7 +47522,7 @@
         <v>601</v>
       </c>
       <c r="N365" s="38" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="O365" s="38" t="s">
         <v>38</v>
@@ -47547,14 +47547,14 @@
         <v>2237</v>
       </c>
       <c r="Y365" s="198" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="Z365" s="490"/>
       <c r="AA365" s="198" t="s">
+        <v>2990</v>
+      </c>
+      <c r="AB365" s="31" t="s">
         <v>2991</v>
-      </c>
-      <c r="AB365" s="31" t="s">
-        <v>2992</v>
       </c>
       <c r="AC365" s="32"/>
       <c r="AD365" s="21"/>
@@ -47574,22 +47574,22 @@
     </row>
     <row r="366" spans="1:43" ht="15.75" customHeight="1">
       <c r="A366" s="282" t="s">
-        <v>3912</v>
+        <v>3911</v>
       </c>
       <c r="B366" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C366" s="249" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="D366" s="235"/>
       <c r="E366" s="58"/>
       <c r="F366" s="47" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="G366" s="32"/>
       <c r="H366" s="206" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="I366" s="192" t="s">
         <v>2506</v>
@@ -47603,7 +47603,7 @@
         <v>542</v>
       </c>
       <c r="N366" s="38" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="O366" s="38"/>
       <c r="P366" s="25"/>
@@ -47624,11 +47624,11 @@
         <v>2237</v>
       </c>
       <c r="Y366" s="30" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="Z366" s="200"/>
       <c r="AA366" s="30" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="AB366" s="41"/>
       <c r="AC366" s="32"/>
@@ -47649,7 +47649,7 @@
     </row>
     <row r="367" spans="1:43" ht="15.75" customHeight="1">
       <c r="A367" s="186" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B367" s="33" t="s">
         <v>434</v>
@@ -47660,11 +47660,11 @@
       <c r="D367" s="235"/>
       <c r="E367" s="58"/>
       <c r="F367" s="47" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="G367" s="39"/>
       <c r="H367" s="206" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="I367" s="192" t="s">
         <v>2506</v>
@@ -47672,20 +47672,20 @@
       <c r="J367" s="22"/>
       <c r="K367" s="22"/>
       <c r="L367" s="22" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="M367" s="137" t="s">
         <v>657</v>
       </c>
       <c r="N367" s="38" t="s">
+        <v>3002</v>
+      </c>
+      <c r="O367" s="38" t="s">
         <v>3003</v>
-      </c>
-      <c r="O367" s="38" t="s">
-        <v>3004</v>
       </c>
       <c r="P367" s="25"/>
       <c r="Q367" s="26" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="R367" s="39" t="s">
         <v>523</v>
@@ -47703,13 +47703,13 @@
         <v>2237</v>
       </c>
       <c r="Y367" s="30" t="s">
+        <v>3005</v>
+      </c>
+      <c r="Z367" s="30" t="s">
         <v>3006</v>
       </c>
-      <c r="Z367" s="30" t="s">
+      <c r="AA367" s="30" t="s">
         <v>3007</v>
-      </c>
-      <c r="AA367" s="30" t="s">
-        <v>3008</v>
       </c>
       <c r="AB367" s="41"/>
       <c r="AC367" s="32"/>
@@ -47730,7 +47730,7 @@
     </row>
     <row r="368" spans="1:43" ht="15.75" customHeight="1">
       <c r="A368" s="186" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B368" s="33" t="s">
         <v>434</v>
@@ -47741,11 +47741,11 @@
       <c r="D368" s="235"/>
       <c r="E368" s="58"/>
       <c r="F368" s="47" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="G368" s="39"/>
       <c r="H368" s="206" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="I368" s="192" t="s">
         <v>2506</v>
@@ -47754,17 +47754,17 @@
       <c r="K368" s="22"/>
       <c r="L368" s="22"/>
       <c r="M368" s="137" t="s">
+        <v>3011</v>
+      </c>
+      <c r="N368" s="38" t="s">
         <v>3012</v>
       </c>
-      <c r="N368" s="38" t="s">
+      <c r="O368" s="38" t="s">
         <v>3013</v>
-      </c>
-      <c r="O368" s="38" t="s">
-        <v>3014</v>
       </c>
       <c r="P368" s="25"/>
       <c r="Q368" s="26" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="R368" s="39" t="s">
         <v>523</v>
@@ -47782,13 +47782,13 @@
         <v>2237</v>
       </c>
       <c r="Y368" s="170" t="s">
+        <v>3015</v>
+      </c>
+      <c r="Z368" s="30" t="s">
         <v>3016</v>
       </c>
-      <c r="Z368" s="30" t="s">
+      <c r="AA368" s="30" t="s">
         <v>3017</v>
-      </c>
-      <c r="AA368" s="30" t="s">
-        <v>3018</v>
       </c>
       <c r="AB368" s="41"/>
       <c r="AC368" s="32"/>
@@ -47809,22 +47809,22 @@
     </row>
     <row r="369" spans="1:43" ht="15.75" customHeight="1">
       <c r="A369" s="391" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="B369" s="392" t="s">
         <v>434</v>
       </c>
       <c r="C369" s="266" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="D369" s="393"/>
       <c r="E369" s="394"/>
       <c r="F369" s="395" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="G369" s="396"/>
       <c r="H369" s="411" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="I369" s="397" t="s">
         <v>2506</v>
@@ -47833,10 +47833,10 @@
       <c r="K369" s="399"/>
       <c r="L369" s="398"/>
       <c r="M369" s="400" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="N369" s="401" t="s">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="O369" s="401" t="s">
         <v>38</v>
@@ -47855,25 +47855,25 @@
       <c r="U369" s="412"/>
       <c r="V369" s="406"/>
       <c r="W369" s="407" t="s">
+        <v>3022</v>
+      </c>
+      <c r="X369" s="407" t="s">
         <v>3023</v>
       </c>
-      <c r="X369" s="407" t="s">
+      <c r="Y369" s="408" t="s">
         <v>3024</v>
       </c>
-      <c r="Y369" s="408" t="s">
+      <c r="Z369" s="494" t="s">
         <v>3025</v>
       </c>
-      <c r="Z369" s="494" t="s">
+      <c r="AA369" s="408" t="s">
         <v>3026</v>
       </c>
-      <c r="AA369" s="408" t="s">
-        <v>3027</v>
-      </c>
       <c r="AB369" s="409" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="AC369" s="413" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="AD369" s="405"/>
       <c r="AE369" s="32"/>
@@ -47892,22 +47892,22 @@
     </row>
     <row r="370" spans="1:43" ht="15.75" customHeight="1">
       <c r="A370" s="281" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="B370" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C370" s="249" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="D370" s="235"/>
       <c r="E370" s="58"/>
       <c r="F370" s="47" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="G370" s="39"/>
       <c r="H370" s="206" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="I370" s="32" t="s">
         <v>2506</v>
@@ -47919,7 +47919,7 @@
         <v>804</v>
       </c>
       <c r="N370" s="54" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="O370" s="38" t="s">
         <v>38</v>
@@ -47944,15 +47944,15 @@
         <v>2237</v>
       </c>
       <c r="Y370" s="198" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="Z370" s="200"/>
       <c r="AA370" s="389" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="AB370" s="497"/>
       <c r="AC370" s="16" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="AD370" s="21"/>
       <c r="AE370" s="32"/>
@@ -47971,42 +47971,42 @@
     </row>
     <row r="371" spans="1:43" ht="15.75" customHeight="1">
       <c r="A371" s="281" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="B371" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C371" s="249" t="s">
+        <v>3036</v>
+      </c>
+      <c r="D371" s="234" t="s">
+        <v>3028</v>
+      </c>
+      <c r="E371" s="58" t="s">
         <v>3037</v>
       </c>
-      <c r="D371" s="234" t="s">
-        <v>3029</v>
-      </c>
-      <c r="E371" s="58" t="s">
+      <c r="F371" s="47" t="s">
         <v>3038</v>
       </c>
-      <c r="F371" s="47" t="s">
+      <c r="G371" s="32" t="s">
         <v>3039</v>
       </c>
-      <c r="G371" s="32" t="s">
+      <c r="H371" s="48" t="s">
         <v>3040</v>
       </c>
-      <c r="H371" s="48" t="s">
+      <c r="I371" s="187" t="s">
         <v>3041</v>
       </c>
-      <c r="I371" s="187" t="s">
-        <v>3042</v>
-      </c>
       <c r="J371" s="22" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="K371" s="22"/>
       <c r="L371" s="22"/>
       <c r="M371" s="137" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N371" s="136" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="O371" s="54"/>
       <c r="P371" s="55"/>
@@ -48050,22 +48050,22 @@
     </row>
     <row r="372" spans="1:43" ht="15.75" customHeight="1">
       <c r="A372" s="281" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B372" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C372" s="249" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="D372" s="235"/>
       <c r="E372" s="58"/>
       <c r="F372" s="16" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="G372" s="39"/>
       <c r="H372" s="206" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="I372" s="192" t="s">
         <v>2506</v>
@@ -48073,13 +48073,13 @@
       <c r="J372" s="82"/>
       <c r="K372" s="82"/>
       <c r="L372" s="82" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="M372" s="212" t="s">
         <v>542</v>
       </c>
       <c r="N372" s="54" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="O372" s="54"/>
       <c r="P372" s="55"/>
@@ -48100,13 +48100,13 @@
         <v>2237</v>
       </c>
       <c r="Y372" s="30" t="s">
+        <v>3049</v>
+      </c>
+      <c r="Z372" s="30" t="s">
         <v>3050</v>
       </c>
-      <c r="Z372" s="30" t="s">
+      <c r="AA372" s="30" t="s">
         <v>3051</v>
-      </c>
-      <c r="AA372" s="30" t="s">
-        <v>3052</v>
       </c>
       <c r="AB372" s="110"/>
       <c r="AC372" s="32"/>
@@ -48127,7 +48127,7 @@
     </row>
     <row r="373" spans="1:43" ht="15.75" customHeight="1">
       <c r="A373" s="186" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="B373" s="33" t="s">
         <v>434</v>
@@ -48138,19 +48138,19 @@
       <c r="D373" s="235"/>
       <c r="E373" s="58"/>
       <c r="F373" s="47" t="s">
+        <v>3053</v>
+      </c>
+      <c r="G373" s="32" t="s">
         <v>3054</v>
       </c>
-      <c r="G373" s="32" t="s">
+      <c r="H373" s="206" t="s">
         <v>3055</v>
       </c>
-      <c r="H373" s="206" t="s">
+      <c r="I373" s="32" t="s">
         <v>3056</v>
       </c>
-      <c r="I373" s="32" t="s">
+      <c r="J373" s="104" t="s">
         <v>3057</v>
-      </c>
-      <c r="J373" s="104" t="s">
-        <v>3058</v>
       </c>
       <c r="K373" s="104"/>
       <c r="L373" s="104"/>
@@ -48158,7 +48158,7 @@
         <v>137</v>
       </c>
       <c r="N373" s="54" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="O373" s="54"/>
       <c r="P373" s="55"/>
@@ -48202,22 +48202,22 @@
     </row>
     <row r="374" spans="1:43" ht="15.75" customHeight="1">
       <c r="A374" s="186" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B374" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C374" s="249" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="D374" s="235"/>
       <c r="E374" s="58"/>
       <c r="F374" s="47" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="G374" s="39"/>
       <c r="H374" s="206" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="I374" s="192" t="s">
         <v>2506</v>
@@ -48231,14 +48231,14 @@
         <v>899</v>
       </c>
       <c r="N374" s="54" t="s">
+        <v>3063</v>
+      </c>
+      <c r="O374" s="54" t="s">
         <v>3064</v>
-      </c>
-      <c r="O374" s="54" t="s">
-        <v>3065</v>
       </c>
       <c r="P374" s="55"/>
       <c r="Q374" s="56" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="R374" s="39" t="s">
         <v>523</v>
@@ -48256,13 +48256,13 @@
         <v>2237</v>
       </c>
       <c r="Y374" s="30" t="s">
+        <v>3066</v>
+      </c>
+      <c r="Z374" s="103" t="s">
         <v>3067</v>
       </c>
-      <c r="Z374" s="103" t="s">
+      <c r="AA374" s="30" t="s">
         <v>3068</v>
-      </c>
-      <c r="AA374" s="30" t="s">
-        <v>3069</v>
       </c>
       <c r="AB374" s="41"/>
       <c r="AC374" s="32"/>
@@ -48283,36 +48283,36 @@
     </row>
     <row r="375" spans="1:43" ht="15.75" customHeight="1">
       <c r="A375" s="186" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="B375" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C375" s="249" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="D375" s="235"/>
       <c r="E375" s="58"/>
       <c r="F375" s="16" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="G375" s="32"/>
       <c r="H375" s="206" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="I375" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J375" s="82" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="K375" s="82"/>
       <c r="L375" s="82"/>
       <c r="M375" s="115" t="s">
+        <v>3074</v>
+      </c>
+      <c r="N375" s="54" t="s">
         <v>3075</v>
-      </c>
-      <c r="N375" s="54" t="s">
-        <v>3076</v>
       </c>
       <c r="O375" s="322" t="s">
         <v>38</v>
@@ -48337,15 +48337,15 @@
         <v>2237</v>
       </c>
       <c r="Y375" s="491" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="Z375" s="490"/>
       <c r="AA375" s="30" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="AB375" s="41"/>
       <c r="AC375" s="66" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="AD375" s="21"/>
       <c r="AE375" s="32"/>
@@ -48364,7 +48364,7 @@
     </row>
     <row r="376" spans="1:43" ht="48" customHeight="1">
       <c r="A376" s="418" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="B376" s="33" t="s">
         <v>434</v>
@@ -48374,14 +48374,14 @@
       </c>
       <c r="E376" s="230"/>
       <c r="F376" s="433" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="G376" s="230"/>
       <c r="H376" s="423" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="I376" s="423" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="J376" s="230"/>
       <c r="K376" s="230"/>
@@ -48402,7 +48402,7 @@
         <v>41</v>
       </c>
       <c r="T376" s="423" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="U376" s="230"/>
       <c r="V376" s="230"/>
@@ -48414,7 +48414,7 @@
       <c r="AB376" s="230"/>
       <c r="AC376" s="230"/>
       <c r="AD376" s="423" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="AE376" s="230"/>
       <c r="AF376" s="230"/>
@@ -48432,7 +48432,7 @@
     </row>
     <row r="377" spans="1:43" ht="15.75" customHeight="1">
       <c r="A377" s="186" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="B377" s="33" t="s">
         <v>434</v>
@@ -48443,11 +48443,11 @@
       <c r="D377" s="235"/>
       <c r="E377" s="58"/>
       <c r="F377" s="290" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="G377" s="32"/>
       <c r="H377" s="206" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="I377" s="32" t="s">
         <v>2506</v>
@@ -48458,17 +48458,17 @@
         <v>424</v>
       </c>
       <c r="M377" s="137" t="s">
+        <v>3084</v>
+      </c>
+      <c r="N377" s="54" t="s">
         <v>3085</v>
-      </c>
-      <c r="N377" s="54" t="s">
-        <v>3086</v>
       </c>
       <c r="O377" s="54"/>
       <c r="P377" s="74" t="s">
+        <v>3086</v>
+      </c>
+      <c r="Q377" s="56" t="s">
         <v>3087</v>
-      </c>
-      <c r="Q377" s="56" t="s">
-        <v>3088</v>
       </c>
       <c r="R377" s="94" t="s">
         <v>544</v>
@@ -48490,7 +48490,7 @@
       </c>
       <c r="Z377" s="490"/>
       <c r="AA377" s="198" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="AB377" s="110"/>
       <c r="AC377" s="32"/>
@@ -48511,7 +48511,7 @@
     </row>
     <row r="378" spans="1:43" ht="15.75" customHeight="1">
       <c r="A378" s="186" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="B378" s="33" t="s">
         <v>434</v>
@@ -48522,11 +48522,11 @@
       <c r="D378" s="235"/>
       <c r="E378" s="58"/>
       <c r="F378" s="47" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="G378" s="32"/>
       <c r="H378" s="206" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="I378" s="192" t="s">
         <v>2506</v>
@@ -48534,13 +48534,13 @@
       <c r="J378" s="35"/>
       <c r="K378" s="109"/>
       <c r="L378" s="109" t="s">
+        <v>3092</v>
+      </c>
+      <c r="M378" s="137" t="s">
         <v>3093</v>
       </c>
-      <c r="M378" s="137" t="s">
+      <c r="N378" s="38" t="s">
         <v>3094</v>
-      </c>
-      <c r="N378" s="38" t="s">
-        <v>3095</v>
       </c>
       <c r="O378" s="38"/>
       <c r="P378" s="25"/>
@@ -48565,10 +48565,10 @@
       </c>
       <c r="Z378" s="200"/>
       <c r="AA378" s="200" t="s">
+        <v>3095</v>
+      </c>
+      <c r="AB378" s="110" t="s">
         <v>3096</v>
-      </c>
-      <c r="AB378" s="110" t="s">
-        <v>3097</v>
       </c>
       <c r="AC378" s="32"/>
       <c r="AD378" s="21"/>
@@ -48588,7 +48588,7 @@
     </row>
     <row r="379" spans="1:43" ht="15.75" customHeight="1">
       <c r="A379" s="186" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="B379" s="33" t="s">
         <v>434</v>
@@ -48599,11 +48599,11 @@
       <c r="D379" s="235"/>
       <c r="E379" s="58"/>
       <c r="F379" s="47" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="G379" s="32"/>
       <c r="H379" s="206" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="I379" s="192" t="s">
         <v>2506</v>
@@ -48612,17 +48612,17 @@
       <c r="K379" s="82"/>
       <c r="L379" s="82"/>
       <c r="M379" s="137" t="s">
+        <v>3100</v>
+      </c>
+      <c r="N379" s="54" t="s">
         <v>3101</v>
       </c>
-      <c r="N379" s="54" t="s">
+      <c r="O379" s="458" t="s">
         <v>3102</v>
-      </c>
-      <c r="O379" s="458" t="s">
-        <v>3103</v>
       </c>
       <c r="P379" s="114"/>
       <c r="Q379" s="56" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="R379" s="39" t="s">
         <v>523</v>
@@ -48640,13 +48640,13 @@
         <v>2237</v>
       </c>
       <c r="Y379" s="170" t="s">
+        <v>3104</v>
+      </c>
+      <c r="Z379" s="30" t="s">
         <v>3105</v>
       </c>
-      <c r="Z379" s="30" t="s">
+      <c r="AA379" s="30" t="s">
         <v>3106</v>
-      </c>
-      <c r="AA379" s="30" t="s">
-        <v>3107</v>
       </c>
       <c r="AB379" s="110"/>
       <c r="AC379" s="32"/>
@@ -48667,22 +48667,22 @@
     </row>
     <row r="380" spans="1:43" ht="15.75" customHeight="1">
       <c r="A380" s="281" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="B380" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C380" s="249" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="D380" s="235"/>
       <c r="E380" s="58"/>
       <c r="F380" s="16" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="G380" s="32"/>
       <c r="H380" s="206" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="I380" s="192" t="s">
         <v>2506</v>
@@ -48690,22 +48690,22 @@
       <c r="J380" s="82"/>
       <c r="K380" s="82"/>
       <c r="L380" s="82" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="M380" s="137" t="s">
         <v>899</v>
       </c>
       <c r="N380" s="38" t="s">
+        <v>3112</v>
+      </c>
+      <c r="O380" s="38" t="s">
         <v>3113</v>
       </c>
-      <c r="O380" s="38" t="s">
+      <c r="P380" s="74" t="s">
         <v>3114</v>
       </c>
-      <c r="P380" s="74" t="s">
+      <c r="Q380" s="56" t="s">
         <v>3115</v>
-      </c>
-      <c r="Q380" s="56" t="s">
-        <v>3116</v>
       </c>
       <c r="R380" s="39" t="s">
         <v>523</v>
@@ -48723,13 +48723,13 @@
         <v>2237</v>
       </c>
       <c r="Y380" s="170" t="s">
+        <v>3116</v>
+      </c>
+      <c r="Z380" s="103" t="s">
         <v>3117</v>
       </c>
-      <c r="Z380" s="103" t="s">
+      <c r="AA380" s="30" t="s">
         <v>3118</v>
-      </c>
-      <c r="AA380" s="30" t="s">
-        <v>3119</v>
       </c>
       <c r="AB380" s="110"/>
       <c r="AC380" s="32"/>
@@ -48750,7 +48750,7 @@
     </row>
     <row r="381" spans="1:43" s="387" customFormat="1" ht="15.75" customHeight="1">
       <c r="A381" s="186" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B381" s="33" t="s">
         <v>434</v>
@@ -48761,11 +48761,11 @@
       <c r="D381" s="235"/>
       <c r="E381" s="58"/>
       <c r="F381" s="437" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="G381" s="32"/>
       <c r="H381" s="206" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="I381" s="32" t="s">
         <v>2506</v>
@@ -48773,13 +48773,13 @@
       <c r="J381" s="98"/>
       <c r="K381" s="104"/>
       <c r="L381" s="104" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="M381" s="137" t="s">
         <v>542</v>
       </c>
       <c r="N381" s="54" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="O381" s="54"/>
       <c r="P381" s="55"/>
@@ -48804,11 +48804,11 @@
       </c>
       <c r="Z381" s="495"/>
       <c r="AA381" s="214" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="AB381" s="110"/>
       <c r="AC381" s="47" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="AD381" s="21"/>
       <c r="AE381" s="377"/>
@@ -48827,7 +48827,7 @@
     </row>
     <row r="382" spans="1:43" ht="15.75" customHeight="1">
       <c r="A382" s="373" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="B382" s="366" t="s">
         <v>434</v>
@@ -48836,11 +48836,11 @@
       <c r="D382" s="375"/>
       <c r="E382" s="376"/>
       <c r="F382" s="436" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="G382" s="377"/>
       <c r="H382" s="378" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="I382" s="378" t="s">
         <v>2506</v>
@@ -48849,10 +48849,10 @@
       <c r="K382" s="379"/>
       <c r="L382" s="379"/>
       <c r="M382" s="380" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="N382" s="370" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="O382" s="370"/>
       <c r="P382" s="371"/>
@@ -48871,10 +48871,10 @@
         <v>2237</v>
       </c>
       <c r="Y382" s="385" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="Z382" s="390" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="AA382" s="386"/>
       <c r="AB382" s="501"/>
@@ -48896,22 +48896,22 @@
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
       <c r="A383" s="281" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C383" s="249" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="D383" s="235"/>
       <c r="E383" s="58"/>
       <c r="F383" s="16" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="G383" s="39"/>
       <c r="H383" s="206" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="I383" s="192" t="s">
         <v>2506</v>
@@ -48920,10 +48920,10 @@
       <c r="K383" s="82"/>
       <c r="L383" s="22"/>
       <c r="M383" s="137" t="s">
+        <v>3129</v>
+      </c>
+      <c r="N383" s="54" t="s">
         <v>3130</v>
-      </c>
-      <c r="N383" s="54" t="s">
-        <v>3131</v>
       </c>
       <c r="O383" s="54" t="s">
         <v>38</v>
@@ -48952,7 +48952,7 @@
       </c>
       <c r="Z383" s="30"/>
       <c r="AA383" s="30" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="AB383" s="41"/>
       <c r="AC383" s="32"/>
@@ -48973,13 +48973,13 @@
     </row>
     <row r="384" spans="1:43" ht="15.75" customHeight="1">
       <c r="A384" s="282" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="B384" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C384" s="249" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="D384" s="235"/>
       <c r="E384" s="58"/>
@@ -48991,7 +48991,7 @@
         <v>2618</v>
       </c>
       <c r="I384" s="192" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="J384" s="98"/>
       <c r="K384" s="82"/>
@@ -49002,7 +49002,7 @@
         <v>863</v>
       </c>
       <c r="N384" s="54" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="O384" s="54"/>
       <c r="P384" s="55"/>
@@ -49014,7 +49014,7 @@
         <v>41</v>
       </c>
       <c r="T384" s="21" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="U384" s="28"/>
       <c r="V384" s="28"/>
@@ -49042,13 +49042,13 @@
     </row>
     <row r="385" spans="1:43" ht="15.75" customHeight="1">
       <c r="A385" s="282" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="B385" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C385" s="249" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="D385" s="235"/>
       <c r="E385" s="58"/>
@@ -49057,10 +49057,10 @@
       </c>
       <c r="G385" s="39"/>
       <c r="H385" s="206" t="s">
+        <v>3136</v>
+      </c>
+      <c r="I385" s="192" t="s">
         <v>3137</v>
-      </c>
-      <c r="I385" s="192" t="s">
-        <v>3138</v>
       </c>
       <c r="J385" s="35"/>
       <c r="K385" s="109"/>
@@ -49071,7 +49071,7 @@
         <v>863</v>
       </c>
       <c r="N385" s="54" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="O385" s="54"/>
       <c r="P385" s="55"/>
@@ -49083,7 +49083,7 @@
         <v>41</v>
       </c>
       <c r="T385" s="21" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="U385" s="28"/>
       <c r="V385" s="28"/>
@@ -49111,22 +49111,22 @@
     </row>
     <row r="386" spans="1:43" ht="15.75" customHeight="1">
       <c r="A386" s="281" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="B386" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C386" s="249" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="D386" s="235"/>
       <c r="E386" s="58"/>
       <c r="F386" s="16" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="G386" s="39"/>
       <c r="H386" s="206" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="I386" s="192" t="s">
         <v>2506</v>
@@ -49159,7 +49159,7 @@
       <c r="Y386" s="30"/>
       <c r="Z386" s="30"/>
       <c r="AA386" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="AB386" s="41"/>
       <c r="AC386" s="32"/>
@@ -49180,22 +49180,22 @@
     </row>
     <row r="387" spans="1:43" ht="15.75" customHeight="1">
       <c r="A387" s="281" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="B387" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C387" s="249" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="D387" s="235"/>
       <c r="E387" s="58"/>
       <c r="F387" s="47" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="G387" s="39"/>
       <c r="H387" s="206" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="I387" s="192" t="s">
         <v>2506</v>
@@ -49206,10 +49206,10 @@
       <c r="K387" s="22"/>
       <c r="L387" s="22"/>
       <c r="M387" s="215" t="s">
+        <v>3148</v>
+      </c>
+      <c r="N387" s="38" t="s">
         <v>3149</v>
-      </c>
-      <c r="N387" s="38" t="s">
-        <v>3150</v>
       </c>
       <c r="O387" s="38"/>
       <c r="P387" s="55"/>
@@ -49224,17 +49224,17 @@
       <c r="U387" s="28"/>
       <c r="V387" s="28"/>
       <c r="W387" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X387" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X387" s="29" t="s">
+      <c r="Y387" s="30" t="s">
         <v>3152</v>
-      </c>
-      <c r="Y387" s="30" t="s">
-        <v>3153</v>
       </c>
       <c r="Z387" s="30"/>
       <c r="AA387" s="30" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="AB387" s="41"/>
       <c r="AC387" s="32"/>
@@ -49255,22 +49255,22 @@
     </row>
     <row r="388" spans="1:43" ht="15.75" customHeight="1">
       <c r="A388" s="282" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="B388" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C388" s="260" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="D388" s="235"/>
       <c r="E388" s="58"/>
       <c r="F388" s="47" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="G388" s="32"/>
       <c r="H388" s="48" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="I388" s="32" t="s">
         <v>2506</v>
@@ -49278,13 +49278,13 @@
       <c r="J388" s="104"/>
       <c r="K388" s="104"/>
       <c r="L388" s="104" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="M388" s="137" t="s">
         <v>657</v>
       </c>
       <c r="N388" s="54" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="O388" s="54"/>
       <c r="P388" s="55"/>
@@ -49296,25 +49296,25 @@
         <v>41</v>
       </c>
       <c r="T388" s="21" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="U388" s="28"/>
       <c r="V388" s="28"/>
       <c r="W388" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X388" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X388" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y388" s="30" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="Z388" s="30"/>
       <c r="AA388" s="30" t="s">
+        <v>3161</v>
+      </c>
+      <c r="AB388" s="46" t="s">
         <v>3162</v>
-      </c>
-      <c r="AB388" s="46" t="s">
-        <v>3163</v>
       </c>
       <c r="AC388" s="32"/>
       <c r="AD388" s="21"/>
@@ -49334,29 +49334,29 @@
     </row>
     <row r="389" spans="1:43" ht="45.75" customHeight="1">
       <c r="A389" s="417" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B389" s="421" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="C389" s="262" t="s">
         <v>171</v>
       </c>
       <c r="E389" s="230"/>
       <c r="F389" s="433" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="G389" s="230"/>
       <c r="H389" s="440" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="I389" s="440" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="J389" s="230"/>
       <c r="K389" s="230"/>
       <c r="L389" s="230" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="M389" s="450" t="s">
         <v>2081</v>
@@ -49374,7 +49374,7 @@
         <v>41</v>
       </c>
       <c r="T389" s="423" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="U389" s="230"/>
       <c r="V389" s="230"/>
@@ -49386,7 +49386,7 @@
       <c r="AB389" s="230"/>
       <c r="AC389" s="230"/>
       <c r="AD389" s="423" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="AE389" s="230"/>
       <c r="AF389" s="230"/>
@@ -49404,7 +49404,7 @@
     </row>
     <row r="390" spans="1:43" ht="15.75" customHeight="1">
       <c r="A390" s="186" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="B390" s="33" t="s">
         <v>434</v>
@@ -49415,25 +49415,25 @@
       <c r="D390" s="235"/>
       <c r="E390" s="58"/>
       <c r="F390" s="290" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="G390" s="32"/>
       <c r="H390" s="48" t="s">
+        <v>3167</v>
+      </c>
+      <c r="I390" s="187" t="s">
         <v>3168</v>
       </c>
-      <c r="I390" s="187" t="s">
+      <c r="J390" s="82" t="s">
         <v>3169</v>
-      </c>
-      <c r="J390" s="82" t="s">
-        <v>3170</v>
       </c>
       <c r="K390" s="82"/>
       <c r="L390" s="22"/>
       <c r="M390" s="212" t="s">
+        <v>3170</v>
+      </c>
+      <c r="N390" s="54" t="s">
         <v>3171</v>
-      </c>
-      <c r="N390" s="54" t="s">
-        <v>3172</v>
       </c>
       <c r="O390" s="458"/>
       <c r="P390" s="114"/>
@@ -49448,13 +49448,13 @@
       <c r="U390" s="28"/>
       <c r="V390" s="28"/>
       <c r="W390" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X390" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X390" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y390" s="30" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="Z390" s="30"/>
       <c r="AA390" s="30"/>
@@ -49477,7 +49477,7 @@
     </row>
     <row r="391" spans="1:43" ht="15.75" customHeight="1">
       <c r="A391" s="186" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B391" s="33" t="s">
         <v>434</v>
@@ -49488,11 +49488,11 @@
       <c r="D391" s="235"/>
       <c r="E391" s="58"/>
       <c r="F391" s="16" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="G391" s="32"/>
       <c r="H391" s="192" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="I391" s="32" t="s">
         <v>2546</v>
@@ -49500,20 +49500,20 @@
       <c r="J391" s="98"/>
       <c r="K391" s="165"/>
       <c r="L391" s="196" t="s">
+        <v>3176</v>
+      </c>
+      <c r="M391" s="137" t="s">
         <v>3177</v>
       </c>
-      <c r="M391" s="137" t="s">
+      <c r="N391" s="136" t="s">
         <v>3178</v>
-      </c>
-      <c r="N391" s="136" t="s">
-        <v>3179</v>
       </c>
       <c r="O391" s="136"/>
       <c r="P391" s="74" t="s">
+        <v>3179</v>
+      </c>
+      <c r="Q391" s="56" t="s">
         <v>3180</v>
-      </c>
-      <c r="Q391" s="56" t="s">
-        <v>3181</v>
       </c>
       <c r="R391" s="333" t="s">
         <v>40</v>
@@ -49531,19 +49531,19 @@
         <v>2629</v>
       </c>
       <c r="W391" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X391" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X391" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y391" s="30" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="Z391" s="30"/>
       <c r="AA391" s="30"/>
       <c r="AB391" s="41"/>
       <c r="AC391" s="32" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="AD391" s="21"/>
       <c r="AE391" s="32"/>
@@ -49562,7 +49562,7 @@
     </row>
     <row r="392" spans="1:43" ht="15.75" customHeight="1">
       <c r="A392" s="193" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="B392" s="33" t="s">
         <v>434</v>
@@ -49573,11 +49573,11 @@
       <c r="D392" s="235"/>
       <c r="E392" s="58"/>
       <c r="F392" s="290" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="G392" s="32"/>
       <c r="H392" s="206" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="I392" s="192" t="s">
         <v>2506</v>
@@ -49589,7 +49589,7 @@
         <v>888</v>
       </c>
       <c r="N392" s="54" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="O392" s="54"/>
       <c r="P392" s="55"/>
@@ -49604,19 +49604,19 @@
       <c r="U392" s="28"/>
       <c r="V392" s="28"/>
       <c r="W392" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X392" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X392" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y392" s="30" t="s">
+        <v>3187</v>
+      </c>
+      <c r="Z392" s="30" t="s">
         <v>3188</v>
       </c>
-      <c r="Z392" s="30" t="s">
+      <c r="AA392" s="30" t="s">
         <v>3189</v>
-      </c>
-      <c r="AA392" s="30" t="s">
-        <v>3190</v>
       </c>
       <c r="AB392" s="41"/>
       <c r="AC392" s="32"/>
@@ -49637,7 +49637,7 @@
     </row>
     <row r="393" spans="1:43" ht="15.75" customHeight="1">
       <c r="A393" s="416" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="B393" s="420" t="s">
         <v>434</v>
@@ -49648,11 +49648,11 @@
       <c r="D393" s="337"/>
       <c r="E393" s="138"/>
       <c r="F393" s="432" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="G393" s="32"/>
       <c r="H393" s="439" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="I393" s="39" t="s">
         <v>2506</v>
@@ -49660,13 +49660,13 @@
       <c r="J393" s="82"/>
       <c r="K393" s="82"/>
       <c r="L393" s="82" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="M393" s="137" t="s">
         <v>542</v>
       </c>
       <c r="N393" s="458" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="O393" s="458"/>
       <c r="P393" s="114"/>
@@ -49678,7 +49678,7 @@
         <v>41</v>
       </c>
       <c r="T393" s="105" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="U393" s="483"/>
       <c r="V393" s="483"/>
@@ -49689,11 +49689,11 @@
         <v>2237</v>
       </c>
       <c r="Y393" s="103" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="Z393" s="103"/>
       <c r="AA393" s="103" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="AB393" s="497"/>
       <c r="AC393" s="39"/>
@@ -49714,7 +49714,7 @@
     </row>
     <row r="394" spans="1:43" ht="15.75" customHeight="1">
       <c r="A394" s="186" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="B394" s="33" t="s">
         <v>434</v>
@@ -49725,17 +49725,17 @@
       <c r="D394" s="235"/>
       <c r="E394" s="58"/>
       <c r="F394" s="47" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="G394" s="32"/>
       <c r="H394" s="206" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="I394" s="32" t="s">
         <v>2506</v>
       </c>
       <c r="J394" s="22" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="K394" s="22"/>
       <c r="L394" s="22"/>
@@ -49743,7 +49743,7 @@
         <v>542</v>
       </c>
       <c r="N394" s="54" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="O394" s="54"/>
       <c r="P394" s="55"/>
@@ -49755,22 +49755,22 @@
         <v>41</v>
       </c>
       <c r="T394" s="21" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="U394" s="28"/>
       <c r="V394" s="28"/>
       <c r="W394" s="72" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X394" s="72" t="s">
         <v>3151</v>
       </c>
-      <c r="X394" s="72" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y394" s="198" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="Z394" s="198"/>
       <c r="AA394" s="30" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="AB394" s="41"/>
       <c r="AC394" s="32"/>
@@ -49791,7 +49791,7 @@
     </row>
     <row r="395" spans="1:43" ht="15.75" customHeight="1">
       <c r="A395" s="186" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B395" s="33" t="s">
         <v>434</v>
@@ -49802,29 +49802,29 @@
       <c r="D395" s="245"/>
       <c r="E395" s="52"/>
       <c r="F395" s="16" t="s">
+        <v>3204</v>
+      </c>
+      <c r="G395" s="48" t="s">
         <v>3205</v>
       </c>
-      <c r="G395" s="48" t="s">
+      <c r="H395" s="48" t="s">
         <v>3206</v>
-      </c>
-      <c r="H395" s="48" t="s">
-        <v>3207</v>
       </c>
       <c r="I395" s="187" t="s">
         <v>2506</v>
       </c>
       <c r="J395" s="82"/>
       <c r="K395" s="82" t="s">
+        <v>3207</v>
+      </c>
+      <c r="L395" s="82" t="s">
         <v>3208</v>
       </c>
-      <c r="L395" s="82" t="s">
+      <c r="M395" s="95" t="s">
+        <v>3952</v>
+      </c>
+      <c r="N395" s="54" t="s">
         <v>3209</v>
-      </c>
-      <c r="M395" s="95" t="s">
-        <v>3953</v>
-      </c>
-      <c r="N395" s="54" t="s">
-        <v>3210</v>
       </c>
       <c r="O395" s="54"/>
       <c r="P395" s="55"/>
@@ -49862,38 +49862,38 @@
     </row>
     <row r="396" spans="1:43" ht="15.75" customHeight="1">
       <c r="A396" s="281" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="B396" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C396" s="251" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="D396" s="235"/>
       <c r="E396" s="58"/>
       <c r="F396" s="16" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="G396" s="32"/>
       <c r="H396" s="206" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="I396" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J396" s="35"/>
       <c r="K396" s="22" t="s">
+        <v>3212</v>
+      </c>
+      <c r="L396" s="22" t="s">
+        <v>3169</v>
+      </c>
+      <c r="M396" s="137" t="s">
         <v>3213</v>
       </c>
-      <c r="L396" s="22" t="s">
-        <v>3170</v>
-      </c>
-      <c r="M396" s="137" t="s">
+      <c r="N396" s="54" t="s">
         <v>3214</v>
-      </c>
-      <c r="N396" s="54" t="s">
-        <v>3215</v>
       </c>
       <c r="O396" s="54"/>
       <c r="P396" s="55"/>
@@ -49908,20 +49908,20 @@
       <c r="U396" s="28"/>
       <c r="V396" s="28"/>
       <c r="W396" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X396" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X396" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y396" s="170" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="Z396" s="103"/>
       <c r="AA396" s="30" t="s">
+        <v>3216</v>
+      </c>
+      <c r="AB396" s="46" t="s">
         <v>3217</v>
-      </c>
-      <c r="AB396" s="46" t="s">
-        <v>3218</v>
       </c>
       <c r="AC396" s="32"/>
       <c r="AD396" s="21"/>
@@ -49941,7 +49941,7 @@
     </row>
     <row r="397" spans="1:43" ht="41.25" customHeight="1">
       <c r="A397" s="186" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="B397" s="33" t="s">
         <v>434</v>
@@ -49952,25 +49952,25 @@
       <c r="D397" s="235"/>
       <c r="E397" s="58"/>
       <c r="F397" s="290" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="G397" s="32"/>
       <c r="H397" s="206" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="I397" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J397" s="68" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="K397" s="109"/>
       <c r="L397" s="109"/>
       <c r="M397" s="137" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="N397" s="54" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="O397" s="54"/>
       <c r="P397" s="55"/>
@@ -49985,26 +49985,26 @@
       <c r="U397" s="28"/>
       <c r="V397" s="28"/>
       <c r="W397" s="29" t="s">
+        <v>3223</v>
+      </c>
+      <c r="X397" s="29" t="s">
         <v>3224</v>
       </c>
-      <c r="X397" s="29" t="s">
+      <c r="Y397" s="198" t="s">
         <v>3225</v>
-      </c>
-      <c r="Y397" s="198" t="s">
-        <v>3226</v>
       </c>
       <c r="Z397" s="200"/>
       <c r="AA397" s="198" t="s">
+        <v>3226</v>
+      </c>
+      <c r="AB397" s="46" t="s">
         <v>3227</v>
       </c>
-      <c r="AB397" s="46" t="s">
+      <c r="AC397" s="47" t="s">
         <v>3228</v>
       </c>
-      <c r="AC397" s="47" t="s">
+      <c r="AD397" s="21" t="s">
         <v>3229</v>
-      </c>
-      <c r="AD397" s="21" t="s">
-        <v>3230</v>
       </c>
       <c r="AE397" s="32"/>
       <c r="AF397" s="32"/>
@@ -50022,7 +50022,7 @@
     </row>
     <row r="398" spans="1:43" ht="15.75" customHeight="1">
       <c r="A398" s="282" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="B398" s="33" t="s">
         <v>434</v>
@@ -50033,11 +50033,11 @@
       <c r="D398" s="235"/>
       <c r="E398" s="58"/>
       <c r="F398" s="290" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="G398" s="32"/>
       <c r="H398" s="292" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="I398" s="192" t="s">
         <v>2506</v>
@@ -50046,10 +50046,10 @@
       <c r="K398" s="22"/>
       <c r="L398" s="22"/>
       <c r="M398" s="137" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="N398" s="54" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="O398" s="54"/>
       <c r="P398" s="216"/>
@@ -50087,7 +50087,7 @@
     </row>
     <row r="399" spans="1:43" ht="15.75" customHeight="1">
       <c r="A399" s="186" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="B399" s="33" t="s">
         <v>434</v>
@@ -50098,25 +50098,25 @@
       <c r="D399" s="235"/>
       <c r="E399" s="58"/>
       <c r="F399" s="290" t="s">
+        <v>3233</v>
+      </c>
+      <c r="G399" s="32" t="s">
         <v>3234</v>
       </c>
-      <c r="G399" s="32" t="s">
+      <c r="H399" s="206" t="s">
         <v>3235</v>
       </c>
-      <c r="H399" s="206" t="s">
+      <c r="I399" s="32" t="s">
         <v>3236</v>
-      </c>
-      <c r="I399" s="32" t="s">
-        <v>3237</v>
       </c>
       <c r="J399" s="22"/>
       <c r="K399" s="22"/>
       <c r="L399" s="22"/>
       <c r="M399" s="212" t="s">
+        <v>3237</v>
+      </c>
+      <c r="N399" s="38" t="s">
         <v>3238</v>
-      </c>
-      <c r="N399" s="38" t="s">
-        <v>3239</v>
       </c>
       <c r="O399" s="38"/>
       <c r="P399" s="126"/>
@@ -50154,7 +50154,7 @@
     </row>
     <row r="400" spans="1:43" ht="15.75" customHeight="1">
       <c r="A400" s="282" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="B400" s="33" t="s">
         <v>434</v>
@@ -50165,32 +50165,32 @@
       <c r="D400" s="235"/>
       <c r="E400" s="58"/>
       <c r="F400" s="290" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="G400" s="32"/>
       <c r="H400" s="206" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="I400" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J400" s="22"/>
       <c r="K400" s="35" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="L400" s="35"/>
       <c r="M400" s="137" t="s">
+        <v>3242</v>
+      </c>
+      <c r="N400" s="136" t="s">
         <v>3243</v>
-      </c>
-      <c r="N400" s="136" t="s">
-        <v>3244</v>
       </c>
       <c r="O400" s="54" t="s">
         <v>38</v>
       </c>
       <c r="P400" s="55"/>
       <c r="Q400" s="56" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="R400" s="32" t="s">
         <v>544</v>
@@ -50202,18 +50202,18 @@
       <c r="U400" s="28"/>
       <c r="V400" s="28"/>
       <c r="W400" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X400" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X400" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y400" s="30" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="Z400" s="30"/>
       <c r="AA400" s="30"/>
       <c r="AB400" s="31" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="AC400" s="32"/>
       <c r="AD400" s="21"/>
@@ -50233,7 +50233,7 @@
     </row>
     <row r="401" spans="1:43" ht="15.75" customHeight="1">
       <c r="A401" s="186" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B401" s="33" t="s">
         <v>434</v>
@@ -50244,11 +50244,11 @@
       <c r="D401" s="235"/>
       <c r="E401" s="58"/>
       <c r="F401" s="16" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="G401" s="32"/>
       <c r="H401" s="192" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I401" s="32" t="s">
         <v>2546</v>
@@ -50259,17 +50259,17 @@
       </c>
       <c r="L401" s="447"/>
       <c r="M401" s="451" t="s">
+        <v>3250</v>
+      </c>
+      <c r="N401" s="38" t="s">
         <v>3251</v>
-      </c>
-      <c r="N401" s="38" t="s">
-        <v>3252</v>
       </c>
       <c r="O401" s="38"/>
       <c r="P401" s="317" t="s">
         <v>38</v>
       </c>
       <c r="Q401" s="319" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="R401" s="324" t="s">
         <v>80</v>
@@ -50281,13 +50281,13 @@
       <c r="U401" s="28"/>
       <c r="V401" s="28"/>
       <c r="W401" s="29" t="s">
+        <v>3252</v>
+      </c>
+      <c r="X401" s="29" t="s">
+        <v>3151</v>
+      </c>
+      <c r="Y401" s="30" t="s">
         <v>3253</v>
-      </c>
-      <c r="X401" s="29" t="s">
-        <v>3152</v>
-      </c>
-      <c r="Y401" s="30" t="s">
-        <v>3254</v>
       </c>
       <c r="Z401" s="30"/>
       <c r="AA401" s="30"/>
@@ -50310,10 +50310,10 @@
     </row>
     <row r="402" spans="1:43" ht="15.75" customHeight="1">
       <c r="A402" s="186" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B402" s="48" t="s">
         <v>3255</v>
-      </c>
-      <c r="B402" s="48" t="s">
-        <v>3256</v>
       </c>
       <c r="C402" s="250" t="s">
         <v>171</v>
@@ -50321,19 +50321,19 @@
       <c r="D402" s="235"/>
       <c r="E402" s="58"/>
       <c r="F402" s="290" t="s">
+        <v>3256</v>
+      </c>
+      <c r="G402" s="48" t="s">
         <v>3257</v>
       </c>
-      <c r="G402" s="48" t="s">
+      <c r="H402" s="206" t="s">
         <v>3258</v>
-      </c>
-      <c r="H402" s="206" t="s">
-        <v>3259</v>
       </c>
       <c r="I402" s="32" t="s">
         <v>2546</v>
       </c>
       <c r="J402" s="22" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="K402" s="22"/>
       <c r="L402" s="22"/>
@@ -50341,7 +50341,7 @@
         <v>137</v>
       </c>
       <c r="N402" s="54" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="O402" s="54"/>
       <c r="P402" s="55"/>
@@ -50356,18 +50356,18 @@
       <c r="U402" s="28"/>
       <c r="V402" s="28"/>
       <c r="W402" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X402" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X402" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y402" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z402" s="30"/>
       <c r="AA402" s="30"/>
       <c r="AB402" s="46" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="AC402" s="32"/>
       <c r="AD402" s="21"/>
@@ -50387,7 +50387,7 @@
     </row>
     <row r="403" spans="1:43" ht="15.75" customHeight="1">
       <c r="A403" s="293" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="B403" s="33" t="s">
         <v>434</v>
@@ -50398,11 +50398,11 @@
       <c r="D403" s="235"/>
       <c r="E403" s="58"/>
       <c r="F403" s="290" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="G403" s="32"/>
       <c r="H403" s="48" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="I403" s="187" t="s">
         <v>2546</v>
@@ -50410,20 +50410,20 @@
       <c r="J403" s="22"/>
       <c r="K403" s="22"/>
       <c r="L403" s="22" t="s">
+        <v>3264</v>
+      </c>
+      <c r="M403" s="451" t="s">
         <v>3265</v>
       </c>
-      <c r="M403" s="451" t="s">
+      <c r="N403" s="38" t="s">
         <v>3266</v>
       </c>
-      <c r="N403" s="38" t="s">
+      <c r="O403" s="38" t="s">
         <v>3267</v>
-      </c>
-      <c r="O403" s="38" t="s">
-        <v>3268</v>
       </c>
       <c r="P403" s="25"/>
       <c r="Q403" s="56" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="R403" s="39" t="s">
         <v>523</v>
@@ -50435,19 +50435,19 @@
       <c r="U403" s="28"/>
       <c r="V403" s="28"/>
       <c r="W403" s="29" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="X403" s="29" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="Y403" s="170" t="s">
+        <v>3269</v>
+      </c>
+      <c r="Z403" s="103" t="s">
         <v>3270</v>
       </c>
-      <c r="Z403" s="103" t="s">
+      <c r="AA403" s="30" t="s">
         <v>3271</v>
-      </c>
-      <c r="AA403" s="30" t="s">
-        <v>3272</v>
       </c>
       <c r="AB403" s="41"/>
       <c r="AC403" s="32"/>
@@ -50468,7 +50468,7 @@
     </row>
     <row r="404" spans="1:43" ht="15.75" customHeight="1">
       <c r="A404" s="186" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B404" s="33" t="s">
         <v>434</v>
@@ -50479,27 +50479,27 @@
       <c r="D404" s="235"/>
       <c r="E404" s="58"/>
       <c r="F404" s="47" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="G404" s="32"/>
       <c r="H404" s="206" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="I404" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J404" s="22" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="K404" s="22"/>
       <c r="L404" s="22" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="M404" s="331" t="s">
         <v>601</v>
       </c>
       <c r="N404" s="38" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="O404" s="38"/>
       <c r="P404" s="25"/>
@@ -50514,23 +50514,23 @@
       <c r="U404" s="28"/>
       <c r="V404" s="28"/>
       <c r="W404" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X404" s="72" t="s">
         <v>3151</v>
       </c>
-      <c r="X404" s="72" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y404" s="198" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="Z404" s="490"/>
       <c r="AA404" s="198" t="s">
+        <v>3279</v>
+      </c>
+      <c r="AB404" s="31" t="s">
         <v>3280</v>
       </c>
-      <c r="AB404" s="31" t="s">
+      <c r="AC404" s="47" t="s">
         <v>3281</v>
-      </c>
-      <c r="AC404" s="47" t="s">
-        <v>3282</v>
       </c>
       <c r="AD404" s="21"/>
       <c r="AE404" s="32"/>
@@ -50549,7 +50549,7 @@
     </row>
     <row r="405" spans="1:43" ht="15.75" customHeight="1">
       <c r="A405" s="186" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="B405" s="33" t="s">
         <v>434</v>
@@ -50560,11 +50560,11 @@
       <c r="D405" s="235"/>
       <c r="E405" s="58"/>
       <c r="F405" s="16" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="G405" s="32"/>
       <c r="H405" s="206" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="I405" s="192" t="s">
         <v>2506</v>
@@ -50576,7 +50576,7 @@
         <v>1287</v>
       </c>
       <c r="N405" s="38" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="O405" s="38"/>
       <c r="P405" s="25" t="s">
@@ -50595,23 +50595,23 @@
       <c r="U405" s="28"/>
       <c r="V405" s="28"/>
       <c r="W405" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X405" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X405" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y405" s="198" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="Z405" s="490"/>
       <c r="AA405" s="198" t="s">
+        <v>3287</v>
+      </c>
+      <c r="AB405" s="46" t="s">
         <v>3288</v>
       </c>
-      <c r="AB405" s="46" t="s">
-        <v>3289</v>
-      </c>
       <c r="AC405" s="47" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="AD405" s="21"/>
       <c r="AE405" s="32"/>
@@ -50630,7 +50630,7 @@
     </row>
     <row r="406" spans="1:43" ht="15.75" customHeight="1">
       <c r="A406" s="282" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="B406" s="14" t="s">
         <v>434</v>
@@ -50641,11 +50641,11 @@
       <c r="D406" s="235"/>
       <c r="E406" s="58"/>
       <c r="F406" s="290" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="G406" s="32"/>
       <c r="H406" s="206" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="I406" s="192" t="s">
         <v>2506</v>
@@ -50654,10 +50654,10 @@
       <c r="K406" s="22"/>
       <c r="L406" s="22"/>
       <c r="M406" s="331" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="N406" s="38" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="O406" s="65" t="s">
         <v>38</v>
@@ -50667,31 +50667,31 @@
         <v>1170</v>
       </c>
       <c r="R406" s="94" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="S406" s="77" t="s">
         <v>41</v>
       </c>
       <c r="T406" s="21" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="U406" s="28"/>
       <c r="V406" s="28"/>
       <c r="W406" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X406" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X406" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y406" s="198" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z406" s="490"/>
       <c r="AA406" s="198" t="s">
+        <v>3294</v>
+      </c>
+      <c r="AB406" s="46" t="s">
         <v>3295</v>
-      </c>
-      <c r="AB406" s="46" t="s">
-        <v>3296</v>
       </c>
       <c r="AC406" s="32"/>
       <c r="AD406" s="21"/>
@@ -50711,7 +50711,7 @@
     </row>
     <row r="407" spans="1:43" ht="15.75" customHeight="1">
       <c r="A407" s="186" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="B407" s="33" t="s">
         <v>434</v>
@@ -50722,11 +50722,11 @@
       <c r="D407" s="235"/>
       <c r="E407" s="58"/>
       <c r="F407" s="290" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="G407" s="32"/>
       <c r="H407" s="206" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="I407" s="192" t="s">
         <v>2506</v>
@@ -50734,13 +50734,13 @@
       <c r="J407" s="22"/>
       <c r="K407" s="22"/>
       <c r="L407" s="22" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="M407" s="137" t="s">
         <v>2685</v>
       </c>
       <c r="N407" s="38" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="O407" s="322"/>
       <c r="P407" s="126"/>
@@ -50755,20 +50755,20 @@
       <c r="U407" s="28"/>
       <c r="V407" s="28"/>
       <c r="W407" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X407" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X407" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y407" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z407" s="200"/>
       <c r="AA407" s="30" t="s">
+        <v>3300</v>
+      </c>
+      <c r="AB407" s="46" t="s">
         <v>3301</v>
-      </c>
-      <c r="AB407" s="46" t="s">
-        <v>3302</v>
       </c>
       <c r="AC407" s="32"/>
       <c r="AD407" s="21"/>
@@ -50788,10 +50788,10 @@
     </row>
     <row r="408" spans="1:43" ht="15.75" customHeight="1">
       <c r="A408" s="186" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B408" s="32" t="s">
         <v>3303</v>
-      </c>
-      <c r="B408" s="32" t="s">
-        <v>3304</v>
       </c>
       <c r="C408" s="250" t="s">
         <v>171</v>
@@ -50799,11 +50799,11 @@
       <c r="D408" s="247"/>
       <c r="E408" s="190"/>
       <c r="F408" s="191" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="G408" s="32"/>
       <c r="H408" s="32" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="I408" s="187" t="s">
         <v>2546</v>
@@ -50811,20 +50811,20 @@
       <c r="J408" s="22"/>
       <c r="K408" s="93"/>
       <c r="L408" s="22" t="s">
+        <v>3306</v>
+      </c>
+      <c r="M408" s="95" t="s">
         <v>3307</v>
       </c>
-      <c r="M408" s="95" t="s">
+      <c r="N408" s="65" t="s">
         <v>3308</v>
-      </c>
-      <c r="N408" s="65" t="s">
-        <v>3309</v>
       </c>
       <c r="O408" s="65"/>
       <c r="P408" s="74" t="s">
+        <v>3309</v>
+      </c>
+      <c r="Q408" s="56" t="s">
         <v>3310</v>
-      </c>
-      <c r="Q408" s="56" t="s">
-        <v>3311</v>
       </c>
       <c r="R408" s="101" t="s">
         <v>40</v>
@@ -50859,42 +50859,42 @@
     </row>
     <row r="409" spans="1:43" ht="15.75" customHeight="1">
       <c r="A409" s="282" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="B409" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C409" s="251" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="D409" s="247"/>
       <c r="E409" s="190"/>
       <c r="F409" s="208" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="G409" s="186"/>
       <c r="H409" s="48" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="I409" s="187" t="s">
         <v>2546</v>
       </c>
       <c r="J409" s="104" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="K409" s="104"/>
       <c r="L409" s="109"/>
       <c r="M409" s="209" t="s">
+        <v>3314</v>
+      </c>
+      <c r="N409" s="38" t="s">
         <v>3315</v>
-      </c>
-      <c r="N409" s="38" t="s">
-        <v>3316</v>
       </c>
       <c r="O409" s="38"/>
       <c r="P409" s="25"/>
       <c r="Q409" s="56"/>
       <c r="R409" s="115" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="S409" s="77" t="s">
         <v>41</v>
@@ -50903,13 +50903,13 @@
       <c r="U409" s="28"/>
       <c r="V409" s="28"/>
       <c r="W409" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X409" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X409" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y409" s="30" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="Z409" s="30"/>
       <c r="AA409" s="30"/>
@@ -50932,22 +50932,22 @@
     </row>
     <row r="410" spans="1:43" ht="15.75" customHeight="1">
       <c r="A410" s="287" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="B410" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C410" s="249" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="D410" s="235"/>
       <c r="E410" s="58"/>
       <c r="F410" s="47" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="G410" s="32"/>
       <c r="H410" s="206" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="I410" s="192" t="s">
         <v>2506</v>
@@ -50957,13 +50957,13 @@
         <v>276150</v>
       </c>
       <c r="L410" s="22" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="M410" s="137" t="s">
         <v>2218</v>
       </c>
       <c r="N410" s="38" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="O410" s="38"/>
       <c r="P410" s="25"/>
@@ -50975,7 +50975,7 @@
         <v>41</v>
       </c>
       <c r="T410" s="21" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="U410" s="28"/>
       <c r="V410" s="28"/>
@@ -50983,10 +50983,10 @@
       <c r="X410" s="29"/>
       <c r="Y410" s="30"/>
       <c r="Z410" s="30" t="s">
+        <v>3324</v>
+      </c>
+      <c r="AA410" s="30" t="s">
         <v>3325</v>
-      </c>
-      <c r="AA410" s="30" t="s">
-        <v>3326</v>
       </c>
       <c r="AB410" s="41"/>
       <c r="AC410" s="32"/>
@@ -51007,7 +51007,7 @@
     </row>
     <row r="411" spans="1:43" ht="15.75" customHeight="1">
       <c r="A411" s="186" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="B411" s="33" t="s">
         <v>434</v>
@@ -51018,18 +51018,18 @@
       <c r="D411" s="235"/>
       <c r="E411" s="58"/>
       <c r="F411" s="47" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="G411" s="32"/>
       <c r="H411" s="206" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="I411" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J411" s="22"/>
       <c r="K411" s="22" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="L411" s="22" t="s">
         <v>803</v>
@@ -51038,7 +51038,7 @@
         <v>1103</v>
       </c>
       <c r="N411" s="38" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="O411" s="38"/>
       <c r="P411" s="25"/>
@@ -51053,13 +51053,13 @@
       <c r="U411" s="28"/>
       <c r="V411" s="28"/>
       <c r="W411" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X411" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X411" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y411" s="30" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="Z411" s="30"/>
       <c r="AA411" s="30"/>
@@ -51082,7 +51082,7 @@
     </row>
     <row r="412" spans="1:43" ht="15.75" customHeight="1">
       <c r="A412" s="186" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="B412" s="33" t="s">
         <v>434</v>
@@ -51093,17 +51093,17 @@
       <c r="D412" s="235"/>
       <c r="E412" s="58"/>
       <c r="F412" s="47" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="G412" s="39"/>
       <c r="H412" s="206" t="s">
+        <v>3334</v>
+      </c>
+      <c r="I412" s="32" t="s">
         <v>3335</v>
       </c>
-      <c r="I412" s="32" t="s">
+      <c r="J412" s="109" t="s">
         <v>3336</v>
-      </c>
-      <c r="J412" s="109" t="s">
-        <v>3337</v>
       </c>
       <c r="K412" s="109"/>
       <c r="L412" s="109"/>
@@ -51111,7 +51111,7 @@
         <v>137</v>
       </c>
       <c r="N412" s="38" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="O412" s="38"/>
       <c r="P412" s="25"/>
@@ -51126,13 +51126,13 @@
       <c r="U412" s="28"/>
       <c r="V412" s="28"/>
       <c r="W412" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X412" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X412" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y412" s="30" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="Z412" s="30"/>
       <c r="AA412" s="30"/>
@@ -51155,7 +51155,7 @@
     </row>
     <row r="413" spans="1:43" ht="15.75" customHeight="1">
       <c r="A413" s="186" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="B413" s="33" t="s">
         <v>434</v>
@@ -51166,19 +51166,19 @@
       <c r="D413" s="235"/>
       <c r="E413" s="58"/>
       <c r="F413" s="16" t="s">
+        <v>3340</v>
+      </c>
+      <c r="G413" s="32" t="s">
         <v>3341</v>
       </c>
-      <c r="G413" s="32" t="s">
+      <c r="H413" s="207" t="s">
         <v>3342</v>
       </c>
-      <c r="H413" s="207" t="s">
+      <c r="I413" s="187" t="s">
         <v>3343</v>
       </c>
-      <c r="I413" s="187" t="s">
-        <v>3344</v>
-      </c>
       <c r="J413" s="109" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="K413" s="109"/>
       <c r="L413" s="109"/>
@@ -51186,7 +51186,7 @@
         <v>137</v>
       </c>
       <c r="N413" s="38" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="O413" s="38"/>
       <c r="P413" s="25"/>
@@ -51201,18 +51201,18 @@
       <c r="U413" s="28"/>
       <c r="V413" s="28"/>
       <c r="W413" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X413" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X413" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y413" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z413" s="30"/>
       <c r="AA413" s="30"/>
       <c r="AB413" s="46" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="AC413" s="32"/>
       <c r="AD413" s="21"/>
@@ -51232,7 +51232,7 @@
     </row>
     <row r="414" spans="1:43" ht="15.75" customHeight="1">
       <c r="A414" s="186" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="B414" s="95" t="s">
         <v>2283</v>
@@ -51243,19 +51243,19 @@
       <c r="D414" s="235"/>
       <c r="E414" s="58"/>
       <c r="F414" s="47" t="s">
+        <v>3347</v>
+      </c>
+      <c r="G414" s="32" t="s">
         <v>3348</v>
       </c>
-      <c r="G414" s="32" t="s">
+      <c r="H414" s="207" t="s">
         <v>3349</v>
       </c>
-      <c r="H414" s="207" t="s">
+      <c r="I414" s="187" t="s">
         <v>3350</v>
       </c>
-      <c r="I414" s="187" t="s">
+      <c r="J414" s="22" t="s">
         <v>3351</v>
-      </c>
-      <c r="J414" s="22" t="s">
-        <v>3352</v>
       </c>
       <c r="K414" s="22"/>
       <c r="L414" s="22"/>
@@ -51263,7 +51263,7 @@
         <v>137</v>
       </c>
       <c r="N414" s="38" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="O414" s="38"/>
       <c r="P414" s="25"/>
@@ -51278,13 +51278,13 @@
       <c r="U414" s="28"/>
       <c r="V414" s="28"/>
       <c r="W414" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X414" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X414" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y414" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z414" s="30"/>
       <c r="AA414" s="30"/>
@@ -51307,29 +51307,29 @@
     </row>
     <row r="415" spans="1:43" ht="15.75" customHeight="1">
       <c r="A415" s="287" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="B415" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C415" s="336" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="D415" s="247"/>
       <c r="E415" s="190"/>
       <c r="F415" s="294" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="G415" s="186"/>
       <c r="H415" s="206" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="I415" s="187" t="s">
         <v>2546</v>
       </c>
       <c r="J415" s="22"/>
       <c r="K415" s="22" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="L415" s="22" t="s">
         <v>1360</v>
@@ -51338,7 +51338,7 @@
         <v>1103</v>
       </c>
       <c r="N415" s="38" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="O415" s="38"/>
       <c r="P415" s="25"/>
@@ -51353,13 +51353,13 @@
       <c r="U415" s="28"/>
       <c r="V415" s="28"/>
       <c r="W415" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X415" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X415" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y415" s="30" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="Z415" s="103"/>
       <c r="AA415" s="30"/>
@@ -51382,22 +51382,22 @@
     </row>
     <row r="416" spans="1:43" ht="15.75" customHeight="1">
       <c r="A416" s="296" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="B416" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C416" s="255" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="D416" s="235"/>
       <c r="E416" s="58"/>
       <c r="F416" s="290" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="G416" s="32"/>
       <c r="H416" s="206" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="I416" s="32" t="s">
         <v>2506</v>
@@ -51409,7 +51409,7 @@
         <v>1840</v>
       </c>
       <c r="N416" s="38" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="O416" s="65" t="s">
         <v>38</v>
@@ -51428,20 +51428,20 @@
       <c r="U416" s="28"/>
       <c r="V416" s="28"/>
       <c r="W416" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X416" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X416" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y416" s="30" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="Z416" s="200"/>
       <c r="AA416" s="30" t="s">
+        <v>3363</v>
+      </c>
+      <c r="AB416" s="46" t="s">
         <v>3364</v>
-      </c>
-      <c r="AB416" s="46" t="s">
-        <v>3365</v>
       </c>
       <c r="AC416" s="32"/>
       <c r="AD416" s="21"/>
@@ -51461,7 +51461,7 @@
     </row>
     <row r="417" spans="1:43" ht="15.75" customHeight="1">
       <c r="A417" s="282" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="B417" s="33" t="s">
         <v>434</v>
@@ -51472,23 +51472,23 @@
       <c r="D417" s="235"/>
       <c r="E417" s="58"/>
       <c r="F417" s="290" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="G417" s="32"/>
       <c r="H417" s="206" t="s">
+        <v>3366</v>
+      </c>
+      <c r="I417" s="32" t="s">
         <v>3367</v>
-      </c>
-      <c r="I417" s="32" t="s">
-        <v>3368</v>
       </c>
       <c r="J417" s="22"/>
       <c r="K417" s="22"/>
       <c r="L417" s="22"/>
       <c r="M417" s="115" t="s">
+        <v>3368</v>
+      </c>
+      <c r="N417" s="38" t="s">
         <v>3369</v>
-      </c>
-      <c r="N417" s="38" t="s">
-        <v>3370</v>
       </c>
       <c r="O417" s="38"/>
       <c r="P417" s="25"/>
@@ -51528,7 +51528,7 @@
     </row>
     <row r="418" spans="1:43" ht="15.75" customHeight="1">
       <c r="A418" s="193" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="B418" s="33" t="s">
         <v>434</v>
@@ -51539,27 +51539,27 @@
       <c r="D418" s="235"/>
       <c r="E418" s="58"/>
       <c r="F418" s="290" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="G418" s="32"/>
       <c r="H418" s="39" t="s">
+        <v>3371</v>
+      </c>
+      <c r="I418" s="192" t="s">
         <v>3372</v>
       </c>
-      <c r="I418" s="192" t="s">
+      <c r="J418" s="109" t="s">
         <v>3373</v>
-      </c>
-      <c r="J418" s="109" t="s">
-        <v>3374</v>
       </c>
       <c r="K418" s="109"/>
       <c r="L418" s="109" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="M418" s="43" t="s">
         <v>137</v>
       </c>
       <c r="N418" s="38" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="O418" s="38"/>
       <c r="P418" s="25"/>
@@ -51597,30 +51597,30 @@
     </row>
     <row r="419" spans="1:43" ht="15.75" customHeight="1">
       <c r="A419" s="186" t="s">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="B419" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C419" s="424" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="D419" s="235"/>
       <c r="E419" s="58"/>
       <c r="F419" s="290" t="s">
+        <v>3375</v>
+      </c>
+      <c r="G419" s="32" t="s">
         <v>3376</v>
       </c>
-      <c r="G419" s="32" t="s">
+      <c r="H419" s="207" t="s">
         <v>3377</v>
       </c>
-      <c r="H419" s="207" t="s">
+      <c r="I419" s="187" t="s">
         <v>3378</v>
       </c>
-      <c r="I419" s="187" t="s">
+      <c r="J419" s="22" t="s">
         <v>3379</v>
-      </c>
-      <c r="J419" s="22" t="s">
-        <v>3380</v>
       </c>
       <c r="K419" s="22"/>
       <c r="L419" s="22"/>
@@ -51628,7 +51628,7 @@
         <v>137</v>
       </c>
       <c r="N419" s="38" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="O419" s="38"/>
       <c r="P419" s="25"/>
@@ -51666,7 +51666,7 @@
     </row>
     <row r="420" spans="1:43" ht="15.75" customHeight="1">
       <c r="A420" s="186" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="B420" s="33" t="s">
         <v>434</v>
@@ -51677,11 +51677,11 @@
       <c r="D420" s="247"/>
       <c r="E420" s="190"/>
       <c r="F420" s="294" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="G420" s="186"/>
       <c r="H420" s="192" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="I420" s="192" t="s">
         <v>2506</v>
@@ -51689,13 +51689,13 @@
       <c r="J420" s="22"/>
       <c r="K420" s="22"/>
       <c r="L420" s="22" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="M420" s="137" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="N420" s="38" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="O420" s="38"/>
       <c r="P420" s="25"/>
@@ -51710,17 +51710,17 @@
       <c r="U420" s="28"/>
       <c r="V420" s="28"/>
       <c r="W420" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X420" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X420" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y420" s="30" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="Z420" s="490"/>
       <c r="AA420" s="30" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="AB420" s="41"/>
       <c r="AC420" s="32"/>
@@ -51741,22 +51741,22 @@
     </row>
     <row r="421" spans="1:43" ht="15.75" customHeight="1">
       <c r="A421" s="186" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="B421" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C421" s="424" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="D421" s="247"/>
       <c r="E421" s="58"/>
       <c r="F421" s="290" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="G421" s="186"/>
       <c r="H421" s="206" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="I421" s="32" t="s">
         <v>2506</v>
@@ -51767,10 +51767,10 @@
         <v>2751</v>
       </c>
       <c r="M421" s="137" t="s">
+        <v>3389</v>
+      </c>
+      <c r="N421" s="38" t="s">
         <v>3390</v>
-      </c>
-      <c r="N421" s="38" t="s">
-        <v>3391</v>
       </c>
       <c r="O421" s="38"/>
       <c r="P421" s="25"/>
@@ -51785,23 +51785,23 @@
       <c r="U421" s="28"/>
       <c r="V421" s="28"/>
       <c r="W421" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X421" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X421" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y421" s="30" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="Z421" s="200"/>
       <c r="AA421" s="30" t="s">
+        <v>3392</v>
+      </c>
+      <c r="AB421" s="46" t="s">
         <v>3393</v>
       </c>
-      <c r="AB421" s="46" t="s">
+      <c r="AC421" s="66" t="s">
         <v>3394</v>
-      </c>
-      <c r="AC421" s="66" t="s">
-        <v>3395</v>
       </c>
       <c r="AD421" s="32"/>
       <c r="AE421" s="32"/>
@@ -51820,7 +51820,7 @@
     </row>
     <row r="422" spans="1:43" ht="15.75" customHeight="1">
       <c r="A422" s="186" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="B422" s="33" t="s">
         <v>434</v>
@@ -51831,17 +51831,17 @@
       <c r="D422" s="247"/>
       <c r="E422" s="190"/>
       <c r="F422" s="191" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="G422" s="186"/>
       <c r="H422" s="206" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="I422" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J422" s="82" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="K422" s="82"/>
       <c r="L422" s="82"/>
@@ -51849,14 +51849,14 @@
         <v>657</v>
       </c>
       <c r="N422" s="38" t="s">
+        <v>3399</v>
+      </c>
+      <c r="O422" s="38" t="s">
         <v>3400</v>
-      </c>
-      <c r="O422" s="38" t="s">
-        <v>3401</v>
       </c>
       <c r="P422" s="25"/>
       <c r="Q422" s="26" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="R422" s="39" t="s">
         <v>523</v>
@@ -51868,22 +51868,22 @@
       <c r="U422" s="28"/>
       <c r="V422" s="28"/>
       <c r="W422" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X422" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X422" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y422" s="30" t="s">
+        <v>3402</v>
+      </c>
+      <c r="Z422" s="30" t="s">
         <v>3403</v>
       </c>
-      <c r="Z422" s="30" t="s">
+      <c r="AA422" s="30" t="s">
         <v>3404</v>
       </c>
-      <c r="AA422" s="30" t="s">
+      <c r="AB422" s="46" t="s">
         <v>3405</v>
-      </c>
-      <c r="AB422" s="46" t="s">
-        <v>3406</v>
       </c>
       <c r="AC422" s="32"/>
       <c r="AD422" s="32"/>
@@ -51903,7 +51903,7 @@
     </row>
     <row r="423" spans="1:43" ht="15.75" customHeight="1">
       <c r="A423" s="186" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="B423" s="33" t="s">
         <v>434</v>
@@ -51914,11 +51914,11 @@
       <c r="D423" s="247"/>
       <c r="E423" s="190"/>
       <c r="F423" s="191" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="G423" s="186"/>
       <c r="H423" s="206" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="I423" s="192" t="s">
         <v>2506</v>
@@ -51932,14 +51932,14 @@
         <v>657</v>
       </c>
       <c r="N423" s="38" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="O423" s="38"/>
       <c r="P423" s="25" t="s">
+        <v>3409</v>
+      </c>
+      <c r="Q423" s="56" t="s">
         <v>3410</v>
-      </c>
-      <c r="Q423" s="56" t="s">
-        <v>3411</v>
       </c>
       <c r="R423" s="99" t="s">
         <v>544</v>
@@ -51948,25 +51948,25 @@
         <v>41</v>
       </c>
       <c r="T423" s="21" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="U423" s="28"/>
       <c r="V423" s="28"/>
       <c r="W423" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X423" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X423" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y423" s="30" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="Z423" s="30"/>
       <c r="AA423" s="30" t="s">
+        <v>3980</v>
+      </c>
+      <c r="AB423" s="41" t="s">
         <v>3981</v>
-      </c>
-      <c r="AB423" s="41" t="s">
-        <v>3982</v>
       </c>
       <c r="AC423" s="32"/>
       <c r="AD423" s="32"/>
@@ -51986,7 +51986,7 @@
     </row>
     <row r="424" spans="1:43" ht="15.75" customHeight="1">
       <c r="A424" s="186" t="s">
-        <v>3916</v>
+        <v>3915</v>
       </c>
       <c r="B424" s="14" t="s">
         <v>434</v>
@@ -51997,14 +51997,14 @@
       <c r="D424" s="235"/>
       <c r="E424" s="58"/>
       <c r="F424" s="290" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="G424" s="32"/>
       <c r="H424" s="206" t="s">
+        <v>3414</v>
+      </c>
+      <c r="I424" s="187" t="s">
         <v>3415</v>
-      </c>
-      <c r="I424" s="187" t="s">
-        <v>3416</v>
       </c>
       <c r="J424" s="82"/>
       <c r="K424" s="82"/>
@@ -52028,13 +52028,13 @@
       <c r="U424" s="28"/>
       <c r="V424" s="28"/>
       <c r="W424" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X424" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X424" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y424" s="30" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="Z424" s="30"/>
       <c r="AA424" s="30"/>
@@ -52057,22 +52057,22 @@
     </row>
     <row r="425" spans="1:43" ht="15.75" customHeight="1">
       <c r="A425" s="287" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
       <c r="B425" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C425" s="257" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="D425" s="235"/>
       <c r="E425" s="58"/>
       <c r="F425" s="16" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="G425" s="32"/>
       <c r="H425" s="206" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="I425" s="217" t="s">
         <v>582</v>
@@ -52080,20 +52080,20 @@
       <c r="J425" s="35"/>
       <c r="K425" s="22"/>
       <c r="L425" s="22" t="s">
+        <v>3420</v>
+      </c>
+      <c r="M425" s="332" t="s">
         <v>3421</v>
       </c>
-      <c r="M425" s="332" t="s">
+      <c r="N425" s="54" t="s">
         <v>3422</v>
-      </c>
-      <c r="N425" s="54" t="s">
-        <v>3423</v>
       </c>
       <c r="O425" s="54"/>
       <c r="P425" s="74" t="s">
+        <v>3423</v>
+      </c>
+      <c r="Q425" s="56" t="s">
         <v>3424</v>
-      </c>
-      <c r="Q425" s="56" t="s">
-        <v>3425</v>
       </c>
       <c r="R425" s="101" t="s">
         <v>40</v>
@@ -52105,13 +52105,13 @@
       <c r="U425" s="28"/>
       <c r="V425" s="28"/>
       <c r="W425" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X425" s="29" t="s">
         <v>3151</v>
       </c>
-      <c r="X425" s="29" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y425" s="30" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="Z425" s="30"/>
       <c r="AA425" s="30"/>
@@ -52134,7 +52134,7 @@
     </row>
     <row r="426" spans="1:43" ht="15.75" customHeight="1">
       <c r="A426" s="186" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="B426" s="33" t="s">
         <v>434</v>
@@ -52145,14 +52145,14 @@
       <c r="D426" s="235"/>
       <c r="E426" s="58"/>
       <c r="F426" s="47" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="G426" s="32"/>
       <c r="H426" s="192" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="I426" s="217" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="J426" s="22"/>
       <c r="K426" s="93"/>
@@ -52199,7 +52199,7 @@
     </row>
     <row r="427" spans="1:43" ht="15.75" customHeight="1">
       <c r="A427" s="186" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="B427" s="33" t="s">
         <v>434</v>
@@ -52210,14 +52210,14 @@
       <c r="D427" s="235"/>
       <c r="E427" s="58"/>
       <c r="F427" s="290" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="G427" s="32"/>
       <c r="H427" s="192" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="I427" s="32" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="J427" s="22"/>
       <c r="K427" s="22"/>
@@ -52266,7 +52266,7 @@
     </row>
     <row r="428" spans="1:43" ht="15.75" customHeight="1">
       <c r="A428" s="186" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="B428" s="14" t="s">
         <v>434</v>
@@ -52277,11 +52277,11 @@
       <c r="D428" s="235"/>
       <c r="E428" s="58"/>
       <c r="F428" s="290" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="G428" s="32"/>
       <c r="H428" s="48" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="I428" s="187" t="s">
         <v>2546</v>
@@ -52289,13 +52289,13 @@
       <c r="J428" s="22"/>
       <c r="K428" s="22"/>
       <c r="L428" s="22" t="s">
+        <v>3434</v>
+      </c>
+      <c r="M428" s="137" t="s">
         <v>3435</v>
       </c>
-      <c r="M428" s="137" t="s">
+      <c r="N428" s="54" t="s">
         <v>3436</v>
-      </c>
-      <c r="N428" s="54" t="s">
-        <v>3437</v>
       </c>
       <c r="O428" s="54"/>
       <c r="P428" s="55"/>
@@ -52310,13 +52310,13 @@
       <c r="U428" s="28"/>
       <c r="V428" s="28"/>
       <c r="W428" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X428" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X428" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y428" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z428" s="30"/>
       <c r="AA428" s="30"/>
@@ -52339,7 +52339,7 @@
     </row>
     <row r="429" spans="1:43" ht="15.75" customHeight="1">
       <c r="A429" s="186" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="B429" s="33" t="s">
         <v>434</v>
@@ -52350,11 +52350,11 @@
       <c r="D429" s="235"/>
       <c r="E429" s="58"/>
       <c r="F429" s="290" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="G429" s="32"/>
       <c r="H429" s="206" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="I429" s="192" t="s">
         <v>2546</v>
@@ -52365,10 +52365,10 @@
         <v>991</v>
       </c>
       <c r="M429" s="137" t="s">
+        <v>3368</v>
+      </c>
+      <c r="N429" s="54" t="s">
         <v>3369</v>
-      </c>
-      <c r="N429" s="54" t="s">
-        <v>3370</v>
       </c>
       <c r="O429" s="458"/>
       <c r="P429" s="114"/>
@@ -52383,13 +52383,13 @@
       <c r="U429" s="28"/>
       <c r="V429" s="28"/>
       <c r="W429" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X429" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X429" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y429" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z429" s="30"/>
       <c r="AA429" s="30"/>
@@ -52412,7 +52412,7 @@
     </row>
     <row r="430" spans="1:43" ht="15.75" customHeight="1">
       <c r="A430" s="282" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
       <c r="B430" s="33" t="s">
         <v>434</v>
@@ -52423,11 +52423,11 @@
       <c r="D430" s="235"/>
       <c r="E430" s="58"/>
       <c r="F430" s="290" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="G430" s="32"/>
       <c r="H430" s="206" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="I430" s="192" t="s">
         <v>2546</v>
@@ -52436,14 +52436,14 @@
       <c r="K430" s="82"/>
       <c r="L430" s="82"/>
       <c r="M430" s="137" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="N430" s="38" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="O430" s="38"/>
       <c r="P430" s="317" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="Q430" s="26"/>
       <c r="R430" s="117" t="s">
@@ -52479,7 +52479,7 @@
     </row>
     <row r="431" spans="1:43" ht="15.75" customHeight="1">
       <c r="A431" s="282" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
       <c r="B431" s="33" t="s">
         <v>434</v>
@@ -52490,11 +52490,11 @@
       <c r="D431" s="235"/>
       <c r="E431" s="58"/>
       <c r="F431" s="47" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="G431" s="32"/>
       <c r="H431" s="206" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I431" s="192" t="s">
         <v>2546</v>
@@ -52503,10 +52503,10 @@
       <c r="K431" s="82"/>
       <c r="L431" s="22"/>
       <c r="M431" s="137" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="N431" s="38" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="O431" s="38"/>
       <c r="P431" s="25"/>
@@ -52544,7 +52544,7 @@
     </row>
     <row r="432" spans="1:43" ht="15.75" customHeight="1">
       <c r="A432" s="282" t="s">
-        <v>3920</v>
+        <v>3919</v>
       </c>
       <c r="B432" s="33" t="s">
         <v>434</v>
@@ -52555,11 +52555,11 @@
       <c r="D432" s="235"/>
       <c r="E432" s="58"/>
       <c r="F432" s="16" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="G432" s="32"/>
       <c r="H432" s="206" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="I432" s="192" t="s">
         <v>2546</v>
@@ -52567,19 +52567,19 @@
       <c r="J432" s="98"/>
       <c r="K432" s="104"/>
       <c r="L432" s="104" t="s">
+        <v>3447</v>
+      </c>
+      <c r="M432" s="137" t="s">
         <v>3448</v>
       </c>
-      <c r="M432" s="137" t="s">
+      <c r="N432" s="54" t="s">
         <v>3449</v>
-      </c>
-      <c r="N432" s="54" t="s">
-        <v>3450</v>
       </c>
       <c r="O432" s="458"/>
       <c r="P432" s="114"/>
       <c r="Q432" s="123"/>
       <c r="R432" s="324" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="S432" s="137" t="s">
         <v>41</v>
@@ -52611,7 +52611,7 @@
     </row>
     <row r="433" spans="1:43" ht="15.75" customHeight="1">
       <c r="A433" s="186" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="B433" s="33" t="s">
         <v>434</v>
@@ -52622,11 +52622,11 @@
       <c r="D433" s="235"/>
       <c r="E433" s="58"/>
       <c r="F433" s="47" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="G433" s="32"/>
       <c r="H433" s="206" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="I433" s="192" t="s">
         <v>2506</v>
@@ -52641,11 +52641,11 @@
         <v>1240</v>
       </c>
       <c r="O433" s="54" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="P433" s="55"/>
       <c r="Q433" s="56" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="R433" s="32" t="s">
         <v>523</v>
@@ -52657,16 +52657,16 @@
       <c r="U433" s="28"/>
       <c r="V433" s="28"/>
       <c r="W433" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X433" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X433" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y433" s="30" t="s">
+        <v>3456</v>
+      </c>
+      <c r="Z433" s="30" t="s">
         <v>3457</v>
-      </c>
-      <c r="Z433" s="30" t="s">
-        <v>3458</v>
       </c>
       <c r="AA433" s="30"/>
       <c r="AB433" s="41"/>
@@ -52688,7 +52688,7 @@
     </row>
     <row r="434" spans="1:43" ht="15.75" customHeight="1">
       <c r="A434" s="186" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="B434" s="33" t="s">
         <v>434</v>
@@ -52699,11 +52699,11 @@
       <c r="D434" s="235"/>
       <c r="E434" s="58"/>
       <c r="F434" s="290" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="G434" s="32"/>
       <c r="H434" s="206" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="I434" s="192" t="s">
         <v>2546</v>
@@ -52715,7 +52715,7 @@
         <v>2729</v>
       </c>
       <c r="N434" s="136" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="O434" s="54"/>
       <c r="P434" s="55"/>
@@ -52730,13 +52730,13 @@
       <c r="U434" s="28"/>
       <c r="V434" s="28"/>
       <c r="W434" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X434" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X434" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y434" s="30" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="Z434" s="30"/>
       <c r="AA434" s="30"/>
@@ -52759,7 +52759,7 @@
     </row>
     <row r="435" spans="1:43" ht="15.75" customHeight="1">
       <c r="A435" s="186" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="B435" s="33" t="s">
         <v>434</v>
@@ -52770,11 +52770,11 @@
       <c r="D435" s="235"/>
       <c r="E435" s="58"/>
       <c r="F435" s="290" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G435" s="32"/>
       <c r="H435" s="206" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="I435" s="192" t="s">
         <v>2546</v>
@@ -52786,7 +52786,7 @@
         <v>253</v>
       </c>
       <c r="N435" s="54" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="O435" s="54"/>
       <c r="P435" s="55"/>
@@ -52824,7 +52824,7 @@
     </row>
     <row r="436" spans="1:43" ht="15.75" customHeight="1">
       <c r="A436" s="282" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="B436" s="33" t="s">
         <v>434</v>
@@ -52835,17 +52835,17 @@
       <c r="D436" s="235"/>
       <c r="E436" s="58"/>
       <c r="F436" s="290" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="G436" s="32"/>
       <c r="H436" s="192" t="s">
+        <v>3467</v>
+      </c>
+      <c r="I436" s="32" t="s">
         <v>3468</v>
       </c>
-      <c r="I436" s="32" t="s">
-        <v>3469</v>
-      </c>
       <c r="J436" s="82" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="K436" s="82"/>
       <c r="L436" s="22"/>
@@ -52891,24 +52891,24 @@
     </row>
     <row r="437" spans="1:43" ht="15.75" customHeight="1">
       <c r="A437" s="281" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="B437" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C437" s="258" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="D437" s="235"/>
       <c r="E437" s="58"/>
       <c r="F437" s="290" t="s">
+        <v>3470</v>
+      </c>
+      <c r="G437" s="32" t="s">
         <v>3471</v>
       </c>
-      <c r="G437" s="32" t="s">
+      <c r="H437" s="206" t="s">
         <v>3472</v>
-      </c>
-      <c r="H437" s="206" t="s">
-        <v>3473</v>
       </c>
       <c r="I437" s="192" t="s">
         <v>2546</v>
@@ -52916,13 +52916,13 @@
       <c r="J437" s="35"/>
       <c r="K437" s="22"/>
       <c r="L437" s="22" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="M437" s="209" t="s">
         <v>480</v>
       </c>
       <c r="N437" s="54" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="O437" s="54"/>
       <c r="P437" s="55"/>
@@ -52935,19 +52935,19 @@
       </c>
       <c r="T437" s="21"/>
       <c r="U437" s="28" t="s">
+        <v>3475</v>
+      </c>
+      <c r="V437" s="28" t="s">
         <v>3476</v>
       </c>
-      <c r="V437" s="28" t="s">
+      <c r="W437" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X437" s="120" t="s">
+        <v>3151</v>
+      </c>
+      <c r="Y437" s="30" t="s">
         <v>3477</v>
-      </c>
-      <c r="W437" s="29" t="s">
-        <v>3151</v>
-      </c>
-      <c r="X437" s="120" t="s">
-        <v>3152</v>
-      </c>
-      <c r="Y437" s="30" t="s">
-        <v>3478</v>
       </c>
       <c r="Z437" s="30"/>
       <c r="AA437" s="30"/>
@@ -52970,7 +52970,7 @@
     </row>
     <row r="438" spans="1:43" ht="15.75" customHeight="1">
       <c r="A438" s="282" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="B438" s="33" t="s">
         <v>434</v>
@@ -52981,17 +52981,17 @@
       <c r="D438" s="235"/>
       <c r="E438" s="58"/>
       <c r="F438" s="290" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="G438" s="32"/>
       <c r="H438" s="206" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="I438" s="192" t="s">
         <v>2546</v>
       </c>
       <c r="J438" s="104" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="K438" s="104"/>
       <c r="L438" s="109"/>
@@ -52999,7 +52999,7 @@
         <v>137</v>
       </c>
       <c r="N438" s="54" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="O438" s="54"/>
       <c r="P438" s="55"/>
@@ -53014,13 +53014,13 @@
       <c r="U438" s="122"/>
       <c r="V438" s="122"/>
       <c r="W438" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X438" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X438" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y438" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z438" s="30"/>
       <c r="AA438" s="30"/>
@@ -53043,7 +53043,7 @@
     </row>
     <row r="439" spans="1:43" ht="15.75" customHeight="1">
       <c r="A439" s="186" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="B439" s="95" t="s">
         <v>2283</v>
@@ -53054,13 +53054,13 @@
       <c r="D439" s="235"/>
       <c r="E439" s="58"/>
       <c r="F439" s="16" t="s">
+        <v>3483</v>
+      </c>
+      <c r="G439" s="32" t="s">
         <v>3484</v>
       </c>
-      <c r="G439" s="32" t="s">
+      <c r="H439" s="206" t="s">
         <v>3485</v>
-      </c>
-      <c r="H439" s="206" t="s">
-        <v>3486</v>
       </c>
       <c r="I439" s="32" t="s">
         <v>2546</v>
@@ -53068,13 +53068,13 @@
       <c r="J439" s="35"/>
       <c r="K439" s="82"/>
       <c r="L439" s="82" t="s">
+        <v>3486</v>
+      </c>
+      <c r="M439" s="209" t="s">
         <v>3487</v>
       </c>
-      <c r="M439" s="209" t="s">
+      <c r="N439" s="54" t="s">
         <v>3488</v>
-      </c>
-      <c r="N439" s="54" t="s">
-        <v>3489</v>
       </c>
       <c r="O439" s="54"/>
       <c r="P439" s="55"/>
@@ -53087,15 +53087,15 @@
       </c>
       <c r="T439" s="105"/>
       <c r="U439" s="106" t="s">
+        <v>3475</v>
+      </c>
+      <c r="V439" s="106" t="s">
         <v>3476</v>
-      </c>
-      <c r="V439" s="106" t="s">
-        <v>3477</v>
       </c>
       <c r="W439" s="113"/>
       <c r="X439" s="113"/>
       <c r="Y439" s="30" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="Z439" s="30"/>
       <c r="AA439" s="30"/>
@@ -53118,7 +53118,7 @@
     </row>
     <row r="440" spans="1:43" ht="15.75" customHeight="1">
       <c r="A440" s="186" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="B440" s="14" t="s">
         <v>434</v>
@@ -53129,11 +53129,11 @@
       <c r="D440" s="235"/>
       <c r="E440" s="58"/>
       <c r="F440" s="290" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="G440" s="32"/>
       <c r="H440" s="206" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="I440" s="32" t="s">
         <v>2546</v>
@@ -53162,19 +53162,19 @@
       <c r="U440" s="28"/>
       <c r="V440" s="28"/>
       <c r="W440" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X440" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X440" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y440" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z440" s="103"/>
       <c r="AA440" s="30"/>
       <c r="AB440" s="41"/>
       <c r="AC440" s="32" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="AD440" s="32"/>
       <c r="AE440" s="32"/>
@@ -53193,22 +53193,22 @@
     </row>
     <row r="441" spans="1:43" ht="15.75" customHeight="1">
       <c r="A441" s="186" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="B441" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C441" s="295" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="D441" s="235"/>
       <c r="E441" s="58"/>
       <c r="F441" s="290" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="G441" s="32"/>
       <c r="H441" s="206" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="I441" s="192" t="s">
         <v>2506</v>
@@ -53217,17 +53217,17 @@
       <c r="K441" s="82"/>
       <c r="L441" s="82"/>
       <c r="M441" s="137" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="N441" s="136" t="s">
         <v>1240</v>
       </c>
       <c r="O441" s="461" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="P441" s="59"/>
       <c r="Q441" s="56" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="R441" s="32" t="s">
         <v>523</v>
@@ -53239,20 +53239,20 @@
       <c r="U441" s="122"/>
       <c r="V441" s="122"/>
       <c r="W441" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X441" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X441" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y441" s="30" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="Z441" s="200"/>
       <c r="AA441" s="30" t="s">
+        <v>3499</v>
+      </c>
+      <c r="AB441" s="31" t="s">
         <v>3500</v>
-      </c>
-      <c r="AB441" s="31" t="s">
-        <v>3501</v>
       </c>
       <c r="AC441" s="32"/>
       <c r="AD441" s="32"/>
@@ -53272,7 +53272,7 @@
     </row>
     <row r="442" spans="1:43" ht="15.75" customHeight="1">
       <c r="A442" s="186" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="B442" s="33" t="s">
         <v>434</v>
@@ -53283,54 +53283,54 @@
       <c r="D442" s="235"/>
       <c r="E442" s="58"/>
       <c r="F442" s="47" t="s">
+        <v>3502</v>
+      </c>
+      <c r="G442" s="32" t="s">
         <v>3503</v>
       </c>
-      <c r="G442" s="32" t="s">
+      <c r="H442" s="206" t="s">
         <v>3504</v>
       </c>
-      <c r="H442" s="206" t="s">
+      <c r="I442" s="187" t="s">
         <v>3505</v>
-      </c>
-      <c r="I442" s="187" t="s">
-        <v>3506</v>
       </c>
       <c r="J442" s="22"/>
       <c r="K442" s="22"/>
       <c r="L442" s="22"/>
       <c r="M442" s="137" t="s">
+        <v>3506</v>
+      </c>
+      <c r="N442" s="73" t="s">
         <v>3507</v>
-      </c>
-      <c r="N442" s="73" t="s">
-        <v>3508</v>
       </c>
       <c r="O442" s="73"/>
       <c r="P442" s="74" t="s">
+        <v>3508</v>
+      </c>
+      <c r="Q442" s="91" t="s">
         <v>3509</v>
       </c>
-      <c r="Q442" s="91" t="s">
-        <v>3510</v>
-      </c>
       <c r="R442" s="115" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="S442" s="115" t="s">
         <v>41</v>
       </c>
       <c r="T442" s="21"/>
       <c r="U442" s="28" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="V442" s="28" t="s">
+        <v>3509</v>
+      </c>
+      <c r="W442" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X442" s="113" t="s">
+        <v>3509</v>
+      </c>
+      <c r="Y442" s="30" t="s">
         <v>3510</v>
-      </c>
-      <c r="W442" s="113" t="s">
-        <v>3151</v>
-      </c>
-      <c r="X442" s="113" t="s">
-        <v>3510</v>
-      </c>
-      <c r="Y442" s="30" t="s">
-        <v>3511</v>
       </c>
       <c r="Z442" s="30"/>
       <c r="AA442" s="30"/>
@@ -53353,7 +53353,7 @@
     </row>
     <row r="443" spans="1:43" ht="15.75" customHeight="1">
       <c r="A443" s="296" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="B443" s="33" t="s">
         <v>434</v>
@@ -53364,13 +53364,13 @@
       <c r="D443" s="235"/>
       <c r="E443" s="58"/>
       <c r="F443" s="290" t="s">
+        <v>3511</v>
+      </c>
+      <c r="G443" s="48" t="s">
         <v>3512</v>
       </c>
-      <c r="G443" s="48" t="s">
+      <c r="H443" s="95" t="s">
         <v>3513</v>
-      </c>
-      <c r="H443" s="95" t="s">
-        <v>3514</v>
       </c>
       <c r="I443" s="187" t="s">
         <v>2487</v>
@@ -53382,7 +53382,7 @@
         <v>657</v>
       </c>
       <c r="N443" s="65" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="O443" s="322"/>
       <c r="P443" s="126"/>
@@ -53397,13 +53397,13 @@
       <c r="U443" s="28"/>
       <c r="V443" s="28"/>
       <c r="W443" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X443" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X443" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y443" s="30" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="Z443" s="30"/>
       <c r="AA443" s="30"/>
@@ -53426,7 +53426,7 @@
     </row>
     <row r="444" spans="1:43" ht="15.75" customHeight="1">
       <c r="A444" s="186" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="B444" s="33" t="s">
         <v>434</v>
@@ -53437,11 +53437,11 @@
       <c r="D444" s="235"/>
       <c r="E444" s="58"/>
       <c r="F444" s="16" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="G444" s="32"/>
       <c r="H444" s="206" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="I444" s="187" t="s">
         <v>2546</v>
@@ -53450,20 +53450,20 @@
       <c r="K444" s="82"/>
       <c r="L444" s="82"/>
       <c r="M444" s="137" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="N444" s="38" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="O444" s="38"/>
       <c r="P444" s="74" t="s">
+        <v>3508</v>
+      </c>
+      <c r="Q444" s="26" t="s">
         <v>3509</v>
       </c>
-      <c r="Q444" s="26" t="s">
-        <v>3510</v>
-      </c>
       <c r="R444" s="33" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="S444" s="77" t="s">
         <v>41</v>
@@ -53495,7 +53495,7 @@
     </row>
     <row r="445" spans="1:43" ht="15.75" customHeight="1">
       <c r="A445" s="186" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="B445" s="33" t="s">
         <v>434</v>
@@ -53506,13 +53506,13 @@
       <c r="D445" s="247"/>
       <c r="E445" s="190"/>
       <c r="F445" s="191" t="s">
+        <v>3522</v>
+      </c>
+      <c r="G445" s="186" t="s">
         <v>3523</v>
       </c>
-      <c r="G445" s="186" t="s">
+      <c r="H445" s="48" t="s">
         <v>3524</v>
-      </c>
-      <c r="H445" s="48" t="s">
-        <v>3525</v>
       </c>
       <c r="I445" s="32" t="s">
         <v>2546</v>
@@ -53520,13 +53520,13 @@
       <c r="J445" s="98"/>
       <c r="K445" s="104"/>
       <c r="L445" s="109" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="M445" s="209" t="s">
         <v>480</v>
       </c>
       <c r="N445" s="38" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="O445" s="38"/>
       <c r="P445" s="25"/>
@@ -53539,24 +53539,24 @@
       </c>
       <c r="T445" s="21"/>
       <c r="U445" s="28" t="s">
+        <v>3475</v>
+      </c>
+      <c r="V445" s="28" t="s">
         <v>3476</v>
       </c>
-      <c r="V445" s="28" t="s">
-        <v>3477</v>
-      </c>
       <c r="W445" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X445" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X445" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y445" s="30" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="Z445" s="30"/>
       <c r="AA445" s="30"/>
       <c r="AB445" s="31" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="AC445" s="32"/>
       <c r="AD445" s="21"/>
@@ -53576,7 +53576,7 @@
     </row>
     <row r="446" spans="1:43" ht="15.75" customHeight="1">
       <c r="A446" s="186" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="B446" s="33" t="s">
         <v>434</v>
@@ -53587,13 +53587,13 @@
       <c r="D446" s="247"/>
       <c r="E446" s="190"/>
       <c r="F446" s="191" t="s">
+        <v>3530</v>
+      </c>
+      <c r="G446" s="186" t="s">
         <v>3531</v>
       </c>
-      <c r="G446" s="186" t="s">
+      <c r="H446" s="48" t="s">
         <v>3532</v>
-      </c>
-      <c r="H446" s="48" t="s">
-        <v>3533</v>
       </c>
       <c r="I446" s="32" t="s">
         <v>2546</v>
@@ -53601,13 +53601,13 @@
       <c r="J446" s="35"/>
       <c r="K446" s="109"/>
       <c r="L446" s="109" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="M446" s="209" t="s">
         <v>480</v>
       </c>
       <c r="N446" s="54" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="O446" s="54"/>
       <c r="P446" s="55"/>
@@ -53620,24 +53620,24 @@
       </c>
       <c r="T446" s="21"/>
       <c r="U446" s="28" t="s">
+        <v>3475</v>
+      </c>
+      <c r="V446" s="122" t="s">
         <v>3476</v>
       </c>
-      <c r="V446" s="122" t="s">
-        <v>3477</v>
-      </c>
       <c r="W446" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X446" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X446" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y446" s="30" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="Z446" s="30"/>
       <c r="AA446" s="30"/>
       <c r="AB446" s="41" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="AC446" s="32"/>
       <c r="AD446" s="21"/>
@@ -53657,7 +53657,7 @@
     </row>
     <row r="447" spans="1:43" ht="15.75" customHeight="1">
       <c r="A447" s="296" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="B447" s="33" t="s">
         <v>434</v>
@@ -53668,17 +53668,17 @@
       <c r="D447" s="235"/>
       <c r="E447" s="58"/>
       <c r="F447" s="47" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="G447" s="32"/>
       <c r="H447" s="206" t="s">
+        <v>3538</v>
+      </c>
+      <c r="I447" s="192" t="s">
         <v>3539</v>
       </c>
-      <c r="I447" s="192" t="s">
+      <c r="J447" s="22" t="s">
         <v>3540</v>
-      </c>
-      <c r="J447" s="22" t="s">
-        <v>3541</v>
       </c>
       <c r="K447" s="22"/>
       <c r="L447" s="22"/>
@@ -53701,13 +53701,13 @@
       <c r="U447" s="122"/>
       <c r="V447" s="122"/>
       <c r="W447" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X447" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X447" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y447" s="30" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="Z447" s="30"/>
       <c r="AA447" s="30"/>
@@ -53730,7 +53730,7 @@
     </row>
     <row r="448" spans="1:43" ht="15.75" customHeight="1">
       <c r="A448" s="186" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="B448" s="33" t="s">
         <v>434</v>
@@ -53741,17 +53741,17 @@
       <c r="D448" s="235"/>
       <c r="E448" s="58"/>
       <c r="F448" s="290" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="G448" s="32"/>
       <c r="H448" s="206" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="I448" s="32" t="s">
         <v>2127</v>
       </c>
       <c r="J448" s="82" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="K448" s="82"/>
       <c r="L448" s="82"/>
@@ -53759,7 +53759,7 @@
         <v>137</v>
       </c>
       <c r="N448" s="54" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="O448" s="54"/>
       <c r="P448" s="55"/>
@@ -53797,7 +53797,7 @@
     </row>
     <row r="449" spans="1:43" ht="15.75" customHeight="1">
       <c r="A449" s="186" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="B449" s="33" t="s">
         <v>434</v>
@@ -53808,11 +53808,11 @@
       <c r="D449" s="235"/>
       <c r="E449" s="58"/>
       <c r="F449" s="47" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="G449" s="32"/>
       <c r="H449" s="206" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="I449" s="192" t="s">
         <v>2546</v>
@@ -53820,13 +53820,13 @@
       <c r="J449" s="98"/>
       <c r="K449" s="104"/>
       <c r="L449" s="104" t="s">
+        <v>3549</v>
+      </c>
+      <c r="M449" s="137" t="s">
         <v>3550</v>
       </c>
-      <c r="M449" s="137" t="s">
+      <c r="N449" s="54" t="s">
         <v>3551</v>
-      </c>
-      <c r="N449" s="54" t="s">
-        <v>3552</v>
       </c>
       <c r="O449" s="54"/>
       <c r="P449" s="55"/>
@@ -53841,13 +53841,13 @@
       <c r="U449" s="122"/>
       <c r="V449" s="122"/>
       <c r="W449" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X449" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X449" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y449" s="30" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="Z449" s="30"/>
       <c r="AA449" s="30"/>
@@ -53870,7 +53870,7 @@
     </row>
     <row r="450" spans="1:43" ht="15.75" customHeight="1">
       <c r="A450" s="186" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="B450" s="33" t="s">
         <v>434</v>
@@ -53881,11 +53881,11 @@
       <c r="D450" s="235"/>
       <c r="E450" s="58"/>
       <c r="F450" s="290" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="G450" s="32"/>
       <c r="H450" s="186" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="I450" s="192" t="s">
         <v>2546</v>
@@ -53893,13 +53893,13 @@
       <c r="J450" s="98"/>
       <c r="K450" s="104"/>
       <c r="L450" s="109" t="s">
+        <v>3549</v>
+      </c>
+      <c r="M450" s="137" t="s">
         <v>3550</v>
       </c>
-      <c r="M450" s="137" t="s">
-        <v>3551</v>
-      </c>
       <c r="N450" s="73" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="O450" s="73"/>
       <c r="P450" s="74"/>
@@ -53914,13 +53914,13 @@
       <c r="U450" s="122"/>
       <c r="V450" s="122"/>
       <c r="W450" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X450" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X450" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y450" s="30" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="Z450" s="30"/>
       <c r="AA450" s="30"/>
@@ -53943,7 +53943,7 @@
     </row>
     <row r="451" spans="1:43" ht="15.75" customHeight="1">
       <c r="A451" s="186" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="B451" s="33" t="s">
         <v>434</v>
@@ -53954,13 +53954,13 @@
       <c r="D451" s="235"/>
       <c r="E451" s="58"/>
       <c r="F451" s="290" t="s">
+        <v>3557</v>
+      </c>
+      <c r="G451" s="32" t="s">
         <v>3558</v>
       </c>
-      <c r="G451" s="32" t="s">
+      <c r="H451" s="206" t="s">
         <v>3559</v>
-      </c>
-      <c r="H451" s="206" t="s">
-        <v>3560</v>
       </c>
       <c r="I451" s="192" t="s">
         <v>2546</v>
@@ -53968,13 +53968,13 @@
       <c r="J451" s="35"/>
       <c r="K451" s="109"/>
       <c r="L451" s="109" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="M451" s="77" t="s">
         <v>480</v>
       </c>
       <c r="N451" s="38" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="O451" s="38"/>
       <c r="P451" s="25"/>
@@ -53987,24 +53987,24 @@
       </c>
       <c r="T451" s="21"/>
       <c r="U451" s="28" t="s">
+        <v>3475</v>
+      </c>
+      <c r="V451" s="122" t="s">
         <v>3476</v>
       </c>
-      <c r="V451" s="122" t="s">
-        <v>3477</v>
-      </c>
       <c r="W451" s="113" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="X451" s="120" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="Y451" s="30" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="Z451" s="30"/>
       <c r="AA451" s="30"/>
       <c r="AB451" s="219" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="AC451" s="32"/>
       <c r="AD451" s="21"/>
@@ -54024,7 +54024,7 @@
     </row>
     <row r="452" spans="1:43" ht="15.75" customHeight="1">
       <c r="A452" s="186" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="B452" s="33" t="s">
         <v>434</v>
@@ -54035,11 +54035,11 @@
       <c r="D452" s="235"/>
       <c r="E452" s="58"/>
       <c r="F452" s="47" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="G452" s="32"/>
       <c r="H452" s="206" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="I452" s="192" t="s">
         <v>2546</v>
@@ -54048,10 +54048,10 @@
       <c r="K452" s="82"/>
       <c r="L452" s="82"/>
       <c r="M452" s="95" t="s">
+        <v>3565</v>
+      </c>
+      <c r="N452" s="89" t="s">
         <v>3566</v>
-      </c>
-      <c r="N452" s="89" t="s">
-        <v>3567</v>
       </c>
       <c r="O452" s="89"/>
       <c r="P452" s="90"/>
@@ -54089,7 +54089,7 @@
     </row>
     <row r="453" spans="1:43" ht="15.75" customHeight="1">
       <c r="A453" s="186" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="B453" s="33" t="s">
         <v>434</v>
@@ -54100,16 +54100,16 @@
       <c r="D453" s="235"/>
       <c r="E453" s="58"/>
       <c r="F453" s="290" t="s">
+        <v>3568</v>
+      </c>
+      <c r="G453" s="32" t="s">
         <v>3569</v>
       </c>
-      <c r="G453" s="32" t="s">
+      <c r="H453" s="48" t="s">
         <v>3570</v>
       </c>
-      <c r="H453" s="48" t="s">
+      <c r="I453" s="187" t="s">
         <v>3571</v>
-      </c>
-      <c r="I453" s="187" t="s">
-        <v>3572</v>
       </c>
       <c r="J453" s="22"/>
       <c r="K453" s="22"/>
@@ -54118,14 +54118,14 @@
         <v>804</v>
       </c>
       <c r="N453" s="136" t="s">
+        <v>3572</v>
+      </c>
+      <c r="O453" s="54" t="s">
         <v>3573</v>
-      </c>
-      <c r="O453" s="54" t="s">
-        <v>3574</v>
       </c>
       <c r="P453" s="55"/>
       <c r="Q453" s="56" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="R453" s="99" t="s">
         <v>1105</v>
@@ -54134,7 +54134,7 @@
         <v>41</v>
       </c>
       <c r="T453" s="121" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="U453" s="122"/>
       <c r="V453" s="122"/>
@@ -54162,7 +54162,7 @@
     </row>
     <row r="454" spans="1:43" ht="15.75" customHeight="1">
       <c r="A454" s="186" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="B454" s="33" t="s">
         <v>434</v>
@@ -54173,16 +54173,16 @@
       <c r="D454" s="235"/>
       <c r="E454" s="58"/>
       <c r="F454" s="290" t="s">
+        <v>3577</v>
+      </c>
+      <c r="G454" s="32" t="s">
         <v>3578</v>
       </c>
-      <c r="G454" s="32" t="s">
+      <c r="H454" s="95" t="s">
         <v>3579</v>
       </c>
-      <c r="H454" s="95" t="s">
-        <v>3580</v>
-      </c>
       <c r="I454" s="187" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="J454" s="22"/>
       <c r="K454" s="82"/>
@@ -54191,7 +54191,7 @@
         <v>804</v>
       </c>
       <c r="N454" s="136" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="O454" s="54"/>
       <c r="P454" s="55"/>
@@ -54206,13 +54206,13 @@
       <c r="U454" s="221"/>
       <c r="V454" s="221"/>
       <c r="W454" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X454" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X454" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y454" s="30" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="Z454" s="30"/>
       <c r="AA454" s="30"/>
@@ -54235,7 +54235,7 @@
     </row>
     <row r="455" spans="1:43" ht="15.75" customHeight="1">
       <c r="A455" s="186" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="B455" s="95" t="s">
         <v>434</v>
@@ -54246,14 +54246,14 @@
       <c r="D455" s="235"/>
       <c r="E455" s="58"/>
       <c r="F455" s="290" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="G455" s="32"/>
       <c r="H455" s="192" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="I455" s="32" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="J455" s="22"/>
       <c r="K455" s="82"/>
@@ -54262,7 +54262,7 @@
         <v>184</v>
       </c>
       <c r="N455" s="38" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="O455" s="38"/>
       <c r="P455" s="25"/>
@@ -54277,18 +54277,18 @@
       <c r="U455" s="122"/>
       <c r="V455" s="122"/>
       <c r="W455" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X455" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X455" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y455" s="30" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="Z455" s="30"/>
       <c r="AA455" s="30"/>
       <c r="AB455" s="46" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="AC455" s="32"/>
       <c r="AD455" s="21"/>
@@ -54308,7 +54308,7 @@
     </row>
     <row r="456" spans="1:43" ht="15.75" customHeight="1">
       <c r="A456" s="186" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="B456" s="95" t="s">
         <v>2283</v>
@@ -54319,34 +54319,34 @@
       <c r="D456" s="235"/>
       <c r="E456" s="58"/>
       <c r="F456" s="290" t="s">
+        <v>3587</v>
+      </c>
+      <c r="G456" s="32" t="s">
         <v>3588</v>
       </c>
-      <c r="G456" s="32" t="s">
+      <c r="H456" s="33" t="s">
         <v>3589</v>
       </c>
-      <c r="H456" s="33" t="s">
+      <c r="I456" s="187" t="s">
+        <v>3041</v>
+      </c>
+      <c r="J456" s="22" t="s">
         <v>3590</v>
-      </c>
-      <c r="I456" s="187" t="s">
-        <v>3042</v>
-      </c>
-      <c r="J456" s="22" t="s">
-        <v>3591</v>
       </c>
       <c r="K456" s="22"/>
       <c r="L456" s="22"/>
       <c r="M456" s="115" t="s">
+        <v>3591</v>
+      </c>
+      <c r="N456" s="65" t="s">
         <v>3592</v>
       </c>
-      <c r="N456" s="65" t="s">
-        <v>3593</v>
-      </c>
       <c r="O456" s="38" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="P456" s="25"/>
       <c r="Q456" s="56" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="R456" s="94" t="s">
         <v>1105</v>
@@ -54358,13 +54358,13 @@
       <c r="U456" s="28"/>
       <c r="V456" s="28"/>
       <c r="W456" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X456" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X456" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y456" s="30" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="Z456" s="30"/>
       <c r="AA456" s="30"/>
@@ -54387,7 +54387,7 @@
     </row>
     <row r="457" spans="1:43" ht="15.75" customHeight="1">
       <c r="A457" s="296" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="B457" s="32" t="s">
         <v>434</v>
@@ -54398,11 +54398,11 @@
       <c r="D457" s="235"/>
       <c r="E457" s="58"/>
       <c r="F457" s="290" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="G457" s="32"/>
       <c r="H457" s="192" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="I457" s="192" t="s">
         <v>2506</v>
@@ -54416,14 +54416,14 @@
         <v>804</v>
       </c>
       <c r="N457" s="38" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="O457" s="38" t="s">
         <v>901</v>
       </c>
       <c r="P457" s="25"/>
       <c r="Q457" s="56" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="R457" s="39" t="s">
         <v>523</v>
@@ -54435,19 +54435,19 @@
       <c r="U457" s="28"/>
       <c r="V457" s="28"/>
       <c r="W457" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X457" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X457" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y457" s="30" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="Z457" s="30" t="s">
+        <v>3597</v>
+      </c>
+      <c r="AA457" s="30" t="s">
         <v>3598</v>
-      </c>
-      <c r="AA457" s="30" t="s">
-        <v>3599</v>
       </c>
       <c r="AB457" s="41"/>
       <c r="AC457" s="32"/>
@@ -54468,7 +54468,7 @@
     </row>
     <row r="458" spans="1:43" ht="15.75" customHeight="1">
       <c r="A458" s="296" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="B458" s="95" t="s">
         <v>2283</v>
@@ -54479,11 +54479,11 @@
       <c r="D458" s="235"/>
       <c r="E458" s="58"/>
       <c r="F458" s="16" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="G458" s="32"/>
       <c r="H458" s="32" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="I458" s="32" t="s">
         <v>2506</v>
@@ -54497,14 +54497,14 @@
         <v>657</v>
       </c>
       <c r="N458" s="65" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="O458" s="65" t="s">
         <v>901</v>
       </c>
       <c r="P458" s="25"/>
       <c r="Q458" s="56" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="R458" s="39" t="s">
         <v>523</v>
@@ -54516,19 +54516,19 @@
       <c r="U458" s="28"/>
       <c r="V458" s="28"/>
       <c r="W458" s="113" t="s">
+        <v>3252</v>
+      </c>
+      <c r="X458" s="120" t="s">
+        <v>3151</v>
+      </c>
+      <c r="Y458" s="30" t="s">
         <v>3253</v>
       </c>
-      <c r="X458" s="120" t="s">
-        <v>3152</v>
-      </c>
-      <c r="Y458" s="30" t="s">
-        <v>3254</v>
-      </c>
       <c r="Z458" s="30" t="s">
+        <v>3602</v>
+      </c>
+      <c r="AA458" s="30" t="s">
         <v>3603</v>
-      </c>
-      <c r="AA458" s="30" t="s">
-        <v>3604</v>
       </c>
       <c r="AB458" s="41"/>
       <c r="AC458" s="32"/>
@@ -54549,7 +54549,7 @@
     </row>
     <row r="459" spans="1:43" ht="15.75" customHeight="1">
       <c r="A459" s="296" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="B459" s="95" t="s">
         <v>2283</v>
@@ -54560,16 +54560,16 @@
       <c r="D459" s="236"/>
       <c r="E459" s="67"/>
       <c r="F459" s="16" t="s">
+        <v>3604</v>
+      </c>
+      <c r="G459" s="32" t="s">
         <v>3605</v>
       </c>
-      <c r="G459" s="32" t="s">
+      <c r="H459" s="32" t="s">
         <v>3606</v>
       </c>
-      <c r="H459" s="32" t="s">
+      <c r="I459" s="187" t="s">
         <v>3607</v>
-      </c>
-      <c r="I459" s="187" t="s">
-        <v>3608</v>
       </c>
       <c r="J459" s="22"/>
       <c r="K459" s="22"/>
@@ -54578,14 +54578,14 @@
         <v>2480</v>
       </c>
       <c r="N459" s="89" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="O459" s="89"/>
       <c r="P459" s="74" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="Q459" s="56" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="R459" s="96" t="s">
         <v>387</v>
@@ -54622,7 +54622,7 @@
     </row>
     <row r="460" spans="1:43" ht="15.75" customHeight="1">
       <c r="A460" s="186" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="B460" s="95" t="s">
         <v>2283</v>
@@ -54633,34 +54633,34 @@
       <c r="D460" s="235"/>
       <c r="E460" s="58"/>
       <c r="F460" s="290" t="s">
+        <v>3610</v>
+      </c>
+      <c r="G460" s="32" t="s">
         <v>3611</v>
       </c>
-      <c r="G460" s="32" t="s">
+      <c r="H460" s="206" t="s">
         <v>3612</v>
       </c>
-      <c r="H460" s="206" t="s">
+      <c r="I460" s="32" t="s">
         <v>3613</v>
-      </c>
-      <c r="I460" s="32" t="s">
-        <v>3614</v>
       </c>
       <c r="J460" s="22"/>
       <c r="K460" s="93" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="L460" s="82"/>
       <c r="M460" s="137" t="s">
         <v>657</v>
       </c>
       <c r="N460" s="136" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="O460" s="38" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="P460" s="55"/>
       <c r="Q460" s="56" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="R460" s="94" t="s">
         <v>1105</v>
@@ -54672,13 +54672,13 @@
       <c r="U460" s="28"/>
       <c r="V460" s="106"/>
       <c r="W460" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X460" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X460" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y460" s="30" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="Z460" s="30"/>
       <c r="AA460" s="30"/>
@@ -54701,43 +54701,43 @@
     </row>
     <row r="461" spans="1:43" ht="15.75" customHeight="1">
       <c r="A461" s="287" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="B461" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C461" s="249" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="D461" s="235"/>
       <c r="E461" s="58"/>
       <c r="F461" s="47" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="G461" s="32"/>
       <c r="H461" s="48" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="I461" s="187" t="s">
         <v>2506</v>
       </c>
       <c r="J461" s="109" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="K461" s="104"/>
       <c r="L461" s="104"/>
       <c r="M461" s="137" t="s">
+        <v>3621</v>
+      </c>
+      <c r="N461" s="136" t="s">
         <v>3622</v>
       </c>
-      <c r="N461" s="136" t="s">
+      <c r="O461" s="458" t="s">
         <v>3623</v>
-      </c>
-      <c r="O461" s="458" t="s">
-        <v>3624</v>
       </c>
       <c r="P461" s="114"/>
       <c r="Q461" s="56" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="R461" s="39" t="s">
         <v>523</v>
@@ -54747,13 +54747,13 @@
       <c r="U461" s="28"/>
       <c r="V461" s="28"/>
       <c r="W461" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X461" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X461" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y461" s="30" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="Z461" s="30"/>
       <c r="AA461" s="30"/>
@@ -54776,7 +54776,7 @@
     </row>
     <row r="462" spans="1:43" ht="15.75" customHeight="1">
       <c r="A462" s="186" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
       <c r="B462" s="95" t="s">
         <v>2283</v>
@@ -54787,11 +54787,11 @@
       <c r="D462" s="235"/>
       <c r="E462" s="58"/>
       <c r="F462" s="47" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="G462" s="32"/>
       <c r="H462" s="186" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="I462" s="32" t="s">
         <v>2047</v>
@@ -54805,14 +54805,14 @@
         <v>683</v>
       </c>
       <c r="N462" s="89" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="O462" s="89"/>
       <c r="P462" s="74" t="s">
         <v>1608</v>
       </c>
       <c r="Q462" s="91" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="R462" s="333" t="s">
         <v>40</v>
@@ -54828,13 +54828,13 @@
         <v>189</v>
       </c>
       <c r="W462" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X462" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X462" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y462" s="30" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="Z462" s="30"/>
       <c r="AA462" s="30"/>
@@ -54857,7 +54857,7 @@
     </row>
     <row r="463" spans="1:43" ht="15.75" customHeight="1">
       <c r="A463" s="186" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="B463" s="95" t="s">
         <v>2283</v>
@@ -54868,13 +54868,13 @@
       <c r="D463" s="236"/>
       <c r="E463" s="67"/>
       <c r="F463" s="16" t="s">
+        <v>3632</v>
+      </c>
+      <c r="G463" s="32" t="s">
         <v>3633</v>
       </c>
-      <c r="G463" s="32" t="s">
+      <c r="H463" s="32" t="s">
         <v>3634</v>
-      </c>
-      <c r="H463" s="32" t="s">
-        <v>3635</v>
       </c>
       <c r="I463" s="187" t="s">
         <v>2638</v>
@@ -54885,10 +54885,10 @@
       <c r="K463" s="22"/>
       <c r="L463" s="22"/>
       <c r="M463" s="115" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N463" s="65" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="O463" s="83"/>
       <c r="P463" s="25"/>
@@ -54903,13 +54903,13 @@
       <c r="U463" s="122"/>
       <c r="V463" s="122"/>
       <c r="W463" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X463" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X463" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y463" s="30" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="Z463" s="30"/>
       <c r="AA463" s="30"/>
@@ -54932,10 +54932,10 @@
     </row>
     <row r="464" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A464" s="297" t="s">
+        <v>3636</v>
+      </c>
+      <c r="B464" s="298" t="s">
         <v>3637</v>
-      </c>
-      <c r="B464" s="298" t="s">
-        <v>3638</v>
       </c>
       <c r="C464" s="299" t="s">
         <v>171</v>
@@ -54943,16 +54943,16 @@
       <c r="D464" s="300"/>
       <c r="E464" s="301"/>
       <c r="F464" s="302" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="G464" s="302" t="s">
         <v>2285</v>
       </c>
       <c r="H464" s="302" t="s">
+        <v>3639</v>
+      </c>
+      <c r="I464" s="303" t="s">
         <v>3640</v>
-      </c>
-      <c r="I464" s="303" t="s">
-        <v>3641</v>
       </c>
       <c r="J464" s="444" t="s">
         <v>2273</v>
@@ -54963,13 +54963,13 @@
         <v>1601</v>
       </c>
       <c r="N464" s="305" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="O464" s="305"/>
       <c r="P464" s="306"/>
       <c r="Q464" s="307"/>
       <c r="R464" s="474" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="S464" s="308" t="s">
         <v>41</v>
@@ -55001,43 +55001,43 @@
     </row>
     <row r="465" spans="1:43" ht="15.75" customHeight="1">
       <c r="A465" s="287" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="B465" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C465" s="249" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="D465" s="235"/>
       <c r="E465" s="58"/>
       <c r="F465" s="47" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="G465" s="32"/>
       <c r="H465" s="48" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="I465" s="187" t="s">
         <v>2506</v>
       </c>
       <c r="J465" s="109" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="K465" s="109"/>
       <c r="L465" s="109"/>
       <c r="M465" s="137" t="s">
+        <v>3647</v>
+      </c>
+      <c r="N465" s="54" t="s">
         <v>3648</v>
       </c>
-      <c r="N465" s="54" t="s">
+      <c r="O465" s="54" t="s">
         <v>3649</v>
-      </c>
-      <c r="O465" s="54" t="s">
-        <v>3650</v>
       </c>
       <c r="P465" s="55"/>
       <c r="Q465" s="56" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="R465" s="39" t="s">
         <v>523</v>
@@ -55051,13 +55051,13 @@
       <c r="W465" s="113"/>
       <c r="X465" s="113"/>
       <c r="Y465" s="30" t="s">
+        <v>3651</v>
+      </c>
+      <c r="Z465" s="30" t="s">
         <v>3652</v>
       </c>
-      <c r="Z465" s="30" t="s">
+      <c r="AA465" s="30" t="s">
         <v>3653</v>
-      </c>
-      <c r="AA465" s="30" t="s">
-        <v>3654</v>
       </c>
       <c r="AB465" s="41"/>
       <c r="AC465" s="32"/>
@@ -55078,7 +55078,7 @@
     </row>
     <row r="466" spans="1:43" ht="15.75" customHeight="1">
       <c r="A466" s="296" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="B466" s="95" t="s">
         <v>434</v>
@@ -55089,13 +55089,13 @@
       <c r="D466" s="235"/>
       <c r="E466" s="58"/>
       <c r="F466" s="47" t="s">
+        <v>3654</v>
+      </c>
+      <c r="G466" s="32" t="s">
         <v>3655</v>
       </c>
-      <c r="G466" s="32" t="s">
+      <c r="H466" s="95" t="s">
         <v>3656</v>
-      </c>
-      <c r="H466" s="95" t="s">
-        <v>3657</v>
       </c>
       <c r="I466" s="187" t="s">
         <v>2638</v>
@@ -55103,20 +55103,20 @@
       <c r="J466" s="93"/>
       <c r="K466" s="22"/>
       <c r="L466" s="22" t="s">
+        <v>3657</v>
+      </c>
+      <c r="M466" s="137" t="s">
         <v>3658</v>
       </c>
-      <c r="M466" s="137" t="s">
+      <c r="N466" s="136" t="s">
         <v>3659</v>
       </c>
-      <c r="N466" s="136" t="s">
-        <v>3660</v>
-      </c>
       <c r="O466" s="38" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="P466" s="55"/>
       <c r="Q466" s="56" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="R466" s="94" t="s">
         <v>1105</v>
@@ -55126,13 +55126,13 @@
       <c r="U466" s="28"/>
       <c r="V466" s="28"/>
       <c r="W466" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X466" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X466" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y466" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z466" s="30"/>
       <c r="AA466" s="30"/>
@@ -55155,50 +55155,50 @@
     </row>
     <row r="467" spans="1:43" ht="15.75" customHeight="1">
       <c r="A467" s="288" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="B467" s="95" t="s">
         <v>434</v>
       </c>
       <c r="C467" s="256" t="s">
+        <v>3660</v>
+      </c>
+      <c r="D467" s="234" t="s">
         <v>3661</v>
       </c>
-      <c r="D467" s="234" t="s">
+      <c r="E467" s="58" t="s">
         <v>3662</v>
       </c>
-      <c r="E467" s="58" t="s">
+      <c r="F467" s="223" t="s">
         <v>3663</v>
       </c>
-      <c r="F467" s="223" t="s">
+      <c r="G467" s="16" t="s">
+        <v>3660</v>
+      </c>
+      <c r="H467" s="207" t="s">
         <v>3664</v>
       </c>
-      <c r="G467" s="16" t="s">
-        <v>3661</v>
-      </c>
-      <c r="H467" s="207" t="s">
+      <c r="I467" s="187" t="s">
         <v>3665</v>
-      </c>
-      <c r="I467" s="187" t="s">
-        <v>3666</v>
       </c>
       <c r="J467" s="22"/>
       <c r="K467" s="22"/>
       <c r="L467" s="22"/>
       <c r="M467" s="137" t="s">
+        <v>3666</v>
+      </c>
+      <c r="N467" s="38" t="s">
         <v>3667</v>
-      </c>
-      <c r="N467" s="38" t="s">
-        <v>3668</v>
       </c>
       <c r="O467" s="38"/>
       <c r="P467" s="25" t="s">
+        <v>3668</v>
+      </c>
+      <c r="Q467" s="56" t="s">
         <v>3669</v>
       </c>
-      <c r="Q467" s="56" t="s">
-        <v>3670</v>
-      </c>
       <c r="R467" s="94" t="s">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="S467" s="77" t="s">
         <v>41</v>
@@ -55230,7 +55230,7 @@
     </row>
     <row r="468" spans="1:43" ht="15.75" customHeight="1">
       <c r="A468" s="186" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="B468" s="95" t="s">
         <v>2283</v>
@@ -55241,13 +55241,13 @@
       <c r="D468" s="236"/>
       <c r="E468" s="67"/>
       <c r="F468" s="290" t="s">
+        <v>3671</v>
+      </c>
+      <c r="G468" s="32" t="s">
         <v>3672</v>
       </c>
-      <c r="G468" s="32" t="s">
+      <c r="H468" s="95" t="s">
         <v>3673</v>
-      </c>
-      <c r="H468" s="95" t="s">
-        <v>3674</v>
       </c>
       <c r="I468" s="187" t="s">
         <v>2638</v>
@@ -55259,7 +55259,7 @@
         <v>1986</v>
       </c>
       <c r="N468" s="65" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="O468" s="38"/>
       <c r="P468" s="25"/>
@@ -55274,18 +55274,18 @@
       <c r="U468" s="28"/>
       <c r="V468" s="28"/>
       <c r="W468" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X468" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X468" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y468" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="Z468" s="30"/>
       <c r="AA468" s="30"/>
       <c r="AB468" s="46" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
       <c r="AC468" s="32"/>
       <c r="AD468" s="32"/>
@@ -55305,28 +55305,28 @@
     </row>
     <row r="469" spans="1:43" ht="15.75" customHeight="1">
       <c r="A469" s="187" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="B469" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C469" s="250" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="D469" s="235"/>
       <c r="E469" s="58"/>
       <c r="F469" s="290" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="G469" s="32"/>
       <c r="H469" s="48" t="s">
+        <v>3678</v>
+      </c>
+      <c r="I469" s="187" t="s">
         <v>3679</v>
       </c>
-      <c r="I469" s="187" t="s">
+      <c r="J469" s="109" t="s">
         <v>3680</v>
-      </c>
-      <c r="J469" s="109" t="s">
-        <v>3681</v>
       </c>
       <c r="K469" s="109"/>
       <c r="L469" s="109"/>
@@ -55334,13 +55334,13 @@
         <v>137</v>
       </c>
       <c r="N469" s="38" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="O469" s="322"/>
       <c r="P469" s="126"/>
       <c r="Q469" s="56"/>
       <c r="R469" s="36" t="s">
-        <v>3683</v>
+        <v>3682</v>
       </c>
       <c r="S469" s="77" t="s">
         <v>41</v>
@@ -55349,19 +55349,19 @@
       <c r="U469" s="28"/>
       <c r="V469" s="28"/>
       <c r="W469" s="112" t="s">
+        <v>3683</v>
+      </c>
+      <c r="X469" s="29" t="s">
         <v>3684</v>
       </c>
-      <c r="X469" s="29" t="s">
+      <c r="Y469" s="30" t="s">
         <v>3685</v>
-      </c>
-      <c r="Y469" s="30" t="s">
-        <v>3686</v>
       </c>
       <c r="Z469" s="30"/>
       <c r="AA469" s="30"/>
       <c r="AB469" s="31"/>
       <c r="AC469" s="69" t="s">
-        <v>3687</v>
+        <v>3686</v>
       </c>
       <c r="AD469" s="21"/>
       <c r="AE469" s="32"/>
@@ -55380,7 +55380,7 @@
     </row>
     <row r="470" spans="1:43" ht="15.75" customHeight="1">
       <c r="A470" s="296" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="B470" s="95" t="s">
         <v>434</v>
@@ -55391,16 +55391,16 @@
       <c r="D470" s="236"/>
       <c r="E470" s="67"/>
       <c r="F470" s="290" t="s">
+        <v>3687</v>
+      </c>
+      <c r="G470" s="438" t="s">
         <v>3688</v>
       </c>
-      <c r="G470" s="438" t="s">
+      <c r="H470" s="48" t="s">
         <v>3689</v>
       </c>
-      <c r="H470" s="48" t="s">
+      <c r="I470" s="187" t="s">
         <v>3690</v>
-      </c>
-      <c r="I470" s="187" t="s">
-        <v>3691</v>
       </c>
       <c r="J470" s="22"/>
       <c r="K470" s="22"/>
@@ -55409,17 +55409,17 @@
         <v>2480</v>
       </c>
       <c r="N470" s="54" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="O470" s="54"/>
       <c r="P470" s="74" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="Q470" s="56" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="R470" s="48" t="s">
-        <v>3998</v>
+        <v>3996</v>
       </c>
       <c r="S470" s="77" t="s">
         <v>41</v>
@@ -55451,7 +55451,7 @@
     </row>
     <row r="471" spans="1:43" ht="15.75" customHeight="1">
       <c r="A471" s="186" t="s">
-        <v>3693</v>
+        <v>3692</v>
       </c>
       <c r="B471" s="95" t="s">
         <v>434</v>
@@ -55462,13 +55462,13 @@
       <c r="D471" s="235"/>
       <c r="E471" s="58"/>
       <c r="F471" s="47" t="s">
+        <v>3693</v>
+      </c>
+      <c r="G471" s="39" t="s">
         <v>3694</v>
       </c>
-      <c r="G471" s="39" t="s">
+      <c r="H471" s="95" t="s">
         <v>3695</v>
-      </c>
-      <c r="H471" s="95" t="s">
-        <v>3696</v>
       </c>
       <c r="I471" s="187" t="s">
         <v>2638</v>
@@ -55476,13 +55476,13 @@
       <c r="J471" s="82"/>
       <c r="K471" s="82"/>
       <c r="L471" s="82" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
       <c r="M471" s="137" t="s">
         <v>804</v>
       </c>
       <c r="N471" s="65" t="s">
-        <v>3698</v>
+        <v>3697</v>
       </c>
       <c r="O471" s="38"/>
       <c r="P471" s="25"/>
@@ -55497,13 +55497,13 @@
       <c r="U471" s="28"/>
       <c r="V471" s="28"/>
       <c r="W471" s="29" t="s">
+        <v>3698</v>
+      </c>
+      <c r="X471" s="29" t="s">
         <v>3699</v>
       </c>
-      <c r="X471" s="29" t="s">
+      <c r="Y471" s="30" t="s">
         <v>3700</v>
-      </c>
-      <c r="Y471" s="30" t="s">
-        <v>3701</v>
       </c>
       <c r="Z471" s="30"/>
       <c r="AA471" s="30"/>
@@ -55526,36 +55526,36 @@
     </row>
     <row r="472" spans="1:43" ht="15.75" customHeight="1">
       <c r="A472" s="186" t="s">
-        <v>3702</v>
+        <v>3701</v>
       </c>
       <c r="B472" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C472" s="295" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="D472" s="235"/>
       <c r="E472" s="58"/>
       <c r="F472" s="290" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="G472" s="39"/>
       <c r="H472" s="48" t="s">
+        <v>3702</v>
+      </c>
+      <c r="I472" s="115" t="s">
         <v>3703</v>
-      </c>
-      <c r="I472" s="115" t="s">
-        <v>3704</v>
       </c>
       <c r="J472" s="82"/>
       <c r="K472" s="82"/>
       <c r="L472" s="82" t="s">
+        <v>3704</v>
+      </c>
+      <c r="M472" s="32" t="s">
         <v>3705</v>
       </c>
-      <c r="M472" s="32" t="s">
+      <c r="N472" s="38" t="s">
         <v>3706</v>
-      </c>
-      <c r="N472" s="38" t="s">
-        <v>3707</v>
       </c>
       <c r="O472" s="38"/>
       <c r="P472" s="25"/>
@@ -55593,7 +55593,7 @@
     </row>
     <row r="473" spans="1:43" ht="15.75" customHeight="1">
       <c r="A473" s="416" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
       <c r="B473" s="95" t="s">
         <v>2283</v>
@@ -55604,13 +55604,13 @@
       <c r="D473" s="236"/>
       <c r="E473" s="67"/>
       <c r="F473" s="328" t="s">
+        <v>3708</v>
+      </c>
+      <c r="G473" s="39" t="s">
         <v>3709</v>
       </c>
-      <c r="G473" s="39" t="s">
+      <c r="H473" s="438" t="s">
         <v>3710</v>
-      </c>
-      <c r="H473" s="438" t="s">
-        <v>3711</v>
       </c>
       <c r="I473" s="441" t="s">
         <v>2638</v>
@@ -55621,10 +55621,10 @@
       <c r="K473" s="82"/>
       <c r="L473" s="82"/>
       <c r="M473" s="331" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N473" s="456" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="O473" s="322"/>
       <c r="P473" s="126"/>
@@ -55662,7 +55662,7 @@
     </row>
     <row r="474" spans="1:43" ht="15.75" customHeight="1">
       <c r="A474" s="186" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="B474" s="95" t="s">
         <v>2283</v>
@@ -55673,11 +55673,11 @@
       <c r="D474" s="235"/>
       <c r="E474" s="58"/>
       <c r="F474" s="290" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="G474" s="39"/>
       <c r="H474" s="206" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="I474" s="192" t="s">
         <v>2506</v>
@@ -55691,7 +55691,7 @@
         <v>804</v>
       </c>
       <c r="N474" s="38" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="O474" s="38" t="s">
         <v>806</v>
@@ -55713,10 +55713,10 @@
       <c r="X474" s="29"/>
       <c r="Y474" s="30"/>
       <c r="Z474" s="30" t="s">
+        <v>3715</v>
+      </c>
+      <c r="AA474" s="30" t="s">
         <v>3716</v>
-      </c>
-      <c r="AA474" s="30" t="s">
-        <v>3717</v>
       </c>
       <c r="AB474" s="41"/>
       <c r="AC474" s="32"/>
@@ -55737,7 +55737,7 @@
     </row>
     <row r="475" spans="1:43" ht="15.75" customHeight="1">
       <c r="A475" s="282" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="B475" s="95" t="s">
         <v>2283</v>
@@ -55748,14 +55748,14 @@
       <c r="D475" s="235"/>
       <c r="E475" s="58"/>
       <c r="F475" s="290" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="G475" s="32"/>
       <c r="H475" s="48" t="s">
+        <v>3718</v>
+      </c>
+      <c r="I475" s="187" t="s">
         <v>3719</v>
-      </c>
-      <c r="I475" s="187" t="s">
-        <v>3720</v>
       </c>
       <c r="J475" s="22"/>
       <c r="K475" s="22"/>
@@ -55764,14 +55764,14 @@
         <v>1619</v>
       </c>
       <c r="N475" s="38" t="s">
+        <v>3720</v>
+      </c>
+      <c r="O475" s="38" t="s">
         <v>3721</v>
-      </c>
-      <c r="O475" s="38" t="s">
-        <v>3722</v>
       </c>
       <c r="P475" s="25"/>
       <c r="Q475" s="26" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="R475" s="32" t="s">
         <v>523</v>
@@ -55783,19 +55783,19 @@
       <c r="U475" s="106"/>
       <c r="V475" s="28"/>
       <c r="W475" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X475" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X475" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y475" s="30" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="Z475" s="30" t="s">
+        <v>3723</v>
+      </c>
+      <c r="AA475" s="30" t="s">
         <v>3724</v>
-      </c>
-      <c r="AA475" s="30" t="s">
-        <v>3725</v>
       </c>
       <c r="AB475" s="41"/>
       <c r="AC475" s="32"/>
@@ -55816,40 +55816,40 @@
     </row>
     <row r="476" spans="1:43" ht="15.75" customHeight="1">
       <c r="A476" s="281" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
       <c r="B476" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C476" s="256" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
       <c r="D476" s="235"/>
       <c r="E476" s="58"/>
       <c r="F476" s="16" t="s">
+        <v>3727</v>
+      </c>
+      <c r="G476" s="32" t="s">
         <v>3728</v>
       </c>
-      <c r="G476" s="32" t="s">
+      <c r="H476" s="95" t="s">
         <v>3729</v>
       </c>
-      <c r="H476" s="95" t="s">
+      <c r="I476" s="187" t="s">
         <v>3730</v>
       </c>
-      <c r="I476" s="187" t="s">
-        <v>3731</v>
-      </c>
       <c r="J476" s="22" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="K476" s="93" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="L476" s="22"/>
       <c r="M476" s="331" t="s">
+        <v>3731</v>
+      </c>
+      <c r="N476" s="65" t="s">
         <v>3732</v>
-      </c>
-      <c r="N476" s="65" t="s">
-        <v>3733</v>
       </c>
       <c r="O476" s="38"/>
       <c r="P476" s="25"/>
@@ -55861,23 +55861,23 @@
         <v>41</v>
       </c>
       <c r="T476" s="21" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
       <c r="U476" s="28"/>
       <c r="V476" s="28"/>
       <c r="W476" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X476" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X476" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y476" s="30" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
       <c r="Z476" s="30"/>
       <c r="AA476" s="30"/>
       <c r="AB476" s="31" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
       <c r="AC476" s="32"/>
       <c r="AD476" s="32"/>
@@ -55897,7 +55897,7 @@
     </row>
     <row r="477" spans="1:43" ht="15.75" customHeight="1">
       <c r="A477" s="186" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
       <c r="B477" s="95" t="s">
         <v>2283</v>
@@ -55908,27 +55908,27 @@
       <c r="D477" s="236"/>
       <c r="E477" s="58"/>
       <c r="F477" s="47" t="s">
+        <v>3737</v>
+      </c>
+      <c r="G477" s="32" t="s">
         <v>3738</v>
       </c>
-      <c r="G477" s="32" t="s">
+      <c r="H477" s="95" t="s">
         <v>3739</v>
-      </c>
-      <c r="H477" s="95" t="s">
-        <v>3740</v>
       </c>
       <c r="I477" s="187" t="s">
         <v>2638</v>
       </c>
       <c r="J477" s="22" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="K477" s="22"/>
       <c r="L477" s="22"/>
       <c r="M477" s="137" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N477" s="136" t="s">
-        <v>3741</v>
+        <v>3740</v>
       </c>
       <c r="O477" s="54"/>
       <c r="P477" s="55"/>
@@ -55940,23 +55940,23 @@
         <v>41</v>
       </c>
       <c r="T477" s="21" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
       <c r="U477" s="28"/>
       <c r="V477" s="28"/>
       <c r="W477" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X477" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X477" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y477" s="30" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="Z477" s="30"/>
       <c r="AA477" s="30"/>
       <c r="AB477" s="46" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
       <c r="AC477" s="32"/>
       <c r="AD477" s="32"/>
@@ -55976,7 +55976,7 @@
     </row>
     <row r="478" spans="1:43" ht="15.75" customHeight="1">
       <c r="A478" s="186" t="s">
-        <v>3745</v>
+        <v>3744</v>
       </c>
       <c r="B478" s="95" t="s">
         <v>2283</v>
@@ -55987,27 +55987,27 @@
       <c r="D478" s="236"/>
       <c r="E478" s="58"/>
       <c r="F478" s="328" t="s">
+        <v>3745</v>
+      </c>
+      <c r="G478" s="32" t="s">
         <v>3746</v>
       </c>
-      <c r="G478" s="32" t="s">
+      <c r="H478" s="95" t="s">
         <v>3747</v>
       </c>
-      <c r="H478" s="95" t="s">
+      <c r="I478" s="187" t="s">
         <v>3748</v>
-      </c>
-      <c r="I478" s="187" t="s">
-        <v>3749</v>
       </c>
       <c r="J478" s="22"/>
       <c r="K478" s="93" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="L478" s="22"/>
       <c r="M478" s="212" t="s">
         <v>2729</v>
       </c>
       <c r="N478" s="136" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="O478" s="54"/>
       <c r="P478" s="55"/>
@@ -56019,18 +56019,18 @@
         <v>41</v>
       </c>
       <c r="T478" s="21" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
       <c r="U478" s="28"/>
       <c r="V478" s="28"/>
       <c r="W478" s="113" t="s">
+        <v>3150</v>
+      </c>
+      <c r="X478" s="120" t="s">
         <v>3151</v>
       </c>
-      <c r="X478" s="120" t="s">
-        <v>3152</v>
-      </c>
       <c r="Y478" s="30" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="Z478" s="30"/>
       <c r="AA478" s="30"/>
@@ -56053,33 +56053,33 @@
     </row>
     <row r="479" spans="1:43" ht="15.75" customHeight="1">
       <c r="A479" s="281" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="B479" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C479" s="249" t="s">
-        <v>3754</v>
+        <v>3753</v>
       </c>
       <c r="D479" s="235"/>
       <c r="E479" s="138"/>
       <c r="F479" s="47" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="G479" s="32"/>
       <c r="H479" s="48" t="s">
+        <v>3755</v>
+      </c>
+      <c r="I479" s="115" t="s">
         <v>3756</v>
       </c>
-      <c r="I479" s="115" t="s">
+      <c r="J479" s="22" t="s">
         <v>3757</v>
-      </c>
-      <c r="J479" s="22" t="s">
-        <v>3758</v>
       </c>
       <c r="K479" s="22"/>
       <c r="L479" s="22"/>
       <c r="M479" s="137" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="N479" s="54" t="s">
         <v>2130</v>
@@ -56094,7 +56094,7 @@
         <v>41</v>
       </c>
       <c r="T479" s="21" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="U479" s="28"/>
       <c r="V479" s="28"/>
@@ -56122,7 +56122,7 @@
     </row>
     <row r="480" spans="1:43" ht="54" customHeight="1">
       <c r="A480" s="48" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="B480" s="95" t="s">
         <v>2283</v>
@@ -56133,27 +56133,27 @@
       <c r="D480" s="236"/>
       <c r="E480" s="58"/>
       <c r="F480" s="47" t="s">
+        <v>3761</v>
+      </c>
+      <c r="G480" s="32" t="s">
         <v>3762</v>
       </c>
-      <c r="G480" s="32" t="s">
+      <c r="H480" s="48" t="s">
         <v>3763</v>
-      </c>
-      <c r="H480" s="48" t="s">
-        <v>3764</v>
       </c>
       <c r="I480" s="32" t="s">
         <v>2638</v>
       </c>
       <c r="J480" s="22"/>
       <c r="K480" s="22" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="L480" s="22"/>
       <c r="M480" s="32" t="s">
         <v>2218</v>
       </c>
       <c r="N480" s="65" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="O480" s="38"/>
       <c r="P480" s="25"/>
@@ -56165,7 +56165,7 @@
         <v>41</v>
       </c>
       <c r="T480" s="21" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="U480" s="28"/>
       <c r="V480" s="28"/>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0B6408-6927-DB48-A504-156D668AE27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5069F2B8-E185-3244-93FA-8740862805E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3760" yWindow="-21000" windowWidth="37740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4240" yWindow="-18180" windowWidth="37740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -12887,9 +12887,6 @@
     </r>
   </si>
   <si>
-    <t>1689-06_305</t>
-  </si>
-  <si>
     <t>Bibliothèque municipale de Lyon, SJ Z 494 a</t>
   </si>
   <si>
@@ -17462,6 +17459,9 @@
   </si>
   <si>
     <t>1689-04a_236</t>
+  </si>
+  <si>
+    <t>1689-06a_305</t>
   </si>
 </sst>
 </file>
@@ -20606,7 +20606,7 @@
     </row>
     <row r="2" spans="1:43" ht="15.75" customHeight="1">
       <c r="A2" s="274" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>30</v>
@@ -20814,7 +20814,7 @@
       <c r="W4" s="29"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="30" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="Z4" s="30"/>
       <c r="AA4" s="30"/>
@@ -20841,7 +20841,7 @@
     </row>
     <row r="5" spans="1:43" ht="15.75" customHeight="1">
       <c r="A5" s="275" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>72</v>
@@ -20916,7 +20916,7 @@
     </row>
     <row r="6" spans="1:43" ht="15.75" customHeight="1">
       <c r="A6" s="289" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>43</v>
@@ -21066,7 +21066,7 @@
     </row>
     <row r="8" spans="1:43" ht="15.75" customHeight="1">
       <c r="A8" s="275" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>100</v>
@@ -21212,7 +21212,7 @@
     </row>
     <row r="10" spans="1:43" ht="15.75" customHeight="1">
       <c r="A10" s="274" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>100</v>
@@ -21364,7 +21364,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="251" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="D12" s="236"/>
       <c r="E12" s="67"/>
@@ -21435,7 +21435,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="251" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="D13" s="235"/>
       <c r="E13" s="58"/>
@@ -21642,13 +21642,13 @@
     </row>
     <row r="16" spans="1:43" ht="15.75" customHeight="1">
       <c r="A16" s="276" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="264" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="D16" s="234" t="s">
         <v>179</v>
@@ -21702,7 +21702,7 @@
         <v>191</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="Z16" s="30"/>
       <c r="AA16" s="30"/>
@@ -21735,7 +21735,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="267" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="D17" s="234" t="s">
         <v>179</v>
@@ -21990,7 +21990,7 @@
     </row>
     <row r="20" spans="1:43" ht="15.75" customHeight="1">
       <c r="A20" s="276" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="B20" s="32" t="s">
         <v>43</v>
@@ -22075,7 +22075,7 @@
     </row>
     <row r="21" spans="1:43" ht="15.75" customHeight="1">
       <c r="A21" s="268" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
       <c r="B21" s="32" t="s">
         <v>43</v>
@@ -22306,7 +22306,7 @@
     </row>
     <row r="24" spans="1:43" ht="15.75" customHeight="1">
       <c r="A24" s="277" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="B24" s="32" t="s">
         <v>247</v>
@@ -22375,7 +22375,7 @@
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
       <c r="A25" s="277" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>247</v>
@@ -22444,13 +22444,13 @@
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
       <c r="A26" s="291" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="250" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="D26" s="234" t="s">
         <v>179</v>
@@ -22515,7 +22515,7 @@
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
       <c r="A27" s="277" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="B27" s="32" t="s">
         <v>247</v>
@@ -22600,7 +22600,7 @@
         <v>43</v>
       </c>
       <c r="C28" s="250" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="D28" s="234" t="s">
         <v>179</v>
@@ -22665,7 +22665,7 @@
     </row>
     <row r="29" spans="1:43" ht="15.75" customHeight="1">
       <c r="A29" s="274" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>279</v>
@@ -22740,7 +22740,7 @@
     </row>
     <row r="30" spans="1:43" ht="15.75" customHeight="1">
       <c r="A30" s="274" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="B30" s="33" t="s">
         <v>292</v>
@@ -22821,13 +22821,13 @@
     </row>
     <row r="31" spans="1:43" ht="15.75" customHeight="1">
       <c r="A31" s="277" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="B31" s="33" t="s">
         <v>292</v>
       </c>
       <c r="C31" s="250" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="D31" s="232"/>
       <c r="E31" s="18"/>
@@ -22894,7 +22894,7 @@
     </row>
     <row r="32" spans="1:43" ht="15.75" customHeight="1">
       <c r="A32" s="274" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="B32" s="32" t="s">
         <v>310</v>
@@ -22975,7 +22975,7 @@
         <v>292</v>
       </c>
       <c r="C33" s="250" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="D33" s="232"/>
       <c r="E33" s="18"/>
@@ -23040,13 +23040,13 @@
     </row>
     <row r="34" spans="1:43" ht="15.75" customHeight="1">
       <c r="A34" s="278" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="B34" s="95" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="251" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="D34" s="234" t="s">
         <v>280</v>
@@ -23121,13 +23121,13 @@
     </row>
     <row r="35" spans="1:43" ht="15.75" customHeight="1">
       <c r="A35" s="277" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="251" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="D35" s="234" t="s">
         <v>280</v>
@@ -23202,13 +23202,13 @@
     </row>
     <row r="36" spans="1:43" ht="15.75" customHeight="1">
       <c r="A36" s="277" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="250" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="D36" s="235"/>
       <c r="E36" s="58"/>
@@ -23352,7 +23352,7 @@
     </row>
     <row r="38" spans="1:43" ht="15.75" customHeight="1">
       <c r="A38" s="274" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>43</v>
@@ -23361,7 +23361,7 @@
         <v>359</v>
       </c>
       <c r="D38" s="235" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="E38" s="58"/>
       <c r="F38" s="32" t="s">
@@ -23431,7 +23431,7 @@
     </row>
     <row r="39" spans="1:43" ht="15.75" customHeight="1">
       <c r="A39" s="274" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>43</v>
@@ -23508,7 +23508,7 @@
         <v>377</v>
       </c>
       <c r="C40" s="250" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="D40" s="235"/>
       <c r="E40" s="58"/>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="48" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="I41" s="43" t="s">
         <v>384</v>
@@ -23595,7 +23595,7 @@
         <v>385</v>
       </c>
       <c r="M41" s="95" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="N41" s="54" t="s">
         <v>386</v>
@@ -23636,13 +23636,13 @@
     </row>
     <row r="42" spans="1:43" ht="15.75" customHeight="1">
       <c r="A42" s="277" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="250" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="D42" s="235"/>
       <c r="E42" s="58"/>
@@ -23707,13 +23707,13 @@
     </row>
     <row r="43" spans="1:43" ht="15.75" customHeight="1">
       <c r="A43" s="277" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="250" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="D43" s="235"/>
       <c r="E43" s="58"/>
@@ -23759,7 +23759,7 @@
         <v>404</v>
       </c>
       <c r="Y43" s="30" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="Z43" s="30"/>
       <c r="AA43" s="30"/>
@@ -23918,13 +23918,13 @@
     </row>
     <row r="46" spans="1:43" ht="15.75" customHeight="1">
       <c r="A46" s="277" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="250" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="D46" s="235"/>
       <c r="E46" s="58"/>
@@ -24001,7 +24001,7 @@
         <v>413</v>
       </c>
       <c r="C47" s="250" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="D47" s="235"/>
       <c r="E47" s="58"/>
@@ -24062,13 +24062,13 @@
     </row>
     <row r="48" spans="1:43" ht="15.75" customHeight="1">
       <c r="A48" s="277" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="B48" s="32" t="s">
         <v>434</v>
       </c>
       <c r="C48" s="250" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="D48" s="235"/>
       <c r="E48" s="58"/>
@@ -24219,13 +24219,13 @@
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>434</v>
       </c>
       <c r="C50" s="250" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="D50" s="235"/>
       <c r="E50" s="58"/>
@@ -24290,13 +24290,13 @@
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>444</v>
       </c>
       <c r="C51" s="250" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
       <c r="D51" s="234" t="s">
         <v>465</v>
@@ -24361,7 +24361,7 @@
     </row>
     <row r="52" spans="1:43" ht="15.75" customHeight="1">
       <c r="A52" s="277" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>471</v>
@@ -24523,7 +24523,7 @@
     </row>
     <row r="54" spans="1:43" ht="15.75" customHeight="1">
       <c r="A54" s="277" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="B54" s="131" t="s">
         <v>497</v>
@@ -24602,7 +24602,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="250" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="D55" s="235"/>
       <c r="E55" s="58"/>
@@ -24742,7 +24742,7 @@
     </row>
     <row r="57" spans="1:43" ht="15.75" customHeight="1">
       <c r="A57" s="277" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="B57" s="32" t="s">
         <v>43</v>
@@ -24809,13 +24809,13 @@
     </row>
     <row r="58" spans="1:43" ht="15.75" customHeight="1">
       <c r="A58" s="277" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="B58" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="250" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="D58" s="234" t="s">
         <v>179</v>
@@ -24884,13 +24884,13 @@
     </row>
     <row r="59" spans="1:43" ht="15.75" customHeight="1">
       <c r="A59" s="277" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="B59" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="250" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="D59" s="234" t="s">
         <v>179</v>
@@ -24955,7 +24955,7 @@
     </row>
     <row r="60" spans="1:43" ht="15.75" customHeight="1">
       <c r="A60" s="277" t="s">
-        <v>3907</v>
+        <v>3906</v>
       </c>
       <c r="B60" s="32" t="s">
         <v>43</v>
@@ -25030,18 +25030,18 @@
     </row>
     <row r="61" spans="1:43" ht="15.75" customHeight="1">
       <c r="A61" s="277" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="B61" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="250" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
       <c r="D61" s="235"/>
       <c r="E61" s="58"/>
       <c r="F61" s="47" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>549</v>
@@ -25101,7 +25101,7 @@
     </row>
     <row r="62" spans="1:43" ht="15.75" customHeight="1">
       <c r="A62" s="277" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="B62" s="32" t="s">
         <v>43</v>
@@ -25174,13 +25174,13 @@
         <v>564</v>
       </c>
       <c r="C63" s="250" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="D63" s="234" t="s">
         <v>565</v>
       </c>
       <c r="E63" s="58" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="F63" s="290" t="s">
         <v>566</v>
@@ -25241,13 +25241,13 @@
     </row>
     <row r="64" spans="1:43" ht="15.75" customHeight="1">
       <c r="A64" s="277" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="250" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="D64" s="235"/>
       <c r="E64" s="58"/>
@@ -25314,13 +25314,13 @@
     </row>
     <row r="65" spans="1:43" ht="15.75" customHeight="1">
       <c r="A65" s="277" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="B65" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="250" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="D65" s="235"/>
       <c r="E65" s="58"/>
@@ -25387,7 +25387,7 @@
     </row>
     <row r="66" spans="1:43" ht="15.75" customHeight="1">
       <c r="A66" s="277" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="B66" s="32" t="s">
         <v>43</v>
@@ -25620,7 +25620,7 @@
     </row>
     <row r="69" spans="1:43" ht="15.75" customHeight="1">
       <c r="A69" s="366" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="B69" s="314" t="s">
         <v>43</v>
@@ -25707,7 +25707,7 @@
     </row>
     <row r="70" spans="1:43" ht="15.75" customHeight="1">
       <c r="A70" s="274" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="B70" s="32" t="s">
         <v>43</v>
@@ -25776,13 +25776,13 @@
     </row>
     <row r="71" spans="1:43" ht="15.75" customHeight="1">
       <c r="A71" s="277" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="B71" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="250" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="D71" s="235"/>
       <c r="E71" s="58"/>
@@ -25845,7 +25845,7 @@
     </row>
     <row r="72" spans="1:43" ht="15.75" customHeight="1">
       <c r="A72" s="274" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="B72" s="32" t="s">
         <v>644</v>
@@ -25991,7 +25991,7 @@
     </row>
     <row r="74" spans="1:43" ht="15.75" customHeight="1">
       <c r="A74" s="274" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="B74" s="39" t="s">
         <v>43</v>
@@ -26066,7 +26066,7 @@
         <v>43</v>
       </c>
       <c r="C75" s="250" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
       <c r="D75" s="337"/>
       <c r="E75" s="58"/>
@@ -26713,7 +26713,7 @@
     </row>
     <row r="84" spans="1:43" ht="15.75" customHeight="1">
       <c r="A84" s="274" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>749</v>
@@ -26849,7 +26849,7 @@
     </row>
     <row r="86" spans="1:43" ht="15.75" customHeight="1">
       <c r="A86" s="274" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>434</v>
@@ -27226,7 +27226,7 @@
     </row>
     <row r="91" spans="1:43" ht="15.75" customHeight="1">
       <c r="A91" s="274" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>43</v>
@@ -27579,7 +27579,7 @@
     </row>
     <row r="96" spans="1:43" ht="15.75" customHeight="1">
       <c r="A96" s="277" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>434</v>
@@ -27646,7 +27646,7 @@
     </row>
     <row r="97" spans="1:43" ht="15.75" customHeight="1">
       <c r="A97" s="277" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="B97" s="32" t="s">
         <v>43</v>
@@ -27849,7 +27849,7 @@
     </row>
     <row r="100" spans="1:43" ht="15.75" customHeight="1">
       <c r="A100" s="277" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="B100" s="32" t="s">
         <v>870</v>
@@ -27995,7 +27995,7 @@
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
       <c r="A102" s="277" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>890</v>
@@ -28141,7 +28141,7 @@
     </row>
     <row r="104" spans="1:43" ht="15.75" customHeight="1">
       <c r="A104" s="277" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="B104" s="32" t="s">
         <v>471</v>
@@ -28354,7 +28354,7 @@
     </row>
     <row r="107" spans="1:43" ht="15.75" customHeight="1">
       <c r="A107" s="277" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="B107" s="32" t="s">
         <v>43</v>
@@ -28437,7 +28437,7 @@
     </row>
     <row r="108" spans="1:43" ht="15.75" customHeight="1">
       <c r="A108" s="277" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="B108" s="32" t="s">
         <v>43</v>
@@ -28644,7 +28644,7 @@
     </row>
     <row r="111" spans="1:43" ht="15.75" customHeight="1">
       <c r="A111" s="277" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="B111" s="32" t="s">
         <v>43</v>
@@ -28857,7 +28857,7 @@
     </row>
     <row r="114" spans="1:43" ht="15.75" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="B114" s="32" t="s">
         <v>434</v>
@@ -29220,7 +29220,7 @@
     </row>
     <row r="119" spans="1:43" ht="15.75" customHeight="1">
       <c r="A119" s="277" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>43</v>
@@ -29235,7 +29235,7 @@
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="32" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="I119" s="43" t="s">
         <v>1037</v>
@@ -29431,7 +29431,7 @@
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
       <c r="A122" s="278" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="B122" s="51" t="s">
         <v>43</v>
@@ -29483,7 +29483,7 @@
       <c r="W122" s="29"/>
       <c r="X122" s="29"/>
       <c r="Y122" s="30" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="Z122" s="30"/>
       <c r="AA122" s="30"/>
@@ -29948,7 +29948,7 @@
     </row>
     <row r="129" spans="1:43" ht="15.75" customHeight="1">
       <c r="A129" s="278" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="B129" s="32" t="s">
         <v>43</v>
@@ -30019,7 +30019,7 @@
     </row>
     <row r="130" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A130" s="277" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>43</v>
@@ -30092,7 +30092,7 @@
     </row>
     <row r="131" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A131" s="277" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="B131" s="33" t="s">
         <v>43</v>
@@ -30528,7 +30528,7 @@
     </row>
     <row r="137" spans="1:43" ht="15.75" customHeight="1">
       <c r="A137" s="277" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>43</v>
@@ -30543,7 +30543,7 @@
       </c>
       <c r="G137" s="32"/>
       <c r="H137" s="48" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="I137" s="43" t="s">
         <v>1185</v>
@@ -30668,7 +30668,7 @@
     </row>
     <row r="139" spans="1:43" ht="15.75" customHeight="1">
       <c r="A139" s="278" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="B139" s="33" t="s">
         <v>43</v>
@@ -30683,7 +30683,7 @@
       </c>
       <c r="G139" s="32"/>
       <c r="H139" s="48" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="I139" s="43" t="s">
         <v>1199</v>
@@ -32733,7 +32733,7 @@
         <v>176</v>
       </c>
       <c r="N167" s="136" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="O167" s="136"/>
       <c r="P167" s="155" t="s">
@@ -32743,7 +32743,7 @@
         <v>1419</v>
       </c>
       <c r="R167" s="39" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="S167" s="21" t="s">
         <v>41</v>
@@ -32856,7 +32856,7 @@
     </row>
     <row r="169" spans="1:43" ht="15.75" customHeight="1">
       <c r="A169" s="277" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="B169" s="33" t="s">
         <v>43</v>
@@ -33286,7 +33286,7 @@
     </row>
     <row r="175" spans="1:43" ht="15.75" customHeight="1">
       <c r="A175" s="277" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="B175" s="33" t="s">
         <v>43</v>
@@ -33355,7 +33355,7 @@
     </row>
     <row r="176" spans="1:43" ht="15.75" customHeight="1">
       <c r="A176" s="277" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="B176" s="33" t="s">
         <v>43</v>
@@ -33422,7 +33422,7 @@
     </row>
     <row r="177" spans="1:43" s="410" customFormat="1" ht="15.75" customHeight="1">
       <c r="A177" s="278" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="B177" s="15" t="s">
         <v>471</v>
@@ -33880,7 +33880,7 @@
     </row>
     <row r="183" spans="1:43" ht="15.75" customHeight="1">
       <c r="A183" s="277" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="B183" s="33" t="s">
         <v>43</v>
@@ -33949,7 +33949,7 @@
     </row>
     <row r="184" spans="1:43" ht="15.75" customHeight="1">
       <c r="A184" s="277" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="B184" s="33" t="s">
         <v>43</v>
@@ -34383,7 +34383,7 @@
     </row>
     <row r="190" spans="1:43" ht="15.75" customHeight="1">
       <c r="A190" s="278" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="B190" s="15" t="s">
         <v>43</v>
@@ -34594,13 +34594,13 @@
     </row>
     <row r="193" spans="1:43" ht="15.75" customHeight="1">
       <c r="A193" s="277" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="B193" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C193" s="251" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="D193" s="235"/>
       <c r="E193" s="58"/>
@@ -34851,7 +34851,7 @@
         <v>1654</v>
       </c>
       <c r="M196" s="95" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="N196" s="54" t="s">
         <v>1655</v>
@@ -35468,7 +35468,7 @@
     </row>
     <row r="205" spans="1:43" ht="15.75" customHeight="1">
       <c r="A205" s="277" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="B205" s="33" t="s">
         <v>43</v>
@@ -35614,7 +35614,7 @@
     </row>
     <row r="207" spans="1:43" ht="15.75" customHeight="1">
       <c r="A207" s="277" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>434</v>
@@ -35932,7 +35932,7 @@
     </row>
     <row r="211" spans="1:43" ht="15.75" customHeight="1">
       <c r="A211" s="277" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>1006</v>
@@ -36094,7 +36094,7 @@
     </row>
     <row r="213" spans="1:43" ht="15.75" customHeight="1">
       <c r="A213" s="277" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>434</v>
@@ -36147,7 +36147,7 @@
       <c r="AB213" s="167"/>
       <c r="AC213" s="32"/>
       <c r="AD213" s="21" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="AE213" s="32"/>
       <c r="AF213" s="32"/>
@@ -36747,7 +36747,7 @@
     </row>
     <row r="222" spans="1:43" ht="15.75" customHeight="1">
       <c r="A222" s="278" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>434</v>
@@ -36905,7 +36905,7 @@
     </row>
     <row r="224" spans="1:43" ht="15.75" customHeight="1">
       <c r="A224" s="277" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>1913</v>
@@ -36986,7 +36986,7 @@
     </row>
     <row r="225" spans="1:43" ht="15.75" customHeight="1">
       <c r="A225" s="277" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="B225" s="14" t="s">
         <v>434</v>
@@ -37144,10 +37144,10 @@
       <c r="K227" s="82"/>
       <c r="L227" s="22"/>
       <c r="M227" s="53" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N227" s="54" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="O227" s="458"/>
       <c r="P227" s="318" t="s">
@@ -37225,10 +37225,10 @@
       <c r="K228" s="22"/>
       <c r="L228" s="22"/>
       <c r="M228" s="53" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N228" s="54" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="O228" s="54"/>
       <c r="P228" s="318" t="s">
@@ -37641,13 +37641,13 @@
     </row>
     <row r="234" spans="1:43" ht="15.75" customHeight="1">
       <c r="A234" s="277" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>434</v>
       </c>
       <c r="C234" s="261" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="D234" s="235"/>
       <c r="E234" s="58"/>
@@ -37981,7 +37981,7 @@
         <v>2007</v>
       </c>
       <c r="M238" s="95" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="N238" s="38" t="s">
         <v>1655</v>
@@ -38068,10 +38068,10 @@
         <v>2018</v>
       </c>
       <c r="M239" s="127" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="N239" s="54" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="O239" s="54"/>
       <c r="P239" s="25" t="s">
@@ -38121,7 +38121,7 @@
     </row>
     <row r="240" spans="1:43" ht="15.75" customHeight="1">
       <c r="A240" s="277" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>434</v>
@@ -38226,7 +38226,7 @@
       <c r="K241" s="82"/>
       <c r="L241" s="82"/>
       <c r="M241" s="53" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N241" s="54" t="s">
         <v>2032</v>
@@ -38298,7 +38298,7 @@
         <v>2036</v>
       </c>
       <c r="H242" s="48" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="I242" s="43" t="s">
         <v>2037</v>
@@ -38307,7 +38307,7 @@
       <c r="K242" s="22"/>
       <c r="L242" s="22"/>
       <c r="M242" s="53" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N242" s="54" t="s">
         <v>2038</v>
@@ -38668,23 +38668,23 @@
     </row>
     <row r="247" spans="1:43" ht="15.75" customHeight="1">
       <c r="A247" s="419" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="B247" s="419" t="s">
         <v>2083</v>
       </c>
       <c r="C247" s="262" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="E247" s="230"/>
       <c r="F247" s="230" t="s">
+        <v>3770</v>
+      </c>
+      <c r="G247" s="230" t="s">
         <v>3771</v>
       </c>
-      <c r="G247" s="230" t="s">
-        <v>3772</v>
-      </c>
       <c r="H247" s="423" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="I247" s="421" t="s">
         <v>1911</v>
@@ -38693,10 +38693,10 @@
       <c r="K247" s="230"/>
       <c r="L247" s="230"/>
       <c r="M247" s="421" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N247" s="460" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="O247" s="459"/>
       <c r="P247" s="318" t="s">
@@ -38712,7 +38712,7 @@
         <v>41</v>
       </c>
       <c r="T247" s="423" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="U247" s="423" t="s">
         <v>1904</v>
@@ -38723,7 +38723,7 @@
       <c r="W247" s="230"/>
       <c r="X247" s="230"/>
       <c r="Y247" s="433" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="Z247" s="230"/>
       <c r="AA247" s="230"/>
@@ -38732,7 +38732,7 @@
         <v>2084</v>
       </c>
       <c r="AD247" s="230" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="AE247" s="230"/>
       <c r="AF247" s="230"/>
@@ -38750,19 +38750,19 @@
     </row>
     <row r="248" spans="1:43" ht="15.75" customHeight="1">
       <c r="A248" s="419" t="s">
+        <v>3765</v>
+      </c>
+      <c r="B248" s="423" t="s">
         <v>3766</v>
       </c>
-      <c r="B248" s="423" t="s">
-        <v>3767</v>
-      </c>
       <c r="C248" s="262" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="E248" s="230"/>
       <c r="F248" s="230"/>
       <c r="G248" s="423"/>
       <c r="H248" s="423" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="I248" s="421" t="s">
         <v>2031</v>
@@ -38771,10 +38771,10 @@
       <c r="K248" s="230"/>
       <c r="L248" s="230"/>
       <c r="M248" s="421" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N248" s="460" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="O248" s="459"/>
       <c r="P248" s="318" t="s">
@@ -38790,7 +38790,7 @@
         <v>41</v>
       </c>
       <c r="T248" s="423" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="U248" s="423" t="s">
         <v>1904</v>
@@ -38801,7 +38801,7 @@
       <c r="W248" s="230"/>
       <c r="X248" s="230"/>
       <c r="Y248" s="423" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="Z248" s="230"/>
       <c r="AA248" s="230"/>
@@ -39122,7 +39122,7 @@
         <v>434</v>
       </c>
       <c r="C253" s="251" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="D253" s="235"/>
       <c r="E253" s="58"/>
@@ -39481,7 +39481,7 @@
     </row>
     <row r="258" spans="1:43" ht="15.75" customHeight="1">
       <c r="A258" s="277" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="B258" s="14" t="s">
         <v>434</v>
@@ -39848,7 +39848,7 @@
     </row>
     <row r="263" spans="1:43" ht="15.75" customHeight="1">
       <c r="A263" s="277" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="B263" s="14" t="s">
         <v>434</v>
@@ -39988,7 +39988,7 @@
     </row>
     <row r="265" spans="1:43" ht="15.75" customHeight="1">
       <c r="A265" s="14" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="B265" s="14" t="s">
         <v>2209</v>
@@ -40014,10 +40014,10 @@
       <c r="K265" s="22"/>
       <c r="L265" s="22"/>
       <c r="M265" s="53" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N265" s="54" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="O265" s="54"/>
       <c r="P265" s="318" t="s">
@@ -40059,7 +40059,7 @@
     </row>
     <row r="266" spans="1:43" ht="15.75" customHeight="1">
       <c r="A266" s="277" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="B266" s="14" t="s">
         <v>434</v>
@@ -40278,7 +40278,7 @@
     </row>
     <row r="269" spans="1:43" ht="15.75" customHeight="1">
       <c r="A269" s="278" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="B269" s="66" t="s">
         <v>2239</v>
@@ -40381,10 +40381,10 @@
       <c r="K270" s="22"/>
       <c r="L270" s="22"/>
       <c r="M270" s="320" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N270" s="73" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="O270" s="73"/>
       <c r="P270" s="318" t="s">
@@ -40409,7 +40409,7 @@
       <c r="W270" s="29"/>
       <c r="X270" s="29"/>
       <c r="Y270" s="30" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="Z270" s="30"/>
       <c r="AA270" s="30"/>
@@ -40635,7 +40635,7 @@
     </row>
     <row r="274" spans="1:43" ht="15.75" customHeight="1">
       <c r="A274" s="14" t="s">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="B274" s="14" t="s">
         <v>434</v>
@@ -40882,10 +40882,10 @@
       <c r="K277" s="82"/>
       <c r="L277" s="22"/>
       <c r="M277" s="320" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N277" s="38" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="O277" s="38"/>
       <c r="P277" s="318" t="s">
@@ -41253,7 +41253,7 @@
       <c r="K282" s="22"/>
       <c r="L282" s="22"/>
       <c r="M282" s="320" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N282" s="504" t="s">
         <v>2457</v>
@@ -41281,7 +41281,7 @@
       <c r="W282" s="29"/>
       <c r="X282" s="29"/>
       <c r="Y282" s="30" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="Z282" s="30"/>
       <c r="AA282" s="30"/>
@@ -41345,7 +41345,7 @@
         <v>1905</v>
       </c>
       <c r="R283" s="32" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="S283" s="32" t="s">
         <v>41</v>
@@ -41541,10 +41541,10 @@
       <c r="K286" s="22"/>
       <c r="L286" s="22"/>
       <c r="M286" s="454" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N286" s="89" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="O286" s="89"/>
       <c r="P286" s="126" t="s">
@@ -41829,7 +41829,7 @@
       <c r="K290" s="82"/>
       <c r="L290" s="22"/>
       <c r="M290" s="320" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N290" s="54" t="s">
         <v>2380</v>
@@ -42121,10 +42121,10 @@
       <c r="K294" s="82"/>
       <c r="L294" s="82"/>
       <c r="M294" s="33" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="N294" s="89" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="O294" s="457"/>
       <c r="P294" s="114" t="s">
@@ -42149,7 +42149,7 @@
       <c r="W294" s="29"/>
       <c r="X294" s="29"/>
       <c r="Y294" s="30" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="Z294" s="30"/>
       <c r="AA294" s="30"/>
@@ -42174,7 +42174,7 @@
     </row>
     <row r="295" spans="1:43" ht="15.75" customHeight="1">
       <c r="A295" s="277" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="B295" s="14" t="s">
         <v>434</v>
@@ -42496,7 +42496,7 @@
       <c r="K299" s="22"/>
       <c r="L299" s="22"/>
       <c r="M299" s="320" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="N299" s="89" t="s">
         <v>2038</v>
@@ -42657,7 +42657,7 @@
         <v>2462</v>
       </c>
       <c r="N301" s="38" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="O301" s="38"/>
       <c r="P301" s="25"/>
@@ -42973,7 +42973,7 @@
     </row>
     <row r="306" spans="1:43" ht="15.75" customHeight="1">
       <c r="A306" s="282" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="B306" s="33" t="s">
         <v>434</v>
@@ -43131,7 +43131,7 @@
     </row>
     <row r="308" spans="1:43" ht="15.75" customHeight="1">
       <c r="A308" s="282" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="B308" s="33" t="s">
         <v>434</v>
@@ -43285,7 +43285,7 @@
     </row>
     <row r="310" spans="1:43" ht="15.75" customHeight="1">
       <c r="A310" s="284" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="B310" s="33" t="s">
         <v>434</v>
@@ -43300,7 +43300,7 @@
       </c>
       <c r="G310" s="32"/>
       <c r="H310" s="414" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="I310" s="32" t="s">
         <v>2506</v>
@@ -43881,13 +43881,13 @@
     </row>
     <row r="318" spans="1:43" ht="15.75" customHeight="1">
       <c r="A318" s="285" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="B318" s="33" t="s">
         <v>2597</v>
       </c>
       <c r="C318" s="263" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="E318" s="58" t="s">
         <v>2598</v>
@@ -44040,7 +44040,7 @@
     </row>
     <row r="320" spans="1:43" ht="15.75" customHeight="1">
       <c r="A320" s="282" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="B320" s="33" t="s">
         <v>434</v>
@@ -44109,7 +44109,7 @@
     </row>
     <row r="321" spans="1:43" ht="15.75" customHeight="1">
       <c r="A321" s="282" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="B321" s="33" t="s">
         <v>434</v>
@@ -44534,7 +44534,7 @@
         <v>2237</v>
       </c>
       <c r="Y326" s="30" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="Z326" s="30"/>
       <c r="AA326" s="30" t="s">
@@ -44646,7 +44646,7 @@
         <v>434</v>
       </c>
       <c r="C328" s="251" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="D328" s="247"/>
       <c r="E328" s="190"/>
@@ -44721,7 +44721,7 @@
     </row>
     <row r="329" spans="1:43" ht="15.75" customHeight="1">
       <c r="A329" s="186" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="B329" s="33" t="s">
         <v>434</v>
@@ -45425,7 +45425,7 @@
       </c>
       <c r="G338" s="48"/>
       <c r="H338" s="32" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="I338" s="187" t="s">
         <v>2766</v>
@@ -45439,7 +45439,7 @@
         <v>2768</v>
       </c>
       <c r="N338" s="38" t="s">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="O338" s="38"/>
       <c r="P338" s="25" t="s">
@@ -45449,7 +45449,7 @@
         <v>2770</v>
       </c>
       <c r="R338" s="503" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="S338" s="77" t="s">
         <v>41</v>
@@ -45716,7 +45716,7 @@
     </row>
     <row r="342" spans="1:43" ht="15.75" customHeight="1">
       <c r="A342" s="282" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="B342" s="33" t="s">
         <v>434</v>
@@ -45945,7 +45945,7 @@
     </row>
     <row r="345" spans="1:43" ht="15.75" customHeight="1">
       <c r="A345" s="282" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
       <c r="B345" s="33" t="s">
         <v>434</v>
@@ -46024,7 +46024,7 @@
     </row>
     <row r="346" spans="1:43" ht="15.75" customHeight="1">
       <c r="A346" s="193" t="s">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="B346" s="33" t="s">
         <v>434</v>
@@ -46259,7 +46259,7 @@
     </row>
     <row r="349" spans="1:43" ht="15.75" customHeight="1">
       <c r="A349" s="186" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="B349" s="33" t="s">
         <v>434</v>
@@ -46417,10 +46417,10 @@
     </row>
     <row r="351" spans="1:43" ht="15.75" customHeight="1">
       <c r="A351" s="186" t="s">
+        <v>4017</v>
+      </c>
+      <c r="B351" s="186" t="s">
         <v>2878</v>
-      </c>
-      <c r="B351" s="186" t="s">
-        <v>2879</v>
       </c>
       <c r="C351" s="250" t="s">
         <v>171</v>
@@ -46428,11 +46428,11 @@
       <c r="D351" s="235"/>
       <c r="E351" s="58"/>
       <c r="F351" s="290" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="G351" s="32"/>
       <c r="H351" s="192" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="I351" s="192" t="s">
         <v>2506</v>
@@ -46446,7 +46446,7 @@
         <v>2693</v>
       </c>
       <c r="N351" s="38" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="O351" s="322"/>
       <c r="P351" s="126"/>
@@ -46467,11 +46467,11 @@
         <v>2237</v>
       </c>
       <c r="Y351" s="30" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="Z351" s="200"/>
       <c r="AA351" s="30" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="AB351" s="31"/>
       <c r="AC351" s="32"/>
@@ -46492,7 +46492,7 @@
     </row>
     <row r="352" spans="1:43" ht="15.75" customHeight="1">
       <c r="A352" s="186" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="B352" s="33" t="s">
         <v>434</v>
@@ -46503,23 +46503,23 @@
       <c r="D352" s="235"/>
       <c r="E352" s="58"/>
       <c r="F352" s="47" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="G352" s="32"/>
       <c r="H352" s="194" t="s">
+        <v>2886</v>
+      </c>
+      <c r="I352" s="187" t="s">
         <v>2887</v>
-      </c>
-      <c r="I352" s="187" t="s">
-        <v>2888</v>
       </c>
       <c r="J352" s="22"/>
       <c r="K352" s="22"/>
       <c r="L352" s="22"/>
       <c r="M352" s="137" t="s">
+        <v>2888</v>
+      </c>
+      <c r="N352" s="38" t="s">
         <v>2889</v>
-      </c>
-      <c r="N352" s="38" t="s">
-        <v>2890</v>
       </c>
       <c r="O352" s="38"/>
       <c r="P352" s="74" t="s">
@@ -46548,7 +46548,7 @@
         <v>2237</v>
       </c>
       <c r="Y352" s="30" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="Z352" s="30"/>
       <c r="AA352" s="30"/>
@@ -46573,7 +46573,7 @@
     </row>
     <row r="353" spans="1:43" ht="15.75" customHeight="1">
       <c r="A353" s="186" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="B353" s="33" t="s">
         <v>434</v>
@@ -46584,17 +46584,17 @@
       <c r="D353" s="235"/>
       <c r="E353" s="58"/>
       <c r="F353" s="47" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="G353" s="32"/>
       <c r="H353" s="206" t="s">
+        <v>2893</v>
+      </c>
+      <c r="I353" s="187" t="s">
         <v>2894</v>
       </c>
-      <c r="I353" s="187" t="s">
+      <c r="J353" s="82" t="s">
         <v>2895</v>
-      </c>
-      <c r="J353" s="82" t="s">
-        <v>2896</v>
       </c>
       <c r="K353" s="82"/>
       <c r="L353" s="22"/>
@@ -46602,7 +46602,7 @@
         <v>137</v>
       </c>
       <c r="N353" s="89" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="O353" s="457"/>
       <c r="P353" s="70"/>
@@ -46623,7 +46623,7 @@
         <v>2237</v>
       </c>
       <c r="Y353" s="30" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="Z353" s="103"/>
       <c r="AA353" s="30"/>
@@ -46646,7 +46646,7 @@
     </row>
     <row r="354" spans="1:43" ht="15.75" customHeight="1">
       <c r="A354" s="186" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="B354" s="33" t="s">
         <v>434</v>
@@ -46657,11 +46657,11 @@
       <c r="D354" s="235"/>
       <c r="E354" s="58"/>
       <c r="F354" s="47" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="G354" s="32"/>
       <c r="H354" s="206" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="I354" s="192" t="s">
         <v>2506</v>
@@ -46675,14 +46675,14 @@
         <v>1103</v>
       </c>
       <c r="N354" s="38" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="O354" s="38" t="s">
         <v>2112</v>
       </c>
       <c r="P354" s="74"/>
       <c r="Q354" s="26" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="R354" s="117" t="s">
         <v>544</v>
@@ -46698,14 +46698,14 @@
         <v>2237</v>
       </c>
       <c r="Y354" s="170" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="Z354" s="200"/>
       <c r="AA354" s="30" t="s">
+        <v>2904</v>
+      </c>
+      <c r="AB354" s="46" t="s">
         <v>2905</v>
-      </c>
-      <c r="AB354" s="46" t="s">
-        <v>2906</v>
       </c>
       <c r="AC354" s="32"/>
       <c r="AD354" s="21"/>
@@ -46725,22 +46725,22 @@
     </row>
     <row r="355" spans="1:43" ht="135" customHeight="1">
       <c r="A355" s="186" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="B355" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C355" s="250" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="D355" s="235"/>
       <c r="E355" s="58"/>
       <c r="F355" s="47" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="G355" s="32"/>
       <c r="H355" s="206" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="I355" s="192" t="s">
         <v>2506</v>
@@ -46754,14 +46754,14 @@
         <v>1619</v>
       </c>
       <c r="N355" s="54" t="s">
+        <v>2909</v>
+      </c>
+      <c r="O355" s="54" t="s">
         <v>2910</v>
-      </c>
-      <c r="O355" s="54" t="s">
-        <v>2911</v>
       </c>
       <c r="P355" s="55"/>
       <c r="Q355" s="56" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="R355" s="32" t="s">
         <v>523</v>
@@ -46782,10 +46782,10 @@
         <v>2807</v>
       </c>
       <c r="Z355" s="30" t="s">
+        <v>2912</v>
+      </c>
+      <c r="AA355" s="30" t="s">
         <v>2913</v>
-      </c>
-      <c r="AA355" s="30" t="s">
-        <v>2914</v>
       </c>
       <c r="AB355" s="41"/>
       <c r="AC355" s="32"/>
@@ -46806,7 +46806,7 @@
     </row>
     <row r="356" spans="1:43" ht="15.75" customHeight="1">
       <c r="A356" s="186" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="B356" s="33" t="s">
         <v>434</v>
@@ -46817,11 +46817,11 @@
       <c r="D356" s="235"/>
       <c r="E356" s="58"/>
       <c r="F356" s="47" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="G356" s="32"/>
       <c r="H356" s="206" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="I356" s="192" t="s">
         <v>2506</v>
@@ -46833,14 +46833,14 @@
         <v>804</v>
       </c>
       <c r="N356" s="54" t="s">
+        <v>2917</v>
+      </c>
+      <c r="O356" s="54" t="s">
         <v>2918</v>
-      </c>
-      <c r="O356" s="54" t="s">
-        <v>2919</v>
       </c>
       <c r="P356" s="55"/>
       <c r="Q356" s="56" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="R356" s="32" t="s">
         <v>523</v>
@@ -46849,7 +46849,7 @@
         <v>41</v>
       </c>
       <c r="T356" s="21" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="U356" s="28"/>
       <c r="V356" s="28"/>
@@ -46860,13 +46860,13 @@
         <v>2237</v>
       </c>
       <c r="Y356" s="30" t="s">
+        <v>2921</v>
+      </c>
+      <c r="Z356" s="30" t="s">
         <v>2922</v>
       </c>
-      <c r="Z356" s="30" t="s">
+      <c r="AA356" s="30" t="s">
         <v>2923</v>
-      </c>
-      <c r="AA356" s="30" t="s">
-        <v>2924</v>
       </c>
       <c r="AB356" s="41"/>
       <c r="AC356" s="32"/>
@@ -46887,22 +46887,22 @@
     </row>
     <row r="357" spans="1:43" ht="15.75" customHeight="1">
       <c r="A357" s="281" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B357" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C357" s="249" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="D357" s="235"/>
       <c r="E357" s="58"/>
       <c r="F357" s="47" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="G357" s="32"/>
       <c r="H357" s="32" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="I357" s="192" t="s">
         <v>2506</v>
@@ -46916,7 +46916,7 @@
         <v>542</v>
       </c>
       <c r="N357" s="54" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="O357" s="54"/>
       <c r="P357" s="55"/>
@@ -46941,10 +46941,10 @@
       </c>
       <c r="Z357" s="30"/>
       <c r="AA357" s="30" t="s">
+        <v>2929</v>
+      </c>
+      <c r="AB357" s="41" t="s">
         <v>2930</v>
-      </c>
-      <c r="AB357" s="41" t="s">
-        <v>2931</v>
       </c>
       <c r="AC357" s="32"/>
       <c r="AD357" s="21"/>
@@ -46964,10 +46964,10 @@
     </row>
     <row r="358" spans="1:43" ht="15.75" customHeight="1">
       <c r="A358" s="186" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B358" s="186" t="s">
         <v>2932</v>
-      </c>
-      <c r="B358" s="186" t="s">
-        <v>2933</v>
       </c>
       <c r="C358" s="250" t="s">
         <v>171</v>
@@ -46975,11 +46975,11 @@
       <c r="D358" s="235"/>
       <c r="E358" s="58"/>
       <c r="F358" s="47" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="G358" s="32"/>
       <c r="H358" s="206" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="I358" s="192" t="s">
         <v>2506</v>
@@ -46988,10 +46988,10 @@
       <c r="K358" s="93"/>
       <c r="L358" s="93"/>
       <c r="M358" s="137" t="s">
+        <v>2935</v>
+      </c>
+      <c r="N358" s="65" t="s">
         <v>2936</v>
-      </c>
-      <c r="N358" s="65" t="s">
-        <v>2937</v>
       </c>
       <c r="O358" s="65"/>
       <c r="P358" s="55"/>
@@ -47012,14 +47012,14 @@
         <v>2237</v>
       </c>
       <c r="Y358" s="210" t="s">
+        <v>2937</v>
+      </c>
+      <c r="Z358" s="211" t="s">
         <v>2938</v>
-      </c>
-      <c r="Z358" s="211" t="s">
-        <v>2939</v>
       </c>
       <c r="AA358" s="211"/>
       <c r="AB358" s="31" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="AC358" s="32"/>
       <c r="AD358" s="21"/>
@@ -47039,38 +47039,38 @@
     </row>
     <row r="359" spans="1:43" ht="15.75" customHeight="1">
       <c r="A359" s="281" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="B359" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C359" s="249" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="D359" s="235"/>
       <c r="E359" s="58"/>
       <c r="F359" s="47" t="s">
+        <v>2942</v>
+      </c>
+      <c r="G359" s="32" t="s">
         <v>2943</v>
       </c>
-      <c r="G359" s="32" t="s">
+      <c r="H359" s="95" t="s">
         <v>2944</v>
-      </c>
-      <c r="H359" s="95" t="s">
-        <v>2945</v>
       </c>
       <c r="I359" s="187" t="s">
         <v>2638</v>
       </c>
       <c r="J359" s="22" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="K359" s="22"/>
       <c r="L359" s="22"/>
       <c r="M359" s="137" t="s">
+        <v>2946</v>
+      </c>
+      <c r="N359" s="136" t="s">
         <v>2947</v>
-      </c>
-      <c r="N359" s="136" t="s">
-        <v>2948</v>
       </c>
       <c r="O359" s="54"/>
       <c r="P359" s="55"/>
@@ -47082,7 +47082,7 @@
         <v>41</v>
       </c>
       <c r="T359" s="21" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="U359" s="28"/>
       <c r="V359" s="28"/>
@@ -47116,7 +47116,7 @@
     </row>
     <row r="360" spans="1:43" ht="15.75" customHeight="1">
       <c r="A360" s="186" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="B360" s="33" t="s">
         <v>434</v>
@@ -47127,11 +47127,11 @@
       <c r="D360" s="235"/>
       <c r="E360" s="58"/>
       <c r="F360" s="47" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="G360" s="32"/>
       <c r="H360" s="48" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="I360" s="187" t="s">
         <v>2506</v>
@@ -47140,17 +47140,17 @@
       <c r="K360" s="22"/>
       <c r="L360" s="22"/>
       <c r="M360" s="137" t="s">
+        <v>2952</v>
+      </c>
+      <c r="N360" s="54" t="s">
         <v>2953</v>
-      </c>
-      <c r="N360" s="54" t="s">
-        <v>2954</v>
       </c>
       <c r="O360" s="54" t="s">
         <v>1869</v>
       </c>
       <c r="P360" s="55"/>
       <c r="Q360" s="56" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="R360" s="32" t="s">
         <v>523</v>
@@ -47168,13 +47168,13 @@
         <v>2237</v>
       </c>
       <c r="Y360" s="30" t="s">
+        <v>2955</v>
+      </c>
+      <c r="Z360" s="30" t="s">
         <v>2956</v>
       </c>
-      <c r="Z360" s="30" t="s">
+      <c r="AA360" s="30" t="s">
         <v>2957</v>
-      </c>
-      <c r="AA360" s="30" t="s">
-        <v>2958</v>
       </c>
       <c r="AB360" s="110"/>
       <c r="AC360" s="32"/>
@@ -47195,7 +47195,7 @@
     </row>
     <row r="361" spans="1:43" ht="15.75" customHeight="1">
       <c r="A361" s="186" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B361" s="33" t="s">
         <v>434</v>
@@ -47209,22 +47209,22 @@
         <v>2284</v>
       </c>
       <c r="G361" s="186" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H361" s="48" t="s">
         <v>2960</v>
       </c>
-      <c r="H361" s="48" t="s">
+      <c r="I361" s="187" t="s">
         <v>2961</v>
-      </c>
-      <c r="I361" s="187" t="s">
-        <v>2962</v>
       </c>
       <c r="J361" s="22"/>
       <c r="K361" s="22"/>
       <c r="L361" s="22"/>
       <c r="M361" s="137" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="N361" s="54" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="O361" s="54"/>
       <c r="P361" s="25" t="s">
@@ -47240,7 +47240,7 @@
         <v>41</v>
       </c>
       <c r="T361" s="21" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="U361" s="28"/>
       <c r="V361" s="28"/>
@@ -47251,7 +47251,7 @@
       <c r="AA361" s="30"/>
       <c r="AB361" s="110"/>
       <c r="AC361" s="32" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="AD361" s="21"/>
       <c r="AE361" s="32"/>
@@ -47270,7 +47270,7 @@
     </row>
     <row r="362" spans="1:43" ht="15.75" customHeight="1">
       <c r="A362" s="186" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="B362" s="33" t="s">
         <v>434</v>
@@ -47281,13 +47281,13 @@
       <c r="D362" s="235"/>
       <c r="E362" s="58"/>
       <c r="F362" s="16" t="s">
+        <v>2966</v>
+      </c>
+      <c r="G362" s="48" t="s">
         <v>2967</v>
       </c>
-      <c r="G362" s="48" t="s">
+      <c r="H362" s="206" t="s">
         <v>2968</v>
-      </c>
-      <c r="H362" s="206" t="s">
-        <v>2969</v>
       </c>
       <c r="I362" s="32" t="s">
         <v>2546</v>
@@ -47296,10 +47296,10 @@
       <c r="K362" s="82"/>
       <c r="L362" s="82"/>
       <c r="M362" s="95" t="s">
+        <v>2969</v>
+      </c>
+      <c r="N362" s="54" t="s">
         <v>2970</v>
-      </c>
-      <c r="N362" s="54" t="s">
-        <v>2971</v>
       </c>
       <c r="O362" s="54"/>
       <c r="P362" s="25" t="s">
@@ -47309,7 +47309,7 @@
         <v>1905</v>
       </c>
       <c r="R362" s="77" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="S362" s="77" t="s">
         <v>41</v>
@@ -47324,7 +47324,7 @@
       <c r="W362" s="113"/>
       <c r="X362" s="113"/>
       <c r="Y362" s="30" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="Z362" s="30"/>
       <c r="AA362" s="30"/>
@@ -47333,7 +47333,7 @@
         <v>1907</v>
       </c>
       <c r="AD362" s="146" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="AE362" s="32"/>
       <c r="AF362" s="32"/>
@@ -47351,7 +47351,7 @@
     </row>
     <row r="363" spans="1:43" ht="15.75" customHeight="1">
       <c r="A363" s="186" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B363" s="33" t="s">
         <v>434</v>
@@ -47362,11 +47362,11 @@
       <c r="D363" s="235"/>
       <c r="E363" s="58"/>
       <c r="F363" s="47" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="G363" s="48"/>
       <c r="H363" s="48" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="I363" s="32" t="s">
         <v>2546</v>
@@ -47378,7 +47378,7 @@
         <v>491</v>
       </c>
       <c r="N363" s="54" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="O363" s="54"/>
       <c r="P363" s="25" t="s">
@@ -47403,7 +47403,7 @@
       <c r="W363" s="113"/>
       <c r="X363" s="113"/>
       <c r="Y363" s="30" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="Z363" s="30"/>
       <c r="AA363" s="30"/>
@@ -47428,7 +47428,7 @@
     </row>
     <row r="364" spans="1:43" ht="15.75" customHeight="1">
       <c r="A364" s="186" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="B364" s="33" t="s">
         <v>434</v>
@@ -47439,21 +47439,21 @@
       <c r="D364" s="235"/>
       <c r="E364" s="58"/>
       <c r="F364" s="16" t="s">
+        <v>2979</v>
+      </c>
+      <c r="G364" s="48" t="s">
         <v>2980</v>
       </c>
-      <c r="G364" s="48" t="s">
+      <c r="H364" s="206" t="s">
         <v>2981</v>
       </c>
-      <c r="H364" s="206" t="s">
+      <c r="I364" s="32" t="s">
         <v>2982</v>
-      </c>
-      <c r="I364" s="32" t="s">
-        <v>2983</v>
       </c>
       <c r="J364" s="22"/>
       <c r="K364" s="22"/>
       <c r="L364" s="22" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="M364" s="183" t="s">
         <v>2081</v>
@@ -47495,7 +47495,7 @@
     </row>
     <row r="365" spans="1:43" ht="15.75" customHeight="1">
       <c r="A365" s="186" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="B365" s="33" t="s">
         <v>434</v>
@@ -47506,11 +47506,11 @@
       <c r="D365" s="235"/>
       <c r="E365" s="58"/>
       <c r="F365" s="47" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="G365" s="32"/>
       <c r="H365" s="206" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="I365" s="32" t="s">
         <v>2506</v>
@@ -47522,7 +47522,7 @@
         <v>601</v>
       </c>
       <c r="N365" s="38" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="O365" s="38" t="s">
         <v>38</v>
@@ -47547,14 +47547,14 @@
         <v>2237</v>
       </c>
       <c r="Y365" s="198" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="Z365" s="490"/>
       <c r="AA365" s="198" t="s">
+        <v>2989</v>
+      </c>
+      <c r="AB365" s="31" t="s">
         <v>2990</v>
-      </c>
-      <c r="AB365" s="31" t="s">
-        <v>2991</v>
       </c>
       <c r="AC365" s="32"/>
       <c r="AD365" s="21"/>
@@ -47574,22 +47574,22 @@
     </row>
     <row r="366" spans="1:43" ht="15.75" customHeight="1">
       <c r="A366" s="282" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="B366" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C366" s="249" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="D366" s="235"/>
       <c r="E366" s="58"/>
       <c r="F366" s="47" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="G366" s="32"/>
       <c r="H366" s="206" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="I366" s="192" t="s">
         <v>2506</v>
@@ -47603,7 +47603,7 @@
         <v>542</v>
       </c>
       <c r="N366" s="38" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="O366" s="38"/>
       <c r="P366" s="25"/>
@@ -47624,11 +47624,11 @@
         <v>2237</v>
       </c>
       <c r="Y366" s="30" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="Z366" s="200"/>
       <c r="AA366" s="30" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="AB366" s="41"/>
       <c r="AC366" s="32"/>
@@ -47649,7 +47649,7 @@
     </row>
     <row r="367" spans="1:43" ht="15.75" customHeight="1">
       <c r="A367" s="186" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="B367" s="33" t="s">
         <v>434</v>
@@ -47660,11 +47660,11 @@
       <c r="D367" s="235"/>
       <c r="E367" s="58"/>
       <c r="F367" s="47" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="G367" s="39"/>
       <c r="H367" s="206" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="I367" s="192" t="s">
         <v>2506</v>
@@ -47672,20 +47672,20 @@
       <c r="J367" s="22"/>
       <c r="K367" s="22"/>
       <c r="L367" s="22" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="M367" s="137" t="s">
         <v>657</v>
       </c>
       <c r="N367" s="38" t="s">
+        <v>3001</v>
+      </c>
+      <c r="O367" s="38" t="s">
         <v>3002</v>
-      </c>
-      <c r="O367" s="38" t="s">
-        <v>3003</v>
       </c>
       <c r="P367" s="25"/>
       <c r="Q367" s="26" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="R367" s="39" t="s">
         <v>523</v>
@@ -47703,13 +47703,13 @@
         <v>2237</v>
       </c>
       <c r="Y367" s="30" t="s">
+        <v>3004</v>
+      </c>
+      <c r="Z367" s="30" t="s">
         <v>3005</v>
       </c>
-      <c r="Z367" s="30" t="s">
+      <c r="AA367" s="30" t="s">
         <v>3006</v>
-      </c>
-      <c r="AA367" s="30" t="s">
-        <v>3007</v>
       </c>
       <c r="AB367" s="41"/>
       <c r="AC367" s="32"/>
@@ -47730,7 +47730,7 @@
     </row>
     <row r="368" spans="1:43" ht="15.75" customHeight="1">
       <c r="A368" s="186" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="B368" s="33" t="s">
         <v>434</v>
@@ -47741,11 +47741,11 @@
       <c r="D368" s="235"/>
       <c r="E368" s="58"/>
       <c r="F368" s="47" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="G368" s="39"/>
       <c r="H368" s="206" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="I368" s="192" t="s">
         <v>2506</v>
@@ -47754,17 +47754,17 @@
       <c r="K368" s="22"/>
       <c r="L368" s="22"/>
       <c r="M368" s="137" t="s">
+        <v>3010</v>
+      </c>
+      <c r="N368" s="38" t="s">
         <v>3011</v>
       </c>
-      <c r="N368" s="38" t="s">
+      <c r="O368" s="38" t="s">
         <v>3012</v>
-      </c>
-      <c r="O368" s="38" t="s">
-        <v>3013</v>
       </c>
       <c r="P368" s="25"/>
       <c r="Q368" s="26" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="R368" s="39" t="s">
         <v>523</v>
@@ -47782,13 +47782,13 @@
         <v>2237</v>
       </c>
       <c r="Y368" s="170" t="s">
+        <v>3014</v>
+      </c>
+      <c r="Z368" s="30" t="s">
         <v>3015</v>
       </c>
-      <c r="Z368" s="30" t="s">
+      <c r="AA368" s="30" t="s">
         <v>3016</v>
-      </c>
-      <c r="AA368" s="30" t="s">
-        <v>3017</v>
       </c>
       <c r="AB368" s="41"/>
       <c r="AC368" s="32"/>
@@ -47809,22 +47809,22 @@
     </row>
     <row r="369" spans="1:43" ht="15.75" customHeight="1">
       <c r="A369" s="391" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B369" s="392" t="s">
         <v>434</v>
       </c>
       <c r="C369" s="266" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="D369" s="393"/>
       <c r="E369" s="394"/>
       <c r="F369" s="395" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="G369" s="396"/>
       <c r="H369" s="411" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="I369" s="397" t="s">
         <v>2506</v>
@@ -47833,10 +47833,10 @@
       <c r="K369" s="399"/>
       <c r="L369" s="398"/>
       <c r="M369" s="400" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="N369" s="401" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="O369" s="401" t="s">
         <v>38</v>
@@ -47855,25 +47855,25 @@
       <c r="U369" s="412"/>
       <c r="V369" s="406"/>
       <c r="W369" s="407" t="s">
+        <v>3021</v>
+      </c>
+      <c r="X369" s="407" t="s">
         <v>3022</v>
       </c>
-      <c r="X369" s="407" t="s">
+      <c r="Y369" s="408" t="s">
         <v>3023</v>
       </c>
-      <c r="Y369" s="408" t="s">
+      <c r="Z369" s="494" t="s">
         <v>3024</v>
       </c>
-      <c r="Z369" s="494" t="s">
+      <c r="AA369" s="408" t="s">
         <v>3025</v>
       </c>
-      <c r="AA369" s="408" t="s">
-        <v>3026</v>
-      </c>
       <c r="AB369" s="409" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="AC369" s="413" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="AD369" s="405"/>
       <c r="AE369" s="32"/>
@@ -47892,22 +47892,22 @@
     </row>
     <row r="370" spans="1:43" ht="15.75" customHeight="1">
       <c r="A370" s="281" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="B370" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C370" s="249" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="D370" s="235"/>
       <c r="E370" s="58"/>
       <c r="F370" s="47" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="G370" s="39"/>
       <c r="H370" s="206" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="I370" s="32" t="s">
         <v>2506</v>
@@ -47919,7 +47919,7 @@
         <v>804</v>
       </c>
       <c r="N370" s="54" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="O370" s="38" t="s">
         <v>38</v>
@@ -47944,15 +47944,15 @@
         <v>2237</v>
       </c>
       <c r="Y370" s="198" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Z370" s="200"/>
       <c r="AA370" s="389" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="AB370" s="497"/>
       <c r="AC370" s="16" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="AD370" s="21"/>
       <c r="AE370" s="32"/>
@@ -47971,42 +47971,42 @@
     </row>
     <row r="371" spans="1:43" ht="15.75" customHeight="1">
       <c r="A371" s="281" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="B371" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C371" s="249" t="s">
+        <v>3035</v>
+      </c>
+      <c r="D371" s="234" t="s">
+        <v>3027</v>
+      </c>
+      <c r="E371" s="58" t="s">
         <v>3036</v>
       </c>
-      <c r="D371" s="234" t="s">
-        <v>3028</v>
-      </c>
-      <c r="E371" s="58" t="s">
+      <c r="F371" s="47" t="s">
         <v>3037</v>
       </c>
-      <c r="F371" s="47" t="s">
+      <c r="G371" s="32" t="s">
         <v>3038</v>
       </c>
-      <c r="G371" s="32" t="s">
+      <c r="H371" s="48" t="s">
         <v>3039</v>
       </c>
-      <c r="H371" s="48" t="s">
+      <c r="I371" s="187" t="s">
         <v>3040</v>
       </c>
-      <c r="I371" s="187" t="s">
-        <v>3041</v>
-      </c>
       <c r="J371" s="22" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="K371" s="22"/>
       <c r="L371" s="22"/>
       <c r="M371" s="137" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="N371" s="136" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="O371" s="54"/>
       <c r="P371" s="55"/>
@@ -48050,22 +48050,22 @@
     </row>
     <row r="372" spans="1:43" ht="15.75" customHeight="1">
       <c r="A372" s="281" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="B372" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C372" s="249" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="D372" s="235"/>
       <c r="E372" s="58"/>
       <c r="F372" s="16" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="G372" s="39"/>
       <c r="H372" s="206" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="I372" s="192" t="s">
         <v>2506</v>
@@ -48073,13 +48073,13 @@
       <c r="J372" s="82"/>
       <c r="K372" s="82"/>
       <c r="L372" s="82" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="M372" s="212" t="s">
         <v>542</v>
       </c>
       <c r="N372" s="54" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="O372" s="54"/>
       <c r="P372" s="55"/>
@@ -48100,13 +48100,13 @@
         <v>2237</v>
       </c>
       <c r="Y372" s="30" t="s">
+        <v>3048</v>
+      </c>
+      <c r="Z372" s="30" t="s">
         <v>3049</v>
       </c>
-      <c r="Z372" s="30" t="s">
+      <c r="AA372" s="30" t="s">
         <v>3050</v>
-      </c>
-      <c r="AA372" s="30" t="s">
-        <v>3051</v>
       </c>
       <c r="AB372" s="110"/>
       <c r="AC372" s="32"/>
@@ -48127,7 +48127,7 @@
     </row>
     <row r="373" spans="1:43" ht="15.75" customHeight="1">
       <c r="A373" s="186" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B373" s="33" t="s">
         <v>434</v>
@@ -48138,19 +48138,19 @@
       <c r="D373" s="235"/>
       <c r="E373" s="58"/>
       <c r="F373" s="47" t="s">
+        <v>3052</v>
+      </c>
+      <c r="G373" s="32" t="s">
         <v>3053</v>
       </c>
-      <c r="G373" s="32" t="s">
+      <c r="H373" s="206" t="s">
         <v>3054</v>
       </c>
-      <c r="H373" s="206" t="s">
+      <c r="I373" s="32" t="s">
         <v>3055</v>
       </c>
-      <c r="I373" s="32" t="s">
+      <c r="J373" s="104" t="s">
         <v>3056</v>
-      </c>
-      <c r="J373" s="104" t="s">
-        <v>3057</v>
       </c>
       <c r="K373" s="104"/>
       <c r="L373" s="104"/>
@@ -48158,7 +48158,7 @@
         <v>137</v>
       </c>
       <c r="N373" s="54" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="O373" s="54"/>
       <c r="P373" s="55"/>
@@ -48202,22 +48202,22 @@
     </row>
     <row r="374" spans="1:43" ht="15.75" customHeight="1">
       <c r="A374" s="186" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B374" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C374" s="249" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="D374" s="235"/>
       <c r="E374" s="58"/>
       <c r="F374" s="47" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="G374" s="39"/>
       <c r="H374" s="206" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="I374" s="192" t="s">
         <v>2506</v>
@@ -48231,14 +48231,14 @@
         <v>899</v>
       </c>
       <c r="N374" s="54" t="s">
+        <v>3062</v>
+      </c>
+      <c r="O374" s="54" t="s">
         <v>3063</v>
-      </c>
-      <c r="O374" s="54" t="s">
-        <v>3064</v>
       </c>
       <c r="P374" s="55"/>
       <c r="Q374" s="56" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="R374" s="39" t="s">
         <v>523</v>
@@ -48256,13 +48256,13 @@
         <v>2237</v>
       </c>
       <c r="Y374" s="30" t="s">
+        <v>3065</v>
+      </c>
+      <c r="Z374" s="103" t="s">
         <v>3066</v>
       </c>
-      <c r="Z374" s="103" t="s">
+      <c r="AA374" s="30" t="s">
         <v>3067</v>
-      </c>
-      <c r="AA374" s="30" t="s">
-        <v>3068</v>
       </c>
       <c r="AB374" s="41"/>
       <c r="AC374" s="32"/>
@@ -48283,36 +48283,36 @@
     </row>
     <row r="375" spans="1:43" ht="15.75" customHeight="1">
       <c r="A375" s="186" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="B375" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C375" s="249" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="D375" s="235"/>
       <c r="E375" s="58"/>
       <c r="F375" s="16" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="G375" s="32"/>
       <c r="H375" s="206" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="I375" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J375" s="82" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="K375" s="82"/>
       <c r="L375" s="82"/>
       <c r="M375" s="115" t="s">
+        <v>3073</v>
+      </c>
+      <c r="N375" s="54" t="s">
         <v>3074</v>
-      </c>
-      <c r="N375" s="54" t="s">
-        <v>3075</v>
       </c>
       <c r="O375" s="322" t="s">
         <v>38</v>
@@ -48337,15 +48337,15 @@
         <v>2237</v>
       </c>
       <c r="Y375" s="491" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="Z375" s="490"/>
       <c r="AA375" s="30" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="AB375" s="41"/>
       <c r="AC375" s="66" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="AD375" s="21"/>
       <c r="AE375" s="32"/>
@@ -48364,7 +48364,7 @@
     </row>
     <row r="376" spans="1:43" ht="48" customHeight="1">
       <c r="A376" s="418" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="B376" s="33" t="s">
         <v>434</v>
@@ -48374,14 +48374,14 @@
       </c>
       <c r="E376" s="230"/>
       <c r="F376" s="433" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="G376" s="230"/>
       <c r="H376" s="423" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="I376" s="423" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="J376" s="230"/>
       <c r="K376" s="230"/>
@@ -48402,7 +48402,7 @@
         <v>41</v>
       </c>
       <c r="T376" s="423" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="U376" s="230"/>
       <c r="V376" s="230"/>
@@ -48414,7 +48414,7 @@
       <c r="AB376" s="230"/>
       <c r="AC376" s="230"/>
       <c r="AD376" s="423" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="AE376" s="230"/>
       <c r="AF376" s="230"/>
@@ -48432,7 +48432,7 @@
     </row>
     <row r="377" spans="1:43" ht="15.75" customHeight="1">
       <c r="A377" s="186" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="B377" s="33" t="s">
         <v>434</v>
@@ -48443,11 +48443,11 @@
       <c r="D377" s="235"/>
       <c r="E377" s="58"/>
       <c r="F377" s="290" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="G377" s="32"/>
       <c r="H377" s="206" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="I377" s="32" t="s">
         <v>2506</v>
@@ -48458,17 +48458,17 @@
         <v>424</v>
       </c>
       <c r="M377" s="137" t="s">
+        <v>3083</v>
+      </c>
+      <c r="N377" s="54" t="s">
         <v>3084</v>
-      </c>
-      <c r="N377" s="54" t="s">
-        <v>3085</v>
       </c>
       <c r="O377" s="54"/>
       <c r="P377" s="74" t="s">
+        <v>3085</v>
+      </c>
+      <c r="Q377" s="56" t="s">
         <v>3086</v>
-      </c>
-      <c r="Q377" s="56" t="s">
-        <v>3087</v>
       </c>
       <c r="R377" s="94" t="s">
         <v>544</v>
@@ -48490,7 +48490,7 @@
       </c>
       <c r="Z377" s="490"/>
       <c r="AA377" s="198" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="AB377" s="110"/>
       <c r="AC377" s="32"/>
@@ -48511,7 +48511,7 @@
     </row>
     <row r="378" spans="1:43" ht="15.75" customHeight="1">
       <c r="A378" s="186" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="B378" s="33" t="s">
         <v>434</v>
@@ -48522,11 +48522,11 @@
       <c r="D378" s="235"/>
       <c r="E378" s="58"/>
       <c r="F378" s="47" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="G378" s="32"/>
       <c r="H378" s="206" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="I378" s="192" t="s">
         <v>2506</v>
@@ -48534,13 +48534,13 @@
       <c r="J378" s="35"/>
       <c r="K378" s="109"/>
       <c r="L378" s="109" t="s">
+        <v>3091</v>
+      </c>
+      <c r="M378" s="137" t="s">
         <v>3092</v>
       </c>
-      <c r="M378" s="137" t="s">
+      <c r="N378" s="38" t="s">
         <v>3093</v>
-      </c>
-      <c r="N378" s="38" t="s">
-        <v>3094</v>
       </c>
       <c r="O378" s="38"/>
       <c r="P378" s="25"/>
@@ -48565,10 +48565,10 @@
       </c>
       <c r="Z378" s="200"/>
       <c r="AA378" s="200" t="s">
+        <v>3094</v>
+      </c>
+      <c r="AB378" s="110" t="s">
         <v>3095</v>
-      </c>
-      <c r="AB378" s="110" t="s">
-        <v>3096</v>
       </c>
       <c r="AC378" s="32"/>
       <c r="AD378" s="21"/>
@@ -48588,7 +48588,7 @@
     </row>
     <row r="379" spans="1:43" ht="15.75" customHeight="1">
       <c r="A379" s="186" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="B379" s="33" t="s">
         <v>434</v>
@@ -48599,11 +48599,11 @@
       <c r="D379" s="235"/>
       <c r="E379" s="58"/>
       <c r="F379" s="47" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="G379" s="32"/>
       <c r="H379" s="206" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="I379" s="192" t="s">
         <v>2506</v>
@@ -48612,17 +48612,17 @@
       <c r="K379" s="82"/>
       <c r="L379" s="82"/>
       <c r="M379" s="137" t="s">
+        <v>3099</v>
+      </c>
+      <c r="N379" s="54" t="s">
         <v>3100</v>
       </c>
-      <c r="N379" s="54" t="s">
+      <c r="O379" s="458" t="s">
         <v>3101</v>
-      </c>
-      <c r="O379" s="458" t="s">
-        <v>3102</v>
       </c>
       <c r="P379" s="114"/>
       <c r="Q379" s="56" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="R379" s="39" t="s">
         <v>523</v>
@@ -48640,13 +48640,13 @@
         <v>2237</v>
       </c>
       <c r="Y379" s="170" t="s">
+        <v>3103</v>
+      </c>
+      <c r="Z379" s="30" t="s">
         <v>3104</v>
       </c>
-      <c r="Z379" s="30" t="s">
+      <c r="AA379" s="30" t="s">
         <v>3105</v>
-      </c>
-      <c r="AA379" s="30" t="s">
-        <v>3106</v>
       </c>
       <c r="AB379" s="110"/>
       <c r="AC379" s="32"/>
@@ -48667,22 +48667,22 @@
     </row>
     <row r="380" spans="1:43" ht="15.75" customHeight="1">
       <c r="A380" s="281" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="B380" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C380" s="249" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="D380" s="235"/>
       <c r="E380" s="58"/>
       <c r="F380" s="16" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="G380" s="32"/>
       <c r="H380" s="206" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="I380" s="192" t="s">
         <v>2506</v>
@@ -48690,22 +48690,22 @@
       <c r="J380" s="82"/>
       <c r="K380" s="82"/>
       <c r="L380" s="82" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="M380" s="137" t="s">
         <v>899</v>
       </c>
       <c r="N380" s="38" t="s">
+        <v>3111</v>
+      </c>
+      <c r="O380" s="38" t="s">
         <v>3112</v>
       </c>
-      <c r="O380" s="38" t="s">
+      <c r="P380" s="74" t="s">
         <v>3113</v>
       </c>
-      <c r="P380" s="74" t="s">
+      <c r="Q380" s="56" t="s">
         <v>3114</v>
-      </c>
-      <c r="Q380" s="56" t="s">
-        <v>3115</v>
       </c>
       <c r="R380" s="39" t="s">
         <v>523</v>
@@ -48723,13 +48723,13 @@
         <v>2237</v>
       </c>
       <c r="Y380" s="170" t="s">
+        <v>3115</v>
+      </c>
+      <c r="Z380" s="103" t="s">
         <v>3116</v>
       </c>
-      <c r="Z380" s="103" t="s">
+      <c r="AA380" s="30" t="s">
         <v>3117</v>
-      </c>
-      <c r="AA380" s="30" t="s">
-        <v>3118</v>
       </c>
       <c r="AB380" s="110"/>
       <c r="AC380" s="32"/>
@@ -48750,7 +48750,7 @@
     </row>
     <row r="381" spans="1:43" s="387" customFormat="1" ht="15.75" customHeight="1">
       <c r="A381" s="186" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B381" s="33" t="s">
         <v>434</v>
@@ -48761,11 +48761,11 @@
       <c r="D381" s="235"/>
       <c r="E381" s="58"/>
       <c r="F381" s="437" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="G381" s="32"/>
       <c r="H381" s="206" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="I381" s="32" t="s">
         <v>2506</v>
@@ -48773,13 +48773,13 @@
       <c r="J381" s="98"/>
       <c r="K381" s="104"/>
       <c r="L381" s="104" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="M381" s="137" t="s">
         <v>542</v>
       </c>
       <c r="N381" s="54" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="O381" s="54"/>
       <c r="P381" s="55"/>
@@ -48804,11 +48804,11 @@
       </c>
       <c r="Z381" s="495"/>
       <c r="AA381" s="214" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="AB381" s="110"/>
       <c r="AC381" s="47" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="AD381" s="21"/>
       <c r="AE381" s="377"/>
@@ -48827,7 +48827,7 @@
     </row>
     <row r="382" spans="1:43" ht="15.75" customHeight="1">
       <c r="A382" s="373" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="B382" s="366" t="s">
         <v>434</v>
@@ -48836,11 +48836,11 @@
       <c r="D382" s="375"/>
       <c r="E382" s="376"/>
       <c r="F382" s="436" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="G382" s="377"/>
       <c r="H382" s="378" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="I382" s="378" t="s">
         <v>2506</v>
@@ -48849,10 +48849,10 @@
       <c r="K382" s="379"/>
       <c r="L382" s="379"/>
       <c r="M382" s="380" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="N382" s="370" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="O382" s="370"/>
       <c r="P382" s="371"/>
@@ -48871,10 +48871,10 @@
         <v>2237</v>
       </c>
       <c r="Y382" s="385" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="Z382" s="390" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="AA382" s="386"/>
       <c r="AB382" s="501"/>
@@ -48896,22 +48896,22 @@
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
       <c r="A383" s="281" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C383" s="249" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="D383" s="235"/>
       <c r="E383" s="58"/>
       <c r="F383" s="16" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="G383" s="39"/>
       <c r="H383" s="206" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="I383" s="192" t="s">
         <v>2506</v>
@@ -48920,10 +48920,10 @@
       <c r="K383" s="82"/>
       <c r="L383" s="22"/>
       <c r="M383" s="137" t="s">
+        <v>3128</v>
+      </c>
+      <c r="N383" s="54" t="s">
         <v>3129</v>
-      </c>
-      <c r="N383" s="54" t="s">
-        <v>3130</v>
       </c>
       <c r="O383" s="54" t="s">
         <v>38</v>
@@ -48952,7 +48952,7 @@
       </c>
       <c r="Z383" s="30"/>
       <c r="AA383" s="30" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="AB383" s="41"/>
       <c r="AC383" s="32"/>
@@ -48973,13 +48973,13 @@
     </row>
     <row r="384" spans="1:43" ht="15.75" customHeight="1">
       <c r="A384" s="282" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="B384" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C384" s="249" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="D384" s="235"/>
       <c r="E384" s="58"/>
@@ -48991,7 +48991,7 @@
         <v>2618</v>
       </c>
       <c r="I384" s="192" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="J384" s="98"/>
       <c r="K384" s="82"/>
@@ -49002,7 +49002,7 @@
         <v>863</v>
       </c>
       <c r="N384" s="54" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="O384" s="54"/>
       <c r="P384" s="55"/>
@@ -49014,7 +49014,7 @@
         <v>41</v>
       </c>
       <c r="T384" s="21" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="U384" s="28"/>
       <c r="V384" s="28"/>
@@ -49042,13 +49042,13 @@
     </row>
     <row r="385" spans="1:43" ht="15.75" customHeight="1">
       <c r="A385" s="282" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="B385" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C385" s="249" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="D385" s="235"/>
       <c r="E385" s="58"/>
@@ -49057,10 +49057,10 @@
       </c>
       <c r="G385" s="39"/>
       <c r="H385" s="206" t="s">
+        <v>3135</v>
+      </c>
+      <c r="I385" s="192" t="s">
         <v>3136</v>
-      </c>
-      <c r="I385" s="192" t="s">
-        <v>3137</v>
       </c>
       <c r="J385" s="35"/>
       <c r="K385" s="109"/>
@@ -49071,7 +49071,7 @@
         <v>863</v>
       </c>
       <c r="N385" s="54" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="O385" s="54"/>
       <c r="P385" s="55"/>
@@ -49083,7 +49083,7 @@
         <v>41</v>
       </c>
       <c r="T385" s="21" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="U385" s="28"/>
       <c r="V385" s="28"/>
@@ -49111,22 +49111,22 @@
     </row>
     <row r="386" spans="1:43" ht="15.75" customHeight="1">
       <c r="A386" s="281" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="B386" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C386" s="249" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="D386" s="235"/>
       <c r="E386" s="58"/>
       <c r="F386" s="16" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="G386" s="39"/>
       <c r="H386" s="206" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="I386" s="192" t="s">
         <v>2506</v>
@@ -49159,7 +49159,7 @@
       <c r="Y386" s="30"/>
       <c r="Z386" s="30"/>
       <c r="AA386" s="30" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="AB386" s="41"/>
       <c r="AC386" s="32"/>
@@ -49180,22 +49180,22 @@
     </row>
     <row r="387" spans="1:43" ht="15.75" customHeight="1">
       <c r="A387" s="281" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B387" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C387" s="249" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="D387" s="235"/>
       <c r="E387" s="58"/>
       <c r="F387" s="47" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="G387" s="39"/>
       <c r="H387" s="206" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="I387" s="192" t="s">
         <v>2506</v>
@@ -49206,10 +49206,10 @@
       <c r="K387" s="22"/>
       <c r="L387" s="22"/>
       <c r="M387" s="215" t="s">
+        <v>3147</v>
+      </c>
+      <c r="N387" s="38" t="s">
         <v>3148</v>
-      </c>
-      <c r="N387" s="38" t="s">
-        <v>3149</v>
       </c>
       <c r="O387" s="38"/>
       <c r="P387" s="55"/>
@@ -49224,17 +49224,17 @@
       <c r="U387" s="28"/>
       <c r="V387" s="28"/>
       <c r="W387" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X387" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X387" s="29" t="s">
+      <c r="Y387" s="30" t="s">
         <v>3151</v>
-      </c>
-      <c r="Y387" s="30" t="s">
-        <v>3152</v>
       </c>
       <c r="Z387" s="30"/>
       <c r="AA387" s="30" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="AB387" s="41"/>
       <c r="AC387" s="32"/>
@@ -49255,22 +49255,22 @@
     </row>
     <row r="388" spans="1:43" ht="15.75" customHeight="1">
       <c r="A388" s="282" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="B388" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C388" s="260" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="D388" s="235"/>
       <c r="E388" s="58"/>
       <c r="F388" s="47" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="G388" s="32"/>
       <c r="H388" s="48" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="I388" s="32" t="s">
         <v>2506</v>
@@ -49278,13 +49278,13 @@
       <c r="J388" s="104"/>
       <c r="K388" s="104"/>
       <c r="L388" s="104" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="M388" s="137" t="s">
         <v>657</v>
       </c>
       <c r="N388" s="54" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="O388" s="54"/>
       <c r="P388" s="55"/>
@@ -49296,25 +49296,25 @@
         <v>41</v>
       </c>
       <c r="T388" s="21" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="U388" s="28"/>
       <c r="V388" s="28"/>
       <c r="W388" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X388" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X388" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y388" s="30" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="Z388" s="30"/>
       <c r="AA388" s="30" t="s">
+        <v>3160</v>
+      </c>
+      <c r="AB388" s="46" t="s">
         <v>3161</v>
-      </c>
-      <c r="AB388" s="46" t="s">
-        <v>3162</v>
       </c>
       <c r="AC388" s="32"/>
       <c r="AD388" s="21"/>
@@ -49334,29 +49334,29 @@
     </row>
     <row r="389" spans="1:43" ht="45.75" customHeight="1">
       <c r="A389" s="417" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="B389" s="421" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="C389" s="262" t="s">
         <v>171</v>
       </c>
       <c r="E389" s="230"/>
       <c r="F389" s="433" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="G389" s="230"/>
       <c r="H389" s="440" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="I389" s="440" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="J389" s="230"/>
       <c r="K389" s="230"/>
       <c r="L389" s="230" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="M389" s="450" t="s">
         <v>2081</v>
@@ -49374,7 +49374,7 @@
         <v>41</v>
       </c>
       <c r="T389" s="423" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="U389" s="230"/>
       <c r="V389" s="230"/>
@@ -49386,7 +49386,7 @@
       <c r="AB389" s="230"/>
       <c r="AC389" s="230"/>
       <c r="AD389" s="423" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="AE389" s="230"/>
       <c r="AF389" s="230"/>
@@ -49404,7 +49404,7 @@
     </row>
     <row r="390" spans="1:43" ht="15.75" customHeight="1">
       <c r="A390" s="186" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="B390" s="33" t="s">
         <v>434</v>
@@ -49415,25 +49415,25 @@
       <c r="D390" s="235"/>
       <c r="E390" s="58"/>
       <c r="F390" s="290" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="G390" s="32"/>
       <c r="H390" s="48" t="s">
+        <v>3166</v>
+      </c>
+      <c r="I390" s="187" t="s">
         <v>3167</v>
       </c>
-      <c r="I390" s="187" t="s">
+      <c r="J390" s="82" t="s">
         <v>3168</v>
-      </c>
-      <c r="J390" s="82" t="s">
-        <v>3169</v>
       </c>
       <c r="K390" s="82"/>
       <c r="L390" s="22"/>
       <c r="M390" s="212" t="s">
+        <v>3169</v>
+      </c>
+      <c r="N390" s="54" t="s">
         <v>3170</v>
-      </c>
-      <c r="N390" s="54" t="s">
-        <v>3171</v>
       </c>
       <c r="O390" s="458"/>
       <c r="P390" s="114"/>
@@ -49448,13 +49448,13 @@
       <c r="U390" s="28"/>
       <c r="V390" s="28"/>
       <c r="W390" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X390" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X390" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y390" s="30" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="Z390" s="30"/>
       <c r="AA390" s="30"/>
@@ -49477,7 +49477,7 @@
     </row>
     <row r="391" spans="1:43" ht="15.75" customHeight="1">
       <c r="A391" s="186" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="B391" s="33" t="s">
         <v>434</v>
@@ -49488,11 +49488,11 @@
       <c r="D391" s="235"/>
       <c r="E391" s="58"/>
       <c r="F391" s="16" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="G391" s="32"/>
       <c r="H391" s="192" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="I391" s="32" t="s">
         <v>2546</v>
@@ -49500,20 +49500,20 @@
       <c r="J391" s="98"/>
       <c r="K391" s="165"/>
       <c r="L391" s="196" t="s">
+        <v>3175</v>
+      </c>
+      <c r="M391" s="137" t="s">
         <v>3176</v>
       </c>
-      <c r="M391" s="137" t="s">
+      <c r="N391" s="136" t="s">
         <v>3177</v>
-      </c>
-      <c r="N391" s="136" t="s">
-        <v>3178</v>
       </c>
       <c r="O391" s="136"/>
       <c r="P391" s="74" t="s">
+        <v>3178</v>
+      </c>
+      <c r="Q391" s="56" t="s">
         <v>3179</v>
-      </c>
-      <c r="Q391" s="56" t="s">
-        <v>3180</v>
       </c>
       <c r="R391" s="333" t="s">
         <v>40</v>
@@ -49531,19 +49531,19 @@
         <v>2629</v>
       </c>
       <c r="W391" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X391" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X391" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y391" s="30" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="Z391" s="30"/>
       <c r="AA391" s="30"/>
       <c r="AB391" s="41"/>
       <c r="AC391" s="32" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="AD391" s="21"/>
       <c r="AE391" s="32"/>
@@ -49562,7 +49562,7 @@
     </row>
     <row r="392" spans="1:43" ht="15.75" customHeight="1">
       <c r="A392" s="193" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B392" s="33" t="s">
         <v>434</v>
@@ -49573,11 +49573,11 @@
       <c r="D392" s="235"/>
       <c r="E392" s="58"/>
       <c r="F392" s="290" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="G392" s="32"/>
       <c r="H392" s="206" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="I392" s="192" t="s">
         <v>2506</v>
@@ -49589,7 +49589,7 @@
         <v>888</v>
       </c>
       <c r="N392" s="54" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="O392" s="54"/>
       <c r="P392" s="55"/>
@@ -49604,19 +49604,19 @@
       <c r="U392" s="28"/>
       <c r="V392" s="28"/>
       <c r="W392" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X392" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X392" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y392" s="30" t="s">
+        <v>3186</v>
+      </c>
+      <c r="Z392" s="30" t="s">
         <v>3187</v>
       </c>
-      <c r="Z392" s="30" t="s">
+      <c r="AA392" s="30" t="s">
         <v>3188</v>
-      </c>
-      <c r="AA392" s="30" t="s">
-        <v>3189</v>
       </c>
       <c r="AB392" s="41"/>
       <c r="AC392" s="32"/>
@@ -49637,7 +49637,7 @@
     </row>
     <row r="393" spans="1:43" ht="15.75" customHeight="1">
       <c r="A393" s="416" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="B393" s="420" t="s">
         <v>434</v>
@@ -49648,11 +49648,11 @@
       <c r="D393" s="337"/>
       <c r="E393" s="138"/>
       <c r="F393" s="432" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="G393" s="32"/>
       <c r="H393" s="439" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="I393" s="39" t="s">
         <v>2506</v>
@@ -49660,13 +49660,13 @@
       <c r="J393" s="82"/>
       <c r="K393" s="82"/>
       <c r="L393" s="82" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="M393" s="137" t="s">
         <v>542</v>
       </c>
       <c r="N393" s="458" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="O393" s="458"/>
       <c r="P393" s="114"/>
@@ -49678,7 +49678,7 @@
         <v>41</v>
       </c>
       <c r="T393" s="105" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="U393" s="483"/>
       <c r="V393" s="483"/>
@@ -49689,11 +49689,11 @@
         <v>2237</v>
       </c>
       <c r="Y393" s="103" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="Z393" s="103"/>
       <c r="AA393" s="103" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="AB393" s="497"/>
       <c r="AC393" s="39"/>
@@ -49714,7 +49714,7 @@
     </row>
     <row r="394" spans="1:43" ht="15.75" customHeight="1">
       <c r="A394" s="186" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="B394" s="33" t="s">
         <v>434</v>
@@ -49725,17 +49725,17 @@
       <c r="D394" s="235"/>
       <c r="E394" s="58"/>
       <c r="F394" s="47" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="G394" s="32"/>
       <c r="H394" s="206" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="I394" s="32" t="s">
         <v>2506</v>
       </c>
       <c r="J394" s="22" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="K394" s="22"/>
       <c r="L394" s="22"/>
@@ -49743,7 +49743,7 @@
         <v>542</v>
       </c>
       <c r="N394" s="54" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="O394" s="54"/>
       <c r="P394" s="55"/>
@@ -49755,22 +49755,22 @@
         <v>41</v>
       </c>
       <c r="T394" s="21" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="U394" s="28"/>
       <c r="V394" s="28"/>
       <c r="W394" s="72" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X394" s="72" t="s">
         <v>3150</v>
       </c>
-      <c r="X394" s="72" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y394" s="198" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="Z394" s="198"/>
       <c r="AA394" s="30" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="AB394" s="41"/>
       <c r="AC394" s="32"/>
@@ -49791,7 +49791,7 @@
     </row>
     <row r="395" spans="1:43" ht="15.75" customHeight="1">
       <c r="A395" s="186" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B395" s="33" t="s">
         <v>434</v>
@@ -49802,29 +49802,29 @@
       <c r="D395" s="245"/>
       <c r="E395" s="52"/>
       <c r="F395" s="16" t="s">
+        <v>3203</v>
+      </c>
+      <c r="G395" s="48" t="s">
         <v>3204</v>
       </c>
-      <c r="G395" s="48" t="s">
+      <c r="H395" s="48" t="s">
         <v>3205</v>
-      </c>
-      <c r="H395" s="48" t="s">
-        <v>3206</v>
       </c>
       <c r="I395" s="187" t="s">
         <v>2506</v>
       </c>
       <c r="J395" s="82"/>
       <c r="K395" s="82" t="s">
+        <v>3206</v>
+      </c>
+      <c r="L395" s="82" t="s">
         <v>3207</v>
       </c>
-      <c r="L395" s="82" t="s">
+      <c r="M395" s="95" t="s">
+        <v>3951</v>
+      </c>
+      <c r="N395" s="54" t="s">
         <v>3208</v>
-      </c>
-      <c r="M395" s="95" t="s">
-        <v>3952</v>
-      </c>
-      <c r="N395" s="54" t="s">
-        <v>3209</v>
       </c>
       <c r="O395" s="54"/>
       <c r="P395" s="55"/>
@@ -49862,38 +49862,38 @@
     </row>
     <row r="396" spans="1:43" ht="15.75" customHeight="1">
       <c r="A396" s="281" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="B396" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C396" s="251" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="D396" s="235"/>
       <c r="E396" s="58"/>
       <c r="F396" s="16" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="G396" s="32"/>
       <c r="H396" s="206" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="I396" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J396" s="35"/>
       <c r="K396" s="22" t="s">
+        <v>3211</v>
+      </c>
+      <c r="L396" s="22" t="s">
+        <v>3168</v>
+      </c>
+      <c r="M396" s="137" t="s">
         <v>3212</v>
       </c>
-      <c r="L396" s="22" t="s">
-        <v>3169</v>
-      </c>
-      <c r="M396" s="137" t="s">
+      <c r="N396" s="54" t="s">
         <v>3213</v>
-      </c>
-      <c r="N396" s="54" t="s">
-        <v>3214</v>
       </c>
       <c r="O396" s="54"/>
       <c r="P396" s="55"/>
@@ -49908,20 +49908,20 @@
       <c r="U396" s="28"/>
       <c r="V396" s="28"/>
       <c r="W396" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X396" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X396" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y396" s="170" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="Z396" s="103"/>
       <c r="AA396" s="30" t="s">
+        <v>3215</v>
+      </c>
+      <c r="AB396" s="46" t="s">
         <v>3216</v>
-      </c>
-      <c r="AB396" s="46" t="s">
-        <v>3217</v>
       </c>
       <c r="AC396" s="32"/>
       <c r="AD396" s="21"/>
@@ -49941,7 +49941,7 @@
     </row>
     <row r="397" spans="1:43" ht="41.25" customHeight="1">
       <c r="A397" s="186" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B397" s="33" t="s">
         <v>434</v>
@@ -49952,25 +49952,25 @@
       <c r="D397" s="235"/>
       <c r="E397" s="58"/>
       <c r="F397" s="290" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="G397" s="32"/>
       <c r="H397" s="206" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="I397" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J397" s="68" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="K397" s="109"/>
       <c r="L397" s="109"/>
       <c r="M397" s="137" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="N397" s="54" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="O397" s="54"/>
       <c r="P397" s="55"/>
@@ -49985,26 +49985,26 @@
       <c r="U397" s="28"/>
       <c r="V397" s="28"/>
       <c r="W397" s="29" t="s">
+        <v>3222</v>
+      </c>
+      <c r="X397" s="29" t="s">
         <v>3223</v>
       </c>
-      <c r="X397" s="29" t="s">
+      <c r="Y397" s="198" t="s">
         <v>3224</v>
-      </c>
-      <c r="Y397" s="198" t="s">
-        <v>3225</v>
       </c>
       <c r="Z397" s="200"/>
       <c r="AA397" s="198" t="s">
+        <v>3225</v>
+      </c>
+      <c r="AB397" s="46" t="s">
         <v>3226</v>
       </c>
-      <c r="AB397" s="46" t="s">
+      <c r="AC397" s="47" t="s">
         <v>3227</v>
       </c>
-      <c r="AC397" s="47" t="s">
+      <c r="AD397" s="21" t="s">
         <v>3228</v>
-      </c>
-      <c r="AD397" s="21" t="s">
-        <v>3229</v>
       </c>
       <c r="AE397" s="32"/>
       <c r="AF397" s="32"/>
@@ -50022,7 +50022,7 @@
     </row>
     <row r="398" spans="1:43" ht="15.75" customHeight="1">
       <c r="A398" s="282" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="B398" s="33" t="s">
         <v>434</v>
@@ -50033,11 +50033,11 @@
       <c r="D398" s="235"/>
       <c r="E398" s="58"/>
       <c r="F398" s="290" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="G398" s="32"/>
       <c r="H398" s="292" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="I398" s="192" t="s">
         <v>2506</v>
@@ -50046,10 +50046,10 @@
       <c r="K398" s="22"/>
       <c r="L398" s="22"/>
       <c r="M398" s="137" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="N398" s="54" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="O398" s="54"/>
       <c r="P398" s="216"/>
@@ -50087,7 +50087,7 @@
     </row>
     <row r="399" spans="1:43" ht="15.75" customHeight="1">
       <c r="A399" s="186" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="B399" s="33" t="s">
         <v>434</v>
@@ -50098,25 +50098,25 @@
       <c r="D399" s="235"/>
       <c r="E399" s="58"/>
       <c r="F399" s="290" t="s">
+        <v>3232</v>
+      </c>
+      <c r="G399" s="32" t="s">
         <v>3233</v>
       </c>
-      <c r="G399" s="32" t="s">
+      <c r="H399" s="206" t="s">
         <v>3234</v>
       </c>
-      <c r="H399" s="206" t="s">
+      <c r="I399" s="32" t="s">
         <v>3235</v>
-      </c>
-      <c r="I399" s="32" t="s">
-        <v>3236</v>
       </c>
       <c r="J399" s="22"/>
       <c r="K399" s="22"/>
       <c r="L399" s="22"/>
       <c r="M399" s="212" t="s">
+        <v>3236</v>
+      </c>
+      <c r="N399" s="38" t="s">
         <v>3237</v>
-      </c>
-      <c r="N399" s="38" t="s">
-        <v>3238</v>
       </c>
       <c r="O399" s="38"/>
       <c r="P399" s="126"/>
@@ -50154,7 +50154,7 @@
     </row>
     <row r="400" spans="1:43" ht="15.75" customHeight="1">
       <c r="A400" s="282" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="B400" s="33" t="s">
         <v>434</v>
@@ -50165,32 +50165,32 @@
       <c r="D400" s="235"/>
       <c r="E400" s="58"/>
       <c r="F400" s="290" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G400" s="32"/>
       <c r="H400" s="206" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="I400" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J400" s="22"/>
       <c r="K400" s="35" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="L400" s="35"/>
       <c r="M400" s="137" t="s">
+        <v>3241</v>
+      </c>
+      <c r="N400" s="136" t="s">
         <v>3242</v>
-      </c>
-      <c r="N400" s="136" t="s">
-        <v>3243</v>
       </c>
       <c r="O400" s="54" t="s">
         <v>38</v>
       </c>
       <c r="P400" s="55"/>
       <c r="Q400" s="56" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="R400" s="32" t="s">
         <v>544</v>
@@ -50202,18 +50202,18 @@
       <c r="U400" s="28"/>
       <c r="V400" s="28"/>
       <c r="W400" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X400" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X400" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y400" s="30" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="Z400" s="30"/>
       <c r="AA400" s="30"/>
       <c r="AB400" s="31" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="AC400" s="32"/>
       <c r="AD400" s="21"/>
@@ -50233,7 +50233,7 @@
     </row>
     <row r="401" spans="1:43" ht="15.75" customHeight="1">
       <c r="A401" s="186" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="B401" s="33" t="s">
         <v>434</v>
@@ -50244,11 +50244,11 @@
       <c r="D401" s="235"/>
       <c r="E401" s="58"/>
       <c r="F401" s="16" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="G401" s="32"/>
       <c r="H401" s="192" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I401" s="32" t="s">
         <v>2546</v>
@@ -50259,17 +50259,17 @@
       </c>
       <c r="L401" s="447"/>
       <c r="M401" s="451" t="s">
+        <v>3249</v>
+      </c>
+      <c r="N401" s="38" t="s">
         <v>3250</v>
-      </c>
-      <c r="N401" s="38" t="s">
-        <v>3251</v>
       </c>
       <c r="O401" s="38"/>
       <c r="P401" s="317" t="s">
         <v>38</v>
       </c>
       <c r="Q401" s="319" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
       <c r="R401" s="324" t="s">
         <v>80</v>
@@ -50281,13 +50281,13 @@
       <c r="U401" s="28"/>
       <c r="V401" s="28"/>
       <c r="W401" s="29" t="s">
+        <v>3251</v>
+      </c>
+      <c r="X401" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="Y401" s="30" t="s">
         <v>3252</v>
-      </c>
-      <c r="X401" s="29" t="s">
-        <v>3151</v>
-      </c>
-      <c r="Y401" s="30" t="s">
-        <v>3253</v>
       </c>
       <c r="Z401" s="30"/>
       <c r="AA401" s="30"/>
@@ -50310,10 +50310,10 @@
     </row>
     <row r="402" spans="1:43" ht="15.75" customHeight="1">
       <c r="A402" s="186" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B402" s="48" t="s">
         <v>3254</v>
-      </c>
-      <c r="B402" s="48" t="s">
-        <v>3255</v>
       </c>
       <c r="C402" s="250" t="s">
         <v>171</v>
@@ -50321,19 +50321,19 @@
       <c r="D402" s="235"/>
       <c r="E402" s="58"/>
       <c r="F402" s="290" t="s">
+        <v>3255</v>
+      </c>
+      <c r="G402" s="48" t="s">
         <v>3256</v>
       </c>
-      <c r="G402" s="48" t="s">
+      <c r="H402" s="206" t="s">
         <v>3257</v>
-      </c>
-      <c r="H402" s="206" t="s">
-        <v>3258</v>
       </c>
       <c r="I402" s="32" t="s">
         <v>2546</v>
       </c>
       <c r="J402" s="22" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="K402" s="22"/>
       <c r="L402" s="22"/>
@@ -50341,7 +50341,7 @@
         <v>137</v>
       </c>
       <c r="N402" s="54" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="O402" s="54"/>
       <c r="P402" s="55"/>
@@ -50356,18 +50356,18 @@
       <c r="U402" s="28"/>
       <c r="V402" s="28"/>
       <c r="W402" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X402" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X402" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y402" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z402" s="30"/>
       <c r="AA402" s="30"/>
       <c r="AB402" s="46" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="AC402" s="32"/>
       <c r="AD402" s="21"/>
@@ -50387,7 +50387,7 @@
     </row>
     <row r="403" spans="1:43" ht="15.75" customHeight="1">
       <c r="A403" s="293" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="B403" s="33" t="s">
         <v>434</v>
@@ -50398,11 +50398,11 @@
       <c r="D403" s="235"/>
       <c r="E403" s="58"/>
       <c r="F403" s="290" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="G403" s="32"/>
       <c r="H403" s="48" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="I403" s="187" t="s">
         <v>2546</v>
@@ -50410,20 +50410,20 @@
       <c r="J403" s="22"/>
       <c r="K403" s="22"/>
       <c r="L403" s="22" t="s">
+        <v>3263</v>
+      </c>
+      <c r="M403" s="451" t="s">
         <v>3264</v>
       </c>
-      <c r="M403" s="451" t="s">
+      <c r="N403" s="38" t="s">
         <v>3265</v>
       </c>
-      <c r="N403" s="38" t="s">
+      <c r="O403" s="38" t="s">
         <v>3266</v>
-      </c>
-      <c r="O403" s="38" t="s">
-        <v>3267</v>
       </c>
       <c r="P403" s="25"/>
       <c r="Q403" s="56" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="R403" s="39" t="s">
         <v>523</v>
@@ -50435,19 +50435,19 @@
       <c r="U403" s="28"/>
       <c r="V403" s="28"/>
       <c r="W403" s="29" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="X403" s="29" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="Y403" s="170" t="s">
+        <v>3268</v>
+      </c>
+      <c r="Z403" s="103" t="s">
         <v>3269</v>
       </c>
-      <c r="Z403" s="103" t="s">
+      <c r="AA403" s="30" t="s">
         <v>3270</v>
-      </c>
-      <c r="AA403" s="30" t="s">
-        <v>3271</v>
       </c>
       <c r="AB403" s="41"/>
       <c r="AC403" s="32"/>
@@ -50468,7 +50468,7 @@
     </row>
     <row r="404" spans="1:43" ht="15.75" customHeight="1">
       <c r="A404" s="186" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="B404" s="33" t="s">
         <v>434</v>
@@ -50479,27 +50479,27 @@
       <c r="D404" s="235"/>
       <c r="E404" s="58"/>
       <c r="F404" s="47" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="G404" s="32"/>
       <c r="H404" s="206" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="I404" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J404" s="22" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="K404" s="22"/>
       <c r="L404" s="22" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="M404" s="331" t="s">
         <v>601</v>
       </c>
       <c r="N404" s="38" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="O404" s="38"/>
       <c r="P404" s="25"/>
@@ -50514,23 +50514,23 @@
       <c r="U404" s="28"/>
       <c r="V404" s="28"/>
       <c r="W404" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X404" s="72" t="s">
         <v>3150</v>
       </c>
-      <c r="X404" s="72" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y404" s="198" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="Z404" s="490"/>
       <c r="AA404" s="198" t="s">
+        <v>3278</v>
+      </c>
+      <c r="AB404" s="31" t="s">
         <v>3279</v>
       </c>
-      <c r="AB404" s="31" t="s">
+      <c r="AC404" s="47" t="s">
         <v>3280</v>
-      </c>
-      <c r="AC404" s="47" t="s">
-        <v>3281</v>
       </c>
       <c r="AD404" s="21"/>
       <c r="AE404" s="32"/>
@@ -50549,7 +50549,7 @@
     </row>
     <row r="405" spans="1:43" ht="15.75" customHeight="1">
       <c r="A405" s="186" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="B405" s="33" t="s">
         <v>434</v>
@@ -50560,11 +50560,11 @@
       <c r="D405" s="235"/>
       <c r="E405" s="58"/>
       <c r="F405" s="16" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="G405" s="32"/>
       <c r="H405" s="206" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="I405" s="192" t="s">
         <v>2506</v>
@@ -50576,7 +50576,7 @@
         <v>1287</v>
       </c>
       <c r="N405" s="38" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="O405" s="38"/>
       <c r="P405" s="25" t="s">
@@ -50595,23 +50595,23 @@
       <c r="U405" s="28"/>
       <c r="V405" s="28"/>
       <c r="W405" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X405" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X405" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y405" s="198" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="Z405" s="490"/>
       <c r="AA405" s="198" t="s">
+        <v>3286</v>
+      </c>
+      <c r="AB405" s="46" t="s">
         <v>3287</v>
       </c>
-      <c r="AB405" s="46" t="s">
-        <v>3288</v>
-      </c>
       <c r="AC405" s="47" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="AD405" s="21"/>
       <c r="AE405" s="32"/>
@@ -50630,7 +50630,7 @@
     </row>
     <row r="406" spans="1:43" ht="15.75" customHeight="1">
       <c r="A406" s="282" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="B406" s="14" t="s">
         <v>434</v>
@@ -50641,11 +50641,11 @@
       <c r="D406" s="235"/>
       <c r="E406" s="58"/>
       <c r="F406" s="290" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="G406" s="32"/>
       <c r="H406" s="206" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="I406" s="192" t="s">
         <v>2506</v>
@@ -50654,10 +50654,10 @@
       <c r="K406" s="22"/>
       <c r="L406" s="22"/>
       <c r="M406" s="331" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="N406" s="38" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="O406" s="65" t="s">
         <v>38</v>
@@ -50667,31 +50667,31 @@
         <v>1170</v>
       </c>
       <c r="R406" s="94" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="S406" s="77" t="s">
         <v>41</v>
       </c>
       <c r="T406" s="21" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="U406" s="28"/>
       <c r="V406" s="28"/>
       <c r="W406" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X406" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X406" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y406" s="198" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z406" s="490"/>
       <c r="AA406" s="198" t="s">
+        <v>3293</v>
+      </c>
+      <c r="AB406" s="46" t="s">
         <v>3294</v>
-      </c>
-      <c r="AB406" s="46" t="s">
-        <v>3295</v>
       </c>
       <c r="AC406" s="32"/>
       <c r="AD406" s="21"/>
@@ -50711,7 +50711,7 @@
     </row>
     <row r="407" spans="1:43" ht="15.75" customHeight="1">
       <c r="A407" s="186" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="B407" s="33" t="s">
         <v>434</v>
@@ -50722,11 +50722,11 @@
       <c r="D407" s="235"/>
       <c r="E407" s="58"/>
       <c r="F407" s="290" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="G407" s="32"/>
       <c r="H407" s="206" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="I407" s="192" t="s">
         <v>2506</v>
@@ -50734,13 +50734,13 @@
       <c r="J407" s="22"/>
       <c r="K407" s="22"/>
       <c r="L407" s="22" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="M407" s="137" t="s">
         <v>2685</v>
       </c>
       <c r="N407" s="38" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="O407" s="322"/>
       <c r="P407" s="126"/>
@@ -50755,20 +50755,20 @@
       <c r="U407" s="28"/>
       <c r="V407" s="28"/>
       <c r="W407" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X407" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X407" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y407" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z407" s="200"/>
       <c r="AA407" s="30" t="s">
+        <v>3299</v>
+      </c>
+      <c r="AB407" s="46" t="s">
         <v>3300</v>
-      </c>
-      <c r="AB407" s="46" t="s">
-        <v>3301</v>
       </c>
       <c r="AC407" s="32"/>
       <c r="AD407" s="21"/>
@@ -50788,10 +50788,10 @@
     </row>
     <row r="408" spans="1:43" ht="15.75" customHeight="1">
       <c r="A408" s="186" t="s">
+        <v>3301</v>
+      </c>
+      <c r="B408" s="32" t="s">
         <v>3302</v>
-      </c>
-      <c r="B408" s="32" t="s">
-        <v>3303</v>
       </c>
       <c r="C408" s="250" t="s">
         <v>171</v>
@@ -50799,11 +50799,11 @@
       <c r="D408" s="247"/>
       <c r="E408" s="190"/>
       <c r="F408" s="191" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="G408" s="32"/>
       <c r="H408" s="32" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="I408" s="187" t="s">
         <v>2546</v>
@@ -50811,20 +50811,20 @@
       <c r="J408" s="22"/>
       <c r="K408" s="93"/>
       <c r="L408" s="22" t="s">
+        <v>3305</v>
+      </c>
+      <c r="M408" s="95" t="s">
         <v>3306</v>
       </c>
-      <c r="M408" s="95" t="s">
+      <c r="N408" s="65" t="s">
         <v>3307</v>
-      </c>
-      <c r="N408" s="65" t="s">
-        <v>3308</v>
       </c>
       <c r="O408" s="65"/>
       <c r="P408" s="74" t="s">
+        <v>3308</v>
+      </c>
+      <c r="Q408" s="56" t="s">
         <v>3309</v>
-      </c>
-      <c r="Q408" s="56" t="s">
-        <v>3310</v>
       </c>
       <c r="R408" s="101" t="s">
         <v>40</v>
@@ -50859,42 +50859,42 @@
     </row>
     <row r="409" spans="1:43" ht="15.75" customHeight="1">
       <c r="A409" s="282" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="B409" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C409" s="251" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="D409" s="247"/>
       <c r="E409" s="190"/>
       <c r="F409" s="208" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="G409" s="186"/>
       <c r="H409" s="48" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="I409" s="187" t="s">
         <v>2546</v>
       </c>
       <c r="J409" s="104" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="K409" s="104"/>
       <c r="L409" s="109"/>
       <c r="M409" s="209" t="s">
+        <v>3313</v>
+      </c>
+      <c r="N409" s="38" t="s">
         <v>3314</v>
-      </c>
-      <c r="N409" s="38" t="s">
-        <v>3315</v>
       </c>
       <c r="O409" s="38"/>
       <c r="P409" s="25"/>
       <c r="Q409" s="56"/>
       <c r="R409" s="115" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="S409" s="77" t="s">
         <v>41</v>
@@ -50903,13 +50903,13 @@
       <c r="U409" s="28"/>
       <c r="V409" s="28"/>
       <c r="W409" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X409" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X409" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y409" s="30" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="Z409" s="30"/>
       <c r="AA409" s="30"/>
@@ -50932,22 +50932,22 @@
     </row>
     <row r="410" spans="1:43" ht="15.75" customHeight="1">
       <c r="A410" s="287" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="B410" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C410" s="249" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="D410" s="235"/>
       <c r="E410" s="58"/>
       <c r="F410" s="47" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="G410" s="32"/>
       <c r="H410" s="206" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="I410" s="192" t="s">
         <v>2506</v>
@@ -50957,13 +50957,13 @@
         <v>276150</v>
       </c>
       <c r="L410" s="22" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="M410" s="137" t="s">
         <v>2218</v>
       </c>
       <c r="N410" s="38" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="O410" s="38"/>
       <c r="P410" s="25"/>
@@ -50975,7 +50975,7 @@
         <v>41</v>
       </c>
       <c r="T410" s="21" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="U410" s="28"/>
       <c r="V410" s="28"/>
@@ -50983,10 +50983,10 @@
       <c r="X410" s="29"/>
       <c r="Y410" s="30"/>
       <c r="Z410" s="30" t="s">
+        <v>3323</v>
+      </c>
+      <c r="AA410" s="30" t="s">
         <v>3324</v>
-      </c>
-      <c r="AA410" s="30" t="s">
-        <v>3325</v>
       </c>
       <c r="AB410" s="41"/>
       <c r="AC410" s="32"/>
@@ -51007,7 +51007,7 @@
     </row>
     <row r="411" spans="1:43" ht="15.75" customHeight="1">
       <c r="A411" s="186" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="B411" s="33" t="s">
         <v>434</v>
@@ -51018,18 +51018,18 @@
       <c r="D411" s="235"/>
       <c r="E411" s="58"/>
       <c r="F411" s="47" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="G411" s="32"/>
       <c r="H411" s="206" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="I411" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J411" s="22"/>
       <c r="K411" s="22" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="L411" s="22" t="s">
         <v>803</v>
@@ -51038,7 +51038,7 @@
         <v>1103</v>
       </c>
       <c r="N411" s="38" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="O411" s="38"/>
       <c r="P411" s="25"/>
@@ -51053,13 +51053,13 @@
       <c r="U411" s="28"/>
       <c r="V411" s="28"/>
       <c r="W411" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X411" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X411" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y411" s="30" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="Z411" s="30"/>
       <c r="AA411" s="30"/>
@@ -51082,7 +51082,7 @@
     </row>
     <row r="412" spans="1:43" ht="15.75" customHeight="1">
       <c r="A412" s="186" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="B412" s="33" t="s">
         <v>434</v>
@@ -51093,17 +51093,17 @@
       <c r="D412" s="235"/>
       <c r="E412" s="58"/>
       <c r="F412" s="47" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="G412" s="39"/>
       <c r="H412" s="206" t="s">
+        <v>3333</v>
+      </c>
+      <c r="I412" s="32" t="s">
         <v>3334</v>
       </c>
-      <c r="I412" s="32" t="s">
+      <c r="J412" s="109" t="s">
         <v>3335</v>
-      </c>
-      <c r="J412" s="109" t="s">
-        <v>3336</v>
       </c>
       <c r="K412" s="109"/>
       <c r="L412" s="109"/>
@@ -51111,7 +51111,7 @@
         <v>137</v>
       </c>
       <c r="N412" s="38" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="O412" s="38"/>
       <c r="P412" s="25"/>
@@ -51126,13 +51126,13 @@
       <c r="U412" s="28"/>
       <c r="V412" s="28"/>
       <c r="W412" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X412" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X412" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y412" s="30" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="Z412" s="30"/>
       <c r="AA412" s="30"/>
@@ -51155,7 +51155,7 @@
     </row>
     <row r="413" spans="1:43" ht="15.75" customHeight="1">
       <c r="A413" s="186" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="B413" s="33" t="s">
         <v>434</v>
@@ -51166,19 +51166,19 @@
       <c r="D413" s="235"/>
       <c r="E413" s="58"/>
       <c r="F413" s="16" t="s">
+        <v>3339</v>
+      </c>
+      <c r="G413" s="32" t="s">
         <v>3340</v>
       </c>
-      <c r="G413" s="32" t="s">
+      <c r="H413" s="207" t="s">
         <v>3341</v>
       </c>
-      <c r="H413" s="207" t="s">
+      <c r="I413" s="187" t="s">
         <v>3342</v>
       </c>
-      <c r="I413" s="187" t="s">
-        <v>3343</v>
-      </c>
       <c r="J413" s="109" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="K413" s="109"/>
       <c r="L413" s="109"/>
@@ -51186,7 +51186,7 @@
         <v>137</v>
       </c>
       <c r="N413" s="38" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="O413" s="38"/>
       <c r="P413" s="25"/>
@@ -51201,18 +51201,18 @@
       <c r="U413" s="28"/>
       <c r="V413" s="28"/>
       <c r="W413" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X413" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X413" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y413" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z413" s="30"/>
       <c r="AA413" s="30"/>
       <c r="AB413" s="46" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="AC413" s="32"/>
       <c r="AD413" s="21"/>
@@ -51232,7 +51232,7 @@
     </row>
     <row r="414" spans="1:43" ht="15.75" customHeight="1">
       <c r="A414" s="186" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="B414" s="95" t="s">
         <v>2283</v>
@@ -51243,19 +51243,19 @@
       <c r="D414" s="235"/>
       <c r="E414" s="58"/>
       <c r="F414" s="47" t="s">
+        <v>3346</v>
+      </c>
+      <c r="G414" s="32" t="s">
         <v>3347</v>
       </c>
-      <c r="G414" s="32" t="s">
+      <c r="H414" s="207" t="s">
         <v>3348</v>
       </c>
-      <c r="H414" s="207" t="s">
+      <c r="I414" s="187" t="s">
         <v>3349</v>
       </c>
-      <c r="I414" s="187" t="s">
+      <c r="J414" s="22" t="s">
         <v>3350</v>
-      </c>
-      <c r="J414" s="22" t="s">
-        <v>3351</v>
       </c>
       <c r="K414" s="22"/>
       <c r="L414" s="22"/>
@@ -51263,7 +51263,7 @@
         <v>137</v>
       </c>
       <c r="N414" s="38" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="O414" s="38"/>
       <c r="P414" s="25"/>
@@ -51278,13 +51278,13 @@
       <c r="U414" s="28"/>
       <c r="V414" s="28"/>
       <c r="W414" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X414" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X414" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y414" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z414" s="30"/>
       <c r="AA414" s="30"/>
@@ -51307,29 +51307,29 @@
     </row>
     <row r="415" spans="1:43" ht="15.75" customHeight="1">
       <c r="A415" s="287" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="B415" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C415" s="336" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="D415" s="247"/>
       <c r="E415" s="190"/>
       <c r="F415" s="294" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="G415" s="186"/>
       <c r="H415" s="206" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="I415" s="187" t="s">
         <v>2546</v>
       </c>
       <c r="J415" s="22"/>
       <c r="K415" s="22" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="L415" s="22" t="s">
         <v>1360</v>
@@ -51338,7 +51338,7 @@
         <v>1103</v>
       </c>
       <c r="N415" s="38" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="O415" s="38"/>
       <c r="P415" s="25"/>
@@ -51353,13 +51353,13 @@
       <c r="U415" s="28"/>
       <c r="V415" s="28"/>
       <c r="W415" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X415" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X415" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y415" s="30" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="Z415" s="103"/>
       <c r="AA415" s="30"/>
@@ -51382,22 +51382,22 @@
     </row>
     <row r="416" spans="1:43" ht="15.75" customHeight="1">
       <c r="A416" s="296" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="B416" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C416" s="255" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="D416" s="235"/>
       <c r="E416" s="58"/>
       <c r="F416" s="290" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="G416" s="32"/>
       <c r="H416" s="206" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="I416" s="32" t="s">
         <v>2506</v>
@@ -51409,7 +51409,7 @@
         <v>1840</v>
       </c>
       <c r="N416" s="38" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="O416" s="65" t="s">
         <v>38</v>
@@ -51428,20 +51428,20 @@
       <c r="U416" s="28"/>
       <c r="V416" s="28"/>
       <c r="W416" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X416" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X416" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y416" s="30" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="Z416" s="200"/>
       <c r="AA416" s="30" t="s">
+        <v>3362</v>
+      </c>
+      <c r="AB416" s="46" t="s">
         <v>3363</v>
-      </c>
-      <c r="AB416" s="46" t="s">
-        <v>3364</v>
       </c>
       <c r="AC416" s="32"/>
       <c r="AD416" s="21"/>
@@ -51461,7 +51461,7 @@
     </row>
     <row r="417" spans="1:43" ht="15.75" customHeight="1">
       <c r="A417" s="282" t="s">
-        <v>3912</v>
+        <v>3911</v>
       </c>
       <c r="B417" s="33" t="s">
         <v>434</v>
@@ -51472,23 +51472,23 @@
       <c r="D417" s="235"/>
       <c r="E417" s="58"/>
       <c r="F417" s="290" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="G417" s="32"/>
       <c r="H417" s="206" t="s">
+        <v>3365</v>
+      </c>
+      <c r="I417" s="32" t="s">
         <v>3366</v>
-      </c>
-      <c r="I417" s="32" t="s">
-        <v>3367</v>
       </c>
       <c r="J417" s="22"/>
       <c r="K417" s="22"/>
       <c r="L417" s="22"/>
       <c r="M417" s="115" t="s">
+        <v>3367</v>
+      </c>
+      <c r="N417" s="38" t="s">
         <v>3368</v>
-      </c>
-      <c r="N417" s="38" t="s">
-        <v>3369</v>
       </c>
       <c r="O417" s="38"/>
       <c r="P417" s="25"/>
@@ -51528,7 +51528,7 @@
     </row>
     <row r="418" spans="1:43" ht="15.75" customHeight="1">
       <c r="A418" s="193" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="B418" s="33" t="s">
         <v>434</v>
@@ -51539,27 +51539,27 @@
       <c r="D418" s="235"/>
       <c r="E418" s="58"/>
       <c r="F418" s="290" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="G418" s="32"/>
       <c r="H418" s="39" t="s">
+        <v>3370</v>
+      </c>
+      <c r="I418" s="192" t="s">
         <v>3371</v>
       </c>
-      <c r="I418" s="192" t="s">
+      <c r="J418" s="109" t="s">
         <v>3372</v>
-      </c>
-      <c r="J418" s="109" t="s">
-        <v>3373</v>
       </c>
       <c r="K418" s="109"/>
       <c r="L418" s="109" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="M418" s="43" t="s">
         <v>137</v>
       </c>
       <c r="N418" s="38" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="O418" s="38"/>
       <c r="P418" s="25"/>
@@ -51597,30 +51597,30 @@
     </row>
     <row r="419" spans="1:43" ht="15.75" customHeight="1">
       <c r="A419" s="186" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="B419" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C419" s="424" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="D419" s="235"/>
       <c r="E419" s="58"/>
       <c r="F419" s="290" t="s">
+        <v>3374</v>
+      </c>
+      <c r="G419" s="32" t="s">
         <v>3375</v>
       </c>
-      <c r="G419" s="32" t="s">
+      <c r="H419" s="207" t="s">
         <v>3376</v>
       </c>
-      <c r="H419" s="207" t="s">
+      <c r="I419" s="187" t="s">
         <v>3377</v>
       </c>
-      <c r="I419" s="187" t="s">
+      <c r="J419" s="22" t="s">
         <v>3378</v>
-      </c>
-      <c r="J419" s="22" t="s">
-        <v>3379</v>
       </c>
       <c r="K419" s="22"/>
       <c r="L419" s="22"/>
@@ -51628,7 +51628,7 @@
         <v>137</v>
       </c>
       <c r="N419" s="38" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="O419" s="38"/>
       <c r="P419" s="25"/>
@@ -51666,7 +51666,7 @@
     </row>
     <row r="420" spans="1:43" ht="15.75" customHeight="1">
       <c r="A420" s="186" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="B420" s="33" t="s">
         <v>434</v>
@@ -51677,11 +51677,11 @@
       <c r="D420" s="247"/>
       <c r="E420" s="190"/>
       <c r="F420" s="294" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G420" s="186"/>
       <c r="H420" s="192" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="I420" s="192" t="s">
         <v>2506</v>
@@ -51689,13 +51689,13 @@
       <c r="J420" s="22"/>
       <c r="K420" s="22"/>
       <c r="L420" s="22" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="M420" s="137" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="N420" s="38" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="O420" s="38"/>
       <c r="P420" s="25"/>
@@ -51710,17 +51710,17 @@
       <c r="U420" s="28"/>
       <c r="V420" s="28"/>
       <c r="W420" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X420" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X420" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y420" s="30" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="Z420" s="490"/>
       <c r="AA420" s="30" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="AB420" s="41"/>
       <c r="AC420" s="32"/>
@@ -51741,22 +51741,22 @@
     </row>
     <row r="421" spans="1:43" ht="15.75" customHeight="1">
       <c r="A421" s="186" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="B421" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C421" s="424" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="D421" s="247"/>
       <c r="E421" s="58"/>
       <c r="F421" s="290" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="G421" s="186"/>
       <c r="H421" s="206" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="I421" s="32" t="s">
         <v>2506</v>
@@ -51767,10 +51767,10 @@
         <v>2751</v>
       </c>
       <c r="M421" s="137" t="s">
+        <v>3388</v>
+      </c>
+      <c r="N421" s="38" t="s">
         <v>3389</v>
-      </c>
-      <c r="N421" s="38" t="s">
-        <v>3390</v>
       </c>
       <c r="O421" s="38"/>
       <c r="P421" s="25"/>
@@ -51785,23 +51785,23 @@
       <c r="U421" s="28"/>
       <c r="V421" s="28"/>
       <c r="W421" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X421" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X421" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y421" s="30" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="Z421" s="200"/>
       <c r="AA421" s="30" t="s">
+        <v>3391</v>
+      </c>
+      <c r="AB421" s="46" t="s">
         <v>3392</v>
       </c>
-      <c r="AB421" s="46" t="s">
+      <c r="AC421" s="66" t="s">
         <v>3393</v>
-      </c>
-      <c r="AC421" s="66" t="s">
-        <v>3394</v>
       </c>
       <c r="AD421" s="32"/>
       <c r="AE421" s="32"/>
@@ -51820,7 +51820,7 @@
     </row>
     <row r="422" spans="1:43" ht="15.75" customHeight="1">
       <c r="A422" s="186" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="B422" s="33" t="s">
         <v>434</v>
@@ -51831,17 +51831,17 @@
       <c r="D422" s="247"/>
       <c r="E422" s="190"/>
       <c r="F422" s="191" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="G422" s="186"/>
       <c r="H422" s="206" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="I422" s="192" t="s">
         <v>2506</v>
       </c>
       <c r="J422" s="82" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="K422" s="82"/>
       <c r="L422" s="82"/>
@@ -51849,14 +51849,14 @@
         <v>657</v>
       </c>
       <c r="N422" s="38" t="s">
+        <v>3398</v>
+      </c>
+      <c r="O422" s="38" t="s">
         <v>3399</v>
-      </c>
-      <c r="O422" s="38" t="s">
-        <v>3400</v>
       </c>
       <c r="P422" s="25"/>
       <c r="Q422" s="26" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="R422" s="39" t="s">
         <v>523</v>
@@ -51868,22 +51868,22 @@
       <c r="U422" s="28"/>
       <c r="V422" s="28"/>
       <c r="W422" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X422" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X422" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y422" s="30" t="s">
+        <v>3401</v>
+      </c>
+      <c r="Z422" s="30" t="s">
         <v>3402</v>
       </c>
-      <c r="Z422" s="30" t="s">
+      <c r="AA422" s="30" t="s">
         <v>3403</v>
       </c>
-      <c r="AA422" s="30" t="s">
+      <c r="AB422" s="46" t="s">
         <v>3404</v>
-      </c>
-      <c r="AB422" s="46" t="s">
-        <v>3405</v>
       </c>
       <c r="AC422" s="32"/>
       <c r="AD422" s="32"/>
@@ -51903,7 +51903,7 @@
     </row>
     <row r="423" spans="1:43" ht="15.75" customHeight="1">
       <c r="A423" s="186" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="B423" s="33" t="s">
         <v>434</v>
@@ -51914,11 +51914,11 @@
       <c r="D423" s="247"/>
       <c r="E423" s="190"/>
       <c r="F423" s="191" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="G423" s="186"/>
       <c r="H423" s="206" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="I423" s="192" t="s">
         <v>2506</v>
@@ -51932,14 +51932,14 @@
         <v>657</v>
       </c>
       <c r="N423" s="38" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="O423" s="38"/>
       <c r="P423" s="25" t="s">
+        <v>3408</v>
+      </c>
+      <c r="Q423" s="56" t="s">
         <v>3409</v>
-      </c>
-      <c r="Q423" s="56" t="s">
-        <v>3410</v>
       </c>
       <c r="R423" s="99" t="s">
         <v>544</v>
@@ -51948,25 +51948,25 @@
         <v>41</v>
       </c>
       <c r="T423" s="21" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="U423" s="28"/>
       <c r="V423" s="28"/>
       <c r="W423" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X423" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X423" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y423" s="30" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="Z423" s="30"/>
       <c r="AA423" s="30" t="s">
+        <v>3979</v>
+      </c>
+      <c r="AB423" s="41" t="s">
         <v>3980</v>
-      </c>
-      <c r="AB423" s="41" t="s">
-        <v>3981</v>
       </c>
       <c r="AC423" s="32"/>
       <c r="AD423" s="32"/>
@@ -51986,7 +51986,7 @@
     </row>
     <row r="424" spans="1:43" ht="15.75" customHeight="1">
       <c r="A424" s="186" t="s">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="B424" s="14" t="s">
         <v>434</v>
@@ -51997,14 +51997,14 @@
       <c r="D424" s="235"/>
       <c r="E424" s="58"/>
       <c r="F424" s="290" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="G424" s="32"/>
       <c r="H424" s="206" t="s">
+        <v>3413</v>
+      </c>
+      <c r="I424" s="187" t="s">
         <v>3414</v>
-      </c>
-      <c r="I424" s="187" t="s">
-        <v>3415</v>
       </c>
       <c r="J424" s="82"/>
       <c r="K424" s="82"/>
@@ -52028,13 +52028,13 @@
       <c r="U424" s="28"/>
       <c r="V424" s="28"/>
       <c r="W424" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X424" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X424" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y424" s="30" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="Z424" s="30"/>
       <c r="AA424" s="30"/>
@@ -52057,22 +52057,22 @@
     </row>
     <row r="425" spans="1:43" ht="15.75" customHeight="1">
       <c r="A425" s="287" t="s">
-        <v>3916</v>
+        <v>3915</v>
       </c>
       <c r="B425" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C425" s="257" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="D425" s="235"/>
       <c r="E425" s="58"/>
       <c r="F425" s="16" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="G425" s="32"/>
       <c r="H425" s="206" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="I425" s="217" t="s">
         <v>582</v>
@@ -52080,20 +52080,20 @@
       <c r="J425" s="35"/>
       <c r="K425" s="22"/>
       <c r="L425" s="22" t="s">
+        <v>3419</v>
+      </c>
+      <c r="M425" s="332" t="s">
         <v>3420</v>
       </c>
-      <c r="M425" s="332" t="s">
+      <c r="N425" s="54" t="s">
         <v>3421</v>
-      </c>
-      <c r="N425" s="54" t="s">
-        <v>3422</v>
       </c>
       <c r="O425" s="54"/>
       <c r="P425" s="74" t="s">
+        <v>3422</v>
+      </c>
+      <c r="Q425" s="56" t="s">
         <v>3423</v>
-      </c>
-      <c r="Q425" s="56" t="s">
-        <v>3424</v>
       </c>
       <c r="R425" s="101" t="s">
         <v>40</v>
@@ -52105,13 +52105,13 @@
       <c r="U425" s="28"/>
       <c r="V425" s="28"/>
       <c r="W425" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X425" s="29" t="s">
         <v>3150</v>
       </c>
-      <c r="X425" s="29" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y425" s="30" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="Z425" s="30"/>
       <c r="AA425" s="30"/>
@@ -52134,7 +52134,7 @@
     </row>
     <row r="426" spans="1:43" ht="15.75" customHeight="1">
       <c r="A426" s="186" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="B426" s="33" t="s">
         <v>434</v>
@@ -52145,14 +52145,14 @@
       <c r="D426" s="235"/>
       <c r="E426" s="58"/>
       <c r="F426" s="47" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="G426" s="32"/>
       <c r="H426" s="192" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="I426" s="217" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="J426" s="22"/>
       <c r="K426" s="93"/>
@@ -52199,7 +52199,7 @@
     </row>
     <row r="427" spans="1:43" ht="15.75" customHeight="1">
       <c r="A427" s="186" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="B427" s="33" t="s">
         <v>434</v>
@@ -52210,14 +52210,14 @@
       <c r="D427" s="235"/>
       <c r="E427" s="58"/>
       <c r="F427" s="290" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="G427" s="32"/>
       <c r="H427" s="192" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="I427" s="32" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="J427" s="22"/>
       <c r="K427" s="22"/>
@@ -52266,7 +52266,7 @@
     </row>
     <row r="428" spans="1:43" ht="15.75" customHeight="1">
       <c r="A428" s="186" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="B428" s="14" t="s">
         <v>434</v>
@@ -52277,11 +52277,11 @@
       <c r="D428" s="235"/>
       <c r="E428" s="58"/>
       <c r="F428" s="290" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="G428" s="32"/>
       <c r="H428" s="48" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="I428" s="187" t="s">
         <v>2546</v>
@@ -52289,13 +52289,13 @@
       <c r="J428" s="22"/>
       <c r="K428" s="22"/>
       <c r="L428" s="22" t="s">
+        <v>3433</v>
+      </c>
+      <c r="M428" s="137" t="s">
         <v>3434</v>
       </c>
-      <c r="M428" s="137" t="s">
+      <c r="N428" s="54" t="s">
         <v>3435</v>
-      </c>
-      <c r="N428" s="54" t="s">
-        <v>3436</v>
       </c>
       <c r="O428" s="54"/>
       <c r="P428" s="55"/>
@@ -52310,13 +52310,13 @@
       <c r="U428" s="28"/>
       <c r="V428" s="28"/>
       <c r="W428" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X428" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X428" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y428" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z428" s="30"/>
       <c r="AA428" s="30"/>
@@ -52339,7 +52339,7 @@
     </row>
     <row r="429" spans="1:43" ht="15.75" customHeight="1">
       <c r="A429" s="186" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="B429" s="33" t="s">
         <v>434</v>
@@ -52350,11 +52350,11 @@
       <c r="D429" s="235"/>
       <c r="E429" s="58"/>
       <c r="F429" s="290" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="G429" s="32"/>
       <c r="H429" s="206" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="I429" s="192" t="s">
         <v>2546</v>
@@ -52365,10 +52365,10 @@
         <v>991</v>
       </c>
       <c r="M429" s="137" t="s">
+        <v>3367</v>
+      </c>
+      <c r="N429" s="54" t="s">
         <v>3368</v>
-      </c>
-      <c r="N429" s="54" t="s">
-        <v>3369</v>
       </c>
       <c r="O429" s="458"/>
       <c r="P429" s="114"/>
@@ -52383,13 +52383,13 @@
       <c r="U429" s="28"/>
       <c r="V429" s="28"/>
       <c r="W429" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X429" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X429" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y429" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z429" s="30"/>
       <c r="AA429" s="30"/>
@@ -52412,7 +52412,7 @@
     </row>
     <row r="430" spans="1:43" ht="15.75" customHeight="1">
       <c r="A430" s="282" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
       <c r="B430" s="33" t="s">
         <v>434</v>
@@ -52423,11 +52423,11 @@
       <c r="D430" s="235"/>
       <c r="E430" s="58"/>
       <c r="F430" s="290" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="G430" s="32"/>
       <c r="H430" s="206" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="I430" s="192" t="s">
         <v>2546</v>
@@ -52436,14 +52436,14 @@
       <c r="K430" s="82"/>
       <c r="L430" s="82"/>
       <c r="M430" s="137" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="N430" s="38" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="O430" s="38"/>
       <c r="P430" s="317" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="Q430" s="26"/>
       <c r="R430" s="117" t="s">
@@ -52479,7 +52479,7 @@
     </row>
     <row r="431" spans="1:43" ht="15.75" customHeight="1">
       <c r="A431" s="282" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
       <c r="B431" s="33" t="s">
         <v>434</v>
@@ -52490,11 +52490,11 @@
       <c r="D431" s="235"/>
       <c r="E431" s="58"/>
       <c r="F431" s="47" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="G431" s="32"/>
       <c r="H431" s="206" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="I431" s="192" t="s">
         <v>2546</v>
@@ -52503,10 +52503,10 @@
       <c r="K431" s="82"/>
       <c r="L431" s="22"/>
       <c r="M431" s="137" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="N431" s="38" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="O431" s="38"/>
       <c r="P431" s="25"/>
@@ -52544,7 +52544,7 @@
     </row>
     <row r="432" spans="1:43" ht="15.75" customHeight="1">
       <c r="A432" s="282" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
       <c r="B432" s="33" t="s">
         <v>434</v>
@@ -52555,11 +52555,11 @@
       <c r="D432" s="235"/>
       <c r="E432" s="58"/>
       <c r="F432" s="16" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="G432" s="32"/>
       <c r="H432" s="206" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="I432" s="192" t="s">
         <v>2546</v>
@@ -52567,19 +52567,19 @@
       <c r="J432" s="98"/>
       <c r="K432" s="104"/>
       <c r="L432" s="104" t="s">
+        <v>3446</v>
+      </c>
+      <c r="M432" s="137" t="s">
         <v>3447</v>
       </c>
-      <c r="M432" s="137" t="s">
+      <c r="N432" s="54" t="s">
         <v>3448</v>
-      </c>
-      <c r="N432" s="54" t="s">
-        <v>3449</v>
       </c>
       <c r="O432" s="458"/>
       <c r="P432" s="114"/>
       <c r="Q432" s="123"/>
       <c r="R432" s="324" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="S432" s="137" t="s">
         <v>41</v>
@@ -52611,7 +52611,7 @@
     </row>
     <row r="433" spans="1:43" ht="15.75" customHeight="1">
       <c r="A433" s="186" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="B433" s="33" t="s">
         <v>434</v>
@@ -52622,11 +52622,11 @@
       <c r="D433" s="235"/>
       <c r="E433" s="58"/>
       <c r="F433" s="47" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="G433" s="32"/>
       <c r="H433" s="206" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="I433" s="192" t="s">
         <v>2506</v>
@@ -52641,11 +52641,11 @@
         <v>1240</v>
       </c>
       <c r="O433" s="54" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="P433" s="55"/>
       <c r="Q433" s="56" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="R433" s="32" t="s">
         <v>523</v>
@@ -52657,16 +52657,16 @@
       <c r="U433" s="28"/>
       <c r="V433" s="28"/>
       <c r="W433" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X433" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X433" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y433" s="30" t="s">
+        <v>3455</v>
+      </c>
+      <c r="Z433" s="30" t="s">
         <v>3456</v>
-      </c>
-      <c r="Z433" s="30" t="s">
-        <v>3457</v>
       </c>
       <c r="AA433" s="30"/>
       <c r="AB433" s="41"/>
@@ -52688,7 +52688,7 @@
     </row>
     <row r="434" spans="1:43" ht="15.75" customHeight="1">
       <c r="A434" s="186" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="B434" s="33" t="s">
         <v>434</v>
@@ -52699,11 +52699,11 @@
       <c r="D434" s="235"/>
       <c r="E434" s="58"/>
       <c r="F434" s="290" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="G434" s="32"/>
       <c r="H434" s="206" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="I434" s="192" t="s">
         <v>2546</v>
@@ -52715,7 +52715,7 @@
         <v>2729</v>
       </c>
       <c r="N434" s="136" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="O434" s="54"/>
       <c r="P434" s="55"/>
@@ -52730,13 +52730,13 @@
       <c r="U434" s="28"/>
       <c r="V434" s="28"/>
       <c r="W434" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X434" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X434" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y434" s="30" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="Z434" s="30"/>
       <c r="AA434" s="30"/>
@@ -52759,7 +52759,7 @@
     </row>
     <row r="435" spans="1:43" ht="15.75" customHeight="1">
       <c r="A435" s="186" t="s">
-        <v>3920</v>
+        <v>3919</v>
       </c>
       <c r="B435" s="33" t="s">
         <v>434</v>
@@ -52770,11 +52770,11 @@
       <c r="D435" s="235"/>
       <c r="E435" s="58"/>
       <c r="F435" s="290" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="G435" s="32"/>
       <c r="H435" s="206" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="I435" s="192" t="s">
         <v>2546</v>
@@ -52786,7 +52786,7 @@
         <v>253</v>
       </c>
       <c r="N435" s="54" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="O435" s="54"/>
       <c r="P435" s="55"/>
@@ -52824,7 +52824,7 @@
     </row>
     <row r="436" spans="1:43" ht="15.75" customHeight="1">
       <c r="A436" s="282" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="B436" s="33" t="s">
         <v>434</v>
@@ -52835,17 +52835,17 @@
       <c r="D436" s="235"/>
       <c r="E436" s="58"/>
       <c r="F436" s="290" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="G436" s="32"/>
       <c r="H436" s="192" t="s">
+        <v>3466</v>
+      </c>
+      <c r="I436" s="32" t="s">
         <v>3467</v>
       </c>
-      <c r="I436" s="32" t="s">
-        <v>3468</v>
-      </c>
       <c r="J436" s="82" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="K436" s="82"/>
       <c r="L436" s="22"/>
@@ -52891,24 +52891,24 @@
     </row>
     <row r="437" spans="1:43" ht="15.75" customHeight="1">
       <c r="A437" s="281" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="B437" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C437" s="258" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="D437" s="235"/>
       <c r="E437" s="58"/>
       <c r="F437" s="290" t="s">
+        <v>3469</v>
+      </c>
+      <c r="G437" s="32" t="s">
         <v>3470</v>
       </c>
-      <c r="G437" s="32" t="s">
+      <c r="H437" s="206" t="s">
         <v>3471</v>
-      </c>
-      <c r="H437" s="206" t="s">
-        <v>3472</v>
       </c>
       <c r="I437" s="192" t="s">
         <v>2546</v>
@@ -52916,13 +52916,13 @@
       <c r="J437" s="35"/>
       <c r="K437" s="22"/>
       <c r="L437" s="22" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="M437" s="209" t="s">
         <v>480</v>
       </c>
       <c r="N437" s="54" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="O437" s="54"/>
       <c r="P437" s="55"/>
@@ -52935,19 +52935,19 @@
       </c>
       <c r="T437" s="21"/>
       <c r="U437" s="28" t="s">
+        <v>3474</v>
+      </c>
+      <c r="V437" s="28" t="s">
         <v>3475</v>
       </c>
-      <c r="V437" s="28" t="s">
+      <c r="W437" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X437" s="120" t="s">
+        <v>3150</v>
+      </c>
+      <c r="Y437" s="30" t="s">
         <v>3476</v>
-      </c>
-      <c r="W437" s="29" t="s">
-        <v>3150</v>
-      </c>
-      <c r="X437" s="120" t="s">
-        <v>3151</v>
-      </c>
-      <c r="Y437" s="30" t="s">
-        <v>3477</v>
       </c>
       <c r="Z437" s="30"/>
       <c r="AA437" s="30"/>
@@ -52970,7 +52970,7 @@
     </row>
     <row r="438" spans="1:43" ht="15.75" customHeight="1">
       <c r="A438" s="282" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="B438" s="33" t="s">
         <v>434</v>
@@ -52981,17 +52981,17 @@
       <c r="D438" s="235"/>
       <c r="E438" s="58"/>
       <c r="F438" s="290" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="G438" s="32"/>
       <c r="H438" s="206" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="I438" s="192" t="s">
         <v>2546</v>
       </c>
       <c r="J438" s="104" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="K438" s="104"/>
       <c r="L438" s="109"/>
@@ -52999,7 +52999,7 @@
         <v>137</v>
       </c>
       <c r="N438" s="54" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="O438" s="54"/>
       <c r="P438" s="55"/>
@@ -53014,13 +53014,13 @@
       <c r="U438" s="122"/>
       <c r="V438" s="122"/>
       <c r="W438" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X438" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X438" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y438" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z438" s="30"/>
       <c r="AA438" s="30"/>
@@ -53043,7 +53043,7 @@
     </row>
     <row r="439" spans="1:43" ht="15.75" customHeight="1">
       <c r="A439" s="186" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="B439" s="95" t="s">
         <v>2283</v>
@@ -53054,13 +53054,13 @@
       <c r="D439" s="235"/>
       <c r="E439" s="58"/>
       <c r="F439" s="16" t="s">
+        <v>3482</v>
+      </c>
+      <c r="G439" s="32" t="s">
         <v>3483</v>
       </c>
-      <c r="G439" s="32" t="s">
+      <c r="H439" s="206" t="s">
         <v>3484</v>
-      </c>
-      <c r="H439" s="206" t="s">
-        <v>3485</v>
       </c>
       <c r="I439" s="32" t="s">
         <v>2546</v>
@@ -53068,13 +53068,13 @@
       <c r="J439" s="35"/>
       <c r="K439" s="82"/>
       <c r="L439" s="82" t="s">
+        <v>3485</v>
+      </c>
+      <c r="M439" s="209" t="s">
         <v>3486</v>
       </c>
-      <c r="M439" s="209" t="s">
+      <c r="N439" s="54" t="s">
         <v>3487</v>
-      </c>
-      <c r="N439" s="54" t="s">
-        <v>3488</v>
       </c>
       <c r="O439" s="54"/>
       <c r="P439" s="55"/>
@@ -53087,15 +53087,15 @@
       </c>
       <c r="T439" s="105"/>
       <c r="U439" s="106" t="s">
+        <v>3474</v>
+      </c>
+      <c r="V439" s="106" t="s">
         <v>3475</v>
-      </c>
-      <c r="V439" s="106" t="s">
-        <v>3476</v>
       </c>
       <c r="W439" s="113"/>
       <c r="X439" s="113"/>
       <c r="Y439" s="30" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="Z439" s="30"/>
       <c r="AA439" s="30"/>
@@ -53118,7 +53118,7 @@
     </row>
     <row r="440" spans="1:43" ht="15.75" customHeight="1">
       <c r="A440" s="186" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="B440" s="14" t="s">
         <v>434</v>
@@ -53129,11 +53129,11 @@
       <c r="D440" s="235"/>
       <c r="E440" s="58"/>
       <c r="F440" s="290" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="G440" s="32"/>
       <c r="H440" s="206" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="I440" s="32" t="s">
         <v>2546</v>
@@ -53162,19 +53162,19 @@
       <c r="U440" s="28"/>
       <c r="V440" s="28"/>
       <c r="W440" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X440" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X440" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y440" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z440" s="103"/>
       <c r="AA440" s="30"/>
       <c r="AB440" s="41"/>
       <c r="AC440" s="32" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="AD440" s="32"/>
       <c r="AE440" s="32"/>
@@ -53193,22 +53193,22 @@
     </row>
     <row r="441" spans="1:43" ht="15.75" customHeight="1">
       <c r="A441" s="186" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="B441" s="33" t="s">
         <v>434</v>
       </c>
       <c r="C441" s="295" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="D441" s="235"/>
       <c r="E441" s="58"/>
       <c r="F441" s="290" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="G441" s="32"/>
       <c r="H441" s="206" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="I441" s="192" t="s">
         <v>2506</v>
@@ -53217,17 +53217,17 @@
       <c r="K441" s="82"/>
       <c r="L441" s="82"/>
       <c r="M441" s="137" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="N441" s="136" t="s">
         <v>1240</v>
       </c>
       <c r="O441" s="461" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="P441" s="59"/>
       <c r="Q441" s="56" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="R441" s="32" t="s">
         <v>523</v>
@@ -53239,20 +53239,20 @@
       <c r="U441" s="122"/>
       <c r="V441" s="122"/>
       <c r="W441" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X441" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X441" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y441" s="30" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="Z441" s="200"/>
       <c r="AA441" s="30" t="s">
+        <v>3498</v>
+      </c>
+      <c r="AB441" s="31" t="s">
         <v>3499</v>
-      </c>
-      <c r="AB441" s="31" t="s">
-        <v>3500</v>
       </c>
       <c r="AC441" s="32"/>
       <c r="AD441" s="32"/>
@@ -53272,7 +53272,7 @@
     </row>
     <row r="442" spans="1:43" ht="15.75" customHeight="1">
       <c r="A442" s="186" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="B442" s="33" t="s">
         <v>434</v>
@@ -53283,54 +53283,54 @@
       <c r="D442" s="235"/>
       <c r="E442" s="58"/>
       <c r="F442" s="47" t="s">
+        <v>3501</v>
+      </c>
+      <c r="G442" s="32" t="s">
         <v>3502</v>
       </c>
-      <c r="G442" s="32" t="s">
+      <c r="H442" s="206" t="s">
         <v>3503</v>
       </c>
-      <c r="H442" s="206" t="s">
+      <c r="I442" s="187" t="s">
         <v>3504</v>
-      </c>
-      <c r="I442" s="187" t="s">
-        <v>3505</v>
       </c>
       <c r="J442" s="22"/>
       <c r="K442" s="22"/>
       <c r="L442" s="22"/>
       <c r="M442" s="137" t="s">
+        <v>3505</v>
+      </c>
+      <c r="N442" s="73" t="s">
         <v>3506</v>
-      </c>
-      <c r="N442" s="73" t="s">
-        <v>3507</v>
       </c>
       <c r="O442" s="73"/>
       <c r="P442" s="74" t="s">
+        <v>3507</v>
+      </c>
+      <c r="Q442" s="91" t="s">
         <v>3508</v>
       </c>
-      <c r="Q442" s="91" t="s">
-        <v>3509</v>
-      </c>
       <c r="R442" s="115" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="S442" s="115" t="s">
         <v>41</v>
       </c>
       <c r="T442" s="21"/>
       <c r="U442" s="28" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="V442" s="28" t="s">
+        <v>3508</v>
+      </c>
+      <c r="W442" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X442" s="113" t="s">
+        <v>3508</v>
+      </c>
+      <c r="Y442" s="30" t="s">
         <v>3509</v>
-      </c>
-      <c r="W442" s="113" t="s">
-        <v>3150</v>
-      </c>
-      <c r="X442" s="113" t="s">
-        <v>3509</v>
-      </c>
-      <c r="Y442" s="30" t="s">
-        <v>3510</v>
       </c>
       <c r="Z442" s="30"/>
       <c r="AA442" s="30"/>
@@ -53353,7 +53353,7 @@
     </row>
     <row r="443" spans="1:43" ht="15.75" customHeight="1">
       <c r="A443" s="296" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="B443" s="33" t="s">
         <v>434</v>
@@ -53364,13 +53364,13 @@
       <c r="D443" s="235"/>
       <c r="E443" s="58"/>
       <c r="F443" s="290" t="s">
+        <v>3510</v>
+      </c>
+      <c r="G443" s="48" t="s">
         <v>3511</v>
       </c>
-      <c r="G443" s="48" t="s">
+      <c r="H443" s="95" t="s">
         <v>3512</v>
-      </c>
-      <c r="H443" s="95" t="s">
-        <v>3513</v>
       </c>
       <c r="I443" s="187" t="s">
         <v>2487</v>
@@ -53382,7 +53382,7 @@
         <v>657</v>
       </c>
       <c r="N443" s="65" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="O443" s="322"/>
       <c r="P443" s="126"/>
@@ -53397,13 +53397,13 @@
       <c r="U443" s="28"/>
       <c r="V443" s="28"/>
       <c r="W443" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X443" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X443" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y443" s="30" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="Z443" s="30"/>
       <c r="AA443" s="30"/>
@@ -53426,7 +53426,7 @@
     </row>
     <row r="444" spans="1:43" ht="15.75" customHeight="1">
       <c r="A444" s="186" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="B444" s="33" t="s">
         <v>434</v>
@@ -53437,11 +53437,11 @@
       <c r="D444" s="235"/>
       <c r="E444" s="58"/>
       <c r="F444" s="16" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="G444" s="32"/>
       <c r="H444" s="206" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="I444" s="187" t="s">
         <v>2546</v>
@@ -53450,20 +53450,20 @@
       <c r="K444" s="82"/>
       <c r="L444" s="82"/>
       <c r="M444" s="137" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="N444" s="38" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="O444" s="38"/>
       <c r="P444" s="74" t="s">
+        <v>3507</v>
+      </c>
+      <c r="Q444" s="26" t="s">
         <v>3508</v>
       </c>
-      <c r="Q444" s="26" t="s">
-        <v>3509</v>
-      </c>
       <c r="R444" s="33" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="S444" s="77" t="s">
         <v>41</v>
@@ -53495,7 +53495,7 @@
     </row>
     <row r="445" spans="1:43" ht="15.75" customHeight="1">
       <c r="A445" s="186" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="B445" s="33" t="s">
         <v>434</v>
@@ -53506,13 +53506,13 @@
       <c r="D445" s="247"/>
       <c r="E445" s="190"/>
       <c r="F445" s="191" t="s">
+        <v>3521</v>
+      </c>
+      <c r="G445" s="186" t="s">
         <v>3522</v>
       </c>
-      <c r="G445" s="186" t="s">
+      <c r="H445" s="48" t="s">
         <v>3523</v>
-      </c>
-      <c r="H445" s="48" t="s">
-        <v>3524</v>
       </c>
       <c r="I445" s="32" t="s">
         <v>2546</v>
@@ -53520,13 +53520,13 @@
       <c r="J445" s="98"/>
       <c r="K445" s="104"/>
       <c r="L445" s="109" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="M445" s="209" t="s">
         <v>480</v>
       </c>
       <c r="N445" s="38" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="O445" s="38"/>
       <c r="P445" s="25"/>
@@ -53539,24 +53539,24 @@
       </c>
       <c r="T445" s="21"/>
       <c r="U445" s="28" t="s">
+        <v>3474</v>
+      </c>
+      <c r="V445" s="28" t="s">
         <v>3475</v>
       </c>
-      <c r="V445" s="28" t="s">
-        <v>3476</v>
-      </c>
       <c r="W445" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X445" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X445" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y445" s="30" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="Z445" s="30"/>
       <c r="AA445" s="30"/>
       <c r="AB445" s="31" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="AC445" s="32"/>
       <c r="AD445" s="21"/>
@@ -53576,7 +53576,7 @@
     </row>
     <row r="446" spans="1:43" ht="15.75" customHeight="1">
       <c r="A446" s="186" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="B446" s="33" t="s">
         <v>434</v>
@@ -53587,13 +53587,13 @@
       <c r="D446" s="247"/>
       <c r="E446" s="190"/>
       <c r="F446" s="191" t="s">
+        <v>3529</v>
+      </c>
+      <c r="G446" s="186" t="s">
         <v>3530</v>
       </c>
-      <c r="G446" s="186" t="s">
+      <c r="H446" s="48" t="s">
         <v>3531</v>
-      </c>
-      <c r="H446" s="48" t="s">
-        <v>3532</v>
       </c>
       <c r="I446" s="32" t="s">
         <v>2546</v>
@@ -53601,13 +53601,13 @@
       <c r="J446" s="35"/>
       <c r="K446" s="109"/>
       <c r="L446" s="109" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="M446" s="209" t="s">
         <v>480</v>
       </c>
       <c r="N446" s="54" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="O446" s="54"/>
       <c r="P446" s="55"/>
@@ -53620,24 +53620,24 @@
       </c>
       <c r="T446" s="21"/>
       <c r="U446" s="28" t="s">
+        <v>3474</v>
+      </c>
+      <c r="V446" s="122" t="s">
         <v>3475</v>
       </c>
-      <c r="V446" s="122" t="s">
-        <v>3476</v>
-      </c>
       <c r="W446" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X446" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X446" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y446" s="30" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="Z446" s="30"/>
       <c r="AA446" s="30"/>
       <c r="AB446" s="41" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="AC446" s="32"/>
       <c r="AD446" s="21"/>
@@ -53657,7 +53657,7 @@
     </row>
     <row r="447" spans="1:43" ht="15.75" customHeight="1">
       <c r="A447" s="296" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="B447" s="33" t="s">
         <v>434</v>
@@ -53668,17 +53668,17 @@
       <c r="D447" s="235"/>
       <c r="E447" s="58"/>
       <c r="F447" s="47" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="G447" s="32"/>
       <c r="H447" s="206" t="s">
+        <v>3537</v>
+      </c>
+      <c r="I447" s="192" t="s">
         <v>3538</v>
       </c>
-      <c r="I447" s="192" t="s">
+      <c r="J447" s="22" t="s">
         <v>3539</v>
-      </c>
-      <c r="J447" s="22" t="s">
-        <v>3540</v>
       </c>
       <c r="K447" s="22"/>
       <c r="L447" s="22"/>
@@ -53701,13 +53701,13 @@
       <c r="U447" s="122"/>
       <c r="V447" s="122"/>
       <c r="W447" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X447" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X447" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y447" s="30" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="Z447" s="30"/>
       <c r="AA447" s="30"/>
@@ -53730,7 +53730,7 @@
     </row>
     <row r="448" spans="1:43" ht="15.75" customHeight="1">
       <c r="A448" s="186" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="B448" s="33" t="s">
         <v>434</v>
@@ -53741,17 +53741,17 @@
       <c r="D448" s="235"/>
       <c r="E448" s="58"/>
       <c r="F448" s="290" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="G448" s="32"/>
       <c r="H448" s="206" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="I448" s="32" t="s">
         <v>2127</v>
       </c>
       <c r="J448" s="82" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="K448" s="82"/>
       <c r="L448" s="82"/>
@@ -53759,7 +53759,7 @@
         <v>137</v>
       </c>
       <c r="N448" s="54" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="O448" s="54"/>
       <c r="P448" s="55"/>
@@ -53797,7 +53797,7 @@
     </row>
     <row r="449" spans="1:43" ht="15.75" customHeight="1">
       <c r="A449" s="186" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="B449" s="33" t="s">
         <v>434</v>
@@ -53808,11 +53808,11 @@
       <c r="D449" s="235"/>
       <c r="E449" s="58"/>
       <c r="F449" s="47" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="G449" s="32"/>
       <c r="H449" s="206" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="I449" s="192" t="s">
         <v>2546</v>
@@ -53820,13 +53820,13 @@
       <c r="J449" s="98"/>
       <c r="K449" s="104"/>
       <c r="L449" s="104" t="s">
+        <v>3548</v>
+      </c>
+      <c r="M449" s="137" t="s">
         <v>3549</v>
       </c>
-      <c r="M449" s="137" t="s">
+      <c r="N449" s="54" t="s">
         <v>3550</v>
-      </c>
-      <c r="N449" s="54" t="s">
-        <v>3551</v>
       </c>
       <c r="O449" s="54"/>
       <c r="P449" s="55"/>
@@ -53841,13 +53841,13 @@
       <c r="U449" s="122"/>
       <c r="V449" s="122"/>
       <c r="W449" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X449" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X449" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y449" s="30" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="Z449" s="30"/>
       <c r="AA449" s="30"/>
@@ -53870,7 +53870,7 @@
     </row>
     <row r="450" spans="1:43" ht="15.75" customHeight="1">
       <c r="A450" s="186" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="B450" s="33" t="s">
         <v>434</v>
@@ -53881,11 +53881,11 @@
       <c r="D450" s="235"/>
       <c r="E450" s="58"/>
       <c r="F450" s="290" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="G450" s="32"/>
       <c r="H450" s="186" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="I450" s="192" t="s">
         <v>2546</v>
@@ -53893,13 +53893,13 @@
       <c r="J450" s="98"/>
       <c r="K450" s="104"/>
       <c r="L450" s="109" t="s">
+        <v>3548</v>
+      </c>
+      <c r="M450" s="137" t="s">
         <v>3549</v>
       </c>
-      <c r="M450" s="137" t="s">
-        <v>3550</v>
-      </c>
       <c r="N450" s="73" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="O450" s="73"/>
       <c r="P450" s="74"/>
@@ -53914,13 +53914,13 @@
       <c r="U450" s="122"/>
       <c r="V450" s="122"/>
       <c r="W450" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X450" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X450" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y450" s="30" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="Z450" s="30"/>
       <c r="AA450" s="30"/>
@@ -53943,7 +53943,7 @@
     </row>
     <row r="451" spans="1:43" ht="15.75" customHeight="1">
       <c r="A451" s="186" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="B451" s="33" t="s">
         <v>434</v>
@@ -53954,13 +53954,13 @@
       <c r="D451" s="235"/>
       <c r="E451" s="58"/>
       <c r="F451" s="290" t="s">
+        <v>3556</v>
+      </c>
+      <c r="G451" s="32" t="s">
         <v>3557</v>
       </c>
-      <c r="G451" s="32" t="s">
+      <c r="H451" s="206" t="s">
         <v>3558</v>
-      </c>
-      <c r="H451" s="206" t="s">
-        <v>3559</v>
       </c>
       <c r="I451" s="192" t="s">
         <v>2546</v>
@@ -53968,13 +53968,13 @@
       <c r="J451" s="35"/>
       <c r="K451" s="109"/>
       <c r="L451" s="109" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="M451" s="77" t="s">
         <v>480</v>
       </c>
       <c r="N451" s="38" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="O451" s="38"/>
       <c r="P451" s="25"/>
@@ -53987,24 +53987,24 @@
       </c>
       <c r="T451" s="21"/>
       <c r="U451" s="28" t="s">
+        <v>3474</v>
+      </c>
+      <c r="V451" s="122" t="s">
         <v>3475</v>
       </c>
-      <c r="V451" s="122" t="s">
-        <v>3476</v>
-      </c>
       <c r="W451" s="113" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="X451" s="120" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="Y451" s="30" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="Z451" s="30"/>
       <c r="AA451" s="30"/>
       <c r="AB451" s="219" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="AC451" s="32"/>
       <c r="AD451" s="21"/>
@@ -54024,7 +54024,7 @@
     </row>
     <row r="452" spans="1:43" ht="15.75" customHeight="1">
       <c r="A452" s="186" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="B452" s="33" t="s">
         <v>434</v>
@@ -54035,11 +54035,11 @@
       <c r="D452" s="235"/>
       <c r="E452" s="58"/>
       <c r="F452" s="47" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="G452" s="32"/>
       <c r="H452" s="206" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="I452" s="192" t="s">
         <v>2546</v>
@@ -54048,10 +54048,10 @@
       <c r="K452" s="82"/>
       <c r="L452" s="82"/>
       <c r="M452" s="95" t="s">
+        <v>3564</v>
+      </c>
+      <c r="N452" s="89" t="s">
         <v>3565</v>
-      </c>
-      <c r="N452" s="89" t="s">
-        <v>3566</v>
       </c>
       <c r="O452" s="89"/>
       <c r="P452" s="90"/>
@@ -54089,7 +54089,7 @@
     </row>
     <row r="453" spans="1:43" ht="15.75" customHeight="1">
       <c r="A453" s="186" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="B453" s="33" t="s">
         <v>434</v>
@@ -54100,16 +54100,16 @@
       <c r="D453" s="235"/>
       <c r="E453" s="58"/>
       <c r="F453" s="290" t="s">
+        <v>3567</v>
+      </c>
+      <c r="G453" s="32" t="s">
         <v>3568</v>
       </c>
-      <c r="G453" s="32" t="s">
+      <c r="H453" s="48" t="s">
         <v>3569</v>
       </c>
-      <c r="H453" s="48" t="s">
+      <c r="I453" s="187" t="s">
         <v>3570</v>
-      </c>
-      <c r="I453" s="187" t="s">
-        <v>3571</v>
       </c>
       <c r="J453" s="22"/>
       <c r="K453" s="22"/>
@@ -54118,14 +54118,14 @@
         <v>804</v>
       </c>
       <c r="N453" s="136" t="s">
+        <v>3571</v>
+      </c>
+      <c r="O453" s="54" t="s">
         <v>3572</v>
-      </c>
-      <c r="O453" s="54" t="s">
-        <v>3573</v>
       </c>
       <c r="P453" s="55"/>
       <c r="Q453" s="56" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="R453" s="99" t="s">
         <v>1105</v>
@@ -54134,7 +54134,7 @@
         <v>41</v>
       </c>
       <c r="T453" s="121" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="U453" s="122"/>
       <c r="V453" s="122"/>
@@ -54162,7 +54162,7 @@
     </row>
     <row r="454" spans="1:43" ht="15.75" customHeight="1">
       <c r="A454" s="186" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="B454" s="33" t="s">
         <v>434</v>
@@ -54173,16 +54173,16 @@
       <c r="D454" s="235"/>
       <c r="E454" s="58"/>
       <c r="F454" s="290" t="s">
+        <v>3576</v>
+      </c>
+      <c r="G454" s="32" t="s">
         <v>3577</v>
       </c>
-      <c r="G454" s="32" t="s">
+      <c r="H454" s="95" t="s">
         <v>3578</v>
       </c>
-      <c r="H454" s="95" t="s">
-        <v>3579</v>
-      </c>
       <c r="I454" s="187" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="J454" s="22"/>
       <c r="K454" s="82"/>
@@ -54191,7 +54191,7 @@
         <v>804</v>
       </c>
       <c r="N454" s="136" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="O454" s="54"/>
       <c r="P454" s="55"/>
@@ -54206,13 +54206,13 @@
       <c r="U454" s="221"/>
       <c r="V454" s="221"/>
       <c r="W454" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X454" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X454" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y454" s="30" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="Z454" s="30"/>
       <c r="AA454" s="30"/>
@@ -54235,7 +54235,7 @@
     </row>
     <row r="455" spans="1:43" ht="15.75" customHeight="1">
       <c r="A455" s="186" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="B455" s="95" t="s">
         <v>434</v>
@@ -54246,14 +54246,14 @@
       <c r="D455" s="235"/>
       <c r="E455" s="58"/>
       <c r="F455" s="290" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="G455" s="32"/>
       <c r="H455" s="192" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="I455" s="32" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="J455" s="22"/>
       <c r="K455" s="82"/>
@@ -54262,7 +54262,7 @@
         <v>184</v>
       </c>
       <c r="N455" s="38" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="O455" s="38"/>
       <c r="P455" s="25"/>
@@ -54277,18 +54277,18 @@
       <c r="U455" s="122"/>
       <c r="V455" s="122"/>
       <c r="W455" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X455" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X455" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y455" s="30" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="Z455" s="30"/>
       <c r="AA455" s="30"/>
       <c r="AB455" s="46" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="AC455" s="32"/>
       <c r="AD455" s="21"/>
@@ -54308,7 +54308,7 @@
     </row>
     <row r="456" spans="1:43" ht="15.75" customHeight="1">
       <c r="A456" s="186" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="B456" s="95" t="s">
         <v>2283</v>
@@ -54319,34 +54319,34 @@
       <c r="D456" s="235"/>
       <c r="E456" s="58"/>
       <c r="F456" s="290" t="s">
+        <v>3586</v>
+      </c>
+      <c r="G456" s="32" t="s">
         <v>3587</v>
       </c>
-      <c r="G456" s="32" t="s">
+      <c r="H456" s="33" t="s">
         <v>3588</v>
       </c>
-      <c r="H456" s="33" t="s">
+      <c r="I456" s="187" t="s">
+        <v>3040</v>
+      </c>
+      <c r="J456" s="22" t="s">
         <v>3589</v>
-      </c>
-      <c r="I456" s="187" t="s">
-        <v>3041</v>
-      </c>
-      <c r="J456" s="22" t="s">
-        <v>3590</v>
       </c>
       <c r="K456" s="22"/>
       <c r="L456" s="22"/>
       <c r="M456" s="115" t="s">
+        <v>3590</v>
+      </c>
+      <c r="N456" s="65" t="s">
         <v>3591</v>
       </c>
-      <c r="N456" s="65" t="s">
-        <v>3592</v>
-      </c>
       <c r="O456" s="38" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="P456" s="25"/>
       <c r="Q456" s="56" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="R456" s="94" t="s">
         <v>1105</v>
@@ -54358,13 +54358,13 @@
       <c r="U456" s="28"/>
       <c r="V456" s="28"/>
       <c r="W456" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X456" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X456" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y456" s="30" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="Z456" s="30"/>
       <c r="AA456" s="30"/>
@@ -54387,7 +54387,7 @@
     </row>
     <row r="457" spans="1:43" ht="15.75" customHeight="1">
       <c r="A457" s="296" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="B457" s="32" t="s">
         <v>434</v>
@@ -54398,11 +54398,11 @@
       <c r="D457" s="235"/>
       <c r="E457" s="58"/>
       <c r="F457" s="290" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="G457" s="32"/>
       <c r="H457" s="192" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="I457" s="192" t="s">
         <v>2506</v>
@@ -54416,14 +54416,14 @@
         <v>804</v>
       </c>
       <c r="N457" s="38" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="O457" s="38" t="s">
         <v>901</v>
       </c>
       <c r="P457" s="25"/>
       <c r="Q457" s="56" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="R457" s="39" t="s">
         <v>523</v>
@@ -54435,19 +54435,19 @@
       <c r="U457" s="28"/>
       <c r="V457" s="28"/>
       <c r="W457" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X457" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X457" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y457" s="30" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="Z457" s="30" t="s">
+        <v>3596</v>
+      </c>
+      <c r="AA457" s="30" t="s">
         <v>3597</v>
-      </c>
-      <c r="AA457" s="30" t="s">
-        <v>3598</v>
       </c>
       <c r="AB457" s="41"/>
       <c r="AC457" s="32"/>
@@ -54468,7 +54468,7 @@
     </row>
     <row r="458" spans="1:43" ht="15.75" customHeight="1">
       <c r="A458" s="296" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="B458" s="95" t="s">
         <v>2283</v>
@@ -54479,11 +54479,11 @@
       <c r="D458" s="235"/>
       <c r="E458" s="58"/>
       <c r="F458" s="16" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="G458" s="32"/>
       <c r="H458" s="32" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="I458" s="32" t="s">
         <v>2506</v>
@@ -54497,14 +54497,14 @@
         <v>657</v>
       </c>
       <c r="N458" s="65" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="O458" s="65" t="s">
         <v>901</v>
       </c>
       <c r="P458" s="25"/>
       <c r="Q458" s="56" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="R458" s="39" t="s">
         <v>523</v>
@@ -54516,19 +54516,19 @@
       <c r="U458" s="28"/>
       <c r="V458" s="28"/>
       <c r="W458" s="113" t="s">
+        <v>3251</v>
+      </c>
+      <c r="X458" s="120" t="s">
+        <v>3150</v>
+      </c>
+      <c r="Y458" s="30" t="s">
         <v>3252</v>
       </c>
-      <c r="X458" s="120" t="s">
-        <v>3151</v>
-      </c>
-      <c r="Y458" s="30" t="s">
-        <v>3253</v>
-      </c>
       <c r="Z458" s="30" t="s">
+        <v>3601</v>
+      </c>
+      <c r="AA458" s="30" t="s">
         <v>3602</v>
-      </c>
-      <c r="AA458" s="30" t="s">
-        <v>3603</v>
       </c>
       <c r="AB458" s="41"/>
       <c r="AC458" s="32"/>
@@ -54549,7 +54549,7 @@
     </row>
     <row r="459" spans="1:43" ht="15.75" customHeight="1">
       <c r="A459" s="296" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="B459" s="95" t="s">
         <v>2283</v>
@@ -54560,16 +54560,16 @@
       <c r="D459" s="236"/>
       <c r="E459" s="67"/>
       <c r="F459" s="16" t="s">
+        <v>3603</v>
+      </c>
+      <c r="G459" s="32" t="s">
         <v>3604</v>
       </c>
-      <c r="G459" s="32" t="s">
+      <c r="H459" s="32" t="s">
         <v>3605</v>
       </c>
-      <c r="H459" s="32" t="s">
+      <c r="I459" s="187" t="s">
         <v>3606</v>
-      </c>
-      <c r="I459" s="187" t="s">
-        <v>3607</v>
       </c>
       <c r="J459" s="22"/>
       <c r="K459" s="22"/>
@@ -54578,14 +54578,14 @@
         <v>2480</v>
       </c>
       <c r="N459" s="89" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="O459" s="89"/>
       <c r="P459" s="74" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="Q459" s="56" t="s">
-        <v>3691</v>
+        <v>3690</v>
       </c>
       <c r="R459" s="96" t="s">
         <v>387</v>
@@ -54622,7 +54622,7 @@
     </row>
     <row r="460" spans="1:43" ht="15.75" customHeight="1">
       <c r="A460" s="186" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="B460" s="95" t="s">
         <v>2283</v>
@@ -54633,34 +54633,34 @@
       <c r="D460" s="235"/>
       <c r="E460" s="58"/>
       <c r="F460" s="290" t="s">
+        <v>3609</v>
+      </c>
+      <c r="G460" s="32" t="s">
         <v>3610</v>
       </c>
-      <c r="G460" s="32" t="s">
+      <c r="H460" s="206" t="s">
         <v>3611</v>
       </c>
-      <c r="H460" s="206" t="s">
+      <c r="I460" s="32" t="s">
         <v>3612</v>
-      </c>
-      <c r="I460" s="32" t="s">
-        <v>3613</v>
       </c>
       <c r="J460" s="22"/>
       <c r="K460" s="93" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="L460" s="82"/>
       <c r="M460" s="137" t="s">
         <v>657</v>
       </c>
       <c r="N460" s="136" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="O460" s="38" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="P460" s="55"/>
       <c r="Q460" s="56" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="R460" s="94" t="s">
         <v>1105</v>
@@ -54672,13 +54672,13 @@
       <c r="U460" s="28"/>
       <c r="V460" s="106"/>
       <c r="W460" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X460" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X460" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y460" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="Z460" s="30"/>
       <c r="AA460" s="30"/>
@@ -54701,43 +54701,43 @@
     </row>
     <row r="461" spans="1:43" ht="15.75" customHeight="1">
       <c r="A461" s="287" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="B461" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C461" s="249" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="D461" s="235"/>
       <c r="E461" s="58"/>
       <c r="F461" s="47" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="G461" s="32"/>
       <c r="H461" s="48" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="I461" s="187" t="s">
         <v>2506</v>
       </c>
       <c r="J461" s="109" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="K461" s="104"/>
       <c r="L461" s="104"/>
       <c r="M461" s="137" t="s">
+        <v>3620</v>
+      </c>
+      <c r="N461" s="136" t="s">
         <v>3621</v>
       </c>
-      <c r="N461" s="136" t="s">
+      <c r="O461" s="458" t="s">
         <v>3622</v>
-      </c>
-      <c r="O461" s="458" t="s">
-        <v>3623</v>
       </c>
       <c r="P461" s="114"/>
       <c r="Q461" s="56" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="R461" s="39" t="s">
         <v>523</v>
@@ -54747,13 +54747,13 @@
       <c r="U461" s="28"/>
       <c r="V461" s="28"/>
       <c r="W461" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X461" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X461" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y461" s="30" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="Z461" s="30"/>
       <c r="AA461" s="30"/>
@@ -54776,7 +54776,7 @@
     </row>
     <row r="462" spans="1:43" ht="15.75" customHeight="1">
       <c r="A462" s="186" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="B462" s="95" t="s">
         <v>2283</v>
@@ -54787,11 +54787,11 @@
       <c r="D462" s="235"/>
       <c r="E462" s="58"/>
       <c r="F462" s="47" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="G462" s="32"/>
       <c r="H462" s="186" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="I462" s="32" t="s">
         <v>2047</v>
@@ -54805,14 +54805,14 @@
         <v>683</v>
       </c>
       <c r="N462" s="89" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="O462" s="89"/>
       <c r="P462" s="74" t="s">
         <v>1608</v>
       </c>
       <c r="Q462" s="91" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="R462" s="333" t="s">
         <v>40</v>
@@ -54828,13 +54828,13 @@
         <v>189</v>
       </c>
       <c r="W462" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X462" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X462" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y462" s="30" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="Z462" s="30"/>
       <c r="AA462" s="30"/>
@@ -54857,7 +54857,7 @@
     </row>
     <row r="463" spans="1:43" ht="15.75" customHeight="1">
       <c r="A463" s="186" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="B463" s="95" t="s">
         <v>2283</v>
@@ -54868,13 +54868,13 @@
       <c r="D463" s="236"/>
       <c r="E463" s="67"/>
       <c r="F463" s="16" t="s">
+        <v>3631</v>
+      </c>
+      <c r="G463" s="32" t="s">
         <v>3632</v>
       </c>
-      <c r="G463" s="32" t="s">
+      <c r="H463" s="32" t="s">
         <v>3633</v>
-      </c>
-      <c r="H463" s="32" t="s">
-        <v>3634</v>
       </c>
       <c r="I463" s="187" t="s">
         <v>2638</v>
@@ -54885,10 +54885,10 @@
       <c r="K463" s="22"/>
       <c r="L463" s="22"/>
       <c r="M463" s="115" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="N463" s="65" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="O463" s="83"/>
       <c r="P463" s="25"/>
@@ -54903,13 +54903,13 @@
       <c r="U463" s="122"/>
       <c r="V463" s="122"/>
       <c r="W463" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X463" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X463" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y463" s="30" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="Z463" s="30"/>
       <c r="AA463" s="30"/>
@@ -54932,10 +54932,10 @@
     </row>
     <row r="464" spans="1:43" s="316" customFormat="1" ht="15.75" customHeight="1">
       <c r="A464" s="297" t="s">
+        <v>3635</v>
+      </c>
+      <c r="B464" s="298" t="s">
         <v>3636</v>
-      </c>
-      <c r="B464" s="298" t="s">
-        <v>3637</v>
       </c>
       <c r="C464" s="299" t="s">
         <v>171</v>
@@ -54943,16 +54943,16 @@
       <c r="D464" s="300"/>
       <c r="E464" s="301"/>
       <c r="F464" s="302" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="G464" s="302" t="s">
         <v>2285</v>
       </c>
       <c r="H464" s="302" t="s">
+        <v>3638</v>
+      </c>
+      <c r="I464" s="303" t="s">
         <v>3639</v>
-      </c>
-      <c r="I464" s="303" t="s">
-        <v>3640</v>
       </c>
       <c r="J464" s="444" t="s">
         <v>2273</v>
@@ -54963,13 +54963,13 @@
         <v>1601</v>
       </c>
       <c r="N464" s="305" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="O464" s="305"/>
       <c r="P464" s="306"/>
       <c r="Q464" s="307"/>
       <c r="R464" s="474" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="S464" s="308" t="s">
         <v>41</v>
@@ -55001,43 +55001,43 @@
     </row>
     <row r="465" spans="1:43" ht="15.75" customHeight="1">
       <c r="A465" s="287" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
       <c r="B465" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C465" s="249" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="D465" s="235"/>
       <c r="E465" s="58"/>
       <c r="F465" s="47" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="G465" s="32"/>
       <c r="H465" s="48" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="I465" s="187" t="s">
         <v>2506</v>
       </c>
       <c r="J465" s="109" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="K465" s="109"/>
       <c r="L465" s="109"/>
       <c r="M465" s="137" t="s">
+        <v>3646</v>
+      </c>
+      <c r="N465" s="54" t="s">
         <v>3647</v>
       </c>
-      <c r="N465" s="54" t="s">
+      <c r="O465" s="54" t="s">
         <v>3648</v>
-      </c>
-      <c r="O465" s="54" t="s">
-        <v>3649</v>
       </c>
       <c r="P465" s="55"/>
       <c r="Q465" s="56" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="R465" s="39" t="s">
         <v>523</v>
@@ -55051,13 +55051,13 @@
       <c r="W465" s="113"/>
       <c r="X465" s="113"/>
       <c r="Y465" s="30" t="s">
+        <v>3650</v>
+      </c>
+      <c r="Z465" s="30" t="s">
         <v>3651</v>
       </c>
-      <c r="Z465" s="30" t="s">
+      <c r="AA465" s="30" t="s">
         <v>3652</v>
-      </c>
-      <c r="AA465" s="30" t="s">
-        <v>3653</v>
       </c>
       <c r="AB465" s="41"/>
       <c r="AC465" s="32"/>
@@ -55078,7 +55078,7 @@
     </row>
     <row r="466" spans="1:43" ht="15.75" customHeight="1">
       <c r="A466" s="296" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="B466" s="95" t="s">
         <v>434</v>
@@ -55089,13 +55089,13 @@
       <c r="D466" s="235"/>
       <c r="E466" s="58"/>
       <c r="F466" s="47" t="s">
+        <v>3653</v>
+      </c>
+      <c r="G466" s="32" t="s">
         <v>3654</v>
       </c>
-      <c r="G466" s="32" t="s">
+      <c r="H466" s="95" t="s">
         <v>3655</v>
-      </c>
-      <c r="H466" s="95" t="s">
-        <v>3656</v>
       </c>
       <c r="I466" s="187" t="s">
         <v>2638</v>
@@ -55103,20 +55103,20 @@
       <c r="J466" s="93"/>
       <c r="K466" s="22"/>
       <c r="L466" s="22" t="s">
+        <v>3656</v>
+      </c>
+      <c r="M466" s="137" t="s">
         <v>3657</v>
       </c>
-      <c r="M466" s="137" t="s">
+      <c r="N466" s="136" t="s">
         <v>3658</v>
       </c>
-      <c r="N466" s="136" t="s">
-        <v>3659</v>
-      </c>
       <c r="O466" s="38" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="P466" s="55"/>
       <c r="Q466" s="56" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="R466" s="94" t="s">
         <v>1105</v>
@@ -55126,13 +55126,13 @@
       <c r="U466" s="28"/>
       <c r="V466" s="28"/>
       <c r="W466" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X466" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X466" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y466" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z466" s="30"/>
       <c r="AA466" s="30"/>
@@ -55155,50 +55155,50 @@
     </row>
     <row r="467" spans="1:43" ht="15.75" customHeight="1">
       <c r="A467" s="288" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="B467" s="95" t="s">
         <v>434</v>
       </c>
       <c r="C467" s="256" t="s">
+        <v>3659</v>
+      </c>
+      <c r="D467" s="234" t="s">
         <v>3660</v>
       </c>
-      <c r="D467" s="234" t="s">
+      <c r="E467" s="58" t="s">
         <v>3661</v>
       </c>
-      <c r="E467" s="58" t="s">
+      <c r="F467" s="223" t="s">
         <v>3662</v>
       </c>
-      <c r="F467" s="223" t="s">
+      <c r="G467" s="16" t="s">
+        <v>3659</v>
+      </c>
+      <c r="H467" s="207" t="s">
         <v>3663</v>
       </c>
-      <c r="G467" s="16" t="s">
-        <v>3660</v>
-      </c>
-      <c r="H467" s="207" t="s">
+      <c r="I467" s="187" t="s">
         <v>3664</v>
-      </c>
-      <c r="I467" s="187" t="s">
-        <v>3665</v>
       </c>
       <c r="J467" s="22"/>
       <c r="K467" s="22"/>
       <c r="L467" s="22"/>
       <c r="M467" s="137" t="s">
+        <v>3665</v>
+      </c>
+      <c r="N467" s="38" t="s">
         <v>3666</v>
-      </c>
-      <c r="N467" s="38" t="s">
-        <v>3667</v>
       </c>
       <c r="O467" s="38"/>
       <c r="P467" s="25" t="s">
+        <v>3667</v>
+      </c>
+      <c r="Q467" s="56" t="s">
         <v>3668</v>
       </c>
-      <c r="Q467" s="56" t="s">
-        <v>3669</v>
-      </c>
       <c r="R467" s="94" t="s">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="S467" s="77" t="s">
         <v>41</v>
@@ -55230,7 +55230,7 @@
     </row>
     <row r="468" spans="1:43" ht="15.75" customHeight="1">
       <c r="A468" s="186" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="B468" s="95" t="s">
         <v>2283</v>
@@ -55241,13 +55241,13 @@
       <c r="D468" s="236"/>
       <c r="E468" s="67"/>
       <c r="F468" s="290" t="s">
+        <v>3670</v>
+      </c>
+      <c r="G468" s="32" t="s">
         <v>3671</v>
       </c>
-      <c r="G468" s="32" t="s">
+      <c r="H468" s="95" t="s">
         <v>3672</v>
-      </c>
-      <c r="H468" s="95" t="s">
-        <v>3673</v>
       </c>
       <c r="I468" s="187" t="s">
         <v>2638</v>
@@ -55259,7 +55259,7 @@
         <v>1986</v>
       </c>
       <c r="N468" s="65" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="O468" s="38"/>
       <c r="P468" s="25"/>
@@ -55274,18 +55274,18 @@
       <c r="U468" s="28"/>
       <c r="V468" s="28"/>
       <c r="W468" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X468" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X468" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y468" s="30" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="Z468" s="30"/>
       <c r="AA468" s="30"/>
       <c r="AB468" s="46" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="AC468" s="32"/>
       <c r="AD468" s="32"/>
@@ -55305,28 +55305,28 @@
     </row>
     <row r="469" spans="1:43" ht="15.75" customHeight="1">
       <c r="A469" s="187" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
       <c r="B469" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C469" s="250" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="D469" s="235"/>
       <c r="E469" s="58"/>
       <c r="F469" s="290" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="G469" s="32"/>
       <c r="H469" s="48" t="s">
+        <v>3677</v>
+      </c>
+      <c r="I469" s="187" t="s">
         <v>3678</v>
       </c>
-      <c r="I469" s="187" t="s">
+      <c r="J469" s="109" t="s">
         <v>3679</v>
-      </c>
-      <c r="J469" s="109" t="s">
-        <v>3680</v>
       </c>
       <c r="K469" s="109"/>
       <c r="L469" s="109"/>
@@ -55334,13 +55334,13 @@
         <v>137</v>
       </c>
       <c r="N469" s="38" t="s">
-        <v>3681</v>
+        <v>3680</v>
       </c>
       <c r="O469" s="322"/>
       <c r="P469" s="126"/>
       <c r="Q469" s="56"/>
       <c r="R469" s="36" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="S469" s="77" t="s">
         <v>41</v>
@@ -55349,19 +55349,19 @@
       <c r="U469" s="28"/>
       <c r="V469" s="28"/>
       <c r="W469" s="112" t="s">
+        <v>3682</v>
+      </c>
+      <c r="X469" s="29" t="s">
         <v>3683</v>
       </c>
-      <c r="X469" s="29" t="s">
+      <c r="Y469" s="30" t="s">
         <v>3684</v>
-      </c>
-      <c r="Y469" s="30" t="s">
-        <v>3685</v>
       </c>
       <c r="Z469" s="30"/>
       <c r="AA469" s="30"/>
       <c r="AB469" s="31"/>
       <c r="AC469" s="69" t="s">
-        <v>3686</v>
+        <v>3685</v>
       </c>
       <c r="AD469" s="21"/>
       <c r="AE469" s="32"/>
@@ -55380,7 +55380,7 @@
     </row>
     <row r="470" spans="1:43" ht="15.75" customHeight="1">
       <c r="A470" s="296" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="B470" s="95" t="s">
         <v>434</v>
@@ -55391,16 +55391,16 @@
       <c r="D470" s="236"/>
       <c r="E470" s="67"/>
       <c r="F470" s="290" t="s">
+        <v>3686</v>
+      </c>
+      <c r="G470" s="438" t="s">
         <v>3687</v>
       </c>
-      <c r="G470" s="438" t="s">
+      <c r="H470" s="48" t="s">
         <v>3688</v>
       </c>
-      <c r="H470" s="48" t="s">
+      <c r="I470" s="187" t="s">
         <v>3689</v>
-      </c>
-      <c r="I470" s="187" t="s">
-        <v>3690</v>
       </c>
       <c r="J470" s="22"/>
       <c r="K470" s="22"/>
@@ -55409,17 +55409,17 @@
         <v>2480</v>
       </c>
       <c r="N470" s="54" t="s">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="O470" s="54"/>
       <c r="P470" s="74" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="Q470" s="56" t="s">
-        <v>3691</v>
+        <v>3690</v>
       </c>
       <c r="R470" s="48" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="S470" s="77" t="s">
         <v>41</v>
@@ -55451,7 +55451,7 @@
     </row>
     <row r="471" spans="1:43" ht="15.75" customHeight="1">
       <c r="A471" s="186" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="B471" s="95" t="s">
         <v>434</v>
@@ -55462,13 +55462,13 @@
       <c r="D471" s="235"/>
       <c r="E471" s="58"/>
       <c r="F471" s="47" t="s">
+        <v>3692</v>
+      </c>
+      <c r="G471" s="39" t="s">
         <v>3693</v>
       </c>
-      <c r="G471" s="39" t="s">
+      <c r="H471" s="95" t="s">
         <v>3694</v>
-      </c>
-      <c r="H471" s="95" t="s">
-        <v>3695</v>
       </c>
       <c r="I471" s="187" t="s">
         <v>2638</v>
@@ -55476,13 +55476,13 @@
       <c r="J471" s="82"/>
       <c r="K471" s="82"/>
       <c r="L471" s="82" t="s">
-        <v>3696</v>
+        <v>3695</v>
       </c>
       <c r="M471" s="137" t="s">
         <v>804</v>
       </c>
       <c r="N471" s="65" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
       <c r="O471" s="38"/>
       <c r="P471" s="25"/>
@@ -55497,13 +55497,13 @@
       <c r="U471" s="28"/>
       <c r="V471" s="28"/>
       <c r="W471" s="29" t="s">
+        <v>3697</v>
+      </c>
+      <c r="X471" s="29" t="s">
         <v>3698</v>
       </c>
-      <c r="X471" s="29" t="s">
+      <c r="Y471" s="30" t="s">
         <v>3699</v>
-      </c>
-      <c r="Y471" s="30" t="s">
-        <v>3700</v>
       </c>
       <c r="Z471" s="30"/>
       <c r="AA471" s="30"/>
@@ -55526,36 +55526,36 @@
     </row>
     <row r="472" spans="1:43" ht="15.75" customHeight="1">
       <c r="A472" s="186" t="s">
-        <v>3701</v>
+        <v>3700</v>
       </c>
       <c r="B472" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C472" s="295" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="D472" s="235"/>
       <c r="E472" s="58"/>
       <c r="F472" s="290" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="G472" s="39"/>
       <c r="H472" s="48" t="s">
+        <v>3701</v>
+      </c>
+      <c r="I472" s="115" t="s">
         <v>3702</v>
-      </c>
-      <c r="I472" s="115" t="s">
-        <v>3703</v>
       </c>
       <c r="J472" s="82"/>
       <c r="K472" s="82"/>
       <c r="L472" s="82" t="s">
+        <v>3703</v>
+      </c>
+      <c r="M472" s="32" t="s">
         <v>3704</v>
       </c>
-      <c r="M472" s="32" t="s">
+      <c r="N472" s="38" t="s">
         <v>3705</v>
-      </c>
-      <c r="N472" s="38" t="s">
-        <v>3706</v>
       </c>
       <c r="O472" s="38"/>
       <c r="P472" s="25"/>
@@ -55593,7 +55593,7 @@
     </row>
     <row r="473" spans="1:43" ht="15.75" customHeight="1">
       <c r="A473" s="416" t="s">
-        <v>3707</v>
+        <v>3706</v>
       </c>
       <c r="B473" s="95" t="s">
         <v>2283</v>
@@ -55604,13 +55604,13 @@
       <c r="D473" s="236"/>
       <c r="E473" s="67"/>
       <c r="F473" s="328" t="s">
+        <v>3707</v>
+      </c>
+      <c r="G473" s="39" t="s">
         <v>3708</v>
       </c>
-      <c r="G473" s="39" t="s">
+      <c r="H473" s="438" t="s">
         <v>3709</v>
-      </c>
-      <c r="H473" s="438" t="s">
-        <v>3710</v>
       </c>
       <c r="I473" s="441" t="s">
         <v>2638</v>
@@ -55621,10 +55621,10 @@
       <c r="K473" s="82"/>
       <c r="L473" s="82"/>
       <c r="M473" s="331" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="N473" s="456" t="s">
-        <v>3711</v>
+        <v>3710</v>
       </c>
       <c r="O473" s="322"/>
       <c r="P473" s="126"/>
@@ -55662,7 +55662,7 @@
     </row>
     <row r="474" spans="1:43" ht="15.75" customHeight="1">
       <c r="A474" s="186" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="B474" s="95" t="s">
         <v>2283</v>
@@ -55673,11 +55673,11 @@
       <c r="D474" s="235"/>
       <c r="E474" s="58"/>
       <c r="F474" s="290" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="G474" s="39"/>
       <c r="H474" s="206" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="I474" s="192" t="s">
         <v>2506</v>
@@ -55691,7 +55691,7 @@
         <v>804</v>
       </c>
       <c r="N474" s="38" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="O474" s="38" t="s">
         <v>806</v>
@@ -55713,10 +55713,10 @@
       <c r="X474" s="29"/>
       <c r="Y474" s="30"/>
       <c r="Z474" s="30" t="s">
+        <v>3714</v>
+      </c>
+      <c r="AA474" s="30" t="s">
         <v>3715</v>
-      </c>
-      <c r="AA474" s="30" t="s">
-        <v>3716</v>
       </c>
       <c r="AB474" s="41"/>
       <c r="AC474" s="32"/>
@@ -55737,7 +55737,7 @@
     </row>
     <row r="475" spans="1:43" ht="15.75" customHeight="1">
       <c r="A475" s="282" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="B475" s="95" t="s">
         <v>2283</v>
@@ -55748,14 +55748,14 @@
       <c r="D475" s="235"/>
       <c r="E475" s="58"/>
       <c r="F475" s="290" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="G475" s="32"/>
       <c r="H475" s="48" t="s">
+        <v>3717</v>
+      </c>
+      <c r="I475" s="187" t="s">
         <v>3718</v>
-      </c>
-      <c r="I475" s="187" t="s">
-        <v>3719</v>
       </c>
       <c r="J475" s="22"/>
       <c r="K475" s="22"/>
@@ -55764,14 +55764,14 @@
         <v>1619</v>
       </c>
       <c r="N475" s="38" t="s">
+        <v>3719</v>
+      </c>
+      <c r="O475" s="38" t="s">
         <v>3720</v>
-      </c>
-      <c r="O475" s="38" t="s">
-        <v>3721</v>
       </c>
       <c r="P475" s="25"/>
       <c r="Q475" s="26" t="s">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="R475" s="32" t="s">
         <v>523</v>
@@ -55783,19 +55783,19 @@
       <c r="U475" s="106"/>
       <c r="V475" s="28"/>
       <c r="W475" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X475" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X475" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y475" s="30" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="Z475" s="30" t="s">
+        <v>3722</v>
+      </c>
+      <c r="AA475" s="30" t="s">
         <v>3723</v>
-      </c>
-      <c r="AA475" s="30" t="s">
-        <v>3724</v>
       </c>
       <c r="AB475" s="41"/>
       <c r="AC475" s="32"/>
@@ -55816,40 +55816,40 @@
     </row>
     <row r="476" spans="1:43" ht="15.75" customHeight="1">
       <c r="A476" s="281" t="s">
-        <v>3725</v>
+        <v>3724</v>
       </c>
       <c r="B476" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C476" s="256" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
       <c r="D476" s="235"/>
       <c r="E476" s="58"/>
       <c r="F476" s="16" t="s">
+        <v>3726</v>
+      </c>
+      <c r="G476" s="32" t="s">
         <v>3727</v>
       </c>
-      <c r="G476" s="32" t="s">
+      <c r="H476" s="95" t="s">
         <v>3728</v>
       </c>
-      <c r="H476" s="95" t="s">
+      <c r="I476" s="187" t="s">
         <v>3729</v>
       </c>
-      <c r="I476" s="187" t="s">
-        <v>3730</v>
-      </c>
       <c r="J476" s="22" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="K476" s="93" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="L476" s="22"/>
       <c r="M476" s="331" t="s">
+        <v>3730</v>
+      </c>
+      <c r="N476" s="65" t="s">
         <v>3731</v>
-      </c>
-      <c r="N476" s="65" t="s">
-        <v>3732</v>
       </c>
       <c r="O476" s="38"/>
       <c r="P476" s="25"/>
@@ -55861,23 +55861,23 @@
         <v>41</v>
       </c>
       <c r="T476" s="21" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="U476" s="28"/>
       <c r="V476" s="28"/>
       <c r="W476" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X476" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X476" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y476" s="30" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
       <c r="Z476" s="30"/>
       <c r="AA476" s="30"/>
       <c r="AB476" s="31" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
       <c r="AC476" s="32"/>
       <c r="AD476" s="32"/>
@@ -55897,7 +55897,7 @@
     </row>
     <row r="477" spans="1:43" ht="15.75" customHeight="1">
       <c r="A477" s="186" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
       <c r="B477" s="95" t="s">
         <v>2283</v>
@@ -55908,27 +55908,27 @@
       <c r="D477" s="236"/>
       <c r="E477" s="58"/>
       <c r="F477" s="47" t="s">
+        <v>3736</v>
+      </c>
+      <c r="G477" s="32" t="s">
         <v>3737</v>
       </c>
-      <c r="G477" s="32" t="s">
+      <c r="H477" s="95" t="s">
         <v>3738</v>
-      </c>
-      <c r="H477" s="95" t="s">
-        <v>3739</v>
       </c>
       <c r="I477" s="187" t="s">
         <v>2638</v>
       </c>
       <c r="J477" s="22" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="K477" s="22"/>
       <c r="L477" s="22"/>
       <c r="M477" s="137" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="N477" s="136" t="s">
-        <v>3740</v>
+        <v>3739</v>
       </c>
       <c r="O477" s="54"/>
       <c r="P477" s="55"/>
@@ -55940,23 +55940,23 @@
         <v>41</v>
       </c>
       <c r="T477" s="21" t="s">
-        <v>3741</v>
+        <v>3740</v>
       </c>
       <c r="U477" s="28"/>
       <c r="V477" s="28"/>
       <c r="W477" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X477" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X477" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y477" s="30" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
       <c r="Z477" s="30"/>
       <c r="AA477" s="30"/>
       <c r="AB477" s="46" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="AC477" s="32"/>
       <c r="AD477" s="32"/>
@@ -55976,7 +55976,7 @@
     </row>
     <row r="478" spans="1:43" ht="15.75" customHeight="1">
       <c r="A478" s="186" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
       <c r="B478" s="95" t="s">
         <v>2283</v>
@@ -55987,27 +55987,27 @@
       <c r="D478" s="236"/>
       <c r="E478" s="58"/>
       <c r="F478" s="328" t="s">
+        <v>3744</v>
+      </c>
+      <c r="G478" s="32" t="s">
         <v>3745</v>
       </c>
-      <c r="G478" s="32" t="s">
+      <c r="H478" s="95" t="s">
         <v>3746</v>
       </c>
-      <c r="H478" s="95" t="s">
+      <c r="I478" s="187" t="s">
         <v>3747</v>
-      </c>
-      <c r="I478" s="187" t="s">
-        <v>3748</v>
       </c>
       <c r="J478" s="22"/>
       <c r="K478" s="93" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="L478" s="22"/>
       <c r="M478" s="212" t="s">
         <v>2729</v>
       </c>
       <c r="N478" s="136" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="O478" s="54"/>
       <c r="P478" s="55"/>
@@ -56019,18 +56019,18 @@
         <v>41</v>
       </c>
       <c r="T478" s="21" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="U478" s="28"/>
       <c r="V478" s="28"/>
       <c r="W478" s="113" t="s">
+        <v>3149</v>
+      </c>
+      <c r="X478" s="120" t="s">
         <v>3150</v>
       </c>
-      <c r="X478" s="120" t="s">
-        <v>3151</v>
-      </c>
       <c r="Y478" s="30" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
       <c r="Z478" s="30"/>
       <c r="AA478" s="30"/>
@@ -56053,33 +56053,33 @@
     </row>
     <row r="479" spans="1:43" ht="15.75" customHeight="1">
       <c r="A479" s="281" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="B479" s="95" t="s">
         <v>2283</v>
       </c>
       <c r="C479" s="249" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="D479" s="235"/>
       <c r="E479" s="138"/>
       <c r="F479" s="47" t="s">
-        <v>3754</v>
+        <v>3753</v>
       </c>
       <c r="G479" s="32"/>
       <c r="H479" s="48" t="s">
+        <v>3754</v>
+      </c>
+      <c r="I479" s="115" t="s">
         <v>3755</v>
       </c>
-      <c r="I479" s="115" t="s">
+      <c r="J479" s="22" t="s">
         <v>3756</v>
-      </c>
-      <c r="J479" s="22" t="s">
-        <v>3757</v>
       </c>
       <c r="K479" s="22"/>
       <c r="L479" s="22"/>
       <c r="M479" s="137" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="N479" s="54" t="s">
         <v>2130</v>
@@ -56094,7 +56094,7 @@
         <v>41</v>
       </c>
       <c r="T479" s="21" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="U479" s="28"/>
       <c r="V479" s="28"/>
@@ -56122,7 +56122,7 @@
     </row>
     <row r="480" spans="1:43" ht="54" customHeight="1">
       <c r="A480" s="48" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="B480" s="95" t="s">
         <v>2283</v>
@@ -56133,27 +56133,27 @@
       <c r="D480" s="236"/>
       <c r="E480" s="58"/>
       <c r="F480" s="47" t="s">
+        <v>3760</v>
+      </c>
+      <c r="G480" s="32" t="s">
         <v>3761</v>
       </c>
-      <c r="G480" s="32" t="s">
+      <c r="H480" s="48" t="s">
         <v>3762</v>
-      </c>
-      <c r="H480" s="48" t="s">
-        <v>3763</v>
       </c>
       <c r="I480" s="32" t="s">
         <v>2638</v>
       </c>
       <c r="J480" s="22"/>
       <c r="K480" s="22" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="L480" s="22"/>
       <c r="M480" s="32" t="s">
         <v>2218</v>
       </c>
       <c r="N480" s="65" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="O480" s="38"/>
       <c r="P480" s="25"/>
@@ -56165,7 +56165,7 @@
         <v>41</v>
       </c>
       <c r="T480" s="21" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="U480" s="28"/>
       <c r="V480" s="28"/>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A82705-5CCB-3240-A9F3-57B6F58BBBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EB3177-0A48-2E41-A8A6-F032761DEA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="560" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1580" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EB3177-0A48-2E41-A8A6-F032761DEA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911C1AC2-CFF0-3146-B3AD-964878A52500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="3180" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -18809,7 +18809,7 @@
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="145" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="506">
+  <cellXfs count="507">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -20250,6 +20250,9 @@
     <xf numFmtId="0" fontId="128" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -22514,7 +22517,7 @@
       <c r="AQ26" s="32"/>
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A27" s="365" t="s">
+      <c r="A27" s="506" t="s">
         <v>4017</v>
       </c>
       <c r="B27" s="32" t="s">
@@ -22751,7 +22754,7 @@
       <c r="D30" s="239" t="s">
         <v>280</v>
       </c>
-      <c r="E30" s="58" t="s">
+      <c r="E30" s="300" t="s">
         <v>292</v>
       </c>
       <c r="F30" s="16" t="s">
@@ -23051,7 +23054,7 @@
       <c r="D34" s="234" t="s">
         <v>279</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="300" t="s">
         <v>324</v>
       </c>
       <c r="F34" s="16" t="s">
@@ -23132,7 +23135,7 @@
       <c r="D35" s="234" t="s">
         <v>279</v>
       </c>
-      <c r="E35" s="58" t="s">
+      <c r="E35" s="300" t="s">
         <v>324</v>
       </c>
       <c r="F35" s="16" t="s">
@@ -25919,7 +25922,7 @@
       <c r="B73" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C73" s="251" t="s">
+      <c r="C73" s="352" t="s">
         <v>143</v>
       </c>
       <c r="D73" s="235"/>
@@ -26645,7 +26648,7 @@
       <c r="B83" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C83" s="251" t="s">
+      <c r="C83" s="352" t="s">
         <v>143</v>
       </c>
       <c r="D83" s="235"/>
@@ -26925,7 +26928,7 @@
       <c r="B87" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="C87" s="251" t="s">
+      <c r="C87" s="352" t="s">
         <v>143</v>
       </c>
       <c r="D87" s="235"/>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A304A9E2-5D98-C749-B61A-865CEEA9D06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32121223-5BF6-1140-A980-A38CEFDB3856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -638,7 +638,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7049" uniqueCount="4022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7051" uniqueCount="4023">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17485,6 +17485,9 @@
   </si>
   <si>
     <t>10,6 x 12,6 cm</t>
+  </si>
+  <si>
+    <t>24,5 x 13,2 cm (l2 img)</t>
   </si>
 </sst>
 </file>
@@ -34762,7 +34765,9 @@
       <c r="S194" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="T194" s="21"/>
+      <c r="T194" s="21" t="s">
+        <v>4022</v>
+      </c>
       <c r="U194" s="28" t="s">
         <v>1063</v>
       </c>
@@ -34841,7 +34846,9 @@
       <c r="S195" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="T195" s="21"/>
+      <c r="T195" s="21" t="s">
+        <v>4022</v>
+      </c>
       <c r="U195" s="28" t="s">
         <v>1063</v>
       </c>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32121223-5BF6-1140-A980-A38CEFDB3856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4A7D3A-83E4-1C4F-9237-8C3EFCF5AAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6100" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -638,7 +638,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7051" uniqueCount="4023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7053" uniqueCount="4026">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17488,6 +17488,15 @@
   </si>
   <si>
     <t>24,5 x 13,2 cm (l2 img)</t>
+  </si>
+  <si>
+    <t>25 x 13 cm</t>
+  </si>
+  <si>
+    <t>25 x 13,4 cm</t>
+  </si>
+  <si>
+    <t>23,9 x 13,6 cm</t>
   </si>
 </sst>
 </file>
@@ -31048,7 +31057,9 @@
       <c r="S143" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="T143" s="21"/>
+      <c r="T143" s="21" t="s">
+        <v>4024</v>
+      </c>
       <c r="U143" s="28"/>
       <c r="V143" s="28"/>
       <c r="W143" s="29"/>
@@ -31117,7 +31128,9 @@
       <c r="S144" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="T144" s="21"/>
+      <c r="T144" s="21" t="s">
+        <v>4025</v>
+      </c>
       <c r="U144" s="28"/>
       <c r="V144" s="28"/>
       <c r="W144" s="29"/>
@@ -34847,7 +34860,7 @@
         <v>41</v>
       </c>
       <c r="T195" s="21" t="s">
-        <v>4022</v>
+        <v>4023</v>
       </c>
       <c r="U195" s="28" t="s">
         <v>1063</v>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A208DC1B-7B1E-E44E-B8E1-33415C5D660C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1D4B39-7C72-084D-B6EE-C659051CE2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3920" yWindow="-15320" windowWidth="36280" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -638,7 +638,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7053" uniqueCount="4031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7054" uniqueCount="4032">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17512,6 +17512,9 @@
   </si>
   <si>
     <t>Relevés décoratifs de la porte de Mars publiés en mai.</t>
+  </si>
+  <si>
+    <t>12,7 x 7,6 cm</t>
   </si>
 </sst>
 </file>
@@ -41635,7 +41638,9 @@
       <c r="S286" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T286" s="21"/>
+      <c r="T286" s="21" t="s">
+        <v>4031</v>
+      </c>
       <c r="U286" s="28"/>
       <c r="V286" s="28"/>
       <c r="W286" s="29"/>
@@ -65274,7 +65279,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{0BF36EE4-3719-004E-B027-B537BF5B40CE}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{F9CA7A1D-0385-2D40-9FD3-9EF31CEC33EB}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1D4B39-7C72-084D-B6EE-C659051CE2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3548EEA2-E878-D042-8B04-F0CFFD6963D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2680" yWindow="-20480" windowWidth="36840" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -638,7 +638,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7054" uniqueCount="4032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7042" uniqueCount="4026">
   <si>
     <t>ID estampe</t>
   </si>
@@ -17169,25 +17169,7 @@
     <t>[Mobilier d'apparat : trois piédestaux renfermant un siège]*</t>
   </si>
   <si>
-    <t>1691-12b_113</t>
-  </si>
-  <si>
-    <t>https://gallica.bnf.fr/ark:/12148/bpt6k6372917v/f113.item#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIO. FEL. INCL. GUILIELMO III. M. BRIT. R. TRIOMPHA PATRIA PATRI. GUB. P. C. L. P. RST. BELG. FOED. LIB. ANGL. SERV. SCOT. PAC. HIB. REDUCI. </t>
-  </si>
-  <si>
-    <t>Sur l'estampe : "J. Dolivar delineavit et fecit". La 1re est dessinée par Jan Smeltzing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">médaille ; arc de triomphe ; navire ; mer ; soleil ; </t>
-  </si>
-  <si>
     <t>article transcrit fichier xml</t>
-  </si>
-  <si>
-    <t>[Planche de quatre médailles (avers et revers) frappées pour le retour triomphal de Guillaume III d'Orange en 1691]*</t>
   </si>
   <si>
     <r>
@@ -18834,7 +18816,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -18878,19 +18860,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -18920,7 +18889,7 @@
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="145" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="490">
+  <cellXfs count="491">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -19861,64 +19830,13 @@
     <xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="141" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -19928,7 +19846,6 @@
     <xf numFmtId="0" fontId="100" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="140" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -20042,9 +19959,6 @@
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -20140,9 +20054,6 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -20195,9 +20106,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="143" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="144" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="123" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -20295,22 +20203,84 @@
     <xf numFmtId="0" fontId="151" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="151" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="151" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="151" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -20668,7 +20638,7 @@
       <c r="AQ1" s="3"/>
     </row>
     <row r="2" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A2" s="462" t="s">
+      <c r="A2" s="441" t="s">
         <v>3821</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -20739,7 +20709,7 @@
       <c r="AQ2" s="32"/>
     </row>
     <row r="3" spans="1:43" ht="54" customHeight="1">
-      <c r="A3" s="462" t="s">
+      <c r="A3" s="441" t="s">
         <v>42</v>
       </c>
       <c r="B3" s="33" t="s">
@@ -20816,7 +20786,7 @@
       <c r="AQ3" s="32"/>
     </row>
     <row r="4" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A4" s="462" t="s">
+      <c r="A4" s="441" t="s">
         <v>55</v>
       </c>
       <c r="B4" s="33" t="s">
@@ -20903,7 +20873,7 @@
       <c r="AQ4" s="32"/>
     </row>
     <row r="5" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A5" s="462" t="s">
+      <c r="A5" s="441" t="s">
         <v>3822</v>
       </c>
       <c r="B5" s="32" t="s">
@@ -20978,7 +20948,7 @@
       <c r="AQ5" s="32"/>
     </row>
     <row r="6" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A6" s="462" t="s">
+      <c r="A6" s="441" t="s">
         <v>3823</v>
       </c>
       <c r="B6" s="33" t="s">
@@ -21057,15 +21027,15 @@
       <c r="AQ6" s="32"/>
     </row>
     <row r="7" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A7" s="462" t="s">
+      <c r="A7" s="441" t="s">
         <v>96</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="380"/>
+      <c r="C7" s="362"/>
       <c r="D7" s="229"/>
-      <c r="E7" s="386"/>
+      <c r="E7" s="368"/>
       <c r="F7" s="19" t="s">
         <v>97</v>
       </c>
@@ -21103,8 +21073,8 @@
       <c r="V7" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="W7" s="436"/>
-      <c r="X7" s="436"/>
+      <c r="W7" s="416"/>
+      <c r="X7" s="416"/>
       <c r="Y7" s="30" t="s">
         <v>99</v>
       </c>
@@ -21128,7 +21098,7 @@
       <c r="AQ7" s="32"/>
     </row>
     <row r="8" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A8" s="462" t="s">
+      <c r="A8" s="441" t="s">
         <v>3824</v>
       </c>
       <c r="B8" s="32" t="s">
@@ -21205,7 +21175,7 @@
       <c r="AQ8" s="32"/>
     </row>
     <row r="9" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A9" s="462" t="s">
+      <c r="A9" s="441" t="s">
         <v>122</v>
       </c>
       <c r="B9" s="32" t="s">
@@ -21240,7 +21210,7 @@
       <c r="O9" s="65"/>
       <c r="P9" s="25"/>
       <c r="Q9" s="26"/>
-      <c r="R9" s="424" t="s">
+      <c r="R9" s="405" t="s">
         <v>80</v>
       </c>
       <c r="S9" s="40" t="s">
@@ -21274,7 +21244,7 @@
       <c r="AQ9" s="32"/>
     </row>
     <row r="10" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A10" s="462" t="s">
+      <c r="A10" s="441" t="s">
         <v>3825</v>
       </c>
       <c r="B10" s="32" t="s">
@@ -21347,7 +21317,7 @@
       <c r="AQ10" s="32"/>
     </row>
     <row r="11" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A11" s="462" t="s">
+      <c r="A11" s="441" t="s">
         <v>130</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -21420,7 +21390,7 @@
       <c r="AQ11" s="32"/>
     </row>
     <row r="12" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A12" s="462" t="s">
+      <c r="A12" s="441" t="s">
         <v>142</v>
       </c>
       <c r="B12" s="14" t="s">
@@ -21451,10 +21421,10 @@
       <c r="M12" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="N12" s="412" t="s">
+      <c r="N12" s="393" t="s">
         <v>148</v>
       </c>
-      <c r="O12" s="412"/>
+      <c r="O12" s="393"/>
       <c r="P12" s="70"/>
       <c r="Q12" s="71"/>
       <c r="R12" s="39" t="s">
@@ -21491,7 +21461,7 @@
       <c r="AQ12" s="32"/>
     </row>
     <row r="13" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A13" s="462" t="s">
+      <c r="A13" s="441" t="s">
         <v>150</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -21562,7 +21532,7 @@
       <c r="AQ13" s="32"/>
     </row>
     <row r="14" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A14" s="476" t="s">
+      <c r="A14" s="455" t="s">
         <v>159</v>
       </c>
       <c r="B14" s="32" t="s">
@@ -21609,7 +21579,7 @@
       <c r="W14" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="X14" s="437" t="s">
+      <c r="X14" s="417" t="s">
         <v>167</v>
       </c>
       <c r="Y14" s="80" t="s">
@@ -21704,8 +21674,8 @@
       <c r="AQ15" s="32"/>
     </row>
     <row r="16" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A16" s="474" t="s">
-        <v>4025</v>
+      <c r="A16" s="453" t="s">
+        <v>4019</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>43</v>
@@ -21765,7 +21735,7 @@
         <v>191</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>3968</v>
+        <v>3962</v>
       </c>
       <c r="Z16" s="30"/>
       <c r="AA16" s="30"/>
@@ -21792,7 +21762,7 @@
     </row>
     <row r="17" spans="1:43" ht="15.75" customHeight="1">
       <c r="A17" s="99" t="s">
-        <v>4026</v>
+        <v>4020</v>
       </c>
       <c r="B17" s="32" t="s">
         <v>43</v>
@@ -21879,7 +21849,7 @@
     </row>
     <row r="18" spans="1:43" ht="15.75" customHeight="1">
       <c r="A18" s="99" t="s">
-        <v>4027</v>
+        <v>4021</v>
       </c>
       <c r="B18" s="87" t="s">
         <v>201</v>
@@ -21943,7 +21913,7 @@
       </c>
       <c r="Z18" s="30"/>
       <c r="AA18" s="30"/>
-      <c r="AB18" s="445" t="s">
+      <c r="AB18" s="425" t="s">
         <v>206</v>
       </c>
       <c r="AC18" s="32" t="s">
@@ -21966,7 +21936,7 @@
     </row>
     <row r="19" spans="1:43" ht="15.75" customHeight="1">
       <c r="A19" s="99" t="s">
-        <v>4028</v>
+        <v>4022</v>
       </c>
       <c r="B19" s="32" t="s">
         <v>43</v>
@@ -22079,7 +22049,7 @@
       <c r="I20" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="J20" s="401"/>
+      <c r="J20" s="382"/>
       <c r="K20" s="302"/>
       <c r="L20" s="82"/>
       <c r="M20" s="32" t="s">
@@ -22115,7 +22085,7 @@
       </c>
       <c r="Z20" s="30"/>
       <c r="AA20" s="30"/>
-      <c r="AB20" s="446" t="s">
+      <c r="AB20" s="426" t="s">
         <v>219</v>
       </c>
       <c r="AC20" s="32" t="s">
@@ -22200,7 +22170,7 @@
       </c>
       <c r="Z21" s="30"/>
       <c r="AA21" s="30"/>
-      <c r="AB21" s="447"/>
+      <c r="AB21" s="427"/>
       <c r="AC21" s="92" t="s">
         <v>226</v>
       </c>
@@ -22220,7 +22190,7 @@
       <c r="AQ21" s="32"/>
     </row>
     <row r="22" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A22" s="462" t="s">
+      <c r="A22" s="441" t="s">
         <v>227</v>
       </c>
       <c r="B22" s="14" t="s">
@@ -22273,7 +22243,7 @@
       <c r="Y22" s="30"/>
       <c r="Z22" s="30"/>
       <c r="AA22" s="30"/>
-      <c r="AB22" s="443" t="s">
+      <c r="AB22" s="423" t="s">
         <v>235</v>
       </c>
       <c r="AC22" s="69" t="s">
@@ -22368,7 +22338,7 @@
       <c r="AQ23" s="32"/>
     </row>
     <row r="24" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A24" s="462" t="s">
+      <c r="A24" s="441" t="s">
         <v>3828</v>
       </c>
       <c r="B24" s="32" t="s">
@@ -22437,8 +22407,8 @@
       <c r="AQ24" s="32"/>
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A25" s="462" t="s">
-        <v>3979</v>
+      <c r="A25" s="441" t="s">
+        <v>3973</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>246</v>
@@ -22506,8 +22476,8 @@
       <c r="AQ25" s="32"/>
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A26" s="462" t="s">
-        <v>4012</v>
+      <c r="A26" s="441" t="s">
+        <v>4006</v>
       </c>
       <c r="B26" s="32" t="s">
         <v>246</v>
@@ -22585,7 +22555,7 @@
       <c r="AQ26" s="32"/>
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A27" s="462" t="s">
+      <c r="A27" s="441" t="s">
         <v>3829</v>
       </c>
       <c r="B27" s="33" t="s">
@@ -22628,11 +22598,11 @@
         <v>40</v>
       </c>
       <c r="S27" s="32"/>
-      <c r="T27" s="454"/>
-      <c r="U27" s="456" t="s">
+      <c r="T27" s="433"/>
+      <c r="U27" s="435" t="s">
         <v>287</v>
       </c>
-      <c r="V27" s="456" t="s">
+      <c r="V27" s="435" t="s">
         <v>288</v>
       </c>
       <c r="W27" s="29"/>
@@ -22660,7 +22630,7 @@
       <c r="AQ27" s="32"/>
     </row>
     <row r="28" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A28" s="462" t="s">
+      <c r="A28" s="441" t="s">
         <v>3830</v>
       </c>
       <c r="B28" s="33" t="s">
@@ -22673,7 +22643,7 @@
         <v>279</v>
       </c>
       <c r="E28" s="99" t="s">
-        <v>4029</v>
+        <v>4023</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>291</v>
@@ -22686,7 +22656,7 @@
         <v>293</v>
       </c>
       <c r="J28" s="35"/>
-      <c r="K28" s="453"/>
+      <c r="K28" s="432"/>
       <c r="L28" s="68" t="s">
         <v>284</v>
       </c>
@@ -22705,16 +22675,16 @@
       <c r="S28" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T28" s="454" t="s">
+      <c r="T28" s="433" t="s">
         <v>296</v>
       </c>
-      <c r="U28" s="456" t="s">
+      <c r="U28" s="435" t="s">
         <v>287</v>
       </c>
-      <c r="V28" s="456" t="s">
+      <c r="V28" s="435" t="s">
         <v>288</v>
       </c>
-      <c r="W28" s="458"/>
+      <c r="W28" s="437"/>
       <c r="X28" s="72"/>
       <c r="Y28" s="30" t="s">
         <v>297</v>
@@ -22723,7 +22693,7 @@
       <c r="AA28" s="30"/>
       <c r="AB28" s="41"/>
       <c r="AC28" s="32"/>
-      <c r="AD28" s="459" t="s">
+      <c r="AD28" s="438" t="s">
         <v>298</v>
       </c>
       <c r="AE28" s="32"/>
@@ -22741,7 +22711,7 @@
       <c r="AQ28" s="32"/>
     </row>
     <row r="29" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A29" s="462" t="s">
+      <c r="A29" s="441" t="s">
         <v>3831</v>
       </c>
       <c r="B29" s="33" t="s">
@@ -22751,7 +22721,7 @@
         <v>3789</v>
       </c>
       <c r="D29" s="229"/>
-      <c r="E29" s="464"/>
+      <c r="E29" s="443"/>
       <c r="F29" s="34" t="s">
         <v>299</v>
       </c>
@@ -22764,7 +22734,7 @@
       <c r="I29" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="J29" s="452" t="s">
+      <c r="J29" s="431" t="s">
         <v>303</v>
       </c>
       <c r="K29" s="103"/>
@@ -22814,7 +22784,7 @@
       <c r="AQ29" s="32"/>
     </row>
     <row r="30" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A30" s="462" t="s">
+      <c r="A30" s="441" t="s">
         <v>3832</v>
       </c>
       <c r="B30" s="32" t="s">
@@ -22858,8 +22828,8 @@
       <c r="T30" s="104" t="s">
         <v>313</v>
       </c>
-      <c r="U30" s="457"/>
-      <c r="V30" s="457"/>
+      <c r="U30" s="436"/>
+      <c r="V30" s="436"/>
       <c r="W30" s="29" t="s">
         <v>166</v>
       </c>
@@ -22889,7 +22859,7 @@
       <c r="AQ30" s="32"/>
     </row>
     <row r="31" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A31" s="462" t="s">
+      <c r="A31" s="441" t="s">
         <v>314</v>
       </c>
       <c r="B31" s="95" t="s">
@@ -22899,7 +22869,7 @@
         <v>3788</v>
       </c>
       <c r="D31" s="229"/>
-      <c r="E31" s="464"/>
+      <c r="E31" s="443"/>
       <c r="F31" s="34" t="s">
         <v>315</v>
       </c>
@@ -22960,7 +22930,7 @@
       <c r="AQ31" s="32"/>
     </row>
     <row r="32" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A32" s="462" t="s">
+      <c r="A32" s="441" t="s">
         <v>3833</v>
       </c>
       <c r="B32" s="95" t="s">
@@ -22973,7 +22943,7 @@
         <v>278</v>
       </c>
       <c r="E32" s="99" t="s">
-        <v>4030</v>
+        <v>4024</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>322</v>
@@ -22988,8 +22958,8 @@
         <v>324</v>
       </c>
       <c r="J32" s="35"/>
-      <c r="K32" s="453"/>
-      <c r="L32" s="453" t="s">
+      <c r="K32" s="432"/>
+      <c r="L32" s="432" t="s">
         <v>284</v>
       </c>
       <c r="M32" s="36" t="s">
@@ -23007,16 +22977,16 @@
       <c r="S32" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="T32" s="455" t="s">
+      <c r="T32" s="434" t="s">
         <v>326</v>
       </c>
-      <c r="U32" s="456" t="s">
+      <c r="U32" s="435" t="s">
         <v>287</v>
       </c>
-      <c r="V32" s="456" t="s">
+      <c r="V32" s="435" t="s">
         <v>288</v>
       </c>
-      <c r="W32" s="435"/>
+      <c r="W32" s="415"/>
       <c r="X32" s="72"/>
       <c r="Y32" s="30" t="s">
         <v>327</v>
@@ -23041,7 +23011,7 @@
       <c r="AQ32" s="32"/>
     </row>
     <row r="33" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A33" s="462" t="s">
+      <c r="A33" s="441" t="s">
         <v>3834</v>
       </c>
       <c r="B33" s="14" t="s">
@@ -23054,7 +23024,7 @@
         <v>278</v>
       </c>
       <c r="E33" s="99" t="s">
-        <v>4030</v>
+        <v>4024</v>
       </c>
       <c r="F33" s="16" t="s">
         <v>328</v>
@@ -23122,7 +23092,7 @@
       <c r="AQ33" s="32"/>
     </row>
     <row r="34" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A34" s="462" t="s">
+      <c r="A34" s="441" t="s">
         <v>3835</v>
       </c>
       <c r="B34" s="14" t="s">
@@ -23185,7 +23155,7 @@
       <c r="AC34" s="32" t="s">
         <v>344</v>
       </c>
-      <c r="AD34" s="460"/>
+      <c r="AD34" s="439"/>
       <c r="AE34" s="32"/>
       <c r="AF34" s="32"/>
       <c r="AG34" s="32"/>
@@ -23201,7 +23171,7 @@
       <c r="AQ34" s="32"/>
     </row>
     <row r="35" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A35" s="462" t="s">
+      <c r="A35" s="441" t="s">
         <v>345</v>
       </c>
       <c r="B35" s="32" t="s">
@@ -23272,7 +23242,7 @@
       <c r="AQ35" s="32"/>
     </row>
     <row r="36" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A36" s="462" t="s">
+      <c r="A36" s="441" t="s">
         <v>3836</v>
       </c>
       <c r="B36" s="14" t="s">
@@ -23320,7 +23290,7 @@
         <v>41</v>
       </c>
       <c r="T36" s="21" t="s">
-        <v>4013</v>
+        <v>4007</v>
       </c>
       <c r="U36" s="28"/>
       <c r="V36" s="28"/>
@@ -23353,7 +23323,7 @@
       <c r="AQ36" s="32"/>
     </row>
     <row r="37" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A37" s="462" t="s">
+      <c r="A37" s="441" t="s">
         <v>3837</v>
       </c>
       <c r="B37" s="14" t="s">
@@ -23388,7 +23358,7 @@
       <c r="O37" s="294" t="s">
         <v>361</v>
       </c>
-      <c r="P37" s="420"/>
+      <c r="P37" s="401"/>
       <c r="Q37" s="56" t="s">
         <v>362</v>
       </c>
@@ -23399,7 +23369,7 @@
         <v>41</v>
       </c>
       <c r="T37" s="21" t="s">
-        <v>4014</v>
+        <v>4008</v>
       </c>
       <c r="U37" s="28"/>
       <c r="V37" s="28"/>
@@ -23426,7 +23396,7 @@
       <c r="AQ37" s="32"/>
     </row>
     <row r="38" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A38" s="462" t="s">
+      <c r="A38" s="441" t="s">
         <v>372</v>
       </c>
       <c r="B38" s="17" t="s">
@@ -23458,7 +23428,7 @@
       <c r="N38" s="54" t="s">
         <v>375</v>
       </c>
-      <c r="O38" s="413"/>
+      <c r="O38" s="394"/>
       <c r="P38" s="112"/>
       <c r="Q38" s="56"/>
       <c r="R38" s="32" t="s">
@@ -23468,7 +23438,7 @@
         <v>41</v>
       </c>
       <c r="T38" s="21" t="s">
-        <v>4015</v>
+        <v>4009</v>
       </c>
       <c r="U38" s="28"/>
       <c r="V38" s="28"/>
@@ -23495,13 +23465,13 @@
       <c r="AQ38" s="32"/>
     </row>
     <row r="39" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A39" s="462" t="s">
-        <v>4010</v>
+      <c r="A39" s="441" t="s">
+        <v>4004</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="451" t="s">
+      <c r="C39" s="430" t="s">
         <v>3787</v>
       </c>
       <c r="D39" s="231" t="s">
@@ -23541,7 +23511,7 @@
         <v>41</v>
       </c>
       <c r="T39" s="21" t="s">
-        <v>4016</v>
+        <v>4010</v>
       </c>
       <c r="U39" s="28"/>
       <c r="V39" s="28"/>
@@ -23568,8 +23538,8 @@
       <c r="AQ39" s="32"/>
     </row>
     <row r="40" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A40" s="462" t="s">
-        <v>4011</v>
+      <c r="A40" s="441" t="s">
+        <v>4005</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>43</v>
@@ -23639,7 +23609,7 @@
       <c r="AQ40" s="32"/>
     </row>
     <row r="41" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A41" s="462" t="s">
+      <c r="A41" s="441" t="s">
         <v>377</v>
       </c>
       <c r="B41" s="14" t="s">
@@ -23706,7 +23676,7 @@
       <c r="AQ41" s="32"/>
     </row>
     <row r="42" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A42" s="462" t="s">
+      <c r="A42" s="441" t="s">
         <v>3838</v>
       </c>
       <c r="B42" s="14" t="s">
@@ -23777,7 +23747,7 @@
       <c r="AQ42" s="32"/>
     </row>
     <row r="43" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A43" s="462" t="s">
+      <c r="A43" s="441" t="s">
         <v>3839</v>
       </c>
       <c r="B43" s="14" t="s">
@@ -23830,7 +23800,7 @@
         <v>400</v>
       </c>
       <c r="Y43" s="30" t="s">
-        <v>3969</v>
+        <v>3963</v>
       </c>
       <c r="Z43" s="30"/>
       <c r="AA43" s="30"/>
@@ -23852,7 +23822,7 @@
       <c r="AQ43" s="32"/>
     </row>
     <row r="44" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A44" s="462" t="s">
+      <c r="A44" s="441" t="s">
         <v>401</v>
       </c>
       <c r="B44" s="32" t="s">
@@ -23869,7 +23839,7 @@
       <c r="G44" s="32" t="s">
         <v>405</v>
       </c>
-      <c r="H44" s="375" t="s">
+      <c r="H44" s="357" t="s">
         <v>406</v>
       </c>
       <c r="I44" s="43" t="s">
@@ -23919,7 +23889,7 @@
       <c r="AQ44" s="32"/>
     </row>
     <row r="45" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A45" s="462" t="s">
+      <c r="A45" s="441" t="s">
         <v>408</v>
       </c>
       <c r="B45" s="32" t="s">
@@ -23988,7 +23958,7 @@
       <c r="AQ45" s="32"/>
     </row>
     <row r="46" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A46" s="462" t="s">
+      <c r="A46" s="441" t="s">
         <v>3893</v>
       </c>
       <c r="B46" s="14" t="s">
@@ -24037,7 +24007,7 @@
       <c r="W46" s="111" t="s">
         <v>341</v>
       </c>
-      <c r="X46" s="347" t="s">
+      <c r="X46" s="330" t="s">
         <v>422</v>
       </c>
       <c r="Y46" s="30" t="s">
@@ -24065,7 +24035,7 @@
       <c r="AQ46" s="32"/>
     </row>
     <row r="47" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A47" s="462" t="s">
+      <c r="A47" s="441" t="s">
         <v>424</v>
       </c>
       <c r="B47" s="32" t="s">
@@ -24132,7 +24102,7 @@
       <c r="AQ47" s="32"/>
     </row>
     <row r="48" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A48" s="462" t="s">
+      <c r="A48" s="441" t="s">
         <v>3894</v>
       </c>
       <c r="B48" s="32" t="s">
@@ -24162,7 +24132,7 @@
       <c r="N48" s="54" t="s">
         <v>435</v>
       </c>
-      <c r="O48" s="413" t="s">
+      <c r="O48" s="394" t="s">
         <v>436</v>
       </c>
       <c r="P48" s="112"/>
@@ -24208,7 +24178,7 @@
       <c r="AQ48" s="32"/>
     </row>
     <row r="49" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A49" s="462" t="s">
+      <c r="A49" s="441" t="s">
         <v>439</v>
       </c>
       <c r="B49" s="14" t="s">
@@ -24240,11 +24210,11 @@
       <c r="N49" s="54" t="s">
         <v>447</v>
       </c>
-      <c r="O49" s="413"/>
+      <c r="O49" s="394"/>
       <c r="P49" s="124" t="s">
         <v>448</v>
       </c>
-      <c r="Q49" s="421" t="s">
+      <c r="Q49" s="402" t="s">
         <v>449</v>
       </c>
       <c r="R49" s="115" t="s">
@@ -24289,8 +24259,8 @@
       <c r="AQ49" s="32"/>
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A50" s="462" t="s">
-        <v>3986</v>
+      <c r="A50" s="441" t="s">
+        <v>3980</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>430</v>
@@ -24323,9 +24293,9 @@
       <c r="N50" s="54" t="s">
         <v>459</v>
       </c>
-      <c r="O50" s="413"/>
+      <c r="O50" s="394"/>
       <c r="P50" s="112"/>
-      <c r="Q50" s="421"/>
+      <c r="Q50" s="402"/>
       <c r="R50" s="43" t="s">
         <v>139</v>
       </c>
@@ -24360,8 +24330,8 @@
       <c r="AQ50" s="32"/>
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A51" s="462" t="s">
-        <v>3985</v>
+      <c r="A51" s="441" t="s">
+        <v>3979</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>440</v>
@@ -24431,7 +24401,7 @@
       <c r="AQ51" s="32"/>
     </row>
     <row r="52" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A52" s="462" t="s">
+      <c r="A52" s="441" t="s">
         <v>3895</v>
       </c>
       <c r="B52" s="14" t="s">
@@ -24514,7 +24484,7 @@
       <c r="AQ52" s="32"/>
     </row>
     <row r="53" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A53" s="462" t="s">
+      <c r="A53" s="441" t="s">
         <v>482</v>
       </c>
       <c r="B53" s="14" t="s">
@@ -24593,7 +24563,7 @@
       <c r="AQ53" s="32"/>
     </row>
     <row r="54" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A54" s="462" t="s">
+      <c r="A54" s="441" t="s">
         <v>3896</v>
       </c>
       <c r="B54" s="129" t="s">
@@ -24666,7 +24636,7 @@
       <c r="AQ54" s="32"/>
     </row>
     <row r="55" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A55" s="462" t="s">
+      <c r="A55" s="441" t="s">
         <v>503</v>
       </c>
       <c r="B55" s="32" t="s">
@@ -24735,7 +24705,7 @@
       <c r="AQ55" s="32"/>
     </row>
     <row r="56" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A56" s="462" t="s">
+      <c r="A56" s="441" t="s">
         <v>509</v>
       </c>
       <c r="B56" s="32" t="s">
@@ -24812,7 +24782,7 @@
       <c r="AQ56" s="32"/>
     </row>
     <row r="57" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A57" s="462" t="s">
+      <c r="A57" s="441" t="s">
         <v>3897</v>
       </c>
       <c r="B57" s="32" t="s">
@@ -24879,7 +24849,7 @@
       <c r="AQ57" s="32"/>
     </row>
     <row r="58" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A58" s="462" t="s">
+      <c r="A58" s="441" t="s">
         <v>3898</v>
       </c>
       <c r="B58" s="32" t="s">
@@ -24954,7 +24924,7 @@
       <c r="AQ58" s="32"/>
     </row>
     <row r="59" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A59" s="462" t="s">
+      <c r="A59" s="441" t="s">
         <v>3899</v>
       </c>
       <c r="B59" s="32" t="s">
@@ -25025,7 +24995,7 @@
       <c r="AQ59" s="32"/>
     </row>
     <row r="60" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A60" s="462" t="s">
+      <c r="A60" s="441" t="s">
         <v>3900</v>
       </c>
       <c r="B60" s="32" t="s">
@@ -25100,7 +25070,7 @@
       <c r="AQ60" s="32"/>
     </row>
     <row r="61" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A61" s="462" t="s">
+      <c r="A61" s="441" t="s">
         <v>3901</v>
       </c>
       <c r="B61" s="32" t="s">
@@ -25171,7 +25141,7 @@
       <c r="AQ61" s="32"/>
     </row>
     <row r="62" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A62" s="462" t="s">
+      <c r="A62" s="441" t="s">
         <v>3892</v>
       </c>
       <c r="B62" s="32" t="s">
@@ -25238,7 +25208,7 @@
       <c r="AQ62" s="32"/>
     </row>
     <row r="63" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A63" s="462" t="s">
+      <c r="A63" s="441" t="s">
         <v>559</v>
       </c>
       <c r="B63" s="32" t="s">
@@ -25311,7 +25281,7 @@
       <c r="AQ63" s="32"/>
     </row>
     <row r="64" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A64" s="462" t="s">
+      <c r="A64" s="441" t="s">
         <v>3891</v>
       </c>
       <c r="B64" s="32" t="s">
@@ -25345,7 +25315,7 @@
       <c r="N64" s="83" t="s">
         <v>573</v>
       </c>
-      <c r="O64" s="418"/>
+      <c r="O64" s="399"/>
       <c r="P64" s="124"/>
       <c r="Q64" s="133"/>
       <c r="R64" s="115" t="s">
@@ -25384,7 +25354,7 @@
       <c r="AQ64" s="32"/>
     </row>
     <row r="65" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A65" s="462" t="s">
+      <c r="A65" s="441" t="s">
         <v>3890</v>
       </c>
       <c r="B65" s="32" t="s">
@@ -25457,7 +25427,7 @@
       <c r="AQ65" s="32"/>
     </row>
     <row r="66" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A66" s="462" t="s">
+      <c r="A66" s="441" t="s">
         <v>3889</v>
       </c>
       <c r="B66" s="32" t="s">
@@ -25530,7 +25500,7 @@
       <c r="AQ66" s="32"/>
     </row>
     <row r="67" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A67" s="462" t="s">
+      <c r="A67" s="441" t="s">
         <v>591</v>
       </c>
       <c r="B67" s="32" t="s">
@@ -25553,22 +25523,22 @@
       <c r="I67" s="43" t="s">
         <v>595</v>
       </c>
-      <c r="J67" s="466" t="s">
+      <c r="J67" s="445" t="s">
         <v>596</v>
       </c>
-      <c r="K67" s="466"/>
-      <c r="L67" s="466"/>
+      <c r="K67" s="445"/>
+      <c r="L67" s="445"/>
       <c r="M67" s="43" t="s">
         <v>597</v>
       </c>
       <c r="N67" s="54" t="s">
         <v>598</v>
       </c>
-      <c r="O67" s="467"/>
-      <c r="P67" s="468" t="s">
+      <c r="O67" s="446"/>
+      <c r="P67" s="447" t="s">
         <v>38</v>
       </c>
-      <c r="Q67" s="468" t="s">
+      <c r="Q67" s="447" t="s">
         <v>599</v>
       </c>
       <c r="R67" s="99" t="s">
@@ -25582,10 +25552,10 @@
       </c>
       <c r="U67" s="48"/>
       <c r="V67" s="48"/>
-      <c r="W67" s="469" t="s">
+      <c r="W67" s="448" t="s">
         <v>190</v>
       </c>
-      <c r="X67" s="469" t="s">
+      <c r="X67" s="448" t="s">
         <v>191</v>
       </c>
       <c r="Y67" s="66" t="s">
@@ -25613,7 +25583,7 @@
       <c r="AQ67" s="32"/>
     </row>
     <row r="68" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A68" s="462" t="s">
+      <c r="A68" s="441" t="s">
         <v>604</v>
       </c>
       <c r="B68" s="32" t="s">
@@ -25634,9 +25604,9 @@
       <c r="I68" s="43" t="s">
         <v>607</v>
       </c>
-      <c r="J68" s="466"/>
-      <c r="K68" s="466"/>
-      <c r="L68" s="466"/>
+      <c r="J68" s="445"/>
+      <c r="K68" s="445"/>
+      <c r="L68" s="445"/>
       <c r="M68" s="43" t="s">
         <v>608</v>
       </c>
@@ -25644,7 +25614,7 @@
         <v>609</v>
       </c>
       <c r="O68" s="294"/>
-      <c r="P68" s="470"/>
+      <c r="P68" s="449"/>
       <c r="Q68" s="38"/>
       <c r="R68" s="32" t="s">
         <v>49</v>
@@ -25668,7 +25638,7 @@
       </c>
       <c r="Z68" s="32"/>
       <c r="AA68" s="32"/>
-      <c r="AB68" s="471" t="s">
+      <c r="AB68" s="450" t="s">
         <v>612</v>
       </c>
       <c r="AC68" s="32" t="s">
@@ -25690,7 +25660,7 @@
       <c r="AQ68" s="32"/>
     </row>
     <row r="69" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A69" s="462" t="s">
+      <c r="A69" s="441" t="s">
         <v>3888</v>
       </c>
       <c r="B69" s="32" t="s">
@@ -25713,13 +25683,13 @@
       <c r="I69" s="43" t="s">
         <v>617</v>
       </c>
-      <c r="J69" s="472" t="s">
+      <c r="J69" s="451" t="s">
         <v>618</v>
       </c>
-      <c r="K69" s="472" t="s">
+      <c r="K69" s="451" t="s">
         <v>63</v>
       </c>
-      <c r="L69" s="466"/>
+      <c r="L69" s="445"/>
       <c r="M69" s="43" t="s">
         <v>619</v>
       </c>
@@ -25755,7 +25725,7 @@
       </c>
       <c r="Z69" s="32"/>
       <c r="AA69" s="32"/>
-      <c r="AB69" s="471" t="s">
+      <c r="AB69" s="450" t="s">
         <v>623</v>
       </c>
       <c r="AC69" s="47" t="s">
@@ -25777,13 +25747,13 @@
       <c r="AQ69" s="32"/>
     </row>
     <row r="70" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A70" s="462" t="s">
+      <c r="A70" s="441" t="s">
         <v>3887</v>
       </c>
       <c r="B70" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C70" s="381" t="s">
+      <c r="C70" s="363" t="s">
         <v>625</v>
       </c>
       <c r="D70" s="232"/>
@@ -25846,7 +25816,7 @@
       <c r="AQ70" s="32"/>
     </row>
     <row r="71" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A71" s="462" t="s">
+      <c r="A71" s="441" t="s">
         <v>3886</v>
       </c>
       <c r="B71" s="32" t="s">
@@ -25915,7 +25885,7 @@
       <c r="AQ71" s="32"/>
     </row>
     <row r="72" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A72" s="462" t="s">
+      <c r="A72" s="441" t="s">
         <v>3885</v>
       </c>
       <c r="B72" s="32" t="s">
@@ -25984,7 +25954,7 @@
       <c r="AQ72" s="32"/>
     </row>
     <row r="73" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A73" s="462" t="s">
+      <c r="A73" s="441" t="s">
         <v>648</v>
       </c>
       <c r="B73" s="32" t="s">
@@ -26061,7 +26031,7 @@
       <c r="AQ73" s="32"/>
     </row>
     <row r="74" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A74" s="462" t="s">
+      <c r="A74" s="441" t="s">
         <v>3884</v>
       </c>
       <c r="B74" s="39" t="s">
@@ -26093,7 +26063,7 @@
       <c r="N74" s="54" t="s">
         <v>666</v>
       </c>
-      <c r="O74" s="413"/>
+      <c r="O74" s="394"/>
       <c r="P74" s="112"/>
       <c r="Q74" s="121"/>
       <c r="R74" s="39" t="s">
@@ -26130,7 +26100,7 @@
       <c r="AQ74" s="32"/>
     </row>
     <row r="75" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A75" s="462" t="s">
+      <c r="A75" s="441" t="s">
         <v>668</v>
       </c>
       <c r="B75" s="32" t="s">
@@ -26197,7 +26167,7 @@
       <c r="AQ75" s="32"/>
     </row>
     <row r="76" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A76" s="462" t="s">
+      <c r="A76" s="441" t="s">
         <v>673</v>
       </c>
       <c r="B76" s="32" t="s">
@@ -26266,7 +26236,7 @@
       <c r="AQ76" s="32"/>
     </row>
     <row r="77" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A77" s="465" t="s">
+      <c r="A77" s="444" t="s">
         <v>683</v>
       </c>
       <c r="B77" s="286" t="s">
@@ -26307,7 +26277,7 @@
       <c r="Q77" s="325" t="s">
         <v>692</v>
       </c>
-      <c r="R77" s="423" t="s">
+      <c r="R77" s="404" t="s">
         <v>519</v>
       </c>
       <c r="S77" s="286" t="s">
@@ -26341,7 +26311,7 @@
       <c r="AQ77" s="32"/>
     </row>
     <row r="78" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A78" s="462" t="s">
+      <c r="A78" s="441" t="s">
         <v>694</v>
       </c>
       <c r="B78" s="14" t="s">
@@ -26410,7 +26380,7 @@
       <c r="AQ78" s="32"/>
     </row>
     <row r="79" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A79" s="462" t="s">
+      <c r="A79" s="441" t="s">
         <v>700</v>
       </c>
       <c r="B79" s="32" t="s">
@@ -26487,7 +26457,7 @@
       <c r="AQ79" s="32"/>
     </row>
     <row r="80" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A80" s="462" t="s">
+      <c r="A80" s="441" t="s">
         <v>709</v>
       </c>
       <c r="B80" s="129" t="s">
@@ -26568,7 +26538,7 @@
       <c r="AQ80" s="32"/>
     </row>
     <row r="81" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A81" s="462" t="s">
+      <c r="A81" s="441" t="s">
         <v>722</v>
       </c>
       <c r="B81" s="14" t="s">
@@ -26577,7 +26547,7 @@
       <c r="C81" s="254" t="s">
         <v>171</v>
       </c>
-      <c r="D81" s="385" t="s">
+      <c r="D81" s="367" t="s">
         <v>592</v>
       </c>
       <c r="E81" s="136" t="s">
@@ -26639,7 +26609,7 @@
       <c r="AQ81" s="32"/>
     </row>
     <row r="82" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A82" s="465" t="s">
+      <c r="A82" s="444" t="s">
         <v>728</v>
       </c>
       <c r="B82" s="311" t="s">
@@ -26661,8 +26631,8 @@
         <v>444</v>
       </c>
       <c r="J82" s="314"/>
-      <c r="K82" s="327"/>
-      <c r="L82" s="327"/>
+      <c r="K82" s="326"/>
+      <c r="L82" s="326"/>
       <c r="M82" s="316" t="s">
         <v>732</v>
       </c>
@@ -26670,23 +26640,23 @@
         <v>733</v>
       </c>
       <c r="O82" s="317"/>
-      <c r="P82" s="328" t="s">
+      <c r="P82" s="327" t="s">
         <v>734</v>
       </c>
       <c r="Q82" s="318" t="s">
         <v>735</v>
       </c>
-      <c r="R82" s="423" t="s">
+      <c r="R82" s="404" t="s">
         <v>49</v>
       </c>
       <c r="S82" s="286" t="s">
         <v>41</v>
       </c>
-      <c r="T82" s="428" t="s">
+      <c r="T82" s="408" t="s">
         <v>736</v>
       </c>
-      <c r="U82" s="432"/>
-      <c r="V82" s="432"/>
+      <c r="U82" s="412"/>
+      <c r="V82" s="412"/>
       <c r="W82" s="320"/>
       <c r="X82" s="320"/>
       <c r="Y82" s="284"/>
@@ -26710,7 +26680,7 @@
       <c r="AQ82" s="32"/>
     </row>
     <row r="83" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A83" s="462" t="s">
+      <c r="A83" s="441" t="s">
         <v>737</v>
       </c>
       <c r="B83" s="14" t="s">
@@ -26783,7 +26753,7 @@
       <c r="AQ83" s="32"/>
     </row>
     <row r="84" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A84" s="463" t="s">
+      <c r="A84" s="442" t="s">
         <v>3883</v>
       </c>
       <c r="B84" s="14" t="s">
@@ -26850,7 +26820,7 @@
       <c r="AQ84" s="32"/>
     </row>
     <row r="85" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A85" s="462" t="s">
+      <c r="A85" s="441" t="s">
         <v>752</v>
       </c>
       <c r="B85" s="14" t="s">
@@ -26919,7 +26889,7 @@
       <c r="AQ85" s="32"/>
     </row>
     <row r="86" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A86" s="463" t="s">
+      <c r="A86" s="442" t="s">
         <v>3882</v>
       </c>
       <c r="B86" s="14" t="s">
@@ -26990,7 +26960,7 @@
       <c r="AQ86" s="32"/>
     </row>
     <row r="87" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A87" s="462" t="s">
+      <c r="A87" s="441" t="s">
         <v>764</v>
       </c>
       <c r="B87" s="14" t="s">
@@ -27069,7 +27039,7 @@
       <c r="AQ87" s="32"/>
     </row>
     <row r="88" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A88" s="462" t="s">
+      <c r="A88" s="441" t="s">
         <v>776</v>
       </c>
       <c r="B88" s="14" t="s">
@@ -27142,7 +27112,7 @@
       <c r="AQ88" s="32"/>
     </row>
     <row r="89" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A89" s="462" t="s">
+      <c r="A89" s="441" t="s">
         <v>785</v>
       </c>
       <c r="B89" s="14" t="s">
@@ -27219,7 +27189,7 @@
       <c r="AQ89" s="32"/>
     </row>
     <row r="90" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A90" s="462" t="s">
+      <c r="A90" s="441" t="s">
         <v>795</v>
       </c>
       <c r="B90" s="14" t="s">
@@ -27296,7 +27266,7 @@
       <c r="AQ90" s="32"/>
     </row>
     <row r="91" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A91" s="463" t="s">
+      <c r="A91" s="442" t="s">
         <v>3881</v>
       </c>
       <c r="B91" s="14" t="s">
@@ -27305,7 +27275,7 @@
       <c r="C91" s="307" t="s">
         <v>778</v>
       </c>
-      <c r="D91" s="383" t="s">
+      <c r="D91" s="365" t="s">
         <v>806</v>
       </c>
       <c r="E91" s="136"/>
@@ -27339,7 +27309,7 @@
       <c r="S91" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="T91" s="429" t="s">
+      <c r="T91" s="409" t="s">
         <v>811</v>
       </c>
       <c r="U91" s="28"/>
@@ -27367,7 +27337,7 @@
       <c r="AQ91" s="32"/>
     </row>
     <row r="92" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A92" s="462" t="s">
+      <c r="A92" s="441" t="s">
         <v>812</v>
       </c>
       <c r="B92" s="14" t="s">
@@ -27438,7 +27408,7 @@
       <c r="AQ92" s="32"/>
     </row>
     <row r="93" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A93" s="462" t="s">
+      <c r="A93" s="441" t="s">
         <v>818</v>
       </c>
       <c r="B93" s="32" t="s">
@@ -27515,7 +27485,7 @@
       <c r="AQ93" s="32"/>
     </row>
     <row r="94" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A94" s="462" t="s">
+      <c r="A94" s="441" t="s">
         <v>829</v>
       </c>
       <c r="B94" s="32" t="s">
@@ -27582,7 +27552,7 @@
       <c r="AQ94" s="32"/>
     </row>
     <row r="95" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A95" s="462" t="s">
+      <c r="A95" s="441" t="s">
         <v>836</v>
       </c>
       <c r="B95" s="32" t="s">
@@ -27649,7 +27619,7 @@
       <c r="AQ95" s="32"/>
     </row>
     <row r="96" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A96" s="462" t="s">
+      <c r="A96" s="441" t="s">
         <v>3880</v>
       </c>
       <c r="B96" s="14" t="s">
@@ -27716,7 +27686,7 @@
       <c r="AQ96" s="32"/>
     </row>
     <row r="97" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A97" s="462" t="s">
+      <c r="A97" s="441" t="s">
         <v>3879</v>
       </c>
       <c r="B97" s="32" t="s">
@@ -27783,7 +27753,7 @@
       <c r="AQ97" s="32"/>
     </row>
     <row r="98" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A98" s="462" t="s">
+      <c r="A98" s="441" t="s">
         <v>854</v>
       </c>
       <c r="B98" s="32" t="s">
@@ -27850,7 +27820,7 @@
       <c r="AQ98" s="32"/>
     </row>
     <row r="99" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A99" s="462" t="s">
+      <c r="A99" s="441" t="s">
         <v>860</v>
       </c>
       <c r="B99" s="14" t="s">
@@ -27919,7 +27889,7 @@
       <c r="AQ99" s="32"/>
     </row>
     <row r="100" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A100" s="462" t="s">
+      <c r="A100" s="441" t="s">
         <v>3878</v>
       </c>
       <c r="B100" s="32" t="s">
@@ -27996,7 +27966,7 @@
       <c r="AQ100" s="32"/>
     </row>
     <row r="101" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A101" s="462" t="s">
+      <c r="A101" s="441" t="s">
         <v>878</v>
       </c>
       <c r="B101" s="14" t="s">
@@ -28065,8 +28035,8 @@
       <c r="AQ101" s="32"/>
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A102" s="462" t="s">
-        <v>3984</v>
+      <c r="A102" s="441" t="s">
+        <v>3978</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>886</v>
@@ -28132,7 +28102,7 @@
       <c r="AQ102" s="32"/>
     </row>
     <row r="103" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A103" s="462" t="s">
+      <c r="A103" s="441" t="s">
         <v>891</v>
       </c>
       <c r="B103" s="32" t="s">
@@ -28211,7 +28181,7 @@
       <c r="AQ103" s="32"/>
     </row>
     <row r="104" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A104" s="462" t="s">
+      <c r="A104" s="441" t="s">
         <v>3877</v>
       </c>
       <c r="B104" s="32" t="s">
@@ -28282,7 +28252,7 @@
       <c r="AQ104" s="32"/>
     </row>
     <row r="105" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A105" s="462" t="s">
+      <c r="A105" s="441" t="s">
         <v>910</v>
       </c>
       <c r="B105" s="14" t="s">
@@ -28357,7 +28327,7 @@
       <c r="AQ105" s="32"/>
     </row>
     <row r="106" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A106" s="462" t="s">
+      <c r="A106" s="441" t="s">
         <v>920</v>
       </c>
       <c r="B106" s="14" t="s">
@@ -28424,7 +28394,7 @@
       <c r="AQ106" s="32"/>
     </row>
     <row r="107" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A107" s="462" t="s">
+      <c r="A107" s="441" t="s">
         <v>3876</v>
       </c>
       <c r="B107" s="32" t="s">
@@ -28507,7 +28477,7 @@
       <c r="AQ107" s="32"/>
     </row>
     <row r="108" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A108" s="462" t="s">
+      <c r="A108" s="441" t="s">
         <v>3875</v>
       </c>
       <c r="B108" s="32" t="s">
@@ -28578,7 +28548,7 @@
       <c r="AQ108" s="32"/>
     </row>
     <row r="109" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A109" s="462" t="s">
+      <c r="A109" s="441" t="s">
         <v>945</v>
       </c>
       <c r="B109" s="32" t="s">
@@ -28643,7 +28613,7 @@
       <c r="AQ109" s="32"/>
     </row>
     <row r="110" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A110" s="462" t="s">
+      <c r="A110" s="441" t="s">
         <v>951</v>
       </c>
       <c r="B110" s="14" t="s">
@@ -28714,7 +28684,7 @@
       <c r="AQ110" s="32"/>
     </row>
     <row r="111" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A111" s="462" t="s">
+      <c r="A111" s="441" t="s">
         <v>3874</v>
       </c>
       <c r="B111" s="32" t="s">
@@ -28781,7 +28751,7 @@
       <c r="AQ111" s="32"/>
     </row>
     <row r="112" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A112" s="463" t="s">
+      <c r="A112" s="442" t="s">
         <v>964</v>
       </c>
       <c r="B112" s="32" t="s">
@@ -28850,7 +28820,7 @@
       <c r="AQ112" s="32"/>
     </row>
     <row r="113" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A113" s="462" t="s">
+      <c r="A113" s="441" t="s">
         <v>972</v>
       </c>
       <c r="B113" s="32" t="s">
@@ -28927,8 +28897,8 @@
       <c r="AQ113" s="32"/>
     </row>
     <row r="114" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A114" s="462" t="s">
-        <v>3983</v>
+      <c r="A114" s="441" t="s">
+        <v>3977</v>
       </c>
       <c r="B114" s="32" t="s">
         <v>430</v>
@@ -29004,7 +28974,7 @@
       <c r="AQ114" s="32"/>
     </row>
     <row r="115" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A115" s="462" t="s">
+      <c r="A115" s="441" t="s">
         <v>994</v>
       </c>
       <c r="B115" s="32" t="s">
@@ -29073,7 +29043,7 @@
       <c r="AQ115" s="32"/>
     </row>
     <row r="116" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A116" s="462" t="s">
+      <c r="A116" s="441" t="s">
         <v>1001</v>
       </c>
       <c r="B116" s="14" t="s">
@@ -29140,7 +29110,7 @@
       <c r="AQ116" s="32"/>
     </row>
     <row r="117" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A117" s="462" t="s">
+      <c r="A117" s="441" t="s">
         <v>1009</v>
       </c>
       <c r="B117" s="14" t="s">
@@ -29215,7 +29185,7 @@
       <c r="AQ117" s="32"/>
     </row>
     <row r="118" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A118" s="475" t="s">
+      <c r="A118" s="454" t="s">
         <v>1019</v>
       </c>
       <c r="B118" s="14" t="s">
@@ -29290,7 +29260,7 @@
       <c r="AQ118" s="32"/>
     </row>
     <row r="119" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A119" s="462" t="s">
+      <c r="A119" s="441" t="s">
         <v>3873</v>
       </c>
       <c r="B119" s="14" t="s">
@@ -29363,7 +29333,7 @@
       <c r="AQ119" s="32"/>
     </row>
     <row r="120" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A120" s="462" t="s">
+      <c r="A120" s="441" t="s">
         <v>1040</v>
       </c>
       <c r="B120" s="32" t="s">
@@ -29395,7 +29365,7 @@
       <c r="N120" s="54" t="s">
         <v>1045</v>
       </c>
-      <c r="O120" s="413"/>
+      <c r="O120" s="394"/>
       <c r="P120" s="112"/>
       <c r="Q120" s="56"/>
       <c r="R120" s="39" t="s">
@@ -29430,7 +29400,7 @@
       <c r="AQ120" s="32"/>
     </row>
     <row r="121" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A121" s="462" t="s">
+      <c r="A121" s="441" t="s">
         <v>1046</v>
       </c>
       <c r="B121" s="14" t="s">
@@ -29459,10 +29429,10 @@
       <c r="M121" s="53" t="s">
         <v>859</v>
       </c>
-      <c r="N121" s="413" t="s">
+      <c r="N121" s="394" t="s">
         <v>37</v>
       </c>
-      <c r="O121" s="413"/>
+      <c r="O121" s="394"/>
       <c r="P121" s="59" t="s">
         <v>1050</v>
       </c>
@@ -29501,8 +29471,8 @@
       <c r="AQ121" s="32"/>
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A122" s="475" t="s">
-        <v>3982</v>
+      <c r="A122" s="454" t="s">
+        <v>3976</v>
       </c>
       <c r="B122" s="51" t="s">
         <v>43</v>
@@ -29535,7 +29505,7 @@
       <c r="N122" s="141" t="s">
         <v>1058</v>
       </c>
-      <c r="O122" s="417"/>
+      <c r="O122" s="398"/>
       <c r="P122" s="59"/>
       <c r="Q122" s="75"/>
       <c r="R122" s="142" t="s">
@@ -29554,7 +29524,7 @@
       <c r="W122" s="29"/>
       <c r="X122" s="29"/>
       <c r="Y122" s="30" t="s">
-        <v>3970</v>
+        <v>3964</v>
       </c>
       <c r="Z122" s="30"/>
       <c r="AA122" s="30"/>
@@ -29580,7 +29550,7 @@
       <c r="AQ122" s="21"/>
     </row>
     <row r="123" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A123" s="462" t="s">
+      <c r="A123" s="441" t="s">
         <v>1064</v>
       </c>
       <c r="B123" s="33" t="s">
@@ -29651,7 +29621,7 @@
       <c r="AQ123" s="32"/>
     </row>
     <row r="124" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A124" s="462" t="s">
+      <c r="A124" s="441" t="s">
         <v>1074</v>
       </c>
       <c r="B124" s="33" t="s">
@@ -29718,7 +29688,7 @@
       <c r="AQ124" s="32"/>
     </row>
     <row r="125" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A125" s="462" t="s">
+      <c r="A125" s="441" t="s">
         <v>1079</v>
       </c>
       <c r="B125" s="33" t="s">
@@ -29805,7 +29775,7 @@
       <c r="AQ125" s="32"/>
     </row>
     <row r="126" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A126" s="462" t="s">
+      <c r="A126" s="441" t="s">
         <v>1094</v>
       </c>
       <c r="B126" s="14" t="s">
@@ -29872,10 +29842,10 @@
       <c r="AQ126" s="32"/>
     </row>
     <row r="127" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A127" s="475" t="s">
+      <c r="A127" s="454" t="s">
         <v>1102</v>
       </c>
-      <c r="B127" s="377" t="s">
+      <c r="B127" s="359" t="s">
         <v>1103</v>
       </c>
       <c r="C127" s="247" t="s">
@@ -29949,7 +29919,7 @@
       <c r="AQ127" s="21"/>
     </row>
     <row r="128" spans="1:43" ht="70.5" customHeight="1">
-      <c r="A128" s="462" t="s">
+      <c r="A128" s="441" t="s">
         <v>1112</v>
       </c>
       <c r="B128" s="145" t="s">
@@ -30018,7 +29988,7 @@
       <c r="AQ128" s="32"/>
     </row>
     <row r="129" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A129" s="475" t="s">
+      <c r="A129" s="454" t="s">
         <v>3872</v>
       </c>
       <c r="B129" s="32" t="s">
@@ -30050,14 +30020,14 @@
       <c r="N129" s="54" t="s">
         <v>1123</v>
       </c>
-      <c r="O129" s="413"/>
+      <c r="O129" s="394"/>
       <c r="P129" s="59" t="s">
         <v>1124</v>
       </c>
       <c r="Q129" s="56" t="s">
         <v>1125</v>
       </c>
-      <c r="R129" s="415" t="s">
+      <c r="R129" s="396" t="s">
         <v>1126</v>
       </c>
       <c r="S129" s="32" t="s">
@@ -30089,7 +30059,7 @@
       <c r="AQ129" s="32"/>
     </row>
     <row r="130" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A130" s="462" t="s">
+      <c r="A130" s="441" t="s">
         <v>3871</v>
       </c>
       <c r="B130" s="14" t="s">
@@ -30115,13 +30085,13 @@
       <c r="L130" s="22" t="s">
         <v>1131</v>
       </c>
-      <c r="M130" s="404" t="s">
+      <c r="M130" s="385" t="s">
         <v>859</v>
       </c>
       <c r="N130" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="O130" s="413"/>
+      <c r="O130" s="394"/>
       <c r="P130" s="59" t="s">
         <v>1132</v>
       </c>
@@ -30162,7 +30132,7 @@
       <c r="AQ130" s="286"/>
     </row>
     <row r="131" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A131" s="462" t="s">
+      <c r="A131" s="441" t="s">
         <v>3870</v>
       </c>
       <c r="B131" s="33" t="s">
@@ -30241,7 +30211,7 @@
       <c r="AQ131" s="286"/>
     </row>
     <row r="132" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A132" s="478" t="s">
+      <c r="A132" s="457" t="s">
         <v>1144</v>
       </c>
       <c r="B132" s="14" t="s">
@@ -30308,7 +30278,7 @@
       <c r="AQ132" s="286"/>
     </row>
     <row r="133" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A133" s="478" t="s">
+      <c r="A133" s="457" t="s">
         <v>1147</v>
       </c>
       <c r="B133" s="14" t="s">
@@ -30340,7 +30310,7 @@
       <c r="N133" s="54" t="s">
         <v>1153</v>
       </c>
-      <c r="O133" s="413"/>
+      <c r="O133" s="394"/>
       <c r="P133" s="112"/>
       <c r="Q133" s="56"/>
       <c r="R133" s="96" t="s">
@@ -30375,7 +30345,7 @@
       <c r="AQ133" s="286"/>
     </row>
     <row r="134" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A134" s="478" t="s">
+      <c r="A134" s="457" t="s">
         <v>1154</v>
       </c>
       <c r="B134" s="14" t="s">
@@ -30448,7 +30418,7 @@
       <c r="AQ134" s="286"/>
     </row>
     <row r="135" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A135" s="478" t="s">
+      <c r="A135" s="457" t="s">
         <v>1161</v>
       </c>
       <c r="B135" s="14" t="s">
@@ -30529,7 +30499,7 @@
       <c r="AQ135" s="32"/>
     </row>
     <row r="136" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A136" s="478" t="s">
+      <c r="A136" s="457" t="s">
         <v>1172</v>
       </c>
       <c r="B136" s="32" t="s">
@@ -30598,7 +30568,7 @@
       <c r="AQ136" s="32"/>
     </row>
     <row r="137" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A137" s="477" t="s">
+      <c r="A137" s="456" t="s">
         <v>3869</v>
       </c>
       <c r="B137" s="14" t="s">
@@ -30630,7 +30600,7 @@
       <c r="N137" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="O137" s="413"/>
+      <c r="O137" s="394"/>
       <c r="P137" s="112"/>
       <c r="Q137" s="56"/>
       <c r="R137" s="296" t="s">
@@ -30667,7 +30637,7 @@
       <c r="AQ137" s="32"/>
     </row>
     <row r="138" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A138" s="478" t="s">
+      <c r="A138" s="457" t="s">
         <v>1184</v>
       </c>
       <c r="B138" s="33" t="s">
@@ -30738,7 +30708,7 @@
       <c r="AQ138" s="32"/>
     </row>
     <row r="139" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A139" s="477" t="s">
+      <c r="A139" s="456" t="s">
         <v>3868</v>
       </c>
       <c r="B139" s="33" t="s">
@@ -30807,7 +30777,7 @@
       <c r="AQ139" s="32"/>
     </row>
     <row r="140" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A140" s="478" t="s">
+      <c r="A140" s="457" t="s">
         <v>1197</v>
       </c>
       <c r="B140" s="14" t="s">
@@ -30874,7 +30844,7 @@
       <c r="AQ140" s="32"/>
     </row>
     <row r="141" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A141" s="478" t="s">
+      <c r="A141" s="457" t="s">
         <v>1204</v>
       </c>
       <c r="B141" s="51" t="s">
@@ -30953,7 +30923,7 @@
       <c r="AQ141" s="21"/>
     </row>
     <row r="142" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A142" s="478" t="s">
+      <c r="A142" s="457" t="s">
         <v>1216</v>
       </c>
       <c r="B142" s="32" t="s">
@@ -31020,7 +30990,7 @@
       <c r="AQ142" s="32"/>
     </row>
     <row r="143" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A143" s="478" t="s">
+      <c r="A143" s="457" t="s">
         <v>1221</v>
       </c>
       <c r="B143" s="21" t="s">
@@ -31064,7 +31034,7 @@
         <v>41</v>
       </c>
       <c r="T143" s="21" t="s">
-        <v>4019</v>
+        <v>4013</v>
       </c>
       <c r="U143" s="28"/>
       <c r="V143" s="28"/>
@@ -31091,7 +31061,7 @@
       <c r="AQ143" s="21"/>
     </row>
     <row r="144" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A144" s="478" t="s">
+      <c r="A144" s="457" t="s">
         <v>1228</v>
       </c>
       <c r="B144" s="21" t="s">
@@ -31135,7 +31105,7 @@
         <v>41</v>
       </c>
       <c r="T144" s="21" t="s">
-        <v>4020</v>
+        <v>4014</v>
       </c>
       <c r="U144" s="28"/>
       <c r="V144" s="28"/>
@@ -31162,7 +31132,7 @@
       <c r="AQ144" s="21"/>
     </row>
     <row r="145" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A145" s="478" t="s">
+      <c r="A145" s="457" t="s">
         <v>1234</v>
       </c>
       <c r="B145" s="14" t="s">
@@ -31320,7 +31290,7 @@
       <c r="AQ146" s="21"/>
     </row>
     <row r="147" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A147" s="475" t="s">
+      <c r="A147" s="454" t="s">
         <v>1251</v>
       </c>
       <c r="B147" s="21" t="s">
@@ -31389,7 +31359,7 @@
       <c r="AQ147" s="21"/>
     </row>
     <row r="148" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A148" s="475" t="s">
+      <c r="A148" s="454" t="s">
         <v>1256</v>
       </c>
       <c r="B148" s="51" t="s">
@@ -31468,7 +31438,7 @@
       <c r="AQ148" s="21"/>
     </row>
     <row r="149" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A149" s="475" t="s">
+      <c r="A149" s="454" t="s">
         <v>1265</v>
       </c>
       <c r="B149" s="51" t="s">
@@ -31547,7 +31517,7 @@
       <c r="AQ149" s="21"/>
     </row>
     <row r="150" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A150" s="462" t="s">
+      <c r="A150" s="441" t="s">
         <v>1274</v>
       </c>
       <c r="B150" s="32" t="s">
@@ -31614,7 +31584,7 @@
       <c r="AQ150" s="32"/>
     </row>
     <row r="151" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A151" s="462" t="s">
+      <c r="A151" s="441" t="s">
         <v>1278</v>
       </c>
       <c r="B151" s="14" t="s">
@@ -31689,7 +31659,7 @@
       <c r="AQ151" s="32"/>
     </row>
     <row r="152" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A152" s="462" t="s">
+      <c r="A152" s="441" t="s">
         <v>1288</v>
       </c>
       <c r="B152" s="32" t="s">
@@ -31756,7 +31726,7 @@
       <c r="AQ152" s="32"/>
     </row>
     <row r="153" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A153" s="462" t="s">
+      <c r="A153" s="441" t="s">
         <v>1294</v>
       </c>
       <c r="B153" s="95" t="s">
@@ -31823,7 +31793,7 @@
       <c r="AQ153" s="32"/>
     </row>
     <row r="154" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A154" s="462" t="s">
+      <c r="A154" s="441" t="s">
         <v>1300</v>
       </c>
       <c r="B154" s="95" t="s">
@@ -31894,7 +31864,7 @@
       <c r="AQ154" s="32"/>
     </row>
     <row r="155" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A155" s="475" t="s">
+      <c r="A155" s="454" t="s">
         <v>1309</v>
       </c>
       <c r="B155" s="21" t="s">
@@ -31975,7 +31945,7 @@
       <c r="AQ155" s="21"/>
     </row>
     <row r="156" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A156" s="475" t="s">
+      <c r="A156" s="454" t="s">
         <v>1322</v>
       </c>
       <c r="B156" s="21" t="s">
@@ -32056,7 +32026,7 @@
       <c r="AQ156" s="21"/>
     </row>
     <row r="157" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A157" s="475" t="s">
+      <c r="A157" s="454" t="s">
         <v>1333</v>
       </c>
       <c r="B157" s="51" t="s">
@@ -32129,7 +32099,7 @@
       <c r="AQ157" s="21"/>
     </row>
     <row r="158" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A158" s="475" t="s">
+      <c r="A158" s="454" t="s">
         <v>1339</v>
       </c>
       <c r="B158" s="51" t="s">
@@ -32198,7 +32168,7 @@
       <c r="AQ158" s="21"/>
     </row>
     <row r="159" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A159" s="462" t="s">
+      <c r="A159" s="441" t="s">
         <v>1347</v>
       </c>
       <c r="B159" s="32" t="s">
@@ -32265,7 +32235,7 @@
       <c r="AQ159" s="32"/>
     </row>
     <row r="160" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A160" s="475" t="s">
+      <c r="A160" s="454" t="s">
         <v>1353</v>
       </c>
       <c r="B160" s="51" t="s">
@@ -32340,7 +32310,7 @@
       <c r="AQ160" s="21"/>
     </row>
     <row r="161" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A161" s="475" t="s">
+      <c r="A161" s="454" t="s">
         <v>1362</v>
       </c>
       <c r="B161" s="51" t="s">
@@ -32419,7 +32389,7 @@
       <c r="AQ161" s="21"/>
     </row>
     <row r="162" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A162" s="462" t="s">
+      <c r="A162" s="441" t="s">
         <v>1370</v>
       </c>
       <c r="B162" s="32" t="s">
@@ -32486,7 +32456,7 @@
       <c r="AQ162" s="32"/>
     </row>
     <row r="163" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A163" s="462" t="s">
+      <c r="A163" s="441" t="s">
         <v>1377</v>
       </c>
       <c r="B163" s="14" t="s">
@@ -32557,7 +32527,7 @@
       <c r="AQ163" s="32"/>
     </row>
     <row r="164" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A164" s="462" t="s">
+      <c r="A164" s="441" t="s">
         <v>1385</v>
       </c>
       <c r="B164" s="14" t="s">
@@ -32634,7 +32604,7 @@
       <c r="AQ164" s="32"/>
     </row>
     <row r="165" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A165" s="462" t="s">
+      <c r="A165" s="441" t="s">
         <v>1396</v>
       </c>
       <c r="B165" s="32" t="s">
@@ -32701,7 +32671,7 @@
       <c r="AQ165" s="32"/>
     </row>
     <row r="166" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A166" s="475" t="s">
+      <c r="A166" s="454" t="s">
         <v>1402</v>
       </c>
       <c r="B166" s="51" t="s">
@@ -32780,7 +32750,7 @@
       <c r="AQ166" s="21"/>
     </row>
     <row r="167" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A167" s="475" t="s">
+      <c r="A167" s="454" t="s">
         <v>1410</v>
       </c>
       <c r="B167" s="51" t="s">
@@ -32808,7 +32778,7 @@
         <v>176</v>
       </c>
       <c r="N167" s="134" t="s">
-        <v>3988</v>
+        <v>3982</v>
       </c>
       <c r="O167" s="134"/>
       <c r="P167" s="153" t="s">
@@ -32818,7 +32788,7 @@
         <v>1415</v>
       </c>
       <c r="R167" s="39" t="s">
-        <v>3989</v>
+        <v>3983</v>
       </c>
       <c r="S167" s="21" t="s">
         <v>41</v>
@@ -32851,7 +32821,7 @@
       <c r="AQ167" s="21"/>
     </row>
     <row r="168" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A168" s="475" t="s">
+      <c r="A168" s="454" t="s">
         <v>1417</v>
       </c>
       <c r="B168" s="51" t="s">
@@ -32930,7 +32900,7 @@
       <c r="AQ168" s="21"/>
     </row>
     <row r="169" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A169" s="462" t="s">
+      <c r="A169" s="441" t="s">
         <v>3867</v>
       </c>
       <c r="B169" s="33" t="s">
@@ -33005,7 +32975,7 @@
       <c r="AQ169" s="32"/>
     </row>
     <row r="170" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A170" s="462" t="s">
+      <c r="A170" s="441" t="s">
         <v>1435</v>
       </c>
       <c r="B170" s="32" t="s">
@@ -33072,7 +33042,7 @@
       <c r="AQ170" s="32"/>
     </row>
     <row r="171" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A171" s="462" t="s">
+      <c r="A171" s="441" t="s">
         <v>1443</v>
       </c>
       <c r="B171" s="33" t="s">
@@ -33141,7 +33111,7 @@
       <c r="AQ171" s="32"/>
     </row>
     <row r="172" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A172" s="462" t="s">
+      <c r="A172" s="441" t="s">
         <v>1451</v>
       </c>
       <c r="B172" s="14" t="s">
@@ -33216,7 +33186,7 @@
       <c r="AQ172" s="32"/>
     </row>
     <row r="173" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A173" s="475" t="s">
+      <c r="A173" s="454" t="s">
         <v>1460</v>
       </c>
       <c r="B173" s="15" t="s">
@@ -33295,7 +33265,7 @@
       <c r="AQ173" s="21"/>
     </row>
     <row r="174" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A174" s="463" t="s">
+      <c r="A174" s="442" t="s">
         <v>1471</v>
       </c>
       <c r="B174" s="14" t="s">
@@ -33325,7 +33295,7 @@
       <c r="N174" s="54" t="s">
         <v>1475</v>
       </c>
-      <c r="O174" s="413"/>
+      <c r="O174" s="394"/>
       <c r="P174" s="112"/>
       <c r="Q174" s="121"/>
       <c r="R174" s="39" t="s">
@@ -33360,7 +33330,7 @@
       <c r="AQ174" s="32"/>
     </row>
     <row r="175" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A175" s="462" t="s">
+      <c r="A175" s="441" t="s">
         <v>3866</v>
       </c>
       <c r="B175" s="33" t="s">
@@ -33429,7 +33399,7 @@
       <c r="AQ175" s="32"/>
     </row>
     <row r="176" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A176" s="462" t="s">
+      <c r="A176" s="441" t="s">
         <v>3865</v>
       </c>
       <c r="B176" s="33" t="s">
@@ -33495,8 +33465,8 @@
       <c r="AP176" s="32"/>
       <c r="AQ176" s="32"/>
     </row>
-    <row r="177" spans="1:43" s="368" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A177" s="475" t="s">
+    <row r="177" spans="1:43" s="350" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A177" s="454" t="s">
         <v>3864</v>
       </c>
       <c r="B177" s="15" t="s">
@@ -33562,22 +33532,22 @@
         <v>1215</v>
       </c>
       <c r="AD177" s="21"/>
-      <c r="AE177" s="363"/>
-      <c r="AF177" s="363"/>
-      <c r="AG177" s="363"/>
-      <c r="AH177" s="363"/>
-      <c r="AI177" s="363"/>
-      <c r="AJ177" s="363"/>
-      <c r="AK177" s="363"/>
-      <c r="AL177" s="363"/>
-      <c r="AM177" s="363"/>
-      <c r="AN177" s="363"/>
-      <c r="AO177" s="363"/>
-      <c r="AP177" s="363"/>
-      <c r="AQ177" s="363"/>
+      <c r="AE177" s="345"/>
+      <c r="AF177" s="345"/>
+      <c r="AG177" s="345"/>
+      <c r="AH177" s="345"/>
+      <c r="AI177" s="345"/>
+      <c r="AJ177" s="345"/>
+      <c r="AK177" s="345"/>
+      <c r="AL177" s="345"/>
+      <c r="AM177" s="345"/>
+      <c r="AN177" s="345"/>
+      <c r="AO177" s="345"/>
+      <c r="AP177" s="345"/>
+      <c r="AQ177" s="345"/>
     </row>
     <row r="178" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A178" s="473" t="s">
+      <c r="A178" s="452" t="s">
         <v>1499</v>
       </c>
       <c r="B178" s="15" t="s">
@@ -33658,7 +33628,7 @@
       <c r="AQ178" s="21"/>
     </row>
     <row r="179" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A179" s="475" t="s">
+      <c r="A179" s="454" t="s">
         <v>1509</v>
       </c>
       <c r="B179" s="15" t="s">
@@ -33733,7 +33703,7 @@
       <c r="AQ179" s="21"/>
     </row>
     <row r="180" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A180" s="473" t="s">
+      <c r="A180" s="452" t="s">
         <v>1518</v>
       </c>
       <c r="B180" s="15" t="s">
@@ -33757,7 +33727,7 @@
         <v>1523</v>
       </c>
       <c r="J180" s="98"/>
-      <c r="K180" s="403"/>
+      <c r="K180" s="384"/>
       <c r="L180" s="117" t="s">
         <v>1524</v>
       </c>
@@ -33802,7 +33772,7 @@
       <c r="AQ180" s="21"/>
     </row>
     <row r="181" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A181" s="475" t="s">
+      <c r="A181" s="454" t="s">
         <v>1525</v>
       </c>
       <c r="B181" s="15" t="s">
@@ -33881,7 +33851,7 @@
       <c r="AQ181" s="21"/>
     </row>
     <row r="182" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A182" s="462" t="s">
+      <c r="A182" s="441" t="s">
         <v>1534</v>
       </c>
       <c r="B182" s="15" t="s">
@@ -33954,7 +33924,7 @@
       <c r="AQ182" s="32"/>
     </row>
     <row r="183" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A183" s="462" t="s">
+      <c r="A183" s="441" t="s">
         <v>3863</v>
       </c>
       <c r="B183" s="33" t="s">
@@ -34023,7 +33993,7 @@
       <c r="AQ183" s="32"/>
     </row>
     <row r="184" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A184" s="462" t="s">
+      <c r="A184" s="441" t="s">
         <v>3862</v>
       </c>
       <c r="B184" s="33" t="s">
@@ -34092,7 +34062,7 @@
       <c r="AQ184" s="32"/>
     </row>
     <row r="185" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A185" s="475" t="s">
+      <c r="A185" s="454" t="s">
         <v>1556</v>
       </c>
       <c r="B185" s="15" t="s">
@@ -34171,7 +34141,7 @@
       <c r="AQ185" s="21"/>
     </row>
     <row r="186" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A186" s="475" t="s">
+      <c r="A186" s="454" t="s">
         <v>1566</v>
       </c>
       <c r="B186" s="15" t="s">
@@ -34250,7 +34220,7 @@
       <c r="AQ186" s="21"/>
     </row>
     <row r="187" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A187" s="475" t="s">
+      <c r="A187" s="454" t="s">
         <v>1573</v>
       </c>
       <c r="B187" s="15" t="s">
@@ -34319,7 +34289,7 @@
       <c r="AQ187" s="21"/>
     </row>
     <row r="188" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A188" s="475" t="s">
+      <c r="A188" s="454" t="s">
         <v>1581</v>
       </c>
       <c r="B188" s="15" t="s">
@@ -34388,7 +34358,7 @@
       <c r="AQ188" s="21"/>
     </row>
     <row r="189" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A189" s="475" t="s">
+      <c r="A189" s="454" t="s">
         <v>1588</v>
       </c>
       <c r="B189" s="51" t="s">
@@ -34457,7 +34427,7 @@
       <c r="AQ189" s="21"/>
     </row>
     <row r="190" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A190" s="475" t="s">
+      <c r="A190" s="454" t="s">
         <v>3861</v>
       </c>
       <c r="B190" s="15" t="s">
@@ -34524,7 +34494,7 @@
       <c r="AQ190" s="21"/>
     </row>
     <row r="191" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A191" s="462" t="s">
+      <c r="A191" s="441" t="s">
         <v>1599</v>
       </c>
       <c r="B191" s="33" t="s">
@@ -34599,7 +34569,7 @@
       <c r="AQ191" s="32"/>
     </row>
     <row r="192" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A192" s="462" t="s">
+      <c r="A192" s="441" t="s">
         <v>1609</v>
       </c>
       <c r="B192" s="33" t="s">
@@ -34668,7 +34638,7 @@
       <c r="AQ192" s="32"/>
     </row>
     <row r="193" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A193" s="462" t="s">
+      <c r="A193" s="441" t="s">
         <v>3860</v>
       </c>
       <c r="B193" s="33" t="s">
@@ -34741,7 +34711,7 @@
       <c r="AQ193" s="32"/>
     </row>
     <row r="194" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A194" s="473" t="s">
+      <c r="A194" s="452" t="s">
         <v>1624</v>
       </c>
       <c r="B194" s="51" t="s">
@@ -34785,7 +34755,7 @@
         <v>41</v>
       </c>
       <c r="T194" s="21" t="s">
-        <v>4017</v>
+        <v>4011</v>
       </c>
       <c r="U194" s="28" t="s">
         <v>1060</v>
@@ -34822,7 +34792,7 @@
       <c r="AQ194" s="21"/>
     </row>
     <row r="195" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A195" s="463" t="s">
+      <c r="A195" s="442" t="s">
         <v>1635</v>
       </c>
       <c r="B195" s="14" t="s">
@@ -34866,7 +34836,7 @@
         <v>41</v>
       </c>
       <c r="T195" s="21" t="s">
-        <v>4018</v>
+        <v>4012</v>
       </c>
       <c r="U195" s="28" t="s">
         <v>1060</v>
@@ -34903,7 +34873,7 @@
       <c r="AQ195" s="32"/>
     </row>
     <row r="196" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A196" s="462" t="s">
+      <c r="A196" s="441" t="s">
         <v>1645</v>
       </c>
       <c r="B196" s="14" t="s">
@@ -34970,7 +34940,7 @@
       <c r="AQ196" s="32"/>
     </row>
     <row r="197" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A197" s="462" t="s">
+      <c r="A197" s="441" t="s">
         <v>1652</v>
       </c>
       <c r="B197" s="33" t="s">
@@ -35037,7 +35007,7 @@
       <c r="AQ197" s="32"/>
     </row>
     <row r="198" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A198" s="462" t="s">
+      <c r="A198" s="441" t="s">
         <v>1659</v>
       </c>
       <c r="B198" s="14" t="s">
@@ -35104,7 +35074,7 @@
       <c r="AQ198" s="32"/>
     </row>
     <row r="199" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A199" s="462" t="s">
+      <c r="A199" s="441" t="s">
         <v>1666</v>
       </c>
       <c r="B199" s="14" t="s">
@@ -35151,7 +35121,7 @@
       <c r="U199" s="105" t="s">
         <v>1060</v>
       </c>
-      <c r="V199" s="433" t="s">
+      <c r="V199" s="413" t="s">
         <v>1672</v>
       </c>
       <c r="W199" s="29"/>
@@ -35183,7 +35153,7 @@
       <c r="AQ199" s="32"/>
     </row>
     <row r="200" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A200" s="462" t="s">
+      <c r="A200" s="441" t="s">
         <v>1674</v>
       </c>
       <c r="B200" s="33" t="s">
@@ -35252,7 +35222,7 @@
       <c r="AQ200" s="32"/>
     </row>
     <row r="201" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A201" s="462" t="s">
+      <c r="A201" s="441" t="s">
         <v>1681</v>
       </c>
       <c r="B201" s="32" t="s">
@@ -35325,7 +35295,7 @@
       <c r="AQ201" s="32"/>
     </row>
     <row r="202" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A202" s="462" t="s">
+      <c r="A202" s="441" t="s">
         <v>1691</v>
       </c>
       <c r="B202" s="14" t="s">
@@ -35406,7 +35376,7 @@
       <c r="AQ202" s="32"/>
     </row>
     <row r="203" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A203" s="462" t="s">
+      <c r="A203" s="441" t="s">
         <v>1699</v>
       </c>
       <c r="B203" s="14" t="s">
@@ -35477,7 +35447,7 @@
       <c r="AQ203" s="32"/>
     </row>
     <row r="204" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A204" s="462" t="s">
+      <c r="A204" s="441" t="s">
         <v>1706</v>
       </c>
       <c r="B204" s="33" t="s">
@@ -35546,7 +35516,7 @@
       <c r="AQ204" s="32"/>
     </row>
     <row r="205" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A205" s="462" t="s">
+      <c r="A205" s="441" t="s">
         <v>3859</v>
       </c>
       <c r="B205" s="33" t="s">
@@ -35615,7 +35585,7 @@
       <c r="AQ205" s="32"/>
     </row>
     <row r="206" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A206" s="462" t="s">
+      <c r="A206" s="441" t="s">
         <v>1719</v>
       </c>
       <c r="B206" s="14" t="s">
@@ -35692,7 +35662,7 @@
       <c r="AQ206" s="32"/>
     </row>
     <row r="207" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A207" s="462" t="s">
+      <c r="A207" s="441" t="s">
         <v>3858</v>
       </c>
       <c r="B207" s="14" t="s">
@@ -35779,7 +35749,7 @@
       <c r="AQ207" s="32"/>
     </row>
     <row r="208" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A208" s="462" t="s">
+      <c r="A208" s="441" t="s">
         <v>1742</v>
       </c>
       <c r="B208" s="14" t="s">
@@ -35852,7 +35822,7 @@
       <c r="AQ208" s="32"/>
     </row>
     <row r="209" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A209" s="462" t="s">
+      <c r="A209" s="441" t="s">
         <v>1750</v>
       </c>
       <c r="B209" s="14" t="s">
@@ -35931,7 +35901,7 @@
       <c r="AQ209" s="32"/>
     </row>
     <row r="210" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A210" s="462" t="s">
+      <c r="A210" s="441" t="s">
         <v>1759</v>
       </c>
       <c r="B210" s="14" t="s">
@@ -36010,7 +35980,7 @@
       <c r="AQ210" s="32"/>
     </row>
     <row r="211" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A211" s="462" t="s">
+      <c r="A211" s="441" t="s">
         <v>3857</v>
       </c>
       <c r="B211" s="14" t="s">
@@ -36089,7 +36059,7 @@
       <c r="AQ211" s="32"/>
     </row>
     <row r="212" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A212" s="462" t="s">
+      <c r="A212" s="441" t="s">
         <v>1774</v>
       </c>
       <c r="B212" s="14" t="s">
@@ -36172,7 +36142,7 @@
       <c r="AQ212" s="32"/>
     </row>
     <row r="213" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A213" s="462" t="s">
+      <c r="A213" s="441" t="s">
         <v>3856</v>
       </c>
       <c r="B213" s="14" t="s">
@@ -36243,7 +36213,7 @@
       <c r="AQ213" s="32"/>
     </row>
     <row r="214" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A214" s="462" t="s">
+      <c r="A214" s="441" t="s">
         <v>1791</v>
       </c>
       <c r="B214" s="14" t="s">
@@ -36324,7 +36294,7 @@
       <c r="AQ214" s="32"/>
     </row>
     <row r="215" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A215" s="462" t="s">
+      <c r="A215" s="441" t="s">
         <v>1800</v>
       </c>
       <c r="B215" s="14" t="s">
@@ -36403,7 +36373,7 @@
       <c r="AQ215" s="32"/>
     </row>
     <row r="216" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A216" s="462" t="s">
+      <c r="A216" s="441" t="s">
         <v>1809</v>
       </c>
       <c r="B216" s="14" t="s">
@@ -36470,17 +36440,17 @@
       <c r="AQ216" s="32"/>
     </row>
     <row r="217" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A217" s="462" t="s">
+      <c r="A217" s="441" t="s">
         <v>1816</v>
       </c>
       <c r="B217" s="14" t="s">
         <v>1002</v>
       </c>
-      <c r="C217" s="461" t="s">
-        <v>4022</v>
+      <c r="C217" s="440" t="s">
+        <v>4016</v>
       </c>
       <c r="D217" s="232" t="s">
-        <v>4021</v>
+        <v>4015</v>
       </c>
       <c r="E217" s="58"/>
       <c r="F217" s="32" t="s">
@@ -36507,7 +36477,7 @@
       <c r="O217" s="54"/>
       <c r="P217" s="55"/>
       <c r="Q217" s="318" t="s">
-        <v>4023</v>
+        <v>4017</v>
       </c>
       <c r="R217" s="115" t="s">
         <v>383</v>
@@ -36545,14 +36515,14 @@
       <c r="AQ217" s="32"/>
     </row>
     <row r="218" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A218" s="462" t="s">
+      <c r="A218" s="441" t="s">
         <v>1823</v>
       </c>
       <c r="B218" s="14" t="s">
         <v>1002</v>
       </c>
       <c r="C218" s="247" t="s">
-        <v>4024</v>
+        <v>4018</v>
       </c>
       <c r="D218" s="232"/>
       <c r="E218" s="58"/>
@@ -36614,7 +36584,7 @@
       <c r="AQ218" s="32"/>
     </row>
     <row r="219" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A219" s="462" t="s">
+      <c r="A219" s="441" t="s">
         <v>1830</v>
       </c>
       <c r="B219" s="32" t="s">
@@ -36689,7 +36659,7 @@
       <c r="AQ219" s="32"/>
     </row>
     <row r="220" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A220" s="462" t="s">
+      <c r="A220" s="441" t="s">
         <v>1841</v>
       </c>
       <c r="B220" s="32" t="s">
@@ -36758,7 +36728,7 @@
       <c r="AQ220" s="32"/>
     </row>
     <row r="221" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A221" s="462" t="s">
+      <c r="A221" s="441" t="s">
         <v>1848</v>
       </c>
       <c r="B221" s="14" t="s">
@@ -36829,7 +36799,7 @@
       <c r="AQ221" s="32"/>
     </row>
     <row r="222" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A222" s="462" t="s">
+      <c r="A222" s="441" t="s">
         <v>3855</v>
       </c>
       <c r="B222" s="14" t="s">
@@ -36904,7 +36874,7 @@
       <c r="AQ222" s="32"/>
     </row>
     <row r="223" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A223" s="462" t="s">
+      <c r="A223" s="441" t="s">
         <v>1867</v>
       </c>
       <c r="B223" s="14" t="s">
@@ -36987,13 +36957,13 @@
       <c r="AQ223" s="32"/>
     </row>
     <row r="224" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A224" s="462" t="s">
+      <c r="A224" s="441" t="s">
         <v>3853</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>1908</v>
       </c>
-      <c r="C224" s="382" t="s">
+      <c r="C224" s="364" t="s">
         <v>1909</v>
       </c>
       <c r="D224" s="229"/>
@@ -37021,7 +36991,7 @@
       <c r="N224" s="65" t="s">
         <v>1915</v>
       </c>
-      <c r="O224" s="419"/>
+      <c r="O224" s="400"/>
       <c r="P224" s="59" t="s">
         <v>1916</v>
       </c>
@@ -37068,7 +37038,7 @@
       <c r="AQ224" s="32"/>
     </row>
     <row r="225" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A225" s="462" t="s">
+      <c r="A225" s="441" t="s">
         <v>3854</v>
       </c>
       <c r="B225" s="14" t="s">
@@ -37133,7 +37103,7 @@
       <c r="AQ225" s="32"/>
     </row>
     <row r="226" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A226" s="462" t="s">
+      <c r="A226" s="441" t="s">
         <v>1888</v>
       </c>
       <c r="B226" s="14" t="s">
@@ -37200,7 +37170,7 @@
       <c r="AQ226" s="32"/>
     </row>
     <row r="227" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A227" s="462" t="s">
+      <c r="A227" s="441" t="s">
         <v>1894</v>
       </c>
       <c r="B227" s="14" t="s">
@@ -37228,9 +37198,9 @@
         <v>3949</v>
       </c>
       <c r="N227" s="54" t="s">
-        <v>3996</v>
-      </c>
-      <c r="O227" s="413"/>
+        <v>3990</v>
+      </c>
+      <c r="O227" s="394"/>
       <c r="P227" s="290" t="s">
         <v>1899</v>
       </c>
@@ -37279,7 +37249,7 @@
       <c r="AQ227" s="32"/>
     </row>
     <row r="228" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A228" s="462" t="s">
+      <c r="A228" s="441" t="s">
         <v>1903</v>
       </c>
       <c r="B228" s="14" t="s">
@@ -37307,7 +37277,7 @@
         <v>3949</v>
       </c>
       <c r="N228" s="54" t="s">
-        <v>3993</v>
+        <v>3987</v>
       </c>
       <c r="O228" s="54"/>
       <c r="P228" s="290" t="s">
@@ -37358,7 +37328,7 @@
       <c r="AQ228" s="32"/>
     </row>
     <row r="229" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A229" s="462" t="s">
+      <c r="A229" s="441" t="s">
         <v>1922</v>
       </c>
       <c r="B229" s="14" t="s">
@@ -37390,7 +37360,7 @@
       <c r="N229" s="65" t="s">
         <v>1926</v>
       </c>
-      <c r="O229" s="411"/>
+      <c r="O229" s="392"/>
       <c r="P229" s="124"/>
       <c r="Q229" s="56"/>
       <c r="R229" s="306" t="s">
@@ -37427,7 +37397,7 @@
       <c r="AQ229" s="32"/>
     </row>
     <row r="230" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A230" s="462" t="s">
+      <c r="A230" s="441" t="s">
         <v>1928</v>
       </c>
       <c r="B230" s="14" t="s">
@@ -37508,7 +37478,7 @@
       <c r="AQ230" s="32"/>
     </row>
     <row r="231" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A231" s="462" t="s">
+      <c r="A231" s="441" t="s">
         <v>1938</v>
       </c>
       <c r="B231" s="14" t="s">
@@ -37540,7 +37510,7 @@
       <c r="N231" s="54" t="s">
         <v>1943</v>
       </c>
-      <c r="O231" s="413"/>
+      <c r="O231" s="394"/>
       <c r="P231" s="112"/>
       <c r="Q231" s="56"/>
       <c r="R231" s="115" t="s">
@@ -37577,7 +37547,7 @@
       <c r="AQ231" s="32"/>
     </row>
     <row r="232" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A232" s="462" t="s">
+      <c r="A232" s="441" t="s">
         <v>1945</v>
       </c>
       <c r="B232" s="14" t="s">
@@ -37652,7 +37622,7 @@
       <c r="AQ232" s="32"/>
     </row>
     <row r="233" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A233" s="462" t="s">
+      <c r="A233" s="441" t="s">
         <v>1955</v>
       </c>
       <c r="B233" s="14" t="s">
@@ -37719,7 +37689,7 @@
       <c r="AQ233" s="32"/>
     </row>
     <row r="234" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A234" s="462" t="s">
+      <c r="A234" s="441" t="s">
         <v>3852</v>
       </c>
       <c r="B234" s="14" t="s">
@@ -37730,7 +37700,7 @@
       </c>
       <c r="D234" s="232"/>
       <c r="E234" s="58"/>
-      <c r="F234" s="389" t="s">
+      <c r="F234" s="371" t="s">
         <v>1961</v>
       </c>
       <c r="G234" s="32"/>
@@ -37790,10 +37760,10 @@
       <c r="AQ234" s="32"/>
     </row>
     <row r="235" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A235" s="462" t="s">
+      <c r="A235" s="441" t="s">
         <v>1966</v>
       </c>
-      <c r="B235" s="375" t="s">
+      <c r="B235" s="357" t="s">
         <v>1002</v>
       </c>
       <c r="C235" s="247" t="s">
@@ -37875,7 +37845,7 @@
       <c r="AQ235" s="32"/>
     </row>
     <row r="236" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A236" s="462" t="s">
+      <c r="A236" s="441" t="s">
         <v>1974</v>
       </c>
       <c r="B236" s="14" t="s">
@@ -37919,7 +37889,7 @@
       <c r="T236" s="21"/>
       <c r="U236" s="28"/>
       <c r="V236" s="28"/>
-      <c r="W236" s="435" t="s">
+      <c r="W236" s="415" t="s">
         <v>1918</v>
       </c>
       <c r="X236" s="118" t="s">
@@ -37950,7 +37920,7 @@
       <c r="AQ236" s="32"/>
     </row>
     <row r="237" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A237" s="462" t="s">
+      <c r="A237" s="441" t="s">
         <v>1985</v>
       </c>
       <c r="B237" s="14" t="s">
@@ -38033,7 +38003,7 @@
       <c r="AQ237" s="32"/>
     </row>
     <row r="238" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A238" s="462" t="s">
+      <c r="A238" s="441" t="s">
         <v>1998</v>
       </c>
       <c r="B238" s="14" t="s">
@@ -38118,7 +38088,7 @@
       <c r="AQ238" s="32"/>
     </row>
     <row r="239" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A239" s="462" t="s">
+      <c r="A239" s="441" t="s">
         <v>2008</v>
       </c>
       <c r="B239" s="14" t="s">
@@ -38150,7 +38120,7 @@
         <v>3944</v>
       </c>
       <c r="N239" s="54" t="s">
-        <v>3994</v>
+        <v>3988</v>
       </c>
       <c r="O239" s="54"/>
       <c r="P239" s="25" t="s">
@@ -38199,7 +38169,7 @@
       <c r="AQ239" s="32"/>
     </row>
     <row r="240" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A240" s="462" t="s">
+      <c r="A240" s="441" t="s">
         <v>3851</v>
       </c>
       <c r="B240" s="14" t="s">
@@ -38278,7 +38248,7 @@
       <c r="AQ240" s="32"/>
     </row>
     <row r="241" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A241" s="462" t="s">
+      <c r="A241" s="441" t="s">
         <v>2023</v>
       </c>
       <c r="B241" s="14" t="s">
@@ -38359,7 +38329,7 @@
       <c r="AQ241" s="32"/>
     </row>
     <row r="242" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A242" s="462" t="s">
+      <c r="A242" s="441" t="s">
         <v>2030</v>
       </c>
       <c r="B242" s="14" t="s">
@@ -38391,7 +38361,7 @@
       <c r="N242" s="54" t="s">
         <v>2033</v>
       </c>
-      <c r="O242" s="413"/>
+      <c r="O242" s="394"/>
       <c r="P242" s="290" t="s">
         <v>1899</v>
       </c>
@@ -38438,7 +38408,7 @@
       <c r="AQ242" s="32"/>
     </row>
     <row r="243" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A243" s="462" t="s">
+      <c r="A243" s="441" t="s">
         <v>2038</v>
       </c>
       <c r="B243" s="14" t="s">
@@ -38521,7 +38491,7 @@
       <c r="AQ243" s="32"/>
     </row>
     <row r="244" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A244" s="462" t="s">
+      <c r="A244" s="441" t="s">
         <v>2047</v>
       </c>
       <c r="B244" s="14" t="s">
@@ -38602,7 +38572,7 @@
       <c r="AQ244" s="32"/>
     </row>
     <row r="245" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A245" s="462" t="s">
+      <c r="A245" s="441" t="s">
         <v>2061</v>
       </c>
       <c r="B245" s="14" t="s">
@@ -38677,7 +38647,7 @@
       <c r="AQ245" s="32"/>
     </row>
     <row r="246" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A246" s="462" t="s">
+      <c r="A246" s="441" t="s">
         <v>2070</v>
       </c>
       <c r="B246" s="14" t="s">
@@ -38746,10 +38716,10 @@
       <c r="AQ246" s="32"/>
     </row>
     <row r="247" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A247" s="480" t="s">
+      <c r="A247" s="459" t="s">
         <v>3764</v>
       </c>
-      <c r="B247" s="374" t="s">
+      <c r="B247" s="356" t="s">
         <v>2078</v>
       </c>
       <c r="C247" s="259" t="s">
@@ -38762,22 +38732,22 @@
       <c r="G247" s="227" t="s">
         <v>3766</v>
       </c>
-      <c r="H247" s="378" t="s">
+      <c r="H247" s="360" t="s">
         <v>3951</v>
       </c>
-      <c r="I247" s="376" t="s">
+      <c r="I247" s="358" t="s">
         <v>1906</v>
       </c>
       <c r="J247" s="227"/>
       <c r="K247" s="227"/>
       <c r="L247" s="227"/>
-      <c r="M247" s="376" t="s">
+      <c r="M247" s="358" t="s">
         <v>3949</v>
       </c>
-      <c r="N247" s="415" t="s">
-        <v>3997</v>
-      </c>
-      <c r="O247" s="414"/>
+      <c r="N247" s="396" t="s">
+        <v>3991</v>
+      </c>
+      <c r="O247" s="395"/>
       <c r="P247" s="290" t="s">
         <v>1899</v>
       </c>
@@ -38787,27 +38757,27 @@
       <c r="R247" s="299" t="s">
         <v>383</v>
       </c>
-      <c r="S247" s="378" t="s">
+      <c r="S247" s="360" t="s">
         <v>41</v>
       </c>
-      <c r="T247" s="378" t="s">
+      <c r="T247" s="360" t="s">
         <v>3767</v>
       </c>
-      <c r="U247" s="378" t="s">
+      <c r="U247" s="360" t="s">
         <v>1899</v>
       </c>
-      <c r="V247" s="378" t="s">
+      <c r="V247" s="360" t="s">
         <v>1900</v>
       </c>
       <c r="W247" s="227"/>
       <c r="X247" s="227"/>
-      <c r="Y247" s="388" t="s">
+      <c r="Y247" s="370" t="s">
         <v>3941</v>
       </c>
       <c r="Z247" s="227"/>
       <c r="AA247" s="227"/>
       <c r="AB247" s="227"/>
-      <c r="AC247" s="378" t="s">
+      <c r="AC247" s="360" t="s">
         <v>2079</v>
       </c>
       <c r="AD247" s="227" t="s">
@@ -38828,10 +38798,10 @@
       <c r="AQ247" s="227"/>
     </row>
     <row r="248" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A248" s="480" t="s">
+      <c r="A248" s="459" t="s">
         <v>3760</v>
       </c>
-      <c r="B248" s="378" t="s">
+      <c r="B248" s="360" t="s">
         <v>3761</v>
       </c>
       <c r="C248" s="259" t="s">
@@ -38839,23 +38809,23 @@
       </c>
       <c r="E248" s="227"/>
       <c r="F248" s="227"/>
-      <c r="G248" s="378"/>
-      <c r="H248" s="378" t="s">
+      <c r="G248" s="360"/>
+      <c r="H248" s="360" t="s">
         <v>3952</v>
       </c>
-      <c r="I248" s="376" t="s">
+      <c r="I248" s="358" t="s">
         <v>2026</v>
       </c>
       <c r="J248" s="227"/>
       <c r="K248" s="227"/>
       <c r="L248" s="227"/>
-      <c r="M248" s="376" t="s">
+      <c r="M248" s="358" t="s">
         <v>3949</v>
       </c>
-      <c r="N248" s="415" t="s">
-        <v>3997</v>
-      </c>
-      <c r="O248" s="414"/>
+      <c r="N248" s="396" t="s">
+        <v>3991</v>
+      </c>
+      <c r="O248" s="395"/>
       <c r="P248" s="290" t="s">
         <v>1899</v>
       </c>
@@ -38865,27 +38835,27 @@
       <c r="R248" s="299" t="s">
         <v>383</v>
       </c>
-      <c r="S248" s="378" t="s">
+      <c r="S248" s="360" t="s">
         <v>41</v>
       </c>
-      <c r="T248" s="378" t="s">
+      <c r="T248" s="360" t="s">
         <v>3762</v>
       </c>
-      <c r="U248" s="378" t="s">
+      <c r="U248" s="360" t="s">
         <v>1899</v>
       </c>
-      <c r="V248" s="378" t="s">
+      <c r="V248" s="360" t="s">
         <v>1900</v>
       </c>
       <c r="W248" s="227"/>
       <c r="X248" s="227"/>
-      <c r="Y248" s="378" t="s">
+      <c r="Y248" s="360" t="s">
         <v>3763</v>
       </c>
       <c r="Z248" s="227"/>
       <c r="AA248" s="227"/>
       <c r="AB248" s="227"/>
-      <c r="AC248" s="378"/>
+      <c r="AC248" s="360"/>
       <c r="AD248" s="227"/>
       <c r="AE248" s="227"/>
       <c r="AF248" s="227"/>
@@ -38902,7 +38872,7 @@
       <c r="AQ248" s="227"/>
     </row>
     <row r="249" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A249" s="462" t="s">
+      <c r="A249" s="441" t="s">
         <v>2080</v>
       </c>
       <c r="B249" s="14" t="s">
@@ -38979,7 +38949,7 @@
       <c r="AQ249" s="32"/>
     </row>
     <row r="250" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A250" s="462" t="s">
+      <c r="A250" s="441" t="s">
         <v>2089</v>
       </c>
       <c r="B250" s="14" t="s">
@@ -39048,7 +39018,7 @@
       <c r="AQ250" s="32"/>
     </row>
     <row r="251" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A251" s="462" t="s">
+      <c r="A251" s="441" t="s">
         <v>2095</v>
       </c>
       <c r="B251" s="14" t="s">
@@ -39119,7 +39089,7 @@
       <c r="AQ251" s="32"/>
     </row>
     <row r="252" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A252" s="462" t="s">
+      <c r="A252" s="441" t="s">
         <v>2103</v>
       </c>
       <c r="B252" s="14" t="s">
@@ -39194,7 +39164,7 @@
       <c r="AQ252" s="32"/>
     </row>
     <row r="253" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A253" s="462" t="s">
+      <c r="A253" s="441" t="s">
         <v>2111</v>
       </c>
       <c r="B253" s="14" t="s">
@@ -39263,7 +39233,7 @@
       <c r="AQ253" s="32"/>
     </row>
     <row r="254" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A254" s="462" t="s">
+      <c r="A254" s="441" t="s">
         <v>2119</v>
       </c>
       <c r="B254" s="14" t="s">
@@ -39336,7 +39306,7 @@
       <c r="AQ254" s="32"/>
     </row>
     <row r="255" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A255" s="462" t="s">
+      <c r="A255" s="441" t="s">
         <v>2128</v>
       </c>
       <c r="B255" s="14" t="s">
@@ -39405,7 +39375,7 @@
       <c r="AQ255" s="32"/>
     </row>
     <row r="256" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A256" s="462" t="s">
+      <c r="A256" s="441" t="s">
         <v>2136</v>
       </c>
       <c r="B256" s="21" t="s">
@@ -39488,7 +39458,7 @@
       <c r="AQ256" s="21"/>
     </row>
     <row r="257" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A257" s="462" t="s">
+      <c r="A257" s="441" t="s">
         <v>2146</v>
       </c>
       <c r="B257" s="14" t="s">
@@ -39559,7 +39529,7 @@
       <c r="AQ257" s="32"/>
     </row>
     <row r="258" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A258" s="462" t="s">
+      <c r="A258" s="441" t="s">
         <v>3850</v>
       </c>
       <c r="B258" s="14" t="s">
@@ -39632,7 +39602,7 @@
       <c r="AQ258" s="32"/>
     </row>
     <row r="259" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A259" s="462" t="s">
+      <c r="A259" s="441" t="s">
         <v>2162</v>
       </c>
       <c r="B259" s="14" t="s">
@@ -39707,7 +39677,7 @@
       <c r="AQ259" s="32"/>
     </row>
     <row r="260" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A260" s="462" t="s">
+      <c r="A260" s="441" t="s">
         <v>2169</v>
       </c>
       <c r="B260" s="14" t="s">
@@ -39780,7 +39750,7 @@
       <c r="AQ260" s="32"/>
     </row>
     <row r="261" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A261" s="462" t="s">
+      <c r="A261" s="441" t="s">
         <v>2177</v>
       </c>
       <c r="B261" s="14" t="s">
@@ -39857,7 +39827,7 @@
       <c r="AQ261" s="32"/>
     </row>
     <row r="262" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A262" s="462" t="s">
+      <c r="A262" s="441" t="s">
         <v>2184</v>
       </c>
       <c r="B262" s="14" t="s">
@@ -39880,7 +39850,7 @@
       <c r="I262" s="43" t="s">
         <v>2188</v>
       </c>
-      <c r="J262" s="400" t="s">
+      <c r="J262" s="381" t="s">
         <v>2189</v>
       </c>
       <c r="K262" s="107"/>
@@ -39926,7 +39896,7 @@
       <c r="AQ262" s="32"/>
     </row>
     <row r="263" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A263" s="462" t="s">
+      <c r="A263" s="441" t="s">
         <v>3849</v>
       </c>
       <c r="B263" s="14" t="s">
@@ -39991,7 +39961,7 @@
       <c r="AQ263" s="32"/>
     </row>
     <row r="264" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A264" s="462" t="s">
+      <c r="A264" s="441" t="s">
         <v>2197</v>
       </c>
       <c r="B264" s="14" t="s">
@@ -40066,8 +40036,8 @@
       <c r="AQ264" s="32"/>
     </row>
     <row r="265" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A265" s="462" t="s">
-        <v>3981</v>
+      <c r="A265" s="441" t="s">
+        <v>3975</v>
       </c>
       <c r="B265" s="14" t="s">
         <v>2204</v>
@@ -40096,7 +40066,7 @@
         <v>3949</v>
       </c>
       <c r="N265" s="54" t="s">
-        <v>3998</v>
+        <v>3992</v>
       </c>
       <c r="O265" s="54"/>
       <c r="P265" s="290" t="s">
@@ -40137,7 +40107,7 @@
       <c r="AQ265" s="32"/>
     </row>
     <row r="266" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A266" s="462" t="s">
+      <c r="A266" s="441" t="s">
         <v>3848</v>
       </c>
       <c r="B266" s="14" t="s">
@@ -40148,7 +40118,7 @@
       </c>
       <c r="D266" s="232"/>
       <c r="E266" s="58"/>
-      <c r="F266" s="389" t="s">
+      <c r="F266" s="371" t="s">
         <v>2209</v>
       </c>
       <c r="G266" s="32"/>
@@ -40208,7 +40178,7 @@
       <c r="AQ266" s="32"/>
     </row>
     <row r="267" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A267" s="462" t="s">
+      <c r="A267" s="441" t="s">
         <v>2216</v>
       </c>
       <c r="B267" s="14" t="s">
@@ -40281,7 +40251,7 @@
       <c r="AQ267" s="32"/>
     </row>
     <row r="268" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A268" s="462" t="s">
+      <c r="A268" s="441" t="s">
         <v>2225</v>
       </c>
       <c r="B268" s="14" t="s">
@@ -40356,7 +40326,7 @@
       <c r="AQ268" s="32"/>
     </row>
     <row r="269" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A269" s="462" t="s">
+      <c r="A269" s="441" t="s">
         <v>3847</v>
       </c>
       <c r="B269" s="66" t="s">
@@ -40433,7 +40403,7 @@
       <c r="AQ269" s="32"/>
     </row>
     <row r="270" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A270" s="462" t="s">
+      <c r="A270" s="441" t="s">
         <v>2245</v>
       </c>
       <c r="B270" s="33" t="s">
@@ -40463,7 +40433,7 @@
         <v>3949</v>
       </c>
       <c r="N270" s="73" t="s">
-        <v>3999</v>
+        <v>3993</v>
       </c>
       <c r="O270" s="73"/>
       <c r="P270" s="290" t="s">
@@ -40482,7 +40452,7 @@
       <c r="U270" s="290" t="s">
         <v>1899</v>
       </c>
-      <c r="V270" s="434" t="s">
+      <c r="V270" s="414" t="s">
         <v>1900</v>
       </c>
       <c r="W270" s="29"/>
@@ -40510,7 +40480,7 @@
       <c r="AQ270" s="32"/>
     </row>
     <row r="271" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A271" s="462" t="s">
+      <c r="A271" s="441" t="s">
         <v>2250</v>
       </c>
       <c r="B271" s="32" t="s">
@@ -40577,7 +40547,7 @@
       <c r="AQ271" s="32"/>
     </row>
     <row r="272" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A272" s="462" t="s">
+      <c r="A272" s="441" t="s">
         <v>2257</v>
       </c>
       <c r="B272" s="14" t="s">
@@ -40644,7 +40614,7 @@
       <c r="AQ272" s="32"/>
     </row>
     <row r="273" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A273" s="476" t="s">
+      <c r="A273" s="455" t="s">
         <v>2263</v>
       </c>
       <c r="B273" s="14" t="s">
@@ -40667,7 +40637,7 @@
       <c r="I273" s="43" t="s">
         <v>2267</v>
       </c>
-      <c r="J273" s="398" t="s">
+      <c r="J273" s="379" t="s">
         <v>2268</v>
       </c>
       <c r="K273" s="103"/>
@@ -40713,8 +40683,8 @@
       <c r="AQ273" s="32"/>
     </row>
     <row r="274" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A274" s="462" t="s">
-        <v>3995</v>
+      <c r="A274" s="441" t="s">
+        <v>3989</v>
       </c>
       <c r="B274" s="14" t="s">
         <v>430</v>
@@ -40784,7 +40754,7 @@
       <c r="AQ274" s="32"/>
     </row>
     <row r="275" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A275" s="462" t="s">
+      <c r="A275" s="441" t="s">
         <v>2277</v>
       </c>
       <c r="B275" s="14" t="s">
@@ -40855,7 +40825,7 @@
       <c r="AQ275" s="32"/>
     </row>
     <row r="276" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A276" s="462" t="s">
+      <c r="A276" s="441" t="s">
         <v>2285</v>
       </c>
       <c r="B276" s="14" t="s">
@@ -40934,7 +40904,7 @@
       <c r="AQ276" s="32"/>
     </row>
     <row r="277" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A277" s="462" t="s">
+      <c r="A277" s="441" t="s">
         <v>2294</v>
       </c>
       <c r="B277" s="14" t="s">
@@ -40964,7 +40934,7 @@
         <v>3949</v>
       </c>
       <c r="N277" s="38" t="s">
-        <v>4000</v>
+        <v>3994</v>
       </c>
       <c r="O277" s="38"/>
       <c r="P277" s="290" t="s">
@@ -40983,7 +40953,7 @@
       <c r="U277" s="290" t="s">
         <v>1899</v>
       </c>
-      <c r="V277" s="434" t="s">
+      <c r="V277" s="414" t="s">
         <v>1900</v>
       </c>
       <c r="W277" s="29"/>
@@ -41011,7 +40981,7 @@
       <c r="AQ277" s="32"/>
     </row>
     <row r="278" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A278" s="481" t="s">
+      <c r="A278" s="460" t="s">
         <v>2297</v>
       </c>
       <c r="B278" s="14" t="s">
@@ -41092,7 +41062,7 @@
       <c r="AQ278" s="32"/>
     </row>
     <row r="279" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A279" s="481" t="s">
+      <c r="A279" s="460" t="s">
         <v>2305</v>
       </c>
       <c r="B279" s="14" t="s">
@@ -41126,7 +41096,7 @@
       <c r="N279" s="89" t="s">
         <v>2077</v>
       </c>
-      <c r="O279" s="412"/>
+      <c r="O279" s="393"/>
       <c r="P279" s="70"/>
       <c r="Q279" s="91"/>
       <c r="R279" s="32" t="s">
@@ -41161,7 +41131,7 @@
       <c r="AQ279" s="32"/>
     </row>
     <row r="280" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A280" s="462" t="s">
+      <c r="A280" s="441" t="s">
         <v>2310</v>
       </c>
       <c r="B280" s="14" t="s">
@@ -41238,7 +41208,7 @@
       <c r="AQ280" s="32"/>
     </row>
     <row r="281" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A281" s="462" t="s">
+      <c r="A281" s="441" t="s">
         <v>2315</v>
       </c>
       <c r="B281" s="95" t="s">
@@ -41305,7 +41275,7 @@
       <c r="AQ281" s="32"/>
     </row>
     <row r="282" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A282" s="462" t="s">
+      <c r="A282" s="441" t="s">
         <v>2320</v>
       </c>
       <c r="B282" s="95" t="s">
@@ -41334,7 +41304,7 @@
       <c r="M282" s="292" t="s">
         <v>3949</v>
       </c>
-      <c r="N282" s="450" t="s">
+      <c r="N282" s="429" t="s">
         <v>2452</v>
       </c>
       <c r="O282" s="294"/>
@@ -41384,7 +41354,7 @@
       <c r="AQ282" s="32"/>
     </row>
     <row r="283" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A283" s="462" t="s">
+      <c r="A283" s="441" t="s">
         <v>2325</v>
       </c>
       <c r="B283" s="95" t="s">
@@ -41410,7 +41380,7 @@
       <c r="J283" s="22"/>
       <c r="K283" s="22"/>
       <c r="L283" s="22"/>
-      <c r="M283" s="410" t="s">
+      <c r="M283" s="391" t="s">
         <v>2331</v>
       </c>
       <c r="N283" s="38" t="s">
@@ -41424,7 +41394,7 @@
         <v>1900</v>
       </c>
       <c r="R283" s="32" t="s">
-        <v>3989</v>
+        <v>3983</v>
       </c>
       <c r="S283" s="32" t="s">
         <v>41</v>
@@ -41457,7 +41427,7 @@
       <c r="AQ283" s="32"/>
     </row>
     <row r="284" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A284" s="462" t="s">
+      <c r="A284" s="441" t="s">
         <v>2333</v>
       </c>
       <c r="B284" s="33" t="s">
@@ -41528,7 +41498,7 @@
       <c r="AQ284" s="32"/>
     </row>
     <row r="285" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A285" s="462" t="s">
+      <c r="A285" s="441" t="s">
         <v>2341</v>
       </c>
       <c r="B285" s="32" t="s">
@@ -41593,7 +41563,7 @@
       <c r="AQ285" s="32"/>
     </row>
     <row r="286" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A286" s="462" t="s">
+      <c r="A286" s="441" t="s">
         <v>2346</v>
       </c>
       <c r="B286" s="14" t="s">
@@ -41619,11 +41589,11 @@
       <c r="J286" s="22"/>
       <c r="K286" s="22"/>
       <c r="L286" s="22"/>
-      <c r="M286" s="409" t="s">
+      <c r="M286" s="390" t="s">
         <v>3949</v>
       </c>
       <c r="N286" s="89" t="s">
-        <v>3999</v>
+        <v>3993</v>
       </c>
       <c r="O286" s="89"/>
       <c r="P286" s="124" t="s">
@@ -41639,7 +41609,7 @@
         <v>41</v>
       </c>
       <c r="T286" s="21" t="s">
-        <v>4031</v>
+        <v>4025</v>
       </c>
       <c r="U286" s="28"/>
       <c r="V286" s="28"/>
@@ -41668,7 +41638,7 @@
       <c r="AQ286" s="32"/>
     </row>
     <row r="287" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A287" s="462" t="s">
+      <c r="A287" s="441" t="s">
         <v>2349</v>
       </c>
       <c r="B287" s="14" t="s">
@@ -41737,7 +41707,7 @@
       <c r="AQ287" s="32"/>
     </row>
     <row r="288" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A288" s="462" t="s">
+      <c r="A288" s="441" t="s">
         <v>2355</v>
       </c>
       <c r="B288" s="14" t="s">
@@ -41804,7 +41774,7 @@
       <c r="AQ288" s="32"/>
     </row>
     <row r="289" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A289" s="462" t="s">
+      <c r="A289" s="441" t="s">
         <v>2360</v>
       </c>
       <c r="B289" s="32" t="s">
@@ -41885,7 +41855,7 @@
       <c r="AQ289" s="32"/>
     </row>
     <row r="290" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A290" s="462" t="s">
+      <c r="A290" s="441" t="s">
         <v>2373</v>
       </c>
       <c r="B290" s="14" t="s">
@@ -41954,7 +41924,7 @@
       <c r="AQ290" s="32"/>
     </row>
     <row r="291" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A291" s="462" t="s">
+      <c r="A291" s="441" t="s">
         <v>2376</v>
       </c>
       <c r="B291" s="32" t="s">
@@ -42023,7 +41993,7 @@
       <c r="AQ291" s="32"/>
     </row>
     <row r="292" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A292" s="462" t="s">
+      <c r="A292" s="441" t="s">
         <v>2383</v>
       </c>
       <c r="B292" s="14" t="s">
@@ -42098,7 +42068,7 @@
       <c r="AQ292" s="32"/>
     </row>
     <row r="293" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A293" s="462" t="s">
+      <c r="A293" s="441" t="s">
         <v>2394</v>
       </c>
       <c r="B293" s="32" t="s">
@@ -42130,7 +42100,7 @@
       <c r="N293" s="54" t="s">
         <v>2399</v>
       </c>
-      <c r="O293" s="413" t="s">
+      <c r="O293" s="394" t="s">
         <v>802</v>
       </c>
       <c r="P293" s="112"/>
@@ -42148,7 +42118,7 @@
       <c r="V293" s="28"/>
       <c r="W293" s="72"/>
       <c r="X293" s="72"/>
-      <c r="Y293" s="440" t="s">
+      <c r="Y293" s="420" t="s">
         <v>2400</v>
       </c>
       <c r="Z293" s="30" t="s">
@@ -42175,7 +42145,7 @@
       <c r="AQ293" s="32"/>
     </row>
     <row r="294" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A294" s="462" t="s">
+      <c r="A294" s="441" t="s">
         <v>2403</v>
       </c>
       <c r="B294" s="33" t="s">
@@ -42186,7 +42156,7 @@
       </c>
       <c r="D294" s="232"/>
       <c r="E294" s="58"/>
-      <c r="F294" s="389" t="s">
+      <c r="F294" s="371" t="s">
         <v>2404</v>
       </c>
       <c r="G294" s="32" t="s">
@@ -42205,9 +42175,9 @@
         <v>3950</v>
       </c>
       <c r="N294" s="89" t="s">
-        <v>4001</v>
-      </c>
-      <c r="O294" s="412"/>
+        <v>3995</v>
+      </c>
+      <c r="O294" s="393"/>
       <c r="P294" s="112" t="s">
         <v>1899</v>
       </c>
@@ -42254,7 +42224,7 @@
       <c r="AQ294" s="32"/>
     </row>
     <row r="295" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A295" s="462" t="s">
+      <c r="A295" s="441" t="s">
         <v>3846</v>
       </c>
       <c r="B295" s="14" t="s">
@@ -42333,7 +42303,7 @@
       <c r="AQ295" s="32"/>
     </row>
     <row r="296" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A296" s="462" t="s">
+      <c r="A296" s="441" t="s">
         <v>2416</v>
       </c>
       <c r="B296" s="14" t="s">
@@ -42414,7 +42384,7 @@
       <c r="AQ296" s="32"/>
     </row>
     <row r="297" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A297" s="462" t="s">
+      <c r="A297" s="441" t="s">
         <v>2427</v>
       </c>
       <c r="B297" s="14" t="s">
@@ -42483,7 +42453,7 @@
       <c r="AQ297" s="32"/>
     </row>
     <row r="298" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A298" s="462" t="s">
+      <c r="A298" s="441" t="s">
         <v>2434</v>
       </c>
       <c r="B298" s="14" t="s">
@@ -42515,7 +42485,7 @@
       <c r="N298" s="89" t="s">
         <v>2174</v>
       </c>
-      <c r="O298" s="412"/>
+      <c r="O298" s="393"/>
       <c r="P298" s="70"/>
       <c r="Q298" s="91"/>
       <c r="R298" s="101" t="s">
@@ -42550,7 +42520,7 @@
       <c r="AQ298" s="32"/>
     </row>
     <row r="299" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A299" s="462" t="s">
+      <c r="A299" s="441" t="s">
         <v>2439</v>
       </c>
       <c r="B299" s="14" t="s">
@@ -42629,7 +42599,7 @@
       <c r="AQ299" s="32"/>
     </row>
     <row r="300" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A300" s="462" t="s">
+      <c r="A300" s="441" t="s">
         <v>2444</v>
       </c>
       <c r="B300" s="33" t="s">
@@ -42706,7 +42676,7 @@
       <c r="AQ300" s="32"/>
     </row>
     <row r="301" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A301" s="462" t="s">
+      <c r="A301" s="441" t="s">
         <v>2452</v>
       </c>
       <c r="B301" s="33" t="s">
@@ -42738,7 +42708,7 @@
         <v>2457</v>
       </c>
       <c r="N301" s="38" t="s">
-        <v>4002</v>
+        <v>3996</v>
       </c>
       <c r="O301" s="38"/>
       <c r="P301" s="25"/>
@@ -42775,7 +42745,7 @@
       <c r="AQ301" s="32"/>
     </row>
     <row r="302" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A302" s="476" t="s">
+      <c r="A302" s="455" t="s">
         <v>2458</v>
       </c>
       <c r="B302" s="33" t="s">
@@ -42848,7 +42818,7 @@
       <c r="AQ302" s="32"/>
     </row>
     <row r="303" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A303" s="479" t="s">
+      <c r="A303" s="458" t="s">
         <v>2466</v>
       </c>
       <c r="B303" s="33" t="s">
@@ -42880,7 +42850,7 @@
       </c>
       <c r="O303" s="38"/>
       <c r="P303" s="25"/>
-      <c r="Q303" s="422"/>
+      <c r="Q303" s="403"/>
       <c r="R303" s="101" t="s">
         <v>540</v>
       </c>
@@ -42915,7 +42885,7 @@
       <c r="AQ303" s="32"/>
     </row>
     <row r="304" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A304" s="479" t="s">
+      <c r="A304" s="458" t="s">
         <v>2472</v>
       </c>
       <c r="B304" s="33" t="s">
@@ -42982,7 +42952,7 @@
       <c r="AQ304" s="32"/>
     </row>
     <row r="305" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A305" s="479" t="s">
+      <c r="A305" s="458" t="s">
         <v>2478</v>
       </c>
       <c r="B305" s="33" t="s">
@@ -43053,7 +43023,7 @@
       <c r="AQ305" s="32"/>
     </row>
     <row r="306" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A306" s="479" t="s">
+      <c r="A306" s="458" t="s">
         <v>3845</v>
       </c>
       <c r="B306" s="33" t="s">
@@ -43134,7 +43104,7 @@
       <c r="AQ306" s="32"/>
     </row>
     <row r="307" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A307" s="479" t="s">
+      <c r="A307" s="458" t="s">
         <v>2498</v>
       </c>
       <c r="B307" s="33" t="s">
@@ -43211,7 +43181,7 @@
       <c r="AQ307" s="32"/>
     </row>
     <row r="308" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A308" s="479" t="s">
+      <c r="A308" s="458" t="s">
         <v>3844</v>
       </c>
       <c r="B308" s="33" t="s">
@@ -43288,7 +43258,7 @@
       <c r="AQ308" s="32"/>
     </row>
     <row r="309" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A309" s="479" t="s">
+      <c r="A309" s="458" t="s">
         <v>2518</v>
       </c>
       <c r="B309" s="14" t="s">
@@ -43365,7 +43335,7 @@
       <c r="AQ309" s="32"/>
     </row>
     <row r="310" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A310" s="479" t="s">
+      <c r="A310" s="458" t="s">
         <v>3843</v>
       </c>
       <c r="B310" s="33" t="s">
@@ -43380,7 +43350,7 @@
         <v>2531</v>
       </c>
       <c r="G310" s="32"/>
-      <c r="H310" s="372" t="s">
+      <c r="H310" s="354" t="s">
         <v>3947</v>
       </c>
       <c r="I310" s="32" t="s">
@@ -43419,7 +43389,7 @@
       <c r="X310" s="29" t="s">
         <v>2534</v>
       </c>
-      <c r="Y310" s="373" t="s">
+      <c r="Y310" s="355" t="s">
         <v>2535</v>
       </c>
       <c r="Z310" s="30" t="s">
@@ -43448,7 +43418,7 @@
       <c r="AQ310" s="32"/>
     </row>
     <row r="311" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A311" s="479" t="s">
+      <c r="A311" s="458" t="s">
         <v>2538</v>
       </c>
       <c r="B311" s="33" t="s">
@@ -43515,7 +43485,7 @@
       <c r="AQ311" s="32"/>
     </row>
     <row r="312" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A312" s="479" t="s">
+      <c r="A312" s="458" t="s">
         <v>2544</v>
       </c>
       <c r="B312" s="33" t="s">
@@ -43586,7 +43556,7 @@
       <c r="AQ312" s="32"/>
     </row>
     <row r="313" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A313" s="479" t="s">
+      <c r="A313" s="458" t="s">
         <v>2552</v>
       </c>
       <c r="B313" s="33" t="s">
@@ -43659,7 +43629,7 @@
       <c r="AQ313" s="32"/>
     </row>
     <row r="314" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A314" s="479" t="s">
+      <c r="A314" s="458" t="s">
         <v>2561</v>
       </c>
       <c r="B314" s="15" t="s">
@@ -43744,7 +43714,7 @@
       <c r="AQ314" s="21"/>
     </row>
     <row r="315" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A315" s="479" t="s">
+      <c r="A315" s="458" t="s">
         <v>2572</v>
       </c>
       <c r="B315" s="33" t="s">
@@ -43787,7 +43757,7 @@
       <c r="S315" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="T315" s="430" t="s">
+      <c r="T315" s="410" t="s">
         <v>2579</v>
       </c>
       <c r="U315" s="28"/>
@@ -43815,7 +43785,7 @@
       <c r="AQ315" s="32"/>
     </row>
     <row r="316" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A316" s="479" t="s">
+      <c r="A316" s="458" t="s">
         <v>2580</v>
       </c>
       <c r="B316" s="33" t="s">
@@ -43886,7 +43856,7 @@
       <c r="AQ316" s="32"/>
     </row>
     <row r="317" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A317" s="479" t="s">
+      <c r="A317" s="458" t="s">
         <v>2585</v>
       </c>
       <c r="B317" s="33" t="s">
@@ -44039,7 +44009,7 @@
       <c r="AQ318" s="32"/>
     </row>
     <row r="319" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A319" s="479" t="s">
+      <c r="A319" s="458" t="s">
         <v>2602</v>
       </c>
       <c r="B319" s="14" t="s">
@@ -44120,7 +44090,7 @@
       <c r="AQ319" s="32"/>
     </row>
     <row r="320" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A320" s="479" t="s">
+      <c r="A320" s="458" t="s">
         <v>3840</v>
       </c>
       <c r="B320" s="33" t="s">
@@ -44146,7 +44116,7 @@
       <c r="L320" s="22" t="s">
         <v>2615</v>
       </c>
-      <c r="M320" s="408" t="s">
+      <c r="M320" s="389" t="s">
         <v>859</v>
       </c>
       <c r="N320" s="38" t="s">
@@ -44189,7 +44159,7 @@
       <c r="AQ320" s="32"/>
     </row>
     <row r="321" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A321" s="479" t="s">
+      <c r="A321" s="458" t="s">
         <v>3841</v>
       </c>
       <c r="B321" s="33" t="s">
@@ -44274,7 +44244,7 @@
       <c r="AQ321" s="32"/>
     </row>
     <row r="322" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A322" s="479" t="s">
+      <c r="A322" s="458" t="s">
         <v>2629</v>
       </c>
       <c r="B322" s="33" t="s">
@@ -44347,7 +44317,7 @@
       <c r="AQ322" s="32"/>
     </row>
     <row r="323" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A323" s="479" t="s">
+      <c r="A323" s="458" t="s">
         <v>2636</v>
       </c>
       <c r="B323" s="33" t="s">
@@ -44420,7 +44390,7 @@
       <c r="AQ323" s="32"/>
     </row>
     <row r="324" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A324" s="479" t="s">
+      <c r="A324" s="458" t="s">
         <v>2644</v>
       </c>
       <c r="B324" s="33" t="s">
@@ -44493,7 +44463,7 @@
       <c r="AQ324" s="32"/>
     </row>
     <row r="325" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A325" s="479" t="s">
+      <c r="A325" s="458" t="s">
         <v>2652</v>
       </c>
       <c r="B325" s="33" t="s">
@@ -44564,7 +44534,7 @@
       <c r="AQ325" s="32"/>
     </row>
     <row r="326" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A326" s="479" t="s">
+      <c r="A326" s="458" t="s">
         <v>2659</v>
       </c>
       <c r="B326" s="33" t="s">
@@ -44573,7 +44543,7 @@
       <c r="C326" s="247" t="s">
         <v>171</v>
       </c>
-      <c r="D326" s="384"/>
+      <c r="D326" s="366"/>
       <c r="E326" s="188"/>
       <c r="F326" s="189" t="s">
         <v>2660</v>
@@ -44615,7 +44585,7 @@
         <v>2232</v>
       </c>
       <c r="Y326" s="30" t="s">
-        <v>3971</v>
+        <v>3965</v>
       </c>
       <c r="Z326" s="30"/>
       <c r="AA326" s="30" t="s">
@@ -44641,7 +44611,7 @@
       <c r="AQ326" s="32"/>
     </row>
     <row r="327" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A327" s="479" t="s">
+      <c r="A327" s="458" t="s">
         <v>2666</v>
       </c>
       <c r="B327" s="33" t="s">
@@ -44720,7 +44690,7 @@
       <c r="AQ327" s="32"/>
     </row>
     <row r="328" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A328" s="479" t="s">
+      <c r="A328" s="458" t="s">
         <v>2676</v>
       </c>
       <c r="B328" s="33" t="s">
@@ -44731,7 +44701,7 @@
       </c>
       <c r="D328" s="244"/>
       <c r="E328" s="188"/>
-      <c r="F328" s="390" t="s">
+      <c r="F328" s="372" t="s">
         <v>2677</v>
       </c>
       <c r="G328" s="184"/>
@@ -44801,8 +44771,8 @@
       <c r="AQ328" s="32"/>
     </row>
     <row r="329" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A329" s="479" t="s">
-        <v>4006</v>
+      <c r="A329" s="458" t="s">
+        <v>4000</v>
       </c>
       <c r="B329" s="33" t="s">
         <v>430</v>
@@ -44884,7 +44854,7 @@
       <c r="AQ329" s="32"/>
     </row>
     <row r="330" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A330" s="479" t="s">
+      <c r="A330" s="458" t="s">
         <v>2695</v>
       </c>
       <c r="B330" s="33" t="s">
@@ -44963,7 +44933,7 @@
       <c r="AQ330" s="32"/>
     </row>
     <row r="331" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A331" s="479" t="s">
+      <c r="A331" s="458" t="s">
         <v>2705</v>
       </c>
       <c r="B331" s="33" t="s">
@@ -45042,7 +45012,7 @@
       <c r="AQ331" s="32"/>
     </row>
     <row r="332" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A332" s="479" t="s">
+      <c r="A332" s="458" t="s">
         <v>2715</v>
       </c>
       <c r="B332" s="33" t="s">
@@ -45117,7 +45087,7 @@
       <c r="AQ332" s="32"/>
     </row>
     <row r="333" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A333" s="479" t="s">
+      <c r="A333" s="458" t="s">
         <v>2722</v>
       </c>
       <c r="B333" s="33" t="s">
@@ -45190,7 +45160,7 @@
       <c r="AQ333" s="32"/>
     </row>
     <row r="334" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A334" s="479" t="s">
+      <c r="A334" s="458" t="s">
         <v>2727</v>
       </c>
       <c r="B334" s="33" t="s">
@@ -45263,7 +45233,7 @@
       <c r="AQ334" s="32"/>
     </row>
     <row r="335" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A335" s="479" t="s">
+      <c r="A335" s="458" t="s">
         <v>2733</v>
       </c>
       <c r="B335" s="33" t="s">
@@ -45336,7 +45306,7 @@
       <c r="AQ335" s="32"/>
     </row>
     <row r="336" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A336" s="479" t="s">
+      <c r="A336" s="458" t="s">
         <v>2741</v>
       </c>
       <c r="B336" s="14" t="s">
@@ -45377,7 +45347,7 @@
       <c r="Q336" s="56" t="s">
         <v>1900</v>
       </c>
-      <c r="R336" s="410" t="s">
+      <c r="R336" s="391" t="s">
         <v>1548</v>
       </c>
       <c r="S336" s="135" t="s">
@@ -45419,7 +45389,7 @@
       <c r="AQ336" s="32"/>
     </row>
     <row r="337" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A337" s="479" t="s">
+      <c r="A337" s="458" t="s">
         <v>2751</v>
       </c>
       <c r="B337" s="33" t="s">
@@ -45490,7 +45460,7 @@
       <c r="AQ337" s="32"/>
     </row>
     <row r="338" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A338" s="479" t="s">
+      <c r="A338" s="458" t="s">
         <v>2760</v>
       </c>
       <c r="B338" s="33" t="s">
@@ -45506,7 +45476,7 @@
       </c>
       <c r="G338" s="48"/>
       <c r="H338" s="32" t="s">
-        <v>3990</v>
+        <v>3984</v>
       </c>
       <c r="I338" s="185" t="s">
         <v>2761</v>
@@ -45520,7 +45490,7 @@
         <v>2763</v>
       </c>
       <c r="N338" s="38" t="s">
-        <v>3991</v>
+        <v>3985</v>
       </c>
       <c r="O338" s="38"/>
       <c r="P338" s="25" t="s">
@@ -45529,8 +45499,8 @@
       <c r="Q338" s="56" t="s">
         <v>2765</v>
       </c>
-      <c r="R338" s="449" t="s">
-        <v>3989</v>
+      <c r="R338" s="428" t="s">
+        <v>3983</v>
       </c>
       <c r="S338" s="77" t="s">
         <v>41</v>
@@ -45563,7 +45533,7 @@
       <c r="AQ338" s="32"/>
     </row>
     <row r="339" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A339" s="479" t="s">
+      <c r="A339" s="458" t="s">
         <v>2767</v>
       </c>
       <c r="B339" s="33" t="s">
@@ -45640,7 +45610,7 @@
       <c r="AQ339" s="32"/>
     </row>
     <row r="340" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A340" s="479" t="s">
+      <c r="A340" s="458" t="s">
         <v>2777</v>
       </c>
       <c r="B340" s="33" t="s">
@@ -45723,7 +45693,7 @@
       <c r="AQ340" s="32"/>
     </row>
     <row r="341" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A341" s="479" t="s">
+      <c r="A341" s="458" t="s">
         <v>2788</v>
       </c>
       <c r="B341" s="33" t="s">
@@ -45796,7 +45766,7 @@
       <c r="AQ341" s="32"/>
     </row>
     <row r="342" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A342" s="479" t="s">
+      <c r="A342" s="458" t="s">
         <v>3902</v>
       </c>
       <c r="B342" s="33" t="s">
@@ -45814,7 +45784,7 @@
       <c r="H342" s="203" t="s">
         <v>2798</v>
       </c>
-      <c r="I342" s="397" t="s">
+      <c r="I342" s="378" t="s">
         <v>2501</v>
       </c>
       <c r="J342" s="22" t="s">
@@ -45849,7 +45819,7 @@
       <c r="Y342" s="30" t="s">
         <v>2802</v>
       </c>
-      <c r="Z342" s="438"/>
+      <c r="Z342" s="418"/>
       <c r="AA342" s="30" t="s">
         <v>2803</v>
       </c>
@@ -45873,7 +45843,7 @@
       <c r="AQ342" s="32"/>
     </row>
     <row r="343" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A343" s="479" t="s">
+      <c r="A343" s="458" t="s">
         <v>2805</v>
       </c>
       <c r="B343" s="14" t="s">
@@ -45946,7 +45916,7 @@
       <c r="AQ343" s="32"/>
     </row>
     <row r="344" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A344" s="479" t="s">
+      <c r="A344" s="458" t="s">
         <v>2812</v>
       </c>
       <c r="B344" s="33" t="s">
@@ -46025,7 +45995,7 @@
       <c r="AQ344" s="32"/>
     </row>
     <row r="345" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A345" s="479" t="s">
+      <c r="A345" s="458" t="s">
         <v>3903</v>
       </c>
       <c r="B345" s="33" t="s">
@@ -46104,8 +46074,8 @@
       <c r="AQ345" s="32"/>
     </row>
     <row r="346" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A346" s="479" t="s">
-        <v>4007</v>
+      <c r="A346" s="458" t="s">
+        <v>4001</v>
       </c>
       <c r="B346" s="33" t="s">
         <v>430</v>
@@ -46185,7 +46155,7 @@
       <c r="AQ346" s="32"/>
     </row>
     <row r="347" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A347" s="479" t="s">
+      <c r="A347" s="458" t="s">
         <v>2840</v>
       </c>
       <c r="B347" s="33" t="s">
@@ -46213,7 +46183,7 @@
       </c>
       <c r="K347" s="22"/>
       <c r="L347" s="22"/>
-      <c r="M347" s="407" t="s">
+      <c r="M347" s="388" t="s">
         <v>2800</v>
       </c>
       <c r="N347" s="65" t="s">
@@ -46260,7 +46230,7 @@
       <c r="AQ347" s="32"/>
     </row>
     <row r="348" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A348" s="479" t="s">
+      <c r="A348" s="458" t="s">
         <v>2848</v>
       </c>
       <c r="B348" s="33" t="s">
@@ -46339,8 +46309,8 @@
       <c r="AQ348" s="32"/>
     </row>
     <row r="349" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A349" s="479" t="s">
-        <v>4008</v>
+      <c r="A349" s="458" t="s">
+        <v>4002</v>
       </c>
       <c r="B349" s="33" t="s">
         <v>430</v>
@@ -46416,7 +46386,7 @@
       <c r="AQ349" s="32"/>
     </row>
     <row r="350" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A350" s="479" t="s">
+      <c r="A350" s="458" t="s">
         <v>2861</v>
       </c>
       <c r="B350" s="33" t="s">
@@ -46497,8 +46467,8 @@
       <c r="AQ350" s="32"/>
     </row>
     <row r="351" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A351" s="479" t="s">
-        <v>4009</v>
+      <c r="A351" s="458" t="s">
+        <v>4003</v>
       </c>
       <c r="B351" s="184" t="s">
         <v>2873</v>
@@ -46572,7 +46542,7 @@
       <c r="AQ351" s="32"/>
     </row>
     <row r="352" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A352" s="479" t="s">
+      <c r="A352" s="458" t="s">
         <v>2879</v>
       </c>
       <c r="B352" s="33" t="s">
@@ -46653,7 +46623,7 @@
       <c r="AQ352" s="32"/>
     </row>
     <row r="353" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A353" s="479" t="s">
+      <c r="A353" s="458" t="s">
         <v>2886</v>
       </c>
       <c r="B353" s="33" t="s">
@@ -46685,7 +46655,7 @@
       <c r="N353" s="89" t="s">
         <v>2891</v>
       </c>
-      <c r="O353" s="412"/>
+      <c r="O353" s="393"/>
       <c r="P353" s="70"/>
       <c r="Q353" s="91"/>
       <c r="R353" s="77" t="s">
@@ -46726,7 +46696,7 @@
       <c r="AQ353" s="32"/>
     </row>
     <row r="354" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A354" s="479" t="s">
+      <c r="A354" s="458" t="s">
         <v>2893</v>
       </c>
       <c r="B354" s="33" t="s">
@@ -46805,14 +46775,14 @@
       <c r="AQ354" s="32"/>
     </row>
     <row r="355" spans="1:43" ht="135" customHeight="1">
-      <c r="A355" s="479" t="s">
+      <c r="A355" s="458" t="s">
         <v>2901</v>
       </c>
       <c r="B355" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C355" s="247" t="s">
-        <v>3966</v>
+        <v>3961</v>
       </c>
       <c r="D355" s="232"/>
       <c r="E355" s="58"/>
@@ -46886,7 +46856,7 @@
       <c r="AQ355" s="32"/>
     </row>
     <row r="356" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A356" s="479" t="s">
+      <c r="A356" s="458" t="s">
         <v>2909</v>
       </c>
       <c r="B356" s="33" t="s">
@@ -46967,7 +46937,7 @@
       <c r="AQ356" s="32"/>
     </row>
     <row r="357" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A357" s="479" t="s">
+      <c r="A357" s="458" t="s">
         <v>2919</v>
       </c>
       <c r="B357" s="33" t="s">
@@ -47044,7 +47014,7 @@
       <c r="AQ357" s="32"/>
     </row>
     <row r="358" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A358" s="479" t="s">
+      <c r="A358" s="458" t="s">
         <v>2926</v>
       </c>
       <c r="B358" s="184" t="s">
@@ -47119,7 +47089,7 @@
       <c r="AQ358" s="32"/>
     </row>
     <row r="359" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A359" s="479" t="s">
+      <c r="A359" s="458" t="s">
         <v>2935</v>
       </c>
       <c r="B359" s="33" t="s">
@@ -47196,7 +47166,7 @@
       <c r="AQ359" s="32"/>
     </row>
     <row r="360" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A360" s="479" t="s">
+      <c r="A360" s="458" t="s">
         <v>2944</v>
       </c>
       <c r="B360" s="33" t="s">
@@ -47275,7 +47245,7 @@
       <c r="AQ360" s="32"/>
     </row>
     <row r="361" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A361" s="479" t="s">
+      <c r="A361" s="458" t="s">
         <v>2953</v>
       </c>
       <c r="B361" s="33" t="s">
@@ -47305,7 +47275,7 @@
         <v>2957</v>
       </c>
       <c r="N361" s="54" t="s">
-        <v>4003</v>
+        <v>3997</v>
       </c>
       <c r="O361" s="54"/>
       <c r="P361" s="25" t="s">
@@ -47350,7 +47320,7 @@
       <c r="AQ361" s="32"/>
     </row>
     <row r="362" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A362" s="479" t="s">
+      <c r="A362" s="458" t="s">
         <v>2960</v>
       </c>
       <c r="B362" s="33" t="s">
@@ -47390,7 +47360,7 @@
         <v>1900</v>
       </c>
       <c r="R362" s="77" t="s">
-        <v>3987</v>
+        <v>3981</v>
       </c>
       <c r="S362" s="77" t="s">
         <v>41</v>
@@ -47431,7 +47401,7 @@
       <c r="AQ362" s="32"/>
     </row>
     <row r="363" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A363" s="479" t="s">
+      <c r="A363" s="458" t="s">
         <v>2968</v>
       </c>
       <c r="B363" s="33" t="s">
@@ -47508,7 +47478,7 @@
       <c r="AQ363" s="32"/>
     </row>
     <row r="364" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A364" s="479" t="s">
+      <c r="A364" s="458" t="s">
         <v>2973</v>
       </c>
       <c r="B364" s="33" t="s">
@@ -47575,7 +47545,7 @@
       <c r="AQ364" s="32"/>
     </row>
     <row r="365" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A365" s="479" t="s">
+      <c r="A365" s="458" t="s">
         <v>2979</v>
       </c>
       <c r="B365" s="33" t="s">
@@ -47630,7 +47600,7 @@
       <c r="Y365" s="195" t="s">
         <v>2983</v>
       </c>
-      <c r="Z365" s="438"/>
+      <c r="Z365" s="418"/>
       <c r="AA365" s="195" t="s">
         <v>2984</v>
       </c>
@@ -47654,7 +47624,7 @@
       <c r="AQ365" s="32"/>
     </row>
     <row r="366" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A366" s="479" t="s">
+      <c r="A366" s="458" t="s">
         <v>3904</v>
       </c>
       <c r="B366" s="33" t="s">
@@ -47729,7 +47699,7 @@
       <c r="AQ366" s="32"/>
     </row>
     <row r="367" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A367" s="479" t="s">
+      <c r="A367" s="458" t="s">
         <v>2992</v>
       </c>
       <c r="B367" s="33" t="s">
@@ -47810,7 +47780,7 @@
       <c r="AQ367" s="32"/>
     </row>
     <row r="368" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A368" s="479" t="s">
+      <c r="A368" s="458" t="s">
         <v>3002</v>
       </c>
       <c r="B368" s="33" t="s">
@@ -47889,74 +47859,74 @@
       <c r="AQ368" s="32"/>
     </row>
     <row r="369" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A369" s="479" t="s">
+      <c r="A369" s="458" t="s">
         <v>3012</v>
       </c>
-      <c r="B369" s="350" t="s">
+      <c r="B369" s="332" t="s">
         <v>430</v>
       </c>
       <c r="C369" s="262" t="s">
         <v>3013</v>
       </c>
-      <c r="D369" s="351"/>
-      <c r="E369" s="352"/>
-      <c r="F369" s="353" t="s">
+      <c r="D369" s="333"/>
+      <c r="E369" s="334"/>
+      <c r="F369" s="335" t="s">
         <v>3014</v>
       </c>
-      <c r="G369" s="354"/>
-      <c r="H369" s="369" t="s">
-        <v>3977</v>
-      </c>
-      <c r="I369" s="355" t="s">
+      <c r="G369" s="336"/>
+      <c r="H369" s="351" t="s">
+        <v>3971</v>
+      </c>
+      <c r="I369" s="337" t="s">
         <v>2501</v>
       </c>
-      <c r="J369" s="357"/>
-      <c r="K369" s="357"/>
-      <c r="L369" s="356"/>
-      <c r="M369" s="358" t="s">
+      <c r="J369" s="339"/>
+      <c r="K369" s="339"/>
+      <c r="L369" s="338"/>
+      <c r="M369" s="340" t="s">
         <v>3015</v>
       </c>
-      <c r="N369" s="359" t="s">
-        <v>4005</v>
-      </c>
-      <c r="O369" s="359" t="s">
+      <c r="N369" s="341" t="s">
+        <v>3999</v>
+      </c>
+      <c r="O369" s="341" t="s">
         <v>38</v>
       </c>
-      <c r="P369" s="360"/>
-      <c r="Q369" s="361" t="s">
+      <c r="P369" s="342"/>
+      <c r="Q369" s="343" t="s">
         <v>1166</v>
       </c>
-      <c r="R369" s="426" t="s">
+      <c r="R369" s="407" t="s">
         <v>519</v>
       </c>
-      <c r="S369" s="362" t="s">
+      <c r="S369" s="344" t="s">
         <v>41</v>
       </c>
-      <c r="T369" s="363"/>
-      <c r="U369" s="370"/>
-      <c r="V369" s="364"/>
-      <c r="W369" s="365" t="s">
+      <c r="T369" s="345"/>
+      <c r="U369" s="352"/>
+      <c r="V369" s="346"/>
+      <c r="W369" s="347" t="s">
         <v>3016</v>
       </c>
-      <c r="X369" s="365" t="s">
+      <c r="X369" s="347" t="s">
         <v>3017</v>
       </c>
-      <c r="Y369" s="366" t="s">
+      <c r="Y369" s="348" t="s">
         <v>3018</v>
       </c>
-      <c r="Z369" s="441" t="s">
+      <c r="Z369" s="421" t="s">
         <v>3019</v>
       </c>
-      <c r="AA369" s="366" t="s">
+      <c r="AA369" s="348" t="s">
         <v>3020</v>
       </c>
-      <c r="AB369" s="367" t="s">
-        <v>3976</v>
-      </c>
-      <c r="AC369" s="371" t="s">
-        <v>3978</v>
-      </c>
-      <c r="AD369" s="363"/>
+      <c r="AB369" s="349" t="s">
+        <v>3970</v>
+      </c>
+      <c r="AC369" s="353" t="s">
+        <v>3972</v>
+      </c>
+      <c r="AD369" s="345"/>
       <c r="AE369" s="32"/>
       <c r="AF369" s="32"/>
       <c r="AG369" s="32"/>
@@ -47972,7 +47942,7 @@
       <c r="AQ369" s="32"/>
     </row>
     <row r="370" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A370" s="479" t="s">
+      <c r="A370" s="458" t="s">
         <v>3021</v>
       </c>
       <c r="B370" s="33" t="s">
@@ -48028,10 +47998,10 @@
         <v>3026</v>
       </c>
       <c r="Z370" s="197"/>
-      <c r="AA370" s="348" t="s">
+      <c r="AA370" s="331" t="s">
         <v>3027</v>
       </c>
-      <c r="AB370" s="444"/>
+      <c r="AB370" s="424"/>
       <c r="AC370" s="16" t="s">
         <v>3028</v>
       </c>
@@ -48051,7 +48021,7 @@
       <c r="AQ370" s="32"/>
     </row>
     <row r="371" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A371" s="479" t="s">
+      <c r="A371" s="458" t="s">
         <v>3029</v>
       </c>
       <c r="B371" s="33" t="s">
@@ -48130,7 +48100,7 @@
       <c r="AQ371" s="32"/>
     </row>
     <row r="372" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A372" s="479" t="s">
+      <c r="A372" s="458" t="s">
         <v>3037</v>
       </c>
       <c r="B372" s="33" t="s">
@@ -48207,7 +48177,7 @@
       <c r="AQ372" s="32"/>
     </row>
     <row r="373" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A373" s="479" t="s">
+      <c r="A373" s="458" t="s">
         <v>3046</v>
       </c>
       <c r="B373" s="33" t="s">
@@ -48282,7 +48252,7 @@
       <c r="AQ373" s="32"/>
     </row>
     <row r="374" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A374" s="479" t="s">
+      <c r="A374" s="458" t="s">
         <v>3053</v>
       </c>
       <c r="B374" s="33" t="s">
@@ -48363,7 +48333,7 @@
       <c r="AQ374" s="32"/>
     </row>
     <row r="375" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A375" s="479" t="s">
+      <c r="A375" s="458" t="s">
         <v>3063</v>
       </c>
       <c r="B375" s="33" t="s">
@@ -48417,10 +48387,10 @@
       <c r="X375" s="29" t="s">
         <v>2232</v>
       </c>
-      <c r="Y375" s="439" t="s">
+      <c r="Y375" s="419" t="s">
         <v>3070</v>
       </c>
-      <c r="Z375" s="438"/>
+      <c r="Z375" s="418"/>
       <c r="AA375" s="30" t="s">
         <v>3071</v>
       </c>
@@ -48444,7 +48414,7 @@
       <c r="AQ375" s="32"/>
     </row>
     <row r="376" spans="1:43" ht="48" customHeight="1">
-      <c r="A376" s="482" t="s">
+      <c r="A376" s="461" t="s">
         <v>3073</v>
       </c>
       <c r="B376" s="33" t="s">
@@ -48454,23 +48424,23 @@
         <v>171</v>
       </c>
       <c r="E376" s="227"/>
-      <c r="F376" s="388" t="s">
+      <c r="F376" s="370" t="s">
         <v>3810</v>
       </c>
       <c r="G376" s="227"/>
-      <c r="H376" s="378" t="s">
+      <c r="H376" s="360" t="s">
         <v>3769</v>
       </c>
-      <c r="I376" s="378" t="s">
+      <c r="I376" s="360" t="s">
         <v>3074</v>
       </c>
       <c r="J376" s="227"/>
       <c r="K376" s="227"/>
       <c r="L376" s="227"/>
-      <c r="M376" s="405" t="s">
+      <c r="M376" s="386" t="s">
         <v>2076</v>
       </c>
-      <c r="N376" s="414" t="s">
+      <c r="N376" s="395" t="s">
         <v>2077</v>
       </c>
       <c r="O376" s="227"/>
@@ -48479,10 +48449,10 @@
       <c r="R376" s="227" t="s">
         <v>638</v>
       </c>
-      <c r="S376" s="378" t="s">
+      <c r="S376" s="360" t="s">
         <v>41</v>
       </c>
-      <c r="T376" s="378" t="s">
+      <c r="T376" s="360" t="s">
         <v>3770</v>
       </c>
       <c r="U376" s="227"/>
@@ -48494,7 +48464,7 @@
       <c r="AA376" s="227"/>
       <c r="AB376" s="227"/>
       <c r="AC376" s="227"/>
-      <c r="AD376" s="378" t="s">
+      <c r="AD376" s="360" t="s">
         <v>3771</v>
       </c>
       <c r="AE376" s="227"/>
@@ -48512,7 +48482,7 @@
       <c r="AQ376" s="227"/>
     </row>
     <row r="377" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A377" s="479" t="s">
+      <c r="A377" s="458" t="s">
         <v>3075</v>
       </c>
       <c r="B377" s="33" t="s">
@@ -48566,10 +48536,10 @@
       <c r="X377" s="29" t="s">
         <v>2232</v>
       </c>
-      <c r="Y377" s="438" t="s">
+      <c r="Y377" s="418" t="s">
         <v>2802</v>
       </c>
-      <c r="Z377" s="438"/>
+      <c r="Z377" s="418"/>
       <c r="AA377" s="195" t="s">
         <v>3082</v>
       </c>
@@ -48591,7 +48561,7 @@
       <c r="AQ377" s="32"/>
     </row>
     <row r="378" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A378" s="479" t="s">
+      <c r="A378" s="458" t="s">
         <v>3083</v>
       </c>
       <c r="B378" s="33" t="s">
@@ -48668,7 +48638,7 @@
       <c r="AQ378" s="32"/>
     </row>
     <row r="379" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A379" s="479" t="s">
+      <c r="A379" s="458" t="s">
         <v>3091</v>
       </c>
       <c r="B379" s="33" t="s">
@@ -48698,7 +48668,7 @@
       <c r="N379" s="54" t="s">
         <v>3095</v>
       </c>
-      <c r="O379" s="413" t="s">
+      <c r="O379" s="394" t="s">
         <v>3096</v>
       </c>
       <c r="P379" s="112"/>
@@ -48747,7 +48717,7 @@
       <c r="AQ379" s="32"/>
     </row>
     <row r="380" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A380" s="479" t="s">
+      <c r="A380" s="458" t="s">
         <v>3101</v>
       </c>
       <c r="B380" s="33" t="s">
@@ -48829,8 +48799,8 @@
       <c r="AP380" s="32"/>
       <c r="AQ380" s="32"/>
     </row>
-    <row r="381" spans="1:43" s="346" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A381" s="479" t="s">
+    <row r="381" spans="1:43" s="329" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A381" s="458" t="s">
         <v>3113</v>
       </c>
       <c r="B381" s="33" t="s">
@@ -48841,7 +48811,7 @@
       </c>
       <c r="D381" s="232"/>
       <c r="E381" s="58"/>
-      <c r="F381" s="392" t="s">
+      <c r="F381" s="373" t="s">
         <v>3114</v>
       </c>
       <c r="G381" s="32"/>
@@ -48883,7 +48853,7 @@
       <c r="Y381" s="195" t="s">
         <v>2802</v>
       </c>
-      <c r="Z381" s="442"/>
+      <c r="Z381" s="422"/>
       <c r="AA381" s="211" t="s">
         <v>3118</v>
       </c>
@@ -48892,92 +48862,23 @@
         <v>3119</v>
       </c>
       <c r="AD381" s="21"/>
-      <c r="AE381" s="336"/>
-      <c r="AF381" s="336"/>
-      <c r="AG381" s="336"/>
-      <c r="AH381" s="336"/>
-      <c r="AI381" s="336"/>
-      <c r="AJ381" s="336"/>
-      <c r="AK381" s="336"/>
-      <c r="AL381" s="336"/>
-      <c r="AM381" s="336"/>
-      <c r="AN381" s="336"/>
-      <c r="AO381" s="336"/>
-      <c r="AP381" s="336"/>
-      <c r="AQ381" s="336"/>
-    </row>
-    <row r="382" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A382" s="332" t="s">
-        <v>3961</v>
-      </c>
-      <c r="B382" s="326" t="s">
-        <v>430</v>
-      </c>
-      <c r="C382" s="333"/>
-      <c r="D382" s="334"/>
-      <c r="E382" s="335"/>
-      <c r="F382" s="391" t="s">
-        <v>3962</v>
-      </c>
-      <c r="G382" s="336"/>
-      <c r="H382" s="337" t="s">
-        <v>3967</v>
-      </c>
-      <c r="I382" s="337" t="s">
-        <v>2501</v>
-      </c>
-      <c r="J382" s="338"/>
-      <c r="K382" s="338"/>
-      <c r="L382" s="338"/>
-      <c r="M382" s="339" t="s">
-        <v>3123</v>
-      </c>
-      <c r="N382" s="329" t="s">
-        <v>3965</v>
-      </c>
-      <c r="O382" s="329"/>
-      <c r="P382" s="330"/>
-      <c r="Q382" s="331"/>
-      <c r="R382" s="427"/>
-      <c r="S382" s="340" t="s">
-        <v>41</v>
-      </c>
-      <c r="T382" s="341"/>
-      <c r="U382" s="342"/>
-      <c r="V382" s="342"/>
-      <c r="W382" s="343" t="s">
-        <v>2231</v>
-      </c>
-      <c r="X382" s="343" t="s">
-        <v>2232</v>
-      </c>
-      <c r="Y382" s="344" t="s">
-        <v>3964</v>
-      </c>
-      <c r="Z382" s="349" t="s">
-        <v>3963</v>
-      </c>
-      <c r="AA382" s="345"/>
-      <c r="AB382" s="448"/>
-      <c r="AC382" s="336"/>
-      <c r="AD382" s="341"/>
-      <c r="AE382" s="32"/>
-      <c r="AF382" s="32"/>
-      <c r="AG382" s="32"/>
-      <c r="AH382" s="32"/>
-      <c r="AI382" s="32"/>
-      <c r="AJ382" s="32"/>
-      <c r="AK382" s="32"/>
-      <c r="AL382" s="32"/>
-      <c r="AM382" s="32"/>
-      <c r="AN382" s="32"/>
-      <c r="AO382" s="32"/>
-      <c r="AP382" s="32"/>
-      <c r="AQ382" s="32"/>
+      <c r="AE381" s="328"/>
+      <c r="AF381" s="328"/>
+      <c r="AG381" s="328"/>
+      <c r="AH381" s="328"/>
+      <c r="AI381" s="328"/>
+      <c r="AJ381" s="328"/>
+      <c r="AK381" s="328"/>
+      <c r="AL381" s="328"/>
+      <c r="AM381" s="328"/>
+      <c r="AN381" s="328"/>
+      <c r="AO381" s="328"/>
+      <c r="AP381" s="328"/>
+      <c r="AQ381" s="328"/>
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A383" s="479" t="s">
-        <v>3980</v>
+      <c r="A383" s="458" t="s">
+        <v>3974</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>430</v>
@@ -49053,7 +48954,7 @@
       <c r="AQ383" s="32"/>
     </row>
     <row r="384" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A384" s="479" t="s">
+      <c r="A384" s="458" t="s">
         <v>3820</v>
       </c>
       <c r="B384" s="33" t="s">
@@ -49122,7 +49023,7 @@
       <c r="AQ384" s="32"/>
     </row>
     <row r="385" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A385" s="479" t="s">
+      <c r="A385" s="458" t="s">
         <v>3819</v>
       </c>
       <c r="B385" s="33" t="s">
@@ -49191,7 +49092,7 @@
       <c r="AQ385" s="32"/>
     </row>
     <row r="386" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A386" s="479" t="s">
+      <c r="A386" s="458" t="s">
         <v>3133</v>
       </c>
       <c r="B386" s="33" t="s">
@@ -49260,7 +49161,7 @@
       <c r="AQ386" s="32"/>
     </row>
     <row r="387" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A387" s="479" t="s">
+      <c r="A387" s="458" t="s">
         <v>3138</v>
       </c>
       <c r="B387" s="33" t="s">
@@ -49335,7 +49236,7 @@
       <c r="AQ387" s="32"/>
     </row>
     <row r="388" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A388" s="479" t="s">
+      <c r="A388" s="458" t="s">
         <v>3818</v>
       </c>
       <c r="B388" s="33" t="s">
@@ -49414,24 +49315,24 @@
       <c r="AQ388" s="32"/>
     </row>
     <row r="389" spans="1:43" ht="45.75" customHeight="1">
-      <c r="A389" s="482" t="s">
+      <c r="A389" s="461" t="s">
         <v>3157</v>
       </c>
-      <c r="B389" s="376" t="s">
+      <c r="B389" s="358" t="s">
         <v>3772</v>
       </c>
       <c r="C389" s="259" t="s">
         <v>171</v>
       </c>
       <c r="E389" s="227"/>
-      <c r="F389" s="388" t="s">
+      <c r="F389" s="370" t="s">
         <v>3773</v>
       </c>
       <c r="G389" s="227"/>
-      <c r="H389" s="395" t="s">
+      <c r="H389" s="376" t="s">
         <v>3774</v>
       </c>
-      <c r="I389" s="395" t="s">
+      <c r="I389" s="376" t="s">
         <v>3158</v>
       </c>
       <c r="J389" s="227"/>
@@ -49439,10 +49340,10 @@
       <c r="L389" s="227" t="s">
         <v>3775</v>
       </c>
-      <c r="M389" s="405" t="s">
+      <c r="M389" s="386" t="s">
         <v>2076</v>
       </c>
-      <c r="N389" s="414" t="s">
+      <c r="N389" s="395" t="s">
         <v>2077</v>
       </c>
       <c r="O389" s="227"/>
@@ -49451,10 +49352,10 @@
       <c r="R389" s="227" t="s">
         <v>638</v>
       </c>
-      <c r="S389" s="378" t="s">
+      <c r="S389" s="360" t="s">
         <v>41</v>
       </c>
-      <c r="T389" s="378" t="s">
+      <c r="T389" s="360" t="s">
         <v>3776</v>
       </c>
       <c r="U389" s="227"/>
@@ -49466,7 +49367,7 @@
       <c r="AA389" s="227"/>
       <c r="AB389" s="227"/>
       <c r="AC389" s="227"/>
-      <c r="AD389" s="378" t="s">
+      <c r="AD389" s="360" t="s">
         <v>3777</v>
       </c>
       <c r="AE389" s="227"/>
@@ -49484,7 +49385,7 @@
       <c r="AQ389" s="227"/>
     </row>
     <row r="390" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A390" s="479" t="s">
+      <c r="A390" s="458" t="s">
         <v>3159</v>
       </c>
       <c r="B390" s="33" t="s">
@@ -49516,7 +49417,7 @@
       <c r="N390" s="54" t="s">
         <v>3165</v>
       </c>
-      <c r="O390" s="413"/>
+      <c r="O390" s="394"/>
       <c r="P390" s="112"/>
       <c r="Q390" s="56"/>
       <c r="R390" s="295" t="s">
@@ -49557,7 +49458,7 @@
       <c r="AQ390" s="32"/>
     </row>
     <row r="391" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A391" s="479" t="s">
+      <c r="A391" s="458" t="s">
         <v>3167</v>
       </c>
       <c r="B391" s="33" t="s">
@@ -49642,7 +49543,7 @@
       <c r="AQ391" s="32"/>
     </row>
     <row r="392" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A392" s="479" t="s">
+      <c r="A392" s="458" t="s">
         <v>3177</v>
       </c>
       <c r="B392" s="33" t="s">
@@ -49717,10 +49618,10 @@
       <c r="AQ392" s="32"/>
     </row>
     <row r="393" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A393" s="483" t="s">
+      <c r="A393" s="462" t="s">
         <v>3184</v>
       </c>
-      <c r="B393" s="375" t="s">
+      <c r="B393" s="357" t="s">
         <v>430</v>
       </c>
       <c r="C393" s="252" t="s">
@@ -49728,11 +49629,11 @@
       </c>
       <c r="D393" s="308"/>
       <c r="E393" s="136"/>
-      <c r="F393" s="387" t="s">
+      <c r="F393" s="369" t="s">
         <v>3185</v>
       </c>
       <c r="G393" s="32"/>
-      <c r="H393" s="394" t="s">
+      <c r="H393" s="375" t="s">
         <v>3186</v>
       </c>
       <c r="I393" s="39" t="s">
@@ -49746,10 +49647,10 @@
       <c r="M393" s="135" t="s">
         <v>538</v>
       </c>
-      <c r="N393" s="413" t="s">
+      <c r="N393" s="394" t="s">
         <v>3187</v>
       </c>
-      <c r="O393" s="413"/>
+      <c r="O393" s="394"/>
       <c r="P393" s="112"/>
       <c r="Q393" s="121"/>
       <c r="R393" s="96" t="s">
@@ -49761,8 +49662,8 @@
       <c r="T393" s="104" t="s">
         <v>3188</v>
       </c>
-      <c r="U393" s="431"/>
-      <c r="V393" s="431"/>
+      <c r="U393" s="411"/>
+      <c r="V393" s="411"/>
       <c r="W393" s="29" t="s">
         <v>2231</v>
       </c>
@@ -49776,7 +49677,7 @@
       <c r="AA393" s="102" t="s">
         <v>3190</v>
       </c>
-      <c r="AB393" s="444"/>
+      <c r="AB393" s="424"/>
       <c r="AC393" s="39"/>
       <c r="AD393" s="104"/>
       <c r="AE393" s="39"/>
@@ -49794,7 +49695,7 @@
       <c r="AQ393" s="39"/>
     </row>
     <row r="394" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A394" s="479" t="s">
+      <c r="A394" s="458" t="s">
         <v>3191</v>
       </c>
       <c r="B394" s="33" t="s">
@@ -49871,7 +49772,7 @@
       <c r="AQ394" s="32"/>
     </row>
     <row r="395" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A395" s="479" t="s">
+      <c r="A395" s="458" t="s">
         <v>3197</v>
       </c>
       <c r="B395" s="33" t="s">
@@ -49942,7 +49843,7 @@
       <c r="AQ395" s="32"/>
     </row>
     <row r="396" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A396" s="479" t="s">
+      <c r="A396" s="458" t="s">
         <v>3204</v>
       </c>
       <c r="B396" s="33" t="s">
@@ -50021,7 +49922,7 @@
       <c r="AQ396" s="32"/>
     </row>
     <row r="397" spans="1:43" ht="41.25" customHeight="1">
-      <c r="A397" s="479" t="s">
+      <c r="A397" s="458" t="s">
         <v>3212</v>
       </c>
       <c r="B397" s="33" t="s">
@@ -50102,7 +50003,7 @@
       <c r="AQ397" s="32"/>
     </row>
     <row r="398" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A398" s="479" t="s">
+      <c r="A398" s="458" t="s">
         <v>3812</v>
       </c>
       <c r="B398" s="33" t="s">
@@ -50167,7 +50068,7 @@
       <c r="AQ398" s="32"/>
     </row>
     <row r="399" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A399" s="479" t="s">
+      <c r="A399" s="458" t="s">
         <v>3226</v>
       </c>
       <c r="B399" s="33" t="s">
@@ -50234,7 +50135,7 @@
       <c r="AQ399" s="32"/>
     </row>
     <row r="400" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A400" s="479" t="s">
+      <c r="A400" s="458" t="s">
         <v>3813</v>
       </c>
       <c r="B400" s="33" t="s">
@@ -50313,7 +50214,7 @@
       <c r="AQ400" s="32"/>
     </row>
     <row r="401" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A401" s="479" t="s">
+      <c r="A401" s="458" t="s">
         <v>3241</v>
       </c>
       <c r="B401" s="33" t="s">
@@ -50335,11 +50236,11 @@
         <v>2541</v>
       </c>
       <c r="J401" s="22"/>
-      <c r="K401" s="402" t="s">
+      <c r="K401" s="383" t="s">
         <v>34</v>
       </c>
-      <c r="L401" s="402"/>
-      <c r="M401" s="406" t="s">
+      <c r="L401" s="383"/>
+      <c r="M401" s="387" t="s">
         <v>3244</v>
       </c>
       <c r="N401" s="38" t="s">
@@ -50390,7 +50291,7 @@
       <c r="AQ401" s="32"/>
     </row>
     <row r="402" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A402" s="479" t="s">
+      <c r="A402" s="458" t="s">
         <v>3248</v>
       </c>
       <c r="B402" s="48" t="s">
@@ -50467,7 +50368,7 @@
       <c r="AQ402" s="32"/>
     </row>
     <row r="403" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A403" s="479" t="s">
+      <c r="A403" s="458" t="s">
         <v>3814</v>
       </c>
       <c r="B403" s="33" t="s">
@@ -50493,7 +50394,7 @@
       <c r="L403" s="22" t="s">
         <v>3258</v>
       </c>
-      <c r="M403" s="406" t="s">
+      <c r="M403" s="387" t="s">
         <v>3259</v>
       </c>
       <c r="N403" s="38" t="s">
@@ -50548,7 +50449,7 @@
       <c r="AQ403" s="32"/>
     </row>
     <row r="404" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A404" s="479" t="s">
+      <c r="A404" s="458" t="s">
         <v>3266</v>
       </c>
       <c r="B404" s="33" t="s">
@@ -50603,7 +50504,7 @@
       <c r="Y404" s="195" t="s">
         <v>3272</v>
       </c>
-      <c r="Z404" s="438"/>
+      <c r="Z404" s="418"/>
       <c r="AA404" s="195" t="s">
         <v>3273</v>
       </c>
@@ -50629,7 +50530,7 @@
       <c r="AQ404" s="32"/>
     </row>
     <row r="405" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A405" s="479" t="s">
+      <c r="A405" s="458" t="s">
         <v>3276</v>
       </c>
       <c r="B405" s="33" t="s">
@@ -50684,7 +50585,7 @@
       <c r="Y405" s="195" t="s">
         <v>3280</v>
       </c>
-      <c r="Z405" s="438"/>
+      <c r="Z405" s="418"/>
       <c r="AA405" s="195" t="s">
         <v>3281</v>
       </c>
@@ -50710,7 +50611,7 @@
       <c r="AQ405" s="32"/>
     </row>
     <row r="406" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A406" s="479" t="s">
+      <c r="A406" s="458" t="s">
         <v>3815</v>
       </c>
       <c r="B406" s="14" t="s">
@@ -50767,7 +50668,7 @@
       <c r="Y406" s="195" t="s">
         <v>3247</v>
       </c>
-      <c r="Z406" s="438"/>
+      <c r="Z406" s="418"/>
       <c r="AA406" s="195" t="s">
         <v>3288</v>
       </c>
@@ -50791,7 +50692,7 @@
       <c r="AQ406" s="32"/>
     </row>
     <row r="407" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A407" s="479" t="s">
+      <c r="A407" s="458" t="s">
         <v>3290</v>
       </c>
       <c r="B407" s="33" t="s">
@@ -50868,7 +50769,7 @@
       <c r="AQ407" s="32"/>
     </row>
     <row r="408" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A408" s="479" t="s">
+      <c r="A408" s="458" t="s">
         <v>3296</v>
       </c>
       <c r="B408" s="32" t="s">
@@ -50939,7 +50840,7 @@
       <c r="AQ408" s="32"/>
     </row>
     <row r="409" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A409" s="479" t="s">
+      <c r="A409" s="458" t="s">
         <v>3786</v>
       </c>
       <c r="B409" s="33" t="s">
@@ -51012,7 +50913,7 @@
       <c r="AQ409" s="32"/>
     </row>
     <row r="410" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A410" s="479" t="s">
+      <c r="A410" s="458" t="s">
         <v>3817</v>
       </c>
       <c r="B410" s="33" t="s">
@@ -51087,7 +50988,7 @@
       <c r="AQ410" s="32"/>
     </row>
     <row r="411" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A411" s="479" t="s">
+      <c r="A411" s="458" t="s">
         <v>3320</v>
       </c>
       <c r="B411" s="33" t="s">
@@ -51162,7 +51063,7 @@
       <c r="AQ411" s="32"/>
     </row>
     <row r="412" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A412" s="479" t="s">
+      <c r="A412" s="458" t="s">
         <v>3326</v>
       </c>
       <c r="B412" s="33" t="s">
@@ -51235,7 +51136,7 @@
       <c r="AQ412" s="32"/>
     </row>
     <row r="413" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A413" s="479" t="s">
+      <c r="A413" s="458" t="s">
         <v>3333</v>
       </c>
       <c r="B413" s="33" t="s">
@@ -51312,7 +51213,7 @@
       <c r="AQ413" s="32"/>
     </row>
     <row r="414" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A414" s="479" t="s">
+      <c r="A414" s="458" t="s">
         <v>3340</v>
       </c>
       <c r="B414" s="95" t="s">
@@ -51387,7 +51288,7 @@
       <c r="AQ414" s="32"/>
     </row>
     <row r="415" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A415" s="479" t="s">
+      <c r="A415" s="458" t="s">
         <v>3816</v>
       </c>
       <c r="B415" s="33" t="s">
@@ -51462,7 +51363,7 @@
       <c r="AQ415" s="32"/>
     </row>
     <row r="416" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A416" s="479" t="s">
+      <c r="A416" s="458" t="s">
         <v>3919</v>
       </c>
       <c r="B416" s="33" t="s">
@@ -51541,7 +51442,7 @@
       <c r="AQ416" s="32"/>
     </row>
     <row r="417" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A417" s="479" t="s">
+      <c r="A417" s="458" t="s">
         <v>3905</v>
       </c>
       <c r="B417" s="33" t="s">
@@ -51608,7 +51509,7 @@
       <c r="AQ417" s="32"/>
     </row>
     <row r="418" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A418" s="479" t="s">
+      <c r="A418" s="458" t="s">
         <v>3906</v>
       </c>
       <c r="B418" s="33" t="s">
@@ -51677,13 +51578,13 @@
       <c r="AQ418" s="32"/>
     </row>
     <row r="419" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A419" s="479" t="s">
+      <c r="A419" s="458" t="s">
         <v>3907</v>
       </c>
       <c r="B419" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="C419" s="379" t="s">
+      <c r="C419" s="361" t="s">
         <v>3939</v>
       </c>
       <c r="D419" s="232"/>
@@ -51746,7 +51647,7 @@
       <c r="AQ419" s="32"/>
     </row>
     <row r="420" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A420" s="479" t="s">
+      <c r="A420" s="458" t="s">
         <v>3375</v>
       </c>
       <c r="B420" s="33" t="s">
@@ -51799,7 +51700,7 @@
       <c r="Y420" s="30" t="s">
         <v>3379</v>
       </c>
-      <c r="Z420" s="438"/>
+      <c r="Z420" s="418"/>
       <c r="AA420" s="30" t="s">
         <v>3380</v>
       </c>
@@ -51821,13 +51722,13 @@
       <c r="AQ420" s="32"/>
     </row>
     <row r="421" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A421" s="479" t="s">
+      <c r="A421" s="458" t="s">
         <v>3381</v>
       </c>
       <c r="B421" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="C421" s="379" t="s">
+      <c r="C421" s="361" t="s">
         <v>3917</v>
       </c>
       <c r="D421" s="244"/>
@@ -51837,7 +51738,7 @@
       </c>
       <c r="G421" s="184"/>
       <c r="H421" s="203" t="s">
-        <v>3975</v>
+        <v>3969</v>
       </c>
       <c r="I421" s="32" t="s">
         <v>2501</v>
@@ -51900,7 +51801,7 @@
       <c r="AQ421" s="32"/>
     </row>
     <row r="422" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A422" s="479" t="s">
+      <c r="A422" s="458" t="s">
         <v>3389</v>
       </c>
       <c r="B422" s="33" t="s">
@@ -51983,7 +51884,7 @@
       <c r="AQ422" s="32"/>
     </row>
     <row r="423" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A423" s="479" t="s">
+      <c r="A423" s="458" t="s">
         <v>3400</v>
       </c>
       <c r="B423" s="33" t="s">
@@ -51999,7 +51900,7 @@
       </c>
       <c r="G423" s="184"/>
       <c r="H423" s="203" t="s">
-        <v>3972</v>
+        <v>3966</v>
       </c>
       <c r="I423" s="190" t="s">
         <v>2501</v>
@@ -52044,10 +51945,10 @@
       </c>
       <c r="Z423" s="30"/>
       <c r="AA423" s="30" t="s">
-        <v>3973</v>
+        <v>3967</v>
       </c>
       <c r="AB423" s="41" t="s">
-        <v>3974</v>
+        <v>3968</v>
       </c>
       <c r="AC423" s="32"/>
       <c r="AD423" s="32"/>
@@ -52066,7 +51967,7 @@
       <c r="AQ423" s="32"/>
     </row>
     <row r="424" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A424" s="479" t="s">
+      <c r="A424" s="458" t="s">
         <v>3908</v>
       </c>
       <c r="B424" s="14" t="s">
@@ -52137,7 +52038,7 @@
       <c r="AQ424" s="32"/>
     </row>
     <row r="425" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A425" s="479" t="s">
+      <c r="A425" s="458" t="s">
         <v>3909</v>
       </c>
       <c r="B425" s="33" t="s">
@@ -52214,7 +52115,7 @@
       <c r="AQ425" s="32"/>
     </row>
     <row r="426" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A426" s="479" t="s">
+      <c r="A426" s="458" t="s">
         <v>3419</v>
       </c>
       <c r="B426" s="33" t="s">
@@ -52279,7 +52180,7 @@
       <c r="AQ426" s="32"/>
     </row>
     <row r="427" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A427" s="479" t="s">
+      <c r="A427" s="458" t="s">
         <v>3422</v>
       </c>
       <c r="B427" s="33" t="s">
@@ -52346,7 +52247,7 @@
       <c r="AQ427" s="32"/>
     </row>
     <row r="428" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A428" s="479" t="s">
+      <c r="A428" s="458" t="s">
         <v>3425</v>
       </c>
       <c r="B428" s="14" t="s">
@@ -52419,7 +52320,7 @@
       <c r="AQ428" s="32"/>
     </row>
     <row r="429" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A429" s="479" t="s">
+      <c r="A429" s="458" t="s">
         <v>3431</v>
       </c>
       <c r="B429" s="33" t="s">
@@ -52451,7 +52352,7 @@
       <c r="N429" s="54" t="s">
         <v>3363</v>
       </c>
-      <c r="O429" s="413"/>
+      <c r="O429" s="394"/>
       <c r="P429" s="112"/>
       <c r="Q429" s="121"/>
       <c r="R429" s="115" t="s">
@@ -52492,7 +52393,7 @@
       <c r="AQ429" s="32"/>
     </row>
     <row r="430" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A430" s="479" t="s">
+      <c r="A430" s="458" t="s">
         <v>3910</v>
       </c>
       <c r="B430" s="33" t="s">
@@ -52559,7 +52460,7 @@
       <c r="AQ430" s="32"/>
     </row>
     <row r="431" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A431" s="479" t="s">
+      <c r="A431" s="458" t="s">
         <v>3911</v>
       </c>
       <c r="B431" s="33" t="s">
@@ -52624,7 +52525,7 @@
       <c r="AQ431" s="32"/>
     </row>
     <row r="432" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A432" s="479" t="s">
+      <c r="A432" s="458" t="s">
         <v>3912</v>
       </c>
       <c r="B432" s="33" t="s">
@@ -52656,7 +52557,7 @@
       <c r="N432" s="54" t="s">
         <v>3443</v>
       </c>
-      <c r="O432" s="413"/>
+      <c r="O432" s="394"/>
       <c r="P432" s="112"/>
       <c r="Q432" s="121"/>
       <c r="R432" s="296" t="s">
@@ -52691,7 +52592,7 @@
       <c r="AQ432" s="32"/>
     </row>
     <row r="433" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A433" s="479" t="s">
+      <c r="A433" s="458" t="s">
         <v>3445</v>
       </c>
       <c r="B433" s="33" t="s">
@@ -52768,7 +52669,7 @@
       <c r="AQ433" s="32"/>
     </row>
     <row r="434" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A434" s="479" t="s">
+      <c r="A434" s="458" t="s">
         <v>3452</v>
       </c>
       <c r="B434" s="33" t="s">
@@ -52839,7 +52740,7 @@
       <c r="AQ434" s="32"/>
     </row>
     <row r="435" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A435" s="479" t="s">
+      <c r="A435" s="458" t="s">
         <v>3913</v>
       </c>
       <c r="B435" s="33" t="s">
@@ -52904,7 +52805,7 @@
       <c r="AQ435" s="32"/>
     </row>
     <row r="436" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A436" s="479" t="s">
+      <c r="A436" s="458" t="s">
         <v>3914</v>
       </c>
       <c r="B436" s="33" t="s">
@@ -52971,7 +52872,7 @@
       <c r="AQ436" s="32"/>
     </row>
     <row r="437" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A437" s="479" t="s">
+      <c r="A437" s="458" t="s">
         <v>3463</v>
       </c>
       <c r="B437" s="33" t="s">
@@ -53050,7 +52951,7 @@
       <c r="AQ437" s="32"/>
     </row>
     <row r="438" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A438" s="479" t="s">
+      <c r="A438" s="458" t="s">
         <v>3915</v>
       </c>
       <c r="B438" s="33" t="s">
@@ -53123,7 +53024,7 @@
       <c r="AQ438" s="32"/>
     </row>
     <row r="439" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A439" s="479" t="s">
+      <c r="A439" s="458" t="s">
         <v>3476</v>
       </c>
       <c r="B439" s="95" t="s">
@@ -53198,7 +53099,7 @@
       <c r="AQ439" s="32"/>
     </row>
     <row r="440" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A440" s="479" t="s">
+      <c r="A440" s="458" t="s">
         <v>3484</v>
       </c>
       <c r="B440" s="14" t="s">
@@ -53230,7 +53131,7 @@
       <c r="N440" s="54" t="s">
         <v>1943</v>
       </c>
-      <c r="O440" s="413"/>
+      <c r="O440" s="394"/>
       <c r="P440" s="112"/>
       <c r="Q440" s="56"/>
       <c r="R440" s="96" t="s">
@@ -53273,7 +53174,7 @@
       <c r="AQ440" s="32"/>
     </row>
     <row r="441" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A441" s="479" t="s">
+      <c r="A441" s="458" t="s">
         <v>3486</v>
       </c>
       <c r="B441" s="33" t="s">
@@ -53303,7 +53204,7 @@
       <c r="N441" s="134" t="s">
         <v>1236</v>
       </c>
-      <c r="O441" s="416" t="s">
+      <c r="O441" s="397" t="s">
         <v>3490</v>
       </c>
       <c r="P441" s="59"/>
@@ -53352,7 +53253,7 @@
       <c r="AQ441" s="32"/>
     </row>
     <row r="442" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A442" s="479" t="s">
+      <c r="A442" s="458" t="s">
         <v>3495</v>
       </c>
       <c r="B442" s="33" t="s">
@@ -53433,7 +53334,7 @@
       <c r="AQ442" s="32"/>
     </row>
     <row r="443" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A443" s="479" t="s">
+      <c r="A443" s="458" t="s">
         <v>3920</v>
       </c>
       <c r="B443" s="33" t="s">
@@ -53506,7 +53407,7 @@
       <c r="AQ443" s="32"/>
     </row>
     <row r="444" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A444" s="479" t="s">
+      <c r="A444" s="458" t="s">
         <v>3510</v>
       </c>
       <c r="B444" s="33" t="s">
@@ -53575,7 +53476,7 @@
       <c r="AQ444" s="32"/>
     </row>
     <row r="445" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A445" s="479" t="s">
+      <c r="A445" s="458" t="s">
         <v>3515</v>
       </c>
       <c r="B445" s="33" t="s">
@@ -53656,7 +53557,7 @@
       <c r="AQ445" s="32"/>
     </row>
     <row r="446" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A446" s="479" t="s">
+      <c r="A446" s="458" t="s">
         <v>3523</v>
       </c>
       <c r="B446" s="33" t="s">
@@ -53737,7 +53638,7 @@
       <c r="AQ446" s="32"/>
     </row>
     <row r="447" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A447" s="479" t="s">
+      <c r="A447" s="458" t="s">
         <v>3921</v>
       </c>
       <c r="B447" s="33" t="s">
@@ -53810,7 +53711,7 @@
       <c r="AQ447" s="32"/>
     </row>
     <row r="448" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A448" s="479" t="s">
+      <c r="A448" s="458" t="s">
         <v>3922</v>
       </c>
       <c r="B448" s="33" t="s">
@@ -53877,7 +53778,7 @@
       <c r="AQ448" s="32"/>
     </row>
     <row r="449" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A449" s="479" t="s">
+      <c r="A449" s="458" t="s">
         <v>3540</v>
       </c>
       <c r="B449" s="33" t="s">
@@ -53950,7 +53851,7 @@
       <c r="AQ449" s="32"/>
     </row>
     <row r="450" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A450" s="479" t="s">
+      <c r="A450" s="458" t="s">
         <v>3546</v>
       </c>
       <c r="B450" s="33" t="s">
@@ -54023,7 +53924,7 @@
       <c r="AQ450" s="32"/>
     </row>
     <row r="451" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A451" s="479" t="s">
+      <c r="A451" s="458" t="s">
         <v>3550</v>
       </c>
       <c r="B451" s="33" t="s">
@@ -54104,7 +54005,7 @@
       <c r="AQ451" s="32"/>
     </row>
     <row r="452" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A452" s="479" t="s">
+      <c r="A452" s="458" t="s">
         <v>3556</v>
       </c>
       <c r="B452" s="33" t="s">
@@ -54169,7 +54070,7 @@
       <c r="AQ452" s="32"/>
     </row>
     <row r="453" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A453" s="479" t="s">
+      <c r="A453" s="458" t="s">
         <v>3561</v>
       </c>
       <c r="B453" s="33" t="s">
@@ -54242,7 +54143,7 @@
       <c r="AQ453" s="32"/>
     </row>
     <row r="454" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A454" s="479" t="s">
+      <c r="A454" s="458" t="s">
         <v>3570</v>
       </c>
       <c r="B454" s="33" t="s">
@@ -54315,7 +54216,7 @@
       <c r="AQ454" s="21"/>
     </row>
     <row r="455" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A455" s="479" t="s">
+      <c r="A455" s="458" t="s">
         <v>3923</v>
       </c>
       <c r="B455" s="95" t="s">
@@ -54388,7 +54289,7 @@
       <c r="AQ455" s="32"/>
     </row>
     <row r="456" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A456" s="479" t="s">
+      <c r="A456" s="458" t="s">
         <v>3580</v>
       </c>
       <c r="B456" s="95" t="s">
@@ -54467,7 +54368,7 @@
       <c r="AQ456" s="32"/>
     </row>
     <row r="457" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A457" s="479" t="s">
+      <c r="A457" s="458" t="s">
         <v>3925</v>
       </c>
       <c r="B457" s="32" t="s">
@@ -54548,7 +54449,7 @@
       <c r="AQ457" s="32"/>
     </row>
     <row r="458" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A458" s="479" t="s">
+      <c r="A458" s="458" t="s">
         <v>3926</v>
       </c>
       <c r="B458" s="95" t="s">
@@ -54629,7 +54530,7 @@
       <c r="AQ458" s="32"/>
     </row>
     <row r="459" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A459" s="479" t="s">
+      <c r="A459" s="458" t="s">
         <v>3927</v>
       </c>
       <c r="B459" s="95" t="s">
@@ -54702,7 +54603,7 @@
       <c r="AQ459" s="32"/>
     </row>
     <row r="460" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A460" s="479" t="s">
+      <c r="A460" s="458" t="s">
         <v>3603</v>
       </c>
       <c r="B460" s="95" t="s">
@@ -54781,7 +54682,7 @@
       <c r="AQ460" s="32"/>
     </row>
     <row r="461" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A461" s="479" t="s">
+      <c r="A461" s="458" t="s">
         <v>3928</v>
       </c>
       <c r="B461" s="95" t="s">
@@ -54813,7 +54714,7 @@
       <c r="N461" s="134" t="s">
         <v>3616</v>
       </c>
-      <c r="O461" s="413" t="s">
+      <c r="O461" s="394" t="s">
         <v>3617</v>
       </c>
       <c r="P461" s="112"/>
@@ -54856,7 +54757,7 @@
       <c r="AQ461" s="32"/>
     </row>
     <row r="462" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A462" s="479" t="s">
+      <c r="A462" s="458" t="s">
         <v>3929</v>
       </c>
       <c r="B462" s="95" t="s">
@@ -54937,7 +54838,7 @@
       <c r="AQ462" s="32"/>
     </row>
     <row r="463" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A463" s="479" t="s">
+      <c r="A463" s="458" t="s">
         <v>3625</v>
       </c>
       <c r="B463" s="95" t="s">
@@ -55035,11 +54936,11 @@
       <c r="I464" s="275" t="s">
         <v>3634</v>
       </c>
-      <c r="J464" s="399" t="s">
+      <c r="J464" s="380" t="s">
         <v>2268</v>
       </c>
-      <c r="K464" s="399"/>
-      <c r="L464" s="399"/>
+      <c r="K464" s="380"/>
+      <c r="L464" s="380"/>
       <c r="M464" s="276" t="s">
         <v>1597</v>
       </c>
@@ -55049,7 +54950,7 @@
       <c r="O464" s="277"/>
       <c r="P464" s="278"/>
       <c r="Q464" s="279"/>
-      <c r="R464" s="425" t="s">
+      <c r="R464" s="406" t="s">
         <v>3636</v>
       </c>
       <c r="S464" s="280" t="s">
@@ -55081,7 +54982,7 @@
       <c r="AQ464" s="286"/>
     </row>
     <row r="465" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A465" s="485" t="s">
+      <c r="A465" s="463" t="s">
         <v>3930</v>
       </c>
       <c r="B465" s="95" t="s">
@@ -55158,7 +55059,7 @@
       <c r="AQ465" s="32"/>
     </row>
     <row r="466" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A466" s="479" t="s">
+      <c r="A466" s="458" t="s">
         <v>3932</v>
       </c>
       <c r="B466" s="95" t="s">
@@ -55235,7 +55136,7 @@
       <c r="AQ466" s="32"/>
     </row>
     <row r="467" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A467" s="486" t="s">
+      <c r="A467" s="464" t="s">
         <v>3931</v>
       </c>
       <c r="B467" s="95" t="s">
@@ -55279,7 +55180,7 @@
         <v>3663</v>
       </c>
       <c r="R467" s="94" t="s">
-        <v>3992</v>
+        <v>3986</v>
       </c>
       <c r="S467" s="77" t="s">
         <v>41</v>
@@ -55310,7 +55211,7 @@
       <c r="AQ467" s="32"/>
     </row>
     <row r="468" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A468" s="479" t="s">
+      <c r="A468" s="458" t="s">
         <v>3664</v>
       </c>
       <c r="B468" s="95" t="s">
@@ -55385,7 +55286,7 @@
       <c r="AQ468" s="32"/>
     </row>
     <row r="469" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A469" s="479" t="s">
+      <c r="A469" s="458" t="s">
         <v>3670</v>
       </c>
       <c r="B469" s="95" t="s">
@@ -55460,7 +55361,7 @@
       <c r="AQ469" s="32"/>
     </row>
     <row r="470" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A470" s="479" t="s">
+      <c r="A470" s="458" t="s">
         <v>3933</v>
       </c>
       <c r="B470" s="95" t="s">
@@ -55474,7 +55375,7 @@
       <c r="F470" s="265" t="s">
         <v>3681</v>
       </c>
-      <c r="G470" s="393" t="s">
+      <c r="G470" s="374" t="s">
         <v>3682</v>
       </c>
       <c r="H470" s="48" t="s">
@@ -55490,7 +55391,7 @@
         <v>2475</v>
       </c>
       <c r="N470" s="54" t="s">
-        <v>4004</v>
+        <v>3998</v>
       </c>
       <c r="O470" s="54"/>
       <c r="P470" s="74" t="s">
@@ -55500,7 +55401,7 @@
         <v>3685</v>
       </c>
       <c r="R470" s="48" t="s">
-        <v>3987</v>
+        <v>3981</v>
       </c>
       <c r="S470" s="77" t="s">
         <v>41</v>
@@ -55531,7 +55432,7 @@
       <c r="AQ470" s="32"/>
     </row>
     <row r="471" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A471" s="479" t="s">
+      <c r="A471" s="458" t="s">
         <v>3686</v>
       </c>
       <c r="B471" s="95" t="s">
@@ -55606,7 +55507,7 @@
       <c r="AQ471" s="32"/>
     </row>
     <row r="472" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A472" s="479" t="s">
+      <c r="A472" s="458" t="s">
         <v>3695</v>
       </c>
       <c r="B472" s="95" t="s">
@@ -55673,7 +55574,7 @@
       <c r="AQ472" s="32"/>
     </row>
     <row r="473" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A473" s="487" t="s">
+      <c r="A473" s="465" t="s">
         <v>3701</v>
       </c>
       <c r="B473" s="95" t="s">
@@ -55690,10 +55591,10 @@
       <c r="G473" s="39" t="s">
         <v>3703</v>
       </c>
-      <c r="H473" s="393" t="s">
+      <c r="H473" s="374" t="s">
         <v>3704</v>
       </c>
-      <c r="I473" s="396" t="s">
+      <c r="I473" s="377" t="s">
         <v>2633</v>
       </c>
       <c r="J473" s="82" t="s">
@@ -55704,7 +55605,7 @@
       <c r="M473" s="303" t="s">
         <v>2941</v>
       </c>
-      <c r="N473" s="411" t="s">
+      <c r="N473" s="392" t="s">
         <v>3705</v>
       </c>
       <c r="O473" s="294"/>
@@ -55742,7 +55643,7 @@
       <c r="AQ473" s="39"/>
     </row>
     <row r="474" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A474" s="479" t="s">
+      <c r="A474" s="458" t="s">
         <v>3937</v>
       </c>
       <c r="B474" s="95" t="s">
@@ -55817,7 +55718,7 @@
       <c r="AQ474" s="32"/>
     </row>
     <row r="475" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A475" s="479" t="s">
+      <c r="A475" s="458" t="s">
         <v>3938</v>
       </c>
       <c r="B475" s="95" t="s">
@@ -55896,7 +55797,7 @@
       <c r="AQ475" s="32"/>
     </row>
     <row r="476" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A476" s="488" t="s">
+      <c r="A476" s="466" t="s">
         <v>3719</v>
       </c>
       <c r="B476" s="95" t="s">
@@ -55977,7 +55878,7 @@
       <c r="AQ476" s="32"/>
     </row>
     <row r="477" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A477" s="479" t="s">
+      <c r="A477" s="458" t="s">
         <v>3730</v>
       </c>
       <c r="B477" s="95" t="s">
@@ -56056,7 +55957,7 @@
       <c r="AQ477" s="32"/>
     </row>
     <row r="478" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A478" s="479" t="s">
+      <c r="A478" s="458" t="s">
         <v>3738</v>
       </c>
       <c r="B478" s="95" t="s">
@@ -56133,7 +56034,7 @@
       <c r="AQ478" s="32"/>
     </row>
     <row r="479" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A479" s="488" t="s">
+      <c r="A479" s="466" t="s">
         <v>3746</v>
       </c>
       <c r="B479" s="95" t="s">
@@ -56202,7 +56103,7 @@
       <c r="AQ479" s="32"/>
     </row>
     <row r="480" spans="1:43" ht="54" customHeight="1">
-      <c r="A480" s="489" t="s">
+      <c r="A480" s="467" t="s">
         <v>3754</v>
       </c>
       <c r="B480" s="95" t="s">
@@ -56272,455 +56173,455 @@
       <c r="AP480" s="32"/>
       <c r="AQ480" s="32"/>
     </row>
-    <row r="481" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A481" s="484"/>
-      <c r="B481" s="99"/>
-      <c r="C481" s="261"/>
-      <c r="D481" s="232"/>
-      <c r="E481" s="221"/>
-      <c r="F481" s="99"/>
-      <c r="G481" s="99"/>
-      <c r="H481" s="222"/>
-      <c r="I481" s="99"/>
-      <c r="J481" s="35"/>
-      <c r="K481" s="35"/>
-      <c r="L481" s="35"/>
-      <c r="M481" s="99"/>
-      <c r="N481" s="99"/>
-      <c r="O481" s="99"/>
-      <c r="P481" s="223"/>
-      <c r="Q481" s="224"/>
-      <c r="R481" s="99"/>
-      <c r="S481" s="99"/>
-      <c r="T481" s="157"/>
-      <c r="U481" s="158"/>
-      <c r="V481" s="158"/>
-      <c r="W481" s="110"/>
-      <c r="X481" s="110"/>
-      <c r="Y481" s="197"/>
-      <c r="Z481" s="197"/>
-      <c r="AA481" s="197"/>
-      <c r="AB481" s="225"/>
-      <c r="AC481" s="99"/>
-      <c r="AD481" s="157"/>
-      <c r="AE481" s="99"/>
-      <c r="AF481" s="99"/>
-      <c r="AG481" s="99"/>
-      <c r="AH481" s="99"/>
-      <c r="AI481" s="99"/>
-      <c r="AJ481" s="99"/>
-      <c r="AK481" s="99"/>
-      <c r="AL481" s="99"/>
-      <c r="AM481" s="99"/>
-      <c r="AN481" s="99"/>
-      <c r="AO481" s="99"/>
-      <c r="AP481" s="99"/>
-      <c r="AQ481" s="99"/>
-    </row>
-    <row r="482" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A482" s="99"/>
-      <c r="B482" s="99"/>
-      <c r="C482" s="261"/>
-      <c r="D482" s="232"/>
-      <c r="E482" s="221"/>
-      <c r="F482" s="99"/>
-      <c r="G482" s="99"/>
-      <c r="H482" s="222"/>
-      <c r="I482" s="99"/>
-      <c r="J482" s="35"/>
-      <c r="K482" s="35"/>
-      <c r="L482" s="35"/>
-      <c r="M482" s="99"/>
-      <c r="N482" s="99"/>
-      <c r="O482" s="99"/>
-      <c r="P482" s="223"/>
-      <c r="Q482" s="224"/>
-      <c r="R482" s="99"/>
-      <c r="S482" s="99"/>
-      <c r="T482" s="157"/>
-      <c r="U482" s="158"/>
-      <c r="V482" s="158"/>
-      <c r="W482" s="110"/>
-      <c r="X482" s="110"/>
-      <c r="Y482" s="197"/>
-      <c r="Z482" s="197"/>
-      <c r="AA482" s="197"/>
-      <c r="AB482" s="225"/>
-      <c r="AC482" s="99"/>
-      <c r="AD482" s="157"/>
-      <c r="AE482" s="99"/>
-      <c r="AF482" s="99"/>
-      <c r="AG482" s="99"/>
-      <c r="AH482" s="99"/>
-      <c r="AI482" s="99"/>
-      <c r="AJ482" s="99"/>
-      <c r="AK482" s="99"/>
-      <c r="AL482" s="99"/>
-      <c r="AM482" s="99"/>
-      <c r="AN482" s="99"/>
-      <c r="AO482" s="99"/>
-      <c r="AP482" s="99"/>
-      <c r="AQ482" s="99"/>
-    </row>
-    <row r="483" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A483" s="99"/>
-      <c r="B483" s="99"/>
-      <c r="C483" s="261"/>
-      <c r="D483" s="232"/>
-      <c r="E483" s="221"/>
-      <c r="F483" s="99"/>
-      <c r="G483" s="99"/>
-      <c r="H483" s="222"/>
-      <c r="I483" s="99"/>
-      <c r="J483" s="35"/>
-      <c r="K483" s="35"/>
-      <c r="L483" s="35"/>
-      <c r="M483" s="99"/>
-      <c r="N483" s="99"/>
-      <c r="O483" s="99"/>
-      <c r="P483" s="223"/>
-      <c r="Q483" s="224"/>
-      <c r="R483" s="99"/>
-      <c r="S483" s="99"/>
-      <c r="T483" s="157"/>
-      <c r="U483" s="158"/>
-      <c r="V483" s="158"/>
-      <c r="W483" s="110"/>
-      <c r="X483" s="110"/>
-      <c r="Y483" s="197"/>
-      <c r="Z483" s="197"/>
-      <c r="AA483" s="197"/>
-      <c r="AB483" s="225"/>
-      <c r="AC483" s="99"/>
-      <c r="AD483" s="157"/>
-      <c r="AE483" s="99"/>
-      <c r="AF483" s="99"/>
-      <c r="AG483" s="99"/>
-      <c r="AH483" s="99"/>
-      <c r="AI483" s="99"/>
-      <c r="AJ483" s="99"/>
-      <c r="AK483" s="99"/>
-      <c r="AL483" s="99"/>
-      <c r="AM483" s="99"/>
-      <c r="AN483" s="99"/>
-      <c r="AO483" s="99"/>
-      <c r="AP483" s="99"/>
-      <c r="AQ483" s="99"/>
-    </row>
-    <row r="484" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A484" s="99"/>
-      <c r="B484" s="99"/>
-      <c r="C484" s="261"/>
-      <c r="D484" s="232"/>
-      <c r="E484" s="221"/>
-      <c r="F484" s="99"/>
-      <c r="G484" s="99"/>
-      <c r="H484" s="222"/>
-      <c r="I484" s="99"/>
-      <c r="J484" s="35"/>
-      <c r="K484" s="35"/>
-      <c r="L484" s="35"/>
-      <c r="M484" s="99"/>
-      <c r="N484" s="99"/>
-      <c r="O484" s="99"/>
-      <c r="P484" s="223"/>
-      <c r="Q484" s="224"/>
-      <c r="R484" s="99"/>
-      <c r="S484" s="99"/>
-      <c r="T484" s="157"/>
-      <c r="U484" s="158"/>
-      <c r="V484" s="158"/>
-      <c r="W484" s="110"/>
-      <c r="X484" s="110"/>
-      <c r="Y484" s="197"/>
-      <c r="Z484" s="197"/>
-      <c r="AA484" s="197"/>
-      <c r="AB484" s="225"/>
-      <c r="AC484" s="99"/>
-      <c r="AD484" s="157"/>
-      <c r="AE484" s="99"/>
-      <c r="AF484" s="99"/>
-      <c r="AG484" s="99"/>
-      <c r="AH484" s="99"/>
-      <c r="AI484" s="99"/>
-      <c r="AJ484" s="99"/>
-      <c r="AK484" s="99"/>
-      <c r="AL484" s="99"/>
-      <c r="AM484" s="99"/>
-      <c r="AN484" s="99"/>
-      <c r="AO484" s="99"/>
-      <c r="AP484" s="99"/>
-      <c r="AQ484" s="99"/>
-    </row>
-    <row r="485" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A485" s="99"/>
-      <c r="B485" s="99"/>
-      <c r="C485" s="261"/>
-      <c r="D485" s="232"/>
-      <c r="E485" s="221"/>
-      <c r="F485" s="99"/>
-      <c r="G485" s="99"/>
-      <c r="H485" s="222"/>
-      <c r="I485" s="99"/>
-      <c r="J485" s="35"/>
-      <c r="K485" s="35"/>
-      <c r="L485" s="35"/>
-      <c r="M485" s="99"/>
-      <c r="N485" s="99"/>
-      <c r="O485" s="99"/>
-      <c r="P485" s="223"/>
-      <c r="Q485" s="224"/>
-      <c r="R485" s="99"/>
-      <c r="S485" s="99"/>
-      <c r="T485" s="157"/>
-      <c r="U485" s="158"/>
-      <c r="V485" s="158"/>
-      <c r="W485" s="110"/>
-      <c r="X485" s="110"/>
-      <c r="Y485" s="197"/>
-      <c r="Z485" s="197"/>
-      <c r="AA485" s="197"/>
-      <c r="AB485" s="225"/>
-      <c r="AC485" s="99"/>
-      <c r="AD485" s="157"/>
-      <c r="AE485" s="99"/>
-      <c r="AF485" s="99"/>
-      <c r="AG485" s="99"/>
-      <c r="AH485" s="99"/>
-      <c r="AI485" s="99"/>
-      <c r="AJ485" s="99"/>
-      <c r="AK485" s="99"/>
-      <c r="AL485" s="99"/>
-      <c r="AM485" s="99"/>
-      <c r="AN485" s="99"/>
-      <c r="AO485" s="99"/>
-      <c r="AP485" s="99"/>
-      <c r="AQ485" s="99"/>
-    </row>
-    <row r="486" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A486" s="99"/>
-      <c r="B486" s="99"/>
-      <c r="C486" s="261"/>
-      <c r="D486" s="232"/>
-      <c r="E486" s="221"/>
-      <c r="F486" s="99"/>
-      <c r="G486" s="99"/>
-      <c r="H486" s="222"/>
-      <c r="I486" s="99"/>
-      <c r="J486" s="35"/>
-      <c r="K486" s="35"/>
-      <c r="L486" s="35"/>
-      <c r="M486" s="99"/>
-      <c r="N486" s="99"/>
-      <c r="O486" s="99"/>
-      <c r="P486" s="223"/>
-      <c r="Q486" s="224"/>
-      <c r="R486" s="99"/>
-      <c r="S486" s="99"/>
-      <c r="T486" s="157"/>
-      <c r="U486" s="158"/>
-      <c r="V486" s="158"/>
-      <c r="W486" s="110"/>
-      <c r="X486" s="110"/>
-      <c r="Y486" s="197"/>
-      <c r="Z486" s="197"/>
-      <c r="AA486" s="197"/>
-      <c r="AB486" s="225"/>
-      <c r="AC486" s="99"/>
-      <c r="AD486" s="157"/>
-      <c r="AE486" s="99"/>
-      <c r="AF486" s="99"/>
-      <c r="AG486" s="99"/>
-      <c r="AH486" s="99"/>
-      <c r="AI486" s="99"/>
-      <c r="AJ486" s="99"/>
-      <c r="AK486" s="99"/>
-      <c r="AL486" s="99"/>
-      <c r="AM486" s="99"/>
-      <c r="AN486" s="99"/>
-      <c r="AO486" s="99"/>
-      <c r="AP486" s="99"/>
-      <c r="AQ486" s="99"/>
-    </row>
-    <row r="487" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A487" s="99"/>
-      <c r="B487" s="99"/>
-      <c r="C487" s="261"/>
-      <c r="D487" s="232"/>
-      <c r="E487" s="221"/>
-      <c r="F487" s="99"/>
-      <c r="G487" s="99"/>
-      <c r="H487" s="222"/>
-      <c r="I487" s="99"/>
-      <c r="J487" s="35"/>
-      <c r="K487" s="35"/>
-      <c r="L487" s="35"/>
-      <c r="M487" s="99"/>
-      <c r="N487" s="99"/>
-      <c r="O487" s="99"/>
-      <c r="P487" s="223"/>
-      <c r="Q487" s="224"/>
-      <c r="R487" s="99"/>
-      <c r="S487" s="99"/>
-      <c r="T487" s="157"/>
-      <c r="U487" s="158"/>
-      <c r="V487" s="158"/>
-      <c r="W487" s="110"/>
-      <c r="X487" s="110"/>
-      <c r="Y487" s="197"/>
-      <c r="Z487" s="197"/>
-      <c r="AA487" s="197"/>
-      <c r="AB487" s="225"/>
-      <c r="AC487" s="99"/>
-      <c r="AD487" s="157"/>
-      <c r="AE487" s="99"/>
-      <c r="AF487" s="99"/>
-      <c r="AG487" s="99"/>
-      <c r="AH487" s="99"/>
-      <c r="AI487" s="99"/>
-      <c r="AJ487" s="99"/>
-      <c r="AK487" s="99"/>
-      <c r="AL487" s="99"/>
-      <c r="AM487" s="99"/>
-      <c r="AN487" s="99"/>
-      <c r="AO487" s="99"/>
-      <c r="AP487" s="99"/>
-      <c r="AQ487" s="99"/>
-    </row>
-    <row r="488" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A488" s="99"/>
-      <c r="B488" s="99"/>
-      <c r="C488" s="261"/>
-      <c r="D488" s="232"/>
-      <c r="E488" s="221"/>
-      <c r="F488" s="99"/>
-      <c r="G488" s="99"/>
-      <c r="H488" s="222"/>
-      <c r="I488" s="99"/>
-      <c r="J488" s="35"/>
-      <c r="K488" s="35"/>
-      <c r="L488" s="35"/>
-      <c r="M488" s="99"/>
-      <c r="N488" s="99"/>
-      <c r="O488" s="99"/>
-      <c r="P488" s="223"/>
-      <c r="Q488" s="224"/>
-      <c r="R488" s="99"/>
-      <c r="S488" s="99"/>
-      <c r="T488" s="157"/>
-      <c r="U488" s="158"/>
-      <c r="V488" s="158"/>
-      <c r="W488" s="110"/>
-      <c r="X488" s="110"/>
-      <c r="Y488" s="197"/>
-      <c r="Z488" s="197"/>
-      <c r="AA488" s="197"/>
-      <c r="AB488" s="225"/>
-      <c r="AC488" s="99"/>
-      <c r="AD488" s="157"/>
-      <c r="AE488" s="99"/>
-      <c r="AF488" s="99"/>
-      <c r="AG488" s="99"/>
-      <c r="AH488" s="99"/>
-      <c r="AI488" s="99"/>
-      <c r="AJ488" s="99"/>
-      <c r="AK488" s="99"/>
-      <c r="AL488" s="99"/>
-      <c r="AM488" s="99"/>
-      <c r="AN488" s="99"/>
-      <c r="AO488" s="99"/>
-      <c r="AP488" s="99"/>
-      <c r="AQ488" s="99"/>
-    </row>
-    <row r="489" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A489" s="99"/>
-      <c r="B489" s="99"/>
-      <c r="C489" s="261"/>
-      <c r="D489" s="232"/>
-      <c r="E489" s="221"/>
-      <c r="F489" s="99"/>
-      <c r="G489" s="99"/>
-      <c r="H489" s="222"/>
-      <c r="I489" s="99"/>
-      <c r="J489" s="35"/>
-      <c r="K489" s="35"/>
-      <c r="L489" s="35"/>
-      <c r="M489" s="99"/>
-      <c r="N489" s="99"/>
-      <c r="O489" s="99"/>
-      <c r="P489" s="223"/>
-      <c r="Q489" s="224"/>
-      <c r="R489" s="99"/>
-      <c r="S489" s="99"/>
-      <c r="T489" s="157"/>
-      <c r="U489" s="158"/>
-      <c r="V489" s="158"/>
-      <c r="W489" s="110"/>
-      <c r="X489" s="110"/>
-      <c r="Y489" s="197"/>
-      <c r="Z489" s="197"/>
-      <c r="AA489" s="197"/>
-      <c r="AB489" s="225"/>
-      <c r="AC489" s="99"/>
-      <c r="AD489" s="157"/>
-      <c r="AE489" s="99"/>
-      <c r="AF489" s="99"/>
-      <c r="AG489" s="99"/>
-      <c r="AH489" s="99"/>
-      <c r="AI489" s="99"/>
-      <c r="AJ489" s="99"/>
-      <c r="AK489" s="99"/>
-      <c r="AL489" s="99"/>
-      <c r="AM489" s="99"/>
-      <c r="AN489" s="99"/>
-      <c r="AO489" s="99"/>
-      <c r="AP489" s="99"/>
-      <c r="AQ489" s="99"/>
-    </row>
-    <row r="490" spans="1:43" ht="15.75" customHeight="1">
-      <c r="A490" s="99"/>
-      <c r="B490" s="99"/>
-      <c r="C490" s="261"/>
-      <c r="D490" s="232"/>
-      <c r="E490" s="221"/>
-      <c r="F490" s="99"/>
-      <c r="G490" s="99"/>
-      <c r="H490" s="222"/>
-      <c r="I490" s="99"/>
-      <c r="J490" s="35"/>
-      <c r="K490" s="35"/>
-      <c r="L490" s="35"/>
-      <c r="M490" s="99"/>
-      <c r="N490" s="99"/>
-      <c r="O490" s="99"/>
-      <c r="P490" s="223"/>
-      <c r="Q490" s="224"/>
-      <c r="R490" s="99"/>
-      <c r="S490" s="99"/>
-      <c r="T490" s="157"/>
-      <c r="U490" s="158"/>
-      <c r="V490" s="158"/>
-      <c r="W490" s="110"/>
-      <c r="X490" s="110"/>
-      <c r="Y490" s="197"/>
-      <c r="Z490" s="197"/>
-      <c r="AA490" s="197"/>
-      <c r="AB490" s="225"/>
-      <c r="AC490" s="99"/>
-      <c r="AD490" s="157"/>
-      <c r="AE490" s="99"/>
-      <c r="AF490" s="99"/>
-      <c r="AG490" s="99"/>
-      <c r="AH490" s="99"/>
-      <c r="AI490" s="99"/>
-      <c r="AJ490" s="99"/>
-      <c r="AK490" s="99"/>
-      <c r="AL490" s="99"/>
-      <c r="AM490" s="99"/>
-      <c r="AN490" s="99"/>
-      <c r="AO490" s="99"/>
-      <c r="AP490" s="99"/>
-      <c r="AQ490" s="99"/>
+    <row r="481" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A481" s="468"/>
+      <c r="B481" s="469"/>
+      <c r="C481" s="470"/>
+      <c r="D481" s="471"/>
+      <c r="E481" s="472"/>
+      <c r="F481" s="473"/>
+      <c r="G481" s="472"/>
+      <c r="H481" s="474"/>
+      <c r="I481" s="474"/>
+      <c r="J481" s="475"/>
+      <c r="K481" s="475"/>
+      <c r="L481" s="475"/>
+      <c r="M481" s="476"/>
+      <c r="N481" s="477"/>
+      <c r="O481" s="477"/>
+      <c r="P481" s="478"/>
+      <c r="Q481" s="477"/>
+      <c r="R481" s="479"/>
+      <c r="S481" s="480"/>
+      <c r="T481" s="472"/>
+      <c r="U481" s="472"/>
+      <c r="V481" s="472"/>
+      <c r="W481" s="472"/>
+      <c r="X481" s="472"/>
+      <c r="Y481" s="481"/>
+      <c r="Z481" s="482"/>
+      <c r="AA481" s="472"/>
+      <c r="AB481" s="483"/>
+      <c r="AC481" s="472"/>
+      <c r="AD481" s="472"/>
+      <c r="AE481" s="484"/>
+      <c r="AF481" s="484"/>
+      <c r="AG481" s="484"/>
+      <c r="AH481" s="484"/>
+      <c r="AI481" s="484"/>
+      <c r="AJ481" s="484"/>
+      <c r="AK481" s="484"/>
+      <c r="AL481" s="484"/>
+      <c r="AM481" s="484"/>
+      <c r="AN481" s="484"/>
+      <c r="AO481" s="484"/>
+      <c r="AP481" s="484"/>
+      <c r="AQ481" s="484"/>
+    </row>
+    <row r="482" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A482" s="468"/>
+      <c r="B482" s="469"/>
+      <c r="C482" s="486"/>
+      <c r="D482" s="487"/>
+      <c r="E482" s="488"/>
+      <c r="F482" s="488"/>
+      <c r="G482" s="488"/>
+      <c r="H482" s="489"/>
+      <c r="I482" s="488"/>
+      <c r="J482" s="488"/>
+      <c r="K482" s="488"/>
+      <c r="L482" s="488"/>
+      <c r="M482" s="488"/>
+      <c r="N482" s="488"/>
+      <c r="O482" s="488"/>
+      <c r="P482" s="488"/>
+      <c r="Q482" s="488"/>
+      <c r="R482" s="488"/>
+      <c r="S482" s="488"/>
+      <c r="T482" s="488"/>
+      <c r="U482" s="488"/>
+      <c r="V482" s="488"/>
+      <c r="W482" s="488"/>
+      <c r="X482" s="488"/>
+      <c r="Y482" s="488"/>
+      <c r="Z482" s="488"/>
+      <c r="AA482" s="488"/>
+      <c r="AB482" s="488"/>
+      <c r="AC482" s="488"/>
+      <c r="AD482" s="488"/>
+      <c r="AE482" s="488"/>
+      <c r="AF482" s="488"/>
+      <c r="AG482" s="488"/>
+      <c r="AH482" s="488"/>
+      <c r="AI482" s="488"/>
+      <c r="AJ482" s="488"/>
+      <c r="AK482" s="488"/>
+      <c r="AL482" s="488"/>
+      <c r="AM482" s="488"/>
+      <c r="AN482" s="488"/>
+      <c r="AO482" s="488"/>
+      <c r="AP482" s="488"/>
+      <c r="AQ482" s="488"/>
+    </row>
+    <row r="483" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A483" s="488"/>
+      <c r="B483" s="469"/>
+      <c r="C483" s="486"/>
+      <c r="D483" s="487"/>
+      <c r="E483" s="488"/>
+      <c r="F483" s="488"/>
+      <c r="G483" s="488"/>
+      <c r="H483" s="489"/>
+      <c r="I483" s="488"/>
+      <c r="J483" s="488"/>
+      <c r="K483" s="488"/>
+      <c r="L483" s="488"/>
+      <c r="M483" s="488"/>
+      <c r="N483" s="488"/>
+      <c r="O483" s="488"/>
+      <c r="P483" s="488"/>
+      <c r="Q483" s="488"/>
+      <c r="R483" s="488"/>
+      <c r="S483" s="488"/>
+      <c r="T483" s="488"/>
+      <c r="U483" s="488"/>
+      <c r="V483" s="488"/>
+      <c r="W483" s="488"/>
+      <c r="X483" s="488"/>
+      <c r="Y483" s="488"/>
+      <c r="Z483" s="488"/>
+      <c r="AA483" s="488"/>
+      <c r="AB483" s="488"/>
+      <c r="AC483" s="488"/>
+      <c r="AD483" s="488"/>
+      <c r="AE483" s="488"/>
+      <c r="AF483" s="488"/>
+      <c r="AG483" s="488"/>
+      <c r="AH483" s="488"/>
+      <c r="AI483" s="488"/>
+      <c r="AJ483" s="488"/>
+      <c r="AK483" s="488"/>
+      <c r="AL483" s="488"/>
+      <c r="AM483" s="488"/>
+      <c r="AN483" s="488"/>
+      <c r="AO483" s="488"/>
+      <c r="AP483" s="488"/>
+      <c r="AQ483" s="488"/>
+    </row>
+    <row r="484" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A484" s="488"/>
+      <c r="B484" s="469"/>
+      <c r="C484" s="486"/>
+      <c r="D484" s="487"/>
+      <c r="E484" s="488"/>
+      <c r="F484" s="488"/>
+      <c r="G484" s="488"/>
+      <c r="H484" s="489"/>
+      <c r="I484" s="488"/>
+      <c r="J484" s="488"/>
+      <c r="K484" s="488"/>
+      <c r="L484" s="488"/>
+      <c r="M484" s="488"/>
+      <c r="N484" s="488"/>
+      <c r="O484" s="488"/>
+      <c r="P484" s="488"/>
+      <c r="Q484" s="488"/>
+      <c r="R484" s="488"/>
+      <c r="S484" s="488"/>
+      <c r="T484" s="488"/>
+      <c r="U484" s="488"/>
+      <c r="V484" s="488"/>
+      <c r="W484" s="488"/>
+      <c r="X484" s="488"/>
+      <c r="Y484" s="488"/>
+      <c r="Z484" s="488"/>
+      <c r="AA484" s="488"/>
+      <c r="AB484" s="488"/>
+      <c r="AC484" s="488"/>
+      <c r="AD484" s="488"/>
+      <c r="AE484" s="488"/>
+      <c r="AF484" s="488"/>
+      <c r="AG484" s="488"/>
+      <c r="AH484" s="488"/>
+      <c r="AI484" s="488"/>
+      <c r="AJ484" s="488"/>
+      <c r="AK484" s="488"/>
+      <c r="AL484" s="488"/>
+      <c r="AM484" s="488"/>
+      <c r="AN484" s="488"/>
+      <c r="AO484" s="488"/>
+      <c r="AP484" s="488"/>
+      <c r="AQ484" s="488"/>
+    </row>
+    <row r="485" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A485" s="488"/>
+      <c r="B485" s="469"/>
+      <c r="C485" s="486"/>
+      <c r="D485" s="487"/>
+      <c r="E485" s="490"/>
+      <c r="F485" s="488"/>
+      <c r="G485" s="488"/>
+      <c r="H485" s="489"/>
+      <c r="I485" s="488"/>
+      <c r="J485" s="488"/>
+      <c r="K485" s="488"/>
+      <c r="L485" s="488"/>
+      <c r="M485" s="488"/>
+      <c r="N485" s="488"/>
+      <c r="O485" s="488"/>
+      <c r="P485" s="488"/>
+      <c r="Q485" s="488"/>
+      <c r="R485" s="488"/>
+      <c r="S485" s="488"/>
+      <c r="T485" s="488"/>
+      <c r="U485" s="488"/>
+      <c r="V485" s="488"/>
+      <c r="W485" s="488"/>
+      <c r="X485" s="488"/>
+      <c r="Y485" s="488"/>
+      <c r="Z485" s="488"/>
+      <c r="AA485" s="488"/>
+      <c r="AB485" s="488"/>
+      <c r="AC485" s="488"/>
+      <c r="AD485" s="488"/>
+      <c r="AE485" s="488"/>
+      <c r="AF485" s="488"/>
+      <c r="AG485" s="488"/>
+      <c r="AH485" s="488"/>
+      <c r="AI485" s="488"/>
+      <c r="AJ485" s="488"/>
+      <c r="AK485" s="488"/>
+      <c r="AL485" s="488"/>
+      <c r="AM485" s="488"/>
+      <c r="AN485" s="488"/>
+      <c r="AO485" s="488"/>
+      <c r="AP485" s="488"/>
+      <c r="AQ485" s="488"/>
+    </row>
+    <row r="486" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A486" s="488"/>
+      <c r="B486" s="469"/>
+      <c r="C486" s="486"/>
+      <c r="D486" s="487"/>
+      <c r="E486" s="488"/>
+      <c r="F486" s="488"/>
+      <c r="G486" s="488"/>
+      <c r="H486" s="489"/>
+      <c r="I486" s="488"/>
+      <c r="J486" s="488"/>
+      <c r="K486" s="488"/>
+      <c r="L486" s="488"/>
+      <c r="M486" s="488"/>
+      <c r="N486" s="488"/>
+      <c r="O486" s="488"/>
+      <c r="P486" s="488"/>
+      <c r="Q486" s="488"/>
+      <c r="R486" s="488"/>
+      <c r="S486" s="488"/>
+      <c r="T486" s="488"/>
+      <c r="U486" s="488"/>
+      <c r="V486" s="488"/>
+      <c r="W486" s="488"/>
+      <c r="X486" s="488"/>
+      <c r="Y486" s="488"/>
+      <c r="Z486" s="488"/>
+      <c r="AA486" s="488"/>
+      <c r="AB486" s="488"/>
+      <c r="AC486" s="488"/>
+      <c r="AD486" s="488"/>
+      <c r="AE486" s="488"/>
+      <c r="AF486" s="488"/>
+      <c r="AG486" s="488"/>
+      <c r="AH486" s="488"/>
+      <c r="AI486" s="488"/>
+      <c r="AJ486" s="488"/>
+      <c r="AK486" s="488"/>
+      <c r="AL486" s="488"/>
+      <c r="AM486" s="488"/>
+      <c r="AN486" s="488"/>
+      <c r="AO486" s="488"/>
+      <c r="AP486" s="488"/>
+      <c r="AQ486" s="488"/>
+    </row>
+    <row r="487" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A487" s="488"/>
+      <c r="B487" s="469"/>
+      <c r="C487" s="486"/>
+      <c r="D487" s="487"/>
+      <c r="E487" s="488"/>
+      <c r="F487" s="488"/>
+      <c r="G487" s="488"/>
+      <c r="H487" s="489"/>
+      <c r="I487" s="488"/>
+      <c r="J487" s="488"/>
+      <c r="K487" s="488"/>
+      <c r="L487" s="488"/>
+      <c r="M487" s="488"/>
+      <c r="N487" s="488"/>
+      <c r="O487" s="488"/>
+      <c r="P487" s="488"/>
+      <c r="Q487" s="488"/>
+      <c r="R487" s="488"/>
+      <c r="S487" s="488"/>
+      <c r="T487" s="488"/>
+      <c r="U487" s="488"/>
+      <c r="V487" s="488"/>
+      <c r="W487" s="488"/>
+      <c r="X487" s="488"/>
+      <c r="Y487" s="488"/>
+      <c r="Z487" s="488"/>
+      <c r="AA487" s="488"/>
+      <c r="AB487" s="488"/>
+      <c r="AC487" s="488"/>
+      <c r="AD487" s="488"/>
+      <c r="AE487" s="488"/>
+      <c r="AF487" s="488"/>
+      <c r="AG487" s="488"/>
+      <c r="AH487" s="488"/>
+      <c r="AI487" s="488"/>
+      <c r="AJ487" s="488"/>
+      <c r="AK487" s="488"/>
+      <c r="AL487" s="488"/>
+      <c r="AM487" s="488"/>
+      <c r="AN487" s="488"/>
+      <c r="AO487" s="488"/>
+      <c r="AP487" s="488"/>
+      <c r="AQ487" s="488"/>
+    </row>
+    <row r="488" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A488" s="488"/>
+      <c r="B488" s="469"/>
+      <c r="C488" s="486"/>
+      <c r="D488" s="487"/>
+      <c r="E488" s="488"/>
+      <c r="F488" s="488"/>
+      <c r="G488" s="488"/>
+      <c r="H488" s="489"/>
+      <c r="I488" s="488"/>
+      <c r="J488" s="488"/>
+      <c r="K488" s="488"/>
+      <c r="L488" s="488"/>
+      <c r="M488" s="488"/>
+      <c r="N488" s="488"/>
+      <c r="O488" s="488"/>
+      <c r="P488" s="488"/>
+      <c r="Q488" s="488"/>
+      <c r="R488" s="488"/>
+      <c r="S488" s="488"/>
+      <c r="T488" s="488"/>
+      <c r="U488" s="488"/>
+      <c r="V488" s="488"/>
+      <c r="W488" s="488"/>
+      <c r="X488" s="488"/>
+      <c r="Y488" s="488"/>
+      <c r="Z488" s="488"/>
+      <c r="AA488" s="488"/>
+      <c r="AB488" s="488"/>
+      <c r="AC488" s="488"/>
+      <c r="AD488" s="488"/>
+      <c r="AE488" s="488"/>
+      <c r="AF488" s="488"/>
+      <c r="AG488" s="488"/>
+      <c r="AH488" s="488"/>
+      <c r="AI488" s="488"/>
+      <c r="AJ488" s="488"/>
+      <c r="AK488" s="488"/>
+      <c r="AL488" s="488"/>
+      <c r="AM488" s="488"/>
+      <c r="AN488" s="488"/>
+      <c r="AO488" s="488"/>
+      <c r="AP488" s="488"/>
+      <c r="AQ488" s="488"/>
+    </row>
+    <row r="489" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A489" s="488"/>
+      <c r="B489" s="469"/>
+      <c r="C489" s="486"/>
+      <c r="D489" s="487"/>
+      <c r="E489" s="488"/>
+      <c r="F489" s="488"/>
+      <c r="G489" s="488"/>
+      <c r="H489" s="489"/>
+      <c r="I489" s="488"/>
+      <c r="J489" s="488"/>
+      <c r="K489" s="488"/>
+      <c r="L489" s="488"/>
+      <c r="M489" s="488"/>
+      <c r="N489" s="488"/>
+      <c r="O489" s="488"/>
+      <c r="P489" s="488"/>
+      <c r="Q489" s="488"/>
+      <c r="R489" s="488"/>
+      <c r="S489" s="488"/>
+      <c r="T489" s="488"/>
+      <c r="U489" s="488"/>
+      <c r="V489" s="488"/>
+      <c r="W489" s="488"/>
+      <c r="X489" s="488"/>
+      <c r="Y489" s="488"/>
+      <c r="Z489" s="488"/>
+      <c r="AA489" s="488"/>
+      <c r="AB489" s="488"/>
+      <c r="AC489" s="488"/>
+      <c r="AD489" s="488"/>
+      <c r="AE489" s="488"/>
+      <c r="AF489" s="488"/>
+      <c r="AG489" s="488"/>
+      <c r="AH489" s="488"/>
+      <c r="AI489" s="488"/>
+      <c r="AJ489" s="488"/>
+      <c r="AK489" s="488"/>
+      <c r="AL489" s="488"/>
+      <c r="AM489" s="488"/>
+      <c r="AN489" s="488"/>
+      <c r="AO489" s="488"/>
+      <c r="AP489" s="488"/>
+      <c r="AQ489" s="488"/>
+    </row>
+    <row r="490" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A490" s="488"/>
+      <c r="B490" s="469"/>
+      <c r="C490" s="486"/>
+      <c r="D490" s="487"/>
+      <c r="E490" s="488"/>
+      <c r="F490" s="488"/>
+      <c r="G490" s="488"/>
+      <c r="H490" s="489"/>
+      <c r="I490" s="488"/>
+      <c r="J490" s="488"/>
+      <c r="K490" s="488"/>
+      <c r="L490" s="488"/>
+      <c r="M490" s="488"/>
+      <c r="N490" s="488"/>
+      <c r="O490" s="488"/>
+      <c r="P490" s="488"/>
+      <c r="Q490" s="488"/>
+      <c r="R490" s="488"/>
+      <c r="S490" s="488"/>
+      <c r="T490" s="488"/>
+      <c r="U490" s="488"/>
+      <c r="V490" s="488"/>
+      <c r="W490" s="488"/>
+      <c r="X490" s="488"/>
+      <c r="Y490" s="488"/>
+      <c r="Z490" s="488"/>
+      <c r="AA490" s="488"/>
+      <c r="AB490" s="488"/>
+      <c r="AC490" s="488"/>
+      <c r="AD490" s="488"/>
+      <c r="AE490" s="488"/>
+      <c r="AF490" s="488"/>
+      <c r="AG490" s="488"/>
+      <c r="AH490" s="488"/>
+      <c r="AI490" s="488"/>
+      <c r="AJ490" s="488"/>
+      <c r="AK490" s="488"/>
+      <c r="AL490" s="488"/>
+      <c r="AM490" s="488"/>
+      <c r="AN490" s="488"/>
+      <c r="AO490" s="488"/>
+      <c r="AP490" s="488"/>
+      <c r="AQ490" s="488"/>
     </row>
     <row r="491" spans="1:43" ht="15.75" customHeight="1">
       <c r="A491" s="99"/>
@@ -65279,7 +65180,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{F9CA7A1D-0385-2D40-9FD3-9EF31CEC33EB}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{CC1BB538-8C14-7C4E-8BF6-2EB108311D6F}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>
@@ -66071,13 +65972,12 @@
     <hyperlink ref="F480" r:id="rId786" xr:uid="{00000000-0004-0000-0000-00001A030000}"/>
     <hyperlink ref="Y247" r:id="rId787" display="https://gallica.bnf.fr/ark:/12148/bpt6k56069895" xr:uid="{406C8F90-712D-EA4E-983E-641EE322383B}"/>
     <hyperlink ref="F389" r:id="rId788" display="https://gallica.bnf.fr/ark:/12148/bpt6k6274143z/f227.item" xr:uid="{E92130F0-40E3-964F-9C82-6A4A8E98FE4A}"/>
-    <hyperlink ref="F382" r:id="rId789" xr:uid="{CB05E3EA-1CBE-F14B-8929-CCBCA00FE15C}"/>
-    <hyperlink ref="AC369" r:id="rId790" xr:uid="{6661D188-986C-EA4F-9D9E-F3E7E746DD57}"/>
-    <hyperlink ref="F274" r:id="rId791" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="F82" r:id="rId792" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="AC369" r:id="rId789" xr:uid="{6661D188-986C-EA4F-9D9E-F3E7E746DD57}"/>
+    <hyperlink ref="F274" r:id="rId790" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="F82" r:id="rId791" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <legacyDrawing r:id="rId793"/>
+  <legacyDrawing r:id="rId792"/>
 </worksheet>
 </file>
--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3548EEA2-E878-D042-8B04-F0CFFD6963D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0F759B-5DC5-D841-AF7E-34A769CB6364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-2680" yWindow="-20480" windowWidth="36840" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18889,7 +18889,7 @@
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="145" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="491">
+  <cellXfs count="485">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -20218,69 +20218,53 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -52424,10 +52408,9 @@
         <v>3436</v>
       </c>
       <c r="O430" s="38"/>
-      <c r="P430" s="289" t="s">
+      <c r="Q430" s="289" t="s">
         <v>3948</v>
       </c>
-      <c r="Q430" s="26"/>
       <c r="R430" s="115" t="s">
         <v>383</v>
       </c>
@@ -56173,7 +56156,7 @@
       <c r="AP480" s="32"/>
       <c r="AQ480" s="32"/>
     </row>
-    <row r="481" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+    <row r="481" spans="1:43" ht="15.75" customHeight="1">
       <c r="A481" s="468"/>
       <c r="B481" s="469"/>
       <c r="C481" s="470"/>
@@ -56204,424 +56187,424 @@
       <c r="AB481" s="483"/>
       <c r="AC481" s="472"/>
       <c r="AD481" s="472"/>
-      <c r="AE481" s="484"/>
-      <c r="AF481" s="484"/>
-      <c r="AG481" s="484"/>
-      <c r="AH481" s="484"/>
-      <c r="AI481" s="484"/>
-      <c r="AJ481" s="484"/>
-      <c r="AK481" s="484"/>
-      <c r="AL481" s="484"/>
-      <c r="AM481" s="484"/>
-      <c r="AN481" s="484"/>
-      <c r="AO481" s="484"/>
-      <c r="AP481" s="484"/>
-      <c r="AQ481" s="484"/>
-    </row>
-    <row r="482" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
+      <c r="AE481" s="32"/>
+      <c r="AF481" s="32"/>
+      <c r="AG481" s="32"/>
+      <c r="AH481" s="32"/>
+      <c r="AI481" s="32"/>
+      <c r="AJ481" s="32"/>
+      <c r="AK481" s="32"/>
+      <c r="AL481" s="32"/>
+      <c r="AM481" s="32"/>
+      <c r="AN481" s="32"/>
+      <c r="AO481" s="32"/>
+      <c r="AP481" s="32"/>
+      <c r="AQ481" s="32"/>
+    </row>
+    <row r="482" spans="1:43" ht="15.75" customHeight="1">
       <c r="A482" s="468"/>
       <c r="B482" s="469"/>
-      <c r="C482" s="486"/>
-      <c r="D482" s="487"/>
-      <c r="E482" s="488"/>
-      <c r="F482" s="488"/>
-      <c r="G482" s="488"/>
-      <c r="H482" s="489"/>
-      <c r="I482" s="488"/>
-      <c r="J482" s="488"/>
-      <c r="K482" s="488"/>
-      <c r="L482" s="488"/>
-      <c r="M482" s="488"/>
-      <c r="N482" s="488"/>
-      <c r="O482" s="488"/>
-      <c r="P482" s="488"/>
-      <c r="Q482" s="488"/>
-      <c r="R482" s="488"/>
-      <c r="S482" s="488"/>
-      <c r="T482" s="488"/>
-      <c r="U482" s="488"/>
-      <c r="V482" s="488"/>
-      <c r="W482" s="488"/>
-      <c r="X482" s="488"/>
-      <c r="Y482" s="488"/>
-      <c r="Z482" s="488"/>
-      <c r="AA482" s="488"/>
-      <c r="AB482" s="488"/>
-      <c r="AC482" s="488"/>
-      <c r="AD482" s="488"/>
-      <c r="AE482" s="488"/>
-      <c r="AF482" s="488"/>
-      <c r="AG482" s="488"/>
-      <c r="AH482" s="488"/>
-      <c r="AI482" s="488"/>
-      <c r="AJ482" s="488"/>
-      <c r="AK482" s="488"/>
-      <c r="AL482" s="488"/>
-      <c r="AM482" s="488"/>
-      <c r="AN482" s="488"/>
-      <c r="AO482" s="488"/>
-      <c r="AP482" s="488"/>
-      <c r="AQ482" s="488"/>
-    </row>
-    <row r="483" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A483" s="488"/>
+      <c r="C482" s="261"/>
+      <c r="D482" s="232"/>
+      <c r="E482" s="99"/>
+      <c r="F482" s="99"/>
+      <c r="G482" s="99"/>
+      <c r="H482" s="222"/>
+      <c r="I482" s="99"/>
+      <c r="J482" s="99"/>
+      <c r="K482" s="99"/>
+      <c r="L482" s="99"/>
+      <c r="M482" s="99"/>
+      <c r="N482" s="99"/>
+      <c r="O482" s="99"/>
+      <c r="P482" s="99"/>
+      <c r="Q482" s="99"/>
+      <c r="R482" s="99"/>
+      <c r="S482" s="99"/>
+      <c r="T482" s="99"/>
+      <c r="U482" s="99"/>
+      <c r="V482" s="99"/>
+      <c r="W482" s="99"/>
+      <c r="X482" s="99"/>
+      <c r="Y482" s="99"/>
+      <c r="Z482" s="99"/>
+      <c r="AA482" s="99"/>
+      <c r="AB482" s="99"/>
+      <c r="AC482" s="99"/>
+      <c r="AD482" s="99"/>
+      <c r="AE482" s="99"/>
+      <c r="AF482" s="99"/>
+      <c r="AG482" s="99"/>
+      <c r="AH482" s="99"/>
+      <c r="AI482" s="99"/>
+      <c r="AJ482" s="99"/>
+      <c r="AK482" s="99"/>
+      <c r="AL482" s="99"/>
+      <c r="AM482" s="99"/>
+      <c r="AN482" s="99"/>
+      <c r="AO482" s="99"/>
+      <c r="AP482" s="99"/>
+      <c r="AQ482" s="99"/>
+    </row>
+    <row r="483" spans="1:43" ht="15.75" customHeight="1">
+      <c r="A483" s="99"/>
       <c r="B483" s="469"/>
-      <c r="C483" s="486"/>
-      <c r="D483" s="487"/>
-      <c r="E483" s="488"/>
-      <c r="F483" s="488"/>
-      <c r="G483" s="488"/>
-      <c r="H483" s="489"/>
-      <c r="I483" s="488"/>
-      <c r="J483" s="488"/>
-      <c r="K483" s="488"/>
-      <c r="L483" s="488"/>
-      <c r="M483" s="488"/>
-      <c r="N483" s="488"/>
-      <c r="O483" s="488"/>
-      <c r="P483" s="488"/>
-      <c r="Q483" s="488"/>
-      <c r="R483" s="488"/>
-      <c r="S483" s="488"/>
-      <c r="T483" s="488"/>
-      <c r="U483" s="488"/>
-      <c r="V483" s="488"/>
-      <c r="W483" s="488"/>
-      <c r="X483" s="488"/>
-      <c r="Y483" s="488"/>
-      <c r="Z483" s="488"/>
-      <c r="AA483" s="488"/>
-      <c r="AB483" s="488"/>
-      <c r="AC483" s="488"/>
-      <c r="AD483" s="488"/>
-      <c r="AE483" s="488"/>
-      <c r="AF483" s="488"/>
-      <c r="AG483" s="488"/>
-      <c r="AH483" s="488"/>
-      <c r="AI483" s="488"/>
-      <c r="AJ483" s="488"/>
-      <c r="AK483" s="488"/>
-      <c r="AL483" s="488"/>
-      <c r="AM483" s="488"/>
-      <c r="AN483" s="488"/>
-      <c r="AO483" s="488"/>
-      <c r="AP483" s="488"/>
-      <c r="AQ483" s="488"/>
-    </row>
-    <row r="484" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A484" s="488"/>
+      <c r="C483" s="261"/>
+      <c r="D483" s="232"/>
+      <c r="E483" s="99"/>
+      <c r="F483" s="99"/>
+      <c r="G483" s="99"/>
+      <c r="H483" s="222"/>
+      <c r="I483" s="99"/>
+      <c r="J483" s="99"/>
+      <c r="K483" s="99"/>
+      <c r="L483" s="99"/>
+      <c r="M483" s="99"/>
+      <c r="N483" s="99"/>
+      <c r="O483" s="99"/>
+      <c r="P483" s="99"/>
+      <c r="Q483" s="99"/>
+      <c r="R483" s="99"/>
+      <c r="S483" s="99"/>
+      <c r="T483" s="99"/>
+      <c r="U483" s="99"/>
+      <c r="V483" s="99"/>
+      <c r="W483" s="99"/>
+      <c r="X483" s="99"/>
+      <c r="Y483" s="99"/>
+      <c r="Z483" s="99"/>
+      <c r="AA483" s="99"/>
+      <c r="AB483" s="99"/>
+      <c r="AC483" s="99"/>
+      <c r="AD483" s="99"/>
+      <c r="AE483" s="99"/>
+      <c r="AF483" s="99"/>
+      <c r="AG483" s="99"/>
+      <c r="AH483" s="99"/>
+      <c r="AI483" s="99"/>
+      <c r="AJ483" s="99"/>
+      <c r="AK483" s="99"/>
+      <c r="AL483" s="99"/>
+      <c r="AM483" s="99"/>
+      <c r="AN483" s="99"/>
+      <c r="AO483" s="99"/>
+      <c r="AP483" s="99"/>
+      <c r="AQ483" s="99"/>
+    </row>
+    <row r="484" spans="1:43" ht="15.75" customHeight="1">
+      <c r="A484" s="99"/>
       <c r="B484" s="469"/>
-      <c r="C484" s="486"/>
-      <c r="D484" s="487"/>
-      <c r="E484" s="488"/>
-      <c r="F484" s="488"/>
-      <c r="G484" s="488"/>
-      <c r="H484" s="489"/>
-      <c r="I484" s="488"/>
-      <c r="J484" s="488"/>
-      <c r="K484" s="488"/>
-      <c r="L484" s="488"/>
-      <c r="M484" s="488"/>
-      <c r="N484" s="488"/>
-      <c r="O484" s="488"/>
-      <c r="P484" s="488"/>
-      <c r="Q484" s="488"/>
-      <c r="R484" s="488"/>
-      <c r="S484" s="488"/>
-      <c r="T484" s="488"/>
-      <c r="U484" s="488"/>
-      <c r="V484" s="488"/>
-      <c r="W484" s="488"/>
-      <c r="X484" s="488"/>
-      <c r="Y484" s="488"/>
-      <c r="Z484" s="488"/>
-      <c r="AA484" s="488"/>
-      <c r="AB484" s="488"/>
-      <c r="AC484" s="488"/>
-      <c r="AD484" s="488"/>
-      <c r="AE484" s="488"/>
-      <c r="AF484" s="488"/>
-      <c r="AG484" s="488"/>
-      <c r="AH484" s="488"/>
-      <c r="AI484" s="488"/>
-      <c r="AJ484" s="488"/>
-      <c r="AK484" s="488"/>
-      <c r="AL484" s="488"/>
-      <c r="AM484" s="488"/>
-      <c r="AN484" s="488"/>
-      <c r="AO484" s="488"/>
-      <c r="AP484" s="488"/>
-      <c r="AQ484" s="488"/>
-    </row>
-    <row r="485" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A485" s="488"/>
+      <c r="C484" s="261"/>
+      <c r="D484" s="232"/>
+      <c r="E484" s="99"/>
+      <c r="F484" s="99"/>
+      <c r="G484" s="99"/>
+      <c r="H484" s="222"/>
+      <c r="I484" s="99"/>
+      <c r="J484" s="99"/>
+      <c r="K484" s="99"/>
+      <c r="L484" s="99"/>
+      <c r="M484" s="99"/>
+      <c r="N484" s="99"/>
+      <c r="O484" s="99"/>
+      <c r="P484" s="99"/>
+      <c r="Q484" s="99"/>
+      <c r="R484" s="99"/>
+      <c r="S484" s="99"/>
+      <c r="T484" s="99"/>
+      <c r="U484" s="99"/>
+      <c r="V484" s="99"/>
+      <c r="W484" s="99"/>
+      <c r="X484" s="99"/>
+      <c r="Y484" s="99"/>
+      <c r="Z484" s="99"/>
+      <c r="AA484" s="99"/>
+      <c r="AB484" s="99"/>
+      <c r="AC484" s="99"/>
+      <c r="AD484" s="99"/>
+      <c r="AE484" s="99"/>
+      <c r="AF484" s="99"/>
+      <c r="AG484" s="99"/>
+      <c r="AH484" s="99"/>
+      <c r="AI484" s="99"/>
+      <c r="AJ484" s="99"/>
+      <c r="AK484" s="99"/>
+      <c r="AL484" s="99"/>
+      <c r="AM484" s="99"/>
+      <c r="AN484" s="99"/>
+      <c r="AO484" s="99"/>
+      <c r="AP484" s="99"/>
+      <c r="AQ484" s="99"/>
+    </row>
+    <row r="485" spans="1:43" ht="15.75" customHeight="1">
+      <c r="A485" s="99"/>
       <c r="B485" s="469"/>
-      <c r="C485" s="486"/>
-      <c r="D485" s="487"/>
-      <c r="E485" s="490"/>
-      <c r="F485" s="488"/>
-      <c r="G485" s="488"/>
-      <c r="H485" s="489"/>
-      <c r="I485" s="488"/>
-      <c r="J485" s="488"/>
-      <c r="K485" s="488"/>
-      <c r="L485" s="488"/>
-      <c r="M485" s="488"/>
-      <c r="N485" s="488"/>
-      <c r="O485" s="488"/>
-      <c r="P485" s="488"/>
-      <c r="Q485" s="488"/>
-      <c r="R485" s="488"/>
-      <c r="S485" s="488"/>
-      <c r="T485" s="488"/>
-      <c r="U485" s="488"/>
-      <c r="V485" s="488"/>
-      <c r="W485" s="488"/>
-      <c r="X485" s="488"/>
-      <c r="Y485" s="488"/>
-      <c r="Z485" s="488"/>
-      <c r="AA485" s="488"/>
-      <c r="AB485" s="488"/>
-      <c r="AC485" s="488"/>
-      <c r="AD485" s="488"/>
-      <c r="AE485" s="488"/>
-      <c r="AF485" s="488"/>
-      <c r="AG485" s="488"/>
-      <c r="AH485" s="488"/>
-      <c r="AI485" s="488"/>
-      <c r="AJ485" s="488"/>
-      <c r="AK485" s="488"/>
-      <c r="AL485" s="488"/>
-      <c r="AM485" s="488"/>
-      <c r="AN485" s="488"/>
-      <c r="AO485" s="488"/>
-      <c r="AP485" s="488"/>
-      <c r="AQ485" s="488"/>
-    </row>
-    <row r="486" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A486" s="488"/>
+      <c r="C485" s="261"/>
+      <c r="D485" s="232"/>
+      <c r="E485" s="484"/>
+      <c r="F485" s="99"/>
+      <c r="G485" s="99"/>
+      <c r="H485" s="222"/>
+      <c r="I485" s="99"/>
+      <c r="J485" s="99"/>
+      <c r="K485" s="99"/>
+      <c r="L485" s="99"/>
+      <c r="M485" s="99"/>
+      <c r="N485" s="99"/>
+      <c r="O485" s="99"/>
+      <c r="P485" s="99"/>
+      <c r="Q485" s="99"/>
+      <c r="R485" s="99"/>
+      <c r="S485" s="99"/>
+      <c r="T485" s="99"/>
+      <c r="U485" s="99"/>
+      <c r="V485" s="99"/>
+      <c r="W485" s="99"/>
+      <c r="X485" s="99"/>
+      <c r="Y485" s="99"/>
+      <c r="Z485" s="99"/>
+      <c r="AA485" s="99"/>
+      <c r="AB485" s="99"/>
+      <c r="AC485" s="99"/>
+      <c r="AD485" s="99"/>
+      <c r="AE485" s="99"/>
+      <c r="AF485" s="99"/>
+      <c r="AG485" s="99"/>
+      <c r="AH485" s="99"/>
+      <c r="AI485" s="99"/>
+      <c r="AJ485" s="99"/>
+      <c r="AK485" s="99"/>
+      <c r="AL485" s="99"/>
+      <c r="AM485" s="99"/>
+      <c r="AN485" s="99"/>
+      <c r="AO485" s="99"/>
+      <c r="AP485" s="99"/>
+      <c r="AQ485" s="99"/>
+    </row>
+    <row r="486" spans="1:43" ht="15.75" customHeight="1">
+      <c r="A486" s="99"/>
       <c r="B486" s="469"/>
-      <c r="C486" s="486"/>
-      <c r="D486" s="487"/>
-      <c r="E486" s="488"/>
-      <c r="F486" s="488"/>
-      <c r="G486" s="488"/>
-      <c r="H486" s="489"/>
-      <c r="I486" s="488"/>
-      <c r="J486" s="488"/>
-      <c r="K486" s="488"/>
-      <c r="L486" s="488"/>
-      <c r="M486" s="488"/>
-      <c r="N486" s="488"/>
-      <c r="O486" s="488"/>
-      <c r="P486" s="488"/>
-      <c r="Q486" s="488"/>
-      <c r="R486" s="488"/>
-      <c r="S486" s="488"/>
-      <c r="T486" s="488"/>
-      <c r="U486" s="488"/>
-      <c r="V486" s="488"/>
-      <c r="W486" s="488"/>
-      <c r="X486" s="488"/>
-      <c r="Y486" s="488"/>
-      <c r="Z486" s="488"/>
-      <c r="AA486" s="488"/>
-      <c r="AB486" s="488"/>
-      <c r="AC486" s="488"/>
-      <c r="AD486" s="488"/>
-      <c r="AE486" s="488"/>
-      <c r="AF486" s="488"/>
-      <c r="AG486" s="488"/>
-      <c r="AH486" s="488"/>
-      <c r="AI486" s="488"/>
-      <c r="AJ486" s="488"/>
-      <c r="AK486" s="488"/>
-      <c r="AL486" s="488"/>
-      <c r="AM486" s="488"/>
-      <c r="AN486" s="488"/>
-      <c r="AO486" s="488"/>
-      <c r="AP486" s="488"/>
-      <c r="AQ486" s="488"/>
-    </row>
-    <row r="487" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A487" s="488"/>
+      <c r="C486" s="261"/>
+      <c r="D486" s="232"/>
+      <c r="E486" s="99"/>
+      <c r="F486" s="99"/>
+      <c r="G486" s="99"/>
+      <c r="H486" s="222"/>
+      <c r="I486" s="99"/>
+      <c r="J486" s="99"/>
+      <c r="K486" s="99"/>
+      <c r="L486" s="99"/>
+      <c r="M486" s="99"/>
+      <c r="N486" s="99"/>
+      <c r="O486" s="99"/>
+      <c r="P486" s="99"/>
+      <c r="Q486" s="99"/>
+      <c r="R486" s="99"/>
+      <c r="S486" s="99"/>
+      <c r="T486" s="99"/>
+      <c r="U486" s="99"/>
+      <c r="V486" s="99"/>
+      <c r="W486" s="99"/>
+      <c r="X486" s="99"/>
+      <c r="Y486" s="99"/>
+      <c r="Z486" s="99"/>
+      <c r="AA486" s="99"/>
+      <c r="AB486" s="99"/>
+      <c r="AC486" s="99"/>
+      <c r="AD486" s="99"/>
+      <c r="AE486" s="99"/>
+      <c r="AF486" s="99"/>
+      <c r="AG486" s="99"/>
+      <c r="AH486" s="99"/>
+      <c r="AI486" s="99"/>
+      <c r="AJ486" s="99"/>
+      <c r="AK486" s="99"/>
+      <c r="AL486" s="99"/>
+      <c r="AM486" s="99"/>
+      <c r="AN486" s="99"/>
+      <c r="AO486" s="99"/>
+      <c r="AP486" s="99"/>
+      <c r="AQ486" s="99"/>
+    </row>
+    <row r="487" spans="1:43" ht="15.75" customHeight="1">
+      <c r="A487" s="99"/>
       <c r="B487" s="469"/>
-      <c r="C487" s="486"/>
-      <c r="D487" s="487"/>
-      <c r="E487" s="488"/>
-      <c r="F487" s="488"/>
-      <c r="G487" s="488"/>
-      <c r="H487" s="489"/>
-      <c r="I487" s="488"/>
-      <c r="J487" s="488"/>
-      <c r="K487" s="488"/>
-      <c r="L487" s="488"/>
-      <c r="M487" s="488"/>
-      <c r="N487" s="488"/>
-      <c r="O487" s="488"/>
-      <c r="P487" s="488"/>
-      <c r="Q487" s="488"/>
-      <c r="R487" s="488"/>
-      <c r="S487" s="488"/>
-      <c r="T487" s="488"/>
-      <c r="U487" s="488"/>
-      <c r="V487" s="488"/>
-      <c r="W487" s="488"/>
-      <c r="X487" s="488"/>
-      <c r="Y487" s="488"/>
-      <c r="Z487" s="488"/>
-      <c r="AA487" s="488"/>
-      <c r="AB487" s="488"/>
-      <c r="AC487" s="488"/>
-      <c r="AD487" s="488"/>
-      <c r="AE487" s="488"/>
-      <c r="AF487" s="488"/>
-      <c r="AG487" s="488"/>
-      <c r="AH487" s="488"/>
-      <c r="AI487" s="488"/>
-      <c r="AJ487" s="488"/>
-      <c r="AK487" s="488"/>
-      <c r="AL487" s="488"/>
-      <c r="AM487" s="488"/>
-      <c r="AN487" s="488"/>
-      <c r="AO487" s="488"/>
-      <c r="AP487" s="488"/>
-      <c r="AQ487" s="488"/>
-    </row>
-    <row r="488" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A488" s="488"/>
+      <c r="C487" s="261"/>
+      <c r="D487" s="232"/>
+      <c r="E487" s="99"/>
+      <c r="F487" s="99"/>
+      <c r="G487" s="99"/>
+      <c r="H487" s="222"/>
+      <c r="I487" s="99"/>
+      <c r="J487" s="99"/>
+      <c r="K487" s="99"/>
+      <c r="L487" s="99"/>
+      <c r="M487" s="99"/>
+      <c r="N487" s="99"/>
+      <c r="O487" s="99"/>
+      <c r="P487" s="99"/>
+      <c r="Q487" s="99"/>
+      <c r="R487" s="99"/>
+      <c r="S487" s="99"/>
+      <c r="T487" s="99"/>
+      <c r="U487" s="99"/>
+      <c r="V487" s="99"/>
+      <c r="W487" s="99"/>
+      <c r="X487" s="99"/>
+      <c r="Y487" s="99"/>
+      <c r="Z487" s="99"/>
+      <c r="AA487" s="99"/>
+      <c r="AB487" s="99"/>
+      <c r="AC487" s="99"/>
+      <c r="AD487" s="99"/>
+      <c r="AE487" s="99"/>
+      <c r="AF487" s="99"/>
+      <c r="AG487" s="99"/>
+      <c r="AH487" s="99"/>
+      <c r="AI487" s="99"/>
+      <c r="AJ487" s="99"/>
+      <c r="AK487" s="99"/>
+      <c r="AL487" s="99"/>
+      <c r="AM487" s="99"/>
+      <c r="AN487" s="99"/>
+      <c r="AO487" s="99"/>
+      <c r="AP487" s="99"/>
+      <c r="AQ487" s="99"/>
+    </row>
+    <row r="488" spans="1:43" ht="15.75" customHeight="1">
+      <c r="A488" s="99"/>
       <c r="B488" s="469"/>
-      <c r="C488" s="486"/>
-      <c r="D488" s="487"/>
-      <c r="E488" s="488"/>
-      <c r="F488" s="488"/>
-      <c r="G488" s="488"/>
-      <c r="H488" s="489"/>
-      <c r="I488" s="488"/>
-      <c r="J488" s="488"/>
-      <c r="K488" s="488"/>
-      <c r="L488" s="488"/>
-      <c r="M488" s="488"/>
-      <c r="N488" s="488"/>
-      <c r="O488" s="488"/>
-      <c r="P488" s="488"/>
-      <c r="Q488" s="488"/>
-      <c r="R488" s="488"/>
-      <c r="S488" s="488"/>
-      <c r="T488" s="488"/>
-      <c r="U488" s="488"/>
-      <c r="V488" s="488"/>
-      <c r="W488" s="488"/>
-      <c r="X488" s="488"/>
-      <c r="Y488" s="488"/>
-      <c r="Z488" s="488"/>
-      <c r="AA488" s="488"/>
-      <c r="AB488" s="488"/>
-      <c r="AC488" s="488"/>
-      <c r="AD488" s="488"/>
-      <c r="AE488" s="488"/>
-      <c r="AF488" s="488"/>
-      <c r="AG488" s="488"/>
-      <c r="AH488" s="488"/>
-      <c r="AI488" s="488"/>
-      <c r="AJ488" s="488"/>
-      <c r="AK488" s="488"/>
-      <c r="AL488" s="488"/>
-      <c r="AM488" s="488"/>
-      <c r="AN488" s="488"/>
-      <c r="AO488" s="488"/>
-      <c r="AP488" s="488"/>
-      <c r="AQ488" s="488"/>
-    </row>
-    <row r="489" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A489" s="488"/>
+      <c r="C488" s="261"/>
+      <c r="D488" s="232"/>
+      <c r="E488" s="99"/>
+      <c r="F488" s="99"/>
+      <c r="G488" s="99"/>
+      <c r="H488" s="222"/>
+      <c r="I488" s="99"/>
+      <c r="J488" s="99"/>
+      <c r="K488" s="99"/>
+      <c r="L488" s="99"/>
+      <c r="M488" s="99"/>
+      <c r="N488" s="99"/>
+      <c r="O488" s="99"/>
+      <c r="P488" s="99"/>
+      <c r="Q488" s="99"/>
+      <c r="R488" s="99"/>
+      <c r="S488" s="99"/>
+      <c r="T488" s="99"/>
+      <c r="U488" s="99"/>
+      <c r="V488" s="99"/>
+      <c r="W488" s="99"/>
+      <c r="X488" s="99"/>
+      <c r="Y488" s="99"/>
+      <c r="Z488" s="99"/>
+      <c r="AA488" s="99"/>
+      <c r="AB488" s="99"/>
+      <c r="AC488" s="99"/>
+      <c r="AD488" s="99"/>
+      <c r="AE488" s="99"/>
+      <c r="AF488" s="99"/>
+      <c r="AG488" s="99"/>
+      <c r="AH488" s="99"/>
+      <c r="AI488" s="99"/>
+      <c r="AJ488" s="99"/>
+      <c r="AK488" s="99"/>
+      <c r="AL488" s="99"/>
+      <c r="AM488" s="99"/>
+      <c r="AN488" s="99"/>
+      <c r="AO488" s="99"/>
+      <c r="AP488" s="99"/>
+      <c r="AQ488" s="99"/>
+    </row>
+    <row r="489" spans="1:43" ht="15.75" customHeight="1">
+      <c r="A489" s="99"/>
       <c r="B489" s="469"/>
-      <c r="C489" s="486"/>
-      <c r="D489" s="487"/>
-      <c r="E489" s="488"/>
-      <c r="F489" s="488"/>
-      <c r="G489" s="488"/>
-      <c r="H489" s="489"/>
-      <c r="I489" s="488"/>
-      <c r="J489" s="488"/>
-      <c r="K489" s="488"/>
-      <c r="L489" s="488"/>
-      <c r="M489" s="488"/>
-      <c r="N489" s="488"/>
-      <c r="O489" s="488"/>
-      <c r="P489" s="488"/>
-      <c r="Q489" s="488"/>
-      <c r="R489" s="488"/>
-      <c r="S489" s="488"/>
-      <c r="T489" s="488"/>
-      <c r="U489" s="488"/>
-      <c r="V489" s="488"/>
-      <c r="W489" s="488"/>
-      <c r="X489" s="488"/>
-      <c r="Y489" s="488"/>
-      <c r="Z489" s="488"/>
-      <c r="AA489" s="488"/>
-      <c r="AB489" s="488"/>
-      <c r="AC489" s="488"/>
-      <c r="AD489" s="488"/>
-      <c r="AE489" s="488"/>
-      <c r="AF489" s="488"/>
-      <c r="AG489" s="488"/>
-      <c r="AH489" s="488"/>
-      <c r="AI489" s="488"/>
-      <c r="AJ489" s="488"/>
-      <c r="AK489" s="488"/>
-      <c r="AL489" s="488"/>
-      <c r="AM489" s="488"/>
-      <c r="AN489" s="488"/>
-      <c r="AO489" s="488"/>
-      <c r="AP489" s="488"/>
-      <c r="AQ489" s="488"/>
-    </row>
-    <row r="490" spans="1:43" s="485" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A490" s="488"/>
+      <c r="C489" s="261"/>
+      <c r="D489" s="232"/>
+      <c r="E489" s="99"/>
+      <c r="F489" s="99"/>
+      <c r="G489" s="99"/>
+      <c r="H489" s="222"/>
+      <c r="I489" s="99"/>
+      <c r="J489" s="99"/>
+      <c r="K489" s="99"/>
+      <c r="L489" s="99"/>
+      <c r="M489" s="99"/>
+      <c r="N489" s="99"/>
+      <c r="O489" s="99"/>
+      <c r="P489" s="99"/>
+      <c r="Q489" s="99"/>
+      <c r="R489" s="99"/>
+      <c r="S489" s="99"/>
+      <c r="T489" s="99"/>
+      <c r="U489" s="99"/>
+      <c r="V489" s="99"/>
+      <c r="W489" s="99"/>
+      <c r="X489" s="99"/>
+      <c r="Y489" s="99"/>
+      <c r="Z489" s="99"/>
+      <c r="AA489" s="99"/>
+      <c r="AB489" s="99"/>
+      <c r="AC489" s="99"/>
+      <c r="AD489" s="99"/>
+      <c r="AE489" s="99"/>
+      <c r="AF489" s="99"/>
+      <c r="AG489" s="99"/>
+      <c r="AH489" s="99"/>
+      <c r="AI489" s="99"/>
+      <c r="AJ489" s="99"/>
+      <c r="AK489" s="99"/>
+      <c r="AL489" s="99"/>
+      <c r="AM489" s="99"/>
+      <c r="AN489" s="99"/>
+      <c r="AO489" s="99"/>
+      <c r="AP489" s="99"/>
+      <c r="AQ489" s="99"/>
+    </row>
+    <row r="490" spans="1:43" ht="15.75" customHeight="1">
+      <c r="A490" s="99"/>
       <c r="B490" s="469"/>
-      <c r="C490" s="486"/>
-      <c r="D490" s="487"/>
-      <c r="E490" s="488"/>
-      <c r="F490" s="488"/>
-      <c r="G490" s="488"/>
-      <c r="H490" s="489"/>
-      <c r="I490" s="488"/>
-      <c r="J490" s="488"/>
-      <c r="K490" s="488"/>
-      <c r="L490" s="488"/>
-      <c r="M490" s="488"/>
-      <c r="N490" s="488"/>
-      <c r="O490" s="488"/>
-      <c r="P490" s="488"/>
-      <c r="Q490" s="488"/>
-      <c r="R490" s="488"/>
-      <c r="S490" s="488"/>
-      <c r="T490" s="488"/>
-      <c r="U490" s="488"/>
-      <c r="V490" s="488"/>
-      <c r="W490" s="488"/>
-      <c r="X490" s="488"/>
-      <c r="Y490" s="488"/>
-      <c r="Z490" s="488"/>
-      <c r="AA490" s="488"/>
-      <c r="AB490" s="488"/>
-      <c r="AC490" s="488"/>
-      <c r="AD490" s="488"/>
-      <c r="AE490" s="488"/>
-      <c r="AF490" s="488"/>
-      <c r="AG490" s="488"/>
-      <c r="AH490" s="488"/>
-      <c r="AI490" s="488"/>
-      <c r="AJ490" s="488"/>
-      <c r="AK490" s="488"/>
-      <c r="AL490" s="488"/>
-      <c r="AM490" s="488"/>
-      <c r="AN490" s="488"/>
-      <c r="AO490" s="488"/>
-      <c r="AP490" s="488"/>
-      <c r="AQ490" s="488"/>
+      <c r="C490" s="261"/>
+      <c r="D490" s="232"/>
+      <c r="E490" s="99"/>
+      <c r="F490" s="99"/>
+      <c r="G490" s="99"/>
+      <c r="H490" s="222"/>
+      <c r="I490" s="99"/>
+      <c r="J490" s="99"/>
+      <c r="K490" s="99"/>
+      <c r="L490" s="99"/>
+      <c r="M490" s="99"/>
+      <c r="N490" s="99"/>
+      <c r="O490" s="99"/>
+      <c r="P490" s="99"/>
+      <c r="Q490" s="99"/>
+      <c r="R490" s="99"/>
+      <c r="S490" s="99"/>
+      <c r="T490" s="99"/>
+      <c r="U490" s="99"/>
+      <c r="V490" s="99"/>
+      <c r="W490" s="99"/>
+      <c r="X490" s="99"/>
+      <c r="Y490" s="99"/>
+      <c r="Z490" s="99"/>
+      <c r="AA490" s="99"/>
+      <c r="AB490" s="99"/>
+      <c r="AC490" s="99"/>
+      <c r="AD490" s="99"/>
+      <c r="AE490" s="99"/>
+      <c r="AF490" s="99"/>
+      <c r="AG490" s="99"/>
+      <c r="AH490" s="99"/>
+      <c r="AI490" s="99"/>
+      <c r="AJ490" s="99"/>
+      <c r="AK490" s="99"/>
+      <c r="AL490" s="99"/>
+      <c r="AM490" s="99"/>
+      <c r="AN490" s="99"/>
+      <c r="AO490" s="99"/>
+      <c r="AP490" s="99"/>
+      <c r="AQ490" s="99"/>
     </row>
     <row r="491" spans="1:43" ht="15.75" customHeight="1">
       <c r="A491" s="99"/>
@@ -65180,7 +65163,7 @@
   <customSheetViews>
     <customSheetView guid="{CDB312C8-EF45-44D8-B316-E4A590B5DAF9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AC678" xr:uid="{CC1BB538-8C14-7C4E-8BF6-2EB108311D6F}"/>
+      <autoFilter ref="A1:AC678" xr:uid="{B6AFF0AA-3A11-B84C-B4F9-0F3C60BCFE21}"/>
     </customSheetView>
   </customSheetViews>
   <hyperlinks>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE432F7-5096-124C-89DF-ABD71B17CD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A419C937-3654-CC4D-876F-DD8B3ACFDE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3740" yWindow="-21100" windowWidth="36840" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12589,9 +12589,6 @@
     <t>https://gallica.bnf.fr/ark:/12148/bpt6k62258617/f295.item</t>
   </si>
   <si>
-    <t>[Médaille représentant le théologien calviniste Pierre Jurieu]*</t>
-  </si>
-  <si>
     <t>emblématique ; religion ;</t>
   </si>
   <si>
@@ -17471,6 +17468,9 @@
   </si>
   <si>
     <t>Une des médailles le plus souvent offertes par le roi aux représentants étrangers</t>
+  </si>
+  <si>
+    <t>[Portrait en médaille de Pierre Jurieu]*</t>
   </si>
 </sst>
 </file>
@@ -20604,7 +20604,7 @@
     </row>
     <row r="2" spans="1:43" ht="15.75" customHeight="1">
       <c r="A2" s="441" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>30</v>
@@ -20812,7 +20812,7 @@
       <c r="W4" s="29"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="30" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="Z4" s="30"/>
       <c r="AA4" s="30"/>
@@ -20839,7 +20839,7 @@
     </row>
     <row r="5" spans="1:43" ht="15.75" customHeight="1">
       <c r="A5" s="441" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>72</v>
@@ -20914,7 +20914,7 @@
     </row>
     <row r="6" spans="1:43" ht="15.75" customHeight="1">
       <c r="A6" s="441" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>43</v>
@@ -21064,7 +21064,7 @@
     </row>
     <row r="8" spans="1:43" ht="15.75" customHeight="1">
       <c r="A8" s="441" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>100</v>
@@ -21210,7 +21210,7 @@
     </row>
     <row r="10" spans="1:43" ht="15.75" customHeight="1">
       <c r="A10" s="441" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>100</v>
@@ -21362,7 +21362,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="248" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="D12" s="233"/>
       <c r="E12" s="67"/>
@@ -21433,7 +21433,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="248" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="D13" s="232"/>
       <c r="E13" s="58"/>
@@ -21640,13 +21640,13 @@
     </row>
     <row r="16" spans="1:43" ht="15.75" customHeight="1">
       <c r="A16" s="453" t="s">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="261" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="D16" s="231" t="s">
         <v>179</v>
@@ -21700,7 +21700,7 @@
         <v>191</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="Z16" s="30"/>
       <c r="AA16" s="30"/>
@@ -21727,13 +21727,13 @@
     </row>
     <row r="17" spans="1:43" ht="15.75" customHeight="1">
       <c r="A17" s="99" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="B17" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="263" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="D17" s="231" t="s">
         <v>179</v>
@@ -21814,7 +21814,7 @@
     </row>
     <row r="18" spans="1:43" ht="15.75" customHeight="1">
       <c r="A18" s="99" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="B18" s="87" t="s">
         <v>201</v>
@@ -21901,7 +21901,7 @@
     </row>
     <row r="19" spans="1:43" ht="15.75" customHeight="1">
       <c r="A19" s="99" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="B19" s="32" t="s">
         <v>43</v>
@@ -21988,7 +21988,7 @@
     </row>
     <row r="20" spans="1:43" ht="15.75" customHeight="1">
       <c r="A20" s="99" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="B20" s="32" t="s">
         <v>43</v>
@@ -22073,7 +22073,7 @@
     </row>
     <row r="21" spans="1:43" ht="15.75" customHeight="1">
       <c r="A21" s="99" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="B21" s="32" t="s">
         <v>43</v>
@@ -22304,7 +22304,7 @@
     </row>
     <row r="24" spans="1:43" ht="15.75" customHeight="1">
       <c r="A24" s="441" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="B24" s="32" t="s">
         <v>246</v>
@@ -22373,7 +22373,7 @@
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
       <c r="A25" s="441" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>246</v>
@@ -22442,7 +22442,7 @@
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
       <c r="A26" s="441" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="B26" s="32" t="s">
         <v>246</v>
@@ -22521,7 +22521,7 @@
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
       <c r="A27" s="441" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="B27" s="33" t="s">
         <v>277</v>
@@ -22596,7 +22596,7 @@
     </row>
     <row r="28" spans="1:43" ht="15.75" customHeight="1">
       <c r="A28" s="441" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="B28" s="33" t="s">
         <v>290</v>
@@ -22608,7 +22608,7 @@
         <v>279</v>
       </c>
       <c r="E28" s="99" t="s">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>291</v>
@@ -22677,13 +22677,13 @@
     </row>
     <row r="29" spans="1:43" ht="15.75" customHeight="1">
       <c r="A29" s="441" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>290</v>
       </c>
       <c r="C29" s="247" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="D29" s="229"/>
       <c r="E29" s="443"/>
@@ -22750,7 +22750,7 @@
     </row>
     <row r="30" spans="1:43" ht="15.75" customHeight="1">
       <c r="A30" s="441" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="B30" s="32" t="s">
         <v>307</v>
@@ -22831,7 +22831,7 @@
         <v>290</v>
       </c>
       <c r="C31" s="247" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="D31" s="229"/>
       <c r="E31" s="443"/>
@@ -22896,19 +22896,19 @@
     </row>
     <row r="32" spans="1:43" ht="15.75" customHeight="1">
       <c r="A32" s="441" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
       <c r="B32" s="95" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="248" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="D32" s="231" t="s">
         <v>278</v>
       </c>
       <c r="E32" s="99" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>322</v>
@@ -22977,19 +22977,19 @@
     </row>
     <row r="33" spans="1:43" ht="15.75" customHeight="1">
       <c r="A33" s="441" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="248" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="D33" s="231" t="s">
         <v>278</v>
       </c>
       <c r="E33" s="99" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="F33" s="16" t="s">
         <v>328</v>
@@ -23058,13 +23058,13 @@
     </row>
     <row r="34" spans="1:43" ht="15.75" customHeight="1">
       <c r="A34" s="441" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="247" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="D34" s="232"/>
       <c r="E34" s="58"/>
@@ -23208,7 +23208,7 @@
     </row>
     <row r="36" spans="1:43" ht="15.75" customHeight="1">
       <c r="A36" s="441" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>43</v>
@@ -23217,7 +23217,7 @@
         <v>355</v>
       </c>
       <c r="D36" s="232" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="E36" s="58"/>
       <c r="F36" s="32" t="s">
@@ -23255,7 +23255,7 @@
         <v>41</v>
       </c>
       <c r="T36" s="21" t="s">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="U36" s="28"/>
       <c r="V36" s="28"/>
@@ -23289,7 +23289,7 @@
     </row>
     <row r="37" spans="1:43" ht="15.75" customHeight="1">
       <c r="A37" s="441" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>43</v>
@@ -23334,7 +23334,7 @@
         <v>41</v>
       </c>
       <c r="T37" s="21" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="U37" s="28"/>
       <c r="V37" s="28"/>
@@ -23368,7 +23368,7 @@
         <v>373</v>
       </c>
       <c r="C38" s="247" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="D38" s="232"/>
       <c r="E38" s="58"/>
@@ -23403,7 +23403,7 @@
         <v>41</v>
       </c>
       <c r="T38" s="21" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="U38" s="28"/>
       <c r="V38" s="28"/>
@@ -23431,13 +23431,13 @@
     </row>
     <row r="39" spans="1:43" ht="15.75" customHeight="1">
       <c r="A39" s="441" t="s">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="430" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="D39" s="231" t="s">
         <v>179</v>
@@ -23476,7 +23476,7 @@
         <v>41</v>
       </c>
       <c r="T39" s="21" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="U39" s="28"/>
       <c r="V39" s="28"/>
@@ -23504,13 +23504,13 @@
     </row>
     <row r="40" spans="1:43" ht="15.75" customHeight="1">
       <c r="A40" s="441" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="247" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="D40" s="231" t="s">
         <v>179</v>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="48" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="I41" s="43" t="s">
         <v>380</v>
@@ -23601,7 +23601,7 @@
         <v>381</v>
       </c>
       <c r="M41" s="95" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="N41" s="54" t="s">
         <v>382</v>
@@ -23642,13 +23642,13 @@
     </row>
     <row r="42" spans="1:43" ht="15.75" customHeight="1">
       <c r="A42" s="441" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="247" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="D42" s="232"/>
       <c r="E42" s="58"/>
@@ -23713,13 +23713,13 @@
     </row>
     <row r="43" spans="1:43" ht="15.75" customHeight="1">
       <c r="A43" s="441" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="247" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="D43" s="232"/>
       <c r="E43" s="58"/>
@@ -23765,7 +23765,7 @@
         <v>400</v>
       </c>
       <c r="Y43" s="30" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="Z43" s="30"/>
       <c r="AA43" s="30"/>
@@ -23924,13 +23924,13 @@
     </row>
     <row r="46" spans="1:43" ht="15.75" customHeight="1">
       <c r="A46" s="441" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="247" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="D46" s="232"/>
       <c r="E46" s="58"/>
@@ -24007,7 +24007,7 @@
         <v>409</v>
       </c>
       <c r="C47" s="247" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="D47" s="232"/>
       <c r="E47" s="58"/>
@@ -24068,13 +24068,13 @@
     </row>
     <row r="48" spans="1:43" ht="15.75" customHeight="1">
       <c r="A48" s="441" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="B48" s="32" t="s">
         <v>430</v>
       </c>
       <c r="C48" s="247" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="D48" s="232"/>
       <c r="E48" s="58"/>
@@ -24225,13 +24225,13 @@
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
       <c r="A50" s="441" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>430</v>
       </c>
       <c r="C50" s="247" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="D50" s="232"/>
       <c r="E50" s="58"/>
@@ -24296,13 +24296,13 @@
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
       <c r="A51" s="441" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>440</v>
       </c>
       <c r="C51" s="247" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="D51" s="231" t="s">
         <v>461</v>
@@ -24367,7 +24367,7 @@
     </row>
     <row r="52" spans="1:43" ht="15.75" customHeight="1">
       <c r="A52" s="441" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>467</v>
@@ -24529,7 +24529,7 @@
     </row>
     <row r="54" spans="1:43" ht="15.75" customHeight="1">
       <c r="A54" s="441" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="B54" s="129" t="s">
         <v>493</v>
@@ -24608,7 +24608,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="247" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="D55" s="232"/>
       <c r="E55" s="58"/>
@@ -24748,7 +24748,7 @@
     </row>
     <row r="57" spans="1:43" ht="15.75" customHeight="1">
       <c r="A57" s="441" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="B57" s="32" t="s">
         <v>43</v>
@@ -24815,13 +24815,13 @@
     </row>
     <row r="58" spans="1:43" ht="15.75" customHeight="1">
       <c r="A58" s="441" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="B58" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="247" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="D58" s="231" t="s">
         <v>179</v>
@@ -24890,13 +24890,13 @@
     </row>
     <row r="59" spans="1:43" ht="15.75" customHeight="1">
       <c r="A59" s="441" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="B59" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="247" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="D59" s="231" t="s">
         <v>179</v>
@@ -24961,7 +24961,7 @@
     </row>
     <row r="60" spans="1:43" ht="15.75" customHeight="1">
       <c r="A60" s="441" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="B60" s="32" t="s">
         <v>43</v>
@@ -25009,7 +25009,7 @@
       <c r="W60" s="111"/>
       <c r="X60" s="111"/>
       <c r="Y60" s="30" t="s">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="Z60" s="30" t="s">
         <v>541</v>
@@ -25036,18 +25036,18 @@
     </row>
     <row r="61" spans="1:43" ht="15.75" customHeight="1">
       <c r="A61" s="441" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="B61" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="247" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="D61" s="232"/>
       <c r="E61" s="58"/>
       <c r="F61" s="47" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>543</v>
@@ -25107,7 +25107,7 @@
     </row>
     <row r="62" spans="1:43" ht="15.75" customHeight="1">
       <c r="A62" s="441" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="B62" s="32" t="s">
         <v>43</v>
@@ -25180,13 +25180,13 @@
         <v>558</v>
       </c>
       <c r="C63" s="247" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="D63" s="231" t="s">
         <v>559</v>
       </c>
       <c r="E63" s="58" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="F63" s="265" t="s">
         <v>560</v>
@@ -25247,13 +25247,13 @@
     </row>
     <row r="64" spans="1:43" ht="15.75" customHeight="1">
       <c r="A64" s="441" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="247" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="D64" s="232"/>
       <c r="E64" s="58"/>
@@ -25320,13 +25320,13 @@
     </row>
     <row r="65" spans="1:43" ht="15.75" customHeight="1">
       <c r="A65" s="441" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="B65" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="247" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="D65" s="232"/>
       <c r="E65" s="58"/>
@@ -25393,7 +25393,7 @@
     </row>
     <row r="66" spans="1:43" ht="15.75" customHeight="1">
       <c r="A66" s="441" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="B66" s="32" t="s">
         <v>43</v>
@@ -25626,7 +25626,7 @@
     </row>
     <row r="69" spans="1:43" ht="15.75" customHeight="1">
       <c r="A69" s="441" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="B69" s="32" t="s">
         <v>43</v>
@@ -25713,7 +25713,7 @@
     </row>
     <row r="70" spans="1:43" ht="15.75" customHeight="1">
       <c r="A70" s="441" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="B70" s="32" t="s">
         <v>43</v>
@@ -25782,13 +25782,13 @@
     </row>
     <row r="71" spans="1:43" ht="15.75" customHeight="1">
       <c r="A71" s="441" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="B71" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="247" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
       <c r="D71" s="232"/>
       <c r="E71" s="58"/>
@@ -25851,7 +25851,7 @@
     </row>
     <row r="72" spans="1:43" ht="15.75" customHeight="1">
       <c r="A72" s="441" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="B72" s="32" t="s">
         <v>638</v>
@@ -25997,7 +25997,7 @@
     </row>
     <row r="74" spans="1:43" ht="15.75" customHeight="1">
       <c r="A74" s="441" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="B74" s="39" t="s">
         <v>43</v>
@@ -26072,7 +26072,7 @@
         <v>43</v>
       </c>
       <c r="C75" s="247" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="D75" s="308"/>
       <c r="E75" s="58"/>
@@ -26719,7 +26719,7 @@
     </row>
     <row r="84" spans="1:43" ht="15.75" customHeight="1">
       <c r="A84" s="442" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>743</v>
@@ -26855,7 +26855,7 @@
     </row>
     <row r="86" spans="1:43" ht="15.75" customHeight="1">
       <c r="A86" s="442" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>430</v>
@@ -27232,7 +27232,7 @@
     </row>
     <row r="91" spans="1:43" ht="15.75" customHeight="1">
       <c r="A91" s="442" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>43</v>
@@ -27585,7 +27585,7 @@
     </row>
     <row r="96" spans="1:43" ht="15.75" customHeight="1">
       <c r="A96" s="441" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>430</v>
@@ -27652,7 +27652,7 @@
     </row>
     <row r="97" spans="1:43" ht="15.75" customHeight="1">
       <c r="A97" s="441" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="B97" s="32" t="s">
         <v>43</v>
@@ -27855,7 +27855,7 @@
     </row>
     <row r="100" spans="1:43" ht="15.75" customHeight="1">
       <c r="A100" s="441" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="B100" s="32" t="s">
         <v>864</v>
@@ -28001,7 +28001,7 @@
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
       <c r="A102" s="441" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>884</v>
@@ -28147,7 +28147,7 @@
     </row>
     <row r="104" spans="1:43" ht="15.75" customHeight="1">
       <c r="A104" s="441" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="B104" s="32" t="s">
         <v>467</v>
@@ -28360,7 +28360,7 @@
     </row>
     <row r="107" spans="1:43" ht="15.75" customHeight="1">
       <c r="A107" s="441" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="B107" s="32" t="s">
         <v>43</v>
@@ -28443,7 +28443,7 @@
     </row>
     <row r="108" spans="1:43" ht="15.75" customHeight="1">
       <c r="A108" s="441" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="B108" s="32" t="s">
         <v>43</v>
@@ -28650,7 +28650,7 @@
     </row>
     <row r="111" spans="1:43" ht="15.75" customHeight="1">
       <c r="A111" s="441" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="B111" s="32" t="s">
         <v>43</v>
@@ -28863,7 +28863,7 @@
     </row>
     <row r="114" spans="1:43" ht="15.75" customHeight="1">
       <c r="A114" s="441" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="B114" s="32" t="s">
         <v>430</v>
@@ -29226,7 +29226,7 @@
     </row>
     <row r="119" spans="1:43" ht="15.75" customHeight="1">
       <c r="A119" s="441" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>43</v>
@@ -29241,7 +29241,7 @@
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="32" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="I119" s="43" t="s">
         <v>1031</v>
@@ -29437,7 +29437,7 @@
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
       <c r="A122" s="454" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="B122" s="51" t="s">
         <v>43</v>
@@ -29489,7 +29489,7 @@
       <c r="W122" s="29"/>
       <c r="X122" s="29"/>
       <c r="Y122" s="30" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="Z122" s="30"/>
       <c r="AA122" s="30"/>
@@ -29954,7 +29954,7 @@
     </row>
     <row r="129" spans="1:43" ht="15.75" customHeight="1">
       <c r="A129" s="454" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="B129" s="32" t="s">
         <v>43</v>
@@ -30025,7 +30025,7 @@
     </row>
     <row r="130" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
       <c r="A130" s="441" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>43</v>
@@ -30098,7 +30098,7 @@
     </row>
     <row r="131" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
       <c r="A131" s="441" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="B131" s="33" t="s">
         <v>43</v>
@@ -30534,7 +30534,7 @@
     </row>
     <row r="137" spans="1:43" ht="15.75" customHeight="1">
       <c r="A137" s="456" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>43</v>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="G137" s="32"/>
       <c r="H137" s="48" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="I137" s="43" t="s">
         <v>1179</v>
@@ -30674,7 +30674,7 @@
     </row>
     <row r="139" spans="1:43" ht="15.75" customHeight="1">
       <c r="A139" s="456" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="B139" s="33" t="s">
         <v>43</v>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="G139" s="32"/>
       <c r="H139" s="48" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="I139" s="43" t="s">
         <v>1193</v>
@@ -30999,7 +30999,7 @@
         <v>41</v>
       </c>
       <c r="T143" s="21" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="U143" s="28"/>
       <c r="V143" s="28"/>
@@ -31070,7 +31070,7 @@
         <v>41</v>
       </c>
       <c r="T144" s="21" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="U144" s="28"/>
       <c r="V144" s="28"/>
@@ -32743,7 +32743,7 @@
         <v>176</v>
       </c>
       <c r="N167" s="134" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="O167" s="134"/>
       <c r="P167" s="153" t="s">
@@ -32753,7 +32753,7 @@
         <v>1413</v>
       </c>
       <c r="R167" s="39" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="S167" s="21" t="s">
         <v>41</v>
@@ -32866,7 +32866,7 @@
     </row>
     <row r="169" spans="1:43" ht="15.75" customHeight="1">
       <c r="A169" s="441" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="B169" s="33" t="s">
         <v>43</v>
@@ -33296,7 +33296,7 @@
     </row>
     <row r="175" spans="1:43" ht="15.75" customHeight="1">
       <c r="A175" s="441" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="B175" s="33" t="s">
         <v>43</v>
@@ -33365,7 +33365,7 @@
     </row>
     <row r="176" spans="1:43" ht="15.75" customHeight="1">
       <c r="A176" s="441" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="B176" s="33" t="s">
         <v>43</v>
@@ -33432,7 +33432,7 @@
     </row>
     <row r="177" spans="1:43" s="350" customFormat="1" ht="15.75" customHeight="1">
       <c r="A177" s="454" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="B177" s="15" t="s">
         <v>467</v>
@@ -33890,7 +33890,7 @@
     </row>
     <row r="183" spans="1:43" ht="15.75" customHeight="1">
       <c r="A183" s="441" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="B183" s="33" t="s">
         <v>43</v>
@@ -33959,7 +33959,7 @@
     </row>
     <row r="184" spans="1:43" ht="15.75" customHeight="1">
       <c r="A184" s="441" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="B184" s="33" t="s">
         <v>43</v>
@@ -34393,7 +34393,7 @@
     </row>
     <row r="190" spans="1:43" ht="15.75" customHeight="1">
       <c r="A190" s="454" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="B190" s="15" t="s">
         <v>43</v>
@@ -34508,7 +34508,7 @@
       <c r="W191" s="29"/>
       <c r="X191" s="110"/>
       <c r="Y191" s="30" t="s">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="Z191" s="30" t="s">
         <v>1604</v>
@@ -34604,13 +34604,13 @@
     </row>
     <row r="193" spans="1:43" ht="15.75" customHeight="1">
       <c r="A193" s="441" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="B193" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C193" s="248" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="D193" s="232"/>
       <c r="E193" s="58"/>
@@ -34720,7 +34720,7 @@
         <v>41</v>
       </c>
       <c r="T194" s="21" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="U194" s="28" t="s">
         <v>1058</v>
@@ -34801,7 +34801,7 @@
         <v>41</v>
       </c>
       <c r="T195" s="21" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="U195" s="28" t="s">
         <v>1058</v>
@@ -34865,7 +34865,7 @@
         <v>1647</v>
       </c>
       <c r="M196" s="95" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="N196" s="54" t="s">
         <v>1648</v>
@@ -35482,7 +35482,7 @@
     </row>
     <row r="205" spans="1:43" ht="15.75" customHeight="1">
       <c r="A205" s="441" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="B205" s="33" t="s">
         <v>43</v>
@@ -35628,7 +35628,7 @@
     </row>
     <row r="207" spans="1:43" ht="15.75" customHeight="1">
       <c r="A207" s="441" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>430</v>
@@ -35946,7 +35946,7 @@
     </row>
     <row r="211" spans="1:43" ht="15.75" customHeight="1">
       <c r="A211" s="441" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>1000</v>
@@ -36108,7 +36108,7 @@
     </row>
     <row r="213" spans="1:43" ht="15.75" customHeight="1">
       <c r="A213" s="441" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>430</v>
@@ -36161,7 +36161,7 @@
       <c r="AB213" s="165"/>
       <c r="AC213" s="32"/>
       <c r="AD213" s="21" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
       <c r="AE213" s="32"/>
       <c r="AF213" s="32"/>
@@ -36412,10 +36412,10 @@
         <v>1000</v>
       </c>
       <c r="C217" s="440" t="s">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="D217" s="232" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="E217" s="58"/>
       <c r="F217" s="32" t="s">
@@ -36442,7 +36442,7 @@
       <c r="O217" s="54"/>
       <c r="P217" s="55"/>
       <c r="Q217" s="318" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="R217" s="115" t="s">
         <v>383</v>
@@ -36487,7 +36487,7 @@
         <v>1000</v>
       </c>
       <c r="C218" s="247" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="D218" s="232"/>
       <c r="E218" s="58"/>
@@ -36765,7 +36765,7 @@
     </row>
     <row r="222" spans="1:43" ht="15.75" customHeight="1">
       <c r="A222" s="441" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>430</v>
@@ -36923,7 +36923,7 @@
     </row>
     <row r="224" spans="1:43" ht="15.75" customHeight="1">
       <c r="A224" s="441" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>1905</v>
@@ -37004,7 +37004,7 @@
     </row>
     <row r="225" spans="1:43" ht="15.75" customHeight="1">
       <c r="A225" s="441" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="B225" s="14" t="s">
         <v>430</v>
@@ -37160,10 +37160,10 @@
       <c r="K227" s="82"/>
       <c r="L227" s="22"/>
       <c r="M227" s="53" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N227" s="54" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="O227" s="394"/>
       <c r="P227" s="290" t="s">
@@ -37239,10 +37239,10 @@
       <c r="K228" s="22"/>
       <c r="L228" s="22"/>
       <c r="M228" s="53" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N228" s="54" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="O228" s="54"/>
       <c r="P228" s="290" t="s">
@@ -37655,13 +37655,13 @@
     </row>
     <row r="234" spans="1:43" ht="15.75" customHeight="1">
       <c r="A234" s="441" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>430</v>
       </c>
       <c r="C234" s="258" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="D234" s="232"/>
       <c r="E234" s="58"/>
@@ -37995,7 +37995,7 @@
         <v>1999</v>
       </c>
       <c r="M238" s="95" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="N238" s="38" t="s">
         <v>1648</v>
@@ -38082,10 +38082,10 @@
         <v>2010</v>
       </c>
       <c r="M239" s="125" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="N239" s="54" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="O239" s="54"/>
       <c r="P239" s="25" t="s">
@@ -38135,7 +38135,7 @@
     </row>
     <row r="240" spans="1:43" ht="15.75" customHeight="1">
       <c r="A240" s="441" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>430</v>
@@ -38240,7 +38240,7 @@
       <c r="K241" s="82"/>
       <c r="L241" s="82"/>
       <c r="M241" s="53" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N241" s="54" t="s">
         <v>2024</v>
@@ -38312,7 +38312,7 @@
         <v>2028</v>
       </c>
       <c r="H242" s="48" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
       <c r="I242" s="43" t="s">
         <v>2029</v>
@@ -38321,7 +38321,7 @@
       <c r="K242" s="22"/>
       <c r="L242" s="22"/>
       <c r="M242" s="53" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N242" s="54" t="s">
         <v>2030</v>
@@ -38682,23 +38682,23 @@
     </row>
     <row r="247" spans="1:43" ht="15.75" customHeight="1">
       <c r="A247" s="459" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="B247" s="356" t="s">
         <v>2075</v>
       </c>
       <c r="C247" s="259" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="E247" s="227"/>
       <c r="F247" s="227" t="s">
+        <v>3761</v>
+      </c>
+      <c r="G247" s="227" t="s">
         <v>3762</v>
       </c>
-      <c r="G247" s="227" t="s">
-        <v>3763</v>
-      </c>
       <c r="H247" s="360" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="I247" s="358" t="s">
         <v>1903</v>
@@ -38707,10 +38707,10 @@
       <c r="K247" s="227"/>
       <c r="L247" s="227"/>
       <c r="M247" s="358" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N247" s="396" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="O247" s="395"/>
       <c r="P247" s="290" t="s">
@@ -38726,7 +38726,7 @@
         <v>41</v>
       </c>
       <c r="T247" s="360" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="U247" s="360" t="s">
         <v>1896</v>
@@ -38737,7 +38737,7 @@
       <c r="W247" s="227"/>
       <c r="X247" s="227"/>
       <c r="Y247" s="370" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="Z247" s="227"/>
       <c r="AA247" s="227"/>
@@ -38746,7 +38746,7 @@
         <v>2076</v>
       </c>
       <c r="AD247" s="227" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="AE247" s="227"/>
       <c r="AF247" s="227"/>
@@ -38764,19 +38764,19 @@
     </row>
     <row r="248" spans="1:43" ht="15.75" customHeight="1">
       <c r="A248" s="459" t="s">
+        <v>3756</v>
+      </c>
+      <c r="B248" s="360" t="s">
         <v>3757</v>
       </c>
-      <c r="B248" s="360" t="s">
-        <v>3758</v>
-      </c>
       <c r="C248" s="259" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="E248" s="227"/>
       <c r="F248" s="227"/>
       <c r="G248" s="360"/>
       <c r="H248" s="360" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="I248" s="358" t="s">
         <v>2023</v>
@@ -38785,10 +38785,10 @@
       <c r="K248" s="227"/>
       <c r="L248" s="227"/>
       <c r="M248" s="358" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N248" s="396" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="O248" s="395"/>
       <c r="P248" s="290" t="s">
@@ -38804,7 +38804,7 @@
         <v>41</v>
       </c>
       <c r="T248" s="360" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="U248" s="360" t="s">
         <v>1896</v>
@@ -38815,7 +38815,7 @@
       <c r="W248" s="227"/>
       <c r="X248" s="227"/>
       <c r="Y248" s="360" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="Z248" s="227"/>
       <c r="AA248" s="227"/>
@@ -39136,7 +39136,7 @@
         <v>430</v>
       </c>
       <c r="C253" s="248" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="D253" s="232"/>
       <c r="E253" s="58"/>
@@ -39495,7 +39495,7 @@
     </row>
     <row r="258" spans="1:43" ht="15.75" customHeight="1">
       <c r="A258" s="441" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="B258" s="14" t="s">
         <v>430</v>
@@ -39862,7 +39862,7 @@
     </row>
     <row r="263" spans="1:43" ht="15.75" customHeight="1">
       <c r="A263" s="441" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="B263" s="14" t="s">
         <v>430</v>
@@ -40002,7 +40002,7 @@
     </row>
     <row r="265" spans="1:43" ht="15.75" customHeight="1">
       <c r="A265" s="441" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="B265" s="14" t="s">
         <v>2201</v>
@@ -40028,10 +40028,10 @@
       <c r="K265" s="22"/>
       <c r="L265" s="22"/>
       <c r="M265" s="53" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N265" s="54" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="O265" s="54"/>
       <c r="P265" s="290" t="s">
@@ -40073,7 +40073,7 @@
     </row>
     <row r="266" spans="1:43" ht="15.75" customHeight="1">
       <c r="A266" s="441" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="B266" s="14" t="s">
         <v>430</v>
@@ -40292,7 +40292,7 @@
     </row>
     <row r="269" spans="1:43" ht="15.75" customHeight="1">
       <c r="A269" s="441" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="B269" s="66" t="s">
         <v>2231</v>
@@ -40395,10 +40395,10 @@
       <c r="K270" s="22"/>
       <c r="L270" s="22"/>
       <c r="M270" s="292" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N270" s="73" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="O270" s="73"/>
       <c r="P270" s="290" t="s">
@@ -40423,7 +40423,7 @@
       <c r="W270" s="29"/>
       <c r="X270" s="29"/>
       <c r="Y270" s="30" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="Z270" s="30"/>
       <c r="AA270" s="30"/>
@@ -40649,7 +40649,7 @@
     </row>
     <row r="274" spans="1:43" ht="15.75" customHeight="1">
       <c r="A274" s="441" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="B274" s="14" t="s">
         <v>430</v>
@@ -40896,10 +40896,10 @@
       <c r="K277" s="82"/>
       <c r="L277" s="22"/>
       <c r="M277" s="292" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N277" s="38" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="O277" s="38"/>
       <c r="P277" s="290" t="s">
@@ -41267,7 +41267,7 @@
       <c r="K282" s="22"/>
       <c r="L282" s="22"/>
       <c r="M282" s="292" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N282" s="429" t="s">
         <v>2449</v>
@@ -41295,7 +41295,7 @@
       <c r="W282" s="29"/>
       <c r="X282" s="29"/>
       <c r="Y282" s="30" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="Z282" s="30"/>
       <c r="AA282" s="30"/>
@@ -41359,7 +41359,7 @@
         <v>1897</v>
       </c>
       <c r="R283" s="32" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="S283" s="32" t="s">
         <v>41</v>
@@ -41555,10 +41555,10 @@
       <c r="K286" s="22"/>
       <c r="L286" s="22"/>
       <c r="M286" s="390" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N286" s="89" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="O286" s="89"/>
       <c r="P286" s="124" t="s">
@@ -41574,7 +41574,7 @@
         <v>41</v>
       </c>
       <c r="T286" s="21" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="U286" s="28"/>
       <c r="V286" s="28"/>
@@ -41845,7 +41845,7 @@
       <c r="K290" s="82"/>
       <c r="L290" s="22"/>
       <c r="M290" s="292" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N290" s="54" t="s">
         <v>2372</v>
@@ -42137,10 +42137,10 @@
       <c r="K294" s="82"/>
       <c r="L294" s="82"/>
       <c r="M294" s="33" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="N294" s="89" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="O294" s="393"/>
       <c r="P294" s="112" t="s">
@@ -42165,7 +42165,7 @@
       <c r="W294" s="29"/>
       <c r="X294" s="29"/>
       <c r="Y294" s="30" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="Z294" s="30"/>
       <c r="AA294" s="30"/>
@@ -42190,7 +42190,7 @@
     </row>
     <row r="295" spans="1:43" ht="15.75" customHeight="1">
       <c r="A295" s="441" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="B295" s="14" t="s">
         <v>430</v>
@@ -42512,7 +42512,7 @@
       <c r="K299" s="22"/>
       <c r="L299" s="22"/>
       <c r="M299" s="292" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="N299" s="89" t="s">
         <v>2030</v>
@@ -42673,7 +42673,7 @@
         <v>2454</v>
       </c>
       <c r="N301" s="38" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="O301" s="38"/>
       <c r="P301" s="25"/>
@@ -42989,7 +42989,7 @@
     </row>
     <row r="306" spans="1:43" ht="15.75" customHeight="1">
       <c r="A306" s="458" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="B306" s="33" t="s">
         <v>430</v>
@@ -43147,7 +43147,7 @@
     </row>
     <row r="308" spans="1:43" ht="15.75" customHeight="1">
       <c r="A308" s="458" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="B308" s="33" t="s">
         <v>430</v>
@@ -43301,7 +43301,7 @@
     </row>
     <row r="310" spans="1:43" ht="15.75" customHeight="1">
       <c r="A310" s="458" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="B310" s="33" t="s">
         <v>430</v>
@@ -43316,7 +43316,7 @@
       </c>
       <c r="G310" s="32"/>
       <c r="H310" s="354" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="I310" s="32" t="s">
         <v>2498</v>
@@ -43897,13 +43897,13 @@
     </row>
     <row r="318" spans="1:43" ht="15.75" customHeight="1">
       <c r="A318" s="99" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="B318" s="33" t="s">
         <v>2589</v>
       </c>
       <c r="C318" s="260" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="E318" s="58" t="s">
         <v>2590</v>
@@ -44056,7 +44056,7 @@
     </row>
     <row r="320" spans="1:43" ht="15.75" customHeight="1">
       <c r="A320" s="458" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="B320" s="33" t="s">
         <v>430</v>
@@ -44125,7 +44125,7 @@
     </row>
     <row r="321" spans="1:43" ht="15.75" customHeight="1">
       <c r="A321" s="458" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="B321" s="33" t="s">
         <v>430</v>
@@ -44550,7 +44550,7 @@
         <v>2229</v>
       </c>
       <c r="Y326" s="30" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="Z326" s="30"/>
       <c r="AA326" s="30" t="s">
@@ -44662,7 +44662,7 @@
         <v>430</v>
       </c>
       <c r="C328" s="248" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="D328" s="244"/>
       <c r="E328" s="188"/>
@@ -44737,7 +44737,7 @@
     </row>
     <row r="329" spans="1:43" ht="15.75" customHeight="1">
       <c r="A329" s="458" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="B329" s="33" t="s">
         <v>430</v>
@@ -45441,7 +45441,7 @@
       </c>
       <c r="G338" s="48"/>
       <c r="H338" s="32" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="I338" s="185" t="s">
         <v>2758</v>
@@ -45455,7 +45455,7 @@
         <v>2760</v>
       </c>
       <c r="N338" s="38" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="O338" s="38"/>
       <c r="P338" s="25" t="s">
@@ -45465,7 +45465,7 @@
         <v>2762</v>
       </c>
       <c r="R338" s="428" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="S338" s="77" t="s">
         <v>41</v>
@@ -45732,7 +45732,7 @@
     </row>
     <row r="342" spans="1:43" ht="15.75" customHeight="1">
       <c r="A342" s="458" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="B342" s="33" t="s">
         <v>430</v>
@@ -45897,7 +45897,7 @@
       </c>
       <c r="G344" s="32"/>
       <c r="H344" s="203" t="s">
-        <v>2812</v>
+        <v>4025</v>
       </c>
       <c r="I344" s="190" t="s">
         <v>2498</v>
@@ -45906,17 +45906,17 @@
       <c r="K344" s="82"/>
       <c r="L344" s="82"/>
       <c r="M344" s="135" t="s">
+        <v>2812</v>
+      </c>
+      <c r="N344" s="294" t="s">
         <v>2813</v>
       </c>
-      <c r="N344" s="294" t="s">
+      <c r="O344" s="294" t="s">
         <v>2814</v>
-      </c>
-      <c r="O344" s="294" t="s">
-        <v>2815</v>
       </c>
       <c r="P344" s="25"/>
       <c r="Q344" s="56" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="R344" s="32" t="s">
         <v>519</v>
@@ -45937,10 +45937,10 @@
         <v>2806</v>
       </c>
       <c r="Z344" s="30" t="s">
+        <v>2816</v>
+      </c>
+      <c r="AA344" s="30" t="s">
         <v>2817</v>
-      </c>
-      <c r="AA344" s="30" t="s">
-        <v>2818</v>
       </c>
       <c r="AB344" s="41"/>
       <c r="AC344" s="32"/>
@@ -45961,27 +45961,27 @@
     </row>
     <row r="345" spans="1:43" ht="15.75" customHeight="1">
       <c r="A345" s="458" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="B345" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C345" s="246" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="D345" s="232"/>
       <c r="E345" s="58"/>
       <c r="F345" s="16" t="s">
+        <v>2819</v>
+      </c>
+      <c r="G345" s="32" t="s">
         <v>2820</v>
       </c>
-      <c r="G345" s="32" t="s">
+      <c r="H345" s="191" t="s">
         <v>2821</v>
       </c>
-      <c r="H345" s="191" t="s">
+      <c r="I345" s="185" t="s">
         <v>2822</v>
-      </c>
-      <c r="I345" s="185" t="s">
-        <v>2823</v>
       </c>
       <c r="J345" s="22"/>
       <c r="K345" s="22"/>
@@ -45989,17 +45989,17 @@
         <v>797</v>
       </c>
       <c r="M345" s="135" t="s">
+        <v>2823</v>
+      </c>
+      <c r="N345" s="131" t="s">
         <v>2824</v>
-      </c>
-      <c r="N345" s="131" t="s">
-        <v>2825</v>
       </c>
       <c r="O345" s="131"/>
       <c r="P345" s="25" t="s">
+        <v>2825</v>
+      </c>
+      <c r="Q345" s="56" t="s">
         <v>2826</v>
-      </c>
-      <c r="Q345" s="56" t="s">
-        <v>2827</v>
       </c>
       <c r="R345" s="115" t="s">
         <v>80</v>
@@ -46017,7 +46017,7 @@
         <v>2229</v>
       </c>
       <c r="Y345" s="30" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="Z345" s="30"/>
       <c r="AA345" s="30"/>
@@ -46040,7 +46040,7 @@
     </row>
     <row r="346" spans="1:43" ht="15.75" customHeight="1">
       <c r="A346" s="458" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="B346" s="33" t="s">
         <v>430</v>
@@ -46051,11 +46051,11 @@
       <c r="D346" s="232"/>
       <c r="E346" s="58"/>
       <c r="F346" s="16" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="G346" s="32"/>
       <c r="H346" s="203" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="I346" s="185" t="s">
         <v>2498</v>
@@ -46069,14 +46069,14 @@
         <v>651</v>
       </c>
       <c r="N346" s="38" t="s">
+        <v>2830</v>
+      </c>
+      <c r="O346" s="38" t="s">
         <v>2831</v>
-      </c>
-      <c r="O346" s="38" t="s">
-        <v>2832</v>
       </c>
       <c r="P346" s="25"/>
       <c r="Q346" s="56" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="R346" s="32" t="s">
         <v>519</v>
@@ -46094,13 +46094,13 @@
         <v>2229</v>
       </c>
       <c r="Y346" s="30" t="s">
+        <v>2833</v>
+      </c>
+      <c r="Z346" s="30" t="s">
         <v>2834</v>
       </c>
-      <c r="Z346" s="30" t="s">
+      <c r="AA346" s="30" t="s">
         <v>2835</v>
-      </c>
-      <c r="AA346" s="30" t="s">
-        <v>2836</v>
       </c>
       <c r="AB346" s="41"/>
       <c r="AC346" s="32"/>
@@ -46121,7 +46121,7 @@
     </row>
     <row r="347" spans="1:43" ht="15.75" customHeight="1">
       <c r="A347" s="458" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="B347" s="33" t="s">
         <v>430</v>
@@ -46132,19 +46132,19 @@
       <c r="D347" s="232"/>
       <c r="E347" s="58"/>
       <c r="F347" s="16" t="s">
+        <v>2837</v>
+      </c>
+      <c r="G347" s="32" t="s">
         <v>2838</v>
       </c>
-      <c r="G347" s="32" t="s">
+      <c r="H347" s="204" t="s">
         <v>2839</v>
       </c>
-      <c r="H347" s="204" t="s">
+      <c r="I347" s="185" t="s">
         <v>2840</v>
       </c>
-      <c r="I347" s="185" t="s">
+      <c r="J347" s="22" t="s">
         <v>2841</v>
-      </c>
-      <c r="J347" s="22" t="s">
-        <v>2842</v>
       </c>
       <c r="K347" s="22"/>
       <c r="L347" s="22"/>
@@ -46152,7 +46152,7 @@
         <v>2797</v>
       </c>
       <c r="N347" s="65" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="O347" s="38"/>
       <c r="P347" s="25"/>
@@ -46173,7 +46173,7 @@
         <v>2229</v>
       </c>
       <c r="Y347" s="30" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="Z347" s="102"/>
       <c r="AA347" s="30"/>
@@ -46196,7 +46196,7 @@
     </row>
     <row r="348" spans="1:43" ht="15.75" customHeight="1">
       <c r="A348" s="458" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="B348" s="33" t="s">
         <v>430</v>
@@ -46207,11 +46207,11 @@
       <c r="D348" s="244"/>
       <c r="E348" s="188"/>
       <c r="F348" s="205" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="G348" s="184"/>
       <c r="H348" s="204" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="I348" s="32" t="s">
         <v>2498</v>
@@ -46220,10 +46220,10 @@
       <c r="K348" s="82"/>
       <c r="L348" s="82"/>
       <c r="M348" s="135" t="s">
+        <v>2847</v>
+      </c>
+      <c r="N348" s="38" t="s">
         <v>2848</v>
-      </c>
-      <c r="N348" s="38" t="s">
-        <v>2849</v>
       </c>
       <c r="O348" s="38" t="s">
         <v>38</v>
@@ -46252,10 +46252,10 @@
       </c>
       <c r="Z348" s="197"/>
       <c r="AA348" s="30" t="s">
+        <v>2849</v>
+      </c>
+      <c r="AB348" s="46" t="s">
         <v>2850</v>
-      </c>
-      <c r="AB348" s="46" t="s">
-        <v>2851</v>
       </c>
       <c r="AC348" s="32"/>
       <c r="AD348" s="21"/>
@@ -46275,7 +46275,7 @@
     </row>
     <row r="349" spans="1:43" ht="15.75" customHeight="1">
       <c r="A349" s="458" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="B349" s="33" t="s">
         <v>430</v>
@@ -46286,32 +46286,32 @@
       <c r="D349" s="232"/>
       <c r="E349" s="58"/>
       <c r="F349" s="47" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="G349" s="32"/>
       <c r="H349" s="204" t="s">
+        <v>2852</v>
+      </c>
+      <c r="I349" s="185" t="s">
         <v>2853</v>
-      </c>
-      <c r="I349" s="185" t="s">
-        <v>2854</v>
       </c>
       <c r="J349" s="22"/>
       <c r="K349" s="22"/>
       <c r="L349" s="22" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="M349" s="135" t="s">
         <v>1022</v>
       </c>
       <c r="N349" s="38" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="O349" s="294" t="s">
         <v>768</v>
       </c>
       <c r="P349" s="124"/>
       <c r="Q349" s="26" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="R349" s="101" t="s">
         <v>539</v>
@@ -46352,7 +46352,7 @@
     </row>
     <row r="350" spans="1:43" ht="15.75" customHeight="1">
       <c r="A350" s="458" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="B350" s="33" t="s">
         <v>430</v>
@@ -46363,30 +46363,30 @@
       <c r="D350" s="242"/>
       <c r="E350" s="52"/>
       <c r="F350" s="16" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="G350" s="48"/>
       <c r="H350" s="32" t="s">
+        <v>2859</v>
+      </c>
+      <c r="I350" s="185" t="s">
         <v>2860</v>
-      </c>
-      <c r="I350" s="185" t="s">
-        <v>2861</v>
       </c>
       <c r="J350" s="22"/>
       <c r="K350" s="22"/>
       <c r="L350" s="22"/>
       <c r="M350" s="32" t="s">
+        <v>2861</v>
+      </c>
+      <c r="N350" s="38" t="s">
         <v>2862</v>
-      </c>
-      <c r="N350" s="38" t="s">
-        <v>2863</v>
       </c>
       <c r="O350" s="38"/>
       <c r="P350" s="74" t="s">
         <v>2362</v>
       </c>
       <c r="Q350" s="56" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="R350" s="32" t="s">
         <v>49</v>
@@ -46395,26 +46395,26 @@
         <v>41</v>
       </c>
       <c r="T350" s="88" t="s">
+        <v>2864</v>
+      </c>
+      <c r="U350" s="45" t="s">
         <v>2865</v>
       </c>
-      <c r="U350" s="45" t="s">
+      <c r="V350" s="45" t="s">
         <v>2866</v>
-      </c>
-      <c r="V350" s="45" t="s">
-        <v>2867</v>
       </c>
       <c r="W350" s="111"/>
       <c r="X350" s="118" t="s">
+        <v>2866</v>
+      </c>
+      <c r="Y350" s="30" t="s">
         <v>2867</v>
-      </c>
-      <c r="Y350" s="30" t="s">
-        <v>2868</v>
       </c>
       <c r="Z350" s="102"/>
       <c r="AA350" s="30"/>
       <c r="AB350" s="31"/>
       <c r="AC350" s="21" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="AD350" s="21"/>
       <c r="AE350" s="32"/>
@@ -46433,10 +46433,10 @@
     </row>
     <row r="351" spans="1:43" ht="15.75" customHeight="1">
       <c r="A351" s="458" t="s">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="B351" s="184" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="C351" s="247" t="s">
         <v>171</v>
@@ -46444,11 +46444,11 @@
       <c r="D351" s="232"/>
       <c r="E351" s="58"/>
       <c r="F351" s="265" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="G351" s="32"/>
       <c r="H351" s="190" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="I351" s="190" t="s">
         <v>2498</v>
@@ -46462,7 +46462,7 @@
         <v>2685</v>
       </c>
       <c r="N351" s="38" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="O351" s="294"/>
       <c r="P351" s="124"/>
@@ -46483,11 +46483,11 @@
         <v>2229</v>
       </c>
       <c r="Y351" s="30" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="Z351" s="197"/>
       <c r="AA351" s="30" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="AB351" s="31"/>
       <c r="AC351" s="32"/>
@@ -46508,7 +46508,7 @@
     </row>
     <row r="352" spans="1:43" ht="15.75" customHeight="1">
       <c r="A352" s="458" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="B352" s="33" t="s">
         <v>430</v>
@@ -46519,23 +46519,23 @@
       <c r="D352" s="232"/>
       <c r="E352" s="58"/>
       <c r="F352" s="47" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="G352" s="32"/>
       <c r="H352" s="191" t="s">
+        <v>2877</v>
+      </c>
+      <c r="I352" s="185" t="s">
         <v>2878</v>
-      </c>
-      <c r="I352" s="185" t="s">
-        <v>2879</v>
       </c>
       <c r="J352" s="22"/>
       <c r="K352" s="22"/>
       <c r="L352" s="22"/>
       <c r="M352" s="135" t="s">
+        <v>2879</v>
+      </c>
+      <c r="N352" s="38" t="s">
         <v>2880</v>
-      </c>
-      <c r="N352" s="38" t="s">
-        <v>2881</v>
       </c>
       <c r="O352" s="38"/>
       <c r="P352" s="74" t="s">
@@ -46564,7 +46564,7 @@
         <v>2229</v>
       </c>
       <c r="Y352" s="30" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="Z352" s="30"/>
       <c r="AA352" s="30"/>
@@ -46589,7 +46589,7 @@
     </row>
     <row r="353" spans="1:43" ht="15.75" customHeight="1">
       <c r="A353" s="458" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="B353" s="33" t="s">
         <v>430</v>
@@ -46600,17 +46600,17 @@
       <c r="D353" s="232"/>
       <c r="E353" s="58"/>
       <c r="F353" s="47" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="G353" s="32"/>
       <c r="H353" s="203" t="s">
+        <v>2884</v>
+      </c>
+      <c r="I353" s="185" t="s">
         <v>2885</v>
       </c>
-      <c r="I353" s="185" t="s">
+      <c r="J353" s="82" t="s">
         <v>2886</v>
-      </c>
-      <c r="J353" s="82" t="s">
-        <v>2887</v>
       </c>
       <c r="K353" s="82"/>
       <c r="L353" s="22"/>
@@ -46618,7 +46618,7 @@
         <v>137</v>
       </c>
       <c r="N353" s="89" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="O353" s="393"/>
       <c r="P353" s="70"/>
@@ -46639,7 +46639,7 @@
         <v>2229</v>
       </c>
       <c r="Y353" s="30" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="Z353" s="102"/>
       <c r="AA353" s="30"/>
@@ -46662,7 +46662,7 @@
     </row>
     <row r="354" spans="1:43" ht="15.75" customHeight="1">
       <c r="A354" s="458" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="B354" s="33" t="s">
         <v>430</v>
@@ -46673,11 +46673,11 @@
       <c r="D354" s="232"/>
       <c r="E354" s="58"/>
       <c r="F354" s="47" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="G354" s="32"/>
       <c r="H354" s="203" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="I354" s="190" t="s">
         <v>2498</v>
@@ -46691,14 +46691,14 @@
         <v>1097</v>
       </c>
       <c r="N354" s="38" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="O354" s="38" t="s">
         <v>2104</v>
       </c>
       <c r="P354" s="74"/>
       <c r="Q354" s="26" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="R354" s="115" t="s">
         <v>539</v>
@@ -46714,14 +46714,14 @@
         <v>2229</v>
       </c>
       <c r="Y354" s="168" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="Z354" s="197"/>
       <c r="AA354" s="30" t="s">
+        <v>2895</v>
+      </c>
+      <c r="AB354" s="46" t="s">
         <v>2896</v>
-      </c>
-      <c r="AB354" s="46" t="s">
-        <v>2897</v>
       </c>
       <c r="AC354" s="32"/>
       <c r="AD354" s="21"/>
@@ -46741,22 +46741,22 @@
     </row>
     <row r="355" spans="1:43" ht="135" customHeight="1">
       <c r="A355" s="458" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="B355" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C355" s="247" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="D355" s="232"/>
       <c r="E355" s="58"/>
       <c r="F355" s="47" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="G355" s="32"/>
       <c r="H355" s="203" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="I355" s="190" t="s">
         <v>2498</v>
@@ -46770,14 +46770,14 @@
         <v>1612</v>
       </c>
       <c r="N355" s="54" t="s">
+        <v>2900</v>
+      </c>
+      <c r="O355" s="54" t="s">
         <v>2901</v>
-      </c>
-      <c r="O355" s="54" t="s">
-        <v>2902</v>
       </c>
       <c r="P355" s="55"/>
       <c r="Q355" s="56" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="R355" s="32" t="s">
         <v>519</v>
@@ -46798,10 +46798,10 @@
         <v>2799</v>
       </c>
       <c r="Z355" s="30" t="s">
+        <v>2903</v>
+      </c>
+      <c r="AA355" s="30" t="s">
         <v>2904</v>
-      </c>
-      <c r="AA355" s="30" t="s">
-        <v>2905</v>
       </c>
       <c r="AB355" s="41"/>
       <c r="AC355" s="32"/>
@@ -46822,7 +46822,7 @@
     </row>
     <row r="356" spans="1:43" ht="15.75" customHeight="1">
       <c r="A356" s="458" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="B356" s="33" t="s">
         <v>430</v>
@@ -46833,11 +46833,11 @@
       <c r="D356" s="232"/>
       <c r="E356" s="58"/>
       <c r="F356" s="47" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="G356" s="32"/>
       <c r="H356" s="203" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="I356" s="190" t="s">
         <v>2498</v>
@@ -46849,14 +46849,14 @@
         <v>798</v>
       </c>
       <c r="N356" s="54" t="s">
+        <v>2908</v>
+      </c>
+      <c r="O356" s="54" t="s">
         <v>2909</v>
-      </c>
-      <c r="O356" s="54" t="s">
-        <v>2910</v>
       </c>
       <c r="P356" s="55"/>
       <c r="Q356" s="56" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="R356" s="32" t="s">
         <v>519</v>
@@ -46865,7 +46865,7 @@
         <v>41</v>
       </c>
       <c r="T356" s="21" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="U356" s="28"/>
       <c r="V356" s="28"/>
@@ -46876,13 +46876,13 @@
         <v>2229</v>
       </c>
       <c r="Y356" s="30" t="s">
+        <v>2912</v>
+      </c>
+      <c r="Z356" s="30" t="s">
         <v>2913</v>
       </c>
-      <c r="Z356" s="30" t="s">
+      <c r="AA356" s="30" t="s">
         <v>2914</v>
-      </c>
-      <c r="AA356" s="30" t="s">
-        <v>2915</v>
       </c>
       <c r="AB356" s="41"/>
       <c r="AC356" s="32"/>
@@ -46903,22 +46903,22 @@
     </row>
     <row r="357" spans="1:43" ht="15.75" customHeight="1">
       <c r="A357" s="458" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="B357" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C357" s="246" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="D357" s="232"/>
       <c r="E357" s="58"/>
       <c r="F357" s="47" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="G357" s="32"/>
       <c r="H357" s="32" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="I357" s="190" t="s">
         <v>2498</v>
@@ -46932,7 +46932,7 @@
         <v>537</v>
       </c>
       <c r="N357" s="54" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="O357" s="54"/>
       <c r="P357" s="55"/>
@@ -46957,10 +46957,10 @@
       </c>
       <c r="Z357" s="30"/>
       <c r="AA357" s="30" t="s">
+        <v>2920</v>
+      </c>
+      <c r="AB357" s="41" t="s">
         <v>2921</v>
-      </c>
-      <c r="AB357" s="41" t="s">
-        <v>2922</v>
       </c>
       <c r="AC357" s="32"/>
       <c r="AD357" s="21"/>
@@ -46980,10 +46980,10 @@
     </row>
     <row r="358" spans="1:43" ht="15.75" customHeight="1">
       <c r="A358" s="458" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B358" s="184" t="s">
         <v>2923</v>
-      </c>
-      <c r="B358" s="184" t="s">
-        <v>2924</v>
       </c>
       <c r="C358" s="247" t="s">
         <v>171</v>
@@ -46991,11 +46991,11 @@
       <c r="D358" s="232"/>
       <c r="E358" s="58"/>
       <c r="F358" s="47" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="G358" s="32"/>
       <c r="H358" s="203" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="I358" s="190" t="s">
         <v>2498</v>
@@ -47004,10 +47004,10 @@
       <c r="K358" s="93"/>
       <c r="L358" s="93"/>
       <c r="M358" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="N358" s="65" t="s">
         <v>2927</v>
-      </c>
-      <c r="N358" s="65" t="s">
-        <v>2928</v>
       </c>
       <c r="O358" s="65"/>
       <c r="P358" s="55"/>
@@ -47028,14 +47028,14 @@
         <v>2229</v>
       </c>
       <c r="Y358" s="207" t="s">
+        <v>2928</v>
+      </c>
+      <c r="Z358" s="208" t="s">
         <v>2929</v>
-      </c>
-      <c r="Z358" s="208" t="s">
-        <v>2930</v>
       </c>
       <c r="AA358" s="208"/>
       <c r="AB358" s="31" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="AC358" s="32"/>
       <c r="AD358" s="21"/>
@@ -47055,38 +47055,38 @@
     </row>
     <row r="359" spans="1:43" ht="15.75" customHeight="1">
       <c r="A359" s="458" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B359" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C359" s="246" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="D359" s="232"/>
       <c r="E359" s="58"/>
       <c r="F359" s="47" t="s">
+        <v>2933</v>
+      </c>
+      <c r="G359" s="32" t="s">
         <v>2934</v>
       </c>
-      <c r="G359" s="32" t="s">
+      <c r="H359" s="95" t="s">
         <v>2935</v>
-      </c>
-      <c r="H359" s="95" t="s">
-        <v>2936</v>
       </c>
       <c r="I359" s="185" t="s">
         <v>2630</v>
       </c>
       <c r="J359" s="22" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="K359" s="22"/>
       <c r="L359" s="22"/>
       <c r="M359" s="135" t="s">
+        <v>2937</v>
+      </c>
+      <c r="N359" s="134" t="s">
         <v>2938</v>
-      </c>
-      <c r="N359" s="134" t="s">
-        <v>2939</v>
       </c>
       <c r="O359" s="54"/>
       <c r="P359" s="55"/>
@@ -47098,7 +47098,7 @@
         <v>41</v>
       </c>
       <c r="T359" s="21" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="U359" s="28"/>
       <c r="V359" s="28"/>
@@ -47132,7 +47132,7 @@
     </row>
     <row r="360" spans="1:43" ht="15.75" customHeight="1">
       <c r="A360" s="458" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="B360" s="33" t="s">
         <v>430</v>
@@ -47143,11 +47143,11 @@
       <c r="D360" s="232"/>
       <c r="E360" s="58"/>
       <c r="F360" s="47" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="G360" s="32"/>
       <c r="H360" s="48" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="I360" s="185" t="s">
         <v>2498</v>
@@ -47156,17 +47156,17 @@
       <c r="K360" s="22"/>
       <c r="L360" s="22"/>
       <c r="M360" s="135" t="s">
+        <v>2943</v>
+      </c>
+      <c r="N360" s="54" t="s">
         <v>2944</v>
-      </c>
-      <c r="N360" s="54" t="s">
-        <v>2945</v>
       </c>
       <c r="O360" s="54" t="s">
         <v>1861</v>
       </c>
       <c r="P360" s="55"/>
       <c r="Q360" s="56" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="R360" s="32" t="s">
         <v>519</v>
@@ -47184,13 +47184,13 @@
         <v>2229</v>
       </c>
       <c r="Y360" s="30" t="s">
+        <v>2946</v>
+      </c>
+      <c r="Z360" s="30" t="s">
         <v>2947</v>
       </c>
-      <c r="Z360" s="30" t="s">
+      <c r="AA360" s="30" t="s">
         <v>2948</v>
-      </c>
-      <c r="AA360" s="30" t="s">
-        <v>2949</v>
       </c>
       <c r="AB360" s="108"/>
       <c r="AC360" s="32"/>
@@ -47211,7 +47211,7 @@
     </row>
     <row r="361" spans="1:43" ht="15.75" customHeight="1">
       <c r="A361" s="458" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="B361" s="33" t="s">
         <v>430</v>
@@ -47225,22 +47225,22 @@
         <v>2276</v>
       </c>
       <c r="G361" s="184" t="s">
+        <v>2950</v>
+      </c>
+      <c r="H361" s="48" t="s">
         <v>2951</v>
       </c>
-      <c r="H361" s="48" t="s">
+      <c r="I361" s="185" t="s">
         <v>2952</v>
-      </c>
-      <c r="I361" s="185" t="s">
-        <v>2953</v>
       </c>
       <c r="J361" s="22"/>
       <c r="K361" s="22"/>
       <c r="L361" s="22"/>
       <c r="M361" s="135" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="N361" s="54" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="O361" s="54"/>
       <c r="P361" s="25" t="s">
@@ -47256,7 +47256,7 @@
         <v>41</v>
       </c>
       <c r="T361" s="21" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="U361" s="28"/>
       <c r="V361" s="28"/>
@@ -47267,7 +47267,7 @@
       <c r="AA361" s="30"/>
       <c r="AB361" s="108"/>
       <c r="AC361" s="32" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="AD361" s="21"/>
       <c r="AE361" s="32"/>
@@ -47286,7 +47286,7 @@
     </row>
     <row r="362" spans="1:43" ht="15.75" customHeight="1">
       <c r="A362" s="458" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="B362" s="33" t="s">
         <v>430</v>
@@ -47297,13 +47297,13 @@
       <c r="D362" s="232"/>
       <c r="E362" s="58"/>
       <c r="F362" s="16" t="s">
+        <v>2957</v>
+      </c>
+      <c r="G362" s="48" t="s">
         <v>2958</v>
       </c>
-      <c r="G362" s="48" t="s">
+      <c r="H362" s="203" t="s">
         <v>2959</v>
-      </c>
-      <c r="H362" s="203" t="s">
-        <v>2960</v>
       </c>
       <c r="I362" s="32" t="s">
         <v>2538</v>
@@ -47312,10 +47312,10 @@
       <c r="K362" s="82"/>
       <c r="L362" s="82"/>
       <c r="M362" s="95" t="s">
+        <v>2960</v>
+      </c>
+      <c r="N362" s="54" t="s">
         <v>2961</v>
-      </c>
-      <c r="N362" s="54" t="s">
-        <v>2962</v>
       </c>
       <c r="O362" s="54"/>
       <c r="P362" s="25" t="s">
@@ -47325,7 +47325,7 @@
         <v>1897</v>
       </c>
       <c r="R362" s="77" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="S362" s="77" t="s">
         <v>41</v>
@@ -47340,7 +47340,7 @@
       <c r="W362" s="111"/>
       <c r="X362" s="111"/>
       <c r="Y362" s="30" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="Z362" s="30"/>
       <c r="AA362" s="30"/>
@@ -47349,7 +47349,7 @@
         <v>1899</v>
       </c>
       <c r="AD362" s="144" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="AE362" s="32"/>
       <c r="AF362" s="32"/>
@@ -47367,7 +47367,7 @@
     </row>
     <row r="363" spans="1:43" ht="15.75" customHeight="1">
       <c r="A363" s="458" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="B363" s="33" t="s">
         <v>430</v>
@@ -47378,11 +47378,11 @@
       <c r="D363" s="232"/>
       <c r="E363" s="58"/>
       <c r="F363" s="47" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="G363" s="48"/>
       <c r="H363" s="48" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="I363" s="32" t="s">
         <v>2538</v>
@@ -47394,7 +47394,7 @@
         <v>487</v>
       </c>
       <c r="N363" s="54" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="O363" s="54"/>
       <c r="P363" s="25" t="s">
@@ -47419,7 +47419,7 @@
       <c r="W363" s="111"/>
       <c r="X363" s="111"/>
       <c r="Y363" s="30" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="Z363" s="30"/>
       <c r="AA363" s="30"/>
@@ -47444,7 +47444,7 @@
     </row>
     <row r="364" spans="1:43" ht="15.75" customHeight="1">
       <c r="A364" s="458" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="B364" s="33" t="s">
         <v>430</v>
@@ -47455,21 +47455,21 @@
       <c r="D364" s="232"/>
       <c r="E364" s="58"/>
       <c r="F364" s="16" t="s">
+        <v>2970</v>
+      </c>
+      <c r="G364" s="48" t="s">
         <v>2971</v>
       </c>
-      <c r="G364" s="48" t="s">
+      <c r="H364" s="203" t="s">
         <v>2972</v>
       </c>
-      <c r="H364" s="203" t="s">
+      <c r="I364" s="32" t="s">
         <v>2973</v>
-      </c>
-      <c r="I364" s="32" t="s">
-        <v>2974</v>
       </c>
       <c r="J364" s="22"/>
       <c r="K364" s="22"/>
       <c r="L364" s="22" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="M364" s="181" t="s">
         <v>2073</v>
@@ -47511,7 +47511,7 @@
     </row>
     <row r="365" spans="1:43" ht="15.75" customHeight="1">
       <c r="A365" s="458" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="B365" s="33" t="s">
         <v>430</v>
@@ -47522,11 +47522,11 @@
       <c r="D365" s="232"/>
       <c r="E365" s="58"/>
       <c r="F365" s="47" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="G365" s="32"/>
       <c r="H365" s="203" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="I365" s="32" t="s">
         <v>2498</v>
@@ -47538,7 +47538,7 @@
         <v>595</v>
       </c>
       <c r="N365" s="38" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="O365" s="38" t="s">
         <v>38</v>
@@ -47563,14 +47563,14 @@
         <v>2229</v>
       </c>
       <c r="Y365" s="195" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="Z365" s="418"/>
       <c r="AA365" s="195" t="s">
+        <v>2980</v>
+      </c>
+      <c r="AB365" s="31" t="s">
         <v>2981</v>
-      </c>
-      <c r="AB365" s="31" t="s">
-        <v>2982</v>
       </c>
       <c r="AC365" s="32"/>
       <c r="AD365" s="21"/>
@@ -47590,22 +47590,22 @@
     </row>
     <row r="366" spans="1:43" ht="15.75" customHeight="1">
       <c r="A366" s="458" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="B366" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C366" s="246" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="D366" s="232"/>
       <c r="E366" s="58"/>
       <c r="F366" s="47" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="G366" s="32"/>
       <c r="H366" s="203" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="I366" s="190" t="s">
         <v>2498</v>
@@ -47619,7 +47619,7 @@
         <v>537</v>
       </c>
       <c r="N366" s="38" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="O366" s="38"/>
       <c r="P366" s="25"/>
@@ -47640,11 +47640,11 @@
         <v>2229</v>
       </c>
       <c r="Y366" s="30" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="Z366" s="197"/>
       <c r="AA366" s="30" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="AB366" s="41"/>
       <c r="AC366" s="32"/>
@@ -47665,7 +47665,7 @@
     </row>
     <row r="367" spans="1:43" ht="15.75" customHeight="1">
       <c r="A367" s="458" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="B367" s="33" t="s">
         <v>430</v>
@@ -47676,11 +47676,11 @@
       <c r="D367" s="232"/>
       <c r="E367" s="58"/>
       <c r="F367" s="47" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="G367" s="39"/>
       <c r="H367" s="203" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="I367" s="190" t="s">
         <v>2498</v>
@@ -47688,20 +47688,20 @@
       <c r="J367" s="22"/>
       <c r="K367" s="22"/>
       <c r="L367" s="22" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="M367" s="135" t="s">
         <v>651</v>
       </c>
       <c r="N367" s="38" t="s">
+        <v>2992</v>
+      </c>
+      <c r="O367" s="38" t="s">
         <v>2993</v>
-      </c>
-      <c r="O367" s="38" t="s">
-        <v>2994</v>
       </c>
       <c r="P367" s="25"/>
       <c r="Q367" s="26" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="R367" s="39" t="s">
         <v>519</v>
@@ -47719,13 +47719,13 @@
         <v>2229</v>
       </c>
       <c r="Y367" s="30" t="s">
+        <v>2995</v>
+      </c>
+      <c r="Z367" s="30" t="s">
         <v>2996</v>
       </c>
-      <c r="Z367" s="30" t="s">
+      <c r="AA367" s="30" t="s">
         <v>2997</v>
-      </c>
-      <c r="AA367" s="30" t="s">
-        <v>2998</v>
       </c>
       <c r="AB367" s="41"/>
       <c r="AC367" s="32"/>
@@ -47746,7 +47746,7 @@
     </row>
     <row r="368" spans="1:43" ht="15.75" customHeight="1">
       <c r="A368" s="458" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B368" s="33" t="s">
         <v>430</v>
@@ -47757,11 +47757,11 @@
       <c r="D368" s="232"/>
       <c r="E368" s="58"/>
       <c r="F368" s="47" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="G368" s="39"/>
       <c r="H368" s="203" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="I368" s="190" t="s">
         <v>2498</v>
@@ -47770,17 +47770,17 @@
       <c r="K368" s="22"/>
       <c r="L368" s="22"/>
       <c r="M368" s="135" t="s">
+        <v>3001</v>
+      </c>
+      <c r="N368" s="38" t="s">
         <v>3002</v>
       </c>
-      <c r="N368" s="38" t="s">
+      <c r="O368" s="38" t="s">
         <v>3003</v>
-      </c>
-      <c r="O368" s="38" t="s">
-        <v>3004</v>
       </c>
       <c r="P368" s="25"/>
       <c r="Q368" s="26" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="R368" s="39" t="s">
         <v>519</v>
@@ -47798,13 +47798,13 @@
         <v>2229</v>
       </c>
       <c r="Y368" s="168" t="s">
+        <v>3005</v>
+      </c>
+      <c r="Z368" s="30" t="s">
         <v>3006</v>
       </c>
-      <c r="Z368" s="30" t="s">
+      <c r="AA368" s="30" t="s">
         <v>3007</v>
-      </c>
-      <c r="AA368" s="30" t="s">
-        <v>3008</v>
       </c>
       <c r="AB368" s="41"/>
       <c r="AC368" s="32"/>
@@ -47825,22 +47825,22 @@
     </row>
     <row r="369" spans="1:43" ht="15.75" customHeight="1">
       <c r="A369" s="458" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B369" s="332" t="s">
         <v>430</v>
       </c>
       <c r="C369" s="262" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="D369" s="333"/>
       <c r="E369" s="334"/>
       <c r="F369" s="335" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="G369" s="336"/>
       <c r="H369" s="351" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="I369" s="337" t="s">
         <v>2498</v>
@@ -47849,10 +47849,10 @@
       <c r="K369" s="339"/>
       <c r="L369" s="338"/>
       <c r="M369" s="340" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="N369" s="341" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="O369" s="341" t="s">
         <v>38</v>
@@ -47871,25 +47871,25 @@
       <c r="U369" s="352"/>
       <c r="V369" s="346"/>
       <c r="W369" s="347" t="s">
+        <v>3012</v>
+      </c>
+      <c r="X369" s="347" t="s">
         <v>3013</v>
       </c>
-      <c r="X369" s="347" t="s">
+      <c r="Y369" s="348" t="s">
         <v>3014</v>
       </c>
-      <c r="Y369" s="348" t="s">
+      <c r="Z369" s="421" t="s">
         <v>3015</v>
       </c>
-      <c r="Z369" s="421" t="s">
+      <c r="AA369" s="348" t="s">
         <v>3016</v>
       </c>
-      <c r="AA369" s="348" t="s">
-        <v>3017</v>
-      </c>
       <c r="AB369" s="349" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="AC369" s="353" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="AD369" s="345"/>
       <c r="AE369" s="32"/>
@@ -47908,22 +47908,22 @@
     </row>
     <row r="370" spans="1:43" ht="15.75" customHeight="1">
       <c r="A370" s="458" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B370" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C370" s="246" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="D370" s="232"/>
       <c r="E370" s="58"/>
       <c r="F370" s="47" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="G370" s="39"/>
       <c r="H370" s="203" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="I370" s="32" t="s">
         <v>2498</v>
@@ -47935,7 +47935,7 @@
         <v>798</v>
       </c>
       <c r="N370" s="54" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="O370" s="38" t="s">
         <v>38</v>
@@ -47960,15 +47960,15 @@
         <v>2229</v>
       </c>
       <c r="Y370" s="195" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="Z370" s="197"/>
       <c r="AA370" s="331" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="AB370" s="424"/>
       <c r="AC370" s="16" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="AD370" s="21"/>
       <c r="AE370" s="32"/>
@@ -47987,42 +47987,42 @@
     </row>
     <row r="371" spans="1:43" ht="15.75" customHeight="1">
       <c r="A371" s="458" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="B371" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C371" s="246" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D371" s="231" t="s">
+        <v>3018</v>
+      </c>
+      <c r="E371" s="58" t="s">
         <v>3027</v>
       </c>
-      <c r="D371" s="231" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E371" s="58" t="s">
+      <c r="F371" s="47" t="s">
         <v>3028</v>
       </c>
-      <c r="F371" s="47" t="s">
+      <c r="G371" s="32" t="s">
         <v>3029</v>
       </c>
-      <c r="G371" s="32" t="s">
+      <c r="H371" s="48" t="s">
         <v>3030</v>
       </c>
-      <c r="H371" s="48" t="s">
+      <c r="I371" s="185" t="s">
         <v>3031</v>
       </c>
-      <c r="I371" s="185" t="s">
-        <v>3032</v>
-      </c>
       <c r="J371" s="22" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="K371" s="22"/>
       <c r="L371" s="22"/>
       <c r="M371" s="135" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="N371" s="134" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="O371" s="54"/>
       <c r="P371" s="55"/>
@@ -48066,22 +48066,22 @@
     </row>
     <row r="372" spans="1:43" ht="15.75" customHeight="1">
       <c r="A372" s="458" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B372" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C372" s="246" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="D372" s="232"/>
       <c r="E372" s="58"/>
       <c r="F372" s="16" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="G372" s="39"/>
       <c r="H372" s="203" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="I372" s="190" t="s">
         <v>2498</v>
@@ -48089,13 +48089,13 @@
       <c r="J372" s="82"/>
       <c r="K372" s="82"/>
       <c r="L372" s="82" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="M372" s="209" t="s">
         <v>537</v>
       </c>
       <c r="N372" s="54" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="O372" s="54"/>
       <c r="P372" s="55"/>
@@ -48116,13 +48116,13 @@
         <v>2229</v>
       </c>
       <c r="Y372" s="30" t="s">
+        <v>3039</v>
+      </c>
+      <c r="Z372" s="30" t="s">
         <v>3040</v>
       </c>
-      <c r="Z372" s="30" t="s">
+      <c r="AA372" s="30" t="s">
         <v>3041</v>
-      </c>
-      <c r="AA372" s="30" t="s">
-        <v>3042</v>
       </c>
       <c r="AB372" s="108"/>
       <c r="AC372" s="32"/>
@@ -48143,7 +48143,7 @@
     </row>
     <row r="373" spans="1:43" ht="15.75" customHeight="1">
       <c r="A373" s="458" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="B373" s="33" t="s">
         <v>430</v>
@@ -48154,19 +48154,19 @@
       <c r="D373" s="232"/>
       <c r="E373" s="58"/>
       <c r="F373" s="47" t="s">
+        <v>3043</v>
+      </c>
+      <c r="G373" s="32" t="s">
         <v>3044</v>
       </c>
-      <c r="G373" s="32" t="s">
+      <c r="H373" s="203" t="s">
         <v>3045</v>
       </c>
-      <c r="H373" s="203" t="s">
+      <c r="I373" s="32" t="s">
         <v>3046</v>
       </c>
-      <c r="I373" s="32" t="s">
+      <c r="J373" s="103" t="s">
         <v>3047</v>
-      </c>
-      <c r="J373" s="103" t="s">
-        <v>3048</v>
       </c>
       <c r="K373" s="103"/>
       <c r="L373" s="103"/>
@@ -48174,7 +48174,7 @@
         <v>137</v>
       </c>
       <c r="N373" s="54" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="O373" s="54"/>
       <c r="P373" s="55"/>
@@ -48218,22 +48218,22 @@
     </row>
     <row r="374" spans="1:43" ht="15.75" customHeight="1">
       <c r="A374" s="458" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="B374" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C374" s="246" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="D374" s="232"/>
       <c r="E374" s="58"/>
       <c r="F374" s="47" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="G374" s="39"/>
       <c r="H374" s="203" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="I374" s="190" t="s">
         <v>2498</v>
@@ -48247,14 +48247,14 @@
         <v>893</v>
       </c>
       <c r="N374" s="54" t="s">
+        <v>3053</v>
+      </c>
+      <c r="O374" s="54" t="s">
         <v>3054</v>
-      </c>
-      <c r="O374" s="54" t="s">
-        <v>3055</v>
       </c>
       <c r="P374" s="55"/>
       <c r="Q374" s="56" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="R374" s="39" t="s">
         <v>519</v>
@@ -48272,13 +48272,13 @@
         <v>2229</v>
       </c>
       <c r="Y374" s="30" t="s">
+        <v>3056</v>
+      </c>
+      <c r="Z374" s="102" t="s">
         <v>3057</v>
       </c>
-      <c r="Z374" s="102" t="s">
+      <c r="AA374" s="30" t="s">
         <v>3058</v>
-      </c>
-      <c r="AA374" s="30" t="s">
-        <v>3059</v>
       </c>
       <c r="AB374" s="41"/>
       <c r="AC374" s="32"/>
@@ -48299,36 +48299,36 @@
     </row>
     <row r="375" spans="1:43" ht="15.75" customHeight="1">
       <c r="A375" s="458" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B375" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C375" s="246" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="D375" s="232"/>
       <c r="E375" s="58"/>
       <c r="F375" s="16" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="G375" s="32"/>
       <c r="H375" s="203" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="I375" s="190" t="s">
         <v>2498</v>
       </c>
       <c r="J375" s="82" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="K375" s="82"/>
       <c r="L375" s="82"/>
       <c r="M375" s="113" t="s">
+        <v>3064</v>
+      </c>
+      <c r="N375" s="54" t="s">
         <v>3065</v>
-      </c>
-      <c r="N375" s="54" t="s">
-        <v>3066</v>
       </c>
       <c r="O375" s="294" t="s">
         <v>38</v>
@@ -48353,15 +48353,15 @@
         <v>2229</v>
       </c>
       <c r="Y375" s="419" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="Z375" s="418"/>
       <c r="AA375" s="30" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="AB375" s="41"/>
       <c r="AC375" s="66" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="AD375" s="21"/>
       <c r="AE375" s="32"/>
@@ -48380,7 +48380,7 @@
     </row>
     <row r="376" spans="1:43" ht="48" customHeight="1">
       <c r="A376" s="461" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="B376" s="33" t="s">
         <v>430</v>
@@ -48390,14 +48390,14 @@
       </c>
       <c r="E376" s="227"/>
       <c r="F376" s="370" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="G376" s="227"/>
       <c r="H376" s="360" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="I376" s="360" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="J376" s="227"/>
       <c r="K376" s="227"/>
@@ -48418,7 +48418,7 @@
         <v>41</v>
       </c>
       <c r="T376" s="360" t="s">
-        <v>3767</v>
+        <v>3766</v>
       </c>
       <c r="U376" s="227"/>
       <c r="V376" s="227"/>
@@ -48430,7 +48430,7 @@
       <c r="AB376" s="227"/>
       <c r="AC376" s="227"/>
       <c r="AD376" s="360" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="AE376" s="227"/>
       <c r="AF376" s="227"/>
@@ -48448,7 +48448,7 @@
     </row>
     <row r="377" spans="1:43" ht="15.75" customHeight="1">
       <c r="A377" s="458" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="B377" s="33" t="s">
         <v>430</v>
@@ -48459,11 +48459,11 @@
       <c r="D377" s="232"/>
       <c r="E377" s="58"/>
       <c r="F377" s="265" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="G377" s="32"/>
       <c r="H377" s="203" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="I377" s="32" t="s">
         <v>2498</v>
@@ -48474,17 +48474,17 @@
         <v>420</v>
       </c>
       <c r="M377" s="135" t="s">
+        <v>3074</v>
+      </c>
+      <c r="N377" s="54" t="s">
         <v>3075</v>
-      </c>
-      <c r="N377" s="54" t="s">
-        <v>3076</v>
       </c>
       <c r="O377" s="54"/>
       <c r="P377" s="74" t="s">
+        <v>3076</v>
+      </c>
+      <c r="Q377" s="56" t="s">
         <v>3077</v>
-      </c>
-      <c r="Q377" s="56" t="s">
-        <v>3078</v>
       </c>
       <c r="R377" s="94" t="s">
         <v>539</v>
@@ -48506,7 +48506,7 @@
       </c>
       <c r="Z377" s="418"/>
       <c r="AA377" s="195" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="AB377" s="108"/>
       <c r="AC377" s="32"/>
@@ -48527,7 +48527,7 @@
     </row>
     <row r="378" spans="1:43" ht="15.75" customHeight="1">
       <c r="A378" s="458" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="B378" s="33" t="s">
         <v>430</v>
@@ -48538,11 +48538,11 @@
       <c r="D378" s="232"/>
       <c r="E378" s="58"/>
       <c r="F378" s="47" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="G378" s="32"/>
       <c r="H378" s="203" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="I378" s="190" t="s">
         <v>2498</v>
@@ -48550,13 +48550,13 @@
       <c r="J378" s="35"/>
       <c r="K378" s="107"/>
       <c r="L378" s="107" t="s">
+        <v>3082</v>
+      </c>
+      <c r="M378" s="135" t="s">
         <v>3083</v>
       </c>
-      <c r="M378" s="135" t="s">
+      <c r="N378" s="38" t="s">
         <v>3084</v>
-      </c>
-      <c r="N378" s="38" t="s">
-        <v>3085</v>
       </c>
       <c r="O378" s="38"/>
       <c r="P378" s="25"/>
@@ -48581,10 +48581,10 @@
       </c>
       <c r="Z378" s="197"/>
       <c r="AA378" s="197" t="s">
+        <v>3085</v>
+      </c>
+      <c r="AB378" s="108" t="s">
         <v>3086</v>
-      </c>
-      <c r="AB378" s="108" t="s">
-        <v>3087</v>
       </c>
       <c r="AC378" s="32"/>
       <c r="AD378" s="21"/>
@@ -48604,7 +48604,7 @@
     </row>
     <row r="379" spans="1:43" ht="15.75" customHeight="1">
       <c r="A379" s="458" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="B379" s="33" t="s">
         <v>430</v>
@@ -48615,11 +48615,11 @@
       <c r="D379" s="232"/>
       <c r="E379" s="58"/>
       <c r="F379" s="47" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="G379" s="32"/>
       <c r="H379" s="203" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="I379" s="190" t="s">
         <v>2498</v>
@@ -48628,17 +48628,17 @@
       <c r="K379" s="82"/>
       <c r="L379" s="82"/>
       <c r="M379" s="135" t="s">
+        <v>3090</v>
+      </c>
+      <c r="N379" s="54" t="s">
         <v>3091</v>
       </c>
-      <c r="N379" s="54" t="s">
+      <c r="O379" s="394" t="s">
         <v>3092</v>
-      </c>
-      <c r="O379" s="394" t="s">
-        <v>3093</v>
       </c>
       <c r="P379" s="112"/>
       <c r="Q379" s="56" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="R379" s="39" t="s">
         <v>519</v>
@@ -48656,13 +48656,13 @@
         <v>2229</v>
       </c>
       <c r="Y379" s="168" t="s">
+        <v>3094</v>
+      </c>
+      <c r="Z379" s="30" t="s">
         <v>3095</v>
       </c>
-      <c r="Z379" s="30" t="s">
+      <c r="AA379" s="30" t="s">
         <v>3096</v>
-      </c>
-      <c r="AA379" s="30" t="s">
-        <v>3097</v>
       </c>
       <c r="AB379" s="108"/>
       <c r="AC379" s="32"/>
@@ -48683,22 +48683,22 @@
     </row>
     <row r="380" spans="1:43" ht="15.75" customHeight="1">
       <c r="A380" s="458" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="B380" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C380" s="246" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="D380" s="232"/>
       <c r="E380" s="58"/>
       <c r="F380" s="16" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="G380" s="32"/>
       <c r="H380" s="203" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="I380" s="190" t="s">
         <v>2498</v>
@@ -48706,22 +48706,22 @@
       <c r="J380" s="82"/>
       <c r="K380" s="82"/>
       <c r="L380" s="82" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="M380" s="135" t="s">
         <v>893</v>
       </c>
       <c r="N380" s="38" t="s">
+        <v>3102</v>
+      </c>
+      <c r="O380" s="38" t="s">
         <v>3103</v>
       </c>
-      <c r="O380" s="38" t="s">
+      <c r="P380" s="74" t="s">
         <v>3104</v>
       </c>
-      <c r="P380" s="74" t="s">
+      <c r="Q380" s="56" t="s">
         <v>3105</v>
-      </c>
-      <c r="Q380" s="56" t="s">
-        <v>3106</v>
       </c>
       <c r="R380" s="39" t="s">
         <v>519</v>
@@ -48739,13 +48739,13 @@
         <v>2229</v>
       </c>
       <c r="Y380" s="168" t="s">
+        <v>3106</v>
+      </c>
+      <c r="Z380" s="102" t="s">
         <v>3107</v>
       </c>
-      <c r="Z380" s="102" t="s">
+      <c r="AA380" s="30" t="s">
         <v>3108</v>
-      </c>
-      <c r="AA380" s="30" t="s">
-        <v>3109</v>
       </c>
       <c r="AB380" s="108"/>
       <c r="AC380" s="32"/>
@@ -48766,7 +48766,7 @@
     </row>
     <row r="381" spans="1:43" s="329" customFormat="1" ht="15.75" customHeight="1">
       <c r="A381" s="458" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="B381" s="33" t="s">
         <v>430</v>
@@ -48777,11 +48777,11 @@
       <c r="D381" s="232"/>
       <c r="E381" s="58"/>
       <c r="F381" s="373" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="G381" s="32"/>
       <c r="H381" s="203" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="I381" s="32" t="s">
         <v>2498</v>
@@ -48789,13 +48789,13 @@
       <c r="J381" s="98"/>
       <c r="K381" s="103"/>
       <c r="L381" s="103" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="M381" s="135" t="s">
         <v>537</v>
       </c>
       <c r="N381" s="54" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="O381" s="54"/>
       <c r="P381" s="55"/>
@@ -48820,11 +48820,11 @@
       </c>
       <c r="Z381" s="422"/>
       <c r="AA381" s="211" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="AB381" s="108"/>
       <c r="AC381" s="47" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="AD381" s="21"/>
       <c r="AE381" s="328"/>
@@ -48843,22 +48843,22 @@
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
       <c r="A383" s="458" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C383" s="246" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="D383" s="232"/>
       <c r="E383" s="58"/>
       <c r="F383" s="16" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="G383" s="39"/>
       <c r="H383" s="203" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="I383" s="190" t="s">
         <v>2498</v>
@@ -48867,10 +48867,10 @@
       <c r="K383" s="82"/>
       <c r="L383" s="22"/>
       <c r="M383" s="135" t="s">
+        <v>3119</v>
+      </c>
+      <c r="N383" s="54" t="s">
         <v>3120</v>
-      </c>
-      <c r="N383" s="54" t="s">
-        <v>3121</v>
       </c>
       <c r="O383" s="54" t="s">
         <v>38</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z383" s="30"/>
       <c r="AA383" s="30" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="AB383" s="41"/>
       <c r="AC383" s="32"/>
@@ -48920,13 +48920,13 @@
     </row>
     <row r="384" spans="1:43" ht="15.75" customHeight="1">
       <c r="A384" s="458" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="B384" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C384" s="246" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="D384" s="232"/>
       <c r="E384" s="58"/>
@@ -48938,7 +48938,7 @@
         <v>2610</v>
       </c>
       <c r="I384" s="190" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="J384" s="98"/>
       <c r="K384" s="82"/>
@@ -48949,7 +48949,7 @@
         <v>857</v>
       </c>
       <c r="N384" s="54" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="O384" s="54"/>
       <c r="P384" s="55"/>
@@ -48961,7 +48961,7 @@
         <v>41</v>
       </c>
       <c r="T384" s="21" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="U384" s="28"/>
       <c r="V384" s="28"/>
@@ -48989,13 +48989,13 @@
     </row>
     <row r="385" spans="1:43" ht="15.75" customHeight="1">
       <c r="A385" s="458" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="B385" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C385" s="246" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="D385" s="232"/>
       <c r="E385" s="58"/>
@@ -49004,10 +49004,10 @@
       </c>
       <c r="G385" s="39"/>
       <c r="H385" s="203" t="s">
+        <v>3126</v>
+      </c>
+      <c r="I385" s="190" t="s">
         <v>3127</v>
-      </c>
-      <c r="I385" s="190" t="s">
-        <v>3128</v>
       </c>
       <c r="J385" s="35"/>
       <c r="K385" s="107"/>
@@ -49018,7 +49018,7 @@
         <v>857</v>
       </c>
       <c r="N385" s="54" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="O385" s="54"/>
       <c r="P385" s="55"/>
@@ -49030,7 +49030,7 @@
         <v>41</v>
       </c>
       <c r="T385" s="21" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="U385" s="28"/>
       <c r="V385" s="28"/>
@@ -49058,22 +49058,22 @@
     </row>
     <row r="386" spans="1:43" ht="15.75" customHeight="1">
       <c r="A386" s="458" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="B386" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C386" s="246" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="D386" s="232"/>
       <c r="E386" s="58"/>
       <c r="F386" s="16" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="G386" s="39"/>
       <c r="H386" s="203" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="I386" s="190" t="s">
         <v>2498</v>
@@ -49106,7 +49106,7 @@
       <c r="Y386" s="30"/>
       <c r="Z386" s="30"/>
       <c r="AA386" s="30" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="AB386" s="41"/>
       <c r="AC386" s="32"/>
@@ -49127,22 +49127,22 @@
     </row>
     <row r="387" spans="1:43" ht="15.75" customHeight="1">
       <c r="A387" s="458" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="B387" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C387" s="246" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="D387" s="232"/>
       <c r="E387" s="58"/>
       <c r="F387" s="47" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="G387" s="39"/>
       <c r="H387" s="203" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="I387" s="190" t="s">
         <v>2498</v>
@@ -49153,10 +49153,10 @@
       <c r="K387" s="22"/>
       <c r="L387" s="22"/>
       <c r="M387" s="212" t="s">
+        <v>3138</v>
+      </c>
+      <c r="N387" s="38" t="s">
         <v>3139</v>
-      </c>
-      <c r="N387" s="38" t="s">
-        <v>3140</v>
       </c>
       <c r="O387" s="38"/>
       <c r="P387" s="55"/>
@@ -49171,17 +49171,17 @@
       <c r="U387" s="28"/>
       <c r="V387" s="28"/>
       <c r="W387" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X387" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X387" s="29" t="s">
+      <c r="Y387" s="30" t="s">
         <v>3142</v>
-      </c>
-      <c r="Y387" s="30" t="s">
-        <v>3143</v>
       </c>
       <c r="Z387" s="30"/>
       <c r="AA387" s="30" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="AB387" s="41"/>
       <c r="AC387" s="32"/>
@@ -49202,22 +49202,22 @@
     </row>
     <row r="388" spans="1:43" ht="15.75" customHeight="1">
       <c r="A388" s="458" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
       <c r="B388" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C388" s="257" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="D388" s="232"/>
       <c r="E388" s="58"/>
       <c r="F388" s="47" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="G388" s="32"/>
       <c r="H388" s="48" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="I388" s="32" t="s">
         <v>2498</v>
@@ -49225,13 +49225,13 @@
       <c r="J388" s="103"/>
       <c r="K388" s="103"/>
       <c r="L388" s="103" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="M388" s="135" t="s">
         <v>651</v>
       </c>
       <c r="N388" s="54" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="O388" s="54"/>
       <c r="P388" s="55"/>
@@ -49243,25 +49243,25 @@
         <v>41</v>
       </c>
       <c r="T388" s="21" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="U388" s="28"/>
       <c r="V388" s="28"/>
       <c r="W388" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X388" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X388" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y388" s="30" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="Z388" s="30"/>
       <c r="AA388" s="30" t="s">
+        <v>3151</v>
+      </c>
+      <c r="AB388" s="46" t="s">
         <v>3152</v>
-      </c>
-      <c r="AB388" s="46" t="s">
-        <v>3153</v>
       </c>
       <c r="AC388" s="32"/>
       <c r="AD388" s="21"/>
@@ -49281,29 +49281,29 @@
     </row>
     <row r="389" spans="1:43" ht="45.75" customHeight="1">
       <c r="A389" s="461" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="B389" s="358" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="C389" s="259" t="s">
         <v>171</v>
       </c>
       <c r="E389" s="227"/>
       <c r="F389" s="370" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="G389" s="227"/>
       <c r="H389" s="376" t="s">
-        <v>3771</v>
+        <v>3770</v>
       </c>
       <c r="I389" s="376" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="J389" s="227"/>
       <c r="K389" s="227"/>
       <c r="L389" s="227" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="M389" s="386" t="s">
         <v>2073</v>
@@ -49321,7 +49321,7 @@
         <v>41</v>
       </c>
       <c r="T389" s="360" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="U389" s="227"/>
       <c r="V389" s="227"/>
@@ -49333,7 +49333,7 @@
       <c r="AB389" s="227"/>
       <c r="AC389" s="227"/>
       <c r="AD389" s="360" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="AE389" s="227"/>
       <c r="AF389" s="227"/>
@@ -49351,7 +49351,7 @@
     </row>
     <row r="390" spans="1:43" ht="15.75" customHeight="1">
       <c r="A390" s="458" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B390" s="33" t="s">
         <v>430</v>
@@ -49362,25 +49362,25 @@
       <c r="D390" s="232"/>
       <c r="E390" s="58"/>
       <c r="F390" s="265" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="G390" s="32"/>
       <c r="H390" s="48" t="s">
+        <v>3157</v>
+      </c>
+      <c r="I390" s="185" t="s">
         <v>3158</v>
       </c>
-      <c r="I390" s="185" t="s">
+      <c r="J390" s="82" t="s">
         <v>3159</v>
-      </c>
-      <c r="J390" s="82" t="s">
-        <v>3160</v>
       </c>
       <c r="K390" s="82"/>
       <c r="L390" s="22"/>
       <c r="M390" s="209" t="s">
+        <v>3160</v>
+      </c>
+      <c r="N390" s="54" t="s">
         <v>3161</v>
-      </c>
-      <c r="N390" s="54" t="s">
-        <v>3162</v>
       </c>
       <c r="O390" s="394"/>
       <c r="P390" s="112"/>
@@ -49395,13 +49395,13 @@
       <c r="U390" s="28"/>
       <c r="V390" s="28"/>
       <c r="W390" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X390" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X390" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y390" s="30" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="Z390" s="30"/>
       <c r="AA390" s="30"/>
@@ -49424,7 +49424,7 @@
     </row>
     <row r="391" spans="1:43" ht="15.75" customHeight="1">
       <c r="A391" s="458" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B391" s="33" t="s">
         <v>430</v>
@@ -49435,11 +49435,11 @@
       <c r="D391" s="232"/>
       <c r="E391" s="58"/>
       <c r="F391" s="16" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="G391" s="32"/>
       <c r="H391" s="190" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="I391" s="32" t="s">
         <v>2538</v>
@@ -49447,20 +49447,20 @@
       <c r="J391" s="98"/>
       <c r="K391" s="163"/>
       <c r="L391" s="193" t="s">
+        <v>3166</v>
+      </c>
+      <c r="M391" s="135" t="s">
         <v>3167</v>
       </c>
-      <c r="M391" s="135" t="s">
+      <c r="N391" s="134" t="s">
         <v>3168</v>
-      </c>
-      <c r="N391" s="134" t="s">
-        <v>3169</v>
       </c>
       <c r="O391" s="134"/>
       <c r="P391" s="74" t="s">
+        <v>3169</v>
+      </c>
+      <c r="Q391" s="56" t="s">
         <v>3170</v>
-      </c>
-      <c r="Q391" s="56" t="s">
-        <v>3171</v>
       </c>
       <c r="R391" s="305" t="s">
         <v>40</v>
@@ -49478,19 +49478,19 @@
         <v>2621</v>
       </c>
       <c r="W391" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X391" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X391" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y391" s="30" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="Z391" s="30"/>
       <c r="AA391" s="30"/>
       <c r="AB391" s="41"/>
       <c r="AC391" s="32" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="AD391" s="21"/>
       <c r="AE391" s="32"/>
@@ -49509,7 +49509,7 @@
     </row>
     <row r="392" spans="1:43" ht="15.75" customHeight="1">
       <c r="A392" s="458" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B392" s="33" t="s">
         <v>430</v>
@@ -49520,11 +49520,11 @@
       <c r="D392" s="232"/>
       <c r="E392" s="58"/>
       <c r="F392" s="265" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="G392" s="32"/>
       <c r="H392" s="203" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="I392" s="190" t="s">
         <v>2498</v>
@@ -49536,7 +49536,7 @@
         <v>882</v>
       </c>
       <c r="N392" s="54" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="O392" s="54"/>
       <c r="P392" s="55"/>
@@ -49551,19 +49551,19 @@
       <c r="U392" s="28"/>
       <c r="V392" s="28"/>
       <c r="W392" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X392" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X392" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y392" s="30" t="s">
+        <v>3177</v>
+      </c>
+      <c r="Z392" s="30" t="s">
         <v>3178</v>
       </c>
-      <c r="Z392" s="30" t="s">
+      <c r="AA392" s="30" t="s">
         <v>3179</v>
-      </c>
-      <c r="AA392" s="30" t="s">
-        <v>3180</v>
       </c>
       <c r="AB392" s="41"/>
       <c r="AC392" s="32"/>
@@ -49584,7 +49584,7 @@
     </row>
     <row r="393" spans="1:43" ht="15.75" customHeight="1">
       <c r="A393" s="462" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="B393" s="357" t="s">
         <v>430</v>
@@ -49595,11 +49595,11 @@
       <c r="D393" s="308"/>
       <c r="E393" s="136"/>
       <c r="F393" s="369" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="G393" s="32"/>
       <c r="H393" s="375" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="I393" s="39" t="s">
         <v>2498</v>
@@ -49607,13 +49607,13 @@
       <c r="J393" s="82"/>
       <c r="K393" s="82"/>
       <c r="L393" s="82" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="M393" s="135" t="s">
         <v>537</v>
       </c>
       <c r="N393" s="394" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="O393" s="394"/>
       <c r="P393" s="112"/>
@@ -49625,7 +49625,7 @@
         <v>41</v>
       </c>
       <c r="T393" s="104" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="U393" s="411"/>
       <c r="V393" s="411"/>
@@ -49636,11 +49636,11 @@
         <v>2229</v>
       </c>
       <c r="Y393" s="102" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="Z393" s="102"/>
       <c r="AA393" s="102" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="AB393" s="424"/>
       <c r="AC393" s="39"/>
@@ -49661,7 +49661,7 @@
     </row>
     <row r="394" spans="1:43" ht="15.75" customHeight="1">
       <c r="A394" s="458" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="B394" s="33" t="s">
         <v>430</v>
@@ -49672,17 +49672,17 @@
       <c r="D394" s="232"/>
       <c r="E394" s="58"/>
       <c r="F394" s="47" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="G394" s="32"/>
       <c r="H394" s="203" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="I394" s="32" t="s">
         <v>2498</v>
       </c>
       <c r="J394" s="22" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="K394" s="22"/>
       <c r="L394" s="22"/>
@@ -49690,7 +49690,7 @@
         <v>537</v>
       </c>
       <c r="N394" s="54" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="O394" s="54"/>
       <c r="P394" s="55"/>
@@ -49702,22 +49702,22 @@
         <v>41</v>
       </c>
       <c r="T394" s="21" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="U394" s="28"/>
       <c r="V394" s="28"/>
       <c r="W394" s="72" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X394" s="72" t="s">
         <v>3141</v>
       </c>
-      <c r="X394" s="72" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y394" s="195" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="Z394" s="195"/>
       <c r="AA394" s="30" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="AB394" s="41"/>
       <c r="AC394" s="32"/>
@@ -49738,7 +49738,7 @@
     </row>
     <row r="395" spans="1:43" ht="15.75" customHeight="1">
       <c r="A395" s="458" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="B395" s="33" t="s">
         <v>430</v>
@@ -49749,29 +49749,29 @@
       <c r="D395" s="242"/>
       <c r="E395" s="52"/>
       <c r="F395" s="16" t="s">
+        <v>3194</v>
+      </c>
+      <c r="G395" s="48" t="s">
         <v>3195</v>
       </c>
-      <c r="G395" s="48" t="s">
+      <c r="H395" s="48" t="s">
         <v>3196</v>
-      </c>
-      <c r="H395" s="48" t="s">
-        <v>3197</v>
       </c>
       <c r="I395" s="185" t="s">
         <v>2498</v>
       </c>
       <c r="J395" s="82"/>
       <c r="K395" s="82" t="s">
+        <v>3197</v>
+      </c>
+      <c r="L395" s="82" t="s">
         <v>3198</v>
       </c>
-      <c r="L395" s="82" t="s">
+      <c r="M395" s="95" t="s">
+        <v>3941</v>
+      </c>
+      <c r="N395" s="54" t="s">
         <v>3199</v>
-      </c>
-      <c r="M395" s="95" t="s">
-        <v>3942</v>
-      </c>
-      <c r="N395" s="54" t="s">
-        <v>3200</v>
       </c>
       <c r="O395" s="54"/>
       <c r="P395" s="55"/>
@@ -49809,38 +49809,38 @@
     </row>
     <row r="396" spans="1:43" ht="15.75" customHeight="1">
       <c r="A396" s="458" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B396" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C396" s="248" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="D396" s="232"/>
       <c r="E396" s="58"/>
       <c r="F396" s="16" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="G396" s="32"/>
       <c r="H396" s="203" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="I396" s="190" t="s">
         <v>2498</v>
       </c>
       <c r="J396" s="35"/>
       <c r="K396" s="22" t="s">
+        <v>3202</v>
+      </c>
+      <c r="L396" s="22" t="s">
+        <v>3159</v>
+      </c>
+      <c r="M396" s="135" t="s">
         <v>3203</v>
       </c>
-      <c r="L396" s="22" t="s">
-        <v>3160</v>
-      </c>
-      <c r="M396" s="135" t="s">
+      <c r="N396" s="54" t="s">
         <v>3204</v>
-      </c>
-      <c r="N396" s="54" t="s">
-        <v>3205</v>
       </c>
       <c r="O396" s="54"/>
       <c r="P396" s="55"/>
@@ -49855,20 +49855,20 @@
       <c r="U396" s="28"/>
       <c r="V396" s="28"/>
       <c r="W396" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X396" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X396" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y396" s="168" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="Z396" s="102"/>
       <c r="AA396" s="30" t="s">
+        <v>3206</v>
+      </c>
+      <c r="AB396" s="46" t="s">
         <v>3207</v>
-      </c>
-      <c r="AB396" s="46" t="s">
-        <v>3208</v>
       </c>
       <c r="AC396" s="32"/>
       <c r="AD396" s="21"/>
@@ -49888,7 +49888,7 @@
     </row>
     <row r="397" spans="1:43" ht="41.25" customHeight="1">
       <c r="A397" s="458" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="B397" s="33" t="s">
         <v>430</v>
@@ -49899,25 +49899,25 @@
       <c r="D397" s="232"/>
       <c r="E397" s="58"/>
       <c r="F397" s="265" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="G397" s="32"/>
       <c r="H397" s="203" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="I397" s="190" t="s">
         <v>2498</v>
       </c>
       <c r="J397" s="68" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="K397" s="107"/>
       <c r="L397" s="107"/>
       <c r="M397" s="135" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="N397" s="54" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="O397" s="54"/>
       <c r="P397" s="55"/>
@@ -49932,26 +49932,26 @@
       <c r="U397" s="28"/>
       <c r="V397" s="28"/>
       <c r="W397" s="29" t="s">
+        <v>3213</v>
+      </c>
+      <c r="X397" s="29" t="s">
         <v>3214</v>
       </c>
-      <c r="X397" s="29" t="s">
+      <c r="Y397" s="195" t="s">
         <v>3215</v>
-      </c>
-      <c r="Y397" s="195" t="s">
-        <v>3216</v>
       </c>
       <c r="Z397" s="197"/>
       <c r="AA397" s="195" t="s">
+        <v>3216</v>
+      </c>
+      <c r="AB397" s="46" t="s">
         <v>3217</v>
       </c>
-      <c r="AB397" s="46" t="s">
+      <c r="AC397" s="47" t="s">
         <v>3218</v>
       </c>
-      <c r="AC397" s="47" t="s">
+      <c r="AD397" s="21" t="s">
         <v>3219</v>
-      </c>
-      <c r="AD397" s="21" t="s">
-        <v>3220</v>
       </c>
       <c r="AE397" s="32"/>
       <c r="AF397" s="32"/>
@@ -49969,7 +49969,7 @@
     </row>
     <row r="398" spans="1:43" ht="15.75" customHeight="1">
       <c r="A398" s="458" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
       <c r="B398" s="33" t="s">
         <v>430</v>
@@ -49980,11 +49980,11 @@
       <c r="D398" s="232"/>
       <c r="E398" s="58"/>
       <c r="F398" s="265" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="G398" s="32"/>
       <c r="H398" s="266" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="I398" s="190" t="s">
         <v>2498</v>
@@ -49993,10 +49993,10 @@
       <c r="K398" s="22"/>
       <c r="L398" s="22"/>
       <c r="M398" s="135" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="N398" s="54" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="O398" s="54"/>
       <c r="P398" s="213"/>
@@ -50034,7 +50034,7 @@
     </row>
     <row r="399" spans="1:43" ht="15.75" customHeight="1">
       <c r="A399" s="458" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="B399" s="33" t="s">
         <v>430</v>
@@ -50045,25 +50045,25 @@
       <c r="D399" s="232"/>
       <c r="E399" s="58"/>
       <c r="F399" s="265" t="s">
+        <v>3223</v>
+      </c>
+      <c r="G399" s="32" t="s">
         <v>3224</v>
       </c>
-      <c r="G399" s="32" t="s">
+      <c r="H399" s="203" t="s">
         <v>3225</v>
       </c>
-      <c r="H399" s="203" t="s">
+      <c r="I399" s="32" t="s">
         <v>3226</v>
-      </c>
-      <c r="I399" s="32" t="s">
-        <v>3227</v>
       </c>
       <c r="J399" s="22"/>
       <c r="K399" s="22"/>
       <c r="L399" s="22"/>
       <c r="M399" s="209" t="s">
+        <v>3227</v>
+      </c>
+      <c r="N399" s="38" t="s">
         <v>3228</v>
-      </c>
-      <c r="N399" s="38" t="s">
-        <v>3229</v>
       </c>
       <c r="O399" s="38"/>
       <c r="P399" s="124"/>
@@ -50101,7 +50101,7 @@
     </row>
     <row r="400" spans="1:43" ht="15.75" customHeight="1">
       <c r="A400" s="458" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="B400" s="33" t="s">
         <v>430</v>
@@ -50112,32 +50112,32 @@
       <c r="D400" s="232"/>
       <c r="E400" s="58"/>
       <c r="F400" s="265" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="G400" s="32"/>
       <c r="H400" s="203" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="I400" s="190" t="s">
         <v>2498</v>
       </c>
       <c r="J400" s="22"/>
       <c r="K400" s="35" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="L400" s="35"/>
       <c r="M400" s="135" t="s">
+        <v>3232</v>
+      </c>
+      <c r="N400" s="134" t="s">
         <v>3233</v>
-      </c>
-      <c r="N400" s="134" t="s">
-        <v>3234</v>
       </c>
       <c r="O400" s="54" t="s">
         <v>38</v>
       </c>
       <c r="P400" s="55"/>
       <c r="Q400" s="56" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="R400" s="32" t="s">
         <v>539</v>
@@ -50149,18 +50149,18 @@
       <c r="U400" s="28"/>
       <c r="V400" s="28"/>
       <c r="W400" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X400" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X400" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y400" s="30" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="Z400" s="30"/>
       <c r="AA400" s="30"/>
       <c r="AB400" s="31" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="AC400" s="32"/>
       <c r="AD400" s="21"/>
@@ -50180,7 +50180,7 @@
     </row>
     <row r="401" spans="1:43" ht="15.75" customHeight="1">
       <c r="A401" s="458" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="B401" s="33" t="s">
         <v>430</v>
@@ -50191,11 +50191,11 @@
       <c r="D401" s="232"/>
       <c r="E401" s="58"/>
       <c r="F401" s="16" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="G401" s="32"/>
       <c r="H401" s="190" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="I401" s="32" t="s">
         <v>2538</v>
@@ -50206,17 +50206,17 @@
       </c>
       <c r="L401" s="383"/>
       <c r="M401" s="387" t="s">
+        <v>3240</v>
+      </c>
+      <c r="N401" s="38" t="s">
         <v>3241</v>
-      </c>
-      <c r="N401" s="38" t="s">
-        <v>3242</v>
       </c>
       <c r="O401" s="38"/>
       <c r="P401" s="289" t="s">
         <v>38</v>
       </c>
       <c r="Q401" s="291" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="R401" s="296" t="s">
         <v>80</v>
@@ -50228,13 +50228,13 @@
       <c r="U401" s="28"/>
       <c r="V401" s="28"/>
       <c r="W401" s="29" t="s">
+        <v>3242</v>
+      </c>
+      <c r="X401" s="29" t="s">
+        <v>3141</v>
+      </c>
+      <c r="Y401" s="30" t="s">
         <v>3243</v>
-      </c>
-      <c r="X401" s="29" t="s">
-        <v>3142</v>
-      </c>
-      <c r="Y401" s="30" t="s">
-        <v>3244</v>
       </c>
       <c r="Z401" s="30"/>
       <c r="AA401" s="30"/>
@@ -50257,10 +50257,10 @@
     </row>
     <row r="402" spans="1:43" ht="15.75" customHeight="1">
       <c r="A402" s="458" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B402" s="48" t="s">
         <v>3245</v>
-      </c>
-      <c r="B402" s="48" t="s">
-        <v>3246</v>
       </c>
       <c r="C402" s="247" t="s">
         <v>171</v>
@@ -50268,19 +50268,19 @@
       <c r="D402" s="232"/>
       <c r="E402" s="58"/>
       <c r="F402" s="265" t="s">
+        <v>3246</v>
+      </c>
+      <c r="G402" s="48" t="s">
         <v>3247</v>
       </c>
-      <c r="G402" s="48" t="s">
+      <c r="H402" s="203" t="s">
         <v>3248</v>
-      </c>
-      <c r="H402" s="203" t="s">
-        <v>3249</v>
       </c>
       <c r="I402" s="32" t="s">
         <v>2538</v>
       </c>
       <c r="J402" s="22" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="K402" s="22"/>
       <c r="L402" s="22"/>
@@ -50288,7 +50288,7 @@
         <v>137</v>
       </c>
       <c r="N402" s="54" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="O402" s="54"/>
       <c r="P402" s="55"/>
@@ -50303,18 +50303,18 @@
       <c r="U402" s="28"/>
       <c r="V402" s="28"/>
       <c r="W402" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X402" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X402" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y402" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z402" s="30"/>
       <c r="AA402" s="30"/>
       <c r="AB402" s="46" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="AC402" s="32"/>
       <c r="AD402" s="21"/>
@@ -50334,7 +50334,7 @@
     </row>
     <row r="403" spans="1:43" ht="15.75" customHeight="1">
       <c r="A403" s="458" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="B403" s="33" t="s">
         <v>430</v>
@@ -50345,11 +50345,11 @@
       <c r="D403" s="232"/>
       <c r="E403" s="58"/>
       <c r="F403" s="265" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="G403" s="32"/>
       <c r="H403" s="48" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I403" s="185" t="s">
         <v>2538</v>
@@ -50357,20 +50357,20 @@
       <c r="J403" s="22"/>
       <c r="K403" s="22"/>
       <c r="L403" s="22" t="s">
+        <v>3254</v>
+      </c>
+      <c r="M403" s="387" t="s">
         <v>3255</v>
       </c>
-      <c r="M403" s="387" t="s">
+      <c r="N403" s="38" t="s">
         <v>3256</v>
       </c>
-      <c r="N403" s="38" t="s">
+      <c r="O403" s="38" t="s">
         <v>3257</v>
-      </c>
-      <c r="O403" s="38" t="s">
-        <v>3258</v>
       </c>
       <c r="P403" s="25"/>
       <c r="Q403" s="56" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="R403" s="39" t="s">
         <v>519</v>
@@ -50382,19 +50382,19 @@
       <c r="U403" s="28"/>
       <c r="V403" s="28"/>
       <c r="W403" s="29" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="X403" s="29" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="Y403" s="168" t="s">
+        <v>3259</v>
+      </c>
+      <c r="Z403" s="102" t="s">
         <v>3260</v>
       </c>
-      <c r="Z403" s="102" t="s">
+      <c r="AA403" s="30" t="s">
         <v>3261</v>
-      </c>
-      <c r="AA403" s="30" t="s">
-        <v>3262</v>
       </c>
       <c r="AB403" s="41"/>
       <c r="AC403" s="32"/>
@@ -50415,7 +50415,7 @@
     </row>
     <row r="404" spans="1:43" ht="15.75" customHeight="1">
       <c r="A404" s="458" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="B404" s="33" t="s">
         <v>430</v>
@@ -50426,27 +50426,27 @@
       <c r="D404" s="232"/>
       <c r="E404" s="58"/>
       <c r="F404" s="47" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="G404" s="32"/>
       <c r="H404" s="203" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="I404" s="190" t="s">
         <v>2498</v>
       </c>
       <c r="J404" s="22" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="K404" s="22"/>
       <c r="L404" s="22" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="M404" s="303" t="s">
         <v>595</v>
       </c>
       <c r="N404" s="38" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="O404" s="38"/>
       <c r="P404" s="25"/>
@@ -50461,23 +50461,23 @@
       <c r="U404" s="28"/>
       <c r="V404" s="28"/>
       <c r="W404" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X404" s="72" t="s">
         <v>3141</v>
       </c>
-      <c r="X404" s="72" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y404" s="195" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="Z404" s="418"/>
       <c r="AA404" s="195" t="s">
+        <v>3269</v>
+      </c>
+      <c r="AB404" s="31" t="s">
         <v>3270</v>
       </c>
-      <c r="AB404" s="31" t="s">
+      <c r="AC404" s="47" t="s">
         <v>3271</v>
-      </c>
-      <c r="AC404" s="47" t="s">
-        <v>3272</v>
       </c>
       <c r="AD404" s="21"/>
       <c r="AE404" s="32"/>
@@ -50496,7 +50496,7 @@
     </row>
     <row r="405" spans="1:43" ht="15.75" customHeight="1">
       <c r="A405" s="458" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B405" s="33" t="s">
         <v>430</v>
@@ -50507,11 +50507,11 @@
       <c r="D405" s="232"/>
       <c r="E405" s="58"/>
       <c r="F405" s="16" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="G405" s="32"/>
       <c r="H405" s="203" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="I405" s="190" t="s">
         <v>2498</v>
@@ -50523,7 +50523,7 @@
         <v>1281</v>
       </c>
       <c r="N405" s="38" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="O405" s="38"/>
       <c r="P405" s="25" t="s">
@@ -50542,23 +50542,23 @@
       <c r="U405" s="28"/>
       <c r="V405" s="28"/>
       <c r="W405" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X405" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X405" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y405" s="195" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="Z405" s="418"/>
       <c r="AA405" s="195" t="s">
+        <v>3277</v>
+      </c>
+      <c r="AB405" s="46" t="s">
         <v>3278</v>
       </c>
-      <c r="AB405" s="46" t="s">
-        <v>3279</v>
-      </c>
       <c r="AC405" s="47" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="AD405" s="21"/>
       <c r="AE405" s="32"/>
@@ -50577,7 +50577,7 @@
     </row>
     <row r="406" spans="1:43" ht="15.75" customHeight="1">
       <c r="A406" s="458" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="B406" s="14" t="s">
         <v>430</v>
@@ -50588,11 +50588,11 @@
       <c r="D406" s="232"/>
       <c r="E406" s="58"/>
       <c r="F406" s="265" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="G406" s="32"/>
       <c r="H406" s="203" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="I406" s="190" t="s">
         <v>2498</v>
@@ -50601,10 +50601,10 @@
       <c r="K406" s="22"/>
       <c r="L406" s="22"/>
       <c r="M406" s="303" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="N406" s="38" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="O406" s="65" t="s">
         <v>38</v>
@@ -50614,31 +50614,31 @@
         <v>1164</v>
       </c>
       <c r="R406" s="94" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="S406" s="77" t="s">
         <v>41</v>
       </c>
       <c r="T406" s="21" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="U406" s="28"/>
       <c r="V406" s="28"/>
       <c r="W406" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X406" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X406" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y406" s="195" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z406" s="418"/>
       <c r="AA406" s="195" t="s">
+        <v>3284</v>
+      </c>
+      <c r="AB406" s="46" t="s">
         <v>3285</v>
-      </c>
-      <c r="AB406" s="46" t="s">
-        <v>3286</v>
       </c>
       <c r="AC406" s="32"/>
       <c r="AD406" s="21"/>
@@ -50658,7 +50658,7 @@
     </row>
     <row r="407" spans="1:43" ht="15.75" customHeight="1">
       <c r="A407" s="458" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="B407" s="33" t="s">
         <v>430</v>
@@ -50669,11 +50669,11 @@
       <c r="D407" s="232"/>
       <c r="E407" s="58"/>
       <c r="F407" s="265" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="G407" s="32"/>
       <c r="H407" s="203" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="I407" s="190" t="s">
         <v>2498</v>
@@ -50681,13 +50681,13 @@
       <c r="J407" s="22"/>
       <c r="K407" s="22"/>
       <c r="L407" s="22" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="M407" s="135" t="s">
         <v>2677</v>
       </c>
       <c r="N407" s="38" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="O407" s="294"/>
       <c r="P407" s="124"/>
@@ -50702,20 +50702,20 @@
       <c r="U407" s="28"/>
       <c r="V407" s="28"/>
       <c r="W407" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X407" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X407" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y407" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z407" s="197"/>
       <c r="AA407" s="30" t="s">
+        <v>3290</v>
+      </c>
+      <c r="AB407" s="46" t="s">
         <v>3291</v>
-      </c>
-      <c r="AB407" s="46" t="s">
-        <v>3292</v>
       </c>
       <c r="AC407" s="32"/>
       <c r="AD407" s="21"/>
@@ -50735,10 +50735,10 @@
     </row>
     <row r="408" spans="1:43" ht="15.75" customHeight="1">
       <c r="A408" s="458" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B408" s="32" t="s">
         <v>3293</v>
-      </c>
-      <c r="B408" s="32" t="s">
-        <v>3294</v>
       </c>
       <c r="C408" s="247" t="s">
         <v>171</v>
@@ -50746,11 +50746,11 @@
       <c r="D408" s="244"/>
       <c r="E408" s="188"/>
       <c r="F408" s="189" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="G408" s="32"/>
       <c r="H408" s="32" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="I408" s="185" t="s">
         <v>2538</v>
@@ -50758,20 +50758,20 @@
       <c r="J408" s="22"/>
       <c r="K408" s="93"/>
       <c r="L408" s="22" t="s">
+        <v>3296</v>
+      </c>
+      <c r="M408" s="95" t="s">
         <v>3297</v>
       </c>
-      <c r="M408" s="95" t="s">
+      <c r="N408" s="65" t="s">
         <v>3298</v>
-      </c>
-      <c r="N408" s="65" t="s">
-        <v>3299</v>
       </c>
       <c r="O408" s="65"/>
       <c r="P408" s="74" t="s">
+        <v>3299</v>
+      </c>
+      <c r="Q408" s="56" t="s">
         <v>3300</v>
-      </c>
-      <c r="Q408" s="56" t="s">
-        <v>3301</v>
       </c>
       <c r="R408" s="101" t="s">
         <v>40</v>
@@ -50806,42 +50806,42 @@
     </row>
     <row r="409" spans="1:43" ht="15.75" customHeight="1">
       <c r="A409" s="458" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="B409" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C409" s="248" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="D409" s="244"/>
       <c r="E409" s="188"/>
       <c r="F409" s="205" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="G409" s="184"/>
       <c r="H409" s="48" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="I409" s="185" t="s">
         <v>2538</v>
       </c>
       <c r="J409" s="103" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="K409" s="103"/>
       <c r="L409" s="107"/>
       <c r="M409" s="206" t="s">
+        <v>3304</v>
+      </c>
+      <c r="N409" s="38" t="s">
         <v>3305</v>
-      </c>
-      <c r="N409" s="38" t="s">
-        <v>3306</v>
       </c>
       <c r="O409" s="38"/>
       <c r="P409" s="25"/>
       <c r="Q409" s="56"/>
       <c r="R409" s="113" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="S409" s="77" t="s">
         <v>41</v>
@@ -50850,13 +50850,13 @@
       <c r="U409" s="28"/>
       <c r="V409" s="28"/>
       <c r="W409" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X409" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X409" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y409" s="30" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="Z409" s="30"/>
       <c r="AA409" s="30"/>
@@ -50879,22 +50879,22 @@
     </row>
     <row r="410" spans="1:43" ht="15.75" customHeight="1">
       <c r="A410" s="458" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="B410" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C410" s="246" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="D410" s="232"/>
       <c r="E410" s="58"/>
       <c r="F410" s="47" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="G410" s="32"/>
       <c r="H410" s="203" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="I410" s="190" t="s">
         <v>2498</v>
@@ -50904,13 +50904,13 @@
         <v>276150</v>
       </c>
       <c r="L410" s="22" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="M410" s="135" t="s">
         <v>2210</v>
       </c>
       <c r="N410" s="38" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="O410" s="38"/>
       <c r="P410" s="25"/>
@@ -50922,7 +50922,7 @@
         <v>41</v>
       </c>
       <c r="T410" s="21" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="U410" s="28"/>
       <c r="V410" s="28"/>
@@ -50930,10 +50930,10 @@
       <c r="X410" s="29"/>
       <c r="Y410" s="30"/>
       <c r="Z410" s="30" t="s">
+        <v>3314</v>
+      </c>
+      <c r="AA410" s="30" t="s">
         <v>3315</v>
-      </c>
-      <c r="AA410" s="30" t="s">
-        <v>3316</v>
       </c>
       <c r="AB410" s="41"/>
       <c r="AC410" s="32"/>
@@ -50954,7 +50954,7 @@
     </row>
     <row r="411" spans="1:43" ht="15.75" customHeight="1">
       <c r="A411" s="458" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="B411" s="33" t="s">
         <v>430</v>
@@ -50965,18 +50965,18 @@
       <c r="D411" s="232"/>
       <c r="E411" s="58"/>
       <c r="F411" s="47" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="G411" s="32"/>
       <c r="H411" s="203" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="I411" s="190" t="s">
         <v>2498</v>
       </c>
       <c r="J411" s="22"/>
       <c r="K411" s="22" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="L411" s="22" t="s">
         <v>797</v>
@@ -50985,7 +50985,7 @@
         <v>1097</v>
       </c>
       <c r="N411" s="38" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="O411" s="38"/>
       <c r="P411" s="25"/>
@@ -51000,13 +51000,13 @@
       <c r="U411" s="28"/>
       <c r="V411" s="28"/>
       <c r="W411" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X411" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X411" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y411" s="30" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="Z411" s="30"/>
       <c r="AA411" s="30"/>
@@ -51029,7 +51029,7 @@
     </row>
     <row r="412" spans="1:43" ht="15.75" customHeight="1">
       <c r="A412" s="458" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="B412" s="33" t="s">
         <v>430</v>
@@ -51040,17 +51040,17 @@
       <c r="D412" s="232"/>
       <c r="E412" s="58"/>
       <c r="F412" s="47" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="G412" s="39"/>
       <c r="H412" s="203" t="s">
+        <v>3324</v>
+      </c>
+      <c r="I412" s="32" t="s">
         <v>3325</v>
       </c>
-      <c r="I412" s="32" t="s">
+      <c r="J412" s="107" t="s">
         <v>3326</v>
-      </c>
-      <c r="J412" s="107" t="s">
-        <v>3327</v>
       </c>
       <c r="K412" s="107"/>
       <c r="L412" s="107"/>
@@ -51058,7 +51058,7 @@
         <v>137</v>
       </c>
       <c r="N412" s="38" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="O412" s="38"/>
       <c r="P412" s="25"/>
@@ -51073,13 +51073,13 @@
       <c r="U412" s="28"/>
       <c r="V412" s="28"/>
       <c r="W412" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X412" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X412" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y412" s="30" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="Z412" s="30"/>
       <c r="AA412" s="30"/>
@@ -51102,7 +51102,7 @@
     </row>
     <row r="413" spans="1:43" ht="15.75" customHeight="1">
       <c r="A413" s="458" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="B413" s="33" t="s">
         <v>430</v>
@@ -51113,19 +51113,19 @@
       <c r="D413" s="232"/>
       <c r="E413" s="58"/>
       <c r="F413" s="16" t="s">
+        <v>3330</v>
+      </c>
+      <c r="G413" s="32" t="s">
         <v>3331</v>
       </c>
-      <c r="G413" s="32" t="s">
+      <c r="H413" s="204" t="s">
         <v>3332</v>
       </c>
-      <c r="H413" s="204" t="s">
+      <c r="I413" s="185" t="s">
         <v>3333</v>
       </c>
-      <c r="I413" s="185" t="s">
-        <v>3334</v>
-      </c>
       <c r="J413" s="107" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="K413" s="107"/>
       <c r="L413" s="107"/>
@@ -51133,7 +51133,7 @@
         <v>137</v>
       </c>
       <c r="N413" s="38" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="O413" s="38"/>
       <c r="P413" s="25"/>
@@ -51148,18 +51148,18 @@
       <c r="U413" s="28"/>
       <c r="V413" s="28"/>
       <c r="W413" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X413" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X413" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y413" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z413" s="30"/>
       <c r="AA413" s="30"/>
       <c r="AB413" s="46" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="AC413" s="32"/>
       <c r="AD413" s="21"/>
@@ -51179,7 +51179,7 @@
     </row>
     <row r="414" spans="1:43" ht="15.75" customHeight="1">
       <c r="A414" s="458" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="B414" s="95" t="s">
         <v>2275</v>
@@ -51190,19 +51190,19 @@
       <c r="D414" s="232"/>
       <c r="E414" s="58"/>
       <c r="F414" s="47" t="s">
+        <v>3337</v>
+      </c>
+      <c r="G414" s="32" t="s">
         <v>3338</v>
       </c>
-      <c r="G414" s="32" t="s">
+      <c r="H414" s="204" t="s">
         <v>3339</v>
       </c>
-      <c r="H414" s="204" t="s">
+      <c r="I414" s="185" t="s">
         <v>3340</v>
       </c>
-      <c r="I414" s="185" t="s">
+      <c r="J414" s="22" t="s">
         <v>3341</v>
-      </c>
-      <c r="J414" s="22" t="s">
-        <v>3342</v>
       </c>
       <c r="K414" s="22"/>
       <c r="L414" s="22"/>
@@ -51210,7 +51210,7 @@
         <v>137</v>
       </c>
       <c r="N414" s="38" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="O414" s="38"/>
       <c r="P414" s="25"/>
@@ -51225,13 +51225,13 @@
       <c r="U414" s="28"/>
       <c r="V414" s="28"/>
       <c r="W414" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X414" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X414" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y414" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z414" s="30"/>
       <c r="AA414" s="30"/>
@@ -51254,29 +51254,29 @@
     </row>
     <row r="415" spans="1:43" ht="15.75" customHeight="1">
       <c r="A415" s="458" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="B415" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C415" s="307" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="D415" s="244"/>
       <c r="E415" s="188"/>
       <c r="F415" s="267" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="G415" s="184"/>
       <c r="H415" s="203" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="I415" s="185" t="s">
         <v>2538</v>
       </c>
       <c r="J415" s="22"/>
       <c r="K415" s="22" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="L415" s="22" t="s">
         <v>1354</v>
@@ -51285,7 +51285,7 @@
         <v>1097</v>
       </c>
       <c r="N415" s="38" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="O415" s="38"/>
       <c r="P415" s="25"/>
@@ -51300,13 +51300,13 @@
       <c r="U415" s="28"/>
       <c r="V415" s="28"/>
       <c r="W415" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X415" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X415" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y415" s="30" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="Z415" s="102"/>
       <c r="AA415" s="30"/>
@@ -51329,22 +51329,22 @@
     </row>
     <row r="416" spans="1:43" ht="15.75" customHeight="1">
       <c r="A416" s="458" t="s">
-        <v>3916</v>
+        <v>3915</v>
       </c>
       <c r="B416" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C416" s="252" t="s">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="D416" s="232"/>
       <c r="E416" s="58"/>
       <c r="F416" s="265" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="G416" s="32"/>
       <c r="H416" s="203" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="I416" s="32" t="s">
         <v>2498</v>
@@ -51356,7 +51356,7 @@
         <v>1832</v>
       </c>
       <c r="N416" s="38" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="O416" s="65" t="s">
         <v>38</v>
@@ -51375,20 +51375,20 @@
       <c r="U416" s="28"/>
       <c r="V416" s="28"/>
       <c r="W416" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X416" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X416" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y416" s="30" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="Z416" s="197"/>
       <c r="AA416" s="30" t="s">
+        <v>3353</v>
+      </c>
+      <c r="AB416" s="46" t="s">
         <v>3354</v>
-      </c>
-      <c r="AB416" s="46" t="s">
-        <v>3355</v>
       </c>
       <c r="AC416" s="32"/>
       <c r="AD416" s="21"/>
@@ -51408,7 +51408,7 @@
     </row>
     <row r="417" spans="1:43" ht="15.75" customHeight="1">
       <c r="A417" s="458" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="B417" s="33" t="s">
         <v>430</v>
@@ -51419,23 +51419,23 @@
       <c r="D417" s="232"/>
       <c r="E417" s="58"/>
       <c r="F417" s="265" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="G417" s="32"/>
       <c r="H417" s="203" t="s">
+        <v>3356</v>
+      </c>
+      <c r="I417" s="32" t="s">
         <v>3357</v>
-      </c>
-      <c r="I417" s="32" t="s">
-        <v>3358</v>
       </c>
       <c r="J417" s="22"/>
       <c r="K417" s="22"/>
       <c r="L417" s="22"/>
       <c r="M417" s="113" t="s">
+        <v>3358</v>
+      </c>
+      <c r="N417" s="38" t="s">
         <v>3359</v>
-      </c>
-      <c r="N417" s="38" t="s">
-        <v>3360</v>
       </c>
       <c r="O417" s="38"/>
       <c r="P417" s="25"/>
@@ -51475,7 +51475,7 @@
     </row>
     <row r="418" spans="1:43" ht="15.75" customHeight="1">
       <c r="A418" s="458" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="B418" s="33" t="s">
         <v>430</v>
@@ -51486,27 +51486,27 @@
       <c r="D418" s="232"/>
       <c r="E418" s="58"/>
       <c r="F418" s="265" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="G418" s="32"/>
       <c r="H418" s="39" t="s">
+        <v>3361</v>
+      </c>
+      <c r="I418" s="190" t="s">
         <v>3362</v>
       </c>
-      <c r="I418" s="190" t="s">
+      <c r="J418" s="107" t="s">
         <v>3363</v>
-      </c>
-      <c r="J418" s="107" t="s">
-        <v>3364</v>
       </c>
       <c r="K418" s="107"/>
       <c r="L418" s="107" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="M418" s="43" t="s">
         <v>137</v>
       </c>
       <c r="N418" s="38" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="O418" s="38"/>
       <c r="P418" s="25"/>
@@ -51544,30 +51544,30 @@
     </row>
     <row r="419" spans="1:43" ht="15.75" customHeight="1">
       <c r="A419" s="458" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="B419" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C419" s="361" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="D419" s="232"/>
       <c r="E419" s="58"/>
       <c r="F419" s="265" t="s">
+        <v>3365</v>
+      </c>
+      <c r="G419" s="32" t="s">
         <v>3366</v>
       </c>
-      <c r="G419" s="32" t="s">
+      <c r="H419" s="204" t="s">
         <v>3367</v>
       </c>
-      <c r="H419" s="204" t="s">
+      <c r="I419" s="185" t="s">
         <v>3368</v>
       </c>
-      <c r="I419" s="185" t="s">
+      <c r="J419" s="22" t="s">
         <v>3369</v>
-      </c>
-      <c r="J419" s="22" t="s">
-        <v>3370</v>
       </c>
       <c r="K419" s="22"/>
       <c r="L419" s="22"/>
@@ -51575,7 +51575,7 @@
         <v>137</v>
       </c>
       <c r="N419" s="38" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="O419" s="38"/>
       <c r="P419" s="25"/>
@@ -51613,7 +51613,7 @@
     </row>
     <row r="420" spans="1:43" ht="15.75" customHeight="1">
       <c r="A420" s="458" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="B420" s="33" t="s">
         <v>430</v>
@@ -51624,11 +51624,11 @@
       <c r="D420" s="244"/>
       <c r="E420" s="188"/>
       <c r="F420" s="267" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="G420" s="184"/>
       <c r="H420" s="190" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="I420" s="190" t="s">
         <v>2498</v>
@@ -51636,13 +51636,13 @@
       <c r="J420" s="22"/>
       <c r="K420" s="22"/>
       <c r="L420" s="22" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M420" s="135" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="N420" s="38" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="O420" s="38"/>
       <c r="P420" s="25"/>
@@ -51657,17 +51657,17 @@
       <c r="U420" s="28"/>
       <c r="V420" s="28"/>
       <c r="W420" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X420" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X420" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y420" s="30" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="Z420" s="418"/>
       <c r="AA420" s="30" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="AB420" s="41"/>
       <c r="AC420" s="32"/>
@@ -51688,22 +51688,22 @@
     </row>
     <row r="421" spans="1:43" ht="15.75" customHeight="1">
       <c r="A421" s="458" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="B421" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C421" s="361" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="D421" s="244"/>
       <c r="E421" s="58"/>
       <c r="F421" s="265" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G421" s="184"/>
       <c r="H421" s="203" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="I421" s="32" t="s">
         <v>2498</v>
@@ -51714,10 +51714,10 @@
         <v>2743</v>
       </c>
       <c r="M421" s="135" t="s">
+        <v>3379</v>
+      </c>
+      <c r="N421" s="38" t="s">
         <v>3380</v>
-      </c>
-      <c r="N421" s="38" t="s">
-        <v>3381</v>
       </c>
       <c r="O421" s="38"/>
       <c r="P421" s="25"/>
@@ -51732,23 +51732,23 @@
       <c r="U421" s="28"/>
       <c r="V421" s="28"/>
       <c r="W421" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X421" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X421" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y421" s="30" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="Z421" s="197"/>
       <c r="AA421" s="30" t="s">
+        <v>3382</v>
+      </c>
+      <c r="AB421" s="46" t="s">
         <v>3383</v>
       </c>
-      <c r="AB421" s="46" t="s">
+      <c r="AC421" s="66" t="s">
         <v>3384</v>
-      </c>
-      <c r="AC421" s="66" t="s">
-        <v>3385</v>
       </c>
       <c r="AD421" s="32"/>
       <c r="AE421" s="32"/>
@@ -51767,7 +51767,7 @@
     </row>
     <row r="422" spans="1:43" ht="15.75" customHeight="1">
       <c r="A422" s="458" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="B422" s="33" t="s">
         <v>430</v>
@@ -51778,17 +51778,17 @@
       <c r="D422" s="244"/>
       <c r="E422" s="188"/>
       <c r="F422" s="189" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="G422" s="184"/>
       <c r="H422" s="203" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="I422" s="190" t="s">
         <v>2498</v>
       </c>
       <c r="J422" s="82" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="K422" s="82"/>
       <c r="L422" s="82"/>
@@ -51796,14 +51796,14 @@
         <v>651</v>
       </c>
       <c r="N422" s="38" t="s">
+        <v>3389</v>
+      </c>
+      <c r="O422" s="38" t="s">
         <v>3390</v>
-      </c>
-      <c r="O422" s="38" t="s">
-        <v>3391</v>
       </c>
       <c r="P422" s="25"/>
       <c r="Q422" s="26" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="R422" s="39" t="s">
         <v>519</v>
@@ -51815,22 +51815,22 @@
       <c r="U422" s="28"/>
       <c r="V422" s="28"/>
       <c r="W422" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X422" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X422" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y422" s="30" t="s">
+        <v>3392</v>
+      </c>
+      <c r="Z422" s="30" t="s">
         <v>3393</v>
       </c>
-      <c r="Z422" s="30" t="s">
+      <c r="AA422" s="30" t="s">
         <v>3394</v>
       </c>
-      <c r="AA422" s="30" t="s">
+      <c r="AB422" s="46" t="s">
         <v>3395</v>
-      </c>
-      <c r="AB422" s="46" t="s">
-        <v>3396</v>
       </c>
       <c r="AC422" s="32"/>
       <c r="AD422" s="32"/>
@@ -51850,7 +51850,7 @@
     </row>
     <row r="423" spans="1:43" ht="15.75" customHeight="1">
       <c r="A423" s="458" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="B423" s="33" t="s">
         <v>430</v>
@@ -51861,11 +51861,11 @@
       <c r="D423" s="244"/>
       <c r="E423" s="188"/>
       <c r="F423" s="189" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="G423" s="184"/>
       <c r="H423" s="203" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="I423" s="190" t="s">
         <v>2498</v>
@@ -51879,14 +51879,14 @@
         <v>651</v>
       </c>
       <c r="N423" s="38" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="O423" s="38"/>
       <c r="P423" s="25" t="s">
+        <v>3399</v>
+      </c>
+      <c r="Q423" s="56" t="s">
         <v>3400</v>
-      </c>
-      <c r="Q423" s="56" t="s">
-        <v>3401</v>
       </c>
       <c r="R423" s="99" t="s">
         <v>539</v>
@@ -51895,25 +51895,25 @@
         <v>41</v>
       </c>
       <c r="T423" s="21" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="U423" s="28"/>
       <c r="V423" s="28"/>
       <c r="W423" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X423" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X423" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y423" s="30" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="Z423" s="30"/>
       <c r="AA423" s="30" t="s">
+        <v>3963</v>
+      </c>
+      <c r="AB423" s="41" t="s">
         <v>3964</v>
-      </c>
-      <c r="AB423" s="41" t="s">
-        <v>3965</v>
       </c>
       <c r="AC423" s="32"/>
       <c r="AD423" s="32"/>
@@ -51933,7 +51933,7 @@
     </row>
     <row r="424" spans="1:43" ht="15.75" customHeight="1">
       <c r="A424" s="458" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="B424" s="14" t="s">
         <v>430</v>
@@ -51944,14 +51944,14 @@
       <c r="D424" s="232"/>
       <c r="E424" s="58"/>
       <c r="F424" s="265" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="G424" s="32"/>
       <c r="H424" s="203" t="s">
+        <v>3404</v>
+      </c>
+      <c r="I424" s="185" t="s">
         <v>3405</v>
-      </c>
-      <c r="I424" s="185" t="s">
-        <v>3406</v>
       </c>
       <c r="J424" s="82"/>
       <c r="K424" s="82"/>
@@ -51975,13 +51975,13 @@
       <c r="U424" s="28"/>
       <c r="V424" s="28"/>
       <c r="W424" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X424" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X424" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y424" s="30" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="Z424" s="30"/>
       <c r="AA424" s="30"/>
@@ -52004,22 +52004,22 @@
     </row>
     <row r="425" spans="1:43" ht="15.75" customHeight="1">
       <c r="A425" s="458" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="B425" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C425" s="254" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="D425" s="232"/>
       <c r="E425" s="58"/>
       <c r="F425" s="16" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="G425" s="32"/>
       <c r="H425" s="203" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="I425" s="214" t="s">
         <v>576</v>
@@ -52027,20 +52027,20 @@
       <c r="J425" s="35"/>
       <c r="K425" s="22"/>
       <c r="L425" s="22" t="s">
+        <v>3410</v>
+      </c>
+      <c r="M425" s="304" t="s">
         <v>3411</v>
       </c>
-      <c r="M425" s="304" t="s">
+      <c r="N425" s="54" t="s">
         <v>3412</v>
-      </c>
-      <c r="N425" s="54" t="s">
-        <v>3413</v>
       </c>
       <c r="O425" s="54"/>
       <c r="P425" s="74" t="s">
+        <v>3413</v>
+      </c>
+      <c r="Q425" s="56" t="s">
         <v>3414</v>
-      </c>
-      <c r="Q425" s="56" t="s">
-        <v>3415</v>
       </c>
       <c r="R425" s="101" t="s">
         <v>40</v>
@@ -52052,13 +52052,13 @@
       <c r="U425" s="28"/>
       <c r="V425" s="28"/>
       <c r="W425" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X425" s="29" t="s">
         <v>3141</v>
       </c>
-      <c r="X425" s="29" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y425" s="30" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="Z425" s="30"/>
       <c r="AA425" s="30"/>
@@ -52081,7 +52081,7 @@
     </row>
     <row r="426" spans="1:43" ht="15.75" customHeight="1">
       <c r="A426" s="458" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="B426" s="33" t="s">
         <v>430</v>
@@ -52092,14 +52092,14 @@
       <c r="D426" s="232"/>
       <c r="E426" s="58"/>
       <c r="F426" s="47" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="G426" s="32"/>
       <c r="H426" s="190" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="I426" s="214" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="J426" s="22"/>
       <c r="K426" s="93"/>
@@ -52146,7 +52146,7 @@
     </row>
     <row r="427" spans="1:43" ht="15.75" customHeight="1">
       <c r="A427" s="458" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="B427" s="33" t="s">
         <v>430</v>
@@ -52157,14 +52157,14 @@
       <c r="D427" s="232"/>
       <c r="E427" s="58"/>
       <c r="F427" s="265" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="G427" s="32"/>
       <c r="H427" s="190" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="I427" s="32" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="J427" s="22"/>
       <c r="K427" s="22"/>
@@ -52213,7 +52213,7 @@
     </row>
     <row r="428" spans="1:43" ht="15.75" customHeight="1">
       <c r="A428" s="458" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="B428" s="14" t="s">
         <v>430</v>
@@ -52224,11 +52224,11 @@
       <c r="D428" s="232"/>
       <c r="E428" s="58"/>
       <c r="F428" s="265" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="G428" s="32"/>
       <c r="H428" s="48" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="I428" s="185" t="s">
         <v>2538</v>
@@ -52236,13 +52236,13 @@
       <c r="J428" s="22"/>
       <c r="K428" s="22"/>
       <c r="L428" s="22" t="s">
+        <v>3424</v>
+      </c>
+      <c r="M428" s="135" t="s">
         <v>3425</v>
       </c>
-      <c r="M428" s="135" t="s">
+      <c r="N428" s="54" t="s">
         <v>3426</v>
-      </c>
-      <c r="N428" s="54" t="s">
-        <v>3427</v>
       </c>
       <c r="O428" s="54"/>
       <c r="P428" s="55"/>
@@ -52257,13 +52257,13 @@
       <c r="U428" s="28"/>
       <c r="V428" s="28"/>
       <c r="W428" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X428" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X428" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y428" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z428" s="30"/>
       <c r="AA428" s="30"/>
@@ -52286,7 +52286,7 @@
     </row>
     <row r="429" spans="1:43" ht="15.75" customHeight="1">
       <c r="A429" s="458" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="B429" s="33" t="s">
         <v>430</v>
@@ -52297,11 +52297,11 @@
       <c r="D429" s="232"/>
       <c r="E429" s="58"/>
       <c r="F429" s="265" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="G429" s="32"/>
       <c r="H429" s="203" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="I429" s="190" t="s">
         <v>2538</v>
@@ -52312,10 +52312,10 @@
         <v>985</v>
       </c>
       <c r="M429" s="135" t="s">
+        <v>3358</v>
+      </c>
+      <c r="N429" s="54" t="s">
         <v>3359</v>
-      </c>
-      <c r="N429" s="54" t="s">
-        <v>3360</v>
       </c>
       <c r="O429" s="394"/>
       <c r="P429" s="112"/>
@@ -52330,13 +52330,13 @@
       <c r="U429" s="28"/>
       <c r="V429" s="28"/>
       <c r="W429" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X429" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X429" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y429" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z429" s="30"/>
       <c r="AA429" s="30"/>
@@ -52359,7 +52359,7 @@
     </row>
     <row r="430" spans="1:43" ht="15.75" customHeight="1">
       <c r="A430" s="458" t="s">
-        <v>3907</v>
+        <v>3906</v>
       </c>
       <c r="B430" s="33" t="s">
         <v>430</v>
@@ -52370,11 +52370,11 @@
       <c r="D430" s="232"/>
       <c r="E430" s="58"/>
       <c r="F430" s="265" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="G430" s="32"/>
       <c r="H430" s="203" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="I430" s="190" t="s">
         <v>2538</v>
@@ -52383,14 +52383,14 @@
       <c r="K430" s="82"/>
       <c r="L430" s="82"/>
       <c r="M430" s="135" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="N430" s="38" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="O430" s="38"/>
       <c r="Q430" s="289" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="R430" s="115" t="s">
         <v>383</v>
@@ -52425,7 +52425,7 @@
     </row>
     <row r="431" spans="1:43" ht="15.75" customHeight="1">
       <c r="A431" s="458" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="B431" s="33" t="s">
         <v>430</v>
@@ -52436,11 +52436,11 @@
       <c r="D431" s="232"/>
       <c r="E431" s="58"/>
       <c r="F431" s="47" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="G431" s="32"/>
       <c r="H431" s="203" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="I431" s="190" t="s">
         <v>2538</v>
@@ -52449,10 +52449,10 @@
       <c r="K431" s="82"/>
       <c r="L431" s="22"/>
       <c r="M431" s="135" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="N431" s="38" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="O431" s="38"/>
       <c r="P431" s="25"/>
@@ -52490,7 +52490,7 @@
     </row>
     <row r="432" spans="1:43" ht="15.75" customHeight="1">
       <c r="A432" s="458" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="B432" s="33" t="s">
         <v>430</v>
@@ -52501,11 +52501,11 @@
       <c r="D432" s="232"/>
       <c r="E432" s="58"/>
       <c r="F432" s="16" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="G432" s="32"/>
       <c r="H432" s="203" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="I432" s="190" t="s">
         <v>2538</v>
@@ -52513,19 +52513,19 @@
       <c r="J432" s="98"/>
       <c r="K432" s="103"/>
       <c r="L432" s="103" t="s">
+        <v>3437</v>
+      </c>
+      <c r="M432" s="135" t="s">
         <v>3438</v>
       </c>
-      <c r="M432" s="135" t="s">
+      <c r="N432" s="54" t="s">
         <v>3439</v>
-      </c>
-      <c r="N432" s="54" t="s">
-        <v>3440</v>
       </c>
       <c r="O432" s="394"/>
       <c r="P432" s="112"/>
       <c r="Q432" s="121"/>
       <c r="R432" s="296" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="S432" s="135" t="s">
         <v>41</v>
@@ -52557,7 +52557,7 @@
     </row>
     <row r="433" spans="1:43" ht="15.75" customHeight="1">
       <c r="A433" s="458" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="B433" s="33" t="s">
         <v>430</v>
@@ -52568,11 +52568,11 @@
       <c r="D433" s="232"/>
       <c r="E433" s="58"/>
       <c r="F433" s="47" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="G433" s="32"/>
       <c r="H433" s="203" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="I433" s="190" t="s">
         <v>2498</v>
@@ -52587,11 +52587,11 @@
         <v>1234</v>
       </c>
       <c r="O433" s="54" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="P433" s="55"/>
       <c r="Q433" s="56" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="R433" s="32" t="s">
         <v>519</v>
@@ -52603,16 +52603,16 @@
       <c r="U433" s="28"/>
       <c r="V433" s="28"/>
       <c r="W433" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X433" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X433" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y433" s="30" t="s">
+        <v>3446</v>
+      </c>
+      <c r="Z433" s="30" t="s">
         <v>3447</v>
-      </c>
-      <c r="Z433" s="30" t="s">
-        <v>3448</v>
       </c>
       <c r="AA433" s="30"/>
       <c r="AB433" s="41"/>
@@ -52634,7 +52634,7 @@
     </row>
     <row r="434" spans="1:43" ht="15.75" customHeight="1">
       <c r="A434" s="458" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="B434" s="33" t="s">
         <v>430</v>
@@ -52645,11 +52645,11 @@
       <c r="D434" s="232"/>
       <c r="E434" s="58"/>
       <c r="F434" s="265" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="G434" s="32"/>
       <c r="H434" s="203" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="I434" s="190" t="s">
         <v>2538</v>
@@ -52661,7 +52661,7 @@
         <v>2721</v>
       </c>
       <c r="N434" s="134" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="O434" s="54"/>
       <c r="P434" s="55"/>
@@ -52676,13 +52676,13 @@
       <c r="U434" s="28"/>
       <c r="V434" s="28"/>
       <c r="W434" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X434" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X434" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y434" s="30" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="Z434" s="30"/>
       <c r="AA434" s="30"/>
@@ -52705,7 +52705,7 @@
     </row>
     <row r="435" spans="1:43" ht="15.75" customHeight="1">
       <c r="A435" s="458" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
       <c r="B435" s="33" t="s">
         <v>430</v>
@@ -52716,11 +52716,11 @@
       <c r="D435" s="232"/>
       <c r="E435" s="58"/>
       <c r="F435" s="265" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="G435" s="32"/>
       <c r="H435" s="203" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="I435" s="190" t="s">
         <v>2538</v>
@@ -52732,7 +52732,7 @@
         <v>252</v>
       </c>
       <c r="N435" s="54" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="O435" s="54"/>
       <c r="P435" s="55"/>
@@ -52770,7 +52770,7 @@
     </row>
     <row r="436" spans="1:43" ht="15.75" customHeight="1">
       <c r="A436" s="458" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="B436" s="33" t="s">
         <v>430</v>
@@ -52781,17 +52781,17 @@
       <c r="D436" s="232"/>
       <c r="E436" s="58"/>
       <c r="F436" s="265" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="G436" s="32"/>
       <c r="H436" s="190" t="s">
+        <v>3457</v>
+      </c>
+      <c r="I436" s="32" t="s">
         <v>3458</v>
       </c>
-      <c r="I436" s="32" t="s">
-        <v>3459</v>
-      </c>
       <c r="J436" s="82" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="K436" s="82"/>
       <c r="L436" s="22"/>
@@ -52837,24 +52837,24 @@
     </row>
     <row r="437" spans="1:43" ht="15.75" customHeight="1">
       <c r="A437" s="458" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="B437" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C437" s="255" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="D437" s="232"/>
       <c r="E437" s="58"/>
       <c r="F437" s="265" t="s">
+        <v>3460</v>
+      </c>
+      <c r="G437" s="32" t="s">
         <v>3461</v>
       </c>
-      <c r="G437" s="32" t="s">
+      <c r="H437" s="203" t="s">
         <v>3462</v>
-      </c>
-      <c r="H437" s="203" t="s">
-        <v>3463</v>
       </c>
       <c r="I437" s="190" t="s">
         <v>2538</v>
@@ -52862,13 +52862,13 @@
       <c r="J437" s="35"/>
       <c r="K437" s="22"/>
       <c r="L437" s="22" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="M437" s="206" t="s">
         <v>476</v>
       </c>
       <c r="N437" s="54" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="O437" s="54"/>
       <c r="P437" s="55"/>
@@ -52881,19 +52881,19 @@
       </c>
       <c r="T437" s="21"/>
       <c r="U437" s="28" t="s">
+        <v>3465</v>
+      </c>
+      <c r="V437" s="28" t="s">
         <v>3466</v>
       </c>
-      <c r="V437" s="28" t="s">
+      <c r="W437" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X437" s="118" t="s">
+        <v>3141</v>
+      </c>
+      <c r="Y437" s="30" t="s">
         <v>3467</v>
-      </c>
-      <c r="W437" s="29" t="s">
-        <v>3141</v>
-      </c>
-      <c r="X437" s="118" t="s">
-        <v>3142</v>
-      </c>
-      <c r="Y437" s="30" t="s">
-        <v>3468</v>
       </c>
       <c r="Z437" s="30"/>
       <c r="AA437" s="30"/>
@@ -52916,7 +52916,7 @@
     </row>
     <row r="438" spans="1:43" ht="15.75" customHeight="1">
       <c r="A438" s="458" t="s">
-        <v>3912</v>
+        <v>3911</v>
       </c>
       <c r="B438" s="33" t="s">
         <v>430</v>
@@ -52927,17 +52927,17 @@
       <c r="D438" s="232"/>
       <c r="E438" s="58"/>
       <c r="F438" s="265" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="G438" s="32"/>
       <c r="H438" s="203" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="I438" s="190" t="s">
         <v>2538</v>
       </c>
       <c r="J438" s="103" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="K438" s="103"/>
       <c r="L438" s="107"/>
@@ -52945,7 +52945,7 @@
         <v>137</v>
       </c>
       <c r="N438" s="54" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="O438" s="54"/>
       <c r="P438" s="55"/>
@@ -52960,13 +52960,13 @@
       <c r="U438" s="120"/>
       <c r="V438" s="120"/>
       <c r="W438" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X438" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X438" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y438" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z438" s="30"/>
       <c r="AA438" s="30"/>
@@ -52989,7 +52989,7 @@
     </row>
     <row r="439" spans="1:43" ht="15.75" customHeight="1">
       <c r="A439" s="458" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="B439" s="95" t="s">
         <v>2275</v>
@@ -53000,13 +53000,13 @@
       <c r="D439" s="232"/>
       <c r="E439" s="58"/>
       <c r="F439" s="16" t="s">
+        <v>3473</v>
+      </c>
+      <c r="G439" s="32" t="s">
         <v>3474</v>
       </c>
-      <c r="G439" s="32" t="s">
+      <c r="H439" s="203" t="s">
         <v>3475</v>
-      </c>
-      <c r="H439" s="203" t="s">
-        <v>3476</v>
       </c>
       <c r="I439" s="32" t="s">
         <v>2538</v>
@@ -53014,13 +53014,13 @@
       <c r="J439" s="35"/>
       <c r="K439" s="82"/>
       <c r="L439" s="82" t="s">
+        <v>3476</v>
+      </c>
+      <c r="M439" s="206" t="s">
         <v>3477</v>
       </c>
-      <c r="M439" s="206" t="s">
+      <c r="N439" s="54" t="s">
         <v>3478</v>
-      </c>
-      <c r="N439" s="54" t="s">
-        <v>3479</v>
       </c>
       <c r="O439" s="54"/>
       <c r="P439" s="55"/>
@@ -53033,15 +53033,15 @@
       </c>
       <c r="T439" s="104"/>
       <c r="U439" s="105" t="s">
+        <v>3465</v>
+      </c>
+      <c r="V439" s="105" t="s">
         <v>3466</v>
-      </c>
-      <c r="V439" s="105" t="s">
-        <v>3467</v>
       </c>
       <c r="W439" s="111"/>
       <c r="X439" s="111"/>
       <c r="Y439" s="30" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="Z439" s="30"/>
       <c r="AA439" s="30"/>
@@ -53064,7 +53064,7 @@
     </row>
     <row r="440" spans="1:43" ht="15.75" customHeight="1">
       <c r="A440" s="458" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="B440" s="14" t="s">
         <v>430</v>
@@ -53075,11 +53075,11 @@
       <c r="D440" s="232"/>
       <c r="E440" s="58"/>
       <c r="F440" s="265" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="G440" s="32"/>
       <c r="H440" s="203" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="I440" s="32" t="s">
         <v>2538</v>
@@ -53108,19 +53108,19 @@
       <c r="U440" s="28"/>
       <c r="V440" s="28"/>
       <c r="W440" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X440" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X440" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y440" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z440" s="102"/>
       <c r="AA440" s="30"/>
       <c r="AB440" s="41"/>
       <c r="AC440" s="32" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="AD440" s="32"/>
       <c r="AE440" s="32"/>
@@ -53139,22 +53139,22 @@
     </row>
     <row r="441" spans="1:43" ht="15.75" customHeight="1">
       <c r="A441" s="458" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="B441" s="33" t="s">
         <v>430</v>
       </c>
       <c r="C441" s="268" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="D441" s="232"/>
       <c r="E441" s="58"/>
       <c r="F441" s="265" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="G441" s="32"/>
       <c r="H441" s="203" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="I441" s="190" t="s">
         <v>2498</v>
@@ -53163,17 +53163,17 @@
       <c r="K441" s="82"/>
       <c r="L441" s="82"/>
       <c r="M441" s="135" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="N441" s="134" t="s">
         <v>1234</v>
       </c>
       <c r="O441" s="397" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="P441" s="59"/>
       <c r="Q441" s="56" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="R441" s="32" t="s">
         <v>519</v>
@@ -53185,24 +53185,24 @@
       <c r="U441" s="120"/>
       <c r="V441" s="120"/>
       <c r="W441" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X441" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X441" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y441" s="30" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="Z441" s="197"/>
       <c r="AA441" s="30" t="s">
+        <v>3489</v>
+      </c>
+      <c r="AB441" s="31" t="s">
         <v>3490</v>
-      </c>
-      <c r="AB441" s="31" t="s">
-        <v>3491</v>
       </c>
       <c r="AC441" s="32"/>
       <c r="AD441" s="485" t="s">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="AE441" s="32"/>
       <c r="AF441" s="32"/>
@@ -53220,7 +53220,7 @@
     </row>
     <row r="442" spans="1:43" ht="15.75" customHeight="1">
       <c r="A442" s="458" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="B442" s="33" t="s">
         <v>430</v>
@@ -53231,54 +53231,54 @@
       <c r="D442" s="232"/>
       <c r="E442" s="58"/>
       <c r="F442" s="47" t="s">
+        <v>3492</v>
+      </c>
+      <c r="G442" s="32" t="s">
         <v>3493</v>
       </c>
-      <c r="G442" s="32" t="s">
+      <c r="H442" s="203" t="s">
         <v>3494</v>
       </c>
-      <c r="H442" s="203" t="s">
+      <c r="I442" s="185" t="s">
         <v>3495</v>
-      </c>
-      <c r="I442" s="185" t="s">
-        <v>3496</v>
       </c>
       <c r="J442" s="22"/>
       <c r="K442" s="22"/>
       <c r="L442" s="22"/>
       <c r="M442" s="135" t="s">
+        <v>3496</v>
+      </c>
+      <c r="N442" s="73" t="s">
         <v>3497</v>
-      </c>
-      <c r="N442" s="73" t="s">
-        <v>3498</v>
       </c>
       <c r="O442" s="73"/>
       <c r="P442" s="74" t="s">
+        <v>3498</v>
+      </c>
+      <c r="Q442" s="91" t="s">
         <v>3499</v>
       </c>
-      <c r="Q442" s="91" t="s">
-        <v>3500</v>
-      </c>
       <c r="R442" s="113" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="S442" s="113" t="s">
         <v>41</v>
       </c>
       <c r="T442" s="21"/>
       <c r="U442" s="28" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="V442" s="28" t="s">
+        <v>3499</v>
+      </c>
+      <c r="W442" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X442" s="111" t="s">
+        <v>3499</v>
+      </c>
+      <c r="Y442" s="30" t="s">
         <v>3500</v>
-      </c>
-      <c r="W442" s="111" t="s">
-        <v>3141</v>
-      </c>
-      <c r="X442" s="111" t="s">
-        <v>3500</v>
-      </c>
-      <c r="Y442" s="30" t="s">
-        <v>3501</v>
       </c>
       <c r="Z442" s="30"/>
       <c r="AA442" s="30"/>
@@ -53301,7 +53301,7 @@
     </row>
     <row r="443" spans="1:43" ht="15.75" customHeight="1">
       <c r="A443" s="458" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
       <c r="B443" s="33" t="s">
         <v>430</v>
@@ -53312,13 +53312,13 @@
       <c r="D443" s="232"/>
       <c r="E443" s="58"/>
       <c r="F443" s="265" t="s">
+        <v>3501</v>
+      </c>
+      <c r="G443" s="48" t="s">
         <v>3502</v>
       </c>
-      <c r="G443" s="48" t="s">
+      <c r="H443" s="95" t="s">
         <v>3503</v>
-      </c>
-      <c r="H443" s="95" t="s">
-        <v>3504</v>
       </c>
       <c r="I443" s="185" t="s">
         <v>2479</v>
@@ -53330,7 +53330,7 @@
         <v>651</v>
       </c>
       <c r="N443" s="65" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="O443" s="294"/>
       <c r="P443" s="124"/>
@@ -53345,13 +53345,13 @@
       <c r="U443" s="28"/>
       <c r="V443" s="28"/>
       <c r="W443" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X443" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X443" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y443" s="30" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="Z443" s="30"/>
       <c r="AA443" s="30"/>
@@ -53374,7 +53374,7 @@
     </row>
     <row r="444" spans="1:43" ht="15.75" customHeight="1">
       <c r="A444" s="458" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="B444" s="33" t="s">
         <v>430</v>
@@ -53385,11 +53385,11 @@
       <c r="D444" s="232"/>
       <c r="E444" s="58"/>
       <c r="F444" s="16" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="G444" s="32"/>
       <c r="H444" s="203" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="I444" s="185" t="s">
         <v>2538</v>
@@ -53398,20 +53398,20 @@
       <c r="K444" s="82"/>
       <c r="L444" s="82"/>
       <c r="M444" s="135" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="N444" s="38" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="O444" s="38"/>
       <c r="P444" s="74" t="s">
+        <v>3498</v>
+      </c>
+      <c r="Q444" s="26" t="s">
         <v>3499</v>
       </c>
-      <c r="Q444" s="26" t="s">
-        <v>3500</v>
-      </c>
       <c r="R444" s="33" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="S444" s="77" t="s">
         <v>41</v>
@@ -53443,7 +53443,7 @@
     </row>
     <row r="445" spans="1:43" ht="15.75" customHeight="1">
       <c r="A445" s="458" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="B445" s="33" t="s">
         <v>430</v>
@@ -53454,13 +53454,13 @@
       <c r="D445" s="244"/>
       <c r="E445" s="188"/>
       <c r="F445" s="189" t="s">
+        <v>3512</v>
+      </c>
+      <c r="G445" s="184" t="s">
         <v>3513</v>
       </c>
-      <c r="G445" s="184" t="s">
+      <c r="H445" s="48" t="s">
         <v>3514</v>
-      </c>
-      <c r="H445" s="48" t="s">
-        <v>3515</v>
       </c>
       <c r="I445" s="32" t="s">
         <v>2538</v>
@@ -53468,13 +53468,13 @@
       <c r="J445" s="98"/>
       <c r="K445" s="103"/>
       <c r="L445" s="107" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="M445" s="206" t="s">
         <v>476</v>
       </c>
       <c r="N445" s="38" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="O445" s="38"/>
       <c r="P445" s="25"/>
@@ -53487,24 +53487,24 @@
       </c>
       <c r="T445" s="21"/>
       <c r="U445" s="28" t="s">
+        <v>3465</v>
+      </c>
+      <c r="V445" s="28" t="s">
         <v>3466</v>
       </c>
-      <c r="V445" s="28" t="s">
-        <v>3467</v>
-      </c>
       <c r="W445" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X445" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X445" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y445" s="30" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="Z445" s="30"/>
       <c r="AA445" s="30"/>
       <c r="AB445" s="31" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="AC445" s="32"/>
       <c r="AD445" s="243"/>
@@ -53524,7 +53524,7 @@
     </row>
     <row r="446" spans="1:43" ht="15.75" customHeight="1">
       <c r="A446" s="458" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="B446" s="33" t="s">
         <v>430</v>
@@ -53535,13 +53535,13 @@
       <c r="D446" s="244"/>
       <c r="E446" s="188"/>
       <c r="F446" s="189" t="s">
+        <v>3520</v>
+      </c>
+      <c r="G446" s="184" t="s">
         <v>3521</v>
       </c>
-      <c r="G446" s="184" t="s">
+      <c r="H446" s="48" t="s">
         <v>3522</v>
-      </c>
-      <c r="H446" s="48" t="s">
-        <v>3523</v>
       </c>
       <c r="I446" s="32" t="s">
         <v>2538</v>
@@ -53549,13 +53549,13 @@
       <c r="J446" s="35"/>
       <c r="K446" s="107"/>
       <c r="L446" s="107" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="M446" s="206" t="s">
         <v>476</v>
       </c>
       <c r="N446" s="54" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="O446" s="54"/>
       <c r="P446" s="55"/>
@@ -53568,24 +53568,24 @@
       </c>
       <c r="T446" s="21"/>
       <c r="U446" s="28" t="s">
+        <v>3465</v>
+      </c>
+      <c r="V446" s="120" t="s">
         <v>3466</v>
       </c>
-      <c r="V446" s="120" t="s">
-        <v>3467</v>
-      </c>
       <c r="W446" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X446" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X446" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y446" s="30" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="Z446" s="30"/>
       <c r="AA446" s="30"/>
       <c r="AB446" s="41" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="AC446" s="32"/>
       <c r="AD446" s="486"/>
@@ -53605,7 +53605,7 @@
     </row>
     <row r="447" spans="1:43" ht="15.75" customHeight="1">
       <c r="A447" s="458" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
       <c r="B447" s="33" t="s">
         <v>430</v>
@@ -53616,17 +53616,17 @@
       <c r="D447" s="232"/>
       <c r="E447" s="58"/>
       <c r="F447" s="47" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="G447" s="32"/>
       <c r="H447" s="203" t="s">
+        <v>3528</v>
+      </c>
+      <c r="I447" s="190" t="s">
         <v>3529</v>
       </c>
-      <c r="I447" s="190" t="s">
+      <c r="J447" s="22" t="s">
         <v>3530</v>
-      </c>
-      <c r="J447" s="22" t="s">
-        <v>3531</v>
       </c>
       <c r="K447" s="22"/>
       <c r="L447" s="22"/>
@@ -53649,13 +53649,13 @@
       <c r="U447" s="120"/>
       <c r="V447" s="120"/>
       <c r="W447" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X447" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X447" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y447" s="30" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="Z447" s="30"/>
       <c r="AA447" s="30"/>
@@ -53678,7 +53678,7 @@
     </row>
     <row r="448" spans="1:43" ht="15.75" customHeight="1">
       <c r="A448" s="458" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
       <c r="B448" s="33" t="s">
         <v>430</v>
@@ -53689,17 +53689,17 @@
       <c r="D448" s="232"/>
       <c r="E448" s="58"/>
       <c r="F448" s="265" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="G448" s="32"/>
       <c r="H448" s="203" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="I448" s="32" t="s">
         <v>2119</v>
       </c>
       <c r="J448" s="82" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="K448" s="82"/>
       <c r="L448" s="82"/>
@@ -53707,7 +53707,7 @@
         <v>137</v>
       </c>
       <c r="N448" s="54" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="O448" s="54"/>
       <c r="P448" s="55"/>
@@ -53745,7 +53745,7 @@
     </row>
     <row r="449" spans="1:43" ht="15.75" customHeight="1">
       <c r="A449" s="458" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="B449" s="33" t="s">
         <v>430</v>
@@ -53756,11 +53756,11 @@
       <c r="D449" s="232"/>
       <c r="E449" s="58"/>
       <c r="F449" s="47" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="G449" s="32"/>
       <c r="H449" s="203" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="I449" s="190" t="s">
         <v>2538</v>
@@ -53768,13 +53768,13 @@
       <c r="J449" s="98"/>
       <c r="K449" s="103"/>
       <c r="L449" s="103" t="s">
+        <v>3539</v>
+      </c>
+      <c r="M449" s="135" t="s">
         <v>3540</v>
       </c>
-      <c r="M449" s="135" t="s">
+      <c r="N449" s="54" t="s">
         <v>3541</v>
-      </c>
-      <c r="N449" s="54" t="s">
-        <v>3542</v>
       </c>
       <c r="O449" s="54"/>
       <c r="P449" s="55"/>
@@ -53789,13 +53789,13 @@
       <c r="U449" s="120"/>
       <c r="V449" s="120"/>
       <c r="W449" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X449" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X449" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y449" s="30" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="Z449" s="30"/>
       <c r="AA449" s="30"/>
@@ -53818,7 +53818,7 @@
     </row>
     <row r="450" spans="1:43" ht="15.75" customHeight="1">
       <c r="A450" s="458" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="B450" s="33" t="s">
         <v>430</v>
@@ -53829,11 +53829,11 @@
       <c r="D450" s="232"/>
       <c r="E450" s="58"/>
       <c r="F450" s="265" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="G450" s="32"/>
       <c r="H450" s="184" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="I450" s="190" t="s">
         <v>2538</v>
@@ -53841,13 +53841,13 @@
       <c r="J450" s="98"/>
       <c r="K450" s="103"/>
       <c r="L450" s="107" t="s">
+        <v>3539</v>
+      </c>
+      <c r="M450" s="135" t="s">
         <v>3540</v>
       </c>
-      <c r="M450" s="135" t="s">
-        <v>3541</v>
-      </c>
       <c r="N450" s="73" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="O450" s="73"/>
       <c r="P450" s="74"/>
@@ -53862,13 +53862,13 @@
       <c r="U450" s="120"/>
       <c r="V450" s="120"/>
       <c r="W450" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X450" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X450" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y450" s="30" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="Z450" s="30"/>
       <c r="AA450" s="30"/>
@@ -53891,7 +53891,7 @@
     </row>
     <row r="451" spans="1:43" ht="15.75" customHeight="1">
       <c r="A451" s="458" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="B451" s="33" t="s">
         <v>430</v>
@@ -53902,13 +53902,13 @@
       <c r="D451" s="232"/>
       <c r="E451" s="58"/>
       <c r="F451" s="265" t="s">
+        <v>3547</v>
+      </c>
+      <c r="G451" s="32" t="s">
         <v>3548</v>
       </c>
-      <c r="G451" s="32" t="s">
+      <c r="H451" s="203" t="s">
         <v>3549</v>
-      </c>
-      <c r="H451" s="203" t="s">
-        <v>3550</v>
       </c>
       <c r="I451" s="190" t="s">
         <v>2538</v>
@@ -53916,13 +53916,13 @@
       <c r="J451" s="35"/>
       <c r="K451" s="107"/>
       <c r="L451" s="107" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="M451" s="77" t="s">
         <v>476</v>
       </c>
       <c r="N451" s="38" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="O451" s="38"/>
       <c r="P451" s="25"/>
@@ -53935,24 +53935,24 @@
       </c>
       <c r="T451" s="21"/>
       <c r="U451" s="28" t="s">
+        <v>3465</v>
+      </c>
+      <c r="V451" s="120" t="s">
         <v>3466</v>
       </c>
-      <c r="V451" s="120" t="s">
-        <v>3467</v>
-      </c>
       <c r="W451" s="111" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="X451" s="118" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="Y451" s="30" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="Z451" s="30"/>
       <c r="AA451" s="30"/>
       <c r="AB451" s="216" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="AC451" s="32"/>
       <c r="AD451" s="21"/>
@@ -53972,7 +53972,7 @@
     </row>
     <row r="452" spans="1:43" ht="15.75" customHeight="1">
       <c r="A452" s="458" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="B452" s="33" t="s">
         <v>430</v>
@@ -53983,11 +53983,11 @@
       <c r="D452" s="232"/>
       <c r="E452" s="58"/>
       <c r="F452" s="47" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="G452" s="32"/>
       <c r="H452" s="203" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="I452" s="190" t="s">
         <v>2538</v>
@@ -53996,10 +53996,10 @@
       <c r="K452" s="82"/>
       <c r="L452" s="82"/>
       <c r="M452" s="95" t="s">
+        <v>3555</v>
+      </c>
+      <c r="N452" s="89" t="s">
         <v>3556</v>
-      </c>
-      <c r="N452" s="89" t="s">
-        <v>3557</v>
       </c>
       <c r="O452" s="89"/>
       <c r="P452" s="90"/>
@@ -54037,7 +54037,7 @@
     </row>
     <row r="453" spans="1:43" ht="15.75" customHeight="1">
       <c r="A453" s="458" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="B453" s="33" t="s">
         <v>430</v>
@@ -54048,16 +54048,16 @@
       <c r="D453" s="232"/>
       <c r="E453" s="58"/>
       <c r="F453" s="265" t="s">
+        <v>3558</v>
+      </c>
+      <c r="G453" s="32" t="s">
         <v>3559</v>
       </c>
-      <c r="G453" s="32" t="s">
+      <c r="H453" s="48" t="s">
         <v>3560</v>
       </c>
-      <c r="H453" s="48" t="s">
+      <c r="I453" s="185" t="s">
         <v>3561</v>
-      </c>
-      <c r="I453" s="185" t="s">
-        <v>3562</v>
       </c>
       <c r="J453" s="22"/>
       <c r="K453" s="22"/>
@@ -54066,14 +54066,14 @@
         <v>798</v>
       </c>
       <c r="N453" s="134" t="s">
+        <v>3562</v>
+      </c>
+      <c r="O453" s="54" t="s">
         <v>3563</v>
-      </c>
-      <c r="O453" s="54" t="s">
-        <v>3564</v>
       </c>
       <c r="P453" s="55"/>
       <c r="Q453" s="56" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="R453" s="99" t="s">
         <v>1099</v>
@@ -54082,7 +54082,7 @@
         <v>41</v>
       </c>
       <c r="T453" s="119" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="U453" s="120"/>
       <c r="V453" s="120"/>
@@ -54110,7 +54110,7 @@
     </row>
     <row r="454" spans="1:43" ht="15.75" customHeight="1">
       <c r="A454" s="458" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="B454" s="33" t="s">
         <v>430</v>
@@ -54121,16 +54121,16 @@
       <c r="D454" s="232"/>
       <c r="E454" s="58"/>
       <c r="F454" s="265" t="s">
+        <v>3567</v>
+      </c>
+      <c r="G454" s="32" t="s">
         <v>3568</v>
       </c>
-      <c r="G454" s="32" t="s">
+      <c r="H454" s="95" t="s">
         <v>3569</v>
       </c>
-      <c r="H454" s="95" t="s">
-        <v>3570</v>
-      </c>
       <c r="I454" s="185" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="J454" s="22"/>
       <c r="K454" s="82"/>
@@ -54139,7 +54139,7 @@
         <v>798</v>
       </c>
       <c r="N454" s="134" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="O454" s="54"/>
       <c r="P454" s="55"/>
@@ -54154,13 +54154,13 @@
       <c r="U454" s="218"/>
       <c r="V454" s="218"/>
       <c r="W454" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X454" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X454" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y454" s="30" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="Z454" s="30"/>
       <c r="AA454" s="30"/>
@@ -54183,7 +54183,7 @@
     </row>
     <row r="455" spans="1:43" ht="15.75" customHeight="1">
       <c r="A455" s="458" t="s">
-        <v>3920</v>
+        <v>3919</v>
       </c>
       <c r="B455" s="95" t="s">
         <v>430</v>
@@ -54194,14 +54194,14 @@
       <c r="D455" s="232"/>
       <c r="E455" s="58"/>
       <c r="F455" s="265" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="G455" s="32"/>
       <c r="H455" s="190" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="I455" s="32" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="J455" s="22"/>
       <c r="K455" s="82"/>
@@ -54210,7 +54210,7 @@
         <v>184</v>
       </c>
       <c r="N455" s="38" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="O455" s="38"/>
       <c r="P455" s="25"/>
@@ -54225,18 +54225,18 @@
       <c r="U455" s="120"/>
       <c r="V455" s="120"/>
       <c r="W455" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X455" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X455" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y455" s="30" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="Z455" s="30"/>
       <c r="AA455" s="30"/>
       <c r="AB455" s="46" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="AC455" s="32"/>
       <c r="AD455" s="21"/>
@@ -54256,7 +54256,7 @@
     </row>
     <row r="456" spans="1:43" ht="15.75" customHeight="1">
       <c r="A456" s="458" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="B456" s="95" t="s">
         <v>2275</v>
@@ -54267,34 +54267,34 @@
       <c r="D456" s="232"/>
       <c r="E456" s="58"/>
       <c r="F456" s="265" t="s">
+        <v>3577</v>
+      </c>
+      <c r="G456" s="32" t="s">
         <v>3578</v>
       </c>
-      <c r="G456" s="32" t="s">
+      <c r="H456" s="33" t="s">
         <v>3579</v>
       </c>
-      <c r="H456" s="33" t="s">
+      <c r="I456" s="185" t="s">
+        <v>3031</v>
+      </c>
+      <c r="J456" s="22" t="s">
         <v>3580</v>
-      </c>
-      <c r="I456" s="185" t="s">
-        <v>3032</v>
-      </c>
-      <c r="J456" s="22" t="s">
-        <v>3581</v>
       </c>
       <c r="K456" s="22"/>
       <c r="L456" s="22"/>
       <c r="M456" s="113" t="s">
+        <v>3581</v>
+      </c>
+      <c r="N456" s="65" t="s">
         <v>3582</v>
       </c>
-      <c r="N456" s="65" t="s">
-        <v>3583</v>
-      </c>
       <c r="O456" s="38" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="P456" s="25"/>
       <c r="Q456" s="56" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="R456" s="94" t="s">
         <v>1099</v>
@@ -54306,13 +54306,13 @@
       <c r="U456" s="28"/>
       <c r="V456" s="28"/>
       <c r="W456" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X456" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X456" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y456" s="30" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="Z456" s="30"/>
       <c r="AA456" s="30"/>
@@ -54335,7 +54335,7 @@
     </row>
     <row r="457" spans="1:43" ht="15.75" customHeight="1">
       <c r="A457" s="458" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="B457" s="32" t="s">
         <v>430</v>
@@ -54346,11 +54346,11 @@
       <c r="D457" s="232"/>
       <c r="E457" s="58"/>
       <c r="F457" s="265" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="G457" s="32"/>
       <c r="H457" s="190" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="I457" s="190" t="s">
         <v>2498</v>
@@ -54364,14 +54364,14 @@
         <v>798</v>
       </c>
       <c r="N457" s="38" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="O457" s="38" t="s">
         <v>895</v>
       </c>
       <c r="P457" s="25"/>
       <c r="Q457" s="56" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="R457" s="39" t="s">
         <v>519</v>
@@ -54383,19 +54383,19 @@
       <c r="U457" s="28"/>
       <c r="V457" s="28"/>
       <c r="W457" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X457" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X457" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y457" s="30" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="Z457" s="30" t="s">
+        <v>3587</v>
+      </c>
+      <c r="AA457" s="30" t="s">
         <v>3588</v>
-      </c>
-      <c r="AA457" s="30" t="s">
-        <v>3589</v>
       </c>
       <c r="AB457" s="41"/>
       <c r="AC457" s="32"/>
@@ -54416,7 +54416,7 @@
     </row>
     <row r="458" spans="1:43" ht="15.75" customHeight="1">
       <c r="A458" s="458" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="B458" s="95" t="s">
         <v>2275</v>
@@ -54427,11 +54427,11 @@
       <c r="D458" s="232"/>
       <c r="E458" s="58"/>
       <c r="F458" s="16" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="G458" s="32"/>
       <c r="H458" s="32" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="I458" s="32" t="s">
         <v>2498</v>
@@ -54445,14 +54445,14 @@
         <v>651</v>
       </c>
       <c r="N458" s="65" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="O458" s="65" t="s">
         <v>895</v>
       </c>
       <c r="P458" s="25"/>
       <c r="Q458" s="56" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="R458" s="39" t="s">
         <v>519</v>
@@ -54464,19 +54464,19 @@
       <c r="U458" s="28"/>
       <c r="V458" s="28"/>
       <c r="W458" s="111" t="s">
+        <v>3242</v>
+      </c>
+      <c r="X458" s="118" t="s">
+        <v>3141</v>
+      </c>
+      <c r="Y458" s="30" t="s">
         <v>3243</v>
       </c>
-      <c r="X458" s="118" t="s">
-        <v>3142</v>
-      </c>
-      <c r="Y458" s="30" t="s">
-        <v>3244</v>
-      </c>
       <c r="Z458" s="30" t="s">
+        <v>3592</v>
+      </c>
+      <c r="AA458" s="30" t="s">
         <v>3593</v>
-      </c>
-      <c r="AA458" s="30" t="s">
-        <v>3594</v>
       </c>
       <c r="AB458" s="41"/>
       <c r="AC458" s="32"/>
@@ -54497,7 +54497,7 @@
     </row>
     <row r="459" spans="1:43" ht="15.75" customHeight="1">
       <c r="A459" s="458" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="B459" s="95" t="s">
         <v>2275</v>
@@ -54508,16 +54508,16 @@
       <c r="D459" s="233"/>
       <c r="E459" s="67"/>
       <c r="F459" s="16" t="s">
+        <v>3594</v>
+      </c>
+      <c r="G459" s="32" t="s">
         <v>3595</v>
       </c>
-      <c r="G459" s="32" t="s">
+      <c r="H459" s="32" t="s">
         <v>3596</v>
       </c>
-      <c r="H459" s="32" t="s">
+      <c r="I459" s="185" t="s">
         <v>3597</v>
-      </c>
-      <c r="I459" s="185" t="s">
-        <v>3598</v>
       </c>
       <c r="J459" s="22"/>
       <c r="K459" s="22"/>
@@ -54526,14 +54526,14 @@
         <v>2472</v>
       </c>
       <c r="N459" s="89" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="O459" s="89"/>
       <c r="P459" s="74" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="Q459" s="56" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="R459" s="96" t="s">
         <v>383</v>
@@ -54570,7 +54570,7 @@
     </row>
     <row r="460" spans="1:43" ht="15.75" customHeight="1">
       <c r="A460" s="458" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="B460" s="95" t="s">
         <v>2275</v>
@@ -54581,34 +54581,34 @@
       <c r="D460" s="232"/>
       <c r="E460" s="58"/>
       <c r="F460" s="265" t="s">
+        <v>3600</v>
+      </c>
+      <c r="G460" s="32" t="s">
         <v>3601</v>
       </c>
-      <c r="G460" s="32" t="s">
+      <c r="H460" s="203" t="s">
         <v>3602</v>
       </c>
-      <c r="H460" s="203" t="s">
+      <c r="I460" s="32" t="s">
         <v>3603</v>
-      </c>
-      <c r="I460" s="32" t="s">
-        <v>3604</v>
       </c>
       <c r="J460" s="22"/>
       <c r="K460" s="93" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="L460" s="82"/>
       <c r="M460" s="135" t="s">
         <v>651</v>
       </c>
       <c r="N460" s="134" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="O460" s="38" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="P460" s="55"/>
       <c r="Q460" s="56" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="R460" s="94" t="s">
         <v>1099</v>
@@ -54620,13 +54620,13 @@
       <c r="U460" s="28"/>
       <c r="V460" s="105"/>
       <c r="W460" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X460" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X460" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y460" s="30" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="Z460" s="30"/>
       <c r="AA460" s="30"/>
@@ -54649,43 +54649,43 @@
     </row>
     <row r="461" spans="1:43" ht="15.75" customHeight="1">
       <c r="A461" s="458" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="B461" s="95" t="s">
         <v>2275</v>
       </c>
       <c r="C461" s="246" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="D461" s="232"/>
       <c r="E461" s="58"/>
       <c r="F461" s="47" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="G461" s="32"/>
       <c r="H461" s="48" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="I461" s="185" t="s">
         <v>2498</v>
       </c>
       <c r="J461" s="107" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="K461" s="103"/>
       <c r="L461" s="103"/>
       <c r="M461" s="135" t="s">
+        <v>3611</v>
+      </c>
+      <c r="N461" s="134" t="s">
         <v>3612</v>
       </c>
-      <c r="N461" s="134" t="s">
+      <c r="O461" s="394" t="s">
         <v>3613</v>
-      </c>
-      <c r="O461" s="394" t="s">
-        <v>3614</v>
       </c>
       <c r="P461" s="112"/>
       <c r="Q461" s="56" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="R461" s="39" t="s">
         <v>519</v>
@@ -54695,13 +54695,13 @@
       <c r="U461" s="28"/>
       <c r="V461" s="28"/>
       <c r="W461" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X461" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X461" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y461" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="Z461" s="30"/>
       <c r="AA461" s="30"/>
@@ -54724,7 +54724,7 @@
     </row>
     <row r="462" spans="1:43" ht="15.75" customHeight="1">
       <c r="A462" s="458" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="B462" s="95" t="s">
         <v>2275</v>
@@ -54735,11 +54735,11 @@
       <c r="D462" s="232"/>
       <c r="E462" s="58"/>
       <c r="F462" s="47" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="G462" s="32"/>
       <c r="H462" s="184" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="I462" s="32" t="s">
         <v>2039</v>
@@ -54753,14 +54753,14 @@
         <v>677</v>
       </c>
       <c r="N462" s="89" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="O462" s="89"/>
       <c r="P462" s="74" t="s">
         <v>1602</v>
       </c>
       <c r="Q462" s="91" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="R462" s="305" t="s">
         <v>40</v>
@@ -54776,13 +54776,13 @@
         <v>189</v>
       </c>
       <c r="W462" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X462" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X462" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y462" s="30" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="Z462" s="30"/>
       <c r="AA462" s="30"/>
@@ -54805,7 +54805,7 @@
     </row>
     <row r="463" spans="1:43" ht="15.75" customHeight="1">
       <c r="A463" s="458" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B463" s="95" t="s">
         <v>2275</v>
@@ -54816,13 +54816,13 @@
       <c r="D463" s="233"/>
       <c r="E463" s="67"/>
       <c r="F463" s="16" t="s">
+        <v>3622</v>
+      </c>
+      <c r="G463" s="32" t="s">
         <v>3623</v>
       </c>
-      <c r="G463" s="32" t="s">
+      <c r="H463" s="32" t="s">
         <v>3624</v>
-      </c>
-      <c r="H463" s="32" t="s">
-        <v>3625</v>
       </c>
       <c r="I463" s="185" t="s">
         <v>2630</v>
@@ -54833,10 +54833,10 @@
       <c r="K463" s="22"/>
       <c r="L463" s="22"/>
       <c r="M463" s="113" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="N463" s="65" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="O463" s="83"/>
       <c r="P463" s="25"/>
@@ -54851,13 +54851,13 @@
       <c r="U463" s="120"/>
       <c r="V463" s="120"/>
       <c r="W463" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X463" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X463" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y463" s="30" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="Z463" s="30"/>
       <c r="AA463" s="30"/>
@@ -54880,10 +54880,10 @@
     </row>
     <row r="464" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
       <c r="A464" s="269" t="s">
+        <v>3626</v>
+      </c>
+      <c r="B464" s="270" t="s">
         <v>3627</v>
-      </c>
-      <c r="B464" s="270" t="s">
-        <v>3628</v>
       </c>
       <c r="C464" s="271" t="s">
         <v>171</v>
@@ -54891,16 +54891,16 @@
       <c r="D464" s="272"/>
       <c r="E464" s="273"/>
       <c r="F464" s="274" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="G464" s="274" t="s">
         <v>2277</v>
       </c>
       <c r="H464" s="274" t="s">
+        <v>3629</v>
+      </c>
+      <c r="I464" s="275" t="s">
         <v>3630</v>
-      </c>
-      <c r="I464" s="275" t="s">
-        <v>3631</v>
       </c>
       <c r="J464" s="380" t="s">
         <v>2265</v>
@@ -54911,13 +54911,13 @@
         <v>1595</v>
       </c>
       <c r="N464" s="277" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="O464" s="277"/>
       <c r="P464" s="278"/>
       <c r="Q464" s="279"/>
       <c r="R464" s="406" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="S464" s="280" t="s">
         <v>41</v>
@@ -54949,43 +54949,43 @@
     </row>
     <row r="465" spans="1:43" ht="15.75" customHeight="1">
       <c r="A465" s="463" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="B465" s="95" t="s">
         <v>2275</v>
       </c>
       <c r="C465" s="246" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="D465" s="232"/>
       <c r="E465" s="58"/>
       <c r="F465" s="47" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="G465" s="32"/>
       <c r="H465" s="48" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="I465" s="185" t="s">
         <v>2498</v>
       </c>
       <c r="J465" s="107" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="K465" s="107"/>
       <c r="L465" s="107"/>
       <c r="M465" s="135" t="s">
+        <v>3637</v>
+      </c>
+      <c r="N465" s="54" t="s">
         <v>3638</v>
       </c>
-      <c r="N465" s="54" t="s">
+      <c r="O465" s="54" t="s">
         <v>3639</v>
-      </c>
-      <c r="O465" s="54" t="s">
-        <v>3640</v>
       </c>
       <c r="P465" s="55"/>
       <c r="Q465" s="56" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="R465" s="39" t="s">
         <v>519</v>
@@ -54999,13 +54999,13 @@
       <c r="W465" s="111"/>
       <c r="X465" s="111"/>
       <c r="Y465" s="30" t="s">
+        <v>3641</v>
+      </c>
+      <c r="Z465" s="30" t="s">
         <v>3642</v>
       </c>
-      <c r="Z465" s="30" t="s">
+      <c r="AA465" s="30" t="s">
         <v>3643</v>
-      </c>
-      <c r="AA465" s="30" t="s">
-        <v>3644</v>
       </c>
       <c r="AB465" s="41"/>
       <c r="AC465" s="32"/>
@@ -55026,7 +55026,7 @@
     </row>
     <row r="466" spans="1:43" ht="15.75" customHeight="1">
       <c r="A466" s="458" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="B466" s="95" t="s">
         <v>430</v>
@@ -55037,13 +55037,13 @@
       <c r="D466" s="232"/>
       <c r="E466" s="58"/>
       <c r="F466" s="47" t="s">
+        <v>3644</v>
+      </c>
+      <c r="G466" s="32" t="s">
         <v>3645</v>
       </c>
-      <c r="G466" s="32" t="s">
+      <c r="H466" s="95" t="s">
         <v>3646</v>
-      </c>
-      <c r="H466" s="95" t="s">
-        <v>3647</v>
       </c>
       <c r="I466" s="185" t="s">
         <v>2630</v>
@@ -55051,20 +55051,20 @@
       <c r="J466" s="93"/>
       <c r="K466" s="22"/>
       <c r="L466" s="22" t="s">
+        <v>3647</v>
+      </c>
+      <c r="M466" s="135" t="s">
         <v>3648</v>
       </c>
-      <c r="M466" s="135" t="s">
+      <c r="N466" s="134" t="s">
         <v>3649</v>
       </c>
-      <c r="N466" s="134" t="s">
-        <v>3650</v>
-      </c>
       <c r="O466" s="38" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="P466" s="55"/>
       <c r="Q466" s="56" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="R466" s="94" t="s">
         <v>1099</v>
@@ -55074,13 +55074,13 @@
       <c r="U466" s="28"/>
       <c r="V466" s="28"/>
       <c r="W466" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X466" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X466" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y466" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z466" s="30"/>
       <c r="AA466" s="30"/>
@@ -55103,50 +55103,50 @@
     </row>
     <row r="467" spans="1:43" ht="15.75" customHeight="1">
       <c r="A467" s="464" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="B467" s="95" t="s">
         <v>430</v>
       </c>
       <c r="C467" s="253" t="s">
+        <v>3650</v>
+      </c>
+      <c r="D467" s="231" t="s">
         <v>3651</v>
       </c>
-      <c r="D467" s="231" t="s">
+      <c r="E467" s="58" t="s">
         <v>3652</v>
       </c>
-      <c r="E467" s="58" t="s">
+      <c r="F467" s="220" t="s">
         <v>3653</v>
       </c>
-      <c r="F467" s="220" t="s">
+      <c r="G467" s="16" t="s">
+        <v>3650</v>
+      </c>
+      <c r="H467" s="204" t="s">
         <v>3654</v>
       </c>
-      <c r="G467" s="16" t="s">
-        <v>3651</v>
-      </c>
-      <c r="H467" s="204" t="s">
+      <c r="I467" s="185" t="s">
         <v>3655</v>
-      </c>
-      <c r="I467" s="185" t="s">
-        <v>3656</v>
       </c>
       <c r="J467" s="22"/>
       <c r="K467" s="22"/>
       <c r="L467" s="22"/>
       <c r="M467" s="135" t="s">
+        <v>3656</v>
+      </c>
+      <c r="N467" s="38" t="s">
         <v>3657</v>
-      </c>
-      <c r="N467" s="38" t="s">
-        <v>3658</v>
       </c>
       <c r="O467" s="38"/>
       <c r="P467" s="25" t="s">
+        <v>3658</v>
+      </c>
+      <c r="Q467" s="56" t="s">
         <v>3659</v>
       </c>
-      <c r="Q467" s="56" t="s">
-        <v>3660</v>
-      </c>
       <c r="R467" s="94" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="S467" s="77" t="s">
         <v>41</v>
@@ -55178,7 +55178,7 @@
     </row>
     <row r="468" spans="1:43" ht="15.75" customHeight="1">
       <c r="A468" s="458" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="B468" s="95" t="s">
         <v>2275</v>
@@ -55189,13 +55189,13 @@
       <c r="D468" s="233"/>
       <c r="E468" s="67"/>
       <c r="F468" s="265" t="s">
+        <v>3661</v>
+      </c>
+      <c r="G468" s="32" t="s">
         <v>3662</v>
       </c>
-      <c r="G468" s="32" t="s">
+      <c r="H468" s="95" t="s">
         <v>3663</v>
-      </c>
-      <c r="H468" s="95" t="s">
-        <v>3664</v>
       </c>
       <c r="I468" s="185" t="s">
         <v>2630</v>
@@ -55207,7 +55207,7 @@
         <v>1978</v>
       </c>
       <c r="N468" s="65" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="O468" s="38"/>
       <c r="P468" s="25"/>
@@ -55222,18 +55222,18 @@
       <c r="U468" s="28"/>
       <c r="V468" s="28"/>
       <c r="W468" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X468" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X468" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y468" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="Z468" s="30"/>
       <c r="AA468" s="30"/>
       <c r="AB468" s="46" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="AC468" s="32"/>
       <c r="AD468" s="32"/>
@@ -55253,28 +55253,28 @@
     </row>
     <row r="469" spans="1:43" ht="15.75" customHeight="1">
       <c r="A469" s="458" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="B469" s="95" t="s">
         <v>2275</v>
       </c>
       <c r="C469" s="247" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="D469" s="232"/>
       <c r="E469" s="58"/>
       <c r="F469" s="265" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="G469" s="32"/>
       <c r="H469" s="48" t="s">
+        <v>3668</v>
+      </c>
+      <c r="I469" s="185" t="s">
         <v>3669</v>
       </c>
-      <c r="I469" s="185" t="s">
+      <c r="J469" s="107" t="s">
         <v>3670</v>
-      </c>
-      <c r="J469" s="107" t="s">
-        <v>3671</v>
       </c>
       <c r="K469" s="107"/>
       <c r="L469" s="107"/>
@@ -55282,13 +55282,13 @@
         <v>137</v>
       </c>
       <c r="N469" s="38" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="O469" s="294"/>
       <c r="P469" s="124"/>
       <c r="Q469" s="56"/>
       <c r="R469" s="36" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="S469" s="77" t="s">
         <v>41</v>
@@ -55297,19 +55297,19 @@
       <c r="U469" s="28"/>
       <c r="V469" s="28"/>
       <c r="W469" s="110" t="s">
+        <v>3673</v>
+      </c>
+      <c r="X469" s="29" t="s">
         <v>3674</v>
       </c>
-      <c r="X469" s="29" t="s">
+      <c r="Y469" s="30" t="s">
         <v>3675</v>
-      </c>
-      <c r="Y469" s="30" t="s">
-        <v>3676</v>
       </c>
       <c r="Z469" s="30"/>
       <c r="AA469" s="30"/>
       <c r="AB469" s="31"/>
       <c r="AC469" s="69" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="AD469" s="21"/>
       <c r="AE469" s="32"/>
@@ -55328,7 +55328,7 @@
     </row>
     <row r="470" spans="1:43" ht="15.75" customHeight="1">
       <c r="A470" s="458" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="B470" s="95" t="s">
         <v>430</v>
@@ -55339,16 +55339,16 @@
       <c r="D470" s="233"/>
       <c r="E470" s="67"/>
       <c r="F470" s="265" t="s">
+        <v>3677</v>
+      </c>
+      <c r="G470" s="374" t="s">
         <v>3678</v>
       </c>
-      <c r="G470" s="374" t="s">
+      <c r="H470" s="48" t="s">
         <v>3679</v>
       </c>
-      <c r="H470" s="48" t="s">
+      <c r="I470" s="185" t="s">
         <v>3680</v>
-      </c>
-      <c r="I470" s="185" t="s">
-        <v>3681</v>
       </c>
       <c r="J470" s="22"/>
       <c r="K470" s="22"/>
@@ -55357,17 +55357,17 @@
         <v>2472</v>
       </c>
       <c r="N470" s="54" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="O470" s="54"/>
       <c r="P470" s="74" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="Q470" s="56" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="R470" s="48" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="S470" s="77" t="s">
         <v>41</v>
@@ -55399,7 +55399,7 @@
     </row>
     <row r="471" spans="1:43" ht="15.75" customHeight="1">
       <c r="A471" s="458" t="s">
-        <v>3683</v>
+        <v>3682</v>
       </c>
       <c r="B471" s="95" t="s">
         <v>430</v>
@@ -55410,13 +55410,13 @@
       <c r="D471" s="232"/>
       <c r="E471" s="58"/>
       <c r="F471" s="47" t="s">
+        <v>3683</v>
+      </c>
+      <c r="G471" s="39" t="s">
         <v>3684</v>
       </c>
-      <c r="G471" s="39" t="s">
+      <c r="H471" s="95" t="s">
         <v>3685</v>
-      </c>
-      <c r="H471" s="95" t="s">
-        <v>3686</v>
       </c>
       <c r="I471" s="185" t="s">
         <v>2630</v>
@@ -55424,13 +55424,13 @@
       <c r="J471" s="82"/>
       <c r="K471" s="82"/>
       <c r="L471" s="82" t="s">
-        <v>3687</v>
+        <v>3686</v>
       </c>
       <c r="M471" s="135" t="s">
         <v>798</v>
       </c>
       <c r="N471" s="65" t="s">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="O471" s="38"/>
       <c r="P471" s="25"/>
@@ -55445,13 +55445,13 @@
       <c r="U471" s="28"/>
       <c r="V471" s="28"/>
       <c r="W471" s="29" t="s">
+        <v>3688</v>
+      </c>
+      <c r="X471" s="29" t="s">
         <v>3689</v>
       </c>
-      <c r="X471" s="29" t="s">
+      <c r="Y471" s="30" t="s">
         <v>3690</v>
-      </c>
-      <c r="Y471" s="30" t="s">
-        <v>3691</v>
       </c>
       <c r="Z471" s="30"/>
       <c r="AA471" s="30"/>
@@ -55474,36 +55474,36 @@
     </row>
     <row r="472" spans="1:43" ht="15.75" customHeight="1">
       <c r="A472" s="458" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="B472" s="95" t="s">
         <v>2275</v>
       </c>
       <c r="C472" s="268" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="D472" s="232"/>
       <c r="E472" s="58"/>
       <c r="F472" s="265" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="G472" s="39"/>
       <c r="H472" s="48" t="s">
+        <v>3692</v>
+      </c>
+      <c r="I472" s="113" t="s">
         <v>3693</v>
-      </c>
-      <c r="I472" s="113" t="s">
-        <v>3694</v>
       </c>
       <c r="J472" s="82"/>
       <c r="K472" s="82"/>
       <c r="L472" s="82" t="s">
+        <v>3694</v>
+      </c>
+      <c r="M472" s="32" t="s">
         <v>3695</v>
       </c>
-      <c r="M472" s="32" t="s">
+      <c r="N472" s="38" t="s">
         <v>3696</v>
-      </c>
-      <c r="N472" s="38" t="s">
-        <v>3697</v>
       </c>
       <c r="O472" s="38"/>
       <c r="P472" s="25"/>
@@ -55541,7 +55541,7 @@
     </row>
     <row r="473" spans="1:43" ht="15.75" customHeight="1">
       <c r="A473" s="465" t="s">
-        <v>3698</v>
+        <v>3697</v>
       </c>
       <c r="B473" s="95" t="s">
         <v>2275</v>
@@ -55552,27 +55552,27 @@
       <c r="D473" s="233"/>
       <c r="E473" s="67"/>
       <c r="F473" s="300" t="s">
+        <v>3698</v>
+      </c>
+      <c r="G473" s="39" t="s">
         <v>3699</v>
       </c>
-      <c r="G473" s="39" t="s">
+      <c r="H473" s="374" t="s">
         <v>3700</v>
-      </c>
-      <c r="H473" s="374" t="s">
-        <v>3701</v>
       </c>
       <c r="I473" s="377" t="s">
         <v>2630</v>
       </c>
       <c r="J473" s="82" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="K473" s="82"/>
       <c r="L473" s="82"/>
       <c r="M473" s="303" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="N473" s="392" t="s">
-        <v>3702</v>
+        <v>3701</v>
       </c>
       <c r="O473" s="294"/>
       <c r="P473" s="124"/>
@@ -55610,7 +55610,7 @@
     </row>
     <row r="474" spans="1:43" ht="15.75" customHeight="1">
       <c r="A474" s="458" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="B474" s="95" t="s">
         <v>2275</v>
@@ -55621,11 +55621,11 @@
       <c r="D474" s="232"/>
       <c r="E474" s="58"/>
       <c r="F474" s="265" t="s">
-        <v>3703</v>
+        <v>3702</v>
       </c>
       <c r="G474" s="39"/>
       <c r="H474" s="203" t="s">
-        <v>3704</v>
+        <v>3703</v>
       </c>
       <c r="I474" s="190" t="s">
         <v>2498</v>
@@ -55639,7 +55639,7 @@
         <v>798</v>
       </c>
       <c r="N474" s="38" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="O474" s="38" t="s">
         <v>800</v>
@@ -55661,10 +55661,10 @@
       <c r="X474" s="29"/>
       <c r="Y474" s="30"/>
       <c r="Z474" s="30" t="s">
+        <v>3705</v>
+      </c>
+      <c r="AA474" s="30" t="s">
         <v>3706</v>
-      </c>
-      <c r="AA474" s="30" t="s">
-        <v>3707</v>
       </c>
       <c r="AB474" s="41"/>
       <c r="AC474" s="32"/>
@@ -55685,7 +55685,7 @@
     </row>
     <row r="475" spans="1:43" ht="15.75" customHeight="1">
       <c r="A475" s="458" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="B475" s="95" t="s">
         <v>2275</v>
@@ -55696,14 +55696,14 @@
       <c r="D475" s="232"/>
       <c r="E475" s="58"/>
       <c r="F475" s="265" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
       <c r="G475" s="32"/>
       <c r="H475" s="48" t="s">
+        <v>3708</v>
+      </c>
+      <c r="I475" s="185" t="s">
         <v>3709</v>
-      </c>
-      <c r="I475" s="185" t="s">
-        <v>3710</v>
       </c>
       <c r="J475" s="22"/>
       <c r="K475" s="22"/>
@@ -55712,14 +55712,14 @@
         <v>1612</v>
       </c>
       <c r="N475" s="38" t="s">
+        <v>3710</v>
+      </c>
+      <c r="O475" s="38" t="s">
         <v>3711</v>
-      </c>
-      <c r="O475" s="38" t="s">
-        <v>3712</v>
       </c>
       <c r="P475" s="25"/>
       <c r="Q475" s="26" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="R475" s="32" t="s">
         <v>519</v>
@@ -55731,19 +55731,19 @@
       <c r="U475" s="105"/>
       <c r="V475" s="28"/>
       <c r="W475" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X475" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X475" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y475" s="30" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="Z475" s="30" t="s">
+        <v>3713</v>
+      </c>
+      <c r="AA475" s="30" t="s">
         <v>3714</v>
-      </c>
-      <c r="AA475" s="30" t="s">
-        <v>3715</v>
       </c>
       <c r="AB475" s="41"/>
       <c r="AC475" s="32"/>
@@ -55764,40 +55764,40 @@
     </row>
     <row r="476" spans="1:43" ht="15.75" customHeight="1">
       <c r="A476" s="466" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="B476" s="95" t="s">
         <v>2275</v>
       </c>
       <c r="C476" s="253" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="D476" s="232"/>
       <c r="E476" s="58"/>
       <c r="F476" s="16" t="s">
+        <v>3717</v>
+      </c>
+      <c r="G476" s="32" t="s">
         <v>3718</v>
       </c>
-      <c r="G476" s="32" t="s">
+      <c r="H476" s="95" t="s">
         <v>3719</v>
       </c>
-      <c r="H476" s="95" t="s">
+      <c r="I476" s="185" t="s">
         <v>3720</v>
       </c>
-      <c r="I476" s="185" t="s">
-        <v>3721</v>
-      </c>
       <c r="J476" s="22" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="K476" s="93" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="L476" s="22"/>
       <c r="M476" s="303" t="s">
+        <v>3721</v>
+      </c>
+      <c r="N476" s="65" t="s">
         <v>3722</v>
-      </c>
-      <c r="N476" s="65" t="s">
-        <v>3723</v>
       </c>
       <c r="O476" s="38"/>
       <c r="P476" s="25"/>
@@ -55809,23 +55809,23 @@
         <v>41</v>
       </c>
       <c r="T476" s="21" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
       <c r="U476" s="28"/>
       <c r="V476" s="28"/>
       <c r="W476" s="29" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X476" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X476" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y476" s="30" t="s">
-        <v>3725</v>
+        <v>3724</v>
       </c>
       <c r="Z476" s="30"/>
       <c r="AA476" s="30"/>
       <c r="AB476" s="31" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
       <c r="AC476" s="32"/>
       <c r="AD476" s="32"/>
@@ -55845,7 +55845,7 @@
     </row>
     <row r="477" spans="1:43" ht="15.75" customHeight="1">
       <c r="A477" s="458" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
       <c r="B477" s="95" t="s">
         <v>2275</v>
@@ -55856,27 +55856,27 @@
       <c r="D477" s="233"/>
       <c r="E477" s="58"/>
       <c r="F477" s="47" t="s">
+        <v>3727</v>
+      </c>
+      <c r="G477" s="32" t="s">
         <v>3728</v>
       </c>
-      <c r="G477" s="32" t="s">
+      <c r="H477" s="95" t="s">
         <v>3729</v>
-      </c>
-      <c r="H477" s="95" t="s">
-        <v>3730</v>
       </c>
       <c r="I477" s="185" t="s">
         <v>2630</v>
       </c>
       <c r="J477" s="22" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="K477" s="22"/>
       <c r="L477" s="22"/>
       <c r="M477" s="135" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="N477" s="134" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="O477" s="54"/>
       <c r="P477" s="55"/>
@@ -55888,23 +55888,23 @@
         <v>41</v>
       </c>
       <c r="T477" s="21" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
       <c r="U477" s="28"/>
       <c r="V477" s="28"/>
       <c r="W477" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X477" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X477" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y477" s="30" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="Z477" s="30"/>
       <c r="AA477" s="30"/>
       <c r="AB477" s="46" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
       <c r="AC477" s="32"/>
       <c r="AD477" s="32"/>
@@ -55924,7 +55924,7 @@
     </row>
     <row r="478" spans="1:43" ht="15.75" customHeight="1">
       <c r="A478" s="458" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
       <c r="B478" s="95" t="s">
         <v>2275</v>
@@ -55935,27 +55935,27 @@
       <c r="D478" s="233"/>
       <c r="E478" s="58"/>
       <c r="F478" s="300" t="s">
+        <v>3735</v>
+      </c>
+      <c r="G478" s="32" t="s">
         <v>3736</v>
       </c>
-      <c r="G478" s="32" t="s">
+      <c r="H478" s="95" t="s">
         <v>3737</v>
       </c>
-      <c r="H478" s="95" t="s">
+      <c r="I478" s="185" t="s">
         <v>3738</v>
-      </c>
-      <c r="I478" s="185" t="s">
-        <v>3739</v>
       </c>
       <c r="J478" s="22"/>
       <c r="K478" s="93" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="L478" s="22"/>
       <c r="M478" s="209" t="s">
         <v>2721</v>
       </c>
       <c r="N478" s="134" t="s">
-        <v>3740</v>
+        <v>3739</v>
       </c>
       <c r="O478" s="54"/>
       <c r="P478" s="55"/>
@@ -55967,18 +55967,18 @@
         <v>41</v>
       </c>
       <c r="T478" s="21" t="s">
-        <v>3741</v>
+        <v>3740</v>
       </c>
       <c r="U478" s="28"/>
       <c r="V478" s="28"/>
       <c r="W478" s="111" t="s">
+        <v>3140</v>
+      </c>
+      <c r="X478" s="118" t="s">
         <v>3141</v>
       </c>
-      <c r="X478" s="118" t="s">
-        <v>3142</v>
-      </c>
       <c r="Y478" s="30" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
       <c r="Z478" s="30"/>
       <c r="AA478" s="30"/>
@@ -56001,33 +56001,33 @@
     </row>
     <row r="479" spans="1:43" ht="15.75" customHeight="1">
       <c r="A479" s="466" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
       <c r="B479" s="95" t="s">
         <v>2275</v>
       </c>
       <c r="C479" s="246" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
       <c r="D479" s="232"/>
       <c r="E479" s="136"/>
       <c r="F479" s="47" t="s">
-        <v>3745</v>
+        <v>3744</v>
       </c>
       <c r="G479" s="32"/>
       <c r="H479" s="48" t="s">
+        <v>3745</v>
+      </c>
+      <c r="I479" s="113" t="s">
         <v>3746</v>
       </c>
-      <c r="I479" s="113" t="s">
+      <c r="J479" s="22" t="s">
         <v>3747</v>
-      </c>
-      <c r="J479" s="22" t="s">
-        <v>3748</v>
       </c>
       <c r="K479" s="22"/>
       <c r="L479" s="22"/>
       <c r="M479" s="135" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="N479" s="54" t="s">
         <v>2122</v>
@@ -56042,7 +56042,7 @@
         <v>41</v>
       </c>
       <c r="T479" s="21" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="U479" s="28"/>
       <c r="V479" s="28"/>
@@ -56070,7 +56070,7 @@
     </row>
     <row r="480" spans="1:43" ht="54" customHeight="1">
       <c r="A480" s="467" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
       <c r="B480" s="95" t="s">
         <v>2275</v>
@@ -56081,27 +56081,27 @@
       <c r="D480" s="233"/>
       <c r="E480" s="58"/>
       <c r="F480" s="47" t="s">
+        <v>3751</v>
+      </c>
+      <c r="G480" s="32" t="s">
         <v>3752</v>
       </c>
-      <c r="G480" s="32" t="s">
+      <c r="H480" s="48" t="s">
         <v>3753</v>
-      </c>
-      <c r="H480" s="48" t="s">
-        <v>3754</v>
       </c>
       <c r="I480" s="32" t="s">
         <v>2630</v>
       </c>
       <c r="J480" s="22"/>
       <c r="K480" s="22" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="L480" s="22"/>
       <c r="M480" s="32" t="s">
         <v>2210</v>
       </c>
       <c r="N480" s="65" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="O480" s="38"/>
       <c r="P480" s="25"/>
@@ -56113,7 +56113,7 @@
         <v>41</v>
       </c>
       <c r="T480" s="21" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="U480" s="28"/>
       <c r="V480" s="28"/>

--- a/indexation-estampes.xlsx
+++ b/indexation-estampes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annepiejus/Documents/Projets:Travaux/MERCURE GALANT/MG ÉDITIONS/mercure-galant-sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11AAE16-9EEB-4C48-A8D6-72CCF256A919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7F2E51-6548-CC4C-858B-0E0A4E5AC364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -528,10 +528,18 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>Numéro pas disponible dans Gallica au 20 ; 05 ; 21 ; BNF, 8-LC2-34 tome 9 p. 320 ; cliché Mazarine
-	-Anne Piéjus</t>
+          <t xml:space="preserve">Numéro pas disponible dans Gallica au 20 ; 05 ; 21 ; BNF, 8-LC2-34 tome 9 p. 320 ; cliché Mazarine
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Anne Piéjus</t>
         </r>
       </text>
     </comment>
@@ -12956,9 +12964,6 @@
     <t>[Médaille représentant Guillaume d'Orange]*</t>
   </si>
   <si>
-    <t>médaille ; mulet ; épée ; chêne ; Absalom</t>
-  </si>
-  <si>
     <t>aae46a2c-35ad-44ab-8713-42db5eefcc4e</t>
   </si>
   <si>
@@ -17474,6 +17479,9 @@
   </si>
   <si>
     <t>Présentation au roi de l'estampe représentant l'obélisque d'Arles</t>
+  </si>
+  <si>
+    <t>médaille ; mulet ; épée ; chêne ; Absalon</t>
   </si>
 </sst>
 </file>
@@ -20608,7 +20616,7 @@
     </row>
     <row r="2" spans="1:43" ht="15.75" customHeight="1">
       <c r="A2" s="441" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>30</v>
@@ -20768,7 +20776,7 @@
         <v>57</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="F4" s="34" t="s">
         <v>58</v>
@@ -20816,7 +20824,7 @@
       <c r="W4" s="29"/>
       <c r="X4" s="29"/>
       <c r="Y4" s="30" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="Z4" s="30"/>
       <c r="AA4" s="30"/>
@@ -20843,7 +20851,7 @@
     </row>
     <row r="5" spans="1:43" ht="15.75" customHeight="1">
       <c r="A5" s="441" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>71</v>
@@ -20918,7 +20926,7 @@
     </row>
     <row r="6" spans="1:43" ht="15.75" customHeight="1">
       <c r="A6" s="441" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>43</v>
@@ -21068,7 +21076,7 @@
     </row>
     <row r="8" spans="1:43" ht="15.75" customHeight="1">
       <c r="A8" s="441" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>99</v>
@@ -21214,7 +21222,7 @@
     </row>
     <row r="10" spans="1:43" ht="15.75" customHeight="1">
       <c r="A10" s="441" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>99</v>
@@ -21366,7 +21374,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="248" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="D12" s="233"/>
       <c r="E12" s="67"/>
@@ -21437,7 +21445,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="248" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="D13" s="232"/>
       <c r="E13" s="58"/>
@@ -21644,13 +21652,13 @@
     </row>
     <row r="16" spans="1:43" ht="15.75" customHeight="1">
       <c r="A16" s="453" t="s">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="B16" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="261" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="D16" s="231" t="s">
         <v>178</v>
@@ -21704,7 +21712,7 @@
         <v>190</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="Z16" s="30"/>
       <c r="AA16" s="30"/>
@@ -21731,13 +21739,13 @@
     </row>
     <row r="17" spans="1:43" ht="15.75" customHeight="1">
       <c r="A17" s="99" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="B17" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="263" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="D17" s="231" t="s">
         <v>178</v>
@@ -21818,7 +21826,7 @@
     </row>
     <row r="18" spans="1:43" ht="15.75" customHeight="1">
       <c r="A18" s="99" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="B18" s="87" t="s">
         <v>200</v>
@@ -21905,7 +21913,7 @@
     </row>
     <row r="19" spans="1:43" ht="15.75" customHeight="1">
       <c r="A19" s="99" t="s">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="B19" s="32" t="s">
         <v>43</v>
@@ -21992,7 +22000,7 @@
     </row>
     <row r="20" spans="1:43" ht="15.75" customHeight="1">
       <c r="A20" s="99" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="B20" s="32" t="s">
         <v>43</v>
@@ -22077,7 +22085,7 @@
     </row>
     <row r="21" spans="1:43" ht="15.75" customHeight="1">
       <c r="A21" s="99" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="B21" s="32" t="s">
         <v>43</v>
@@ -22308,7 +22316,7 @@
     </row>
     <row r="24" spans="1:43" ht="15.75" customHeight="1">
       <c r="A24" s="441" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="B24" s="32" t="s">
         <v>245</v>
@@ -22377,7 +22385,7 @@
     </row>
     <row r="25" spans="1:43" ht="15.75" customHeight="1">
       <c r="A25" s="441" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="B25" s="32" t="s">
         <v>245</v>
@@ -22446,7 +22454,7 @@
     </row>
     <row r="26" spans="1:43" ht="15.75" customHeight="1">
       <c r="A26" s="441" t="s">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="B26" s="32" t="s">
         <v>245</v>
@@ -22525,7 +22533,7 @@
     </row>
     <row r="27" spans="1:43" ht="15.75" customHeight="1">
       <c r="A27" s="441" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="B27" s="33" t="s">
         <v>276</v>
@@ -22600,7 +22608,7 @@
     </row>
     <row r="28" spans="1:43" ht="15.75" customHeight="1">
       <c r="A28" s="441" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="B28" s="33" t="s">
         <v>289</v>
@@ -22612,7 +22620,7 @@
         <v>278</v>
       </c>
       <c r="E28" s="99" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>290</v>
@@ -22681,13 +22689,13 @@
     </row>
     <row r="29" spans="1:43" ht="15.75" customHeight="1">
       <c r="A29" s="441" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>289</v>
       </c>
       <c r="C29" s="247" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="D29" s="229"/>
       <c r="E29" s="443"/>
@@ -22754,7 +22762,7 @@
     </row>
     <row r="30" spans="1:43" ht="15.75" customHeight="1">
       <c r="A30" s="441" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="B30" s="32" t="s">
         <v>306</v>
@@ -22835,7 +22843,7 @@
         <v>289</v>
       </c>
       <c r="C31" s="247" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="D31" s="229"/>
       <c r="E31" s="443"/>
@@ -22900,19 +22908,19 @@
     </row>
     <row r="32" spans="1:43" ht="15.75" customHeight="1">
       <c r="A32" s="441" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="B32" s="95" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="248" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="D32" s="231" t="s">
         <v>277</v>
       </c>
       <c r="E32" s="99" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>321</v>
@@ -22981,19 +22989,19 @@
     </row>
     <row r="33" spans="1:43" ht="15.75" customHeight="1">
       <c r="A33" s="441" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="248" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="D33" s="231" t="s">
         <v>277</v>
       </c>
       <c r="E33" s="99" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="F33" s="16" t="s">
         <v>327</v>
@@ -23062,13 +23070,13 @@
     </row>
     <row r="34" spans="1:43" ht="15.75" customHeight="1">
       <c r="A34" s="441" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="247" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="D34" s="232"/>
       <c r="E34" s="58"/>
@@ -23212,7 +23220,7 @@
     </row>
     <row r="36" spans="1:43" ht="15.75" customHeight="1">
       <c r="A36" s="441" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>43</v>
@@ -23221,7 +23229,7 @@
         <v>354</v>
       </c>
       <c r="D36" s="232" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="E36" s="58"/>
       <c r="F36" s="32" t="s">
@@ -23259,7 +23267,7 @@
         <v>41</v>
       </c>
       <c r="T36" s="21" t="s">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="U36" s="28"/>
       <c r="V36" s="28"/>
@@ -23293,7 +23301,7 @@
     </row>
     <row r="37" spans="1:43" ht="15.75" customHeight="1">
       <c r="A37" s="441" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>43</v>
@@ -23338,7 +23346,7 @@
         <v>41</v>
       </c>
       <c r="T37" s="21" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="U37" s="28"/>
       <c r="V37" s="28"/>
@@ -23372,7 +23380,7 @@
         <v>372</v>
       </c>
       <c r="C38" s="247" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="D38" s="232"/>
       <c r="E38" s="58"/>
@@ -23407,7 +23415,7 @@
         <v>41</v>
       </c>
       <c r="T38" s="21" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="U38" s="28"/>
       <c r="V38" s="28"/>
@@ -23435,13 +23443,13 @@
     </row>
     <row r="39" spans="1:43" ht="15.75" customHeight="1">
       <c r="A39" s="441" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="430" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="D39" s="231" t="s">
         <v>178</v>
@@ -23480,7 +23488,7 @@
         <v>41</v>
       </c>
       <c r="T39" s="21" t="s">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="U39" s="28"/>
       <c r="V39" s="28"/>
@@ -23508,13 +23516,13 @@
     </row>
     <row r="40" spans="1:43" ht="15.75" customHeight="1">
       <c r="A40" s="441" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="247" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="D40" s="231" t="s">
         <v>178</v>
@@ -23594,7 +23602,7 @@
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="48" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
       <c r="I41" s="43" t="s">
         <v>379</v>
@@ -23605,7 +23613,7 @@
         <v>380</v>
       </c>
       <c r="M41" s="95" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="N41" s="54" t="s">
         <v>381</v>
@@ -23646,13 +23654,13 @@
     </row>
     <row r="42" spans="1:43" ht="15.75" customHeight="1">
       <c r="A42" s="441" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="247" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="D42" s="232"/>
       <c r="E42" s="58"/>
@@ -23717,13 +23725,13 @@
     </row>
     <row r="43" spans="1:43" ht="15.75" customHeight="1">
       <c r="A43" s="441" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="247" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="D43" s="232"/>
       <c r="E43" s="58"/>
@@ -23769,7 +23777,7 @@
         <v>399</v>
       </c>
       <c r="Y43" s="30" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="Z43" s="30"/>
       <c r="AA43" s="30"/>
@@ -23928,13 +23936,13 @@
     </row>
     <row r="46" spans="1:43" ht="15.75" customHeight="1">
       <c r="A46" s="441" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="247" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="D46" s="232"/>
       <c r="E46" s="58"/>
@@ -24011,7 +24019,7 @@
         <v>408</v>
       </c>
       <c r="C47" s="247" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="D47" s="232"/>
       <c r="E47" s="58"/>
@@ -24072,13 +24080,13 @@
     </row>
     <row r="48" spans="1:43" ht="15.75" customHeight="1">
       <c r="A48" s="441" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="B48" s="32" t="s">
         <v>429</v>
       </c>
       <c r="C48" s="247" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="D48" s="232"/>
       <c r="E48" s="58"/>
@@ -24229,13 +24237,13 @@
     </row>
     <row r="50" spans="1:43" ht="15.75" customHeight="1">
       <c r="A50" s="441" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>429</v>
       </c>
       <c r="C50" s="247" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="D50" s="232"/>
       <c r="E50" s="58"/>
@@ -24300,13 +24308,13 @@
     </row>
     <row r="51" spans="1:43" ht="15.75" customHeight="1">
       <c r="A51" s="441" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>439</v>
       </c>
       <c r="C51" s="247" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="D51" s="231" t="s">
         <v>460</v>
@@ -24371,7 +24379,7 @@
     </row>
     <row r="52" spans="1:43" ht="15.75" customHeight="1">
       <c r="A52" s="441" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>466</v>
@@ -24533,7 +24541,7 @@
     </row>
     <row r="54" spans="1:43" ht="15.75" customHeight="1">
       <c r="A54" s="441" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="B54" s="129" t="s">
         <v>492</v>
@@ -24612,7 +24620,7 @@
         <v>43</v>
       </c>
       <c r="C55" s="247" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="D55" s="232"/>
       <c r="E55" s="58"/>
@@ -24752,7 +24760,7 @@
     </row>
     <row r="57" spans="1:43" ht="15.75" customHeight="1">
       <c r="A57" s="441" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="B57" s="32" t="s">
         <v>43</v>
@@ -24819,13 +24827,13 @@
     </row>
     <row r="58" spans="1:43" ht="15.75" customHeight="1">
       <c r="A58" s="441" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="B58" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="247" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="D58" s="231" t="s">
         <v>178</v>
@@ -24894,13 +24902,13 @@
     </row>
     <row r="59" spans="1:43" ht="15.75" customHeight="1">
       <c r="A59" s="441" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="B59" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="247" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="D59" s="231" t="s">
         <v>178</v>
@@ -24965,7 +24973,7 @@
     </row>
     <row r="60" spans="1:43" ht="15.75" customHeight="1">
       <c r="A60" s="441" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="B60" s="32" t="s">
         <v>43</v>
@@ -25013,7 +25021,7 @@
       <c r="W60" s="111"/>
       <c r="X60" s="111"/>
       <c r="Y60" s="30" t="s">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="Z60" s="30" t="s">
         <v>540</v>
@@ -25040,18 +25048,18 @@
     </row>
     <row r="61" spans="1:43" ht="15.75" customHeight="1">
       <c r="A61" s="441" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="B61" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="247" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="D61" s="232"/>
       <c r="E61" s="58"/>
       <c r="F61" s="47" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>542</v>
@@ -25111,7 +25119,7 @@
     </row>
     <row r="62" spans="1:43" ht="15.75" customHeight="1">
       <c r="A62" s="441" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="B62" s="32" t="s">
         <v>43</v>
@@ -25184,13 +25192,13 @@
         <v>557</v>
       </c>
       <c r="C63" s="247" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="D63" s="231" t="s">
         <v>558</v>
       </c>
       <c r="E63" s="58" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="F63" s="265" t="s">
         <v>559</v>
@@ -25251,13 +25259,13 @@
     </row>
     <row r="64" spans="1:43" ht="15.75" customHeight="1">
       <c r="A64" s="441" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="247" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="D64" s="232"/>
       <c r="E64" s="58"/>
@@ -25324,13 +25332,13 @@
     </row>
     <row r="65" spans="1:43" ht="15.75" customHeight="1">
       <c r="A65" s="441" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="B65" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="247" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="D65" s="232"/>
       <c r="E65" s="58"/>
@@ -25397,7 +25405,7 @@
     </row>
     <row r="66" spans="1:43" ht="15.75" customHeight="1">
       <c r="A66" s="441" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="B66" s="32" t="s">
         <v>43</v>
@@ -25630,7 +25638,7 @@
     </row>
     <row r="69" spans="1:43" ht="15.75" customHeight="1">
       <c r="A69" s="441" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="B69" s="32" t="s">
         <v>43</v>
@@ -25717,7 +25725,7 @@
     </row>
     <row r="70" spans="1:43" ht="15.75" customHeight="1">
       <c r="A70" s="441" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="B70" s="32" t="s">
         <v>43</v>
@@ -25786,13 +25794,13 @@
     </row>
     <row r="71" spans="1:43" ht="15.75" customHeight="1">
       <c r="A71" s="441" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="B71" s="32" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="247" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="D71" s="232"/>
       <c r="E71" s="58"/>
@@ -25855,7 +25863,7 @@
     </row>
     <row r="72" spans="1:43" ht="15.75" customHeight="1">
       <c r="A72" s="441" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="B72" s="32" t="s">
         <v>637</v>
@@ -26001,7 +26009,7 @@
     </row>
     <row r="74" spans="1:43" ht="15.75" customHeight="1">
       <c r="A74" s="441" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="B74" s="39" t="s">
         <v>43</v>
@@ -26076,7 +26084,7 @@
         <v>43</v>
       </c>
       <c r="C75" s="247" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="D75" s="308"/>
       <c r="E75" s="58"/>
@@ -26723,7 +26731,7 @@
     </row>
     <row r="84" spans="1:43" ht="15.75" customHeight="1">
       <c r="A84" s="442" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>742</v>
@@ -26859,7 +26867,7 @@
     </row>
     <row r="86" spans="1:43" ht="15.75" customHeight="1">
       <c r="A86" s="442" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>429</v>
@@ -27236,7 +27244,7 @@
     </row>
     <row r="91" spans="1:43" ht="15.75" customHeight="1">
       <c r="A91" s="442" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>43</v>
@@ -27589,7 +27597,7 @@
     </row>
     <row r="96" spans="1:43" ht="15.75" customHeight="1">
       <c r="A96" s="441" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>429</v>
@@ -27656,7 +27664,7 @@
     </row>
     <row r="97" spans="1:43" ht="15.75" customHeight="1">
       <c r="A97" s="441" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
       <c r="B97" s="32" t="s">
         <v>43</v>
@@ -27859,7 +27867,7 @@
     </row>
     <row r="100" spans="1:43" ht="15.75" customHeight="1">
       <c r="A100" s="441" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="B100" s="32" t="s">
         <v>863</v>
@@ -28005,7 +28013,7 @@
     </row>
     <row r="102" spans="1:43" ht="15.75" customHeight="1">
       <c r="A102" s="441" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="B102" s="32" t="s">
         <v>883</v>
@@ -28151,7 +28159,7 @@
     </row>
     <row r="104" spans="1:43" ht="15.75" customHeight="1">
       <c r="A104" s="441" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="B104" s="32" t="s">
         <v>466</v>
@@ -28364,7 +28372,7 @@
     </row>
     <row r="107" spans="1:43" ht="15.75" customHeight="1">
       <c r="A107" s="441" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="B107" s="32" t="s">
         <v>43</v>
@@ -28447,7 +28455,7 @@
     </row>
     <row r="108" spans="1:43" ht="15.75" customHeight="1">
       <c r="A108" s="441" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="B108" s="32" t="s">
         <v>43</v>
@@ -28654,7 +28662,7 @@
     </row>
     <row r="111" spans="1:43" ht="15.75" customHeight="1">
       <c r="A111" s="441" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="B111" s="32" t="s">
         <v>43</v>
@@ -28867,7 +28875,7 @@
     </row>
     <row r="114" spans="1:43" ht="15.75" customHeight="1">
       <c r="A114" s="441" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="B114" s="32" t="s">
         <v>429</v>
@@ -29230,7 +29238,7 @@
     </row>
     <row r="119" spans="1:43" ht="15.75" customHeight="1">
       <c r="A119" s="441" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>43</v>
@@ -29245,7 +29253,7 @@
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="32" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="I119" s="43" t="s">
         <v>1030</v>
@@ -29441,7 +29449,7 @@
     </row>
     <row r="122" spans="1:43" ht="15.75" customHeight="1">
       <c r="A122" s="454" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="B122" s="51" t="s">
         <v>43</v>
@@ -29493,7 +29501,7 @@
       <c r="W122" s="29"/>
       <c r="X122" s="29"/>
       <c r="Y122" s="30" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="Z122" s="30"/>
       <c r="AA122" s="30"/>
@@ -29958,7 +29966,7 @@
     </row>
     <row r="129" spans="1:43" ht="15.75" customHeight="1">
       <c r="A129" s="454" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="B129" s="32" t="s">
         <v>43</v>
@@ -30029,7 +30037,7 @@
     </row>
     <row r="130" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
       <c r="A130" s="441" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>43</v>
@@ -30102,7 +30110,7 @@
     </row>
     <row r="131" spans="1:43" s="288" customFormat="1" ht="15.75" customHeight="1">
       <c r="A131" s="441" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="B131" s="33" t="s">
         <v>43</v>
@@ -30538,7 +30546,7 @@
     </row>
     <row r="137" spans="1:43" ht="15.75" customHeight="1">
       <c r="A137" s="456" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>43</v>
@@ -30553,7 +30561,7 @@
       </c>
       <c r="G137" s="32"/>
       <c r="H137" s="48" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="I137" s="43" t="s">
         <v>1178</v>
@@ -30678,7 +30686,7 @@
     </row>
     <row r="139" spans="1:43" ht="15.75" customHeight="1">
       <c r="A139" s="456" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="B139" s="33" t="s">
         <v>43</v>
@@ -30693,7 +30701,7 @@
       </c>
       <c r="G139" s="32"/>
       <c r="H139" s="48" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="I139" s="43" t="s">
         <v>1192</v>
@@ -31003,7 +31011,7 @@
         <v>41</v>
       </c>
       <c r="T143" s="21" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="U143" s="28"/>
       <c r="V143" s="28"/>
@@ -31074,7 +31082,7 @@
         <v>41</v>
       </c>
       <c r="T144" s="21" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="U144" s="28"/>
       <c r="V144" s="28"/>
@@ -32747,7 +32755,7 @@
         <v>175</v>
       </c>
       <c r="N167" s="134" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="O167" s="134"/>
       <c r="P167" s="153" t="s">
@@ -32757,7 +32765,7 @@
         <v>1412</v>
       </c>
       <c r="R167" s="39" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="S167" s="21" t="s">
         <v>41</v>
@@ -32870,7 +32878,7 @@
     </row>
     <row r="169" spans="1:43" ht="15.75" customHeight="1">
       <c r="A169" s="441" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="B169" s="33" t="s">
         <v>43</v>
@@ -33300,7 +33308,7 @@
     </row>
     <row r="175" spans="1:43" ht="15.75" customHeight="1">
       <c r="A175" s="441" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="B175" s="33" t="s">
         <v>43</v>
@@ -33369,7 +33377,7 @@
     </row>
     <row r="176" spans="1:43" ht="15.75" customHeight="1">
       <c r="A176" s="441" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="B176" s="33" t="s">
         <v>43</v>
@@ -33436,7 +33444,7 @@
     </row>
     <row r="177" spans="1:43" s="350" customFormat="1" ht="15.75" customHeight="1">
       <c r="A177" s="454" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="B177" s="15" t="s">
         <v>466</v>
@@ -33894,7 +33902,7 @@
     </row>
     <row r="183" spans="1:43" ht="15.75" customHeight="1">
       <c r="A183" s="441" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="B183" s="33" t="s">
         <v>43</v>
@@ -33963,7 +33971,7 @@
     </row>
     <row r="184" spans="1:43" ht="15.75" customHeight="1">
       <c r="A184" s="441" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="B184" s="33" t="s">
         <v>43</v>
@@ -34397,7 +34405,7 @@
     </row>
     <row r="190" spans="1:43" ht="15.75" customHeight="1">
       <c r="A190" s="454" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="B190" s="15" t="s">
         <v>43</v>
@@ -34512,7 +34520,7 @@
       <c r="W191" s="29"/>
       <c r="X191" s="110"/>
       <c r="Y191" s="30" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="Z191" s="30" t="s">
         <v>1603</v>
@@ -34608,13 +34616,13 @@
     </row>
     <row r="193" spans="1:43" ht="15.75" customHeight="1">
       <c r="A193" s="441" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="B193" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C193" s="248" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="D193" s="232"/>
       <c r="E193" s="58"/>
@@ -34724,7 +34732,7 @@
         <v>41</v>
       </c>
       <c r="T194" s="21" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="U194" s="28" t="s">
         <v>1057</v>
@@ -34805,7 +34813,7 @@
         <v>41</v>
       </c>
       <c r="T195" s="21" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="U195" s="28" t="s">
         <v>1057</v>
@@ -34869,7 +34877,7 @@
         <v>1646</v>
       </c>
       <c r="M196" s="95" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="N196" s="54" t="s">
         <v>1647</v>
@@ -35486,7 +35494,7 @@
     </row>
     <row r="205" spans="1:43" ht="15.75" customHeight="1">
       <c r="A205" s="441" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="B205" s="33" t="s">
         <v>43</v>
@@ -35632,7 +35640,7 @@
     </row>
     <row r="207" spans="1:43" ht="15.75" customHeight="1">
       <c r="A207" s="441" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>429</v>
@@ -35950,7 +35958,7 @@
     </row>
     <row r="211" spans="1:43" ht="15.75" customHeight="1">
       <c r="A211" s="441" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>999</v>
@@ -36112,7 +36120,7 @@
     </row>
     <row r="213" spans="1:43" ht="15.75" customHeight="1">
       <c r="A213" s="441" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>429</v>
@@ -36165,7 +36173,7 @@
       <c r="AB213" s="165"/>
       <c r="AC213" s="32"/>
       <c r="AD213" s="21" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="AE213" s="32"/>
       <c r="AF213" s="32"/>
@@ -36416,10 +36424,10 @@
         <v>999</v>
       </c>
       <c r="C217" s="440" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="D217" s="232" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="E217" s="58"/>
       <c r="F217" s="32" t="s">
@@ -36446,7 +36454,7 @@
       <c r="O217" s="54"/>
       <c r="P217" s="55"/>
       <c r="Q217" s="318" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="R217" s="115" t="s">
         <v>382</v>
@@ -36491,7 +36499,7 @@
         <v>999</v>
       </c>
       <c r="C218" s="247" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="D218" s="232"/>
       <c r="E218" s="58"/>
@@ -36742,13 +36750,13 @@
       <c r="U221" s="170"/>
       <c r="V221" s="170"/>
       <c r="W221" s="29" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="X221" s="29" t="s">
+        <v>4023</v>
+      </c>
+      <c r="Y221" s="227" t="s">
         <v>4024</v>
-      </c>
-      <c r="Y221" s="227" t="s">
-        <v>4025</v>
       </c>
       <c r="Z221" s="30"/>
       <c r="AA221" s="30"/>
@@ -36773,7 +36781,7 @@
     </row>
     <row r="222" spans="1:43" ht="15.75" customHeight="1">
       <c r="A222" s="441" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>429</v>
@@ -36929,7 +36937,7 @@
     </row>
     <row r="224" spans="1:43" ht="15.75" customHeight="1">
       <c r="A224" s="441" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>1903</v>
@@ -37010,7 +37018,7 @@
     </row>
     <row r="225" spans="1:43" ht="15.75" customHeight="1">
       <c r="A225" s="441" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
       <c r="B225" s="14" t="s">
         <v>429</v>
@@ -37166,10 +37174,10 @@
       <c r="K227" s="82"/>
       <c r="L227" s="22"/>
       <c r="M227" s="53" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N227" s="54" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="O227" s="394"/>
       <c r="P227" s="290" t="s">
@@ -37245,10 +37253,10 @@
       <c r="K228" s="22"/>
       <c r="L228" s="22"/>
       <c r="M228" s="53" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N228" s="54" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="O228" s="54"/>
       <c r="P228" s="290" t="s">
@@ -37661,13 +37669,13 @@
     </row>
     <row r="234" spans="1:43" ht="15.75" customHeight="1">
       <c r="A234" s="441" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>429</v>
       </c>
       <c r="C234" s="258" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="D234" s="232"/>
       <c r="E234" s="58"/>
@@ -38001,7 +38009,7 @@
         <v>1997</v>
       </c>
       <c r="M238" s="95" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="N238" s="38" t="s">
         <v>1647</v>
@@ -38088,10 +38096,10 @@
         <v>2008</v>
       </c>
       <c r="M239" s="125" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
       <c r="N239" s="54" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="O239" s="54"/>
       <c r="P239" s="25" t="s">
@@ -38141,7 +38149,7 @@
     </row>
     <row r="240" spans="1:43" ht="15.75" customHeight="1">
       <c r="A240" s="441" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>429</v>
@@ -38246,7 +38254,7 @@
       <c r="K241" s="82"/>
       <c r="L241" s="82"/>
       <c r="M241" s="53" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N241" s="54" t="s">
         <v>2022</v>
@@ -38318,7 +38326,7 @@
         <v>2026</v>
       </c>
       <c r="H242" s="48" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="I242" s="43" t="s">
         <v>2027</v>
@@ -38327,7 +38335,7 @@
       <c r="K242" s="22"/>
       <c r="L242" s="22"/>
       <c r="M242" s="53" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N242" s="54" t="s">
         <v>2028</v>
@@ -38688,23 +38696,23 @@
     </row>
     <row r="247" spans="1:43" ht="15.75" customHeight="1">
       <c r="A247" s="459" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="B247" s="356" t="s">
         <v>2073</v>
       </c>
       <c r="C247" s="259" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="E247" s="227"/>
       <c r="F247" s="227" t="s">
+        <v>3758</v>
+      </c>
+      <c r="G247" s="227" t="s">
         <v>3759</v>
       </c>
-      <c r="G247" s="227" t="s">
-        <v>3760</v>
-      </c>
       <c r="H247" s="360" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="I247" s="358" t="s">
         <v>1901</v>
@@ -38713,10 +38721,10 @@
       <c r="K247" s="227"/>
       <c r="L247" s="227"/>
       <c r="M247" s="358" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N247" s="396" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="O247" s="395"/>
       <c r="P247" s="290" t="s">
@@ -38732,7 +38740,7 @@
         <v>41</v>
       </c>
       <c r="T247" s="360" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="U247" s="360" t="s">
         <v>1894</v>
@@ -38743,7 +38751,7 @@
       <c r="W247" s="227"/>
       <c r="X247" s="227"/>
       <c r="Y247" s="370" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="Z247" s="227"/>
       <c r="AA247" s="227"/>
@@ -38752,7 +38760,7 @@
         <v>2074</v>
       </c>
       <c r="AD247" s="227" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="AE247" s="227"/>
       <c r="AF247" s="227"/>
@@ -38770,19 +38778,19 @@
     </row>
     <row r="248" spans="1:43" ht="15.75" customHeight="1">
       <c r="A248" s="459" t="s">
+        <v>3753</v>
+      </c>
+      <c r="B248" s="360" t="s">
         <v>3754</v>
       </c>
-      <c r="B248" s="360" t="s">
-        <v>3755</v>
-      </c>
       <c r="C248" s="259" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="E248" s="227"/>
       <c r="F248" s="227"/>
       <c r="G248" s="360"/>
       <c r="H248" s="360" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="I248" s="358" t="s">
         <v>2021</v>
@@ -38791,10 +38799,10 @@
       <c r="K248" s="227"/>
       <c r="L248" s="227"/>
       <c r="M248" s="358" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N248" s="396" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="O248" s="395"/>
       <c r="P248" s="290" t="s">
@@ -38810,7 +38818,7 @@
         <v>41</v>
       </c>
       <c r="T248" s="360" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="U248" s="360" t="s">
         <v>1894</v>
@@ -38821,7 +38829,7 @@
       <c r="W248" s="227"/>
       <c r="X248" s="227"/>
       <c r="Y248" s="360" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
       <c r="Z248" s="227"/>
       <c r="AA248" s="227"/>
@@ -39142,7 +39150,7 @@
         <v>429</v>
       </c>
       <c r="C253" s="248" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="D253" s="232"/>
       <c r="E253" s="58"/>
@@ -39501,7 +39509,7 @@
     </row>
     <row r="258" spans="1:43" ht="15.75" customHeight="1">
       <c r="A258" s="441" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="B258" s="14" t="s">
         <v>429</v>
@@ -39868,7 +39876,7 @@
     </row>
     <row r="263" spans="1:43" ht="15.75" customHeight="1">
       <c r="A263" s="441" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
       <c r="B263" s="14" t="s">
         <v>429</v>
@@ -40008,7 +40016,7 @@
     </row>
     <row r="265" spans="1:43" ht="15.75" customHeight="1">
       <c r="A265" s="441" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="B265" s="14" t="s">
         <v>2199</v>
@@ -40034,10 +40042,10 @@
       <c r="K265" s="22"/>
       <c r="L265" s="22"/>
       <c r="M265" s="53" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N265" s="54" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="O265" s="54"/>
       <c r="P265" s="290" t="s">
@@ -40079,7 +40087,7 @@
     </row>
     <row r="266" spans="1:43" ht="15.75" customHeight="1">
       <c r="A266" s="441" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
       <c r="B266" s="14" t="s">
         <v>429</v>
@@ -40298,7 +40306,7 @@
     </row>
     <row r="269" spans="1:43" ht="15.75" customHeight="1">
       <c r="A269" s="441" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="B269" s="66" t="s">
         <v>2229</v>
@@ -40401,10 +40409,10 @@
       <c r="K270" s="22"/>
       <c r="L270" s="22"/>
       <c r="M270" s="292" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N270" s="73" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="O270" s="73"/>
       <c r="P270" s="290" t="s">
@@ -40429,7 +40437,7 @@
       <c r="W270" s="29"/>
       <c r="X270" s="29"/>
       <c r="Y270" s="30" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="Z270" s="30"/>
       <c r="AA270" s="30"/>
@@ -40655,7 +40663,7 @@
     </row>
     <row r="274" spans="1:43" ht="15.75" customHeight="1">
       <c r="A274" s="441" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="B274" s="14" t="s">
         <v>429</v>
@@ -40902,10 +40910,10 @@
       <c r="K277" s="82"/>
       <c r="L277" s="22"/>
       <c r="M277" s="292" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N277" s="38" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="O277" s="38"/>
       <c r="P277" s="290" t="s">
@@ -41273,7 +41281,7 @@
       <c r="K282" s="22"/>
       <c r="L282" s="22"/>
       <c r="M282" s="292" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N282" s="429" t="s">
         <v>2447</v>
@@ -41301,7 +41309,7 @@
       <c r="W282" s="29"/>
       <c r="X282" s="29"/>
       <c r="Y282" s="30" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="Z282" s="30"/>
       <c r="AA282" s="30"/>
@@ -41365,7 +41373,7 @@
         <v>1895</v>
       </c>
       <c r="R283" s="32" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="S283" s="32" t="s">
         <v>41</v>
@@ -41561,10 +41569,10 @@
       <c r="K286" s="22"/>
       <c r="L286" s="22"/>
       <c r="M286" s="390" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N286" s="89" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="O286" s="89"/>
       <c r="P286" s="124" t="s">
@@ -41580,7 +41588,7 @@
         <v>41</v>
       </c>
       <c r="T286" s="21" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="U286" s="28"/>
       <c r="V286" s="28"/>
@@ -41851,7 +41859,7 @@
       <c r="K290" s="82"/>
       <c r="L290" s="22"/>
       <c r="M290" s="292" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N290" s="54" t="s">
         <v>2370</v>
@@ -42143,10 +42151,10 @@
       <c r="K294" s="82"/>
       <c r="L294" s="82"/>
       <c r="M294" s="33" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
       <c r="N294" s="89" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="O294" s="393"/>
       <c r="P294" s="112" t="s">
@@ -42171,7 +42179,7 @@
       <c r="W294" s="29"/>
       <c r="X294" s="29"/>
       <c r="Y294" s="30" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
       <c r="Z294" s="30"/>
       <c r="AA294" s="30"/>
@@ -42196,7 +42204,7 @@
     </row>
     <row r="295" spans="1:43" ht="15.75" customHeight="1">
       <c r="A295" s="441" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="B295" s="14" t="s">
         <v>429</v>
@@ -42518,7 +42526,7 @@
       <c r="K299" s="22"/>
       <c r="L299" s="22"/>
       <c r="M299" s="292" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="N299" s="89" t="s">
         <v>2028</v>
@@ -42679,7 +42687,7 @@
         <v>2452</v>
       </c>
       <c r="N301" s="38" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="O301" s="38"/>
       <c r="P301" s="25"/>
@@ -42995,7 +43003,7 @@
     </row>
     <row r="306" spans="1:43" ht="15.75" customHeight="1">
       <c r="A306" s="458" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="B306" s="33" t="s">
         <v>429</v>
@@ -43153,7 +43161,7 @@
     </row>
     <row r="308" spans="1:43" ht="15.75" customHeight="1">
       <c r="A308" s="458" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
       <c r="B308" s="33" t="s">
         <v>429</v>
@@ -43307,7 +43315,7 @@
     </row>
     <row r="310" spans="1:43" ht="15.75" customHeight="1">
       <c r="A310" s="458" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="B310" s="33" t="s">
         <v>429</v>
@@ -43322,7 +43330,7 @@
       </c>
       <c r="G310" s="32"/>
       <c r="H310" s="354" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="I310" s="32" t="s">
         <v>2496</v>
@@ -43903,13 +43911,13 @@
     </row>
     <row r="318" spans="1:43" ht="15.75" customHeight="1">
       <c r="A318" s="99" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
       <c r="B318" s="33" t="s">
         <v>2587</v>
       </c>
       <c r="C318" s="260" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="E318" s="58" t="s">
         <v>2588</v>
@@ -44062,7 +44070,7 @@
     </row>
     <row r="320" spans="1:43" ht="15.75" customHeight="1">
       <c r="A320" s="458" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
       <c r="B320" s="33" t="s">
         <v>429</v>
@@ -44131,7 +44139,7 @@
     </row>
     <row r="321" spans="1:43" ht="15.75" customHeight="1">
       <c r="A321" s="458" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
       <c r="B321" s="33" t="s">
         <v>429</v>
@@ -44556,7 +44564,7 @@
         <v>2227</v>
       </c>
       <c r="Y326" s="30" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="Z326" s="30"/>
       <c r="AA326" s="30" t="s">
@@ -44668,7 +44676,7 @@
         <v>429</v>
       </c>
       <c r="C328" s="248" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="D328" s="244"/>
       <c r="E328" s="188"/>
@@ -44743,7 +44751,7 @@
     </row>
     <row r="329" spans="1:43" ht="15.75" customHeight="1">
       <c r="A329" s="458" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="B329" s="33" t="s">
         <v>429</v>
@@ -45447,7 +45455,7 @@
       </c>
       <c r="G338" s="48"/>
       <c r="H338" s="32" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="I338" s="185" t="s">
         <v>2756</v>
@@ -45461,7 +45469,7 @@
         <v>2758</v>
       </c>
       <c r="N338" s="38" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="O338" s="38"/>
       <c r="P338" s="25" t="s">
@@ -45471,7 +45479,7 @@
         <v>2760</v>
       </c>
       <c r="R338" s="428" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="S338" s="77" t="s">
         <v>41</v>
@@ -45738,7 +45746,7 @@
     </row>
     <row r="342" spans="1:43" ht="15.75" customHeight="1">
       <c r="A342" s="458" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="B342" s="33" t="s">
         <v>429</v>
@@ -45903,7 +45911,7 @@
       </c>
       <c r="G344" s="32"/>
       <c r="H344" s="203" t="s">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="I344" s="190" t="s">
         <v>2496</v>
@@ -45967,7 +45975,7 @@
     </row>
     <row r="345" spans="1:43" ht="15.75" customHeight="1">
       <c r="A345" s="458" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="B345" s="33" t="s">
         <v>429</v>
@@ -46046,7 +46054,7 @@
     </row>
     <row r="346" spans="1:43" ht="15.75" customHeight="1">
       <c r="A346" s="458" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="B346" s="33" t="s">
         <v>429</v>
@@ -46281,7 +46289,7 @@
     </row>
     <row r="349" spans="1:43" ht="15.75" customHeight="1">
       <c r="A349" s="458" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="B349" s="33" t="s">
         <v>429</v>
@@ -46439,7 +46447,7 @@
     </row>
     <row r="351" spans="1:43" ht="15.75" customHeight="1">
       <c r="A351" s="458" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="B351" s="184" t="s">
         <v>2867</v>
@@ -46753,7 +46761,7 @@
         <v>429</v>
       </c>
       <c r="C355" s="247" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="D355" s="232"/>
       <c r="E355" s="58"/>
@@ -46776,14 +46784,14 @@
         <v>1611</v>
       </c>
       <c r="N355" s="54" t="s">
+        <v>4026</v>
+      </c>
+      <c r="O355" s="54" t="s">
         <v>2898</v>
-      </c>
-      <c r="O355" s="54" t="s">
-        <v>2899</v>
       </c>
       <c r="P355" s="55"/>
       <c r="Q355" s="56" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="R355" s="32" t="s">
         <v>518</v>
@@ -46804,10 +46812,10 @@
         <v>2797</v>
       </c>
       <c r="Z355" s="30" t="s">
+        <v>2900</v>
+      </c>
+      <c r="AA355" s="30" t="s">
         <v>2901</v>
-      </c>
-      <c r="AA355" s="30" t="s">
-        <v>2902</v>
       </c>
       <c r="AB355" s="41"/>
       <c r="AC355" s="32"/>
@@ -46828,7 +46836,7 @@
     </row>
     <row r="356" spans="1:43" ht="15.75" customHeight="1">
       <c r="A356" s="458" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="B356" s="33" t="s">
         <v>429</v>
@@ -46839,11 +46847,11 @@
       <c r="D356" s="232"/>
       <c r="E356" s="58"/>
       <c r="F356" s="47" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="G356" s="32"/>
       <c r="H356" s="203" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="I356" s="190" t="s">
         <v>2496</v>
@@ -46855,14 +46863,14 @@
         <v>797</v>
       </c>
       <c r="N356" s="54" t="s">
+        <v>2905</v>
+      </c>
+      <c r="O356" s="54" t="s">
         <v>2906</v>
-      </c>
-      <c r="O356" s="54" t="s">
-        <v>2907</v>
       </c>
       <c r="P356" s="55"/>
       <c r="Q356" s="56" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="R356" s="32" t="s">
         <v>518</v>
@@ -46871,7 +46879,7 @@
         <v>41</v>
       </c>
       <c r="T356" s="21" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="U356" s="28"/>
       <c r="V356" s="28"/>
@@ -46882,13 +46890,13 @@
         <v>2227</v>
       </c>
       <c r="Y356" s="30" t="s">
+        <v>2909</v>
+      </c>
+      <c r="Z356" s="30" t="s">
         <v>2910</v>
       </c>
-      <c r="Z356" s="30" t="s">
+      <c r="AA356" s="30" t="s">
         <v>2911</v>
-      </c>
-      <c r="AA356" s="30" t="s">
-        <v>2912</v>
       </c>
       <c r="AB356" s="41"/>
       <c r="AC356" s="32"/>
@@ -46909,22 +46917,22 @@
     </row>
     <row r="357" spans="1:43" ht="15.75" customHeight="1">
       <c r="A357" s="458" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="B357" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C357" s="246" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="D357" s="232"/>
       <c r="E357" s="58"/>
       <c r="F357" s="47" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="G357" s="32"/>
       <c r="H357" s="32" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="I357" s="190" t="s">
         <v>2496</v>
@@ -46938,7 +46946,7 @@
         <v>536</v>
       </c>
       <c r="N357" s="54" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="O357" s="54"/>
       <c r="P357" s="55"/>
@@ -46963,10 +46971,10 @@
       </c>
       <c r="Z357" s="30"/>
       <c r="AA357" s="30" t="s">
+        <v>2917</v>
+      </c>
+      <c r="AB357" s="41" t="s">
         <v>2918</v>
-      </c>
-      <c r="AB357" s="41" t="s">
-        <v>2919</v>
       </c>
       <c r="AC357" s="32"/>
       <c r="AD357" s="21"/>
@@ -46986,10 +46994,10 @@
     </row>
     <row r="358" spans="1:43" ht="15.75" customHeight="1">
       <c r="A358" s="458" t="s">
+        <v>2919</v>
+      </c>
+      <c r="B358" s="184" t="s">
         <v>2920</v>
-      </c>
-      <c r="B358" s="184" t="s">
-        <v>2921</v>
       </c>
       <c r="C358" s="247" t="s">
         <v>170</v>
@@ -46997,11 +47005,11 @@
       <c r="D358" s="232"/>
       <c r="E358" s="58"/>
       <c r="F358" s="47" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="G358" s="32"/>
       <c r="H358" s="203" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="I358" s="190" t="s">
         <v>2496</v>
@@ -47010,10 +47018,10 @@
       <c r="K358" s="93"/>
       <c r="L358" s="93"/>
       <c r="M358" s="135" t="s">
+        <v>2923</v>
+      </c>
+      <c r="N358" s="65" t="s">
         <v>2924</v>
-      </c>
-      <c r="N358" s="65" t="s">
-        <v>2925</v>
       </c>
       <c r="O358" s="65"/>
       <c r="P358" s="55"/>
@@ -47034,14 +47042,14 @@
         <v>2227</v>
       </c>
       <c r="Y358" s="207" t="s">
+        <v>2925</v>
+      </c>
+      <c r="Z358" s="208" t="s">
         <v>2926</v>
-      </c>
-      <c r="Z358" s="208" t="s">
-        <v>2927</v>
       </c>
       <c r="AA358" s="208"/>
       <c r="AB358" s="31" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="AC358" s="32"/>
       <c r="AD358" s="21"/>
@@ -47061,38 +47069,38 @@
     </row>
     <row r="359" spans="1:43" ht="15.75" customHeight="1">
       <c r="A359" s="458" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="B359" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C359" s="246" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="D359" s="232"/>
       <c r="E359" s="58"/>
       <c r="F359" s="47" t="s">
+        <v>2930</v>
+      </c>
+      <c r="G359" s="32" t="s">
         <v>2931</v>
       </c>
-      <c r="G359" s="32" t="s">
+      <c r="H359" s="95" t="s">
         <v>2932</v>
-      </c>
-      <c r="H359" s="95" t="s">
-        <v>2933</v>
       </c>
       <c r="I359" s="185" t="s">
         <v>2628</v>
       </c>
       <c r="J359" s="22" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="K359" s="22"/>
       <c r="L359" s="22"/>
       <c r="M359" s="135" t="s">
+        <v>2934</v>
+      </c>
+      <c r="N359" s="134" t="s">
         <v>2935</v>
-      </c>
-      <c r="N359" s="134" t="s">
-        <v>2936</v>
       </c>
       <c r="O359" s="54"/>
       <c r="P359" s="55"/>
@@ -47104,7 +47112,7 @@
         <v>41</v>
       </c>
       <c r="T359" s="21" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="U359" s="28"/>
       <c r="V359" s="28"/>
@@ -47138,7 +47146,7 @@
     </row>
     <row r="360" spans="1:43" ht="15.75" customHeight="1">
       <c r="A360" s="458" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="B360" s="33" t="s">
         <v>429</v>
@@ -47149,11 +47157,11 @@
       <c r="D360" s="232"/>
       <c r="E360" s="58"/>
       <c r="F360" s="47" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="G360" s="32"/>
       <c r="H360" s="48" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="I360" s="185" t="s">
         <v>2496</v>
@@ -47162,17 +47170,17 @@
       <c r="K360" s="22"/>
       <c r="L360" s="22"/>
       <c r="M360" s="135" t="s">
+        <v>2940</v>
+      </c>
+      <c r="N360" s="54" t="s">
         <v>2941</v>
-      </c>
-      <c r="N360" s="54" t="s">
-        <v>2942</v>
       </c>
       <c r="O360" s="54" t="s">
         <v>1860</v>
       </c>
       <c r="P360" s="55"/>
       <c r="Q360" s="56" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="R360" s="32" t="s">
         <v>518</v>
@@ -47190,13 +47198,13 @@
         <v>2227</v>
       </c>
       <c r="Y360" s="30" t="s">
+        <v>2943</v>
+      </c>
+      <c r="Z360" s="30" t="s">
         <v>2944</v>
       </c>
-      <c r="Z360" s="30" t="s">
+      <c r="AA360" s="30" t="s">
         <v>2945</v>
-      </c>
-      <c r="AA360" s="30" t="s">
-        <v>2946</v>
       </c>
       <c r="AB360" s="108"/>
       <c r="AC360" s="32"/>
@@ -47217,7 +47225,7 @@
     </row>
     <row r="361" spans="1:43" ht="15.75" customHeight="1">
       <c r="A361" s="458" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="B361" s="33" t="s">
         <v>429</v>
@@ -47231,22 +47239,22 @@
         <v>2274</v>
       </c>
       <c r="G361" s="184" t="s">
+        <v>2947</v>
+      </c>
+      <c r="H361" s="48" t="s">
         <v>2948</v>
       </c>
-      <c r="H361" s="48" t="s">
+      <c r="I361" s="185" t="s">
         <v>2949</v>
-      </c>
-      <c r="I361" s="185" t="s">
-        <v>2950</v>
       </c>
       <c r="J361" s="22"/>
       <c r="K361" s="22"/>
       <c r="L361" s="22"/>
       <c r="M361" s="135" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="N361" s="54" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="O361" s="54"/>
       <c r="P361" s="25" t="s">
@@ -47262,7 +47270,7 @@
         <v>41</v>
       </c>
       <c r="T361" s="21" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="U361" s="28"/>
       <c r="V361" s="28"/>
@@ -47273,7 +47281,7 @@
       <c r="AA361" s="30"/>
       <c r="AB361" s="108"/>
       <c r="AC361" s="32" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="AD361" s="21"/>
       <c r="AE361" s="32"/>
@@ -47292,7 +47300,7 @@
     </row>
     <row r="362" spans="1:43" ht="15.75" customHeight="1">
       <c r="A362" s="458" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="B362" s="33" t="s">
         <v>429</v>
@@ -47303,13 +47311,13 @@
       <c r="D362" s="232"/>
       <c r="E362" s="58"/>
       <c r="F362" s="16" t="s">
+        <v>2954</v>
+      </c>
+      <c r="G362" s="48" t="s">
         <v>2955</v>
       </c>
-      <c r="G362" s="48" t="s">
+      <c r="H362" s="203" t="s">
         <v>2956</v>
-      </c>
-      <c r="H362" s="203" t="s">
-        <v>2957</v>
       </c>
       <c r="I362" s="32" t="s">
         <v>2536</v>
@@ -47318,10 +47326,10 @@
       <c r="K362" s="82"/>
       <c r="L362" s="82"/>
       <c r="M362" s="95" t="s">
+        <v>2957</v>
+      </c>
+      <c r="N362" s="54" t="s">
         <v>2958</v>
-      </c>
-      <c r="N362" s="54" t="s">
-        <v>2959</v>
       </c>
       <c r="O362" s="54"/>
       <c r="P362" s="25" t="s">
@@ -47331,7 +47339,7 @@
         <v>1895</v>
       </c>
       <c r="R362" s="77" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="S362" s="77" t="s">
         <v>41</v>
@@ -47346,7 +47354,7 @@
       <c r="W362" s="111"/>
       <c r="X362" s="111"/>
       <c r="Y362" s="30" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="Z362" s="30"/>
       <c r="AA362" s="30"/>
@@ -47355,7 +47363,7 @@
         <v>1897</v>
       </c>
       <c r="AD362" s="144" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="AE362" s="32"/>
       <c r="AF362" s="32"/>
@@ -47373,7 +47381,7 @@
     </row>
     <row r="363" spans="1:43" ht="15.75" customHeight="1">
       <c r="A363" s="458" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="B363" s="33" t="s">
         <v>429</v>
@@ -47384,11 +47392,11 @@
       <c r="D363" s="232"/>
       <c r="E363" s="58"/>
       <c r="F363" s="47" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="G363" s="48"/>
       <c r="H363" s="48" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I363" s="32" t="s">
         <v>2536</v>
@@ -47400,7 +47408,7 @@
         <v>486</v>
       </c>
       <c r="N363" s="54" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="O363" s="54"/>
       <c r="P363" s="25" t="s">
@@ -47425,7 +47433,7 @@
       <c r="W363" s="111"/>
       <c r="X363" s="111"/>
       <c r="Y363" s="30" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="Z363" s="30"/>
       <c r="AA363" s="30"/>
@@ -47450,7 +47458,7 @@
     </row>
     <row r="364" spans="1:43" ht="15.75" customHeight="1">
       <c r="A364" s="458" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="B364" s="33" t="s">
         <v>429</v>
@@ -47461,21 +47469,21 @@
       <c r="D364" s="232"/>
       <c r="E364" s="58"/>
       <c r="F364" s="16" t="s">
+        <v>2967</v>
+      </c>
+      <c r="G364" s="48" t="s">
         <v>2968</v>
       </c>
-      <c r="G364" s="48" t="s">
+      <c r="H364" s="203" t="s">
         <v>2969</v>
       </c>
-      <c r="H364" s="203" t="s">
+      <c r="I364" s="32" t="s">
         <v>2970</v>
-      </c>
-      <c r="I364" s="32" t="s">
-        <v>2971</v>
       </c>
       <c r="J364" s="22"/>
       <c r="K364" s="22"/>
       <c r="L364" s="22" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="M364" s="181" t="s">
         <v>2071</v>
@@ -47517,7 +47525,7 @@
     </row>
     <row r="365" spans="1:43" ht="15.75" customHeight="1">
       <c r="A365" s="458" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="B365" s="33" t="s">
         <v>429</v>
@@ -47528,11 +47536,11 @@
       <c r="D365" s="232"/>
       <c r="E365" s="58"/>
       <c r="F365" s="47" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="G365" s="32"/>
       <c r="H365" s="203" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="I365" s="32" t="s">
         <v>2496</v>
@@ -47544,7 +47552,7 @@
         <v>594</v>
       </c>
       <c r="N365" s="38" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="O365" s="38" t="s">
         <v>38</v>
@@ -47569,14 +47577,14 @@
         <v>2227</v>
       </c>
       <c r="Y365" s="195" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="Z365" s="418"/>
       <c r="AA365" s="195" t="s">
+        <v>2977</v>
+      </c>
+      <c r="AB365" s="31" t="s">
         <v>2978</v>
-      </c>
-      <c r="AB365" s="31" t="s">
-        <v>2979</v>
       </c>
       <c r="AC365" s="32"/>
       <c r="AD365" s="21"/>
@@ -47596,22 +47604,22 @@
     </row>
     <row r="366" spans="1:43" ht="15.75" customHeight="1">
       <c r="A366" s="458" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="B366" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C366" s="246" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="D366" s="232"/>
       <c r="E366" s="58"/>
       <c r="F366" s="47" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="G366" s="32"/>
       <c r="H366" s="203" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="I366" s="190" t="s">
         <v>2496</v>
@@ -47625,7 +47633,7 @@
         <v>536</v>
       </c>
       <c r="N366" s="38" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="O366" s="38"/>
       <c r="P366" s="25"/>
@@ -47646,11 +47654,11 @@
         <v>2227</v>
       </c>
       <c r="Y366" s="30" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="Z366" s="197"/>
       <c r="AA366" s="30" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="AB366" s="41"/>
       <c r="AC366" s="32"/>
@@ -47671,7 +47679,7 @@
     </row>
     <row r="367" spans="1:43" ht="15.75" customHeight="1">
       <c r="A367" s="458" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="B367" s="33" t="s">
         <v>429</v>
@@ -47682,11 +47690,11 @@
       <c r="D367" s="232"/>
       <c r="E367" s="58"/>
       <c r="F367" s="47" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="G367" s="39"/>
       <c r="H367" s="203" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="I367" s="190" t="s">
         <v>2496</v>
@@ -47694,20 +47702,20 @@
       <c r="J367" s="22"/>
       <c r="K367" s="22"/>
       <c r="L367" s="22" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="M367" s="135" t="s">
         <v>650</v>
       </c>
       <c r="N367" s="38" t="s">
+        <v>2989</v>
+      </c>
+      <c r="O367" s="38" t="s">
         <v>2990</v>
-      </c>
-      <c r="O367" s="38" t="s">
-        <v>2991</v>
       </c>
       <c r="P367" s="25"/>
       <c r="Q367" s="26" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="R367" s="39" t="s">
         <v>518</v>
@@ -47725,13 +47733,13 @@
         <v>2227</v>
       </c>
       <c r="Y367" s="30" t="s">
+        <v>2992</v>
+      </c>
+      <c r="Z367" s="30" t="s">
         <v>2993</v>
       </c>
-      <c r="Z367" s="30" t="s">
+      <c r="AA367" s="30" t="s">
         <v>2994</v>
-      </c>
-      <c r="AA367" s="30" t="s">
-        <v>2995</v>
       </c>
       <c r="AB367" s="41"/>
       <c r="AC367" s="32"/>
@@ -47752,7 +47760,7 @@
     </row>
     <row r="368" spans="1:43" ht="15.75" customHeight="1">
       <c r="A368" s="458" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="B368" s="33" t="s">
         <v>429</v>
@@ -47763,11 +47771,11 @@
       <c r="D368" s="232"/>
       <c r="E368" s="58"/>
       <c r="F368" s="47" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="G368" s="39"/>
       <c r="H368" s="203" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="I368" s="190" t="s">
         <v>2496</v>
@@ -47776,17 +47784,17 @@
       <c r="K368" s="22"/>
       <c r="L368" s="22"/>
       <c r="M368" s="135" t="s">
+        <v>2998</v>
+      </c>
+      <c r="N368" s="38" t="s">
         <v>2999</v>
       </c>
-      <c r="N368" s="38" t="s">
+      <c r="O368" s="38" t="s">
         <v>3000</v>
-      </c>
-      <c r="O368" s="38" t="s">
-        <v>3001</v>
       </c>
       <c r="P368" s="25"/>
       <c r="Q368" s="26" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="R368" s="39" t="s">
         <v>518</v>
@@ -47804,13 +47812,13 @@
         <v>2227</v>
       </c>
       <c r="Y368" s="168" t="s">
+        <v>3002</v>
+      </c>
+      <c r="Z368" s="30" t="s">
         <v>3003</v>
       </c>
-      <c r="Z368" s="30" t="s">
+      <c r="AA368" s="30" t="s">
         <v>3004</v>
-      </c>
-      <c r="AA368" s="30" t="s">
-        <v>3005</v>
       </c>
       <c r="AB368" s="41"/>
       <c r="AC368" s="32"/>
@@ -47831,22 +47839,22 @@
     </row>
     <row r="369" spans="1:43" ht="15.75" customHeight="1">
       <c r="A369" s="458" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B369" s="332" t="s">
         <v>429</v>
       </c>
       <c r="C369" s="262" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D369" s="333"/>
       <c r="E369" s="334"/>
       <c r="F369" s="335" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="G369" s="336"/>
       <c r="H369" s="351" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="I369" s="337" t="s">
         <v>2496</v>
@@ -47855,10 +47863,10 @@
       <c r="K369" s="339"/>
       <c r="L369" s="338"/>
       <c r="M369" s="340" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="N369" s="341" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="O369" s="341" t="s">
         <v>38</v>
@@ -47877,25 +47885,25 @@
       <c r="U369" s="352"/>
       <c r="V369" s="346"/>
       <c r="W369" s="347" t="s">
+        <v>3009</v>
+      </c>
+      <c r="X369" s="347" t="s">
         <v>3010</v>
       </c>
-      <c r="X369" s="347" t="s">
+      <c r="Y369" s="348" t="s">
         <v>3011</v>
       </c>
-      <c r="Y369" s="348" t="s">
+      <c r="Z369" s="421" t="s">
         <v>3012</v>
       </c>
-      <c r="Z369" s="421" t="s">
+      <c r="AA369" s="348" t="s">
         <v>3013</v>
       </c>
-      <c r="AA369" s="348" t="s">
-        <v>3014</v>
-      </c>
       <c r="AB369" s="349" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="AC369" s="353" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="AD369" s="345"/>
       <c r="AE369" s="32"/>
@@ -47914,22 +47922,22 @@
     </row>
     <row r="370" spans="1:43" ht="15.75" customHeight="1">
       <c r="A370" s="458" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="B370" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C370" s="246" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="D370" s="232"/>
       <c r="E370" s="58"/>
       <c r="F370" s="47" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="G370" s="39"/>
       <c r="H370" s="203" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="I370" s="32" t="s">
         <v>2496</v>
@@ -47941,7 +47949,7 @@
         <v>797</v>
       </c>
       <c r="N370" s="54" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="O370" s="38" t="s">
         <v>38</v>
@@ -47966,15 +47974,15 @@
         <v>2227</v>
       </c>
       <c r="Y370" s="195" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="Z370" s="197"/>
       <c r="AA370" s="331" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="AB370" s="424"/>
       <c r="AC370" s="16" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="AD370" s="21"/>
       <c r="AE370" s="32"/>
@@ -47993,42 +48001,42 @@
     </row>
     <row r="371" spans="1:43" ht="15.75" customHeight="1">
       <c r="A371" s="458" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="B371" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C371" s="246" t="s">
+        <v>3023</v>
+      </c>
+      <c r="D371" s="231" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E371" s="58" t="s">
         <v>3024</v>
       </c>
-      <c r="D371" s="231" t="s">
-        <v>3016</v>
-      </c>
-      <c r="E371" s="58" t="s">
+      <c r="F371" s="47" t="s">
         <v>3025</v>
       </c>
-      <c r="F371" s="47" t="s">
+      <c r="G371" s="32" t="s">
         <v>3026</v>
       </c>
-      <c r="G371" s="32" t="s">
+      <c r="H371" s="48" t="s">
         <v>3027</v>
       </c>
-      <c r="H371" s="48" t="s">
+      <c r="I371" s="185" t="s">
         <v>3028</v>
       </c>
-      <c r="I371" s="185" t="s">
-        <v>3029</v>
-      </c>
       <c r="J371" s="22" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="K371" s="22"/>
       <c r="L371" s="22"/>
       <c r="M371" s="135" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="N371" s="134" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="O371" s="54"/>
       <c r="P371" s="55"/>
@@ -48072,22 +48080,22 @@
     </row>
     <row r="372" spans="1:43" ht="15.75" customHeight="1">
       <c r="A372" s="458" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="B372" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C372" s="246" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="D372" s="232"/>
       <c r="E372" s="58"/>
       <c r="F372" s="16" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="G372" s="39"/>
       <c r="H372" s="203" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="I372" s="190" t="s">
         <v>2496</v>
@@ -48095,13 +48103,13 @@
       <c r="J372" s="82"/>
       <c r="K372" s="82"/>
       <c r="L372" s="82" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="M372" s="209" t="s">
         <v>536</v>
       </c>
       <c r="N372" s="54" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="O372" s="54"/>
       <c r="P372" s="55"/>
@@ -48122,13 +48130,13 @@
         <v>2227</v>
       </c>
       <c r="Y372" s="30" t="s">
+        <v>3036</v>
+      </c>
+      <c r="Z372" s="30" t="s">
         <v>3037</v>
       </c>
-      <c r="Z372" s="30" t="s">
+      <c r="AA372" s="30" t="s">
         <v>3038</v>
-      </c>
-      <c r="AA372" s="30" t="s">
-        <v>3039</v>
       </c>
       <c r="AB372" s="108"/>
       <c r="AC372" s="32"/>
@@ -48149,7 +48157,7 @@
     </row>
     <row r="373" spans="1:43" ht="15.75" customHeight="1">
       <c r="A373" s="458" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="B373" s="33" t="s">
         <v>429</v>
@@ -48160,19 +48168,19 @@
       <c r="D373" s="232"/>
       <c r="E373" s="58"/>
       <c r="F373" s="47" t="s">
+        <v>3040</v>
+      </c>
+      <c r="G373" s="32" t="s">
         <v>3041</v>
       </c>
-      <c r="G373" s="32" t="s">
+      <c r="H373" s="203" t="s">
         <v>3042</v>
       </c>
-      <c r="H373" s="203" t="s">
+      <c r="I373" s="32" t="s">
         <v>3043</v>
       </c>
-      <c r="I373" s="32" t="s">
+      <c r="J373" s="103" t="s">
         <v>3044</v>
-      </c>
-      <c r="J373" s="103" t="s">
-        <v>3045</v>
       </c>
       <c r="K373" s="103"/>
       <c r="L373" s="103"/>
@@ -48180,7 +48188,7 @@
         <v>136</v>
       </c>
       <c r="N373" s="54" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="O373" s="54"/>
       <c r="P373" s="55"/>
@@ -48224,22 +48232,22 @@
     </row>
     <row r="374" spans="1:43" ht="15.75" customHeight="1">
       <c r="A374" s="458" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="B374" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C374" s="246" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="D374" s="232"/>
       <c r="E374" s="58"/>
       <c r="F374" s="47" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="G374" s="39"/>
       <c r="H374" s="203" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="I374" s="190" t="s">
         <v>2496</v>
@@ -48253,14 +48261,14 @@
         <v>892</v>
       </c>
       <c r="N374" s="54" t="s">
+        <v>3050</v>
+      </c>
+      <c r="O374" s="54" t="s">
         <v>3051</v>
-      </c>
-      <c r="O374" s="54" t="s">
-        <v>3052</v>
       </c>
       <c r="P374" s="55"/>
       <c r="Q374" s="56" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="R374" s="39" t="s">
         <v>518</v>
@@ -48278,13 +48286,13 @@
         <v>2227</v>
       </c>
       <c r="Y374" s="30" t="s">
+        <v>3053</v>
+      </c>
+      <c r="Z374" s="102" t="s">
         <v>3054</v>
       </c>
-      <c r="Z374" s="102" t="s">
+      <c r="AA374" s="30" t="s">
         <v>3055</v>
-      </c>
-      <c r="AA374" s="30" t="s">
-        <v>3056</v>
       </c>
       <c r="AB374" s="41"/>
       <c r="AC374" s="32"/>
@@ -48305,36 +48313,36 @@
     </row>
     <row r="375" spans="1:43" ht="15.75" customHeight="1">
       <c r="A375" s="458" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="B375" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C375" s="246" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="D375" s="232"/>
       <c r="E375" s="58"/>
       <c r="F375" s="16" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="G375" s="32"/>
       <c r="H375" s="203" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="I375" s="190" t="s">
         <v>2496</v>
       </c>
       <c r="J375" s="82" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="K375" s="82"/>
       <c r="L375" s="82"/>
       <c r="M375" s="113" t="s">
+        <v>3061</v>
+      </c>
+      <c r="N375" s="54" t="s">
         <v>3062</v>
-      </c>
-      <c r="N375" s="54" t="s">
-        <v>3063</v>
       </c>
       <c r="O375" s="294" t="s">
         <v>38</v>
@@ -48359,15 +48367,15 @@
         <v>2227</v>
       </c>
       <c r="Y375" s="419" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="Z375" s="418"/>
       <c r="AA375" s="30" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="AB375" s="41"/>
       <c r="AC375" s="66" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="AD375" s="21"/>
       <c r="AE375" s="32"/>
@@ -48386,7 +48394,7 @@
     </row>
     <row r="376" spans="1:43" ht="48" customHeight="1">
       <c r="A376" s="461" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="B376" s="33" t="s">
         <v>429</v>
@@ -48396,14 +48404,14 @@
       </c>
       <c r="E376" s="227"/>
       <c r="F376" s="370" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="G376" s="227"/>
       <c r="H376" s="360" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="I376" s="360" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="J376" s="227"/>
       <c r="K376" s="227"/>
@@ -48424,7 +48432,7 @@
         <v>41</v>
       </c>
       <c r="T376" s="360" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="U376" s="227"/>
       <c r="V376" s="227"/>
@@ -48436,7 +48444,7 @@
       <c r="AB376" s="227"/>
       <c r="AC376" s="227"/>
       <c r="AD376" s="360" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="AE376" s="227"/>
       <c r="AF376" s="227"/>
@@ -48454,7 +48462,7 @@
     </row>
     <row r="377" spans="1:43" ht="15.75" customHeight="1">
       <c r="A377" s="458" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="B377" s="33" t="s">
         <v>429</v>
@@ -48465,11 +48473,11 @@
       <c r="D377" s="232"/>
       <c r="E377" s="58"/>
       <c r="F377" s="265" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="G377" s="32"/>
       <c r="H377" s="203" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="I377" s="32" t="s">
         <v>2496</v>
@@ -48480,17 +48488,17 @@
         <v>419</v>
       </c>
       <c r="M377" s="135" t="s">
+        <v>3071</v>
+      </c>
+      <c r="N377" s="54" t="s">
         <v>3072</v>
-      </c>
-      <c r="N377" s="54" t="s">
-        <v>3073</v>
       </c>
       <c r="O377" s="54"/>
       <c r="P377" s="74" t="s">
+        <v>3073</v>
+      </c>
+      <c r="Q377" s="56" t="s">
         <v>3074</v>
-      </c>
-      <c r="Q377" s="56" t="s">
-        <v>3075</v>
       </c>
       <c r="R377" s="94" t="s">
         <v>538</v>
@@ -48512,7 +48520,7 @@
       </c>
       <c r="Z377" s="418"/>
       <c r="AA377" s="195" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="AB377" s="108"/>
       <c r="AC377" s="32"/>
@@ -48533,7 +48541,7 @@
     </row>
     <row r="378" spans="1:43" ht="15.75" customHeight="1">
       <c r="A378" s="458" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="B378" s="33" t="s">
         <v>429</v>
@@ -48544,11 +48552,11 @@
       <c r="D378" s="232"/>
       <c r="E378" s="58"/>
       <c r="F378" s="47" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="G378" s="32"/>
       <c r="H378" s="203" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="I378" s="190" t="s">
         <v>2496</v>
@@ -48556,13 +48564,13 @@
       <c r="J378" s="35"/>
       <c r="K378" s="107"/>
       <c r="L378" s="107" t="s">
+        <v>3079</v>
+      </c>
+      <c r="M378" s="135" t="s">
         <v>3080</v>
       </c>
-      <c r="M378" s="135" t="s">
+      <c r="N378" s="38" t="s">
         <v>3081</v>
-      </c>
-      <c r="N378" s="38" t="s">
-        <v>3082</v>
       </c>
       <c r="O378" s="38"/>
       <c r="P378" s="25"/>
@@ -48587,10 +48595,10 @@
       </c>
       <c r="Z378" s="197"/>
       <c r="AA378" s="197" t="s">
+        <v>3082</v>
+      </c>
+      <c r="AB378" s="108" t="s">
         <v>3083</v>
-      </c>
-      <c r="AB378" s="108" t="s">
-        <v>3084</v>
       </c>
       <c r="AC378" s="32"/>
       <c r="AD378" s="21"/>
@@ -48610,7 +48618,7 @@
     </row>
     <row r="379" spans="1:43" ht="15.75" customHeight="1">
       <c r="A379" s="458" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="B379" s="33" t="s">
         <v>429</v>
@@ -48621,11 +48629,11 @@
       <c r="D379" s="232"/>
       <c r="E379" s="58"/>
       <c r="F379" s="47" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="G379" s="32"/>
       <c r="H379" s="203" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="I379" s="190" t="s">
         <v>2496</v>
@@ -48634,17 +48642,17 @@
       <c r="K379" s="82"/>
       <c r="L379" s="82"/>
       <c r="M379" s="135" t="s">
+        <v>3087</v>
+      </c>
+      <c r="N379" s="54" t="s">
         <v>3088</v>
       </c>
-      <c r="N379" s="54" t="s">
+      <c r="O379" s="394" t="s">
         <v>3089</v>
-      </c>
-      <c r="O379" s="394" t="s">
-        <v>3090</v>
       </c>
       <c r="P379" s="112"/>
       <c r="Q379" s="56" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="R379" s="39" t="s">
         <v>518</v>
@@ -48662,13 +48670,13 @@
         <v>2227</v>
       </c>
       <c r="Y379" s="168" t="s">
+        <v>3091</v>
+      </c>
+      <c r="Z379" s="30" t="s">
         <v>3092</v>
       </c>
-      <c r="Z379" s="30" t="s">
+      <c r="AA379" s="30" t="s">
         <v>3093</v>
-      </c>
-      <c r="AA379" s="30" t="s">
-        <v>3094</v>
       </c>
       <c r="AB379" s="108"/>
       <c r="AC379" s="32"/>
@@ -48689,22 +48697,22 @@
     </row>
     <row r="380" spans="1:43" ht="15.75" customHeight="1">
       <c r="A380" s="458" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="B380" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C380" s="246" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="D380" s="232"/>
       <c r="E380" s="58"/>
       <c r="F380" s="16" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G380" s="32"/>
       <c r="H380" s="203" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="I380" s="190" t="s">
         <v>2496</v>
@@ -48712,22 +48720,22 @@
       <c r="J380" s="82"/>
       <c r="K380" s="82"/>
       <c r="L380" s="82" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="M380" s="135" t="s">
         <v>892</v>
       </c>
       <c r="N380" s="38" t="s">
+        <v>3099</v>
+      </c>
+      <c r="O380" s="38" t="s">
         <v>3100</v>
       </c>
-      <c r="O380" s="38" t="s">
+      <c r="P380" s="74" t="s">
         <v>3101</v>
       </c>
-      <c r="P380" s="74" t="s">
+      <c r="Q380" s="56" t="s">
         <v>3102</v>
-      </c>
-      <c r="Q380" s="56" t="s">
-        <v>3103</v>
       </c>
       <c r="R380" s="39" t="s">
         <v>518</v>
@@ -48745,13 +48753,13 @@
         <v>2227</v>
       </c>
       <c r="Y380" s="168" t="s">
+        <v>3103</v>
+      </c>
+      <c r="Z380" s="102" t="s">
         <v>3104</v>
       </c>
-      <c r="Z380" s="102" t="s">
+      <c r="AA380" s="30" t="s">
         <v>3105</v>
-      </c>
-      <c r="AA380" s="30" t="s">
-        <v>3106</v>
       </c>
       <c r="AB380" s="108"/>
       <c r="AC380" s="32"/>
@@ -48772,7 +48780,7 @@
     </row>
     <row r="381" spans="1:43" s="329" customFormat="1" ht="15.75" customHeight="1">
       <c r="A381" s="458" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="B381" s="33" t="s">
         <v>429</v>
@@ -48783,11 +48791,11 @@
       <c r="D381" s="232"/>
       <c r="E381" s="58"/>
       <c r="F381" s="373" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="G381" s="32"/>
       <c r="H381" s="203" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="I381" s="32" t="s">
         <v>2496</v>
@@ -48795,13 +48803,13 @@
       <c r="J381" s="98"/>
       <c r="K381" s="103"/>
       <c r="L381" s="103" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="M381" s="135" t="s">
         <v>536</v>
       </c>
       <c r="N381" s="54" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="O381" s="54"/>
       <c r="P381" s="55"/>
@@ -48826,11 +48834,11 @@
       </c>
       <c r="Z381" s="422"/>
       <c r="AA381" s="211" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="AB381" s="108"/>
       <c r="AC381" s="47" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="AD381" s="21"/>
       <c r="AE381" s="328"/>
@@ -48849,22 +48857,22 @@
     </row>
     <row r="383" spans="1:43" ht="15.75" customHeight="1">
       <c r="A383" s="458" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="B383" s="33" t="s">
         <v>429</v>
       </c>
       <c r="C383" s="246" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="D383" s="232"/>
       <c r="E383" s="58"/>
       <c r="F383" s="16" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
  